--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7668FA-29F4-4F60-9DF8-76745E8E155D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE62BAC-E3F7-414B-85C2-8C155BBE24BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,12 +805,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,6 +813,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1176,6 +1176,8 @@
       <sheetName val="INVENTARIO NACIONAL 08-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 09-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1307,6 +1309,8 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1634,242 +1638,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2234,85 +2238,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5330</v>
+        <v>4593</v>
       </c>
       <c r="F13" s="14">
-        <v>7248.8</v>
+        <v>6246.4800000000005</v>
       </c>
       <c r="G13" s="14">
-        <v>6.8401096657527853</v>
+        <v>5.8943008808259929</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-2462.2727272727279</v>
+        <v>-3199.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>4194</v>
+        <v>3020</v>
       </c>
       <c r="K13" s="13">
-        <v>5703.84</v>
+        <v>4107.2000000000007</v>
       </c>
       <c r="L13" s="14">
-        <v>17.227035100821507</v>
+        <v>12.404779686333084</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>1759.4545454545455</v>
+        <v>585.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>554</v>
+        <v>214</v>
       </c>
       <c r="P13" s="17">
-        <v>753.44</v>
+        <v>291.04000000000002</v>
       </c>
       <c r="Q13" s="14">
-        <v>14.155632984901279</v>
+        <v>5.4680603948896636</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>-33.045454545454504</v>
+        <v>-373.0454545454545</v>
       </c>
       <c r="T13" s="18">
-        <v>857</v>
+        <v>621</v>
       </c>
       <c r="U13" s="17">
-        <v>1165.52</v>
+        <v>844.56000000000006</v>
       </c>
       <c r="V13" s="14">
-        <v>15.790619765494137</v>
+        <v>11.442211055276381</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>42.909090909090878</v>
+        <v>-193.09090909090912</v>
       </c>
       <c r="Y13" s="18">
-        <v>438</v>
+        <v>347</v>
       </c>
       <c r="Z13" s="17">
-        <v>595.68000000000006</v>
+        <v>471.92</v>
       </c>
       <c r="AA13" s="14">
-        <v>17.322033898305087</v>
+        <v>13.88</v>
       </c>
       <c r="AB13" s="16">
-        <v>556.28571428571422</v>
+        <v>550</v>
       </c>
       <c r="AC13" s="15">
-        <v>58.714285714285779</v>
+        <v>-28</v>
       </c>
       <c r="AD13" s="19">
-        <v>11373</v>
+        <v>8795</v>
       </c>
       <c r="AE13" s="20">
-        <v>15467.28</v>
+        <v>11961.2</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2348,19 +2352,19 @@
         <v>1.59</v>
       </c>
       <c r="E14" s="13">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="F14" s="14">
-        <v>174.9</v>
+        <v>98.58</v>
       </c>
       <c r="G14" s="14">
-        <v>3.1758530183727038</v>
+        <v>1.7900262467191603</v>
       </c>
       <c r="H14" s="30">
         <v>762</v>
       </c>
       <c r="I14" s="15">
-        <v>-236.36363636363632</v>
+        <v>-284.36363636363632</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2378,55 +2382,55 @@
         <v>-260.90909090909088</v>
       </c>
       <c r="O14" s="16">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P14" s="17">
-        <v>248.04000000000002</v>
+        <v>244.86</v>
       </c>
       <c r="Q14" s="14">
-        <v>20.188235294117646</v>
+        <v>19.929411764705883</v>
       </c>
       <c r="R14" s="16">
         <v>170</v>
       </c>
       <c r="S14" s="15">
-        <v>40.090909090909093</v>
+        <v>38.090909090909093</v>
       </c>
       <c r="T14" s="18">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="U14" s="17">
-        <v>49.29</v>
+        <v>30.21</v>
       </c>
       <c r="V14" s="14">
-        <v>12.178571428571429</v>
+        <v>7.4642857142857144</v>
       </c>
       <c r="W14" s="16">
         <v>56</v>
       </c>
       <c r="X14" s="15">
-        <v>-7.1818181818181799</v>
+        <v>-19.18181818181818</v>
       </c>
       <c r="Y14" s="18">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="Z14" s="17">
-        <v>157.41</v>
+        <v>131.97</v>
       </c>
       <c r="AA14" s="14">
-        <v>49.5</v>
+        <v>53.357142857142854</v>
       </c>
       <c r="AB14" s="16">
-        <v>44</v>
+        <v>34.222222222222221</v>
       </c>
       <c r="AC14" s="15">
-        <v>69</v>
+        <v>59.666666666666671</v>
       </c>
       <c r="AD14" s="19">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="AE14" s="20">
-        <v>629.64</v>
+        <v>505.62</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2462,85 +2466,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1183</v>
+        <v>227</v>
       </c>
       <c r="F15" s="14">
-        <v>2401.4899999999998</v>
+        <v>460.80999999999995</v>
       </c>
       <c r="G15" s="14">
-        <v>3.7718840579710147</v>
+        <v>0.72376811594202906</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-1953.363636363636</v>
+        <v>-2909.363636363636</v>
       </c>
       <c r="J15" s="16">
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="K15" s="13">
-        <v>0</v>
+        <v>5958.0499999999993</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>21.387876780390858</v>
       </c>
       <c r="M15" s="30">
         <v>3019</v>
       </c>
       <c r="N15" s="15">
-        <v>-1372.2727272727273</v>
+        <v>1562.7272727272727</v>
       </c>
       <c r="O15" s="16">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="P15" s="17">
-        <v>483.13999999999993</v>
+        <v>430.35999999999996</v>
       </c>
       <c r="Q15" s="14">
-        <v>17.62962962962963</v>
+        <v>15.703703703703704</v>
       </c>
       <c r="R15" s="16">
         <v>297</v>
       </c>
       <c r="S15" s="15">
-        <v>35.5</v>
+        <v>9.5</v>
       </c>
       <c r="T15" s="18">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="U15" s="17">
-        <v>54.809999999999995</v>
+        <v>0</v>
       </c>
       <c r="V15" s="14">
-        <v>1.711815561959654</v>
+        <v>0</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>-209.59090909090912</v>
+        <v>-236.59090909090912</v>
       </c>
       <c r="Y15" s="18">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="Z15" s="17">
-        <v>477.04999999999995</v>
+        <v>452.68999999999994</v>
       </c>
       <c r="AA15" s="14">
-        <v>40.121951219512191</v>
+        <v>42.702127659574465</v>
       </c>
       <c r="AB15" s="16">
-        <v>128.85714285714286</v>
+        <v>114.88888888888889</v>
       </c>
       <c r="AC15" s="15">
-        <v>147.14285714285714</v>
+        <v>144.66666666666669</v>
       </c>
       <c r="AD15" s="19">
-        <v>1683</v>
+        <v>3597</v>
       </c>
       <c r="AE15" s="20">
-        <v>3416.49</v>
+        <v>7301.9099999999989</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2575,34 +2579,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="F16" s="14">
-        <v>1083</v>
+        <v>1397.07</v>
       </c>
       <c r="G16" s="14">
-        <v>4.7244094488188972</v>
+        <v>6.0944881889763778</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-335</v>
+        <v>-248</v>
       </c>
       <c r="J16" s="16">
-        <v>520</v>
+        <v>379</v>
       </c>
       <c r="K16" s="13">
-        <v>1877.2</v>
+        <v>1368.19</v>
       </c>
       <c r="L16" s="14">
-        <v>20.990825688073393</v>
+        <v>15.299082568807339</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>272.27272727272725</v>
+        <v>131.27272727272725</v>
       </c>
       <c r="O16" s="16">
         <v>16</v>
@@ -2620,40 +2624,40 @@
         <v>-15.36363636363637</v>
       </c>
       <c r="T16" s="18">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="U16" s="17">
-        <v>97.47</v>
+        <v>86.64</v>
       </c>
       <c r="V16" s="14">
-        <v>12.122448979591837</v>
+        <v>10.775510204081634</v>
       </c>
       <c r="W16" s="16">
         <v>49</v>
       </c>
       <c r="X16" s="15">
-        <v>-6.4090909090909065</v>
+        <v>-9.4090909090909065</v>
       </c>
       <c r="Y16" s="18">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z16" s="17">
-        <v>259.92</v>
+        <v>249.09</v>
       </c>
       <c r="AA16" s="14">
-        <v>38.769230769230766</v>
+        <v>47.769230769230766</v>
       </c>
       <c r="AB16" s="16">
-        <v>40.857142857142861</v>
+        <v>31.777777777777779</v>
       </c>
       <c r="AC16" s="15">
-        <v>44.142857142857139</v>
+        <v>47.333333333333329</v>
       </c>
       <c r="AD16" s="19">
-        <v>935</v>
+        <v>875</v>
       </c>
       <c r="AE16" s="20">
-        <v>3375.35</v>
+        <v>3158.75</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2688,34 +2692,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F17" s="14">
-        <v>228.27999999999997</v>
+        <v>316.08</v>
       </c>
       <c r="G17" s="14">
-        <v>3.4251497005988023</v>
+        <v>4.7425149700598803</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-49.909090909090907</v>
+        <v>-39.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="K17" s="13">
-        <v>711.18</v>
+        <v>395.09999999999997</v>
       </c>
       <c r="L17" s="14">
-        <v>25.826086956521738</v>
+        <v>14.347826086956522</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>49.63636363636364</v>
+        <v>13.636363636363637</v>
       </c>
       <c r="O17" s="16">
         <v>13</v>
@@ -2754,19 +2758,19 @@
         <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>12.833333333333332</v>
+        <v>16.5</v>
       </c>
       <c r="AB17" s="16">
-        <v>18.857142857142858</v>
+        <v>14.666666666666666</v>
       </c>
       <c r="AC17" s="15">
-        <v>-1.8571428571428577</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="19">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="AE17" s="20">
-        <v>1299.4399999999998</v>
+        <v>1071.1599999999999</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2801,85 +2805,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>8422</v>
+        <v>6210</v>
       </c>
       <c r="F18" s="14">
-        <v>5305.86</v>
+        <v>3912.3</v>
       </c>
       <c r="G18" s="14">
-        <v>10.149767187072035</v>
+        <v>7.4839769926047657</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>124.27272727272793</v>
+        <v>-2087.7272727272721</v>
       </c>
       <c r="J18" s="16">
-        <v>3246</v>
+        <v>5125</v>
       </c>
       <c r="K18" s="13">
-        <v>2044.98</v>
+        <v>3228.75</v>
       </c>
       <c r="L18" s="14">
-        <v>10.319653179190752</v>
+        <v>16.293352601156069</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>100.5454545454545</v>
+        <v>1979.5454545454545</v>
       </c>
       <c r="O18" s="16">
-        <v>915</v>
+        <v>760</v>
       </c>
       <c r="P18" s="17">
-        <v>576.45000000000005</v>
+        <v>478.8</v>
       </c>
       <c r="Q18" s="14">
-        <v>13.930795847750863</v>
+        <v>11.570934256055363</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-70.227272727272748</v>
+        <v>-225.22727272727275</v>
       </c>
       <c r="T18" s="18">
-        <v>861</v>
+        <v>254</v>
       </c>
       <c r="U18" s="17">
-        <v>542.42999999999995</v>
+        <v>160.02000000000001</v>
       </c>
       <c r="V18" s="14">
-        <v>4.9097978227060652</v>
+        <v>1.4484188698807672</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-1769.4545454545455</v>
+        <v>-2376.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="Z18" s="17">
-        <v>203.49</v>
+        <v>195.93</v>
       </c>
       <c r="AA18" s="14">
-        <v>25.988505747126435</v>
+        <v>28.561224489795919</v>
       </c>
       <c r="AB18" s="16">
-        <v>273.42857142857144</v>
+        <v>239.55555555555557</v>
       </c>
       <c r="AC18" s="15">
-        <v>136.57142857142856</v>
+        <v>147.66666666666666</v>
       </c>
       <c r="AD18" s="19">
-        <v>13767</v>
+        <v>12660</v>
       </c>
       <c r="AE18" s="20">
-        <v>8673.2100000000009</v>
+        <v>7975.8</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2914,34 +2918,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>997</v>
+        <v>916</v>
       </c>
       <c r="F19" s="14">
-        <v>628.11</v>
+        <v>577.08000000000004</v>
       </c>
       <c r="G19" s="14">
-        <v>14.770370370370374</v>
+        <v>13.570370370370373</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>322.00000000000011</v>
+        <v>241.00000000000011</v>
       </c>
       <c r="J19" s="16">
-        <v>977</v>
+        <v>1391</v>
       </c>
       <c r="K19" s="13">
-        <v>615.51</v>
+        <v>876.33</v>
       </c>
       <c r="L19" s="14">
-        <v>19.122775800711743</v>
+        <v>27.22597864768683</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>466.09090909090907</v>
+        <v>880.09090909090901</v>
       </c>
       <c r="O19" s="16">
         <v>85</v>
@@ -2959,40 +2963,40 @@
         <v>20.909090909090907</v>
       </c>
       <c r="T19" s="18">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="U19" s="17">
-        <v>17.010000000000002</v>
+        <v>2.52</v>
       </c>
       <c r="V19" s="14">
-        <v>1.752212389380531</v>
+        <v>0.25958702064896755</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>-204.13636363636363</v>
+        <v>-227.13636363636363</v>
       </c>
       <c r="Y19" s="18">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="Z19" s="17">
-        <v>132.93</v>
+        <v>129.15</v>
       </c>
       <c r="AA19" s="14">
-        <v>15.881720430107528</v>
+        <v>18.088235294117645</v>
       </c>
       <c r="AB19" s="16">
-        <v>292.28571428571428</v>
+        <v>249.33333333333334</v>
       </c>
       <c r="AC19" s="15">
-        <v>11.714285714285722</v>
+        <v>35</v>
       </c>
       <c r="AD19" s="19">
-        <v>2297</v>
+        <v>2601</v>
       </c>
       <c r="AE19" s="20">
-        <v>1447.11</v>
+        <v>1638.63</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3027,49 +3031,49 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1639</v>
+        <v>1514</v>
       </c>
       <c r="F20" s="14">
-        <v>1032.57</v>
+        <v>953.82</v>
       </c>
       <c r="G20" s="14">
-        <v>10.683851851851852</v>
+        <v>9.8690370370370371</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>104.90909090909099</v>
+        <v>-20.090909090909008</v>
       </c>
       <c r="J20" s="16">
-        <v>1014</v>
+        <v>1798</v>
       </c>
       <c r="K20" s="13">
-        <v>638.82000000000005</v>
+        <v>1132.74</v>
       </c>
       <c r="L20" s="14">
-        <v>10.08955223880597</v>
+        <v>17.890547263681594</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>9</v>
+        <v>793</v>
       </c>
       <c r="O20" s="16">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P20" s="17">
-        <v>144.27000000000001</v>
+        <v>140.49</v>
       </c>
       <c r="Q20" s="14">
-        <v>18.057347670250895</v>
+        <v>17.584229390681003</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>38.77272727272728</v>
+        <v>32.77272727272728</v>
       </c>
       <c r="T20" s="18">
         <v>0</v>
@@ -3087,25 +3091,25 @@
         <v>-799.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="Z20" s="17">
-        <v>203.49</v>
+        <v>196.56</v>
       </c>
       <c r="AA20" s="14">
-        <v>23.552083333333332</v>
+        <v>26.490566037735846</v>
       </c>
       <c r="AB20" s="16">
-        <v>301.71428571428572</v>
+        <v>259.11111111111114</v>
       </c>
       <c r="AC20" s="15">
-        <v>117.28571428571428</v>
+        <v>135.33333333333331</v>
       </c>
       <c r="AD20" s="19">
-        <v>3205</v>
+        <v>3847</v>
       </c>
       <c r="AE20" s="20">
-        <v>2019.15</v>
+        <v>2423.61</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3140,85 +3144,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>3143</v>
+        <v>2955</v>
       </c>
       <c r="F21" s="14">
-        <v>3425.8700000000003</v>
+        <v>3220.9500000000003</v>
       </c>
       <c r="G21" s="14">
-        <v>10.834534628643059</v>
+        <v>10.186461924161705</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>242.09090909090946</v>
+        <v>54.090909090909463</v>
       </c>
       <c r="J21" s="16">
-        <v>0</v>
+        <v>4927</v>
       </c>
       <c r="K21" s="13">
-        <v>0</v>
+        <v>5370.43</v>
       </c>
       <c r="L21" s="14">
-        <v>0</v>
+        <v>15.996753246753247</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>-3080</v>
+        <v>1847</v>
       </c>
       <c r="O21" s="16">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="P21" s="17">
-        <v>367.33000000000004</v>
+        <v>330.27000000000004</v>
       </c>
       <c r="Q21" s="14">
-        <v>14.06831119544592</v>
+        <v>12.648956356736244</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>-22.318181818181813</v>
+        <v>-56.318181818181813</v>
       </c>
       <c r="T21" s="18">
-        <v>337</v>
+        <v>55</v>
       </c>
       <c r="U21" s="17">
-        <v>367.33000000000004</v>
+        <v>59.95</v>
       </c>
       <c r="V21" s="14">
-        <v>3.5799130854659582</v>
+        <v>0.58425881216803477</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-1075.0454545454545</v>
+        <v>-1357.0454545454545</v>
       </c>
       <c r="Y21" s="18">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="Z21" s="17">
-        <v>427.28000000000003</v>
+        <v>380.41</v>
       </c>
       <c r="AA21" s="14">
-        <v>18.172185430463575</v>
+        <v>17.547486033519554</v>
       </c>
       <c r="AB21" s="16">
-        <v>474.57142857142861</v>
+        <v>437.55555555555554</v>
       </c>
       <c r="AC21" s="15">
-        <v>68.428571428571388</v>
+        <v>50.666666666666686</v>
       </c>
       <c r="AD21" s="19">
-        <v>4209</v>
+        <v>8589</v>
       </c>
       <c r="AE21" s="20">
-        <v>4587.8100000000004</v>
+        <v>9362.01</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3253,85 +3257,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>803</v>
+        <v>1977</v>
       </c>
       <c r="F22" s="14">
-        <v>875.2700000000001</v>
+        <v>2154.9300000000003</v>
       </c>
       <c r="G22" s="14">
-        <v>4.1189088365586377</v>
+        <v>10.140825367218465</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>-1146.5454545454547</v>
+        <v>27.454545454545269</v>
       </c>
       <c r="J22" s="16">
-        <v>5240</v>
+        <v>3746</v>
       </c>
       <c r="K22" s="13">
-        <v>5711.6</v>
+        <v>4083.1400000000003</v>
       </c>
       <c r="L22" s="14">
-        <v>47.695490277203149</v>
+        <v>34.096814232519655</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>4141.363636363636</v>
+        <v>2647.3636363636365</v>
       </c>
       <c r="O22" s="16">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="P22" s="17">
-        <v>199.47000000000003</v>
+        <v>194.02</v>
       </c>
       <c r="Q22" s="14">
-        <v>19.735294117647062</v>
+        <v>19.196078431372552</v>
       </c>
       <c r="R22" s="16">
         <v>203.99999999999997</v>
       </c>
       <c r="S22" s="15">
-        <v>43.909090909090935</v>
+        <v>38.909090909090935</v>
       </c>
       <c r="T22" s="18">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="U22" s="17">
-        <v>517.75</v>
+        <v>440.36</v>
       </c>
       <c r="V22" s="14">
-        <v>14.739069111424541</v>
+        <v>12.535966149506347</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-8.4090909090908781</v>
+        <v>-79.409090909090878</v>
       </c>
       <c r="Y22" s="18">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="Z22" s="17">
-        <v>223.45000000000002</v>
+        <v>206.01000000000002</v>
       </c>
       <c r="AA22" s="14">
         <v>0</v>
       </c>
       <c r="AB22" s="16">
-        <v>34.571428571428569</v>
+        <v>41.555555555555557</v>
       </c>
       <c r="AC22" s="15">
-        <v>181.42857142857144</v>
+        <v>160.66666666666666</v>
       </c>
       <c r="AD22" s="19">
-        <v>6906</v>
+        <v>6494</v>
       </c>
       <c r="AE22" s="20">
-        <v>7527.5400000000009</v>
+        <v>7078.4600000000009</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3366,85 +3370,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>13185</v>
+        <v>13253</v>
       </c>
       <c r="F23" s="14">
-        <v>15294.599999999999</v>
+        <v>15373.48</v>
       </c>
       <c r="G23" s="14">
-        <v>7.6947767726874821</v>
+        <v>7.7344616282462795</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>-3950</v>
+        <v>-3882</v>
       </c>
       <c r="J23" s="16">
-        <v>15901</v>
+        <v>18500</v>
       </c>
       <c r="K23" s="13">
-        <v>18445.16</v>
+        <v>21460</v>
       </c>
       <c r="L23" s="14">
-        <v>18.281787300757774</v>
+        <v>21.269924222628692</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>7203.2727272727279</v>
+        <v>9802.2727272727279</v>
       </c>
       <c r="O23" s="16">
-        <v>2020</v>
+        <v>1755</v>
       </c>
       <c r="P23" s="17">
-        <v>2343.1999999999998</v>
+        <v>2035.8</v>
       </c>
       <c r="Q23" s="14">
-        <v>14.094513162067873</v>
+        <v>12.245480494766889</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>-129.77272727272702</v>
+        <v>-394.77272727272702</v>
       </c>
       <c r="T23" s="18">
-        <v>5800</v>
+        <v>3885</v>
       </c>
       <c r="U23" s="17">
-        <v>6727.9999999999991</v>
+        <v>4506.5999999999995</v>
       </c>
       <c r="V23" s="14">
-        <v>9.64328899637243</v>
+        <v>6.4593409915356705</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-3221.818181818182</v>
+        <v>-5136.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>557</v>
+        <v>388</v>
       </c>
       <c r="Z23" s="17">
-        <v>646.12</v>
+        <v>450.08</v>
       </c>
       <c r="AA23" s="14">
-        <v>9.2833333333333332</v>
+        <v>6.5149253731343286</v>
       </c>
       <c r="AB23" s="16">
-        <v>1320</v>
+        <v>1310.2222222222222</v>
       </c>
       <c r="AC23" s="15">
-        <v>-343</v>
+        <v>-505.33333333333326</v>
       </c>
       <c r="AD23" s="19">
-        <v>37463</v>
+        <v>37781</v>
       </c>
       <c r="AE23" s="20">
-        <v>43457.079999999994</v>
+        <v>43825.96</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3479,85 +3483,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>6893</v>
+        <v>8803</v>
       </c>
       <c r="F24" s="14">
-        <v>7995.8799999999992</v>
+        <v>10211.48</v>
       </c>
       <c r="G24" s="14">
-        <v>5.6462134187206798</v>
+        <v>7.210737955171644</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>-5315.181818181818</v>
+        <v>-3405.181818181818</v>
       </c>
       <c r="J24" s="16">
-        <v>12920</v>
+        <v>8461</v>
       </c>
       <c r="K24" s="13">
-        <v>14987.199999999999</v>
+        <v>9814.76</v>
       </c>
       <c r="L24" s="14">
-        <v>23.821656050955415</v>
+        <v>15.600234663090848</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>7496.363636363636</v>
+        <v>3037.363636363636</v>
       </c>
       <c r="O24" s="16">
-        <v>1184</v>
+        <v>1034</v>
       </c>
       <c r="P24" s="17">
-        <v>1373.4399999999998</v>
+        <v>1199.4399999999998</v>
       </c>
       <c r="Q24" s="14">
-        <v>13.789306511381684</v>
+        <v>12.042350449973531</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>-103.9545454545455</v>
+        <v>-253.9545454545455</v>
       </c>
       <c r="T24" s="18">
-        <v>4753</v>
+        <v>3640</v>
       </c>
       <c r="U24" s="17">
-        <v>5513.48</v>
+        <v>4222.3999999999996</v>
       </c>
       <c r="V24" s="14">
-        <v>14.379262926292629</v>
+        <v>11.012101210121012</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-205.18181818181802</v>
+        <v>-1318.181818181818</v>
       </c>
       <c r="Y24" s="18">
-        <v>688</v>
+        <v>599</v>
       </c>
       <c r="Z24" s="17">
-        <v>798.07999999999993</v>
+        <v>694.83999999999992</v>
       </c>
       <c r="AA24" s="14">
-        <v>16.54982817869416</v>
+        <v>15.717201166180757</v>
       </c>
       <c r="AB24" s="16">
-        <v>914.57142857142856</v>
+        <v>838.44444444444457</v>
       </c>
       <c r="AC24" s="15">
-        <v>64.428571428571445</v>
+        <v>27.333333333333258</v>
       </c>
       <c r="AD24" s="19">
-        <v>26438</v>
+        <v>22537</v>
       </c>
       <c r="AE24" s="20">
-        <v>30668.079999999998</v>
+        <v>26142.92</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3592,85 +3596,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>7640</v>
+        <v>6475</v>
       </c>
       <c r="F25" s="14">
-        <v>8862.4</v>
+        <v>7510.9999999999991</v>
       </c>
       <c r="G25" s="14">
-        <v>6.5086741016109046</v>
+        <v>5.5161864931846347</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-4098.181818181818</v>
+        <v>-5263.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>8815</v>
+        <v>6830</v>
       </c>
       <c r="K25" s="13">
-        <v>10225.4</v>
+        <v>7922.7999999999993</v>
       </c>
       <c r="L25" s="14">
-        <v>16.28158844765343</v>
+        <v>12.615229619679289</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>3400.909090909091</v>
+        <v>1415.909090909091</v>
       </c>
       <c r="O25" s="16">
-        <v>1300</v>
+        <v>1086</v>
       </c>
       <c r="P25" s="17">
-        <v>1508</v>
+        <v>1259.76</v>
       </c>
       <c r="Q25" s="14">
-        <v>13.017751479289942</v>
+        <v>10.874829312699136</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-197.9545454545455</v>
+        <v>-411.9545454545455</v>
       </c>
       <c r="T25" s="18">
-        <v>4523</v>
+        <v>3424</v>
       </c>
       <c r="U25" s="17">
-        <v>5246.6799999999994</v>
+        <v>3971.8399999999997</v>
       </c>
       <c r="V25" s="14">
-        <v>13.808770469053567</v>
+        <v>10.453510963086316</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-390.18181818181802</v>
+        <v>-1489.181818181818</v>
       </c>
       <c r="Y25" s="18">
-        <v>763</v>
+        <v>729</v>
       </c>
       <c r="Z25" s="17">
-        <v>885.07999999999993</v>
+        <v>845.64</v>
       </c>
       <c r="AA25" s="14">
-        <v>23.528634361233479</v>
+        <v>27.337499999999995</v>
       </c>
       <c r="AB25" s="16">
-        <v>713.42857142857144</v>
+        <v>586.66666666666674</v>
       </c>
       <c r="AC25" s="15">
-        <v>276.57142857142856</v>
+        <v>328.99999999999994</v>
       </c>
       <c r="AD25" s="19">
-        <v>23041</v>
+        <v>18544</v>
       </c>
       <c r="AE25" s="20">
-        <v>26727.559999999998</v>
+        <v>21511.039999999997</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3705,85 +3709,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>4160</v>
+        <v>8959</v>
       </c>
       <c r="F26" s="14">
-        <v>4825.5999999999995</v>
+        <v>10392.439999999999</v>
       </c>
       <c r="G26" s="14">
-        <v>2.9169721115537848</v>
+        <v>6.2820079681274894</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>-10101.363636363638</v>
+        <v>-5302.3636363636379</v>
       </c>
       <c r="J26" s="16">
-        <v>16424</v>
+        <v>17753</v>
       </c>
       <c r="K26" s="13">
-        <v>19051.84</v>
+        <v>20593.48</v>
       </c>
       <c r="L26" s="14">
-        <v>25.627916873537131</v>
+        <v>27.701680970281579</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>10015.363636363636</v>
+        <v>11344.363636363636</v>
       </c>
       <c r="O26" s="16">
-        <v>1145</v>
+        <v>990</v>
       </c>
       <c r="P26" s="17">
-        <v>1328.1999999999998</v>
+        <v>1148.3999999999999</v>
       </c>
       <c r="Q26" s="14">
-        <v>13.840659340659339</v>
+        <v>11.967032967032965</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-95.909090909090992</v>
+        <v>-250.90909090909099</v>
       </c>
       <c r="T26" s="18">
-        <v>3738</v>
+        <v>2417</v>
       </c>
       <c r="U26" s="17">
-        <v>4336.08</v>
+        <v>2803.72</v>
       </c>
       <c r="V26" s="14">
-        <v>9.8770117703579157</v>
+        <v>6.3865001201056932</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-1938.818181818182</v>
+        <v>-3259.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>861</v>
+        <v>726</v>
       </c>
       <c r="Z26" s="17">
-        <v>998.75999999999988</v>
+        <v>842.16</v>
       </c>
       <c r="AA26" s="14">
-        <v>19.255591054313097</v>
+        <v>16.840206185567009</v>
       </c>
       <c r="AB26" s="16">
-        <v>983.71428571428578</v>
+        <v>948.44444444444457</v>
       </c>
       <c r="AC26" s="15">
-        <v>190.28571428571422</v>
+        <v>79.333333333333258</v>
       </c>
       <c r="AD26" s="19">
-        <v>26328</v>
+        <v>30845</v>
       </c>
       <c r="AE26" s="20">
-        <v>30540.48</v>
+        <v>35780.199999999997</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3818,85 +3822,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1169</v>
+        <v>1393</v>
       </c>
       <c r="F27" s="14">
-        <v>1356.04</v>
+        <v>1615.8799999999999</v>
       </c>
       <c r="G27" s="14">
-        <v>7.0907085745795415</v>
+        <v>8.4494072236007707</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>-479.63636363636374</v>
+        <v>-255.63636363636374</v>
       </c>
       <c r="J27" s="16">
-        <v>2824</v>
+        <v>2085</v>
       </c>
       <c r="K27" s="13">
-        <v>3275.8399999999997</v>
+        <v>2418.6</v>
       </c>
       <c r="L27" s="14">
-        <v>24.52743782076589</v>
+        <v>18.108961705487562</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>1672.6363636363635</v>
+        <v>933.63636363636351</v>
       </c>
       <c r="O27" s="16">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="P27" s="17">
-        <v>675.12</v>
+        <v>654.24</v>
       </c>
       <c r="Q27" s="14">
-        <v>30.485714285714288</v>
+        <v>29.542857142857144</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>295.63636363636363</v>
+        <v>277.63636363636363</v>
       </c>
       <c r="T27" s="18">
-        <v>919</v>
+        <v>537</v>
       </c>
       <c r="U27" s="17">
-        <v>1066.04</v>
+        <v>622.91999999999996</v>
       </c>
       <c r="V27" s="14">
-        <v>13.240340537000659</v>
+        <v>7.736738703339884</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-122.13636363636328</v>
+        <v>-504.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="Z27" s="17">
-        <v>602.04</v>
+        <v>577.67999999999995</v>
       </c>
       <c r="AA27" s="14">
-        <v>40.82022471910112</v>
+        <v>42.283018867924525</v>
       </c>
       <c r="AB27" s="16">
-        <v>279.71428571428572</v>
+        <v>259.11111111111114</v>
       </c>
       <c r="AC27" s="15">
-        <v>328.28571428571428</v>
+        <v>321.33333333333331</v>
       </c>
       <c r="AD27" s="19">
-        <v>6013</v>
+        <v>5077</v>
       </c>
       <c r="AE27" s="20">
-        <v>6975.08</v>
+        <v>5889.32</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3931,85 +3935,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>2021</v>
+        <v>952</v>
       </c>
       <c r="F28" s="14">
-        <v>2344.3599999999997</v>
+        <v>1104.32</v>
       </c>
       <c r="G28" s="14">
-        <v>11.847055688782307</v>
+        <v>5.5806021849187317</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>315.09090909090901</v>
+        <v>-753.90909090909099</v>
       </c>
       <c r="J28" s="16">
-        <v>1475</v>
+        <v>895</v>
       </c>
       <c r="K28" s="13">
-        <v>1710.9999999999998</v>
+        <v>1038.1999999999998</v>
       </c>
       <c r="L28" s="14">
-        <v>9.7243032664069524</v>
+        <v>5.9005094396164219</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>-41.818181818181984</v>
+        <v>-621.81818181818198</v>
       </c>
       <c r="O28" s="16">
-        <v>558</v>
+        <v>503</v>
       </c>
       <c r="P28" s="17">
-        <v>647.28</v>
+        <v>583.4799999999999</v>
       </c>
       <c r="Q28" s="14">
-        <v>23.25</v>
+        <v>20.958333333333332</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="T28" s="18">
-        <v>855</v>
+        <v>397</v>
       </c>
       <c r="U28" s="17">
-        <v>991.8</v>
+        <v>460.52</v>
       </c>
       <c r="V28" s="14">
-        <v>14.502698535080956</v>
+        <v>6.7340015420200467</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-29.318181818181756</v>
+        <v>-487.31818181818176</v>
       </c>
       <c r="Y28" s="18">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="Z28" s="17">
-        <v>541.71999999999991</v>
+        <v>523.16</v>
       </c>
       <c r="AA28" s="14">
-        <v>25.146153846153844</v>
+        <v>27.06</v>
       </c>
       <c r="AB28" s="16">
-        <v>408.57142857142861</v>
+        <v>366.66666666666669</v>
       </c>
       <c r="AC28" s="15">
-        <v>188.42857142857139</v>
+        <v>200.99999999999997</v>
       </c>
       <c r="AD28" s="19">
-        <v>5376</v>
+        <v>3198</v>
       </c>
       <c r="AE28" s="20">
-        <v>6236.16</v>
+        <v>3709.68</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4044,85 +4048,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>855</v>
+        <v>1600</v>
       </c>
       <c r="F29" s="14">
-        <v>991.8</v>
+        <v>1855.9999999999998</v>
       </c>
       <c r="G29" s="14">
-        <v>4.9434954007884357</v>
+        <v>9.2509855453350855</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-874.54545454545473</v>
+        <v>-129.54545454545473</v>
       </c>
       <c r="J29" s="16">
-        <v>3047</v>
+        <v>1709</v>
       </c>
       <c r="K29" s="13">
-        <v>3534.52</v>
+        <v>1982.4399999999998</v>
       </c>
       <c r="L29" s="14">
-        <v>24.6902394106814</v>
+        <v>13.848250460405156</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>1812.909090909091</v>
+        <v>474.90909090909099</v>
       </c>
       <c r="O29" s="16">
-        <v>545</v>
+        <v>477</v>
       </c>
       <c r="P29" s="17">
-        <v>632.19999999999993</v>
+        <v>553.31999999999994</v>
       </c>
       <c r="Q29" s="14">
-        <v>25.031315240083508</v>
+        <v>21.908141962421713</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>218.40909090909088</v>
+        <v>150.40909090909088</v>
       </c>
       <c r="T29" s="18">
-        <v>798</v>
+        <v>363</v>
       </c>
       <c r="U29" s="17">
-        <v>925.68</v>
+        <v>421.08</v>
       </c>
       <c r="V29" s="14">
-        <v>15.386503067484661</v>
+        <v>6.9991235758106916</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>20.045454545454504</v>
+        <v>-414.9545454545455</v>
       </c>
       <c r="Y29" s="18">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="Z29" s="17">
-        <v>530.12</v>
+        <v>499.96</v>
       </c>
       <c r="AA29" s="14">
-        <v>20.908496732026144</v>
+        <v>22.039772727272727</v>
       </c>
       <c r="AB29" s="16">
-        <v>480.85714285714289</v>
+        <v>430.22222222222229</v>
       </c>
       <c r="AC29" s="15">
-        <v>129.14285714285711</v>
+        <v>137.66666666666663</v>
       </c>
       <c r="AD29" s="19">
-        <v>5702</v>
+        <v>4580</v>
       </c>
       <c r="AE29" s="20">
-        <v>6614.32</v>
+        <v>5312.7999999999993</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4157,34 +4161,34 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>964</v>
+        <v>483</v>
       </c>
       <c r="F30" s="14">
-        <v>3547.52</v>
+        <v>1777.44</v>
       </c>
       <c r="G30" s="14">
-        <v>10.684130982367757</v>
+        <v>5.3531486146095713</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>61.727272727272634</v>
+        <v>-419.27272727272737</v>
       </c>
       <c r="J30" s="16">
-        <v>789</v>
+        <v>1197</v>
       </c>
       <c r="K30" s="13">
-        <v>2903.52</v>
+        <v>4404.96</v>
       </c>
       <c r="L30" s="14">
-        <v>7.808367071524966</v>
+        <v>11.846153846153847</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>-221.4545454545455</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="O30" s="16">
         <v>75</v>
@@ -4202,40 +4206,40 @@
         <v>19.090909090909093</v>
       </c>
       <c r="T30" s="18">
-        <v>461</v>
+        <v>334</v>
       </c>
       <c r="U30" s="17">
-        <v>1696.48</v>
+        <v>1229.1200000000001</v>
       </c>
       <c r="V30" s="14">
-        <v>14.530085959885387</v>
+        <v>10.527220630372494</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-14.909090909090878</v>
+        <v>-141.90909090909088</v>
       </c>
       <c r="Y30" s="18">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="Z30" s="17">
-        <v>272.32</v>
+        <v>195.04000000000002</v>
       </c>
       <c r="AA30" s="14">
-        <v>18.5</v>
+        <v>11.924999999999999</v>
       </c>
       <c r="AB30" s="16">
-        <v>88</v>
+        <v>97.777777777777786</v>
       </c>
       <c r="AC30" s="15">
-        <v>14</v>
+        <v>-13.666666666666671</v>
       </c>
       <c r="AD30" s="19">
-        <v>2363</v>
+        <v>2142</v>
       </c>
       <c r="AE30" s="20">
-        <v>8695.84</v>
+        <v>7882.56</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4270,34 +4274,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="F31" s="14">
-        <v>1773.76</v>
+        <v>1913.6000000000001</v>
       </c>
       <c r="G31" s="14">
-        <v>8.8440366972477058</v>
+        <v>9.5412844036697244</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-63</v>
+        <v>-25</v>
       </c>
       <c r="J31" s="16">
-        <v>874</v>
+        <v>653</v>
       </c>
       <c r="K31" s="13">
-        <v>3216.32</v>
+        <v>2403.04</v>
       </c>
       <c r="L31" s="14">
-        <v>13.133879781420768</v>
+        <v>9.8128415300546461</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>208.54545454545473</v>
+        <v>-12.454545454545269</v>
       </c>
       <c r="O31" s="16">
         <v>32</v>
@@ -4315,40 +4319,40 @@
         <v>4.7272727272727266</v>
       </c>
       <c r="T31" s="18">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="U31" s="17">
-        <v>655.04000000000008</v>
+        <v>430.56</v>
       </c>
       <c r="V31" s="14">
-        <v>14.889733840304181</v>
+        <v>9.7870722433460067</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>-1.318181818181813</v>
+        <v>-62.318181818181813</v>
       </c>
       <c r="Y31" s="18">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Z31" s="17">
-        <v>228.16</v>
+        <v>217.12</v>
       </c>
       <c r="AA31" s="14">
-        <v>36.166666666666664</v>
+        <v>44.25</v>
       </c>
       <c r="AB31" s="16">
-        <v>37.714285714285715</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AC31" s="15">
-        <v>36.285714285714285</v>
+        <v>39</v>
       </c>
       <c r="AD31" s="19">
-        <v>1628</v>
+        <v>1381</v>
       </c>
       <c r="AE31" s="20">
-        <v>5991.04</v>
+        <v>5082.08</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4383,85 +4387,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>795</v>
+        <v>944</v>
       </c>
       <c r="F32" s="14">
-        <v>3299.2500000000005</v>
+        <v>3917.6000000000004</v>
       </c>
       <c r="G32" s="14">
-        <v>3.6399583766909469</v>
+        <v>4.3221644120707596</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>-1389.090909090909</v>
+        <v>-1240.090909090909</v>
       </c>
       <c r="J32" s="16">
-        <v>1176</v>
+        <v>1684</v>
       </c>
       <c r="K32" s="13">
-        <v>4880.4000000000005</v>
+        <v>6988.6</v>
       </c>
       <c r="L32" s="14">
-        <v>6.8607796340493223</v>
+        <v>9.8244497480774324</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>-538.09090909090946</v>
+        <v>-30.090909090909463</v>
       </c>
       <c r="O32" s="16">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P32" s="17">
-        <v>834.15000000000009</v>
+        <v>813.40000000000009</v>
       </c>
       <c r="Q32" s="14">
-        <v>15.736654804270461</v>
+        <v>15.345195729537366</v>
       </c>
       <c r="R32" s="16">
         <v>281</v>
       </c>
       <c r="S32" s="15">
-        <v>9.4090909090909065</v>
+        <v>4.4090909090909065</v>
       </c>
       <c r="T32" s="18">
-        <v>891</v>
+        <v>688</v>
       </c>
       <c r="U32" s="17">
-        <v>3697.65</v>
+        <v>2855.2000000000003</v>
       </c>
       <c r="V32" s="14">
-        <v>10.705625341343527</v>
+        <v>8.2665210267613318</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-357.40909090909099</v>
+        <v>-560.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="Z32" s="17">
-        <v>1282.3500000000001</v>
+        <v>1257.45</v>
       </c>
       <c r="AA32" s="14">
-        <v>52.756097560975604</v>
+        <v>66.512195121951223</v>
       </c>
       <c r="AB32" s="16">
-        <v>128.85714285714286</v>
+        <v>100.22222222222221</v>
       </c>
       <c r="AC32" s="15">
-        <v>221.14285714285714</v>
+        <v>234.66666666666669</v>
       </c>
       <c r="AD32" s="19">
-        <v>3372</v>
+        <v>3815</v>
       </c>
       <c r="AE32" s="20">
-        <v>13993.800000000001</v>
+        <v>15832.250000000002</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4496,85 +4500,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>441</v>
+        <v>1550</v>
       </c>
       <c r="F33" s="14">
-        <v>1830.15</v>
+        <v>6432.5000000000009</v>
       </c>
       <c r="G33" s="14">
-        <v>1.1012485811577752</v>
+        <v>3.8706015891032917</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-3563.5454545454545</v>
+        <v>-2454.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>2524</v>
+        <v>3345</v>
       </c>
       <c r="K33" s="13">
-        <v>10474.6</v>
+        <v>13881.750000000002</v>
       </c>
       <c r="L33" s="14">
-        <v>10.945791444904396</v>
+        <v>14.506209343583679</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>218.09090909090901</v>
+        <v>1039.090909090909</v>
       </c>
       <c r="O33" s="16">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="P33" s="17">
-        <v>946.2</v>
+        <v>892.25000000000011</v>
       </c>
       <c r="Q33" s="14">
-        <v>13.97214484679666</v>
+        <v>13.17548746518106</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>-16.772727272727252</v>
+        <v>-29.772727272727252</v>
       </c>
       <c r="T33" s="18">
-        <v>1407</v>
+        <v>1211</v>
       </c>
       <c r="U33" s="17">
-        <v>5839.05</v>
+        <v>5025.6500000000005</v>
       </c>
       <c r="V33" s="14">
-        <v>12.081967213114755</v>
+        <v>10.398907103825136</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-339.81818181818176</v>
+        <v>-535.81818181818176</v>
       </c>
       <c r="Y33" s="18">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="Z33" s="17">
-        <v>759.45</v>
+        <v>597.6</v>
       </c>
       <c r="AA33" s="14">
-        <v>15.621951219512194</v>
+        <v>11.571428571428571</v>
       </c>
       <c r="AB33" s="16">
-        <v>257.71428571428572</v>
+        <v>273.77777777777777</v>
       </c>
       <c r="AC33" s="15">
-        <v>7.2857142857142776</v>
+        <v>-42.666666666666657</v>
       </c>
       <c r="AD33" s="19">
-        <v>4783</v>
+        <v>6465</v>
       </c>
       <c r="AE33" s="20">
-        <v>19849.45</v>
+        <v>26829.750000000004</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4609,25 +4613,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="F34" s="14">
-        <v>1996.15</v>
+        <v>1925.6000000000001</v>
       </c>
       <c r="G34" s="14">
-        <v>7.15</v>
+        <v>6.8972972972972979</v>
       </c>
       <c r="H34" s="30">
         <v>1480</v>
       </c>
       <c r="I34" s="15">
-        <v>-191.72727272727263</v>
+        <v>-208.72727272727263</v>
       </c>
       <c r="J34" s="16">
-        <v>72</v>
+        <v>1073</v>
       </c>
       <c r="K34" s="13">
-        <v>298.8</v>
+        <v>4452.9500000000007</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4636,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>72</v>
+        <v>1073</v>
       </c>
       <c r="O34" s="16">
         <v>32</v>
@@ -4684,10 +4688,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>691</v>
+        <v>1675</v>
       </c>
       <c r="AE34" s="20">
-        <v>2867.65</v>
+        <v>6951.2500000000009</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4722,85 +4726,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1637</v>
+        <v>1597</v>
       </c>
       <c r="F35" s="14">
-        <v>2668.31</v>
+        <v>2603.1099999999997</v>
       </c>
       <c r="G35" s="14">
-        <v>3.36768281279222</v>
+        <v>3.2853936786983358</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-3223.909090909091</v>
+        <v>-3263.909090909091</v>
       </c>
       <c r="J35" s="16">
-        <v>566</v>
+        <v>5413</v>
       </c>
       <c r="K35" s="13">
-        <v>922.57999999999993</v>
+        <v>8823.1899999999987</v>
       </c>
       <c r="L35" s="14">
-        <v>3.8658801614405465</v>
+        <v>36.971747904377523</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>-898.09090909090901</v>
+        <v>3948.909090909091</v>
       </c>
       <c r="O35" s="16">
-        <v>648</v>
+        <v>618</v>
       </c>
       <c r="P35" s="17">
-        <v>1056.24</v>
+        <v>1007.3399999999999</v>
       </c>
       <c r="Q35" s="14">
-        <v>14.927748691099477</v>
+        <v>14.236649214659687</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>-3.136363636363626</v>
+        <v>-33.136363636363626</v>
       </c>
       <c r="T35" s="18">
-        <v>390</v>
+        <v>248</v>
       </c>
       <c r="U35" s="17">
-        <v>635.69999999999993</v>
+        <v>404.23999999999995</v>
       </c>
       <c r="V35" s="14">
-        <v>6.2995594713656393</v>
+        <v>4.0058737151248165</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-538.63636363636363</v>
+        <v>-680.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="Z35" s="17">
-        <v>689.49</v>
+        <v>650.37</v>
       </c>
       <c r="AA35" s="14">
-        <v>37.96153846153846</v>
+        <v>41.275862068965523</v>
       </c>
       <c r="AB35" s="16">
-        <v>245.14285714285714</v>
+        <v>212.66666666666666</v>
       </c>
       <c r="AC35" s="15">
-        <v>255.85714285714286</v>
+        <v>254</v>
       </c>
       <c r="AD35" s="19">
-        <v>3664</v>
+        <v>8275</v>
       </c>
       <c r="AE35" s="20">
-        <v>5972.32</v>
+        <v>13488.25</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4835,85 +4839,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>1218</v>
+        <v>578</v>
       </c>
       <c r="F36" s="14">
-        <v>1985.34</v>
+        <v>942.14</v>
       </c>
       <c r="G36" s="14">
-        <v>1.6292332948258039</v>
+        <v>0.77315011856265581</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-6257.909090909091</v>
+        <v>-6897.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>2164</v>
+        <v>4500</v>
       </c>
       <c r="K36" s="13">
-        <v>3527.3199999999997</v>
+        <v>7334.9999999999991</v>
       </c>
       <c r="L36" s="14">
-        <v>9.6489663558978513</v>
+        <v>20.064856100526956</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>-78.727272727272975</v>
+        <v>2257.272727272727</v>
       </c>
       <c r="O36" s="16">
-        <v>723</v>
+        <v>573</v>
       </c>
       <c r="P36" s="17">
-        <v>1178.49</v>
+        <v>933.9899999999999</v>
       </c>
       <c r="Q36" s="14">
-        <v>7.9410883674488266</v>
+        <v>6.2935596605092359</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-642.68181818181824</v>
+        <v>-792.68181818181824</v>
       </c>
       <c r="T36" s="18">
-        <v>2003</v>
+        <v>1572</v>
       </c>
       <c r="U36" s="17">
-        <v>3264.89</v>
+        <v>2562.3599999999997</v>
       </c>
       <c r="V36" s="14">
-        <v>14.998638529611982</v>
+        <v>11.771272974812799</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-0.18181818181801646</v>
+        <v>-431.18181818181802</v>
       </c>
       <c r="Y36" s="18">
-        <v>508</v>
+        <v>451</v>
       </c>
       <c r="Z36" s="17">
-        <v>828.04</v>
+        <v>735.13</v>
       </c>
       <c r="AA36" s="14">
-        <v>18.424870466321245</v>
+        <v>18.967289719626169</v>
       </c>
       <c r="AB36" s="16">
-        <v>606.57142857142856</v>
+        <v>523.11111111111109</v>
       </c>
       <c r="AC36" s="15">
-        <v>94.428571428571445</v>
+        <v>94.333333333333371</v>
       </c>
       <c r="AD36" s="19">
-        <v>6616</v>
+        <v>7674</v>
       </c>
       <c r="AE36" s="20">
-        <v>10784.08</v>
+        <v>12508.619999999999</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4948,85 +4952,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>767</v>
+        <v>1300</v>
       </c>
       <c r="F37" s="14">
-        <v>1250.2099999999998</v>
+        <v>2119</v>
       </c>
       <c r="G37" s="14">
-        <v>2.8316831683168315</v>
+        <v>4.7994629971471721</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-1941.636363636364</v>
+        <v>-1408.636363636364</v>
       </c>
       <c r="J37" s="16">
-        <v>2756</v>
+        <v>698</v>
       </c>
       <c r="K37" s="13">
-        <v>4492.28</v>
+        <v>1137.74</v>
       </c>
       <c r="L37" s="14">
-        <v>25.03385631709331</v>
+        <v>6.3402146985962009</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>1655.090909090909</v>
+        <v>-402.90909090909099</v>
       </c>
       <c r="O37" s="16">
-        <v>375</v>
+        <v>313</v>
       </c>
       <c r="P37" s="17">
-        <v>611.25</v>
+        <v>510.18999999999994</v>
       </c>
       <c r="Q37" s="14">
-        <v>8.112094395280236</v>
+        <v>6.7708947885939041</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-318.40909090909088</v>
+        <v>-380.40909090909088</v>
       </c>
       <c r="T37" s="18">
-        <v>716</v>
+        <v>533</v>
       </c>
       <c r="U37" s="17">
-        <v>1167.08</v>
+        <v>868.79</v>
       </c>
       <c r="V37" s="14">
-        <v>10.34274458305975</v>
+        <v>7.6992777413000653</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-322.40909090909099</v>
+        <v>-505.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="Z37" s="17">
-        <v>286.88</v>
+        <v>171.14999999999998</v>
       </c>
       <c r="AA37" s="14">
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>301.71428571428572</v>
+        <v>344.66666666666663</v>
       </c>
       <c r="AC37" s="15">
-        <v>-29.714285714285722</v>
+        <v>-129.99999999999997</v>
       </c>
       <c r="AD37" s="19">
-        <v>4790</v>
+        <v>2949</v>
       </c>
       <c r="AE37" s="20">
-        <v>7807.7</v>
+        <v>4806.87</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5061,85 +5065,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1459</v>
+        <v>1401</v>
       </c>
       <c r="F38" s="14">
-        <v>2378.1699999999996</v>
+        <v>2283.6299999999997</v>
       </c>
       <c r="G38" s="14">
-        <v>7.8116330007301045</v>
+        <v>7.5010951569724993</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>-408.72727272727275</v>
+        <v>-466.72727272727275</v>
       </c>
       <c r="J38" s="16">
-        <v>2763</v>
+        <v>1206</v>
       </c>
       <c r="K38" s="13">
-        <v>4503.6899999999996</v>
+        <v>1965.78</v>
       </c>
       <c r="L38" s="14">
-        <v>29.139980824544583</v>
+        <v>12.719079578139981</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>1814.818181818182</v>
+        <v>257.81818181818187</v>
       </c>
       <c r="O38" s="16">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="P38" s="17">
-        <v>762.83999999999992</v>
+        <v>665.04</v>
       </c>
       <c r="Q38" s="14">
-        <v>13.70972037283622</v>
+        <v>11.952063914780295</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>-44.045454545454504</v>
+        <v>-104.0454545454545</v>
       </c>
       <c r="T38" s="18">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="U38" s="17">
-        <v>749.8</v>
+        <v>563.98</v>
       </c>
       <c r="V38" s="14">
-        <v>9.873170731707317</v>
+        <v>7.4263414634146336</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-238.86363636363637</v>
+        <v>-352.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>455</v>
+        <v>354</v>
       </c>
       <c r="Z38" s="17">
-        <v>741.65</v>
+        <v>577.02</v>
       </c>
       <c r="AA38" s="14">
-        <v>16.502590673575131</v>
+        <v>12.543307086614172</v>
       </c>
       <c r="AB38" s="16">
-        <v>606.57142857142856</v>
+        <v>620.88888888888891</v>
       </c>
       <c r="AC38" s="15">
-        <v>41.428571428571445</v>
+        <v>-69.333333333333371</v>
       </c>
       <c r="AD38" s="19">
-        <v>5605</v>
+        <v>3715</v>
       </c>
       <c r="AE38" s="20">
-        <v>9136.15</v>
+        <v>6055.45</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5174,85 +5178,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1796</v>
+        <v>499</v>
       </c>
       <c r="F39" s="14">
-        <v>2927.48</v>
+        <v>813.36999999999989</v>
       </c>
       <c r="G39" s="14">
-        <v>211.29411764705881</v>
+        <v>58.705882352941174</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>1711</v>
+        <v>414</v>
       </c>
       <c r="J39" s="16">
-        <v>6520</v>
+        <v>6051</v>
       </c>
       <c r="K39" s="13">
-        <v>10627.599999999999</v>
+        <v>9863.1299999999992</v>
       </c>
       <c r="L39" s="14">
-        <v>175.78431372549022</v>
+        <v>163.13970588235296</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>6149.090909090909</v>
+        <v>5680.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>522</v>
+        <v>474</v>
       </c>
       <c r="P39" s="17">
-        <v>850.8599999999999</v>
+        <v>772.62</v>
       </c>
       <c r="Q39" s="14">
-        <v>1044</v>
+        <v>948</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>514.5</v>
+        <v>466.5</v>
       </c>
       <c r="T39" s="18">
-        <v>415</v>
+        <v>294</v>
       </c>
       <c r="U39" s="17">
-        <v>676.44999999999993</v>
+        <v>479.21999999999997</v>
       </c>
       <c r="V39" s="14">
-        <v>16.970260223048328</v>
+        <v>12.022304832713756</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>48.181818181818187</v>
+        <v>-72.818181818181813</v>
       </c>
       <c r="Y39" s="18">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="Z39" s="17">
-        <v>795.43999999999994</v>
+        <v>790.55</v>
       </c>
       <c r="AA39" s="14">
-        <v>92.324324324324323</v>
+        <v>114.86842105263158</v>
       </c>
       <c r="AB39" s="16">
-        <v>116.28571428571428</v>
+        <v>92.888888888888886</v>
       </c>
       <c r="AC39" s="15">
-        <v>408.71428571428572</v>
+        <v>421.66666666666669</v>
       </c>
       <c r="AD39" s="19">
-        <v>9741</v>
+        <v>7803</v>
       </c>
       <c r="AE39" s="20">
-        <v>15877.829999999998</v>
+        <v>12718.89</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5287,85 +5291,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1675</v>
+        <v>333</v>
       </c>
       <c r="F40" s="14">
-        <v>2730.25</v>
+        <v>542.79</v>
       </c>
       <c r="G40" s="14">
-        <v>199.18918918918922</v>
+        <v>39.6</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>1590.909090909091</v>
+        <v>248.90909090909093</v>
       </c>
       <c r="J40" s="16">
-        <v>6649</v>
+        <v>6448</v>
       </c>
       <c r="K40" s="13">
-        <v>10837.869999999999</v>
+        <v>10510.24</v>
       </c>
       <c r="L40" s="14">
-        <v>204.87114845938376</v>
+        <v>198.67787114845939</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>6324.454545454546</v>
+        <v>6123.454545454546</v>
       </c>
       <c r="O40" s="16">
-        <v>483</v>
+        <v>420</v>
       </c>
       <c r="P40" s="17">
-        <v>787.29</v>
+        <v>684.59999999999991</v>
       </c>
       <c r="Q40" s="14">
-        <v>966</v>
+        <v>840</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>475.5</v>
+        <v>412.5</v>
       </c>
       <c r="T40" s="18">
-        <v>415</v>
+        <v>269</v>
       </c>
       <c r="U40" s="17">
-        <v>676.44999999999993</v>
+        <v>438.46999999999997</v>
       </c>
       <c r="V40" s="14">
-        <v>16.21669626998224</v>
+        <v>10.511545293072825</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>31.136363636363626</v>
+        <v>-114.86363636363637</v>
       </c>
       <c r="Y40" s="18">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="Z40" s="17">
-        <v>800.32999999999993</v>
+        <v>795.43999999999994</v>
       </c>
       <c r="AA40" s="14">
-        <v>79.930232558139537</v>
+        <v>102.13953488372093</v>
       </c>
       <c r="AB40" s="16">
-        <v>135.14285714285714</v>
+        <v>105.11111111111111</v>
       </c>
       <c r="AC40" s="15">
-        <v>398.85714285714289</v>
+        <v>416.33333333333331</v>
       </c>
       <c r="AD40" s="19">
-        <v>9713</v>
+        <v>7958</v>
       </c>
       <c r="AE40" s="20">
-        <v>15832.189999999999</v>
+        <v>12971.539999999999</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5400,85 +5404,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>351</v>
+        <v>234</v>
       </c>
       <c r="F41" s="14">
-        <v>2158.65</v>
+        <v>1439.1000000000001</v>
       </c>
       <c r="G41" s="14">
-        <v>5.7540983606557381</v>
+        <v>3.8360655737704916</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-259</v>
+        <v>-376</v>
       </c>
       <c r="J41" s="16">
-        <v>327</v>
+        <v>194</v>
       </c>
       <c r="K41" s="13">
-        <v>2011.0500000000002</v>
+        <v>1193.1000000000001</v>
       </c>
       <c r="L41" s="14">
-        <v>9.0833333333333339</v>
+        <v>5.3888888888888893</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>-33</v>
+        <v>-166</v>
       </c>
       <c r="O41" s="16">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P41" s="17">
-        <v>430.5</v>
+        <v>295.20000000000005</v>
       </c>
       <c r="Q41" s="14">
-        <v>18.554216867469879</v>
+        <v>12.72289156626506</v>
       </c>
       <c r="R41" s="16">
         <v>83</v>
       </c>
       <c r="S41" s="15">
-        <v>13.409090909090907</v>
+        <v>-8.5909090909090935</v>
       </c>
       <c r="T41" s="18">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="U41" s="17">
-        <v>1512.9</v>
+        <v>1414.5</v>
       </c>
       <c r="V41" s="14">
-        <v>14.548387096774192</v>
+        <v>13.602150537634408</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-7.6363636363636545</v>
+        <v>-23.636363636363654</v>
       </c>
       <c r="Y41" s="18">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="Z41" s="17">
-        <v>492</v>
+        <v>258.3</v>
       </c>
       <c r="AA41" s="14">
         <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>53.428571428571423</v>
+        <v>97.777777777777786</v>
       </c>
       <c r="AC41" s="15">
-        <v>43.571428571428577</v>
+        <v>-24.666666666666671</v>
       </c>
       <c r="AD41" s="19">
-        <v>1074</v>
+        <v>748</v>
       </c>
       <c r="AE41" s="20">
-        <v>6605.1</v>
+        <v>4600.2</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5513,85 +5517,85 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>364</v>
+        <v>209</v>
       </c>
       <c r="F42" s="14">
-        <v>2238.6</v>
+        <v>1285.3500000000001</v>
       </c>
       <c r="G42" s="14">
-        <v>5.6713881019830028</v>
+        <v>3.2563739376770537</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-277.81818181818187</v>
+        <v>-432.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>358</v>
+        <v>211</v>
       </c>
       <c r="K42" s="13">
-        <v>2201.7000000000003</v>
+        <v>1297.6500000000001</v>
       </c>
       <c r="L42" s="14">
-        <v>8.5053995680345569</v>
+        <v>5.0129589632829372</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>-62.909090909090935</v>
+        <v>-209.90909090909093</v>
       </c>
       <c r="O42" s="16">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="P42" s="17">
-        <v>399.75</v>
+        <v>270.60000000000002</v>
       </c>
       <c r="Q42" s="14">
-        <v>17.654320987654323</v>
+        <v>11.950617283950617</v>
       </c>
       <c r="R42" s="16">
         <v>81</v>
       </c>
       <c r="S42" s="15">
-        <v>9.7727272727272734</v>
+        <v>-11.227272727272727</v>
       </c>
       <c r="T42" s="18">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="U42" s="17">
-        <v>2207.85</v>
+        <v>1845</v>
       </c>
       <c r="V42" s="14">
-        <v>14.901886792452832</v>
+        <v>12.452830188679245</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-2.363636363636374</v>
+        <v>-61.363636363636374</v>
       </c>
       <c r="Y42" s="18">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="Z42" s="17">
-        <v>645.75</v>
+        <v>590.40000000000009</v>
       </c>
       <c r="AA42" s="14">
-        <v>18.846153846153847</v>
+        <v>19.2</v>
       </c>
       <c r="AB42" s="16">
-        <v>122.57142857142857</v>
+        <v>110</v>
       </c>
       <c r="AC42" s="15">
-        <v>21.428571428571431</v>
+        <v>21</v>
       </c>
       <c r="AD42" s="19">
-        <v>1251</v>
+        <v>860</v>
       </c>
       <c r="AE42" s="20">
-        <v>7693.6500000000005</v>
+        <v>5289</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5626,85 +5630,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2358</v>
+        <v>3040</v>
       </c>
       <c r="F43" s="14">
-        <v>2735.2799999999997</v>
+        <v>3526.3999999999996</v>
       </c>
       <c r="G43" s="14">
-        <v>7.0283159463487328</v>
+        <v>9.0611028315946349</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-997</v>
+        <v>-315</v>
       </c>
       <c r="J43" s="16">
-        <v>4565</v>
+        <v>3164</v>
       </c>
       <c r="K43" s="13">
-        <v>5295.4</v>
+        <v>3670.24</v>
       </c>
       <c r="L43" s="14">
-        <v>36.586520947176687</v>
+        <v>25.358105646630239</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>3317.272727272727</v>
+        <v>1916.2727272727273</v>
       </c>
       <c r="O43" s="16">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="P43" s="17">
-        <v>429.2</v>
+        <v>382.79999999999995</v>
       </c>
       <c r="Q43" s="14">
-        <v>7.1591908531222517</v>
+        <v>6.3852242744063323</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-405.22727272727275</v>
+        <v>-445.22727272727275</v>
       </c>
       <c r="T43" s="18">
-        <v>1300</v>
+        <v>916</v>
       </c>
       <c r="U43" s="17">
-        <v>1508</v>
+        <v>1062.56</v>
       </c>
       <c r="V43" s="14">
-        <v>13.783132530120483</v>
+        <v>9.7118072289156636</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-114.77272727272725</v>
+        <v>-498.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>383</v>
+        <v>314</v>
       </c>
       <c r="Z43" s="17">
-        <v>444.28</v>
+        <v>364.23999999999995</v>
       </c>
       <c r="AA43" s="14">
-        <v>12.29816513761468</v>
+        <v>10.911196911196912</v>
       </c>
       <c r="AB43" s="16">
-        <v>685.14285714285711</v>
+        <v>633.11111111111109</v>
       </c>
       <c r="AC43" s="15">
-        <v>-84.14285714285711</v>
+        <v>-117.66666666666663</v>
       </c>
       <c r="AD43" s="19">
-        <v>8976</v>
+        <v>7764</v>
       </c>
       <c r="AE43" s="20">
-        <v>10412.16</v>
+        <v>9006.24</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5739,85 +5743,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>923</v>
+        <v>2004</v>
       </c>
       <c r="F44" s="14">
-        <v>1070.6799999999998</v>
+        <v>2324.64</v>
       </c>
       <c r="G44" s="14">
-        <v>3.1540851196023612</v>
+        <v>6.8480894687791238</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-2003.363636363636</v>
+        <v>-922.36363636363603</v>
       </c>
       <c r="J44" s="16">
-        <v>4144</v>
+        <v>2556</v>
       </c>
       <c r="K44" s="13">
-        <v>4807.04</v>
+        <v>2964.9599999999996</v>
       </c>
       <c r="L44" s="14">
-        <v>24.195329087048837</v>
+        <v>14.923566878980894</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>2431.2727272727275</v>
+        <v>843.27272727272748</v>
       </c>
       <c r="O44" s="16">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="P44" s="17">
-        <v>476.76</v>
+        <v>460.52</v>
       </c>
       <c r="Q44" s="14">
-        <v>12.023936170212767</v>
+        <v>11.61436170212766</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>-101.72727272727275</v>
+        <v>-115.72727272727275</v>
       </c>
       <c r="T44" s="18">
-        <v>1220</v>
+        <v>1025</v>
       </c>
       <c r="U44" s="17">
-        <v>1415.1999999999998</v>
+        <v>1189</v>
       </c>
       <c r="V44" s="14">
-        <v>14.43010752688172</v>
+        <v>12.123655913978494</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-48.181818181818244</v>
+        <v>-243.18181818181824</v>
       </c>
       <c r="Y44" s="18">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="Z44" s="17">
-        <v>571.88</v>
+        <v>502.28</v>
       </c>
       <c r="AA44" s="14">
-        <v>18.356382978723403</v>
+        <v>17.243362831858409</v>
       </c>
       <c r="AB44" s="16">
-        <v>590.85714285714289</v>
+        <v>552.44444444444446</v>
       </c>
       <c r="AC44" s="15">
-        <v>90.14285714285711</v>
+        <v>56.333333333333314</v>
       </c>
       <c r="AD44" s="19">
-        <v>7191</v>
+        <v>6415</v>
       </c>
       <c r="AE44" s="20">
-        <v>8341.56</v>
+        <v>7441.4</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5852,85 +5856,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2150</v>
+        <v>3171</v>
       </c>
       <c r="F45" s="14">
-        <v>2494</v>
+        <v>3678.3599999999997</v>
       </c>
       <c r="G45" s="14">
-        <v>5.5804624823029734</v>
+        <v>8.2305332704105716</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-1702.7272727272725</v>
+        <v>-681.72727272727252</v>
       </c>
       <c r="J45" s="16">
-        <v>4297</v>
+        <v>4717</v>
       </c>
       <c r="K45" s="13">
-        <v>4984.5199999999995</v>
+        <v>5471.7199999999993</v>
       </c>
       <c r="L45" s="14">
-        <v>17.480399408284025</v>
+        <v>19.188979289940828</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>1838.818181818182</v>
+        <v>2258.818181818182</v>
       </c>
       <c r="O45" s="16">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="P45" s="17">
-        <v>795.76</v>
+        <v>783</v>
       </c>
       <c r="Q45" s="14">
-        <v>13.487042001787309</v>
+        <v>13.270777479892761</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>-76.954545454545496</v>
+        <v>-87.954545454545496</v>
       </c>
       <c r="T45" s="18">
-        <v>1627</v>
+        <v>1330</v>
       </c>
       <c r="U45" s="17">
-        <v>1887.32</v>
+        <v>1542.8</v>
       </c>
       <c r="V45" s="14">
-        <v>14.147826086956522</v>
+        <v>11.565217391304348</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-98</v>
+        <v>-395</v>
       </c>
       <c r="Y45" s="18">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="Z45" s="17">
-        <v>455.88</v>
+        <v>390.91999999999996</v>
       </c>
       <c r="AA45" s="14">
-        <v>13.16267942583732</v>
+        <v>12.083665338645417</v>
       </c>
       <c r="AB45" s="16">
-        <v>656.85714285714289</v>
+        <v>613.55555555555554</v>
       </c>
       <c r="AC45" s="15">
-        <v>-54.85714285714289</v>
+        <v>-81.333333333333314</v>
       </c>
       <c r="AD45" s="19">
-        <v>9153</v>
+        <v>10230</v>
       </c>
       <c r="AE45" s="20">
-        <v>10617.48</v>
+        <v>11866.8</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5965,85 +5969,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2494</v>
+        <v>2473</v>
       </c>
       <c r="F46" s="14">
-        <v>2893.04</v>
+        <v>2868.68</v>
       </c>
       <c r="G46" s="14">
-        <v>9.6598591549295776</v>
+        <v>9.5785211267605632</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>-87.818181818181984</v>
+        <v>-108.81818181818198</v>
       </c>
       <c r="J46" s="16">
-        <v>4185</v>
+        <v>5140</v>
       </c>
       <c r="K46" s="13">
-        <v>4854.5999999999995</v>
+        <v>5962.4</v>
       </c>
       <c r="L46" s="14">
-        <v>23.191435768261965</v>
+        <v>28.483627204030224</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>2380.454545454545</v>
+        <v>3335.454545454545</v>
       </c>
       <c r="O46" s="16">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="P46" s="17">
-        <v>664.68</v>
+        <v>657.71999999999991</v>
       </c>
       <c r="Q46" s="14">
-        <v>15.335766423357663</v>
+        <v>15.175182481751824</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>12.545454545454504</v>
+        <v>6.5454545454545041</v>
       </c>
       <c r="T46" s="18">
-        <v>890</v>
+        <v>458</v>
       </c>
       <c r="U46" s="17">
-        <v>1032.3999999999999</v>
+        <v>531.28</v>
       </c>
       <c r="V46" s="14">
-        <v>15.739549839228296</v>
+        <v>8.09967845659164</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>41.818181818181756</v>
+        <v>-390.18181818181824</v>
       </c>
       <c r="Y46" s="18">
-        <v>345</v>
+        <v>260</v>
       </c>
       <c r="Z46" s="17">
-        <v>400.2</v>
+        <v>301.59999999999997</v>
       </c>
       <c r="AA46" s="14">
-        <v>19.4758064516129</v>
+        <v>12.857142857142858</v>
       </c>
       <c r="AB46" s="16">
-        <v>389.71428571428572</v>
+        <v>444.88888888888886</v>
       </c>
       <c r="AC46" s="15">
-        <v>79.285714285714278</v>
+        <v>-43.333333333333314</v>
       </c>
       <c r="AD46" s="19">
-        <v>8487</v>
+        <v>8898</v>
       </c>
       <c r="AE46" s="20">
-        <v>9844.92</v>
+        <v>10321.679999999998</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6077,9 +6081,7 @@
       <c r="D47" s="12">
         <v>18</v>
       </c>
-      <c r="E47" s="13">
-        <v>0</v>
-      </c>
+      <c r="E47" s="13"/>
       <c r="F47" s="14">
         <v>0</v>
       </c>
@@ -6093,19 +6095,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K47" s="13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L47" s="14">
-        <v>0</v>
+        <v>6.875</v>
       </c>
       <c r="M47" s="30">
         <v>32</v>
       </c>
       <c r="N47" s="15">
-        <v>-14.545454545454547</v>
+        <v>-4.5454545454545467</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6123,25 +6125,25 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U47" s="17">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="V47" s="14">
-        <v>12.1</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-2.6363636363636367</v>
+        <v>-10.636363636363637</v>
       </c>
       <c r="Y47" s="18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="17">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="14">
         <v>0</v>
@@ -6150,13 +6152,13 @@
         <v>0</v>
       </c>
       <c r="AC47" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE47" s="20">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6190,9 +6192,7 @@
       <c r="D48" s="12">
         <v>18</v>
       </c>
-      <c r="E48" s="13">
-        <v>0</v>
-      </c>
+      <c r="E48" s="13"/>
       <c r="F48" s="14">
         <v>0</v>
       </c>
@@ -6206,19 +6206,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K48" s="13">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L48" s="14">
-        <v>0</v>
+        <v>26.888888888888886</v>
       </c>
       <c r="M48" s="30">
         <v>9</v>
       </c>
       <c r="N48" s="15">
-        <v>-4.0909090909090908</v>
+        <v>6.9090909090909092</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE48" s="20">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6304,34 +6304,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>1032</v>
+        <v>731</v>
       </c>
       <c r="F49" s="14">
-        <v>1197.1199999999999</v>
+        <v>847.95999999999992</v>
       </c>
       <c r="G49" s="14">
-        <v>18.354082457558611</v>
+        <v>13.000808407437349</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>469.72727272727275</v>
+        <v>168.72727272727275</v>
       </c>
       <c r="J49" s="16">
-        <v>259</v>
+        <v>380</v>
       </c>
       <c r="K49" s="13">
-        <v>300.44</v>
+        <v>440.79999999999995</v>
       </c>
       <c r="L49" s="14">
-        <v>4.6212489862124899</v>
+        <v>6.7802108678021087</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>-301.4545454545455</v>
+        <v>-180.4545454545455</v>
       </c>
       <c r="O49" s="16">
         <v>39</v>
@@ -6349,40 +6349,40 @@
         <v>-37.36363636363636</v>
       </c>
       <c r="T49" s="18">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="U49" s="17">
-        <v>212.27999999999997</v>
+        <v>135.72</v>
       </c>
       <c r="V49" s="14">
-        <v>17.353448275862071</v>
+        <v>11.094827586206897</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>24.818181818181813</v>
+        <v>-41.181818181818187</v>
       </c>
       <c r="Y49" s="18">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="Z49" s="17">
-        <v>95.11999999999999</v>
+        <v>87</v>
       </c>
       <c r="AA49" s="14">
-        <v>14.35</v>
+        <v>16.071428571428569</v>
       </c>
       <c r="AB49" s="16">
-        <v>125.71428571428572</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="AC49" s="15">
-        <v>-3.7142857142857224</v>
+        <v>5</v>
       </c>
       <c r="AD49" s="19">
-        <v>1595</v>
+        <v>1342</v>
       </c>
       <c r="AE49" s="20">
-        <v>1850.1999999999998</v>
+        <v>1556.7199999999998</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6417,49 +6417,49 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1325</v>
+        <v>2090</v>
       </c>
       <c r="F50" s="14">
-        <v>1537</v>
+        <v>2424.3999999999996</v>
       </c>
       <c r="G50" s="14">
-        <v>5.1979315263908701</v>
+        <v>8.199001426533524</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-1224.090909090909</v>
+        <v>-459.09090909090901</v>
       </c>
       <c r="J50" s="16">
-        <v>3138</v>
+        <v>1644</v>
       </c>
       <c r="K50" s="13">
-        <v>3640.08</v>
+        <v>1907.04</v>
       </c>
       <c r="L50" s="14">
-        <v>19.30536912751678</v>
+        <v>10.114093959731544</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>1512.5454545454547</v>
+        <v>18.545454545454731</v>
       </c>
       <c r="O50" s="16">
-        <v>316</v>
+        <v>254</v>
       </c>
       <c r="P50" s="17">
-        <v>366.56</v>
+        <v>294.64</v>
       </c>
       <c r="Q50" s="14">
-        <v>14.483333333333334</v>
+        <v>11.641666666666667</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>-11.272727272727252</v>
+        <v>-73.272727272727252</v>
       </c>
       <c r="T50" s="18">
         <v>0</v>
@@ -6477,25 +6477,25 @@
         <v>-1199.3181818181818</v>
       </c>
       <c r="Y50" s="18">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="Z50" s="17">
-        <v>170.51999999999998</v>
+        <v>154.28</v>
       </c>
       <c r="AA50" s="14">
-        <v>10.393939393939396</v>
+        <v>10.881818181818183</v>
       </c>
       <c r="AB50" s="16">
-        <v>311.14285714285711</v>
+        <v>268.88888888888886</v>
       </c>
       <c r="AC50" s="15">
-        <v>-65.14285714285711</v>
+        <v>-50.333333333333314</v>
       </c>
       <c r="AD50" s="19">
-        <v>4926</v>
+        <v>4121</v>
       </c>
       <c r="AE50" s="20">
-        <v>5714.16</v>
+        <v>4780.3599999999997</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6533,40 +6533,40 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>691</v>
+        <v>929</v>
       </c>
       <c r="F51" s="14">
-        <v>801.56</v>
+        <v>1077.6399999999999</v>
       </c>
       <c r="G51" s="14">
-        <v>11.96066089693155</v>
+        <v>16.080251770259636</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>113.27272727272725</v>
+        <v>351.27272727272725</v>
       </c>
       <c r="J51" s="16">
-        <v>3678</v>
+        <v>3148</v>
       </c>
       <c r="K51" s="13">
-        <v>4266.4799999999996</v>
+        <v>3651.68</v>
       </c>
       <c r="L51" s="14">
-        <v>82.567346938775515</v>
+        <v>70.669387755102036</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>3232.5454545454545</v>
+        <v>2702.5454545454545</v>
       </c>
       <c r="O51" s="16">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="P51" s="17">
-        <v>415.28</v>
+        <v>388.59999999999997</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
@@ -6575,43 +6575,43 @@
         <v>0</v>
       </c>
       <c r="S51" s="15">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="T51" s="18">
-        <v>209</v>
+        <v>38</v>
       </c>
       <c r="U51" s="17">
-        <v>242.43999999999997</v>
+        <v>44.08</v>
       </c>
       <c r="V51" s="14">
-        <v>8.5464684014869885</v>
+        <v>1.5539033457249072</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>-157.81818181818181</v>
+        <v>-328.81818181818181</v>
       </c>
       <c r="Y51" s="18">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="Z51" s="17">
-        <v>157.76</v>
+        <v>142.67999999999998</v>
       </c>
       <c r="AA51" s="14">
         <v>0</v>
       </c>
       <c r="AB51" s="16">
-        <v>81.714285714285722</v>
+        <v>90.444444444444429</v>
       </c>
       <c r="AC51" s="15">
-        <v>80.285714285714278</v>
+        <v>61.333333333333343</v>
       </c>
       <c r="AD51" s="19">
-        <v>5072</v>
+        <v>4573</v>
       </c>
       <c r="AE51" s="20">
-        <v>5883.5199999999995</v>
+        <v>5304.6799999999994</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6650,34 +6650,34 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>4320</v>
+        <v>3646</v>
       </c>
       <c r="F52" s="14">
-        <v>3499.2000000000003</v>
+        <v>2953.26</v>
       </c>
       <c r="G52" s="14">
-        <v>35.91836734693878</v>
+        <v>30.314436885865458</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>3117.272727272727</v>
+        <v>2443.272727272727</v>
       </c>
       <c r="J52" s="16">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="K52" s="13">
-        <v>0</v>
+        <v>891.81000000000006</v>
       </c>
       <c r="L52" s="14">
-        <v>0</v>
+        <v>12.511363636363637</v>
       </c>
       <c r="M52" s="30">
         <v>1936</v>
       </c>
       <c r="N52" s="15">
-        <v>-880</v>
+        <v>221</v>
       </c>
       <c r="O52" s="16">
         <v>0</v>
@@ -6695,19 +6695,19 @@
         <v>-339.54545454545456</v>
       </c>
       <c r="T52" s="18">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="U52" s="17">
-        <v>64.800000000000011</v>
+        <v>45.36</v>
       </c>
       <c r="V52" s="14">
-        <v>1.9533851276359602</v>
+        <v>1.3673695893451721</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-534.31818181818176</v>
+        <v>-558.31818181818176</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>72.285714285714278</v>
+        <v>56.222222222222214</v>
       </c>
       <c r="AC52" s="15">
-        <v>-49.285714285714278</v>
+        <v>-38.333333333333329</v>
       </c>
       <c r="AD52" s="19">
-        <v>4400</v>
+        <v>4803</v>
       </c>
       <c r="AE52" s="20">
-        <v>3564.0000000000005</v>
+        <v>3890.4300000000003</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6763,85 +6763,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1914</v>
+        <v>1313</v>
       </c>
       <c r="F53" s="14">
-        <v>1550.3400000000001</v>
+        <v>1063.53</v>
       </c>
       <c r="G53" s="14">
-        <v>8.2001947419668948</v>
+        <v>5.6253164556962023</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>-420.09090909090901</v>
+        <v>-1021.090909090909</v>
       </c>
       <c r="J53" s="16">
-        <v>3861</v>
+        <v>4441</v>
       </c>
       <c r="K53" s="13">
-        <v>3127.4100000000003</v>
+        <v>3597.21</v>
       </c>
       <c r="L53" s="14">
-        <v>26.753385826771648</v>
+        <v>30.772283464566925</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>2417.8181818181815</v>
+        <v>2997.8181818181815</v>
       </c>
       <c r="O53" s="16">
-        <v>336</v>
+        <v>262</v>
       </c>
       <c r="P53" s="17">
-        <v>272.16000000000003</v>
+        <v>212.22000000000003</v>
       </c>
       <c r="Q53" s="14">
-        <v>8.3714609286523203</v>
+        <v>6.5277463193657974</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-266.04545454545462</v>
+        <v>-340.04545454545462</v>
       </c>
       <c r="T53" s="18">
-        <v>720</v>
+        <v>622</v>
       </c>
       <c r="U53" s="17">
-        <v>583.20000000000005</v>
+        <v>503.82000000000005</v>
       </c>
       <c r="V53" s="14">
-        <v>9.5941853422168375</v>
+        <v>8.2883101150817691</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-405.68181818181824</v>
+        <v>-503.68181818181824</v>
       </c>
       <c r="Y53" s="18">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="Z53" s="17">
-        <v>68.040000000000006</v>
+        <v>42.93</v>
       </c>
       <c r="AA53" s="14">
-        <v>16.8</v>
+        <v>7.2272727272727284</v>
       </c>
       <c r="AB53" s="16">
-        <v>110</v>
+        <v>161.33333333333331</v>
       </c>
       <c r="AC53" s="15">
-        <v>9</v>
+        <v>-56.999999999999986</v>
       </c>
       <c r="AD53" s="19">
-        <v>6915</v>
+        <v>6691</v>
       </c>
       <c r="AE53" s="20">
-        <v>5601.1500000000005</v>
+        <v>5419.71</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6876,85 +6876,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1985</v>
+        <v>1926</v>
       </c>
       <c r="F54" s="14">
-        <v>1607.8500000000001</v>
+        <v>1560.0600000000002</v>
       </c>
       <c r="G54" s="14">
-        <v>12.687391051714119</v>
+        <v>12.3102847181871</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>420.45454545454527</v>
+        <v>361.45454545454527</v>
       </c>
       <c r="J54" s="16">
-        <v>6136</v>
+        <v>5992</v>
       </c>
       <c r="K54" s="13">
-        <v>4970.1600000000008</v>
+        <v>4853.5200000000004</v>
       </c>
       <c r="L54" s="14">
-        <v>77.315005727376871</v>
+        <v>75.500572737686142</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>5342.363636363636</v>
+        <v>5198.363636363636</v>
       </c>
       <c r="O54" s="16">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="P54" s="17">
-        <v>217.89000000000001</v>
+        <v>268.92</v>
       </c>
       <c r="Q54" s="14">
-        <v>17.304093567251464</v>
+        <v>21.35672514619883</v>
       </c>
       <c r="R54" s="16">
         <v>342</v>
       </c>
       <c r="S54" s="15">
-        <v>35.818181818181813</v>
+        <v>98.818181818181813</v>
       </c>
       <c r="T54" s="18">
-        <v>807</v>
+        <v>761</v>
       </c>
       <c r="U54" s="17">
-        <v>653.67000000000007</v>
+        <v>616.41000000000008</v>
       </c>
       <c r="V54" s="14">
-        <v>28.728155339805827</v>
+        <v>27.090614886731391</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>385.63636363636363</v>
+        <v>339.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="Z54" s="17">
-        <v>152.28</v>
+        <v>136.89000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>19.64179104477612</v>
+        <v>19.012499999999999</v>
       </c>
       <c r="AB54" s="16">
-        <v>210.57142857142856</v>
+        <v>195.55555555555557</v>
       </c>
       <c r="AC54" s="15">
-        <v>44.428571428571445</v>
+        <v>35.666666666666657</v>
       </c>
       <c r="AD54" s="19">
-        <v>9385</v>
+        <v>9180</v>
       </c>
       <c r="AE54" s="20">
-        <v>7601.85</v>
+        <v>7435.8</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6989,85 +6989,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>5048</v>
+        <v>4213</v>
       </c>
       <c r="F55" s="14">
-        <v>4088.88</v>
+        <v>3412.53</v>
       </c>
       <c r="G55" s="14">
-        <v>40.76945668135096</v>
+        <v>34.025697503671076</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>3809.818181818182</v>
+        <v>2974.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>8007</v>
+        <v>9177</v>
       </c>
       <c r="K55" s="13">
-        <v>6485.67</v>
+        <v>7433.3700000000008</v>
       </c>
       <c r="L55" s="14">
-        <v>90.104347826086951</v>
+        <v>103.2705882352941</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>7118.363636363636</v>
+        <v>8288.363636363636</v>
       </c>
       <c r="O55" s="16">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="P55" s="17">
-        <v>246.24</v>
+        <v>239.76000000000002</v>
       </c>
       <c r="Q55" s="14">
-        <v>14.862222222222224</v>
+        <v>14.471111111111112</v>
       </c>
       <c r="R55" s="16">
         <v>449.99999999999994</v>
       </c>
       <c r="S55" s="15">
-        <v>-2.818181818181813</v>
+        <v>-10.818181818181813</v>
       </c>
       <c r="T55" s="18">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="U55" s="17">
-        <v>353.97</v>
+        <v>324.81</v>
       </c>
       <c r="V55" s="14">
-        <v>13.559943582510579</v>
+        <v>12.442877291960508</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>-46.409090909090878</v>
+        <v>-82.409090909090878</v>
       </c>
       <c r="Y55" s="18">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="Z55" s="17">
-        <v>161.19</v>
+        <v>148.23000000000002</v>
       </c>
       <c r="AA55" s="14">
-        <v>20.791044776119403</v>
+        <v>19.843373493975907</v>
       </c>
       <c r="AB55" s="16">
-        <v>210.57142857142856</v>
+        <v>202.88888888888886</v>
       </c>
       <c r="AC55" s="15">
-        <v>55.428571428571445</v>
+        <v>44.666666666666686</v>
       </c>
       <c r="AD55" s="19">
-        <v>13995</v>
+        <v>14270</v>
       </c>
       <c r="AE55" s="20">
-        <v>11335.95</v>
+        <v>11558.7</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7102,85 +7102,85 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="F56" s="14">
-        <v>314.40000000000003</v>
+        <v>550.20000000000005</v>
       </c>
       <c r="G56" s="14">
-        <v>5.2905811623246493</v>
+        <v>9.2585170340681362</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>-106.81818181818184</v>
+        <v>-16.818181818181841</v>
       </c>
       <c r="J56" s="32">
-        <v>455</v>
+        <v>703</v>
       </c>
       <c r="K56" s="13">
-        <v>1192.1000000000001</v>
+        <v>1841.8600000000001</v>
       </c>
       <c r="L56" s="14">
-        <v>22.49438202247191</v>
+        <v>34.755056179775281</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>252.72727272727275</v>
+        <v>500.72727272727275</v>
       </c>
       <c r="O56" s="32">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P56" s="17">
-        <v>57.64</v>
+        <v>73.36</v>
       </c>
       <c r="Q56" s="14">
-        <v>16.133333333333333</v>
+        <v>20.533333333333335</v>
       </c>
       <c r="R56" s="16">
         <v>30</v>
       </c>
       <c r="S56" s="15">
-        <v>1.5454545454545467</v>
+        <v>7.5454545454545467</v>
       </c>
       <c r="T56" s="18">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="U56" s="17">
-        <v>196.5</v>
+        <v>280.34000000000003</v>
       </c>
       <c r="V56" s="14">
-        <v>8.7765957446808507</v>
+        <v>12.521276595744682</v>
       </c>
       <c r="W56" s="16">
         <v>188</v>
       </c>
       <c r="X56" s="15">
-        <v>-53.181818181818187</v>
+        <v>-21.181818181818187</v>
       </c>
       <c r="Y56" s="18">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="Z56" s="17">
-        <v>167.68</v>
+        <v>151.96</v>
       </c>
       <c r="AA56" s="14">
-        <v>37.333333333333329</v>
+        <v>29</v>
       </c>
       <c r="AB56" s="16">
-        <v>37.714285714285715</v>
+        <v>44</v>
       </c>
       <c r="AC56" s="15">
-        <v>38.285714285714285</v>
+        <v>28</v>
       </c>
       <c r="AD56" s="19">
-        <v>736</v>
+        <v>1106</v>
       </c>
       <c r="AE56" s="20">
-        <v>1928.3200000000002</v>
+        <v>2897.7200000000003</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7215,34 +7215,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>8</v>
+        <v>153</v>
       </c>
       <c r="F57" s="14">
-        <v>20.96</v>
+        <v>400.86</v>
       </c>
       <c r="G57" s="14">
-        <v>0.19361936193619361</v>
+        <v>3.7029702970297027</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-405.18181818181819</v>
+        <v>-260.18181818181819</v>
       </c>
       <c r="J57" s="32">
-        <v>149</v>
+        <v>311</v>
       </c>
       <c r="K57" s="13">
-        <v>390.38</v>
+        <v>814.82</v>
       </c>
       <c r="L57" s="14">
-        <v>3.8116279069767445</v>
+        <v>7.9558139534883727</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>-241.90909090909088</v>
+        <v>-79.909090909090878</v>
       </c>
       <c r="O57" s="32">
         <v>53</v>
@@ -7260,40 +7260,40 @@
         <v>5.9545454545454533</v>
       </c>
       <c r="T57" s="18">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="U57" s="17">
-        <v>510.90000000000003</v>
+        <v>448.02000000000004</v>
       </c>
       <c r="V57" s="14">
-        <v>13.883495145631068</v>
+        <v>12.174757281553399</v>
       </c>
       <c r="W57" s="16">
         <v>309</v>
       </c>
       <c r="X57" s="15">
-        <v>-15.681818181818187</v>
+        <v>-39.681818181818187</v>
       </c>
       <c r="Y57" s="18">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="Z57" s="17">
-        <v>209.60000000000002</v>
+        <v>178.16</v>
       </c>
       <c r="AA57" s="14">
-        <v>46.666666666666664</v>
+        <v>25.5</v>
       </c>
       <c r="AB57" s="16">
-        <v>37.714285714285715</v>
+        <v>58.666666666666664</v>
       </c>
       <c r="AC57" s="15">
-        <v>54.285714285714285</v>
+        <v>28</v>
       </c>
       <c r="AD57" s="19">
-        <v>485</v>
+        <v>756</v>
       </c>
       <c r="AE57" s="20">
-        <v>1270.7</v>
+        <v>1980.72</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7328,34 +7328,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F58" s="14">
-        <v>385.14000000000004</v>
+        <v>369.42</v>
       </c>
       <c r="G58" s="14">
-        <v>7.6635071090047386</v>
+        <v>7.3507109004739331</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>-44.818181818181841</v>
+        <v>-50.818181818181841</v>
       </c>
       <c r="J58" s="32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K58" s="13">
-        <v>31.44</v>
+        <v>20.96</v>
       </c>
       <c r="L58" s="14">
-        <v>0.64864864864864868</v>
+        <v>0.43243243243243246</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>-173</v>
+        <v>-177</v>
       </c>
       <c r="O58" s="32">
         <v>45</v>
@@ -7373,40 +7373,40 @@
         <v>14.31818181818182</v>
       </c>
       <c r="T58" s="18">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="U58" s="17">
-        <v>175.54000000000002</v>
+        <v>112.66000000000001</v>
       </c>
       <c r="V58" s="14">
-        <v>13.279279279279278</v>
+        <v>8.5225225225225216</v>
       </c>
       <c r="W58" s="16">
         <v>111</v>
       </c>
       <c r="X58" s="15">
-        <v>-8.681818181818187</v>
+        <v>-32.681818181818187</v>
       </c>
       <c r="Y58" s="18">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="Z58" s="17">
-        <v>141.48000000000002</v>
+        <v>125.76</v>
       </c>
       <c r="AA58" s="14">
-        <v>18</v>
+        <v>20.571428571428569</v>
       </c>
       <c r="AB58" s="16">
-        <v>66</v>
+        <v>51.333333333333336</v>
       </c>
       <c r="AC58" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AD58" s="19">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="AE58" s="20">
-        <v>851.5</v>
+        <v>746.7</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7444,34 +7444,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F59" s="14">
-        <v>57.64</v>
+        <v>141.48000000000002</v>
       </c>
       <c r="G59" s="14">
-        <v>0.95088408644400779</v>
+        <v>2.3339882121807465</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-209.36363636363637</v>
+        <v>-177.36363636363637</v>
       </c>
       <c r="J59" s="32">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="K59" s="13">
-        <v>227.94</v>
+        <v>13.100000000000001</v>
       </c>
       <c r="L59" s="14">
-        <v>4.7376237623762378</v>
+        <v>0.2722772277227723</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>-96.636363636363626</v>
+        <v>-178.63636363636363</v>
       </c>
       <c r="O59" s="32">
         <v>14</v>
@@ -7489,19 +7489,19 @@
         <v>-3.7272727272727266</v>
       </c>
       <c r="T59" s="18">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="U59" s="17">
-        <v>322.26</v>
+        <v>306.54000000000002</v>
       </c>
       <c r="V59" s="14">
-        <v>13.876923076923074</v>
+        <v>13.199999999999998</v>
       </c>
       <c r="W59" s="16">
         <v>195.00000000000003</v>
       </c>
       <c r="X59" s="15">
-        <v>-9.9545454545454675</v>
+        <v>-15.954545454545467</v>
       </c>
       <c r="Y59" s="18">
         <v>56</v>
@@ -7510,19 +7510,19 @@
         <v>146.72</v>
       </c>
       <c r="AA59" s="14">
-        <v>32.666666666666664</v>
+        <v>42</v>
       </c>
       <c r="AB59" s="16">
-        <v>37.714285714285715</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AC59" s="15">
-        <v>30.285714285714285</v>
+        <v>36</v>
       </c>
       <c r="AD59" s="19">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="AE59" s="20">
-        <v>791.24</v>
+        <v>644.52</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7596,10 +7596,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7629,17 +7629,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>119111.75999999997</v>
+        <v>122597.34999999999</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>28.588151863414243</v>
+        <v>29.545092617914708</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7677,11 +7677,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>194005.48000000004</v>
+        <v>209920.82999999993</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>46.563480588101271</v>
+        <v>50.589432518561992</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7719,11 +7719,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>24037.210000000006</v>
+        <v>21108.940000000002</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.7691986908159185</v>
+        <v>5.0871049608005761</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7761,11 +7761,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>60211.55</v>
+        <v>44404.19000000001</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>14.451444049954098</v>
+        <v>10.701095139278967</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7803,11 +7803,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>19148.489999999998</v>
+        <v>16785.849999999999</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>4.5958513254700391</v>
+        <v>4.0452709044724333</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7839,19 +7839,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>416647.29000000004</v>
-      </c>
-      <c r="E67" s="66">
+        <v>414949.9599999999</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
-        <v>99.999999999999986</v>
-      </c>
-      <c r="F67" s="66"/>
+        <v>100</v>
+      </c>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7951,17 +7951,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>94843</v>
+        <v>96518</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>30.346943803615023</v>
+        <v>31.477640367355459</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -7998,11 +7998,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>147189</v>
+        <v>154780</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>47.096109481040159</v>
+        <v>50.478762262575664</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8040,11 +8040,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>17778</v>
+        <v>15642</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.688432113499867</v>
+        <v>5.1013619286161553</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8082,11 +8082,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>40004</v>
+        <v>28442</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>12.800092151448345</v>
+        <v>9.2758557712377367</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8124,11 +8124,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>12715</v>
+        <v>11242</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>4.0684224503966036</v>
+        <v>3.6663796702149862</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8160,19 +8160,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>312529</v>
-      </c>
-      <c r="E75" s="66">
+        <v>306624</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8719,6 +8719,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8727,17 +8738,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE62BAC-E3F7-414B-85C2-8C155BBE24BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94AD47-DC7F-466E-8226-5613E204499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,6 +805,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,12 +819,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1638,242 +1638,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2304,13 +2304,13 @@
         <v>471.92</v>
       </c>
       <c r="AA13" s="14">
-        <v>13.88</v>
+        <v>9.7593750000000004</v>
       </c>
       <c r="AB13" s="16">
-        <v>550</v>
+        <v>782.22222222222229</v>
       </c>
       <c r="AC13" s="15">
-        <v>-28</v>
+        <v>-186.33333333333337</v>
       </c>
       <c r="AD13" s="19">
         <v>8795</v>
@@ -2418,13 +2418,13 @@
         <v>131.97</v>
       </c>
       <c r="AA14" s="14">
-        <v>53.357142857142854</v>
+        <v>24.899999999999995</v>
       </c>
       <c r="AB14" s="16">
-        <v>34.222222222222221</v>
+        <v>73.333333333333343</v>
       </c>
       <c r="AC14" s="15">
-        <v>59.666666666666671</v>
+        <v>32.999999999999993</v>
       </c>
       <c r="AD14" s="19">
         <v>318</v>
@@ -2532,13 +2532,13 @@
         <v>452.68999999999994</v>
       </c>
       <c r="AA15" s="14">
-        <v>42.702127659574465</v>
+        <v>36.490909090909092</v>
       </c>
       <c r="AB15" s="16">
-        <v>114.88888888888889</v>
+        <v>134.44444444444443</v>
       </c>
       <c r="AC15" s="15">
-        <v>144.66666666666669</v>
+        <v>131.33333333333334</v>
       </c>
       <c r="AD15" s="19">
         <v>3597</v>
@@ -2645,13 +2645,13 @@
         <v>249.09</v>
       </c>
       <c r="AA16" s="14">
-        <v>47.769230769230766</v>
+        <v>25.875</v>
       </c>
       <c r="AB16" s="16">
-        <v>31.777777777777779</v>
+        <v>58.666666666666664</v>
       </c>
       <c r="AC16" s="15">
-        <v>47.333333333333329</v>
+        <v>29</v>
       </c>
       <c r="AD16" s="19">
         <v>875</v>
@@ -2871,13 +2871,13 @@
         <v>195.93</v>
       </c>
       <c r="AA18" s="14">
-        <v>28.561224489795919</v>
+        <v>24.129310344827587</v>
       </c>
       <c r="AB18" s="16">
-        <v>239.55555555555557</v>
+        <v>283.55555555555554</v>
       </c>
       <c r="AC18" s="15">
-        <v>147.66666666666666</v>
+        <v>117.66666666666669</v>
       </c>
       <c r="AD18" s="19">
         <v>12660</v>
@@ -2984,13 +2984,13 @@
         <v>129.15</v>
       </c>
       <c r="AA19" s="14">
-        <v>18.088235294117645</v>
+        <v>14.879032258064516</v>
       </c>
       <c r="AB19" s="16">
-        <v>249.33333333333334</v>
+        <v>303.11111111111114</v>
       </c>
       <c r="AC19" s="15">
-        <v>35</v>
+        <v>-1.6666666666666856</v>
       </c>
       <c r="AD19" s="19">
         <v>2601</v>
@@ -3097,13 +3097,13 @@
         <v>196.56</v>
       </c>
       <c r="AA20" s="14">
-        <v>26.490566037735846</v>
+        <v>21.6</v>
       </c>
       <c r="AB20" s="16">
-        <v>259.11111111111114</v>
+        <v>317.77777777777777</v>
       </c>
       <c r="AC20" s="15">
-        <v>135.33333333333331</v>
+        <v>95.333333333333343</v>
       </c>
       <c r="AD20" s="19">
         <v>3847</v>
@@ -3210,13 +3210,13 @@
         <v>380.41</v>
       </c>
       <c r="AA21" s="14">
-        <v>17.547486033519554</v>
+        <v>14.085201793721975</v>
       </c>
       <c r="AB21" s="16">
-        <v>437.55555555555554</v>
+        <v>545.11111111111109</v>
       </c>
       <c r="AC21" s="15">
-        <v>50.666666666666686</v>
+        <v>-22.666666666666629</v>
       </c>
       <c r="AD21" s="19">
         <v>8589</v>
@@ -3326,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="AB22" s="16">
-        <v>41.555555555555557</v>
+        <v>124.66666666666667</v>
       </c>
       <c r="AC22" s="15">
-        <v>160.66666666666666</v>
+        <v>104</v>
       </c>
       <c r="AD22" s="19">
         <v>6494</v>
@@ -3436,13 +3436,13 @@
         <v>450.08</v>
       </c>
       <c r="AA23" s="14">
-        <v>6.5149253731343286</v>
+        <v>5.6504854368932032</v>
       </c>
       <c r="AB23" s="16">
-        <v>1310.2222222222222</v>
+        <v>1510.6666666666667</v>
       </c>
       <c r="AC23" s="15">
-        <v>-505.33333333333326</v>
+        <v>-642</v>
       </c>
       <c r="AD23" s="19">
         <v>37781</v>
@@ -3549,13 +3549,13 @@
         <v>694.83999999999992</v>
       </c>
       <c r="AA24" s="14">
-        <v>15.717201166180757</v>
+        <v>13.377171215880892</v>
       </c>
       <c r="AB24" s="16">
-        <v>838.44444444444457</v>
+        <v>985.11111111111109</v>
       </c>
       <c r="AC24" s="15">
-        <v>27.333333333333258</v>
+        <v>-72.666666666666629</v>
       </c>
       <c r="AD24" s="19">
         <v>22537</v>
@@ -3662,13 +3662,13 @@
         <v>845.64</v>
       </c>
       <c r="AA25" s="14">
-        <v>27.337499999999995</v>
+        <v>21.725165562913908</v>
       </c>
       <c r="AB25" s="16">
-        <v>586.66666666666674</v>
+        <v>738.22222222222229</v>
       </c>
       <c r="AC25" s="15">
-        <v>328.99999999999994</v>
+        <v>225.66666666666663</v>
       </c>
       <c r="AD25" s="19">
         <v>18544</v>
@@ -3775,13 +3775,13 @@
         <v>842.16</v>
       </c>
       <c r="AA26" s="14">
-        <v>16.840206185567009</v>
+        <v>13.669456066945607</v>
       </c>
       <c r="AB26" s="16">
-        <v>948.44444444444457</v>
+        <v>1168.4444444444446</v>
       </c>
       <c r="AC26" s="15">
-        <v>79.333333333333258</v>
+        <v>-70.666666666666742</v>
       </c>
       <c r="AD26" s="19">
         <v>30845</v>
@@ -3888,13 +3888,13 @@
         <v>577.67999999999995</v>
       </c>
       <c r="AA27" s="14">
-        <v>42.283018867924525</v>
+        <v>37.041322314049587</v>
       </c>
       <c r="AB27" s="16">
-        <v>259.11111111111114</v>
+        <v>295.77777777777777</v>
       </c>
       <c r="AC27" s="15">
-        <v>321.33333333333331</v>
+        <v>296.33333333333337</v>
       </c>
       <c r="AD27" s="19">
         <v>5077</v>
@@ -4001,13 +4001,13 @@
         <v>523.16</v>
       </c>
       <c r="AA28" s="14">
-        <v>27.06</v>
+        <v>22.180327868852459</v>
       </c>
       <c r="AB28" s="16">
-        <v>366.66666666666669</v>
+        <v>447.33333333333331</v>
       </c>
       <c r="AC28" s="15">
-        <v>200.99999999999997</v>
+        <v>146</v>
       </c>
       <c r="AD28" s="19">
         <v>3198</v>
@@ -4114,13 +4114,13 @@
         <v>499.96</v>
       </c>
       <c r="AA29" s="14">
-        <v>22.039772727272727</v>
+        <v>20.308900523560212</v>
       </c>
       <c r="AB29" s="16">
-        <v>430.22222222222229</v>
+        <v>466.88888888888886</v>
       </c>
       <c r="AC29" s="15">
-        <v>137.66666666666663</v>
+        <v>112.66666666666669</v>
       </c>
       <c r="AD29" s="19">
         <v>4580</v>
@@ -4227,13 +4227,13 @@
         <v>195.04000000000002</v>
       </c>
       <c r="AA30" s="14">
-        <v>11.924999999999999</v>
+        <v>9.7346938775510203</v>
       </c>
       <c r="AB30" s="16">
-        <v>97.777777777777786</v>
+        <v>119.77777777777779</v>
       </c>
       <c r="AC30" s="15">
-        <v>-13.666666666666671</v>
+        <v>-28.666666666666671</v>
       </c>
       <c r="AD30" s="19">
         <v>2142</v>
@@ -4340,13 +4340,13 @@
         <v>217.12</v>
       </c>
       <c r="AA31" s="14">
-        <v>44.25</v>
+        <v>29.5</v>
       </c>
       <c r="AB31" s="16">
-        <v>29.333333333333332</v>
+        <v>44</v>
       </c>
       <c r="AC31" s="15">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="AD31" s="19">
         <v>1381</v>
@@ -4453,13 +4453,13 @@
         <v>1257.45</v>
       </c>
       <c r="AA32" s="14">
-        <v>66.512195121951223</v>
+        <v>53.470588235294116</v>
       </c>
       <c r="AB32" s="16">
-        <v>100.22222222222221</v>
+        <v>124.66666666666667</v>
       </c>
       <c r="AC32" s="15">
-        <v>234.66666666666669</v>
+        <v>218</v>
       </c>
       <c r="AD32" s="19">
         <v>3815</v>
@@ -4566,13 +4566,13 @@
         <v>597.6</v>
       </c>
       <c r="AA33" s="14">
-        <v>11.571428571428571</v>
+        <v>10.204724409448819</v>
       </c>
       <c r="AB33" s="16">
-        <v>273.77777777777777</v>
+        <v>310.44444444444446</v>
       </c>
       <c r="AC33" s="15">
-        <v>-42.666666666666657</v>
+        <v>-67.666666666666686</v>
       </c>
       <c r="AD33" s="19">
         <v>6465</v>
@@ -4792,13 +4792,13 @@
         <v>650.37</v>
       </c>
       <c r="AA35" s="14">
-        <v>41.275862068965523</v>
+        <v>26.40441176470588</v>
       </c>
       <c r="AB35" s="16">
-        <v>212.66666666666666</v>
+        <v>332.44444444444446</v>
       </c>
       <c r="AC35" s="15">
-        <v>254</v>
+        <v>172.33333333333331</v>
       </c>
       <c r="AD35" s="19">
         <v>8275</v>
@@ -4905,13 +4905,13 @@
         <v>735.13</v>
       </c>
       <c r="AA36" s="14">
-        <v>18.967289719626169</v>
+        <v>15.611538461538462</v>
       </c>
       <c r="AB36" s="16">
-        <v>523.11111111111109</v>
+        <v>635.55555555555554</v>
       </c>
       <c r="AC36" s="15">
-        <v>94.333333333333371</v>
+        <v>17.666666666666686</v>
       </c>
       <c r="AD36" s="19">
         <v>7674</v>
@@ -5021,10 +5021,10 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>344.66666666666663</v>
+        <v>498.66666666666669</v>
       </c>
       <c r="AC37" s="15">
-        <v>-129.99999999999997</v>
+        <v>-235</v>
       </c>
       <c r="AD37" s="19">
         <v>2949</v>
@@ -5131,13 +5131,13 @@
         <v>577.02</v>
       </c>
       <c r="AA38" s="14">
-        <v>12.543307086614172</v>
+        <v>11.378571428571428</v>
       </c>
       <c r="AB38" s="16">
-        <v>620.88888888888891</v>
+        <v>684.44444444444446</v>
       </c>
       <c r="AC38" s="15">
-        <v>-69.333333333333371</v>
+        <v>-112.66666666666669</v>
       </c>
       <c r="AD38" s="19">
         <v>3715</v>
@@ -5244,13 +5244,13 @@
         <v>790.55</v>
       </c>
       <c r="AA39" s="14">
-        <v>114.86842105263158</v>
+        <v>92.872340425531917</v>
       </c>
       <c r="AB39" s="16">
-        <v>92.888888888888886</v>
+        <v>114.88888888888889</v>
       </c>
       <c r="AC39" s="15">
-        <v>421.66666666666669</v>
+        <v>406.66666666666669</v>
       </c>
       <c r="AD39" s="19">
         <v>7803</v>
@@ -5357,13 +5357,13 @@
         <v>795.43999999999994</v>
       </c>
       <c r="AA40" s="14">
-        <v>102.13953488372093</v>
+        <v>89.632653061224488</v>
       </c>
       <c r="AB40" s="16">
-        <v>105.11111111111111</v>
+        <v>119.77777777777779</v>
       </c>
       <c r="AC40" s="15">
-        <v>416.33333333333331</v>
+        <v>406.33333333333331</v>
       </c>
       <c r="AD40" s="19">
         <v>7958</v>
@@ -5473,10 +5473,10 @@
         <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>97.777777777777786</v>
+        <v>119.77777777777779</v>
       </c>
       <c r="AC41" s="15">
-        <v>-24.666666666666671</v>
+        <v>-39.666666666666671</v>
       </c>
       <c r="AD41" s="19">
         <v>748</v>
@@ -5583,13 +5583,13 @@
         <v>590.40000000000009</v>
       </c>
       <c r="AA42" s="14">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="AB42" s="16">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="AC42" s="15">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AD42" s="19">
         <v>860</v>
@@ -5696,13 +5696,13 @@
         <v>364.23999999999995</v>
       </c>
       <c r="AA43" s="14">
-        <v>10.911196911196912</v>
+        <v>9.2052117263843645</v>
       </c>
       <c r="AB43" s="16">
-        <v>633.11111111111109</v>
+        <v>750.44444444444457</v>
       </c>
       <c r="AC43" s="15">
-        <v>-117.66666666666663</v>
+        <v>-197.66666666666674</v>
       </c>
       <c r="AD43" s="19">
         <v>7764</v>
@@ -5809,13 +5809,13 @@
         <v>502.28</v>
       </c>
       <c r="AA44" s="14">
-        <v>17.243362831858409</v>
+        <v>14.274725274725277</v>
       </c>
       <c r="AB44" s="16">
-        <v>552.44444444444446</v>
+        <v>667.33333333333326</v>
       </c>
       <c r="AC44" s="15">
-        <v>56.333333333333314</v>
+        <v>-21.999999999999943</v>
       </c>
       <c r="AD44" s="19">
         <v>6415</v>
@@ -5922,13 +5922,13 @@
         <v>390.91999999999996</v>
       </c>
       <c r="AA45" s="14">
-        <v>12.083665338645417</v>
+        <v>9.65923566878981</v>
       </c>
       <c r="AB45" s="16">
-        <v>613.55555555555554</v>
+        <v>767.55555555555543</v>
       </c>
       <c r="AC45" s="15">
-        <v>-81.333333333333314</v>
+        <v>-186.33333333333326</v>
       </c>
       <c r="AD45" s="19">
         <v>10230</v>
@@ -6035,13 +6035,13 @@
         <v>301.59999999999997</v>
       </c>
       <c r="AA46" s="14">
-        <v>12.857142857142858</v>
+        <v>8.7313432835820901</v>
       </c>
       <c r="AB46" s="16">
-        <v>444.88888888888886</v>
+        <v>655.11111111111109</v>
       </c>
       <c r="AC46" s="15">
-        <v>-43.333333333333314</v>
+        <v>-186.66666666666663</v>
       </c>
       <c r="AD46" s="19">
         <v>8898</v>
@@ -6370,13 +6370,13 @@
         <v>87</v>
       </c>
       <c r="AA49" s="14">
-        <v>16.071428571428569</v>
+        <v>14.0625</v>
       </c>
       <c r="AB49" s="16">
-        <v>102.66666666666667</v>
+        <v>117.33333333333333</v>
       </c>
       <c r="AC49" s="15">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AD49" s="19">
         <v>1342</v>
@@ -6483,13 +6483,13 @@
         <v>154.28</v>
       </c>
       <c r="AA50" s="14">
-        <v>10.881818181818183</v>
+        <v>9.5760000000000005</v>
       </c>
       <c r="AB50" s="16">
-        <v>268.88888888888886</v>
+        <v>305.55555555555554</v>
       </c>
       <c r="AC50" s="15">
-        <v>-50.333333333333314</v>
+        <v>-75.333333333333314</v>
       </c>
       <c r="AD50" s="19">
         <v>4121</v>
@@ -6602,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="AB51" s="16">
-        <v>90.444444444444429</v>
+        <v>105.11111111111111</v>
       </c>
       <c r="AC51" s="15">
-        <v>61.333333333333343</v>
+        <v>51.333333333333329</v>
       </c>
       <c r="AD51" s="19">
         <v>4573</v>
@@ -6829,13 +6829,13 @@
         <v>42.93</v>
       </c>
       <c r="AA53" s="14">
-        <v>7.2272727272727284</v>
+        <v>5.6785714285714279</v>
       </c>
       <c r="AB53" s="16">
-        <v>161.33333333333331</v>
+        <v>205.33333333333334</v>
       </c>
       <c r="AC53" s="15">
-        <v>-56.999999999999986</v>
+        <v>-87</v>
       </c>
       <c r="AD53" s="19">
         <v>6691</v>
@@ -6942,13 +6942,13 @@
         <v>136.89000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>19.012499999999999</v>
+        <v>15.84375</v>
       </c>
       <c r="AB54" s="16">
-        <v>195.55555555555557</v>
+        <v>234.66666666666666</v>
       </c>
       <c r="AC54" s="15">
-        <v>35.666666666666657</v>
+        <v>9</v>
       </c>
       <c r="AD54" s="19">
         <v>9180</v>
@@ -7055,13 +7055,13 @@
         <v>148.23000000000002</v>
       </c>
       <c r="AA55" s="14">
-        <v>19.843373493975907</v>
+        <v>17.15625</v>
       </c>
       <c r="AB55" s="16">
-        <v>202.88888888888886</v>
+        <v>234.66666666666666</v>
       </c>
       <c r="AC55" s="15">
-        <v>44.666666666666686</v>
+        <v>23</v>
       </c>
       <c r="AD55" s="19">
         <v>14270</v>
@@ -7596,10 +7596,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7629,10 +7629,10 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
         <v>122597.34999999999</v>
@@ -7839,19 +7839,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
         <v>414949.9599999999</v>
       </c>
-      <c r="E67" s="69">
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7951,10 +7951,10 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
         <v>96518</v>
@@ -8160,19 +8160,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
         <v>306624</v>
       </c>
-      <c r="E75" s="69">
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8719,17 +8719,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8738,6 +8727,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">
@@ -8824,6 +8824,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94AD47-DC7F-466E-8226-5613E204499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF88D668-CE05-4530-A442-889CF7D43554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -805,12 +805,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -819,6 +813,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1178,6 +1178,8 @@
       <sheetName val="INVENTARIO NACIONAL 10-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1311,6 +1313,8 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1638,242 +1642,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -7596,10 +7600,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7629,10 +7633,10 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
         <v>122597.34999999999</v>
@@ -7839,19 +7843,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
         <v>414949.9599999999</v>
       </c>
-      <c r="E67" s="66">
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7951,10 +7955,10 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
         <v>96518</v>
@@ -8160,19 +8164,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
         <v>306624</v>
       </c>
-      <c r="E75" s="66">
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8719,6 +8723,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8727,17 +8742,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF88D668-CE05-4530-A442-889CF7D43554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7DB67-4F53-4813-B8A3-42115672C7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Sistema Integral de Control de Inventarios</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>Griego Mykonos 700g</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Cremigurt Power Natural 150g</t>
@@ -805,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1180,6 +1177,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1315,6 +1313,7 @@
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1642,242 +1641,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2242,85 +2241,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>4593</v>
+        <v>3205</v>
       </c>
       <c r="F13" s="14">
-        <v>6246.4800000000005</v>
+        <v>4358.8</v>
       </c>
       <c r="G13" s="14">
-        <v>5.8943008808259929</v>
+        <v>4.1130490579245169</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-3199.2727272727279</v>
+        <v>-4587.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>3020</v>
+        <v>3188</v>
       </c>
       <c r="K13" s="13">
-        <v>4107.2000000000007</v>
+        <v>4335.68</v>
       </c>
       <c r="L13" s="14">
-        <v>12.404779686333084</v>
+        <v>13.094846900672144</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>585.4545454545455</v>
+        <v>753.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="P13" s="17">
-        <v>291.04000000000002</v>
+        <v>334.56</v>
       </c>
       <c r="Q13" s="14">
-        <v>5.4680603948896636</v>
+        <v>6.2857142857142865</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>-373.0454545454545</v>
+        <v>-536.72727272727263</v>
       </c>
       <c r="T13" s="18">
-        <v>621</v>
+        <v>830</v>
       </c>
       <c r="U13" s="17">
-        <v>844.56000000000006</v>
+        <v>1128.8000000000002</v>
       </c>
       <c r="V13" s="14">
-        <v>11.442211055276381</v>
+        <v>15.293132328308207</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>-193.09090909090912</v>
+        <v>15.909090909090878</v>
       </c>
       <c r="Y13" s="18">
-        <v>347</v>
+        <v>235</v>
       </c>
       <c r="Z13" s="17">
-        <v>471.92</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="AA13" s="14">
-        <v>9.7593750000000004</v>
+        <v>8.2941176470588243</v>
       </c>
       <c r="AB13" s="16">
-        <v>782.22222222222229</v>
+        <v>623.33333333333326</v>
       </c>
       <c r="AC13" s="15">
-        <v>-186.33333333333337</v>
+        <v>-189.99999999999994</v>
       </c>
       <c r="AD13" s="19">
-        <v>8795</v>
+        <v>7704</v>
       </c>
       <c r="AE13" s="20">
-        <v>11961.2</v>
+        <v>10477.44</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2356,19 +2355,19 @@
         <v>1.59</v>
       </c>
       <c r="E14" s="13">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>98.58</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
-        <v>1.7900262467191603</v>
+        <v>0</v>
       </c>
       <c r="H14" s="30">
         <v>762</v>
       </c>
       <c r="I14" s="15">
-        <v>-284.36363636363632</v>
+        <v>-346.36363636363632</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2386,55 +2385,55 @@
         <v>-260.90909090909088</v>
       </c>
       <c r="O14" s="16">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="P14" s="17">
-        <v>244.86</v>
+        <v>186.03</v>
       </c>
       <c r="Q14" s="14">
-        <v>19.929411764705883</v>
+        <v>15.141176470588235</v>
       </c>
       <c r="R14" s="16">
         <v>170</v>
       </c>
       <c r="S14" s="15">
-        <v>38.090909090909093</v>
+        <v>-37.545454545454561</v>
       </c>
       <c r="T14" s="18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="U14" s="17">
-        <v>30.21</v>
+        <v>25.44</v>
       </c>
       <c r="V14" s="14">
-        <v>7.4642857142857144</v>
+        <v>6.2857142857142856</v>
       </c>
       <c r="W14" s="16">
         <v>56</v>
       </c>
       <c r="X14" s="15">
-        <v>-19.18181818181818</v>
+        <v>-22.18181818181818</v>
       </c>
       <c r="Y14" s="18">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="Z14" s="17">
-        <v>131.97</v>
+        <v>106.53</v>
       </c>
       <c r="AA14" s="14">
-        <v>24.899999999999995</v>
+        <v>26.8</v>
       </c>
       <c r="AB14" s="16">
-        <v>73.333333333333343</v>
+        <v>55</v>
       </c>
       <c r="AC14" s="15">
-        <v>32.999999999999993</v>
+        <v>29.5</v>
       </c>
       <c r="AD14" s="19">
+        <v>200</v>
+      </c>
+      <c r="AE14" s="20">
         <v>318</v>
-      </c>
-      <c r="AE14" s="20">
-        <v>505.62</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2470,85 +2469,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>227</v>
+        <v>645</v>
       </c>
       <c r="F15" s="14">
-        <v>460.80999999999995</v>
+        <v>1309.3499999999999</v>
       </c>
       <c r="G15" s="14">
-        <v>0.72376811594202906</v>
+        <v>2.0565217391304347</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-2909.363636363636</v>
+        <v>-2491.363636363636</v>
       </c>
       <c r="J15" s="16">
-        <v>2935</v>
+        <v>2298</v>
       </c>
       <c r="K15" s="13">
-        <v>5958.0499999999993</v>
+        <v>4664.9399999999996</v>
       </c>
       <c r="L15" s="14">
-        <v>21.387876780390858</v>
+        <v>16.745942365021531</v>
       </c>
       <c r="M15" s="30">
         <v>3019</v>
       </c>
       <c r="N15" s="15">
-        <v>1562.7272727272727</v>
+        <v>925.72727272727275</v>
       </c>
       <c r="O15" s="16">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="P15" s="17">
-        <v>430.35999999999996</v>
+        <v>308.55999999999995</v>
       </c>
       <c r="Q15" s="14">
-        <v>15.703703703703704</v>
+        <v>11.25925925925926</v>
       </c>
       <c r="R15" s="16">
         <v>297</v>
       </c>
       <c r="S15" s="15">
-        <v>9.5</v>
+        <v>-118</v>
       </c>
       <c r="T15" s="18">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="U15" s="17">
-        <v>0</v>
+        <v>594.79</v>
       </c>
       <c r="V15" s="14">
-        <v>0</v>
+        <v>18.576368876080689</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>-236.59090909090912</v>
+        <v>56.409090909090878</v>
       </c>
       <c r="Y15" s="18">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="Z15" s="17">
-        <v>452.68999999999994</v>
+        <v>420.21</v>
       </c>
       <c r="AA15" s="14">
-        <v>36.490909090909092</v>
+        <v>35.485714285714295</v>
       </c>
       <c r="AB15" s="16">
-        <v>134.44444444444443</v>
+        <v>128.33333333333331</v>
       </c>
       <c r="AC15" s="15">
-        <v>131.33333333333334</v>
+        <v>119.50000000000001</v>
       </c>
       <c r="AD15" s="19">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="AE15" s="20">
-        <v>7301.9099999999989</v>
+        <v>7297.8499999999995</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2583,85 +2582,85 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="F16" s="14">
-        <v>1397.07</v>
+        <v>299.63</v>
       </c>
       <c r="G16" s="14">
-        <v>6.0944881889763778</v>
+        <v>1.3070866141732282</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-248</v>
+        <v>-552</v>
       </c>
       <c r="J16" s="16">
-        <v>379</v>
+        <v>104</v>
       </c>
       <c r="K16" s="13">
-        <v>1368.19</v>
+        <v>375.44</v>
       </c>
       <c r="L16" s="14">
-        <v>15.299082568807339</v>
+        <v>4.1981651376146791</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>131.27272727272725</v>
+        <v>-143.72727272727275</v>
       </c>
       <c r="O16" s="16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P16" s="17">
-        <v>57.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="14">
-        <v>7.6521739130434767</v>
+        <v>0</v>
       </c>
       <c r="R16" s="16">
         <v>46.000000000000007</v>
       </c>
       <c r="S16" s="15">
-        <v>-15.36363636363637</v>
+        <v>-41.818181818181827</v>
       </c>
       <c r="T16" s="18">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="U16" s="17">
-        <v>86.64</v>
+        <v>187.72</v>
       </c>
       <c r="V16" s="14">
-        <v>10.775510204081634</v>
+        <v>23.346938775510207</v>
       </c>
       <c r="W16" s="16">
         <v>49</v>
       </c>
       <c r="X16" s="15">
-        <v>-9.4090909090909065</v>
+        <v>18.590909090909093</v>
       </c>
       <c r="Y16" s="18">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="Z16" s="17">
-        <v>249.09</v>
+        <v>209.38</v>
       </c>
       <c r="AA16" s="14">
-        <v>25.875</v>
+        <v>29</v>
       </c>
       <c r="AB16" s="16">
-        <v>58.666666666666664</v>
+        <v>44</v>
       </c>
       <c r="AC16" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AD16" s="19">
-        <v>875</v>
+        <v>297</v>
       </c>
       <c r="AE16" s="20">
-        <v>3158.75</v>
+        <v>1072.17</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2696,34 +2695,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F17" s="14">
-        <v>316.08</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="G17" s="14">
-        <v>4.7425149700598803</v>
+        <v>0.52694610778443118</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-39.909090909090907</v>
+        <v>-71.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="K17" s="13">
-        <v>395.09999999999997</v>
+        <v>96.58</v>
       </c>
       <c r="L17" s="14">
-        <v>14.347826086956522</v>
+        <v>3.5072463768115942</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>13.636363636363637</v>
+        <v>-20.363636363636363</v>
       </c>
       <c r="O17" s="16">
         <v>13</v>
@@ -2738,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="S17" s="15">
-        <v>7.545454545454545</v>
+        <v>5.7272727272727266</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2762,19 +2761,19 @@
         <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AB17" s="16">
-        <v>14.666666666666666</v>
+        <v>11</v>
       </c>
       <c r="AC17" s="15">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" s="19">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="AE17" s="20">
-        <v>1071.1599999999999</v>
+        <v>491.67999999999995</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2809,85 +2808,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6210</v>
+        <v>6120</v>
       </c>
       <c r="F18" s="14">
-        <v>3912.3</v>
+        <v>3855.6</v>
       </c>
       <c r="G18" s="14">
-        <v>7.4839769926047657</v>
+        <v>7.3755135579293345</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>-2087.7272727272721</v>
+        <v>-2177.7272727272721</v>
       </c>
       <c r="J18" s="16">
-        <v>5125</v>
+        <v>9356</v>
       </c>
       <c r="K18" s="13">
-        <v>3228.75</v>
+        <v>5894.28</v>
       </c>
       <c r="L18" s="14">
-        <v>16.293352601156069</v>
+        <v>29.744508670520229</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>1979.5454545454545</v>
+        <v>6210.545454545454</v>
       </c>
       <c r="O18" s="16">
-        <v>760</v>
+        <v>630</v>
       </c>
       <c r="P18" s="17">
-        <v>478.8</v>
+        <v>396.9</v>
       </c>
       <c r="Q18" s="14">
-        <v>11.570934256055363</v>
+        <v>9.5916955017301024</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-225.22727272727275</v>
+        <v>-683.63636363636374</v>
       </c>
       <c r="T18" s="18">
-        <v>254</v>
+        <v>1451</v>
       </c>
       <c r="U18" s="17">
-        <v>160.02000000000001</v>
+        <v>914.13</v>
       </c>
       <c r="V18" s="14">
-        <v>1.4484188698807672</v>
+        <v>8.2742353551062724</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-2376.4545454545455</v>
+        <v>-1179.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="Z18" s="17">
-        <v>195.93</v>
+        <v>171.36</v>
       </c>
       <c r="AA18" s="14">
-        <v>24.129310344827587</v>
+        <v>20.024539877300612</v>
       </c>
       <c r="AB18" s="16">
-        <v>283.55555555555554</v>
+        <v>298.83333333333337</v>
       </c>
       <c r="AC18" s="15">
-        <v>117.66666666666669</v>
+        <v>68.249999999999972</v>
       </c>
       <c r="AD18" s="19">
-        <v>12660</v>
+        <v>17829</v>
       </c>
       <c r="AE18" s="20">
-        <v>7975.8</v>
+        <v>11232.27</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2922,85 +2921,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>916</v>
+        <v>657</v>
       </c>
       <c r="F19" s="14">
-        <v>577.08000000000004</v>
+        <v>413.91</v>
       </c>
       <c r="G19" s="14">
-        <v>13.570370370370373</v>
+        <v>9.7333333333333361</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>241.00000000000011</v>
+        <v>-17.999999999999886</v>
       </c>
       <c r="J19" s="16">
-        <v>1391</v>
+        <v>852</v>
       </c>
       <c r="K19" s="13">
-        <v>876.33</v>
+        <v>536.76</v>
       </c>
       <c r="L19" s="14">
-        <v>27.22597864768683</v>
+        <v>16.676156583629894</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>880.09090909090901</v>
+        <v>341.09090909090907</v>
       </c>
       <c r="O19" s="16">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="P19" s="17">
-        <v>53.55</v>
+        <v>25.830000000000002</v>
       </c>
       <c r="Q19" s="14">
-        <v>19.893617021276597</v>
+        <v>9.5957446808510642</v>
       </c>
       <c r="R19" s="16">
         <v>94</v>
       </c>
       <c r="S19" s="15">
-        <v>20.909090909090907</v>
+        <v>-44.454545454545453</v>
       </c>
       <c r="T19" s="18">
-        <v>4</v>
+        <v>282</v>
       </c>
       <c r="U19" s="17">
-        <v>2.52</v>
+        <v>177.66</v>
       </c>
       <c r="V19" s="14">
-        <v>0.25958702064896755</v>
+        <v>18.300884955752213</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>-227.13636363636363</v>
+        <v>50.863636363636374</v>
       </c>
       <c r="Y19" s="18">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="Z19" s="17">
-        <v>129.15</v>
+        <v>105.84</v>
       </c>
       <c r="AA19" s="14">
-        <v>14.879032258064516</v>
+        <v>14</v>
       </c>
       <c r="AB19" s="16">
-        <v>303.11111111111114</v>
+        <v>264</v>
       </c>
       <c r="AC19" s="15">
-        <v>-1.6666666666666856</v>
+        <v>-12</v>
       </c>
       <c r="AD19" s="19">
-        <v>2601</v>
+        <v>2000</v>
       </c>
       <c r="AE19" s="20">
-        <v>1638.63</v>
+        <v>1260</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3035,85 +3034,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1514</v>
+        <v>1440</v>
       </c>
       <c r="F20" s="14">
-        <v>953.82</v>
+        <v>907.2</v>
       </c>
       <c r="G20" s="14">
-        <v>9.8690370370370371</v>
+        <v>9.3866666666666667</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>-20.090909090909008</v>
+        <v>-94.090909090909008</v>
       </c>
       <c r="J20" s="16">
-        <v>1798</v>
+        <v>2429</v>
       </c>
       <c r="K20" s="13">
-        <v>1132.74</v>
+        <v>1530.27</v>
       </c>
       <c r="L20" s="14">
-        <v>17.890547263681594</v>
+        <v>24.169154228855721</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>793</v>
+        <v>1424</v>
       </c>
       <c r="O20" s="16">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="P20" s="17">
-        <v>140.49</v>
+        <v>105.21</v>
       </c>
       <c r="Q20" s="14">
-        <v>17.584229390681003</v>
+        <v>13.168458781362007</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>32.77272727272728</v>
+        <v>-86.636363636363626</v>
       </c>
       <c r="T20" s="18">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="U20" s="17">
-        <v>0</v>
+        <v>383.04</v>
       </c>
       <c r="V20" s="14">
-        <v>0</v>
+        <v>11.41296928327645</v>
       </c>
       <c r="W20" s="16">
         <v>1172</v>
       </c>
       <c r="X20" s="15">
-        <v>-799.09090909090912</v>
+        <v>-191.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="Z20" s="17">
-        <v>196.56</v>
+        <v>168.21</v>
       </c>
       <c r="AA20" s="14">
-        <v>21.6</v>
+        <v>18.101694915254239</v>
       </c>
       <c r="AB20" s="16">
-        <v>317.77777777777777</v>
+        <v>324.5</v>
       </c>
       <c r="AC20" s="15">
-        <v>95.333333333333343</v>
+        <v>45.75</v>
       </c>
       <c r="AD20" s="19">
-        <v>3847</v>
+        <v>4911</v>
       </c>
       <c r="AE20" s="20">
-        <v>2423.61</v>
+        <v>3093.93</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3148,85 +3147,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2955</v>
+        <v>2790</v>
       </c>
       <c r="F21" s="14">
-        <v>3220.9500000000003</v>
+        <v>3041.1000000000004</v>
       </c>
       <c r="G21" s="14">
-        <v>10.186461924161705</v>
+        <v>9.6176747101222198</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>54.090909090909463</v>
+        <v>-110.90909090909054</v>
       </c>
       <c r="J21" s="16">
-        <v>4927</v>
+        <v>5247</v>
       </c>
       <c r="K21" s="13">
-        <v>5370.43</v>
+        <v>5719.2300000000005</v>
       </c>
       <c r="L21" s="14">
-        <v>15.996753246753247</v>
+        <v>17.035714285714285</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>1847</v>
+        <v>2167</v>
       </c>
       <c r="O21" s="16">
-        <v>303</v>
+        <v>165</v>
       </c>
       <c r="P21" s="17">
-        <v>330.27000000000004</v>
+        <v>179.85000000000002</v>
       </c>
       <c r="Q21" s="14">
-        <v>12.648956356736244</v>
+        <v>6.8880455407969645</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>-56.318181818181813</v>
+        <v>-314.09090909090907</v>
       </c>
       <c r="T21" s="18">
-        <v>55</v>
+        <v>1321</v>
       </c>
       <c r="U21" s="17">
-        <v>59.95</v>
+        <v>1439.89</v>
       </c>
       <c r="V21" s="14">
-        <v>0.58425881216803477</v>
+        <v>14.032834379526799</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-1357.0454545454545</v>
+        <v>-91.045454545454504</v>
       </c>
       <c r="Y21" s="18">
-        <v>349</v>
+        <v>280</v>
       </c>
       <c r="Z21" s="17">
-        <v>380.41</v>
+        <v>305.20000000000005</v>
       </c>
       <c r="AA21" s="14">
-        <v>14.085201793721975</v>
+        <v>13.023255813953488</v>
       </c>
       <c r="AB21" s="16">
-        <v>545.11111111111109</v>
+        <v>473</v>
       </c>
       <c r="AC21" s="15">
-        <v>-22.666666666666629</v>
+        <v>-42.5</v>
       </c>
       <c r="AD21" s="19">
-        <v>8589</v>
+        <v>9803</v>
       </c>
       <c r="AE21" s="20">
-        <v>9362.01</v>
+        <v>10685.27</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3261,85 +3260,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1977</v>
+        <v>1804</v>
       </c>
       <c r="F22" s="14">
-        <v>2154.9300000000003</v>
+        <v>1966.3600000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>10.140825367218465</v>
+        <v>9.2534390300769402</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>27.454545454545269</v>
+        <v>-145.54545454545473</v>
       </c>
       <c r="J22" s="16">
-        <v>3746</v>
+        <v>2635</v>
       </c>
       <c r="K22" s="13">
-        <v>4083.1400000000003</v>
+        <v>2872.15</v>
       </c>
       <c r="L22" s="14">
-        <v>34.096814232519655</v>
+        <v>23.984278030616469</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>2647.3636363636365</v>
+        <v>1536.3636363636365</v>
       </c>
       <c r="O22" s="16">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="P22" s="17">
-        <v>194.02</v>
+        <v>158.05000000000001</v>
       </c>
       <c r="Q22" s="14">
-        <v>19.196078431372552</v>
+        <v>15.637254901960786</v>
       </c>
       <c r="R22" s="16">
         <v>203.99999999999997</v>
       </c>
       <c r="S22" s="15">
-        <v>38.909090909090935</v>
+        <v>-40.454545454545439</v>
       </c>
       <c r="T22" s="18">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="U22" s="17">
-        <v>440.36</v>
+        <v>488.32000000000005</v>
       </c>
       <c r="V22" s="14">
-        <v>12.535966149506347</v>
+        <v>13.901269393511988</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-79.409090909090878</v>
+        <v>-35.409090909090878</v>
       </c>
       <c r="Y22" s="18">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="Z22" s="17">
-        <v>206.01000000000002</v>
+        <v>158.05000000000001</v>
       </c>
       <c r="AA22" s="14">
-        <v>0</v>
+        <v>31.071428571428569</v>
       </c>
       <c r="AB22" s="16">
-        <v>124.66666666666667</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="AC22" s="15">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AD22" s="19">
-        <v>6494</v>
+        <v>5177</v>
       </c>
       <c r="AE22" s="20">
-        <v>7078.4600000000009</v>
+        <v>5642.93</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3374,85 +3373,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>13253</v>
+        <v>20091</v>
       </c>
       <c r="F23" s="14">
-        <v>15373.48</v>
+        <v>23305.559999999998</v>
       </c>
       <c r="G23" s="14">
-        <v>7.7344616282462795</v>
+        <v>11.725124015173622</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>-3882</v>
+        <v>2956</v>
       </c>
       <c r="J23" s="16">
-        <v>18500</v>
+        <v>10432</v>
       </c>
       <c r="K23" s="13">
-        <v>21460</v>
+        <v>12101.119999999999</v>
       </c>
       <c r="L23" s="14">
-        <v>21.269924222628692</v>
+        <v>11.993937810295272</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>9802.2727272727279</v>
+        <v>1734.2727272727279</v>
       </c>
       <c r="O23" s="16">
-        <v>1755</v>
+        <v>1199</v>
       </c>
       <c r="P23" s="17">
-        <v>2035.8</v>
+        <v>1390.84</v>
       </c>
       <c r="Q23" s="14">
-        <v>12.245480494766889</v>
+        <v>8.3660006343165243</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>-394.77272727272702</v>
+        <v>-1667.363636363636</v>
       </c>
       <c r="T23" s="18">
-        <v>3885</v>
+        <v>5235</v>
       </c>
       <c r="U23" s="17">
-        <v>4506.5999999999995</v>
+        <v>6072.5999999999995</v>
       </c>
       <c r="V23" s="14">
-        <v>6.4593409915356705</v>
+        <v>8.7038996372430457</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-5136.818181818182</v>
+        <v>-3786.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>388</v>
+        <v>221</v>
       </c>
       <c r="Z23" s="17">
-        <v>450.08</v>
+        <v>256.35999999999996</v>
       </c>
       <c r="AA23" s="14">
-        <v>5.6504854368932032</v>
+        <v>3.622950819672131</v>
       </c>
       <c r="AB23" s="16">
-        <v>1510.6666666666667</v>
+        <v>1342</v>
       </c>
       <c r="AC23" s="15">
-        <v>-642</v>
+        <v>-694</v>
       </c>
       <c r="AD23" s="19">
-        <v>37781</v>
+        <v>37178</v>
       </c>
       <c r="AE23" s="20">
-        <v>43825.96</v>
+        <v>43126.479999999996</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3487,85 +3486,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>8803</v>
+        <v>12602</v>
       </c>
       <c r="F24" s="14">
-        <v>10211.48</v>
+        <v>14618.32</v>
       </c>
       <c r="G24" s="14">
-        <v>7.210737955171644</v>
+        <v>10.322585449400552</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>-3405.181818181818</v>
+        <v>393.81818181818198</v>
       </c>
       <c r="J24" s="16">
-        <v>8461</v>
+        <v>9058</v>
       </c>
       <c r="K24" s="13">
-        <v>9814.76</v>
+        <v>10507.279999999999</v>
       </c>
       <c r="L24" s="14">
-        <v>15.600234663090848</v>
+        <v>16.700972175662084</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>3037.363636363636</v>
+        <v>3634.363636363636</v>
       </c>
       <c r="O24" s="16">
-        <v>1034</v>
+        <v>693</v>
       </c>
       <c r="P24" s="17">
-        <v>1199.4399999999998</v>
+        <v>803.88</v>
       </c>
       <c r="Q24" s="14">
-        <v>12.042350449973531</v>
+        <v>8.070937003705664</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>-253.9545454545455</v>
+        <v>-1024.2727272727273</v>
       </c>
       <c r="T24" s="18">
-        <v>3640</v>
+        <v>2938</v>
       </c>
       <c r="U24" s="17">
-        <v>4222.3999999999996</v>
+        <v>3408.08</v>
       </c>
       <c r="V24" s="14">
-        <v>11.012101210121012</v>
+        <v>8.8883388338833882</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-1318.181818181818</v>
+        <v>-2020.181818181818</v>
       </c>
       <c r="Y24" s="18">
-        <v>599</v>
+        <v>487</v>
       </c>
       <c r="Z24" s="17">
-        <v>694.83999999999992</v>
+        <v>564.91999999999996</v>
       </c>
       <c r="AA24" s="14">
-        <v>13.377171215880892</v>
+        <v>12.303157894736842</v>
       </c>
       <c r="AB24" s="16">
-        <v>985.11111111111109</v>
+        <v>870.83333333333337</v>
       </c>
       <c r="AC24" s="15">
-        <v>-72.666666666666629</v>
+        <v>-106.75</v>
       </c>
       <c r="AD24" s="19">
-        <v>22537</v>
+        <v>25778</v>
       </c>
       <c r="AE24" s="20">
-        <v>26142.92</v>
+        <v>29902.48</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3600,85 +3599,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>6475</v>
+        <v>5034</v>
       </c>
       <c r="F25" s="14">
-        <v>7510.9999999999991</v>
+        <v>5839.44</v>
       </c>
       <c r="G25" s="14">
-        <v>5.5161864931846347</v>
+        <v>4.2885687732342008</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-5263.181818181818</v>
+        <v>-6704.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>6830</v>
+        <v>11949</v>
       </c>
       <c r="K25" s="13">
-        <v>7922.7999999999993</v>
+        <v>13860.839999999998</v>
       </c>
       <c r="L25" s="14">
-        <v>12.615229619679289</v>
+        <v>22.070187221895729</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>1415.909090909091</v>
+        <v>6534.909090909091</v>
       </c>
       <c r="O25" s="16">
-        <v>1086</v>
+        <v>725</v>
       </c>
       <c r="P25" s="17">
-        <v>1259.76</v>
+        <v>840.99999999999989</v>
       </c>
       <c r="Q25" s="14">
-        <v>10.874829312699136</v>
+        <v>7.2598998634501593</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-411.9545454545455</v>
+        <v>-1272.2727272727273</v>
       </c>
       <c r="T25" s="18">
-        <v>3424</v>
+        <v>4309</v>
       </c>
       <c r="U25" s="17">
-        <v>3971.8399999999997</v>
+        <v>4998.4399999999996</v>
       </c>
       <c r="V25" s="14">
-        <v>10.453510963086316</v>
+        <v>13.155426033860671</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-1489.181818181818</v>
+        <v>-604.18181818181802</v>
       </c>
       <c r="Y25" s="18">
-        <v>729</v>
+        <v>635</v>
       </c>
       <c r="Z25" s="17">
-        <v>845.64</v>
+        <v>736.59999999999991</v>
       </c>
       <c r="AA25" s="14">
-        <v>21.725165562913908</v>
+        <v>22.346041055718473</v>
       </c>
       <c r="AB25" s="16">
-        <v>738.22222222222229</v>
+        <v>625.16666666666674</v>
       </c>
       <c r="AC25" s="15">
-        <v>225.66666666666663</v>
+        <v>208.74999999999994</v>
       </c>
       <c r="AD25" s="19">
-        <v>18544</v>
+        <v>22652</v>
       </c>
       <c r="AE25" s="20">
-        <v>21511.039999999997</v>
+        <v>26276.32</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3713,85 +3712,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>8959</v>
+        <v>15499</v>
       </c>
       <c r="F26" s="14">
-        <v>10392.439999999999</v>
+        <v>17978.84</v>
       </c>
       <c r="G26" s="14">
-        <v>6.2820079681274894</v>
+        <v>10.867824701195218</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>-5302.3636363636379</v>
+        <v>1237.6363636363621</v>
       </c>
       <c r="J26" s="16">
-        <v>17753</v>
+        <v>14306</v>
       </c>
       <c r="K26" s="13">
-        <v>20593.48</v>
+        <v>16594.96</v>
       </c>
       <c r="L26" s="14">
-        <v>27.701680970281579</v>
+        <v>22.323001631321372</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>11344.363636363636</v>
+        <v>7897.363636363636</v>
       </c>
       <c r="O26" s="16">
-        <v>990</v>
+        <v>616</v>
       </c>
       <c r="P26" s="17">
-        <v>1148.3999999999999</v>
+        <v>714.56</v>
       </c>
       <c r="Q26" s="14">
-        <v>11.967032967032965</v>
+        <v>7.4461538461538455</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-250.90909090909099</v>
+        <v>-1038.5454545454547</v>
       </c>
       <c r="T26" s="18">
-        <v>2417</v>
+        <v>3425</v>
       </c>
       <c r="U26" s="17">
-        <v>2803.72</v>
+        <v>3972.9999999999995</v>
       </c>
       <c r="V26" s="14">
-        <v>6.3865001201056932</v>
+        <v>9.0499639682920971</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-3259.818181818182</v>
+        <v>-2251.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>726</v>
+        <v>598</v>
       </c>
       <c r="Z26" s="17">
-        <v>842.16</v>
+        <v>693.68</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.669456066945607</v>
+        <v>13.118829981718463</v>
       </c>
       <c r="AB26" s="16">
-        <v>1168.4444444444446</v>
+        <v>1002.8333333333334</v>
       </c>
       <c r="AC26" s="15">
-        <v>-70.666666666666742</v>
+        <v>-85.75</v>
       </c>
       <c r="AD26" s="19">
-        <v>30845</v>
+        <v>34444</v>
       </c>
       <c r="AE26" s="20">
-        <v>35780.199999999997</v>
+        <v>39955.040000000001</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3826,85 +3825,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1393</v>
+        <v>2025</v>
       </c>
       <c r="F27" s="14">
-        <v>1615.8799999999999</v>
+        <v>2349</v>
       </c>
       <c r="G27" s="14">
-        <v>8.4494072236007707</v>
+        <v>12.282878411910669</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>-255.63636363636374</v>
+        <v>376.36363636363626</v>
       </c>
       <c r="J27" s="16">
-        <v>2085</v>
+        <v>3788</v>
       </c>
       <c r="K27" s="13">
-        <v>2418.6</v>
+        <v>4394.08</v>
       </c>
       <c r="L27" s="14">
-        <v>18.108961705487562</v>
+        <v>32.900118436636397</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>933.63636363636351</v>
+        <v>2636.6363636363635</v>
       </c>
       <c r="O27" s="16">
-        <v>564</v>
+        <v>433</v>
       </c>
       <c r="P27" s="17">
-        <v>654.24</v>
+        <v>502.28</v>
       </c>
       <c r="Q27" s="14">
-        <v>29.542857142857144</v>
+        <v>22.680952380952384</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>277.63636363636363</v>
+        <v>51.181818181818187</v>
       </c>
       <c r="T27" s="18">
-        <v>537</v>
+        <v>796</v>
       </c>
       <c r="U27" s="17">
-        <v>622.91999999999996</v>
+        <v>923.3599999999999</v>
       </c>
       <c r="V27" s="14">
-        <v>7.736738703339884</v>
+        <v>11.46823837590046</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-504.13636363636328</v>
+        <v>-245.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="Z27" s="17">
-        <v>577.67999999999995</v>
+        <v>535.91999999999996</v>
       </c>
       <c r="AA27" s="14">
-        <v>37.041322314049587</v>
+        <v>36.473684210526322</v>
       </c>
       <c r="AB27" s="16">
-        <v>295.77777777777777</v>
+        <v>278.66666666666663</v>
       </c>
       <c r="AC27" s="15">
-        <v>296.33333333333337</v>
+        <v>272</v>
       </c>
       <c r="AD27" s="19">
-        <v>5077</v>
+        <v>7504</v>
       </c>
       <c r="AE27" s="20">
-        <v>5889.32</v>
+        <v>8704.64</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3939,85 +3938,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1104.32</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14">
-        <v>5.5806021849187317</v>
+        <v>0</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>-753.90909090909099</v>
+        <v>-1705.909090909091</v>
       </c>
       <c r="J28" s="16">
-        <v>895</v>
+        <v>9936</v>
       </c>
       <c r="K28" s="13">
-        <v>1038.1999999999998</v>
+        <v>11525.759999999998</v>
       </c>
       <c r="L28" s="14">
-        <v>5.9005094396164219</v>
+        <v>65.505543901708123</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>-621.81818181818198</v>
+        <v>8419.181818181818</v>
       </c>
       <c r="O28" s="16">
-        <v>503</v>
+        <v>277</v>
       </c>
       <c r="P28" s="17">
-        <v>583.4799999999999</v>
+        <v>321.32</v>
       </c>
       <c r="Q28" s="14">
-        <v>20.958333333333332</v>
+        <v>11.541666666666666</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>143</v>
+        <v>-203</v>
       </c>
       <c r="T28" s="18">
-        <v>397</v>
+        <v>101</v>
       </c>
       <c r="U28" s="17">
-        <v>460.52</v>
+        <v>117.16</v>
       </c>
       <c r="V28" s="14">
-        <v>6.7340015420200467</v>
+        <v>1.7131842713955281</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-487.31818181818176</v>
+        <v>-783.31818181818176</v>
       </c>
       <c r="Y28" s="18">
-        <v>451</v>
+        <v>395</v>
       </c>
       <c r="Z28" s="17">
-        <v>523.16</v>
+        <v>458.2</v>
       </c>
       <c r="AA28" s="14">
-        <v>22.180327868852459</v>
+        <v>22.149532710280376</v>
       </c>
       <c r="AB28" s="16">
-        <v>447.33333333333331</v>
+        <v>392.33333333333331</v>
       </c>
       <c r="AC28" s="15">
-        <v>146</v>
+        <v>127.5</v>
       </c>
       <c r="AD28" s="19">
-        <v>3198</v>
+        <v>10709</v>
       </c>
       <c r="AE28" s="20">
-        <v>3709.68</v>
+        <v>12422.439999999999</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4052,85 +4051,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1855.9999999999998</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14">
-        <v>9.2509855453350855</v>
+        <v>0</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-129.54545454545473</v>
+        <v>-1729.5454545454547</v>
       </c>
       <c r="J29" s="16">
-        <v>1709</v>
+        <v>4048</v>
       </c>
       <c r="K29" s="13">
-        <v>1982.4399999999998</v>
+        <v>4695.6799999999994</v>
       </c>
       <c r="L29" s="14">
-        <v>13.848250460405156</v>
+        <v>32.801473296500923</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>474.90909090909099</v>
+        <v>2813.909090909091</v>
       </c>
       <c r="O29" s="16">
-        <v>477</v>
+        <v>275</v>
       </c>
       <c r="P29" s="17">
-        <v>553.31999999999994</v>
+        <v>319</v>
       </c>
       <c r="Q29" s="14">
-        <v>21.908141962421713</v>
+        <v>12.630480167014614</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>150.40909090909088</v>
+        <v>-160.4545454545455</v>
       </c>
       <c r="T29" s="18">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="U29" s="17">
-        <v>421.08</v>
+        <v>393.23999999999995</v>
       </c>
       <c r="V29" s="14">
-        <v>6.9991235758106916</v>
+        <v>6.5363716038562663</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>-414.9545454545455</v>
+        <v>-438.9545454545455</v>
       </c>
       <c r="Y29" s="18">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="Z29" s="17">
-        <v>499.96</v>
+        <v>458.2</v>
       </c>
       <c r="AA29" s="14">
-        <v>20.308900523560212</v>
+        <v>21.447963800904976</v>
       </c>
       <c r="AB29" s="16">
-        <v>466.88888888888886</v>
+        <v>405.16666666666669</v>
       </c>
       <c r="AC29" s="15">
-        <v>112.66666666666669</v>
+        <v>118.75</v>
       </c>
       <c r="AD29" s="19">
-        <v>4580</v>
+        <v>5057</v>
       </c>
       <c r="AE29" s="20">
-        <v>5312.7999999999993</v>
+        <v>5866.12</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4165,85 +4164,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>483</v>
+        <v>882</v>
       </c>
       <c r="F30" s="14">
-        <v>1777.44</v>
+        <v>3245.76</v>
       </c>
       <c r="G30" s="14">
-        <v>5.3531486146095713</v>
+        <v>9.7753148614609557</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>-419.27272727272737</v>
+        <v>-20.272727272727366</v>
       </c>
       <c r="J30" s="16">
-        <v>1197</v>
+        <v>825</v>
       </c>
       <c r="K30" s="13">
-        <v>4404.96</v>
+        <v>3036</v>
       </c>
       <c r="L30" s="14">
-        <v>11.846153846153847</v>
+        <v>8.1646423751686914</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>186.5454545454545</v>
+        <v>-185.4545454545455</v>
       </c>
       <c r="O30" s="16">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="P30" s="17">
-        <v>276</v>
+        <v>80.960000000000008</v>
       </c>
       <c r="Q30" s="14">
-        <v>20.121951219512198</v>
+        <v>5.9024390243902438</v>
       </c>
       <c r="R30" s="16">
         <v>82</v>
       </c>
       <c r="S30" s="15">
-        <v>19.090909090909093</v>
+        <v>-52.545454545454547</v>
       </c>
       <c r="T30" s="18">
-        <v>334</v>
+        <v>453</v>
       </c>
       <c r="U30" s="17">
-        <v>1229.1200000000001</v>
+        <v>1667.04</v>
       </c>
       <c r="V30" s="14">
-        <v>10.527220630372494</v>
+        <v>14.277936962750717</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-141.90909090909088</v>
+        <v>-22.909090909090878</v>
       </c>
       <c r="Y30" s="18">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z30" s="17">
-        <v>195.04000000000002</v>
+        <v>143.52000000000001</v>
       </c>
       <c r="AA30" s="14">
-        <v>9.7346938775510203</v>
+        <v>8.068965517241379</v>
       </c>
       <c r="AB30" s="16">
-        <v>119.77777777777779</v>
+        <v>106.33333333333333</v>
       </c>
       <c r="AC30" s="15">
-        <v>-28.666666666666671</v>
+        <v>-33.5</v>
       </c>
       <c r="AD30" s="19">
-        <v>2142</v>
+        <v>2221</v>
       </c>
       <c r="AE30" s="20">
-        <v>7882.56</v>
+        <v>8173.2800000000007</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4278,85 +4277,85 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>520</v>
+        <v>364</v>
       </c>
       <c r="F31" s="14">
-        <v>1913.6000000000001</v>
+        <v>1339.52</v>
       </c>
       <c r="G31" s="14">
-        <v>9.5412844036697244</v>
+        <v>6.6788990825688073</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-25</v>
+        <v>-181</v>
       </c>
       <c r="J31" s="16">
-        <v>653</v>
+        <v>332</v>
       </c>
       <c r="K31" s="13">
-        <v>2403.04</v>
+        <v>1221.76</v>
       </c>
       <c r="L31" s="14">
-        <v>9.8128415300546461</v>
+        <v>4.9890710382513674</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>-12.454545454545269</v>
+        <v>-333.45454545454527</v>
       </c>
       <c r="O31" s="16">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="P31" s="17">
-        <v>117.76</v>
+        <v>95.68</v>
       </c>
       <c r="Q31" s="14">
-        <v>17.600000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="R31" s="16">
         <v>40</v>
       </c>
       <c r="S31" s="15">
-        <v>4.7272727272727266</v>
+        <v>-10.36363636363636</v>
       </c>
       <c r="T31" s="18">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="U31" s="17">
-        <v>430.56</v>
+        <v>695.52</v>
       </c>
       <c r="V31" s="14">
-        <v>9.7870722433460067</v>
+        <v>15.809885931558934</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>-62.318181818181813</v>
+        <v>9.681818181818187</v>
       </c>
       <c r="Y31" s="18">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Z31" s="17">
-        <v>217.12</v>
+        <v>184</v>
       </c>
       <c r="AA31" s="14">
-        <v>29.5</v>
+        <v>28.571428571428573</v>
       </c>
       <c r="AB31" s="16">
-        <v>44</v>
+        <v>38.5</v>
       </c>
       <c r="AC31" s="15">
-        <v>29</v>
+        <v>23.75</v>
       </c>
       <c r="AD31" s="19">
-        <v>1381</v>
+        <v>961</v>
       </c>
       <c r="AE31" s="20">
-        <v>5082.08</v>
+        <v>3536.48</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4391,85 +4390,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>944</v>
+        <v>2255</v>
       </c>
       <c r="F32" s="14">
-        <v>3917.6000000000004</v>
+        <v>9358.25</v>
       </c>
       <c r="G32" s="14">
-        <v>4.3221644120707596</v>
+        <v>10.324661810613945</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>-1240.090909090909</v>
+        <v>70.909090909090992</v>
       </c>
       <c r="J32" s="16">
-        <v>1684</v>
+        <v>1924</v>
       </c>
       <c r="K32" s="13">
-        <v>6988.6</v>
+        <v>7984.6</v>
       </c>
       <c r="L32" s="14">
-        <v>9.8244497480774324</v>
+        <v>11.224608857067089</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>-30.090909090909463</v>
+        <v>209.90909090909054</v>
       </c>
       <c r="O32" s="16">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="P32" s="17">
-        <v>813.40000000000009</v>
+        <v>593.45000000000005</v>
       </c>
       <c r="Q32" s="14">
-        <v>15.345195729537366</v>
+        <v>11.195729537366548</v>
       </c>
       <c r="R32" s="16">
         <v>281</v>
       </c>
       <c r="S32" s="15">
-        <v>4.4090909090909065</v>
+        <v>-112.45454545454547</v>
       </c>
       <c r="T32" s="18">
-        <v>688</v>
+        <v>767</v>
       </c>
       <c r="U32" s="17">
-        <v>2855.2000000000003</v>
+        <v>3183.05</v>
       </c>
       <c r="V32" s="14">
-        <v>8.2665210267613318</v>
+        <v>9.2157291097760776</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-560.40909090909099</v>
+        <v>-481.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="Z32" s="17">
-        <v>1257.45</v>
+        <v>1191.0500000000002</v>
       </c>
       <c r="AA32" s="14">
-        <v>53.470588235294116</v>
+        <v>57.4</v>
       </c>
       <c r="AB32" s="16">
-        <v>124.66666666666667</v>
+        <v>110</v>
       </c>
       <c r="AC32" s="15">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AD32" s="19">
-        <v>3815</v>
+        <v>5376</v>
       </c>
       <c r="AE32" s="20">
-        <v>15832.250000000002</v>
+        <v>22310.400000000001</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4504,85 +4503,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1550</v>
+        <v>1946</v>
       </c>
       <c r="F33" s="14">
-        <v>6432.5000000000009</v>
+        <v>8075.9000000000005</v>
       </c>
       <c r="G33" s="14">
-        <v>3.8706015891032917</v>
+        <v>4.8594778660612938</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-2454.5454545454545</v>
+        <v>-2058.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>3345</v>
+        <v>2310</v>
       </c>
       <c r="K33" s="13">
-        <v>13881.750000000002</v>
+        <v>9586.5</v>
       </c>
       <c r="L33" s="14">
-        <v>14.506209343583679</v>
+        <v>10.017740981667652</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>1039.090909090909</v>
+        <v>4.0909090909090082</v>
       </c>
       <c r="O33" s="16">
-        <v>215</v>
+        <v>129</v>
       </c>
       <c r="P33" s="17">
-        <v>892.25000000000011</v>
+        <v>535.35</v>
       </c>
       <c r="Q33" s="14">
-        <v>13.17548746518106</v>
+        <v>7.9052924791086356</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>-29.772727272727252</v>
+        <v>-197.36363636363632</v>
       </c>
       <c r="T33" s="18">
-        <v>1211</v>
+        <v>1191</v>
       </c>
       <c r="U33" s="17">
-        <v>5025.6500000000005</v>
+        <v>4942.6500000000005</v>
       </c>
       <c r="V33" s="14">
-        <v>10.398907103825136</v>
+        <v>10.227166276346605</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-535.81818181818176</v>
+        <v>-555.81818181818176</v>
       </c>
       <c r="Y33" s="18">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="Z33" s="17">
-        <v>597.6</v>
+        <v>444.05</v>
       </c>
       <c r="AA33" s="14">
-        <v>10.204724409448819</v>
+        <v>7.9751552795031069</v>
       </c>
       <c r="AB33" s="16">
-        <v>310.44444444444446</v>
+        <v>295.16666666666663</v>
       </c>
       <c r="AC33" s="15">
-        <v>-67.666666666666686</v>
+        <v>-94.249999999999972</v>
       </c>
       <c r="AD33" s="19">
-        <v>6465</v>
+        <v>5683</v>
       </c>
       <c r="AE33" s="20">
-        <v>26829.750000000004</v>
+        <v>23584.45</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4617,25 +4616,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F34" s="14">
-        <v>1925.6000000000001</v>
+        <v>1983.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>6.8972972972972979</v>
+        <v>7.1054054054054063</v>
       </c>
       <c r="H34" s="30">
         <v>1480</v>
       </c>
       <c r="I34" s="15">
-        <v>-208.72727272727263</v>
+        <v>-194.72727272727263</v>
       </c>
       <c r="J34" s="16">
-        <v>1073</v>
+        <v>752</v>
       </c>
       <c r="K34" s="13">
-        <v>4452.9500000000007</v>
+        <v>3120.8</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4644,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>1073</v>
+        <v>752</v>
       </c>
       <c r="O34" s="16">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="P34" s="17">
         <v>0</v>
@@ -4658,23 +4657,23 @@
       <c r="R34" s="16">
         <v>0</v>
       </c>
-      <c r="S34" s="15" t="s">
-        <v>56</v>
+      <c r="S34" s="15">
+        <v>64</v>
       </c>
       <c r="T34" s="18">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="U34" s="17">
-        <v>307.10000000000002</v>
+        <v>265.60000000000002</v>
       </c>
       <c r="V34" s="14">
-        <v>17.319148936170215</v>
+        <v>14.978723404255319</v>
       </c>
       <c r="W34" s="16">
         <v>94</v>
       </c>
       <c r="X34" s="15">
-        <v>9.9090909090909065</v>
+        <v>-9.0909090909093493E-2</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4692,10 +4691,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1675</v>
+        <v>1390</v>
       </c>
       <c r="AE34" s="20">
-        <v>6951.2500000000009</v>
+        <v>5768.5000000000009</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4724,91 +4723,91 @@
         <v>131150</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="12">
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1597</v>
+        <v>3608</v>
       </c>
       <c r="F35" s="14">
-        <v>2603.1099999999997</v>
+        <v>5881.04</v>
       </c>
       <c r="G35" s="14">
-        <v>3.2853936786983358</v>
+        <v>7.422479895268375</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-3263.909090909091</v>
+        <v>-1252.909090909091</v>
       </c>
       <c r="J35" s="16">
-        <v>5413</v>
+        <v>2528</v>
       </c>
       <c r="K35" s="13">
-        <v>8823.1899999999987</v>
+        <v>4120.6399999999994</v>
       </c>
       <c r="L35" s="14">
-        <v>36.971747904377523</v>
+        <v>17.266687364172618</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>3948.909090909091</v>
+        <v>1063.909090909091</v>
       </c>
       <c r="O35" s="16">
-        <v>618</v>
+        <v>424</v>
       </c>
       <c r="P35" s="17">
-        <v>1007.3399999999999</v>
+        <v>691.12</v>
       </c>
       <c r="Q35" s="14">
-        <v>14.236649214659687</v>
+        <v>9.7675392670157066</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>-33.136363636363626</v>
+        <v>-444.18181818181813</v>
       </c>
       <c r="T35" s="18">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="U35" s="17">
-        <v>404.23999999999995</v>
+        <v>506.92999999999995</v>
       </c>
       <c r="V35" s="14">
-        <v>4.0058737151248165</v>
+        <v>5.023494860499266</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-680.63636363636363</v>
+        <v>-617.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>399</v>
+        <v>322</v>
       </c>
       <c r="Z35" s="17">
-        <v>650.37</v>
+        <v>524.86</v>
       </c>
       <c r="AA35" s="14">
-        <v>26.40441176470588</v>
+        <v>23.418181818181818</v>
       </c>
       <c r="AB35" s="16">
-        <v>332.44444444444446</v>
+        <v>302.5</v>
       </c>
       <c r="AC35" s="15">
-        <v>172.33333333333331</v>
+        <v>115.75</v>
       </c>
       <c r="AD35" s="19">
-        <v>8275</v>
+        <v>7193</v>
       </c>
       <c r="AE35" s="20">
-        <v>13488.25</v>
+        <v>11724.589999999998</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4837,91 +4836,91 @@
         <v>131151</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="12">
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>578</v>
+        <v>6270</v>
       </c>
       <c r="F36" s="14">
-        <v>942.14</v>
+        <v>10220.099999999999</v>
       </c>
       <c r="G36" s="14">
-        <v>0.77315011856265581</v>
+        <v>8.3869398674530302</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-6897.909090909091</v>
+        <v>-1205.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>4500</v>
+        <v>2929</v>
       </c>
       <c r="K36" s="13">
-        <v>7334.9999999999991</v>
+        <v>4774.2699999999995</v>
       </c>
       <c r="L36" s="14">
-        <v>20.064856100526956</v>
+        <v>13.059991892987433</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>2257.272727272727</v>
+        <v>686.27272727272702</v>
       </c>
       <c r="O36" s="16">
-        <v>573</v>
+        <v>199</v>
       </c>
       <c r="P36" s="17">
-        <v>933.9899999999999</v>
+        <v>324.37</v>
       </c>
       <c r="Q36" s="14">
-        <v>6.2935596605092359</v>
+        <v>2.1857214178731903</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-792.68181818181824</v>
+        <v>-1621.909090909091</v>
       </c>
       <c r="T36" s="18">
-        <v>1572</v>
+        <v>1313</v>
       </c>
       <c r="U36" s="17">
-        <v>2562.3599999999997</v>
+        <v>2140.19</v>
       </c>
       <c r="V36" s="14">
-        <v>11.771272974812799</v>
+        <v>9.8318584070796469</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-431.18181818181802</v>
+        <v>-690.18181818181802</v>
       </c>
       <c r="Y36" s="18">
-        <v>451</v>
+        <v>361</v>
       </c>
       <c r="Z36" s="17">
-        <v>735.13</v>
+        <v>588.42999999999995</v>
       </c>
       <c r="AA36" s="14">
-        <v>15.611538461538462</v>
+        <v>13.929260450160768</v>
       </c>
       <c r="AB36" s="16">
-        <v>635.55555555555554</v>
+        <v>570.16666666666674</v>
       </c>
       <c r="AC36" s="15">
-        <v>17.666666666666686</v>
+        <v>-27.750000000000057</v>
       </c>
       <c r="AD36" s="19">
-        <v>7674</v>
+        <v>11072</v>
       </c>
       <c r="AE36" s="20">
-        <v>12508.619999999999</v>
+        <v>18047.36</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4950,91 +4949,91 @@
         <v>131152</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="12">
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1300</v>
+        <v>964</v>
       </c>
       <c r="F37" s="14">
-        <v>2119</v>
+        <v>1571.32</v>
       </c>
       <c r="G37" s="14">
-        <v>4.7994629971471721</v>
+        <v>3.5589864071152877</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-1408.636363636364</v>
+        <v>-1744.636363636364</v>
       </c>
       <c r="J37" s="16">
-        <v>698</v>
+        <v>1203</v>
       </c>
       <c r="K37" s="13">
-        <v>1137.74</v>
+        <v>1960.8899999999999</v>
       </c>
       <c r="L37" s="14">
-        <v>6.3402146985962009</v>
+        <v>10.927332782824113</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>-402.90909090909099</v>
+        <v>102.09090909090901</v>
       </c>
       <c r="O37" s="16">
-        <v>313</v>
+        <v>27</v>
       </c>
       <c r="P37" s="17">
-        <v>510.18999999999994</v>
+        <v>44.01</v>
       </c>
       <c r="Q37" s="14">
-        <v>6.7708947885939041</v>
+        <v>0.58407079646017701</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-380.40909090909088</v>
+        <v>-897.5454545454545</v>
       </c>
       <c r="T37" s="18">
-        <v>533</v>
+        <v>357</v>
       </c>
       <c r="U37" s="17">
-        <v>868.79</v>
+        <v>581.91</v>
       </c>
       <c r="V37" s="14">
-        <v>7.6992777413000653</v>
+        <v>5.1569271175311879</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-505.40909090909099</v>
+        <v>-681.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="Z37" s="17">
-        <v>171.14999999999998</v>
+        <v>21.189999999999998</v>
       </c>
       <c r="AA37" s="14">
-        <v>0</v>
+        <v>0.65546218487394958</v>
       </c>
       <c r="AB37" s="16">
-        <v>498.66666666666669</v>
+        <v>436.33333333333331</v>
       </c>
       <c r="AC37" s="15">
-        <v>-235</v>
+        <v>-284.5</v>
       </c>
       <c r="AD37" s="19">
-        <v>2949</v>
+        <v>2564</v>
       </c>
       <c r="AE37" s="20">
-        <v>4806.87</v>
+        <v>4179.32</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5063,91 +5062,91 @@
         <v>131153</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" s="12">
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1401</v>
+        <v>336</v>
       </c>
       <c r="F38" s="14">
-        <v>2283.6299999999997</v>
+        <v>547.67999999999995</v>
       </c>
       <c r="G38" s="14">
-        <v>7.5010951569724993</v>
+        <v>1.7989778534923337</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>-466.72727272727275</v>
+        <v>-1531.7272727272727</v>
       </c>
       <c r="J38" s="16">
-        <v>1206</v>
+        <v>448</v>
       </c>
       <c r="K38" s="13">
-        <v>1965.78</v>
+        <v>730.24</v>
       </c>
       <c r="L38" s="14">
-        <v>12.719079578139981</v>
+        <v>4.724832214765101</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>257.81818181818187</v>
+        <v>-500.18181818181813</v>
       </c>
       <c r="O38" s="16">
-        <v>408</v>
+        <v>173</v>
       </c>
       <c r="P38" s="17">
-        <v>665.04</v>
+        <v>281.99</v>
       </c>
       <c r="Q38" s="14">
-        <v>11.952063914780295</v>
+        <v>5.0679094540612519</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>-104.0454545454545</v>
+        <v>-509.72727272727263</v>
       </c>
       <c r="T38" s="18">
-        <v>346</v>
+        <v>495</v>
       </c>
       <c r="U38" s="17">
-        <v>563.98</v>
+        <v>806.84999999999991</v>
       </c>
       <c r="V38" s="14">
-        <v>7.4263414634146336</v>
+        <v>10.624390243902438</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-352.86363636363637</v>
+        <v>-203.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>354</v>
+        <v>290</v>
       </c>
       <c r="Z38" s="17">
-        <v>577.02</v>
+        <v>472.7</v>
       </c>
       <c r="AA38" s="14">
-        <v>11.378571428571428</v>
+        <v>10.943396226415095</v>
       </c>
       <c r="AB38" s="16">
-        <v>684.44444444444446</v>
+        <v>583</v>
       </c>
       <c r="AC38" s="15">
-        <v>-112.66666666666669</v>
+        <v>-107.5</v>
       </c>
       <c r="AD38" s="19">
-        <v>3715</v>
+        <v>1742</v>
       </c>
       <c r="AE38" s="20">
-        <v>6055.45</v>
+        <v>2839.46</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5176,91 +5175,91 @@
         <v>131154</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D39" s="12">
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>499</v>
+        <v>2058</v>
       </c>
       <c r="F39" s="14">
-        <v>813.36999999999989</v>
+        <v>3354.54</v>
       </c>
       <c r="G39" s="14">
-        <v>58.705882352941174</v>
+        <v>242.11764705882354</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>414</v>
+        <v>1973</v>
       </c>
       <c r="J39" s="16">
-        <v>6051</v>
+        <v>4177</v>
       </c>
       <c r="K39" s="13">
-        <v>9863.1299999999992</v>
+        <v>6808.5099999999993</v>
       </c>
       <c r="L39" s="14">
-        <v>163.13970588235296</v>
+        <v>112.61519607843138</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>5680.090909090909</v>
+        <v>3806.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>474</v>
+        <v>314</v>
       </c>
       <c r="P39" s="17">
-        <v>772.62</v>
+        <v>511.82</v>
       </c>
       <c r="Q39" s="14">
-        <v>948</v>
+        <v>628</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>466.5</v>
+        <v>304</v>
       </c>
       <c r="T39" s="18">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="U39" s="17">
-        <v>479.21999999999997</v>
+        <v>567.24</v>
       </c>
       <c r="V39" s="14">
-        <v>12.022304832713756</v>
+        <v>14.230483271375466</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>-72.818181818181813</v>
+        <v>-18.818181818181813</v>
       </c>
       <c r="Y39" s="18">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="Z39" s="17">
-        <v>790.55</v>
+        <v>751.43</v>
       </c>
       <c r="AA39" s="14">
-        <v>92.872340425531917</v>
+        <v>89.225806451612897</v>
       </c>
       <c r="AB39" s="16">
-        <v>114.88888888888889</v>
+        <v>113.66666666666667</v>
       </c>
       <c r="AC39" s="15">
-        <v>406.66666666666669</v>
+        <v>383.5</v>
       </c>
       <c r="AD39" s="19">
-        <v>7803</v>
+        <v>7358</v>
       </c>
       <c r="AE39" s="20">
-        <v>12718.89</v>
+        <v>11993.539999999999</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5289,91 +5288,91 @@
         <v>131155</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40" s="12">
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>333</v>
+        <v>1834</v>
       </c>
       <c r="F40" s="14">
-        <v>542.79</v>
+        <v>2989.4199999999996</v>
       </c>
       <c r="G40" s="14">
-        <v>39.6</v>
+        <v>218.09729729729733</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>248.90909090909093</v>
+        <v>1749.909090909091</v>
       </c>
       <c r="J40" s="16">
-        <v>6448</v>
+        <v>4228</v>
       </c>
       <c r="K40" s="13">
-        <v>10510.24</v>
+        <v>6891.6399999999994</v>
       </c>
       <c r="L40" s="14">
-        <v>198.67787114845939</v>
+        <v>130.27450980392157</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>6123.454545454546</v>
+        <v>3903.4545454545455</v>
       </c>
       <c r="O40" s="16">
-        <v>420</v>
+        <v>235</v>
       </c>
       <c r="P40" s="17">
-        <v>684.59999999999991</v>
+        <v>383.04999999999995</v>
       </c>
       <c r="Q40" s="14">
-        <v>840</v>
+        <v>470</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>412.5</v>
+        <v>225</v>
       </c>
       <c r="T40" s="18">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="U40" s="17">
-        <v>438.46999999999997</v>
+        <v>510.18999999999994</v>
       </c>
       <c r="V40" s="14">
-        <v>10.511545293072825</v>
+        <v>12.230905861456483</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>-114.86363636363637</v>
+        <v>-70.863636363636374</v>
       </c>
       <c r="Y40" s="18">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="Z40" s="17">
-        <v>795.43999999999994</v>
+        <v>766.09999999999991</v>
       </c>
       <c r="AA40" s="14">
-        <v>89.632653061224488</v>
+        <v>92.459016393442624</v>
       </c>
       <c r="AB40" s="16">
-        <v>119.77777777777779</v>
+        <v>111.83333333333333</v>
       </c>
       <c r="AC40" s="15">
-        <v>406.33333333333331</v>
+        <v>393.75</v>
       </c>
       <c r="AD40" s="19">
-        <v>7958</v>
+        <v>7080</v>
       </c>
       <c r="AE40" s="20">
-        <v>12971.539999999999</v>
+        <v>11540.4</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5402,91 +5401,91 @@
         <v>131700</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D41" s="12">
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="F41" s="14">
-        <v>1439.1000000000001</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
-        <v>3.8360655737704916</v>
+        <v>0</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-376</v>
+        <v>-610</v>
       </c>
       <c r="J41" s="16">
-        <v>194</v>
+        <v>480</v>
       </c>
       <c r="K41" s="13">
-        <v>1193.1000000000001</v>
+        <v>2952</v>
       </c>
       <c r="L41" s="14">
-        <v>5.3888888888888893</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>-166</v>
+        <v>120</v>
       </c>
       <c r="O41" s="16">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P41" s="17">
-        <v>295.20000000000005</v>
+        <v>282.90000000000003</v>
       </c>
       <c r="Q41" s="14">
-        <v>12.72289156626506</v>
+        <v>12.192771084337348</v>
       </c>
       <c r="R41" s="16">
         <v>83</v>
       </c>
       <c r="S41" s="15">
-        <v>-8.5909090909090935</v>
+        <v>-29.454545454545453</v>
       </c>
       <c r="T41" s="18">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="U41" s="17">
-        <v>1414.5</v>
+        <v>1236.1500000000001</v>
       </c>
       <c r="V41" s="14">
-        <v>13.602150537634408</v>
+        <v>11.887096774193548</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-23.636363636363654</v>
+        <v>-52.636363636363654</v>
       </c>
       <c r="Y41" s="18">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="Z41" s="17">
-        <v>258.3</v>
+        <v>141.45000000000002</v>
       </c>
       <c r="AA41" s="14">
-        <v>0</v>
+        <v>4.2461538461538462</v>
       </c>
       <c r="AB41" s="16">
-        <v>119.77777777777779</v>
+        <v>119.16666666666667</v>
       </c>
       <c r="AC41" s="15">
-        <v>-39.666666666666671</v>
+        <v>-58.25</v>
       </c>
       <c r="AD41" s="19">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AE41" s="20">
-        <v>4600.2</v>
+        <v>4612.5</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5515,91 +5514,91 @@
         <v>131701</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="12">
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="F42" s="14">
-        <v>1285.3500000000001</v>
+        <v>1408.3500000000001</v>
       </c>
       <c r="G42" s="14">
-        <v>3.2563739376770537</v>
+        <v>3.5679886685552407</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-432.81818181818187</v>
+        <v>-412.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="K42" s="13">
-        <v>1297.6500000000001</v>
+        <v>1801.95</v>
       </c>
       <c r="L42" s="14">
-        <v>5.0129589632829372</v>
+        <v>6.9611231101511875</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>-209.90909090909093</v>
+        <v>-127.90909090909093</v>
       </c>
       <c r="O42" s="16">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="P42" s="17">
-        <v>270.60000000000002</v>
+        <v>104.55000000000001</v>
       </c>
       <c r="Q42" s="14">
-        <v>11.950617283950617</v>
+        <v>4.617283950617284</v>
       </c>
       <c r="R42" s="16">
         <v>81</v>
       </c>
       <c r="S42" s="15">
-        <v>-11.227272727272727</v>
+        <v>-56.636363636363626</v>
       </c>
       <c r="T42" s="18">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="U42" s="17">
-        <v>1845</v>
+        <v>1629.75</v>
       </c>
       <c r="V42" s="14">
-        <v>12.452830188679245</v>
+        <v>11</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-61.363636363636374</v>
+        <v>-96.363636363636374</v>
       </c>
       <c r="Y42" s="18">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="17">
-        <v>590.40000000000009</v>
+        <v>535.05000000000007</v>
       </c>
       <c r="AA42" s="14">
-        <v>16</v>
+        <v>18.315789473684209</v>
       </c>
       <c r="AB42" s="16">
-        <v>132</v>
+        <v>104.5</v>
       </c>
       <c r="AC42" s="15">
-        <v>6</v>
+        <v>15.75</v>
       </c>
       <c r="AD42" s="19">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="AE42" s="20">
-        <v>5289</v>
+        <v>5479.6500000000005</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5628,91 +5627,91 @@
         <v>132150</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D43" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>3040</v>
+        <v>3135</v>
       </c>
       <c r="F43" s="14">
-        <v>3526.3999999999996</v>
+        <v>3636.6</v>
       </c>
       <c r="G43" s="14">
-        <v>9.0611028315946349</v>
+        <v>9.3442622950819665</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-315</v>
+        <v>-220</v>
       </c>
       <c r="J43" s="16">
-        <v>3164</v>
+        <v>2865</v>
       </c>
       <c r="K43" s="13">
-        <v>3670.24</v>
+        <v>3323.3999999999996</v>
       </c>
       <c r="L43" s="14">
-        <v>25.358105646630239</v>
+        <v>22.961748633879782</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>1916.2727272727273</v>
+        <v>1617.2727272727273</v>
       </c>
       <c r="O43" s="16">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="P43" s="17">
-        <v>382.79999999999995</v>
+        <v>146.16</v>
       </c>
       <c r="Q43" s="14">
-        <v>6.3852242744063323</v>
+        <v>2.4379947229551453</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-445.22727272727275</v>
+        <v>-907.63636363636351</v>
       </c>
       <c r="T43" s="18">
-        <v>916</v>
+        <v>1134</v>
       </c>
       <c r="U43" s="17">
-        <v>1062.56</v>
+        <v>1315.4399999999998</v>
       </c>
       <c r="V43" s="14">
-        <v>9.7118072289156636</v>
+        <v>12.023132530120483</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-498.77272727272725</v>
+        <v>-280.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>314</v>
+        <v>228</v>
       </c>
       <c r="Z43" s="17">
-        <v>364.23999999999995</v>
+        <v>264.47999999999996</v>
       </c>
       <c r="AA43" s="14">
-        <v>9.2052117263843645</v>
+        <v>7.8847262247838605</v>
       </c>
       <c r="AB43" s="16">
-        <v>750.44444444444457</v>
+        <v>636.16666666666674</v>
       </c>
       <c r="AC43" s="15">
-        <v>-197.66666666666674</v>
+        <v>-205.75000000000006</v>
       </c>
       <c r="AD43" s="19">
-        <v>7764</v>
+        <v>7488</v>
       </c>
       <c r="AE43" s="20">
-        <v>9006.24</v>
+        <v>8686.08</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5741,91 +5740,91 @@
         <v>132151</v>
       </c>
       <c r="C44" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D44" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2004</v>
+        <v>2871</v>
       </c>
       <c r="F44" s="14">
-        <v>2324.64</v>
+        <v>3330.3599999999997</v>
       </c>
       <c r="G44" s="14">
-        <v>6.8480894687791238</v>
+        <v>9.8108108108108105</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-922.36363636363603</v>
+        <v>-55.363636363636033</v>
       </c>
       <c r="J44" s="16">
-        <v>2556</v>
+        <v>2788</v>
       </c>
       <c r="K44" s="13">
-        <v>2964.9599999999996</v>
+        <v>3234.08</v>
       </c>
       <c r="L44" s="14">
-        <v>14.923566878980894</v>
+        <v>16.278131634819534</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>843.27272727272748</v>
+        <v>1075.2727272727275</v>
       </c>
       <c r="O44" s="16">
-        <v>397</v>
+        <v>231</v>
       </c>
       <c r="P44" s="17">
-        <v>460.52</v>
+        <v>267.95999999999998</v>
       </c>
       <c r="Q44" s="14">
-        <v>11.61436170212766</v>
+        <v>6.7579787234042561</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>-115.72727272727275</v>
+        <v>-452.63636363636363</v>
       </c>
       <c r="T44" s="18">
-        <v>1025</v>
+        <v>870</v>
       </c>
       <c r="U44" s="17">
-        <v>1189</v>
+        <v>1009.1999999999999</v>
       </c>
       <c r="V44" s="14">
-        <v>12.123655913978494</v>
+        <v>10.290322580645162</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-243.18181818181824</v>
+        <v>-398.18181818181824</v>
       </c>
       <c r="Y44" s="18">
-        <v>433</v>
+        <v>341</v>
       </c>
       <c r="Z44" s="17">
-        <v>502.28</v>
+        <v>395.55999999999995</v>
       </c>
       <c r="AA44" s="14">
-        <v>14.274725274725277</v>
+        <v>12.668730650154796</v>
       </c>
       <c r="AB44" s="16">
-        <v>667.33333333333326</v>
+        <v>592.16666666666674</v>
       </c>
       <c r="AC44" s="15">
-        <v>-21.999999999999943</v>
+        <v>-62.750000000000057</v>
       </c>
       <c r="AD44" s="19">
-        <v>6415</v>
+        <v>7101</v>
       </c>
       <c r="AE44" s="20">
-        <v>7441.4</v>
+        <v>8237.16</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5854,91 +5853,91 @@
         <v>132152</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D45" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3171</v>
+        <v>3241</v>
       </c>
       <c r="F45" s="14">
-        <v>3678.3599999999997</v>
+        <v>3759.56</v>
       </c>
       <c r="G45" s="14">
-        <v>8.2305332704105716</v>
+        <v>8.4122227465785748</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-681.72727272727252</v>
+        <v>-611.72727272727252</v>
       </c>
       <c r="J45" s="16">
-        <v>4717</v>
+        <v>2488</v>
       </c>
       <c r="K45" s="13">
-        <v>5471.7199999999993</v>
+        <v>2886.08</v>
       </c>
       <c r="L45" s="14">
-        <v>19.188979289940828</v>
+        <v>10.121301775147929</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>2258.818181818182</v>
+        <v>29.818181818181984</v>
       </c>
       <c r="O45" s="16">
-        <v>675</v>
+        <v>330</v>
       </c>
       <c r="P45" s="17">
-        <v>783</v>
+        <v>382.79999999999995</v>
       </c>
       <c r="Q45" s="14">
-        <v>13.270777479892761</v>
+        <v>6.487935656836461</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>-87.954545454545496</v>
+        <v>-687.27272727272737</v>
       </c>
       <c r="T45" s="18">
-        <v>1330</v>
+        <v>1134</v>
       </c>
       <c r="U45" s="17">
-        <v>1542.8</v>
+        <v>1315.4399999999998</v>
       </c>
       <c r="V45" s="14">
-        <v>11.565217391304348</v>
+        <v>9.8608695652173921</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-395</v>
+        <v>-591</v>
       </c>
       <c r="Y45" s="18">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="Z45" s="17">
-        <v>390.91999999999996</v>
+        <v>295.79999999999995</v>
       </c>
       <c r="AA45" s="14">
-        <v>9.65923566878981</v>
+        <v>9.1343283582089541</v>
       </c>
       <c r="AB45" s="16">
-        <v>767.55555555555543</v>
+        <v>614.16666666666674</v>
       </c>
       <c r="AC45" s="15">
-        <v>-186.33333333333326</v>
+        <v>-163.75000000000006</v>
       </c>
       <c r="AD45" s="19">
-        <v>10230</v>
+        <v>7448</v>
       </c>
       <c r="AE45" s="20">
-        <v>11866.8</v>
+        <v>8639.68</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5967,91 +5966,91 @@
         <v>132153</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2473</v>
+        <v>1985</v>
       </c>
       <c r="F46" s="14">
-        <v>2868.68</v>
+        <v>2302.6</v>
       </c>
       <c r="G46" s="14">
-        <v>9.5785211267605632</v>
+        <v>7.688380281690141</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>-108.81818181818198</v>
+        <v>-596.81818181818198</v>
       </c>
       <c r="J46" s="16">
-        <v>5140</v>
+        <v>3851</v>
       </c>
       <c r="K46" s="13">
-        <v>5962.4</v>
+        <v>4467.16</v>
       </c>
       <c r="L46" s="14">
-        <v>28.483627204030224</v>
+        <v>21.340554156171283</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>3335.454545454545</v>
+        <v>2046.4545454545453</v>
       </c>
       <c r="O46" s="16">
-        <v>567</v>
+        <v>364</v>
       </c>
       <c r="P46" s="17">
-        <v>657.71999999999991</v>
+        <v>422.23999999999995</v>
       </c>
       <c r="Q46" s="14">
-        <v>15.175182481751824</v>
+        <v>9.7420924574209238</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>6.5454545454545041</v>
+        <v>-383.27272727272737</v>
       </c>
       <c r="T46" s="18">
-        <v>458</v>
+        <v>599</v>
       </c>
       <c r="U46" s="17">
-        <v>531.28</v>
+        <v>694.83999999999992</v>
       </c>
       <c r="V46" s="14">
-        <v>8.09967845659164</v>
+        <v>10.593247588424438</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>-390.18181818181824</v>
+        <v>-249.18181818181824</v>
       </c>
       <c r="Y46" s="18">
-        <v>260</v>
+        <v>146</v>
       </c>
       <c r="Z46" s="17">
-        <v>301.59999999999997</v>
+        <v>169.35999999999999</v>
       </c>
       <c r="AA46" s="14">
-        <v>8.7313432835820901</v>
+        <v>5.8205980066445191</v>
       </c>
       <c r="AB46" s="16">
-        <v>655.11111111111109</v>
+        <v>551.83333333333326</v>
       </c>
       <c r="AC46" s="15">
-        <v>-186.66666666666663</v>
+        <v>-230.24999999999994</v>
       </c>
       <c r="AD46" s="19">
-        <v>8898</v>
+        <v>6945</v>
       </c>
       <c r="AE46" s="20">
-        <v>10321.679999999998</v>
+        <v>8056.2</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6080,7 +6079,7 @@
         <v>134000</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" s="12">
         <v>18</v>
@@ -6099,19 +6098,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K47" s="13">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="L47" s="14">
-        <v>6.875</v>
+        <v>4.125</v>
       </c>
       <c r="M47" s="30">
         <v>32</v>
       </c>
       <c r="N47" s="15">
-        <v>-4.5454545454545467</v>
+        <v>-8.5454545454545467</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6129,19 +6128,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U47" s="17">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="V47" s="14">
-        <v>3.3000000000000003</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-10.636363636363637</v>
+        <v>-11.636363636363637</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6159,10 +6158,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE47" s="20">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6191,7 +6190,7 @@
         <v>134001</v>
       </c>
       <c r="C48" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D48" s="12">
         <v>18</v>
@@ -6210,19 +6209,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K48" s="13">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="L48" s="14">
-        <v>26.888888888888886</v>
+        <v>24.444444444444443</v>
       </c>
       <c r="M48" s="30">
         <v>9</v>
       </c>
       <c r="N48" s="15">
-        <v>6.9090909090909092</v>
+        <v>5.9090909090909092</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6270,10 +6269,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE48" s="20">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6302,91 +6301,91 @@
         <v>140230</v>
       </c>
       <c r="C49" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D49" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>731</v>
+        <v>478</v>
       </c>
       <c r="F49" s="14">
-        <v>847.95999999999992</v>
+        <v>554.48</v>
       </c>
       <c r="G49" s="14">
-        <v>13.000808407437349</v>
+        <v>8.5012126111560224</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>168.72727272727275</v>
+        <v>-84.272727272727252</v>
       </c>
       <c r="J49" s="16">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="K49" s="13">
-        <v>440.79999999999995</v>
+        <v>495.32</v>
       </c>
       <c r="L49" s="14">
-        <v>6.7802108678021087</v>
+        <v>7.6188158961881589</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>-180.4545454545455</v>
+        <v>-133.4545454545455</v>
       </c>
       <c r="O49" s="16">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P49" s="17">
-        <v>45.239999999999995</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="14">
-        <v>7.6607142857142856</v>
+        <v>0</v>
       </c>
       <c r="R49" s="16">
         <v>112</v>
       </c>
       <c r="S49" s="15">
-        <v>-37.36363636363636</v>
+        <v>-101.81818181818181</v>
       </c>
       <c r="T49" s="18">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="U49" s="17">
-        <v>135.72</v>
+        <v>100.91999999999999</v>
       </c>
       <c r="V49" s="14">
-        <v>11.094827586206897</v>
+        <v>8.25</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>-41.181818181818187</v>
+        <v>-71.181818181818187</v>
       </c>
       <c r="Y49" s="18">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="Z49" s="17">
-        <v>87</v>
+        <v>73.08</v>
       </c>
       <c r="AA49" s="14">
-        <v>14.0625</v>
+        <v>13.03448275862069</v>
       </c>
       <c r="AB49" s="16">
-        <v>117.33333333333333</v>
+        <v>106.33333333333333</v>
       </c>
       <c r="AC49" s="15">
-        <v>-5</v>
+        <v>-9.5</v>
       </c>
       <c r="AD49" s="19">
-        <v>1342</v>
+        <v>1055</v>
       </c>
       <c r="AE49" s="20">
-        <v>1556.7199999999998</v>
+        <v>1223.8</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6415,91 +6414,91 @@
         <v>140231</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>2090</v>
+        <v>306</v>
       </c>
       <c r="F50" s="14">
-        <v>2424.3999999999996</v>
+        <v>354.96</v>
       </c>
       <c r="G50" s="14">
-        <v>8.199001426533524</v>
+        <v>1.2004279600570613</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-459.09090909090901</v>
+        <v>-2243.090909090909</v>
       </c>
       <c r="J50" s="16">
-        <v>1644</v>
+        <v>4125</v>
       </c>
       <c r="K50" s="13">
-        <v>1907.04</v>
+        <v>4785</v>
       </c>
       <c r="L50" s="14">
-        <v>10.114093959731544</v>
+        <v>25.377516778523493</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>18.545454545454731</v>
+        <v>2499.545454545455</v>
       </c>
       <c r="O50" s="16">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="P50" s="17">
-        <v>294.64</v>
+        <v>95.11999999999999</v>
       </c>
       <c r="Q50" s="14">
-        <v>11.641666666666667</v>
+        <v>3.7583333333333337</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>-73.272727272727252</v>
+        <v>-354.36363636363632</v>
       </c>
       <c r="T50" s="18">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="U50" s="17">
-        <v>0</v>
+        <v>568.4</v>
       </c>
       <c r="V50" s="14">
-        <v>0</v>
+        <v>6.1284820920977827</v>
       </c>
       <c r="W50" s="16">
         <v>1759</v>
       </c>
       <c r="X50" s="15">
-        <v>-1199.3181818181818</v>
+        <v>-709.31818181818176</v>
       </c>
       <c r="Y50" s="18">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="Z50" s="17">
-        <v>154.28</v>
+        <v>129.91999999999999</v>
       </c>
       <c r="AA50" s="14">
-        <v>9.5760000000000005</v>
+        <v>9.9555555555555557</v>
       </c>
       <c r="AB50" s="16">
-        <v>305.55555555555554</v>
+        <v>247.5</v>
       </c>
       <c r="AC50" s="15">
-        <v>-75.333333333333314</v>
+        <v>-56.75</v>
       </c>
       <c r="AD50" s="19">
-        <v>4121</v>
+        <v>5115</v>
       </c>
       <c r="AE50" s="20">
-        <v>4780.3599999999997</v>
+        <v>5933.4</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6531,46 +6530,46 @@
         <v>140232</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D51" s="12">
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>929</v>
+        <v>384</v>
       </c>
       <c r="F51" s="14">
-        <v>1077.6399999999999</v>
+        <v>445.43999999999994</v>
       </c>
       <c r="G51" s="14">
-        <v>16.080251770259636</v>
+        <v>6.6467348544453184</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>351.27272727272725</v>
+        <v>-193.72727272727275</v>
       </c>
       <c r="J51" s="16">
-        <v>3148</v>
+        <v>2431</v>
       </c>
       <c r="K51" s="13">
-        <v>3651.68</v>
+        <v>2819.9599999999996</v>
       </c>
       <c r="L51" s="14">
-        <v>70.669387755102036</v>
+        <v>54.573469387755104</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>2702.5454545454545</v>
+        <v>1985.5454545454545</v>
       </c>
       <c r="O51" s="16">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="P51" s="17">
-        <v>388.59999999999997</v>
+        <v>269.12</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
@@ -6579,43 +6578,43 @@
         <v>0</v>
       </c>
       <c r="S51" s="15">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="T51" s="18">
-        <v>38</v>
+        <v>530</v>
       </c>
       <c r="U51" s="17">
-        <v>44.08</v>
+        <v>614.79999999999995</v>
       </c>
       <c r="V51" s="14">
-        <v>1.5539033457249072</v>
+        <v>21.6728624535316</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>-328.81818181818181</v>
+        <v>163.18181818181819</v>
       </c>
       <c r="Y51" s="18">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="Z51" s="17">
-        <v>142.67999999999998</v>
+        <v>128.76</v>
       </c>
       <c r="AA51" s="14">
-        <v>0</v>
+        <v>28.340425531914899</v>
       </c>
       <c r="AB51" s="16">
-        <v>105.11111111111111</v>
+        <v>86.166666666666657</v>
       </c>
       <c r="AC51" s="15">
-        <v>51.333333333333329</v>
+        <v>52.250000000000007</v>
       </c>
       <c r="AD51" s="19">
-        <v>4573</v>
+        <v>3688</v>
       </c>
       <c r="AE51" s="20">
-        <v>5304.6799999999994</v>
+        <v>4278.08</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6648,40 +6647,40 @@
         <v>150360</v>
       </c>
       <c r="C52" s="29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" s="12">
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>3646</v>
+        <v>3709</v>
       </c>
       <c r="F52" s="14">
-        <v>2953.26</v>
+        <v>3004.2900000000004</v>
       </c>
       <c r="G52" s="14">
-        <v>30.314436885865458</v>
+        <v>30.838246409674984</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>2443.272727272727</v>
+        <v>2506.272727272727</v>
       </c>
       <c r="J52" s="16">
-        <v>1101</v>
+        <v>175</v>
       </c>
       <c r="K52" s="13">
-        <v>891.81000000000006</v>
+        <v>141.75</v>
       </c>
       <c r="L52" s="14">
-        <v>12.511363636363637</v>
+        <v>1.9886363636363635</v>
       </c>
       <c r="M52" s="30">
         <v>1936</v>
       </c>
       <c r="N52" s="15">
-        <v>221</v>
+        <v>-705</v>
       </c>
       <c r="O52" s="16">
         <v>0</v>
@@ -6696,22 +6695,22 @@
         <v>498</v>
       </c>
       <c r="S52" s="15">
-        <v>-339.54545454545456</v>
+        <v>-452.72727272727275</v>
       </c>
       <c r="T52" s="18">
-        <v>56</v>
+        <v>563</v>
       </c>
       <c r="U52" s="17">
-        <v>45.36</v>
+        <v>456.03000000000003</v>
       </c>
       <c r="V52" s="14">
-        <v>1.3673695893451721</v>
+        <v>13.746947835738069</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-558.31818181818176</v>
+        <v>-51.318181818181756</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6723,16 +6722,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>56.222222222222214</v>
+        <v>42.166666666666671</v>
       </c>
       <c r="AC52" s="15">
-        <v>-38.333333333333329</v>
+        <v>-28.750000000000004</v>
       </c>
       <c r="AD52" s="19">
-        <v>4803</v>
+        <v>4447</v>
       </c>
       <c r="AE52" s="20">
-        <v>3890.4300000000003</v>
+        <v>3602.07</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6761,91 +6760,91 @@
         <v>150361</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="12">
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1313</v>
+        <v>1998</v>
       </c>
       <c r="F53" s="14">
-        <v>1063.53</v>
+        <v>1618.38</v>
       </c>
       <c r="G53" s="14">
-        <v>5.6253164556962023</v>
+        <v>8.5600778967867583</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>-1021.090909090909</v>
+        <v>-336.09090909090901</v>
       </c>
       <c r="J53" s="16">
-        <v>4441</v>
+        <v>2216</v>
       </c>
       <c r="K53" s="13">
-        <v>3597.21</v>
+        <v>1794.96</v>
       </c>
       <c r="L53" s="14">
-        <v>30.772283464566925</v>
+        <v>15.354960629921257</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>2997.8181818181815</v>
+        <v>772.81818181818153</v>
       </c>
       <c r="O53" s="16">
-        <v>262</v>
+        <v>133</v>
       </c>
       <c r="P53" s="17">
-        <v>212.22000000000003</v>
+        <v>107.73</v>
       </c>
       <c r="Q53" s="14">
-        <v>6.5277463193657974</v>
+        <v>3.3137032842582101</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-340.04545454545462</v>
+        <v>-669.72727272727275</v>
       </c>
       <c r="T53" s="18">
-        <v>622</v>
+        <v>851</v>
       </c>
       <c r="U53" s="17">
-        <v>503.82000000000005</v>
+        <v>689.31000000000006</v>
       </c>
       <c r="V53" s="14">
-        <v>8.2883101150817691</v>
+        <v>11.339794064203513</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-503.68181818181824</v>
+        <v>-274.68181818181824</v>
       </c>
       <c r="Y53" s="18">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="Z53" s="17">
-        <v>42.93</v>
+        <v>28.35</v>
       </c>
       <c r="AA53" s="14">
-        <v>5.6785714285714279</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="AB53" s="16">
-        <v>205.33333333333334</v>
+        <v>165</v>
       </c>
       <c r="AC53" s="15">
-        <v>-87</v>
+        <v>-77.5</v>
       </c>
       <c r="AD53" s="19">
-        <v>6691</v>
+        <v>5233</v>
       </c>
       <c r="AE53" s="20">
-        <v>5419.71</v>
+        <v>4238.7300000000005</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6874,91 +6873,91 @@
         <v>150362</v>
       </c>
       <c r="C54" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" s="12">
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1926</v>
+        <v>1563</v>
       </c>
       <c r="F54" s="14">
-        <v>1560.0600000000002</v>
+        <v>1266.03</v>
       </c>
       <c r="G54" s="14">
-        <v>12.3102847181871</v>
+        <v>9.9901220220801843</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>361.45454545454527</v>
+        <v>-1.5454545454547315</v>
       </c>
       <c r="J54" s="16">
-        <v>5992</v>
+        <v>5744</v>
       </c>
       <c r="K54" s="13">
-        <v>4853.5200000000004</v>
+        <v>4652.6400000000003</v>
       </c>
       <c r="L54" s="14">
-        <v>75.500572737686142</v>
+        <v>72.375715922107673</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>5198.363636363636</v>
+        <v>4950.363636363636</v>
       </c>
       <c r="O54" s="16">
-        <v>332</v>
+        <v>246</v>
       </c>
       <c r="P54" s="17">
-        <v>268.92</v>
+        <v>199.26000000000002</v>
       </c>
       <c r="Q54" s="14">
-        <v>21.35672514619883</v>
+        <v>15.824561403508772</v>
       </c>
       <c r="R54" s="16">
         <v>342</v>
       </c>
       <c r="S54" s="15">
-        <v>98.818181818181813</v>
+        <v>-64.909090909090878</v>
       </c>
       <c r="T54" s="18">
-        <v>761</v>
+        <v>611</v>
       </c>
       <c r="U54" s="17">
-        <v>616.41000000000008</v>
+        <v>494.91</v>
       </c>
       <c r="V54" s="14">
-        <v>27.090614886731391</v>
+        <v>21.750809061488674</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>339.63636363636363</v>
+        <v>189.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="Z54" s="17">
-        <v>136.89000000000001</v>
+        <v>123.93</v>
       </c>
       <c r="AA54" s="14">
-        <v>15.84375</v>
+        <v>18</v>
       </c>
       <c r="AB54" s="16">
-        <v>234.66666666666666</v>
+        <v>187</v>
       </c>
       <c r="AC54" s="15">
-        <v>9</v>
+        <v>25.5</v>
       </c>
       <c r="AD54" s="19">
-        <v>9180</v>
+        <v>8317</v>
       </c>
       <c r="AE54" s="20">
-        <v>7435.8</v>
+        <v>6736.77</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6987,91 +6986,91 @@
         <v>150363</v>
       </c>
       <c r="C55" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D55" s="12">
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>4213</v>
+        <v>3897</v>
       </c>
       <c r="F55" s="14">
-        <v>3412.53</v>
+        <v>3156.57</v>
       </c>
       <c r="G55" s="14">
-        <v>34.025697503671076</v>
+        <v>31.473568281938327</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>2974.818181818182</v>
+        <v>2658.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>9177</v>
+        <v>7232</v>
       </c>
       <c r="K55" s="13">
-        <v>7433.3700000000008</v>
+        <v>5857.92</v>
       </c>
       <c r="L55" s="14">
-        <v>103.2705882352941</v>
+        <v>81.383120204603571</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>8288.363636363636</v>
+        <v>6343.363636363636</v>
       </c>
       <c r="O55" s="16">
-        <v>296</v>
+        <v>203</v>
       </c>
       <c r="P55" s="17">
-        <v>239.76000000000002</v>
+        <v>164.43</v>
       </c>
       <c r="Q55" s="14">
-        <v>14.471111111111112</v>
+        <v>9.9244444444444451</v>
       </c>
       <c r="R55" s="16">
         <v>449.99999999999994</v>
       </c>
       <c r="S55" s="15">
-        <v>-10.818181818181813</v>
+        <v>-206.09090909090907</v>
       </c>
       <c r="T55" s="18">
-        <v>401</v>
+        <v>575</v>
       </c>
       <c r="U55" s="17">
-        <v>324.81</v>
+        <v>465.75000000000006</v>
       </c>
       <c r="V55" s="14">
-        <v>12.442877291960508</v>
+        <v>17.842031029619182</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>-82.409090909090878</v>
+        <v>91.590909090909122</v>
       </c>
       <c r="Y55" s="18">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="Z55" s="17">
-        <v>148.23000000000002</v>
+        <v>137.70000000000002</v>
       </c>
       <c r="AA55" s="14">
-        <v>17.15625</v>
+        <v>20</v>
       </c>
       <c r="AB55" s="16">
-        <v>234.66666666666666</v>
+        <v>187</v>
       </c>
       <c r="AC55" s="15">
-        <v>23</v>
+        <v>42.5</v>
       </c>
       <c r="AD55" s="19">
-        <v>14270</v>
+        <v>12077</v>
       </c>
       <c r="AE55" s="20">
-        <v>11558.7</v>
+        <v>9782.3700000000008</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7100,70 +7099,70 @@
         <v>151500</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D56" s="12">
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>210</v>
+        <v>546</v>
       </c>
       <c r="F56" s="14">
-        <v>550.20000000000005</v>
+        <v>1430.52</v>
       </c>
       <c r="G56" s="14">
-        <v>9.2585170340681362</v>
+        <v>24.072144288577153</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>-16.818181818181841</v>
+        <v>319.18181818181813</v>
       </c>
       <c r="J56" s="32">
-        <v>703</v>
+        <v>253</v>
       </c>
       <c r="K56" s="13">
-        <v>1841.8600000000001</v>
+        <v>662.86</v>
       </c>
       <c r="L56" s="14">
-        <v>34.755056179775281</v>
+        <v>12.507865168539325</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>500.72727272727275</v>
+        <v>50.727272727272748</v>
       </c>
       <c r="O56" s="32">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P56" s="17">
-        <v>73.36</v>
+        <v>2.62</v>
       </c>
       <c r="Q56" s="14">
-        <v>20.533333333333335</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="R56" s="16">
         <v>30</v>
       </c>
       <c r="S56" s="15">
-        <v>7.5454545454545467</v>
+        <v>-26.27272727272727</v>
       </c>
       <c r="T56" s="18">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="U56" s="17">
-        <v>280.34000000000003</v>
+        <v>193.88</v>
       </c>
       <c r="V56" s="14">
-        <v>12.521276595744682</v>
+        <v>8.6595744680851077</v>
       </c>
       <c r="W56" s="16">
         <v>188</v>
       </c>
       <c r="X56" s="15">
-        <v>-21.181818181818187</v>
+        <v>-54.181818181818187</v>
       </c>
       <c r="Y56" s="18">
         <v>58</v>
@@ -7172,19 +7171,19 @@
         <v>151.96</v>
       </c>
       <c r="AA56" s="14">
-        <v>29</v>
+        <v>26.76923076923077</v>
       </c>
       <c r="AB56" s="16">
-        <v>44</v>
+        <v>47.666666666666664</v>
       </c>
       <c r="AC56" s="15">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="AD56" s="19">
-        <v>1106</v>
+        <v>932</v>
       </c>
       <c r="AE56" s="20">
-        <v>2897.7200000000003</v>
+        <v>2441.84</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7213,70 +7212,70 @@
         <v>151501</v>
       </c>
       <c r="C57" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D57" s="12">
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="F57" s="14">
-        <v>400.86</v>
+        <v>751.94</v>
       </c>
       <c r="G57" s="14">
-        <v>3.7029702970297027</v>
+        <v>6.9460946094609461</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-260.18181818181819</v>
+        <v>-126.18181818181819</v>
       </c>
       <c r="J57" s="32">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="K57" s="13">
-        <v>814.82</v>
+        <v>678.58</v>
       </c>
       <c r="L57" s="14">
-        <v>7.9558139534883727</v>
+        <v>6.6255813953488376</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>-79.909090909090878</v>
+        <v>-131.90909090909088</v>
       </c>
       <c r="O57" s="32">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="P57" s="17">
-        <v>138.86000000000001</v>
+        <v>49.78</v>
       </c>
       <c r="Q57" s="14">
-        <v>16.898550724637683</v>
+        <v>6.0579710144927539</v>
       </c>
       <c r="R57" s="16">
         <v>69</v>
       </c>
       <c r="S57" s="15">
-        <v>5.9545454545454533</v>
+        <v>-43.727272727272727</v>
       </c>
       <c r="T57" s="18">
-        <v>171</v>
+        <v>51</v>
       </c>
       <c r="U57" s="17">
-        <v>448.02000000000004</v>
+        <v>133.62</v>
       </c>
       <c r="V57" s="14">
-        <v>12.174757281553399</v>
+        <v>3.6310679611650487</v>
       </c>
       <c r="W57" s="16">
         <v>309</v>
       </c>
       <c r="X57" s="15">
-        <v>-39.681818181818187</v>
+        <v>-159.68181818181819</v>
       </c>
       <c r="Y57" s="18">
         <v>68</v>
@@ -7294,10 +7293,10 @@
         <v>28</v>
       </c>
       <c r="AD57" s="19">
-        <v>756</v>
+        <v>684</v>
       </c>
       <c r="AE57" s="20">
-        <v>1980.72</v>
+        <v>1792.0800000000002</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7326,70 +7325,70 @@
         <v>151502</v>
       </c>
       <c r="C58" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D58" s="12">
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F58" s="14">
-        <v>369.42</v>
+        <v>413.96000000000004</v>
       </c>
       <c r="G58" s="14">
-        <v>7.3507109004739331</v>
+        <v>8.2369668246445489</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>-50.818181818181841</v>
+        <v>-33.818181818181841</v>
       </c>
       <c r="J58" s="32">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="K58" s="13">
-        <v>20.96</v>
+        <v>382.52000000000004</v>
       </c>
       <c r="L58" s="14">
-        <v>0.43243243243243246</v>
+        <v>7.8918918918918921</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>-177</v>
+        <v>-39</v>
       </c>
       <c r="O58" s="32">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="P58" s="17">
-        <v>117.9</v>
+        <v>81.22</v>
       </c>
       <c r="Q58" s="14">
-        <v>22</v>
+        <v>15.155555555555555</v>
       </c>
       <c r="R58" s="16">
         <v>45</v>
       </c>
       <c r="S58" s="15">
-        <v>14.31818181818182</v>
+        <v>-9.9090909090909065</v>
       </c>
       <c r="T58" s="18">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="U58" s="17">
-        <v>112.66000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="V58" s="14">
-        <v>8.5225225225225216</v>
+        <v>0.79279279279279269</v>
       </c>
       <c r="W58" s="16">
         <v>111</v>
       </c>
       <c r="X58" s="15">
-        <v>-32.681818181818187</v>
+        <v>-71.681818181818187</v>
       </c>
       <c r="Y58" s="18">
         <v>48</v>
@@ -7398,19 +7397,19 @@
         <v>125.76</v>
       </c>
       <c r="AA58" s="14">
-        <v>20.571428571428569</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="AB58" s="16">
-        <v>51.333333333333336</v>
+        <v>49.5</v>
       </c>
       <c r="AC58" s="15">
-        <v>13</v>
+        <v>14.25</v>
       </c>
       <c r="AD58" s="19">
-        <v>285</v>
+        <v>387</v>
       </c>
       <c r="AE58" s="20">
-        <v>746.7</v>
+        <v>1013.94</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7442,70 +7441,70 @@
         <v>151503</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D59" s="12">
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="F59" s="14">
-        <v>141.48000000000002</v>
+        <v>351.08000000000004</v>
       </c>
       <c r="G59" s="14">
-        <v>2.3339882121807465</v>
+        <v>5.7917485265225936</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-177.36363636363637</v>
+        <v>-97.363636363636374</v>
       </c>
       <c r="J59" s="32">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="K59" s="13">
-        <v>13.100000000000001</v>
+        <v>285.58</v>
       </c>
       <c r="L59" s="14">
-        <v>0.2722772277227723</v>
+        <v>5.935643564356436</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>-178.63636363636363</v>
+        <v>-74.636363636363626</v>
       </c>
       <c r="O59" s="32">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P59" s="17">
-        <v>36.68</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="14">
-        <v>11.846153846153845</v>
+        <v>0</v>
       </c>
       <c r="R59" s="16">
         <v>26</v>
       </c>
       <c r="S59" s="15">
-        <v>-3.7272727272727266</v>
+        <v>-23.636363636363637</v>
       </c>
       <c r="T59" s="18">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="U59" s="17">
-        <v>306.54000000000002</v>
+        <v>196.5</v>
       </c>
       <c r="V59" s="14">
-        <v>13.199999999999998</v>
+        <v>8.4615384615384599</v>
       </c>
       <c r="W59" s="16">
         <v>195.00000000000003</v>
       </c>
       <c r="X59" s="15">
-        <v>-15.954545454545467</v>
+        <v>-57.954545454545467</v>
       </c>
       <c r="Y59" s="18">
         <v>56</v>
@@ -7514,19 +7513,19 @@
         <v>146.72</v>
       </c>
       <c r="AA59" s="14">
-        <v>42</v>
+        <v>44.8</v>
       </c>
       <c r="AB59" s="16">
-        <v>29.333333333333332</v>
+        <v>27.5</v>
       </c>
       <c r="AC59" s="15">
-        <v>36</v>
+        <v>37.25</v>
       </c>
       <c r="AD59" s="19">
-        <v>246</v>
+        <v>374</v>
       </c>
       <c r="AE59" s="20">
-        <v>644.52</v>
+        <v>979.88</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7600,10 +7599,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7633,17 +7632,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>122597.34999999999</v>
+        <v>156630.57999999996</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>29.545092617914708</v>
+        <v>36.631785406215464</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7681,11 +7680,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>209920.82999999993</v>
+        <v>191450.65999999997</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>50.589432518561992</v>
+        <v>44.77528904635556</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7723,11 +7722,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>21108.940000000002</v>
+        <v>12819.699999999999</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.0871049608005761</v>
+        <v>2.9981916645655047</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7765,11 +7764,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>44404.19000000001</v>
+        <v>52403.520000000011</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>10.701095139278967</v>
+        <v>12.255809173217138</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7807,11 +7806,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>16785.849999999999</v>
+        <v>14011.010000000002</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>4.0452709044724333</v>
+        <v>3.2768078343599258</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7843,19 +7842,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>414949.9599999999</v>
-      </c>
-      <c r="E67" s="69">
+        <v>427581.07000000012</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7955,17 +7954,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>96518</v>
+        <v>117915</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>31.477640367355459</v>
+        <v>36.792788407533607</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8002,11 +8001,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>154780</v>
+        <v>147191</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>50.478762262575664</v>
+        <v>45.927721820746122</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8044,11 +8043,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>15642</v>
+        <v>9711</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.1013619286161553</v>
+        <v>3.0301044669936719</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8086,11 +8085,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>28442</v>
+        <v>36378</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>9.2758557712377367</v>
+        <v>11.350956678024488</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8128,11 +8127,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>11242</v>
+        <v>9289</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>3.6663796702149862</v>
+        <v>2.8984286267021129</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8164,19 +8163,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>306624</v>
-      </c>
-      <c r="E75" s="69">
+        <v>320484</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8723,17 +8722,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8742,6 +8730,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7DB67-4F53-4813-B8A3-42115672C7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62468858-632B-4EB1-9912-1DD114D93E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1178,6 +1178,8 @@
       <sheetName val="INVENTARIO NACIONAL 15-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 16-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
+      <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1314,6 +1316,8 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1641,242 +1645,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2241,85 +2245,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>3205</v>
+        <v>3135</v>
       </c>
       <c r="F13" s="14">
-        <v>4358.8</v>
+        <v>4263.6000000000004</v>
       </c>
       <c r="G13" s="14">
-        <v>4.1130490579245169</v>
+        <v>4.0232164731960562</v>
       </c>
       <c r="H13" s="30">
         <v>17143</v>
       </c>
       <c r="I13" s="15">
-        <v>-4587.2727272727279</v>
+        <v>-4657.2727272727279</v>
       </c>
       <c r="J13" s="16">
-        <v>3188</v>
+        <v>4374</v>
       </c>
       <c r="K13" s="13">
-        <v>4335.68</v>
+        <v>5948.64</v>
       </c>
       <c r="L13" s="14">
-        <v>13.094846900672144</v>
+        <v>17.9663928304705</v>
       </c>
       <c r="M13" s="30">
         <v>5356</v>
       </c>
       <c r="N13" s="15">
-        <v>753.4545454545455</v>
+        <v>1939.4545454545455</v>
       </c>
       <c r="O13" s="16">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="P13" s="17">
-        <v>334.56</v>
+        <v>276.08000000000004</v>
       </c>
       <c r="Q13" s="14">
-        <v>6.2857142857142865</v>
+        <v>5.1869918699186996</v>
       </c>
       <c r="R13" s="16">
         <v>861</v>
       </c>
       <c r="S13" s="15">
-        <v>-536.72727272727263</v>
+        <v>-579.72727272727263</v>
       </c>
       <c r="T13" s="18">
-        <v>830</v>
+        <v>274</v>
       </c>
       <c r="U13" s="17">
-        <v>1128.8000000000002</v>
+        <v>372.64000000000004</v>
       </c>
       <c r="V13" s="14">
-        <v>15.293132328308207</v>
+        <v>5.0485762144053599</v>
       </c>
       <c r="W13" s="16">
         <v>1194</v>
       </c>
       <c r="X13" s="15">
-        <v>15.909090909090878</v>
+        <v>-540.09090909090912</v>
       </c>
       <c r="Y13" s="18">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="Z13" s="17">
-        <v>319.60000000000002</v>
+        <v>212.16000000000003</v>
       </c>
       <c r="AA13" s="14">
-        <v>8.2941176470588243</v>
+        <v>4.6620689655172418</v>
       </c>
       <c r="AB13" s="16">
-        <v>623.33333333333326</v>
+        <v>736.15384615384608</v>
       </c>
       <c r="AC13" s="15">
-        <v>-189.99999999999994</v>
+        <v>-345.92307692307691</v>
       </c>
       <c r="AD13" s="19">
-        <v>7704</v>
+        <v>8142</v>
       </c>
       <c r="AE13" s="20">
-        <v>10477.44</v>
+        <v>11073.12</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2415,25 +2419,25 @@
         <v>-22.18181818181818</v>
       </c>
       <c r="Y14" s="18">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="Z14" s="17">
-        <v>106.53</v>
+        <v>49.29</v>
       </c>
       <c r="AA14" s="14">
-        <v>26.8</v>
+        <v>6.1060606060606064</v>
       </c>
       <c r="AB14" s="16">
-        <v>55</v>
+        <v>111.69230769230768</v>
       </c>
       <c r="AC14" s="15">
-        <v>29.5</v>
+        <v>-45.153846153846146</v>
       </c>
       <c r="AD14" s="19">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="AE14" s="20">
-        <v>318</v>
+        <v>260.76</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2469,85 +2473,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>645</v>
+        <v>1774</v>
       </c>
       <c r="F15" s="14">
-        <v>1309.3499999999999</v>
+        <v>3601.22</v>
       </c>
       <c r="G15" s="14">
-        <v>2.0565217391304347</v>
+        <v>5.6562318840579708</v>
       </c>
       <c r="H15" s="30">
         <v>6900</v>
       </c>
       <c r="I15" s="15">
-        <v>-2491.363636363636</v>
+        <v>-1362.363636363636</v>
       </c>
       <c r="J15" s="16">
-        <v>2298</v>
+        <v>2566</v>
       </c>
       <c r="K15" s="13">
-        <v>4664.9399999999996</v>
+        <v>5208.9799999999996</v>
       </c>
       <c r="L15" s="14">
-        <v>16.745942365021531</v>
+        <v>18.698906922822129</v>
       </c>
       <c r="M15" s="30">
         <v>3019</v>
       </c>
       <c r="N15" s="15">
-        <v>925.72727272727275</v>
+        <v>1193.7272727272727</v>
       </c>
       <c r="O15" s="16">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="P15" s="17">
-        <v>308.55999999999995</v>
+        <v>292.32</v>
       </c>
       <c r="Q15" s="14">
-        <v>11.25925925925926</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="R15" s="16">
         <v>297</v>
       </c>
       <c r="S15" s="15">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="T15" s="18">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="U15" s="17">
-        <v>594.79</v>
+        <v>539.9799999999999</v>
       </c>
       <c r="V15" s="14">
-        <v>18.576368876080689</v>
+        <v>16.864553314121036</v>
       </c>
       <c r="W15" s="16">
         <v>347.00000000000006</v>
       </c>
       <c r="X15" s="15">
-        <v>56.409090909090878</v>
+        <v>29.409090909090878</v>
       </c>
       <c r="Y15" s="18">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="Z15" s="17">
-        <v>420.21</v>
+        <v>286.22999999999996</v>
       </c>
       <c r="AA15" s="14">
-        <v>35.485714285714295</v>
+        <v>14.209302325581396</v>
       </c>
       <c r="AB15" s="16">
-        <v>128.33333333333331</v>
+        <v>218.30769230769232</v>
       </c>
       <c r="AC15" s="15">
-        <v>119.50000000000001</v>
+        <v>-7.8461538461538396</v>
       </c>
       <c r="AD15" s="19">
-        <v>3595</v>
+        <v>4891</v>
       </c>
       <c r="AE15" s="20">
-        <v>7297.8499999999995</v>
+        <v>9928.73</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2582,34 +2586,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="F16" s="14">
-        <v>299.63</v>
+        <v>176.89</v>
       </c>
       <c r="G16" s="14">
-        <v>1.3070866141732282</v>
+        <v>0.77165354330708658</v>
       </c>
       <c r="H16" s="30">
         <v>1397</v>
       </c>
       <c r="I16" s="15">
-        <v>-552</v>
+        <v>-586</v>
       </c>
       <c r="J16" s="16">
-        <v>104</v>
+        <v>643</v>
       </c>
       <c r="K16" s="13">
-        <v>375.44</v>
+        <v>2321.23</v>
       </c>
       <c r="L16" s="14">
-        <v>4.1981651376146791</v>
+        <v>25.955963302752291</v>
       </c>
       <c r="M16" s="30">
         <v>545</v>
       </c>
       <c r="N16" s="15">
-        <v>-143.72727272727275</v>
+        <v>395.27272727272725</v>
       </c>
       <c r="O16" s="16">
         <v>0</v>
@@ -2642,25 +2646,25 @@
         <v>18.590909090909093</v>
       </c>
       <c r="Y16" s="18">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Z16" s="17">
-        <v>209.38</v>
+        <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>29</v>
+        <v>5.7017543859649118</v>
       </c>
       <c r="AB16" s="16">
-        <v>44</v>
+        <v>96.461538461538467</v>
       </c>
       <c r="AC16" s="15">
-        <v>28</v>
+        <v>-40.769230769230774</v>
       </c>
       <c r="AD16" s="19">
-        <v>297</v>
+        <v>769</v>
       </c>
       <c r="AE16" s="20">
-        <v>1072.17</v>
+        <v>2776.0899999999997</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2695,49 +2699,49 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>35.119999999999997</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
-        <v>0.52694610778443118</v>
+        <v>0</v>
       </c>
       <c r="H17" s="30">
         <v>167</v>
       </c>
       <c r="I17" s="15">
-        <v>-71.909090909090907</v>
+        <v>-75.909090909090907</v>
       </c>
       <c r="J17" s="16">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="K17" s="13">
-        <v>96.58</v>
+        <v>781.42</v>
       </c>
       <c r="L17" s="14">
-        <v>3.5072463768115942</v>
+        <v>28.376811594202898</v>
       </c>
       <c r="M17" s="30">
         <v>69</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.363636363636363</v>
+        <v>57.63636363636364</v>
       </c>
       <c r="O17" s="16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P17" s="17">
-        <v>114.13999999999999</v>
+        <v>96.58</v>
       </c>
       <c r="Q17" s="14">
-        <v>35.75</v>
+        <v>30.25</v>
       </c>
       <c r="R17" s="16">
         <v>8</v>
       </c>
       <c r="S17" s="15">
-        <v>5.7272727272727266</v>
+        <v>3.7272727272727266</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2761,19 +2765,19 @@
         <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>22</v>
+        <v>23.833333333333329</v>
       </c>
       <c r="AB17" s="16">
-        <v>11</v>
+        <v>10.153846153846155</v>
       </c>
       <c r="AC17" s="15">
-        <v>3.5</v>
+        <v>4.0769230769230758</v>
       </c>
       <c r="AD17" s="19">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="AE17" s="20">
-        <v>491.67999999999995</v>
+        <v>1123.8399999999999</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2808,85 +2812,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6120</v>
+        <v>8284</v>
       </c>
       <c r="F18" s="14">
-        <v>3855.6</v>
+        <v>5218.92</v>
       </c>
       <c r="G18" s="14">
-        <v>7.3755135579293345</v>
+        <v>9.9834565872363736</v>
       </c>
       <c r="H18" s="30">
         <v>18255</v>
       </c>
       <c r="I18" s="15">
-        <v>-2177.7272727272721</v>
+        <v>-13.727272727272066</v>
       </c>
       <c r="J18" s="16">
-        <v>9356</v>
+        <v>5047</v>
       </c>
       <c r="K18" s="13">
-        <v>5894.28</v>
+        <v>3179.61</v>
       </c>
       <c r="L18" s="14">
-        <v>29.744508670520229</v>
+        <v>16.045375722543351</v>
       </c>
       <c r="M18" s="30">
         <v>6920</v>
       </c>
       <c r="N18" s="15">
-        <v>6210.545454545454</v>
+        <v>1901.5454545454545</v>
       </c>
       <c r="O18" s="16">
-        <v>630</v>
+        <v>552</v>
       </c>
       <c r="P18" s="17">
-        <v>396.9</v>
+        <v>347.76</v>
       </c>
       <c r="Q18" s="14">
-        <v>9.5916955017301024</v>
+        <v>8.4041522491349472</v>
       </c>
       <c r="R18" s="16">
         <v>1445</v>
       </c>
       <c r="S18" s="15">
-        <v>-683.63636363636374</v>
+        <v>-761.63636363636374</v>
       </c>
       <c r="T18" s="18">
-        <v>1451</v>
+        <v>1290</v>
       </c>
       <c r="U18" s="17">
-        <v>914.13</v>
+        <v>812.7</v>
       </c>
       <c r="V18" s="14">
-        <v>8.2742353551062724</v>
+        <v>7.3561430793157072</v>
       </c>
       <c r="W18" s="16">
         <v>3858</v>
       </c>
       <c r="X18" s="15">
-        <v>-1179.4545454545455</v>
+        <v>-1340.4545454545455</v>
       </c>
       <c r="Y18" s="18">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="Z18" s="17">
-        <v>171.36</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="AA18" s="14">
-        <v>20.024539877300612</v>
+        <v>17.049180327868854</v>
       </c>
       <c r="AB18" s="16">
-        <v>298.83333333333337</v>
+        <v>309.69230769230768</v>
       </c>
       <c r="AC18" s="15">
-        <v>68.249999999999972</v>
+        <v>28.84615384615384</v>
       </c>
       <c r="AD18" s="19">
-        <v>17829</v>
+        <v>15413</v>
       </c>
       <c r="AE18" s="20">
-        <v>11232.27</v>
+        <v>9710.19</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2921,34 +2925,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>657</v>
+        <v>610</v>
       </c>
       <c r="F19" s="14">
-        <v>413.91</v>
+        <v>384.3</v>
       </c>
       <c r="G19" s="14">
-        <v>9.7333333333333361</v>
+        <v>9.0370370370370381</v>
       </c>
       <c r="H19" s="30">
         <v>1484.9999999999998</v>
       </c>
       <c r="I19" s="15">
-        <v>-17.999999999999886</v>
+        <v>-64.999999999999886</v>
       </c>
       <c r="J19" s="16">
-        <v>852</v>
+        <v>741</v>
       </c>
       <c r="K19" s="13">
-        <v>536.76</v>
+        <v>466.83</v>
       </c>
       <c r="L19" s="14">
-        <v>16.676156583629894</v>
+        <v>14.503558718861209</v>
       </c>
       <c r="M19" s="30">
         <v>1124</v>
       </c>
       <c r="N19" s="15">
-        <v>341.09090909090907</v>
+        <v>230.09090909090907</v>
       </c>
       <c r="O19" s="16">
         <v>41</v>
@@ -2966,40 +2970,40 @@
         <v>-44.454545454545453</v>
       </c>
       <c r="T19" s="18">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="U19" s="17">
-        <v>177.66</v>
+        <v>171.99</v>
       </c>
       <c r="V19" s="14">
-        <v>18.300884955752213</v>
+        <v>17.716814159292035</v>
       </c>
       <c r="W19" s="16">
         <v>339</v>
       </c>
       <c r="X19" s="15">
-        <v>50.863636363636374</v>
+        <v>41.863636363636374</v>
       </c>
       <c r="Y19" s="18">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="Z19" s="17">
-        <v>105.84</v>
+        <v>102.69</v>
       </c>
       <c r="AA19" s="14">
-        <v>14</v>
+        <v>14.033112582781458</v>
       </c>
       <c r="AB19" s="16">
-        <v>264</v>
+        <v>255.53846153846152</v>
       </c>
       <c r="AC19" s="15">
-        <v>-12</v>
+        <v>-11.230769230769226</v>
       </c>
       <c r="AD19" s="19">
-        <v>2000</v>
+        <v>1828</v>
       </c>
       <c r="AE19" s="20">
-        <v>1260</v>
+        <v>1151.6400000000001</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3034,85 +3038,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1440</v>
+        <v>1380</v>
       </c>
       <c r="F20" s="14">
-        <v>907.2</v>
+        <v>869.4</v>
       </c>
       <c r="G20" s="14">
-        <v>9.3866666666666667</v>
+        <v>8.9955555555555549</v>
       </c>
       <c r="H20" s="30">
         <v>3375</v>
       </c>
       <c r="I20" s="15">
-        <v>-94.090909090909008</v>
+        <v>-154.09090909090901</v>
       </c>
       <c r="J20" s="16">
-        <v>2429</v>
+        <v>1992</v>
       </c>
       <c r="K20" s="13">
-        <v>1530.27</v>
+        <v>1254.96</v>
       </c>
       <c r="L20" s="14">
-        <v>24.169154228855721</v>
+        <v>19.82089552238806</v>
       </c>
       <c r="M20" s="30">
         <v>2211</v>
       </c>
       <c r="N20" s="15">
-        <v>1424</v>
+        <v>987</v>
       </c>
       <c r="O20" s="16">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="P20" s="17">
-        <v>105.21</v>
+        <v>97.65</v>
       </c>
       <c r="Q20" s="14">
-        <v>13.168458781362007</v>
+        <v>12.222222222222223</v>
       </c>
       <c r="R20" s="16">
         <v>279</v>
       </c>
       <c r="S20" s="15">
-        <v>-86.636363636363626</v>
+        <v>-98.636363636363626</v>
       </c>
       <c r="T20" s="18">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="U20" s="17">
-        <v>383.04</v>
+        <v>366.03000000000003</v>
       </c>
       <c r="V20" s="14">
-        <v>11.41296928327645</v>
+        <v>10.906143344709898</v>
       </c>
       <c r="W20" s="16">
         <v>1172</v>
       </c>
       <c r="X20" s="15">
-        <v>-191.09090909090912</v>
+        <v>-218.09090909090912</v>
       </c>
       <c r="Y20" s="18">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="Z20" s="17">
-        <v>168.21</v>
+        <v>148.05000000000001</v>
       </c>
       <c r="AA20" s="14">
-        <v>18.101694915254239</v>
+        <v>16.078947368421051</v>
       </c>
       <c r="AB20" s="16">
-        <v>324.5</v>
+        <v>321.53846153846155</v>
       </c>
       <c r="AC20" s="15">
-        <v>45.75</v>
+        <v>15.769230769230774</v>
       </c>
       <c r="AD20" s="19">
-        <v>4911</v>
+        <v>4343</v>
       </c>
       <c r="AE20" s="20">
-        <v>3093.93</v>
+        <v>2736.09</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3147,85 +3151,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2790</v>
+        <v>2045</v>
       </c>
       <c r="F21" s="14">
-        <v>3041.1000000000004</v>
+        <v>2229.0500000000002</v>
       </c>
       <c r="G21" s="14">
-        <v>9.6176747101222198</v>
+        <v>7.0495142588530246</v>
       </c>
       <c r="H21" s="30">
         <v>6382</v>
       </c>
       <c r="I21" s="15">
-        <v>-110.90909090909054</v>
+        <v>-855.90909090909054</v>
       </c>
       <c r="J21" s="16">
-        <v>5247</v>
+        <v>4544</v>
       </c>
       <c r="K21" s="13">
-        <v>5719.2300000000005</v>
+        <v>4952.96</v>
       </c>
       <c r="L21" s="14">
-        <v>17.035714285714285</v>
+        <v>14.753246753246753</v>
       </c>
       <c r="M21" s="30">
         <v>6776</v>
       </c>
       <c r="N21" s="15">
-        <v>2167</v>
+        <v>1464</v>
       </c>
       <c r="O21" s="16">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="P21" s="17">
-        <v>179.85000000000002</v>
+        <v>163.5</v>
       </c>
       <c r="Q21" s="14">
-        <v>6.8880455407969645</v>
+        <v>6.2618595825426953</v>
       </c>
       <c r="R21" s="16">
         <v>527</v>
       </c>
       <c r="S21" s="15">
-        <v>-314.09090909090907</v>
+        <v>-329.09090909090907</v>
       </c>
       <c r="T21" s="18">
-        <v>1321</v>
+        <v>1201</v>
       </c>
       <c r="U21" s="17">
-        <v>1439.89</v>
+        <v>1309.0900000000001</v>
       </c>
       <c r="V21" s="14">
-        <v>14.032834379526799</v>
+        <v>12.758087880251086</v>
       </c>
       <c r="W21" s="16">
         <v>2071</v>
       </c>
       <c r="X21" s="15">
-        <v>-91.045454545454504</v>
+        <v>-211.0454545454545</v>
       </c>
       <c r="Y21" s="18">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="Z21" s="17">
-        <v>305.20000000000005</v>
+        <v>289.94</v>
       </c>
       <c r="AA21" s="14">
-        <v>13.023255813953488</v>
+        <v>13.3</v>
       </c>
       <c r="AB21" s="16">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="AC21" s="15">
-        <v>-42.5</v>
+        <v>-34</v>
       </c>
       <c r="AD21" s="19">
-        <v>9803</v>
+        <v>8206</v>
       </c>
       <c r="AE21" s="20">
-        <v>10685.27</v>
+        <v>8944.5400000000009</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3260,85 +3264,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1804</v>
+        <v>1706</v>
       </c>
       <c r="F22" s="14">
-        <v>1966.3600000000001</v>
+        <v>1859.5400000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>9.2534390300769402</v>
+        <v>8.7507577523898341</v>
       </c>
       <c r="H22" s="30">
         <v>4289</v>
       </c>
       <c r="I22" s="15">
-        <v>-145.54545454545473</v>
+        <v>-243.54545454545473</v>
       </c>
       <c r="J22" s="16">
-        <v>2635</v>
+        <v>2404</v>
       </c>
       <c r="K22" s="13">
-        <v>2872.15</v>
+        <v>2620.36</v>
       </c>
       <c r="L22" s="14">
-        <v>23.984278030616469</v>
+        <v>21.881671493587092</v>
       </c>
       <c r="M22" s="30">
         <v>2417</v>
       </c>
       <c r="N22" s="15">
-        <v>1536.3636363636365</v>
+        <v>1305.3636363636365</v>
       </c>
       <c r="O22" s="16">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="P22" s="17">
-        <v>158.05000000000001</v>
+        <v>144.97</v>
       </c>
       <c r="Q22" s="14">
-        <v>15.637254901960786</v>
+        <v>14.343137254901963</v>
       </c>
       <c r="R22" s="16">
         <v>203.99999999999997</v>
       </c>
       <c r="S22" s="15">
-        <v>-40.454545454545439</v>
+        <v>-52.454545454545439</v>
       </c>
       <c r="T22" s="18">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="U22" s="17">
-        <v>488.32000000000005</v>
+        <v>487.23</v>
       </c>
       <c r="V22" s="14">
-        <v>13.901269393511988</v>
+        <v>13.870239774330043</v>
       </c>
       <c r="W22" s="16">
         <v>709</v>
       </c>
       <c r="X22" s="15">
-        <v>-35.409090909090878</v>
+        <v>-36.409090909090878</v>
       </c>
       <c r="Y22" s="18">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Z22" s="17">
-        <v>158.05000000000001</v>
+        <v>155.87</v>
       </c>
       <c r="AA22" s="14">
-        <v>31.071428571428569</v>
+        <v>33.196428571428577</v>
       </c>
       <c r="AB22" s="16">
-        <v>102.66666666666667</v>
+        <v>94.769230769230759</v>
       </c>
       <c r="AC22" s="15">
-        <v>75</v>
+        <v>78.384615384615387</v>
       </c>
       <c r="AD22" s="19">
-        <v>5177</v>
+        <v>4833</v>
       </c>
       <c r="AE22" s="20">
-        <v>5642.93</v>
+        <v>5267.97</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3373,85 +3377,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>20091</v>
+        <v>19731</v>
       </c>
       <c r="F23" s="14">
-        <v>23305.559999999998</v>
+        <v>22887.96</v>
       </c>
       <c r="G23" s="14">
-        <v>11.725124015173622</v>
+        <v>11.515027721038809</v>
       </c>
       <c r="H23" s="30">
         <v>37697</v>
       </c>
       <c r="I23" s="15">
-        <v>2956</v>
+        <v>2596</v>
       </c>
       <c r="J23" s="16">
-        <v>10432</v>
+        <v>8542</v>
       </c>
       <c r="K23" s="13">
-        <v>12101.119999999999</v>
+        <v>9908.7199999999993</v>
       </c>
       <c r="L23" s="14">
-        <v>11.993937810295272</v>
+        <v>9.8209563626861769</v>
       </c>
       <c r="M23" s="30">
         <v>19135</v>
       </c>
       <c r="N23" s="15">
-        <v>1734.2727272727279</v>
+        <v>-155.72727272727207</v>
       </c>
       <c r="O23" s="16">
-        <v>1199</v>
+        <v>1030</v>
       </c>
       <c r="P23" s="17">
-        <v>1390.84</v>
+        <v>1194.8</v>
       </c>
       <c r="Q23" s="14">
-        <v>8.3660006343165243</v>
+        <v>7.1868062163019353</v>
       </c>
       <c r="R23" s="16">
         <v>3153</v>
       </c>
       <c r="S23" s="15">
-        <v>-1667.363636363636</v>
+        <v>-1836.363636363636</v>
       </c>
       <c r="T23" s="18">
-        <v>5235</v>
+        <v>4631</v>
       </c>
       <c r="U23" s="17">
-        <v>6072.5999999999995</v>
+        <v>5371.96</v>
       </c>
       <c r="V23" s="14">
-        <v>8.7038996372430457</v>
+        <v>7.6996674727932284</v>
       </c>
       <c r="W23" s="16">
         <v>13232</v>
       </c>
       <c r="X23" s="15">
-        <v>-3786.818181818182</v>
+        <v>-4390.818181818182</v>
       </c>
       <c r="Y23" s="18">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="Z23" s="17">
-        <v>256.35999999999996</v>
+        <v>167.04</v>
       </c>
       <c r="AA23" s="14">
-        <v>3.622950819672131</v>
+        <v>2.3517587939698492</v>
       </c>
       <c r="AB23" s="16">
-        <v>1342</v>
+        <v>1347.0769230769231</v>
       </c>
       <c r="AC23" s="15">
-        <v>-694</v>
+        <v>-774.46153846153845</v>
       </c>
       <c r="AD23" s="19">
-        <v>37178</v>
+        <v>34078</v>
       </c>
       <c r="AE23" s="20">
-        <v>43126.479999999996</v>
+        <v>39530.479999999996</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3486,85 +3490,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>12602</v>
+        <v>11708</v>
       </c>
       <c r="F24" s="14">
-        <v>14618.32</v>
+        <v>13581.279999999999</v>
       </c>
       <c r="G24" s="14">
-        <v>10.322585449400552</v>
+        <v>9.5902896716062251</v>
       </c>
       <c r="H24" s="30">
         <v>26858</v>
       </c>
       <c r="I24" s="15">
-        <v>393.81818181818198</v>
+        <v>-500.18181818181802</v>
       </c>
       <c r="J24" s="16">
-        <v>9058</v>
+        <v>5618</v>
       </c>
       <c r="K24" s="13">
-        <v>10507.279999999999</v>
+        <v>6516.8799999999992</v>
       </c>
       <c r="L24" s="14">
-        <v>16.700972175662084</v>
+        <v>10.358364063023801</v>
       </c>
       <c r="M24" s="30">
         <v>11932</v>
       </c>
       <c r="N24" s="15">
-        <v>3634.363636363636</v>
+        <v>194.36363636363603</v>
       </c>
       <c r="O24" s="16">
-        <v>693</v>
+        <v>593</v>
       </c>
       <c r="P24" s="17">
-        <v>803.88</v>
+        <v>687.88</v>
       </c>
       <c r="Q24" s="14">
-        <v>8.070937003705664</v>
+        <v>6.9062996294335628</v>
       </c>
       <c r="R24" s="16">
         <v>1889</v>
       </c>
       <c r="S24" s="15">
-        <v>-1024.2727272727273</v>
+        <v>-1124.2727272727273</v>
       </c>
       <c r="T24" s="18">
-        <v>2938</v>
+        <v>2622</v>
       </c>
       <c r="U24" s="17">
-        <v>3408.08</v>
+        <v>3041.52</v>
       </c>
       <c r="V24" s="14">
-        <v>8.8883388338833882</v>
+        <v>7.9323432343234321</v>
       </c>
       <c r="W24" s="16">
         <v>7272</v>
       </c>
       <c r="X24" s="15">
-        <v>-2020.181818181818</v>
+        <v>-2336.181818181818</v>
       </c>
       <c r="Y24" s="18">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="Z24" s="17">
-        <v>564.91999999999996</v>
+        <v>517.36</v>
       </c>
       <c r="AA24" s="14">
-        <v>12.303157894736842</v>
+        <v>11.368627450980391</v>
       </c>
       <c r="AB24" s="16">
-        <v>870.83333333333337</v>
+        <v>863.07692307692309</v>
       </c>
       <c r="AC24" s="15">
-        <v>-106.75</v>
+        <v>-142.46153846153845</v>
       </c>
       <c r="AD24" s="19">
-        <v>25778</v>
+        <v>20987</v>
       </c>
       <c r="AE24" s="20">
-        <v>29902.48</v>
+        <v>24344.92</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3599,85 +3603,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>5034</v>
+        <v>6643</v>
       </c>
       <c r="F25" s="14">
-        <v>5839.44</v>
+        <v>7705.8799999999992</v>
       </c>
       <c r="G25" s="14">
-        <v>4.2885687732342008</v>
+        <v>5.6593091697645601</v>
       </c>
       <c r="H25" s="30">
         <v>25824</v>
       </c>
       <c r="I25" s="15">
-        <v>-6704.181818181818</v>
+        <v>-5095.181818181818</v>
       </c>
       <c r="J25" s="16">
-        <v>11949</v>
+        <v>5322</v>
       </c>
       <c r="K25" s="13">
-        <v>13860.839999999998</v>
+        <v>6173.5199999999995</v>
       </c>
       <c r="L25" s="14">
-        <v>22.070187221895729</v>
+        <v>9.8299051297120315</v>
       </c>
       <c r="M25" s="30">
         <v>11911</v>
       </c>
       <c r="N25" s="15">
-        <v>6534.909090909091</v>
+        <v>-92.090909090909008</v>
       </c>
       <c r="O25" s="16">
-        <v>725</v>
+        <v>601</v>
       </c>
       <c r="P25" s="17">
-        <v>840.99999999999989</v>
+        <v>697.16</v>
       </c>
       <c r="Q25" s="14">
-        <v>7.2598998634501593</v>
+        <v>6.0182066454255807</v>
       </c>
       <c r="R25" s="16">
         <v>2197</v>
       </c>
       <c r="S25" s="15">
-        <v>-1272.2727272727273</v>
+        <v>-1396.2727272727273</v>
       </c>
       <c r="T25" s="18">
-        <v>4309</v>
+        <v>3939</v>
       </c>
       <c r="U25" s="17">
-        <v>4998.4399999999996</v>
+        <v>4569.24</v>
       </c>
       <c r="V25" s="14">
-        <v>13.155426033860671</v>
+        <v>12.025811823480433</v>
       </c>
       <c r="W25" s="16">
         <v>7206.0000000000009</v>
       </c>
       <c r="X25" s="15">
-        <v>-604.18181818181802</v>
+        <v>-974.18181818181802</v>
       </c>
       <c r="Y25" s="18">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="Z25" s="17">
-        <v>736.59999999999991</v>
+        <v>715.71999999999991</v>
       </c>
       <c r="AA25" s="14">
-        <v>22.346041055718473</v>
+        <v>21.915300546448087</v>
       </c>
       <c r="AB25" s="16">
-        <v>625.16666666666674</v>
+        <v>619.38461538461536</v>
       </c>
       <c r="AC25" s="15">
-        <v>208.74999999999994</v>
+        <v>194.69230769230768</v>
       </c>
       <c r="AD25" s="19">
-        <v>22652</v>
+        <v>17122</v>
       </c>
       <c r="AE25" s="20">
-        <v>26276.32</v>
+        <v>19861.52</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3712,85 +3716,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>15499</v>
+        <v>14777</v>
       </c>
       <c r="F26" s="14">
-        <v>17978.84</v>
+        <v>17141.32</v>
       </c>
       <c r="G26" s="14">
-        <v>10.867824701195218</v>
+        <v>10.361561752988047</v>
       </c>
       <c r="H26" s="30">
         <v>31375</v>
       </c>
       <c r="I26" s="15">
-        <v>1237.6363636363621</v>
+        <v>515.63636363636215</v>
       </c>
       <c r="J26" s="16">
-        <v>14306</v>
+        <v>10391</v>
       </c>
       <c r="K26" s="13">
-        <v>16594.96</v>
+        <v>12053.56</v>
       </c>
       <c r="L26" s="14">
-        <v>22.323001631321372</v>
+        <v>16.214057734591105</v>
       </c>
       <c r="M26" s="30">
         <v>14099</v>
       </c>
       <c r="N26" s="15">
-        <v>7897.363636363636</v>
+        <v>3982.363636363636</v>
       </c>
       <c r="O26" s="16">
-        <v>616</v>
+        <v>525</v>
       </c>
       <c r="P26" s="17">
-        <v>714.56</v>
+        <v>609</v>
       </c>
       <c r="Q26" s="14">
-        <v>7.4461538461538455</v>
+        <v>6.3461538461538458</v>
       </c>
       <c r="R26" s="16">
         <v>1820</v>
       </c>
       <c r="S26" s="15">
-        <v>-1038.5454545454547</v>
+        <v>-1129.5454545454547</v>
       </c>
       <c r="T26" s="18">
-        <v>3425</v>
+        <v>2991</v>
       </c>
       <c r="U26" s="17">
-        <v>3972.9999999999995</v>
+        <v>3469.56</v>
       </c>
       <c r="V26" s="14">
-        <v>9.0499639682920971</v>
+        <v>7.9031948114340622</v>
       </c>
       <c r="W26" s="16">
         <v>8326</v>
       </c>
       <c r="X26" s="15">
-        <v>-2251.818181818182</v>
+        <v>-2685.818181818182</v>
       </c>
       <c r="Y26" s="18">
-        <v>598</v>
+        <v>542</v>
       </c>
       <c r="Z26" s="17">
-        <v>693.68</v>
+        <v>628.71999999999991</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.118829981718463</v>
+        <v>12.318181818181818</v>
       </c>
       <c r="AB26" s="16">
-        <v>1002.8333333333334</v>
+        <v>968</v>
       </c>
       <c r="AC26" s="15">
-        <v>-85.75</v>
+        <v>-118</v>
       </c>
       <c r="AD26" s="19">
-        <v>34444</v>
+        <v>29226</v>
       </c>
       <c r="AE26" s="20">
-        <v>39955.040000000001</v>
+        <v>33902.159999999996</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3825,85 +3829,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>2025</v>
+        <v>1716</v>
       </c>
       <c r="F27" s="14">
-        <v>2349</v>
+        <v>1990.56</v>
       </c>
       <c r="G27" s="14">
-        <v>12.282878411910669</v>
+        <v>10.408602150537634</v>
       </c>
       <c r="H27" s="30">
         <v>3627</v>
       </c>
       <c r="I27" s="15">
-        <v>376.36363636363626</v>
+        <v>67.36363636363626</v>
       </c>
       <c r="J27" s="16">
-        <v>3788</v>
+        <v>3188</v>
       </c>
       <c r="K27" s="13">
-        <v>4394.08</v>
+        <v>3698.08</v>
       </c>
       <c r="L27" s="14">
-        <v>32.900118436636397</v>
+        <v>27.688906435057245</v>
       </c>
       <c r="M27" s="30">
         <v>2533</v>
       </c>
       <c r="N27" s="15">
-        <v>2636.6363636363635</v>
+        <v>2036.6363636363635</v>
       </c>
       <c r="O27" s="16">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="P27" s="17">
-        <v>502.28</v>
+        <v>466.32</v>
       </c>
       <c r="Q27" s="14">
-        <v>22.680952380952384</v>
+        <v>21.057142857142857</v>
       </c>
       <c r="R27" s="16">
         <v>420</v>
       </c>
       <c r="S27" s="15">
-        <v>51.181818181818187</v>
+        <v>20.181818181818187</v>
       </c>
       <c r="T27" s="18">
-        <v>796</v>
+        <v>682</v>
       </c>
       <c r="U27" s="17">
-        <v>923.3599999999999</v>
+        <v>791.11999999999989</v>
       </c>
       <c r="V27" s="14">
-        <v>11.46823837590046</v>
+        <v>9.8258022265880829</v>
       </c>
       <c r="W27" s="16">
         <v>1526.9999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-245.13636363636328</v>
+        <v>-359.13636363636328</v>
       </c>
       <c r="Y27" s="18">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="Z27" s="17">
-        <v>535.91999999999996</v>
+        <v>524.31999999999994</v>
       </c>
       <c r="AA27" s="14">
-        <v>36.473684210526322</v>
+        <v>36.725000000000001</v>
       </c>
       <c r="AB27" s="16">
-        <v>278.66666666666663</v>
+        <v>270.76923076923077</v>
       </c>
       <c r="AC27" s="15">
-        <v>272</v>
+        <v>267.38461538461536</v>
       </c>
       <c r="AD27" s="19">
-        <v>7504</v>
+        <v>6440</v>
       </c>
       <c r="AE27" s="20">
-        <v>8704.64</v>
+        <v>7470.4</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3938,85 +3942,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>0</v>
+        <v>1559</v>
       </c>
       <c r="F28" s="14">
-        <v>0</v>
+        <v>1808.4399999999998</v>
       </c>
       <c r="G28" s="14">
-        <v>0</v>
+        <v>9.138822275512922</v>
       </c>
       <c r="H28" s="30">
         <v>3753</v>
       </c>
       <c r="I28" s="15">
-        <v>-1705.909090909091</v>
+        <v>-146.90909090909099</v>
       </c>
       <c r="J28" s="16">
-        <v>9936</v>
+        <v>7126</v>
       </c>
       <c r="K28" s="13">
-        <v>11525.759999999998</v>
+        <v>8266.16</v>
       </c>
       <c r="L28" s="14">
-        <v>65.505543901708123</v>
+        <v>46.979922085705724</v>
       </c>
       <c r="M28" s="30">
         <v>3337</v>
       </c>
       <c r="N28" s="15">
-        <v>8419.181818181818</v>
+        <v>5609.181818181818</v>
       </c>
       <c r="O28" s="16">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="P28" s="17">
-        <v>321.32</v>
+        <v>264.47999999999996</v>
       </c>
       <c r="Q28" s="14">
-        <v>11.541666666666666</v>
+        <v>9.5</v>
       </c>
       <c r="R28" s="16">
         <v>528</v>
       </c>
       <c r="S28" s="15">
-        <v>-203</v>
+        <v>-252</v>
       </c>
       <c r="T28" s="18">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="U28" s="17">
-        <v>117.16</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="V28" s="14">
-        <v>1.7131842713955281</v>
+        <v>0.13569776407093292</v>
       </c>
       <c r="W28" s="16">
         <v>1297</v>
       </c>
       <c r="X28" s="15">
-        <v>-783.31818181818176</v>
+        <v>-876.31818181818176</v>
       </c>
       <c r="Y28" s="18">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="Z28" s="17">
-        <v>458.2</v>
+        <v>446.59999999999997</v>
       </c>
       <c r="AA28" s="14">
-        <v>22.149532710280376</v>
+        <v>21.951754385964911</v>
       </c>
       <c r="AB28" s="16">
-        <v>392.33333333333331</v>
+        <v>385.84615384615387</v>
       </c>
       <c r="AC28" s="15">
-        <v>127.5</v>
+        <v>121.92307692307691</v>
       </c>
       <c r="AD28" s="19">
-        <v>10709</v>
+        <v>9306</v>
       </c>
       <c r="AE28" s="20">
-        <v>12422.439999999999</v>
+        <v>10794.96</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4051,85 +4055,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>0</v>
+        <v>1578</v>
       </c>
       <c r="F29" s="14">
-        <v>0</v>
+        <v>1830.4799999999998</v>
       </c>
       <c r="G29" s="14">
-        <v>0</v>
+        <v>9.1237844940867276</v>
       </c>
       <c r="H29" s="30">
         <v>3805.0000000000005</v>
       </c>
       <c r="I29" s="15">
-        <v>-1729.5454545454547</v>
+        <v>-151.54545454545473</v>
       </c>
       <c r="J29" s="16">
-        <v>4048</v>
+        <v>1562</v>
       </c>
       <c r="K29" s="13">
-        <v>4695.6799999999994</v>
+        <v>1811.9199999999998</v>
       </c>
       <c r="L29" s="14">
-        <v>32.801473296500923</v>
+        <v>12.657090239410682</v>
       </c>
       <c r="M29" s="30">
         <v>2715</v>
       </c>
       <c r="N29" s="15">
-        <v>2813.909090909091</v>
+        <v>327.90909090909099</v>
       </c>
       <c r="O29" s="16">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="P29" s="17">
-        <v>319</v>
+        <v>272.59999999999997</v>
       </c>
       <c r="Q29" s="14">
-        <v>12.630480167014614</v>
+        <v>10.793319415448851</v>
       </c>
       <c r="R29" s="16">
         <v>479</v>
       </c>
       <c r="S29" s="15">
-        <v>-160.4545454545455</v>
+        <v>-200.4545454545455</v>
       </c>
       <c r="T29" s="18">
-        <v>339</v>
+        <v>169</v>
       </c>
       <c r="U29" s="17">
-        <v>393.23999999999995</v>
+        <v>196.04</v>
       </c>
       <c r="V29" s="14">
-        <v>6.5363716038562663</v>
+        <v>3.2585451358457491</v>
       </c>
       <c r="W29" s="16">
         <v>1141</v>
       </c>
       <c r="X29" s="15">
-        <v>-438.9545454545455</v>
+        <v>-608.9545454545455</v>
       </c>
       <c r="Y29" s="18">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="Z29" s="17">
-        <v>458.2</v>
+        <v>447.76</v>
       </c>
       <c r="AA29" s="14">
-        <v>21.447963800904976</v>
+        <v>21.262711864406782</v>
       </c>
       <c r="AB29" s="16">
-        <v>405.16666666666669</v>
+        <v>399.38461538461536</v>
       </c>
       <c r="AC29" s="15">
-        <v>118.75</v>
+        <v>113.69230769230768</v>
       </c>
       <c r="AD29" s="19">
-        <v>5057</v>
+        <v>3930</v>
       </c>
       <c r="AE29" s="20">
-        <v>5866.12</v>
+        <v>4558.7999999999993</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4164,85 +4168,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>882</v>
+        <v>856</v>
       </c>
       <c r="F30" s="14">
-        <v>3245.76</v>
+        <v>3150.08</v>
       </c>
       <c r="G30" s="14">
-        <v>9.7753148614609557</v>
+        <v>9.4871536523929461</v>
       </c>
       <c r="H30" s="30">
         <v>1985</v>
       </c>
       <c r="I30" s="15">
-        <v>-20.272727272727366</v>
+        <v>-46.272727272727366</v>
       </c>
       <c r="J30" s="16">
-        <v>825</v>
+        <v>332</v>
       </c>
       <c r="K30" s="13">
-        <v>3036</v>
+        <v>1221.76</v>
       </c>
       <c r="L30" s="14">
-        <v>8.1646423751686914</v>
+        <v>3.2856500224921277</v>
       </c>
       <c r="M30" s="30">
         <v>2223</v>
       </c>
       <c r="N30" s="15">
-        <v>-185.4545454545455</v>
+        <v>-678.4545454545455</v>
       </c>
       <c r="O30" s="16">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P30" s="17">
-        <v>80.960000000000008</v>
+        <v>40.480000000000004</v>
       </c>
       <c r="Q30" s="14">
-        <v>5.9024390243902438</v>
+        <v>2.9512195121951219</v>
       </c>
       <c r="R30" s="16">
         <v>82</v>
       </c>
       <c r="S30" s="15">
-        <v>-52.545454545454547</v>
+        <v>-63.545454545454547</v>
       </c>
       <c r="T30" s="18">
-        <v>453</v>
+        <v>375</v>
       </c>
       <c r="U30" s="17">
-        <v>1667.04</v>
+        <v>1380</v>
       </c>
       <c r="V30" s="14">
-        <v>14.277936962750717</v>
+        <v>11.819484240687679</v>
       </c>
       <c r="W30" s="16">
         <v>698</v>
       </c>
       <c r="X30" s="15">
-        <v>-22.909090909090878</v>
+        <v>-100.90909090909088</v>
       </c>
       <c r="Y30" s="18">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="Z30" s="17">
-        <v>143.52000000000001</v>
+        <v>106.72</v>
       </c>
       <c r="AA30" s="14">
-        <v>8.068965517241379</v>
+        <v>5.890625</v>
       </c>
       <c r="AB30" s="16">
-        <v>106.33333333333333</v>
+        <v>108.30769230769232</v>
       </c>
       <c r="AC30" s="15">
-        <v>-33.5</v>
+        <v>-44.846153846153854</v>
       </c>
       <c r="AD30" s="19">
-        <v>2221</v>
+        <v>1603</v>
       </c>
       <c r="AE30" s="20">
-        <v>8173.2800000000007</v>
+        <v>5899.04</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4277,34 +4281,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="F31" s="14">
-        <v>1339.52</v>
+        <v>1273.28</v>
       </c>
       <c r="G31" s="14">
-        <v>6.6788990825688073</v>
+        <v>6.3486238532110093</v>
       </c>
       <c r="H31" s="30">
         <v>1199</v>
       </c>
       <c r="I31" s="15">
-        <v>-181</v>
+        <v>-199</v>
       </c>
       <c r="J31" s="16">
-        <v>332</v>
+        <v>680</v>
       </c>
       <c r="K31" s="13">
-        <v>1221.76</v>
+        <v>2502.4</v>
       </c>
       <c r="L31" s="14">
-        <v>4.9890710382513674</v>
+        <v>10.21857923497268</v>
       </c>
       <c r="M31" s="30">
         <v>1463.9999999999998</v>
       </c>
       <c r="N31" s="15">
-        <v>-333.45454545454527</v>
+        <v>14.545454545454731</v>
       </c>
       <c r="O31" s="16">
         <v>26</v>
@@ -4322,40 +4326,40 @@
         <v>-10.36363636363636</v>
       </c>
       <c r="T31" s="18">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="U31" s="17">
-        <v>695.52</v>
+        <v>614.56000000000006</v>
       </c>
       <c r="V31" s="14">
-        <v>15.809885931558934</v>
+        <v>13.969581749049429</v>
       </c>
       <c r="W31" s="16">
         <v>263</v>
       </c>
       <c r="X31" s="15">
-        <v>9.681818181818187</v>
+        <v>-12.318181818181813</v>
       </c>
       <c r="Y31" s="18">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Z31" s="17">
-        <v>184</v>
+        <v>172.96</v>
       </c>
       <c r="AA31" s="14">
-        <v>28.571428571428573</v>
+        <v>29.095238095238095</v>
       </c>
       <c r="AB31" s="16">
-        <v>38.5</v>
+        <v>35.53846153846154</v>
       </c>
       <c r="AC31" s="15">
-        <v>23.75</v>
+        <v>22.76923076923077</v>
       </c>
       <c r="AD31" s="19">
-        <v>961</v>
+        <v>1266</v>
       </c>
       <c r="AE31" s="20">
-        <v>3536.48</v>
+        <v>4658.88</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4390,85 +4394,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>2255</v>
+        <v>2190</v>
       </c>
       <c r="F32" s="14">
-        <v>9358.25</v>
+        <v>9088.5</v>
       </c>
       <c r="G32" s="14">
-        <v>10.324661810613945</v>
+        <v>10.027055150884495</v>
       </c>
       <c r="H32" s="30">
         <v>4805</v>
       </c>
       <c r="I32" s="15">
-        <v>70.909090909090992</v>
+        <v>5.9090909090909918</v>
       </c>
       <c r="J32" s="16">
-        <v>1924</v>
+        <v>1499</v>
       </c>
       <c r="K32" s="13">
-        <v>7984.6</v>
+        <v>6220.85</v>
       </c>
       <c r="L32" s="14">
-        <v>11.224608857067089</v>
+        <v>8.7451604348979046</v>
       </c>
       <c r="M32" s="30">
         <v>3771.0000000000005</v>
       </c>
       <c r="N32" s="15">
-        <v>209.90909090909054</v>
+        <v>-215.09090909090946</v>
       </c>
       <c r="O32" s="16">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="P32" s="17">
-        <v>593.45000000000005</v>
+        <v>319.55</v>
       </c>
       <c r="Q32" s="14">
-        <v>11.195729537366548</v>
+        <v>6.0284697508896796</v>
       </c>
       <c r="R32" s="16">
         <v>281</v>
       </c>
       <c r="S32" s="15">
-        <v>-112.45454545454547</v>
+        <v>-178.45454545454547</v>
       </c>
       <c r="T32" s="18">
-        <v>767</v>
+        <v>661</v>
       </c>
       <c r="U32" s="17">
-        <v>3183.05</v>
+        <v>2743.15</v>
       </c>
       <c r="V32" s="14">
-        <v>9.2157291097760776</v>
+        <v>7.9421081376297096</v>
       </c>
       <c r="W32" s="16">
         <v>1831</v>
       </c>
       <c r="X32" s="15">
-        <v>-481.40909090909099</v>
+        <v>-587.40909090909099</v>
       </c>
       <c r="Y32" s="18">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Z32" s="17">
-        <v>1191.0500000000002</v>
+        <v>1203.5</v>
       </c>
       <c r="AA32" s="14">
-        <v>57.4</v>
+        <v>62.833333333333336</v>
       </c>
       <c r="AB32" s="16">
-        <v>110</v>
+        <v>101.53846153846153</v>
       </c>
       <c r="AC32" s="15">
-        <v>212</v>
+        <v>220.76923076923077</v>
       </c>
       <c r="AD32" s="19">
-        <v>5376</v>
+        <v>4717</v>
       </c>
       <c r="AE32" s="20">
-        <v>22310.400000000001</v>
+        <v>19575.550000000003</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4503,85 +4507,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1946</v>
+        <v>2908</v>
       </c>
       <c r="F33" s="14">
-        <v>8075.9000000000005</v>
+        <v>12068.2</v>
       </c>
       <c r="G33" s="14">
-        <v>4.8594778660612938</v>
+        <v>7.2617480136208856</v>
       </c>
       <c r="H33" s="30">
         <v>8810</v>
       </c>
       <c r="I33" s="15">
-        <v>-2058.5454545454545</v>
+        <v>-1096.5454545454545</v>
       </c>
       <c r="J33" s="16">
-        <v>2310</v>
+        <v>2029</v>
       </c>
       <c r="K33" s="13">
-        <v>9586.5</v>
+        <v>8420.35</v>
       </c>
       <c r="L33" s="14">
-        <v>10.017740981667652</v>
+        <v>8.7991326631184705</v>
       </c>
       <c r="M33" s="30">
         <v>5073</v>
       </c>
       <c r="N33" s="15">
-        <v>4.0909090909090082</v>
+        <v>-276.90909090909099</v>
       </c>
       <c r="O33" s="16">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="P33" s="17">
-        <v>535.35</v>
+        <v>315.40000000000003</v>
       </c>
       <c r="Q33" s="14">
-        <v>7.9052924791086356</v>
+        <v>4.6573816155988865</v>
       </c>
       <c r="R33" s="16">
         <v>359</v>
       </c>
       <c r="S33" s="15">
-        <v>-197.36363636363632</v>
+        <v>-250.36363636363632</v>
       </c>
       <c r="T33" s="18">
-        <v>1191</v>
+        <v>1058</v>
       </c>
       <c r="U33" s="17">
-        <v>4942.6500000000005</v>
+        <v>4390.7000000000007</v>
       </c>
       <c r="V33" s="14">
-        <v>10.227166276346605</v>
+        <v>9.0850897736143637</v>
       </c>
       <c r="W33" s="16">
         <v>2562</v>
       </c>
       <c r="X33" s="15">
-        <v>-555.81818181818176</v>
+        <v>-688.81818181818176</v>
       </c>
       <c r="Y33" s="18">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="Z33" s="17">
-        <v>444.05</v>
+        <v>340.3</v>
       </c>
       <c r="AA33" s="14">
-        <v>7.9751552795031069</v>
+        <v>6.1264367816091951</v>
       </c>
       <c r="AB33" s="16">
-        <v>295.16666666666663</v>
+        <v>294.46153846153845</v>
       </c>
       <c r="AC33" s="15">
-        <v>-94.249999999999972</v>
+        <v>-118.76923076923077</v>
       </c>
       <c r="AD33" s="19">
-        <v>5683</v>
+        <v>6153</v>
       </c>
       <c r="AE33" s="20">
-        <v>23584.45</v>
+        <v>25534.95</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4616,25 +4620,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>478</v>
+        <v>798</v>
       </c>
       <c r="F34" s="14">
-        <v>1983.7000000000003</v>
+        <v>3311.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>7.1054054054054063</v>
+        <v>11.862162162162162</v>
       </c>
       <c r="H34" s="30">
         <v>1480</v>
       </c>
       <c r="I34" s="15">
-        <v>-194.72727272727263</v>
+        <v>125.27272727272737</v>
       </c>
       <c r="J34" s="16">
-        <v>752</v>
+        <v>336</v>
       </c>
       <c r="K34" s="13">
-        <v>3120.8</v>
+        <v>1394.4</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4643,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>752</v>
+        <v>336</v>
       </c>
       <c r="O34" s="16">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="P34" s="17">
         <v>0</v>
@@ -4658,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="15">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="T34" s="18">
         <v>64</v>
@@ -4691,10 +4695,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1390</v>
+        <v>1262</v>
       </c>
       <c r="AE34" s="20">
-        <v>5768.5000000000009</v>
+        <v>5237.3</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4729,85 +4733,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>3608</v>
+        <v>4046</v>
       </c>
       <c r="F35" s="14">
-        <v>5881.04</v>
+        <v>6594.98</v>
       </c>
       <c r="G35" s="14">
-        <v>7.422479895268375</v>
+        <v>8.3235459135964103</v>
       </c>
       <c r="H35" s="30">
         <v>10694</v>
       </c>
       <c r="I35" s="15">
-        <v>-1252.909090909091</v>
+        <v>-814.90909090909099</v>
       </c>
       <c r="J35" s="16">
-        <v>2528</v>
+        <v>842</v>
       </c>
       <c r="K35" s="13">
-        <v>4120.6399999999994</v>
+        <v>1372.4599999999998</v>
       </c>
       <c r="L35" s="14">
-        <v>17.266687364172618</v>
+        <v>5.7510090034150885</v>
       </c>
       <c r="M35" s="30">
         <v>3221</v>
       </c>
       <c r="N35" s="15">
-        <v>1063.909090909091</v>
+        <v>-622.09090909090901</v>
       </c>
       <c r="O35" s="16">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="P35" s="17">
-        <v>691.12</v>
+        <v>652</v>
       </c>
       <c r="Q35" s="14">
-        <v>9.7675392670157066</v>
+        <v>9.2146596858638752</v>
       </c>
       <c r="R35" s="16">
         <v>955</v>
       </c>
       <c r="S35" s="15">
-        <v>-444.18181818181813</v>
+        <v>-468.18181818181813</v>
       </c>
       <c r="T35" s="18">
-        <v>311</v>
+        <v>237</v>
       </c>
       <c r="U35" s="17">
-        <v>506.92999999999995</v>
+        <v>386.31</v>
       </c>
       <c r="V35" s="14">
-        <v>5.023494860499266</v>
+        <v>3.8281938325991192</v>
       </c>
       <c r="W35" s="16">
         <v>1362</v>
       </c>
       <c r="X35" s="15">
-        <v>-617.63636363636363</v>
+        <v>-691.63636363636363</v>
       </c>
       <c r="Y35" s="18">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="Z35" s="17">
-        <v>524.86</v>
+        <v>498.78</v>
       </c>
       <c r="AA35" s="14">
-        <v>23.418181818181818</v>
+        <v>21.857142857142858</v>
       </c>
       <c r="AB35" s="16">
-        <v>302.5</v>
+        <v>308</v>
       </c>
       <c r="AC35" s="15">
-        <v>115.75</v>
+        <v>96</v>
       </c>
       <c r="AD35" s="19">
-        <v>7193</v>
+        <v>5831</v>
       </c>
       <c r="AE35" s="20">
-        <v>11724.589999999998</v>
+        <v>9504.5299999999988</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4842,85 +4846,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>6270</v>
+        <v>5580</v>
       </c>
       <c r="F36" s="14">
-        <v>10220.099999999999</v>
+        <v>9095.4</v>
       </c>
       <c r="G36" s="14">
-        <v>8.3869398674530302</v>
+        <v>7.4639751930443241</v>
       </c>
       <c r="H36" s="30">
         <v>16447</v>
       </c>
       <c r="I36" s="15">
-        <v>-1205.909090909091</v>
+        <v>-1895.909090909091</v>
       </c>
       <c r="J36" s="16">
-        <v>2929</v>
+        <v>3076</v>
       </c>
       <c r="K36" s="13">
-        <v>4774.2699999999995</v>
+        <v>5013.88</v>
       </c>
       <c r="L36" s="14">
-        <v>13.059991892987433</v>
+        <v>13.715443858937981</v>
       </c>
       <c r="M36" s="30">
         <v>4934</v>
       </c>
       <c r="N36" s="15">
-        <v>686.27272727272702</v>
+        <v>833.27272727272702</v>
       </c>
       <c r="O36" s="16">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="P36" s="17">
-        <v>324.37</v>
+        <v>16.299999999999997</v>
       </c>
       <c r="Q36" s="14">
-        <v>2.1857214178731903</v>
+        <v>0.10983524712930604</v>
       </c>
       <c r="R36" s="16">
         <v>2003</v>
       </c>
       <c r="S36" s="15">
-        <v>-1621.909090909091</v>
+        <v>-1810.909090909091</v>
       </c>
       <c r="T36" s="18">
-        <v>1313</v>
+        <v>1205</v>
       </c>
       <c r="U36" s="17">
-        <v>2140.19</v>
+        <v>1964.1499999999999</v>
       </c>
       <c r="V36" s="14">
-        <v>9.8318584070796469</v>
+        <v>9.0231449965963257</v>
       </c>
       <c r="W36" s="16">
         <v>2938</v>
       </c>
       <c r="X36" s="15">
-        <v>-690.18181818181802</v>
+        <v>-798.18181818181802</v>
       </c>
       <c r="Y36" s="18">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="Z36" s="17">
-        <v>588.42999999999995</v>
+        <v>547.67999999999995</v>
       </c>
       <c r="AA36" s="14">
-        <v>13.929260450160768</v>
+        <v>13.196374622356497</v>
       </c>
       <c r="AB36" s="16">
-        <v>570.16666666666674</v>
+        <v>560.15384615384608</v>
       </c>
       <c r="AC36" s="15">
-        <v>-27.750000000000057</v>
+        <v>-45.923076923076849</v>
       </c>
       <c r="AD36" s="19">
-        <v>11072</v>
+        <v>10207</v>
       </c>
       <c r="AE36" s="20">
-        <v>18047.36</v>
+        <v>16637.41</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4955,85 +4959,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>964</v>
+        <v>836</v>
       </c>
       <c r="F37" s="14">
-        <v>1571.32</v>
+        <v>1362.6799999999998</v>
       </c>
       <c r="G37" s="14">
-        <v>3.5589864071152877</v>
+        <v>3.0864238966269508</v>
       </c>
       <c r="H37" s="30">
         <v>5959</v>
       </c>
       <c r="I37" s="15">
-        <v>-1744.636363636364</v>
+        <v>-1872.636363636364</v>
       </c>
       <c r="J37" s="16">
-        <v>1203</v>
+        <v>2586</v>
       </c>
       <c r="K37" s="13">
-        <v>1960.8899999999999</v>
+        <v>4215.1799999999994</v>
       </c>
       <c r="L37" s="14">
-        <v>10.927332782824113</v>
+        <v>23.489677952105698</v>
       </c>
       <c r="M37" s="30">
         <v>2422</v>
       </c>
       <c r="N37" s="15">
-        <v>102.09090909090901</v>
+        <v>1485.090909090909</v>
       </c>
       <c r="O37" s="16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P37" s="17">
-        <v>44.01</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="14">
-        <v>0.58407079646017701</v>
+        <v>0</v>
       </c>
       <c r="R37" s="16">
         <v>1017</v>
       </c>
       <c r="S37" s="15">
-        <v>-897.5454545454545</v>
+        <v>-924.5454545454545</v>
       </c>
       <c r="T37" s="18">
-        <v>357</v>
+        <v>197</v>
       </c>
       <c r="U37" s="17">
-        <v>581.91</v>
+        <v>321.10999999999996</v>
       </c>
       <c r="V37" s="14">
-        <v>5.1569271175311879</v>
+        <v>2.8456992777412999</v>
       </c>
       <c r="W37" s="16">
         <v>1523</v>
       </c>
       <c r="X37" s="15">
-        <v>-681.40909090909099</v>
+        <v>-841.40909090909099</v>
       </c>
       <c r="Y37" s="18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="17">
-        <v>21.189999999999998</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="14">
-        <v>0.65546218487394958</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>436.33333333333331</v>
+        <v>416.30769230769232</v>
       </c>
       <c r="AC37" s="15">
-        <v>-284.5</v>
+        <v>-283.84615384615387</v>
       </c>
       <c r="AD37" s="19">
-        <v>2564</v>
+        <v>3619</v>
       </c>
       <c r="AE37" s="20">
-        <v>4179.32</v>
+        <v>5898.9699999999993</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5068,85 +5072,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>336</v>
+        <v>190</v>
       </c>
       <c r="F38" s="14">
-        <v>547.67999999999995</v>
+        <v>309.7</v>
       </c>
       <c r="G38" s="14">
-        <v>1.7989778534923337</v>
+        <v>1.0172791433438793</v>
       </c>
       <c r="H38" s="30">
         <v>4109</v>
       </c>
       <c r="I38" s="15">
-        <v>-1531.7272727272727</v>
+        <v>-1677.7272727272727</v>
       </c>
       <c r="J38" s="16">
-        <v>448</v>
+        <v>1838</v>
       </c>
       <c r="K38" s="13">
-        <v>730.24</v>
+        <v>2995.9399999999996</v>
       </c>
       <c r="L38" s="14">
-        <v>4.724832214765101</v>
+        <v>19.384467881112176</v>
       </c>
       <c r="M38" s="30">
         <v>2086</v>
       </c>
       <c r="N38" s="15">
-        <v>-500.18181818181813</v>
+        <v>889.81818181818187</v>
       </c>
       <c r="O38" s="16">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="P38" s="17">
-        <v>281.99</v>
+        <v>91.28</v>
       </c>
       <c r="Q38" s="14">
-        <v>5.0679094540612519</v>
+        <v>1.6404793608521973</v>
       </c>
       <c r="R38" s="16">
         <v>751</v>
       </c>
       <c r="S38" s="15">
-        <v>-509.72727272727263</v>
+        <v>-626.72727272727263</v>
       </c>
       <c r="T38" s="18">
-        <v>495</v>
+        <v>434</v>
       </c>
       <c r="U38" s="17">
-        <v>806.84999999999991</v>
+        <v>707.42</v>
       </c>
       <c r="V38" s="14">
-        <v>10.624390243902438</v>
+        <v>9.3151219512195116</v>
       </c>
       <c r="W38" s="16">
         <v>1025</v>
       </c>
       <c r="X38" s="15">
-        <v>-203.86363636363637</v>
+        <v>-264.86363636363637</v>
       </c>
       <c r="Y38" s="18">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="Z38" s="17">
-        <v>472.7</v>
+        <v>425.42999999999995</v>
       </c>
       <c r="AA38" s="14">
-        <v>10.943396226415095</v>
+        <v>9.7220630372492831</v>
       </c>
       <c r="AB38" s="16">
-        <v>583</v>
+        <v>590.61538461538464</v>
       </c>
       <c r="AC38" s="15">
-        <v>-107.5</v>
+        <v>-141.69230769230768</v>
       </c>
       <c r="AD38" s="19">
-        <v>1742</v>
+        <v>2779</v>
       </c>
       <c r="AE38" s="20">
-        <v>2839.46</v>
+        <v>4529.7699999999995</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5181,64 +5185,64 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>2058</v>
+        <v>1933</v>
       </c>
       <c r="F39" s="14">
-        <v>3354.54</v>
+        <v>3150.79</v>
       </c>
       <c r="G39" s="14">
-        <v>242.11764705882354</v>
+        <v>227.41176470588235</v>
       </c>
       <c r="H39" s="30">
         <v>187</v>
       </c>
       <c r="I39" s="15">
-        <v>1973</v>
+        <v>1848</v>
       </c>
       <c r="J39" s="16">
-        <v>4177</v>
+        <v>3769</v>
       </c>
       <c r="K39" s="13">
-        <v>6808.5099999999993</v>
+        <v>6143.4699999999993</v>
       </c>
       <c r="L39" s="14">
-        <v>112.61519607843138</v>
+        <v>101.61519607843138</v>
       </c>
       <c r="M39" s="30">
         <v>815.99999999999989</v>
       </c>
       <c r="N39" s="15">
-        <v>3806.090909090909</v>
+        <v>3398.090909090909</v>
       </c>
       <c r="O39" s="16">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="P39" s="17">
-        <v>511.82</v>
+        <v>420.53999999999996</v>
       </c>
       <c r="Q39" s="14">
-        <v>628</v>
+        <v>516</v>
       </c>
       <c r="R39" s="16">
         <v>11</v>
       </c>
       <c r="S39" s="15">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="T39" s="18">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="U39" s="17">
-        <v>567.24</v>
+        <v>492.26</v>
       </c>
       <c r="V39" s="14">
-        <v>14.230483271375466</v>
+        <v>12.349442379182157</v>
       </c>
       <c r="W39" s="16">
         <v>538</v>
       </c>
       <c r="X39" s="15">
-        <v>-18.818181818181813</v>
+        <v>-64.818181818181813</v>
       </c>
       <c r="Y39" s="18">
         <v>461</v>
@@ -5247,19 +5251,19 @@
         <v>751.43</v>
       </c>
       <c r="AA39" s="14">
-        <v>89.225806451612897</v>
+        <v>93.640625</v>
       </c>
       <c r="AB39" s="16">
-        <v>113.66666666666667</v>
+        <v>108.30769230769232</v>
       </c>
       <c r="AC39" s="15">
-        <v>383.5</v>
+        <v>387.15384615384613</v>
       </c>
       <c r="AD39" s="19">
-        <v>7358</v>
+        <v>6723</v>
       </c>
       <c r="AE39" s="20">
-        <v>11993.539999999999</v>
+        <v>10958.49</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5294,64 +5298,64 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1834</v>
+        <v>1618</v>
       </c>
       <c r="F40" s="14">
-        <v>2989.4199999999996</v>
+        <v>2637.3399999999997</v>
       </c>
       <c r="G40" s="14">
-        <v>218.09729729729733</v>
+        <v>192.41081081081083</v>
       </c>
       <c r="H40" s="30">
         <v>185</v>
       </c>
       <c r="I40" s="15">
-        <v>1749.909090909091</v>
+        <v>1533.909090909091</v>
       </c>
       <c r="J40" s="16">
-        <v>4228</v>
+        <v>3810</v>
       </c>
       <c r="K40" s="13">
-        <v>6891.6399999999994</v>
+        <v>6210.2999999999993</v>
       </c>
       <c r="L40" s="14">
-        <v>130.27450980392157</v>
+        <v>117.39495798319328</v>
       </c>
       <c r="M40" s="30">
         <v>714</v>
       </c>
       <c r="N40" s="15">
-        <v>3903.4545454545455</v>
+        <v>3485.4545454545455</v>
       </c>
       <c r="O40" s="16">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="P40" s="17">
-        <v>383.04999999999995</v>
+        <v>288.51</v>
       </c>
       <c r="Q40" s="14">
-        <v>470</v>
+        <v>354</v>
       </c>
       <c r="R40" s="16">
         <v>11</v>
       </c>
       <c r="S40" s="15">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="T40" s="18">
-        <v>313</v>
+        <v>245</v>
       </c>
       <c r="U40" s="17">
-        <v>510.18999999999994</v>
+        <v>399.34999999999997</v>
       </c>
       <c r="V40" s="14">
-        <v>12.230905861456483</v>
+        <v>9.5737122557726462</v>
       </c>
       <c r="W40" s="16">
         <v>563</v>
       </c>
       <c r="X40" s="15">
-        <v>-70.863636363636374</v>
+        <v>-138.86363636363637</v>
       </c>
       <c r="Y40" s="18">
         <v>470</v>
@@ -5360,19 +5364,19 @@
         <v>766.09999999999991</v>
       </c>
       <c r="AA40" s="14">
-        <v>92.459016393442624</v>
+        <v>96.984126984126988</v>
       </c>
       <c r="AB40" s="16">
-        <v>111.83333333333333</v>
+        <v>106.61538461538461</v>
       </c>
       <c r="AC40" s="15">
-        <v>393.75</v>
+        <v>397.30769230769232</v>
       </c>
       <c r="AD40" s="19">
-        <v>7080</v>
+        <v>6320</v>
       </c>
       <c r="AE40" s="20">
-        <v>11540.4</v>
+        <v>10301.599999999999</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5407,85 +5411,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F41" s="14">
-        <v>0</v>
+        <v>1439.1000000000001</v>
       </c>
       <c r="G41" s="14">
-        <v>0</v>
+        <v>3.8360655737704916</v>
       </c>
       <c r="H41" s="30">
         <v>1342</v>
       </c>
       <c r="I41" s="15">
-        <v>-610</v>
+        <v>-376</v>
       </c>
       <c r="J41" s="16">
-        <v>480</v>
+        <v>818</v>
       </c>
       <c r="K41" s="13">
-        <v>2952</v>
+        <v>5030.7000000000007</v>
       </c>
       <c r="L41" s="14">
-        <v>13.333333333333334</v>
+        <v>22.722222222222221</v>
       </c>
       <c r="M41" s="30">
         <v>792</v>
       </c>
       <c r="N41" s="15">
-        <v>120</v>
+        <v>458</v>
       </c>
       <c r="O41" s="16">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="P41" s="17">
-        <v>282.90000000000003</v>
+        <v>172.20000000000002</v>
       </c>
       <c r="Q41" s="14">
-        <v>12.192771084337348</v>
+        <v>7.4216867469879517</v>
       </c>
       <c r="R41" s="16">
         <v>83</v>
       </c>
       <c r="S41" s="15">
-        <v>-29.454545454545453</v>
+        <v>-47.454545454545453</v>
       </c>
       <c r="T41" s="18">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="U41" s="17">
-        <v>1236.1500000000001</v>
+        <v>1063.95</v>
       </c>
       <c r="V41" s="14">
-        <v>11.887096774193548</v>
+        <v>10.231182795698924</v>
       </c>
       <c r="W41" s="16">
         <v>372</v>
       </c>
       <c r="X41" s="15">
-        <v>-52.636363636363654</v>
+        <v>-80.636363636363654</v>
       </c>
       <c r="Y41" s="18">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Z41" s="17">
-        <v>141.45000000000002</v>
+        <v>104.55000000000001</v>
       </c>
       <c r="AA41" s="14">
-        <v>4.2461538461538462</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" s="16">
-        <v>119.16666666666667</v>
+        <v>110</v>
       </c>
       <c r="AC41" s="15">
-        <v>-58.25</v>
+        <v>-58</v>
       </c>
       <c r="AD41" s="19">
-        <v>750</v>
+        <v>1270</v>
       </c>
       <c r="AE41" s="20">
-        <v>4612.5</v>
+        <v>7810.5</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5520,85 +5524,85 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="F42" s="14">
-        <v>1408.3500000000001</v>
+        <v>1088.55</v>
       </c>
       <c r="G42" s="14">
-        <v>3.5679886685552407</v>
+        <v>2.7577903682719547</v>
       </c>
       <c r="H42" s="30">
         <v>1412</v>
       </c>
       <c r="I42" s="15">
-        <v>-412.81818181818187</v>
+        <v>-464.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>293</v>
+        <v>858</v>
       </c>
       <c r="K42" s="13">
-        <v>1801.95</v>
+        <v>5276.7000000000007</v>
       </c>
       <c r="L42" s="14">
-        <v>6.9611231101511875</v>
+        <v>20.384449244060473</v>
       </c>
       <c r="M42" s="30">
         <v>926</v>
       </c>
       <c r="N42" s="15">
-        <v>-127.90909090909093</v>
+        <v>437.09090909090907</v>
       </c>
       <c r="O42" s="16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P42" s="17">
-        <v>104.55000000000001</v>
+        <v>98.4</v>
       </c>
       <c r="Q42" s="14">
-        <v>4.617283950617284</v>
+        <v>4.3456790123456788</v>
       </c>
       <c r="R42" s="16">
         <v>81</v>
       </c>
       <c r="S42" s="15">
-        <v>-56.636363636363626</v>
+        <v>-57.636363636363626</v>
       </c>
       <c r="T42" s="18">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="U42" s="17">
-        <v>1629.75</v>
+        <v>1482.15</v>
       </c>
       <c r="V42" s="14">
-        <v>11</v>
+        <v>10.003773584905661</v>
       </c>
       <c r="W42" s="16">
         <v>530</v>
       </c>
       <c r="X42" s="15">
-        <v>-96.363636363636374</v>
+        <v>-120.36363636363637</v>
       </c>
       <c r="Y42" s="18">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Z42" s="17">
-        <v>535.05000000000007</v>
+        <v>516.6</v>
       </c>
       <c r="AA42" s="14">
-        <v>18.315789473684209</v>
+        <v>19.157894736842103</v>
       </c>
       <c r="AB42" s="16">
-        <v>104.5</v>
+        <v>96.461538461538467</v>
       </c>
       <c r="AC42" s="15">
-        <v>15.75</v>
+        <v>18.230769230769226</v>
       </c>
       <c r="AD42" s="19">
-        <v>891</v>
+        <v>1376</v>
       </c>
       <c r="AE42" s="20">
-        <v>5479.6500000000005</v>
+        <v>8462.4</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5633,85 +5637,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>3135</v>
+        <v>2989</v>
       </c>
       <c r="F43" s="14">
-        <v>3636.6</v>
+        <v>3467.24</v>
       </c>
       <c r="G43" s="14">
-        <v>9.3442622950819665</v>
+        <v>8.9090909090909083</v>
       </c>
       <c r="H43" s="30">
         <v>7381</v>
       </c>
       <c r="I43" s="15">
-        <v>-220</v>
+        <v>-366</v>
       </c>
       <c r="J43" s="16">
-        <v>2865</v>
+        <v>1534</v>
       </c>
       <c r="K43" s="13">
-        <v>3323.3999999999996</v>
+        <v>1779.4399999999998</v>
       </c>
       <c r="L43" s="14">
-        <v>22.961748633879782</v>
+        <v>12.294353369763206</v>
       </c>
       <c r="M43" s="30">
         <v>2745</v>
       </c>
       <c r="N43" s="15">
-        <v>1617.2727272727273</v>
+        <v>286.27272727272725</v>
       </c>
       <c r="O43" s="16">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="P43" s="17">
-        <v>146.16</v>
+        <v>40.599999999999994</v>
       </c>
       <c r="Q43" s="14">
-        <v>2.4379947229551453</v>
+        <v>0.6772207563764292</v>
       </c>
       <c r="R43" s="16">
         <v>1137</v>
       </c>
       <c r="S43" s="15">
-        <v>-907.63636363636351</v>
+        <v>-998.63636363636351</v>
       </c>
       <c r="T43" s="18">
-        <v>1134</v>
+        <v>956</v>
       </c>
       <c r="U43" s="17">
-        <v>1315.4399999999998</v>
+        <v>1108.96</v>
       </c>
       <c r="V43" s="14">
-        <v>12.023132530120483</v>
+        <v>10.135903614457831</v>
       </c>
       <c r="W43" s="16">
         <v>2075</v>
       </c>
       <c r="X43" s="15">
-        <v>-280.77272727272725</v>
+        <v>-458.77272727272725</v>
       </c>
       <c r="Y43" s="18">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="Z43" s="17">
-        <v>264.47999999999996</v>
+        <v>248.23999999999998</v>
       </c>
       <c r="AA43" s="14">
-        <v>7.8847262247838605</v>
+        <v>7.6428571428571432</v>
       </c>
       <c r="AB43" s="16">
-        <v>636.16666666666674</v>
+        <v>616</v>
       </c>
       <c r="AC43" s="15">
-        <v>-205.75000000000006</v>
+        <v>-206</v>
       </c>
       <c r="AD43" s="19">
-        <v>7488</v>
+        <v>5728</v>
       </c>
       <c r="AE43" s="20">
-        <v>8686.08</v>
+        <v>6644.48</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5746,85 +5750,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2871</v>
+        <v>2767</v>
       </c>
       <c r="F44" s="14">
-        <v>3330.3599999999997</v>
+        <v>3209.72</v>
       </c>
       <c r="G44" s="14">
-        <v>9.8108108108108105</v>
+        <v>9.4554209381795591</v>
       </c>
       <c r="H44" s="30">
         <v>6438</v>
       </c>
       <c r="I44" s="15">
-        <v>-55.363636363636033</v>
+        <v>-159.36363636363603</v>
       </c>
       <c r="J44" s="16">
-        <v>2788</v>
+        <v>1678</v>
       </c>
       <c r="K44" s="13">
-        <v>3234.08</v>
+        <v>1946.4799999999998</v>
       </c>
       <c r="L44" s="14">
-        <v>16.278131634819534</v>
+        <v>9.7972399150743108</v>
       </c>
       <c r="M44" s="30">
         <v>3767.9999999999995</v>
       </c>
       <c r="N44" s="15">
-        <v>1075.2727272727275</v>
+        <v>-34.727272727272521</v>
       </c>
       <c r="O44" s="16">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="P44" s="17">
-        <v>267.95999999999998</v>
+        <v>258.68</v>
       </c>
       <c r="Q44" s="14">
-        <v>6.7579787234042561</v>
+        <v>6.5239361702127665</v>
       </c>
       <c r="R44" s="16">
         <v>752</v>
       </c>
       <c r="S44" s="15">
-        <v>-452.63636363636363</v>
+        <v>-460.63636363636363</v>
       </c>
       <c r="T44" s="18">
-        <v>870</v>
+        <v>791</v>
       </c>
       <c r="U44" s="17">
-        <v>1009.1999999999999</v>
+        <v>917.56</v>
       </c>
       <c r="V44" s="14">
-        <v>10.290322580645162</v>
+        <v>9.3559139784946233</v>
       </c>
       <c r="W44" s="16">
         <v>1860</v>
       </c>
       <c r="X44" s="15">
-        <v>-398.18181818181824</v>
+        <v>-477.18181818181824</v>
       </c>
       <c r="Y44" s="18">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="Z44" s="17">
-        <v>395.55999999999995</v>
+        <v>382.79999999999995</v>
       </c>
       <c r="AA44" s="14">
-        <v>12.668730650154796</v>
+        <v>12.844311377245509</v>
       </c>
       <c r="AB44" s="16">
-        <v>592.16666666666674</v>
+        <v>565.23076923076928</v>
       </c>
       <c r="AC44" s="15">
-        <v>-62.750000000000057</v>
+        <v>-55.384615384615415</v>
       </c>
       <c r="AD44" s="19">
-        <v>7101</v>
+        <v>5789</v>
       </c>
       <c r="AE44" s="20">
-        <v>8237.16</v>
+        <v>6715.24</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5859,85 +5863,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3241</v>
+        <v>3031</v>
       </c>
       <c r="F45" s="14">
-        <v>3759.56</v>
+        <v>3515.9599999999996</v>
       </c>
       <c r="G45" s="14">
-        <v>8.4122227465785748</v>
+        <v>7.8671543180745642</v>
       </c>
       <c r="H45" s="30">
         <v>8476</v>
       </c>
       <c r="I45" s="15">
-        <v>-611.72727272727252</v>
+        <v>-821.72727272727252</v>
       </c>
       <c r="J45" s="16">
-        <v>2488</v>
+        <v>1335</v>
       </c>
       <c r="K45" s="13">
-        <v>2886.08</v>
+        <v>1548.6</v>
       </c>
       <c r="L45" s="14">
-        <v>10.121301775147929</v>
+        <v>5.4308431952662719</v>
       </c>
       <c r="M45" s="30">
         <v>5408</v>
       </c>
       <c r="N45" s="15">
-        <v>29.818181818181984</v>
+        <v>-1123.181818181818</v>
       </c>
       <c r="O45" s="16">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P45" s="17">
-        <v>382.79999999999995</v>
+        <v>379.32</v>
       </c>
       <c r="Q45" s="14">
-        <v>6.487935656836461</v>
+        <v>6.4289544235924927</v>
       </c>
       <c r="R45" s="16">
         <v>1119</v>
       </c>
       <c r="S45" s="15">
-        <v>-687.27272727272737</v>
+        <v>-690.27272727272737</v>
       </c>
       <c r="T45" s="18">
-        <v>1134</v>
+        <v>1011</v>
       </c>
       <c r="U45" s="17">
-        <v>1315.4399999999998</v>
+        <v>1172.76</v>
       </c>
       <c r="V45" s="14">
-        <v>9.8608695652173921</v>
+        <v>8.7913043478260864</v>
       </c>
       <c r="W45" s="16">
         <v>2530</v>
       </c>
       <c r="X45" s="15">
-        <v>-591</v>
+        <v>-714</v>
       </c>
       <c r="Y45" s="18">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Z45" s="17">
-        <v>295.79999999999995</v>
+        <v>286.52</v>
       </c>
       <c r="AA45" s="14">
-        <v>9.1343283582089541</v>
+        <v>9.2803468208092479</v>
       </c>
       <c r="AB45" s="16">
-        <v>614.16666666666674</v>
+        <v>585.53846153846155</v>
       </c>
       <c r="AC45" s="15">
-        <v>-163.75000000000006</v>
+        <v>-152.23076923076923</v>
       </c>
       <c r="AD45" s="19">
-        <v>7448</v>
+        <v>5951</v>
       </c>
       <c r="AE45" s="20">
-        <v>8639.68</v>
+        <v>6903.16</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5972,85 +5976,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>1985</v>
+        <v>2400</v>
       </c>
       <c r="F46" s="14">
-        <v>2302.6</v>
+        <v>2784</v>
       </c>
       <c r="G46" s="14">
-        <v>7.688380281690141</v>
+        <v>9.295774647887324</v>
       </c>
       <c r="H46" s="30">
         <v>5680</v>
       </c>
       <c r="I46" s="15">
-        <v>-596.81818181818198</v>
+        <v>-181.81818181818198</v>
       </c>
       <c r="J46" s="16">
-        <v>3851</v>
+        <v>2518</v>
       </c>
       <c r="K46" s="13">
-        <v>4467.16</v>
+        <v>2920.8799999999997</v>
       </c>
       <c r="L46" s="14">
-        <v>21.340554156171283</v>
+        <v>13.953652392947102</v>
       </c>
       <c r="M46" s="30">
         <v>3970</v>
       </c>
       <c r="N46" s="15">
-        <v>2046.4545454545453</v>
+        <v>713.45454545454527</v>
       </c>
       <c r="O46" s="16">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="P46" s="17">
-        <v>422.23999999999995</v>
+        <v>418.76</v>
       </c>
       <c r="Q46" s="14">
-        <v>9.7420924574209238</v>
+        <v>9.6618004866180041</v>
       </c>
       <c r="R46" s="16">
         <v>822.00000000000011</v>
       </c>
       <c r="S46" s="15">
-        <v>-383.27272727272737</v>
+        <v>-386.27272727272737</v>
       </c>
       <c r="T46" s="18">
-        <v>599</v>
+        <v>540</v>
       </c>
       <c r="U46" s="17">
-        <v>694.83999999999992</v>
+        <v>626.4</v>
       </c>
       <c r="V46" s="14">
-        <v>10.593247588424438</v>
+        <v>9.54983922829582</v>
       </c>
       <c r="W46" s="16">
         <v>1244</v>
       </c>
       <c r="X46" s="15">
-        <v>-249.18181818181824</v>
+        <v>-308.18181818181824</v>
       </c>
       <c r="Y46" s="18">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="Z46" s="17">
-        <v>169.35999999999999</v>
+        <v>124.11999999999999</v>
       </c>
       <c r="AA46" s="14">
-        <v>5.8205980066445191</v>
+        <v>4.1897590361445776</v>
       </c>
       <c r="AB46" s="16">
-        <v>551.83333333333326</v>
+        <v>561.84615384615392</v>
       </c>
       <c r="AC46" s="15">
-        <v>-230.24999999999994</v>
+        <v>-276.07692307692315</v>
       </c>
       <c r="AD46" s="19">
-        <v>6945</v>
+        <v>5926</v>
       </c>
       <c r="AE46" s="20">
-        <v>8056.2</v>
+        <v>6874.16</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6128,19 +6132,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" s="17">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="V47" s="14">
-        <v>2.2000000000000002</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="W47" s="16">
         <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-11.636363636363637</v>
+        <v>-12.636363636363637</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6158,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE47" s="20">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6307,34 +6311,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F49" s="14">
-        <v>554.48</v>
+        <v>519.67999999999995</v>
       </c>
       <c r="G49" s="14">
-        <v>8.5012126111560224</v>
+        <v>7.967663702506063</v>
       </c>
       <c r="H49" s="30">
         <v>1237</v>
       </c>
       <c r="I49" s="15">
-        <v>-84.272727272727252</v>
+        <v>-114.27272727272725</v>
       </c>
       <c r="J49" s="16">
-        <v>427</v>
+        <v>279</v>
       </c>
       <c r="K49" s="13">
-        <v>495.32</v>
+        <v>323.64</v>
       </c>
       <c r="L49" s="14">
-        <v>7.6188158961881589</v>
+        <v>4.9781021897810218</v>
       </c>
       <c r="M49" s="30">
         <v>1233</v>
       </c>
       <c r="N49" s="15">
-        <v>-133.4545454545455</v>
+        <v>-281.4545454545455</v>
       </c>
       <c r="O49" s="16">
         <v>0</v>
@@ -6352,40 +6356,40 @@
         <v>-101.81818181818181</v>
       </c>
       <c r="T49" s="18">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="U49" s="17">
-        <v>100.91999999999999</v>
+        <v>56.839999999999996</v>
       </c>
       <c r="V49" s="14">
-        <v>8.25</v>
+        <v>4.6465517241379315</v>
       </c>
       <c r="W49" s="16">
         <v>232</v>
       </c>
       <c r="X49" s="15">
-        <v>-71.181818181818187</v>
+        <v>-109.18181818181819</v>
       </c>
       <c r="Y49" s="18">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Z49" s="17">
-        <v>73.08</v>
+        <v>64.959999999999994</v>
       </c>
       <c r="AA49" s="14">
-        <v>13.03448275862069</v>
+        <v>11.934426229508196</v>
       </c>
       <c r="AB49" s="16">
-        <v>106.33333333333333</v>
+        <v>103.23076923076924</v>
       </c>
       <c r="AC49" s="15">
-        <v>-9.5</v>
+        <v>-14.384615384615387</v>
       </c>
       <c r="AD49" s="19">
-        <v>1055</v>
+        <v>832</v>
       </c>
       <c r="AE49" s="20">
-        <v>1223.8</v>
+        <v>965.11999999999989</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6420,85 +6424,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>306</v>
+        <v>2359</v>
       </c>
       <c r="F50" s="14">
-        <v>354.96</v>
+        <v>2736.4399999999996</v>
       </c>
       <c r="G50" s="14">
-        <v>1.2004279600570613</v>
+        <v>9.2542796005706141</v>
       </c>
       <c r="H50" s="30">
         <v>5608</v>
       </c>
       <c r="I50" s="15">
-        <v>-2243.090909090909</v>
+        <v>-190.09090909090901</v>
       </c>
       <c r="J50" s="16">
-        <v>4125</v>
+        <v>1674</v>
       </c>
       <c r="K50" s="13">
-        <v>4785</v>
+        <v>1941.84</v>
       </c>
       <c r="L50" s="14">
-        <v>25.377516778523493</v>
+        <v>10.298657718120806</v>
       </c>
       <c r="M50" s="30">
         <v>3576</v>
       </c>
       <c r="N50" s="15">
-        <v>2499.545454545455</v>
+        <v>48.545454545454731</v>
       </c>
       <c r="O50" s="16">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="P50" s="17">
-        <v>95.11999999999999</v>
+        <v>49.879999999999995</v>
       </c>
       <c r="Q50" s="14">
-        <v>3.7583333333333337</v>
+        <v>1.9708333333333334</v>
       </c>
       <c r="R50" s="16">
         <v>480</v>
       </c>
       <c r="S50" s="15">
-        <v>-354.36363636363632</v>
+        <v>-393.36363636363632</v>
       </c>
       <c r="T50" s="18">
-        <v>490</v>
+        <v>355</v>
       </c>
       <c r="U50" s="17">
-        <v>568.4</v>
+        <v>411.79999999999995</v>
       </c>
       <c r="V50" s="14">
-        <v>6.1284820920977827</v>
+        <v>4.4400227401932915</v>
       </c>
       <c r="W50" s="16">
         <v>1759</v>
       </c>
       <c r="X50" s="15">
-        <v>-709.31818181818176</v>
+        <v>-844.31818181818176</v>
       </c>
       <c r="Y50" s="18">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="Z50" s="17">
-        <v>129.91999999999999</v>
+        <v>121.8</v>
       </c>
       <c r="AA50" s="14">
-        <v>9.9555555555555557</v>
+        <v>9.8201438848920866</v>
       </c>
       <c r="AB50" s="16">
-        <v>247.5</v>
+        <v>235.23076923076923</v>
       </c>
       <c r="AC50" s="15">
-        <v>-56.75</v>
+        <v>-55.384615384615387</v>
       </c>
       <c r="AD50" s="19">
-        <v>5115</v>
+        <v>4536</v>
       </c>
       <c r="AE50" s="20">
-        <v>5933.4</v>
+        <v>5261.7599999999993</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6536,40 +6540,40 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="F51" s="14">
-        <v>445.43999999999994</v>
+        <v>481.4</v>
       </c>
       <c r="G51" s="14">
-        <v>6.6467348544453184</v>
+        <v>7.1833202202989774</v>
       </c>
       <c r="H51" s="30">
         <v>1271</v>
       </c>
       <c r="I51" s="15">
-        <v>-193.72727272727275</v>
+        <v>-162.72727272727275</v>
       </c>
       <c r="J51" s="16">
-        <v>2431</v>
+        <v>2940</v>
       </c>
       <c r="K51" s="13">
-        <v>2819.9599999999996</v>
+        <v>3410.3999999999996</v>
       </c>
       <c r="L51" s="14">
-        <v>54.573469387755104</v>
+        <v>66</v>
       </c>
       <c r="M51" s="30">
         <v>980</v>
       </c>
       <c r="N51" s="15">
-        <v>1985.5454545454545</v>
+        <v>2494.5454545454545</v>
       </c>
       <c r="O51" s="16">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="P51" s="17">
-        <v>269.12</v>
+        <v>228.51999999999998</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
@@ -6578,43 +6582,43 @@
         <v>0</v>
       </c>
       <c r="S51" s="15">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="T51" s="18">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="U51" s="17">
-        <v>614.79999999999995</v>
+        <v>551</v>
       </c>
       <c r="V51" s="14">
-        <v>21.6728624535316</v>
+        <v>19.423791821561338</v>
       </c>
       <c r="W51" s="16">
         <v>538</v>
       </c>
       <c r="X51" s="15">
-        <v>163.18181818181819</v>
+        <v>108.18181818181819</v>
       </c>
       <c r="Y51" s="18">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Z51" s="17">
-        <v>128.76</v>
+        <v>127.6</v>
       </c>
       <c r="AA51" s="14">
-        <v>28.340425531914899</v>
+        <v>27.5</v>
       </c>
       <c r="AB51" s="16">
-        <v>86.166666666666657</v>
+        <v>88</v>
       </c>
       <c r="AC51" s="15">
-        <v>52.250000000000007</v>
+        <v>50</v>
       </c>
       <c r="AD51" s="19">
-        <v>3688</v>
+        <v>4137</v>
       </c>
       <c r="AE51" s="20">
-        <v>4278.08</v>
+        <v>4798.92</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6653,34 +6657,34 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>3709</v>
+        <v>3123</v>
       </c>
       <c r="F52" s="14">
-        <v>3004.2900000000004</v>
+        <v>2529.63</v>
       </c>
       <c r="G52" s="14">
-        <v>30.838246409674984</v>
+        <v>25.965986394557824</v>
       </c>
       <c r="H52" s="30">
         <v>2646</v>
       </c>
       <c r="I52" s="15">
-        <v>2506.272727272727</v>
+        <v>1920.2727272727273</v>
       </c>
       <c r="J52" s="16">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="K52" s="13">
-        <v>141.75</v>
+        <v>59.13</v>
       </c>
       <c r="L52" s="14">
-        <v>1.9886363636363635</v>
+        <v>0.82954545454545459</v>
       </c>
       <c r="M52" s="30">
         <v>1936</v>
       </c>
       <c r="N52" s="15">
-        <v>-705</v>
+        <v>-807</v>
       </c>
       <c r="O52" s="16">
         <v>0</v>
@@ -6698,19 +6702,19 @@
         <v>-452.72727272727275</v>
       </c>
       <c r="T52" s="18">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="U52" s="17">
-        <v>456.03000000000003</v>
+        <v>446.31</v>
       </c>
       <c r="V52" s="14">
-        <v>13.746947835738069</v>
+        <v>13.453940066592676</v>
       </c>
       <c r="W52" s="16">
         <v>901</v>
       </c>
       <c r="X52" s="15">
-        <v>-51.318181818181756</v>
+        <v>-63.318181818181756</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6722,16 +6726,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>42.166666666666671</v>
+        <v>38.92307692307692</v>
       </c>
       <c r="AC52" s="15">
-        <v>-28.750000000000004</v>
+        <v>-26.538461538461537</v>
       </c>
       <c r="AD52" s="19">
-        <v>4447</v>
+        <v>3747</v>
       </c>
       <c r="AE52" s="20">
-        <v>3602.07</v>
+        <v>3035.07</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6766,85 +6770,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1998</v>
+        <v>1867</v>
       </c>
       <c r="F53" s="14">
-        <v>1618.38</v>
+        <v>1512.2700000000002</v>
       </c>
       <c r="G53" s="14">
-        <v>8.5600778967867583</v>
+        <v>7.9988315481986367</v>
       </c>
       <c r="H53" s="30">
         <v>5135</v>
       </c>
       <c r="I53" s="15">
-        <v>-336.09090909090901</v>
+        <v>-467.09090909090901</v>
       </c>
       <c r="J53" s="16">
-        <v>2216</v>
+        <v>1154</v>
       </c>
       <c r="K53" s="13">
-        <v>1794.96</v>
+        <v>934.74</v>
       </c>
       <c r="L53" s="14">
-        <v>15.354960629921257</v>
+        <v>7.9962204724409434</v>
       </c>
       <c r="M53" s="30">
         <v>3175.0000000000005</v>
       </c>
       <c r="N53" s="15">
-        <v>772.81818181818153</v>
+        <v>-289.18181818181847</v>
       </c>
       <c r="O53" s="16">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="P53" s="17">
-        <v>107.73</v>
+        <v>55.89</v>
       </c>
       <c r="Q53" s="14">
-        <v>3.3137032842582101</v>
+        <v>1.7191392978482445</v>
       </c>
       <c r="R53" s="16">
         <v>883.00000000000011</v>
       </c>
       <c r="S53" s="15">
-        <v>-669.72727272727275</v>
+        <v>-733.72727272727275</v>
       </c>
       <c r="T53" s="18">
-        <v>851</v>
+        <v>751</v>
       </c>
       <c r="U53" s="17">
-        <v>689.31000000000006</v>
+        <v>608.31000000000006</v>
       </c>
       <c r="V53" s="14">
-        <v>11.339794064203513</v>
+        <v>10.007268322228953</v>
       </c>
       <c r="W53" s="16">
         <v>1651</v>
       </c>
       <c r="X53" s="15">
-        <v>-274.68181818181824</v>
+        <v>-374.68181818181824</v>
       </c>
       <c r="Y53" s="18">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Z53" s="17">
-        <v>28.35</v>
+        <v>23.490000000000002</v>
       </c>
       <c r="AA53" s="14">
-        <v>4.666666666666667</v>
+        <v>4.053763440860215</v>
       </c>
       <c r="AB53" s="16">
-        <v>165</v>
+        <v>157.38461538461539</v>
       </c>
       <c r="AC53" s="15">
-        <v>-77.5</v>
+        <v>-78.307692307692307</v>
       </c>
       <c r="AD53" s="19">
-        <v>5233</v>
+        <v>3870</v>
       </c>
       <c r="AE53" s="20">
-        <v>4238.7300000000005</v>
+        <v>3134.7000000000003</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6879,85 +6883,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1563</v>
+        <v>1475</v>
       </c>
       <c r="F54" s="14">
-        <v>1266.03</v>
+        <v>1194.75</v>
       </c>
       <c r="G54" s="14">
-        <v>9.9901220220801843</v>
+        <v>9.4276583381754779</v>
       </c>
       <c r="H54" s="30">
         <v>3442</v>
       </c>
       <c r="I54" s="15">
-        <v>-1.5454545454547315</v>
+        <v>-89.545454545454731</v>
       </c>
       <c r="J54" s="16">
-        <v>5744</v>
+        <v>5624</v>
       </c>
       <c r="K54" s="13">
-        <v>4652.6400000000003</v>
+        <v>4555.4400000000005</v>
       </c>
       <c r="L54" s="14">
-        <v>72.375715922107673</v>
+        <v>70.863688430698744</v>
       </c>
       <c r="M54" s="30">
         <v>1746</v>
       </c>
       <c r="N54" s="15">
-        <v>4950.363636363636</v>
+        <v>4830.363636363636</v>
       </c>
       <c r="O54" s="16">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="P54" s="17">
-        <v>199.26000000000002</v>
+        <v>188.73000000000002</v>
       </c>
       <c r="Q54" s="14">
-        <v>15.824561403508772</v>
+        <v>14.988304093567251</v>
       </c>
       <c r="R54" s="16">
         <v>342</v>
       </c>
       <c r="S54" s="15">
-        <v>-64.909090909090878</v>
+        <v>-77.909090909090878</v>
       </c>
       <c r="T54" s="18">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="U54" s="17">
-        <v>494.91</v>
+        <v>463.32000000000005</v>
       </c>
       <c r="V54" s="14">
-        <v>21.750809061488674</v>
+        <v>20.362459546925567</v>
       </c>
       <c r="W54" s="16">
         <v>618</v>
       </c>
       <c r="X54" s="15">
-        <v>189.63636363636363</v>
+        <v>150.63636363636363</v>
       </c>
       <c r="Y54" s="18">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="Z54" s="17">
-        <v>123.93</v>
+        <v>119.07000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="AB54" s="16">
-        <v>187</v>
+        <v>177.69230769230768</v>
       </c>
       <c r="AC54" s="15">
-        <v>25.5</v>
+        <v>25.846153846153854</v>
       </c>
       <c r="AD54" s="19">
-        <v>8317</v>
+        <v>8051</v>
       </c>
       <c r="AE54" s="20">
-        <v>6736.77</v>
+        <v>6521.31</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6992,85 +6996,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>3897</v>
+        <v>3854</v>
       </c>
       <c r="F55" s="14">
-        <v>3156.57</v>
+        <v>3121.7400000000002</v>
       </c>
       <c r="G55" s="14">
-        <v>31.473568281938327</v>
+        <v>31.126284875183554</v>
       </c>
       <c r="H55" s="30">
         <v>2724</v>
       </c>
       <c r="I55" s="15">
-        <v>2658.818181818182</v>
+        <v>2615.818181818182</v>
       </c>
       <c r="J55" s="16">
-        <v>7232</v>
+        <v>6980</v>
       </c>
       <c r="K55" s="13">
-        <v>5857.92</v>
+        <v>5653.8</v>
       </c>
       <c r="L55" s="14">
-        <v>81.383120204603571</v>
+        <v>78.5473145780051</v>
       </c>
       <c r="M55" s="30">
         <v>1955.0000000000002</v>
       </c>
       <c r="N55" s="15">
-        <v>6343.363636363636</v>
+        <v>6091.363636363636</v>
       </c>
       <c r="O55" s="16">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="P55" s="17">
-        <v>164.43</v>
+        <v>154.71</v>
       </c>
       <c r="Q55" s="14">
-        <v>9.9244444444444451</v>
+        <v>9.3377777777777791</v>
       </c>
       <c r="R55" s="16">
         <v>449.99999999999994</v>
       </c>
       <c r="S55" s="15">
-        <v>-206.09090909090907</v>
+        <v>-218.09090909090907</v>
       </c>
       <c r="T55" s="18">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="U55" s="17">
-        <v>465.75000000000006</v>
+        <v>446.31</v>
       </c>
       <c r="V55" s="14">
-        <v>17.842031029619182</v>
+        <v>17.09732016925247</v>
       </c>
       <c r="W55" s="16">
         <v>709</v>
       </c>
       <c r="X55" s="15">
-        <v>91.590909090909122</v>
+        <v>67.590909090909122</v>
       </c>
       <c r="Y55" s="18">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="Z55" s="17">
-        <v>137.70000000000002</v>
+        <v>132.84</v>
       </c>
       <c r="AA55" s="14">
-        <v>20</v>
+        <v>20.304761904761904</v>
       </c>
       <c r="AB55" s="16">
-        <v>187</v>
+        <v>177.69230769230768</v>
       </c>
       <c r="AC55" s="15">
-        <v>42.5</v>
+        <v>42.846153846153854</v>
       </c>
       <c r="AD55" s="19">
-        <v>12077</v>
+        <v>11740</v>
       </c>
       <c r="AE55" s="20">
-        <v>9782.3700000000008</v>
+        <v>9509.4000000000015</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7105,34 +7109,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F56" s="14">
-        <v>1430.52</v>
+        <v>1420.04</v>
       </c>
       <c r="G56" s="14">
-        <v>24.072144288577153</v>
+        <v>23.895791583166332</v>
       </c>
       <c r="H56" s="30">
         <v>499</v>
       </c>
       <c r="I56" s="15">
-        <v>319.18181818181813</v>
+        <v>315.18181818181813</v>
       </c>
       <c r="J56" s="32">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="K56" s="13">
-        <v>662.86</v>
+        <v>804.34</v>
       </c>
       <c r="L56" s="14">
-        <v>12.507865168539325</v>
+        <v>15.177528089887641</v>
       </c>
       <c r="M56" s="30">
         <v>445</v>
       </c>
       <c r="N56" s="15">
-        <v>50.727272727272748</v>
+        <v>104.72727272727275</v>
       </c>
       <c r="O56" s="32">
         <v>1</v>
@@ -7165,25 +7169,25 @@
         <v>-54.181818181818187</v>
       </c>
       <c r="Y56" s="18">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="Z56" s="17">
-        <v>151.96</v>
+        <v>131</v>
       </c>
       <c r="AA56" s="14">
-        <v>26.76923076923077</v>
+        <v>25</v>
       </c>
       <c r="AB56" s="16">
-        <v>47.666666666666664</v>
+        <v>44</v>
       </c>
       <c r="AC56" s="15">
-        <v>25.5</v>
+        <v>20</v>
       </c>
       <c r="AD56" s="19">
-        <v>932</v>
+        <v>974</v>
       </c>
       <c r="AE56" s="20">
-        <v>2441.84</v>
+        <v>2551.88</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7218,49 +7222,49 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>287</v>
+        <v>456</v>
       </c>
       <c r="F57" s="14">
-        <v>751.94</v>
+        <v>1194.72</v>
       </c>
       <c r="G57" s="14">
-        <v>6.9460946094609461</v>
+        <v>11.036303630363037</v>
       </c>
       <c r="H57" s="30">
         <v>909</v>
       </c>
       <c r="I57" s="15">
-        <v>-126.18181818181819</v>
+        <v>42.818181818181813</v>
       </c>
       <c r="J57" s="32">
-        <v>259</v>
+        <v>398</v>
       </c>
       <c r="K57" s="13">
-        <v>678.58</v>
+        <v>1042.76</v>
       </c>
       <c r="L57" s="14">
-        <v>6.6255813953488376</v>
+        <v>10.18139534883721</v>
       </c>
       <c r="M57" s="30">
         <v>859.99999999999989</v>
       </c>
       <c r="N57" s="15">
-        <v>-131.90909090909088</v>
+        <v>7.0909090909091219</v>
       </c>
       <c r="O57" s="32">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="P57" s="17">
-        <v>49.78</v>
+        <v>34.06</v>
       </c>
       <c r="Q57" s="14">
-        <v>6.0579710144927539</v>
+        <v>4.1449275362318838</v>
       </c>
       <c r="R57" s="16">
         <v>69</v>
       </c>
       <c r="S57" s="15">
-        <v>-43.727272727272727</v>
+        <v>-49.727272727272727</v>
       </c>
       <c r="T57" s="18">
         <v>51</v>
@@ -7278,25 +7282,25 @@
         <v>-159.68181818181819</v>
       </c>
       <c r="Y57" s="18">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="Z57" s="17">
-        <v>178.16</v>
+        <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>25.5</v>
+        <v>24.375</v>
       </c>
       <c r="AB57" s="16">
-        <v>58.666666666666664</v>
+        <v>54.15384615384616</v>
       </c>
       <c r="AC57" s="15">
-        <v>28</v>
+        <v>23.076923076923073</v>
       </c>
       <c r="AD57" s="19">
-        <v>684</v>
+        <v>978</v>
       </c>
       <c r="AE57" s="20">
-        <v>1792.0800000000002</v>
+        <v>2562.36</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7331,34 +7335,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F58" s="14">
-        <v>413.96000000000004</v>
+        <v>398.24</v>
       </c>
       <c r="G58" s="14">
-        <v>8.2369668246445489</v>
+        <v>7.9241706161137433</v>
       </c>
       <c r="H58" s="30">
         <v>422</v>
       </c>
       <c r="I58" s="15">
-        <v>-33.818181818181841</v>
+        <v>-39.818181818181841</v>
       </c>
       <c r="J58" s="32">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="K58" s="13">
-        <v>382.52000000000004</v>
+        <v>471.6</v>
       </c>
       <c r="L58" s="14">
-        <v>7.8918918918918921</v>
+        <v>9.7297297297297298</v>
       </c>
       <c r="M58" s="30">
         <v>407</v>
       </c>
       <c r="N58" s="15">
-        <v>-39</v>
+        <v>-5</v>
       </c>
       <c r="O58" s="32">
         <v>31</v>
@@ -7391,25 +7395,25 @@
         <v>-71.681818181818187</v>
       </c>
       <c r="Y58" s="18">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z58" s="17">
-        <v>125.76</v>
+        <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>21.333333333333332</v>
+        <v>20.222222222222221</v>
       </c>
       <c r="AB58" s="16">
-        <v>49.5</v>
+        <v>45.692307692307693</v>
       </c>
       <c r="AC58" s="15">
-        <v>14.25</v>
+        <v>10.846153846153843</v>
       </c>
       <c r="AD58" s="19">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="AE58" s="20">
-        <v>1013.94</v>
+        <v>1071.5800000000002</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7447,34 +7451,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F59" s="14">
-        <v>351.08000000000004</v>
+        <v>303.92</v>
       </c>
       <c r="G59" s="14">
-        <v>5.7917485265225936</v>
+        <v>5.0137524557956779</v>
       </c>
       <c r="H59" s="30">
         <v>509</v>
       </c>
       <c r="I59" s="15">
-        <v>-97.363636363636374</v>
+        <v>-115.36363636363637</v>
       </c>
       <c r="J59" s="32">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="K59" s="13">
-        <v>285.58</v>
+        <v>222.70000000000002</v>
       </c>
       <c r="L59" s="14">
-        <v>5.935643564356436</v>
+        <v>4.6287128712871288</v>
       </c>
       <c r="M59" s="30">
         <v>404</v>
       </c>
       <c r="N59" s="15">
-        <v>-74.636363636363626</v>
+        <v>-98.636363636363626</v>
       </c>
       <c r="O59" s="32">
         <v>0</v>
@@ -7507,25 +7511,25 @@
         <v>-57.954545454545467</v>
       </c>
       <c r="Y59" s="18">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Z59" s="17">
-        <v>146.72</v>
+        <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>44.8</v>
+        <v>45.933333333333337</v>
       </c>
       <c r="AB59" s="16">
-        <v>27.5</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="AC59" s="15">
-        <v>37.25</v>
+        <v>35.692307692307693</v>
       </c>
       <c r="AD59" s="19">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="AE59" s="20">
-        <v>979.88</v>
+        <v>861.98</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7599,10 +7603,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7632,17 +7636,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>156630.57999999996</v>
+        <v>168508.88999999996</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>36.631785406215464</v>
+        <v>42.535271870104289</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7680,11 +7684,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>191450.65999999997</v>
+        <v>159086.01000000004</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>44.77528904635556</v>
+        <v>40.156734081389608</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7722,11 +7726,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>12819.699999999999</v>
+        <v>10226.289999999997</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>2.9981916645655047</v>
+        <v>2.581335770311755</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7764,11 +7768,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>52403.520000000011</v>
+        <v>45443.56</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>12.255809173217138</v>
+        <v>11.470932954014456</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7806,11 +7810,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>14011.010000000002</v>
+        <v>12765.170000000002</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>3.2768078343599258</v>
+        <v>3.2222037449662118</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7842,19 +7846,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>427581.07000000012</v>
-      </c>
-      <c r="E67" s="66">
+        <v>396162.71999999986</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7954,17 +7958,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>117915</v>
+        <v>124401</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>36.792788407533607</v>
+        <v>43.505067390346426</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8001,11 +8005,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>147191</v>
+        <v>113397</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>45.927721820746122</v>
+        <v>39.65678834465249</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8043,11 +8047,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>9711</v>
+        <v>8011</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>3.0301044669936719</v>
+        <v>2.8015779203066313</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8085,11 +8089,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>36378</v>
+        <v>31625</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>11.350956678024488</v>
+        <v>11.059780517999902</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8127,11 +8131,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>9289</v>
+        <v>8512</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>2.8984286267021129</v>
+        <v>2.9767858266945506</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8163,19 +8167,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>320484</v>
-      </c>
-      <c r="E75" s="66">
+        <v>285946</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8722,6 +8726,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8730,17 +8745,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62468858-632B-4EB1-9912-1DD114D93E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6A1D5D-0321-4318-A608-A7D55026C137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1180,6 +1180,7 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1318,6 +1319,7 @@
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1645,242 +1647,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2311,13 +2313,13 @@
         <v>212.16000000000003</v>
       </c>
       <c r="AA13" s="14">
-        <v>4.6620689655172418</v>
+        <v>4.9078651685393266</v>
       </c>
       <c r="AB13" s="16">
-        <v>736.15384615384608</v>
+        <v>699.28571428571422</v>
       </c>
       <c r="AC13" s="15">
-        <v>-345.92307692307691</v>
+        <v>-320.78571428571422</v>
       </c>
       <c r="AD13" s="19">
         <v>8142</v>
@@ -2425,13 +2427,13 @@
         <v>49.29</v>
       </c>
       <c r="AA14" s="14">
-        <v>6.1060606060606064</v>
+        <v>6.5757575757575752</v>
       </c>
       <c r="AB14" s="16">
-        <v>111.69230769230768</v>
+        <v>103.71428571428572</v>
       </c>
       <c r="AC14" s="15">
-        <v>-45.153846153846146</v>
+        <v>-39.714285714285722</v>
       </c>
       <c r="AD14" s="19">
         <v>164</v>
@@ -2539,13 +2541,13 @@
         <v>286.22999999999996</v>
       </c>
       <c r="AA15" s="14">
-        <v>14.209302325581396</v>
+        <v>14.304347826086955</v>
       </c>
       <c r="AB15" s="16">
-        <v>218.30769230769232</v>
+        <v>216.85714285714286</v>
       </c>
       <c r="AC15" s="15">
-        <v>-7.8461538461538396</v>
+        <v>-6.8571428571428612</v>
       </c>
       <c r="AD15" s="19">
         <v>4891</v>
@@ -2652,13 +2654,13 @@
         <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>5.7017543859649118</v>
+        <v>6.1403508771929829</v>
       </c>
       <c r="AB16" s="16">
-        <v>96.461538461538467</v>
+        <v>89.571428571428569</v>
       </c>
       <c r="AC16" s="15">
-        <v>-40.769230769230774</v>
+        <v>-36.071428571428569</v>
       </c>
       <c r="AD16" s="19">
         <v>769</v>
@@ -2765,13 +2767,13 @@
         <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>23.833333333333329</v>
+        <v>25.666666666666664</v>
       </c>
       <c r="AB17" s="16">
-        <v>10.153846153846155</v>
+        <v>9.4285714285714288</v>
       </c>
       <c r="AC17" s="15">
-        <v>4.0769230769230758</v>
+        <v>4.5714285714285712</v>
       </c>
       <c r="AD17" s="19">
         <v>128</v>
@@ -2878,13 +2880,13 @@
         <v>151.19999999999999</v>
       </c>
       <c r="AA18" s="14">
-        <v>17.049180327868854</v>
+        <v>17.591623036649217</v>
       </c>
       <c r="AB18" s="16">
-        <v>309.69230769230768</v>
+        <v>300.14285714285711</v>
       </c>
       <c r="AC18" s="15">
-        <v>28.84615384615384</v>
+        <v>35.35714285714289</v>
       </c>
       <c r="AD18" s="19">
         <v>15413</v>
@@ -2991,13 +2993,13 @@
         <v>102.69</v>
       </c>
       <c r="AA19" s="14">
-        <v>14.033112582781458</v>
+        <v>14.915032679738562</v>
       </c>
       <c r="AB19" s="16">
-        <v>255.53846153846152</v>
+        <v>240.42857142857144</v>
       </c>
       <c r="AC19" s="15">
-        <v>-11.230769230769226</v>
+        <v>-0.92857142857144481</v>
       </c>
       <c r="AD19" s="19">
         <v>1828</v>
@@ -3104,13 +3106,13 @@
         <v>148.05000000000001</v>
       </c>
       <c r="AA20" s="14">
-        <v>16.078947368421051</v>
+        <v>17.135416666666664</v>
       </c>
       <c r="AB20" s="16">
-        <v>321.53846153846155</v>
+        <v>301.71428571428572</v>
       </c>
       <c r="AC20" s="15">
-        <v>15.769230769230774</v>
+        <v>29.285714285714278</v>
       </c>
       <c r="AD20" s="19">
         <v>4343</v>
@@ -3217,13 +3219,13 @@
         <v>289.94</v>
       </c>
       <c r="AA21" s="14">
-        <v>13.3</v>
+        <v>13.895522388059701</v>
       </c>
       <c r="AB21" s="16">
-        <v>440</v>
+        <v>421.14285714285711</v>
       </c>
       <c r="AC21" s="15">
-        <v>-34</v>
+        <v>-21.14285714285711</v>
       </c>
       <c r="AD21" s="19">
         <v>8206</v>
@@ -3330,13 +3332,13 @@
         <v>155.87</v>
       </c>
       <c r="AA22" s="14">
-        <v>33.196428571428577</v>
+        <v>33.932203389830505</v>
       </c>
       <c r="AB22" s="16">
-        <v>94.769230769230759</v>
+        <v>92.714285714285722</v>
       </c>
       <c r="AC22" s="15">
-        <v>78.384615384615387</v>
+        <v>79.785714285714278</v>
       </c>
       <c r="AD22" s="19">
         <v>4833</v>
@@ -3443,13 +3445,13 @@
         <v>167.04</v>
       </c>
       <c r="AA23" s="14">
-        <v>2.3517587939698492</v>
+        <v>2.4981412639405205</v>
       </c>
       <c r="AB23" s="16">
-        <v>1347.0769230769231</v>
+        <v>1268.1428571428571</v>
       </c>
       <c r="AC23" s="15">
-        <v>-774.46153846153845</v>
+        <v>-720.64285714285711</v>
       </c>
       <c r="AD23" s="19">
         <v>34078</v>
@@ -3556,13 +3558,13 @@
         <v>517.36</v>
       </c>
       <c r="AA24" s="14">
-        <v>11.368627450980391</v>
+        <v>12.054054054054054</v>
       </c>
       <c r="AB24" s="16">
-        <v>863.07692307692309</v>
+        <v>814</v>
       </c>
       <c r="AC24" s="15">
-        <v>-142.46153846153845</v>
+        <v>-109</v>
       </c>
       <c r="AD24" s="19">
         <v>20987</v>
@@ -3669,13 +3671,13 @@
         <v>715.71999999999991</v>
       </c>
       <c r="AA25" s="14">
-        <v>21.915300546448087</v>
+        <v>23.409214092140921</v>
       </c>
       <c r="AB25" s="16">
-        <v>619.38461538461536</v>
+        <v>579.85714285714289</v>
       </c>
       <c r="AC25" s="15">
-        <v>194.69230769230768</v>
+        <v>221.64285714285711</v>
       </c>
       <c r="AD25" s="19">
         <v>17122</v>
@@ -3782,13 +3784,13 @@
         <v>628.71999999999991</v>
       </c>
       <c r="AA26" s="14">
-        <v>12.318181818181818</v>
+        <v>13.196521739130436</v>
       </c>
       <c r="AB26" s="16">
-        <v>968</v>
+        <v>903.57142857142856</v>
       </c>
       <c r="AC26" s="15">
-        <v>-118</v>
+        <v>-74.071428571428555</v>
       </c>
       <c r="AD26" s="19">
         <v>29226</v>
@@ -3895,13 +3897,13 @@
         <v>524.31999999999994</v>
       </c>
       <c r="AA27" s="14">
-        <v>36.725000000000001</v>
+        <v>38.822085889570559</v>
       </c>
       <c r="AB27" s="16">
-        <v>270.76923076923077</v>
+        <v>256.14285714285711</v>
       </c>
       <c r="AC27" s="15">
-        <v>267.38461538461536</v>
+        <v>277.35714285714289</v>
       </c>
       <c r="AD27" s="19">
         <v>6440</v>
@@ -4008,13 +4010,13 @@
         <v>446.59999999999997</v>
       </c>
       <c r="AA28" s="14">
-        <v>21.951754385964911</v>
+        <v>22.647058823529413</v>
       </c>
       <c r="AB28" s="16">
-        <v>385.84615384615387</v>
+        <v>374</v>
       </c>
       <c r="AC28" s="15">
-        <v>121.92307692307691</v>
+        <v>130</v>
       </c>
       <c r="AD28" s="19">
         <v>9306</v>
@@ -4121,13 +4123,13 @@
         <v>447.76</v>
       </c>
       <c r="AA29" s="14">
-        <v>21.262711864406782</v>
+        <v>22.610878661087863</v>
       </c>
       <c r="AB29" s="16">
-        <v>399.38461538461536</v>
+        <v>375.57142857142861</v>
       </c>
       <c r="AC29" s="15">
-        <v>113.69230769230768</v>
+        <v>129.92857142857139</v>
       </c>
       <c r="AD29" s="19">
         <v>3930</v>
@@ -4234,13 +4236,13 @@
         <v>106.72</v>
       </c>
       <c r="AA30" s="14">
-        <v>5.890625</v>
+        <v>6.34375</v>
       </c>
       <c r="AB30" s="16">
-        <v>108.30769230769232</v>
+        <v>100.57142857142857</v>
       </c>
       <c r="AC30" s="15">
-        <v>-44.846153846153854</v>
+        <v>-39.571428571428569</v>
       </c>
       <c r="AD30" s="19">
         <v>1603</v>
@@ -4347,13 +4349,13 @@
         <v>172.96</v>
       </c>
       <c r="AA31" s="14">
-        <v>29.095238095238095</v>
+        <v>31.333333333333332</v>
       </c>
       <c r="AB31" s="16">
-        <v>35.53846153846154</v>
+        <v>33</v>
       </c>
       <c r="AC31" s="15">
-        <v>22.76923076923077</v>
+        <v>24.5</v>
       </c>
       <c r="AD31" s="19">
         <v>1266</v>
@@ -4460,13 +4462,13 @@
         <v>1203.5</v>
       </c>
       <c r="AA32" s="14">
-        <v>62.833333333333336</v>
+        <v>66.557377049180332</v>
       </c>
       <c r="AB32" s="16">
-        <v>101.53846153846153</v>
+        <v>95.857142857142847</v>
       </c>
       <c r="AC32" s="15">
-        <v>220.76923076923077</v>
+        <v>224.64285714285717</v>
       </c>
       <c r="AD32" s="19">
         <v>4717</v>
@@ -4573,13 +4575,13 @@
         <v>340.3</v>
       </c>
       <c r="AA33" s="14">
-        <v>6.1264367816091951</v>
+        <v>6.5977011494252871</v>
       </c>
       <c r="AB33" s="16">
-        <v>294.46153846153845</v>
+        <v>273.42857142857144</v>
       </c>
       <c r="AC33" s="15">
-        <v>-118.76923076923077</v>
+        <v>-104.42857142857144</v>
       </c>
       <c r="AD33" s="19">
         <v>6153</v>
@@ -4799,13 +4801,13 @@
         <v>498.78</v>
       </c>
       <c r="AA35" s="14">
-        <v>21.857142857142858</v>
+        <v>22.666666666666668</v>
       </c>
       <c r="AB35" s="16">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="AC35" s="15">
-        <v>96</v>
+        <v>103.5</v>
       </c>
       <c r="AD35" s="19">
         <v>5831</v>
@@ -4912,13 +4914,13 @@
         <v>547.67999999999995</v>
       </c>
       <c r="AA36" s="14">
-        <v>13.196374622356497</v>
+        <v>13.917159763313609</v>
       </c>
       <c r="AB36" s="16">
-        <v>560.15384615384608</v>
+        <v>531.14285714285711</v>
       </c>
       <c r="AC36" s="15">
-        <v>-45.923076923076849</v>
+        <v>-26.14285714285711</v>
       </c>
       <c r="AD36" s="19">
         <v>10207</v>
@@ -5028,10 +5030,10 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>416.30769230769232</v>
+        <v>386.57142857142861</v>
       </c>
       <c r="AC37" s="15">
-        <v>-283.84615384615387</v>
+        <v>-263.57142857142861</v>
       </c>
       <c r="AD37" s="19">
         <v>3619</v>
@@ -5138,13 +5140,13 @@
         <v>425.42999999999995</v>
       </c>
       <c r="AA38" s="14">
-        <v>9.7220630372492831</v>
+        <v>10.264044943820224</v>
       </c>
       <c r="AB38" s="16">
-        <v>590.61538461538464</v>
+        <v>559.42857142857144</v>
       </c>
       <c r="AC38" s="15">
-        <v>-141.69230769230768</v>
+        <v>-120.42857142857144</v>
       </c>
       <c r="AD38" s="19">
         <v>2779</v>
@@ -5251,13 +5253,13 @@
         <v>751.43</v>
       </c>
       <c r="AA39" s="14">
-        <v>93.640625</v>
+        <v>100.84375</v>
       </c>
       <c r="AB39" s="16">
-        <v>108.30769230769232</v>
+        <v>100.57142857142857</v>
       </c>
       <c r="AC39" s="15">
-        <v>387.15384615384613</v>
+        <v>392.42857142857144</v>
       </c>
       <c r="AD39" s="19">
         <v>6723</v>
@@ -5364,13 +5366,13 @@
         <v>766.09999999999991</v>
       </c>
       <c r="AA40" s="14">
-        <v>96.984126984126988</v>
+        <v>104.44444444444444</v>
       </c>
       <c r="AB40" s="16">
-        <v>106.61538461538461</v>
+        <v>99</v>
       </c>
       <c r="AC40" s="15">
-        <v>397.30769230769232</v>
+        <v>402.5</v>
       </c>
       <c r="AD40" s="19">
         <v>6320</v>
@@ -5477,13 +5479,13 @@
         <v>104.55000000000001</v>
       </c>
       <c r="AA41" s="14">
-        <v>3.4</v>
+        <v>3.6615384615384614</v>
       </c>
       <c r="AB41" s="16">
-        <v>110</v>
+        <v>102.14285714285715</v>
       </c>
       <c r="AC41" s="15">
-        <v>-58</v>
+        <v>-52.642857142857153</v>
       </c>
       <c r="AD41" s="19">
         <v>1270</v>
@@ -5590,13 +5592,13 @@
         <v>516.6</v>
       </c>
       <c r="AA42" s="14">
-        <v>19.157894736842103</v>
+        <v>20.631578947368421</v>
       </c>
       <c r="AB42" s="16">
-        <v>96.461538461538467</v>
+        <v>89.571428571428569</v>
       </c>
       <c r="AC42" s="15">
-        <v>18.230769230769226</v>
+        <v>22.928571428571431</v>
       </c>
       <c r="AD42" s="19">
         <v>1376</v>
@@ -5703,13 +5705,13 @@
         <v>248.23999999999998</v>
       </c>
       <c r="AA43" s="14">
-        <v>7.6428571428571432</v>
+        <v>8.0754716981132084</v>
       </c>
       <c r="AB43" s="16">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="AC43" s="15">
-        <v>-206</v>
+        <v>-183.5</v>
       </c>
       <c r="AD43" s="19">
         <v>5728</v>
@@ -5816,13 +5818,13 @@
         <v>382.79999999999995</v>
       </c>
       <c r="AA44" s="14">
-        <v>12.844311377245509</v>
+        <v>13.50877192982456</v>
       </c>
       <c r="AB44" s="16">
-        <v>565.23076923076928</v>
+        <v>537.42857142857144</v>
       </c>
       <c r="AC44" s="15">
-        <v>-55.384615384615415</v>
+        <v>-36.428571428571445</v>
       </c>
       <c r="AD44" s="19">
         <v>5789</v>
@@ -5929,13 +5931,13 @@
         <v>286.52</v>
       </c>
       <c r="AA45" s="14">
-        <v>9.2803468208092479</v>
+        <v>9.7134831460674143</v>
       </c>
       <c r="AB45" s="16">
-        <v>585.53846153846155</v>
+        <v>559.42857142857144</v>
       </c>
       <c r="AC45" s="15">
-        <v>-152.23076923076923</v>
+        <v>-134.42857142857144</v>
       </c>
       <c r="AD45" s="19">
         <v>5951</v>
@@ -6042,13 +6044,13 @@
         <v>124.11999999999999</v>
       </c>
       <c r="AA46" s="14">
-        <v>4.1897590361445776</v>
+        <v>4.4716417910447754</v>
       </c>
       <c r="AB46" s="16">
-        <v>561.84615384615392</v>
+        <v>526.42857142857144</v>
       </c>
       <c r="AC46" s="15">
-        <v>-276.07692307692315</v>
+        <v>-251.92857142857144</v>
       </c>
       <c r="AD46" s="19">
         <v>5926</v>
@@ -6377,13 +6379,13 @@
         <v>64.959999999999994</v>
       </c>
       <c r="AA49" s="14">
-        <v>11.934426229508196</v>
+        <v>12.25</v>
       </c>
       <c r="AB49" s="16">
-        <v>103.23076923076924</v>
+        <v>100.57142857142857</v>
       </c>
       <c r="AC49" s="15">
-        <v>-14.384615384615387</v>
+        <v>-12.571428571428569</v>
       </c>
       <c r="AD49" s="19">
         <v>832</v>
@@ -6490,13 +6492,13 @@
         <v>121.8</v>
       </c>
       <c r="AA50" s="14">
-        <v>9.8201438848920866</v>
+        <v>9.8657718120805367</v>
       </c>
       <c r="AB50" s="16">
-        <v>235.23076923076923</v>
+        <v>234.14285714285714</v>
       </c>
       <c r="AC50" s="15">
-        <v>-55.384615384615387</v>
+        <v>-54.642857142857139</v>
       </c>
       <c r="AD50" s="19">
         <v>4536</v>
@@ -6606,13 +6608,13 @@
         <v>127.6</v>
       </c>
       <c r="AA51" s="14">
-        <v>27.5</v>
+        <v>27.999999999999996</v>
       </c>
       <c r="AB51" s="16">
-        <v>88</v>
+        <v>86.428571428571431</v>
       </c>
       <c r="AC51" s="15">
-        <v>50</v>
+        <v>51.071428571428569</v>
       </c>
       <c r="AD51" s="19">
         <v>4137</v>
@@ -6726,10 +6728,10 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>38.92307692307692</v>
+        <v>36.142857142857139</v>
       </c>
       <c r="AC52" s="15">
-        <v>-26.538461538461537</v>
+        <v>-24.642857142857139</v>
       </c>
       <c r="AD52" s="19">
         <v>3747</v>
@@ -6836,13 +6838,13 @@
         <v>23.490000000000002</v>
       </c>
       <c r="AA53" s="14">
-        <v>4.053763440860215</v>
+        <v>4.0198019801980198</v>
       </c>
       <c r="AB53" s="16">
-        <v>157.38461538461539</v>
+        <v>158.71428571428572</v>
       </c>
       <c r="AC53" s="15">
-        <v>-78.307692307692307</v>
+        <v>-79.214285714285722</v>
       </c>
       <c r="AD53" s="19">
         <v>3870</v>
@@ -6949,13 +6951,13 @@
         <v>119.07000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>18.2</v>
+        <v>18.212389380530976</v>
       </c>
       <c r="AB54" s="16">
-        <v>177.69230769230768</v>
+        <v>177.57142857142856</v>
       </c>
       <c r="AC54" s="15">
-        <v>25.846153846153854</v>
+        <v>25.928571428571431</v>
       </c>
       <c r="AD54" s="19">
         <v>8051</v>
@@ -7062,13 +7064,13 @@
         <v>132.84</v>
       </c>
       <c r="AA55" s="14">
-        <v>20.304761904761904</v>
+        <v>20.318584070796462</v>
       </c>
       <c r="AB55" s="16">
-        <v>177.69230769230768</v>
+        <v>177.57142857142856</v>
       </c>
       <c r="AC55" s="15">
-        <v>42.846153846153854</v>
+        <v>42.928571428571431</v>
       </c>
       <c r="AD55" s="19">
         <v>11740</v>
@@ -7175,13 +7177,13 @@
         <v>131</v>
       </c>
       <c r="AA56" s="14">
-        <v>25</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="AB56" s="16">
-        <v>44</v>
+        <v>40.857142857142861</v>
       </c>
       <c r="AC56" s="15">
-        <v>20</v>
+        <v>22.142857142857139</v>
       </c>
       <c r="AD56" s="19">
         <v>974</v>
@@ -7288,13 +7290,13 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>24.375</v>
+        <v>26.25</v>
       </c>
       <c r="AB57" s="16">
-        <v>54.15384615384616</v>
+        <v>50.285714285714285</v>
       </c>
       <c r="AC57" s="15">
-        <v>23.076923076923073</v>
+        <v>25.714285714285715</v>
       </c>
       <c r="AD57" s="19">
         <v>978</v>
@@ -7401,13 +7403,13 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>20.222222222222221</v>
+        <v>21.777777777777779</v>
       </c>
       <c r="AB58" s="16">
-        <v>45.692307692307693</v>
+        <v>42.428571428571431</v>
       </c>
       <c r="AC58" s="15">
-        <v>10.846153846153843</v>
+        <v>13.071428571428569</v>
       </c>
       <c r="AD58" s="19">
         <v>409</v>
@@ -7517,13 +7519,13 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>45.933333333333337</v>
+        <v>49.466666666666669</v>
       </c>
       <c r="AB59" s="16">
-        <v>25.384615384615383</v>
+        <v>23.571428571428569</v>
       </c>
       <c r="AC59" s="15">
-        <v>35.692307692307693</v>
+        <v>36.928571428571431</v>
       </c>
       <c r="AD59" s="19">
         <v>329</v>
@@ -7603,10 +7605,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7636,10 +7638,10 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
         <v>168508.88999999996</v>
@@ -7846,19 +7848,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
         <v>396162.71999999986</v>
       </c>
-      <c r="E67" s="69">
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7958,10 +7960,10 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
         <v>124401</v>
@@ -8167,19 +8169,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
         <v>285946</v>
       </c>
-      <c r="E75" s="69">
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8726,17 +8728,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8745,6 +8736,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6A1D5D-0321-4318-A608-A7D55026C137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7C0934-F254-4434-B6F0-5D5C5A424620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1180,7 +1180,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-09-16;15"/>
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1320,6 +1321,7 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1647,242 +1649,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2247,85 +2249,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>3135</v>
+        <v>1541</v>
       </c>
       <c r="F13" s="14">
-        <v>4263.6000000000004</v>
+        <v>2095.7600000000002</v>
       </c>
       <c r="G13" s="14">
-        <v>4.0232164731960562</v>
+        <v>1.9233649525711431</v>
       </c>
       <c r="H13" s="30">
-        <v>17143</v>
+        <v>17626.400000000001</v>
       </c>
       <c r="I13" s="15">
-        <v>-4657.2727272727279</v>
+        <v>-6471</v>
       </c>
       <c r="J13" s="16">
-        <v>4374</v>
+        <v>3754</v>
       </c>
       <c r="K13" s="13">
-        <v>5948.64</v>
+        <v>5105.4400000000005</v>
       </c>
       <c r="L13" s="14">
-        <v>17.9663928304705</v>
+        <v>14.449576597382601</v>
       </c>
       <c r="M13" s="30">
-        <v>5356</v>
+        <v>5715.6</v>
       </c>
       <c r="N13" s="15">
-        <v>1939.4545454545455</v>
+        <v>1156</v>
       </c>
       <c r="O13" s="16">
-        <v>203</v>
+        <v>649</v>
       </c>
       <c r="P13" s="17">
-        <v>276.08000000000004</v>
+        <v>882.6400000000001</v>
       </c>
       <c r="Q13" s="14">
-        <v>5.1869918699186996</v>
+        <v>13.335616438356167</v>
       </c>
       <c r="R13" s="16">
-        <v>861</v>
+        <v>1070.6666666666665</v>
       </c>
       <c r="S13" s="15">
-        <v>-579.72727272727263</v>
+        <v>-324.33333333333314</v>
       </c>
       <c r="T13" s="18">
-        <v>274</v>
+        <v>689</v>
       </c>
       <c r="U13" s="17">
-        <v>372.64000000000004</v>
+        <v>937.04000000000008</v>
       </c>
       <c r="V13" s="14">
-        <v>5.0485762144053599</v>
+        <v>14.722222222222223</v>
       </c>
       <c r="W13" s="16">
-        <v>1194</v>
+        <v>1029.5999999999999</v>
       </c>
       <c r="X13" s="15">
-        <v>-540.09090909090912</v>
+        <v>-13</v>
       </c>
       <c r="Y13" s="18">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="Z13" s="17">
-        <v>212.16000000000003</v>
+        <v>164.56</v>
       </c>
       <c r="AA13" s="14">
-        <v>4.9078651685393266</v>
+        <v>4.0066225165562912</v>
       </c>
       <c r="AB13" s="16">
-        <v>699.28571428571422</v>
+        <v>664.4</v>
       </c>
       <c r="AC13" s="15">
-        <v>-320.78571428571422</v>
+        <v>-332</v>
       </c>
       <c r="AD13" s="19">
-        <v>8142</v>
+        <v>6754</v>
       </c>
       <c r="AE13" s="20">
-        <v>11073.12</v>
+        <v>9185.44</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2370,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>762</v>
+        <v>683.4666666666667</v>
       </c>
       <c r="I14" s="15">
-        <v>-346.36363636363632</v>
+        <v>-310.66666666666669</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2385,40 +2387,40 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>574</v>
+        <v>365.20000000000005</v>
       </c>
       <c r="N14" s="15">
-        <v>-260.90909090909088</v>
+        <v>-166</v>
       </c>
       <c r="O14" s="16">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="P14" s="17">
-        <v>186.03</v>
+        <v>171.72</v>
       </c>
       <c r="Q14" s="14">
-        <v>15.141176470588235</v>
+        <v>21.6</v>
       </c>
       <c r="R14" s="16">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="S14" s="15">
-        <v>-37.545454545454561</v>
+        <v>8</v>
       </c>
       <c r="T14" s="18">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U14" s="17">
-        <v>25.44</v>
+        <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>6.2857142857142856</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="W14" s="16">
-        <v>56</v>
+        <v>39.6</v>
       </c>
       <c r="X14" s="15">
-        <v>-22.18181818181818</v>
+        <v>-20</v>
       </c>
       <c r="Y14" s="18">
         <v>31</v>
@@ -2427,19 +2429,19 @@
         <v>49.29</v>
       </c>
       <c r="AA14" s="14">
-        <v>6.5757575757575752</v>
+        <v>7.045454545454545</v>
       </c>
       <c r="AB14" s="16">
-        <v>103.71428571428572</v>
+        <v>96.800000000000011</v>
       </c>
       <c r="AC14" s="15">
-        <v>-39.714285714285722</v>
+        <v>-35</v>
       </c>
       <c r="AD14" s="19">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="AE14" s="20">
-        <v>260.76</v>
+        <v>232.14000000000001</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2475,85 +2477,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1774</v>
+        <v>1226</v>
       </c>
       <c r="F15" s="14">
-        <v>3601.22</v>
+        <v>2488.7799999999997</v>
       </c>
       <c r="G15" s="14">
-        <v>5.6562318840579708</v>
+        <v>3.51894374282434</v>
       </c>
       <c r="H15" s="30">
-        <v>6900</v>
+        <v>7664.7999999999993</v>
       </c>
       <c r="I15" s="15">
-        <v>-1362.363636363636</v>
+        <v>-2258</v>
       </c>
       <c r="J15" s="16">
-        <v>2566</v>
+        <v>2219</v>
       </c>
       <c r="K15" s="13">
-        <v>5208.9799999999996</v>
+        <v>4504.57</v>
       </c>
       <c r="L15" s="14">
-        <v>18.698906922822129</v>
+        <v>21.013257575757578</v>
       </c>
       <c r="M15" s="30">
-        <v>3019</v>
+        <v>2323.1999999999998</v>
       </c>
       <c r="N15" s="15">
-        <v>1193.7272727272727</v>
+        <v>1163</v>
       </c>
       <c r="O15" s="16">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="P15" s="17">
-        <v>292.32</v>
+        <v>499.37999999999994</v>
       </c>
       <c r="Q15" s="14">
-        <v>10.666666666666666</v>
+        <v>20.5</v>
       </c>
       <c r="R15" s="16">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="S15" s="15">
-        <v>-126</v>
+        <v>6</v>
       </c>
       <c r="T15" s="18">
-        <v>266</v>
+        <v>201</v>
       </c>
       <c r="U15" s="17">
-        <v>539.9799999999999</v>
+        <v>408.03</v>
       </c>
       <c r="V15" s="14">
-        <v>16.864553314121036</v>
+        <v>14.425837320574161</v>
       </c>
       <c r="W15" s="16">
-        <v>347.00000000000006</v>
+        <v>306.53333333333336</v>
       </c>
       <c r="X15" s="15">
-        <v>29.409090909090878</v>
+        <v>-8.0000000000000284</v>
       </c>
       <c r="Y15" s="18">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="Z15" s="17">
-        <v>286.22999999999996</v>
+        <v>267.95999999999998</v>
       </c>
       <c r="AA15" s="14">
-        <v>14.304347826086955</v>
+        <v>14.142857142857142</v>
       </c>
       <c r="AB15" s="16">
-        <v>216.85714285714286</v>
+        <v>205.33333333333334</v>
       </c>
       <c r="AC15" s="15">
-        <v>-6.8571428571428612</v>
+        <v>-8</v>
       </c>
       <c r="AD15" s="19">
-        <v>4891</v>
+        <v>4024</v>
       </c>
       <c r="AE15" s="20">
-        <v>9928.73</v>
+        <v>8168.7199999999993</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2588,64 +2590,64 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>176.89</v>
+        <v>0</v>
       </c>
       <c r="G16" s="14">
-        <v>0.77165354330708658</v>
+        <v>0</v>
       </c>
       <c r="H16" s="30">
-        <v>1397</v>
+        <v>1579.6</v>
       </c>
       <c r="I16" s="15">
-        <v>-586</v>
+        <v>-718</v>
       </c>
       <c r="J16" s="16">
-        <v>643</v>
+        <v>520</v>
       </c>
       <c r="K16" s="13">
-        <v>2321.23</v>
+        <v>1877.2</v>
       </c>
       <c r="L16" s="14">
-        <v>25.955963302752291</v>
+        <v>20.207253886010363</v>
       </c>
       <c r="M16" s="30">
-        <v>545</v>
+        <v>566.13333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>395.27272727272725</v>
+        <v>262.66666666666663</v>
       </c>
       <c r="O16" s="16">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="P16" s="17">
-        <v>0</v>
+        <v>194.94</v>
       </c>
       <c r="Q16" s="14">
-        <v>0</v>
+        <v>23.823529411764707</v>
       </c>
       <c r="R16" s="16">
-        <v>46.000000000000007</v>
+        <v>49.866666666666667</v>
       </c>
       <c r="S16" s="15">
-        <v>-41.818181818181827</v>
+        <v>8.6666666666666714</v>
       </c>
       <c r="T16" s="18">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U16" s="17">
-        <v>187.72</v>
+        <v>180.5</v>
       </c>
       <c r="V16" s="14">
-        <v>23.346938775510207</v>
+        <v>53.571428571428562</v>
       </c>
       <c r="W16" s="16">
-        <v>49</v>
+        <v>20.533333333333335</v>
       </c>
       <c r="X16" s="15">
-        <v>18.590909090909093</v>
+        <v>36</v>
       </c>
       <c r="Y16" s="18">
         <v>25</v>
@@ -2654,19 +2656,19 @@
         <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>6.1403508771929829</v>
+        <v>6.5789473684210531</v>
       </c>
       <c r="AB16" s="16">
-        <v>89.571428571428569</v>
+        <v>83.6</v>
       </c>
       <c r="AC16" s="15">
-        <v>-36.071428571428569</v>
+        <v>-32</v>
       </c>
       <c r="AD16" s="19">
-        <v>769</v>
+        <v>649</v>
       </c>
       <c r="AE16" s="20">
-        <v>2776.0899999999997</v>
+        <v>2342.89</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2710,40 +2712,40 @@
         <v>0</v>
       </c>
       <c r="H17" s="30">
-        <v>167</v>
+        <v>214.13333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>-75.909090909090907</v>
+        <v>-97.333333333333329</v>
       </c>
       <c r="J17" s="16">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K17" s="13">
-        <v>781.42</v>
+        <v>746.3</v>
       </c>
       <c r="L17" s="14">
-        <v>28.376811594202898</v>
+        <v>39.84375</v>
       </c>
       <c r="M17" s="30">
-        <v>69</v>
+        <v>46.93333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>57.63636363636364</v>
+        <v>63.666666666666671</v>
       </c>
       <c r="O17" s="16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="17">
-        <v>96.58</v>
+        <v>87.8</v>
       </c>
       <c r="Q17" s="14">
-        <v>30.25</v>
+        <v>18.75</v>
       </c>
       <c r="R17" s="16">
-        <v>8</v>
+        <v>11.733333333333333</v>
       </c>
       <c r="S17" s="15">
-        <v>3.7272727272727266</v>
+        <v>-0.66666666666666607</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2767,19 +2769,19 @@
         <v>96.58</v>
       </c>
       <c r="AA17" s="14">
-        <v>25.666666666666664</v>
+        <v>27.5</v>
       </c>
       <c r="AB17" s="16">
-        <v>9.4285714285714288</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="AC17" s="15">
-        <v>4.5714285714285712</v>
+        <v>5</v>
       </c>
       <c r="AD17" s="19">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AE17" s="20">
-        <v>1123.8399999999999</v>
+        <v>1079.9399999999998</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2814,85 +2816,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>8284</v>
+        <v>5156</v>
       </c>
       <c r="F18" s="14">
-        <v>5218.92</v>
+        <v>3248.28</v>
       </c>
       <c r="G18" s="14">
-        <v>9.9834565872363736</v>
+        <v>5.9726619816202033</v>
       </c>
       <c r="H18" s="30">
-        <v>18255</v>
+        <v>18991.866666666665</v>
       </c>
       <c r="I18" s="15">
-        <v>-13.727272727272066</v>
+        <v>-3476.6666666666661</v>
       </c>
       <c r="J18" s="16">
-        <v>5047</v>
+        <v>4460</v>
       </c>
       <c r="K18" s="13">
-        <v>3179.61</v>
+        <v>2809.8</v>
       </c>
       <c r="L18" s="14">
-        <v>16.045375722543351</v>
+        <v>13.776771004942338</v>
       </c>
       <c r="M18" s="30">
-        <v>6920</v>
+        <v>7122.1333333333332</v>
       </c>
       <c r="N18" s="15">
-        <v>1901.5454545454545</v>
+        <v>1222.6666666666665</v>
       </c>
       <c r="O18" s="16">
-        <v>552</v>
+        <v>1107</v>
       </c>
       <c r="P18" s="17">
-        <v>347.76</v>
+        <v>697.41</v>
       </c>
       <c r="Q18" s="14">
-        <v>8.4041522491349472</v>
+        <v>18.187294633077766</v>
       </c>
       <c r="R18" s="16">
-        <v>1445</v>
+        <v>1339.0666666666666</v>
       </c>
       <c r="S18" s="15">
-        <v>-761.63636363636374</v>
+        <v>-110.33333333333326</v>
       </c>
       <c r="T18" s="18">
-        <v>1290</v>
+        <v>2196</v>
       </c>
       <c r="U18" s="17">
-        <v>812.7</v>
+        <v>1383.48</v>
       </c>
       <c r="V18" s="14">
-        <v>7.3561430793157072</v>
+        <v>14.705357142857142</v>
       </c>
       <c r="W18" s="16">
-        <v>3858</v>
+        <v>3285.3333333333335</v>
       </c>
       <c r="X18" s="15">
-        <v>-1340.4545454545455</v>
+        <v>-44</v>
       </c>
       <c r="Y18" s="18">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="Z18" s="17">
-        <v>151.19999999999999</v>
+        <v>137.34</v>
       </c>
       <c r="AA18" s="14">
-        <v>17.591623036649217</v>
+        <v>16.188118811881189</v>
       </c>
       <c r="AB18" s="16">
-        <v>300.14285714285711</v>
+        <v>296.26666666666665</v>
       </c>
       <c r="AC18" s="15">
-        <v>35.35714285714289</v>
+        <v>16</v>
       </c>
       <c r="AD18" s="19">
-        <v>15413</v>
+        <v>13137</v>
       </c>
       <c r="AE18" s="20">
-        <v>9710.19</v>
+        <v>8276.31</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2927,85 +2929,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>610</v>
+        <v>561</v>
       </c>
       <c r="F19" s="14">
-        <v>384.3</v>
+        <v>353.43</v>
       </c>
       <c r="G19" s="14">
-        <v>9.0370370370370381</v>
+        <v>9.9940617577197148</v>
       </c>
       <c r="H19" s="30">
-        <v>1484.9999999999998</v>
+        <v>1234.9333333333334</v>
       </c>
       <c r="I19" s="15">
-        <v>-64.999999999999886</v>
+        <v>-0.33333333333337123</v>
       </c>
       <c r="J19" s="16">
-        <v>741</v>
+        <v>571</v>
       </c>
       <c r="K19" s="13">
-        <v>466.83</v>
+        <v>359.73</v>
       </c>
       <c r="L19" s="14">
-        <v>14.503558718861209</v>
+        <v>9.8448275862068968</v>
       </c>
       <c r="M19" s="30">
-        <v>1124</v>
+        <v>1276</v>
       </c>
       <c r="N19" s="15">
-        <v>230.09090909090907</v>
+        <v>-9</v>
       </c>
       <c r="O19" s="16">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="P19" s="17">
-        <v>25.830000000000002</v>
+        <v>52.92</v>
       </c>
       <c r="Q19" s="14">
-        <v>9.5957446808510642</v>
+        <v>17.027027027027025</v>
       </c>
       <c r="R19" s="16">
-        <v>94</v>
+        <v>108.53333333333333</v>
       </c>
       <c r="S19" s="15">
-        <v>-44.454545454545453</v>
+        <v>-14.666666666666671</v>
       </c>
       <c r="T19" s="18">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="U19" s="17">
-        <v>171.99</v>
+        <v>161.91</v>
       </c>
       <c r="V19" s="14">
-        <v>17.716814159292035</v>
+        <v>21.536312849162009</v>
       </c>
       <c r="W19" s="16">
-        <v>339</v>
+        <v>262.53333333333336</v>
       </c>
       <c r="X19" s="15">
-        <v>41.863636363636374</v>
+        <v>77.999999999999972</v>
       </c>
       <c r="Y19" s="18">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="Z19" s="17">
-        <v>102.69</v>
+        <v>97.02</v>
       </c>
       <c r="AA19" s="14">
-        <v>14.915032679738562</v>
+        <v>14.085365853658537</v>
       </c>
       <c r="AB19" s="16">
-        <v>240.42857142857144</v>
+        <v>240.53333333333333</v>
       </c>
       <c r="AC19" s="15">
-        <v>-0.92857142857144481</v>
+        <v>-10</v>
       </c>
       <c r="AD19" s="19">
-        <v>1828</v>
+        <v>1627</v>
       </c>
       <c r="AE19" s="20">
-        <v>1151.6400000000001</v>
+        <v>1025.01</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3040,85 +3042,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1380</v>
+        <v>1081</v>
       </c>
       <c r="F20" s="14">
-        <v>869.4</v>
+        <v>681.03</v>
       </c>
       <c r="G20" s="14">
-        <v>8.9955555555555549</v>
+        <v>8.6158342189160457</v>
       </c>
       <c r="H20" s="30">
-        <v>3375</v>
+        <v>2760.2666666666669</v>
       </c>
       <c r="I20" s="15">
-        <v>-154.09090909090901</v>
+        <v>-173.66666666666674</v>
       </c>
       <c r="J20" s="16">
-        <v>1992</v>
+        <v>1577</v>
       </c>
       <c r="K20" s="13">
-        <v>1254.96</v>
+        <v>993.51</v>
       </c>
       <c r="L20" s="14">
-        <v>19.82089552238806</v>
+        <v>12.269190871369295</v>
       </c>
       <c r="M20" s="30">
-        <v>2211</v>
+        <v>2827.7333333333331</v>
       </c>
       <c r="N20" s="15">
-        <v>987</v>
+        <v>291.66666666666674</v>
       </c>
       <c r="O20" s="16">
-        <v>155</v>
+        <v>264</v>
       </c>
       <c r="P20" s="17">
-        <v>97.65</v>
+        <v>166.32</v>
       </c>
       <c r="Q20" s="14">
-        <v>12.222222222222223</v>
+        <v>29.774436090225564</v>
       </c>
       <c r="R20" s="16">
-        <v>279</v>
+        <v>195.06666666666666</v>
       </c>
       <c r="S20" s="15">
-        <v>-98.636363636363626</v>
+        <v>86.666666666666657</v>
       </c>
       <c r="T20" s="18">
-        <v>581</v>
+        <v>757</v>
       </c>
       <c r="U20" s="17">
-        <v>366.03000000000003</v>
+        <v>476.91</v>
       </c>
       <c r="V20" s="14">
-        <v>10.906143344709898</v>
+        <v>46.158536585365859</v>
       </c>
       <c r="W20" s="16">
-        <v>1172</v>
+        <v>360.79999999999995</v>
       </c>
       <c r="X20" s="15">
-        <v>-218.09090909090912</v>
+        <v>511</v>
       </c>
       <c r="Y20" s="18">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="Z20" s="17">
-        <v>148.05000000000001</v>
+        <v>142.38</v>
       </c>
       <c r="AA20" s="14">
-        <v>17.135416666666664</v>
+        <v>16.699507389162562</v>
       </c>
       <c r="AB20" s="16">
-        <v>301.71428571428572</v>
+        <v>297.73333333333335</v>
       </c>
       <c r="AC20" s="15">
-        <v>29.285714285714278</v>
+        <v>23</v>
       </c>
       <c r="AD20" s="19">
-        <v>4343</v>
+        <v>3905</v>
       </c>
       <c r="AE20" s="20">
-        <v>2736.09</v>
+        <v>2460.15</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3153,85 +3155,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2045</v>
+        <v>1952</v>
       </c>
       <c r="F21" s="14">
-        <v>2229.0500000000002</v>
+        <v>2127.6800000000003</v>
       </c>
       <c r="G21" s="14">
-        <v>7.0495142588530246</v>
+        <v>6.6606005459508646</v>
       </c>
       <c r="H21" s="30">
-        <v>6382</v>
+        <v>6447.4666666666662</v>
       </c>
       <c r="I21" s="15">
-        <v>-855.90909090909054</v>
+        <v>-978.66666666666652</v>
       </c>
       <c r="J21" s="16">
-        <v>4544</v>
+        <v>3608</v>
       </c>
       <c r="K21" s="13">
-        <v>4952.96</v>
+        <v>3932.7200000000003</v>
       </c>
       <c r="L21" s="14">
-        <v>14.753246753246753</v>
+        <v>11.291466722303358</v>
       </c>
       <c r="M21" s="30">
-        <v>6776</v>
+        <v>7029.7333333333336</v>
       </c>
       <c r="N21" s="15">
-        <v>1464</v>
+        <v>412.66666666666652</v>
       </c>
       <c r="O21" s="16">
-        <v>150</v>
+        <v>383</v>
       </c>
       <c r="P21" s="17">
-        <v>163.5</v>
+        <v>417.47</v>
       </c>
       <c r="Q21" s="14">
-        <v>6.2618595825426953</v>
+        <v>14.255583126550867</v>
       </c>
       <c r="R21" s="16">
-        <v>527</v>
+        <v>591.06666666666672</v>
       </c>
       <c r="S21" s="15">
-        <v>-329.09090909090907</v>
+        <v>-154.33333333333337</v>
       </c>
       <c r="T21" s="18">
-        <v>1201</v>
+        <v>1122</v>
       </c>
       <c r="U21" s="17">
-        <v>1309.0900000000001</v>
+        <v>1222.98</v>
       </c>
       <c r="V21" s="14">
-        <v>12.758087880251086</v>
+        <v>15.847457627118645</v>
       </c>
       <c r="W21" s="16">
-        <v>2071</v>
+        <v>1557.6</v>
       </c>
       <c r="X21" s="15">
-        <v>-211.0454545454545</v>
+        <v>60</v>
       </c>
       <c r="Y21" s="18">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="Z21" s="17">
-        <v>289.94</v>
+        <v>279.04000000000002</v>
       </c>
       <c r="AA21" s="14">
-        <v>13.895522388059701</v>
+        <v>13.963636363636365</v>
       </c>
       <c r="AB21" s="16">
-        <v>421.14285714285711</v>
+        <v>403.33333333333331</v>
       </c>
       <c r="AC21" s="15">
-        <v>-21.14285714285711</v>
+        <v>-19</v>
       </c>
       <c r="AD21" s="19">
-        <v>8206</v>
+        <v>7321</v>
       </c>
       <c r="AE21" s="20">
-        <v>8944.5400000000009</v>
+        <v>7979.89</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3266,85 +3268,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1706</v>
+        <v>1315</v>
       </c>
       <c r="F22" s="14">
-        <v>1859.5400000000002</v>
+        <v>1433.3500000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>8.7507577523898341</v>
+        <v>7.7504911591355601</v>
       </c>
       <c r="H22" s="30">
-        <v>4289</v>
+        <v>3732.6666666666665</v>
       </c>
       <c r="I22" s="15">
-        <v>-243.54545454545473</v>
+        <v>-381.66666666666652</v>
       </c>
       <c r="J22" s="16">
-        <v>2404</v>
+        <v>1996</v>
       </c>
       <c r="K22" s="13">
-        <v>2620.36</v>
+        <v>2175.6400000000003</v>
       </c>
       <c r="L22" s="14">
-        <v>21.881671493587092</v>
+        <v>14.135977337110482</v>
       </c>
       <c r="M22" s="30">
-        <v>2417</v>
+        <v>3106.3999999999996</v>
       </c>
       <c r="N22" s="15">
-        <v>1305.3636363636365</v>
+        <v>584</v>
       </c>
       <c r="O22" s="16">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="P22" s="17">
-        <v>144.97</v>
+        <v>151.51000000000002</v>
       </c>
       <c r="Q22" s="14">
-        <v>14.343137254901963</v>
+        <v>26.0625</v>
       </c>
       <c r="R22" s="16">
-        <v>203.99999999999997</v>
+        <v>117.33333333333333</v>
       </c>
       <c r="S22" s="15">
-        <v>-52.454545454545439</v>
+        <v>32.333333333333343</v>
       </c>
       <c r="T22" s="18">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="U22" s="17">
-        <v>487.23</v>
+        <v>492.68000000000006</v>
       </c>
       <c r="V22" s="14">
-        <v>13.870239774330043</v>
+        <v>20.178571428571431</v>
       </c>
       <c r="W22" s="16">
-        <v>709</v>
+        <v>492.79999999999995</v>
       </c>
       <c r="X22" s="15">
-        <v>-36.409090909090878</v>
+        <v>116</v>
       </c>
       <c r="Y22" s="18">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="Z22" s="17">
-        <v>155.87</v>
+        <v>150.42000000000002</v>
       </c>
       <c r="AA22" s="14">
-        <v>33.932203389830505</v>
+        <v>31.36363636363636</v>
       </c>
       <c r="AB22" s="16">
-        <v>92.714285714285722</v>
+        <v>96.800000000000011</v>
       </c>
       <c r="AC22" s="15">
-        <v>79.785714285714278</v>
+        <v>72</v>
       </c>
       <c r="AD22" s="19">
-        <v>4833</v>
+        <v>4040</v>
       </c>
       <c r="AE22" s="20">
-        <v>5267.97</v>
+        <v>4403.6000000000004</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3379,85 +3381,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>19731</v>
+        <v>16580</v>
       </c>
       <c r="F23" s="14">
-        <v>22887.96</v>
+        <v>19232.8</v>
       </c>
       <c r="G23" s="14">
-        <v>11.515027721038809</v>
+        <v>9.9939722724532842</v>
       </c>
       <c r="H23" s="30">
-        <v>37697</v>
+        <v>36498</v>
       </c>
       <c r="I23" s="15">
-        <v>2596</v>
+        <v>-8305</v>
       </c>
       <c r="J23" s="16">
-        <v>8542</v>
+        <v>22442</v>
       </c>
       <c r="K23" s="13">
-        <v>9908.7199999999993</v>
+        <v>26032.719999999998</v>
       </c>
       <c r="L23" s="14">
-        <v>9.8209563626861769</v>
+        <v>24.345845085701889</v>
       </c>
       <c r="M23" s="30">
-        <v>19135</v>
+        <v>20279.599999999999</v>
       </c>
       <c r="N23" s="15">
-        <v>-155.72727272727207</v>
+        <v>13224</v>
       </c>
       <c r="O23" s="16">
-        <v>1030</v>
+        <v>2226</v>
       </c>
       <c r="P23" s="17">
-        <v>1194.8</v>
+        <v>2582.16</v>
       </c>
       <c r="Q23" s="14">
-        <v>7.1868062163019353</v>
+        <v>14.807095343680709</v>
       </c>
       <c r="R23" s="16">
-        <v>3153</v>
+        <v>3307.3333333333335</v>
       </c>
       <c r="S23" s="15">
-        <v>-1836.363636363636</v>
+        <v>-780.66666666666697</v>
       </c>
       <c r="T23" s="18">
-        <v>4631</v>
+        <v>7360</v>
       </c>
       <c r="U23" s="17">
-        <v>5371.96</v>
+        <v>8537.5999999999985</v>
       </c>
       <c r="V23" s="14">
-        <v>7.6996674727932284</v>
+        <v>13.51781559936329</v>
       </c>
       <c r="W23" s="16">
-        <v>13232</v>
+        <v>11978.266666666666</v>
       </c>
       <c r="X23" s="15">
-        <v>-4390.818181818182</v>
+        <v>-807</v>
       </c>
       <c r="Y23" s="18">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="Z23" s="17">
-        <v>167.04</v>
+        <v>111.35999999999999</v>
       </c>
       <c r="AA23" s="14">
-        <v>2.4981412639405205</v>
+        <v>1.7454545454545454</v>
       </c>
       <c r="AB23" s="16">
-        <v>1268.1428571428571</v>
+        <v>1210</v>
       </c>
       <c r="AC23" s="15">
-        <v>-720.64285714285711</v>
+        <v>-729</v>
       </c>
       <c r="AD23" s="19">
-        <v>34078</v>
+        <v>48704</v>
       </c>
       <c r="AE23" s="20">
-        <v>39530.479999999996</v>
+        <v>56496.639999999999</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3492,85 +3494,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>11708</v>
+        <v>9658</v>
       </c>
       <c r="F24" s="14">
-        <v>13581.279999999999</v>
+        <v>11203.279999999999</v>
       </c>
       <c r="G24" s="14">
-        <v>9.5902896716062251</v>
+        <v>8.8855495583905793</v>
       </c>
       <c r="H24" s="30">
-        <v>26858</v>
+        <v>23912.533333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>-500.18181818181802</v>
+        <v>-1211.3333333333339</v>
       </c>
       <c r="J24" s="16">
-        <v>5618</v>
+        <v>8473</v>
       </c>
       <c r="K24" s="13">
-        <v>6516.8799999999992</v>
+        <v>9828.6799999999985</v>
       </c>
       <c r="L24" s="14">
-        <v>10.358364063023801</v>
+        <v>14.975256274301875</v>
       </c>
       <c r="M24" s="30">
-        <v>11932</v>
+        <v>12447.599999999999</v>
       </c>
       <c r="N24" s="15">
-        <v>194.36363636363603</v>
+        <v>2815</v>
       </c>
       <c r="O24" s="16">
-        <v>593</v>
+        <v>1327</v>
       </c>
       <c r="P24" s="17">
-        <v>687.88</v>
+        <v>1539.32</v>
       </c>
       <c r="Q24" s="14">
-        <v>6.9062996294335628</v>
+        <v>15.229533282325937</v>
       </c>
       <c r="R24" s="16">
-        <v>1889</v>
+        <v>1916.9333333333334</v>
       </c>
       <c r="S24" s="15">
-        <v>-1124.2727272727273</v>
+        <v>-415.66666666666674</v>
       </c>
       <c r="T24" s="18">
-        <v>2622</v>
+        <v>4150</v>
       </c>
       <c r="U24" s="17">
-        <v>3041.52</v>
+        <v>4814</v>
       </c>
       <c r="V24" s="14">
-        <v>7.9323432343234321</v>
+        <v>14.453215695379615</v>
       </c>
       <c r="W24" s="16">
-        <v>7272</v>
+        <v>6316.9333333333334</v>
       </c>
       <c r="X24" s="15">
-        <v>-2336.181818181818</v>
+        <v>-157</v>
       </c>
       <c r="Y24" s="18">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="Z24" s="17">
-        <v>517.36</v>
+        <v>475.59999999999997</v>
       </c>
       <c r="AA24" s="14">
-        <v>12.054054054054054</v>
+        <v>11.647727272727272</v>
       </c>
       <c r="AB24" s="16">
-        <v>814</v>
+        <v>774.40000000000009</v>
       </c>
       <c r="AC24" s="15">
-        <v>-109</v>
+        <v>-118</v>
       </c>
       <c r="AD24" s="19">
-        <v>20987</v>
+        <v>24018</v>
       </c>
       <c r="AE24" s="20">
-        <v>24344.92</v>
+        <v>27860.879999999997</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3605,85 +3607,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>6643</v>
+        <v>6546</v>
       </c>
       <c r="F25" s="14">
-        <v>7705.8799999999992</v>
+        <v>7593.36</v>
       </c>
       <c r="G25" s="14">
-        <v>5.6593091697645601</v>
+        <v>6.1063432835820892</v>
       </c>
       <c r="H25" s="30">
-        <v>25824</v>
+        <v>23584</v>
       </c>
       <c r="I25" s="15">
-        <v>-5095.181818181818</v>
+        <v>-4174</v>
       </c>
       <c r="J25" s="16">
-        <v>5322</v>
+        <v>18897</v>
       </c>
       <c r="K25" s="13">
-        <v>6173.5199999999995</v>
+        <v>21920.519999999997</v>
       </c>
       <c r="L25" s="14">
-        <v>9.8299051297120315</v>
+        <v>31.169452386188695</v>
       </c>
       <c r="M25" s="30">
-        <v>11911</v>
+        <v>13337.866666666667</v>
       </c>
       <c r="N25" s="15">
-        <v>-92.090909090909008</v>
+        <v>12834.333333333334</v>
       </c>
       <c r="O25" s="16">
-        <v>601</v>
+        <v>1599</v>
       </c>
       <c r="P25" s="17">
-        <v>697.16</v>
+        <v>1854.84</v>
       </c>
       <c r="Q25" s="14">
-        <v>6.0182066454255807</v>
+        <v>14.823856613102597</v>
       </c>
       <c r="R25" s="16">
-        <v>2197</v>
+        <v>2373.0666666666666</v>
       </c>
       <c r="S25" s="15">
-        <v>-1396.2727272727273</v>
+        <v>-558.33333333333303</v>
       </c>
       <c r="T25" s="18">
-        <v>3939</v>
+        <v>4058</v>
       </c>
       <c r="U25" s="17">
-        <v>4569.24</v>
+        <v>4707.28</v>
       </c>
       <c r="V25" s="14">
-        <v>12.025811823480433</v>
+        <v>13.97703788748565</v>
       </c>
       <c r="W25" s="16">
-        <v>7206.0000000000009</v>
+        <v>6387.333333333333</v>
       </c>
       <c r="X25" s="15">
-        <v>-974.18181818181802</v>
+        <v>-297</v>
       </c>
       <c r="Y25" s="18">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="Z25" s="17">
-        <v>715.71999999999991</v>
+        <v>687.88</v>
       </c>
       <c r="AA25" s="14">
-        <v>23.409214092140921</v>
+        <v>23.469656992084435</v>
       </c>
       <c r="AB25" s="16">
-        <v>579.85714285714289</v>
+        <v>555.86666666666667</v>
       </c>
       <c r="AC25" s="15">
-        <v>221.64285714285711</v>
+        <v>214</v>
       </c>
       <c r="AD25" s="19">
-        <v>17122</v>
+        <v>31693</v>
       </c>
       <c r="AE25" s="20">
-        <v>19861.52</v>
+        <v>36763.879999999997</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3718,85 +3720,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>14777</v>
+        <v>12557</v>
       </c>
       <c r="F26" s="14">
-        <v>17141.32</v>
+        <v>14566.119999999999</v>
       </c>
       <c r="G26" s="14">
-        <v>10.361561752988047</v>
+        <v>9.0364133563615443</v>
       </c>
       <c r="H26" s="30">
-        <v>31375</v>
+        <v>30571.199999999997</v>
       </c>
       <c r="I26" s="15">
-        <v>515.63636363636215</v>
+        <v>-8287</v>
       </c>
       <c r="J26" s="16">
-        <v>10391</v>
+        <v>21797</v>
       </c>
       <c r="K26" s="13">
-        <v>12053.56</v>
+        <v>25284.519999999997</v>
       </c>
       <c r="L26" s="14">
-        <v>16.214057734591105</v>
+        <v>30.809932152280435</v>
       </c>
       <c r="M26" s="30">
-        <v>14099</v>
+        <v>15564.266666666666</v>
       </c>
       <c r="N26" s="15">
-        <v>3982.363636363636</v>
+        <v>14722.333333333332</v>
       </c>
       <c r="O26" s="16">
-        <v>525</v>
+        <v>1423</v>
       </c>
       <c r="P26" s="17">
-        <v>609</v>
+        <v>1650.6799999999998</v>
       </c>
       <c r="Q26" s="14">
-        <v>6.3461538461538458</v>
+        <v>17.227602905569007</v>
       </c>
       <c r="R26" s="16">
-        <v>1820</v>
+        <v>1817.1999999999998</v>
       </c>
       <c r="S26" s="15">
-        <v>-1129.5454545454547</v>
+        <v>-229</v>
       </c>
       <c r="T26" s="18">
-        <v>2991</v>
+        <v>4598</v>
       </c>
       <c r="U26" s="17">
-        <v>3469.56</v>
+        <v>5333.6799999999994</v>
       </c>
       <c r="V26" s="14">
-        <v>7.9031948114340622</v>
+        <v>12.793544796883696</v>
       </c>
       <c r="W26" s="16">
-        <v>8326</v>
+        <v>7906.7999999999993</v>
       </c>
       <c r="X26" s="15">
-        <v>-2685.818181818182</v>
+        <v>-793</v>
       </c>
       <c r="Y26" s="18">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="Z26" s="17">
-        <v>628.71999999999991</v>
+        <v>621.76</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.196521739130436</v>
+        <v>13.767123287671234</v>
       </c>
       <c r="AB26" s="16">
-        <v>903.57142857142856</v>
+        <v>856.5333333333333</v>
       </c>
       <c r="AC26" s="15">
-        <v>-74.071428571428555</v>
+        <v>-48</v>
       </c>
       <c r="AD26" s="19">
-        <v>29226</v>
+        <v>40911</v>
       </c>
       <c r="AE26" s="20">
-        <v>33902.159999999996</v>
+        <v>47456.759999999995</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3831,85 +3833,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1716</v>
+        <v>1142</v>
       </c>
       <c r="F27" s="14">
-        <v>1990.56</v>
+        <v>1324.7199999999998</v>
       </c>
       <c r="G27" s="14">
-        <v>10.408602150537634</v>
+        <v>3.4260000000000002</v>
       </c>
       <c r="H27" s="30">
-        <v>3627</v>
+        <v>7333.333333333333</v>
       </c>
       <c r="I27" s="15">
-        <v>67.36363636363626</v>
+        <v>-2191.333333333333</v>
       </c>
       <c r="J27" s="16">
-        <v>3188</v>
+        <v>6535</v>
       </c>
       <c r="K27" s="13">
-        <v>3698.08</v>
+        <v>7580.5999999999995</v>
       </c>
       <c r="L27" s="14">
-        <v>27.688906435057245</v>
+        <v>34.060111188325223</v>
       </c>
       <c r="M27" s="30">
-        <v>2533</v>
+        <v>4221.0666666666666</v>
       </c>
       <c r="N27" s="15">
-        <v>2036.6363636363635</v>
+        <v>4616.333333333333</v>
       </c>
       <c r="O27" s="16">
-        <v>402</v>
+        <v>287</v>
       </c>
       <c r="P27" s="17">
-        <v>466.32</v>
+        <v>332.91999999999996</v>
       </c>
       <c r="Q27" s="14">
-        <v>21.057142857142857</v>
+        <v>10.274463007159904</v>
       </c>
       <c r="R27" s="16">
-        <v>420</v>
+        <v>614.5333333333333</v>
       </c>
       <c r="S27" s="15">
-        <v>20.181818181818187</v>
+        <v>-271.66666666666663</v>
       </c>
       <c r="T27" s="18">
-        <v>682</v>
+        <v>1031</v>
       </c>
       <c r="U27" s="17">
-        <v>791.11999999999989</v>
+        <v>1195.9599999999998</v>
       </c>
       <c r="V27" s="14">
-        <v>9.8258022265880829</v>
+        <v>8.9186851211072664</v>
       </c>
       <c r="W27" s="16">
-        <v>1526.9999999999998</v>
+        <v>2543.1999999999998</v>
       </c>
       <c r="X27" s="15">
-        <v>-359.13636363636328</v>
+        <v>-703</v>
       </c>
       <c r="Y27" s="18">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="Z27" s="17">
-        <v>524.31999999999994</v>
+        <v>501.11999999999995</v>
       </c>
       <c r="AA27" s="14">
-        <v>38.822085889570559</v>
+        <v>37.456647398843934</v>
       </c>
       <c r="AB27" s="16">
-        <v>256.14285714285711</v>
+        <v>253.73333333333332</v>
       </c>
       <c r="AC27" s="15">
-        <v>277.35714285714289</v>
+        <v>259</v>
       </c>
       <c r="AD27" s="19">
-        <v>6440</v>
+        <v>9427</v>
       </c>
       <c r="AE27" s="20">
-        <v>7470.4</v>
+        <v>10935.32</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3944,85 +3946,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>1559</v>
+        <v>957</v>
       </c>
       <c r="F28" s="14">
-        <v>1808.4399999999998</v>
+        <v>1110.1199999999999</v>
       </c>
       <c r="G28" s="14">
-        <v>9.138822275512922</v>
+        <v>2.9403932814420322</v>
       </c>
       <c r="H28" s="30">
-        <v>3753</v>
+        <v>7160.2666666666664</v>
       </c>
       <c r="I28" s="15">
-        <v>-146.90909090909099</v>
+        <v>-2297.6666666666665</v>
       </c>
       <c r="J28" s="16">
-        <v>7126</v>
+        <v>6469</v>
       </c>
       <c r="K28" s="13">
-        <v>8266.16</v>
+        <v>7504.0399999999991</v>
       </c>
       <c r="L28" s="14">
-        <v>46.979922085705724</v>
+        <v>24.472887767969738</v>
       </c>
       <c r="M28" s="30">
-        <v>3337</v>
+        <v>5815.333333333333</v>
       </c>
       <c r="N28" s="15">
-        <v>5609.181818181818</v>
+        <v>3825.666666666667</v>
       </c>
       <c r="O28" s="16">
-        <v>228</v>
+        <v>336</v>
       </c>
       <c r="P28" s="17">
-        <v>264.47999999999996</v>
+        <v>389.76</v>
       </c>
       <c r="Q28" s="14">
-        <v>9.5</v>
+        <v>8.7197231833910038</v>
       </c>
       <c r="R28" s="16">
-        <v>528</v>
+        <v>847.73333333333335</v>
       </c>
       <c r="S28" s="15">
-        <v>-252</v>
+        <v>-434.66666666666663</v>
       </c>
       <c r="T28" s="18">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="U28" s="17">
-        <v>9.2799999999999994</v>
+        <v>799.2399999999999</v>
       </c>
       <c r="V28" s="14">
-        <v>0.13569776407093292</v>
+        <v>5.1392342118349079</v>
       </c>
       <c r="W28" s="16">
-        <v>1297</v>
+        <v>2949.4666666666667</v>
       </c>
       <c r="X28" s="15">
-        <v>-876.31818181818176</v>
+        <v>-1322</v>
       </c>
       <c r="Y28" s="18">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="Z28" s="17">
-        <v>446.59999999999997</v>
+        <v>412.96</v>
       </c>
       <c r="AA28" s="14">
-        <v>22.647058823529413</v>
+        <v>21.36</v>
       </c>
       <c r="AB28" s="16">
-        <v>374</v>
+        <v>366.66666666666669</v>
       </c>
       <c r="AC28" s="15">
-        <v>130</v>
+        <v>105.99999999999997</v>
       </c>
       <c r="AD28" s="19">
-        <v>9306</v>
+        <v>8807</v>
       </c>
       <c r="AE28" s="20">
-        <v>10794.96</v>
+        <v>10216.119999999999</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4057,85 +4059,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1578</v>
+        <v>965</v>
       </c>
       <c r="F29" s="14">
-        <v>1830.4799999999998</v>
+        <v>1119.3999999999999</v>
       </c>
       <c r="G29" s="14">
-        <v>9.1237844940867276</v>
+        <v>2.7106741573033708</v>
       </c>
       <c r="H29" s="30">
-        <v>3805.0000000000005</v>
+        <v>7832</v>
       </c>
       <c r="I29" s="15">
-        <v>-151.54545454545473</v>
+        <v>-2595</v>
       </c>
       <c r="J29" s="16">
-        <v>1562</v>
+        <v>923</v>
       </c>
       <c r="K29" s="13">
-        <v>1811.9199999999998</v>
+        <v>1070.6799999999998</v>
       </c>
       <c r="L29" s="14">
-        <v>12.657090239410682</v>
+        <v>3.3992143383255584</v>
       </c>
       <c r="M29" s="30">
-        <v>2715</v>
+        <v>5973.7333333333336</v>
       </c>
       <c r="N29" s="15">
-        <v>327.90909090909099</v>
+        <v>-1792.3333333333335</v>
       </c>
       <c r="O29" s="16">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="P29" s="17">
-        <v>272.59999999999997</v>
+        <v>279.56</v>
       </c>
       <c r="Q29" s="14">
-        <v>10.793319415448851</v>
+        <v>6.1064189189189184</v>
       </c>
       <c r="R29" s="16">
-        <v>479</v>
+        <v>868.26666666666665</v>
       </c>
       <c r="S29" s="15">
-        <v>-200.4545454545455</v>
+        <v>-548.33333333333337</v>
       </c>
       <c r="T29" s="18">
-        <v>169</v>
+        <v>452</v>
       </c>
       <c r="U29" s="17">
-        <v>196.04</v>
+        <v>524.31999999999994</v>
       </c>
       <c r="V29" s="14">
-        <v>3.2585451358457491</v>
+        <v>3.1072410632447296</v>
       </c>
       <c r="W29" s="16">
-        <v>1141</v>
+        <v>3200.2666666666669</v>
       </c>
       <c r="X29" s="15">
-        <v>-608.9545454545455</v>
+        <v>-1730</v>
       </c>
       <c r="Y29" s="18">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="Z29" s="17">
-        <v>447.76</v>
+        <v>416.44</v>
       </c>
       <c r="AA29" s="14">
-        <v>22.610878661087863</v>
+        <v>21.626506024096383</v>
       </c>
       <c r="AB29" s="16">
-        <v>375.57142857142861</v>
+        <v>365.20000000000005</v>
       </c>
       <c r="AC29" s="15">
-        <v>129.92857142857139</v>
+        <v>109.99999999999997</v>
       </c>
       <c r="AD29" s="19">
-        <v>3930</v>
+        <v>2940</v>
       </c>
       <c r="AE29" s="20">
-        <v>4558.7999999999993</v>
+        <v>3410.3999999999996</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4170,64 +4172,64 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>856</v>
+        <v>610</v>
       </c>
       <c r="F30" s="14">
-        <v>3150.08</v>
+        <v>2244.8000000000002</v>
       </c>
       <c r="G30" s="14">
-        <v>9.4871536523929461</v>
+        <v>6.5357142857142874</v>
       </c>
       <c r="H30" s="30">
-        <v>1985</v>
+        <v>2053.333333333333</v>
       </c>
       <c r="I30" s="15">
-        <v>-46.272727272727366</v>
+        <v>-323.33333333333314</v>
       </c>
       <c r="J30" s="16">
-        <v>332</v>
+        <v>1117</v>
       </c>
       <c r="K30" s="13">
-        <v>1221.76</v>
+        <v>4110.5600000000004</v>
       </c>
       <c r="L30" s="14">
-        <v>3.2856500224921277</v>
+        <v>9.3342618384401099</v>
       </c>
       <c r="M30" s="30">
-        <v>2223</v>
+        <v>2632.666666666667</v>
       </c>
       <c r="N30" s="15">
-        <v>-678.4545454545455</v>
+        <v>-79.66666666666697</v>
       </c>
       <c r="O30" s="16">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="P30" s="17">
-        <v>40.480000000000004</v>
+        <v>184</v>
       </c>
       <c r="Q30" s="14">
-        <v>2.9512195121951219</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="R30" s="16">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S30" s="15">
-        <v>-63.545454545454547</v>
+        <v>-70</v>
       </c>
       <c r="T30" s="18">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="U30" s="17">
-        <v>1380</v>
+        <v>1288</v>
       </c>
       <c r="V30" s="14">
-        <v>11.819484240687679</v>
+        <v>12.681159420289854</v>
       </c>
       <c r="W30" s="16">
-        <v>698</v>
+        <v>607.20000000000005</v>
       </c>
       <c r="X30" s="15">
-        <v>-100.90909090909088</v>
+        <v>-64</v>
       </c>
       <c r="Y30" s="18">
         <v>29</v>
@@ -4236,19 +4238,19 @@
         <v>106.72</v>
       </c>
       <c r="AA30" s="14">
-        <v>6.34375</v>
+        <v>6.796875</v>
       </c>
       <c r="AB30" s="16">
-        <v>100.57142857142857</v>
+        <v>93.86666666666666</v>
       </c>
       <c r="AC30" s="15">
-        <v>-39.571428571428569</v>
+        <v>-35</v>
       </c>
       <c r="AD30" s="19">
-        <v>1603</v>
+        <v>2156</v>
       </c>
       <c r="AE30" s="20">
-        <v>5899.04</v>
+        <v>7934.08</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4283,64 +4285,64 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>346</v>
+        <v>206</v>
       </c>
       <c r="F31" s="14">
-        <v>1273.28</v>
+        <v>758.08</v>
       </c>
       <c r="G31" s="14">
-        <v>6.3486238532110093</v>
+        <v>4.6960486322188446</v>
       </c>
       <c r="H31" s="30">
-        <v>1199</v>
+        <v>965.06666666666672</v>
       </c>
       <c r="I31" s="15">
-        <v>-199</v>
+        <v>-232.66666666666669</v>
       </c>
       <c r="J31" s="16">
-        <v>680</v>
+        <v>1155</v>
       </c>
       <c r="K31" s="13">
-        <v>2502.4</v>
+        <v>4250.4000000000005</v>
       </c>
       <c r="L31" s="14">
-        <v>10.21857923497268</v>
+        <v>17.678571428571431</v>
       </c>
       <c r="M31" s="30">
-        <v>1463.9999999999998</v>
+        <v>1437.3333333333333</v>
       </c>
       <c r="N31" s="15">
-        <v>14.545454545454731</v>
+        <v>501.66666666666674</v>
       </c>
       <c r="O31" s="16">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P31" s="17">
-        <v>95.68</v>
+        <v>136.16</v>
       </c>
       <c r="Q31" s="14">
-        <v>14.3</v>
+        <v>55.5</v>
       </c>
       <c r="R31" s="16">
-        <v>40</v>
+        <v>14.666666666666666</v>
       </c>
       <c r="S31" s="15">
-        <v>-10.36363636363636</v>
+        <v>23.666666666666668</v>
       </c>
       <c r="T31" s="18">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="U31" s="17">
-        <v>614.56000000000006</v>
+        <v>585.12</v>
       </c>
       <c r="V31" s="14">
-        <v>13.969581749049429</v>
+        <v>20.921052631578949</v>
       </c>
       <c r="W31" s="16">
-        <v>263</v>
+        <v>167.2</v>
       </c>
       <c r="X31" s="15">
-        <v>-12.318181818181813</v>
+        <v>45</v>
       </c>
       <c r="Y31" s="18">
         <v>47</v>
@@ -4349,19 +4351,19 @@
         <v>172.96</v>
       </c>
       <c r="AA31" s="14">
-        <v>31.333333333333332</v>
+        <v>33.571428571428577</v>
       </c>
       <c r="AB31" s="16">
-        <v>33</v>
+        <v>30.799999999999997</v>
       </c>
       <c r="AC31" s="15">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="AD31" s="19">
-        <v>1266</v>
+        <v>1604</v>
       </c>
       <c r="AE31" s="20">
-        <v>4658.88</v>
+        <v>5902.72</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4396,85 +4398,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>2190</v>
+        <v>1693</v>
       </c>
       <c r="F32" s="14">
-        <v>9088.5</v>
+        <v>7025.9500000000007</v>
       </c>
       <c r="G32" s="14">
-        <v>10.027055150884495</v>
+        <v>7.8719776813391205</v>
       </c>
       <c r="H32" s="30">
-        <v>4805</v>
+        <v>4731.4666666666662</v>
       </c>
       <c r="I32" s="15">
-        <v>5.9090909090909918</v>
+        <v>-457.66666666666652</v>
       </c>
       <c r="J32" s="16">
-        <v>1499</v>
+        <v>2191</v>
       </c>
       <c r="K32" s="13">
-        <v>6220.85</v>
+        <v>9092.6500000000015</v>
       </c>
       <c r="L32" s="14">
-        <v>8.7451604348979046</v>
+        <v>12.336711711711713</v>
       </c>
       <c r="M32" s="30">
-        <v>3771.0000000000005</v>
+        <v>3907.2</v>
       </c>
       <c r="N32" s="15">
-        <v>-215.09090909090946</v>
+        <v>415</v>
       </c>
       <c r="O32" s="16">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="P32" s="17">
-        <v>319.55</v>
+        <v>664</v>
       </c>
       <c r="Q32" s="14">
-        <v>6.0284697508896796</v>
+        <v>11.538461538461538</v>
       </c>
       <c r="R32" s="16">
-        <v>281</v>
+        <v>305.06666666666666</v>
       </c>
       <c r="S32" s="15">
-        <v>-178.45454545454547</v>
+        <v>-117.33333333333337</v>
       </c>
       <c r="T32" s="18">
-        <v>661</v>
+        <v>867</v>
       </c>
       <c r="U32" s="17">
-        <v>2743.15</v>
+        <v>3598.05</v>
       </c>
       <c r="V32" s="14">
-        <v>7.9421081376297096</v>
+        <v>10.547445255474452</v>
       </c>
       <c r="W32" s="16">
-        <v>1831</v>
+        <v>1808.4</v>
       </c>
       <c r="X32" s="15">
-        <v>-587.40909090909099</v>
+        <v>-366</v>
       </c>
       <c r="Y32" s="18">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z32" s="17">
-        <v>1203.5</v>
+        <v>1199.3500000000001</v>
       </c>
       <c r="AA32" s="14">
-        <v>66.557377049180332</v>
+        <v>71.06557377049181</v>
       </c>
       <c r="AB32" s="16">
-        <v>95.857142857142847</v>
+        <v>89.466666666666669</v>
       </c>
       <c r="AC32" s="15">
-        <v>224.64285714285717</v>
+        <v>228</v>
       </c>
       <c r="AD32" s="19">
-        <v>4717</v>
+        <v>5200</v>
       </c>
       <c r="AE32" s="20">
-        <v>19575.550000000003</v>
+        <v>21580.000000000004</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4509,64 +4511,64 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>2908</v>
+        <v>1926</v>
       </c>
       <c r="F33" s="14">
-        <v>12068.2</v>
+        <v>7992.9000000000005</v>
       </c>
       <c r="G33" s="14">
-        <v>7.2617480136208856</v>
+        <v>4.5988538681948423</v>
       </c>
       <c r="H33" s="30">
-        <v>8810</v>
+        <v>9213.6</v>
       </c>
       <c r="I33" s="15">
-        <v>-1096.5454545454545</v>
+        <v>-2262</v>
       </c>
       <c r="J33" s="16">
-        <v>2029</v>
+        <v>3671</v>
       </c>
       <c r="K33" s="13">
-        <v>8420.35</v>
+        <v>15234.650000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>8.7991326631184705</v>
+        <v>14.19201030927835</v>
       </c>
       <c r="M33" s="30">
-        <v>5073</v>
+        <v>5690.666666666667</v>
       </c>
       <c r="N33" s="15">
-        <v>-276.90909090909099</v>
+        <v>1084.333333333333</v>
       </c>
       <c r="O33" s="16">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="P33" s="17">
-        <v>315.40000000000003</v>
+        <v>975.25000000000011</v>
       </c>
       <c r="Q33" s="14">
-        <v>4.6573816155988865</v>
+        <v>11.710963455149502</v>
       </c>
       <c r="R33" s="16">
-        <v>359</v>
+        <v>441.46666666666664</v>
       </c>
       <c r="S33" s="15">
-        <v>-250.36363636363632</v>
+        <v>-166.33333333333331</v>
       </c>
       <c r="T33" s="18">
-        <v>1058</v>
+        <v>1199</v>
       </c>
       <c r="U33" s="17">
-        <v>4390.7000000000007</v>
+        <v>4975.8500000000004</v>
       </c>
       <c r="V33" s="14">
-        <v>9.0850897736143637</v>
+        <v>11.448122215149587</v>
       </c>
       <c r="W33" s="16">
-        <v>2562</v>
+        <v>2304.1333333333332</v>
       </c>
       <c r="X33" s="15">
-        <v>-688.81818181818176</v>
+        <v>-372</v>
       </c>
       <c r="Y33" s="18">
         <v>82</v>
@@ -4575,19 +4577,19 @@
         <v>340.3</v>
       </c>
       <c r="AA33" s="14">
-        <v>6.5977011494252871</v>
+        <v>7.0689655172413799</v>
       </c>
       <c r="AB33" s="16">
-        <v>273.42857142857144</v>
+        <v>255.2</v>
       </c>
       <c r="AC33" s="15">
-        <v>-104.42857142857144</v>
+        <v>-92</v>
       </c>
       <c r="AD33" s="19">
-        <v>6153</v>
+        <v>7113</v>
       </c>
       <c r="AE33" s="20">
-        <v>25534.95</v>
+        <v>29518.95</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4628,13 +4630,13 @@
         <v>3311.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>11.862162162162162</v>
+        <v>13.449438202247189</v>
       </c>
       <c r="H34" s="30">
-        <v>1480</v>
+        <v>1305.3333333333335</v>
       </c>
       <c r="I34" s="15">
-        <v>125.27272727272737</v>
+        <v>204.66666666666652</v>
       </c>
       <c r="J34" s="16">
         <v>336</v>
@@ -4652,7 +4654,7 @@
         <v>336</v>
       </c>
       <c r="O34" s="16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P34" s="17">
         <v>0</v>
@@ -4661,25 +4663,25 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>0</v>
+        <v>46.93333333333333</v>
       </c>
       <c r="S34" s="15">
-        <v>32</v>
+        <v>-42.666666666666664</v>
       </c>
       <c r="T34" s="18">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="U34" s="17">
-        <v>265.60000000000002</v>
+        <v>539.5</v>
       </c>
       <c r="V34" s="14">
-        <v>14.978723404255319</v>
+        <v>17.72727272727273</v>
       </c>
       <c r="W34" s="16">
-        <v>94</v>
+        <v>161.33333333333331</v>
       </c>
       <c r="X34" s="15">
-        <v>-9.0909090909093493E-2</v>
+        <v>20.000000000000014</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4697,10 +4699,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1262</v>
+        <v>1296</v>
       </c>
       <c r="AE34" s="20">
-        <v>5237.3</v>
+        <v>5378.4000000000005</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4735,85 +4737,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>4046</v>
+        <v>3317</v>
       </c>
       <c r="F35" s="14">
-        <v>6594.98</v>
+        <v>5406.71</v>
       </c>
       <c r="G35" s="14">
-        <v>8.3235459135964103</v>
+        <v>7.6996285979572887</v>
       </c>
       <c r="H35" s="30">
-        <v>10694</v>
+        <v>9477.6</v>
       </c>
       <c r="I35" s="15">
-        <v>-814.90909090909099</v>
+        <v>-991</v>
       </c>
       <c r="J35" s="16">
-        <v>842</v>
+        <v>620</v>
       </c>
       <c r="K35" s="13">
-        <v>1372.4599999999998</v>
+        <v>1010.5999999999999</v>
       </c>
       <c r="L35" s="14">
-        <v>5.7510090034150885</v>
+        <v>3.8525269262634629</v>
       </c>
       <c r="M35" s="30">
-        <v>3221</v>
+        <v>3540.5333333333333</v>
       </c>
       <c r="N35" s="15">
-        <v>-622.09090909090901</v>
+        <v>-989.33333333333348</v>
       </c>
       <c r="O35" s="16">
-        <v>400</v>
+        <v>770</v>
       </c>
       <c r="P35" s="17">
-        <v>652</v>
+        <v>1255.0999999999999</v>
       </c>
       <c r="Q35" s="14">
-        <v>9.2146596858638752</v>
+        <v>20.961887477313972</v>
       </c>
       <c r="R35" s="16">
-        <v>955</v>
+        <v>808.13333333333333</v>
       </c>
       <c r="S35" s="15">
-        <v>-468.18181818181813</v>
+        <v>35.333333333333258</v>
       </c>
       <c r="T35" s="18">
-        <v>237</v>
+        <v>371</v>
       </c>
       <c r="U35" s="17">
-        <v>386.31</v>
+        <v>604.7299999999999</v>
       </c>
       <c r="V35" s="14">
-        <v>3.8281938325991192</v>
+        <v>8.5615384615384613</v>
       </c>
       <c r="W35" s="16">
-        <v>1362</v>
+        <v>953.33333333333337</v>
       </c>
       <c r="X35" s="15">
-        <v>-691.63636363636363</v>
+        <v>-279</v>
       </c>
       <c r="Y35" s="18">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="Z35" s="17">
-        <v>498.78</v>
+        <v>480.84999999999997</v>
       </c>
       <c r="AA35" s="14">
-        <v>22.666666666666668</v>
+        <v>23.412698412698415</v>
       </c>
       <c r="AB35" s="16">
-        <v>297</v>
+        <v>277.2</v>
       </c>
       <c r="AC35" s="15">
-        <v>103.5</v>
+        <v>106</v>
       </c>
       <c r="AD35" s="19">
-        <v>5831</v>
+        <v>5373</v>
       </c>
       <c r="AE35" s="20">
-        <v>9504.5299999999988</v>
+        <v>8757.99</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4848,85 +4850,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>5580</v>
+        <v>4632</v>
       </c>
       <c r="F36" s="14">
-        <v>9095.4</v>
+        <v>7550.16</v>
       </c>
       <c r="G36" s="14">
-        <v>7.4639751930443241</v>
+        <v>7.399361022364217</v>
       </c>
       <c r="H36" s="30">
-        <v>16447</v>
+        <v>13772</v>
       </c>
       <c r="I36" s="15">
-        <v>-1895.909090909091</v>
+        <v>-1628</v>
       </c>
       <c r="J36" s="16">
-        <v>3076</v>
+        <v>3342</v>
       </c>
       <c r="K36" s="13">
-        <v>5013.88</v>
+        <v>5447.46</v>
       </c>
       <c r="L36" s="14">
-        <v>13.715443858937981</v>
+        <v>14.726792009400702</v>
       </c>
       <c r="M36" s="30">
-        <v>4934</v>
+        <v>4992.5333333333338</v>
       </c>
       <c r="N36" s="15">
-        <v>833.27272727272702</v>
+        <v>1072.6666666666665</v>
       </c>
       <c r="O36" s="16">
-        <v>10</v>
+        <v>988</v>
       </c>
       <c r="P36" s="17">
-        <v>16.299999999999997</v>
+        <v>1610.4399999999998</v>
       </c>
       <c r="Q36" s="14">
-        <v>0.10983524712930604</v>
+        <v>10.533049040511727</v>
       </c>
       <c r="R36" s="16">
-        <v>2003</v>
+        <v>2063.6</v>
       </c>
       <c r="S36" s="15">
-        <v>-1810.909090909091</v>
+        <v>-888</v>
       </c>
       <c r="T36" s="18">
-        <v>1205</v>
+        <v>968</v>
       </c>
       <c r="U36" s="17">
-        <v>1964.1499999999999</v>
+        <v>1577.84</v>
       </c>
       <c r="V36" s="14">
-        <v>9.0231449965963257</v>
+        <v>9.0977443609022544</v>
       </c>
       <c r="W36" s="16">
-        <v>2938</v>
+        <v>2340.8000000000002</v>
       </c>
       <c r="X36" s="15">
-        <v>-798.18181818181802</v>
+        <v>-628</v>
       </c>
       <c r="Y36" s="18">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="Z36" s="17">
-        <v>547.67999999999995</v>
+        <v>516.70999999999992</v>
       </c>
       <c r="AA36" s="14">
-        <v>13.917159763313609</v>
+        <v>13.903508771929824</v>
       </c>
       <c r="AB36" s="16">
-        <v>531.14285714285711</v>
+        <v>501.6</v>
       </c>
       <c r="AC36" s="15">
-        <v>-26.14285714285711</v>
+        <v>-25</v>
       </c>
       <c r="AD36" s="19">
-        <v>10207</v>
+        <v>10247</v>
       </c>
       <c r="AE36" s="20">
-        <v>16637.41</v>
+        <v>16702.61</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4961,64 +4963,64 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>836</v>
+        <v>322</v>
       </c>
       <c r="F37" s="14">
-        <v>1362.6799999999998</v>
+        <v>524.86</v>
       </c>
       <c r="G37" s="14">
-        <v>3.0864238966269508</v>
+        <v>1.1922981979758085</v>
       </c>
       <c r="H37" s="30">
-        <v>5959</v>
+        <v>5941.4666666666662</v>
       </c>
       <c r="I37" s="15">
-        <v>-1872.636363636364</v>
+        <v>-2378.6666666666665</v>
       </c>
       <c r="J37" s="16">
-        <v>2586</v>
+        <v>2252</v>
       </c>
       <c r="K37" s="13">
-        <v>4215.1799999999994</v>
+        <v>3670.7599999999998</v>
       </c>
       <c r="L37" s="14">
-        <v>23.489677952105698</v>
+        <v>17.017632241813601</v>
       </c>
       <c r="M37" s="30">
-        <v>2422</v>
+        <v>2911.3333333333335</v>
       </c>
       <c r="N37" s="15">
-        <v>1485.090909090909</v>
+        <v>928.66666666666652</v>
       </c>
       <c r="O37" s="16">
-        <v>0</v>
+        <v>479</v>
       </c>
       <c r="P37" s="17">
-        <v>0</v>
+        <v>780.77</v>
       </c>
       <c r="Q37" s="14">
-        <v>0</v>
+        <v>8.2681242807825086</v>
       </c>
       <c r="R37" s="16">
-        <v>1017</v>
+        <v>1274.5333333333333</v>
       </c>
       <c r="S37" s="15">
-        <v>-924.5454545454545</v>
+        <v>-679.66666666666652</v>
       </c>
       <c r="T37" s="18">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="U37" s="17">
-        <v>321.10999999999996</v>
+        <v>363.48999999999995</v>
       </c>
       <c r="V37" s="14">
-        <v>2.8456992777412999</v>
+        <v>4.0693430656934311</v>
       </c>
       <c r="W37" s="16">
-        <v>1523</v>
+        <v>1205.5999999999999</v>
       </c>
       <c r="X37" s="15">
-        <v>-841.40909090909099</v>
+        <v>-599</v>
       </c>
       <c r="Y37" s="18">
         <v>0</v>
@@ -5030,16 +5032,16 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>386.57142857142861</v>
+        <v>360.79999999999995</v>
       </c>
       <c r="AC37" s="15">
-        <v>-263.57142857142861</v>
+        <v>-245.99999999999997</v>
       </c>
       <c r="AD37" s="19">
-        <v>3619</v>
+        <v>3276</v>
       </c>
       <c r="AE37" s="20">
-        <v>5898.9699999999993</v>
+        <v>5339.8799999999992</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5074,85 +5076,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="F38" s="14">
-        <v>309.7</v>
+        <v>0</v>
       </c>
       <c r="G38" s="14">
-        <v>1.0172791433438793</v>
+        <v>0</v>
       </c>
       <c r="H38" s="30">
-        <v>4109</v>
+        <v>4210.8</v>
       </c>
       <c r="I38" s="15">
-        <v>-1677.7272727272727</v>
+        <v>-1914</v>
       </c>
       <c r="J38" s="16">
-        <v>1838</v>
+        <v>1507</v>
       </c>
       <c r="K38" s="13">
-        <v>2995.9399999999996</v>
+        <v>2456.41</v>
       </c>
       <c r="L38" s="14">
-        <v>19.384467881112176</v>
+        <v>15.019933554817278</v>
       </c>
       <c r="M38" s="30">
-        <v>2086</v>
+        <v>2207.333333333333</v>
       </c>
       <c r="N38" s="15">
-        <v>889.81818181818187</v>
+        <v>503.66666666666686</v>
       </c>
       <c r="O38" s="16">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="P38" s="17">
-        <v>91.28</v>
+        <v>236.35</v>
       </c>
       <c r="Q38" s="14">
-        <v>1.6404793608521973</v>
+        <v>3.8908765652951702</v>
       </c>
       <c r="R38" s="16">
-        <v>751</v>
+        <v>819.86666666666667</v>
       </c>
       <c r="S38" s="15">
-        <v>-626.72727272727263</v>
+        <v>-600.33333333333326</v>
       </c>
       <c r="T38" s="18">
-        <v>434</v>
+        <v>364</v>
       </c>
       <c r="U38" s="17">
-        <v>707.42</v>
+        <v>593.31999999999994</v>
       </c>
       <c r="V38" s="14">
-        <v>9.3151219512195116</v>
+        <v>10.985915492957746</v>
       </c>
       <c r="W38" s="16">
-        <v>1025</v>
+        <v>728.93333333333328</v>
       </c>
       <c r="X38" s="15">
-        <v>-264.86363636363637</v>
+        <v>-133</v>
       </c>
       <c r="Y38" s="18">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="Z38" s="17">
-        <v>425.42999999999995</v>
+        <v>400.97999999999996</v>
       </c>
       <c r="AA38" s="14">
-        <v>10.264044943820224</v>
+        <v>10.278551532033426</v>
       </c>
       <c r="AB38" s="16">
-        <v>559.42857142857144</v>
+        <v>526.5333333333333</v>
       </c>
       <c r="AC38" s="15">
-        <v>-120.42857142857144</v>
+        <v>-113</v>
       </c>
       <c r="AD38" s="19">
-        <v>2779</v>
+        <v>2262</v>
       </c>
       <c r="AE38" s="20">
-        <v>4529.7699999999995</v>
+        <v>3687.06</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5187,85 +5189,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1933</v>
+        <v>1669</v>
       </c>
       <c r="F39" s="14">
-        <v>3150.79</v>
+        <v>2720.47</v>
       </c>
       <c r="G39" s="14">
-        <v>227.41176470588235</v>
+        <v>17.617874736101339</v>
       </c>
       <c r="H39" s="30">
-        <v>187</v>
+        <v>2084.1333333333332</v>
       </c>
       <c r="I39" s="15">
-        <v>1848</v>
+        <v>721.66666666666663</v>
       </c>
       <c r="J39" s="16">
-        <v>3769</v>
+        <v>3625</v>
       </c>
       <c r="K39" s="13">
-        <v>6143.4699999999993</v>
+        <v>5908.75</v>
       </c>
       <c r="L39" s="14">
-        <v>101.61519607843138</v>
+        <v>64.121462264150949</v>
       </c>
       <c r="M39" s="30">
-        <v>815.99999999999989</v>
+        <v>1243.7333333333333</v>
       </c>
       <c r="N39" s="15">
-        <v>3398.090909090909</v>
+        <v>3059.666666666667</v>
       </c>
       <c r="O39" s="16">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="P39" s="17">
-        <v>420.53999999999996</v>
+        <v>322.73999999999995</v>
       </c>
       <c r="Q39" s="14">
-        <v>516</v>
+        <v>6.2790697674418601</v>
       </c>
       <c r="R39" s="16">
-        <v>11</v>
+        <v>693.73333333333335</v>
       </c>
       <c r="S39" s="15">
-        <v>248</v>
+        <v>-432.66666666666674</v>
       </c>
       <c r="T39" s="18">
-        <v>302</v>
+        <v>515</v>
       </c>
       <c r="U39" s="17">
-        <v>492.26</v>
+        <v>839.44999999999993</v>
       </c>
       <c r="V39" s="14">
-        <v>12.349442379182157</v>
+        <v>9.9935316946959905</v>
       </c>
       <c r="W39" s="16">
-        <v>538</v>
+        <v>1133.7333333333333</v>
       </c>
       <c r="X39" s="15">
-        <v>-64.818181818181813</v>
+        <v>-258</v>
       </c>
       <c r="Y39" s="18">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="Z39" s="17">
-        <v>751.43</v>
+        <v>733.5</v>
       </c>
       <c r="AA39" s="14">
-        <v>100.84375</v>
+        <v>99.264705882352942</v>
       </c>
       <c r="AB39" s="16">
-        <v>100.57142857142857</v>
+        <v>99.733333333333334</v>
       </c>
       <c r="AC39" s="15">
-        <v>392.42857142857144</v>
+        <v>382</v>
       </c>
       <c r="AD39" s="19">
-        <v>6723</v>
+        <v>6457</v>
       </c>
       <c r="AE39" s="20">
-        <v>10958.49</v>
+        <v>10524.91</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5300,85 +5302,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1618</v>
+        <v>1305</v>
       </c>
       <c r="F40" s="14">
-        <v>2637.3399999999997</v>
+        <v>2127.1499999999996</v>
       </c>
       <c r="G40" s="14">
-        <v>192.41081081081083</v>
+        <v>10.690879300928454</v>
       </c>
       <c r="H40" s="30">
-        <v>185</v>
+        <v>2685.4666666666667</v>
       </c>
       <c r="I40" s="15">
-        <v>1533.909090909091</v>
+        <v>84.333333333333485</v>
       </c>
       <c r="J40" s="16">
-        <v>3810</v>
+        <v>3582</v>
       </c>
       <c r="K40" s="13">
-        <v>6210.2999999999993</v>
+        <v>5838.66</v>
       </c>
       <c r="L40" s="14">
-        <v>117.39495798319328</v>
+        <v>52.114451988360813</v>
       </c>
       <c r="M40" s="30">
-        <v>714</v>
+        <v>1512.1333333333334</v>
       </c>
       <c r="N40" s="15">
-        <v>3485.4545454545455</v>
+        <v>2894.6666666666665</v>
       </c>
       <c r="O40" s="16">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="P40" s="17">
-        <v>288.51</v>
+        <v>145.07</v>
       </c>
       <c r="Q40" s="14">
-        <v>354</v>
+        <v>2.2361809045226133</v>
       </c>
       <c r="R40" s="16">
-        <v>11</v>
+        <v>875.59999999999991</v>
       </c>
       <c r="S40" s="15">
-        <v>167</v>
+        <v>-707</v>
       </c>
       <c r="T40" s="18">
-        <v>245</v>
+        <v>374</v>
       </c>
       <c r="U40" s="17">
-        <v>399.34999999999997</v>
+        <v>609.62</v>
       </c>
       <c r="V40" s="14">
-        <v>9.5737122557726462</v>
+        <v>5.9302325581395348</v>
       </c>
       <c r="W40" s="16">
-        <v>563</v>
+        <v>1387.4666666666667</v>
       </c>
       <c r="X40" s="15">
-        <v>-138.86363636363637</v>
+        <v>-572</v>
       </c>
       <c r="Y40" s="18">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="Z40" s="17">
-        <v>766.09999999999991</v>
+        <v>759.57999999999993</v>
       </c>
       <c r="AA40" s="14">
-        <v>104.44444444444444</v>
+        <v>110.95238095238095</v>
       </c>
       <c r="AB40" s="16">
-        <v>99</v>
+        <v>92.4</v>
       </c>
       <c r="AC40" s="15">
-        <v>402.5</v>
+        <v>403</v>
       </c>
       <c r="AD40" s="19">
-        <v>6320</v>
+        <v>5816</v>
       </c>
       <c r="AE40" s="20">
-        <v>10301.599999999999</v>
+        <v>9480.08</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5413,64 +5415,64 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="F41" s="14">
-        <v>1439.1000000000001</v>
+        <v>990.15000000000009</v>
       </c>
       <c r="G41" s="14">
-        <v>3.8360655737704916</v>
+        <v>2.4320241691842899</v>
       </c>
       <c r="H41" s="30">
-        <v>1342</v>
+        <v>1456.4</v>
       </c>
       <c r="I41" s="15">
-        <v>-376</v>
+        <v>-501</v>
       </c>
       <c r="J41" s="16">
-        <v>818</v>
+        <v>726</v>
       </c>
       <c r="K41" s="13">
-        <v>5030.7000000000007</v>
+        <v>4464.9000000000005</v>
       </c>
       <c r="L41" s="14">
-        <v>22.722222222222221</v>
+        <v>20.625</v>
       </c>
       <c r="M41" s="30">
-        <v>792</v>
+        <v>774.40000000000009</v>
       </c>
       <c r="N41" s="15">
-        <v>458</v>
+        <v>374</v>
       </c>
       <c r="O41" s="16">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="P41" s="17">
-        <v>172.20000000000002</v>
+        <v>307.5</v>
       </c>
       <c r="Q41" s="14">
-        <v>7.4216867469879517</v>
+        <v>9.375</v>
       </c>
       <c r="R41" s="16">
-        <v>83</v>
+        <v>117.33333333333333</v>
       </c>
       <c r="S41" s="15">
-        <v>-47.454545454545453</v>
+        <v>-56.666666666666657</v>
       </c>
       <c r="T41" s="18">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="U41" s="17">
-        <v>1063.95</v>
+        <v>984</v>
       </c>
       <c r="V41" s="14">
-        <v>10.231182795698924</v>
+        <v>15.789473684210527</v>
       </c>
       <c r="W41" s="16">
-        <v>372</v>
+        <v>222.93333333333334</v>
       </c>
       <c r="X41" s="15">
-        <v>-80.636363636363654</v>
+        <v>8</v>
       </c>
       <c r="Y41" s="18">
         <v>17</v>
@@ -5479,19 +5481,19 @@
         <v>104.55000000000001</v>
       </c>
       <c r="AA41" s="14">
-        <v>3.6615384615384614</v>
+        <v>3.9230769230769234</v>
       </c>
       <c r="AB41" s="16">
-        <v>102.14285714285715</v>
+        <v>95.333333333333329</v>
       </c>
       <c r="AC41" s="15">
-        <v>-52.642857142857153</v>
+        <v>-48</v>
       </c>
       <c r="AD41" s="19">
-        <v>1270</v>
+        <v>1114</v>
       </c>
       <c r="AE41" s="20">
-        <v>7810.5</v>
+        <v>6851.1</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5526,64 +5528,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="F42" s="14">
-        <v>1088.55</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14">
-        <v>2.7577903682719547</v>
+        <v>0</v>
       </c>
       <c r="H42" s="30">
-        <v>1412</v>
+        <v>1509.1999999999998</v>
       </c>
       <c r="I42" s="15">
-        <v>-464.81818181818187</v>
+        <v>-686</v>
       </c>
       <c r="J42" s="16">
-        <v>858</v>
+        <v>744</v>
       </c>
       <c r="K42" s="13">
-        <v>5276.7000000000007</v>
+        <v>4575.6000000000004</v>
       </c>
       <c r="L42" s="14">
-        <v>20.384449244060473</v>
+        <v>20.62846580406654</v>
       </c>
       <c r="M42" s="30">
-        <v>926</v>
+        <v>793.4666666666667</v>
       </c>
       <c r="N42" s="15">
-        <v>437.09090909090907</v>
+        <v>383.33333333333331</v>
       </c>
       <c r="O42" s="16">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="P42" s="17">
-        <v>98.4</v>
+        <v>356.70000000000005</v>
       </c>
       <c r="Q42" s="14">
-        <v>4.3456790123456788</v>
+        <v>8.2075471698113205</v>
       </c>
       <c r="R42" s="16">
-        <v>81</v>
+        <v>155.46666666666667</v>
       </c>
       <c r="S42" s="15">
-        <v>-57.636363636363626</v>
+        <v>-83.333333333333314</v>
       </c>
       <c r="T42" s="18">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="U42" s="17">
-        <v>1482.15</v>
+        <v>1230</v>
       </c>
       <c r="V42" s="14">
-        <v>10.003773584905661</v>
+        <v>12.295081967213115</v>
       </c>
       <c r="W42" s="16">
-        <v>530</v>
+        <v>357.86666666666667</v>
       </c>
       <c r="X42" s="15">
-        <v>-120.36363636363637</v>
+        <v>-44</v>
       </c>
       <c r="Y42" s="18">
         <v>84</v>
@@ -5592,19 +5594,19 @@
         <v>516.6</v>
       </c>
       <c r="AA42" s="14">
-        <v>20.631578947368421</v>
+        <v>22.105263157894736</v>
       </c>
       <c r="AB42" s="16">
-        <v>89.571428571428569</v>
+        <v>83.6</v>
       </c>
       <c r="AC42" s="15">
-        <v>22.928571428571431</v>
+        <v>27</v>
       </c>
       <c r="AD42" s="19">
-        <v>1376</v>
+        <v>1086</v>
       </c>
       <c r="AE42" s="20">
-        <v>8462.4</v>
+        <v>6678.9000000000005</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5639,85 +5641,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2989</v>
+        <v>2276</v>
       </c>
       <c r="F43" s="14">
-        <v>3467.24</v>
+        <v>2640.16</v>
       </c>
       <c r="G43" s="14">
-        <v>8.9090909090909083</v>
+        <v>7.3214668668239327</v>
       </c>
       <c r="H43" s="30">
-        <v>7381</v>
+        <v>6839.0666666666666</v>
       </c>
       <c r="I43" s="15">
-        <v>-366</v>
+        <v>-832.66666666666697</v>
       </c>
       <c r="J43" s="16">
-        <v>1534</v>
+        <v>3566</v>
       </c>
       <c r="K43" s="13">
-        <v>1779.4399999999998</v>
+        <v>4136.5599999999995</v>
       </c>
       <c r="L43" s="14">
-        <v>12.294353369763206</v>
+        <v>15.788075560802833</v>
       </c>
       <c r="M43" s="30">
-        <v>2745</v>
+        <v>4969.0666666666666</v>
       </c>
       <c r="N43" s="15">
-        <v>286.27272727272725</v>
+        <v>1307.333333333333</v>
       </c>
       <c r="O43" s="16">
-        <v>35</v>
+        <v>833</v>
       </c>
       <c r="P43" s="17">
-        <v>40.599999999999994</v>
+        <v>966.28</v>
       </c>
       <c r="Q43" s="14">
-        <v>0.6772207563764292</v>
+        <v>17.850000000000005</v>
       </c>
       <c r="R43" s="16">
-        <v>1137</v>
+        <v>1026.6666666666665</v>
       </c>
       <c r="S43" s="15">
-        <v>-998.63636363636351</v>
+        <v>-100.33333333333314</v>
       </c>
       <c r="T43" s="18">
-        <v>956</v>
+        <v>1125</v>
       </c>
       <c r="U43" s="17">
-        <v>1108.96</v>
+        <v>1305</v>
       </c>
       <c r="V43" s="14">
-        <v>10.135903614457831</v>
+        <v>9.7543352601156084</v>
       </c>
       <c r="W43" s="16">
-        <v>2075</v>
+        <v>2537.333333333333</v>
       </c>
       <c r="X43" s="15">
-        <v>-458.77272727272725</v>
+        <v>-604.99999999999977</v>
       </c>
       <c r="Y43" s="18">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="Z43" s="17">
-        <v>248.23999999999998</v>
+        <v>228.51999999999998</v>
       </c>
       <c r="AA43" s="14">
-        <v>8.0754716981132084</v>
+        <v>7.7559055118110241</v>
       </c>
       <c r="AB43" s="16">
-        <v>583</v>
+        <v>558.79999999999995</v>
       </c>
       <c r="AC43" s="15">
-        <v>-183.5</v>
+        <v>-184</v>
       </c>
       <c r="AD43" s="19">
-        <v>5728</v>
+        <v>7997</v>
       </c>
       <c r="AE43" s="20">
-        <v>6644.48</v>
+        <v>9276.5199999999986</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5752,85 +5754,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2767</v>
+        <v>2097</v>
       </c>
       <c r="F44" s="14">
-        <v>3209.72</v>
+        <v>2432.52</v>
       </c>
       <c r="G44" s="14">
-        <v>9.4554209381795591</v>
+        <v>7.5612980769230775</v>
       </c>
       <c r="H44" s="30">
-        <v>6438</v>
+        <v>6101.333333333333</v>
       </c>
       <c r="I44" s="15">
-        <v>-159.36363636363603</v>
+        <v>-676.33333333333303</v>
       </c>
       <c r="J44" s="16">
-        <v>1678</v>
+        <v>3394</v>
       </c>
       <c r="K44" s="13">
-        <v>1946.4799999999998</v>
+        <v>3937.0399999999995</v>
       </c>
       <c r="L44" s="14">
-        <v>9.7972399150743108</v>
+        <v>18.485838779956428</v>
       </c>
       <c r="M44" s="30">
-        <v>3767.9999999999995</v>
+        <v>4039.2</v>
       </c>
       <c r="N44" s="15">
-        <v>-34.727272727272521</v>
+        <v>1558</v>
       </c>
       <c r="O44" s="16">
-        <v>223</v>
+        <v>633</v>
       </c>
       <c r="P44" s="17">
-        <v>258.68</v>
+        <v>734.28</v>
       </c>
       <c r="Q44" s="14">
-        <v>6.5239361702127665</v>
+        <v>22.879518072289152</v>
       </c>
       <c r="R44" s="16">
-        <v>752</v>
+        <v>608.66666666666674</v>
       </c>
       <c r="S44" s="15">
-        <v>-460.63636363636363</v>
+        <v>79.666666666666515</v>
       </c>
       <c r="T44" s="18">
-        <v>791</v>
+        <v>1206</v>
       </c>
       <c r="U44" s="17">
-        <v>917.56</v>
+        <v>1398.9599999999998</v>
       </c>
       <c r="V44" s="14">
-        <v>9.3559139784946233</v>
+        <v>20.234899328859061</v>
       </c>
       <c r="W44" s="16">
-        <v>1860</v>
+        <v>1311.2</v>
       </c>
       <c r="X44" s="15">
-        <v>-477.18181818181824</v>
+        <v>312</v>
       </c>
       <c r="Y44" s="18">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="Z44" s="17">
-        <v>382.79999999999995</v>
+        <v>346.84</v>
       </c>
       <c r="AA44" s="14">
-        <v>13.50877192982456</v>
+        <v>12.705382436260622</v>
       </c>
       <c r="AB44" s="16">
-        <v>537.42857142857144</v>
+        <v>517.73333333333335</v>
       </c>
       <c r="AC44" s="15">
-        <v>-36.428571428571445</v>
+        <v>-54</v>
       </c>
       <c r="AD44" s="19">
-        <v>5789</v>
+        <v>7629</v>
       </c>
       <c r="AE44" s="20">
-        <v>6715.24</v>
+        <v>8849.64</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5865,85 +5867,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3031</v>
+        <v>2307</v>
       </c>
       <c r="F45" s="14">
-        <v>3515.9599999999996</v>
+        <v>2676.12</v>
       </c>
       <c r="G45" s="14">
-        <v>7.8671543180745642</v>
+        <v>6.3425586510263923</v>
       </c>
       <c r="H45" s="30">
-        <v>8476</v>
+        <v>8002.1333333333332</v>
       </c>
       <c r="I45" s="15">
-        <v>-821.72727272727252</v>
+        <v>-1330.3333333333335</v>
       </c>
       <c r="J45" s="16">
-        <v>1335</v>
+        <v>3431</v>
       </c>
       <c r="K45" s="13">
-        <v>1548.6</v>
+        <v>3979.9599999999996</v>
       </c>
       <c r="L45" s="14">
-        <v>5.4308431952662719</v>
+        <v>13.845843422114609</v>
       </c>
       <c r="M45" s="30">
-        <v>5408</v>
+        <v>5451.6</v>
       </c>
       <c r="N45" s="15">
-        <v>-1123.181818181818</v>
+        <v>953</v>
       </c>
       <c r="O45" s="16">
-        <v>327</v>
+        <v>911</v>
       </c>
       <c r="P45" s="17">
-        <v>379.32</v>
+        <v>1056.76</v>
       </c>
       <c r="Q45" s="14">
-        <v>6.4289544235924927</v>
+        <v>22.075928917609048</v>
       </c>
       <c r="R45" s="16">
-        <v>1119</v>
+        <v>907.86666666666667</v>
       </c>
       <c r="S45" s="15">
-        <v>-690.27272727272737</v>
+        <v>85.666666666666742</v>
       </c>
       <c r="T45" s="18">
-        <v>1011</v>
+        <v>1192</v>
       </c>
       <c r="U45" s="17">
-        <v>1172.76</v>
+        <v>1382.7199999999998</v>
       </c>
       <c r="V45" s="14">
-        <v>8.7913043478260864</v>
+        <v>13.303571428571429</v>
       </c>
       <c r="W45" s="16">
-        <v>2530</v>
+        <v>1971.1999999999998</v>
       </c>
       <c r="X45" s="15">
-        <v>-714</v>
+        <v>-152</v>
       </c>
       <c r="Y45" s="18">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="Z45" s="17">
-        <v>286.52</v>
+        <v>250.55999999999997</v>
       </c>
       <c r="AA45" s="14">
-        <v>9.7134831460674143</v>
+        <v>8.8283378746594003</v>
       </c>
       <c r="AB45" s="16">
-        <v>559.42857142857144</v>
+        <v>538.26666666666665</v>
       </c>
       <c r="AC45" s="15">
-        <v>-134.42857142857144</v>
+        <v>-151</v>
       </c>
       <c r="AD45" s="19">
-        <v>5951</v>
+        <v>8057</v>
       </c>
       <c r="AE45" s="20">
-        <v>6903.16</v>
+        <v>9346.119999999999</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5978,85 +5980,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2400</v>
+        <v>1392</v>
       </c>
       <c r="F46" s="14">
-        <v>2784</v>
+        <v>1614.7199999999998</v>
       </c>
       <c r="G46" s="14">
-        <v>9.295774647887324</v>
+        <v>5.225225225225226</v>
       </c>
       <c r="H46" s="30">
-        <v>5680</v>
+        <v>5860.7999999999993</v>
       </c>
       <c r="I46" s="15">
-        <v>-181.81818181818198</v>
+        <v>-1272</v>
       </c>
       <c r="J46" s="16">
-        <v>2518</v>
+        <v>4768</v>
       </c>
       <c r="K46" s="13">
-        <v>2920.8799999999997</v>
+        <v>5530.8799999999992</v>
       </c>
       <c r="L46" s="14">
-        <v>13.953652392947102</v>
+        <v>32.332730560578661</v>
       </c>
       <c r="M46" s="30">
-        <v>3970</v>
+        <v>3244.2666666666669</v>
       </c>
       <c r="N46" s="15">
-        <v>713.45454545454527</v>
+        <v>3293.333333333333</v>
       </c>
       <c r="O46" s="16">
-        <v>361</v>
+        <v>646</v>
       </c>
       <c r="P46" s="17">
-        <v>418.76</v>
+        <v>749.3599999999999</v>
       </c>
       <c r="Q46" s="14">
-        <v>9.6618004866180041</v>
+        <v>27.528409090909093</v>
       </c>
       <c r="R46" s="16">
-        <v>822.00000000000011</v>
+        <v>516.26666666666665</v>
       </c>
       <c r="S46" s="15">
-        <v>-386.27272727272737</v>
+        <v>176.66666666666669</v>
       </c>
       <c r="T46" s="18">
-        <v>540</v>
+        <v>800</v>
       </c>
       <c r="U46" s="17">
-        <v>626.4</v>
+        <v>927.99999999999989</v>
       </c>
       <c r="V46" s="14">
-        <v>9.54983922829582</v>
+        <v>20.689655172413794</v>
       </c>
       <c r="W46" s="16">
-        <v>1244</v>
+        <v>850.66666666666663</v>
       </c>
       <c r="X46" s="15">
-        <v>-308.18181818181824</v>
+        <v>220</v>
       </c>
       <c r="Y46" s="18">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="Z46" s="17">
-        <v>124.11999999999999</v>
+        <v>95.11999999999999</v>
       </c>
       <c r="AA46" s="14">
-        <v>4.4716417910447754</v>
+        <v>3.5860058309037899</v>
       </c>
       <c r="AB46" s="16">
-        <v>526.42857142857144</v>
+        <v>503.06666666666666</v>
       </c>
       <c r="AC46" s="15">
-        <v>-251.92857142857144</v>
+        <v>-261</v>
       </c>
       <c r="AD46" s="19">
-        <v>5926</v>
+        <v>7688</v>
       </c>
       <c r="AE46" s="20">
-        <v>6874.16</v>
+        <v>8918.08</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6104,19 +6106,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K47" s="13">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="L47" s="14">
-        <v>4.125</v>
+        <v>1.125</v>
       </c>
       <c r="M47" s="30">
-        <v>32</v>
+        <v>58.666666666666664</v>
       </c>
       <c r="N47" s="15">
-        <v>-8.5454545454545467</v>
+        <v>-23.666666666666664</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6134,19 +6136,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U47" s="17">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="V47" s="14">
-        <v>1.1000000000000001</v>
+        <v>5</v>
       </c>
       <c r="W47" s="16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X47" s="15">
-        <v>-12.636363636363637</v>
+        <v>-10</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6164,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE47" s="20">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6221,13 +6223,13 @@
         <v>180</v>
       </c>
       <c r="L48" s="14">
-        <v>24.444444444444443</v>
+        <v>21.428571428571427</v>
       </c>
       <c r="M48" s="30">
-        <v>9</v>
+        <v>10.266666666666667</v>
       </c>
       <c r="N48" s="15">
-        <v>5.9090909090909092</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6313,85 +6315,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>448</v>
+        <v>350</v>
       </c>
       <c r="F49" s="14">
-        <v>519.67999999999995</v>
+        <v>406</v>
       </c>
       <c r="G49" s="14">
-        <v>7.967663702506063</v>
+        <v>6.7917205692108666</v>
       </c>
       <c r="H49" s="30">
-        <v>1237</v>
+        <v>1133.7333333333333</v>
       </c>
       <c r="I49" s="15">
-        <v>-114.27272727272725</v>
+        <v>-165.33333333333326</v>
       </c>
       <c r="J49" s="16">
-        <v>279</v>
+        <v>140</v>
       </c>
       <c r="K49" s="13">
-        <v>323.64</v>
+        <v>162.39999999999998</v>
       </c>
       <c r="L49" s="14">
-        <v>4.9781021897810218</v>
+        <v>2.1806853582554515</v>
       </c>
       <c r="M49" s="30">
-        <v>1233</v>
+        <v>1412.4</v>
       </c>
       <c r="N49" s="15">
-        <v>-281.4545454545455</v>
+        <v>-502</v>
       </c>
       <c r="O49" s="16">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="P49" s="17">
-        <v>0</v>
+        <v>90.47999999999999</v>
       </c>
       <c r="Q49" s="14">
-        <v>0</v>
+        <v>11.699999999999998</v>
       </c>
       <c r="R49" s="16">
-        <v>112</v>
+        <v>146.66666666666669</v>
       </c>
       <c r="S49" s="15">
-        <v>-101.81818181818181</v>
+        <v>-55.333333333333371</v>
       </c>
       <c r="T49" s="18">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="U49" s="17">
-        <v>56.839999999999996</v>
+        <v>47.559999999999995</v>
       </c>
       <c r="V49" s="14">
-        <v>4.6465517241379315</v>
+        <v>3.1701030927835046</v>
       </c>
       <c r="W49" s="16">
-        <v>232</v>
+        <v>284.53333333333336</v>
       </c>
       <c r="X49" s="15">
-        <v>-109.18181818181819</v>
+        <v>-153.00000000000003</v>
       </c>
       <c r="Y49" s="18">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Z49" s="17">
-        <v>64.959999999999994</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="AA49" s="14">
-        <v>12.25</v>
+        <v>11.71875</v>
       </c>
       <c r="AB49" s="16">
-        <v>100.57142857142857</v>
+        <v>93.86666666666666</v>
       </c>
       <c r="AC49" s="15">
-        <v>-12.571428571428569</v>
+        <v>-14</v>
       </c>
       <c r="AD49" s="19">
-        <v>832</v>
+        <v>659</v>
       </c>
       <c r="AE49" s="20">
-        <v>965.11999999999989</v>
+        <v>764.43999999999994</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6426,85 +6428,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>2359</v>
+        <v>1719</v>
       </c>
       <c r="F50" s="14">
-        <v>2736.4399999999996</v>
+        <v>1994.04</v>
       </c>
       <c r="G50" s="14">
-        <v>9.2542796005706141</v>
+        <v>6.2936294849890162</v>
       </c>
       <c r="H50" s="30">
-        <v>5608</v>
+        <v>6008.9333333333334</v>
       </c>
       <c r="I50" s="15">
-        <v>-190.09090909090901</v>
+        <v>-1012.333333333333</v>
       </c>
       <c r="J50" s="16">
-        <v>1674</v>
+        <v>1211</v>
       </c>
       <c r="K50" s="13">
-        <v>1941.84</v>
+        <v>1404.76</v>
       </c>
       <c r="L50" s="14">
-        <v>10.298657718120806</v>
+        <v>6.5388768898488125</v>
       </c>
       <c r="M50" s="30">
-        <v>3576</v>
+        <v>4074.3999999999996</v>
       </c>
       <c r="N50" s="15">
-        <v>48.545454545454731</v>
+        <v>-641</v>
       </c>
       <c r="O50" s="16">
-        <v>43</v>
+        <v>320</v>
       </c>
       <c r="P50" s="17">
-        <v>49.879999999999995</v>
+        <v>371.2</v>
       </c>
       <c r="Q50" s="14">
-        <v>1.9708333333333334</v>
+        <v>7.6555023923444985</v>
       </c>
       <c r="R50" s="16">
-        <v>480</v>
+        <v>919.59999999999991</v>
       </c>
       <c r="S50" s="15">
-        <v>-393.36363636363632</v>
+        <v>-516</v>
       </c>
       <c r="T50" s="18">
-        <v>355</v>
+        <v>958</v>
       </c>
       <c r="U50" s="17">
-        <v>411.79999999999995</v>
+        <v>1111.28</v>
       </c>
       <c r="V50" s="14">
-        <v>4.4400227401932915</v>
+        <v>38.733153638814017</v>
       </c>
       <c r="W50" s="16">
-        <v>1759</v>
+        <v>544.13333333333333</v>
       </c>
       <c r="X50" s="15">
-        <v>-844.31818181818176</v>
+        <v>587</v>
       </c>
       <c r="Y50" s="18">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="Z50" s="17">
-        <v>121.8</v>
+        <v>105.55999999999999</v>
       </c>
       <c r="AA50" s="14">
-        <v>9.8657718120805367</v>
+        <v>8.8636363636363633</v>
       </c>
       <c r="AB50" s="16">
-        <v>234.14285714285714</v>
+        <v>225.86666666666667</v>
       </c>
       <c r="AC50" s="15">
-        <v>-54.642857142857139</v>
+        <v>-63</v>
       </c>
       <c r="AD50" s="19">
-        <v>4536</v>
+        <v>4299</v>
       </c>
       <c r="AE50" s="20">
-        <v>5261.7599999999993</v>
+        <v>4986.8399999999992</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6542,85 +6544,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="F51" s="14">
-        <v>481.4</v>
+        <v>0</v>
       </c>
       <c r="G51" s="14">
-        <v>7.1833202202989774</v>
+        <v>0</v>
       </c>
       <c r="H51" s="30">
-        <v>1271</v>
+        <v>4243.0666666666666</v>
       </c>
       <c r="I51" s="15">
-        <v>-162.72727272727275</v>
+        <v>-1928.6666666666667</v>
       </c>
       <c r="J51" s="16">
-        <v>2940</v>
+        <v>2692</v>
       </c>
       <c r="K51" s="13">
-        <v>3410.3999999999996</v>
+        <v>3122.72</v>
       </c>
       <c r="L51" s="14">
-        <v>66</v>
+        <v>16.256038647342997</v>
       </c>
       <c r="M51" s="30">
-        <v>980</v>
+        <v>3643.2</v>
       </c>
       <c r="N51" s="15">
-        <v>2494.5454545454545</v>
+        <v>1036</v>
       </c>
       <c r="O51" s="16">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="P51" s="17">
-        <v>228.51999999999998</v>
+        <v>169.35999999999999</v>
       </c>
       <c r="Q51" s="14">
         <v>0</v>
       </c>
       <c r="R51" s="16">
-        <v>0</v>
+        <v>281.60000000000002</v>
       </c>
       <c r="S51" s="15">
-        <v>197</v>
+        <v>-110</v>
       </c>
       <c r="T51" s="18">
-        <v>475</v>
+        <v>426</v>
       </c>
       <c r="U51" s="17">
-        <v>551</v>
+        <v>494.15999999999997</v>
       </c>
       <c r="V51" s="14">
-        <v>19.423791821561338</v>
+        <v>13.175257731958762</v>
       </c>
       <c r="W51" s="16">
-        <v>538</v>
+        <v>711.33333333333337</v>
       </c>
       <c r="X51" s="15">
-        <v>108.18181818181819</v>
+        <v>-59.000000000000057</v>
       </c>
       <c r="Y51" s="18">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Z51" s="17">
-        <v>127.6</v>
+        <v>118.32</v>
       </c>
       <c r="AA51" s="14">
-        <v>27.999999999999996</v>
+        <v>27.818181818181824</v>
       </c>
       <c r="AB51" s="16">
-        <v>86.428571428571431</v>
+        <v>80.666666666666657</v>
       </c>
       <c r="AC51" s="15">
-        <v>51.071428571428569</v>
+        <v>47.000000000000007</v>
       </c>
       <c r="AD51" s="19">
-        <v>4137</v>
+        <v>3366</v>
       </c>
       <c r="AE51" s="20">
-        <v>4798.92</v>
+        <v>3904.56</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6659,64 +6661,64 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>3123</v>
+        <v>2857</v>
       </c>
       <c r="F52" s="14">
-        <v>2529.63</v>
+        <v>2314.17</v>
       </c>
       <c r="G52" s="14">
-        <v>25.965986394557824</v>
+        <v>20.186057465850212</v>
       </c>
       <c r="H52" s="30">
-        <v>2646</v>
+        <v>3113.7333333333331</v>
       </c>
       <c r="I52" s="15">
-        <v>1920.2727272727273</v>
+        <v>1441.6666666666667</v>
       </c>
       <c r="J52" s="16">
-        <v>73</v>
+        <v>1353</v>
       </c>
       <c r="K52" s="13">
-        <v>59.13</v>
+        <v>1095.93</v>
       </c>
       <c r="L52" s="14">
-        <v>0.82954545454545459</v>
+        <v>41.082995951417011</v>
       </c>
       <c r="M52" s="30">
-        <v>1936</v>
+        <v>724.5333333333333</v>
       </c>
       <c r="N52" s="15">
-        <v>-807</v>
+        <v>1023.6666666666667</v>
       </c>
       <c r="O52" s="16">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="P52" s="17">
-        <v>0</v>
+        <v>21.87</v>
       </c>
       <c r="Q52" s="14">
-        <v>0</v>
+        <v>3.4615384615384617</v>
       </c>
       <c r="R52" s="16">
-        <v>498</v>
+        <v>171.6</v>
       </c>
       <c r="S52" s="15">
-        <v>-452.72727272727275</v>
+        <v>-129</v>
       </c>
       <c r="T52" s="18">
-        <v>551</v>
+        <v>473</v>
       </c>
       <c r="U52" s="17">
-        <v>446.31</v>
+        <v>383.13000000000005</v>
       </c>
       <c r="V52" s="14">
-        <v>13.453940066592676</v>
+        <v>24.381443298969074</v>
       </c>
       <c r="W52" s="16">
-        <v>901</v>
+        <v>426.79999999999995</v>
       </c>
       <c r="X52" s="15">
-        <v>-63.318181818181756</v>
+        <v>182</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6728,16 +6730,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>36.142857142857139</v>
+        <v>33.733333333333334</v>
       </c>
       <c r="AC52" s="15">
-        <v>-24.642857142857139</v>
+        <v>-23</v>
       </c>
       <c r="AD52" s="19">
-        <v>3747</v>
+        <v>4710</v>
       </c>
       <c r="AE52" s="20">
-        <v>3035.07</v>
+        <v>3815.1000000000004</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6772,85 +6774,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1867</v>
+        <v>1436</v>
       </c>
       <c r="F53" s="14">
-        <v>1512.2700000000002</v>
+        <v>1163.1600000000001</v>
       </c>
       <c r="G53" s="14">
-        <v>7.9988315481986367</v>
+        <v>5.4991064590247642</v>
       </c>
       <c r="H53" s="30">
-        <v>5135</v>
+        <v>5744.9333333333334</v>
       </c>
       <c r="I53" s="15">
-        <v>-467.09090909090901</v>
+        <v>-1175.333333333333</v>
       </c>
       <c r="J53" s="16">
-        <v>1154</v>
+        <v>3098</v>
       </c>
       <c r="K53" s="13">
-        <v>934.74</v>
+        <v>2509.38</v>
       </c>
       <c r="L53" s="14">
-        <v>7.9962204724409434</v>
+        <v>26.923522595596758</v>
       </c>
       <c r="M53" s="30">
-        <v>3175.0000000000005</v>
+        <v>2531.4666666666667</v>
       </c>
       <c r="N53" s="15">
-        <v>-289.18181818181847</v>
+        <v>1947.3333333333335</v>
       </c>
       <c r="O53" s="16">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="P53" s="17">
-        <v>55.89</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="Q53" s="14">
-        <v>1.7191392978482445</v>
+        <v>1.5286624203821657</v>
       </c>
       <c r="R53" s="16">
-        <v>883.00000000000011</v>
+        <v>690.8</v>
       </c>
       <c r="S53" s="15">
-        <v>-733.72727272727275</v>
+        <v>-580</v>
       </c>
       <c r="T53" s="18">
-        <v>751</v>
+        <v>872</v>
       </c>
       <c r="U53" s="17">
-        <v>608.31000000000006</v>
+        <v>706.32</v>
       </c>
       <c r="V53" s="14">
-        <v>10.007268322228953</v>
+        <v>16.747759282970549</v>
       </c>
       <c r="W53" s="16">
-        <v>1651</v>
+        <v>1145.4666666666667</v>
       </c>
       <c r="X53" s="15">
-        <v>-374.68181818181824</v>
+        <v>91</v>
       </c>
       <c r="Y53" s="18">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Z53" s="17">
-        <v>23.490000000000002</v>
+        <v>14.580000000000002</v>
       </c>
       <c r="AA53" s="14">
-        <v>4.0198019801980198</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="AB53" s="16">
-        <v>158.71428571428572</v>
+        <v>161.33333333333331</v>
       </c>
       <c r="AC53" s="15">
-        <v>-79.214285714285722</v>
+        <v>-91.999999999999986</v>
       </c>
       <c r="AD53" s="19">
-        <v>3870</v>
+        <v>5472</v>
       </c>
       <c r="AE53" s="20">
-        <v>3134.7000000000003</v>
+        <v>4432.3200000000006</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6885,85 +6887,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1475</v>
+        <v>1272</v>
       </c>
       <c r="F54" s="14">
-        <v>1194.75</v>
+        <v>1030.3200000000002</v>
       </c>
       <c r="G54" s="14">
-        <v>9.4276583381754779</v>
+        <v>7.2796642502861513</v>
       </c>
       <c r="H54" s="30">
-        <v>3442</v>
+        <v>3844.1333333333332</v>
       </c>
       <c r="I54" s="15">
-        <v>-89.545454545454731</v>
+        <v>-475.33333333333326</v>
       </c>
       <c r="J54" s="16">
-        <v>5624</v>
+        <v>5488</v>
       </c>
       <c r="K54" s="13">
-        <v>4555.4400000000005</v>
+        <v>4445.2800000000007</v>
       </c>
       <c r="L54" s="14">
-        <v>70.863688430698744</v>
+        <v>93.016949152542367</v>
       </c>
       <c r="M54" s="30">
-        <v>1746</v>
+        <v>1298</v>
       </c>
       <c r="N54" s="15">
-        <v>4830.363636363636</v>
+        <v>4898</v>
       </c>
       <c r="O54" s="16">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="P54" s="17">
-        <v>188.73000000000002</v>
+        <v>210.60000000000002</v>
       </c>
       <c r="Q54" s="14">
-        <v>14.988304093567251</v>
+        <v>23.076923076923077</v>
       </c>
       <c r="R54" s="16">
-        <v>342</v>
+        <v>247.86666666666667</v>
       </c>
       <c r="S54" s="15">
-        <v>-77.909090909090878</v>
+        <v>34.666666666666657</v>
       </c>
       <c r="T54" s="18">
-        <v>572</v>
+        <v>500</v>
       </c>
       <c r="U54" s="17">
-        <v>463.32000000000005</v>
+        <v>405</v>
       </c>
       <c r="V54" s="14">
-        <v>20.362459546925567</v>
+        <v>19.480519480519476</v>
       </c>
       <c r="W54" s="16">
-        <v>618</v>
+        <v>564.66666666666674</v>
       </c>
       <c r="X54" s="15">
-        <v>150.63636363636363</v>
+        <v>114.99999999999994</v>
       </c>
       <c r="Y54" s="18">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="Z54" s="17">
-        <v>119.07000000000001</v>
+        <v>110.16000000000001</v>
       </c>
       <c r="AA54" s="14">
-        <v>18.212389380530976</v>
+        <v>16.451612903225804</v>
       </c>
       <c r="AB54" s="16">
-        <v>177.57142857142856</v>
+        <v>181.86666666666667</v>
       </c>
       <c r="AC54" s="15">
-        <v>25.928571428571431</v>
+        <v>11.999999999999986</v>
       </c>
       <c r="AD54" s="19">
-        <v>8051</v>
+        <v>7656</v>
       </c>
       <c r="AE54" s="20">
-        <v>6521.31</v>
+        <v>6201.3600000000006</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6998,85 +7000,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>3854</v>
+        <v>2892</v>
       </c>
       <c r="F55" s="14">
-        <v>3121.7400000000002</v>
+        <v>2342.52</v>
       </c>
       <c r="G55" s="14">
-        <v>31.126284875183554</v>
+        <v>18.373570520965693</v>
       </c>
       <c r="H55" s="30">
-        <v>2724</v>
+        <v>3462.8</v>
       </c>
       <c r="I55" s="15">
-        <v>2615.818181818182</v>
+        <v>1318</v>
       </c>
       <c r="J55" s="16">
-        <v>6980</v>
+        <v>6777</v>
       </c>
       <c r="K55" s="13">
-        <v>5653.8</v>
+        <v>5489.3700000000008</v>
       </c>
       <c r="L55" s="14">
-        <v>78.5473145780051</v>
+        <v>92.162284678150499</v>
       </c>
       <c r="M55" s="30">
-        <v>1955.0000000000002</v>
+        <v>1617.7333333333333</v>
       </c>
       <c r="N55" s="15">
-        <v>6091.363636363636</v>
+        <v>6041.666666666667</v>
       </c>
       <c r="O55" s="16">
-        <v>191</v>
+        <v>314</v>
       </c>
       <c r="P55" s="17">
-        <v>154.71</v>
+        <v>254.34</v>
       </c>
       <c r="Q55" s="14">
-        <v>9.3377777777777791</v>
+        <v>18.326848249027236</v>
       </c>
       <c r="R55" s="16">
-        <v>449.99999999999994</v>
+        <v>376.93333333333334</v>
       </c>
       <c r="S55" s="15">
-        <v>-218.09090909090907</v>
+        <v>-28.666666666666629</v>
       </c>
       <c r="T55" s="18">
-        <v>551</v>
+        <v>467</v>
       </c>
       <c r="U55" s="17">
-        <v>446.31</v>
+        <v>378.27000000000004</v>
       </c>
       <c r="V55" s="14">
-        <v>17.09732016925247</v>
+        <v>16.405152224824356</v>
       </c>
       <c r="W55" s="16">
-        <v>709</v>
+        <v>626.26666666666665</v>
       </c>
       <c r="X55" s="15">
-        <v>67.590909090909122</v>
+        <v>40</v>
       </c>
       <c r="Y55" s="18">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="Z55" s="17">
-        <v>132.84</v>
+        <v>123.93</v>
       </c>
       <c r="AA55" s="14">
-        <v>20.318584070796462</v>
+        <v>18.508064516129032</v>
       </c>
       <c r="AB55" s="16">
-        <v>177.57142857142856</v>
+        <v>181.86666666666667</v>
       </c>
       <c r="AC55" s="15">
-        <v>42.928571428571431</v>
+        <v>28.999999999999986</v>
       </c>
       <c r="AD55" s="19">
-        <v>11740</v>
+        <v>10603</v>
       </c>
       <c r="AE55" s="20">
-        <v>9509.4000000000015</v>
+        <v>8588.43</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7111,64 +7113,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>542</v>
+        <v>236</v>
       </c>
       <c r="F56" s="14">
-        <v>1420.04</v>
+        <v>618.32000000000005</v>
       </c>
       <c r="G56" s="14">
-        <v>23.895791583166332</v>
+        <v>6.7686424474187383</v>
       </c>
       <c r="H56" s="30">
-        <v>499</v>
+        <v>767.06666666666672</v>
       </c>
       <c r="I56" s="15">
-        <v>315.18181818181813</v>
+        <v>-112.66666666666669</v>
       </c>
       <c r="J56" s="32">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="K56" s="13">
-        <v>804.34</v>
+        <v>1024.42</v>
       </c>
       <c r="L56" s="14">
-        <v>15.177528089887641</v>
+        <v>32.22527472527473</v>
       </c>
       <c r="M56" s="30">
-        <v>445</v>
+        <v>266.93333333333334</v>
       </c>
       <c r="N56" s="15">
-        <v>104.72727272727275</v>
+        <v>269.66666666666669</v>
       </c>
       <c r="O56" s="32">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P56" s="17">
-        <v>2.62</v>
+        <v>49.78</v>
       </c>
       <c r="Q56" s="14">
-        <v>0.73333333333333339</v>
+        <v>6.7857142857142865</v>
       </c>
       <c r="R56" s="16">
-        <v>30</v>
+        <v>61.599999999999994</v>
       </c>
       <c r="S56" s="15">
-        <v>-26.27272727272727</v>
+        <v>-37</v>
       </c>
       <c r="T56" s="18">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="U56" s="17">
-        <v>193.88</v>
+        <v>241.04000000000002</v>
       </c>
       <c r="V56" s="14">
-        <v>8.6595744680851077</v>
+        <v>12.432432432432432</v>
       </c>
       <c r="W56" s="16">
-        <v>188</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="X56" s="15">
-        <v>-54.181818181818187</v>
+        <v>-19</v>
       </c>
       <c r="Y56" s="18">
         <v>50</v>
@@ -7177,19 +7179,19 @@
         <v>131</v>
       </c>
       <c r="AA56" s="14">
-        <v>26.92307692307692</v>
+        <v>24.193548387096772</v>
       </c>
       <c r="AB56" s="16">
-        <v>40.857142857142861</v>
+        <v>45.466666666666669</v>
       </c>
       <c r="AC56" s="15">
-        <v>22.142857142857139</v>
+        <v>18.999999999999996</v>
       </c>
       <c r="AD56" s="19">
-        <v>974</v>
+        <v>788</v>
       </c>
       <c r="AE56" s="20">
-        <v>2551.88</v>
+        <v>2064.56</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7224,64 +7226,64 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="F57" s="14">
-        <v>1194.72</v>
+        <v>0</v>
       </c>
       <c r="G57" s="14">
-        <v>11.036303630363037</v>
+        <v>0</v>
       </c>
       <c r="H57" s="30">
-        <v>909</v>
+        <v>1532.6666666666667</v>
       </c>
       <c r="I57" s="15">
-        <v>42.818181818181813</v>
+        <v>-696.66666666666674</v>
       </c>
       <c r="J57" s="32">
-        <v>398</v>
+        <v>322</v>
       </c>
       <c r="K57" s="13">
-        <v>1042.76</v>
+        <v>843.64</v>
       </c>
       <c r="L57" s="14">
-        <v>10.18139534883721</v>
+        <v>11.5</v>
       </c>
       <c r="M57" s="30">
-        <v>859.99999999999989</v>
+        <v>616</v>
       </c>
       <c r="N57" s="15">
-        <v>7.0909090909091219</v>
+        <v>42</v>
       </c>
       <c r="O57" s="32">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="P57" s="17">
-        <v>34.06</v>
+        <v>96.94</v>
       </c>
       <c r="Q57" s="14">
-        <v>4.1449275362318838</v>
+        <v>6.8518518518518512</v>
       </c>
       <c r="R57" s="16">
-        <v>69</v>
+        <v>118.80000000000001</v>
       </c>
       <c r="S57" s="15">
-        <v>-49.727272727272727</v>
+        <v>-71</v>
       </c>
       <c r="T57" s="18">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="U57" s="17">
-        <v>133.62</v>
+        <v>0</v>
       </c>
       <c r="V57" s="14">
-        <v>3.6310679611650487</v>
+        <v>0</v>
       </c>
       <c r="W57" s="16">
-        <v>309</v>
+        <v>486.93333333333334</v>
       </c>
       <c r="X57" s="15">
-        <v>-159.68181818181819</v>
+        <v>-332</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7290,19 +7292,19 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>26.25</v>
+        <v>28.125</v>
       </c>
       <c r="AB57" s="16">
-        <v>50.285714285714285</v>
+        <v>46.93333333333333</v>
       </c>
       <c r="AC57" s="15">
-        <v>25.714285714285715</v>
+        <v>28</v>
       </c>
       <c r="AD57" s="19">
-        <v>978</v>
+        <v>419</v>
       </c>
       <c r="AE57" s="20">
-        <v>2562.36</v>
+        <v>1097.78</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7337,64 +7339,64 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F58" s="14">
-        <v>398.24</v>
+        <v>395.62</v>
       </c>
       <c r="G58" s="14">
-        <v>7.9241706161137433</v>
+        <v>6.0561497326203204</v>
       </c>
       <c r="H58" s="30">
-        <v>422</v>
+        <v>548.5333333333333</v>
       </c>
       <c r="I58" s="15">
-        <v>-39.818181818181841</v>
+        <v>-98.333333333333343</v>
       </c>
       <c r="J58" s="32">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="K58" s="13">
-        <v>471.6</v>
+        <v>330.12</v>
       </c>
       <c r="L58" s="14">
-        <v>9.7297297297297298</v>
+        <v>12.945205479452056</v>
       </c>
       <c r="M58" s="30">
-        <v>407</v>
+        <v>214.13333333333333</v>
       </c>
       <c r="N58" s="15">
-        <v>-5</v>
+        <v>28.666666666666671</v>
       </c>
       <c r="O58" s="32">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="P58" s="17">
-        <v>81.22</v>
+        <v>112.66000000000001</v>
       </c>
       <c r="Q58" s="14">
-        <v>15.155555555555555</v>
+        <v>46.071428571428562</v>
       </c>
       <c r="R58" s="16">
-        <v>45</v>
+        <v>20.533333333333335</v>
       </c>
       <c r="S58" s="15">
-        <v>-9.9090909090909065</v>
+        <v>24.333333333333332</v>
       </c>
       <c r="T58" s="18">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="U58" s="17">
-        <v>10.48</v>
+        <v>136.24</v>
       </c>
       <c r="V58" s="14">
-        <v>0.79279279279279269</v>
+        <v>8.387096774193548</v>
       </c>
       <c r="W58" s="16">
-        <v>111</v>
+        <v>136.4</v>
       </c>
       <c r="X58" s="15">
-        <v>-71.681818181818187</v>
+        <v>-41</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7403,19 +7405,19 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>21.777777777777779</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="AB58" s="16">
-        <v>42.428571428571431</v>
+        <v>39.6</v>
       </c>
       <c r="AC58" s="15">
-        <v>13.071428571428569</v>
+        <v>15</v>
       </c>
       <c r="AD58" s="19">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AE58" s="20">
-        <v>1071.5800000000002</v>
+        <v>1084.68</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7453,64 +7455,64 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F59" s="14">
-        <v>303.92</v>
+        <v>296.06</v>
       </c>
       <c r="G59" s="14">
-        <v>5.0137524557956779</v>
+        <v>3.2785299806576402</v>
       </c>
       <c r="H59" s="30">
-        <v>509</v>
+        <v>758.26666666666665</v>
       </c>
       <c r="I59" s="15">
-        <v>-115.36363636363637</v>
+        <v>-231.66666666666669</v>
       </c>
       <c r="J59" s="32">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="K59" s="13">
-        <v>222.70000000000002</v>
+        <v>848.88</v>
       </c>
       <c r="L59" s="14">
-        <v>4.6287128712871288</v>
+        <v>37.384615384615387</v>
       </c>
       <c r="M59" s="30">
-        <v>404</v>
+        <v>190.66666666666666</v>
       </c>
       <c r="N59" s="15">
-        <v>-98.636363636363626</v>
+        <v>237.33333333333334</v>
       </c>
       <c r="O59" s="32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P59" s="17">
-        <v>0</v>
+        <v>62.88</v>
       </c>
       <c r="Q59" s="14">
-        <v>0</v>
+        <v>12.413793103448276</v>
       </c>
       <c r="R59" s="16">
-        <v>26</v>
+        <v>42.533333333333331</v>
       </c>
       <c r="S59" s="15">
-        <v>-23.636363636363637</v>
+        <v>-14.666666666666664</v>
       </c>
       <c r="T59" s="18">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="U59" s="17">
-        <v>196.5</v>
+        <v>117.9</v>
       </c>
       <c r="V59" s="14">
-        <v>8.4615384615384599</v>
+        <v>7.03125</v>
       </c>
       <c r="W59" s="16">
-        <v>195.00000000000003</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="X59" s="15">
-        <v>-57.954545454545467</v>
+        <v>-51</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7519,19 +7521,19 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>49.466666666666669</v>
+        <v>53</v>
       </c>
       <c r="AB59" s="16">
-        <v>23.571428571428569</v>
+        <v>22</v>
       </c>
       <c r="AC59" s="15">
-        <v>36.928571428571431</v>
+        <v>38</v>
       </c>
       <c r="AD59" s="19">
-        <v>329</v>
+        <v>559</v>
       </c>
       <c r="AE59" s="20">
-        <v>861.98</v>
+        <v>1464.5800000000002</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7605,10 +7607,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7638,17 +7640,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>168508.88999999996</v>
+        <v>129154.76999999999</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>42.535271870104289</v>
+        <v>28.589891067572839</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7686,11 +7688,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>159086.01000000004</v>
+        <v>228277.81</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>40.156734081389608</v>
+        <v>50.531913928104174</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7728,11 +7730,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>10226.289999999997</v>
+        <v>23911.099999999995</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>2.581335770311755</v>
+        <v>5.2929964902251845</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7770,11 +7772,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>45443.56</v>
+        <v>58250.549999999988</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>11.470932954014456</v>
+        <v>12.894427972936695</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7812,11 +7814,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>12765.170000000002</v>
+        <v>12155.550000000003</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>3.2222037449662118</v>
+        <v>2.6907705411610827</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7848,19 +7850,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>396162.71999999986</v>
-      </c>
-      <c r="E67" s="66">
+        <v>451749.78000000009</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7960,17 +7962,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>124401</v>
+        <v>96974</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>43.505067390346426</v>
+        <v>29.247798286886233</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8007,11 +8009,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>113397</v>
+        <v>166288</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>39.65678834465249</v>
+        <v>50.153215104355169</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8049,11 +8051,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>8011</v>
+        <v>18081</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>2.8015779203066313</v>
+        <v>5.4533116178067322</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8091,11 +8093,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>31625</v>
+        <v>42220</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>11.059780517999902</v>
+        <v>12.733743515502473</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8133,11 +8135,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>8512</v>
+        <v>7997</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>2.9767858266945506</v>
+        <v>2.4119314754493906</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8169,19 +8171,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>285946</v>
-      </c>
-      <c r="E75" s="66">
+        <v>331560</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8728,6 +8730,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8736,17 +8749,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7C0934-F254-4434-B6F0-5D5C5A424620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37916A4-34E4-4B13-AC73-B26C6553CA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -1182,6 +1182,7 @@
       <sheetName val="INVENTARIO NACIONAL 18-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1322,6 +1323,7 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2249,82 +2251,82 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>1541</v>
+        <v>2636</v>
       </c>
       <c r="F13" s="14">
-        <v>2095.7600000000002</v>
+        <v>3584.96</v>
       </c>
       <c r="G13" s="14">
-        <v>1.9233649525711431</v>
+        <v>3.2921707907267193</v>
       </c>
       <c r="H13" s="30">
-        <v>17626.400000000001</v>
+        <v>17615.125</v>
       </c>
       <c r="I13" s="15">
-        <v>-6471</v>
+        <v>-5370.875</v>
       </c>
       <c r="J13" s="16">
-        <v>3754</v>
+        <v>3237</v>
       </c>
       <c r="K13" s="13">
-        <v>5105.4400000000005</v>
+        <v>4402.3200000000006</v>
       </c>
       <c r="L13" s="14">
-        <v>14.449576597382601</v>
+        <v>12.152041295166589</v>
       </c>
       <c r="M13" s="30">
-        <v>5715.6</v>
+        <v>5860.25</v>
       </c>
       <c r="N13" s="15">
-        <v>1156</v>
+        <v>573.25</v>
       </c>
       <c r="O13" s="16">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="P13" s="17">
-        <v>882.6400000000001</v>
+        <v>866.32</v>
       </c>
       <c r="Q13" s="14">
-        <v>13.335616438356167</v>
+        <v>13.571238348868176</v>
       </c>
       <c r="R13" s="16">
-        <v>1070.6666666666665</v>
+        <v>1032.625</v>
       </c>
       <c r="S13" s="15">
-        <v>-324.33333333333314</v>
+        <v>-301.75</v>
       </c>
       <c r="T13" s="18">
-        <v>689</v>
+        <v>656</v>
       </c>
       <c r="U13" s="17">
-        <v>937.04000000000008</v>
+        <v>892.16000000000008</v>
       </c>
       <c r="V13" s="14">
-        <v>14.722222222222223</v>
+        <v>14.280272108843537</v>
       </c>
       <c r="W13" s="16">
-        <v>1029.5999999999999</v>
+        <v>1010.625</v>
       </c>
       <c r="X13" s="15">
-        <v>-13</v>
+        <v>-33.0625</v>
       </c>
       <c r="Y13" s="18">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="Z13" s="17">
-        <v>164.56</v>
+        <v>146.88000000000002</v>
       </c>
       <c r="AA13" s="14">
-        <v>4.0066225165562912</v>
+        <v>3.676595744680851</v>
       </c>
       <c r="AB13" s="16">
-        <v>664.4</v>
+        <v>646.25</v>
       </c>
       <c r="AC13" s="15">
-        <v>-332</v>
+        <v>-479.5</v>
       </c>
       <c r="AD13" s="19">
-        <v>6754</v>
+        <v>7274</v>
       </c>
       <c r="AE13" s="20">
         <v>9185.44</v>
@@ -2372,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>683.4666666666667</v>
+        <v>640.75</v>
       </c>
       <c r="I14" s="15">
-        <v>-310.66666666666669</v>
+        <v>-291.25</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2387,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>365.20000000000005</v>
+        <v>342.375</v>
       </c>
       <c r="N14" s="15">
-        <v>-166</v>
+        <v>-155.625</v>
       </c>
       <c r="O14" s="16">
         <v>108</v>
@@ -2399,13 +2401,13 @@
         <v>171.72</v>
       </c>
       <c r="Q14" s="14">
-        <v>21.6</v>
+        <v>23.04</v>
       </c>
       <c r="R14" s="16">
-        <v>110</v>
+        <v>103.125</v>
       </c>
       <c r="S14" s="15">
-        <v>8</v>
+        <v>14.25</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2414,13 +2416,13 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>3.8888888888888888</v>
+        <v>4.1481481481481479</v>
       </c>
       <c r="W14" s="16">
-        <v>39.6</v>
+        <v>37.125</v>
       </c>
       <c r="X14" s="15">
-        <v>-20</v>
+        <v>-18.3125</v>
       </c>
       <c r="Y14" s="18">
         <v>31</v>
@@ -2429,13 +2431,13 @@
         <v>49.29</v>
       </c>
       <c r="AA14" s="14">
-        <v>7.045454545454545</v>
+        <v>7.5151515151515156</v>
       </c>
       <c r="AB14" s="16">
-        <v>96.800000000000011</v>
+        <v>90.75</v>
       </c>
       <c r="AC14" s="15">
-        <v>-35</v>
+        <v>-51.5</v>
       </c>
       <c r="AD14" s="19">
         <v>146</v>
@@ -2477,34 +2479,34 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1226</v>
+        <v>2285</v>
       </c>
       <c r="F15" s="14">
-        <v>2488.7799999999997</v>
+        <v>4638.5499999999993</v>
       </c>
       <c r="G15" s="14">
-        <v>3.51894374282434</v>
+        <v>6.6739686016794453</v>
       </c>
       <c r="H15" s="30">
-        <v>7664.7999999999993</v>
+        <v>7532.25</v>
       </c>
       <c r="I15" s="15">
-        <v>-2258</v>
+        <v>-1138.75</v>
       </c>
       <c r="J15" s="16">
-        <v>2219</v>
+        <v>1243</v>
       </c>
       <c r="K15" s="13">
-        <v>4504.57</v>
+        <v>2523.29</v>
       </c>
       <c r="L15" s="14">
-        <v>21.013257575757578</v>
+        <v>11.223476297968396</v>
       </c>
       <c r="M15" s="30">
-        <v>2323.1999999999998</v>
+        <v>2436.5</v>
       </c>
       <c r="N15" s="15">
-        <v>1163</v>
+        <v>135.5</v>
       </c>
       <c r="O15" s="16">
         <v>246</v>
@@ -2513,46 +2515,46 @@
         <v>499.37999999999994</v>
       </c>
       <c r="Q15" s="14">
-        <v>20.5</v>
+        <v>21.866666666666667</v>
       </c>
       <c r="R15" s="16">
-        <v>264</v>
+        <v>247.5</v>
       </c>
       <c r="S15" s="15">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T15" s="18">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="U15" s="17">
-        <v>408.03</v>
+        <v>373.52</v>
       </c>
       <c r="V15" s="14">
-        <v>14.425837320574161</v>
+        <v>13.026548672566372</v>
       </c>
       <c r="W15" s="16">
-        <v>306.53333333333336</v>
+        <v>310.75</v>
       </c>
       <c r="X15" s="15">
-        <v>-8.0000000000000284</v>
+        <v>-27.875</v>
       </c>
       <c r="Y15" s="18">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Z15" s="17">
-        <v>267.95999999999998</v>
+        <v>251.71999999999997</v>
       </c>
       <c r="AA15" s="14">
-        <v>14.142857142857142</v>
+        <v>13.58904109589041</v>
       </c>
       <c r="AB15" s="16">
-        <v>205.33333333333334</v>
+        <v>200.75</v>
       </c>
       <c r="AC15" s="15">
-        <v>-8</v>
+        <v>-58.5</v>
       </c>
       <c r="AD15" s="19">
-        <v>4024</v>
+        <v>4082</v>
       </c>
       <c r="AE15" s="20">
         <v>8168.7199999999993</v>
@@ -2590,34 +2592,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="F16" s="14">
-        <v>0</v>
+        <v>989.14</v>
       </c>
       <c r="G16" s="14">
-        <v>0</v>
+        <v>3.7663230240549828</v>
       </c>
       <c r="H16" s="30">
-        <v>1579.6</v>
+        <v>1600.5</v>
       </c>
       <c r="I16" s="15">
-        <v>-718</v>
+        <v>-453.5</v>
       </c>
       <c r="J16" s="16">
-        <v>520</v>
+        <v>174</v>
       </c>
       <c r="K16" s="13">
-        <v>1877.2</v>
+        <v>628.14</v>
       </c>
       <c r="L16" s="14">
-        <v>20.207253886010363</v>
+        <v>6.3561643835616435</v>
       </c>
       <c r="M16" s="30">
-        <v>566.13333333333333</v>
+        <v>602.25</v>
       </c>
       <c r="N16" s="15">
-        <v>262.66666666666663</v>
+        <v>-99.75</v>
       </c>
       <c r="O16" s="16">
         <v>54</v>
@@ -2626,13 +2628,13 @@
         <v>194.94</v>
       </c>
       <c r="Q16" s="14">
-        <v>23.823529411764707</v>
+        <v>25.411764705882351</v>
       </c>
       <c r="R16" s="16">
-        <v>49.866666666666667</v>
+        <v>46.75</v>
       </c>
       <c r="S16" s="15">
-        <v>8.6666666666666714</v>
+        <v>11.5</v>
       </c>
       <c r="T16" s="18">
         <v>50</v>
@@ -2641,13 +2643,13 @@
         <v>180.5</v>
       </c>
       <c r="V16" s="14">
-        <v>53.571428571428562</v>
+        <v>57.142857142857146</v>
       </c>
       <c r="W16" s="16">
-        <v>20.533333333333335</v>
+        <v>19.25</v>
       </c>
       <c r="X16" s="15">
-        <v>36</v>
+        <v>36.875</v>
       </c>
       <c r="Y16" s="18">
         <v>25</v>
@@ -2656,16 +2658,16 @@
         <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>6.5789473684210531</v>
+        <v>7.0175438596491224</v>
       </c>
       <c r="AB16" s="16">
-        <v>83.6</v>
+        <v>78.375</v>
       </c>
       <c r="AC16" s="15">
-        <v>-32</v>
+        <v>-46.25</v>
       </c>
       <c r="AD16" s="19">
-        <v>649</v>
+        <v>577</v>
       </c>
       <c r="AE16" s="20">
         <v>2342.89</v>
@@ -2703,34 +2705,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>316.08</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>3.7647058823529411</v>
       </c>
       <c r="H17" s="30">
-        <v>214.13333333333333</v>
+        <v>210.375</v>
       </c>
       <c r="I17" s="15">
-        <v>-97.333333333333329</v>
+        <v>-59.625</v>
       </c>
       <c r="J17" s="16">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="K17" s="13">
-        <v>746.3</v>
+        <v>386.32</v>
       </c>
       <c r="L17" s="14">
-        <v>39.84375</v>
+        <v>20.114285714285714</v>
       </c>
       <c r="M17" s="30">
-        <v>46.93333333333333</v>
+        <v>48.125</v>
       </c>
       <c r="N17" s="15">
-        <v>63.666666666666671</v>
+        <v>22.125</v>
       </c>
       <c r="O17" s="16">
         <v>10</v>
@@ -2739,13 +2741,13 @@
         <v>87.8</v>
       </c>
       <c r="Q17" s="14">
-        <v>18.75</v>
+        <v>20</v>
       </c>
       <c r="R17" s="16">
-        <v>11.733333333333333</v>
+        <v>11</v>
       </c>
       <c r="S17" s="15">
-        <v>-0.66666666666666607</v>
+        <v>0</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2763,22 +2765,22 @@
         <v>15.636363636363637</v>
       </c>
       <c r="Y17" s="18">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="17">
-        <v>96.58</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="AA17" s="14">
-        <v>27.5</v>
+        <v>14.222222222222221</v>
       </c>
       <c r="AB17" s="16">
-        <v>8.8000000000000007</v>
+        <v>12.375</v>
       </c>
       <c r="AC17" s="15">
-        <v>5</v>
+        <v>-3.25</v>
       </c>
       <c r="AD17" s="19">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AE17" s="20">
         <v>1079.9399999999998</v>
@@ -2816,82 +2818,82 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>5156</v>
+        <v>6820</v>
       </c>
       <c r="F18" s="14">
-        <v>3248.28</v>
+        <v>4296.6000000000004</v>
       </c>
       <c r="G18" s="14">
-        <v>5.9726619816202033</v>
+        <v>7.9806918744971842</v>
       </c>
       <c r="H18" s="30">
-        <v>18991.866666666665</v>
+        <v>18800.375</v>
       </c>
       <c r="I18" s="15">
-        <v>-3476.6666666666661</v>
+        <v>-1725.625</v>
       </c>
       <c r="J18" s="16">
-        <v>4460</v>
+        <v>7304</v>
       </c>
       <c r="K18" s="13">
-        <v>2809.8</v>
+        <v>4601.5200000000004</v>
       </c>
       <c r="L18" s="14">
-        <v>13.776771004942338</v>
+        <v>21.954536915273341</v>
       </c>
       <c r="M18" s="30">
-        <v>7122.1333333333332</v>
+        <v>7319.125</v>
       </c>
       <c r="N18" s="15">
-        <v>1222.6666666666665</v>
+        <v>3977.125</v>
       </c>
       <c r="O18" s="16">
-        <v>1107</v>
+        <v>1084</v>
       </c>
       <c r="P18" s="17">
-        <v>697.41</v>
+        <v>682.92</v>
       </c>
       <c r="Q18" s="14">
-        <v>18.187294633077766</v>
+        <v>18.529914529914532</v>
       </c>
       <c r="R18" s="16">
-        <v>1339.0666666666666</v>
+        <v>1287</v>
       </c>
       <c r="S18" s="15">
-        <v>-110.33333333333326</v>
+        <v>-86</v>
       </c>
       <c r="T18" s="18">
-        <v>2196</v>
+        <v>2039</v>
       </c>
       <c r="U18" s="17">
-        <v>1383.48</v>
+        <v>1284.57</v>
       </c>
       <c r="V18" s="14">
-        <v>14.705357142857142</v>
+        <v>13.587671803415244</v>
       </c>
       <c r="W18" s="16">
-        <v>3285.3333333333335</v>
+        <v>3301.375</v>
       </c>
       <c r="X18" s="15">
-        <v>-44</v>
+        <v>-211.9375</v>
       </c>
       <c r="Y18" s="18">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="Z18" s="17">
-        <v>137.34</v>
+        <v>119.07000000000001</v>
       </c>
       <c r="AA18" s="14">
-        <v>16.188118811881189</v>
+        <v>13.380530973451327</v>
       </c>
       <c r="AB18" s="16">
-        <v>296.26666666666665</v>
+        <v>310.75</v>
       </c>
       <c r="AC18" s="15">
-        <v>16</v>
+        <v>-93.5</v>
       </c>
       <c r="AD18" s="19">
-        <v>13137</v>
+        <v>17436</v>
       </c>
       <c r="AE18" s="20">
         <v>8276.31</v>
@@ -2929,82 +2931,82 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="F19" s="14">
-        <v>353.43</v>
+        <v>368.55</v>
       </c>
       <c r="G19" s="14">
-        <v>9.9940617577197148</v>
+        <v>9.473684210526315</v>
       </c>
       <c r="H19" s="30">
-        <v>1234.9333333333334</v>
+        <v>1358.5</v>
       </c>
       <c r="I19" s="15">
-        <v>-0.33333333333337123</v>
+        <v>-32.5</v>
       </c>
       <c r="J19" s="16">
-        <v>571</v>
+        <v>417</v>
       </c>
       <c r="K19" s="13">
-        <v>359.73</v>
+        <v>262.70999999999998</v>
       </c>
       <c r="L19" s="14">
-        <v>9.8448275862068968</v>
+        <v>7.3480176211453747</v>
       </c>
       <c r="M19" s="30">
-        <v>1276</v>
+        <v>1248.5</v>
       </c>
       <c r="N19" s="15">
-        <v>-9</v>
+        <v>-150.5</v>
       </c>
       <c r="O19" s="16">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P19" s="17">
-        <v>52.92</v>
+        <v>49.77</v>
       </c>
       <c r="Q19" s="14">
-        <v>17.027027027027025</v>
+        <v>16</v>
       </c>
       <c r="R19" s="16">
-        <v>108.53333333333333</v>
+        <v>108.625</v>
       </c>
       <c r="S19" s="15">
-        <v>-14.666666666666671</v>
+        <v>-19.75</v>
       </c>
       <c r="T19" s="18">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="U19" s="17">
-        <v>161.91</v>
+        <v>146.79</v>
       </c>
       <c r="V19" s="14">
-        <v>21.536312849162009</v>
+        <v>19.216494845360824</v>
       </c>
       <c r="W19" s="16">
-        <v>262.53333333333336</v>
+        <v>266.75</v>
       </c>
       <c r="X19" s="15">
-        <v>77.999999999999972</v>
+        <v>51.125</v>
       </c>
       <c r="Y19" s="18">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="Z19" s="17">
-        <v>97.02</v>
+        <v>90.09</v>
       </c>
       <c r="AA19" s="14">
-        <v>14.085365853658537</v>
+        <v>13.458823529411765</v>
       </c>
       <c r="AB19" s="16">
-        <v>240.53333333333333</v>
+        <v>233.75</v>
       </c>
       <c r="AC19" s="15">
-        <v>-10</v>
+        <v>-69.5</v>
       </c>
       <c r="AD19" s="19">
-        <v>1627</v>
+        <v>1457</v>
       </c>
       <c r="AE19" s="20">
         <v>1025.01</v>
@@ -3042,82 +3044,82 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1081</v>
+        <v>1148</v>
       </c>
       <c r="F20" s="14">
-        <v>681.03</v>
+        <v>723.24</v>
       </c>
       <c r="G20" s="14">
-        <v>8.6158342189160457</v>
+        <v>8.7550047664442321</v>
       </c>
       <c r="H20" s="30">
-        <v>2760.2666666666669</v>
+        <v>2884.75</v>
       </c>
       <c r="I20" s="15">
-        <v>-173.66666666666674</v>
+        <v>-163.25</v>
       </c>
       <c r="J20" s="16">
-        <v>1577</v>
+        <v>2672</v>
       </c>
       <c r="K20" s="13">
-        <v>993.51</v>
+        <v>1683.36</v>
       </c>
       <c r="L20" s="14">
-        <v>12.269190871369295</v>
+        <v>20.723218613669413</v>
       </c>
       <c r="M20" s="30">
-        <v>2827.7333333333331</v>
+        <v>2836.625</v>
       </c>
       <c r="N20" s="15">
-        <v>291.66666666666674</v>
+        <v>1382.625</v>
       </c>
       <c r="O20" s="16">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="P20" s="17">
-        <v>166.32</v>
+        <v>151.83000000000001</v>
       </c>
       <c r="Q20" s="14">
-        <v>29.774436090225564</v>
+        <v>24.717948717948719</v>
       </c>
       <c r="R20" s="16">
-        <v>195.06666666666666</v>
+        <v>214.5</v>
       </c>
       <c r="S20" s="15">
-        <v>86.666666666666657</v>
+        <v>46</v>
       </c>
       <c r="T20" s="18">
-        <v>757</v>
+        <v>650</v>
       </c>
       <c r="U20" s="17">
-        <v>476.91</v>
+        <v>409.5</v>
       </c>
       <c r="V20" s="14">
-        <v>46.158536585365859</v>
+        <v>31.231231231231231</v>
       </c>
       <c r="W20" s="16">
-        <v>360.79999999999995</v>
+        <v>457.875</v>
       </c>
       <c r="X20" s="15">
-        <v>511</v>
+        <v>337.8125</v>
       </c>
       <c r="Y20" s="18">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="Z20" s="17">
-        <v>142.38</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="AA20" s="14">
-        <v>16.699507389162562</v>
+        <v>15.553488372093023</v>
       </c>
       <c r="AB20" s="16">
-        <v>297.73333333333335</v>
+        <v>295.625</v>
       </c>
       <c r="AC20" s="15">
-        <v>23</v>
+        <v>-59.75</v>
       </c>
       <c r="AD20" s="19">
-        <v>3905</v>
+        <v>4920</v>
       </c>
       <c r="AE20" s="20">
         <v>2460.15</v>
@@ -3155,82 +3157,82 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>1952</v>
+        <v>2322</v>
       </c>
       <c r="F21" s="14">
-        <v>2127.6800000000003</v>
+        <v>2530.98</v>
       </c>
       <c r="G21" s="14">
-        <v>6.6606005459508646</v>
+        <v>7.6224866639310624</v>
       </c>
       <c r="H21" s="30">
-        <v>6447.4666666666662</v>
+        <v>6701.75</v>
       </c>
       <c r="I21" s="15">
-        <v>-978.66666666666652</v>
+        <v>-724.25</v>
       </c>
       <c r="J21" s="16">
-        <v>3608</v>
+        <v>5240</v>
       </c>
       <c r="K21" s="13">
-        <v>3932.7200000000003</v>
+        <v>5711.6</v>
       </c>
       <c r="L21" s="14">
-        <v>11.291466722303358</v>
+        <v>15.914958238420652</v>
       </c>
       <c r="M21" s="30">
-        <v>7029.7333333333336</v>
+        <v>7243.5</v>
       </c>
       <c r="N21" s="15">
-        <v>412.66666666666652</v>
+        <v>1947.5</v>
       </c>
       <c r="O21" s="16">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="P21" s="17">
-        <v>417.47</v>
+        <v>389.13000000000005</v>
       </c>
       <c r="Q21" s="14">
-        <v>14.255583126550867</v>
+        <v>13.070938215102975</v>
       </c>
       <c r="R21" s="16">
-        <v>591.06666666666672</v>
+        <v>600.875</v>
       </c>
       <c r="S21" s="15">
-        <v>-154.33333333333337</v>
+        <v>-189.25</v>
       </c>
       <c r="T21" s="18">
-        <v>1122</v>
+        <v>945</v>
       </c>
       <c r="U21" s="17">
-        <v>1222.98</v>
+        <v>1030.0500000000002</v>
       </c>
       <c r="V21" s="14">
-        <v>15.847457627118645</v>
+        <v>12.342857142857143</v>
       </c>
       <c r="W21" s="16">
-        <v>1557.6</v>
+        <v>1684.375</v>
       </c>
       <c r="X21" s="15">
-        <v>60</v>
+        <v>-203.4375</v>
       </c>
       <c r="Y21" s="18">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="Z21" s="17">
-        <v>279.04000000000002</v>
+        <v>241.98000000000002</v>
       </c>
       <c r="AA21" s="14">
-        <v>13.963636363636365</v>
+        <v>11.684210526315789</v>
       </c>
       <c r="AB21" s="16">
-        <v>403.33333333333331</v>
+        <v>418</v>
       </c>
       <c r="AC21" s="15">
-        <v>-19</v>
+        <v>-158</v>
       </c>
       <c r="AD21" s="19">
-        <v>7321</v>
+        <v>9086</v>
       </c>
       <c r="AE21" s="20">
         <v>7979.89</v>
@@ -3268,34 +3270,34 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1315</v>
+        <v>1704</v>
       </c>
       <c r="F22" s="14">
-        <v>1433.3500000000001</v>
+        <v>1857.3600000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>7.7504911591355601</v>
+        <v>9.6305192511480051</v>
       </c>
       <c r="H22" s="30">
-        <v>3732.6666666666665</v>
+        <v>3892.625</v>
       </c>
       <c r="I22" s="15">
-        <v>-381.66666666666652</v>
+        <v>-65.375</v>
       </c>
       <c r="J22" s="16">
-        <v>1996</v>
+        <v>3682</v>
       </c>
       <c r="K22" s="13">
-        <v>2175.6400000000003</v>
+        <v>4013.38</v>
       </c>
       <c r="L22" s="14">
-        <v>14.135977337110482</v>
+        <v>24.639063153492263</v>
       </c>
       <c r="M22" s="30">
-        <v>3106.3999999999996</v>
+        <v>3287.625</v>
       </c>
       <c r="N22" s="15">
-        <v>584</v>
+        <v>2187.625</v>
       </c>
       <c r="O22" s="16">
         <v>139</v>
@@ -3304,46 +3306,46 @@
         <v>151.51000000000002</v>
       </c>
       <c r="Q22" s="14">
-        <v>26.0625</v>
+        <v>24.173913043478262</v>
       </c>
       <c r="R22" s="16">
-        <v>117.33333333333333</v>
+        <v>126.5</v>
       </c>
       <c r="S22" s="15">
-        <v>32.333333333333343</v>
+        <v>24</v>
       </c>
       <c r="T22" s="18">
-        <v>452</v>
+        <v>382</v>
       </c>
       <c r="U22" s="17">
-        <v>492.68000000000006</v>
+        <v>416.38000000000005</v>
       </c>
       <c r="V22" s="14">
-        <v>20.178571428571431</v>
+        <v>16.342245989304814</v>
       </c>
       <c r="W22" s="16">
-        <v>492.79999999999995</v>
+        <v>514.25</v>
       </c>
       <c r="X22" s="15">
+        <v>31.375</v>
+      </c>
+      <c r="Y22" s="18">
         <v>116</v>
       </c>
-      <c r="Y22" s="18">
-        <v>138</v>
-      </c>
       <c r="Z22" s="17">
-        <v>150.42000000000002</v>
+        <v>126.44000000000001</v>
       </c>
       <c r="AA22" s="14">
-        <v>31.36363636363636</v>
+        <v>22.095238095238095</v>
       </c>
       <c r="AB22" s="16">
-        <v>96.800000000000011</v>
+        <v>115.5</v>
       </c>
       <c r="AC22" s="15">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="AD22" s="19">
-        <v>4040</v>
+        <v>6023</v>
       </c>
       <c r="AE22" s="20">
         <v>4403.6000000000004</v>
@@ -3381,82 +3383,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>16580</v>
+        <v>20949</v>
       </c>
       <c r="F23" s="14">
-        <v>19232.8</v>
+        <v>24300.839999999997</v>
       </c>
       <c r="G23" s="14">
-        <v>9.9939722724532842</v>
+        <v>12.752882091085493</v>
       </c>
       <c r="H23" s="30">
-        <v>36498</v>
+        <v>36139.125</v>
       </c>
       <c r="I23" s="15">
-        <v>-8305</v>
+        <v>-3691.3125</v>
       </c>
       <c r="J23" s="16">
-        <v>22442</v>
+        <v>23090</v>
       </c>
       <c r="K23" s="13">
-        <v>26032.719999999998</v>
+        <v>26784.399999999998</v>
       </c>
       <c r="L23" s="14">
-        <v>24.345845085701889</v>
+        <v>24.390308311876939</v>
       </c>
       <c r="M23" s="30">
-        <v>20279.599999999999</v>
+        <v>20827.125</v>
       </c>
       <c r="N23" s="15">
-        <v>13224</v>
+        <v>13623.125</v>
       </c>
       <c r="O23" s="16">
-        <v>2226</v>
+        <v>2110</v>
       </c>
       <c r="P23" s="17">
-        <v>2582.16</v>
+        <v>2447.6</v>
       </c>
       <c r="Q23" s="14">
-        <v>14.807095343680709</v>
+        <v>14.090150250417363</v>
       </c>
       <c r="R23" s="16">
-        <v>3307.3333333333335</v>
+        <v>3294.5</v>
       </c>
       <c r="S23" s="15">
-        <v>-780.66666666666697</v>
+        <v>-885</v>
       </c>
       <c r="T23" s="18">
-        <v>7360</v>
+        <v>6887</v>
       </c>
       <c r="U23" s="17">
-        <v>8537.5999999999985</v>
+        <v>7988.9199999999992</v>
       </c>
       <c r="V23" s="14">
-        <v>13.51781559936329</v>
+        <v>12.799628295969335</v>
       </c>
       <c r="W23" s="16">
-        <v>11978.266666666666</v>
+        <v>11837.375</v>
       </c>
       <c r="X23" s="15">
-        <v>-807</v>
+        <v>-1183.9375</v>
       </c>
       <c r="Y23" s="18">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="Z23" s="17">
-        <v>111.35999999999999</v>
+        <v>15.079999999999998</v>
       </c>
       <c r="AA23" s="14">
-        <v>1.7454545454545454</v>
+        <v>0.23059866962305986</v>
       </c>
       <c r="AB23" s="16">
-        <v>1210</v>
+        <v>1240.25</v>
       </c>
       <c r="AC23" s="15">
-        <v>-729</v>
+        <v>-1114.5</v>
       </c>
       <c r="AD23" s="19">
-        <v>48704</v>
+        <v>53049</v>
       </c>
       <c r="AE23" s="20">
         <v>56496.639999999999</v>
@@ -3494,82 +3496,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>9658</v>
+        <v>10278</v>
       </c>
       <c r="F24" s="14">
-        <v>11203.279999999999</v>
+        <v>11922.48</v>
       </c>
       <c r="G24" s="14">
-        <v>8.8855495583905793</v>
+        <v>9.3681212259314108</v>
       </c>
       <c r="H24" s="30">
-        <v>23912.533333333333</v>
+        <v>24136.75</v>
       </c>
       <c r="I24" s="15">
-        <v>-1211.3333333333339</v>
+        <v>-693.25</v>
       </c>
       <c r="J24" s="16">
-        <v>8473</v>
+        <v>8070</v>
       </c>
       <c r="K24" s="13">
-        <v>9828.6799999999985</v>
+        <v>9361.1999999999989</v>
       </c>
       <c r="L24" s="14">
-        <v>14.975256274301875</v>
+        <v>13.961937716262975</v>
       </c>
       <c r="M24" s="30">
-        <v>12447.599999999999</v>
+        <v>12716</v>
       </c>
       <c r="N24" s="15">
-        <v>2815</v>
+        <v>2290</v>
       </c>
       <c r="O24" s="16">
-        <v>1327</v>
+        <v>1292</v>
       </c>
       <c r="P24" s="17">
-        <v>1539.32</v>
+        <v>1498.7199999999998</v>
       </c>
       <c r="Q24" s="14">
-        <v>15.229533282325937</v>
+        <v>14.925631768953069</v>
       </c>
       <c r="R24" s="16">
-        <v>1916.9333333333334</v>
+        <v>1904.375</v>
       </c>
       <c r="S24" s="15">
-        <v>-415.66666666666674</v>
+        <v>-439.25</v>
       </c>
       <c r="T24" s="18">
-        <v>4150</v>
+        <v>3881</v>
       </c>
       <c r="U24" s="17">
-        <v>4814</v>
+        <v>4501.96</v>
       </c>
       <c r="V24" s="14">
-        <v>14.453215695379615</v>
+        <v>13.56993006993007</v>
       </c>
       <c r="W24" s="16">
-        <v>6316.9333333333334</v>
+        <v>6292</v>
       </c>
       <c r="X24" s="15">
-        <v>-157</v>
+        <v>-409</v>
       </c>
       <c r="Y24" s="18">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="Z24" s="17">
-        <v>475.59999999999997</v>
+        <v>415.28</v>
       </c>
       <c r="AA24" s="14">
-        <v>11.647727272727272</v>
+        <v>9.6430976430976436</v>
       </c>
       <c r="AB24" s="16">
-        <v>774.40000000000009</v>
+        <v>816.75</v>
       </c>
       <c r="AC24" s="15">
-        <v>-118</v>
+        <v>-384.5</v>
       </c>
       <c r="AD24" s="19">
-        <v>24018</v>
+        <v>23879</v>
       </c>
       <c r="AE24" s="20">
         <v>27860.879999999997</v>
@@ -3607,82 +3609,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>6546</v>
+        <v>5823</v>
       </c>
       <c r="F25" s="14">
-        <v>7593.36</v>
+        <v>6754.6799999999994</v>
       </c>
       <c r="G25" s="14">
-        <v>6.1063432835820892</v>
+        <v>5.4091964700418025</v>
       </c>
       <c r="H25" s="30">
-        <v>23584</v>
+        <v>23683</v>
       </c>
       <c r="I25" s="15">
-        <v>-4174</v>
+        <v>-4942</v>
       </c>
       <c r="J25" s="16">
-        <v>18897</v>
+        <v>18060</v>
       </c>
       <c r="K25" s="13">
-        <v>21920.519999999997</v>
+        <v>20949.599999999999</v>
       </c>
       <c r="L25" s="14">
-        <v>31.169452386188695</v>
+        <v>29.076272891929968</v>
       </c>
       <c r="M25" s="30">
-        <v>13337.866666666667</v>
+        <v>13664.75</v>
       </c>
       <c r="N25" s="15">
-        <v>12834.333333333334</v>
+        <v>11848.75</v>
       </c>
       <c r="O25" s="16">
-        <v>1599</v>
+        <v>1537</v>
       </c>
       <c r="P25" s="17">
-        <v>1854.84</v>
+        <v>1782.9199999999998</v>
       </c>
       <c r="Q25" s="14">
-        <v>14.823856613102597</v>
+        <v>14.465882352941177</v>
       </c>
       <c r="R25" s="16">
-        <v>2373.0666666666666</v>
+        <v>2337.5</v>
       </c>
       <c r="S25" s="15">
-        <v>-558.33333333333303</v>
+        <v>-588</v>
       </c>
       <c r="T25" s="18">
-        <v>4058</v>
+        <v>3739</v>
       </c>
       <c r="U25" s="17">
-        <v>4707.28</v>
+        <v>4337.24</v>
       </c>
       <c r="V25" s="14">
-        <v>13.97703788748565</v>
+        <v>12.802054354804195</v>
       </c>
       <c r="W25" s="16">
-        <v>6387.333333333333</v>
+        <v>6425.375</v>
       </c>
       <c r="X25" s="15">
-        <v>-297</v>
+        <v>-641.9375</v>
       </c>
       <c r="Y25" s="18">
-        <v>593</v>
+        <v>532</v>
       </c>
       <c r="Z25" s="17">
-        <v>687.88</v>
+        <v>617.12</v>
       </c>
       <c r="AA25" s="14">
-        <v>23.469656992084435</v>
+        <v>18.915555555555557</v>
       </c>
       <c r="AB25" s="16">
-        <v>555.86666666666667</v>
+        <v>618.75</v>
       </c>
       <c r="AC25" s="15">
-        <v>214</v>
+        <v>-30.5</v>
       </c>
       <c r="AD25" s="19">
-        <v>31693</v>
+        <v>29691</v>
       </c>
       <c r="AE25" s="20">
         <v>36763.879999999997</v>
@@ -3720,82 +3722,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>12557</v>
+        <v>19042</v>
       </c>
       <c r="F26" s="14">
-        <v>14566.119999999999</v>
+        <v>22088.719999999998</v>
       </c>
       <c r="G26" s="14">
-        <v>9.0364133563615443</v>
+        <v>13.756806790987493</v>
       </c>
       <c r="H26" s="30">
-        <v>30571.199999999997</v>
+        <v>30452.125</v>
       </c>
       <c r="I26" s="15">
-        <v>-8287</v>
+        <v>-1720.8125</v>
       </c>
       <c r="J26" s="16">
-        <v>21797</v>
+        <v>18459</v>
       </c>
       <c r="K26" s="13">
-        <v>25284.519999999997</v>
+        <v>21412.44</v>
       </c>
       <c r="L26" s="14">
-        <v>30.809932152280435</v>
+        <v>25.588632819268756</v>
       </c>
       <c r="M26" s="30">
-        <v>15564.266666666666</v>
+        <v>15870.25</v>
       </c>
       <c r="N26" s="15">
-        <v>14722.333333333332</v>
+        <v>11245.25</v>
       </c>
       <c r="O26" s="16">
-        <v>1423</v>
+        <v>1361</v>
       </c>
       <c r="P26" s="17">
-        <v>1650.6799999999998</v>
+        <v>1578.76</v>
       </c>
       <c r="Q26" s="14">
-        <v>17.227602905569007</v>
+        <v>16.50947687642153</v>
       </c>
       <c r="R26" s="16">
-        <v>1817.1999999999998</v>
+        <v>1813.625</v>
       </c>
       <c r="S26" s="15">
-        <v>-229</v>
+        <v>-287.75</v>
       </c>
       <c r="T26" s="18">
-        <v>4598</v>
+        <v>4254</v>
       </c>
       <c r="U26" s="17">
-        <v>5333.6799999999994</v>
+        <v>4934.6399999999994</v>
       </c>
       <c r="V26" s="14">
-        <v>12.793544796883696</v>
+        <v>11.876461350549642</v>
       </c>
       <c r="W26" s="16">
-        <v>7906.7999999999993</v>
+        <v>7880.125</v>
       </c>
       <c r="X26" s="15">
-        <v>-793</v>
+        <v>-1118.8125</v>
       </c>
       <c r="Y26" s="18">
-        <v>536</v>
+        <v>447</v>
       </c>
       <c r="Z26" s="17">
-        <v>621.76</v>
+        <v>518.52</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.767123287671234</v>
+        <v>10.471449487554905</v>
       </c>
       <c r="AB26" s="16">
-        <v>856.5333333333333</v>
+        <v>939.125</v>
       </c>
       <c r="AC26" s="15">
-        <v>-48</v>
+        <v>-406.75</v>
       </c>
       <c r="AD26" s="19">
-        <v>40911</v>
+        <v>43563</v>
       </c>
       <c r="AE26" s="20">
         <v>47456.759999999995</v>
@@ -3833,82 +3835,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1142</v>
+        <v>893</v>
       </c>
       <c r="F27" s="14">
-        <v>1324.7199999999998</v>
+        <v>1035.8799999999999</v>
       </c>
       <c r="G27" s="14">
-        <v>3.4260000000000002</v>
+        <v>2.5459729151817534</v>
       </c>
       <c r="H27" s="30">
-        <v>7333.333333333333</v>
+        <v>7716.5</v>
       </c>
       <c r="I27" s="15">
-        <v>-2191.333333333333</v>
+        <v>-2614.5</v>
       </c>
       <c r="J27" s="16">
-        <v>6535</v>
+        <v>6413</v>
       </c>
       <c r="K27" s="13">
-        <v>7580.5999999999995</v>
+        <v>7439.08</v>
       </c>
       <c r="L27" s="14">
-        <v>34.060111188325223</v>
+        <v>32.307304785894203</v>
       </c>
       <c r="M27" s="30">
-        <v>4221.0666666666666</v>
+        <v>4367</v>
       </c>
       <c r="N27" s="15">
-        <v>4616.333333333333</v>
+        <v>4428</v>
       </c>
       <c r="O27" s="16">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="P27" s="17">
-        <v>332.91999999999996</v>
+        <v>306.23999999999995</v>
       </c>
       <c r="Q27" s="14">
-        <v>10.274463007159904</v>
+        <v>9.0838709677419356</v>
       </c>
       <c r="R27" s="16">
-        <v>614.5333333333333</v>
+        <v>639.375</v>
       </c>
       <c r="S27" s="15">
-        <v>-271.66666666666663</v>
+        <v>-317.25</v>
       </c>
       <c r="T27" s="18">
-        <v>1031</v>
+        <v>897</v>
       </c>
       <c r="U27" s="17">
-        <v>1195.9599999999998</v>
+        <v>1040.52</v>
       </c>
       <c r="V27" s="14">
-        <v>8.9186851211072664</v>
+        <v>7.6913183279742769</v>
       </c>
       <c r="W27" s="16">
-        <v>2543.1999999999998</v>
+        <v>2565.75</v>
       </c>
       <c r="X27" s="15">
-        <v>-703</v>
+        <v>-852.375</v>
       </c>
       <c r="Y27" s="18">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="Z27" s="17">
-        <v>501.11999999999995</v>
+        <v>463.99999999999994</v>
       </c>
       <c r="AA27" s="14">
-        <v>37.456647398843934</v>
+        <v>31.372549019607842</v>
       </c>
       <c r="AB27" s="16">
-        <v>253.73333333333332</v>
+        <v>280.5</v>
       </c>
       <c r="AC27" s="15">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="AD27" s="19">
-        <v>9427</v>
+        <v>8867</v>
       </c>
       <c r="AE27" s="20">
         <v>10935.32</v>
@@ -3946,82 +3948,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>957</v>
+        <v>1141</v>
       </c>
       <c r="F28" s="14">
-        <v>1110.1199999999999</v>
+        <v>1323.56</v>
       </c>
       <c r="G28" s="14">
-        <v>2.9403932814420322</v>
+        <v>3.3180661577608141</v>
       </c>
       <c r="H28" s="30">
-        <v>7160.2666666666664</v>
+        <v>7565.25</v>
       </c>
       <c r="I28" s="15">
-        <v>-2297.6666666666665</v>
+        <v>-2297.75</v>
       </c>
       <c r="J28" s="16">
-        <v>6469</v>
+        <v>5543</v>
       </c>
       <c r="K28" s="13">
-        <v>7504.0399999999991</v>
+        <v>6429.8799999999992</v>
       </c>
       <c r="L28" s="14">
-        <v>24.472887767969738</v>
+        <v>20.304029304029303</v>
       </c>
       <c r="M28" s="30">
-        <v>5815.333333333333</v>
+        <v>6006</v>
       </c>
       <c r="N28" s="15">
-        <v>3825.666666666667</v>
+        <v>2813</v>
       </c>
       <c r="O28" s="16">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="P28" s="17">
-        <v>389.76</v>
+        <v>354.96</v>
       </c>
       <c r="Q28" s="14">
-        <v>8.7197231833910038</v>
+        <v>7.821086261980831</v>
       </c>
       <c r="R28" s="16">
-        <v>847.73333333333335</v>
+        <v>860.75</v>
       </c>
       <c r="S28" s="15">
-        <v>-434.66666666666663</v>
+        <v>-476.5</v>
       </c>
       <c r="T28" s="18">
-        <v>689</v>
+        <v>492</v>
       </c>
       <c r="U28" s="17">
-        <v>799.2399999999999</v>
+        <v>570.71999999999991</v>
       </c>
       <c r="V28" s="14">
-        <v>5.1392342118349079</v>
+        <v>3.5994513031550071</v>
       </c>
       <c r="W28" s="16">
-        <v>2949.4666666666667</v>
+        <v>3007.125</v>
       </c>
       <c r="X28" s="15">
-        <v>-1322</v>
+        <v>-1558.3125</v>
       </c>
       <c r="Y28" s="18">
-        <v>356</v>
+        <v>309</v>
       </c>
       <c r="Z28" s="17">
-        <v>412.96</v>
+        <v>358.44</v>
       </c>
       <c r="AA28" s="14">
-        <v>21.36</v>
+        <v>16.989690721649485</v>
       </c>
       <c r="AB28" s="16">
-        <v>366.66666666666669</v>
+        <v>400.125</v>
       </c>
       <c r="AC28" s="15">
-        <v>105.99999999999997</v>
+        <v>-54.75</v>
       </c>
       <c r="AD28" s="19">
-        <v>8807</v>
+        <v>7791</v>
       </c>
       <c r="AE28" s="20">
         <v>10216.119999999999</v>
@@ -4059,82 +4061,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>965</v>
+        <v>908</v>
       </c>
       <c r="F29" s="14">
-        <v>1119.3999999999999</v>
+        <v>1053.28</v>
       </c>
       <c r="G29" s="14">
-        <v>2.7106741573033708</v>
+        <v>2.4221407135711903</v>
       </c>
       <c r="H29" s="30">
-        <v>7832</v>
+        <v>8247.25</v>
       </c>
       <c r="I29" s="15">
-        <v>-2595</v>
+        <v>-2840.75</v>
       </c>
       <c r="J29" s="16">
-        <v>923</v>
+        <v>5284</v>
       </c>
       <c r="K29" s="13">
-        <v>1070.6799999999998</v>
+        <v>6129.44</v>
       </c>
       <c r="L29" s="14">
-        <v>3.3992143383255584</v>
+        <v>19.080117354998873</v>
       </c>
       <c r="M29" s="30">
-        <v>5973.7333333333336</v>
+        <v>6092.625</v>
       </c>
       <c r="N29" s="15">
-        <v>-1792.3333333333335</v>
+        <v>2514.625</v>
       </c>
       <c r="O29" s="16">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="P29" s="17">
-        <v>279.56</v>
+        <v>242.43999999999997</v>
       </c>
       <c r="Q29" s="14">
-        <v>6.1064189189189184</v>
+        <v>5.1925465838509313</v>
       </c>
       <c r="R29" s="16">
-        <v>868.26666666666665</v>
+        <v>885.5</v>
       </c>
       <c r="S29" s="15">
-        <v>-548.33333333333337</v>
+        <v>-596</v>
       </c>
       <c r="T29" s="18">
-        <v>452</v>
+        <v>297</v>
       </c>
       <c r="U29" s="17">
-        <v>524.31999999999994</v>
+        <v>344.52</v>
       </c>
       <c r="V29" s="14">
-        <v>3.1072410632447296</v>
+        <v>2.0465116279069768</v>
       </c>
       <c r="W29" s="16">
-        <v>3200.2666666666669</v>
+        <v>3192.75</v>
       </c>
       <c r="X29" s="15">
-        <v>-1730</v>
+        <v>-1879.875</v>
       </c>
       <c r="Y29" s="18">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="Z29" s="17">
-        <v>416.44</v>
+        <v>377</v>
       </c>
       <c r="AA29" s="14">
-        <v>21.626506024096383</v>
+        <v>18.637992831541219</v>
       </c>
       <c r="AB29" s="16">
-        <v>365.20000000000005</v>
+        <v>383.625</v>
       </c>
       <c r="AC29" s="15">
-        <v>109.99999999999997</v>
+        <v>-23.75</v>
       </c>
       <c r="AD29" s="19">
-        <v>2940</v>
+        <v>7023</v>
       </c>
       <c r="AE29" s="20">
         <v>3410.3999999999996</v>
@@ -4172,82 +4174,82 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>610</v>
+        <v>502</v>
       </c>
       <c r="F30" s="14">
-        <v>2244.8000000000002</v>
+        <v>1847.3600000000001</v>
       </c>
       <c r="G30" s="14">
-        <v>6.5357142857142874</v>
+        <v>5.0452261306532664</v>
       </c>
       <c r="H30" s="30">
-        <v>2053.333333333333</v>
+        <v>2189</v>
       </c>
       <c r="I30" s="15">
-        <v>-323.33333333333314</v>
+        <v>-493</v>
       </c>
       <c r="J30" s="16">
-        <v>1117</v>
+        <v>897</v>
       </c>
       <c r="K30" s="13">
-        <v>4110.5600000000004</v>
+        <v>3300.96</v>
       </c>
       <c r="L30" s="14">
-        <v>9.3342618384401099</v>
+        <v>7.2302267002518894</v>
       </c>
       <c r="M30" s="30">
-        <v>2632.666666666667</v>
+        <v>2729.375</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.66666666666697</v>
+        <v>-343.625</v>
       </c>
       <c r="O30" s="16">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="P30" s="17">
-        <v>184</v>
+        <v>161.92000000000002</v>
       </c>
       <c r="Q30" s="14">
-        <v>8.3333333333333339</v>
+        <v>6.9702970297029703</v>
       </c>
       <c r="R30" s="16">
-        <v>132</v>
+        <v>138.875</v>
       </c>
       <c r="S30" s="15">
-        <v>-70</v>
+        <v>-82.25</v>
       </c>
       <c r="T30" s="18">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="U30" s="17">
-        <v>1288</v>
+        <v>1045.1200000000001</v>
       </c>
       <c r="V30" s="14">
-        <v>12.681159420289854</v>
+        <v>9.5663157894736841</v>
       </c>
       <c r="W30" s="16">
-        <v>607.20000000000005</v>
+        <v>653.125</v>
       </c>
       <c r="X30" s="15">
-        <v>-64</v>
+        <v>-161.3125</v>
       </c>
       <c r="Y30" s="18">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Z30" s="17">
-        <v>106.72</v>
+        <v>44.160000000000004</v>
       </c>
       <c r="AA30" s="14">
-        <v>6.796875</v>
+        <v>2.1098901098901099</v>
       </c>
       <c r="AB30" s="16">
-        <v>93.86666666666666</v>
+        <v>125.125</v>
       </c>
       <c r="AC30" s="15">
-        <v>-35</v>
+        <v>-101.75</v>
       </c>
       <c r="AD30" s="19">
-        <v>2156</v>
+        <v>1739</v>
       </c>
       <c r="AE30" s="20">
         <v>7934.08</v>
@@ -4285,34 +4287,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>206</v>
+        <v>316</v>
       </c>
       <c r="F31" s="14">
-        <v>758.08</v>
+        <v>1162.8800000000001</v>
       </c>
       <c r="G31" s="14">
-        <v>4.6960486322188446</v>
+        <v>6.7234042553191493</v>
       </c>
       <c r="H31" s="30">
-        <v>965.06666666666672</v>
+        <v>1034</v>
       </c>
       <c r="I31" s="15">
-        <v>-232.66666666666669</v>
+        <v>-154</v>
       </c>
       <c r="J31" s="16">
-        <v>1155</v>
+        <v>777</v>
       </c>
       <c r="K31" s="13">
-        <v>4250.4000000000005</v>
+        <v>2859.36</v>
       </c>
       <c r="L31" s="14">
-        <v>17.678571428571431</v>
+        <v>11.395050412465627</v>
       </c>
       <c r="M31" s="30">
-        <v>1437.3333333333333</v>
+        <v>1500.125</v>
       </c>
       <c r="N31" s="15">
-        <v>501.66666666666674</v>
+        <v>95.125</v>
       </c>
       <c r="O31" s="16">
         <v>37</v>
@@ -4321,46 +4323,46 @@
         <v>136.16</v>
       </c>
       <c r="Q31" s="14">
-        <v>55.5</v>
+        <v>59.2</v>
       </c>
       <c r="R31" s="16">
-        <v>14.666666666666666</v>
+        <v>13.75</v>
       </c>
       <c r="S31" s="15">
-        <v>23.666666666666668</v>
+        <v>24.5</v>
       </c>
       <c r="T31" s="18">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="U31" s="17">
-        <v>585.12</v>
+        <v>500.48</v>
       </c>
       <c r="V31" s="14">
-        <v>20.921052631578949</v>
+        <v>15.883211678832117</v>
       </c>
       <c r="W31" s="16">
-        <v>167.2</v>
+        <v>188.375</v>
       </c>
       <c r="X31" s="15">
-        <v>45</v>
+        <v>7.5625</v>
       </c>
       <c r="Y31" s="18">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Z31" s="17">
-        <v>172.96</v>
+        <v>161.92000000000002</v>
       </c>
       <c r="AA31" s="14">
-        <v>33.571428571428577</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AB31" s="16">
-        <v>30.799999999999997</v>
+        <v>33</v>
       </c>
       <c r="AC31" s="15">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AD31" s="19">
-        <v>1604</v>
+        <v>1310</v>
       </c>
       <c r="AE31" s="20">
         <v>5902.72</v>
@@ -4398,82 +4400,82 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1693</v>
+        <v>1488</v>
       </c>
       <c r="F32" s="14">
-        <v>7025.9500000000007</v>
+        <v>6175.2000000000007</v>
       </c>
       <c r="G32" s="14">
-        <v>7.8719776813391205</v>
+        <v>6.725423728813559</v>
       </c>
       <c r="H32" s="30">
-        <v>4731.4666666666662</v>
+        <v>4867.5</v>
       </c>
       <c r="I32" s="15">
-        <v>-457.66666666666652</v>
+        <v>-724.5</v>
       </c>
       <c r="J32" s="16">
-        <v>2191</v>
+        <v>1930</v>
       </c>
       <c r="K32" s="13">
-        <v>9092.6500000000015</v>
+        <v>8009.5000000000009</v>
       </c>
       <c r="L32" s="14">
-        <v>12.336711711711713</v>
+        <v>10.655624568668047</v>
       </c>
       <c r="M32" s="30">
-        <v>3907.2</v>
+        <v>3984.75</v>
       </c>
       <c r="N32" s="15">
-        <v>415</v>
+        <v>118.75</v>
       </c>
       <c r="O32" s="16">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="P32" s="17">
-        <v>664</v>
+        <v>585.15000000000009</v>
       </c>
       <c r="Q32" s="14">
-        <v>11.538461538461538</v>
+        <v>9.9383259911894282</v>
       </c>
       <c r="R32" s="16">
-        <v>305.06666666666666</v>
+        <v>312.125</v>
       </c>
       <c r="S32" s="15">
-        <v>-117.33333333333337</v>
+        <v>-142.75</v>
       </c>
       <c r="T32" s="18">
-        <v>867</v>
+        <v>811</v>
       </c>
       <c r="U32" s="17">
-        <v>3598.05</v>
+        <v>3365.65</v>
       </c>
       <c r="V32" s="14">
-        <v>10.547445255474452</v>
+        <v>10.090202177293934</v>
       </c>
       <c r="W32" s="16">
-        <v>1808.4</v>
+        <v>1768.25</v>
       </c>
       <c r="X32" s="15">
-        <v>-366</v>
+        <v>-394.625</v>
       </c>
       <c r="Y32" s="18">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="Z32" s="17">
-        <v>1199.3500000000001</v>
+        <v>1174.45</v>
       </c>
       <c r="AA32" s="14">
-        <v>71.06557377049181</v>
+        <v>67.582089552238813</v>
       </c>
       <c r="AB32" s="16">
-        <v>89.466666666666669</v>
+        <v>92.125</v>
       </c>
       <c r="AC32" s="15">
-        <v>228</v>
+        <v>199.25</v>
       </c>
       <c r="AD32" s="19">
-        <v>5200</v>
+        <v>4653</v>
       </c>
       <c r="AE32" s="20">
         <v>21580.000000000004</v>
@@ -4511,82 +4513,82 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>1926</v>
+        <v>3223</v>
       </c>
       <c r="F33" s="14">
-        <v>7992.9000000000005</v>
+        <v>13375.45</v>
       </c>
       <c r="G33" s="14">
-        <v>4.5988538681948423</v>
+        <v>7.4509463950296198</v>
       </c>
       <c r="H33" s="30">
-        <v>9213.6</v>
+        <v>9516.375</v>
       </c>
       <c r="I33" s="15">
-        <v>-2262</v>
+        <v>-1102.625</v>
       </c>
       <c r="J33" s="16">
-        <v>3671</v>
+        <v>3387</v>
       </c>
       <c r="K33" s="13">
-        <v>15234.650000000001</v>
+        <v>14056.050000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>14.19201030927835</v>
+        <v>12.691334894613583</v>
       </c>
       <c r="M33" s="30">
-        <v>5690.666666666667</v>
+        <v>5871.25</v>
       </c>
       <c r="N33" s="15">
-        <v>1084.333333333333</v>
+        <v>718.25</v>
       </c>
       <c r="O33" s="16">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="P33" s="17">
-        <v>975.25000000000011</v>
+        <v>900.55000000000007</v>
       </c>
       <c r="Q33" s="14">
-        <v>11.710963455149502</v>
+        <v>10.952681388012618</v>
       </c>
       <c r="R33" s="16">
-        <v>441.46666666666664</v>
+        <v>435.875</v>
       </c>
       <c r="S33" s="15">
-        <v>-166.33333333333331</v>
+        <v>-179.25</v>
       </c>
       <c r="T33" s="18">
-        <v>1199</v>
+        <v>1075</v>
       </c>
       <c r="U33" s="17">
-        <v>4975.8500000000004</v>
+        <v>4461.25</v>
       </c>
       <c r="V33" s="14">
-        <v>11.448122215149587</v>
+        <v>10.225921521997622</v>
       </c>
       <c r="W33" s="16">
-        <v>2304.1333333333332</v>
+        <v>2312.75</v>
       </c>
       <c r="X33" s="15">
-        <v>-372</v>
+        <v>-501.875</v>
       </c>
       <c r="Y33" s="18">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="Z33" s="17">
-        <v>340.3</v>
+        <v>315.40000000000003</v>
       </c>
       <c r="AA33" s="14">
-        <v>7.0689655172413799</v>
+        <v>6.6448087431693992</v>
       </c>
       <c r="AB33" s="16">
-        <v>255.2</v>
+        <v>251.625</v>
       </c>
       <c r="AC33" s="15">
-        <v>-92</v>
+        <v>-152.75</v>
       </c>
       <c r="AD33" s="19">
-        <v>7113</v>
+        <v>7978</v>
       </c>
       <c r="AE33" s="20">
         <v>29518.95</v>
@@ -4630,13 +4632,13 @@
         <v>3311.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>13.449438202247189</v>
+        <v>14.346067415730337</v>
       </c>
       <c r="H34" s="30">
-        <v>1305.3333333333335</v>
+        <v>1223.75</v>
       </c>
       <c r="I34" s="15">
-        <v>204.66666666666652</v>
+        <v>241.75</v>
       </c>
       <c r="J34" s="16">
         <v>336</v>
@@ -4663,25 +4665,25 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>46.93333333333333</v>
+        <v>44</v>
       </c>
       <c r="S34" s="15">
-        <v>-42.666666666666664</v>
+        <v>-40</v>
       </c>
       <c r="T34" s="18">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="U34" s="17">
-        <v>539.5</v>
+        <v>373.50000000000006</v>
       </c>
       <c r="V34" s="14">
-        <v>17.72727272727273</v>
+        <v>13.090909090909092</v>
       </c>
       <c r="W34" s="16">
-        <v>161.33333333333331</v>
+        <v>151.25</v>
       </c>
       <c r="X34" s="15">
-        <v>20.000000000000014</v>
+        <v>-13.125</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4699,7 +4701,7 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1296</v>
+        <v>1256</v>
       </c>
       <c r="AE34" s="20">
         <v>5378.4000000000005</v>
@@ -4737,82 +4739,82 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>3317</v>
+        <v>3046</v>
       </c>
       <c r="F35" s="14">
-        <v>5406.71</v>
+        <v>4964.9799999999996</v>
       </c>
       <c r="G35" s="14">
-        <v>7.6996285979572887</v>
+        <v>7.1649514848573945</v>
       </c>
       <c r="H35" s="30">
-        <v>9477.6</v>
+        <v>9352.75</v>
       </c>
       <c r="I35" s="15">
-        <v>-991</v>
+        <v>-1205.25</v>
       </c>
       <c r="J35" s="16">
-        <v>620</v>
+        <v>2076</v>
       </c>
       <c r="K35" s="13">
-        <v>1010.5999999999999</v>
+        <v>3383.8799999999997</v>
       </c>
       <c r="L35" s="14">
-        <v>3.8525269262634629</v>
+        <v>11.978362783988461</v>
       </c>
       <c r="M35" s="30">
-        <v>3540.5333333333333</v>
+        <v>3812.875</v>
       </c>
       <c r="N35" s="15">
-        <v>-989.33333333333348</v>
+        <v>342.875</v>
       </c>
       <c r="O35" s="16">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="P35" s="17">
-        <v>1255.0999999999999</v>
+        <v>1237.1699999999998</v>
       </c>
       <c r="Q35" s="14">
-        <v>20.961887477313972</v>
+        <v>20.830188679245282</v>
       </c>
       <c r="R35" s="16">
-        <v>808.13333333333333</v>
+        <v>801.625</v>
       </c>
       <c r="S35" s="15">
-        <v>35.333333333333258</v>
+        <v>30.25</v>
       </c>
       <c r="T35" s="18">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="U35" s="17">
-        <v>604.7299999999999</v>
+        <v>565.61</v>
       </c>
       <c r="V35" s="14">
-        <v>8.5615384615384613</v>
+        <v>8.2130177514792901</v>
       </c>
       <c r="W35" s="16">
-        <v>953.33333333333337</v>
+        <v>929.5</v>
       </c>
       <c r="X35" s="15">
-        <v>-279</v>
+        <v>-286.75</v>
       </c>
       <c r="Y35" s="18">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="Z35" s="17">
-        <v>480.84999999999997</v>
+        <v>459.65999999999997</v>
       </c>
       <c r="AA35" s="14">
-        <v>23.412698412698415</v>
+        <v>21.383886255924171</v>
       </c>
       <c r="AB35" s="16">
-        <v>277.2</v>
+        <v>290.125</v>
       </c>
       <c r="AC35" s="15">
-        <v>106</v>
+        <v>18.25</v>
       </c>
       <c r="AD35" s="19">
-        <v>5373</v>
+        <v>6510</v>
       </c>
       <c r="AE35" s="20">
         <v>8757.99</v>
@@ -4850,82 +4852,82 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>4632</v>
+        <v>5535</v>
       </c>
       <c r="F36" s="14">
-        <v>7550.16</v>
+        <v>9022.0499999999993</v>
       </c>
       <c r="G36" s="14">
-        <v>7.399361022364217</v>
+        <v>8.8471528471528469</v>
       </c>
       <c r="H36" s="30">
-        <v>13772</v>
+        <v>13763.75</v>
       </c>
       <c r="I36" s="15">
-        <v>-1628</v>
+        <v>-721.25</v>
       </c>
       <c r="J36" s="16">
-        <v>3342</v>
+        <v>3716</v>
       </c>
       <c r="K36" s="13">
-        <v>5447.46</v>
+        <v>6057.08</v>
       </c>
       <c r="L36" s="14">
-        <v>14.726792009400702</v>
+        <v>15.475273295158772</v>
       </c>
       <c r="M36" s="30">
-        <v>4992.5333333333338</v>
+        <v>5282.75</v>
       </c>
       <c r="N36" s="15">
-        <v>1072.6666666666665</v>
+        <v>1314.75</v>
       </c>
       <c r="O36" s="16">
-        <v>988</v>
+        <v>943</v>
       </c>
       <c r="P36" s="17">
-        <v>1610.4399999999998</v>
+        <v>1537.09</v>
       </c>
       <c r="Q36" s="14">
-        <v>10.533049040511727</v>
+        <v>10.153432032301481</v>
       </c>
       <c r="R36" s="16">
-        <v>2063.6</v>
+        <v>2043.25</v>
       </c>
       <c r="S36" s="15">
-        <v>-888</v>
+        <v>-914.5</v>
       </c>
       <c r="T36" s="18">
-        <v>968</v>
+        <v>936</v>
       </c>
       <c r="U36" s="17">
-        <v>1577.84</v>
+        <v>1525.6799999999998</v>
       </c>
       <c r="V36" s="14">
-        <v>9.0977443609022544</v>
+        <v>9.1428571428571423</v>
       </c>
       <c r="W36" s="16">
-        <v>2340.8000000000002</v>
+        <v>2252.25</v>
       </c>
       <c r="X36" s="15">
-        <v>-628</v>
+        <v>-599.625</v>
       </c>
       <c r="Y36" s="18">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="Z36" s="17">
-        <v>516.70999999999992</v>
+        <v>446.61999999999995</v>
       </c>
       <c r="AA36" s="14">
-        <v>13.903508771929824</v>
+        <v>11.09873417721519</v>
       </c>
       <c r="AB36" s="16">
-        <v>501.6</v>
+        <v>543.125</v>
       </c>
       <c r="AC36" s="15">
-        <v>-25</v>
+        <v>-219.75</v>
       </c>
       <c r="AD36" s="19">
-        <v>10247</v>
+        <v>11404</v>
       </c>
       <c r="AE36" s="20">
         <v>16702.61</v>
@@ -4963,64 +4965,64 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>322</v>
+        <v>1260</v>
       </c>
       <c r="F37" s="14">
-        <v>524.86</v>
+        <v>2053.7999999999997</v>
       </c>
       <c r="G37" s="14">
-        <v>1.1922981979758085</v>
+        <v>4.3988653720270561</v>
       </c>
       <c r="H37" s="30">
-        <v>5941.4666666666662</v>
+        <v>6301.625</v>
       </c>
       <c r="I37" s="15">
-        <v>-2378.6666666666665</v>
+        <v>-1604.375</v>
       </c>
       <c r="J37" s="16">
-        <v>2252</v>
+        <v>2660</v>
       </c>
       <c r="K37" s="13">
-        <v>3670.7599999999998</v>
+        <v>4335.7999999999993</v>
       </c>
       <c r="L37" s="14">
-        <v>17.017632241813601</v>
+        <v>18.848538529672275</v>
       </c>
       <c r="M37" s="30">
-        <v>2911.3333333333335</v>
+        <v>3104.75</v>
       </c>
       <c r="N37" s="15">
-        <v>928.66666666666652</v>
+        <v>1248.75</v>
       </c>
       <c r="O37" s="16">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="P37" s="17">
-        <v>780.77</v>
+        <v>748.17</v>
       </c>
       <c r="Q37" s="14">
-        <v>8.2681242807825086</v>
+        <v>7.9566630552546043</v>
       </c>
       <c r="R37" s="16">
-        <v>1274.5333333333333</v>
+        <v>1269.125</v>
       </c>
       <c r="S37" s="15">
-        <v>-679.66666666666652</v>
+        <v>-694.75</v>
       </c>
       <c r="T37" s="18">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="U37" s="17">
-        <v>363.48999999999995</v>
+        <v>257.53999999999996</v>
       </c>
       <c r="V37" s="14">
-        <v>4.0693430656934311</v>
+        <v>2.8629671574178936</v>
       </c>
       <c r="W37" s="16">
-        <v>1205.5999999999999</v>
+        <v>1214.125</v>
       </c>
       <c r="X37" s="15">
-        <v>-599</v>
+        <v>-669.8125</v>
       </c>
       <c r="Y37" s="18">
         <v>0</v>
@@ -5032,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>360.79999999999995</v>
+        <v>338.25</v>
       </c>
       <c r="AC37" s="15">
-        <v>-245.99999999999997</v>
+        <v>-307.5</v>
       </c>
       <c r="AD37" s="19">
-        <v>3276</v>
+        <v>4537</v>
       </c>
       <c r="AE37" s="20">
         <v>5339.8799999999992</v>
@@ -5076,82 +5078,82 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="F38" s="14">
-        <v>0</v>
+        <v>816.63</v>
       </c>
       <c r="G38" s="14">
-        <v>0</v>
+        <v>2.6490416391275611</v>
       </c>
       <c r="H38" s="30">
-        <v>4210.8</v>
+        <v>4160.75</v>
       </c>
       <c r="I38" s="15">
-        <v>-1914</v>
+        <v>-1390.25</v>
       </c>
       <c r="J38" s="16">
-        <v>1507</v>
+        <v>2726</v>
       </c>
       <c r="K38" s="13">
-        <v>2456.41</v>
+        <v>4443.38</v>
       </c>
       <c r="L38" s="14">
-        <v>15.019933554817278</v>
+        <v>24.163988919667592</v>
       </c>
       <c r="M38" s="30">
-        <v>2207.333333333333</v>
+        <v>2481.875</v>
       </c>
       <c r="N38" s="15">
-        <v>503.66666666666686</v>
+        <v>1597.875</v>
       </c>
       <c r="O38" s="16">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="P38" s="17">
-        <v>236.35</v>
+        <v>208.64</v>
       </c>
       <c r="Q38" s="14">
-        <v>3.8908765652951702</v>
+        <v>3.3573770491803279</v>
       </c>
       <c r="R38" s="16">
-        <v>819.86666666666667</v>
+        <v>838.75</v>
       </c>
       <c r="S38" s="15">
-        <v>-600.33333333333326</v>
+        <v>-634.5</v>
       </c>
       <c r="T38" s="18">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="U38" s="17">
-        <v>593.31999999999994</v>
+        <v>506.92999999999995</v>
       </c>
       <c r="V38" s="14">
-        <v>10.985915492957746</v>
+        <v>9.0802919708029197</v>
       </c>
       <c r="W38" s="16">
-        <v>728.93333333333328</v>
+        <v>753.5</v>
       </c>
       <c r="X38" s="15">
-        <v>-133</v>
+        <v>-202.75</v>
       </c>
       <c r="Y38" s="18">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="Z38" s="17">
-        <v>400.97999999999996</v>
+        <v>348.82</v>
       </c>
       <c r="AA38" s="14">
-        <v>10.278551532033426</v>
+        <v>8.4127764127764131</v>
       </c>
       <c r="AB38" s="16">
-        <v>526.5333333333333</v>
+        <v>559.625</v>
       </c>
       <c r="AC38" s="15">
-        <v>-113</v>
+        <v>-294.75</v>
       </c>
       <c r="AD38" s="19">
-        <v>2262</v>
+        <v>3880</v>
       </c>
       <c r="AE38" s="20">
         <v>3687.06</v>
@@ -5189,82 +5191,82 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1669</v>
+        <v>1633</v>
       </c>
       <c r="F39" s="14">
-        <v>2720.47</v>
+        <v>2661.79</v>
       </c>
       <c r="G39" s="14">
-        <v>17.617874736101339</v>
+        <v>17.932738503774878</v>
       </c>
       <c r="H39" s="30">
-        <v>2084.1333333333332</v>
+        <v>2003.375</v>
       </c>
       <c r="I39" s="15">
-        <v>721.66666666666663</v>
+        <v>722.375</v>
       </c>
       <c r="J39" s="16">
-        <v>3625</v>
+        <v>3518</v>
       </c>
       <c r="K39" s="13">
-        <v>5908.75</v>
+        <v>5734.3399999999992</v>
       </c>
       <c r="L39" s="14">
-        <v>64.121462264150949</v>
+        <v>58.450674974039458</v>
       </c>
       <c r="M39" s="30">
-        <v>1243.7333333333333</v>
+        <v>1324.125</v>
       </c>
       <c r="N39" s="15">
-        <v>3059.666666666667</v>
+        <v>2916.125</v>
       </c>
       <c r="O39" s="16">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="P39" s="17">
-        <v>322.73999999999995</v>
+        <v>312.95999999999998</v>
       </c>
       <c r="Q39" s="14">
-        <v>6.2790697674418601</v>
+        <v>6.2566191446028512</v>
       </c>
       <c r="R39" s="16">
-        <v>693.73333333333335</v>
+        <v>675.125</v>
       </c>
       <c r="S39" s="15">
-        <v>-432.66666666666674</v>
+        <v>-421.75</v>
       </c>
       <c r="T39" s="18">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="U39" s="17">
-        <v>839.44999999999993</v>
+        <v>798.69999999999993</v>
       </c>
       <c r="V39" s="14">
-        <v>9.9935316946959905</v>
+        <v>9.7633872976338729</v>
       </c>
       <c r="W39" s="16">
-        <v>1133.7333333333333</v>
+        <v>1104.125</v>
       </c>
       <c r="X39" s="15">
-        <v>-258</v>
+        <v>-262.8125</v>
       </c>
       <c r="Y39" s="18">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Z39" s="17">
-        <v>733.5</v>
+        <v>731.87</v>
       </c>
       <c r="AA39" s="14">
-        <v>99.264705882352942</v>
+        <v>101.1830985915493</v>
       </c>
       <c r="AB39" s="16">
-        <v>99.733333333333334</v>
+        <v>97.625</v>
       </c>
       <c r="AC39" s="15">
-        <v>382</v>
+        <v>360.25</v>
       </c>
       <c r="AD39" s="19">
-        <v>6457</v>
+        <v>6282</v>
       </c>
       <c r="AE39" s="20">
         <v>10524.91</v>
@@ -5302,82 +5304,82 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1305</v>
+        <v>1225</v>
       </c>
       <c r="F40" s="14">
-        <v>2127.1499999999996</v>
+        <v>1996.7499999999998</v>
       </c>
       <c r="G40" s="14">
-        <v>10.690879300928454</v>
+        <v>10.566037735849056</v>
       </c>
       <c r="H40" s="30">
-        <v>2685.4666666666667</v>
+        <v>2550.625</v>
       </c>
       <c r="I40" s="15">
-        <v>84.333333333333485</v>
+        <v>65.625</v>
       </c>
       <c r="J40" s="16">
-        <v>3582</v>
+        <v>3470</v>
       </c>
       <c r="K40" s="13">
-        <v>5838.66</v>
+        <v>5656.0999999999995</v>
       </c>
       <c r="L40" s="14">
-        <v>52.114451988360813</v>
+        <v>49.219858156028366</v>
       </c>
       <c r="M40" s="30">
-        <v>1512.1333333333334</v>
+        <v>1551</v>
       </c>
       <c r="N40" s="15">
-        <v>2894.6666666666665</v>
+        <v>2765</v>
       </c>
       <c r="O40" s="16">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="P40" s="17">
-        <v>145.07</v>
+        <v>122.24999999999999</v>
       </c>
       <c r="Q40" s="14">
-        <v>2.2361809045226133</v>
+        <v>1.9639934533551555</v>
       </c>
       <c r="R40" s="16">
-        <v>875.59999999999991</v>
+        <v>840.125</v>
       </c>
       <c r="S40" s="15">
-        <v>-707</v>
+        <v>-688.75</v>
       </c>
       <c r="T40" s="18">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="U40" s="17">
-        <v>609.62</v>
+        <v>596.57999999999993</v>
       </c>
       <c r="V40" s="14">
-        <v>5.9302325581395348</v>
+        <v>6.0873180873180877</v>
       </c>
       <c r="W40" s="16">
-        <v>1387.4666666666667</v>
+        <v>1322.75</v>
       </c>
       <c r="X40" s="15">
-        <v>-572</v>
+        <v>-535.875</v>
       </c>
       <c r="Y40" s="18">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="Z40" s="17">
-        <v>759.57999999999993</v>
+        <v>749.8</v>
       </c>
       <c r="AA40" s="14">
-        <v>110.95238095238095</v>
+        <v>106.66666666666667</v>
       </c>
       <c r="AB40" s="16">
-        <v>92.4</v>
+        <v>94.875</v>
       </c>
       <c r="AC40" s="15">
-        <v>403</v>
+        <v>373.75</v>
       </c>
       <c r="AD40" s="19">
-        <v>5816</v>
+        <v>5596</v>
       </c>
       <c r="AE40" s="20">
         <v>9480.08</v>
@@ -5415,34 +5417,34 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>161</v>
+        <v>497</v>
       </c>
       <c r="F41" s="14">
-        <v>990.15000000000009</v>
+        <v>3056.55</v>
       </c>
       <c r="G41" s="14">
-        <v>2.4320241691842899</v>
+        <v>7.2094288304623753</v>
       </c>
       <c r="H41" s="30">
-        <v>1456.4</v>
+        <v>1516.625</v>
       </c>
       <c r="I41" s="15">
-        <v>-501</v>
+        <v>-192.375</v>
       </c>
       <c r="J41" s="16">
-        <v>726</v>
+        <v>676</v>
       </c>
       <c r="K41" s="13">
-        <v>4464.9000000000005</v>
+        <v>4157.4000000000005</v>
       </c>
       <c r="L41" s="14">
-        <v>20.625</v>
+        <v>16.821150855365474</v>
       </c>
       <c r="M41" s="30">
-        <v>774.40000000000009</v>
+        <v>884.125</v>
       </c>
       <c r="N41" s="15">
-        <v>374</v>
+        <v>274.125</v>
       </c>
       <c r="O41" s="16">
         <v>50</v>
@@ -5451,46 +5453,46 @@
         <v>307.5</v>
       </c>
       <c r="Q41" s="14">
-        <v>9.375</v>
+        <v>10</v>
       </c>
       <c r="R41" s="16">
-        <v>117.33333333333333</v>
+        <v>110</v>
       </c>
       <c r="S41" s="15">
-        <v>-56.666666666666657</v>
+        <v>-50</v>
       </c>
       <c r="T41" s="18">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="U41" s="17">
-        <v>984</v>
+        <v>885.6</v>
       </c>
       <c r="V41" s="14">
-        <v>15.789473684210527</v>
+        <v>13.879518072289157</v>
       </c>
       <c r="W41" s="16">
-        <v>222.93333333333334</v>
+        <v>228.25</v>
       </c>
       <c r="X41" s="15">
-        <v>8</v>
+        <v>-11.625</v>
       </c>
       <c r="Y41" s="18">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z41" s="17">
-        <v>104.55000000000001</v>
+        <v>86.100000000000009</v>
       </c>
       <c r="AA41" s="14">
-        <v>3.9230769230769234</v>
+        <v>3.2941176470588234</v>
       </c>
       <c r="AB41" s="16">
-        <v>95.333333333333329</v>
+        <v>93.5</v>
       </c>
       <c r="AC41" s="15">
-        <v>-48</v>
+        <v>-71</v>
       </c>
       <c r="AD41" s="19">
-        <v>1114</v>
+        <v>1381</v>
       </c>
       <c r="AE41" s="20">
         <v>6851.1</v>
@@ -5528,34 +5530,34 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="F42" s="14">
-        <v>0</v>
+        <v>2447.7000000000003</v>
       </c>
       <c r="G42" s="14">
-        <v>0</v>
+        <v>5.9127205199628596</v>
       </c>
       <c r="H42" s="30">
-        <v>1509.1999999999998</v>
+        <v>1480.875</v>
       </c>
       <c r="I42" s="15">
-        <v>-686</v>
+        <v>-275.125</v>
       </c>
       <c r="J42" s="16">
-        <v>744</v>
+        <v>248</v>
       </c>
       <c r="K42" s="13">
-        <v>4575.6000000000004</v>
+        <v>1525.2</v>
       </c>
       <c r="L42" s="14">
-        <v>20.62846580406654</v>
+        <v>6.0580152671755725</v>
       </c>
       <c r="M42" s="30">
-        <v>793.4666666666667</v>
+        <v>900.625</v>
       </c>
       <c r="N42" s="15">
-        <v>383.33333333333331</v>
+        <v>-161.375</v>
       </c>
       <c r="O42" s="16">
         <v>58</v>
@@ -5564,46 +5566,46 @@
         <v>356.70000000000005</v>
       </c>
       <c r="Q42" s="14">
-        <v>8.2075471698113205</v>
+        <v>8.7547169811320753</v>
       </c>
       <c r="R42" s="16">
-        <v>155.46666666666667</v>
+        <v>145.75</v>
       </c>
       <c r="S42" s="15">
-        <v>-83.333333333333314</v>
+        <v>-74.5</v>
       </c>
       <c r="T42" s="18">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="U42" s="17">
-        <v>1230</v>
+        <v>1088.55</v>
       </c>
       <c r="V42" s="14">
-        <v>12.295081967213115</v>
+        <v>10.727272727272727</v>
       </c>
       <c r="W42" s="16">
-        <v>357.86666666666667</v>
+        <v>363</v>
       </c>
       <c r="X42" s="15">
-        <v>-44</v>
+        <v>-70.5</v>
       </c>
       <c r="Y42" s="18">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Z42" s="17">
-        <v>516.6</v>
+        <v>504.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>22.105263157894736</v>
+        <v>22.237288135593221</v>
       </c>
       <c r="AB42" s="16">
-        <v>83.6</v>
+        <v>81.125</v>
       </c>
       <c r="AC42" s="15">
-        <v>27</v>
+        <v>8.25</v>
       </c>
       <c r="AD42" s="19">
-        <v>1086</v>
+        <v>963</v>
       </c>
       <c r="AE42" s="20">
         <v>6678.9000000000005</v>
@@ -5641,82 +5643,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2276</v>
+        <v>2810</v>
       </c>
       <c r="F43" s="14">
-        <v>2640.16</v>
+        <v>3259.6</v>
       </c>
       <c r="G43" s="14">
-        <v>7.3214668668239327</v>
+        <v>8.8312708701630331</v>
       </c>
       <c r="H43" s="30">
-        <v>6839.0666666666666</v>
+        <v>7000.125</v>
       </c>
       <c r="I43" s="15">
-        <v>-832.66666666666697</v>
+        <v>-371.875</v>
       </c>
       <c r="J43" s="16">
-        <v>3566</v>
+        <v>2371</v>
       </c>
       <c r="K43" s="13">
-        <v>4136.5599999999995</v>
+        <v>2750.3599999999997</v>
       </c>
       <c r="L43" s="14">
-        <v>15.788075560802833</v>
+        <v>9.9805314390949746</v>
       </c>
       <c r="M43" s="30">
-        <v>4969.0666666666666</v>
+        <v>5226.375</v>
       </c>
       <c r="N43" s="15">
-        <v>1307.333333333333</v>
+        <v>-4.625</v>
       </c>
       <c r="O43" s="16">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="P43" s="17">
-        <v>966.28</v>
+        <v>939.59999999999991</v>
       </c>
       <c r="Q43" s="14">
-        <v>17.850000000000005</v>
+        <v>17.632653061224488</v>
       </c>
       <c r="R43" s="16">
-        <v>1026.6666666666665</v>
+        <v>1010.625</v>
       </c>
       <c r="S43" s="15">
-        <v>-100.33333333333314</v>
+        <v>-108.75</v>
       </c>
       <c r="T43" s="18">
-        <v>1125</v>
+        <v>981</v>
       </c>
       <c r="U43" s="17">
-        <v>1305</v>
+        <v>1137.9599999999998</v>
       </c>
       <c r="V43" s="14">
-        <v>9.7543352601156084</v>
+        <v>8.4341751746372911</v>
       </c>
       <c r="W43" s="16">
-        <v>2537.333333333333</v>
+        <v>2558.875</v>
       </c>
       <c r="X43" s="15">
-        <v>-604.99999999999977</v>
+        <v>-763.6875</v>
       </c>
       <c r="Y43" s="18">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="Z43" s="17">
-        <v>228.51999999999998</v>
+        <v>142.67999999999998</v>
       </c>
       <c r="AA43" s="14">
-        <v>7.7559055118110241</v>
+        <v>4.3063457330415753</v>
       </c>
       <c r="AB43" s="16">
-        <v>558.79999999999995</v>
+        <v>628.375</v>
       </c>
       <c r="AC43" s="15">
-        <v>-184</v>
+        <v>-448.25</v>
       </c>
       <c r="AD43" s="19">
-        <v>7997</v>
+        <v>7095</v>
       </c>
       <c r="AE43" s="20">
         <v>9276.5199999999986</v>
@@ -5754,82 +5756,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2097</v>
+        <v>1916</v>
       </c>
       <c r="F44" s="14">
-        <v>2432.52</v>
+        <v>2222.56</v>
       </c>
       <c r="G44" s="14">
-        <v>7.5612980769230775</v>
+        <v>6.8185053380782916</v>
       </c>
       <c r="H44" s="30">
-        <v>6101.333333333333</v>
+        <v>6182</v>
       </c>
       <c r="I44" s="15">
-        <v>-676.33333333333303</v>
+        <v>-894</v>
       </c>
       <c r="J44" s="16">
-        <v>3394</v>
+        <v>3135</v>
       </c>
       <c r="K44" s="13">
-        <v>3937.0399999999995</v>
+        <v>3636.6</v>
       </c>
       <c r="L44" s="14">
-        <v>18.485838779956428</v>
+        <v>16.5</v>
       </c>
       <c r="M44" s="30">
-        <v>4039.2</v>
+        <v>4180</v>
       </c>
       <c r="N44" s="15">
-        <v>1558</v>
+        <v>1235</v>
       </c>
       <c r="O44" s="16">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="P44" s="17">
-        <v>734.28</v>
+        <v>728.4799999999999</v>
       </c>
       <c r="Q44" s="14">
-        <v>22.879518072289152</v>
+        <v>23.25925925925926</v>
       </c>
       <c r="R44" s="16">
-        <v>608.66666666666674</v>
+        <v>594</v>
       </c>
       <c r="S44" s="15">
-        <v>79.666666666666515</v>
+        <v>88</v>
       </c>
       <c r="T44" s="18">
-        <v>1206</v>
+        <v>1070</v>
       </c>
       <c r="U44" s="17">
-        <v>1398.9599999999998</v>
+        <v>1241.1999999999998</v>
       </c>
       <c r="V44" s="14">
-        <v>20.234899328859061</v>
+        <v>16.735092864125122</v>
       </c>
       <c r="W44" s="16">
-        <v>1311.2</v>
+        <v>1406.625</v>
       </c>
       <c r="X44" s="15">
-        <v>312</v>
+        <v>110.9375</v>
       </c>
       <c r="Y44" s="18">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="Z44" s="17">
-        <v>346.84</v>
+        <v>281.88</v>
       </c>
       <c r="AA44" s="14">
-        <v>12.705382436260622</v>
+        <v>9.5061124694376531</v>
       </c>
       <c r="AB44" s="16">
-        <v>517.73333333333335</v>
+        <v>562.375</v>
       </c>
       <c r="AC44" s="15">
-        <v>-54</v>
+        <v>-268.25</v>
       </c>
       <c r="AD44" s="19">
-        <v>7629</v>
+        <v>6992</v>
       </c>
       <c r="AE44" s="20">
         <v>8849.64</v>
@@ -5867,82 +5869,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2307</v>
+        <v>1937</v>
       </c>
       <c r="F45" s="14">
-        <v>2676.12</v>
+        <v>2246.9199999999996</v>
       </c>
       <c r="G45" s="14">
-        <v>6.3425586510263923</v>
+        <v>5.2078642245000841</v>
       </c>
       <c r="H45" s="30">
-        <v>8002.1333333333332</v>
+        <v>8182.625</v>
       </c>
       <c r="I45" s="15">
-        <v>-1330.3333333333335</v>
+        <v>-1782.375</v>
       </c>
       <c r="J45" s="16">
-        <v>3431</v>
+        <v>3122</v>
       </c>
       <c r="K45" s="13">
-        <v>3979.9599999999996</v>
+        <v>3621.5199999999995</v>
       </c>
       <c r="L45" s="14">
-        <v>13.845843422114609</v>
+        <v>12.330782522833868</v>
       </c>
       <c r="M45" s="30">
-        <v>5451.6</v>
+        <v>5570.125</v>
       </c>
       <c r="N45" s="15">
-        <v>953</v>
+        <v>590.125</v>
       </c>
       <c r="O45" s="16">
-        <v>911</v>
+        <v>875</v>
       </c>
       <c r="P45" s="17">
-        <v>1056.76</v>
+        <v>1014.9999999999999</v>
       </c>
       <c r="Q45" s="14">
-        <v>22.075928917609048</v>
+        <v>20.989505247376311</v>
       </c>
       <c r="R45" s="16">
-        <v>907.86666666666667</v>
+        <v>917.125</v>
       </c>
       <c r="S45" s="15">
-        <v>85.666666666666742</v>
+        <v>41.25</v>
       </c>
       <c r="T45" s="18">
-        <v>1192</v>
+        <v>1026</v>
       </c>
       <c r="U45" s="17">
-        <v>1382.7199999999998</v>
+        <v>1190.1599999999999</v>
       </c>
       <c r="V45" s="14">
-        <v>13.303571428571429</v>
+        <v>10.965931863727455</v>
       </c>
       <c r="W45" s="16">
-        <v>1971.1999999999998</v>
+        <v>2058.375</v>
       </c>
       <c r="X45" s="15">
-        <v>-152</v>
+        <v>-377.4375</v>
       </c>
       <c r="Y45" s="18">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="Z45" s="17">
-        <v>250.55999999999997</v>
+        <v>213.44</v>
       </c>
       <c r="AA45" s="14">
-        <v>8.8283378746594003</v>
+        <v>7.215686274509804</v>
       </c>
       <c r="AB45" s="16">
-        <v>538.26666666666665</v>
+        <v>561</v>
       </c>
       <c r="AC45" s="15">
-        <v>-151</v>
+        <v>-326</v>
       </c>
       <c r="AD45" s="19">
-        <v>8057</v>
+        <v>7144</v>
       </c>
       <c r="AE45" s="20">
         <v>9346.119999999999</v>
@@ -5980,82 +5982,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>1392</v>
+        <v>2107</v>
       </c>
       <c r="F46" s="14">
-        <v>1614.7199999999998</v>
+        <v>2444.12</v>
       </c>
       <c r="G46" s="14">
-        <v>5.225225225225226</v>
+        <v>7.7784956160590681</v>
       </c>
       <c r="H46" s="30">
-        <v>5860.7999999999993</v>
+        <v>5959.25</v>
       </c>
       <c r="I46" s="15">
-        <v>-1272</v>
+        <v>-601.75</v>
       </c>
       <c r="J46" s="16">
-        <v>4768</v>
+        <v>4005</v>
       </c>
       <c r="K46" s="13">
-        <v>5530.8799999999992</v>
+        <v>4645.7999999999993</v>
       </c>
       <c r="L46" s="14">
-        <v>32.332730560578661</v>
+        <v>26.059373729158196</v>
       </c>
       <c r="M46" s="30">
-        <v>3244.2666666666669</v>
+        <v>3381.125</v>
       </c>
       <c r="N46" s="15">
-        <v>3293.333333333333</v>
+        <v>2468.125</v>
       </c>
       <c r="O46" s="16">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="P46" s="17">
-        <v>749.3599999999999</v>
+        <v>741.2399999999999</v>
       </c>
       <c r="Q46" s="14">
-        <v>27.528409090909093</v>
+        <v>27.557951482479783</v>
       </c>
       <c r="R46" s="16">
-        <v>516.26666666666665</v>
+        <v>510.125</v>
       </c>
       <c r="S46" s="15">
-        <v>176.66666666666669</v>
+        <v>175.25</v>
       </c>
       <c r="T46" s="18">
-        <v>800</v>
+        <v>728</v>
       </c>
       <c r="U46" s="17">
-        <v>927.99999999999989</v>
+        <v>844.4799999999999</v>
       </c>
       <c r="V46" s="14">
-        <v>20.689655172413794</v>
+        <v>18.00309119010819</v>
       </c>
       <c r="W46" s="16">
-        <v>850.66666666666663</v>
+        <v>889.625</v>
       </c>
       <c r="X46" s="15">
-        <v>220</v>
+        <v>121.4375</v>
       </c>
       <c r="Y46" s="18">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="Z46" s="17">
-        <v>95.11999999999999</v>
+        <v>49.879999999999995</v>
       </c>
       <c r="AA46" s="14">
-        <v>3.5860058309037899</v>
+        <v>1.7551020408163265</v>
       </c>
       <c r="AB46" s="16">
-        <v>503.06666666666666</v>
+        <v>539</v>
       </c>
       <c r="AC46" s="15">
-        <v>-261</v>
+        <v>-447</v>
       </c>
       <c r="AD46" s="19">
-        <v>7688</v>
+        <v>7522</v>
       </c>
       <c r="AE46" s="20">
         <v>8918.08</v>
@@ -6106,19 +6108,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="K47" s="13">
-        <v>54</v>
+        <v>594</v>
       </c>
       <c r="L47" s="14">
-        <v>1.125</v>
+        <v>13.2</v>
       </c>
       <c r="M47" s="30">
-        <v>58.666666666666664</v>
+        <v>55</v>
       </c>
       <c r="N47" s="15">
-        <v>-23.666666666666664</v>
+        <v>8</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6136,19 +6138,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U47" s="17">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="V47" s="14">
-        <v>5</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="W47" s="16">
-        <v>22</v>
+        <v>24.75</v>
       </c>
       <c r="X47" s="15">
-        <v>-10</v>
+        <v>-14.875</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6166,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="AE47" s="20">
         <v>144</v>
@@ -6223,13 +6225,13 @@
         <v>180</v>
       </c>
       <c r="L48" s="14">
-        <v>21.428571428571427</v>
+        <v>22.857142857142858</v>
       </c>
       <c r="M48" s="30">
-        <v>10.266666666666667</v>
+        <v>9.625</v>
       </c>
       <c r="N48" s="15">
-        <v>5.333333333333333</v>
+        <v>5.625</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6315,82 +6317,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="F49" s="14">
-        <v>406</v>
+        <v>303.91999999999996</v>
       </c>
       <c r="G49" s="14">
-        <v>6.7917205692108666</v>
+        <v>4.8518518518518521</v>
       </c>
       <c r="H49" s="30">
-        <v>1133.7333333333333</v>
+        <v>1188</v>
       </c>
       <c r="I49" s="15">
-        <v>-165.33333333333326</v>
+        <v>-278</v>
       </c>
       <c r="J49" s="16">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="K49" s="13">
-        <v>162.39999999999998</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="L49" s="14">
-        <v>2.1806853582554515</v>
+        <v>0.49230769230769234</v>
       </c>
       <c r="M49" s="30">
-        <v>1412.4</v>
+        <v>1430</v>
       </c>
       <c r="N49" s="15">
-        <v>-502</v>
+        <v>-618</v>
       </c>
       <c r="O49" s="16">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P49" s="17">
-        <v>90.47999999999999</v>
+        <v>87</v>
       </c>
       <c r="Q49" s="14">
-        <v>11.699999999999998</v>
+        <v>10.344827586206897</v>
       </c>
       <c r="R49" s="16">
-        <v>146.66666666666669</v>
+        <v>159.5</v>
       </c>
       <c r="S49" s="15">
-        <v>-55.333333333333371</v>
+        <v>-70</v>
       </c>
       <c r="T49" s="18">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="U49" s="17">
-        <v>47.559999999999995</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="V49" s="14">
-        <v>3.1701030927835046</v>
+        <v>2.5221674876847291</v>
       </c>
       <c r="W49" s="16">
-        <v>284.53333333333336</v>
+        <v>279.125</v>
       </c>
       <c r="X49" s="15">
-        <v>-153.00000000000003</v>
+        <v>-158.3125</v>
       </c>
       <c r="Y49" s="18">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="Z49" s="17">
-        <v>57.999999999999993</v>
+        <v>33.64</v>
       </c>
       <c r="AA49" s="14">
-        <v>11.71875</v>
+        <v>5.4588235294117649</v>
       </c>
       <c r="AB49" s="16">
-        <v>93.86666666666666</v>
+        <v>116.875</v>
       </c>
       <c r="AC49" s="15">
-        <v>-14</v>
+        <v>-77.25</v>
       </c>
       <c r="AD49" s="19">
-        <v>659</v>
+        <v>430</v>
       </c>
       <c r="AE49" s="20">
         <v>764.43999999999994</v>
@@ -6428,82 +6430,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1719</v>
+        <v>812</v>
       </c>
       <c r="F50" s="14">
-        <v>1994.04</v>
+        <v>941.92</v>
       </c>
       <c r="G50" s="14">
-        <v>6.2936294849890162</v>
+        <v>2.8756086764054891</v>
       </c>
       <c r="H50" s="30">
-        <v>6008.9333333333334</v>
+        <v>6212.25</v>
       </c>
       <c r="I50" s="15">
-        <v>-1012.333333333333</v>
+        <v>-2011.75</v>
       </c>
       <c r="J50" s="16">
-        <v>1211</v>
+        <v>71</v>
       </c>
       <c r="K50" s="13">
-        <v>1404.76</v>
+        <v>82.36</v>
       </c>
       <c r="L50" s="14">
-        <v>6.5388768898488125</v>
+        <v>0.35802080050425467</v>
       </c>
       <c r="M50" s="30">
-        <v>4074.3999999999996</v>
+        <v>4362.875</v>
       </c>
       <c r="N50" s="15">
-        <v>-641</v>
+        <v>-1912.125</v>
       </c>
       <c r="O50" s="16">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="P50" s="17">
-        <v>371.2</v>
+        <v>330.59999999999997</v>
       </c>
       <c r="Q50" s="14">
-        <v>7.6555023923444985</v>
+        <v>6.6472303206997081</v>
       </c>
       <c r="R50" s="16">
-        <v>919.59999999999991</v>
+        <v>943.25</v>
       </c>
       <c r="S50" s="15">
-        <v>-516</v>
+        <v>-572.5</v>
       </c>
       <c r="T50" s="18">
-        <v>958</v>
+        <v>870</v>
       </c>
       <c r="U50" s="17">
-        <v>1111.28</v>
+        <v>1009.1999999999999</v>
       </c>
       <c r="V50" s="14">
-        <v>38.733153638814017</v>
+        <v>30.728476821192054</v>
       </c>
       <c r="W50" s="16">
-        <v>544.13333333333333</v>
+        <v>622.875</v>
       </c>
       <c r="X50" s="15">
-        <v>587</v>
+        <v>445.3125</v>
       </c>
       <c r="Y50" s="18">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="Z50" s="17">
-        <v>105.55999999999999</v>
+        <v>61.48</v>
       </c>
       <c r="AA50" s="14">
-        <v>8.8636363636363633</v>
+        <v>4.5347593582887704</v>
       </c>
       <c r="AB50" s="16">
-        <v>225.86666666666667</v>
+        <v>257.125</v>
       </c>
       <c r="AC50" s="15">
-        <v>-63</v>
+        <v>-180.75</v>
       </c>
       <c r="AD50" s="19">
-        <v>4299</v>
+        <v>2091</v>
       </c>
       <c r="AE50" s="20">
         <v>4986.8399999999992</v>
@@ -6544,82 +6546,82 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="F51" s="14">
-        <v>0</v>
+        <v>564.91999999999996</v>
       </c>
       <c r="G51" s="14">
-        <v>0</v>
+        <v>2.5741658407664354</v>
       </c>
       <c r="H51" s="30">
-        <v>4243.0666666666666</v>
+        <v>4162.125</v>
       </c>
       <c r="I51" s="15">
-        <v>-1928.6666666666667</v>
+        <v>-1404.875</v>
       </c>
       <c r="J51" s="16">
-        <v>2692</v>
+        <v>1932</v>
       </c>
       <c r="K51" s="13">
-        <v>3122.72</v>
+        <v>2241.12</v>
       </c>
       <c r="L51" s="14">
-        <v>16.256038647342997</v>
+        <v>11.634173880316146</v>
       </c>
       <c r="M51" s="30">
-        <v>3643.2</v>
+        <v>3653.375</v>
       </c>
       <c r="N51" s="15">
-        <v>1036</v>
+        <v>271.375</v>
       </c>
       <c r="O51" s="16">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="P51" s="17">
-        <v>169.35999999999999</v>
+        <v>151.95999999999998</v>
       </c>
       <c r="Q51" s="14">
-        <v>0</v>
+        <v>9.5707762557077629</v>
       </c>
       <c r="R51" s="16">
-        <v>281.60000000000002</v>
+        <v>301.125</v>
       </c>
       <c r="S51" s="15">
-        <v>-110</v>
+        <v>-142.75</v>
       </c>
       <c r="T51" s="18">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="U51" s="17">
-        <v>494.15999999999997</v>
+        <v>436.15999999999997</v>
       </c>
       <c r="V51" s="14">
-        <v>13.175257731958762</v>
+        <v>11.547024952015356</v>
       </c>
       <c r="W51" s="16">
-        <v>711.33333333333337</v>
+        <v>716.375</v>
       </c>
       <c r="X51" s="15">
-        <v>-59.000000000000057</v>
+        <v>-112.4375</v>
       </c>
       <c r="Y51" s="18">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="Z51" s="17">
-        <v>118.32</v>
+        <v>105.55999999999999</v>
       </c>
       <c r="AA51" s="14">
-        <v>27.818181818181824</v>
+        <v>22.060606060606062</v>
       </c>
       <c r="AB51" s="16">
-        <v>80.666666666666657</v>
+        <v>90.75</v>
       </c>
       <c r="AC51" s="15">
-        <v>47.000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="AD51" s="19">
-        <v>3366</v>
+        <v>3017</v>
       </c>
       <c r="AE51" s="20">
         <v>3904.56</v>
@@ -6661,64 +6663,64 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>2857</v>
+        <v>2659</v>
       </c>
       <c r="F52" s="14">
-        <v>2314.17</v>
+        <v>2153.79</v>
       </c>
       <c r="G52" s="14">
-        <v>20.186057465850212</v>
+        <v>18.60253607345868</v>
       </c>
       <c r="H52" s="30">
-        <v>3113.7333333333331</v>
+        <v>3144.625</v>
       </c>
       <c r="I52" s="15">
-        <v>1441.6666666666667</v>
+        <v>1229.625</v>
       </c>
       <c r="J52" s="16">
-        <v>1353</v>
+        <v>1245</v>
       </c>
       <c r="K52" s="13">
-        <v>1095.93</v>
+        <v>1008.45</v>
       </c>
       <c r="L52" s="14">
-        <v>41.082995951417011</v>
+        <v>34.109589041095887</v>
       </c>
       <c r="M52" s="30">
-        <v>724.5333333333333</v>
+        <v>803</v>
       </c>
       <c r="N52" s="15">
-        <v>1023.6666666666667</v>
+        <v>880</v>
       </c>
       <c r="O52" s="16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P52" s="17">
-        <v>21.87</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="14">
-        <v>3.4615384615384617</v>
+        <v>0</v>
       </c>
       <c r="R52" s="16">
-        <v>171.6</v>
+        <v>160.875</v>
       </c>
       <c r="S52" s="15">
-        <v>-129</v>
+        <v>-146.25</v>
       </c>
       <c r="T52" s="18">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="U52" s="17">
-        <v>383.13000000000005</v>
+        <v>353.97</v>
       </c>
       <c r="V52" s="14">
-        <v>24.381443298969074</v>
+        <v>21.781931464174455</v>
       </c>
       <c r="W52" s="16">
-        <v>426.79999999999995</v>
+        <v>441.375</v>
       </c>
       <c r="X52" s="15">
-        <v>182</v>
+        <v>136.0625</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6730,13 +6732,13 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>33.733333333333334</v>
+        <v>31.625</v>
       </c>
       <c r="AC52" s="15">
-        <v>-23</v>
+        <v>-28.75</v>
       </c>
       <c r="AD52" s="19">
-        <v>4710</v>
+        <v>4341</v>
       </c>
       <c r="AE52" s="20">
         <v>3815.1000000000004</v>
@@ -6774,82 +6776,82 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1436</v>
+        <v>1608</v>
       </c>
       <c r="F53" s="14">
-        <v>1163.1600000000001</v>
+        <v>1302.48</v>
       </c>
       <c r="G53" s="14">
-        <v>5.4991064590247642</v>
+        <v>5.9818646826319464</v>
       </c>
       <c r="H53" s="30">
-        <v>5744.9333333333334</v>
+        <v>5913.875</v>
       </c>
       <c r="I53" s="15">
-        <v>-1175.333333333333</v>
+        <v>-1080.125</v>
       </c>
       <c r="J53" s="16">
-        <v>3098</v>
+        <v>1455</v>
       </c>
       <c r="K53" s="13">
-        <v>2509.38</v>
+        <v>1178.5500000000002</v>
       </c>
       <c r="L53" s="14">
-        <v>26.923522595596758</v>
+        <v>12.462526766595289</v>
       </c>
       <c r="M53" s="30">
-        <v>2531.4666666666667</v>
+        <v>2568.5</v>
       </c>
       <c r="N53" s="15">
-        <v>1947.3333333333335</v>
+        <v>287.5</v>
       </c>
       <c r="O53" s="16">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P53" s="17">
-        <v>38.880000000000003</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="14">
-        <v>1.5286624203821657</v>
+        <v>0</v>
       </c>
       <c r="R53" s="16">
-        <v>690.8</v>
+        <v>647.625</v>
       </c>
       <c r="S53" s="15">
-        <v>-580</v>
+        <v>-588.75</v>
       </c>
       <c r="T53" s="18">
-        <v>872</v>
+        <v>825</v>
       </c>
       <c r="U53" s="17">
-        <v>706.32</v>
+        <v>668.25</v>
       </c>
       <c r="V53" s="14">
-        <v>16.747759282970549</v>
+        <v>16.038882138517618</v>
       </c>
       <c r="W53" s="16">
-        <v>1145.4666666666667</v>
+        <v>1131.625</v>
       </c>
       <c r="X53" s="15">
-        <v>91</v>
+        <v>53.4375</v>
       </c>
       <c r="Y53" s="18">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Z53" s="17">
-        <v>14.580000000000002</v>
+        <v>7.2900000000000009</v>
       </c>
       <c r="AA53" s="14">
-        <v>2.454545454545455</v>
+        <v>1.3090909090909091</v>
       </c>
       <c r="AB53" s="16">
-        <v>161.33333333333331</v>
+        <v>151.25</v>
       </c>
       <c r="AC53" s="15">
-        <v>-91.999999999999986</v>
+        <v>-128.5</v>
       </c>
       <c r="AD53" s="19">
-        <v>5472</v>
+        <v>3897</v>
       </c>
       <c r="AE53" s="20">
         <v>4432.3200000000006</v>
@@ -6887,82 +6889,82 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1272</v>
+        <v>1711</v>
       </c>
       <c r="F54" s="14">
-        <v>1030.3200000000002</v>
+        <v>1385.91</v>
       </c>
       <c r="G54" s="14">
-        <v>7.2796642502861513</v>
+        <v>9.8723404255319149</v>
       </c>
       <c r="H54" s="30">
-        <v>3844.1333333333332</v>
+        <v>3812.875</v>
       </c>
       <c r="I54" s="15">
-        <v>-475.33333333333326</v>
+        <v>-22.125</v>
       </c>
       <c r="J54" s="16">
-        <v>5488</v>
+        <v>4795</v>
       </c>
       <c r="K54" s="13">
-        <v>4445.2800000000007</v>
+        <v>3883.9500000000003</v>
       </c>
       <c r="L54" s="14">
-        <v>93.016949152542367</v>
+        <v>79.338159255429161</v>
       </c>
       <c r="M54" s="30">
-        <v>1298</v>
+        <v>1329.625</v>
       </c>
       <c r="N54" s="15">
-        <v>4898</v>
+        <v>4190.625</v>
       </c>
       <c r="O54" s="16">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="P54" s="17">
-        <v>210.60000000000002</v>
+        <v>187.92000000000002</v>
       </c>
       <c r="Q54" s="14">
-        <v>23.076923076923077</v>
+        <v>18.842639593908629</v>
       </c>
       <c r="R54" s="16">
-        <v>247.86666666666667</v>
+        <v>270.875</v>
       </c>
       <c r="S54" s="15">
-        <v>34.666666666666657</v>
+        <v>-14.25</v>
       </c>
       <c r="T54" s="18">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="U54" s="17">
-        <v>405</v>
+        <v>390.42</v>
       </c>
       <c r="V54" s="14">
-        <v>19.480519480519476</v>
+        <v>19.136476426799007</v>
       </c>
       <c r="W54" s="16">
-        <v>564.66666666666674</v>
+        <v>554.125</v>
       </c>
       <c r="X54" s="15">
-        <v>114.99999999999994</v>
+        <v>104.1875</v>
       </c>
       <c r="Y54" s="18">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="Z54" s="17">
-        <v>110.16000000000001</v>
+        <v>96.39</v>
       </c>
       <c r="AA54" s="14">
-        <v>16.451612903225804</v>
+        <v>14.646153846153846</v>
       </c>
       <c r="AB54" s="16">
-        <v>181.86666666666667</v>
+        <v>178.75</v>
       </c>
       <c r="AC54" s="15">
-        <v>11.999999999999986</v>
+        <v>-43.5</v>
       </c>
       <c r="AD54" s="19">
-        <v>7656</v>
+        <v>7339</v>
       </c>
       <c r="AE54" s="20">
         <v>6201.3600000000006</v>
@@ -7000,82 +7002,82 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>2892</v>
+        <v>2756</v>
       </c>
       <c r="F55" s="14">
-        <v>2342.52</v>
+        <v>2232.36</v>
       </c>
       <c r="G55" s="14">
-        <v>18.373570520965693</v>
+        <v>17.687926193341355</v>
       </c>
       <c r="H55" s="30">
-        <v>3462.8</v>
+        <v>3427.875</v>
       </c>
       <c r="I55" s="15">
-        <v>1318</v>
+        <v>1197.875</v>
       </c>
       <c r="J55" s="16">
-        <v>6777</v>
+        <v>6669</v>
       </c>
       <c r="K55" s="13">
-        <v>5489.3700000000008</v>
+        <v>5401.89</v>
       </c>
       <c r="L55" s="14">
-        <v>92.162284678150499</v>
+        <v>86.540145985401466</v>
       </c>
       <c r="M55" s="30">
-        <v>1617.7333333333333</v>
+        <v>1695.375</v>
       </c>
       <c r="N55" s="15">
-        <v>6041.666666666667</v>
+        <v>5898.375</v>
       </c>
       <c r="O55" s="16">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="P55" s="17">
-        <v>254.34</v>
+        <v>231.66000000000003</v>
       </c>
       <c r="Q55" s="14">
-        <v>18.326848249027236</v>
+        <v>16.056140350877193</v>
       </c>
       <c r="R55" s="16">
-        <v>376.93333333333334</v>
+        <v>391.875</v>
       </c>
       <c r="S55" s="15">
-        <v>-28.666666666666629</v>
+        <v>-70.25</v>
       </c>
       <c r="T55" s="18">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="U55" s="17">
-        <v>378.27000000000004</v>
+        <v>363.69</v>
       </c>
       <c r="V55" s="14">
-        <v>16.405152224824356</v>
+        <v>16.1438202247191</v>
       </c>
       <c r="W55" s="16">
-        <v>626.26666666666665</v>
+        <v>611.875</v>
       </c>
       <c r="X55" s="15">
-        <v>40</v>
+        <v>31.8125</v>
       </c>
       <c r="Y55" s="18">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="Z55" s="17">
-        <v>123.93</v>
+        <v>105.30000000000001</v>
       </c>
       <c r="AA55" s="14">
-        <v>18.508064516129032</v>
+        <v>15.294117647058824</v>
       </c>
       <c r="AB55" s="16">
-        <v>181.86666666666667</v>
+        <v>187</v>
       </c>
       <c r="AC55" s="15">
-        <v>28.999999999999986</v>
+        <v>-40</v>
       </c>
       <c r="AD55" s="19">
-        <v>10603</v>
+        <v>10290</v>
       </c>
       <c r="AE55" s="20">
         <v>8588.43</v>
@@ -7113,34 +7115,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="F56" s="14">
-        <v>618.32000000000005</v>
+        <v>579.02</v>
       </c>
       <c r="G56" s="14">
-        <v>6.7686424474187383</v>
+        <v>6.4761904761904763</v>
       </c>
       <c r="H56" s="30">
-        <v>767.06666666666672</v>
+        <v>750.75</v>
       </c>
       <c r="I56" s="15">
-        <v>-112.66666666666669</v>
+        <v>-120.25</v>
       </c>
       <c r="J56" s="32">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="K56" s="13">
-        <v>1024.42</v>
+        <v>906.52</v>
       </c>
       <c r="L56" s="14">
-        <v>32.22527472527473</v>
+        <v>24.069565217391304</v>
       </c>
       <c r="M56" s="30">
-        <v>266.93333333333334</v>
+        <v>316.25</v>
       </c>
       <c r="N56" s="15">
-        <v>269.66666666666669</v>
+        <v>202.25</v>
       </c>
       <c r="O56" s="32">
         <v>19</v>
@@ -7149,46 +7151,46 @@
         <v>49.78</v>
       </c>
       <c r="Q56" s="14">
-        <v>6.7857142857142865</v>
+        <v>7.2380952380952381</v>
       </c>
       <c r="R56" s="16">
-        <v>61.599999999999994</v>
+        <v>57.75</v>
       </c>
       <c r="S56" s="15">
-        <v>-37</v>
+        <v>-33.5</v>
       </c>
       <c r="T56" s="18">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="U56" s="17">
-        <v>241.04000000000002</v>
+        <v>222.70000000000002</v>
       </c>
       <c r="V56" s="14">
-        <v>12.432432432432432</v>
+        <v>11.623931623931623</v>
       </c>
       <c r="W56" s="16">
-        <v>162.80000000000001</v>
+        <v>160.875</v>
       </c>
       <c r="X56" s="15">
-        <v>-19</v>
+        <v>-24.6875</v>
       </c>
       <c r="Y56" s="18">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z56" s="17">
-        <v>131</v>
+        <v>117.9</v>
       </c>
       <c r="AA56" s="14">
-        <v>24.193548387096772</v>
+        <v>23.225806451612904</v>
       </c>
       <c r="AB56" s="16">
-        <v>45.466666666666669</v>
+        <v>42.625</v>
       </c>
       <c r="AC56" s="15">
-        <v>18.999999999999996</v>
+        <v>6.25</v>
       </c>
       <c r="AD56" s="19">
-        <v>788</v>
+        <v>716</v>
       </c>
       <c r="AE56" s="20">
         <v>2064.56</v>
@@ -7226,34 +7228,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="F57" s="14">
-        <v>0</v>
+        <v>613.08000000000004</v>
       </c>
       <c r="G57" s="14">
-        <v>0</v>
+        <v>3.4634597594819612</v>
       </c>
       <c r="H57" s="30">
-        <v>1532.6666666666667</v>
+        <v>1486.375</v>
       </c>
       <c r="I57" s="15">
-        <v>-696.66666666666674</v>
+        <v>-441.625</v>
       </c>
       <c r="J57" s="32">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="K57" s="13">
-        <v>843.64</v>
+        <v>1066.3400000000001</v>
       </c>
       <c r="L57" s="14">
-        <v>11.5</v>
+        <v>13.235772357723578</v>
       </c>
       <c r="M57" s="30">
-        <v>616</v>
+        <v>676.5</v>
       </c>
       <c r="N57" s="15">
-        <v>42</v>
+        <v>99.5</v>
       </c>
       <c r="O57" s="32">
         <v>37</v>
@@ -7262,13 +7264,13 @@
         <v>96.94</v>
       </c>
       <c r="Q57" s="14">
-        <v>6.8518518518518512</v>
+        <v>7.3086419753086416</v>
       </c>
       <c r="R57" s="16">
-        <v>118.80000000000001</v>
+        <v>111.375</v>
       </c>
       <c r="S57" s="15">
-        <v>-71</v>
+        <v>-64.25</v>
       </c>
       <c r="T57" s="18">
         <v>0</v>
@@ -7280,10 +7282,10 @@
         <v>0</v>
       </c>
       <c r="W57" s="16">
-        <v>486.93333333333334</v>
+        <v>456.5</v>
       </c>
       <c r="X57" s="15">
-        <v>-332</v>
+        <v>-311.25</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7292,16 +7294,16 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>28.125</v>
+        <v>30</v>
       </c>
       <c r="AB57" s="16">
-        <v>46.93333333333333</v>
+        <v>44</v>
       </c>
       <c r="AC57" s="15">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AD57" s="19">
-        <v>419</v>
+        <v>738</v>
       </c>
       <c r="AE57" s="20">
         <v>1097.78</v>
@@ -7339,34 +7341,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="F58" s="14">
-        <v>395.62</v>
+        <v>324.88</v>
       </c>
       <c r="G58" s="14">
-        <v>6.0561497326203204</v>
+        <v>4.9108910891089108</v>
       </c>
       <c r="H58" s="30">
-        <v>548.5333333333333</v>
+        <v>555.5</v>
       </c>
       <c r="I58" s="15">
-        <v>-98.333333333333343</v>
+        <v>-128.5</v>
       </c>
       <c r="J58" s="32">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K58" s="13">
-        <v>330.12</v>
+        <v>298.68</v>
       </c>
       <c r="L58" s="14">
-        <v>12.945205479452056</v>
+        <v>11.4</v>
       </c>
       <c r="M58" s="30">
-        <v>214.13333333333333</v>
+        <v>220</v>
       </c>
       <c r="N58" s="15">
-        <v>28.666666666666671</v>
+        <v>14</v>
       </c>
       <c r="O58" s="32">
         <v>43</v>
@@ -7375,13 +7377,13 @@
         <v>112.66000000000001</v>
       </c>
       <c r="Q58" s="14">
-        <v>46.071428571428562</v>
+        <v>49.142857142857146</v>
       </c>
       <c r="R58" s="16">
-        <v>20.533333333333335</v>
+        <v>19.25</v>
       </c>
       <c r="S58" s="15">
-        <v>24.333333333333332</v>
+        <v>25.5</v>
       </c>
       <c r="T58" s="18">
         <v>52</v>
@@ -7390,13 +7392,13 @@
         <v>136.24</v>
       </c>
       <c r="V58" s="14">
-        <v>8.387096774193548</v>
+        <v>8.9462365591397841</v>
       </c>
       <c r="W58" s="16">
-        <v>136.4</v>
+        <v>127.875</v>
       </c>
       <c r="X58" s="15">
-        <v>-41</v>
+        <v>-35.1875</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7405,16 +7407,16 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>23.333333333333332</v>
+        <v>24.888888888888889</v>
       </c>
       <c r="AB58" s="16">
-        <v>39.6</v>
+        <v>37.125</v>
       </c>
       <c r="AC58" s="15">
-        <v>15</v>
+        <v>8.25</v>
       </c>
       <c r="AD58" s="19">
-        <v>414</v>
+        <v>375</v>
       </c>
       <c r="AE58" s="20">
         <v>1084.68</v>
@@ -7455,34 +7457,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>113</v>
+        <v>209</v>
       </c>
       <c r="F59" s="14">
-        <v>296.06</v>
+        <v>547.58000000000004</v>
       </c>
       <c r="G59" s="14">
-        <v>3.2785299806576402</v>
+        <v>6.1470588235294121</v>
       </c>
       <c r="H59" s="30">
-        <v>758.26666666666665</v>
+        <v>748</v>
       </c>
       <c r="I59" s="15">
-        <v>-231.66666666666669</v>
+        <v>-131</v>
       </c>
       <c r="J59" s="32">
-        <v>324</v>
+        <v>166</v>
       </c>
       <c r="K59" s="13">
-        <v>848.88</v>
+        <v>434.92</v>
       </c>
       <c r="L59" s="14">
-        <v>37.384615384615387</v>
+        <v>13.978947368421053</v>
       </c>
       <c r="M59" s="30">
-        <v>190.66666666666666</v>
+        <v>261.25</v>
       </c>
       <c r="N59" s="15">
-        <v>237.33333333333334</v>
+        <v>47.25</v>
       </c>
       <c r="O59" s="32">
         <v>24</v>
@@ -7491,28 +7493,28 @@
         <v>62.88</v>
       </c>
       <c r="Q59" s="14">
-        <v>12.413793103448276</v>
+        <v>13.241379310344827</v>
       </c>
       <c r="R59" s="16">
-        <v>42.533333333333331</v>
+        <v>39.875</v>
       </c>
       <c r="S59" s="15">
-        <v>-14.666666666666664</v>
+        <v>-12.25</v>
       </c>
       <c r="T59" s="18">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U59" s="17">
-        <v>117.9</v>
+        <v>102.18</v>
       </c>
       <c r="V59" s="14">
-        <v>7.03125</v>
+        <v>6.117647058823529</v>
       </c>
       <c r="W59" s="16">
-        <v>140.80000000000001</v>
+        <v>140.25</v>
       </c>
       <c r="X59" s="15">
-        <v>-51</v>
+        <v>-56.625</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7521,16 +7523,16 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>53</v>
+        <v>56.533333333333331</v>
       </c>
       <c r="AB59" s="16">
-        <v>22</v>
+        <v>20.625</v>
       </c>
       <c r="AC59" s="15">
-        <v>38</v>
+        <v>34.25</v>
       </c>
       <c r="AD59" s="19">
-        <v>559</v>
+        <v>491</v>
       </c>
       <c r="AE59" s="20">
         <v>1464.5800000000002</v>
@@ -7646,11 +7648,11 @@
       <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>129154.76999999999</v>
+        <v>161800.80000000002</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>28.589891067572839</v>
+        <v>35.816464592412196</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7688,11 +7690,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>228277.81</v>
+        <v>219600.30999999997</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>50.531913928104174</v>
+        <v>48.61104968330033</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7730,11 +7732,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>23911.099999999995</v>
+        <v>22806.939999999991</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.2929964902251845</v>
+        <v>5.048577998200682</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7772,11 +7774,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>58250.549999999988</v>
+        <v>52753.3</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>12.894427972936695</v>
+        <v>11.677548575673903</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7814,11 +7816,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>12155.550000000003</v>
+        <v>10860.509999999998</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.6907705411610827</v>
+        <v>2.4040985697879025</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7968,11 +7970,11 @@
       <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>96974</v>
+        <v>117119</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>29.247798286886233</v>
+        <v>33.948421842888656</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8009,11 +8011,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>166288</v>
+        <v>165257</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>50.153215104355169</v>
+        <v>47.901829323083788</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8051,11 +8053,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>18081</v>
+        <v>17221</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.4533116178067322</v>
+        <v>4.9917244217965102</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8093,11 +8095,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>42220</v>
+        <v>38389</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>12.733743515502473</v>
+        <v>11.127536660376647</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8135,11 +8137,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>7997</v>
+        <v>7005</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>2.4119314754493906</v>
+        <v>2.030487751854396</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8177,7 +8179,7 @@
       <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>331560</v>
+        <v>344991</v>
       </c>
       <c r="E75" s="69">
         <f>D75*100/D75</f>

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37916A4-34E4-4B13-AC73-B26C6553CA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE21835-B095-4FE2-93B1-C9BC69F65256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1183,6 +1183,7 @@
       <sheetName val="INVENTARIO NACIONAL 21-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1324,6 +1325,7 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1651,242 +1653,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2251,85 +2253,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>2636</v>
+        <v>1783</v>
       </c>
       <c r="F13" s="14">
-        <v>3584.96</v>
+        <v>2424.88</v>
       </c>
       <c r="G13" s="14">
-        <v>3.2921707907267193</v>
+        <v>2.2447604236095682</v>
       </c>
       <c r="H13" s="30">
-        <v>17615.125</v>
+        <v>17474.470588235294</v>
       </c>
       <c r="I13" s="15">
-        <v>-5370.875</v>
+        <v>-6159.9411764705874</v>
       </c>
       <c r="J13" s="16">
-        <v>3237</v>
+        <v>1319</v>
       </c>
       <c r="K13" s="13">
-        <v>4402.3200000000006</v>
+        <v>1793.8400000000001</v>
       </c>
       <c r="L13" s="14">
-        <v>12.152041295166589</v>
+        <v>5.261145002346316</v>
       </c>
       <c r="M13" s="30">
-        <v>5860.25</v>
+        <v>5515.5294117647063</v>
       </c>
       <c r="N13" s="15">
-        <v>573.25</v>
+        <v>-1188.0588235294117</v>
       </c>
       <c r="O13" s="16">
-        <v>637</v>
+        <v>992</v>
       </c>
       <c r="P13" s="17">
-        <v>866.32</v>
+        <v>1349.1200000000001</v>
       </c>
       <c r="Q13" s="14">
-        <v>13.571238348868176</v>
+        <v>20.845488257107537</v>
       </c>
       <c r="R13" s="16">
-        <v>1032.625</v>
+        <v>1046.9411764705883</v>
       </c>
       <c r="S13" s="15">
-        <v>-301.75</v>
+        <v>40.235294117646959</v>
       </c>
       <c r="T13" s="18">
-        <v>656</v>
+        <v>791</v>
       </c>
       <c r="U13" s="17">
-        <v>892.16000000000008</v>
+        <v>1075.76</v>
       </c>
       <c r="V13" s="14">
-        <v>14.280272108843537</v>
+        <v>16.458996328029372</v>
       </c>
       <c r="W13" s="16">
-        <v>1010.625</v>
+        <v>1057.294117647059</v>
       </c>
       <c r="X13" s="15">
-        <v>-33.0625</v>
+        <v>22.058823529411598</v>
       </c>
       <c r="Y13" s="18">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="Z13" s="17">
-        <v>146.88000000000002</v>
+        <v>102.00000000000001</v>
       </c>
       <c r="AA13" s="14">
-        <v>3.676595744680851</v>
+        <v>2.5653923541247488</v>
       </c>
       <c r="AB13" s="16">
-        <v>646.25</v>
+        <v>643.17647058823525</v>
       </c>
       <c r="AC13" s="15">
-        <v>-479.5</v>
+        <v>-568.17647058823525</v>
       </c>
       <c r="AD13" s="19">
-        <v>7274</v>
+        <v>4960</v>
       </c>
       <c r="AE13" s="20">
-        <v>9185.44</v>
+        <v>6745.6</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2374,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>640.75</v>
+        <v>603.05882352941171</v>
       </c>
       <c r="I14" s="15">
-        <v>-291.25</v>
+        <v>-274.11764705882354</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2389,25 +2391,25 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>342.375</v>
+        <v>322.23529411764707</v>
       </c>
       <c r="N14" s="15">
-        <v>-155.625</v>
+        <v>-146.47058823529414</v>
       </c>
       <c r="O14" s="16">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="P14" s="17">
-        <v>171.72</v>
+        <v>139.92000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>23.04</v>
+        <v>14.384615384615387</v>
       </c>
       <c r="R14" s="16">
-        <v>103.125</v>
+        <v>134.58823529411762</v>
       </c>
       <c r="S14" s="15">
-        <v>14.25</v>
+        <v>-34.352941176470566</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2416,13 +2418,13 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>4.1481481481481479</v>
+        <v>4.4074074074074074</v>
       </c>
       <c r="W14" s="16">
-        <v>37.125</v>
+        <v>34.941176470588232</v>
       </c>
       <c r="X14" s="15">
-        <v>-18.3125</v>
+        <v>-18.411764705882351</v>
       </c>
       <c r="Y14" s="18">
         <v>31</v>
@@ -2431,19 +2433,19 @@
         <v>49.29</v>
       </c>
       <c r="AA14" s="14">
-        <v>7.5151515151515156</v>
+        <v>7.9848484848484853</v>
       </c>
       <c r="AB14" s="16">
-        <v>90.75</v>
+        <v>85.411764705882348</v>
       </c>
       <c r="AC14" s="15">
-        <v>-51.5</v>
+        <v>-54.411764705882348</v>
       </c>
       <c r="AD14" s="19">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="AE14" s="20">
-        <v>232.14000000000001</v>
+        <v>200.34</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2479,85 +2481,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2285</v>
+        <v>1686</v>
       </c>
       <c r="F15" s="14">
-        <v>4638.5499999999993</v>
+        <v>3422.5799999999995</v>
       </c>
       <c r="G15" s="14">
-        <v>6.6739686016794453</v>
+        <v>4.982096297583869</v>
       </c>
       <c r="H15" s="30">
-        <v>7532.25</v>
+        <v>7445.0588235294126</v>
       </c>
       <c r="I15" s="15">
-        <v>-1138.75</v>
+        <v>-1698.1176470588239</v>
       </c>
       <c r="J15" s="16">
-        <v>1243</v>
+        <v>959</v>
       </c>
       <c r="K15" s="13">
-        <v>2523.29</v>
+        <v>1946.7699999999998</v>
       </c>
       <c r="L15" s="14">
-        <v>11.223476297968396</v>
+        <v>8.5088726513569934</v>
       </c>
       <c r="M15" s="30">
-        <v>2436.5</v>
+        <v>2479.5294117647059</v>
       </c>
       <c r="N15" s="15">
-        <v>135.5</v>
+        <v>-168.05882352941171</v>
       </c>
       <c r="O15" s="16">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="P15" s="17">
-        <v>499.37999999999994</v>
+        <v>466.9</v>
       </c>
       <c r="Q15" s="14">
-        <v>21.866666666666667</v>
+        <v>19.747474747474744</v>
       </c>
       <c r="R15" s="16">
-        <v>247.5</v>
+        <v>256.23529411764707</v>
       </c>
       <c r="S15" s="15">
-        <v>21</v>
+        <v>-2.9411764705882604</v>
       </c>
       <c r="T15" s="18">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="U15" s="17">
-        <v>373.52</v>
+        <v>481.10999999999996</v>
       </c>
       <c r="V15" s="14">
-        <v>13.026548672566372</v>
+        <v>15.616279069767442</v>
       </c>
       <c r="W15" s="16">
-        <v>310.75</v>
+        <v>333.88235294117646</v>
       </c>
       <c r="X15" s="15">
-        <v>-27.875</v>
+        <v>-5.8235294117646959</v>
       </c>
       <c r="Y15" s="18">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="Z15" s="17">
-        <v>251.71999999999997</v>
+        <v>235.48</v>
       </c>
       <c r="AA15" s="14">
-        <v>13.58904109589041</v>
+        <v>12.805194805194805</v>
       </c>
       <c r="AB15" s="16">
-        <v>200.75</v>
+        <v>199.29411764705881</v>
       </c>
       <c r="AC15" s="15">
-        <v>-58.5</v>
+        <v>-83.294117647058812</v>
       </c>
       <c r="AD15" s="19">
-        <v>4082</v>
+        <v>3228</v>
       </c>
       <c r="AE15" s="20">
-        <v>8168.7199999999993</v>
+        <v>6552.8399999999992</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2592,64 +2594,64 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="F16" s="14">
-        <v>989.14</v>
+        <v>678.68</v>
       </c>
       <c r="G16" s="14">
-        <v>3.7663230240549828</v>
+        <v>2.5547561950439648</v>
       </c>
       <c r="H16" s="30">
-        <v>1600.5</v>
+        <v>1618.9411764705883</v>
       </c>
       <c r="I16" s="15">
-        <v>-453.5</v>
+        <v>-547.88235294117658</v>
       </c>
       <c r="J16" s="16">
-        <v>174</v>
+        <v>41</v>
       </c>
       <c r="K16" s="13">
-        <v>628.14</v>
+        <v>148.01</v>
       </c>
       <c r="L16" s="14">
-        <v>6.3561643835616435</v>
+        <v>1.4861407249466949</v>
       </c>
       <c r="M16" s="30">
-        <v>602.25</v>
+        <v>606.94117647058829</v>
       </c>
       <c r="N16" s="15">
-        <v>-99.75</v>
+        <v>-234.88235294117646</v>
       </c>
       <c r="O16" s="16">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="P16" s="17">
-        <v>194.94</v>
+        <v>158.84</v>
       </c>
       <c r="Q16" s="14">
-        <v>25.411764705882351</v>
+        <v>17</v>
       </c>
       <c r="R16" s="16">
-        <v>46.75</v>
+        <v>56.941176470588239</v>
       </c>
       <c r="S16" s="15">
-        <v>11.5</v>
+        <v>-7.764705882352942</v>
       </c>
       <c r="T16" s="18">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="U16" s="17">
-        <v>180.5</v>
+        <v>166.06</v>
       </c>
       <c r="V16" s="14">
-        <v>57.142857142857146</v>
+        <v>55.857142857142861</v>
       </c>
       <c r="W16" s="16">
-        <v>19.25</v>
+        <v>18.117647058823529</v>
       </c>
       <c r="X16" s="15">
-        <v>36.875</v>
+        <v>32.82352941176471</v>
       </c>
       <c r="Y16" s="18">
         <v>25</v>
@@ -2658,19 +2660,19 @@
         <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>7.0175438596491224</v>
+        <v>7.4561403508771926</v>
       </c>
       <c r="AB16" s="16">
-        <v>78.375</v>
+        <v>73.764705882352942</v>
       </c>
       <c r="AC16" s="15">
-        <v>-46.25</v>
+        <v>-48.764705882352942</v>
       </c>
       <c r="AD16" s="19">
-        <v>577</v>
+        <v>344</v>
       </c>
       <c r="AE16" s="20">
-        <v>2342.89</v>
+        <v>1241.8399999999999</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2705,49 +2707,49 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F17" s="14">
-        <v>316.08</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="G17" s="14">
-        <v>3.7647058823529411</v>
+        <v>1.4406779661016949</v>
       </c>
       <c r="H17" s="30">
-        <v>210.375</v>
+        <v>229.05882352941177</v>
       </c>
       <c r="I17" s="15">
-        <v>-59.625</v>
+        <v>-89.117647058823536</v>
       </c>
       <c r="J17" s="16">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="K17" s="13">
-        <v>386.32</v>
+        <v>166.82</v>
       </c>
       <c r="L17" s="14">
-        <v>20.114285714285714</v>
+        <v>8.5</v>
       </c>
       <c r="M17" s="30">
-        <v>48.125</v>
+        <v>49.176470588235297</v>
       </c>
       <c r="N17" s="15">
-        <v>22.125</v>
+        <v>-3.352941176470587</v>
       </c>
       <c r="O17" s="16">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="P17" s="17">
-        <v>87.8</v>
+        <v>166.82</v>
       </c>
       <c r="Q17" s="14">
-        <v>20</v>
+        <v>29.363636363636363</v>
       </c>
       <c r="R17" s="16">
-        <v>11</v>
+        <v>14.23529411764706</v>
       </c>
       <c r="S17" s="15">
-        <v>0</v>
+        <v>6.0588235294117645</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2762,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="X17" s="15">
-        <v>15.636363636363637</v>
+        <v>15.545454545454545</v>
       </c>
       <c r="Y17" s="18">
         <v>8</v>
@@ -2771,19 +2773,19 @@
         <v>70.239999999999995</v>
       </c>
       <c r="AA17" s="14">
-        <v>14.222222222222221</v>
+        <v>15.111111111111111</v>
       </c>
       <c r="AB17" s="16">
-        <v>12.375</v>
+        <v>11.647058823529411</v>
       </c>
       <c r="AC17" s="15">
-        <v>-3.25</v>
+        <v>-3.6470588235294112</v>
       </c>
       <c r="AD17" s="19">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AE17" s="20">
-        <v>1079.9399999999998</v>
+        <v>684.83999999999992</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2818,85 +2820,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6820</v>
+        <v>7727</v>
       </c>
       <c r="F18" s="14">
-        <v>4296.6000000000004</v>
+        <v>4868.01</v>
       </c>
       <c r="G18" s="14">
-        <v>7.9806918744971842</v>
+        <v>9.2833215547703176</v>
       </c>
       <c r="H18" s="30">
-        <v>18800.375</v>
+        <v>18311.764705882353</v>
       </c>
       <c r="I18" s="15">
-        <v>-1725.625</v>
+        <v>-596.52941176470631</v>
       </c>
       <c r="J18" s="16">
-        <v>7304</v>
+        <v>4517</v>
       </c>
       <c r="K18" s="13">
-        <v>4601.5200000000004</v>
+        <v>2845.71</v>
       </c>
       <c r="L18" s="14">
-        <v>21.954536915273341</v>
+        <v>13.250905953408111</v>
       </c>
       <c r="M18" s="30">
-        <v>7319.125</v>
+        <v>7499.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>3977.125</v>
+        <v>1108.1764705882351</v>
       </c>
       <c r="O18" s="16">
-        <v>1084</v>
+        <v>1205</v>
       </c>
       <c r="P18" s="17">
-        <v>682.92</v>
+        <v>759.15</v>
       </c>
       <c r="Q18" s="14">
-        <v>18.529914529914532</v>
+        <v>21.654334038054969</v>
       </c>
       <c r="R18" s="16">
-        <v>1287</v>
+        <v>1224.2352941176471</v>
       </c>
       <c r="S18" s="15">
-        <v>-86</v>
+        <v>92.058823529411711</v>
       </c>
       <c r="T18" s="18">
-        <v>2039</v>
+        <v>2416</v>
       </c>
       <c r="U18" s="17">
-        <v>1284.57</v>
+        <v>1522.08</v>
       </c>
       <c r="V18" s="14">
-        <v>13.587671803415244</v>
+        <v>15.077826725403817</v>
       </c>
       <c r="W18" s="16">
-        <v>3301.375</v>
+        <v>3525.1764705882356</v>
       </c>
       <c r="X18" s="15">
-        <v>-211.9375</v>
+        <v>-147.76470588235316</v>
       </c>
       <c r="Y18" s="18">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="Z18" s="17">
-        <v>119.07000000000001</v>
+        <v>112.77</v>
       </c>
       <c r="AA18" s="14">
-        <v>13.380530973451327</v>
+        <v>13.230434782608695</v>
       </c>
       <c r="AB18" s="16">
-        <v>310.75</v>
+        <v>297.64705882352939</v>
       </c>
       <c r="AC18" s="15">
-        <v>-93.5</v>
+        <v>-118.64705882352939</v>
       </c>
       <c r="AD18" s="19">
-        <v>17436</v>
+        <v>16044</v>
       </c>
       <c r="AE18" s="20">
-        <v>8276.31</v>
+        <v>10107.719999999999</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2931,85 +2933,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>585</v>
+        <v>461</v>
       </c>
       <c r="F19" s="14">
-        <v>368.55</v>
+        <v>290.43</v>
       </c>
       <c r="G19" s="14">
-        <v>9.473684210526315</v>
+        <v>7.4496197718631176</v>
       </c>
       <c r="H19" s="30">
-        <v>1358.5</v>
+        <v>1361.4117647058824</v>
       </c>
       <c r="I19" s="15">
-        <v>-32.5</v>
+        <v>-157.82352941176475</v>
       </c>
       <c r="J19" s="16">
-        <v>417</v>
+        <v>199</v>
       </c>
       <c r="K19" s="13">
-        <v>262.70999999999998</v>
+        <v>125.37</v>
       </c>
       <c r="L19" s="14">
-        <v>7.3480176211453747</v>
+        <v>3.5093360995850622</v>
       </c>
       <c r="M19" s="30">
-        <v>1248.5</v>
+        <v>1247.5294117647059</v>
       </c>
       <c r="N19" s="15">
-        <v>-150.5</v>
+        <v>-368.05882352941171</v>
       </c>
       <c r="O19" s="16">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="P19" s="17">
-        <v>49.77</v>
+        <v>87.570000000000007</v>
       </c>
       <c r="Q19" s="14">
-        <v>16</v>
+        <v>29.911392405063289</v>
       </c>
       <c r="R19" s="16">
-        <v>108.625</v>
+        <v>102.23529411764707</v>
       </c>
       <c r="S19" s="15">
-        <v>-19.75</v>
+        <v>46.058823529411754</v>
       </c>
       <c r="T19" s="18">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="U19" s="17">
-        <v>146.79</v>
+        <v>143.01</v>
       </c>
       <c r="V19" s="14">
-        <v>19.216494845360824</v>
+        <v>17.701834862385319</v>
       </c>
       <c r="W19" s="16">
-        <v>266.75</v>
+        <v>282.11764705882354</v>
       </c>
       <c r="X19" s="15">
-        <v>51.125</v>
+        <v>21.823529411764696</v>
       </c>
       <c r="Y19" s="18">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="Z19" s="17">
-        <v>90.09</v>
+        <v>83.79</v>
       </c>
       <c r="AA19" s="14">
-        <v>13.458823529411765</v>
+        <v>12.994252873563219</v>
       </c>
       <c r="AB19" s="16">
-        <v>233.75</v>
+        <v>225.17647058823528</v>
       </c>
       <c r="AC19" s="15">
-        <v>-69.5</v>
+        <v>-92.176470588235276</v>
       </c>
       <c r="AD19" s="19">
-        <v>1457</v>
+        <v>1159</v>
       </c>
       <c r="AE19" s="20">
-        <v>1025.01</v>
+        <v>730.17</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3044,34 +3046,34 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1148</v>
+        <v>1117</v>
       </c>
       <c r="F20" s="14">
-        <v>723.24</v>
+        <v>703.71</v>
       </c>
       <c r="G20" s="14">
-        <v>8.7550047664442321</v>
+        <v>8.248913987836664</v>
       </c>
       <c r="H20" s="30">
-        <v>2884.75</v>
+        <v>2979.0588235294117</v>
       </c>
       <c r="I20" s="15">
-        <v>-163.25</v>
+        <v>-237.11764705882342</v>
       </c>
       <c r="J20" s="16">
-        <v>2672</v>
+        <v>2171</v>
       </c>
       <c r="K20" s="13">
-        <v>1683.36</v>
+        <v>1367.73</v>
       </c>
       <c r="L20" s="14">
-        <v>20.723218613669413</v>
+        <v>16.527989252127185</v>
       </c>
       <c r="M20" s="30">
-        <v>2836.625</v>
+        <v>2889.7647058823527</v>
       </c>
       <c r="N20" s="15">
-        <v>1382.625</v>
+        <v>857.47058823529414</v>
       </c>
       <c r="O20" s="16">
         <v>241</v>
@@ -3080,49 +3082,49 @@
         <v>151.83000000000001</v>
       </c>
       <c r="Q20" s="14">
-        <v>24.717948717948719</v>
+        <v>25.767295597484274</v>
       </c>
       <c r="R20" s="16">
-        <v>214.5</v>
+        <v>205.76470588235296</v>
       </c>
       <c r="S20" s="15">
-        <v>46</v>
+        <v>53.941176470588232</v>
       </c>
       <c r="T20" s="18">
-        <v>650</v>
+        <v>584</v>
       </c>
       <c r="U20" s="17">
-        <v>409.5</v>
+        <v>367.92</v>
       </c>
       <c r="V20" s="14">
-        <v>31.231231231231231</v>
+        <v>21.724288840262584</v>
       </c>
       <c r="W20" s="16">
-        <v>457.875</v>
+        <v>591.41176470588232</v>
       </c>
       <c r="X20" s="15">
-        <v>337.8125</v>
+        <v>153.88235294117652</v>
       </c>
       <c r="Y20" s="18">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="Z20" s="17">
-        <v>131.66999999999999</v>
+        <v>125.37</v>
       </c>
       <c r="AA20" s="14">
-        <v>15.553488372093023</v>
+        <v>15.447488584474886</v>
       </c>
       <c r="AB20" s="16">
-        <v>295.625</v>
+        <v>283.41176470588238</v>
       </c>
       <c r="AC20" s="15">
-        <v>-59.75</v>
+        <v>-84.411764705882376</v>
       </c>
       <c r="AD20" s="19">
-        <v>4920</v>
+        <v>4312</v>
       </c>
       <c r="AE20" s="20">
-        <v>2460.15</v>
+        <v>2716.56</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3157,85 +3159,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2322</v>
+        <v>2444</v>
       </c>
       <c r="F21" s="14">
-        <v>2530.98</v>
+        <v>2663.96</v>
       </c>
       <c r="G21" s="14">
-        <v>7.6224866639310624</v>
+        <v>7.8853672423609797</v>
       </c>
       <c r="H21" s="30">
-        <v>6701.75</v>
+        <v>6818.7058823529414</v>
       </c>
       <c r="I21" s="15">
-        <v>-724.25</v>
+        <v>-655.41176470588243</v>
       </c>
       <c r="J21" s="16">
-        <v>5240</v>
+        <v>3085</v>
       </c>
       <c r="K21" s="13">
-        <v>5711.6</v>
+        <v>3362.65</v>
       </c>
       <c r="L21" s="14">
-        <v>15.914958238420652</v>
+        <v>8.9710913445090661</v>
       </c>
       <c r="M21" s="30">
-        <v>7243.5</v>
+        <v>7565.411764705882</v>
       </c>
       <c r="N21" s="15">
-        <v>1947.5</v>
+        <v>-353.82352941176487</v>
       </c>
       <c r="O21" s="16">
-        <v>357</v>
+        <v>605</v>
       </c>
       <c r="P21" s="17">
-        <v>389.13000000000005</v>
+        <v>659.45</v>
       </c>
       <c r="Q21" s="14">
-        <v>13.070938215102975</v>
+        <v>22.118279569892476</v>
       </c>
       <c r="R21" s="16">
-        <v>600.875</v>
+        <v>601.76470588235293</v>
       </c>
       <c r="S21" s="15">
-        <v>-189.25</v>
+        <v>57.941176470588289</v>
       </c>
       <c r="T21" s="18">
-        <v>945</v>
+        <v>1234</v>
       </c>
       <c r="U21" s="17">
-        <v>1030.0500000000002</v>
+        <v>1345.0600000000002</v>
       </c>
       <c r="V21" s="14">
-        <v>12.342857142857143</v>
+        <v>15.643549589858315</v>
       </c>
       <c r="W21" s="16">
-        <v>1684.375</v>
+        <v>1735.4117647058822</v>
       </c>
       <c r="X21" s="15">
-        <v>-203.4375</v>
+        <v>-28.117647058823422</v>
       </c>
       <c r="Y21" s="18">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="Z21" s="17">
-        <v>241.98000000000002</v>
+        <v>224.54000000000002</v>
       </c>
       <c r="AA21" s="14">
-        <v>11.684210526315789</v>
+        <v>11.012578616352201</v>
       </c>
       <c r="AB21" s="16">
-        <v>418</v>
+        <v>411.52941176470591</v>
       </c>
       <c r="AC21" s="15">
-        <v>-158</v>
+        <v>-205.52941176470591</v>
       </c>
       <c r="AD21" s="19">
-        <v>9086</v>
+        <v>7574</v>
       </c>
       <c r="AE21" s="20">
-        <v>7979.89</v>
+        <v>8255.66</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3270,85 +3272,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1704</v>
+        <v>1395</v>
       </c>
       <c r="F22" s="14">
-        <v>1857.3600000000001</v>
+        <v>1520.5500000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>9.6305192511480051</v>
+        <v>7.6648351648351651</v>
       </c>
       <c r="H22" s="30">
-        <v>3892.625</v>
+        <v>4004</v>
       </c>
       <c r="I22" s="15">
-        <v>-65.375</v>
+        <v>-425</v>
       </c>
       <c r="J22" s="16">
-        <v>3682</v>
+        <v>3300</v>
       </c>
       <c r="K22" s="13">
-        <v>4013.38</v>
+        <v>3597.0000000000005</v>
       </c>
       <c r="L22" s="14">
-        <v>24.639063153492263</v>
+        <v>21.090225563909776</v>
       </c>
       <c r="M22" s="30">
-        <v>3287.625</v>
+        <v>3442.3529411764707</v>
       </c>
       <c r="N22" s="15">
-        <v>2187.625</v>
+        <v>1735.2941176470588</v>
       </c>
       <c r="O22" s="16">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="P22" s="17">
-        <v>151.51000000000002</v>
+        <v>140.61000000000001</v>
       </c>
       <c r="Q22" s="14">
-        <v>24.173913043478262</v>
+        <v>15.891304347826088</v>
       </c>
       <c r="R22" s="16">
-        <v>126.5</v>
+        <v>178.58823529411762</v>
       </c>
       <c r="S22" s="15">
-        <v>24</v>
+        <v>-33.35294117647058</v>
       </c>
       <c r="T22" s="18">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="U22" s="17">
-        <v>416.38000000000005</v>
+        <v>445.81000000000006</v>
       </c>
       <c r="V22" s="14">
-        <v>16.342245989304814</v>
+        <v>16.673860911270978</v>
       </c>
       <c r="W22" s="16">
-        <v>514.25</v>
+        <v>539.64705882352951</v>
       </c>
       <c r="X22" s="15">
-        <v>31.375</v>
+        <v>16.529411764705799</v>
       </c>
       <c r="Y22" s="18">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="Z22" s="17">
-        <v>126.44000000000001</v>
+        <v>116.63000000000001</v>
       </c>
       <c r="AA22" s="14">
-        <v>22.095238095238095</v>
+        <v>19.771739130434781</v>
       </c>
       <c r="AB22" s="16">
-        <v>115.5</v>
+        <v>119.05882352941177</v>
       </c>
       <c r="AC22" s="15">
-        <v>11</v>
+        <v>-12.058823529411768</v>
       </c>
       <c r="AD22" s="19">
-        <v>6023</v>
+        <v>5340</v>
       </c>
       <c r="AE22" s="20">
-        <v>4403.6000000000004</v>
+        <v>5820.6</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3383,85 +3385,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>20949</v>
+        <v>21486</v>
       </c>
       <c r="F23" s="14">
-        <v>24300.839999999997</v>
+        <v>24923.759999999998</v>
       </c>
       <c r="G23" s="14">
-        <v>12.752882091085493</v>
+        <v>12.97740353869111</v>
       </c>
       <c r="H23" s="30">
-        <v>36139.125</v>
+        <v>36424.23529411765</v>
       </c>
       <c r="I23" s="15">
-        <v>-3691.3125</v>
+        <v>-3348.7058823529442</v>
       </c>
       <c r="J23" s="16">
-        <v>23090</v>
+        <v>14839</v>
       </c>
       <c r="K23" s="13">
-        <v>26784.399999999998</v>
+        <v>17213.239999999998</v>
       </c>
       <c r="L23" s="14">
-        <v>24.390308311876939</v>
+        <v>15.209393464367539</v>
       </c>
       <c r="M23" s="30">
-        <v>20827.125</v>
+        <v>21464.235294117647</v>
       </c>
       <c r="N23" s="15">
-        <v>13623.125</v>
+        <v>5082.5294117647063</v>
       </c>
       <c r="O23" s="16">
-        <v>2110</v>
+        <v>3044</v>
       </c>
       <c r="P23" s="17">
-        <v>2447.6</v>
+        <v>3531.04</v>
       </c>
       <c r="Q23" s="14">
-        <v>14.090150250417363</v>
+        <v>20.649640861931367</v>
       </c>
       <c r="R23" s="16">
-        <v>3294.5</v>
+        <v>3243.0588235294117</v>
       </c>
       <c r="S23" s="15">
-        <v>-885</v>
+        <v>95.764705882353155</v>
       </c>
       <c r="T23" s="18">
-        <v>6887</v>
+        <v>8360</v>
       </c>
       <c r="U23" s="17">
-        <v>7988.9199999999992</v>
+        <v>9697.5999999999985</v>
       </c>
       <c r="V23" s="14">
-        <v>12.799628295969335</v>
+        <v>14.861445153194605</v>
       </c>
       <c r="W23" s="16">
-        <v>11837.375</v>
+        <v>12375.647058823528</v>
       </c>
       <c r="X23" s="15">
-        <v>-1183.9375</v>
+        <v>-640.47058823529369</v>
       </c>
       <c r="Y23" s="18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="17">
-        <v>15.079999999999998</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AA23" s="14">
-        <v>0.23059866962305986</v>
+        <v>1.8660812294182216E-2</v>
       </c>
       <c r="AB23" s="16">
-        <v>1240.25</v>
+        <v>1178.9411764705883</v>
       </c>
       <c r="AC23" s="15">
-        <v>-1114.5</v>
+        <v>-1177.9411764705883</v>
       </c>
       <c r="AD23" s="19">
-        <v>53049</v>
+        <v>47730</v>
       </c>
       <c r="AE23" s="20">
-        <v>56496.639999999999</v>
+        <v>55366.799999999996</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3496,85 +3498,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>10278</v>
+        <v>8777</v>
       </c>
       <c r="F24" s="14">
-        <v>11922.48</v>
+        <v>10181.32</v>
       </c>
       <c r="G24" s="14">
-        <v>9.3681212259314108</v>
+        <v>8.0371128467546455</v>
       </c>
       <c r="H24" s="30">
-        <v>24136.75</v>
+        <v>24025.294117647056</v>
       </c>
       <c r="I24" s="15">
-        <v>-693.25</v>
+        <v>-2143.5882352941171</v>
       </c>
       <c r="J24" s="16">
-        <v>8070</v>
+        <v>13886</v>
       </c>
       <c r="K24" s="13">
-        <v>9361.1999999999989</v>
+        <v>16107.759999999998</v>
       </c>
       <c r="L24" s="14">
-        <v>13.961937716262975</v>
+        <v>23.458412004372452</v>
       </c>
       <c r="M24" s="30">
-        <v>12716</v>
+        <v>13022.705882352942</v>
       </c>
       <c r="N24" s="15">
-        <v>2290</v>
+        <v>7966.5882352941171</v>
       </c>
       <c r="O24" s="16">
-        <v>1292</v>
+        <v>1743</v>
       </c>
       <c r="P24" s="17">
-        <v>1498.7199999999998</v>
+        <v>2021.8799999999999</v>
       </c>
       <c r="Q24" s="14">
-        <v>14.925631768953069</v>
+        <v>19.940107671601616</v>
       </c>
       <c r="R24" s="16">
-        <v>1904.375</v>
+        <v>1923.0588235294117</v>
       </c>
       <c r="S24" s="15">
-        <v>-439.25</v>
+        <v>-5.2352941176468448</v>
       </c>
       <c r="T24" s="18">
-        <v>3881</v>
+        <v>4623</v>
       </c>
       <c r="U24" s="17">
-        <v>4501.96</v>
+        <v>5362.6799999999994</v>
       </c>
       <c r="V24" s="14">
-        <v>13.56993006993007</v>
+        <v>15.699360767079503</v>
       </c>
       <c r="W24" s="16">
-        <v>6292</v>
+        <v>6478.3529411764712</v>
       </c>
       <c r="X24" s="15">
-        <v>-409</v>
+        <v>-88.52941176470631</v>
       </c>
       <c r="Y24" s="18">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="Z24" s="17">
-        <v>415.28</v>
+        <v>345.67999999999995</v>
       </c>
       <c r="AA24" s="14">
-        <v>9.6430976430976436</v>
+        <v>7.965408805031446</v>
       </c>
       <c r="AB24" s="16">
-        <v>816.75</v>
+        <v>823.05882352941182</v>
       </c>
       <c r="AC24" s="15">
-        <v>-384.5</v>
+        <v>-525.05882352941182</v>
       </c>
       <c r="AD24" s="19">
-        <v>23879</v>
+        <v>29327</v>
       </c>
       <c r="AE24" s="20">
-        <v>27860.879999999997</v>
+        <v>34019.32</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3609,85 +3611,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>5823</v>
+        <v>9487</v>
       </c>
       <c r="F25" s="14">
-        <v>6754.6799999999994</v>
+        <v>11004.92</v>
       </c>
       <c r="G25" s="14">
-        <v>5.4091964700418025</v>
+        <v>8.9212855404358891</v>
       </c>
       <c r="H25" s="30">
-        <v>23683</v>
+        <v>23395.058823529413</v>
       </c>
       <c r="I25" s="15">
-        <v>-4942</v>
+        <v>-1147.1176470588252</v>
       </c>
       <c r="J25" s="16">
-        <v>18060</v>
+        <v>10090</v>
       </c>
       <c r="K25" s="13">
-        <v>20949.599999999999</v>
+        <v>11704.4</v>
       </c>
       <c r="L25" s="14">
-        <v>29.076272891929968</v>
+        <v>15.907446907168692</v>
       </c>
       <c r="M25" s="30">
-        <v>13664.75</v>
+        <v>13954.470588235294</v>
       </c>
       <c r="N25" s="15">
-        <v>11848.75</v>
+        <v>3747.0588235294126</v>
       </c>
       <c r="O25" s="16">
-        <v>1537</v>
+        <v>2157</v>
       </c>
       <c r="P25" s="17">
-        <v>1782.9199999999998</v>
+        <v>2502.12</v>
       </c>
       <c r="Q25" s="14">
-        <v>14.465882352941177</v>
+        <v>20.417037861915368</v>
       </c>
       <c r="R25" s="16">
-        <v>2337.5</v>
+        <v>2324.2352941176468</v>
       </c>
       <c r="S25" s="15">
-        <v>-588</v>
+        <v>44.058823529411711</v>
       </c>
       <c r="T25" s="18">
-        <v>3739</v>
+        <v>4700</v>
       </c>
       <c r="U25" s="17">
-        <v>4337.24</v>
+        <v>5452</v>
       </c>
       <c r="V25" s="14">
-        <v>12.802054354804195</v>
+        <v>15.648256952604777</v>
       </c>
       <c r="W25" s="16">
-        <v>6425.375</v>
+        <v>6607.7647058823532</v>
       </c>
       <c r="X25" s="15">
-        <v>-641.9375</v>
+        <v>-105.64705882352973</v>
       </c>
       <c r="Y25" s="18">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="Z25" s="17">
-        <v>617.12</v>
+        <v>593.91999999999996</v>
       </c>
       <c r="AA25" s="14">
-        <v>18.915555555555557</v>
+        <v>19.256637168141591</v>
       </c>
       <c r="AB25" s="16">
-        <v>618.75</v>
+        <v>584.94117647058829</v>
       </c>
       <c r="AC25" s="15">
-        <v>-30.5</v>
+        <v>-72.941176470588289</v>
       </c>
       <c r="AD25" s="19">
-        <v>29691</v>
+        <v>26946</v>
       </c>
       <c r="AE25" s="20">
-        <v>36763.879999999997</v>
+        <v>31257.359999999997</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3722,85 +3724,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>19042</v>
+        <v>16443</v>
       </c>
       <c r="F26" s="14">
-        <v>22088.719999999998</v>
+        <v>19073.879999999997</v>
       </c>
       <c r="G26" s="14">
-        <v>13.756806790987493</v>
+        <v>11.838514314755209</v>
       </c>
       <c r="H26" s="30">
-        <v>30452.125</v>
+        <v>30556.705882352944</v>
       </c>
       <c r="I26" s="15">
-        <v>-1720.8125</v>
+        <v>-4391.1176470588252</v>
       </c>
       <c r="J26" s="16">
-        <v>18459</v>
+        <v>13264</v>
       </c>
       <c r="K26" s="13">
-        <v>21412.44</v>
+        <v>15386.24</v>
       </c>
       <c r="L26" s="14">
-        <v>25.588632819268756</v>
+        <v>17.836418288245532</v>
       </c>
       <c r="M26" s="30">
-        <v>15870.25</v>
+        <v>16360.235294117647</v>
       </c>
       <c r="N26" s="15">
-        <v>11245.25</v>
+        <v>5827.5294117647063</v>
       </c>
       <c r="O26" s="16">
-        <v>1361</v>
+        <v>1693</v>
       </c>
       <c r="P26" s="17">
-        <v>1578.76</v>
+        <v>1963.8799999999999</v>
       </c>
       <c r="Q26" s="14">
-        <v>16.50947687642153</v>
+        <v>20.239803094233476</v>
       </c>
       <c r="R26" s="16">
-        <v>1813.625</v>
+        <v>1840.2352941176468</v>
       </c>
       <c r="S26" s="15">
-        <v>-287.75</v>
+        <v>20.058823529411939</v>
       </c>
       <c r="T26" s="18">
-        <v>4254</v>
+        <v>5575</v>
       </c>
       <c r="U26" s="17">
-        <v>4934.6399999999994</v>
+        <v>6467</v>
       </c>
       <c r="V26" s="14">
-        <v>11.876461350549642</v>
+        <v>14.799344159900061</v>
       </c>
       <c r="W26" s="16">
-        <v>7880.125</v>
+        <v>8287.5294117647063</v>
       </c>
       <c r="X26" s="15">
-        <v>-1118.8125</v>
+        <v>-452.29411764705947</v>
       </c>
       <c r="Y26" s="18">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="Z26" s="17">
-        <v>518.52</v>
+        <v>457.03999999999996</v>
       </c>
       <c r="AA26" s="14">
-        <v>10.471449487554905</v>
+        <v>9.3417015341701521</v>
       </c>
       <c r="AB26" s="16">
-        <v>939.125</v>
+        <v>927.88235294117658</v>
       </c>
       <c r="AC26" s="15">
-        <v>-406.75</v>
+        <v>-533.88235294117658</v>
       </c>
       <c r="AD26" s="19">
-        <v>43563</v>
+        <v>37369</v>
       </c>
       <c r="AE26" s="20">
-        <v>47456.759999999995</v>
+        <v>43348.039999999994</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3835,85 +3837,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>893</v>
+        <v>2716</v>
       </c>
       <c r="F27" s="14">
-        <v>1035.8799999999999</v>
+        <v>3150.56</v>
       </c>
       <c r="G27" s="14">
-        <v>2.5459729151817534</v>
+        <v>7.6254335260115607</v>
       </c>
       <c r="H27" s="30">
-        <v>7716.5</v>
+        <v>7835.8823529411766</v>
       </c>
       <c r="I27" s="15">
-        <v>-2614.5</v>
+        <v>-845.76470588235316</v>
       </c>
       <c r="J27" s="16">
-        <v>6413</v>
+        <v>4705</v>
       </c>
       <c r="K27" s="13">
-        <v>7439.08</v>
+        <v>5457.7999999999993</v>
       </c>
       <c r="L27" s="14">
-        <v>32.307304785894203</v>
+        <v>23.545775684427436</v>
       </c>
       <c r="M27" s="30">
-        <v>4367</v>
+        <v>4396.1176470588234</v>
       </c>
       <c r="N27" s="15">
-        <v>4428</v>
+        <v>2706.7647058823532</v>
       </c>
       <c r="O27" s="16">
-        <v>264</v>
+        <v>628</v>
       </c>
       <c r="P27" s="17">
-        <v>306.23999999999995</v>
+        <v>728.4799999999999</v>
       </c>
       <c r="Q27" s="14">
-        <v>9.0838709677419356</v>
+        <v>21.309381237524953</v>
       </c>
       <c r="R27" s="16">
-        <v>639.375</v>
+        <v>648.35294117647049</v>
       </c>
       <c r="S27" s="15">
-        <v>-317.25</v>
+        <v>38.588235294117794</v>
       </c>
       <c r="T27" s="18">
-        <v>897</v>
+        <v>1890</v>
       </c>
       <c r="U27" s="17">
-        <v>1040.52</v>
+        <v>2192.3999999999996</v>
       </c>
       <c r="V27" s="14">
-        <v>7.6913183279742769</v>
+        <v>15.657894736842106</v>
       </c>
       <c r="W27" s="16">
-        <v>2565.75</v>
+        <v>2655.5294117647059</v>
       </c>
       <c r="X27" s="15">
-        <v>-852.375</v>
+        <v>-41.294117647058783</v>
       </c>
       <c r="Y27" s="18">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="Z27" s="17">
-        <v>463.99999999999994</v>
+        <v>454.71999999999997</v>
       </c>
       <c r="AA27" s="14">
-        <v>31.372549019607842</v>
+        <v>32.349514563106794</v>
       </c>
       <c r="AB27" s="16">
-        <v>280.5</v>
+        <v>266.58823529411762</v>
       </c>
       <c r="AC27" s="15">
-        <v>145</v>
+        <v>125.41176470588238</v>
       </c>
       <c r="AD27" s="19">
-        <v>8867</v>
+        <v>10331</v>
       </c>
       <c r="AE27" s="20">
-        <v>10935.32</v>
+        <v>11983.96</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3948,85 +3950,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>1141</v>
+        <v>2342</v>
       </c>
       <c r="F28" s="14">
-        <v>1323.56</v>
+        <v>2716.72</v>
       </c>
       <c r="G28" s="14">
-        <v>3.3180661577608141</v>
+        <v>6.5429745275267051</v>
       </c>
       <c r="H28" s="30">
-        <v>7565.25</v>
+        <v>7874.7058823529414</v>
       </c>
       <c r="I28" s="15">
-        <v>-2297.75</v>
+        <v>-1237.4117647058824</v>
       </c>
       <c r="J28" s="16">
-        <v>5543</v>
+        <v>7242</v>
       </c>
       <c r="K28" s="13">
-        <v>6429.8799999999992</v>
+        <v>8400.7199999999993</v>
       </c>
       <c r="L28" s="14">
-        <v>20.304029304029303</v>
+        <v>25.793840351979888</v>
       </c>
       <c r="M28" s="30">
-        <v>6006</v>
+        <v>6176.823529411764</v>
       </c>
       <c r="N28" s="15">
-        <v>2813</v>
+        <v>4434.3529411764703</v>
       </c>
       <c r="O28" s="16">
-        <v>306</v>
+        <v>821</v>
       </c>
       <c r="P28" s="17">
-        <v>354.96</v>
+        <v>952.3599999999999</v>
       </c>
       <c r="Q28" s="14">
-        <v>7.821086261980831</v>
+        <v>20.464809384164223</v>
       </c>
       <c r="R28" s="16">
-        <v>860.75</v>
+        <v>882.58823529411768</v>
       </c>
       <c r="S28" s="15">
-        <v>-476.5</v>
+        <v>18.647058823529392</v>
       </c>
       <c r="T28" s="18">
-        <v>492</v>
+        <v>2205</v>
       </c>
       <c r="U28" s="17">
-        <v>570.71999999999991</v>
+        <v>2557.7999999999997</v>
       </c>
       <c r="V28" s="14">
-        <v>3.5994513031550071</v>
+        <v>15.3125</v>
       </c>
       <c r="W28" s="16">
-        <v>3007.125</v>
+        <v>3168</v>
       </c>
       <c r="X28" s="15">
-        <v>-1558.3125</v>
+        <v>-99</v>
       </c>
       <c r="Y28" s="18">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="Z28" s="17">
-        <v>358.44</v>
+        <v>352.64</v>
       </c>
       <c r="AA28" s="14">
-        <v>16.989690721649485</v>
+        <v>17.638225255972696</v>
       </c>
       <c r="AB28" s="16">
-        <v>400.125</v>
+        <v>379.17647058823525</v>
       </c>
       <c r="AC28" s="15">
-        <v>-54.75</v>
+        <v>-75.176470588235247</v>
       </c>
       <c r="AD28" s="19">
-        <v>7791</v>
+        <v>12914</v>
       </c>
       <c r="AE28" s="20">
-        <v>10216.119999999999</v>
+        <v>14980.24</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4061,85 +4063,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>908</v>
+        <v>2489</v>
       </c>
       <c r="F29" s="14">
-        <v>1053.28</v>
+        <v>2887.24</v>
       </c>
       <c r="G29" s="14">
-        <v>2.4221407135711903</v>
+        <v>6.4600000000000009</v>
       </c>
       <c r="H29" s="30">
-        <v>8247.25</v>
+        <v>8476.4705882352937</v>
       </c>
       <c r="I29" s="15">
-        <v>-2840.75</v>
+        <v>-1363.9411764705878</v>
       </c>
       <c r="J29" s="16">
-        <v>5284</v>
+        <v>696</v>
       </c>
       <c r="K29" s="13">
-        <v>6129.44</v>
+        <v>807.3599999999999</v>
       </c>
       <c r="L29" s="14">
-        <v>19.080117354998873</v>
+        <v>2.5571644694186295</v>
       </c>
       <c r="M29" s="30">
-        <v>6092.625</v>
+        <v>5987.8823529411766</v>
       </c>
       <c r="N29" s="15">
-        <v>2514.625</v>
+        <v>-2025.7647058823532</v>
       </c>
       <c r="O29" s="16">
-        <v>209</v>
+        <v>832</v>
       </c>
       <c r="P29" s="17">
-        <v>242.43999999999997</v>
+        <v>965.11999999999989</v>
       </c>
       <c r="Q29" s="14">
-        <v>5.1925465838509313</v>
+        <v>20.205714285714283</v>
       </c>
       <c r="R29" s="16">
-        <v>885.5</v>
+        <v>905.88235294117658</v>
       </c>
       <c r="S29" s="15">
-        <v>-596</v>
+        <v>8.4705882352940307</v>
       </c>
       <c r="T29" s="18">
-        <v>297</v>
+        <v>1513</v>
       </c>
       <c r="U29" s="17">
-        <v>344.52</v>
+        <v>1755.08</v>
       </c>
       <c r="V29" s="14">
-        <v>2.0465116279069768</v>
+        <v>10.288399999999999</v>
       </c>
       <c r="W29" s="16">
-        <v>3192.75</v>
+        <v>3235.294117647059</v>
       </c>
       <c r="X29" s="15">
-        <v>-1879.875</v>
+        <v>-839.94117647058829</v>
       </c>
       <c r="Y29" s="18">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="Z29" s="17">
-        <v>377</v>
+        <v>371.2</v>
       </c>
       <c r="AA29" s="14">
-        <v>18.637992831541219</v>
+        <v>19.359430604982204</v>
       </c>
       <c r="AB29" s="16">
-        <v>383.625</v>
+        <v>363.64705882352945</v>
       </c>
       <c r="AC29" s="15">
-        <v>-23.75</v>
+        <v>-43.647058823529449</v>
       </c>
       <c r="AD29" s="19">
-        <v>7023</v>
+        <v>5850</v>
       </c>
       <c r="AE29" s="20">
-        <v>3410.3999999999996</v>
+        <v>6785.9999999999991</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4174,85 +4176,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>502</v>
+        <v>141</v>
       </c>
       <c r="F30" s="14">
-        <v>1847.3600000000001</v>
+        <v>518.88</v>
       </c>
       <c r="G30" s="14">
-        <v>5.0452261306532664</v>
+        <v>1.3069792802617233</v>
       </c>
       <c r="H30" s="30">
-        <v>2189</v>
+        <v>2373.411764705882</v>
       </c>
       <c r="I30" s="15">
-        <v>-493</v>
+        <v>-937.82352941176441</v>
       </c>
       <c r="J30" s="16">
-        <v>897</v>
+        <v>211</v>
       </c>
       <c r="K30" s="13">
-        <v>3300.96</v>
+        <v>776.48</v>
       </c>
       <c r="L30" s="14">
-        <v>7.2302267002518894</v>
+        <v>1.6785212915301826</v>
       </c>
       <c r="M30" s="30">
-        <v>2729.375</v>
+        <v>2765.5294117647059</v>
       </c>
       <c r="N30" s="15">
-        <v>-343.625</v>
+        <v>-1046.0588235294117</v>
       </c>
       <c r="O30" s="16">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="P30" s="17">
-        <v>161.92000000000002</v>
+        <v>496.8</v>
       </c>
       <c r="Q30" s="14">
-        <v>6.9702970297029703</v>
+        <v>21.055045871559631</v>
       </c>
       <c r="R30" s="16">
-        <v>138.875</v>
+        <v>141.05882352941177</v>
       </c>
       <c r="S30" s="15">
-        <v>-82.25</v>
+        <v>6.7647058823529278</v>
       </c>
       <c r="T30" s="18">
-        <v>284</v>
+        <v>486</v>
       </c>
       <c r="U30" s="17">
-        <v>1045.1200000000001</v>
+        <v>1788.48</v>
       </c>
       <c r="V30" s="14">
-        <v>9.5663157894736841</v>
+        <v>16.524000000000001</v>
       </c>
       <c r="W30" s="16">
-        <v>653.125</v>
+        <v>647.05882352941171</v>
       </c>
       <c r="X30" s="15">
-        <v>-161.3125</v>
+        <v>15.411764705882376</v>
       </c>
       <c r="Y30" s="18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="17">
-        <v>44.160000000000004</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="14">
-        <v>2.1098901098901099</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="16">
-        <v>125.125</v>
+        <v>120.35294117647059</v>
       </c>
       <c r="AC30" s="15">
-        <v>-101.75</v>
+        <v>-120.35294117647059</v>
       </c>
       <c r="AD30" s="19">
-        <v>1739</v>
+        <v>973</v>
       </c>
       <c r="AE30" s="20">
-        <v>7934.08</v>
+        <v>3580.6400000000003</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4287,64 +4289,64 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="F31" s="14">
-        <v>1162.8800000000001</v>
+        <v>1258.56</v>
       </c>
       <c r="G31" s="14">
-        <v>6.7234042553191493</v>
+        <v>7.0132689987937287</v>
       </c>
       <c r="H31" s="30">
-        <v>1034</v>
+        <v>1072.8235294117646</v>
       </c>
       <c r="I31" s="15">
-        <v>-154</v>
+        <v>-145.64705882352933</v>
       </c>
       <c r="J31" s="16">
-        <v>777</v>
+        <v>503</v>
       </c>
       <c r="K31" s="13">
-        <v>2859.36</v>
+        <v>1851.0400000000002</v>
       </c>
       <c r="L31" s="14">
-        <v>11.395050412465627</v>
+        <v>7.0903814262023221</v>
       </c>
       <c r="M31" s="30">
-        <v>1500.125</v>
+        <v>1560.705882352941</v>
       </c>
       <c r="N31" s="15">
-        <v>95.125</v>
+        <v>-206.41176470588232</v>
       </c>
       <c r="O31" s="16">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P31" s="17">
-        <v>136.16</v>
+        <v>125.12</v>
       </c>
       <c r="Q31" s="14">
-        <v>59.2</v>
+        <v>32.111111111111114</v>
       </c>
       <c r="R31" s="16">
-        <v>13.75</v>
+        <v>23.294117647058822</v>
       </c>
       <c r="S31" s="15">
-        <v>24.5</v>
+        <v>12.823529411764707</v>
       </c>
       <c r="T31" s="18">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="U31" s="17">
-        <v>500.48</v>
+        <v>526.24</v>
       </c>
       <c r="V31" s="14">
-        <v>15.883211678832117</v>
+        <v>16.425675675675677</v>
       </c>
       <c r="W31" s="16">
-        <v>188.375</v>
+        <v>191.52941176470586</v>
       </c>
       <c r="X31" s="15">
-        <v>7.5625</v>
+        <v>3.7058823529411882</v>
       </c>
       <c r="Y31" s="18">
         <v>44</v>
@@ -4353,19 +4355,19 @@
         <v>161.92000000000002</v>
       </c>
       <c r="AA31" s="14">
-        <v>29.333333333333332</v>
+        <v>31.166666666666664</v>
       </c>
       <c r="AB31" s="16">
-        <v>33</v>
+        <v>31.058823529411768</v>
       </c>
       <c r="AC31" s="15">
-        <v>14</v>
+        <v>12.941176470588232</v>
       </c>
       <c r="AD31" s="19">
-        <v>1310</v>
+        <v>1066</v>
       </c>
       <c r="AE31" s="20">
-        <v>5902.72</v>
+        <v>3922.88</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4400,64 +4402,64 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1488</v>
+        <v>1687</v>
       </c>
       <c r="F32" s="14">
-        <v>6175.2000000000007</v>
+        <v>7001.05</v>
       </c>
       <c r="G32" s="14">
-        <v>6.725423728813559</v>
+        <v>7.5253214379427966</v>
       </c>
       <c r="H32" s="30">
-        <v>4867.5</v>
+        <v>4931.8823529411766</v>
       </c>
       <c r="I32" s="15">
-        <v>-724.5</v>
+        <v>-554.76470588235316</v>
       </c>
       <c r="J32" s="16">
-        <v>1930</v>
+        <v>395</v>
       </c>
       <c r="K32" s="13">
-        <v>8009.5000000000009</v>
+        <v>1639.2500000000002</v>
       </c>
       <c r="L32" s="14">
-        <v>10.655624568668047</v>
+        <v>2.0912488321395206</v>
       </c>
       <c r="M32" s="30">
-        <v>3984.75</v>
+        <v>4155.411764705882</v>
       </c>
       <c r="N32" s="15">
-        <v>118.75</v>
+        <v>-1493.8235294117646</v>
       </c>
       <c r="O32" s="16">
-        <v>141</v>
+        <v>289</v>
       </c>
       <c r="P32" s="17">
-        <v>585.15000000000009</v>
+        <v>1199.3500000000001</v>
       </c>
       <c r="Q32" s="14">
-        <v>9.9383259911894282</v>
+        <v>19.971544715447155</v>
       </c>
       <c r="R32" s="16">
-        <v>312.125</v>
+        <v>318.35294117647061</v>
       </c>
       <c r="S32" s="15">
-        <v>-142.75</v>
+        <v>-0.41176470588237635</v>
       </c>
       <c r="T32" s="18">
-        <v>811</v>
+        <v>1290</v>
       </c>
       <c r="U32" s="17">
-        <v>3365.65</v>
+        <v>5353.5000000000009</v>
       </c>
       <c r="V32" s="14">
-        <v>10.090202177293934</v>
+        <v>15.389473684210525</v>
       </c>
       <c r="W32" s="16">
-        <v>1768.25</v>
+        <v>1844.1176470588236</v>
       </c>
       <c r="X32" s="15">
-        <v>-394.625</v>
+        <v>-51.176470588235361</v>
       </c>
       <c r="Y32" s="18">
         <v>283</v>
@@ -4466,19 +4468,19 @@
         <v>1174.45</v>
       </c>
       <c r="AA32" s="14">
-        <v>67.582089552238813</v>
+        <v>71.805970149253724</v>
       </c>
       <c r="AB32" s="16">
-        <v>92.125</v>
+        <v>86.705882352941188</v>
       </c>
       <c r="AC32" s="15">
-        <v>199.25</v>
+        <v>196.29411764705881</v>
       </c>
       <c r="AD32" s="19">
-        <v>4653</v>
+        <v>3944</v>
       </c>
       <c r="AE32" s="20">
-        <v>21580.000000000004</v>
+        <v>16367.600000000002</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4513,85 +4515,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3223</v>
+        <v>3021</v>
       </c>
       <c r="F33" s="14">
-        <v>13375.45</v>
+        <v>12537.150000000001</v>
       </c>
       <c r="G33" s="14">
-        <v>7.4509463950296198</v>
+        <v>6.8284802552852009</v>
       </c>
       <c r="H33" s="30">
-        <v>9516.375</v>
+        <v>9733.0588235294126</v>
       </c>
       <c r="I33" s="15">
-        <v>-1102.625</v>
+        <v>-1403.1176470588234</v>
       </c>
       <c r="J33" s="16">
-        <v>3387</v>
+        <v>1349</v>
       </c>
       <c r="K33" s="13">
-        <v>14056.050000000001</v>
+        <v>5598.35</v>
       </c>
       <c r="L33" s="14">
-        <v>12.691334894613583</v>
+        <v>4.866935483870968</v>
       </c>
       <c r="M33" s="30">
-        <v>5871.25</v>
+        <v>6097.8823529411766</v>
       </c>
       <c r="N33" s="15">
-        <v>718.25</v>
+        <v>-1422.7647058823532</v>
       </c>
       <c r="O33" s="16">
-        <v>217</v>
+        <v>395</v>
       </c>
       <c r="P33" s="17">
-        <v>900.55000000000007</v>
+        <v>1639.2500000000002</v>
       </c>
       <c r="Q33" s="14">
-        <v>10.952681388012618</v>
+        <v>19.520348837209305</v>
       </c>
       <c r="R33" s="16">
-        <v>435.875</v>
+        <v>445.17647058823525</v>
       </c>
       <c r="S33" s="15">
-        <v>-179.25</v>
+        <v>-9.7058823529411598</v>
       </c>
       <c r="T33" s="18">
-        <v>1075</v>
+        <v>1696</v>
       </c>
       <c r="U33" s="17">
-        <v>4461.25</v>
+        <v>7038.4000000000005</v>
       </c>
       <c r="V33" s="14">
-        <v>10.225921521997622</v>
+        <v>15.644058600108519</v>
       </c>
       <c r="W33" s="16">
-        <v>2312.75</v>
+        <v>2385.0588235294117</v>
       </c>
       <c r="X33" s="15">
-        <v>-501.875</v>
+        <v>-38.588235294117567</v>
       </c>
       <c r="Y33" s="18">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="Z33" s="17">
-        <v>315.40000000000003</v>
+        <v>124.50000000000001</v>
       </c>
       <c r="AA33" s="14">
-        <v>6.6448087431693992</v>
+        <v>2.2566371681415927</v>
       </c>
       <c r="AB33" s="16">
-        <v>251.625</v>
+        <v>292.47058823529414</v>
       </c>
       <c r="AC33" s="15">
-        <v>-152.75</v>
+        <v>-262.47058823529414</v>
       </c>
       <c r="AD33" s="19">
-        <v>7978</v>
+        <v>6491</v>
       </c>
       <c r="AE33" s="20">
-        <v>29518.95</v>
+        <v>26937.65</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4632,19 +4634,19 @@
         <v>3311.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>14.346067415730337</v>
+        <v>15.242696629213484</v>
       </c>
       <c r="H34" s="30">
-        <v>1223.75</v>
+        <v>1151.7647058823529</v>
       </c>
       <c r="I34" s="15">
-        <v>241.75</v>
+        <v>274.47058823529414</v>
       </c>
       <c r="J34" s="16">
-        <v>336</v>
+        <v>256</v>
       </c>
       <c r="K34" s="13">
-        <v>1394.4</v>
+        <v>1062.4000000000001</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4653,37 +4655,35 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>336</v>
+        <v>256</v>
       </c>
       <c r="O34" s="16">
-        <v>0</v>
-      </c>
-      <c r="P34" s="17">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P34" s="17"/>
       <c r="Q34" s="14">
-        <v>0</v>
+        <v>25.499999999999996</v>
       </c>
       <c r="R34" s="16">
-        <v>44</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="S34" s="15">
-        <v>-40</v>
+        <v>10.352941176470587</v>
       </c>
       <c r="T34" s="18">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="U34" s="17">
-        <v>373.50000000000006</v>
+        <v>506.30000000000007</v>
       </c>
       <c r="V34" s="14">
-        <v>13.090909090909092</v>
+        <v>18.854545454545455</v>
       </c>
       <c r="W34" s="16">
-        <v>151.25</v>
+        <v>142.35294117647058</v>
       </c>
       <c r="X34" s="15">
-        <v>-13.125</v>
+        <v>18.47058823529413</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4704,7 +4704,7 @@
         <v>1256</v>
       </c>
       <c r="AE34" s="20">
-        <v>5378.4000000000005</v>
+        <v>5212.4000000000005</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4739,85 +4739,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>3046</v>
+        <v>2304</v>
       </c>
       <c r="F35" s="14">
-        <v>4964.9799999999996</v>
+        <v>3755.5199999999995</v>
       </c>
       <c r="G35" s="14">
-        <v>7.1649514848573945</v>
+        <v>5.4581939799331112</v>
       </c>
       <c r="H35" s="30">
-        <v>9352.75</v>
+        <v>9286.5882352941171</v>
       </c>
       <c r="I35" s="15">
-        <v>-1205.25</v>
+        <v>-1917.1764705882351</v>
       </c>
       <c r="J35" s="16">
-        <v>2076</v>
+        <v>1559</v>
       </c>
       <c r="K35" s="13">
-        <v>3383.8799999999997</v>
+        <v>2541.1699999999996</v>
       </c>
       <c r="L35" s="14">
-        <v>11.978362783988461</v>
+        <v>9.0639534883720927</v>
       </c>
       <c r="M35" s="30">
-        <v>3812.875</v>
+        <v>3784</v>
       </c>
       <c r="N35" s="15">
-        <v>342.875</v>
+        <v>-161</v>
       </c>
       <c r="O35" s="16">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="P35" s="17">
-        <v>1237.1699999999998</v>
+        <v>1263.25</v>
       </c>
       <c r="Q35" s="14">
-        <v>20.830188679245282</v>
+        <v>20.979299363057326</v>
       </c>
       <c r="R35" s="16">
-        <v>801.625</v>
+        <v>812.7058823529411</v>
       </c>
       <c r="S35" s="15">
-        <v>30.25</v>
+        <v>36.176470588235361</v>
       </c>
       <c r="T35" s="18">
-        <v>347</v>
+        <v>705</v>
       </c>
       <c r="U35" s="17">
-        <v>565.61</v>
+        <v>1149.1499999999999</v>
       </c>
       <c r="V35" s="14">
-        <v>8.2130177514792901</v>
+        <v>16.531034482758621</v>
       </c>
       <c r="W35" s="16">
-        <v>929.5</v>
+        <v>938.23529411764707</v>
       </c>
       <c r="X35" s="15">
-        <v>-286.75</v>
+        <v>22.647058823529392</v>
       </c>
       <c r="Y35" s="18">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="Z35" s="17">
-        <v>459.65999999999997</v>
+        <v>423.79999999999995</v>
       </c>
       <c r="AA35" s="14">
-        <v>21.383886255924171</v>
+        <v>19.732142857142858</v>
       </c>
       <c r="AB35" s="16">
-        <v>290.125</v>
+        <v>289.88235294117646</v>
       </c>
       <c r="AC35" s="15">
-        <v>18.25</v>
+        <v>-29.882352941176464</v>
       </c>
       <c r="AD35" s="19">
-        <v>6510</v>
+        <v>5603</v>
       </c>
       <c r="AE35" s="20">
-        <v>8757.99</v>
+        <v>9132.89</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4852,85 +4852,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>5535</v>
+        <v>5615</v>
       </c>
       <c r="F36" s="14">
-        <v>9022.0499999999993</v>
+        <v>9152.4499999999989</v>
       </c>
       <c r="G36" s="14">
-        <v>8.8471528471528469</v>
+        <v>9.1695485110470702</v>
       </c>
       <c r="H36" s="30">
-        <v>13763.75</v>
+        <v>13471.764705882353</v>
       </c>
       <c r="I36" s="15">
-        <v>-721.25</v>
+        <v>-508.52941176470631</v>
       </c>
       <c r="J36" s="16">
-        <v>3716</v>
+        <v>2693</v>
       </c>
       <c r="K36" s="13">
-        <v>6057.08</v>
+        <v>4389.59</v>
       </c>
       <c r="L36" s="14">
-        <v>15.475273295158772</v>
+        <v>11.473934837092731</v>
       </c>
       <c r="M36" s="30">
-        <v>5282.75</v>
+        <v>5163.5294117647063</v>
       </c>
       <c r="N36" s="15">
-        <v>1314.75</v>
+        <v>345.94117647058829</v>
       </c>
       <c r="O36" s="16">
-        <v>943</v>
+        <v>1868</v>
       </c>
       <c r="P36" s="17">
-        <v>1537.09</v>
+        <v>3044.8399999999997</v>
       </c>
       <c r="Q36" s="14">
-        <v>10.153432032301481</v>
+        <v>20.421864951768487</v>
       </c>
       <c r="R36" s="16">
-        <v>2043.25</v>
+        <v>2012.3529411764705</v>
       </c>
       <c r="S36" s="15">
-        <v>-914.5</v>
+        <v>38.588235294117567</v>
       </c>
       <c r="T36" s="18">
-        <v>936</v>
+        <v>1649</v>
       </c>
       <c r="U36" s="17">
-        <v>1525.6799999999998</v>
+        <v>2687.87</v>
       </c>
       <c r="V36" s="14">
-        <v>9.1428571428571423</v>
+        <v>16.000570776255707</v>
       </c>
       <c r="W36" s="16">
-        <v>2252.25</v>
+        <v>2267.294117647059</v>
       </c>
       <c r="X36" s="15">
-        <v>-599.625</v>
+        <v>5.8823529411711206E-2</v>
       </c>
       <c r="Y36" s="18">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="Z36" s="17">
-        <v>446.61999999999995</v>
+        <v>381.41999999999996</v>
       </c>
       <c r="AA36" s="14">
-        <v>11.09873417721519</v>
+        <v>9.3820754716981138</v>
       </c>
       <c r="AB36" s="16">
-        <v>543.125</v>
+        <v>548.70588235294122</v>
       </c>
       <c r="AC36" s="15">
-        <v>-219.75</v>
+        <v>-314.70588235294122</v>
       </c>
       <c r="AD36" s="19">
-        <v>11404</v>
+        <v>12059</v>
       </c>
       <c r="AE36" s="20">
-        <v>16702.61</v>
+        <v>19656.169999999998</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4965,64 +4965,64 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1260</v>
+        <v>1434</v>
       </c>
       <c r="F37" s="14">
-        <v>2053.7999999999997</v>
+        <v>2337.42</v>
       </c>
       <c r="G37" s="14">
-        <v>4.3988653720270561</v>
+        <v>4.942822384428224</v>
       </c>
       <c r="H37" s="30">
-        <v>6301.625</v>
+        <v>6382.588235294118</v>
       </c>
       <c r="I37" s="15">
-        <v>-1604.375</v>
+        <v>-1467.1764705882351</v>
       </c>
       <c r="J37" s="16">
-        <v>2660</v>
+        <v>278</v>
       </c>
       <c r="K37" s="13">
-        <v>4335.7999999999993</v>
+        <v>453.14</v>
       </c>
       <c r="L37" s="14">
-        <v>18.848538529672275</v>
+        <v>1.9329243353783232</v>
       </c>
       <c r="M37" s="30">
-        <v>3104.75</v>
+        <v>3164.1176470588234</v>
       </c>
       <c r="N37" s="15">
-        <v>1248.75</v>
+        <v>-1160.2352941176468</v>
       </c>
       <c r="O37" s="16">
-        <v>459</v>
+        <v>1174</v>
       </c>
       <c r="P37" s="17">
-        <v>748.17</v>
+        <v>1913.62</v>
       </c>
       <c r="Q37" s="14">
-        <v>7.9566630552546043</v>
+        <v>19.977977977977979</v>
       </c>
       <c r="R37" s="16">
-        <v>1269.125</v>
+        <v>1292.8235294117646</v>
       </c>
       <c r="S37" s="15">
-        <v>-694.75</v>
+        <v>-1.2941176470587834</v>
       </c>
       <c r="T37" s="18">
-        <v>158</v>
+        <v>550</v>
       </c>
       <c r="U37" s="17">
-        <v>257.53999999999996</v>
+        <v>896.49999999999989</v>
       </c>
       <c r="V37" s="14">
-        <v>2.8629671574178936</v>
+        <v>9.8008385744234801</v>
       </c>
       <c r="W37" s="16">
-        <v>1214.125</v>
+        <v>1234.5882352941176</v>
       </c>
       <c r="X37" s="15">
-        <v>-669.8125</v>
+        <v>-347.88235294117646</v>
       </c>
       <c r="Y37" s="18">
         <v>0</v>
@@ -5034,16 +5034,16 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>338.25</v>
+        <v>318.35294117647061</v>
       </c>
       <c r="AC37" s="15">
-        <v>-307.5</v>
+        <v>-318.35294117647061</v>
       </c>
       <c r="AD37" s="19">
-        <v>4537</v>
+        <v>3436</v>
       </c>
       <c r="AE37" s="20">
-        <v>5339.8799999999992</v>
+        <v>5600.6799999999994</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5078,85 +5078,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>501</v>
+        <v>962</v>
       </c>
       <c r="F38" s="14">
-        <v>816.63</v>
+        <v>1568.06</v>
       </c>
       <c r="G38" s="14">
-        <v>2.6490416391275611</v>
+        <v>5.0134886572654818</v>
       </c>
       <c r="H38" s="30">
-        <v>4160.75</v>
+        <v>4221.411764705882</v>
       </c>
       <c r="I38" s="15">
-        <v>-1390.25</v>
+        <v>-956.82352941176464</v>
       </c>
       <c r="J38" s="16">
-        <v>2726</v>
+        <v>423</v>
       </c>
       <c r="K38" s="13">
-        <v>4443.38</v>
+        <v>689.49</v>
       </c>
       <c r="L38" s="14">
-        <v>24.163988919667592</v>
+        <v>3.6484018264840183</v>
       </c>
       <c r="M38" s="30">
-        <v>2481.875</v>
+        <v>2550.705882352941</v>
       </c>
       <c r="N38" s="15">
-        <v>1597.875</v>
+        <v>-736.41176470588243</v>
       </c>
       <c r="O38" s="16">
-        <v>128</v>
+        <v>761</v>
       </c>
       <c r="P38" s="17">
-        <v>208.64</v>
+        <v>1240.4299999999998</v>
       </c>
       <c r="Q38" s="14">
-        <v>3.3573770491803279</v>
+        <v>19.872503840245773</v>
       </c>
       <c r="R38" s="16">
-        <v>838.75</v>
+        <v>842.47058823529414</v>
       </c>
       <c r="S38" s="15">
-        <v>-634.5</v>
+        <v>-4.8823529411765776</v>
       </c>
       <c r="T38" s="18">
-        <v>311</v>
+        <v>588</v>
       </c>
       <c r="U38" s="17">
-        <v>506.92999999999995</v>
+        <v>958.43999999999994</v>
       </c>
       <c r="V38" s="14">
-        <v>9.0802919708029197</v>
+        <v>16.174757281553397</v>
       </c>
       <c r="W38" s="16">
-        <v>753.5</v>
+        <v>799.76470588235293</v>
       </c>
       <c r="X38" s="15">
-        <v>-202.75</v>
+        <v>6.3529411764706083</v>
       </c>
       <c r="Y38" s="18">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="Z38" s="17">
-        <v>348.82</v>
+        <v>277.09999999999997</v>
       </c>
       <c r="AA38" s="14">
-        <v>8.4127764127764131</v>
+        <v>6.6436781609195394</v>
       </c>
       <c r="AB38" s="16">
-        <v>559.625</v>
+        <v>562.94117647058829</v>
       </c>
       <c r="AC38" s="15">
-        <v>-294.75</v>
+        <v>-392.94117647058829</v>
       </c>
       <c r="AD38" s="19">
-        <v>3880</v>
+        <v>2904</v>
       </c>
       <c r="AE38" s="20">
-        <v>3687.06</v>
+        <v>4733.5199999999995</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5191,85 +5191,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1633</v>
+        <v>1572</v>
       </c>
       <c r="F39" s="14">
-        <v>2661.79</v>
+        <v>2562.3599999999997</v>
       </c>
       <c r="G39" s="14">
-        <v>17.932738503774878</v>
+        <v>18.044564483457123</v>
       </c>
       <c r="H39" s="30">
-        <v>2003.375</v>
+        <v>1916.5882352941178</v>
       </c>
       <c r="I39" s="15">
-        <v>722.375</v>
+        <v>700.82352941176464</v>
       </c>
       <c r="J39" s="16">
-        <v>3518</v>
+        <v>2623</v>
       </c>
       <c r="K39" s="13">
-        <v>5734.3399999999992</v>
+        <v>4275.49</v>
       </c>
       <c r="L39" s="14">
-        <v>58.450674974039458</v>
+        <v>45.041414141414137</v>
       </c>
       <c r="M39" s="30">
-        <v>1324.125</v>
+        <v>1281.1764705882354</v>
       </c>
       <c r="N39" s="15">
-        <v>2916.125</v>
+        <v>2040.6470588235293</v>
       </c>
       <c r="O39" s="16">
-        <v>192</v>
+        <v>662</v>
       </c>
       <c r="P39" s="17">
-        <v>312.95999999999998</v>
+        <v>1079.06</v>
       </c>
       <c r="Q39" s="14">
-        <v>6.2566191446028512</v>
+        <v>22.598393574297187</v>
       </c>
       <c r="R39" s="16">
-        <v>675.125</v>
+        <v>644.47058823529414</v>
       </c>
       <c r="S39" s="15">
-        <v>-421.75</v>
+        <v>76.117647058823422</v>
       </c>
       <c r="T39" s="18">
-        <v>490</v>
+        <v>847</v>
       </c>
       <c r="U39" s="17">
-        <v>798.69999999999993</v>
+        <v>1380.61</v>
       </c>
       <c r="V39" s="14">
-        <v>9.7633872976338729</v>
+        <v>16.178651685393259</v>
       </c>
       <c r="W39" s="16">
-        <v>1104.125</v>
+        <v>1151.7647058823529</v>
       </c>
       <c r="X39" s="15">
-        <v>-262.8125</v>
+        <v>9.3529411764706083</v>
       </c>
       <c r="Y39" s="18">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="Z39" s="17">
-        <v>731.87</v>
+        <v>726.9799999999999</v>
       </c>
       <c r="AA39" s="14">
-        <v>101.1830985915493</v>
+        <v>106.78873239436619</v>
       </c>
       <c r="AB39" s="16">
-        <v>97.625</v>
+        <v>91.882352941176478</v>
       </c>
       <c r="AC39" s="15">
-        <v>360.25</v>
+        <v>354.11764705882354</v>
       </c>
       <c r="AD39" s="19">
-        <v>6282</v>
+        <v>6150</v>
       </c>
       <c r="AE39" s="20">
-        <v>10524.91</v>
+        <v>10024.5</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5304,64 +5304,64 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1225</v>
+        <v>1346</v>
       </c>
       <c r="F40" s="14">
-        <v>1996.7499999999998</v>
+        <v>2193.98</v>
       </c>
       <c r="G40" s="14">
-        <v>10.566037735849056</v>
+        <v>11.728344438749359</v>
       </c>
       <c r="H40" s="30">
-        <v>2550.625</v>
+        <v>2524.8235294117649</v>
       </c>
       <c r="I40" s="15">
-        <v>65.625</v>
+        <v>198.35294117647049</v>
       </c>
       <c r="J40" s="16">
-        <v>3470</v>
+        <v>1728</v>
       </c>
       <c r="K40" s="13">
-        <v>5656.0999999999995</v>
+        <v>2816.64</v>
       </c>
       <c r="L40" s="14">
-        <v>49.219858156028366</v>
+        <v>25.129170230966636</v>
       </c>
       <c r="M40" s="30">
-        <v>1551</v>
+        <v>1512.8235294117646</v>
       </c>
       <c r="N40" s="15">
-        <v>2765</v>
+        <v>1040.3529411764707</v>
       </c>
       <c r="O40" s="16">
-        <v>75</v>
+        <v>812</v>
       </c>
       <c r="P40" s="17">
-        <v>122.24999999999999</v>
+        <v>1323.56</v>
       </c>
       <c r="Q40" s="14">
-        <v>1.9639934533551555</v>
+        <v>22.157303370786515</v>
       </c>
       <c r="R40" s="16">
-        <v>840.125</v>
+        <v>806.23529411764707</v>
       </c>
       <c r="S40" s="15">
-        <v>-688.75</v>
+        <v>79.058823529411711</v>
       </c>
       <c r="T40" s="18">
-        <v>366</v>
+        <v>981</v>
       </c>
       <c r="U40" s="17">
-        <v>596.57999999999993</v>
+        <v>1599.03</v>
       </c>
       <c r="V40" s="14">
-        <v>6.0873180873180877</v>
+        <v>15.897998093422308</v>
       </c>
       <c r="W40" s="16">
-        <v>1322.75</v>
+        <v>1357.5294117647059</v>
       </c>
       <c r="X40" s="15">
-        <v>-535.875</v>
+        <v>-6.2941176470587834</v>
       </c>
       <c r="Y40" s="18">
         <v>460</v>
@@ -5370,19 +5370,19 @@
         <v>749.8</v>
       </c>
       <c r="AA40" s="14">
-        <v>106.66666666666667</v>
+        <v>113.33333333333334</v>
       </c>
       <c r="AB40" s="16">
-        <v>94.875</v>
+        <v>89.294117647058812</v>
       </c>
       <c r="AC40" s="15">
-        <v>373.75</v>
+        <v>370.70588235294122</v>
       </c>
       <c r="AD40" s="19">
-        <v>5596</v>
+        <v>5327</v>
       </c>
       <c r="AE40" s="20">
-        <v>9480.08</v>
+        <v>8683.01</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5417,85 +5417,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F41" s="14">
-        <v>3056.55</v>
+        <v>3025.8</v>
       </c>
       <c r="G41" s="14">
-        <v>7.2094288304623753</v>
+        <v>7.1365187713310583</v>
       </c>
       <c r="H41" s="30">
-        <v>1516.625</v>
+        <v>1516.705882352941</v>
       </c>
       <c r="I41" s="15">
-        <v>-192.375</v>
+        <v>-197.41176470588232</v>
       </c>
       <c r="J41" s="16">
-        <v>676</v>
+        <v>268</v>
       </c>
       <c r="K41" s="13">
-        <v>4157.4000000000005</v>
+        <v>1648.2</v>
       </c>
       <c r="L41" s="14">
-        <v>16.821150855365474</v>
+        <v>6.5743145743145739</v>
       </c>
       <c r="M41" s="30">
-        <v>884.125</v>
+        <v>896.82352941176475</v>
       </c>
       <c r="N41" s="15">
-        <v>274.125</v>
+        <v>-139.64705882352939</v>
       </c>
       <c r="O41" s="16">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="P41" s="17">
-        <v>307.5</v>
+        <v>688.80000000000007</v>
       </c>
       <c r="Q41" s="14">
-        <v>10</v>
+        <v>23.219512195121954</v>
       </c>
       <c r="R41" s="16">
-        <v>110</v>
+        <v>106.11764705882352</v>
       </c>
       <c r="S41" s="15">
-        <v>-50</v>
+        <v>15.529411764705884</v>
       </c>
       <c r="T41" s="18">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="U41" s="17">
-        <v>885.6</v>
+        <v>1156.2</v>
       </c>
       <c r="V41" s="14">
-        <v>13.879518072289157</v>
+        <v>17.755555555555556</v>
       </c>
       <c r="W41" s="16">
-        <v>228.25</v>
+        <v>232.94117647058823</v>
       </c>
       <c r="X41" s="15">
-        <v>-11.625</v>
+        <v>18.588235294117652</v>
       </c>
       <c r="Y41" s="18">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="17">
-        <v>86.100000000000009</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="14">
-        <v>3.2941176470588234</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>93.5</v>
+        <v>106.11764705882352</v>
       </c>
       <c r="AC41" s="15">
-        <v>-71</v>
+        <v>-106.11764705882352</v>
       </c>
       <c r="AD41" s="19">
-        <v>1381</v>
+        <v>1060</v>
       </c>
       <c r="AE41" s="20">
-        <v>6851.1</v>
+        <v>6519</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5530,64 +5530,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>398</v>
+        <v>253</v>
       </c>
       <c r="F42" s="14">
-        <v>2447.7000000000003</v>
+        <v>1555.95</v>
       </c>
       <c r="G42" s="14">
-        <v>5.9127205199628596</v>
+        <v>3.6697952218430037</v>
       </c>
       <c r="H42" s="30">
-        <v>1480.875</v>
+        <v>1516.705882352941</v>
       </c>
       <c r="I42" s="15">
-        <v>-275.125</v>
+        <v>-436.41176470588232</v>
       </c>
       <c r="J42" s="16">
-        <v>248</v>
+        <v>901</v>
       </c>
       <c r="K42" s="13">
-        <v>1525.2</v>
+        <v>5541.1500000000005</v>
       </c>
       <c r="L42" s="14">
-        <v>6.0580152671755725</v>
+        <v>21.975609756097562</v>
       </c>
       <c r="M42" s="30">
-        <v>900.625</v>
+        <v>902</v>
       </c>
       <c r="N42" s="15">
-        <v>-161.375</v>
+        <v>491</v>
       </c>
       <c r="O42" s="16">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="P42" s="17">
-        <v>356.70000000000005</v>
+        <v>848.7</v>
       </c>
       <c r="Q42" s="14">
-        <v>8.7547169811320753</v>
+        <v>20.22413793103448</v>
       </c>
       <c r="R42" s="16">
-        <v>145.75</v>
+        <v>150.11764705882354</v>
       </c>
       <c r="S42" s="15">
-        <v>-74.5</v>
+        <v>1.5294117647058556</v>
       </c>
       <c r="T42" s="18">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="U42" s="17">
-        <v>1088.55</v>
+        <v>1740.45</v>
       </c>
       <c r="V42" s="14">
-        <v>10.727272727272727</v>
+        <v>17.558394160583941</v>
       </c>
       <c r="W42" s="16">
-        <v>363</v>
+        <v>354.58823529411762</v>
       </c>
       <c r="X42" s="15">
-        <v>-70.5</v>
+        <v>25.117647058823536</v>
       </c>
       <c r="Y42" s="18">
         <v>82</v>
@@ -5596,19 +5596,19 @@
         <v>504.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>22.237288135593221</v>
+        <v>23.627118644067796</v>
       </c>
       <c r="AB42" s="16">
-        <v>81.125</v>
+        <v>76.352941176470594</v>
       </c>
       <c r="AC42" s="15">
-        <v>8.25</v>
+        <v>5.6470588235294059</v>
       </c>
       <c r="AD42" s="19">
-        <v>963</v>
+        <v>1657</v>
       </c>
       <c r="AE42" s="20">
-        <v>6678.9000000000005</v>
+        <v>10190.550000000001</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5643,85 +5643,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2810</v>
+        <v>2071</v>
       </c>
       <c r="F43" s="14">
-        <v>3259.6</v>
+        <v>2402.3599999999997</v>
       </c>
       <c r="G43" s="14">
-        <v>8.8312708701630331</v>
+        <v>6.3299172959367134</v>
       </c>
       <c r="H43" s="30">
-        <v>7000.125</v>
+        <v>7197.8823529411766</v>
       </c>
       <c r="I43" s="15">
-        <v>-371.875</v>
+        <v>-1200.7647058823532</v>
       </c>
       <c r="J43" s="16">
-        <v>2371</v>
+        <v>3499</v>
       </c>
       <c r="K43" s="13">
-        <v>2750.3599999999997</v>
+        <v>4058.8399999999997</v>
       </c>
       <c r="L43" s="14">
-        <v>9.9805314390949746</v>
+        <v>14.278204512722038</v>
       </c>
       <c r="M43" s="30">
-        <v>5226.375</v>
+        <v>5391.2941176470586</v>
       </c>
       <c r="N43" s="15">
-        <v>-4.625</v>
+        <v>1048.4117647058824</v>
       </c>
       <c r="O43" s="16">
-        <v>810</v>
+        <v>922</v>
       </c>
       <c r="P43" s="17">
-        <v>939.59999999999991</v>
+        <v>1069.52</v>
       </c>
       <c r="Q43" s="14">
-        <v>17.632653061224488</v>
+        <v>19.56803995006242</v>
       </c>
       <c r="R43" s="16">
-        <v>1010.625</v>
+        <v>1036.5882352941176</v>
       </c>
       <c r="S43" s="15">
-        <v>-108.75</v>
+        <v>-20.352941176470608</v>
       </c>
       <c r="T43" s="18">
-        <v>981</v>
+        <v>1710</v>
       </c>
       <c r="U43" s="17">
-        <v>1137.9599999999998</v>
+        <v>1983.6</v>
       </c>
       <c r="V43" s="14">
-        <v>8.4341751746372911</v>
+        <v>14.527736131934033</v>
       </c>
       <c r="W43" s="16">
-        <v>2558.875</v>
+        <v>2589.5294117647059</v>
       </c>
       <c r="X43" s="15">
-        <v>-763.6875</v>
+        <v>-173.29411764705878</v>
       </c>
       <c r="Y43" s="18">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="Z43" s="17">
-        <v>142.67999999999998</v>
+        <v>125.27999999999999</v>
       </c>
       <c r="AA43" s="14">
-        <v>4.3063457330415753</v>
+        <v>3.9483870967741939</v>
       </c>
       <c r="AB43" s="16">
-        <v>628.375</v>
+        <v>601.76470588235293</v>
       </c>
       <c r="AC43" s="15">
-        <v>-448.25</v>
+        <v>-493.76470588235293</v>
       </c>
       <c r="AD43" s="19">
-        <v>7095</v>
+        <v>8310</v>
       </c>
       <c r="AE43" s="20">
-        <v>9276.5199999999986</v>
+        <v>9639.5999999999985</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5756,85 +5756,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>1916</v>
+        <v>2158</v>
       </c>
       <c r="F44" s="14">
-        <v>2222.56</v>
+        <v>2503.2799999999997</v>
       </c>
       <c r="G44" s="14">
-        <v>6.8185053380782916</v>
+        <v>7.5454545454545459</v>
       </c>
       <c r="H44" s="30">
-        <v>6182</v>
+        <v>6292</v>
       </c>
       <c r="I44" s="15">
-        <v>-894</v>
+        <v>-702</v>
       </c>
       <c r="J44" s="16">
-        <v>3135</v>
+        <v>2035</v>
       </c>
       <c r="K44" s="13">
-        <v>3636.6</v>
+        <v>2360.6</v>
       </c>
       <c r="L44" s="14">
-        <v>16.5</v>
+        <v>10.68736484399135</v>
       </c>
       <c r="M44" s="30">
-        <v>4180</v>
+        <v>4189.0588235294117</v>
       </c>
       <c r="N44" s="15">
-        <v>1235</v>
+        <v>130.88235294117658</v>
       </c>
       <c r="O44" s="16">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="P44" s="17">
-        <v>728.4799999999999</v>
+        <v>693.68</v>
       </c>
       <c r="Q44" s="14">
-        <v>23.25925925925926</v>
+        <v>20.874743326488705</v>
       </c>
       <c r="R44" s="16">
-        <v>594</v>
+        <v>630.23529411764707</v>
       </c>
       <c r="S44" s="15">
-        <v>88</v>
+        <v>25.058823529411711</v>
       </c>
       <c r="T44" s="18">
-        <v>1070</v>
+        <v>1024</v>
       </c>
       <c r="U44" s="17">
-        <v>1241.1999999999998</v>
+        <v>1187.8399999999999</v>
       </c>
       <c r="V44" s="14">
-        <v>16.735092864125122</v>
+        <v>16.029465930018414</v>
       </c>
       <c r="W44" s="16">
-        <v>1406.625</v>
+        <v>1405.4117647058824</v>
       </c>
       <c r="X44" s="15">
-        <v>110.9375</v>
+        <v>1.8823529411764639</v>
       </c>
       <c r="Y44" s="18">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="Z44" s="17">
-        <v>281.88</v>
+        <v>225.04</v>
       </c>
       <c r="AA44" s="14">
-        <v>9.5061124694376531</v>
+        <v>7.3452115812917596</v>
       </c>
       <c r="AB44" s="16">
-        <v>562.375</v>
+        <v>581.05882352941171</v>
       </c>
       <c r="AC44" s="15">
-        <v>-268.25</v>
+        <v>-387.05882352941171</v>
       </c>
       <c r="AD44" s="19">
-        <v>6992</v>
+        <v>6009</v>
       </c>
       <c r="AE44" s="20">
-        <v>8849.64</v>
+        <v>6970.44</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5869,85 +5869,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>1937</v>
+        <v>1739</v>
       </c>
       <c r="F45" s="14">
-        <v>2246.9199999999996</v>
+        <v>2017.2399999999998</v>
       </c>
       <c r="G45" s="14">
-        <v>5.2078642245000841</v>
+        <v>4.6127320954907161</v>
       </c>
       <c r="H45" s="30">
-        <v>8182.625</v>
+        <v>8294</v>
       </c>
       <c r="I45" s="15">
-        <v>-1782.375</v>
+        <v>-2031</v>
       </c>
       <c r="J45" s="16">
-        <v>3122</v>
+        <v>5610</v>
       </c>
       <c r="K45" s="13">
-        <v>3621.5199999999995</v>
+        <v>6507.5999999999995</v>
       </c>
       <c r="L45" s="14">
-        <v>12.330782522833868</v>
+        <v>22.005076142131976</v>
       </c>
       <c r="M45" s="30">
-        <v>5570.125</v>
+        <v>5608.7058823529414</v>
       </c>
       <c r="N45" s="15">
-        <v>590.125</v>
+        <v>3060.5882352941176</v>
       </c>
       <c r="O45" s="16">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="P45" s="17">
-        <v>1014.9999999999999</v>
+        <v>1021.9599999999999</v>
       </c>
       <c r="Q45" s="14">
-        <v>20.989505247376311</v>
+        <v>20.266576454668471</v>
       </c>
       <c r="R45" s="16">
-        <v>917.125</v>
+        <v>956.35294117647049</v>
       </c>
       <c r="S45" s="15">
-        <v>41.25</v>
+        <v>11.58823529411768</v>
       </c>
       <c r="T45" s="18">
-        <v>1026</v>
+        <v>1500</v>
       </c>
       <c r="U45" s="17">
-        <v>1190.1599999999999</v>
+        <v>1739.9999999999998</v>
       </c>
       <c r="V45" s="14">
-        <v>10.965931863727455</v>
+        <v>15.828677839851023</v>
       </c>
       <c r="W45" s="16">
-        <v>2058.375</v>
+        <v>2084.8235294117649</v>
       </c>
       <c r="X45" s="15">
-        <v>-377.4375</v>
+        <v>-16.235294117647072</v>
       </c>
       <c r="Y45" s="18">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="Z45" s="17">
-        <v>213.44</v>
+        <v>189.07999999999998</v>
       </c>
       <c r="AA45" s="14">
-        <v>7.215686274509804</v>
+        <v>6.7094430992736074</v>
       </c>
       <c r="AB45" s="16">
-        <v>561</v>
+        <v>534.47058823529414</v>
       </c>
       <c r="AC45" s="15">
-        <v>-326</v>
+        <v>-371.47058823529414</v>
       </c>
       <c r="AD45" s="19">
-        <v>7144</v>
+        <v>9893</v>
       </c>
       <c r="AE45" s="20">
-        <v>9346.119999999999</v>
+        <v>11475.88</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5982,85 +5982,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2107</v>
+        <v>2116</v>
       </c>
       <c r="F46" s="14">
-        <v>2444.12</v>
+        <v>2454.56</v>
       </c>
       <c r="G46" s="14">
-        <v>7.7784956160590681</v>
+        <v>7.6585054289972314</v>
       </c>
       <c r="H46" s="30">
-        <v>5959.25</v>
+        <v>6078.4705882352946</v>
       </c>
       <c r="I46" s="15">
-        <v>-601.75</v>
+        <v>-646.94117647058829</v>
       </c>
       <c r="J46" s="16">
-        <v>4005</v>
+        <v>2669</v>
       </c>
       <c r="K46" s="13">
-        <v>4645.7999999999993</v>
+        <v>3096.04</v>
       </c>
       <c r="L46" s="14">
-        <v>26.059373729158196</v>
+        <v>16.886118347599552</v>
       </c>
       <c r="M46" s="30">
-        <v>3381.125</v>
+        <v>3477.294117647059</v>
       </c>
       <c r="N46" s="15">
-        <v>2468.125</v>
+        <v>1088.4117647058824</v>
       </c>
       <c r="O46" s="16">
-        <v>639</v>
+        <v>595</v>
       </c>
       <c r="P46" s="17">
-        <v>741.2399999999999</v>
+        <v>690.19999999999993</v>
       </c>
       <c r="Q46" s="14">
-        <v>27.557951482479783</v>
+        <v>23.041002277904326</v>
       </c>
       <c r="R46" s="16">
-        <v>510.125</v>
+        <v>568.11764705882354</v>
       </c>
       <c r="S46" s="15">
-        <v>175.25</v>
+        <v>78.529411764705856</v>
       </c>
       <c r="T46" s="18">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="U46" s="17">
-        <v>844.4799999999999</v>
+        <v>825.92</v>
       </c>
       <c r="V46" s="14">
-        <v>18.00309119010819</v>
+        <v>18.256410256410255</v>
       </c>
       <c r="W46" s="16">
-        <v>889.625</v>
+        <v>858</v>
       </c>
       <c r="X46" s="15">
-        <v>121.4375</v>
+        <v>88</v>
       </c>
       <c r="Y46" s="18">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="17">
-        <v>49.879999999999995</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="14">
-        <v>1.7551020408163265</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="16">
-        <v>539</v>
+        <v>551.29411764705878</v>
       </c>
       <c r="AC46" s="15">
-        <v>-447</v>
+        <v>-551.29411764705878</v>
       </c>
       <c r="AD46" s="19">
-        <v>7522</v>
+        <v>6092</v>
       </c>
       <c r="AE46" s="20">
-        <v>8918.08</v>
+        <v>7066.7199999999993</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6108,19 +6108,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="K47" s="13">
-        <v>594</v>
+        <v>162</v>
       </c>
       <c r="L47" s="14">
-        <v>13.2</v>
+        <v>3.0599999999999992</v>
       </c>
       <c r="M47" s="30">
-        <v>55</v>
+        <v>64.705882352941188</v>
       </c>
       <c r="N47" s="15">
-        <v>8</v>
+        <v>-20.411764705882359</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6138,19 +6138,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="U47" s="17">
-        <v>36</v>
+        <v>288</v>
       </c>
       <c r="V47" s="14">
-        <v>1.7777777777777777</v>
+        <v>14.315789473684211</v>
       </c>
       <c r="W47" s="16">
-        <v>24.75</v>
+        <v>24.588235294117649</v>
       </c>
       <c r="X47" s="15">
-        <v>-14.875</v>
+        <v>-1.882352941176471</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6168,10 +6168,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AE47" s="20">
-        <v>144</v>
+        <v>450</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6219,19 +6219,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K48" s="13">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="L48" s="14">
-        <v>22.857142857142858</v>
+        <v>9.2727272727272716</v>
       </c>
       <c r="M48" s="30">
-        <v>9.625</v>
+        <v>14.23529411764706</v>
       </c>
       <c r="N48" s="15">
-        <v>5.625</v>
+        <v>-0.47058823529411775</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6279,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE48" s="20">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6317,34 +6317,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>262</v>
+        <v>134</v>
       </c>
       <c r="F49" s="14">
-        <v>303.91999999999996</v>
+        <v>155.44</v>
       </c>
       <c r="G49" s="14">
-        <v>4.8518518518518521</v>
+        <v>2.3729166666666668</v>
       </c>
       <c r="H49" s="30">
-        <v>1188</v>
+        <v>1242.3529411764705</v>
       </c>
       <c r="I49" s="15">
-        <v>-278</v>
+        <v>-430.70588235294122</v>
       </c>
       <c r="J49" s="16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K49" s="13">
-        <v>37.119999999999997</v>
+        <v>0</v>
       </c>
       <c r="L49" s="14">
-        <v>0.49230769230769234</v>
+        <v>0</v>
       </c>
       <c r="M49" s="30">
-        <v>1430</v>
+        <v>1450.705882352941</v>
       </c>
       <c r="N49" s="15">
-        <v>-618</v>
+        <v>-659.41176470588232</v>
       </c>
       <c r="O49" s="16">
         <v>75</v>
@@ -6353,13 +6353,13 @@
         <v>87</v>
       </c>
       <c r="Q49" s="14">
-        <v>10.344827586206897</v>
+        <v>9.9609374999999982</v>
       </c>
       <c r="R49" s="16">
-        <v>159.5</v>
+        <v>165.64705882352942</v>
       </c>
       <c r="S49" s="15">
-        <v>-70</v>
+        <v>-75.588235294117652</v>
       </c>
       <c r="T49" s="18">
         <v>32</v>
@@ -6368,13 +6368,13 @@
         <v>37.119999999999997</v>
       </c>
       <c r="V49" s="14">
-        <v>2.5221674876847291</v>
+        <v>2.6407766990291264</v>
       </c>
       <c r="W49" s="16">
-        <v>279.125</v>
+        <v>266.58823529411762</v>
       </c>
       <c r="X49" s="15">
-        <v>-158.3125</v>
+        <v>-161.88235294117646</v>
       </c>
       <c r="Y49" s="18">
         <v>29</v>
@@ -6383,19 +6383,19 @@
         <v>33.64</v>
       </c>
       <c r="AA49" s="14">
-        <v>5.4588235294117649</v>
+        <v>5.8</v>
       </c>
       <c r="AB49" s="16">
-        <v>116.875</v>
+        <v>110</v>
       </c>
       <c r="AC49" s="15">
-        <v>-77.25</v>
+        <v>-81</v>
       </c>
       <c r="AD49" s="19">
-        <v>430</v>
+        <v>270</v>
       </c>
       <c r="AE49" s="20">
-        <v>764.43999999999994</v>
+        <v>313.2</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6430,85 +6430,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>812</v>
+        <v>750</v>
       </c>
       <c r="F50" s="14">
-        <v>941.92</v>
+        <v>869.99999999999989</v>
       </c>
       <c r="G50" s="14">
-        <v>2.8756086764054891</v>
+        <v>2.5925172834485561</v>
       </c>
       <c r="H50" s="30">
-        <v>6212.25</v>
+        <v>6364.4705882352946</v>
       </c>
       <c r="I50" s="15">
-        <v>-2011.75</v>
+        <v>-2142.9411764705883</v>
       </c>
       <c r="J50" s="16">
-        <v>71</v>
+        <v>3830</v>
       </c>
       <c r="K50" s="13">
-        <v>82.36</v>
+        <v>4442.7999999999993</v>
       </c>
       <c r="L50" s="14">
-        <v>0.35802080050425467</v>
+        <v>19.978521018717398</v>
       </c>
       <c r="M50" s="30">
-        <v>4362.875</v>
+        <v>4217.5294117647063</v>
       </c>
       <c r="N50" s="15">
-        <v>-1912.125</v>
+        <v>1912.9411764705881</v>
       </c>
       <c r="O50" s="16">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="P50" s="17">
-        <v>330.59999999999997</v>
+        <v>310.88</v>
       </c>
       <c r="Q50" s="14">
-        <v>6.6472303206997081</v>
+        <v>6.2841379310344827</v>
       </c>
       <c r="R50" s="16">
-        <v>943.25</v>
+        <v>938.23529411764707</v>
       </c>
       <c r="S50" s="15">
-        <v>-572.5</v>
+        <v>-584.94117647058829</v>
       </c>
       <c r="T50" s="18">
-        <v>870</v>
+        <v>815</v>
       </c>
       <c r="U50" s="17">
-        <v>1009.1999999999999</v>
+        <v>945.4</v>
       </c>
       <c r="V50" s="14">
-        <v>30.728476821192054</v>
+        <v>24.179755671902271</v>
       </c>
       <c r="W50" s="16">
-        <v>622.875</v>
+        <v>741.52941176470586</v>
       </c>
       <c r="X50" s="15">
-        <v>445.3125</v>
+        <v>275.70588235294122</v>
       </c>
       <c r="Y50" s="18">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Z50" s="17">
-        <v>61.48</v>
+        <v>47.559999999999995</v>
       </c>
       <c r="AA50" s="14">
-        <v>4.5347593582887704</v>
+        <v>3.5025125628140708</v>
       </c>
       <c r="AB50" s="16">
-        <v>257.125</v>
+        <v>257.52941176470586</v>
       </c>
       <c r="AC50" s="15">
-        <v>-180.75</v>
+        <v>-216.52941176470586</v>
       </c>
       <c r="AD50" s="19">
-        <v>2091</v>
+        <v>5704</v>
       </c>
       <c r="AE50" s="20">
-        <v>4986.8399999999992</v>
+        <v>6616.6399999999994</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6546,85 +6546,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>487</v>
+        <v>771</v>
       </c>
       <c r="F51" s="14">
-        <v>564.91999999999996</v>
+        <v>894.3599999999999</v>
       </c>
       <c r="G51" s="14">
-        <v>2.5741658407664354</v>
+        <v>4.0641860465116277</v>
       </c>
       <c r="H51" s="30">
-        <v>4162.125</v>
+        <v>4173.5294117647063</v>
       </c>
       <c r="I51" s="15">
-        <v>-1404.875</v>
+        <v>-1126.0588235294119</v>
       </c>
       <c r="J51" s="16">
-        <v>1932</v>
+        <v>1833</v>
       </c>
       <c r="K51" s="13">
-        <v>2241.12</v>
+        <v>2126.2799999999997</v>
       </c>
       <c r="L51" s="14">
-        <v>11.634173880316146</v>
+        <v>10.675231243576567</v>
       </c>
       <c r="M51" s="30">
-        <v>3653.375</v>
+        <v>3777.5294117647063</v>
       </c>
       <c r="N51" s="15">
-        <v>271.375</v>
+        <v>115.94117647058806</v>
       </c>
       <c r="O51" s="16">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="P51" s="17">
-        <v>151.95999999999998</v>
+        <v>331.76</v>
       </c>
       <c r="Q51" s="14">
-        <v>9.5707762557077629</v>
+        <v>20.777777777777775</v>
       </c>
       <c r="R51" s="16">
-        <v>301.125</v>
+        <v>302.82352941176475</v>
       </c>
       <c r="S51" s="15">
-        <v>-142.75</v>
+        <v>10.705882352941103</v>
       </c>
       <c r="T51" s="18">
-        <v>376</v>
+        <v>563</v>
       </c>
       <c r="U51" s="17">
-        <v>436.15999999999997</v>
+        <v>653.07999999999993</v>
       </c>
       <c r="V51" s="14">
-        <v>11.547024952015356</v>
+        <v>16.616319444444443</v>
       </c>
       <c r="W51" s="16">
-        <v>716.375</v>
+        <v>745.41176470588232</v>
       </c>
       <c r="X51" s="15">
-        <v>-112.4375</v>
+        <v>20.882352941176464</v>
       </c>
       <c r="Y51" s="18">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="Z51" s="17">
-        <v>105.55999999999999</v>
+        <v>98.6</v>
       </c>
       <c r="AA51" s="14">
-        <v>22.060606060606062</v>
+        <v>20.069444444444443</v>
       </c>
       <c r="AB51" s="16">
-        <v>90.75</v>
+        <v>93.17647058823529</v>
       </c>
       <c r="AC51" s="15">
-        <v>8.5</v>
+        <v>-8.1764705882352899</v>
       </c>
       <c r="AD51" s="19">
-        <v>3017</v>
+        <v>3538</v>
       </c>
       <c r="AE51" s="20">
-        <v>3904.56</v>
+        <v>4104.08</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6663,64 +6663,64 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>2659</v>
+        <v>2235</v>
       </c>
       <c r="F52" s="14">
-        <v>2153.79</v>
+        <v>1810.3500000000001</v>
       </c>
       <c r="G52" s="14">
-        <v>18.60253607345868</v>
+        <v>14.310734463276836</v>
       </c>
       <c r="H52" s="30">
-        <v>3144.625</v>
+        <v>3435.8823529411766</v>
       </c>
       <c r="I52" s="15">
-        <v>1229.625</v>
+        <v>673.23529411764684</v>
       </c>
       <c r="J52" s="16">
-        <v>1245</v>
+        <v>789</v>
       </c>
       <c r="K52" s="13">
-        <v>1008.45</v>
+        <v>639.09</v>
       </c>
       <c r="L52" s="14">
-        <v>34.109589041095887</v>
+        <v>17.556282722513089</v>
       </c>
       <c r="M52" s="30">
-        <v>803</v>
+        <v>988.7058823529411</v>
       </c>
       <c r="N52" s="15">
-        <v>880</v>
+        <v>339.58823529411768</v>
       </c>
       <c r="O52" s="16">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="P52" s="17">
-        <v>0</v>
+        <v>126.36000000000001</v>
       </c>
       <c r="Q52" s="14">
-        <v>0</v>
+        <v>22.666666666666661</v>
       </c>
       <c r="R52" s="16">
-        <v>160.875</v>
+        <v>151.41176470588238</v>
       </c>
       <c r="S52" s="15">
-        <v>-146.25</v>
+        <v>18.352941176470551</v>
       </c>
       <c r="T52" s="18">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="U52" s="17">
-        <v>353.97</v>
+        <v>328.05</v>
       </c>
       <c r="V52" s="14">
-        <v>21.781931464174455</v>
+        <v>19.125</v>
       </c>
       <c r="W52" s="16">
-        <v>441.375</v>
+        <v>465.88235294117646</v>
       </c>
       <c r="X52" s="15">
-        <v>136.0625</v>
+        <v>66.176470588235304</v>
       </c>
       <c r="Y52" s="18">
         <v>0</v>
@@ -6732,16 +6732,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>31.625</v>
+        <v>29.764705882352942</v>
       </c>
       <c r="AC52" s="15">
-        <v>-28.75</v>
+        <v>-29.764705882352942</v>
       </c>
       <c r="AD52" s="19">
-        <v>4341</v>
+        <v>3585</v>
       </c>
       <c r="AE52" s="20">
-        <v>3815.1000000000004</v>
+        <v>2903.8500000000004</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6776,64 +6776,64 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1608</v>
+        <v>977</v>
       </c>
       <c r="F53" s="14">
-        <v>1302.48</v>
+        <v>791.37</v>
       </c>
       <c r="G53" s="14">
-        <v>5.9818646826319464</v>
+        <v>3.4630942452043367</v>
       </c>
       <c r="H53" s="30">
-        <v>5913.875</v>
+        <v>6206.588235294118</v>
       </c>
       <c r="I53" s="15">
-        <v>-1080.125</v>
+        <v>-1844.1764705882351</v>
       </c>
       <c r="J53" s="16">
-        <v>1455</v>
+        <v>318</v>
       </c>
       <c r="K53" s="13">
-        <v>1178.5500000000002</v>
+        <v>257.58000000000004</v>
       </c>
       <c r="L53" s="14">
-        <v>12.462526766595289</v>
+        <v>2.533270852858482</v>
       </c>
       <c r="M53" s="30">
-        <v>2568.5</v>
+        <v>2761.6470588235293</v>
       </c>
       <c r="N53" s="15">
-        <v>287.5</v>
+        <v>-937.29411764705878</v>
       </c>
       <c r="O53" s="16">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="P53" s="17">
-        <v>0</v>
+        <v>481.14000000000004</v>
       </c>
       <c r="Q53" s="14">
-        <v>0</v>
+        <v>21.439490445859875</v>
       </c>
       <c r="R53" s="16">
-        <v>647.625</v>
+        <v>609.52941176470586</v>
       </c>
       <c r="S53" s="15">
-        <v>-588.75</v>
+        <v>39.882352941176578</v>
       </c>
       <c r="T53" s="18">
-        <v>825</v>
+        <v>875</v>
       </c>
       <c r="U53" s="17">
-        <v>668.25</v>
+        <v>708.75</v>
       </c>
       <c r="V53" s="14">
-        <v>16.038882138517618</v>
+        <v>16.564587973273944</v>
       </c>
       <c r="W53" s="16">
-        <v>1131.625</v>
+        <v>1162.1176470588234</v>
       </c>
       <c r="X53" s="15">
-        <v>53.4375</v>
+        <v>29.823529411764753</v>
       </c>
       <c r="Y53" s="18">
         <v>9</v>
@@ -6842,19 +6842,19 @@
         <v>7.2900000000000009</v>
       </c>
       <c r="AA53" s="14">
-        <v>1.3090909090909091</v>
+        <v>1.3909090909090911</v>
       </c>
       <c r="AB53" s="16">
-        <v>151.25</v>
+        <v>142.35294117647058</v>
       </c>
       <c r="AC53" s="15">
-        <v>-128.5</v>
+        <v>-133.35294117647058</v>
       </c>
       <c r="AD53" s="19">
-        <v>3897</v>
+        <v>2773</v>
       </c>
       <c r="AE53" s="20">
-        <v>4432.3200000000006</v>
+        <v>2246.13</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6889,85 +6889,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1711</v>
+        <v>2423</v>
       </c>
       <c r="F54" s="14">
-        <v>1385.91</v>
+        <v>1962.63</v>
       </c>
       <c r="G54" s="14">
-        <v>9.8723404255319149</v>
+        <v>12.884266499843605</v>
       </c>
       <c r="H54" s="30">
-        <v>3812.875</v>
+        <v>4137.2941176470586</v>
       </c>
       <c r="I54" s="15">
-        <v>-22.125</v>
+        <v>542.41176470588266</v>
       </c>
       <c r="J54" s="16">
-        <v>4795</v>
+        <v>3340</v>
       </c>
       <c r="K54" s="13">
-        <v>3883.9500000000003</v>
+        <v>2705.4</v>
       </c>
       <c r="L54" s="14">
-        <v>79.338159255429161</v>
+        <v>52.671614100185536</v>
       </c>
       <c r="M54" s="30">
-        <v>1329.625</v>
+        <v>1395.0588235294117</v>
       </c>
       <c r="N54" s="15">
-        <v>4190.625</v>
+        <v>2705.8823529411766</v>
       </c>
       <c r="O54" s="16">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="P54" s="17">
-        <v>187.92000000000002</v>
+        <v>201.69000000000003</v>
       </c>
       <c r="Q54" s="14">
-        <v>18.842639593908629</v>
+        <v>19.067567567567565</v>
       </c>
       <c r="R54" s="16">
-        <v>270.875</v>
+        <v>287.29411764705884</v>
       </c>
       <c r="S54" s="15">
-        <v>-14.25</v>
+        <v>-12.176470588235304</v>
       </c>
       <c r="T54" s="18">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="U54" s="17">
-        <v>390.42</v>
+        <v>383.13000000000005</v>
       </c>
       <c r="V54" s="14">
-        <v>19.136476426799007</v>
+        <v>19.236842105263158</v>
       </c>
       <c r="W54" s="16">
-        <v>554.125</v>
+        <v>540.94117647058829</v>
       </c>
       <c r="X54" s="15">
-        <v>104.1875</v>
+        <v>79.588235294117624</v>
       </c>
       <c r="Y54" s="18">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Z54" s="17">
-        <v>96.39</v>
+        <v>93.15</v>
       </c>
       <c r="AA54" s="14">
-        <v>14.646153846153846</v>
+        <v>14.589552238805968</v>
       </c>
       <c r="AB54" s="16">
-        <v>178.75</v>
+        <v>173.41176470588238</v>
       </c>
       <c r="AC54" s="15">
-        <v>-43.5</v>
+        <v>-58.411764705882376</v>
       </c>
       <c r="AD54" s="19">
-        <v>7339</v>
+        <v>6600</v>
       </c>
       <c r="AE54" s="20">
-        <v>6201.3600000000006</v>
+        <v>5346</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7002,85 +7002,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>2756</v>
+        <v>2298</v>
       </c>
       <c r="F55" s="14">
-        <v>2232.36</v>
+        <v>1861.38</v>
       </c>
       <c r="G55" s="14">
-        <v>17.687926193341355</v>
+        <v>13.588173913043478</v>
       </c>
       <c r="H55" s="30">
-        <v>3427.875</v>
+        <v>3720.588235294118</v>
       </c>
       <c r="I55" s="15">
-        <v>1197.875</v>
+        <v>606.82352941176464</v>
       </c>
       <c r="J55" s="16">
-        <v>6669</v>
+        <v>6333</v>
       </c>
       <c r="K55" s="13">
-        <v>5401.89</v>
+        <v>5129.7300000000005</v>
       </c>
       <c r="L55" s="14">
-        <v>86.540145985401466</v>
+        <v>81.009029345372468</v>
       </c>
       <c r="M55" s="30">
-        <v>1695.375</v>
+        <v>1719.8823529411764</v>
       </c>
       <c r="N55" s="15">
-        <v>5898.375</v>
+        <v>5551.2352941176468</v>
       </c>
       <c r="O55" s="16">
-        <v>286</v>
+        <v>361</v>
       </c>
       <c r="P55" s="17">
-        <v>231.66000000000003</v>
+        <v>292.41000000000003</v>
       </c>
       <c r="Q55" s="14">
-        <v>16.056140350877193</v>
+        <v>19.669871794871796</v>
       </c>
       <c r="R55" s="16">
-        <v>391.875</v>
+        <v>403.76470588235293</v>
       </c>
       <c r="S55" s="15">
-        <v>-70.25</v>
+        <v>-6.0588235294117112</v>
       </c>
       <c r="T55" s="18">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="U55" s="17">
-        <v>363.69</v>
+        <v>387.99</v>
       </c>
       <c r="V55" s="14">
-        <v>16.1438202247191</v>
+        <v>17.702173913043477</v>
       </c>
       <c r="W55" s="16">
-        <v>611.875</v>
+        <v>595.29411764705878</v>
       </c>
       <c r="X55" s="15">
-        <v>31.8125</v>
+        <v>46.058823529411768</v>
       </c>
       <c r="Y55" s="18">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Z55" s="17">
-        <v>105.30000000000001</v>
+        <v>102.06</v>
       </c>
       <c r="AA55" s="14">
-        <v>15.294117647058824</v>
+        <v>15.3</v>
       </c>
       <c r="AB55" s="16">
-        <v>187</v>
+        <v>181.17647058823528</v>
       </c>
       <c r="AC55" s="15">
-        <v>-40</v>
+        <v>-55.176470588235276</v>
       </c>
       <c r="AD55" s="19">
-        <v>10290</v>
+        <v>9597</v>
       </c>
       <c r="AE55" s="20">
-        <v>8588.43</v>
+        <v>7773.5700000000006</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7115,64 +7115,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>221</v>
+        <v>318</v>
       </c>
       <c r="F56" s="14">
-        <v>579.02</v>
+        <v>833.16000000000008</v>
       </c>
       <c r="G56" s="14">
-        <v>6.4761904761904763</v>
+        <v>9.6363636363636367</v>
       </c>
       <c r="H56" s="30">
-        <v>750.75</v>
+        <v>726</v>
       </c>
       <c r="I56" s="15">
-        <v>-120.25</v>
+        <v>-12</v>
       </c>
       <c r="J56" s="32">
-        <v>346</v>
+        <v>127</v>
       </c>
       <c r="K56" s="13">
-        <v>906.52</v>
+        <v>332.74</v>
       </c>
       <c r="L56" s="14">
-        <v>24.069565217391304</v>
+        <v>9.03347280334728</v>
       </c>
       <c r="M56" s="30">
-        <v>316.25</v>
+        <v>309.29411764705884</v>
       </c>
       <c r="N56" s="15">
-        <v>202.25</v>
+        <v>-13.588235294117652</v>
       </c>
       <c r="O56" s="32">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="P56" s="17">
-        <v>49.78</v>
+        <v>144.1</v>
       </c>
       <c r="Q56" s="14">
-        <v>7.2380952380952381</v>
+        <v>19.479166666666664</v>
       </c>
       <c r="R56" s="16">
-        <v>57.75</v>
+        <v>62.117647058823536</v>
       </c>
       <c r="S56" s="15">
-        <v>-33.5</v>
+        <v>-1.4705882352941231</v>
       </c>
       <c r="T56" s="18">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="U56" s="17">
-        <v>222.70000000000002</v>
+        <v>330.12</v>
       </c>
       <c r="V56" s="14">
-        <v>11.623931623931623</v>
+        <v>17.414634146341463</v>
       </c>
       <c r="W56" s="16">
-        <v>160.875</v>
+        <v>159.1764705882353</v>
       </c>
       <c r="X56" s="15">
-        <v>-24.6875</v>
+        <v>10.235294117647058</v>
       </c>
       <c r="Y56" s="18">
         <v>45</v>
@@ -7181,19 +7181,19 @@
         <v>117.9</v>
       </c>
       <c r="AA56" s="14">
-        <v>23.225806451612904</v>
+        <v>24.677419354838712</v>
       </c>
       <c r="AB56" s="16">
-        <v>42.625</v>
+        <v>40.117647058823529</v>
       </c>
       <c r="AC56" s="15">
-        <v>6.25</v>
+        <v>4.882352941176471</v>
       </c>
       <c r="AD56" s="19">
-        <v>716</v>
+        <v>671</v>
       </c>
       <c r="AE56" s="20">
-        <v>2064.56</v>
+        <v>1758.02</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7228,64 +7228,64 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="F57" s="14">
-        <v>613.08000000000004</v>
+        <v>799.1</v>
       </c>
       <c r="G57" s="14">
-        <v>3.4634597594819612</v>
+        <v>4.6502242152466362</v>
       </c>
       <c r="H57" s="30">
-        <v>1486.375</v>
+        <v>1442.9411764705883</v>
       </c>
       <c r="I57" s="15">
-        <v>-441.625</v>
+        <v>-350.88235294117658</v>
       </c>
       <c r="J57" s="32">
-        <v>407</v>
+        <v>60</v>
       </c>
       <c r="K57" s="13">
-        <v>1066.3400000000001</v>
+        <v>157.20000000000002</v>
       </c>
       <c r="L57" s="14">
-        <v>13.235772357723578</v>
+        <v>2.0278330019880713</v>
       </c>
       <c r="M57" s="30">
-        <v>676.5</v>
+        <v>650.94117647058829</v>
       </c>
       <c r="N57" s="15">
-        <v>99.5</v>
+        <v>-235.88235294117646</v>
       </c>
       <c r="O57" s="32">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="P57" s="17">
-        <v>96.94</v>
+        <v>275.10000000000002</v>
       </c>
       <c r="Q57" s="14">
-        <v>7.3086419753086416</v>
+        <v>16.22727272727273</v>
       </c>
       <c r="R57" s="16">
-        <v>111.375</v>
+        <v>142.35294117647058</v>
       </c>
       <c r="S57" s="15">
-        <v>-64.25</v>
+        <v>-24.411764705882348</v>
       </c>
       <c r="T57" s="18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U57" s="17">
-        <v>0</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="V57" s="14">
-        <v>0</v>
+        <v>6.1445783132530112</v>
       </c>
       <c r="W57" s="16">
-        <v>456.5</v>
+        <v>429.64705882352945</v>
       </c>
       <c r="X57" s="15">
-        <v>-311.25</v>
+        <v>-192.47058823529414</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7294,19 +7294,19 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>30</v>
+        <v>31.874999999999996</v>
       </c>
       <c r="AB57" s="16">
-        <v>44</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="AC57" s="15">
-        <v>20</v>
+        <v>18.588235294117645</v>
       </c>
       <c r="AD57" s="19">
-        <v>738</v>
+        <v>650</v>
       </c>
       <c r="AE57" s="20">
-        <v>1097.78</v>
+        <v>1703</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7341,64 +7341,64 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="F58" s="14">
-        <v>324.88</v>
+        <v>248.9</v>
       </c>
       <c r="G58" s="14">
-        <v>4.9108910891089108</v>
+        <v>3.8089622641509435</v>
       </c>
       <c r="H58" s="30">
-        <v>555.5</v>
+        <v>548.70588235294122</v>
       </c>
       <c r="I58" s="15">
-        <v>-128.5</v>
+        <v>-154.41176470588235</v>
       </c>
       <c r="J58" s="32">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="K58" s="13">
-        <v>298.68</v>
+        <v>154.58000000000001</v>
       </c>
       <c r="L58" s="14">
-        <v>11.4</v>
+        <v>6.1533742331288348</v>
       </c>
       <c r="M58" s="30">
-        <v>220</v>
+        <v>210.94117647058823</v>
       </c>
       <c r="N58" s="15">
-        <v>14</v>
+        <v>-36.882352941176464</v>
       </c>
       <c r="O58" s="32">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="P58" s="17">
-        <v>112.66000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="Q58" s="14">
-        <v>49.142857142857146</v>
+        <v>13.281249999999998</v>
       </c>
       <c r="R58" s="16">
-        <v>19.25</v>
+        <v>41.411764705882355</v>
       </c>
       <c r="S58" s="15">
-        <v>25.5</v>
+        <v>-12.647058823529413</v>
       </c>
       <c r="T58" s="18">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="U58" s="17">
-        <v>136.24</v>
+        <v>262</v>
       </c>
       <c r="V58" s="14">
-        <v>8.9462365591397841</v>
+        <v>18.279569892473116</v>
       </c>
       <c r="W58" s="16">
-        <v>127.875</v>
+        <v>120.35294117647059</v>
       </c>
       <c r="X58" s="15">
-        <v>-35.1875</v>
+        <v>12.470588235294116</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7407,19 +7407,19 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>24.888888888888889</v>
+        <v>26.444444444444446</v>
       </c>
       <c r="AB58" s="16">
-        <v>37.125</v>
+        <v>34.941176470588232</v>
       </c>
       <c r="AC58" s="15">
-        <v>8.25</v>
+        <v>7.058823529411768</v>
       </c>
       <c r="AD58" s="19">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="AE58" s="20">
-        <v>1084.68</v>
+        <v>841.02</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7457,64 +7457,64 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="F59" s="14">
-        <v>547.58000000000004</v>
+        <v>476.84000000000003</v>
       </c>
       <c r="G59" s="14">
-        <v>6.1470588235294121</v>
+        <v>5.6875</v>
       </c>
       <c r="H59" s="30">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="I59" s="15">
-        <v>-131</v>
+        <v>-138</v>
       </c>
       <c r="J59" s="32">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="K59" s="13">
-        <v>434.92</v>
+        <v>136.24</v>
       </c>
       <c r="L59" s="14">
-        <v>13.978947368421053</v>
+        <v>4.5803108808290149</v>
       </c>
       <c r="M59" s="30">
-        <v>261.25</v>
+        <v>249.76470588235296</v>
       </c>
       <c r="N59" s="15">
-        <v>47.25</v>
+        <v>-61.529411764705884</v>
       </c>
       <c r="O59" s="32">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P59" s="17">
-        <v>62.88</v>
+        <v>99.56</v>
       </c>
       <c r="Q59" s="14">
-        <v>13.241379310344827</v>
+        <v>12.666666666666666</v>
       </c>
       <c r="R59" s="16">
-        <v>39.875</v>
+        <v>66</v>
       </c>
       <c r="S59" s="15">
-        <v>-12.25</v>
+        <v>-22</v>
       </c>
       <c r="T59" s="18">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="U59" s="17">
-        <v>102.18</v>
+        <v>290.82</v>
       </c>
       <c r="V59" s="14">
-        <v>6.117647058823529</v>
+        <v>18.5</v>
       </c>
       <c r="W59" s="16">
-        <v>140.25</v>
+        <v>132</v>
       </c>
       <c r="X59" s="15">
-        <v>-56.625</v>
+        <v>15</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7523,19 +7523,19 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>56.533333333333331</v>
+        <v>60.06666666666667</v>
       </c>
       <c r="AB59" s="16">
-        <v>20.625</v>
+        <v>19.411764705882351</v>
       </c>
       <c r="AC59" s="15">
-        <v>34.25</v>
+        <v>33.588235294117652</v>
       </c>
       <c r="AD59" s="19">
-        <v>491</v>
+        <v>436</v>
       </c>
       <c r="AE59" s="20">
-        <v>1464.5800000000002</v>
+        <v>1142.32</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7609,10 +7609,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7642,17 +7642,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>161800.80000000002</v>
+        <v>161502.74999999997</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>35.816464592412196</v>
+        <v>36.554147823588373</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7690,11 +7690,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>219600.30999999997</v>
+        <v>156088.52999999994</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>48.61104968330033</v>
+        <v>35.32870616250564</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7732,11 +7732,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>22806.939999999991</v>
+        <v>37498.729999999996</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.048577998200682</v>
+        <v>8.4873732466897813</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7774,11 +7774,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>52753.3</v>
+        <v>76639.150000000009</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>11.677548575673903</v>
+        <v>17.346322698369928</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7816,11 +7816,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>10860.509999999998</v>
+        <v>9889.4900000000034</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.4040985697879025</v>
+        <v>2.2383636152319335</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7852,19 +7852,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>451749.78000000009</v>
-      </c>
-      <c r="E67" s="69">
+        <v>441817.85000000009</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7964,17 +7964,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>117119</v>
+        <v>119095</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>33.948421842888656</v>
+        <v>36.085238669486543</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8011,11 +8011,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>165257</v>
+        <v>124088</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>47.901829323083788</v>
+        <v>37.598094764845257</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8053,11 +8053,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>17221</v>
+        <v>27021</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>4.9917244217965102</v>
+        <v>8.1872390452008563</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8095,11 +8095,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>38389</v>
+        <v>53423</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>11.127536660376647</v>
+        <v>16.186923929971702</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8137,11 +8137,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>7005</v>
+        <v>6411</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>2.030487751854396</v>
+        <v>1.9425035904956398</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8173,19 +8173,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>344991</v>
-      </c>
-      <c r="E75" s="69">
+        <v>330038</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8732,17 +8732,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8751,6 +8740,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE21835-B095-4FE2-93B1-C9BC69F65256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE3822F-1448-4319-BD51-EE92E462B763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1184,6 +1184,7 @@
       <sheetName val="INVENTARIO NACIONAL 22-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1326,6 +1327,7 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1653,242 +1655,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2253,85 +2255,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>1783</v>
+        <v>1191</v>
       </c>
       <c r="F13" s="14">
-        <v>2424.88</v>
+        <v>1619.7600000000002</v>
       </c>
       <c r="G13" s="14">
-        <v>2.2447604236095682</v>
+        <v>1.5125943695759545</v>
       </c>
       <c r="H13" s="30">
-        <v>17474.470588235294</v>
+        <v>17322.555555555555</v>
       </c>
       <c r="I13" s="15">
-        <v>-6159.9411764705874</v>
+        <v>-6682.8888888888878</v>
       </c>
       <c r="J13" s="16">
-        <v>1319</v>
+        <v>8051</v>
       </c>
       <c r="K13" s="13">
-        <v>1793.8400000000001</v>
+        <v>10949.36</v>
       </c>
       <c r="L13" s="14">
-        <v>5.261145002346316</v>
+        <v>31.997792007065577</v>
       </c>
       <c r="M13" s="30">
-        <v>5515.5294117647063</v>
+        <v>5535.4444444444443</v>
       </c>
       <c r="N13" s="15">
-        <v>-1188.0588235294117</v>
+        <v>5534.8888888888887</v>
       </c>
       <c r="O13" s="16">
-        <v>992</v>
+        <v>969</v>
       </c>
       <c r="P13" s="17">
-        <v>1349.1200000000001</v>
+        <v>1317.8400000000001</v>
       </c>
       <c r="Q13" s="14">
-        <v>20.845488257107537</v>
+        <v>20.813842482100242</v>
       </c>
       <c r="R13" s="16">
-        <v>1046.9411764705883</v>
+        <v>1024.2222222222222</v>
       </c>
       <c r="S13" s="15">
-        <v>40.235294117646959</v>
+        <v>37.888888888889028</v>
       </c>
       <c r="T13" s="18">
-        <v>791</v>
+        <v>642</v>
       </c>
       <c r="U13" s="17">
-        <v>1075.76</v>
+        <v>873.12000000000012</v>
       </c>
       <c r="V13" s="14">
-        <v>16.458996328029372</v>
+        <v>12.940649496080626</v>
       </c>
       <c r="W13" s="16">
-        <v>1057.294117647059</v>
+        <v>1091.4444444444446</v>
       </c>
       <c r="X13" s="15">
-        <v>22.058823529411598</v>
+        <v>-151.77777777777783</v>
       </c>
       <c r="Y13" s="18">
-        <v>75</v>
+        <v>640</v>
       </c>
       <c r="Z13" s="17">
-        <v>102.00000000000001</v>
+        <v>870.40000000000009</v>
       </c>
       <c r="AA13" s="14">
-        <v>2.5653923541247488</v>
+        <v>20.13986013986014</v>
       </c>
       <c r="AB13" s="16">
-        <v>643.17647058823525</v>
+        <v>699.11111111111109</v>
       </c>
       <c r="AC13" s="15">
-        <v>-568.17647058823525</v>
+        <v>-59.111111111111086</v>
       </c>
       <c r="AD13" s="19">
-        <v>4960</v>
+        <v>11493</v>
       </c>
       <c r="AE13" s="20">
-        <v>6745.6</v>
+        <v>15630.480000000001</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2376,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>603.05882352941171</v>
+        <v>569.55555555555554</v>
       </c>
       <c r="I14" s="15">
-        <v>-274.11764705882354</v>
+        <v>-258.88888888888891</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2391,10 +2393,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>322.23529411764707</v>
+        <v>304.33333333333337</v>
       </c>
       <c r="N14" s="15">
-        <v>-146.47058823529414</v>
+        <v>-138.33333333333337</v>
       </c>
       <c r="O14" s="16">
         <v>88</v>
@@ -2403,13 +2405,13 @@
         <v>139.92000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>14.384615384615387</v>
+        <v>15.230769230769232</v>
       </c>
       <c r="R14" s="16">
-        <v>134.58823529411762</v>
+        <v>127.11111111111111</v>
       </c>
       <c r="S14" s="15">
-        <v>-34.352941176470566</v>
+        <v>-27.555555555555557</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2418,34 +2420,34 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>4.4074074074074074</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="W14" s="16">
-        <v>34.941176470588232</v>
+        <v>33</v>
       </c>
       <c r="X14" s="15">
-        <v>-18.411764705882351</v>
+        <v>-17</v>
       </c>
       <c r="Y14" s="18">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Z14" s="17">
-        <v>49.29</v>
+        <v>34.980000000000004</v>
       </c>
       <c r="AA14" s="14">
-        <v>7.9848484848484853</v>
+        <v>5.2799999999999994</v>
       </c>
       <c r="AB14" s="16">
-        <v>85.411764705882348</v>
+        <v>91.666666666666671</v>
       </c>
       <c r="AC14" s="15">
-        <v>-54.411764705882348</v>
+        <v>-69.666666666666671</v>
       </c>
       <c r="AD14" s="19">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="AE14" s="20">
-        <v>200.34</v>
+        <v>186.03</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2481,85 +2483,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1686</v>
+        <v>1418</v>
       </c>
       <c r="F15" s="14">
-        <v>3422.5799999999995</v>
+        <v>2878.5399999999995</v>
       </c>
       <c r="G15" s="14">
-        <v>4.982096297583869</v>
+        <v>4.2118811881188121</v>
       </c>
       <c r="H15" s="30">
-        <v>7445.0588235294126</v>
+        <v>7406.666666666667</v>
       </c>
       <c r="I15" s="15">
-        <v>-1698.1176470588239</v>
+        <v>-1948.666666666667</v>
       </c>
       <c r="J15" s="16">
-        <v>959</v>
+        <v>2656</v>
       </c>
       <c r="K15" s="13">
-        <v>1946.7699999999998</v>
+        <v>5391.6799999999994</v>
       </c>
       <c r="L15" s="14">
-        <v>8.5088726513569934</v>
+        <v>23.21903836813987</v>
       </c>
       <c r="M15" s="30">
-        <v>2479.5294117647059</v>
+        <v>2516.5555555555557</v>
       </c>
       <c r="N15" s="15">
-        <v>-168.05882352941171</v>
+        <v>1512.1111111111111</v>
       </c>
       <c r="O15" s="16">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P15" s="17">
-        <v>466.9</v>
+        <v>444.56999999999994</v>
       </c>
       <c r="Q15" s="14">
-        <v>19.747474747474744</v>
+        <v>18.861244019138756</v>
       </c>
       <c r="R15" s="16">
-        <v>256.23529411764707</v>
+        <v>255.44444444444443</v>
       </c>
       <c r="S15" s="15">
-        <v>-2.9411764705882604</v>
+        <v>-13.222222222222229</v>
       </c>
       <c r="T15" s="18">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="U15" s="17">
-        <v>481.10999999999996</v>
+        <v>326.83</v>
       </c>
       <c r="V15" s="14">
-        <v>15.616279069767442</v>
+        <v>9.3786407766990276</v>
       </c>
       <c r="W15" s="16">
-        <v>333.88235294117646</v>
+        <v>377.66666666666669</v>
       </c>
       <c r="X15" s="15">
-        <v>-5.8235294117646959</v>
+        <v>-113.66666666666669</v>
       </c>
       <c r="Y15" s="18">
-        <v>116</v>
+        <v>221</v>
       </c>
       <c r="Z15" s="17">
-        <v>235.48</v>
+        <v>448.62999999999994</v>
       </c>
       <c r="AA15" s="14">
-        <v>12.805194805194805</v>
+        <v>23.538461538461537</v>
       </c>
       <c r="AB15" s="16">
-        <v>199.29411764705881</v>
+        <v>206.55555555555557</v>
       </c>
       <c r="AC15" s="15">
-        <v>-83.294117647058812</v>
+        <v>14.444444444444429</v>
       </c>
       <c r="AD15" s="19">
-        <v>3228</v>
+        <v>4675</v>
       </c>
       <c r="AE15" s="20">
-        <v>6552.8399999999992</v>
+        <v>9490.2499999999982</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2594,34 +2596,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="F16" s="14">
-        <v>678.68</v>
+        <v>407.93</v>
       </c>
       <c r="G16" s="14">
-        <v>2.5547561950439648</v>
+        <v>1.5190440627333832</v>
       </c>
       <c r="H16" s="30">
-        <v>1618.9411764705883</v>
+        <v>1636.5555555555554</v>
       </c>
       <c r="I16" s="15">
-        <v>-547.88235294117658</v>
+        <v>-630.88888888888891</v>
       </c>
       <c r="J16" s="16">
-        <v>41</v>
+        <v>524</v>
       </c>
       <c r="K16" s="13">
-        <v>148.01</v>
+        <v>1891.6399999999999</v>
       </c>
       <c r="L16" s="14">
-        <v>1.4861407249466949</v>
+        <v>19.170731707317078</v>
       </c>
       <c r="M16" s="30">
-        <v>606.94117647058829</v>
+        <v>601.33333333333326</v>
       </c>
       <c r="N16" s="15">
-        <v>-234.88235294117646</v>
+        <v>250.66666666666674</v>
       </c>
       <c r="O16" s="16">
         <v>44</v>
@@ -2630,49 +2632,49 @@
         <v>158.84</v>
       </c>
       <c r="Q16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R16" s="16">
-        <v>56.941176470588239</v>
+        <v>53.777777777777786</v>
       </c>
       <c r="S16" s="15">
-        <v>-7.764705882352942</v>
+        <v>-4.8888888888888928</v>
       </c>
       <c r="T16" s="18">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U16" s="17">
-        <v>166.06</v>
+        <v>140.79</v>
       </c>
       <c r="V16" s="14">
-        <v>55.857142857142861</v>
+        <v>33.428571428571423</v>
       </c>
       <c r="W16" s="16">
-        <v>18.117647058823529</v>
+        <v>25.666666666666668</v>
       </c>
       <c r="X16" s="15">
-        <v>32.82352941176471</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="Y16" s="18">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="Z16" s="17">
-        <v>90.25</v>
+        <v>292.40999999999997</v>
       </c>
       <c r="AA16" s="14">
-        <v>7.4561403508771926</v>
+        <v>25.578947368421058</v>
       </c>
       <c r="AB16" s="16">
-        <v>73.764705882352942</v>
+        <v>69.666666666666657</v>
       </c>
       <c r="AC16" s="15">
-        <v>-48.764705882352942</v>
+        <v>11.333333333333343</v>
       </c>
       <c r="AD16" s="19">
-        <v>344</v>
+        <v>801</v>
       </c>
       <c r="AE16" s="20">
-        <v>1241.8399999999999</v>
+        <v>2891.61</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2707,49 +2709,49 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F17" s="14">
-        <v>131.69999999999999</v>
+        <v>79.02</v>
       </c>
       <c r="G17" s="14">
-        <v>1.4406779661016949</v>
+        <v>0.86631016042780751</v>
       </c>
       <c r="H17" s="30">
-        <v>229.05882352941177</v>
+        <v>228.55555555555557</v>
       </c>
       <c r="I17" s="15">
-        <v>-89.117647058823536</v>
+        <v>-94.888888888888886</v>
       </c>
       <c r="J17" s="16">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="K17" s="13">
-        <v>166.82</v>
+        <v>1044.82</v>
       </c>
       <c r="L17" s="14">
-        <v>8.5</v>
+        <v>56.368421052631575</v>
       </c>
       <c r="M17" s="30">
-        <v>49.176470588235297</v>
+        <v>46.444444444444443</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.352941176470587</v>
+        <v>97.888888888888886</v>
       </c>
       <c r="O17" s="16">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P17" s="17">
-        <v>166.82</v>
+        <v>122.91999999999999</v>
       </c>
       <c r="Q17" s="14">
-        <v>29.363636363636363</v>
+        <v>22.909090909090907</v>
       </c>
       <c r="R17" s="16">
-        <v>14.23529411764706</v>
+        <v>13.444444444444446</v>
       </c>
       <c r="S17" s="15">
-        <v>6.0588235294117645</v>
+        <v>1.7777777777777768</v>
       </c>
       <c r="T17" s="18">
         <v>17</v>
@@ -2767,25 +2769,25 @@
         <v>15.545454545454545</v>
       </c>
       <c r="Y17" s="18">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z17" s="17">
-        <v>70.239999999999995</v>
+        <v>114.13999999999999</v>
       </c>
       <c r="AA17" s="14">
-        <v>15.111111111111111</v>
+        <v>26</v>
       </c>
       <c r="AB17" s="16">
-        <v>11.647058823529411</v>
+        <v>11</v>
       </c>
       <c r="AC17" s="15">
-        <v>-3.6470588235294112</v>
+        <v>2</v>
       </c>
       <c r="AD17" s="19">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="AE17" s="20">
-        <v>684.83999999999992</v>
+        <v>1510.1599999999999</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2820,85 +2822,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>7727</v>
+        <v>7062</v>
       </c>
       <c r="F18" s="14">
-        <v>4868.01</v>
+        <v>4449.0600000000004</v>
       </c>
       <c r="G18" s="14">
-        <v>9.2833215547703176</v>
+        <v>8.4586105935586922</v>
       </c>
       <c r="H18" s="30">
-        <v>18311.764705882353</v>
+        <v>18367.555555555555</v>
       </c>
       <c r="I18" s="15">
-        <v>-596.52941176470631</v>
+        <v>-1286.8888888888887</v>
       </c>
       <c r="J18" s="16">
-        <v>4517</v>
+        <v>4220</v>
       </c>
       <c r="K18" s="13">
-        <v>2845.71</v>
+        <v>2658.6</v>
       </c>
       <c r="L18" s="14">
-        <v>13.250905953408111</v>
+        <v>12.057142857142857</v>
       </c>
       <c r="M18" s="30">
-        <v>7499.411764705882</v>
+        <v>7700</v>
       </c>
       <c r="N18" s="15">
-        <v>1108.1764705882351</v>
+        <v>720</v>
       </c>
       <c r="O18" s="16">
-        <v>1205</v>
+        <v>1081</v>
       </c>
       <c r="P18" s="17">
-        <v>759.15</v>
+        <v>681.03</v>
       </c>
       <c r="Q18" s="14">
-        <v>21.654334038054969</v>
+        <v>18.513796384395814</v>
       </c>
       <c r="R18" s="16">
-        <v>1224.2352941176471</v>
+        <v>1284.5555555555554</v>
       </c>
       <c r="S18" s="15">
-        <v>92.058823529411711</v>
+        <v>-86.777777777777828</v>
       </c>
       <c r="T18" s="18">
-        <v>2416</v>
+        <v>1960</v>
       </c>
       <c r="U18" s="17">
-        <v>1522.08</v>
+        <v>1234.8</v>
       </c>
       <c r="V18" s="14">
-        <v>15.077826725403817</v>
+        <v>11.922946941534303</v>
       </c>
       <c r="W18" s="16">
-        <v>3525.1764705882356</v>
+        <v>3616.5555555555557</v>
       </c>
       <c r="X18" s="15">
-        <v>-147.76470588235316</v>
+        <v>-670.22222222222217</v>
       </c>
       <c r="Y18" s="18">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="Z18" s="17">
-        <v>112.77</v>
+        <v>208.53</v>
       </c>
       <c r="AA18" s="14">
-        <v>13.230434782608695</v>
+        <v>23.09302325581395</v>
       </c>
       <c r="AB18" s="16">
-        <v>297.64705882352939</v>
+        <v>315.33333333333337</v>
       </c>
       <c r="AC18" s="15">
-        <v>-118.64705882352939</v>
+        <v>15.666666666666629</v>
       </c>
       <c r="AD18" s="19">
-        <v>16044</v>
+        <v>14654</v>
       </c>
       <c r="AE18" s="20">
-        <v>10107.719999999999</v>
+        <v>9232.02</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2933,85 +2935,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>461</v>
+        <v>369</v>
       </c>
       <c r="F19" s="14">
-        <v>290.43</v>
+        <v>232.47</v>
       </c>
       <c r="G19" s="14">
-        <v>7.4496197718631176</v>
+        <v>5.6575809199318563</v>
       </c>
       <c r="H19" s="30">
-        <v>1361.4117647058824</v>
+        <v>1434.8888888888891</v>
       </c>
       <c r="I19" s="15">
-        <v>-157.82352941176475</v>
+        <v>-283.22222222222229</v>
       </c>
       <c r="J19" s="16">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="K19" s="13">
-        <v>125.37</v>
+        <v>78.75</v>
       </c>
       <c r="L19" s="14">
-        <v>3.5093360995850622</v>
+        <v>2.1510516252390057</v>
       </c>
       <c r="M19" s="30">
-        <v>1247.5294117647059</v>
+        <v>1278.4444444444446</v>
       </c>
       <c r="N19" s="15">
-        <v>-368.05882352941171</v>
+        <v>-456.11111111111109</v>
       </c>
       <c r="O19" s="16">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="P19" s="17">
-        <v>87.570000000000007</v>
+        <v>79.38</v>
       </c>
       <c r="Q19" s="14">
-        <v>29.911392405063289</v>
+        <v>24.65217391304348</v>
       </c>
       <c r="R19" s="16">
-        <v>102.23529411764707</v>
+        <v>112.44444444444443</v>
       </c>
       <c r="S19" s="15">
-        <v>46.058823529411754</v>
+        <v>23.777777777777786</v>
       </c>
       <c r="T19" s="18">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="U19" s="17">
-        <v>143.01</v>
+        <v>114.03</v>
       </c>
       <c r="V19" s="14">
-        <v>17.701834862385319</v>
+        <v>13.243902439024392</v>
       </c>
       <c r="W19" s="16">
-        <v>282.11764705882354</v>
+        <v>300.66666666666663</v>
       </c>
       <c r="X19" s="15">
-        <v>21.823529411764696</v>
+        <v>-37.666666666666629</v>
       </c>
       <c r="Y19" s="18">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="Z19" s="17">
-        <v>83.79</v>
+        <v>148.68</v>
       </c>
       <c r="AA19" s="14">
-        <v>12.994252873563219</v>
+        <v>22.240837696335081</v>
       </c>
       <c r="AB19" s="16">
-        <v>225.17647058823528</v>
+        <v>233.44444444444443</v>
       </c>
       <c r="AC19" s="15">
-        <v>-92.176470588235276</v>
+        <v>2.5555555555555713</v>
       </c>
       <c r="AD19" s="19">
-        <v>1159</v>
+        <v>1037</v>
       </c>
       <c r="AE19" s="20">
-        <v>730.17</v>
+        <v>653.31000000000006</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3046,85 +3048,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1117</v>
+        <v>896</v>
       </c>
       <c r="F20" s="14">
-        <v>703.71</v>
+        <v>564.48</v>
       </c>
       <c r="G20" s="14">
-        <v>8.248913987836664</v>
+        <v>6.656211308295501</v>
       </c>
       <c r="H20" s="30">
-        <v>2979.0588235294117</v>
+        <v>2961.4444444444443</v>
       </c>
       <c r="I20" s="15">
-        <v>-237.11764705882342</v>
+        <v>-450.11111111111109</v>
       </c>
       <c r="J20" s="16">
-        <v>2171</v>
+        <v>2062</v>
       </c>
       <c r="K20" s="13">
-        <v>1367.73</v>
+        <v>1299.06</v>
       </c>
       <c r="L20" s="14">
-        <v>16.527989252127185</v>
+        <v>15.568791946308723</v>
       </c>
       <c r="M20" s="30">
-        <v>2889.7647058823527</v>
+        <v>2913.7777777777783</v>
       </c>
       <c r="N20" s="15">
-        <v>857.47058823529414</v>
+        <v>737.55555555555543</v>
       </c>
       <c r="O20" s="16">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="P20" s="17">
-        <v>151.83000000000001</v>
+        <v>142.38</v>
       </c>
       <c r="Q20" s="14">
-        <v>25.767295597484274</v>
+        <v>23.379310344827587</v>
       </c>
       <c r="R20" s="16">
-        <v>205.76470588235296</v>
+        <v>212.66666666666666</v>
       </c>
       <c r="S20" s="15">
-        <v>53.941176470588232</v>
+        <v>32.666666666666686</v>
       </c>
       <c r="T20" s="18">
-        <v>584</v>
+        <v>441</v>
       </c>
       <c r="U20" s="17">
-        <v>367.92</v>
+        <v>277.83</v>
       </c>
       <c r="V20" s="14">
-        <v>21.724288840262584</v>
+        <v>14.7</v>
       </c>
       <c r="W20" s="16">
-        <v>591.41176470588232</v>
+        <v>660</v>
       </c>
       <c r="X20" s="15">
-        <v>153.88235294117652</v>
+        <v>-39</v>
       </c>
       <c r="Y20" s="18">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="Z20" s="17">
-        <v>125.37</v>
+        <v>183.33</v>
       </c>
       <c r="AA20" s="14">
-        <v>15.447488584474886</v>
+        <v>21.206477732793523</v>
       </c>
       <c r="AB20" s="16">
-        <v>283.41176470588238</v>
+        <v>301.88888888888886</v>
       </c>
       <c r="AC20" s="15">
-        <v>-84.411764705882376</v>
+        <v>-10.888888888888857</v>
       </c>
       <c r="AD20" s="19">
-        <v>4312</v>
+        <v>3916</v>
       </c>
       <c r="AE20" s="20">
-        <v>2716.56</v>
+        <v>2467.08</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3159,85 +3161,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2444</v>
+        <v>2195</v>
       </c>
       <c r="F21" s="14">
-        <v>2663.96</v>
+        <v>2392.5500000000002</v>
       </c>
       <c r="G21" s="14">
-        <v>7.8853672423609797</v>
+        <v>7.0793764558322883</v>
       </c>
       <c r="H21" s="30">
-        <v>6818.7058823529414</v>
+        <v>6821.2222222222217</v>
       </c>
       <c r="I21" s="15">
-        <v>-655.41176470588243</v>
+        <v>-905.55555555555566</v>
       </c>
       <c r="J21" s="16">
-        <v>3085</v>
+        <v>2767</v>
       </c>
       <c r="K21" s="13">
-        <v>3362.65</v>
+        <v>3016.03</v>
       </c>
       <c r="L21" s="14">
-        <v>8.9710913445090661</v>
+        <v>7.9842898364860533</v>
       </c>
       <c r="M21" s="30">
-        <v>7565.411764705882</v>
+        <v>7624.2222222222217</v>
       </c>
       <c r="N21" s="15">
-        <v>-353.82352941176487</v>
+        <v>-698.55555555555566</v>
       </c>
       <c r="O21" s="16">
-        <v>605</v>
+        <v>540</v>
       </c>
       <c r="P21" s="17">
-        <v>659.45</v>
+        <v>588.6</v>
       </c>
       <c r="Q21" s="14">
-        <v>22.118279569892476</v>
+        <v>20.334728033472803</v>
       </c>
       <c r="R21" s="16">
-        <v>601.76470588235293</v>
+        <v>584.22222222222229</v>
       </c>
       <c r="S21" s="15">
-        <v>57.941176470588289</v>
+        <v>8.8888888888889142</v>
       </c>
       <c r="T21" s="18">
-        <v>1234</v>
+        <v>995</v>
       </c>
       <c r="U21" s="17">
-        <v>1345.0600000000002</v>
+        <v>1084.5500000000002</v>
       </c>
       <c r="V21" s="14">
-        <v>15.643549589858315</v>
+        <v>11.971925133689838</v>
       </c>
       <c r="W21" s="16">
-        <v>1735.4117647058822</v>
+        <v>1828.4444444444446</v>
       </c>
       <c r="X21" s="15">
-        <v>-28.117647058823422</v>
+        <v>-334.77777777777783</v>
       </c>
       <c r="Y21" s="18">
-        <v>206</v>
+        <v>400</v>
       </c>
       <c r="Z21" s="17">
-        <v>224.54000000000002</v>
+        <v>436.00000000000006</v>
       </c>
       <c r="AA21" s="14">
-        <v>11.012578616352201</v>
+        <v>21.176470588235293</v>
       </c>
       <c r="AB21" s="16">
-        <v>411.52941176470591</v>
+        <v>415.55555555555554</v>
       </c>
       <c r="AC21" s="15">
-        <v>-205.52941176470591</v>
+        <v>-15.555555555555543</v>
       </c>
       <c r="AD21" s="19">
-        <v>7574</v>
+        <v>6897</v>
       </c>
       <c r="AE21" s="20">
-        <v>8255.66</v>
+        <v>7517.7300000000005</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3272,85 +3274,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1395</v>
+        <v>1212</v>
       </c>
       <c r="F22" s="14">
-        <v>1520.5500000000002</v>
+        <v>1321.0800000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>7.6648351648351651</v>
+        <v>6.5572587917042373</v>
       </c>
       <c r="H22" s="30">
-        <v>4004</v>
+        <v>4066.3333333333335</v>
       </c>
       <c r="I22" s="15">
-        <v>-425</v>
+        <v>-636.33333333333348</v>
       </c>
       <c r="J22" s="16">
-        <v>3300</v>
+        <v>3189</v>
       </c>
       <c r="K22" s="13">
-        <v>3597.0000000000005</v>
+        <v>3476.01</v>
       </c>
       <c r="L22" s="14">
-        <v>21.090225563909776</v>
+        <v>20.603732950466618</v>
       </c>
       <c r="M22" s="30">
-        <v>3442.3529411764707</v>
+        <v>3405.1111111111109</v>
       </c>
       <c r="N22" s="15">
-        <v>1735.2941176470588</v>
+        <v>1641.2222222222222</v>
       </c>
       <c r="O22" s="16">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="P22" s="17">
-        <v>140.61000000000001</v>
+        <v>132.98000000000002</v>
       </c>
       <c r="Q22" s="14">
-        <v>15.891304347826088</v>
+        <v>15.144827586206898</v>
       </c>
       <c r="R22" s="16">
-        <v>178.58823529411762</v>
+        <v>177.22222222222223</v>
       </c>
       <c r="S22" s="15">
-        <v>-33.35294117647058</v>
+        <v>-39.111111111111114</v>
       </c>
       <c r="T22" s="18">
-        <v>409</v>
+        <v>345</v>
       </c>
       <c r="U22" s="17">
-        <v>445.81000000000006</v>
+        <v>376.05</v>
       </c>
       <c r="V22" s="14">
-        <v>16.673860911270978</v>
+        <v>13.708609271523176</v>
       </c>
       <c r="W22" s="16">
-        <v>539.64705882352951</v>
+        <v>553.66666666666674</v>
       </c>
       <c r="X22" s="15">
-        <v>16.529411764705799</v>
+        <v>-57.666666666666742</v>
       </c>
       <c r="Y22" s="18">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="Z22" s="17">
-        <v>116.63000000000001</v>
+        <v>54.500000000000007</v>
       </c>
       <c r="AA22" s="14">
-        <v>19.771739130434781</v>
+        <v>6.0402684563758386</v>
       </c>
       <c r="AB22" s="16">
-        <v>119.05882352941177</v>
+        <v>182.11111111111114</v>
       </c>
       <c r="AC22" s="15">
-        <v>-12.058823529411768</v>
+        <v>-132.11111111111114</v>
       </c>
       <c r="AD22" s="19">
-        <v>5340</v>
+        <v>4918</v>
       </c>
       <c r="AE22" s="20">
-        <v>5820.6</v>
+        <v>5360.6200000000008</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3385,85 +3387,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>21486</v>
+        <v>20177</v>
       </c>
       <c r="F23" s="14">
-        <v>24923.759999999998</v>
+        <v>23405.32</v>
       </c>
       <c r="G23" s="14">
-        <v>12.97740353869111</v>
+        <v>12.1931780030887</v>
       </c>
       <c r="H23" s="30">
-        <v>36424.23529411765</v>
+        <v>36405.111111111109</v>
       </c>
       <c r="I23" s="15">
-        <v>-3348.7058823529442</v>
+        <v>-4644.6666666666642</v>
       </c>
       <c r="J23" s="16">
-        <v>14839</v>
+        <v>13824</v>
       </c>
       <c r="K23" s="13">
-        <v>17213.239999999998</v>
+        <v>16035.839999999998</v>
       </c>
       <c r="L23" s="14">
-        <v>15.209393464367539</v>
+        <v>14.059099384145997</v>
       </c>
       <c r="M23" s="30">
-        <v>21464.235294117647</v>
+        <v>21632.111111111113</v>
       </c>
       <c r="N23" s="15">
-        <v>5082.5294117647063</v>
+        <v>3991.2222222222226</v>
       </c>
       <c r="O23" s="16">
-        <v>3044</v>
+        <v>2792</v>
       </c>
       <c r="P23" s="17">
-        <v>3531.04</v>
+        <v>3238.72</v>
       </c>
       <c r="Q23" s="14">
-        <v>20.649640861931367</v>
+        <v>18.599555884529977</v>
       </c>
       <c r="R23" s="16">
-        <v>3243.0588235294117</v>
+        <v>3302.4444444444443</v>
       </c>
       <c r="S23" s="15">
-        <v>95.764705882353155</v>
+        <v>-210.22222222222217</v>
       </c>
       <c r="T23" s="18">
-        <v>8360</v>
+        <v>6963</v>
       </c>
       <c r="U23" s="17">
-        <v>9697.5999999999985</v>
+        <v>8077.079999999999</v>
       </c>
       <c r="V23" s="14">
-        <v>14.861445153194605</v>
+        <v>12.349394028968371</v>
       </c>
       <c r="W23" s="16">
-        <v>12375.647058823528</v>
+        <v>12404.333333333334</v>
       </c>
       <c r="X23" s="15">
-        <v>-640.47058823529369</v>
+        <v>-2058.3333333333339</v>
       </c>
       <c r="Y23" s="18">
-        <v>1</v>
+        <v>1243</v>
       </c>
       <c r="Z23" s="17">
-        <v>1.1599999999999999</v>
+        <v>1441.8799999999999</v>
       </c>
       <c r="AA23" s="14">
-        <v>1.8660812294182216E-2</v>
+        <v>24.559824368825463</v>
       </c>
       <c r="AB23" s="16">
-        <v>1178.9411764705883</v>
+        <v>1113.4444444444446</v>
       </c>
       <c r="AC23" s="15">
-        <v>-1177.9411764705883</v>
+        <v>129.55555555555543</v>
       </c>
       <c r="AD23" s="19">
-        <v>47730</v>
+        <v>44999</v>
       </c>
       <c r="AE23" s="20">
-        <v>55366.799999999996</v>
+        <v>52198.84</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3498,85 +3500,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>8777</v>
+        <v>7961</v>
       </c>
       <c r="F24" s="14">
-        <v>10181.32</v>
+        <v>9234.76</v>
       </c>
       <c r="G24" s="14">
-        <v>8.0371128467546455</v>
+        <v>7.2475217479263616</v>
       </c>
       <c r="H24" s="30">
-        <v>24025.294117647056</v>
+        <v>24165.777777777774</v>
       </c>
       <c r="I24" s="15">
-        <v>-2143.5882352941171</v>
+        <v>-3023.4444444444434</v>
       </c>
       <c r="J24" s="16">
-        <v>13886</v>
+        <v>13188</v>
       </c>
       <c r="K24" s="13">
-        <v>16107.759999999998</v>
+        <v>15298.079999999998</v>
       </c>
       <c r="L24" s="14">
-        <v>23.458412004372452</v>
+        <v>21.925187032418954</v>
       </c>
       <c r="M24" s="30">
-        <v>13022.705882352942</v>
+        <v>13233</v>
       </c>
       <c r="N24" s="15">
-        <v>7966.5882352941171</v>
+        <v>7173</v>
       </c>
       <c r="O24" s="16">
-        <v>1743</v>
+        <v>1574</v>
       </c>
       <c r="P24" s="17">
-        <v>2021.8799999999999</v>
+        <v>1825.84</v>
       </c>
       <c r="Q24" s="14">
-        <v>19.940107671601616</v>
+        <v>17.763009404388715</v>
       </c>
       <c r="R24" s="16">
-        <v>1923.0588235294117</v>
+        <v>1949.4444444444446</v>
       </c>
       <c r="S24" s="15">
-        <v>-5.2352941176468448</v>
+        <v>-198.22222222222217</v>
       </c>
       <c r="T24" s="18">
-        <v>4623</v>
+        <v>3972</v>
       </c>
       <c r="U24" s="17">
-        <v>5362.6799999999994</v>
+        <v>4607.5199999999995</v>
       </c>
       <c r="V24" s="14">
-        <v>15.699360767079503</v>
+        <v>13.237548602110721</v>
       </c>
       <c r="W24" s="16">
-        <v>6478.3529411764712</v>
+        <v>6601.2222222222217</v>
       </c>
       <c r="X24" s="15">
-        <v>-88.52941176470631</v>
+        <v>-828.88888888888869</v>
       </c>
       <c r="Y24" s="18">
-        <v>298</v>
+        <v>744</v>
       </c>
       <c r="Z24" s="17">
-        <v>345.67999999999995</v>
+        <v>863.04</v>
       </c>
       <c r="AA24" s="14">
-        <v>7.965408805031446</v>
+        <v>18.446280991735534</v>
       </c>
       <c r="AB24" s="16">
-        <v>823.05882352941182</v>
+        <v>887.33333333333337</v>
       </c>
       <c r="AC24" s="15">
-        <v>-525.05882352941182</v>
+        <v>-143.33333333333337</v>
       </c>
       <c r="AD24" s="19">
-        <v>29327</v>
+        <v>27439</v>
       </c>
       <c r="AE24" s="20">
-        <v>34019.32</v>
+        <v>31829.239999999998</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3611,85 +3613,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>9487</v>
+        <v>8472</v>
       </c>
       <c r="F25" s="14">
-        <v>11004.92</v>
+        <v>9827.5199999999986</v>
       </c>
       <c r="G25" s="14">
-        <v>8.9212855404358891</v>
+        <v>7.9338223817699394</v>
       </c>
       <c r="H25" s="30">
-        <v>23395.058823529413</v>
+        <v>23492.333333333332</v>
       </c>
       <c r="I25" s="15">
-        <v>-1147.1176470588252</v>
+        <v>-2206.3333333333321</v>
       </c>
       <c r="J25" s="16">
-        <v>10090</v>
+        <v>19047</v>
       </c>
       <c r="K25" s="13">
-        <v>11704.4</v>
+        <v>22094.519999999997</v>
       </c>
       <c r="L25" s="14">
-        <v>15.907446907168692</v>
+        <v>29.828258221680876</v>
       </c>
       <c r="M25" s="30">
-        <v>13954.470588235294</v>
+        <v>14048.222222222223</v>
       </c>
       <c r="N25" s="15">
-        <v>3747.0588235294126</v>
+        <v>12661.444444444445</v>
       </c>
       <c r="O25" s="16">
-        <v>2157</v>
+        <v>1967</v>
       </c>
       <c r="P25" s="17">
-        <v>2502.12</v>
+        <v>2281.7199999999998</v>
       </c>
       <c r="Q25" s="14">
-        <v>20.417037861915368</v>
+        <v>18.421436004162331</v>
       </c>
       <c r="R25" s="16">
-        <v>2324.2352941176468</v>
+        <v>2349.1111111111109</v>
       </c>
       <c r="S25" s="15">
-        <v>44.058823529411711</v>
+        <v>-168.55555555555566</v>
       </c>
       <c r="T25" s="18">
-        <v>4700</v>
+        <v>4030</v>
       </c>
       <c r="U25" s="17">
-        <v>5452</v>
+        <v>4674.7999999999993</v>
       </c>
       <c r="V25" s="14">
-        <v>15.648256952604777</v>
+        <v>13.280849505675576</v>
       </c>
       <c r="W25" s="16">
-        <v>6607.7647058823532</v>
+        <v>6675.7777777777783</v>
       </c>
       <c r="X25" s="15">
-        <v>-105.64705882352973</v>
+        <v>-825.11111111111131</v>
       </c>
       <c r="Y25" s="18">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="Z25" s="17">
-        <v>593.91999999999996</v>
+        <v>624.07999999999993</v>
       </c>
       <c r="AA25" s="14">
-        <v>19.256637168141591</v>
+        <v>18.445714285714281</v>
       </c>
       <c r="AB25" s="16">
-        <v>584.94117647058829</v>
+        <v>641.66666666666674</v>
       </c>
       <c r="AC25" s="15">
-        <v>-72.941176470588289</v>
+        <v>-103.66666666666674</v>
       </c>
       <c r="AD25" s="19">
-        <v>26946</v>
+        <v>34054</v>
       </c>
       <c r="AE25" s="20">
-        <v>31257.359999999997</v>
+        <v>39502.639999999999</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3724,85 +3726,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>16443</v>
+        <v>17010</v>
       </c>
       <c r="F26" s="14">
-        <v>19073.879999999997</v>
+        <v>19731.599999999999</v>
       </c>
       <c r="G26" s="14">
-        <v>11.838514314755209</v>
+        <v>12.254552731638983</v>
       </c>
       <c r="H26" s="30">
-        <v>30556.705882352944</v>
+        <v>30537.222222222226</v>
       </c>
       <c r="I26" s="15">
-        <v>-4391.1176470588252</v>
+        <v>-3810.8333333333358</v>
       </c>
       <c r="J26" s="16">
-        <v>13264</v>
+        <v>12463</v>
       </c>
       <c r="K26" s="13">
-        <v>15386.24</v>
+        <v>14457.079999999998</v>
       </c>
       <c r="L26" s="14">
-        <v>17.836418288245532</v>
+        <v>16.598890122086566</v>
       </c>
       <c r="M26" s="30">
-        <v>16360.235294117647</v>
+        <v>16518.333333333336</v>
       </c>
       <c r="N26" s="15">
-        <v>5827.5294117647063</v>
+        <v>4954.6666666666652</v>
       </c>
       <c r="O26" s="16">
-        <v>1693</v>
+        <v>1531</v>
       </c>
       <c r="P26" s="17">
-        <v>1963.8799999999999</v>
+        <v>1775.9599999999998</v>
       </c>
       <c r="Q26" s="14">
-        <v>20.239803094233476</v>
+        <v>18</v>
       </c>
       <c r="R26" s="16">
-        <v>1840.2352941176468</v>
+        <v>1871.2222222222222</v>
       </c>
       <c r="S26" s="15">
-        <v>20.058823529411939</v>
+        <v>-170.11111111111109</v>
       </c>
       <c r="T26" s="18">
-        <v>5575</v>
+        <v>4710</v>
       </c>
       <c r="U26" s="17">
-        <v>6467</v>
+        <v>5463.5999999999995</v>
       </c>
       <c r="V26" s="14">
-        <v>14.799344159900061</v>
+        <v>12.297650130548304</v>
       </c>
       <c r="W26" s="16">
-        <v>8287.5294117647063</v>
+        <v>8426</v>
       </c>
       <c r="X26" s="15">
-        <v>-452.29411764705947</v>
+        <v>-1418</v>
       </c>
       <c r="Y26" s="18">
-        <v>394</v>
+        <v>909</v>
       </c>
       <c r="Z26" s="17">
-        <v>457.03999999999996</v>
+        <v>1054.4399999999998</v>
       </c>
       <c r="AA26" s="14">
-        <v>9.3417015341701521</v>
+        <v>20.555276381909547</v>
       </c>
       <c r="AB26" s="16">
-        <v>927.88235294117658</v>
+        <v>972.88888888888891</v>
       </c>
       <c r="AC26" s="15">
-        <v>-533.88235294117658</v>
+        <v>-63.888888888888914</v>
       </c>
       <c r="AD26" s="19">
-        <v>37369</v>
+        <v>36623</v>
       </c>
       <c r="AE26" s="20">
-        <v>43348.039999999994</v>
+        <v>42482.68</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3837,85 +3839,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>2716</v>
+        <v>2389</v>
       </c>
       <c r="F27" s="14">
-        <v>3150.56</v>
+        <v>2771.24</v>
       </c>
       <c r="G27" s="14">
-        <v>7.6254335260115607</v>
+        <v>6.6330402591392872</v>
       </c>
       <c r="H27" s="30">
-        <v>7835.8823529411766</v>
+        <v>7923.666666666667</v>
       </c>
       <c r="I27" s="15">
-        <v>-845.76470588235316</v>
+        <v>-1212.666666666667</v>
       </c>
       <c r="J27" s="16">
-        <v>4705</v>
+        <v>4486</v>
       </c>
       <c r="K27" s="13">
-        <v>5457.7999999999993</v>
+        <v>5203.7599999999993</v>
       </c>
       <c r="L27" s="14">
-        <v>23.545775684427436</v>
+        <v>22.0382096069869</v>
       </c>
       <c r="M27" s="30">
-        <v>4396.1176470588234</v>
+        <v>4478.2222222222217</v>
       </c>
       <c r="N27" s="15">
-        <v>2706.7647058823532</v>
+        <v>2450.4444444444443</v>
       </c>
       <c r="O27" s="16">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="P27" s="17">
-        <v>728.4799999999999</v>
+        <v>696</v>
       </c>
       <c r="Q27" s="14">
-        <v>21.309381237524953</v>
+        <v>20.224719101123593</v>
       </c>
       <c r="R27" s="16">
-        <v>648.35294117647049</v>
+        <v>652.66666666666674</v>
       </c>
       <c r="S27" s="15">
-        <v>38.588235294117794</v>
+        <v>6.6666666666665151</v>
       </c>
       <c r="T27" s="18">
-        <v>1890</v>
+        <v>1667</v>
       </c>
       <c r="U27" s="17">
-        <v>2192.3999999999996</v>
+        <v>1933.7199999999998</v>
       </c>
       <c r="V27" s="14">
-        <v>15.657894736842106</v>
+        <v>13.814917127071821</v>
       </c>
       <c r="W27" s="16">
-        <v>2655.5294117647059</v>
+        <v>2654.666666666667</v>
       </c>
       <c r="X27" s="15">
-        <v>-41.294117647058783</v>
+        <v>-263.66666666666697</v>
       </c>
       <c r="Y27" s="18">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="Z27" s="17">
-        <v>454.71999999999997</v>
+        <v>407.15999999999997</v>
       </c>
       <c r="AA27" s="14">
-        <v>32.349514563106794</v>
+        <v>26.771186440677962</v>
       </c>
       <c r="AB27" s="16">
-        <v>266.58823529411762</v>
+        <v>288.44444444444446</v>
       </c>
       <c r="AC27" s="15">
-        <v>125.41176470588238</v>
+        <v>62.555555555555543</v>
       </c>
       <c r="AD27" s="19">
-        <v>10331</v>
+        <v>9493</v>
       </c>
       <c r="AE27" s="20">
-        <v>11983.96</v>
+        <v>11011.88</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3950,85 +3952,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>2342</v>
+        <v>2015</v>
       </c>
       <c r="F28" s="14">
-        <v>2716.72</v>
+        <v>2337.3999999999996</v>
       </c>
       <c r="G28" s="14">
-        <v>6.5429745275267051</v>
+        <v>5.5264360810604911</v>
       </c>
       <c r="H28" s="30">
-        <v>7874.7058823529414</v>
+        <v>8021.4444444444434</v>
       </c>
       <c r="I28" s="15">
-        <v>-1237.4117647058824</v>
+        <v>-1631.1111111111109</v>
       </c>
       <c r="J28" s="16">
-        <v>7242</v>
+        <v>6913</v>
       </c>
       <c r="K28" s="13">
-        <v>8400.7199999999993</v>
+        <v>8019.079999999999</v>
       </c>
       <c r="L28" s="14">
-        <v>25.793840351979888</v>
+        <v>24.115116279069767</v>
       </c>
       <c r="M28" s="30">
-        <v>6176.823529411764</v>
+        <v>6306.666666666667</v>
       </c>
       <c r="N28" s="15">
-        <v>4434.3529411764703</v>
+        <v>4046.333333333333</v>
       </c>
       <c r="O28" s="16">
-        <v>821</v>
+        <v>750</v>
       </c>
       <c r="P28" s="17">
-        <v>952.3599999999999</v>
+        <v>869.99999999999989</v>
       </c>
       <c r="Q28" s="14">
-        <v>20.464809384164223</v>
+        <v>18.417462482946796</v>
       </c>
       <c r="R28" s="16">
-        <v>882.58823529411768</v>
+        <v>895.88888888888891</v>
       </c>
       <c r="S28" s="15">
-        <v>18.647058823529392</v>
+        <v>-64.444444444444457</v>
       </c>
       <c r="T28" s="18">
-        <v>2205</v>
+        <v>1120</v>
       </c>
       <c r="U28" s="17">
-        <v>2557.7999999999997</v>
+        <v>1299.1999999999998</v>
       </c>
       <c r="V28" s="14">
-        <v>15.3125</v>
+        <v>7.6392572944297079</v>
       </c>
       <c r="W28" s="16">
-        <v>3168</v>
+        <v>3225.4444444444443</v>
       </c>
       <c r="X28" s="15">
-        <v>-99</v>
+        <v>-1225.7777777777778</v>
       </c>
       <c r="Y28" s="18">
-        <v>304</v>
+        <v>433</v>
       </c>
       <c r="Z28" s="17">
-        <v>352.64</v>
+        <v>502.28</v>
       </c>
       <c r="AA28" s="14">
-        <v>17.638225255972696</v>
+        <v>24.130030959752325</v>
       </c>
       <c r="AB28" s="16">
-        <v>379.17647058823525</v>
+        <v>394.77777777777771</v>
       </c>
       <c r="AC28" s="15">
-        <v>-75.176470588235247</v>
+        <v>38.222222222222285</v>
       </c>
       <c r="AD28" s="19">
-        <v>12914</v>
+        <v>11231</v>
       </c>
       <c r="AE28" s="20">
-        <v>14980.24</v>
+        <v>13027.96</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4063,85 +4065,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>2489</v>
+        <v>2166</v>
       </c>
       <c r="F29" s="14">
-        <v>2887.24</v>
+        <v>2512.56</v>
       </c>
       <c r="G29" s="14">
-        <v>6.4600000000000009</v>
+        <v>5.5325670498084287</v>
       </c>
       <c r="H29" s="30">
-        <v>8476.4705882352937</v>
+        <v>8613</v>
       </c>
       <c r="I29" s="15">
-        <v>-1363.9411764705878</v>
+        <v>-1749</v>
       </c>
       <c r="J29" s="16">
-        <v>696</v>
+        <v>448</v>
       </c>
       <c r="K29" s="13">
-        <v>807.3599999999999</v>
+        <v>519.67999999999995</v>
       </c>
       <c r="L29" s="14">
-        <v>2.5571644694186295</v>
+        <v>1.6460502143294549</v>
       </c>
       <c r="M29" s="30">
-        <v>5987.8823529411766</v>
+        <v>5987.666666666667</v>
       </c>
       <c r="N29" s="15">
-        <v>-2025.7647058823532</v>
+        <v>-2273.666666666667</v>
       </c>
       <c r="O29" s="16">
-        <v>832</v>
+        <v>755</v>
       </c>
       <c r="P29" s="17">
-        <v>965.11999999999989</v>
+        <v>875.8</v>
       </c>
       <c r="Q29" s="14">
-        <v>20.205714285714283</v>
+        <v>18.439620081411128</v>
       </c>
       <c r="R29" s="16">
-        <v>905.88235294117658</v>
+        <v>900.77777777777771</v>
       </c>
       <c r="S29" s="15">
-        <v>8.4705882352940307</v>
+        <v>-63.888888888888914</v>
       </c>
       <c r="T29" s="18">
-        <v>1513</v>
+        <v>1034</v>
       </c>
       <c r="U29" s="17">
-        <v>1755.08</v>
+        <v>1199.4399999999998</v>
       </c>
       <c r="V29" s="14">
-        <v>10.288399999999999</v>
+        <v>6.9838649155722337</v>
       </c>
       <c r="W29" s="16">
-        <v>3235.294117647059</v>
+        <v>3257.2222222222217</v>
       </c>
       <c r="X29" s="15">
-        <v>-839.94117647058829</v>
+        <v>-1334.8888888888887</v>
       </c>
       <c r="Y29" s="18">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="Z29" s="17">
-        <v>371.2</v>
+        <v>448.91999999999996</v>
       </c>
       <c r="AA29" s="14">
-        <v>19.359430604982204</v>
+        <v>22.39871382636656</v>
       </c>
       <c r="AB29" s="16">
-        <v>363.64705882352945</v>
+        <v>380.11111111111114</v>
       </c>
       <c r="AC29" s="15">
-        <v>-43.647058823529449</v>
+        <v>6.8888888888888573</v>
       </c>
       <c r="AD29" s="19">
-        <v>5850</v>
+        <v>4790</v>
       </c>
       <c r="AE29" s="20">
-        <v>6785.9999999999991</v>
+        <v>5556.4</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4176,85 +4178,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>141</v>
+        <v>715</v>
       </c>
       <c r="F30" s="14">
-        <v>518.88</v>
+        <v>2631.2000000000003</v>
       </c>
       <c r="G30" s="14">
-        <v>1.3069792802617233</v>
+        <v>6.6649404453650964</v>
       </c>
       <c r="H30" s="30">
-        <v>2373.411764705882</v>
+        <v>2360.1111111111109</v>
       </c>
       <c r="I30" s="15">
-        <v>-937.82352941176441</v>
+        <v>-357.77777777777783</v>
       </c>
       <c r="J30" s="16">
-        <v>211</v>
+        <v>1191</v>
       </c>
       <c r="K30" s="13">
-        <v>776.48</v>
+        <v>4382.88</v>
       </c>
       <c r="L30" s="14">
-        <v>1.6785212915301826</v>
+        <v>9.6480648064806473</v>
       </c>
       <c r="M30" s="30">
-        <v>2765.5294117647059</v>
+        <v>2715.7777777777778</v>
       </c>
       <c r="N30" s="15">
-        <v>-1046.0588235294117</v>
+        <v>-43.444444444444343</v>
       </c>
       <c r="O30" s="16">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="P30" s="17">
-        <v>496.8</v>
+        <v>482.08000000000004</v>
       </c>
       <c r="Q30" s="14">
-        <v>21.055045871559631</v>
+        <v>21.633027522935777</v>
       </c>
       <c r="R30" s="16">
-        <v>141.05882352941177</v>
+        <v>133.22222222222223</v>
       </c>
       <c r="S30" s="15">
-        <v>6.7647058823529278</v>
+        <v>9.8888888888888715</v>
       </c>
       <c r="T30" s="18">
-        <v>486</v>
+        <v>377</v>
       </c>
       <c r="U30" s="17">
-        <v>1788.48</v>
+        <v>1387.3600000000001</v>
       </c>
       <c r="V30" s="14">
-        <v>16.524000000000001</v>
+        <v>12.520295202952029</v>
       </c>
       <c r="W30" s="16">
-        <v>647.05882352941171</v>
+        <v>662.44444444444446</v>
       </c>
       <c r="X30" s="15">
-        <v>15.411764705882376</v>
+        <v>-104.77777777777777</v>
       </c>
       <c r="Y30" s="18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z30" s="17">
-        <v>0</v>
+        <v>471.04</v>
       </c>
       <c r="AA30" s="14">
-        <v>0</v>
+        <v>24.774193548387096</v>
       </c>
       <c r="AB30" s="16">
-        <v>120.35294117647059</v>
+        <v>113.66666666666667</v>
       </c>
       <c r="AC30" s="15">
-        <v>-120.35294117647059</v>
+        <v>14.333333333333329</v>
       </c>
       <c r="AD30" s="19">
-        <v>973</v>
+        <v>2542</v>
       </c>
       <c r="AE30" s="20">
-        <v>3580.6400000000003</v>
+        <v>9354.5600000000013</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4289,34 +4291,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>342</v>
+        <v>279</v>
       </c>
       <c r="F31" s="14">
-        <v>1258.56</v>
+        <v>1026.72</v>
       </c>
       <c r="G31" s="14">
-        <v>7.0132689987937287</v>
+        <v>5.58</v>
       </c>
       <c r="H31" s="30">
-        <v>1072.8235294117646</v>
+        <v>1100</v>
       </c>
       <c r="I31" s="15">
-        <v>-145.64705882352933</v>
+        <v>-221</v>
       </c>
       <c r="J31" s="16">
-        <v>503</v>
+        <v>1511</v>
       </c>
       <c r="K31" s="13">
-        <v>1851.0400000000002</v>
+        <v>5560.4800000000005</v>
       </c>
       <c r="L31" s="14">
-        <v>7.0903814262023221</v>
+        <v>21.483412322274884</v>
       </c>
       <c r="M31" s="30">
-        <v>1560.705882352941</v>
+        <v>1547.3333333333333</v>
       </c>
       <c r="N31" s="15">
-        <v>-206.41176470588232</v>
+        <v>807.66666666666674</v>
       </c>
       <c r="O31" s="16">
         <v>34</v>
@@ -4325,28 +4327,28 @@
         <v>125.12</v>
       </c>
       <c r="Q31" s="14">
-        <v>32.111111111111114</v>
+        <v>34</v>
       </c>
       <c r="R31" s="16">
-        <v>23.294117647058822</v>
+        <v>22</v>
       </c>
       <c r="S31" s="15">
-        <v>12.823529411764707</v>
+        <v>14</v>
       </c>
       <c r="T31" s="18">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="U31" s="17">
-        <v>526.24</v>
+        <v>423.20000000000005</v>
       </c>
       <c r="V31" s="14">
-        <v>16.425675675675677</v>
+        <v>12.034883720930234</v>
       </c>
       <c r="W31" s="16">
-        <v>191.52941176470586</v>
+        <v>210.22222222222223</v>
       </c>
       <c r="X31" s="15">
-        <v>3.7058823529411882</v>
+        <v>-37.888888888888886</v>
       </c>
       <c r="Y31" s="18">
         <v>44</v>
@@ -4355,19 +4357,19 @@
         <v>161.92000000000002</v>
       </c>
       <c r="AA31" s="14">
-        <v>31.166666666666664</v>
+        <v>33</v>
       </c>
       <c r="AB31" s="16">
-        <v>31.058823529411768</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="AC31" s="15">
-        <v>12.941176470588232</v>
+        <v>14.666666666666668</v>
       </c>
       <c r="AD31" s="19">
-        <v>1066</v>
+        <v>1983</v>
       </c>
       <c r="AE31" s="20">
-        <v>3922.88</v>
+        <v>7297.4400000000005</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4402,85 +4404,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1687</v>
+        <v>1612</v>
       </c>
       <c r="F32" s="14">
-        <v>7001.05</v>
+        <v>6689.8</v>
       </c>
       <c r="G32" s="14">
-        <v>7.5253214379427966</v>
+        <v>7.2503748125937015</v>
       </c>
       <c r="H32" s="30">
-        <v>4931.8823529411766</v>
+        <v>4891.3333333333339</v>
       </c>
       <c r="I32" s="15">
-        <v>-554.76470588235316</v>
+        <v>-611.33333333333394</v>
       </c>
       <c r="J32" s="16">
-        <v>395</v>
+        <v>1861</v>
       </c>
       <c r="K32" s="13">
-        <v>1639.2500000000002</v>
+        <v>7723.1500000000005</v>
       </c>
       <c r="L32" s="14">
-        <v>2.0912488321395206</v>
+        <v>9.9845007451564829</v>
       </c>
       <c r="M32" s="30">
-        <v>4155.411764705882</v>
+        <v>4100.5555555555557</v>
       </c>
       <c r="N32" s="15">
-        <v>-1493.8235294117646</v>
+        <v>-2.8888888888889142</v>
       </c>
       <c r="O32" s="16">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="P32" s="17">
-        <v>1199.3500000000001</v>
+        <v>1186.9000000000001</v>
       </c>
       <c r="Q32" s="14">
-        <v>19.971544715447155</v>
+        <v>20.926829268292686</v>
       </c>
       <c r="R32" s="16">
-        <v>318.35294117647061</v>
+        <v>300.66666666666663</v>
       </c>
       <c r="S32" s="15">
-        <v>-0.41176470588237635</v>
+        <v>12.666666666666742</v>
       </c>
       <c r="T32" s="18">
-        <v>1290</v>
+        <v>1093</v>
       </c>
       <c r="U32" s="17">
-        <v>5353.5000000000009</v>
+        <v>4535.9500000000007</v>
       </c>
       <c r="V32" s="14">
-        <v>15.389473684210525</v>
+        <v>13.257412398921833</v>
       </c>
       <c r="W32" s="16">
-        <v>1844.1176470588236</v>
+        <v>1813.7777777777778</v>
       </c>
       <c r="X32" s="15">
-        <v>-51.176470588235361</v>
+        <v>-226.11111111111109</v>
       </c>
       <c r="Y32" s="18">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Z32" s="17">
-        <v>1174.45</v>
+        <v>1153.7</v>
       </c>
       <c r="AA32" s="14">
-        <v>71.805970149253724</v>
+        <v>69.5</v>
       </c>
       <c r="AB32" s="16">
-        <v>86.705882352941188</v>
+        <v>88</v>
       </c>
       <c r="AC32" s="15">
-        <v>196.29411764705881</v>
+        <v>190</v>
       </c>
       <c r="AD32" s="19">
-        <v>3944</v>
+        <v>5130</v>
       </c>
       <c r="AE32" s="20">
-        <v>16367.600000000002</v>
+        <v>21289.500000000004</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4515,34 +4517,34 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3021</v>
+        <v>2670</v>
       </c>
       <c r="F33" s="14">
-        <v>12537.150000000001</v>
+        <v>11080.500000000002</v>
       </c>
       <c r="G33" s="14">
-        <v>6.8284802552852009</v>
+        <v>6.0135135135135132</v>
       </c>
       <c r="H33" s="30">
-        <v>9733.0588235294126</v>
+        <v>9768</v>
       </c>
       <c r="I33" s="15">
-        <v>-1403.1176470588234</v>
+        <v>-1770</v>
       </c>
       <c r="J33" s="16">
-        <v>1349</v>
+        <v>3076</v>
       </c>
       <c r="K33" s="13">
-        <v>5598.35</v>
+        <v>12765.400000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>4.866935483870968</v>
+        <v>10.946619217081851</v>
       </c>
       <c r="M33" s="30">
-        <v>6097.8823529411766</v>
+        <v>6182</v>
       </c>
       <c r="N33" s="15">
-        <v>-1422.7647058823532</v>
+        <v>266</v>
       </c>
       <c r="O33" s="16">
         <v>395</v>
@@ -4551,49 +4553,49 @@
         <v>1639.2500000000002</v>
       </c>
       <c r="Q33" s="14">
-        <v>19.520348837209305</v>
+        <v>20.549132947976879</v>
       </c>
       <c r="R33" s="16">
-        <v>445.17647058823525</v>
+        <v>422.88888888888886</v>
       </c>
       <c r="S33" s="15">
-        <v>-9.7058823529411598</v>
+        <v>10.555555555555543</v>
       </c>
       <c r="T33" s="18">
-        <v>1696</v>
+        <v>1204</v>
       </c>
       <c r="U33" s="17">
-        <v>7038.4000000000005</v>
+        <v>4996.6000000000004</v>
       </c>
       <c r="V33" s="14">
-        <v>15.644058600108519</v>
+        <v>11.096774193548388</v>
       </c>
       <c r="W33" s="16">
-        <v>2385.0588235294117</v>
+        <v>2387</v>
       </c>
       <c r="X33" s="15">
-        <v>-38.588235294117567</v>
+        <v>-532</v>
       </c>
       <c r="Y33" s="18">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Z33" s="17">
-        <v>124.50000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="AA33" s="14">
-        <v>2.2566371681415927</v>
+        <v>1.7768240343347639</v>
       </c>
       <c r="AB33" s="16">
-        <v>292.47058823529414</v>
+        <v>284.77777777777777</v>
       </c>
       <c r="AC33" s="15">
-        <v>-262.47058823529414</v>
+        <v>-261.77777777777777</v>
       </c>
       <c r="AD33" s="19">
-        <v>6491</v>
+        <v>7368</v>
       </c>
       <c r="AE33" s="20">
-        <v>26937.65</v>
+        <v>30577.200000000004</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4634,13 +4636,13 @@
         <v>3311.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>15.242696629213484</v>
+        <v>14.22178217821782</v>
       </c>
       <c r="H34" s="30">
-        <v>1151.7647058823529</v>
+        <v>1234.4444444444446</v>
       </c>
       <c r="I34" s="15">
-        <v>274.47058823529414</v>
+        <v>236.88888888888891</v>
       </c>
       <c r="J34" s="16">
         <v>256</v>
@@ -4662,13 +4664,13 @@
       </c>
       <c r="P34" s="17"/>
       <c r="Q34" s="14">
-        <v>25.499999999999996</v>
+        <v>27</v>
       </c>
       <c r="R34" s="16">
-        <v>41.411764705882355</v>
+        <v>39.111111111111107</v>
       </c>
       <c r="S34" s="15">
-        <v>10.352941176470587</v>
+        <v>12.444444444444443</v>
       </c>
       <c r="T34" s="18">
         <v>122</v>
@@ -4677,13 +4679,13 @@
         <v>506.30000000000007</v>
       </c>
       <c r="V34" s="14">
-        <v>18.854545454545455</v>
+        <v>19.963636363636365</v>
       </c>
       <c r="W34" s="16">
-        <v>142.35294117647058</v>
+        <v>134.44444444444443</v>
       </c>
       <c r="X34" s="15">
-        <v>18.47058823529413</v>
+        <v>24.222222222222229</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4739,85 +4741,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>2304</v>
+        <v>1916</v>
       </c>
       <c r="F35" s="14">
-        <v>3755.5199999999995</v>
+        <v>3123.08</v>
       </c>
       <c r="G35" s="14">
-        <v>5.4581939799331112</v>
+        <v>4.5182759072448571</v>
       </c>
       <c r="H35" s="30">
-        <v>9286.5882352941171</v>
+        <v>9329.2222222222226</v>
       </c>
       <c r="I35" s="15">
-        <v>-1917.1764705882351</v>
+        <v>-2324.5555555555557</v>
       </c>
       <c r="J35" s="16">
-        <v>1559</v>
+        <v>1375</v>
       </c>
       <c r="K35" s="13">
-        <v>2541.1699999999996</v>
+        <v>2241.25</v>
       </c>
       <c r="L35" s="14">
-        <v>9.0639534883720927</v>
+        <v>7.9607590865229971</v>
       </c>
       <c r="M35" s="30">
-        <v>3784</v>
+        <v>3799.8888888888891</v>
       </c>
       <c r="N35" s="15">
-        <v>-161</v>
+        <v>-352.22222222222217</v>
       </c>
       <c r="O35" s="16">
-        <v>775</v>
+        <v>705</v>
       </c>
       <c r="P35" s="17">
-        <v>1263.25</v>
+        <v>1149.1499999999999</v>
       </c>
       <c r="Q35" s="14">
-        <v>20.979299363057326</v>
+        <v>18.444767441860467</v>
       </c>
       <c r="R35" s="16">
-        <v>812.7058823529411</v>
+        <v>840.88888888888891</v>
       </c>
       <c r="S35" s="15">
-        <v>36.176470588235361</v>
+        <v>-59.444444444444457</v>
       </c>
       <c r="T35" s="18">
-        <v>705</v>
+        <v>581</v>
       </c>
       <c r="U35" s="17">
-        <v>1149.1499999999999</v>
+        <v>947.03</v>
       </c>
       <c r="V35" s="14">
-        <v>16.531034482758621</v>
+        <v>12.645707376058041</v>
       </c>
       <c r="W35" s="16">
-        <v>938.23529411764707</v>
+        <v>1010.7777777777777</v>
       </c>
       <c r="X35" s="15">
-        <v>22.647058823529392</v>
+        <v>-154.11111111111109</v>
       </c>
       <c r="Y35" s="18">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="Z35" s="17">
-        <v>423.79999999999995</v>
+        <v>464.54999999999995</v>
       </c>
       <c r="AA35" s="14">
-        <v>19.732142857142858</v>
+        <v>20.276679841897234</v>
       </c>
       <c r="AB35" s="16">
-        <v>289.88235294117646</v>
+        <v>309.22222222222223</v>
       </c>
       <c r="AC35" s="15">
-        <v>-29.882352941176464</v>
+        <v>-24.222222222222229</v>
       </c>
       <c r="AD35" s="19">
-        <v>5603</v>
+        <v>4862</v>
       </c>
       <c r="AE35" s="20">
-        <v>9132.89</v>
+        <v>7925.0599999999995</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4852,85 +4854,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>5615</v>
+        <v>4467</v>
       </c>
       <c r="F36" s="14">
-        <v>9152.4499999999989</v>
+        <v>7281.2099999999991</v>
       </c>
       <c r="G36" s="14">
-        <v>9.1695485110470702</v>
+        <v>7.2100071736011477</v>
       </c>
       <c r="H36" s="30">
-        <v>13471.764705882353</v>
+        <v>13630.222222222223</v>
       </c>
       <c r="I36" s="15">
-        <v>-508.52941176470631</v>
+        <v>-1728.5555555555557</v>
       </c>
       <c r="J36" s="16">
-        <v>2693</v>
+        <v>2460</v>
       </c>
       <c r="K36" s="13">
-        <v>4389.59</v>
+        <v>4009.7999999999997</v>
       </c>
       <c r="L36" s="14">
-        <v>11.473934837092731</v>
+        <v>10.433553251649386</v>
       </c>
       <c r="M36" s="30">
-        <v>5163.5294117647063</v>
+        <v>5187.1111111111113</v>
       </c>
       <c r="N36" s="15">
-        <v>345.94117647058829</v>
+        <v>102.22222222222217</v>
       </c>
       <c r="O36" s="16">
-        <v>1868</v>
+        <v>1761</v>
       </c>
       <c r="P36" s="17">
-        <v>3044.8399999999997</v>
+        <v>2870.43</v>
       </c>
       <c r="Q36" s="14">
-        <v>20.421864951768487</v>
+        <v>19.339841366687004</v>
       </c>
       <c r="R36" s="16">
-        <v>2012.3529411764705</v>
+        <v>2003.2222222222222</v>
       </c>
       <c r="S36" s="15">
-        <v>38.588235294117567</v>
+        <v>-60.111111111111086</v>
       </c>
       <c r="T36" s="18">
-        <v>1649</v>
+        <v>1437</v>
       </c>
       <c r="U36" s="17">
-        <v>2687.87</v>
+        <v>2342.31</v>
       </c>
       <c r="V36" s="14">
-        <v>16.000570776255707</v>
+        <v>13.729299363057322</v>
       </c>
       <c r="W36" s="16">
-        <v>2267.294117647059</v>
+        <v>2302.666666666667</v>
       </c>
       <c r="X36" s="15">
-        <v>5.8823529411711206E-2</v>
+        <v>-237.66666666666697</v>
       </c>
       <c r="Y36" s="18">
-        <v>234</v>
+        <v>507</v>
       </c>
       <c r="Z36" s="17">
-        <v>381.41999999999996</v>
+        <v>826.41</v>
       </c>
       <c r="AA36" s="14">
-        <v>9.3820754716981138</v>
+        <v>19.5</v>
       </c>
       <c r="AB36" s="16">
-        <v>548.70588235294122</v>
+        <v>572</v>
       </c>
       <c r="AC36" s="15">
-        <v>-314.70588235294122</v>
+        <v>-65</v>
       </c>
       <c r="AD36" s="19">
-        <v>12059</v>
+        <v>10632</v>
       </c>
       <c r="AE36" s="20">
-        <v>19656.169999999998</v>
+        <v>17330.16</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4965,85 +4967,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1434</v>
+        <v>1265</v>
       </c>
       <c r="F37" s="14">
-        <v>2337.42</v>
+        <v>2061.9499999999998</v>
       </c>
       <c r="G37" s="14">
-        <v>4.942822384428224</v>
+        <v>4.3620689655172411</v>
       </c>
       <c r="H37" s="30">
-        <v>6382.588235294118</v>
+        <v>6380</v>
       </c>
       <c r="I37" s="15">
-        <v>-1467.1764705882351</v>
+        <v>-1635</v>
       </c>
       <c r="J37" s="16">
-        <v>278</v>
+        <v>215</v>
       </c>
       <c r="K37" s="13">
-        <v>453.14</v>
+        <v>350.45</v>
       </c>
       <c r="L37" s="14">
-        <v>1.9329243353783232</v>
+        <v>1.5075964160498636</v>
       </c>
       <c r="M37" s="30">
-        <v>3164.1176470588234</v>
+        <v>3137.4444444444443</v>
       </c>
       <c r="N37" s="15">
-        <v>-1160.2352941176468</v>
+        <v>-1211.1111111111111</v>
       </c>
       <c r="O37" s="16">
-        <v>1174</v>
+        <v>1145</v>
       </c>
       <c r="P37" s="17">
-        <v>1913.62</v>
+        <v>1866.35</v>
       </c>
       <c r="Q37" s="14">
-        <v>19.977977977977979</v>
+        <v>20.365612648221344</v>
       </c>
       <c r="R37" s="16">
-        <v>1292.8235294117646</v>
+        <v>1236.8888888888889</v>
       </c>
       <c r="S37" s="15">
-        <v>-1.2941176470587834</v>
+        <v>20.555555555555657</v>
       </c>
       <c r="T37" s="18">
-        <v>550</v>
+        <v>453</v>
       </c>
       <c r="U37" s="17">
-        <v>896.49999999999989</v>
+        <v>738.39</v>
       </c>
       <c r="V37" s="14">
-        <v>9.8008385744234801</v>
+        <v>8.0176991150442483</v>
       </c>
       <c r="W37" s="16">
-        <v>1234.5882352941176</v>
+        <v>1243</v>
       </c>
       <c r="X37" s="15">
-        <v>-347.88235294117646</v>
+        <v>-451</v>
       </c>
       <c r="Y37" s="18">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="Z37" s="17">
-        <v>0</v>
+        <v>352.08</v>
       </c>
       <c r="AA37" s="14">
-        <v>0</v>
+        <v>15.804878048780491</v>
       </c>
       <c r="AB37" s="16">
-        <v>318.35294117647061</v>
+        <v>300.66666666666663</v>
       </c>
       <c r="AC37" s="15">
-        <v>-318.35294117647061</v>
+        <v>-84.666666666666629</v>
       </c>
       <c r="AD37" s="19">
-        <v>3436</v>
+        <v>3294</v>
       </c>
       <c r="AE37" s="20">
-        <v>5600.6799999999994</v>
+        <v>5369.2199999999993</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5078,85 +5080,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>962</v>
+        <v>782</v>
       </c>
       <c r="F38" s="14">
-        <v>1568.06</v>
+        <v>1274.6599999999999</v>
       </c>
       <c r="G38" s="14">
-        <v>5.0134886572654818</v>
+        <v>3.9617224880382778</v>
       </c>
       <c r="H38" s="30">
-        <v>4221.411764705882</v>
+        <v>4342.5555555555557</v>
       </c>
       <c r="I38" s="15">
-        <v>-956.82352941176464</v>
+        <v>-1191.8888888888889</v>
       </c>
       <c r="J38" s="16">
-        <v>423</v>
+        <v>269</v>
       </c>
       <c r="K38" s="13">
-        <v>689.49</v>
+        <v>438.46999999999997</v>
       </c>
       <c r="L38" s="14">
-        <v>3.6484018264840183</v>
+        <v>2.2679156908665106</v>
       </c>
       <c r="M38" s="30">
-        <v>2550.705882352941</v>
+        <v>2609.4444444444443</v>
       </c>
       <c r="N38" s="15">
-        <v>-736.41176470588243</v>
+        <v>-917.11111111111109</v>
       </c>
       <c r="O38" s="16">
-        <v>761</v>
+        <v>721</v>
       </c>
       <c r="P38" s="17">
-        <v>1240.4299999999998</v>
+        <v>1175.23</v>
       </c>
       <c r="Q38" s="14">
-        <v>19.872503840245773</v>
+        <v>19.545180722891569</v>
       </c>
       <c r="R38" s="16">
-        <v>842.47058823529414</v>
+        <v>811.55555555555543</v>
       </c>
       <c r="S38" s="15">
-        <v>-4.8823529411765776</v>
+        <v>-16.777777777777715</v>
       </c>
       <c r="T38" s="18">
-        <v>588</v>
+        <v>514</v>
       </c>
       <c r="U38" s="17">
-        <v>958.43999999999994</v>
+        <v>837.81999999999994</v>
       </c>
       <c r="V38" s="14">
-        <v>16.174757281553397</v>
+        <v>14.146788990825687</v>
       </c>
       <c r="W38" s="16">
-        <v>799.76470588235293</v>
+        <v>799.33333333333337</v>
       </c>
       <c r="X38" s="15">
-        <v>6.3529411764706083</v>
+        <v>-67.333333333333371</v>
       </c>
       <c r="Y38" s="18">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="Z38" s="17">
-        <v>277.09999999999997</v>
+        <v>751.43</v>
       </c>
       <c r="AA38" s="14">
-        <v>6.6436781609195394</v>
+        <v>15.896551724137931</v>
       </c>
       <c r="AB38" s="16">
-        <v>562.94117647058829</v>
+        <v>638</v>
       </c>
       <c r="AC38" s="15">
-        <v>-392.94117647058829</v>
+        <v>-177</v>
       </c>
       <c r="AD38" s="19">
-        <v>2904</v>
+        <v>2747</v>
       </c>
       <c r="AE38" s="20">
-        <v>4733.5199999999995</v>
+        <v>4477.6099999999997</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5191,85 +5193,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1572</v>
+        <v>1202</v>
       </c>
       <c r="F39" s="14">
-        <v>2562.3599999999997</v>
+        <v>1959.2599999999998</v>
       </c>
       <c r="G39" s="14">
-        <v>18.044564483457123</v>
+        <v>13.413515189088654</v>
       </c>
       <c r="H39" s="30">
-        <v>1916.5882352941178</v>
+        <v>1971.4444444444446</v>
       </c>
       <c r="I39" s="15">
-        <v>700.82352941176464</v>
+        <v>305.88888888888891</v>
       </c>
       <c r="J39" s="16">
-        <v>2623</v>
+        <v>2572</v>
       </c>
       <c r="K39" s="13">
-        <v>4275.49</v>
+        <v>4192.3599999999997</v>
       </c>
       <c r="L39" s="14">
-        <v>45.041414141414137</v>
+        <v>44.302392344497612</v>
       </c>
       <c r="M39" s="30">
-        <v>1281.1764705882354</v>
+        <v>1277.2222222222222</v>
       </c>
       <c r="N39" s="15">
-        <v>2040.6470588235293</v>
+        <v>1991.4444444444443</v>
       </c>
       <c r="O39" s="16">
-        <v>662</v>
+        <v>613</v>
       </c>
       <c r="P39" s="17">
-        <v>1079.06</v>
+        <v>999.18999999999994</v>
       </c>
       <c r="Q39" s="14">
-        <v>22.598393574297187</v>
+        <v>20.471243042671617</v>
       </c>
       <c r="R39" s="16">
-        <v>644.47058823529414</v>
+        <v>658.77777777777771</v>
       </c>
       <c r="S39" s="15">
-        <v>76.117647058823422</v>
+        <v>14.111111111111086</v>
       </c>
       <c r="T39" s="18">
-        <v>847</v>
+        <v>646</v>
       </c>
       <c r="U39" s="17">
-        <v>1380.61</v>
+        <v>1052.98</v>
       </c>
       <c r="V39" s="14">
-        <v>16.178651685393259</v>
+        <v>11.344390243902438</v>
       </c>
       <c r="W39" s="16">
-        <v>1151.7647058823529</v>
+        <v>1252.7777777777778</v>
       </c>
       <c r="X39" s="15">
-        <v>9.3529411764706083</v>
+        <v>-265.1111111111112</v>
       </c>
       <c r="Y39" s="18">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="Z39" s="17">
-        <v>726.9799999999999</v>
+        <v>702.53</v>
       </c>
       <c r="AA39" s="14">
-        <v>106.78873239436619</v>
+        <v>93.469879518072304</v>
       </c>
       <c r="AB39" s="16">
-        <v>91.882352941176478</v>
+        <v>101.44444444444443</v>
       </c>
       <c r="AC39" s="15">
-        <v>354.11764705882354</v>
+        <v>329.55555555555554</v>
       </c>
       <c r="AD39" s="19">
-        <v>6150</v>
+        <v>5464</v>
       </c>
       <c r="AE39" s="20">
-        <v>10024.5</v>
+        <v>8906.32</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5304,85 +5306,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1346</v>
+        <v>864</v>
       </c>
       <c r="F40" s="14">
-        <v>2193.98</v>
+        <v>1408.32</v>
       </c>
       <c r="G40" s="14">
-        <v>11.728344438749359</v>
+        <v>7.2979821679962456</v>
       </c>
       <c r="H40" s="30">
-        <v>2524.8235294117649</v>
+        <v>2604.5555555555557</v>
       </c>
       <c r="I40" s="15">
-        <v>198.35294117647049</v>
+        <v>-319.88888888888891</v>
       </c>
       <c r="J40" s="16">
-        <v>1728</v>
+        <v>1660</v>
       </c>
       <c r="K40" s="13">
-        <v>2816.64</v>
+        <v>2705.7999999999997</v>
       </c>
       <c r="L40" s="14">
-        <v>25.129170230966636</v>
+        <v>24.431725265739985</v>
       </c>
       <c r="M40" s="30">
-        <v>1512.8235294117646</v>
+        <v>1494.7777777777778</v>
       </c>
       <c r="N40" s="15">
-        <v>1040.3529411764707</v>
+        <v>980.55555555555554</v>
       </c>
       <c r="O40" s="16">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="P40" s="17">
-        <v>1323.56</v>
+        <v>1310.52</v>
       </c>
       <c r="Q40" s="14">
-        <v>22.157303370786515</v>
+        <v>21.535714285714285</v>
       </c>
       <c r="R40" s="16">
-        <v>806.23529411764707</v>
+        <v>821.33333333333337</v>
       </c>
       <c r="S40" s="15">
-        <v>79.058823529411711</v>
+        <v>57.333333333333258</v>
       </c>
       <c r="T40" s="18">
-        <v>981</v>
+        <v>785</v>
       </c>
       <c r="U40" s="17">
-        <v>1599.03</v>
+        <v>1279.55</v>
       </c>
       <c r="V40" s="14">
-        <v>15.897998093422308</v>
+        <v>11.98473282442748</v>
       </c>
       <c r="W40" s="16">
-        <v>1357.5294117647059</v>
+        <v>1441</v>
       </c>
       <c r="X40" s="15">
-        <v>-6.2941176470587834</v>
+        <v>-263</v>
       </c>
       <c r="Y40" s="18">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="Z40" s="17">
-        <v>749.8</v>
+        <v>713.93999999999994</v>
       </c>
       <c r="AA40" s="14">
-        <v>113.33333333333334</v>
+        <v>93.857142857142847</v>
       </c>
       <c r="AB40" s="16">
-        <v>89.294117647058812</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="AC40" s="15">
-        <v>370.70588235294122</v>
+        <v>335.33333333333331</v>
       </c>
       <c r="AD40" s="19">
-        <v>5327</v>
+        <v>4551</v>
       </c>
       <c r="AE40" s="20">
-        <v>8683.01</v>
+        <v>7418.1299999999992</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5417,34 +5419,34 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="F41" s="14">
-        <v>3025.8</v>
+        <v>2730.6000000000004</v>
       </c>
       <c r="G41" s="14">
-        <v>7.1365187713310583</v>
+        <v>6.460792239288601</v>
       </c>
       <c r="H41" s="30">
-        <v>1516.705882352941</v>
+        <v>1511.8888888888891</v>
       </c>
       <c r="I41" s="15">
-        <v>-197.41176470588232</v>
+        <v>-243.22222222222229</v>
       </c>
       <c r="J41" s="16">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="K41" s="13">
-        <v>1648.2</v>
+        <v>1457.5500000000002</v>
       </c>
       <c r="L41" s="14">
-        <v>6.5743145743145739</v>
+        <v>5.8278688524590168</v>
       </c>
       <c r="M41" s="30">
-        <v>896.82352941176475</v>
+        <v>894.66666666666663</v>
       </c>
       <c r="N41" s="15">
-        <v>-139.64705882352939</v>
+        <v>-169.66666666666663</v>
       </c>
       <c r="O41" s="16">
         <v>112</v>
@@ -5453,49 +5455,49 @@
         <v>688.80000000000007</v>
       </c>
       <c r="Q41" s="14">
-        <v>23.219512195121954</v>
+        <v>24.585365853658537</v>
       </c>
       <c r="R41" s="16">
-        <v>106.11764705882352</v>
+        <v>100.22222222222221</v>
       </c>
       <c r="S41" s="15">
-        <v>15.529411764705884</v>
+        <v>20.888888888888886</v>
       </c>
       <c r="T41" s="18">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="U41" s="17">
-        <v>1156.2</v>
+        <v>971.7</v>
       </c>
       <c r="V41" s="14">
-        <v>17.755555555555556</v>
+        <v>14.22</v>
       </c>
       <c r="W41" s="16">
-        <v>232.94117647058823</v>
+        <v>244.44444444444443</v>
       </c>
       <c r="X41" s="15">
-        <v>18.588235294117652</v>
+        <v>-19.777777777777771</v>
       </c>
       <c r="Y41" s="18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z41" s="17">
-        <v>0</v>
+        <v>590.40000000000009</v>
       </c>
       <c r="AA41" s="14">
-        <v>0</v>
+        <v>21.073170731707318</v>
       </c>
       <c r="AB41" s="16">
-        <v>106.11764705882352</v>
+        <v>100.22222222222221</v>
       </c>
       <c r="AC41" s="15">
-        <v>-106.11764705882352</v>
+        <v>-4.2222222222222143</v>
       </c>
       <c r="AD41" s="19">
-        <v>1060</v>
+        <v>1047</v>
       </c>
       <c r="AE41" s="20">
-        <v>6519</v>
+        <v>6439.05</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5530,64 +5532,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="F42" s="14">
-        <v>1555.95</v>
+        <v>1303.8000000000002</v>
       </c>
       <c r="G42" s="14">
-        <v>3.6697952218430037</v>
+        <v>3.0430622009569377</v>
       </c>
       <c r="H42" s="30">
-        <v>1516.705882352941</v>
+        <v>1532.6666666666667</v>
       </c>
       <c r="I42" s="15">
-        <v>-436.41176470588232</v>
+        <v>-484.66666666666674</v>
       </c>
       <c r="J42" s="16">
-        <v>901</v>
+        <v>848</v>
       </c>
       <c r="K42" s="13">
-        <v>5541.1500000000005</v>
+        <v>5215.2000000000007</v>
       </c>
       <c r="L42" s="14">
-        <v>21.975609756097562</v>
+        <v>20.137203166226911</v>
       </c>
       <c r="M42" s="30">
-        <v>902</v>
+        <v>926.44444444444457</v>
       </c>
       <c r="N42" s="15">
-        <v>491</v>
+        <v>426.88888888888886</v>
       </c>
       <c r="O42" s="16">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P42" s="17">
-        <v>848.7</v>
+        <v>836.40000000000009</v>
       </c>
       <c r="Q42" s="14">
-        <v>20.22413793103448</v>
+        <v>21.103448275862071</v>
       </c>
       <c r="R42" s="16">
-        <v>150.11764705882354</v>
+        <v>141.77777777777777</v>
       </c>
       <c r="S42" s="15">
-        <v>1.5294117647058556</v>
+        <v>7.1111111111111143</v>
       </c>
       <c r="T42" s="18">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="U42" s="17">
-        <v>1740.45</v>
+        <v>1580.5500000000002</v>
       </c>
       <c r="V42" s="14">
-        <v>17.558394160583941</v>
+        <v>15.842465753424658</v>
       </c>
       <c r="W42" s="16">
-        <v>354.58823529411762</v>
+        <v>356.88888888888886</v>
       </c>
       <c r="X42" s="15">
-        <v>25.117647058823536</v>
+        <v>-2.5555555555555429</v>
       </c>
       <c r="Y42" s="18">
         <v>82</v>
@@ -5596,19 +5598,19 @@
         <v>504.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>23.627118644067796</v>
+        <v>25.01694915254237</v>
       </c>
       <c r="AB42" s="16">
-        <v>76.352941176470594</v>
+        <v>72.111111111111114</v>
       </c>
       <c r="AC42" s="15">
-        <v>5.6470588235294059</v>
+        <v>9.8888888888888857</v>
       </c>
       <c r="AD42" s="19">
-        <v>1657</v>
+        <v>1535</v>
       </c>
       <c r="AE42" s="20">
-        <v>10190.550000000001</v>
+        <v>9440.25</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5643,85 +5645,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2071</v>
+        <v>1802</v>
       </c>
       <c r="F43" s="14">
-        <v>2402.3599999999997</v>
+        <v>2090.3199999999997</v>
       </c>
       <c r="G43" s="14">
-        <v>6.3299172959367134</v>
+        <v>5.4957641477465264</v>
       </c>
       <c r="H43" s="30">
-        <v>7197.8823529411766</v>
+        <v>7213.5555555555566</v>
       </c>
       <c r="I43" s="15">
-        <v>-1200.7647058823532</v>
+        <v>-1476.8888888888891</v>
       </c>
       <c r="J43" s="16">
-        <v>3499</v>
+        <v>3140</v>
       </c>
       <c r="K43" s="13">
-        <v>4058.8399999999997</v>
+        <v>3642.3999999999996</v>
       </c>
       <c r="L43" s="14">
-        <v>14.278204512722038</v>
+        <v>12.454825914499779</v>
       </c>
       <c r="M43" s="30">
-        <v>5391.2941176470586</v>
+        <v>5546.4444444444443</v>
       </c>
       <c r="N43" s="15">
-        <v>1048.4117647058824</v>
+        <v>618.88888888888869</v>
       </c>
       <c r="O43" s="16">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="P43" s="17">
-        <v>1069.52</v>
+        <v>1013.8399999999999</v>
       </c>
       <c r="Q43" s="14">
-        <v>19.56803995006242</v>
+        <v>19.350553505535057</v>
       </c>
       <c r="R43" s="16">
-        <v>1036.5882352941176</v>
+        <v>993.66666666666663</v>
       </c>
       <c r="S43" s="15">
-        <v>-20.352941176470608</v>
+        <v>-29.333333333333258</v>
       </c>
       <c r="T43" s="18">
-        <v>1710</v>
+        <v>1520</v>
       </c>
       <c r="U43" s="17">
-        <v>1983.6</v>
+        <v>1763.1999999999998</v>
       </c>
       <c r="V43" s="14">
-        <v>14.527736131934033</v>
+        <v>12.82099343955014</v>
       </c>
       <c r="W43" s="16">
-        <v>2589.5294117647059</v>
+        <v>2608.2222222222222</v>
       </c>
       <c r="X43" s="15">
-        <v>-173.29411764705878</v>
+        <v>-376.88888888888891</v>
       </c>
       <c r="Y43" s="18">
-        <v>108</v>
+        <v>560</v>
       </c>
       <c r="Z43" s="17">
-        <v>125.27999999999999</v>
+        <v>649.59999999999991</v>
       </c>
       <c r="AA43" s="14">
-        <v>3.9483870967741939</v>
+        <v>18.294010889292196</v>
       </c>
       <c r="AB43" s="16">
-        <v>601.76470588235293</v>
+        <v>673.44444444444446</v>
       </c>
       <c r="AC43" s="15">
-        <v>-493.76470588235293</v>
+        <v>-113.44444444444446</v>
       </c>
       <c r="AD43" s="19">
-        <v>8310</v>
+        <v>7896</v>
       </c>
       <c r="AE43" s="20">
-        <v>9639.5999999999985</v>
+        <v>9159.3599999999988</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5756,85 +5758,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2158</v>
+        <v>1879</v>
       </c>
       <c r="F44" s="14">
-        <v>2503.2799999999997</v>
+        <v>2179.64</v>
       </c>
       <c r="G44" s="14">
-        <v>7.5454545454545459</v>
+        <v>6.4793103448275859</v>
       </c>
       <c r="H44" s="30">
-        <v>6292</v>
+        <v>6380</v>
       </c>
       <c r="I44" s="15">
-        <v>-702</v>
+        <v>-1021</v>
       </c>
       <c r="J44" s="16">
-        <v>2035</v>
+        <v>4279</v>
       </c>
       <c r="K44" s="13">
-        <v>2360.6</v>
+        <v>4963.6399999999994</v>
       </c>
       <c r="L44" s="14">
-        <v>10.68736484399135</v>
+        <v>22.075666380051587</v>
       </c>
       <c r="M44" s="30">
-        <v>4189.0588235294117</v>
+        <v>4264.3333333333339</v>
       </c>
       <c r="N44" s="15">
-        <v>130.88235294117658</v>
+        <v>2340.6666666666661</v>
       </c>
       <c r="O44" s="16">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="P44" s="17">
-        <v>693.68</v>
+        <v>670.4799999999999</v>
       </c>
       <c r="Q44" s="14">
-        <v>20.874743326488705</v>
+        <v>20.849699398797593</v>
       </c>
       <c r="R44" s="16">
-        <v>630.23529411764707</v>
+        <v>609.88888888888891</v>
       </c>
       <c r="S44" s="15">
-        <v>25.058823529411711</v>
+        <v>23.555555555555543</v>
       </c>
       <c r="T44" s="18">
-        <v>1024</v>
+        <v>941</v>
       </c>
       <c r="U44" s="17">
-        <v>1187.8399999999999</v>
+        <v>1091.56</v>
       </c>
       <c r="V44" s="14">
-        <v>16.029465930018414</v>
+        <v>14.754355400696864</v>
       </c>
       <c r="W44" s="16">
-        <v>1405.4117647058824</v>
+        <v>1403.1111111111111</v>
       </c>
       <c r="X44" s="15">
-        <v>1.8823529411764639</v>
+        <v>-79.444444444444457</v>
       </c>
       <c r="Y44" s="18">
-        <v>194</v>
+        <v>479</v>
       </c>
       <c r="Z44" s="17">
-        <v>225.04</v>
+        <v>555.64</v>
       </c>
       <c r="AA44" s="14">
-        <v>7.3452115812917596</v>
+        <v>16.026022304832715</v>
       </c>
       <c r="AB44" s="16">
-        <v>581.05882352941171</v>
+        <v>657.55555555555554</v>
       </c>
       <c r="AC44" s="15">
-        <v>-387.05882352941171</v>
+        <v>-178.55555555555554</v>
       </c>
       <c r="AD44" s="19">
-        <v>6009</v>
+        <v>8156</v>
       </c>
       <c r="AE44" s="20">
-        <v>6970.44</v>
+        <v>9460.9599999999991</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5869,85 +5871,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>1739</v>
+        <v>1501</v>
       </c>
       <c r="F45" s="14">
-        <v>2017.2399999999998</v>
+        <v>1741.1599999999999</v>
       </c>
       <c r="G45" s="14">
-        <v>4.6127320954907161</v>
+        <v>3.9896633195510929</v>
       </c>
       <c r="H45" s="30">
-        <v>8294</v>
+        <v>8276.8888888888887</v>
       </c>
       <c r="I45" s="15">
-        <v>-2031</v>
+        <v>-2261.2222222222222</v>
       </c>
       <c r="J45" s="16">
-        <v>5610</v>
+        <v>5293</v>
       </c>
       <c r="K45" s="13">
-        <v>6507.5999999999995</v>
+        <v>6139.8799999999992</v>
       </c>
       <c r="L45" s="14">
-        <v>22.005076142131976</v>
+        <v>20.379465240641711</v>
       </c>
       <c r="M45" s="30">
-        <v>5608.7058823529414</v>
+        <v>5713.8888888888887</v>
       </c>
       <c r="N45" s="15">
-        <v>3060.5882352941176</v>
+        <v>2695.7777777777778</v>
       </c>
       <c r="O45" s="16">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="P45" s="17">
-        <v>1021.9599999999999</v>
+        <v>1010.3599999999999</v>
       </c>
       <c r="Q45" s="14">
-        <v>20.266576454668471</v>
+        <v>21.186486486486483</v>
       </c>
       <c r="R45" s="16">
-        <v>956.35294117647049</v>
+        <v>904.44444444444457</v>
       </c>
       <c r="S45" s="15">
-        <v>11.58823529411768</v>
+        <v>48.777777777777715</v>
       </c>
       <c r="T45" s="18">
-        <v>1500</v>
+        <v>1368</v>
       </c>
       <c r="U45" s="17">
-        <v>1739.9999999999998</v>
+        <v>1586.8799999999999</v>
       </c>
       <c r="V45" s="14">
-        <v>15.828677839851023</v>
+        <v>14.527433628318581</v>
       </c>
       <c r="W45" s="16">
-        <v>2084.8235294117649</v>
+        <v>2071.666666666667</v>
       </c>
       <c r="X45" s="15">
-        <v>-16.235294117647072</v>
+        <v>-138.66666666666697</v>
       </c>
       <c r="Y45" s="18">
-        <v>163</v>
+        <v>489</v>
       </c>
       <c r="Z45" s="17">
-        <v>189.07999999999998</v>
+        <v>567.24</v>
       </c>
       <c r="AA45" s="14">
-        <v>6.7094430992736074</v>
+        <v>17.225048923679061</v>
       </c>
       <c r="AB45" s="16">
-        <v>534.47058823529414</v>
+        <v>624.55555555555554</v>
       </c>
       <c r="AC45" s="15">
-        <v>-371.47058823529414</v>
+        <v>-135.55555555555554</v>
       </c>
       <c r="AD45" s="19">
-        <v>9893</v>
+        <v>9522</v>
       </c>
       <c r="AE45" s="20">
-        <v>11475.88</v>
+        <v>11045.519999999999</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5982,85 +5984,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2116</v>
+        <v>1878</v>
       </c>
       <c r="F46" s="14">
-        <v>2454.56</v>
+        <v>2178.48</v>
       </c>
       <c r="G46" s="14">
-        <v>7.6585054289972314</v>
+        <v>6.7473053892215571</v>
       </c>
       <c r="H46" s="30">
-        <v>6078.4705882352946</v>
+        <v>6123.333333333333</v>
       </c>
       <c r="I46" s="15">
-        <v>-646.94117647058829</v>
+        <v>-905.33333333333303</v>
       </c>
       <c r="J46" s="16">
-        <v>2669</v>
+        <v>2401</v>
       </c>
       <c r="K46" s="13">
-        <v>3096.04</v>
+        <v>2785.16</v>
       </c>
       <c r="L46" s="14">
-        <v>16.886118347599552</v>
+        <v>14.755206555138273</v>
       </c>
       <c r="M46" s="30">
-        <v>3477.294117647059</v>
+        <v>3579.8888888888891</v>
       </c>
       <c r="N46" s="15">
-        <v>1088.4117647058824</v>
+        <v>773.77777777777783</v>
       </c>
       <c r="O46" s="16">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="P46" s="17">
-        <v>690.19999999999993</v>
+        <v>661.19999999999993</v>
       </c>
       <c r="Q46" s="14">
-        <v>23.041002277904326</v>
+        <v>22.749445676274942</v>
       </c>
       <c r="R46" s="16">
-        <v>568.11764705882354</v>
+        <v>551.22222222222229</v>
       </c>
       <c r="S46" s="15">
-        <v>78.529411764705856</v>
+        <v>68.888888888888857</v>
       </c>
       <c r="T46" s="18">
-        <v>712</v>
+        <v>665</v>
       </c>
       <c r="U46" s="17">
-        <v>825.92</v>
+        <v>771.4</v>
       </c>
       <c r="V46" s="14">
-        <v>18.256410256410255</v>
+        <v>16.859154929577464</v>
       </c>
       <c r="W46" s="16">
-        <v>858</v>
+        <v>867.77777777777771</v>
       </c>
       <c r="X46" s="15">
-        <v>88</v>
+        <v>33.888888888888914</v>
       </c>
       <c r="Y46" s="18">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="Z46" s="17">
-        <v>0</v>
+        <v>626.4</v>
       </c>
       <c r="AA46" s="14">
-        <v>0</v>
+        <v>22.8169014084507</v>
       </c>
       <c r="AB46" s="16">
-        <v>551.29411764705878</v>
+        <v>520.66666666666674</v>
       </c>
       <c r="AC46" s="15">
-        <v>-551.29411764705878</v>
+        <v>19.333333333333258</v>
       </c>
       <c r="AD46" s="19">
-        <v>6092</v>
+        <v>6054</v>
       </c>
       <c r="AE46" s="20">
-        <v>7066.7199999999993</v>
+        <v>7022.6399999999994</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6108,19 +6110,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K47" s="13">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="L47" s="14">
-        <v>3.0599999999999992</v>
+        <v>0.31034482758620691</v>
       </c>
       <c r="M47" s="30">
-        <v>64.705882352941188</v>
+        <v>70.888888888888886</v>
       </c>
       <c r="N47" s="15">
-        <v>-20.411764705882359</v>
+        <v>-31.222222222222221</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6144,13 +6146,13 @@
         <v>288</v>
       </c>
       <c r="V47" s="14">
-        <v>14.315789473684211</v>
+        <v>15.157894736842104</v>
       </c>
       <c r="W47" s="16">
-        <v>24.588235294117649</v>
+        <v>23.222222222222221</v>
       </c>
       <c r="X47" s="15">
-        <v>-1.882352941176471</v>
+        <v>-0.88888888888888928</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6168,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AE47" s="20">
-        <v>450</v>
+        <v>306</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6225,13 +6227,13 @@
         <v>108</v>
       </c>
       <c r="L48" s="14">
-        <v>9.2727272727272716</v>
+        <v>9.8181818181818166</v>
       </c>
       <c r="M48" s="30">
-        <v>14.23529411764706</v>
+        <v>13.444444444444446</v>
       </c>
       <c r="N48" s="15">
-        <v>-0.47058823529411775</v>
+        <v>-0.1111111111111116</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6317,19 +6319,19 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="F49" s="14">
-        <v>155.44</v>
+        <v>91.64</v>
       </c>
       <c r="G49" s="14">
-        <v>2.3729166666666668</v>
+        <v>1.4205794205794204</v>
       </c>
       <c r="H49" s="30">
-        <v>1242.3529411764705</v>
+        <v>1223.4444444444446</v>
       </c>
       <c r="I49" s="15">
-        <v>-430.70588235294122</v>
+        <v>-477.11111111111109</v>
       </c>
       <c r="J49" s="16">
         <v>0</v>
@@ -6341,61 +6343,61 @@
         <v>0</v>
       </c>
       <c r="M49" s="30">
-        <v>1450.705882352941</v>
+        <v>1370.1111111111111</v>
       </c>
       <c r="N49" s="15">
-        <v>-659.41176470588232</v>
+        <v>-622.77777777777783</v>
       </c>
       <c r="O49" s="16">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="P49" s="17">
-        <v>87</v>
+        <v>47.559999999999995</v>
       </c>
       <c r="Q49" s="14">
-        <v>9.9609374999999982</v>
+        <v>5.5074626865671643</v>
       </c>
       <c r="R49" s="16">
-        <v>165.64705882352942</v>
+        <v>163.77777777777777</v>
       </c>
       <c r="S49" s="15">
-        <v>-75.588235294117652</v>
+        <v>-107.88888888888889</v>
       </c>
       <c r="T49" s="18">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="U49" s="17">
-        <v>37.119999999999997</v>
+        <v>26.68</v>
       </c>
       <c r="V49" s="14">
-        <v>2.6407766990291264</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="W49" s="16">
-        <v>266.58823529411762</v>
+        <v>281.11111111111114</v>
       </c>
       <c r="X49" s="15">
-        <v>-161.88235294117646</v>
+        <v>-181.44444444444446</v>
       </c>
       <c r="Y49" s="18">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z49" s="17">
-        <v>33.64</v>
+        <v>27.839999999999996</v>
       </c>
       <c r="AA49" s="14">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AB49" s="16">
         <v>110</v>
       </c>
       <c r="AC49" s="15">
-        <v>-81</v>
+        <v>-86</v>
       </c>
       <c r="AD49" s="19">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="AE49" s="20">
-        <v>313.2</v>
+        <v>193.72</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6430,85 +6432,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>750</v>
+        <v>540</v>
       </c>
       <c r="F50" s="14">
-        <v>869.99999999999989</v>
+        <v>626.4</v>
       </c>
       <c r="G50" s="14">
-        <v>2.5925172834485561</v>
+        <v>1.8822618125484119</v>
       </c>
       <c r="H50" s="30">
-        <v>6364.4705882352946</v>
+        <v>6311.5555555555566</v>
       </c>
       <c r="I50" s="15">
-        <v>-2142.9411764705883</v>
+        <v>-2328.8888888888891</v>
       </c>
       <c r="J50" s="16">
-        <v>3830</v>
+        <v>3666</v>
       </c>
       <c r="K50" s="13">
-        <v>4442.7999999999993</v>
+        <v>4252.5599999999995</v>
       </c>
       <c r="L50" s="14">
-        <v>19.978521018717398</v>
+        <v>19.300380228136881</v>
       </c>
       <c r="M50" s="30">
-        <v>4217.5294117647063</v>
+        <v>4178.7777777777783</v>
       </c>
       <c r="N50" s="15">
-        <v>1912.9411764705881</v>
+        <v>1766.5555555555554</v>
       </c>
       <c r="O50" s="16">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="P50" s="17">
-        <v>310.88</v>
+        <v>219.23999999999998</v>
       </c>
       <c r="Q50" s="14">
-        <v>6.2841379310344827</v>
+        <v>4.4763157894736842</v>
       </c>
       <c r="R50" s="16">
-        <v>938.23529411764707</v>
+        <v>928.88888888888891</v>
       </c>
       <c r="S50" s="15">
-        <v>-584.94117647058829</v>
+        <v>-655.44444444444446</v>
       </c>
       <c r="T50" s="18">
-        <v>815</v>
+        <v>670</v>
       </c>
       <c r="U50" s="17">
-        <v>945.4</v>
+        <v>777.19999999999993</v>
       </c>
       <c r="V50" s="14">
-        <v>24.179755671902271</v>
+        <v>18.582434514637903</v>
       </c>
       <c r="W50" s="16">
-        <v>741.52941176470586</v>
+        <v>793.22222222222229</v>
       </c>
       <c r="X50" s="15">
-        <v>275.70588235294122</v>
+        <v>93.111111111111086</v>
       </c>
       <c r="Y50" s="18">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="Z50" s="17">
-        <v>47.559999999999995</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="AA50" s="14">
-        <v>3.5025125628140708</v>
+        <v>2.5714285714285721</v>
       </c>
       <c r="AB50" s="16">
-        <v>257.52941176470586</v>
+        <v>256.66666666666663</v>
       </c>
       <c r="AC50" s="15">
-        <v>-216.52941176470586</v>
+        <v>-226.66666666666663</v>
       </c>
       <c r="AD50" s="19">
-        <v>5704</v>
+        <v>5095</v>
       </c>
       <c r="AE50" s="20">
-        <v>6616.6399999999994</v>
+        <v>5910.2</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6546,85 +6548,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>771</v>
+        <v>547</v>
       </c>
       <c r="F51" s="14">
-        <v>894.3599999999999</v>
+        <v>634.52</v>
       </c>
       <c r="G51" s="14">
-        <v>4.0641860465116277</v>
+        <v>2.832566168009206</v>
       </c>
       <c r="H51" s="30">
-        <v>4173.5294117647063</v>
+        <v>4248.4444444444443</v>
       </c>
       <c r="I51" s="15">
-        <v>-1126.0588235294119</v>
+        <v>-1384.1111111111111</v>
       </c>
       <c r="J51" s="16">
-        <v>1833</v>
+        <v>2533</v>
       </c>
       <c r="K51" s="13">
-        <v>2126.2799999999997</v>
+        <v>2938.2799999999997</v>
       </c>
       <c r="L51" s="14">
-        <v>10.675231243576567</v>
+        <v>14.736263736263737</v>
       </c>
       <c r="M51" s="30">
-        <v>3777.5294117647063</v>
+        <v>3781.5555555555557</v>
       </c>
       <c r="N51" s="15">
-        <v>115.94117647058806</v>
+        <v>814.11111111111109</v>
       </c>
       <c r="O51" s="16">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="P51" s="17">
-        <v>331.76</v>
+        <v>299.27999999999997</v>
       </c>
       <c r="Q51" s="14">
-        <v>20.777777777777775</v>
+        <v>17.861538461538462</v>
       </c>
       <c r="R51" s="16">
-        <v>302.82352941176475</v>
+        <v>317.77777777777777</v>
       </c>
       <c r="S51" s="15">
-        <v>10.705882352941103</v>
+        <v>-30.888888888888914</v>
       </c>
       <c r="T51" s="18">
-        <v>563</v>
+        <v>491</v>
       </c>
       <c r="U51" s="17">
-        <v>653.07999999999993</v>
+        <v>569.55999999999995</v>
       </c>
       <c r="V51" s="14">
-        <v>16.616319444444443</v>
+        <v>14.277867528271408</v>
       </c>
       <c r="W51" s="16">
-        <v>745.41176470588232</v>
+        <v>756.55555555555543</v>
       </c>
       <c r="X51" s="15">
-        <v>20.882352941176464</v>
+        <v>-59.222222222222172</v>
       </c>
       <c r="Y51" s="18">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="Z51" s="17">
-        <v>98.6</v>
+        <v>153.11999999999998</v>
       </c>
       <c r="AA51" s="14">
-        <v>20.069444444444443</v>
+        <v>30.075949367088604</v>
       </c>
       <c r="AB51" s="16">
-        <v>93.17647058823529</v>
+        <v>96.555555555555571</v>
       </c>
       <c r="AC51" s="15">
-        <v>-8.1764705882352899</v>
+        <v>35.444444444444429</v>
       </c>
       <c r="AD51" s="19">
-        <v>3538</v>
+        <v>3961</v>
       </c>
       <c r="AE51" s="20">
-        <v>4104.08</v>
+        <v>4594.7599999999993</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6663,34 +6665,34 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>2235</v>
+        <v>2195</v>
       </c>
       <c r="F52" s="14">
-        <v>1810.3500000000001</v>
+        <v>1777.95</v>
       </c>
       <c r="G52" s="14">
-        <v>14.310734463276836</v>
+        <v>14.005671747607231</v>
       </c>
       <c r="H52" s="30">
-        <v>3435.8823529411766</v>
+        <v>3447.8888888888891</v>
       </c>
       <c r="I52" s="15">
-        <v>673.23529411764684</v>
+        <v>627.77777777777783</v>
       </c>
       <c r="J52" s="16">
-        <v>789</v>
+        <v>694</v>
       </c>
       <c r="K52" s="13">
-        <v>639.09</v>
+        <v>562.14</v>
       </c>
       <c r="L52" s="14">
-        <v>17.556282722513089</v>
+        <v>14.276571428571428</v>
       </c>
       <c r="M52" s="30">
-        <v>988.7058823529411</v>
+        <v>1069.4444444444446</v>
       </c>
       <c r="N52" s="15">
-        <v>339.58823529411768</v>
+        <v>207.88888888888886</v>
       </c>
       <c r="O52" s="16">
         <v>156</v>
@@ -6699,49 +6701,49 @@
         <v>126.36000000000001</v>
       </c>
       <c r="Q52" s="14">
-        <v>22.666666666666661</v>
+        <v>24</v>
       </c>
       <c r="R52" s="16">
-        <v>151.41176470588238</v>
+        <v>143</v>
       </c>
       <c r="S52" s="15">
-        <v>18.352941176470551</v>
+        <v>26</v>
       </c>
       <c r="T52" s="18">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="U52" s="17">
-        <v>328.05</v>
+        <v>315.90000000000003</v>
       </c>
       <c r="V52" s="14">
-        <v>19.125</v>
+        <v>19.180327868852459</v>
       </c>
       <c r="W52" s="16">
-        <v>465.88235294117646</v>
+        <v>447.33333333333331</v>
       </c>
       <c r="X52" s="15">
-        <v>66.176470588235304</v>
+        <v>64.666666666666686</v>
       </c>
       <c r="Y52" s="18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Z52" s="17">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="AA52" s="14">
-        <v>0</v>
+        <v>93.913043478260875</v>
       </c>
       <c r="AB52" s="16">
-        <v>29.764705882352942</v>
+        <v>28.111111111111107</v>
       </c>
       <c r="AC52" s="15">
-        <v>-29.764705882352942</v>
+        <v>91.888888888888886</v>
       </c>
       <c r="AD52" s="19">
-        <v>3585</v>
+        <v>3555</v>
       </c>
       <c r="AE52" s="20">
-        <v>2903.8500000000004</v>
+        <v>2879.55</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6776,85 +6778,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>977</v>
+        <v>383</v>
       </c>
       <c r="F53" s="14">
-        <v>791.37</v>
+        <v>310.23</v>
       </c>
       <c r="G53" s="14">
-        <v>3.4630942452043367</v>
+        <v>1.3713944698627412</v>
       </c>
       <c r="H53" s="30">
-        <v>6206.588235294118</v>
+        <v>6144.1111111111113</v>
       </c>
       <c r="I53" s="15">
-        <v>-1844.1764705882351</v>
+        <v>-2409.7777777777778</v>
       </c>
       <c r="J53" s="16">
-        <v>318</v>
+        <v>141</v>
       </c>
       <c r="K53" s="13">
-        <v>257.58000000000004</v>
+        <v>114.21000000000001</v>
       </c>
       <c r="L53" s="14">
-        <v>2.533270852858482</v>
+        <v>1.0963282937365011</v>
       </c>
       <c r="M53" s="30">
-        <v>2761.6470588235293</v>
+        <v>2829.4444444444443</v>
       </c>
       <c r="N53" s="15">
-        <v>-937.29411764705878</v>
+        <v>-1145.1111111111111</v>
       </c>
       <c r="O53" s="16">
-        <v>594</v>
+        <v>560</v>
       </c>
       <c r="P53" s="17">
-        <v>481.14000000000004</v>
+        <v>453.6</v>
       </c>
       <c r="Q53" s="14">
-        <v>21.439490445859875</v>
+        <v>21.401273885350314</v>
       </c>
       <c r="R53" s="16">
-        <v>609.52941176470586</v>
+        <v>575.66666666666674</v>
       </c>
       <c r="S53" s="15">
-        <v>39.882352941176578</v>
+        <v>36.666666666666515</v>
       </c>
       <c r="T53" s="18">
-        <v>875</v>
+        <v>848</v>
       </c>
       <c r="U53" s="17">
-        <v>708.75</v>
+        <v>686.88</v>
       </c>
       <c r="V53" s="14">
-        <v>16.564587973273944</v>
+        <v>16.773626373626374</v>
       </c>
       <c r="W53" s="16">
-        <v>1162.1176470588234</v>
+        <v>1112.2222222222222</v>
       </c>
       <c r="X53" s="15">
-        <v>29.823529411764753</v>
+        <v>39.1111111111112</v>
       </c>
       <c r="Y53" s="18">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="Z53" s="17">
-        <v>7.2900000000000009</v>
+        <v>194.4</v>
       </c>
       <c r="AA53" s="14">
-        <v>1.3909090909090911</v>
+        <v>36.30252100840336</v>
       </c>
       <c r="AB53" s="16">
-        <v>142.35294117647058</v>
+        <v>145.44444444444443</v>
       </c>
       <c r="AC53" s="15">
-        <v>-133.35294117647058</v>
+        <v>94.555555555555571</v>
       </c>
       <c r="AD53" s="19">
-        <v>2773</v>
+        <v>2172</v>
       </c>
       <c r="AE53" s="20">
-        <v>2246.13</v>
+        <v>1759.3200000000002</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6889,85 +6891,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>2423</v>
+        <v>2260</v>
       </c>
       <c r="F54" s="14">
-        <v>1962.63</v>
+        <v>1830.6000000000001</v>
       </c>
       <c r="G54" s="14">
-        <v>12.884266499843605</v>
+        <v>11.815277374382804</v>
       </c>
       <c r="H54" s="30">
-        <v>4137.2941176470586</v>
+        <v>4208.1111111111113</v>
       </c>
       <c r="I54" s="15">
-        <v>542.41176470588266</v>
+        <v>347.22222222222194</v>
       </c>
       <c r="J54" s="16">
-        <v>3340</v>
+        <v>3308</v>
       </c>
       <c r="K54" s="13">
-        <v>2705.4</v>
+        <v>2679.48</v>
       </c>
       <c r="L54" s="14">
-        <v>52.671614100185536</v>
+        <v>52.507936507936506</v>
       </c>
       <c r="M54" s="30">
-        <v>1395.0588235294117</v>
+        <v>1386</v>
       </c>
       <c r="N54" s="15">
-        <v>2705.8823529411766</v>
+        <v>2678</v>
       </c>
       <c r="O54" s="16">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="P54" s="17">
-        <v>201.69000000000003</v>
+        <v>193.59</v>
       </c>
       <c r="Q54" s="14">
-        <v>19.067567567567565</v>
+        <v>19.378378378378375</v>
       </c>
       <c r="R54" s="16">
-        <v>287.29411764705884</v>
+        <v>271.33333333333337</v>
       </c>
       <c r="S54" s="15">
-        <v>-12.176470588235304</v>
+        <v>-7.666666666666714</v>
       </c>
       <c r="T54" s="18">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="U54" s="17">
-        <v>383.13000000000005</v>
+        <v>378.27000000000004</v>
       </c>
       <c r="V54" s="14">
-        <v>19.236842105263158</v>
+        <v>20.110047846889952</v>
       </c>
       <c r="W54" s="16">
-        <v>540.94117647058829</v>
+        <v>510.88888888888886</v>
       </c>
       <c r="X54" s="15">
-        <v>79.588235294117624</v>
+        <v>95.444444444444457</v>
       </c>
       <c r="Y54" s="18">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="Z54" s="17">
-        <v>93.15</v>
+        <v>170.91000000000003</v>
       </c>
       <c r="AA54" s="14">
-        <v>14.589552238805968</v>
+        <v>24.037974683544302</v>
       </c>
       <c r="AB54" s="16">
-        <v>173.41176470588238</v>
+        <v>193.11111111111114</v>
       </c>
       <c r="AC54" s="15">
-        <v>-58.411764705882376</v>
+        <v>17.888888888888857</v>
       </c>
       <c r="AD54" s="19">
-        <v>6600</v>
+        <v>6485</v>
       </c>
       <c r="AE54" s="20">
-        <v>5346</v>
+        <v>5252.85</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7002,85 +7004,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>2298</v>
+        <v>2196</v>
       </c>
       <c r="F55" s="14">
-        <v>1861.38</v>
+        <v>1778.7600000000002</v>
       </c>
       <c r="G55" s="14">
-        <v>13.588173913043478</v>
+        <v>12.888164329964134</v>
       </c>
       <c r="H55" s="30">
-        <v>3720.588235294118</v>
+        <v>3748.5555555555557</v>
       </c>
       <c r="I55" s="15">
-        <v>606.82352941176464</v>
+        <v>492.11111111111109</v>
       </c>
       <c r="J55" s="16">
-        <v>6333</v>
+        <v>6276</v>
       </c>
       <c r="K55" s="13">
-        <v>5129.7300000000005</v>
+        <v>5083.5600000000004</v>
       </c>
       <c r="L55" s="14">
-        <v>81.009029345372468</v>
+        <v>80.576319543509271</v>
       </c>
       <c r="M55" s="30">
-        <v>1719.8823529411764</v>
+        <v>1713.5555555555554</v>
       </c>
       <c r="N55" s="15">
-        <v>5551.2352941176468</v>
+        <v>5497.1111111111113</v>
       </c>
       <c r="O55" s="16">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="P55" s="17">
-        <v>292.41000000000003</v>
+        <v>284.31</v>
       </c>
       <c r="Q55" s="14">
-        <v>19.669871794871796</v>
+        <v>20.25</v>
       </c>
       <c r="R55" s="16">
-        <v>403.76470588235293</v>
+        <v>381.33333333333331</v>
       </c>
       <c r="S55" s="15">
-        <v>-6.0588235294117112</v>
+        <v>4.3333333333333712</v>
       </c>
       <c r="T55" s="18">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="U55" s="17">
-        <v>387.99</v>
+        <v>380.70000000000005</v>
       </c>
       <c r="V55" s="14">
-        <v>17.702173913043477</v>
+        <v>18.391304347826086</v>
       </c>
       <c r="W55" s="16">
-        <v>595.29411764705878</v>
+        <v>562.22222222222229</v>
       </c>
       <c r="X55" s="15">
-        <v>46.058823529411768</v>
+        <v>61.111111111111086</v>
       </c>
       <c r="Y55" s="18">
-        <v>126</v>
+        <v>225</v>
       </c>
       <c r="Z55" s="17">
-        <v>102.06</v>
+        <v>182.25</v>
       </c>
       <c r="AA55" s="14">
-        <v>15.3</v>
+        <v>25.155279503105589</v>
       </c>
       <c r="AB55" s="16">
-        <v>181.17647058823528</v>
+        <v>196.77777777777777</v>
       </c>
       <c r="AC55" s="15">
-        <v>-55.176470588235276</v>
+        <v>28.222222222222229</v>
       </c>
       <c r="AD55" s="19">
-        <v>9597</v>
+        <v>9518</v>
       </c>
       <c r="AE55" s="20">
-        <v>7773.5700000000006</v>
+        <v>7709.5800000000008</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7115,34 +7117,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F56" s="14">
-        <v>833.16000000000008</v>
+        <v>822.68000000000006</v>
       </c>
       <c r="G56" s="14">
-        <v>9.6363636363636367</v>
+        <v>9.8638743455497391</v>
       </c>
       <c r="H56" s="30">
-        <v>726</v>
+        <v>700.33333333333326</v>
       </c>
       <c r="I56" s="15">
-        <v>-12</v>
+        <v>-4.3333333333332575</v>
       </c>
       <c r="J56" s="32">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K56" s="13">
-        <v>332.74</v>
+        <v>317.02000000000004</v>
       </c>
       <c r="L56" s="14">
-        <v>9.03347280334728</v>
+        <v>9.1129707112970699</v>
       </c>
       <c r="M56" s="30">
-        <v>309.29411764705884</v>
+        <v>292.11111111111114</v>
       </c>
       <c r="N56" s="15">
-        <v>-13.588235294117652</v>
+        <v>-11.777777777777771</v>
       </c>
       <c r="O56" s="32">
         <v>55</v>
@@ -7151,13 +7153,13 @@
         <v>144.1</v>
       </c>
       <c r="Q56" s="14">
-        <v>19.479166666666664</v>
+        <v>20.625</v>
       </c>
       <c r="R56" s="16">
-        <v>62.117647058823536</v>
+        <v>58.666666666666664</v>
       </c>
       <c r="S56" s="15">
-        <v>-1.4705882352941231</v>
+        <v>1.6666666666666714</v>
       </c>
       <c r="T56" s="18">
         <v>126</v>
@@ -7166,13 +7168,13 @@
         <v>330.12</v>
       </c>
       <c r="V56" s="14">
-        <v>17.414634146341463</v>
+        <v>18.439024390243905</v>
       </c>
       <c r="W56" s="16">
-        <v>159.1764705882353</v>
+        <v>150.33333333333331</v>
       </c>
       <c r="X56" s="15">
-        <v>10.235294117647058</v>
+        <v>16.666666666666686</v>
       </c>
       <c r="Y56" s="18">
         <v>45</v>
@@ -7181,19 +7183,19 @@
         <v>117.9</v>
       </c>
       <c r="AA56" s="14">
-        <v>24.677419354838712</v>
+        <v>26.129032258064516</v>
       </c>
       <c r="AB56" s="16">
-        <v>40.117647058823529</v>
+        <v>37.888888888888893</v>
       </c>
       <c r="AC56" s="15">
-        <v>4.882352941176471</v>
+        <v>7.1111111111111072</v>
       </c>
       <c r="AD56" s="19">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="AE56" s="20">
-        <v>1758.02</v>
+        <v>1731.8200000000002</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7228,34 +7230,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="F57" s="14">
-        <v>799.1</v>
+        <v>599.98</v>
       </c>
       <c r="G57" s="14">
-        <v>4.6502242152466362</v>
+        <v>3.3241935483870968</v>
       </c>
       <c r="H57" s="30">
-        <v>1442.9411764705883</v>
+        <v>1515.5555555555554</v>
       </c>
       <c r="I57" s="15">
-        <v>-350.88235294117658</v>
+        <v>-459.88888888888891</v>
       </c>
       <c r="J57" s="32">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K57" s="13">
-        <v>157.20000000000002</v>
+        <v>89.08</v>
       </c>
       <c r="L57" s="14">
-        <v>2.0278330019880713</v>
+        <v>1.1657142857142855</v>
       </c>
       <c r="M57" s="30">
-        <v>650.94117647058829</v>
+        <v>641.66666666666674</v>
       </c>
       <c r="N57" s="15">
-        <v>-235.88235294117646</v>
+        <v>-257.66666666666674</v>
       </c>
       <c r="O57" s="32">
         <v>105</v>
@@ -7264,13 +7266,13 @@
         <v>275.10000000000002</v>
       </c>
       <c r="Q57" s="14">
-        <v>16.22727272727273</v>
+        <v>17.181818181818183</v>
       </c>
       <c r="R57" s="16">
-        <v>142.35294117647058</v>
+        <v>134.44444444444443</v>
       </c>
       <c r="S57" s="15">
-        <v>-24.411764705882348</v>
+        <v>-17.222222222222214</v>
       </c>
       <c r="T57" s="18">
         <v>120</v>
@@ -7279,13 +7281,13 @@
         <v>314.40000000000003</v>
       </c>
       <c r="V57" s="14">
-        <v>6.1445783132530112</v>
+        <v>6.5060240963855431</v>
       </c>
       <c r="W57" s="16">
-        <v>429.64705882352945</v>
+        <v>405.77777777777771</v>
       </c>
       <c r="X57" s="15">
-        <v>-192.47058823529414</v>
+        <v>-175.11111111111109</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7294,19 +7296,19 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>31.874999999999996</v>
+        <v>33.75</v>
       </c>
       <c r="AB57" s="16">
-        <v>41.411764705882355</v>
+        <v>39.111111111111107</v>
       </c>
       <c r="AC57" s="15">
-        <v>18.588235294117645</v>
+        <v>20.888888888888893</v>
       </c>
       <c r="AD57" s="19">
-        <v>650</v>
+        <v>548</v>
       </c>
       <c r="AE57" s="20">
-        <v>1703</v>
+        <v>1435.76</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7341,34 +7343,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F58" s="14">
-        <v>248.9</v>
+        <v>220.08</v>
       </c>
       <c r="G58" s="14">
-        <v>3.8089622641509435</v>
+        <v>3.2869565217391301</v>
       </c>
       <c r="H58" s="30">
-        <v>548.70588235294122</v>
+        <v>562.22222222222229</v>
       </c>
       <c r="I58" s="15">
-        <v>-154.41176470588235</v>
+        <v>-171.55555555555557</v>
       </c>
       <c r="J58" s="32">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K58" s="13">
-        <v>154.58000000000001</v>
+        <v>151.96</v>
       </c>
       <c r="L58" s="14">
-        <v>6.1533742331288348</v>
+        <v>6.2142857142857135</v>
       </c>
       <c r="M58" s="30">
-        <v>210.94117647058823</v>
+        <v>205.33333333333334</v>
       </c>
       <c r="N58" s="15">
-        <v>-36.882352941176464</v>
+        <v>-35.333333333333343</v>
       </c>
       <c r="O58" s="32">
         <v>25</v>
@@ -7377,13 +7379,13 @@
         <v>65.5</v>
       </c>
       <c r="Q58" s="14">
-        <v>13.281249999999998</v>
+        <v>14.0625</v>
       </c>
       <c r="R58" s="16">
-        <v>41.411764705882355</v>
+        <v>39.111111111111107</v>
       </c>
       <c r="S58" s="15">
-        <v>-12.647058823529413</v>
+        <v>-10.555555555555557</v>
       </c>
       <c r="T58" s="18">
         <v>100</v>
@@ -7392,13 +7394,13 @@
         <v>262</v>
       </c>
       <c r="V58" s="14">
-        <v>18.279569892473116</v>
+        <v>19.35483870967742</v>
       </c>
       <c r="W58" s="16">
-        <v>120.35294117647059</v>
+        <v>113.66666666666667</v>
       </c>
       <c r="X58" s="15">
-        <v>12.470588235294116</v>
+        <v>17.333333333333329</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7407,19 +7409,19 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>26.444444444444446</v>
+        <v>28</v>
       </c>
       <c r="AB58" s="16">
-        <v>34.941176470588232</v>
+        <v>33</v>
       </c>
       <c r="AC58" s="15">
-        <v>7.058823529411768</v>
+        <v>9</v>
       </c>
       <c r="AD58" s="19">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="AE58" s="20">
-        <v>841.02</v>
+        <v>809.58</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7457,34 +7459,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="F59" s="14">
-        <v>476.84000000000003</v>
+        <v>419.20000000000005</v>
       </c>
       <c r="G59" s="14">
-        <v>5.6875</v>
+        <v>4.816053511705686</v>
       </c>
       <c r="H59" s="30">
-        <v>704</v>
+        <v>730.88888888888891</v>
       </c>
       <c r="I59" s="15">
-        <v>-138</v>
+        <v>-172.22222222222223</v>
       </c>
       <c r="J59" s="32">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K59" s="13">
-        <v>136.24</v>
+        <v>104.80000000000001</v>
       </c>
       <c r="L59" s="14">
-        <v>4.5803108808290149</v>
+        <v>3.4285714285714293</v>
       </c>
       <c r="M59" s="30">
-        <v>249.76470588235296</v>
+        <v>256.66666666666663</v>
       </c>
       <c r="N59" s="15">
-        <v>-61.529411764705884</v>
+        <v>-76.666666666666643</v>
       </c>
       <c r="O59" s="32">
         <v>38</v>
@@ -7493,28 +7495,28 @@
         <v>99.56</v>
       </c>
       <c r="Q59" s="14">
-        <v>12.666666666666666</v>
+        <v>13.411764705882351</v>
       </c>
       <c r="R59" s="16">
-        <v>66</v>
+        <v>62.333333333333336</v>
       </c>
       <c r="S59" s="15">
-        <v>-22</v>
+        <v>-18.666666666666671</v>
       </c>
       <c r="T59" s="18">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U59" s="17">
-        <v>290.82</v>
+        <v>298.68</v>
       </c>
       <c r="V59" s="14">
-        <v>18.5</v>
+        <v>20.117647058823529</v>
       </c>
       <c r="W59" s="16">
-        <v>132</v>
+        <v>124.66666666666667</v>
       </c>
       <c r="X59" s="15">
-        <v>15</v>
+        <v>23.333333333333329</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7523,19 +7525,19 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>60.06666666666667</v>
+        <v>63.599999999999987</v>
       </c>
       <c r="AB59" s="16">
-        <v>19.411764705882351</v>
+        <v>18.333333333333336</v>
       </c>
       <c r="AC59" s="15">
-        <v>33.588235294117652</v>
+        <v>34.666666666666664</v>
       </c>
       <c r="AD59" s="19">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="AE59" s="20">
-        <v>1142.32</v>
+        <v>1061.1000000000001</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7609,10 +7611,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7642,17 +7644,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>161502.74999999997</v>
+        <v>146949.73000000007</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>36.554147823588373</v>
+        <v>31.805473083743799</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7690,11 +7692,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>156088.52999999994</v>
+        <v>197489.34999999989</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>35.32870616250564</v>
+        <v>42.744156152931012</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7732,11 +7734,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>37498.729999999996</v>
+        <v>35265.999999999978</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>8.4873732466897813</v>
+        <v>7.6328946897099259</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7774,11 +7776,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>76639.150000000009</v>
+        <v>63284.919999999984</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>17.346322698369928</v>
+        <v>13.697247485020068</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7816,11 +7818,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>9889.4900000000034</v>
+        <v>18837.350000000006</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.2383636152319335</v>
+        <v>4.0771141831567919</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7852,19 +7854,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>441817.85000000009</v>
-      </c>
-      <c r="E67" s="66">
+        <v>462026.55</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7964,17 +7966,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>119095</v>
+        <v>107928</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>36.085238669486543</v>
+        <v>32.28989340218461</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8011,11 +8013,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>124088</v>
+        <v>143604</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>37.598094764845257</v>
+        <v>42.963437218583863</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8053,11 +8055,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>27021</v>
+        <v>25199</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>8.1872390452008563</v>
+        <v>7.539035503684401</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8095,11 +8097,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>53423</v>
+        <v>44355</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>16.186923929971702</v>
+        <v>13.270126583035898</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8137,11 +8139,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>6411</v>
+        <v>13161</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>1.9425035904956398</v>
+        <v>3.9375072925112269</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8173,19 +8175,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>330038</v>
-      </c>
-      <c r="E75" s="66">
+        <v>334247</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8732,6 +8734,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8740,17 +8753,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE3822F-1448-4319-BD51-EE92E462B763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42BC924-C54E-44B0-A129-7C465A19A683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1185,6 +1185,7 @@
       <sheetName val="INVENTARIO NACIONAL 23-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1328,6 +1329,7 @@
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1655,242 +1657,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2255,85 +2257,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>1191</v>
+        <v>3063</v>
       </c>
       <c r="F13" s="14">
-        <v>1619.7600000000002</v>
+        <v>4165.68</v>
       </c>
       <c r="G13" s="14">
-        <v>1.5125943695759545</v>
+        <v>3.942084942084942</v>
       </c>
       <c r="H13" s="30">
-        <v>17322.555555555555</v>
+        <v>17094</v>
       </c>
       <c r="I13" s="15">
-        <v>-6682.8888888888878</v>
+        <v>-4707</v>
       </c>
       <c r="J13" s="16">
-        <v>8051</v>
+        <v>6993</v>
       </c>
       <c r="K13" s="13">
-        <v>10949.36</v>
+        <v>9510.4800000000014</v>
       </c>
       <c r="L13" s="14">
-        <v>31.997792007065577</v>
+        <v>29.03562062937063</v>
       </c>
       <c r="M13" s="30">
-        <v>5535.4444444444443</v>
+        <v>5298.5263157894733</v>
       </c>
       <c r="N13" s="15">
-        <v>5534.8888888888887</v>
+        <v>4584.5789473684217</v>
       </c>
       <c r="O13" s="16">
-        <v>969</v>
+        <v>922</v>
       </c>
       <c r="P13" s="17">
-        <v>1317.8400000000001</v>
+        <v>1253.92</v>
       </c>
       <c r="Q13" s="14">
-        <v>20.813842482100242</v>
+        <v>20.182027649769587</v>
       </c>
       <c r="R13" s="16">
-        <v>1024.2222222222222</v>
+        <v>1005.0526315789473</v>
       </c>
       <c r="S13" s="15">
-        <v>37.888888888889028</v>
+        <v>8.3157894736842763</v>
       </c>
       <c r="T13" s="18">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="U13" s="17">
-        <v>873.12000000000012</v>
+        <v>848.6400000000001</v>
       </c>
       <c r="V13" s="14">
-        <v>12.940649496080626</v>
+        <v>12.943231441048034</v>
       </c>
       <c r="W13" s="16">
-        <v>1091.4444444444446</v>
+        <v>1060.6315789473683</v>
       </c>
       <c r="X13" s="15">
-        <v>-151.77777777777783</v>
+        <v>-147.36842105263156</v>
       </c>
       <c r="Y13" s="18">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="17">
-        <v>870.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="14">
-        <v>20.13986013986014</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="16">
-        <v>699.11111111111109</v>
+        <v>662.31578947368416</v>
       </c>
       <c r="AC13" s="15">
-        <v>-59.111111111111086</v>
+        <v>-662.31578947368416</v>
       </c>
       <c r="AD13" s="19">
-        <v>11493</v>
+        <v>11602</v>
       </c>
       <c r="AE13" s="20">
-        <v>15630.480000000001</v>
+        <v>15778.720000000001</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2378,25 +2380,25 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>569.55555555555554</v>
+        <v>539.57894736842104</v>
       </c>
       <c r="I14" s="15">
-        <v>-258.88888888888891</v>
+        <v>-245.26315789473685</v>
       </c>
       <c r="J14" s="16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K14" s="13">
-        <v>0</v>
+        <v>46.11</v>
       </c>
       <c r="L14" s="14">
-        <v>0</v>
+        <v>2.2128514056224899</v>
       </c>
       <c r="M14" s="30">
-        <v>304.33333333333337</v>
+        <v>288.31578947368422</v>
       </c>
       <c r="N14" s="15">
-        <v>-138.33333333333337</v>
+        <v>-102.05263157894737</v>
       </c>
       <c r="O14" s="16">
         <v>88</v>
@@ -2405,13 +2407,13 @@
         <v>139.92000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>15.230769230769232</v>
+        <v>16.076923076923077</v>
       </c>
       <c r="R14" s="16">
-        <v>127.11111111111111</v>
+        <v>120.42105263157895</v>
       </c>
       <c r="S14" s="15">
-        <v>-27.555555555555557</v>
+        <v>-21.473684210526315</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2420,13 +2422,13 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>4.666666666666667</v>
+        <v>4.9259259259259256</v>
       </c>
       <c r="W14" s="16">
-        <v>33</v>
+        <v>31.263157894736842</v>
       </c>
       <c r="X14" s="15">
-        <v>-17</v>
+        <v>-15.736842105263158</v>
       </c>
       <c r="Y14" s="18">
         <v>22</v>
@@ -2435,19 +2437,19 @@
         <v>34.980000000000004</v>
       </c>
       <c r="AA14" s="14">
-        <v>5.2799999999999994</v>
+        <v>5.5733333333333333</v>
       </c>
       <c r="AB14" s="16">
-        <v>91.666666666666671</v>
+        <v>86.84210526315789</v>
       </c>
       <c r="AC14" s="15">
-        <v>-69.666666666666671</v>
+        <v>-64.84210526315789</v>
       </c>
       <c r="AD14" s="19">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="AE14" s="20">
-        <v>186.03</v>
+        <v>232.14000000000001</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2483,85 +2485,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>1418</v>
+        <v>2346</v>
       </c>
       <c r="F15" s="14">
-        <v>2878.5399999999995</v>
+        <v>4762.3799999999992</v>
       </c>
       <c r="G15" s="14">
-        <v>4.2118811881188121</v>
+        <v>6.8989320538616319</v>
       </c>
       <c r="H15" s="30">
-        <v>7406.666666666667</v>
+        <v>7481.1578947368416</v>
       </c>
       <c r="I15" s="15">
-        <v>-1948.666666666667</v>
+        <v>-1054.5263157894733</v>
       </c>
       <c r="J15" s="16">
-        <v>2656</v>
+        <v>2243</v>
       </c>
       <c r="K15" s="13">
-        <v>5391.6799999999994</v>
+        <v>4553.29</v>
       </c>
       <c r="L15" s="14">
-        <v>23.21903836813987</v>
+        <v>20.488942307692309</v>
       </c>
       <c r="M15" s="30">
-        <v>2516.5555555555557</v>
+        <v>2408.4210526315787</v>
       </c>
       <c r="N15" s="15">
-        <v>1512.1111111111111</v>
+        <v>1148.2631578947371</v>
       </c>
       <c r="O15" s="16">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="P15" s="17">
-        <v>444.56999999999994</v>
+        <v>428.33</v>
       </c>
       <c r="Q15" s="14">
-        <v>18.861244019138756</v>
+        <v>18.821596244131456</v>
       </c>
       <c r="R15" s="16">
-        <v>255.44444444444443</v>
+        <v>246.63157894736844</v>
       </c>
       <c r="S15" s="15">
-        <v>-13.222222222222229</v>
+        <v>-13.21052631578948</v>
       </c>
       <c r="T15" s="18">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="U15" s="17">
-        <v>326.83</v>
+        <v>322.77</v>
       </c>
       <c r="V15" s="14">
-        <v>9.3786407766990276</v>
+        <v>9.2668711656441705</v>
       </c>
       <c r="W15" s="16">
-        <v>377.66666666666669</v>
+        <v>377.47368421052636</v>
       </c>
       <c r="X15" s="15">
-        <v>-113.66666666666669</v>
+        <v>-115.5263157894737</v>
       </c>
       <c r="Y15" s="18">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="Z15" s="17">
-        <v>448.62999999999994</v>
+        <v>192.85</v>
       </c>
       <c r="AA15" s="14">
-        <v>23.538461538461537</v>
+        <v>10.314285714285713</v>
       </c>
       <c r="AB15" s="16">
-        <v>206.55555555555557</v>
+        <v>202.63157894736844</v>
       </c>
       <c r="AC15" s="15">
-        <v>14.444444444444429</v>
+        <v>-107.63157894736844</v>
       </c>
       <c r="AD15" s="19">
-        <v>4675</v>
+        <v>5054</v>
       </c>
       <c r="AE15" s="20">
-        <v>9490.2499999999982</v>
+        <v>10259.619999999999</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2596,34 +2598,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="F16" s="14">
-        <v>407.93</v>
+        <v>1169.6399999999999</v>
       </c>
       <c r="G16" s="14">
-        <v>1.5190440627333832</v>
+        <v>4.5465288035450522</v>
       </c>
       <c r="H16" s="30">
-        <v>1636.5555555555554</v>
+        <v>1567.7894736842104</v>
       </c>
       <c r="I16" s="15">
-        <v>-630.88888888888891</v>
+        <v>-388.63157894736833</v>
       </c>
       <c r="J16" s="16">
-        <v>524</v>
+        <v>338</v>
       </c>
       <c r="K16" s="13">
-        <v>1891.6399999999999</v>
+        <v>1220.18</v>
       </c>
       <c r="L16" s="14">
-        <v>19.170731707317078</v>
+        <v>12.895582329317268</v>
       </c>
       <c r="M16" s="30">
-        <v>601.33333333333326</v>
+        <v>576.63157894736844</v>
       </c>
       <c r="N16" s="15">
-        <v>250.66666666666674</v>
+        <v>75.89473684210526</v>
       </c>
       <c r="O16" s="16">
         <v>44</v>
@@ -2632,13 +2634,13 @@
         <v>158.84</v>
       </c>
       <c r="Q16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R16" s="16">
-        <v>53.777777777777786</v>
+        <v>50.94736842105263</v>
       </c>
       <c r="S16" s="15">
-        <v>-4.8888888888888928</v>
+        <v>-2.3157894736842124</v>
       </c>
       <c r="T16" s="18">
         <v>39</v>
@@ -2647,34 +2649,34 @@
         <v>140.79</v>
       </c>
       <c r="V16" s="14">
-        <v>33.428571428571423</v>
+        <v>35.285714285714285</v>
       </c>
       <c r="W16" s="16">
-        <v>25.666666666666668</v>
+        <v>24.315789473684212</v>
       </c>
       <c r="X16" s="15">
-        <v>20.333333333333332</v>
+        <v>21.315789473684209</v>
       </c>
       <c r="Y16" s="18">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="Z16" s="17">
-        <v>292.40999999999997</v>
+        <v>90.25</v>
       </c>
       <c r="AA16" s="14">
-        <v>25.578947368421058</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="AB16" s="16">
-        <v>69.666666666666657</v>
+        <v>66</v>
       </c>
       <c r="AC16" s="15">
-        <v>11.333333333333343</v>
+        <v>-41</v>
       </c>
       <c r="AD16" s="19">
-        <v>801</v>
+        <v>770</v>
       </c>
       <c r="AE16" s="20">
-        <v>2891.61</v>
+        <v>2779.7</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2709,85 +2711,85 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="F17" s="14">
-        <v>79.02</v>
+        <v>465.34</v>
       </c>
       <c r="G17" s="14">
-        <v>0.86631016042780751</v>
+        <v>5.3850267379679142</v>
       </c>
       <c r="H17" s="30">
-        <v>228.55555555555557</v>
+        <v>216.5263157894737</v>
       </c>
       <c r="I17" s="15">
-        <v>-94.888888888888886</v>
+        <v>-45.421052631578959</v>
       </c>
       <c r="J17" s="16">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="K17" s="13">
-        <v>1044.82</v>
+        <v>746.3</v>
       </c>
       <c r="L17" s="14">
-        <v>56.368421052631575</v>
+        <v>41.410256410256409</v>
       </c>
       <c r="M17" s="30">
-        <v>46.444444444444443</v>
+        <v>45.15789473684211</v>
       </c>
       <c r="N17" s="15">
-        <v>97.888888888888886</v>
+        <v>64.473684210526315</v>
       </c>
       <c r="O17" s="16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P17" s="17">
-        <v>122.91999999999999</v>
+        <v>105.35999999999999</v>
       </c>
       <c r="Q17" s="14">
-        <v>22.909090909090907</v>
+        <v>20.727272727272727</v>
       </c>
       <c r="R17" s="16">
-        <v>13.444444444444446</v>
+        <v>12.736842105263158</v>
       </c>
       <c r="S17" s="15">
-        <v>1.7777777777777768</v>
+        <v>0.4210526315789469</v>
       </c>
       <c r="T17" s="18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U17" s="17">
-        <v>149.26</v>
+        <v>140.47999999999999</v>
       </c>
       <c r="V17" s="14">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="W17" s="16">
         <v>2</v>
       </c>
       <c r="X17" s="15">
-        <v>15.545454545454545</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="Y17" s="18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="17">
-        <v>114.13999999999999</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="AA17" s="14">
-        <v>26</v>
+        <v>16.888888888888889</v>
       </c>
       <c r="AB17" s="16">
-        <v>11</v>
+        <v>10.421052631578947</v>
       </c>
       <c r="AC17" s="15">
-        <v>2</v>
+        <v>-2.4210526315789469</v>
       </c>
       <c r="AD17" s="19">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AE17" s="20">
-        <v>1510.1599999999999</v>
+        <v>1527.7199999999998</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2822,85 +2824,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>7062</v>
+        <v>6147</v>
       </c>
       <c r="F18" s="14">
-        <v>4449.0600000000004</v>
+        <v>3872.61</v>
       </c>
       <c r="G18" s="14">
-        <v>8.4586105935586922</v>
+        <v>7.4423628369336647</v>
       </c>
       <c r="H18" s="30">
-        <v>18367.555555555555</v>
+        <v>18170.842105263157</v>
       </c>
       <c r="I18" s="15">
-        <v>-1286.8888888888887</v>
+        <v>-2112.4736842105267</v>
       </c>
       <c r="J18" s="16">
-        <v>4220</v>
+        <v>8387</v>
       </c>
       <c r="K18" s="13">
-        <v>2658.6</v>
+        <v>5283.81</v>
       </c>
       <c r="L18" s="14">
-        <v>12.057142857142857</v>
+        <v>25.246039290240812</v>
       </c>
       <c r="M18" s="30">
-        <v>7700</v>
+        <v>7308.6315789473683</v>
       </c>
       <c r="N18" s="15">
-        <v>720</v>
+        <v>5064.894736842105</v>
       </c>
       <c r="O18" s="16">
-        <v>1081</v>
+        <v>1097</v>
       </c>
       <c r="P18" s="17">
-        <v>681.03</v>
+        <v>691.11</v>
       </c>
       <c r="Q18" s="14">
-        <v>18.513796384395814</v>
+        <v>19.12201834862385</v>
       </c>
       <c r="R18" s="16">
-        <v>1284.5555555555554</v>
+        <v>1262.1052631578948</v>
       </c>
       <c r="S18" s="15">
-        <v>-86.777777777777828</v>
+        <v>-50.368421052631675</v>
       </c>
       <c r="T18" s="18">
-        <v>1960</v>
+        <v>1848</v>
       </c>
       <c r="U18" s="17">
-        <v>1234.8</v>
+        <v>1164.24</v>
       </c>
       <c r="V18" s="14">
-        <v>11.922946941534303</v>
+        <v>11.333763718528083</v>
       </c>
       <c r="W18" s="16">
-        <v>3616.5555555555557</v>
+        <v>3587.1578947368421</v>
       </c>
       <c r="X18" s="15">
-        <v>-670.22222222222217</v>
+        <v>-760.84210526315792</v>
       </c>
       <c r="Y18" s="18">
-        <v>331</v>
+        <v>145</v>
       </c>
       <c r="Z18" s="17">
-        <v>208.53</v>
+        <v>91.35</v>
       </c>
       <c r="AA18" s="14">
-        <v>23.09302325581395</v>
+        <v>10.435606060606062</v>
       </c>
       <c r="AB18" s="16">
-        <v>315.33333333333337</v>
+        <v>305.68421052631578</v>
       </c>
       <c r="AC18" s="15">
-        <v>15.666666666666629</v>
+        <v>-160.68421052631578</v>
       </c>
       <c r="AD18" s="19">
-        <v>14654</v>
+        <v>17624</v>
       </c>
       <c r="AE18" s="20">
-        <v>9232.02</v>
+        <v>11103.12</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2935,34 +2937,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>369</v>
+        <v>313</v>
       </c>
       <c r="F19" s="14">
-        <v>232.47</v>
+        <v>197.19</v>
       </c>
       <c r="G19" s="14">
-        <v>5.6575809199318563</v>
+        <v>5.044105173876166</v>
       </c>
       <c r="H19" s="30">
-        <v>1434.8888888888891</v>
+        <v>1365.1578947368421</v>
       </c>
       <c r="I19" s="15">
-        <v>-283.22222222222229</v>
+        <v>-307.52631578947376</v>
       </c>
       <c r="J19" s="16">
-        <v>125</v>
+        <v>389</v>
       </c>
       <c r="K19" s="13">
-        <v>78.75</v>
+        <v>245.07</v>
       </c>
       <c r="L19" s="14">
-        <v>2.1510516252390057</v>
+        <v>7.0390476190476177</v>
       </c>
       <c r="M19" s="30">
-        <v>1278.4444444444446</v>
+        <v>1215.7894736842106</v>
       </c>
       <c r="N19" s="15">
-        <v>-456.11111111111109</v>
+        <v>-163.63157894736855</v>
       </c>
       <c r="O19" s="16">
         <v>126</v>
@@ -2971,49 +2973,49 @@
         <v>79.38</v>
       </c>
       <c r="Q19" s="14">
-        <v>24.65217391304348</v>
+        <v>26.021739130434781</v>
       </c>
       <c r="R19" s="16">
-        <v>112.44444444444443</v>
+        <v>106.52631578947368</v>
       </c>
       <c r="S19" s="15">
-        <v>23.777777777777786</v>
+        <v>29.15789473684211</v>
       </c>
       <c r="T19" s="18">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="U19" s="17">
-        <v>114.03</v>
+        <v>103.95</v>
       </c>
       <c r="V19" s="14">
-        <v>13.243902439024392</v>
+        <v>11.568265682656826</v>
       </c>
       <c r="W19" s="16">
-        <v>300.66666666666663</v>
+        <v>313.78947368421052</v>
       </c>
       <c r="X19" s="15">
-        <v>-37.666666666666629</v>
+        <v>-63.21052631578948</v>
       </c>
       <c r="Y19" s="18">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="Z19" s="17">
-        <v>148.68</v>
+        <v>73.08</v>
       </c>
       <c r="AA19" s="14">
-        <v>22.240837696335081</v>
+        <v>11.539267015706807</v>
       </c>
       <c r="AB19" s="16">
-        <v>233.44444444444443</v>
+        <v>221.15789473684211</v>
       </c>
       <c r="AC19" s="15">
-        <v>2.5555555555555713</v>
+        <v>-105.15789473684211</v>
       </c>
       <c r="AD19" s="19">
-        <v>1037</v>
+        <v>1109</v>
       </c>
       <c r="AE19" s="20">
-        <v>653.31000000000006</v>
+        <v>698.67</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3048,34 +3050,34 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>896</v>
+        <v>1428</v>
       </c>
       <c r="F20" s="14">
-        <v>564.48</v>
+        <v>899.64</v>
       </c>
       <c r="G20" s="14">
-        <v>6.656211308295501</v>
+        <v>11.137931034482758</v>
       </c>
       <c r="H20" s="30">
-        <v>2961.4444444444443</v>
+        <v>2820.6315789473683</v>
       </c>
       <c r="I20" s="15">
-        <v>-450.11111111111109</v>
+        <v>145.8947368421052</v>
       </c>
       <c r="J20" s="16">
-        <v>2062</v>
+        <v>3765</v>
       </c>
       <c r="K20" s="13">
-        <v>1299.06</v>
+        <v>2371.9499999999998</v>
       </c>
       <c r="L20" s="14">
-        <v>15.568791946308723</v>
+        <v>29.993710691823896</v>
       </c>
       <c r="M20" s="30">
-        <v>2913.7777777777783</v>
+        <v>2761.5789473684213</v>
       </c>
       <c r="N20" s="15">
-        <v>737.55555555555543</v>
+        <v>2509.7368421052629</v>
       </c>
       <c r="O20" s="16">
         <v>226</v>
@@ -3084,49 +3086,49 @@
         <v>142.38</v>
       </c>
       <c r="Q20" s="14">
-        <v>23.379310344827587</v>
+        <v>24.678160919540232</v>
       </c>
       <c r="R20" s="16">
-        <v>212.66666666666666</v>
+        <v>201.4736842105263</v>
       </c>
       <c r="S20" s="15">
-        <v>32.666666666666686</v>
+        <v>42.842105263157919</v>
       </c>
       <c r="T20" s="18">
-        <v>441</v>
+        <v>375</v>
       </c>
       <c r="U20" s="17">
-        <v>277.83</v>
+        <v>236.25</v>
       </c>
       <c r="V20" s="14">
-        <v>14.7</v>
+        <v>11.604234527687296</v>
       </c>
       <c r="W20" s="16">
-        <v>660</v>
+        <v>710.94736842105272</v>
       </c>
       <c r="X20" s="15">
-        <v>-39</v>
+        <v>-142.0526315789474</v>
       </c>
       <c r="Y20" s="18">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="Z20" s="17">
-        <v>183.33</v>
+        <v>103.95</v>
       </c>
       <c r="AA20" s="14">
-        <v>21.206477732793523</v>
+        <v>12.391304347826086</v>
       </c>
       <c r="AB20" s="16">
-        <v>301.88888888888886</v>
+        <v>292.94736842105266</v>
       </c>
       <c r="AC20" s="15">
-        <v>-10.888888888888857</v>
+        <v>-127.94736842105266</v>
       </c>
       <c r="AD20" s="19">
-        <v>3916</v>
+        <v>5959</v>
       </c>
       <c r="AE20" s="20">
-        <v>2467.08</v>
+        <v>3754.17</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3161,85 +3163,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2195</v>
+        <v>1924</v>
       </c>
       <c r="F21" s="14">
-        <v>2392.5500000000002</v>
+        <v>2097.1600000000003</v>
       </c>
       <c r="G21" s="14">
-        <v>7.0793764558322883</v>
+        <v>6.3377253814147023</v>
       </c>
       <c r="H21" s="30">
-        <v>6821.2222222222217</v>
+        <v>6678.7368421052633</v>
       </c>
       <c r="I21" s="15">
-        <v>-905.55555555555566</v>
+        <v>-1111.7894736842104</v>
       </c>
       <c r="J21" s="16">
-        <v>2767</v>
+        <v>3125</v>
       </c>
       <c r="K21" s="13">
-        <v>3016.03</v>
+        <v>3406.2500000000005</v>
       </c>
       <c r="L21" s="14">
-        <v>7.9842898364860533</v>
+        <v>9.4051956280690643</v>
       </c>
       <c r="M21" s="30">
-        <v>7624.2222222222217</v>
+        <v>7309.78947368421</v>
       </c>
       <c r="N21" s="15">
-        <v>-698.55555555555566</v>
+        <v>-197.63157894736833</v>
       </c>
       <c r="O21" s="16">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="P21" s="17">
-        <v>588.6</v>
+        <v>547.18000000000006</v>
       </c>
       <c r="Q21" s="14">
-        <v>20.334728033472803</v>
+        <v>17.373406193078324</v>
       </c>
       <c r="R21" s="16">
-        <v>584.22222222222229</v>
+        <v>635.68421052631584</v>
       </c>
       <c r="S21" s="15">
-        <v>8.8888888888889142</v>
+        <v>-75.894736842105317</v>
       </c>
       <c r="T21" s="18">
-        <v>995</v>
+        <v>900</v>
       </c>
       <c r="U21" s="17">
-        <v>1084.5500000000002</v>
+        <v>981.00000000000011</v>
       </c>
       <c r="V21" s="14">
-        <v>11.971925133689838</v>
+        <v>10.568603213844252</v>
       </c>
       <c r="W21" s="16">
-        <v>1828.4444444444446</v>
+        <v>1873.4736842105265</v>
       </c>
       <c r="X21" s="15">
-        <v>-334.77777777777783</v>
+        <v>-462.52631578947376</v>
       </c>
       <c r="Y21" s="18">
-        <v>400</v>
+        <v>178</v>
       </c>
       <c r="Z21" s="17">
-        <v>436.00000000000006</v>
+        <v>194.02</v>
       </c>
       <c r="AA21" s="14">
-        <v>21.176470588235293</v>
+        <v>9.8028985507246365</v>
       </c>
       <c r="AB21" s="16">
-        <v>415.55555555555554</v>
+        <v>399.47368421052636</v>
       </c>
       <c r="AC21" s="15">
-        <v>-15.555555555555543</v>
+        <v>-221.47368421052636</v>
       </c>
       <c r="AD21" s="19">
-        <v>6897</v>
+        <v>6629</v>
       </c>
       <c r="AE21" s="20">
-        <v>7517.7300000000005</v>
+        <v>7225.6100000000006</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3274,34 +3276,34 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1212</v>
+        <v>1730</v>
       </c>
       <c r="F22" s="14">
-        <v>1321.0800000000002</v>
+        <v>1885.7</v>
       </c>
       <c r="G22" s="14">
-        <v>6.5572587917042373</v>
+        <v>9.4698934024776733</v>
       </c>
       <c r="H22" s="30">
-        <v>4066.3333333333335</v>
+        <v>4019.0526315789471</v>
       </c>
       <c r="I22" s="15">
-        <v>-636.33333333333348</v>
+        <v>-96.842105263157919</v>
       </c>
       <c r="J22" s="16">
-        <v>3189</v>
+        <v>2811</v>
       </c>
       <c r="K22" s="13">
-        <v>3476.01</v>
+        <v>3063.9900000000002</v>
       </c>
       <c r="L22" s="14">
-        <v>20.603732950466618</v>
+        <v>19.081457663451232</v>
       </c>
       <c r="M22" s="30">
-        <v>3405.1111111111109</v>
+        <v>3240.9473684210529</v>
       </c>
       <c r="N22" s="15">
-        <v>1641.2222222222222</v>
+        <v>1337.8421052631579</v>
       </c>
       <c r="O22" s="16">
         <v>122</v>
@@ -3310,49 +3312,49 @@
         <v>132.98000000000002</v>
       </c>
       <c r="Q22" s="14">
-        <v>15.144827586206898</v>
+        <v>15.986206896551725</v>
       </c>
       <c r="R22" s="16">
-        <v>177.22222222222223</v>
+        <v>167.89473684210526</v>
       </c>
       <c r="S22" s="15">
-        <v>-39.111111111111114</v>
+        <v>-30.631578947368439</v>
       </c>
       <c r="T22" s="18">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="U22" s="17">
-        <v>376.05</v>
+        <v>355.34000000000003</v>
       </c>
       <c r="V22" s="14">
-        <v>13.708609271523176</v>
+        <v>12.985324947589099</v>
       </c>
       <c r="W22" s="16">
-        <v>553.66666666666674</v>
+        <v>552.31578947368416</v>
       </c>
       <c r="X22" s="15">
-        <v>-57.666666666666742</v>
+        <v>-75.68421052631578</v>
       </c>
       <c r="Y22" s="18">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z22" s="17">
-        <v>54.500000000000007</v>
+        <v>49.050000000000004</v>
       </c>
       <c r="AA22" s="14">
-        <v>6.0402684563758386</v>
+        <v>5.5519480519480524</v>
       </c>
       <c r="AB22" s="16">
-        <v>182.11111111111114</v>
+        <v>178.31578947368419</v>
       </c>
       <c r="AC22" s="15">
-        <v>-132.11111111111114</v>
+        <v>-133.31578947368419</v>
       </c>
       <c r="AD22" s="19">
-        <v>4918</v>
+        <v>5034</v>
       </c>
       <c r="AE22" s="20">
-        <v>5360.6200000000008</v>
+        <v>5487.06</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3387,85 +3389,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>20177</v>
+        <v>18628</v>
       </c>
       <c r="F23" s="14">
-        <v>23405.32</v>
+        <v>21608.48</v>
       </c>
       <c r="G23" s="14">
-        <v>12.1931780030887</v>
+        <v>11.395840041213214</v>
       </c>
       <c r="H23" s="30">
-        <v>36405.111111111109</v>
+        <v>35961.894736842107</v>
       </c>
       <c r="I23" s="15">
-        <v>-4644.6666666666642</v>
+        <v>-5891.4736842105267</v>
       </c>
       <c r="J23" s="16">
-        <v>13824</v>
+        <v>31144</v>
       </c>
       <c r="K23" s="13">
-        <v>16035.839999999998</v>
+        <v>36127.040000000001</v>
       </c>
       <c r="L23" s="14">
-        <v>14.059099384145997</v>
+        <v>33.13933691756273</v>
       </c>
       <c r="M23" s="30">
-        <v>21632.111111111113</v>
+        <v>20675.36842105263</v>
       </c>
       <c r="N23" s="15">
-        <v>3991.2222222222226</v>
+        <v>21746.105263157897</v>
       </c>
       <c r="O23" s="16">
-        <v>2792</v>
+        <v>1522</v>
       </c>
       <c r="P23" s="17">
-        <v>3238.72</v>
+        <v>1765.52</v>
       </c>
       <c r="Q23" s="14">
-        <v>18.599555884529977</v>
+        <v>10.090020935101187</v>
       </c>
       <c r="R23" s="16">
-        <v>3302.4444444444443</v>
+        <v>3318.5263157894738</v>
       </c>
       <c r="S23" s="15">
-        <v>-210.22222222222217</v>
+        <v>-1494.8421052631579</v>
       </c>
       <c r="T23" s="18">
-        <v>6963</v>
+        <v>6681</v>
       </c>
       <c r="U23" s="17">
-        <v>8077.079999999999</v>
+        <v>7749.9599999999991</v>
       </c>
       <c r="V23" s="14">
-        <v>12.349394028968371</v>
+        <v>11.941580432737535</v>
       </c>
       <c r="W23" s="16">
-        <v>12404.333333333334</v>
+        <v>12308.42105263158</v>
       </c>
       <c r="X23" s="15">
-        <v>-2058.3333333333339</v>
+        <v>-2270.5789473684217</v>
       </c>
       <c r="Y23" s="18">
-        <v>1243</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="17">
-        <v>1441.8799999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AA23" s="14">
-        <v>24.559824368825463</v>
+        <v>2.0856201975850714E-2</v>
       </c>
       <c r="AB23" s="16">
-        <v>1113.4444444444446</v>
+        <v>1054.8421052631579</v>
       </c>
       <c r="AC23" s="15">
-        <v>129.55555555555543</v>
+        <v>-1053.8421052631579</v>
       </c>
       <c r="AD23" s="19">
-        <v>44999</v>
+        <v>57976</v>
       </c>
       <c r="AE23" s="20">
-        <v>52198.84</v>
+        <v>67252.159999999989</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3500,85 +3502,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>7961</v>
+        <v>9962</v>
       </c>
       <c r="F24" s="14">
-        <v>9234.76</v>
+        <v>11555.92</v>
       </c>
       <c r="G24" s="14">
-        <v>7.2475217479263616</v>
+        <v>8.9965302533390368</v>
       </c>
       <c r="H24" s="30">
-        <v>24165.777777777774</v>
+        <v>24360.947368421053</v>
       </c>
       <c r="I24" s="15">
-        <v>-3023.4444444444434</v>
+        <v>-1111.1578947368416</v>
       </c>
       <c r="J24" s="16">
-        <v>13188</v>
+        <v>13917</v>
       </c>
       <c r="K24" s="13">
-        <v>15298.079999999998</v>
+        <v>16143.72</v>
       </c>
       <c r="L24" s="14">
-        <v>21.925187032418954</v>
+        <v>24.196833821376281</v>
       </c>
       <c r="M24" s="30">
-        <v>13233</v>
+        <v>12653.473684210527</v>
       </c>
       <c r="N24" s="15">
-        <v>7173</v>
+        <v>8165.4210526315792</v>
       </c>
       <c r="O24" s="16">
-        <v>1574</v>
+        <v>1871</v>
       </c>
       <c r="P24" s="17">
-        <v>1825.84</v>
+        <v>2170.3599999999997</v>
       </c>
       <c r="Q24" s="14">
-        <v>17.763009404388715</v>
+        <v>20.898883009994123</v>
       </c>
       <c r="R24" s="16">
-        <v>1949.4444444444446</v>
+        <v>1969.578947368421</v>
       </c>
       <c r="S24" s="15">
-        <v>-198.22222222222217</v>
+        <v>80.473684210526244</v>
       </c>
       <c r="T24" s="18">
-        <v>3972</v>
+        <v>3816</v>
       </c>
       <c r="U24" s="17">
-        <v>4607.5199999999995</v>
+        <v>4426.5599999999995</v>
       </c>
       <c r="V24" s="14">
-        <v>13.237548602110721</v>
+        <v>12.791813690896259</v>
       </c>
       <c r="W24" s="16">
-        <v>6601.2222222222217</v>
+        <v>6562.9473684210525</v>
       </c>
       <c r="X24" s="15">
-        <v>-828.88888888888869</v>
+        <v>-957.05263157894751</v>
       </c>
       <c r="Y24" s="18">
-        <v>744</v>
+        <v>202</v>
       </c>
       <c r="Z24" s="17">
-        <v>863.04</v>
+        <v>234.32</v>
       </c>
       <c r="AA24" s="14">
-        <v>18.446280991735534</v>
+        <v>5.2719780219780219</v>
       </c>
       <c r="AB24" s="16">
-        <v>887.33333333333337</v>
+        <v>842.94736842105272</v>
       </c>
       <c r="AC24" s="15">
-        <v>-143.33333333333337</v>
+        <v>-640.94736842105272</v>
       </c>
       <c r="AD24" s="19">
-        <v>27439</v>
+        <v>29768</v>
       </c>
       <c r="AE24" s="20">
-        <v>31829.239999999998</v>
+        <v>34530.879999999997</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3613,85 +3615,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>8472</v>
+        <v>7533</v>
       </c>
       <c r="F25" s="14">
-        <v>9827.5199999999986</v>
+        <v>8738.2799999999988</v>
       </c>
       <c r="G25" s="14">
-        <v>7.9338223817699394</v>
+        <v>7.1172053704624565</v>
       </c>
       <c r="H25" s="30">
-        <v>23492.333333333332</v>
+        <v>23285.263157894737</v>
       </c>
       <c r="I25" s="15">
-        <v>-2206.3333333333321</v>
+        <v>-3051.21052631579</v>
       </c>
       <c r="J25" s="16">
-        <v>19047</v>
+        <v>23666</v>
       </c>
       <c r="K25" s="13">
-        <v>22094.519999999997</v>
+        <v>27452.559999999998</v>
       </c>
       <c r="L25" s="14">
-        <v>29.828258221680876</v>
+        <v>38.880587980977083</v>
       </c>
       <c r="M25" s="30">
-        <v>14048.222222222223</v>
+        <v>13391.052631578948</v>
       </c>
       <c r="N25" s="15">
-        <v>12661.444444444445</v>
+        <v>17579.15789473684</v>
       </c>
       <c r="O25" s="16">
-        <v>1967</v>
+        <v>1469</v>
       </c>
       <c r="P25" s="17">
-        <v>2281.7199999999998</v>
+        <v>1704.04</v>
       </c>
       <c r="Q25" s="14">
-        <v>18.421436004162331</v>
+        <v>13.431665062560155</v>
       </c>
       <c r="R25" s="16">
-        <v>2349.1111111111109</v>
+        <v>2406.1052631578946</v>
       </c>
       <c r="S25" s="15">
-        <v>-168.55555555555566</v>
+        <v>-718.36842105263167</v>
       </c>
       <c r="T25" s="18">
-        <v>4030</v>
+        <v>3866</v>
       </c>
       <c r="U25" s="17">
-        <v>4674.7999999999993</v>
+        <v>4484.5599999999995</v>
       </c>
       <c r="V25" s="14">
-        <v>13.280849505675576</v>
+        <v>12.785726718885989</v>
       </c>
       <c r="W25" s="16">
-        <v>6675.7777777777783</v>
+        <v>6652.1052631578941</v>
       </c>
       <c r="X25" s="15">
-        <v>-825.11111111111131</v>
+        <v>-971.89473684210498</v>
       </c>
       <c r="Y25" s="18">
-        <v>538</v>
+        <v>427</v>
       </c>
       <c r="Z25" s="17">
-        <v>624.07999999999993</v>
+        <v>495.32</v>
       </c>
       <c r="AA25" s="14">
-        <v>18.445714285714281</v>
+        <v>15.365530303030305</v>
       </c>
       <c r="AB25" s="16">
-        <v>641.66666666666674</v>
+        <v>611.36842105263156</v>
       </c>
       <c r="AC25" s="15">
-        <v>-103.66666666666674</v>
+        <v>-184.36842105263156</v>
       </c>
       <c r="AD25" s="19">
-        <v>34054</v>
+        <v>36961</v>
       </c>
       <c r="AE25" s="20">
-        <v>39502.639999999999</v>
+        <v>42874.759999999995</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3726,85 +3728,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>17010</v>
+        <v>15874</v>
       </c>
       <c r="F26" s="14">
-        <v>19731.599999999999</v>
+        <v>18413.84</v>
       </c>
       <c r="G26" s="14">
-        <v>12.254552731638983</v>
+        <v>11.538102524866105</v>
       </c>
       <c r="H26" s="30">
-        <v>30537.222222222226</v>
+        <v>30267.368421052633</v>
       </c>
       <c r="I26" s="15">
-        <v>-3810.8333333333358</v>
+        <v>-4762.8421052631602</v>
       </c>
       <c r="J26" s="16">
-        <v>12463</v>
+        <v>16709</v>
       </c>
       <c r="K26" s="13">
-        <v>14457.079999999998</v>
+        <v>19382.439999999999</v>
       </c>
       <c r="L26" s="14">
-        <v>16.598890122086566</v>
+        <v>23.307466412157694</v>
       </c>
       <c r="M26" s="30">
-        <v>16518.333333333336</v>
+        <v>15771.684210526317</v>
       </c>
       <c r="N26" s="15">
-        <v>4954.6666666666652</v>
+        <v>9540.0526315789466</v>
       </c>
       <c r="O26" s="16">
-        <v>1531</v>
+        <v>0</v>
       </c>
       <c r="P26" s="17">
-        <v>1775.9599999999998</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="14">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R26" s="16">
-        <v>1871.2222222222222</v>
+        <v>1896.6315789473686</v>
       </c>
       <c r="S26" s="15">
-        <v>-170.11111111111109</v>
+        <v>-1724.2105263157896</v>
       </c>
       <c r="T26" s="18">
-        <v>4710</v>
+        <v>4466</v>
       </c>
       <c r="U26" s="17">
-        <v>5463.5999999999995</v>
+        <v>5180.5599999999995</v>
       </c>
       <c r="V26" s="14">
-        <v>12.297650130548304</v>
+        <v>11.710460943969085</v>
       </c>
       <c r="W26" s="16">
-        <v>8426</v>
+        <v>8390.105263157895</v>
       </c>
       <c r="X26" s="15">
-        <v>-1418</v>
+        <v>-1635.8947368421059</v>
       </c>
       <c r="Y26" s="18">
-        <v>909</v>
+        <v>312</v>
       </c>
       <c r="Z26" s="17">
-        <v>1054.4399999999998</v>
+        <v>361.91999999999996</v>
       </c>
       <c r="AA26" s="14">
-        <v>20.555276381909547</v>
+        <v>7.4192740926157699</v>
       </c>
       <c r="AB26" s="16">
-        <v>972.88888888888891</v>
+        <v>925.15789473684208</v>
       </c>
       <c r="AC26" s="15">
-        <v>-63.888888888888914</v>
+        <v>-613.15789473684208</v>
       </c>
       <c r="AD26" s="19">
-        <v>36623</v>
+        <v>37361</v>
       </c>
       <c r="AE26" s="20">
-        <v>42482.68</v>
+        <v>43338.759999999995</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3839,85 +3841,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>2389</v>
+        <v>3366</v>
       </c>
       <c r="F27" s="14">
-        <v>2771.24</v>
+        <v>3904.56</v>
       </c>
       <c r="G27" s="14">
-        <v>6.6330402591392872</v>
+        <v>9.6636446056210339</v>
       </c>
       <c r="H27" s="30">
-        <v>7923.666666666667</v>
+        <v>7662.9473684210525</v>
       </c>
       <c r="I27" s="15">
-        <v>-1212.666666666667</v>
+        <v>-117.15789473684208</v>
       </c>
       <c r="J27" s="16">
-        <v>4486</v>
+        <v>4761</v>
       </c>
       <c r="K27" s="13">
-        <v>5203.7599999999993</v>
+        <v>5522.7599999999993</v>
       </c>
       <c r="L27" s="14">
-        <v>22.0382096069869</v>
+        <v>24.468217473627263</v>
       </c>
       <c r="M27" s="30">
-        <v>4478.2222222222217</v>
+        <v>4280.7368421052633</v>
       </c>
       <c r="N27" s="15">
-        <v>2450.4444444444443</v>
+        <v>2815.2105263157891</v>
       </c>
       <c r="O27" s="16">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="P27" s="17">
-        <v>696</v>
+        <v>701.8</v>
       </c>
       <c r="Q27" s="14">
-        <v>20.224719101123593</v>
+        <v>21.287037037037035</v>
       </c>
       <c r="R27" s="16">
-        <v>652.66666666666674</v>
+        <v>625.26315789473688</v>
       </c>
       <c r="S27" s="15">
-        <v>6.6666666666665151</v>
+        <v>36.578947368421041</v>
       </c>
       <c r="T27" s="18">
-        <v>1667</v>
+        <v>1565</v>
       </c>
       <c r="U27" s="17">
-        <v>1933.7199999999998</v>
+        <v>1815.3999999999999</v>
       </c>
       <c r="V27" s="14">
-        <v>13.814917127071821</v>
+        <v>12.783748925193466</v>
       </c>
       <c r="W27" s="16">
-        <v>2654.666666666667</v>
+        <v>2693.2631578947367</v>
       </c>
       <c r="X27" s="15">
-        <v>-263.66666666666697</v>
+        <v>-393.73684210526312</v>
       </c>
       <c r="Y27" s="18">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Z27" s="17">
-        <v>407.15999999999997</v>
+        <v>404.84</v>
       </c>
       <c r="AA27" s="14">
-        <v>26.771186440677962</v>
+        <v>28.097457627118644</v>
       </c>
       <c r="AB27" s="16">
-        <v>288.44444444444446</v>
+        <v>273.26315789473682</v>
       </c>
       <c r="AC27" s="15">
-        <v>62.555555555555543</v>
+        <v>75.736842105263179</v>
       </c>
       <c r="AD27" s="19">
-        <v>9493</v>
+        <v>10646</v>
       </c>
       <c r="AE27" s="20">
-        <v>11011.88</v>
+        <v>12349.359999999999</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3952,85 +3954,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>2015</v>
+        <v>3300</v>
       </c>
       <c r="F28" s="14">
-        <v>2337.3999999999996</v>
+        <v>3827.9999999999995</v>
       </c>
       <c r="G28" s="14">
-        <v>5.5264360810604911</v>
+        <v>9.3526252983293556</v>
       </c>
       <c r="H28" s="30">
-        <v>8021.4444444444434</v>
+        <v>7762.5263157894742</v>
       </c>
       <c r="I28" s="15">
-        <v>-1631.1111111111109</v>
+        <v>-228.42105263157919</v>
       </c>
       <c r="J28" s="16">
-        <v>6913</v>
+        <v>6895</v>
       </c>
       <c r="K28" s="13">
-        <v>8019.079999999999</v>
+        <v>7998.2</v>
       </c>
       <c r="L28" s="14">
-        <v>24.115116279069767</v>
+        <v>25.149740833173357</v>
       </c>
       <c r="M28" s="30">
-        <v>6306.666666666667</v>
+        <v>6031.4736842105258</v>
       </c>
       <c r="N28" s="15">
-        <v>4046.333333333333</v>
+        <v>4153.4210526315792</v>
       </c>
       <c r="O28" s="16">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P28" s="17">
-        <v>869.99999999999989</v>
+        <v>868.83999999999992</v>
       </c>
       <c r="Q28" s="14">
-        <v>18.417462482946796</v>
+        <v>18.457846952010375</v>
       </c>
       <c r="R28" s="16">
-        <v>895.88888888888891</v>
+        <v>892.73684210526324</v>
       </c>
       <c r="S28" s="15">
-        <v>-64.444444444444457</v>
+        <v>-62.578947368421041</v>
       </c>
       <c r="T28" s="18">
-        <v>1120</v>
+        <v>1002</v>
       </c>
       <c r="U28" s="17">
-        <v>1299.1999999999998</v>
+        <v>1162.32</v>
       </c>
       <c r="V28" s="14">
-        <v>7.6392572944297079</v>
+        <v>6.7058823529411757</v>
       </c>
       <c r="W28" s="16">
-        <v>3225.4444444444443</v>
+        <v>3287.2631578947371</v>
       </c>
       <c r="X28" s="15">
-        <v>-1225.7777777777778</v>
+        <v>-1388.7368421052633</v>
       </c>
       <c r="Y28" s="18">
-        <v>433</v>
+        <v>262</v>
       </c>
       <c r="Z28" s="17">
-        <v>502.28</v>
+        <v>303.91999999999996</v>
       </c>
       <c r="AA28" s="14">
-        <v>24.130030959752325</v>
+        <v>15.039274924471298</v>
       </c>
       <c r="AB28" s="16">
-        <v>394.77777777777771</v>
+        <v>383.26315789473688</v>
       </c>
       <c r="AC28" s="15">
-        <v>38.222222222222285</v>
+        <v>-121.26315789473688</v>
       </c>
       <c r="AD28" s="19">
-        <v>11231</v>
+        <v>12208</v>
       </c>
       <c r="AE28" s="20">
-        <v>13027.96</v>
+        <v>14161.279999999999</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4065,85 +4067,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>2166</v>
+        <v>3326</v>
       </c>
       <c r="F29" s="14">
-        <v>2512.56</v>
+        <v>3858.16</v>
       </c>
       <c r="G29" s="14">
-        <v>5.5325670498084287</v>
+        <v>8.8050717570015316</v>
       </c>
       <c r="H29" s="30">
-        <v>8613</v>
+        <v>8310.21052631579</v>
       </c>
       <c r="I29" s="15">
-        <v>-1749</v>
+        <v>-451.36842105263167</v>
       </c>
       <c r="J29" s="16">
-        <v>448</v>
+        <v>1775</v>
       </c>
       <c r="K29" s="13">
-        <v>519.67999999999995</v>
+        <v>2059</v>
       </c>
       <c r="L29" s="14">
-        <v>1.6460502143294549</v>
+        <v>6.8200202224469164</v>
       </c>
       <c r="M29" s="30">
-        <v>5987.666666666667</v>
+        <v>5725.78947368421</v>
       </c>
       <c r="N29" s="15">
-        <v>-2273.666666666667</v>
+        <v>-827.63157894736833</v>
       </c>
       <c r="O29" s="16">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P29" s="17">
-        <v>875.8</v>
+        <v>874.64</v>
       </c>
       <c r="Q29" s="14">
-        <v>18.439620081411128</v>
+        <v>18.020125786163522</v>
       </c>
       <c r="R29" s="16">
-        <v>900.77777777777771</v>
+        <v>920.52631578947376</v>
       </c>
       <c r="S29" s="15">
-        <v>-63.888888888888914</v>
+        <v>-82.842105263157919</v>
       </c>
       <c r="T29" s="18">
-        <v>1034</v>
+        <v>920</v>
       </c>
       <c r="U29" s="17">
-        <v>1199.4399999999998</v>
+        <v>1067.1999999999998</v>
       </c>
       <c r="V29" s="14">
-        <v>6.9838649155722337</v>
+        <v>6.2162162162162158</v>
       </c>
       <c r="W29" s="16">
-        <v>3257.2222222222217</v>
+        <v>3256</v>
       </c>
       <c r="X29" s="15">
-        <v>-1334.8888888888887</v>
+        <v>-1448</v>
       </c>
       <c r="Y29" s="18">
-        <v>387</v>
+        <v>275</v>
       </c>
       <c r="Z29" s="17">
-        <v>448.91999999999996</v>
+        <v>319</v>
       </c>
       <c r="AA29" s="14">
-        <v>22.39871382636656</v>
+        <v>16.640127388535031</v>
       </c>
       <c r="AB29" s="16">
-        <v>380.11111111111114</v>
+        <v>363.57894736842104</v>
       </c>
       <c r="AC29" s="15">
-        <v>6.8888888888888573</v>
+        <v>-88.578947368421041</v>
       </c>
       <c r="AD29" s="19">
-        <v>4790</v>
+        <v>7050</v>
       </c>
       <c r="AE29" s="20">
-        <v>5556.4</v>
+        <v>8177.9999999999991</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4178,85 +4180,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>715</v>
+        <v>121</v>
       </c>
       <c r="F30" s="14">
-        <v>2631.2000000000003</v>
+        <v>445.28000000000003</v>
       </c>
       <c r="G30" s="14">
-        <v>6.6649404453650964</v>
+        <v>1.1381188118811882</v>
       </c>
       <c r="H30" s="30">
-        <v>2360.1111111111109</v>
+        <v>2338.9473684210525</v>
       </c>
       <c r="I30" s="15">
-        <v>-357.77777777777783</v>
+        <v>-942.15789473684208</v>
       </c>
       <c r="J30" s="16">
-        <v>1191</v>
+        <v>1335</v>
       </c>
       <c r="K30" s="13">
-        <v>4382.88</v>
+        <v>4912.8</v>
       </c>
       <c r="L30" s="14">
-        <v>9.6480648064806473</v>
+        <v>11.213527851458887</v>
       </c>
       <c r="M30" s="30">
-        <v>2715.7777777777778</v>
+        <v>2619.1578947368421</v>
       </c>
       <c r="N30" s="15">
-        <v>-43.444444444444343</v>
+        <v>144.47368421052624</v>
       </c>
       <c r="O30" s="16">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="P30" s="17">
-        <v>482.08000000000004</v>
+        <v>456.32</v>
       </c>
       <c r="Q30" s="14">
-        <v>21.633027522935777</v>
+        <v>20.310344827586206</v>
       </c>
       <c r="R30" s="16">
-        <v>133.22222222222223</v>
+        <v>134.31578947368422</v>
       </c>
       <c r="S30" s="15">
-        <v>9.8888888888888715</v>
+        <v>1.8947368421052602</v>
       </c>
       <c r="T30" s="18">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="U30" s="17">
-        <v>1387.3600000000001</v>
+        <v>1354.24</v>
       </c>
       <c r="V30" s="14">
-        <v>12.520295202952029</v>
+        <v>12.288224956063267</v>
       </c>
       <c r="W30" s="16">
-        <v>662.44444444444446</v>
+        <v>658.84210526315792</v>
       </c>
       <c r="X30" s="15">
-        <v>-104.77777777777777</v>
+        <v>-111.15789473684214</v>
       </c>
       <c r="Y30" s="18">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="17">
-        <v>471.04</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="14">
-        <v>24.774193548387096</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="16">
-        <v>113.66666666666667</v>
+        <v>107.68421052631578</v>
       </c>
       <c r="AC30" s="15">
-        <v>14.333333333333329</v>
+        <v>-107.68421052631578</v>
       </c>
       <c r="AD30" s="19">
-        <v>2542</v>
+        <v>1948</v>
       </c>
       <c r="AE30" s="20">
-        <v>9354.5600000000013</v>
+        <v>7168.64</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4291,34 +4293,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="F31" s="14">
-        <v>1026.72</v>
+        <v>1589.76</v>
       </c>
       <c r="G31" s="14">
-        <v>5.58</v>
+        <v>8.3840653728294168</v>
       </c>
       <c r="H31" s="30">
-        <v>1100</v>
+        <v>1133.578947368421</v>
       </c>
       <c r="I31" s="15">
-        <v>-221</v>
+        <v>-83.263157894736878</v>
       </c>
       <c r="J31" s="16">
-        <v>1511</v>
+        <v>1352</v>
       </c>
       <c r="K31" s="13">
-        <v>5560.4800000000005</v>
+        <v>4975.3600000000006</v>
       </c>
       <c r="L31" s="14">
-        <v>21.483412322274884</v>
+        <v>20.115896632732966</v>
       </c>
       <c r="M31" s="30">
-        <v>1547.3333333333333</v>
+        <v>1478.6315789473686</v>
       </c>
       <c r="N31" s="15">
-        <v>807.66666666666674</v>
+        <v>679.8947368421052</v>
       </c>
       <c r="O31" s="16">
         <v>34</v>
@@ -4327,28 +4329,28 @@
         <v>125.12</v>
       </c>
       <c r="Q31" s="14">
-        <v>34</v>
+        <v>35.888888888888893</v>
       </c>
       <c r="R31" s="16">
-        <v>22</v>
+        <v>20.842105263157894</v>
       </c>
       <c r="S31" s="15">
-        <v>14</v>
+        <v>15.05263157894737</v>
       </c>
       <c r="T31" s="18">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U31" s="17">
-        <v>423.20000000000005</v>
+        <v>412.16</v>
       </c>
       <c r="V31" s="14">
-        <v>12.034883720930234</v>
+        <v>11.319148936170212</v>
       </c>
       <c r="W31" s="16">
-        <v>210.22222222222223</v>
+        <v>217.68421052631581</v>
       </c>
       <c r="X31" s="15">
-        <v>-37.888888888888886</v>
+        <v>-46.31578947368422</v>
       </c>
       <c r="Y31" s="18">
         <v>44</v>
@@ -4357,19 +4359,19 @@
         <v>161.92000000000002</v>
       </c>
       <c r="AA31" s="14">
-        <v>33</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="AB31" s="16">
-        <v>29.333333333333332</v>
+        <v>27.789473684210524</v>
       </c>
       <c r="AC31" s="15">
-        <v>14.666666666666668</v>
+        <v>16.210526315789476</v>
       </c>
       <c r="AD31" s="19">
-        <v>1983</v>
+        <v>1974</v>
       </c>
       <c r="AE31" s="20">
-        <v>7297.4400000000005</v>
+        <v>7264.3200000000006</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4404,64 +4406,64 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1612</v>
+        <v>1331</v>
       </c>
       <c r="F32" s="14">
-        <v>6689.8</v>
+        <v>5523.6500000000005</v>
       </c>
       <c r="G32" s="14">
-        <v>7.2503748125937015</v>
+        <v>5.9841457643161382</v>
       </c>
       <c r="H32" s="30">
-        <v>4891.3333333333339</v>
+        <v>4893.2631578947367</v>
       </c>
       <c r="I32" s="15">
-        <v>-611.33333333333394</v>
+        <v>-893.21052631578914</v>
       </c>
       <c r="J32" s="16">
-        <v>1861</v>
+        <v>4052</v>
       </c>
       <c r="K32" s="13">
-        <v>7723.1500000000005</v>
+        <v>16815.800000000003</v>
       </c>
       <c r="L32" s="14">
-        <v>9.9845007451564829</v>
+        <v>22.603640634174983</v>
       </c>
       <c r="M32" s="30">
-        <v>4100.5555555555557</v>
+        <v>3943.7894736842109</v>
       </c>
       <c r="N32" s="15">
-        <v>-2.8888888888889142</v>
+        <v>2259.3684210526317</v>
       </c>
       <c r="O32" s="16">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="P32" s="17">
-        <v>1186.9000000000001</v>
+        <v>1087.3000000000002</v>
       </c>
       <c r="Q32" s="14">
-        <v>20.926829268292686</v>
+        <v>18.437037037037037</v>
       </c>
       <c r="R32" s="16">
-        <v>300.66666666666663</v>
+        <v>312.63157894736844</v>
       </c>
       <c r="S32" s="15">
-        <v>12.666666666666742</v>
+        <v>-22.21052631578948</v>
       </c>
       <c r="T32" s="18">
-        <v>1093</v>
+        <v>1072</v>
       </c>
       <c r="U32" s="17">
-        <v>4535.9500000000007</v>
+        <v>4448.8</v>
       </c>
       <c r="V32" s="14">
-        <v>13.257412398921833</v>
+        <v>13.166127989657403</v>
       </c>
       <c r="W32" s="16">
-        <v>1813.7777777777778</v>
+        <v>1791.2631578947369</v>
       </c>
       <c r="X32" s="15">
-        <v>-226.11111111111109</v>
+        <v>-230.73684210526312</v>
       </c>
       <c r="Y32" s="18">
         <v>278</v>
@@ -4470,19 +4472,19 @@
         <v>1153.7</v>
       </c>
       <c r="AA32" s="14">
-        <v>69.5</v>
+        <v>73.361111111111114</v>
       </c>
       <c r="AB32" s="16">
-        <v>88</v>
+        <v>83.368421052631575</v>
       </c>
       <c r="AC32" s="15">
-        <v>190</v>
+        <v>194.63157894736844</v>
       </c>
       <c r="AD32" s="19">
-        <v>5130</v>
+        <v>6995</v>
       </c>
       <c r="AE32" s="20">
-        <v>21289.500000000004</v>
+        <v>29029.250000000004</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4517,64 +4519,64 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>2670</v>
+        <v>2532</v>
       </c>
       <c r="F33" s="14">
-        <v>11080.500000000002</v>
+        <v>10507.800000000001</v>
       </c>
       <c r="G33" s="14">
-        <v>6.0135135135135132</v>
+        <v>5.7087931648273402</v>
       </c>
       <c r="H33" s="30">
-        <v>9768</v>
+        <v>9757.5789473684217</v>
       </c>
       <c r="I33" s="15">
-        <v>-1770</v>
+        <v>-1903.2631578947367</v>
       </c>
       <c r="J33" s="16">
-        <v>3076</v>
+        <v>3710</v>
       </c>
       <c r="K33" s="13">
-        <v>12765.400000000001</v>
+        <v>15396.500000000002</v>
       </c>
       <c r="L33" s="14">
-        <v>10.946619217081851</v>
+        <v>13.767578125</v>
       </c>
       <c r="M33" s="30">
-        <v>6182</v>
+        <v>5928.4210526315783</v>
       </c>
       <c r="N33" s="15">
-        <v>266</v>
+        <v>1015.2631578947371</v>
       </c>
       <c r="O33" s="16">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="P33" s="17">
-        <v>1639.2500000000002</v>
+        <v>1568.7</v>
       </c>
       <c r="Q33" s="14">
-        <v>20.549132947976879</v>
+        <v>19.785123966942148</v>
       </c>
       <c r="R33" s="16">
-        <v>422.88888888888886</v>
+        <v>420.31578947368422</v>
       </c>
       <c r="S33" s="15">
-        <v>10.555555555555543</v>
+        <v>-4.1052631578947398</v>
       </c>
       <c r="T33" s="18">
-        <v>1204</v>
+        <v>1163</v>
       </c>
       <c r="U33" s="17">
-        <v>4996.6000000000004</v>
+        <v>4826.4500000000007</v>
       </c>
       <c r="V33" s="14">
-        <v>11.096774193548388</v>
+        <v>10.960813492063492</v>
       </c>
       <c r="W33" s="16">
-        <v>2387</v>
+        <v>2334.3157894736842</v>
       </c>
       <c r="X33" s="15">
-        <v>-532</v>
+        <v>-534.68421052631584</v>
       </c>
       <c r="Y33" s="18">
         <v>23</v>
@@ -4583,19 +4585,19 @@
         <v>95.45</v>
       </c>
       <c r="AA33" s="14">
-        <v>1.7768240343347639</v>
+        <v>1.8755364806866952</v>
       </c>
       <c r="AB33" s="16">
-        <v>284.77777777777777</v>
+        <v>269.78947368421052</v>
       </c>
       <c r="AC33" s="15">
-        <v>-261.77777777777777</v>
+        <v>-246.78947368421052</v>
       </c>
       <c r="AD33" s="19">
-        <v>7368</v>
+        <v>7806</v>
       </c>
       <c r="AE33" s="20">
-        <v>30577.200000000004</v>
+        <v>32394.9</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4630,25 +4632,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>798</v>
+        <v>678</v>
       </c>
       <c r="F34" s="14">
-        <v>3311.7000000000003</v>
+        <v>2813.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>14.22178217821782</v>
+        <v>12.754455445544554</v>
       </c>
       <c r="H34" s="30">
-        <v>1234.4444444444446</v>
+        <v>1169.4736842105262</v>
       </c>
       <c r="I34" s="15">
-        <v>236.88888888888891</v>
+        <v>146.42105263157896</v>
       </c>
       <c r="J34" s="16">
-        <v>256</v>
+        <v>433</v>
       </c>
       <c r="K34" s="13">
-        <v>1062.4000000000001</v>
+        <v>1796.95</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4657,20 +4659,20 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>256</v>
+        <v>433</v>
       </c>
       <c r="O34" s="16">
         <v>48</v>
       </c>
       <c r="P34" s="17"/>
       <c r="Q34" s="14">
-        <v>27</v>
+        <v>28.499999999999996</v>
       </c>
       <c r="R34" s="16">
-        <v>39.111111111111107</v>
+        <v>37.05263157894737</v>
       </c>
       <c r="S34" s="15">
-        <v>12.444444444444443</v>
+        <v>14.315789473684205</v>
       </c>
       <c r="T34" s="18">
         <v>122</v>
@@ -4679,13 +4681,13 @@
         <v>506.30000000000007</v>
       </c>
       <c r="V34" s="14">
-        <v>19.963636363636365</v>
+        <v>21.072727272727271</v>
       </c>
       <c r="W34" s="16">
-        <v>134.44444444444443</v>
+        <v>127.36842105263159</v>
       </c>
       <c r="X34" s="15">
-        <v>24.222222222222229</v>
+        <v>29.368421052631575</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4703,10 +4705,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1256</v>
+        <v>1313</v>
       </c>
       <c r="AE34" s="20">
-        <v>5212.4000000000005</v>
+        <v>5448.9500000000007</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4741,85 +4743,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1916</v>
+        <v>1452</v>
       </c>
       <c r="F35" s="14">
-        <v>3123.08</v>
+        <v>2366.7599999999998</v>
       </c>
       <c r="G35" s="14">
-        <v>4.5182759072448571</v>
+        <v>3.3705558949297494</v>
       </c>
       <c r="H35" s="30">
-        <v>9329.2222222222226</v>
+        <v>9477.3684210526317</v>
       </c>
       <c r="I35" s="15">
-        <v>-2324.5555555555557</v>
+        <v>-2855.894736842105</v>
       </c>
       <c r="J35" s="16">
-        <v>1375</v>
+        <v>3957</v>
       </c>
       <c r="K35" s="13">
-        <v>2241.25</v>
+        <v>6449.91</v>
       </c>
       <c r="L35" s="14">
-        <v>7.9607590865229971</v>
+        <v>24.050863723608447</v>
       </c>
       <c r="M35" s="30">
-        <v>3799.8888888888891</v>
+        <v>3619.5789473684208</v>
       </c>
       <c r="N35" s="15">
-        <v>-352.22222222222217</v>
+        <v>2311.7368421052633</v>
       </c>
       <c r="O35" s="16">
-        <v>705</v>
+        <v>739</v>
       </c>
       <c r="P35" s="17">
-        <v>1149.1499999999999</v>
+        <v>1204.57</v>
       </c>
       <c r="Q35" s="14">
-        <v>18.444767441860467</v>
+        <v>19.888101983002834</v>
       </c>
       <c r="R35" s="16">
-        <v>840.88888888888891</v>
+        <v>817.47368421052624</v>
       </c>
       <c r="S35" s="15">
-        <v>-59.444444444444457</v>
+        <v>-4.1578947368420813</v>
       </c>
       <c r="T35" s="18">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="U35" s="17">
-        <v>947.03</v>
+        <v>924.20999999999992</v>
       </c>
       <c r="V35" s="14">
-        <v>12.645707376058041</v>
+        <v>12.570595099183196</v>
       </c>
       <c r="W35" s="16">
-        <v>1010.7777777777777</v>
+        <v>992.31578947368428</v>
       </c>
       <c r="X35" s="15">
-        <v>-154.11111111111109</v>
+        <v>-154.68421052631584</v>
       </c>
       <c r="Y35" s="18">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="Z35" s="17">
-        <v>464.54999999999995</v>
+        <v>376.53</v>
       </c>
       <c r="AA35" s="14">
-        <v>20.276679841897234</v>
+        <v>17.34782608695652</v>
       </c>
       <c r="AB35" s="16">
-        <v>309.22222222222223</v>
+        <v>292.94736842105266</v>
       </c>
       <c r="AC35" s="15">
-        <v>-24.222222222222229</v>
+        <v>-61.947368421052659</v>
       </c>
       <c r="AD35" s="19">
-        <v>4862</v>
+        <v>6946</v>
       </c>
       <c r="AE35" s="20">
-        <v>7925.0599999999995</v>
+        <v>11321.98</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4854,85 +4856,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>4467</v>
+        <v>3894</v>
       </c>
       <c r="F36" s="14">
-        <v>7281.2099999999991</v>
+        <v>6347.2199999999993</v>
       </c>
       <c r="G36" s="14">
-        <v>7.2100071736011477</v>
+        <v>6.133300174086048</v>
       </c>
       <c r="H36" s="30">
-        <v>13630.222222222223</v>
+        <v>13967.684210526317</v>
       </c>
       <c r="I36" s="15">
-        <v>-1728.5555555555557</v>
+        <v>-2454.9473684210534</v>
       </c>
       <c r="J36" s="16">
-        <v>2460</v>
+        <v>6299</v>
       </c>
       <c r="K36" s="13">
-        <v>4009.7999999999997</v>
+        <v>10267.369999999999</v>
       </c>
       <c r="L36" s="14">
-        <v>10.433553251649386</v>
+        <v>28.094131455399062</v>
       </c>
       <c r="M36" s="30">
-        <v>5187.1111111111113</v>
+        <v>4932.6315789473683</v>
       </c>
       <c r="N36" s="15">
-        <v>102.22222222222217</v>
+        <v>4056.894736842105</v>
       </c>
       <c r="O36" s="16">
-        <v>1761</v>
+        <v>1678</v>
       </c>
       <c r="P36" s="17">
-        <v>2870.43</v>
+        <v>2735.14</v>
       </c>
       <c r="Q36" s="14">
-        <v>19.339841366687004</v>
+        <v>18.396999422965955</v>
       </c>
       <c r="R36" s="16">
-        <v>2003.2222222222222</v>
+        <v>2006.6315789473686</v>
       </c>
       <c r="S36" s="15">
-        <v>-60.111111111111086</v>
+        <v>-146.21052631578959</v>
       </c>
       <c r="T36" s="18">
-        <v>1437</v>
+        <v>1399</v>
       </c>
       <c r="U36" s="17">
-        <v>2342.31</v>
+        <v>2280.37</v>
       </c>
       <c r="V36" s="14">
-        <v>13.729299363057322</v>
+        <v>13.575587334014299</v>
       </c>
       <c r="W36" s="16">
-        <v>2302.666666666667</v>
+        <v>2267.1578947368421</v>
       </c>
       <c r="X36" s="15">
-        <v>-237.66666666666697</v>
+        <v>-249.84210526315792</v>
       </c>
       <c r="Y36" s="18">
-        <v>507</v>
+        <v>186</v>
       </c>
       <c r="Z36" s="17">
-        <v>826.41</v>
+        <v>303.18</v>
       </c>
       <c r="AA36" s="14">
-        <v>19.5</v>
+        <v>7.5512820512820502</v>
       </c>
       <c r="AB36" s="16">
-        <v>572</v>
+        <v>541.89473684210532</v>
       </c>
       <c r="AC36" s="15">
-        <v>-65</v>
+        <v>-355.89473684210532</v>
       </c>
       <c r="AD36" s="19">
-        <v>10632</v>
+        <v>13456</v>
       </c>
       <c r="AE36" s="20">
-        <v>17330.16</v>
+        <v>21933.279999999999</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4967,85 +4969,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1265</v>
+        <v>875</v>
       </c>
       <c r="F37" s="14">
-        <v>2061.9499999999998</v>
+        <v>1426.25</v>
       </c>
       <c r="G37" s="14">
-        <v>4.3620689655172411</v>
+        <v>3.0199818346957308</v>
       </c>
       <c r="H37" s="30">
-        <v>6380</v>
+        <v>6374.21052631579</v>
       </c>
       <c r="I37" s="15">
-        <v>-1635</v>
+        <v>-2022.3684210526317</v>
       </c>
       <c r="J37" s="16">
-        <v>215</v>
+        <v>1011</v>
       </c>
       <c r="K37" s="13">
-        <v>350.45</v>
+        <v>1647.9299999999998</v>
       </c>
       <c r="L37" s="14">
-        <v>1.5075964160498636</v>
+        <v>7.4830541488118421</v>
       </c>
       <c r="M37" s="30">
-        <v>3137.4444444444443</v>
+        <v>2972.3157894736842</v>
       </c>
       <c r="N37" s="15">
-        <v>-1211.1111111111111</v>
+        <v>-340.05263157894751</v>
       </c>
       <c r="O37" s="16">
-        <v>1145</v>
+        <v>1059</v>
       </c>
       <c r="P37" s="17">
-        <v>1866.35</v>
+        <v>1726.1699999999998</v>
       </c>
       <c r="Q37" s="14">
-        <v>20.365612648221344</v>
+        <v>17.981233243967829</v>
       </c>
       <c r="R37" s="16">
-        <v>1236.8888888888889</v>
+        <v>1295.6842105263158</v>
       </c>
       <c r="S37" s="15">
-        <v>20.555555555555657</v>
+        <v>-118.89473684210543</v>
       </c>
       <c r="T37" s="18">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="U37" s="17">
-        <v>738.39</v>
+        <v>676.44999999999993</v>
       </c>
       <c r="V37" s="14">
-        <v>8.0176991150442483</v>
+        <v>7.2472426470588225</v>
       </c>
       <c r="W37" s="16">
-        <v>1243</v>
+        <v>1259.7894736842106</v>
       </c>
       <c r="X37" s="15">
-        <v>-451</v>
+        <v>-501.21052631578959</v>
       </c>
       <c r="Y37" s="18">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="17">
-        <v>352.08</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="14">
-        <v>15.804878048780491</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>300.66666666666663</v>
+        <v>284.84210526315792</v>
       </c>
       <c r="AC37" s="15">
-        <v>-84.666666666666629</v>
+        <v>-284.84210526315792</v>
       </c>
       <c r="AD37" s="19">
-        <v>3294</v>
+        <v>3360</v>
       </c>
       <c r="AE37" s="20">
-        <v>5369.2199999999993</v>
+        <v>5476.7999999999993</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5080,85 +5082,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>782</v>
+        <v>536</v>
       </c>
       <c r="F38" s="14">
-        <v>1274.6599999999999</v>
+        <v>873.68</v>
       </c>
       <c r="G38" s="14">
-        <v>3.9617224880382778</v>
+        <v>2.7487179487179487</v>
       </c>
       <c r="H38" s="30">
-        <v>4342.5555555555557</v>
+        <v>4290</v>
       </c>
       <c r="I38" s="15">
-        <v>-1191.8888888888889</v>
+        <v>-1414</v>
       </c>
       <c r="J38" s="16">
-        <v>269</v>
+        <v>4048</v>
       </c>
       <c r="K38" s="13">
-        <v>438.46999999999997</v>
+        <v>6598.24</v>
       </c>
       <c r="L38" s="14">
-        <v>2.2679156908665106</v>
+        <v>35.673469387755105</v>
       </c>
       <c r="M38" s="30">
-        <v>2609.4444444444443</v>
+        <v>2496.4210526315787</v>
       </c>
       <c r="N38" s="15">
-        <v>-917.11111111111109</v>
+        <v>2913.2631578947371</v>
       </c>
       <c r="O38" s="16">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="P38" s="17">
-        <v>1175.23</v>
+        <v>1129.5899999999999</v>
       </c>
       <c r="Q38" s="14">
-        <v>19.545180722891569</v>
+        <v>18.415384615384617</v>
       </c>
       <c r="R38" s="16">
-        <v>811.55555555555543</v>
+        <v>827.8947368421052</v>
       </c>
       <c r="S38" s="15">
-        <v>-16.777777777777715</v>
+        <v>-59.631578947368325</v>
       </c>
       <c r="T38" s="18">
-        <v>514</v>
+        <v>480</v>
       </c>
       <c r="U38" s="17">
-        <v>837.81999999999994</v>
+        <v>782.4</v>
       </c>
       <c r="V38" s="14">
-        <v>14.146788990825687</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="W38" s="16">
-        <v>799.33333333333337</v>
+        <v>792</v>
       </c>
       <c r="X38" s="15">
-        <v>-67.333333333333371</v>
+        <v>-96</v>
       </c>
       <c r="Y38" s="18">
-        <v>461</v>
+        <v>83</v>
       </c>
       <c r="Z38" s="17">
-        <v>751.43</v>
+        <v>135.29</v>
       </c>
       <c r="AA38" s="14">
-        <v>15.896551724137931</v>
+        <v>3.0210727969348659</v>
       </c>
       <c r="AB38" s="16">
-        <v>638</v>
+        <v>604.42105263157896</v>
       </c>
       <c r="AC38" s="15">
-        <v>-177</v>
+        <v>-521.42105263157896</v>
       </c>
       <c r="AD38" s="19">
-        <v>2747</v>
+        <v>5840</v>
       </c>
       <c r="AE38" s="20">
-        <v>4477.6099999999997</v>
+        <v>9519.1999999999989</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5193,34 +5195,34 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1202</v>
+        <v>1091</v>
       </c>
       <c r="F39" s="14">
-        <v>1959.2599999999998</v>
+        <v>1778.33</v>
       </c>
       <c r="G39" s="14">
-        <v>13.413515189088654</v>
+        <v>10.635710620831196</v>
       </c>
       <c r="H39" s="30">
-        <v>1971.4444444444446</v>
+        <v>2256.7368421052633</v>
       </c>
       <c r="I39" s="15">
-        <v>305.88888888888891</v>
+        <v>65.210526315789366</v>
       </c>
       <c r="J39" s="16">
-        <v>2572</v>
+        <v>4105</v>
       </c>
       <c r="K39" s="13">
-        <v>4192.3599999999997</v>
+        <v>6691.15</v>
       </c>
       <c r="L39" s="14">
-        <v>44.302392344497612</v>
+        <v>73.999051233396585</v>
       </c>
       <c r="M39" s="30">
-        <v>1277.2222222222222</v>
+        <v>1220.421052631579</v>
       </c>
       <c r="N39" s="15">
-        <v>1991.4444444444443</v>
+        <v>3550.2631578947367</v>
       </c>
       <c r="O39" s="16">
         <v>613</v>
@@ -5229,28 +5231,28 @@
         <v>999.18999999999994</v>
       </c>
       <c r="Q39" s="14">
-        <v>20.471243042671617</v>
+        <v>20.947841726618705</v>
       </c>
       <c r="R39" s="16">
-        <v>658.77777777777771</v>
+        <v>643.78947368421052</v>
       </c>
       <c r="S39" s="15">
-        <v>14.111111111111086</v>
+        <v>27.736842105263122</v>
       </c>
       <c r="T39" s="18">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="U39" s="17">
-        <v>1052.98</v>
+        <v>1051.3499999999999</v>
       </c>
       <c r="V39" s="14">
-        <v>11.344390243902438</v>
+        <v>11.817743490838959</v>
       </c>
       <c r="W39" s="16">
-        <v>1252.7777777777778</v>
+        <v>1200.7368421052631</v>
       </c>
       <c r="X39" s="15">
-        <v>-265.1111111111112</v>
+        <v>-228.26315789473676</v>
       </c>
       <c r="Y39" s="18">
         <v>431</v>
@@ -5259,19 +5261,19 @@
         <v>702.53</v>
       </c>
       <c r="AA39" s="14">
-        <v>93.469879518072304</v>
+        <v>98.662650602409641</v>
       </c>
       <c r="AB39" s="16">
-        <v>101.44444444444443</v>
+        <v>96.10526315789474</v>
       </c>
       <c r="AC39" s="15">
-        <v>329.55555555555554</v>
+        <v>334.89473684210526</v>
       </c>
       <c r="AD39" s="19">
-        <v>5464</v>
+        <v>6885</v>
       </c>
       <c r="AE39" s="20">
-        <v>8906.32</v>
+        <v>11222.55</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5306,64 +5308,64 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>864</v>
+        <v>1033</v>
       </c>
       <c r="F40" s="14">
-        <v>1408.32</v>
+        <v>1683.79</v>
       </c>
       <c r="G40" s="14">
-        <v>7.2979821679962456</v>
+        <v>7.8039761431411527</v>
       </c>
       <c r="H40" s="30">
-        <v>2604.5555555555557</v>
+        <v>2912.105263157895</v>
       </c>
       <c r="I40" s="15">
-        <v>-319.88888888888891</v>
+        <v>-290.68421052631584</v>
       </c>
       <c r="J40" s="16">
-        <v>1660</v>
+        <v>2802</v>
       </c>
       <c r="K40" s="13">
-        <v>2705.7999999999997</v>
+        <v>4567.2599999999993</v>
       </c>
       <c r="L40" s="14">
-        <v>24.431725265739985</v>
+        <v>43.318144833197721</v>
       </c>
       <c r="M40" s="30">
-        <v>1494.7777777777778</v>
+        <v>1423.0526315789475</v>
       </c>
       <c r="N40" s="15">
-        <v>980.55555555555554</v>
+        <v>2155.1578947368421</v>
       </c>
       <c r="O40" s="16">
-        <v>804</v>
+        <v>764</v>
       </c>
       <c r="P40" s="17">
-        <v>1310.52</v>
+        <v>1245.32</v>
       </c>
       <c r="Q40" s="14">
-        <v>21.535714285714285</v>
+        <v>21.441654357459381</v>
       </c>
       <c r="R40" s="16">
-        <v>821.33333333333337</v>
+        <v>783.8947368421052</v>
       </c>
       <c r="S40" s="15">
-        <v>57.333333333333258</v>
+        <v>51.368421052631675</v>
       </c>
       <c r="T40" s="18">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="U40" s="17">
-        <v>1279.55</v>
+        <v>1258.3599999999999</v>
       </c>
       <c r="V40" s="14">
-        <v>11.98473282442748</v>
+        <v>12.192851205320032</v>
       </c>
       <c r="W40" s="16">
-        <v>1441</v>
+        <v>1392.9473684210527</v>
       </c>
       <c r="X40" s="15">
-        <v>-263</v>
+        <v>-241.0526315789474</v>
       </c>
       <c r="Y40" s="18">
         <v>438</v>
@@ -5372,19 +5374,19 @@
         <v>713.93999999999994</v>
       </c>
       <c r="AA40" s="14">
-        <v>93.857142857142847</v>
+        <v>99.071428571428555</v>
       </c>
       <c r="AB40" s="16">
-        <v>102.66666666666667</v>
+        <v>97.26315789473685</v>
       </c>
       <c r="AC40" s="15">
-        <v>335.33333333333331</v>
+        <v>340.73684210526312</v>
       </c>
       <c r="AD40" s="19">
-        <v>4551</v>
+        <v>5809</v>
       </c>
       <c r="AE40" s="20">
-        <v>7418.1299999999992</v>
+        <v>9468.67</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5419,49 +5421,49 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="F41" s="14">
-        <v>2730.6000000000004</v>
+        <v>2410.8000000000002</v>
       </c>
       <c r="G41" s="14">
-        <v>6.460792239288601</v>
+        <v>5.7248270561106844</v>
       </c>
       <c r="H41" s="30">
-        <v>1511.8888888888891</v>
+        <v>1506.421052631579</v>
       </c>
       <c r="I41" s="15">
-        <v>-243.22222222222229</v>
+        <v>-292.73684210526312</v>
       </c>
       <c r="J41" s="16">
-        <v>237</v>
+        <v>984</v>
       </c>
       <c r="K41" s="13">
-        <v>1457.5500000000002</v>
+        <v>6051.6</v>
       </c>
       <c r="L41" s="14">
-        <v>5.8278688524590168</v>
+        <v>25.471389645776568</v>
       </c>
       <c r="M41" s="30">
-        <v>894.66666666666663</v>
+        <v>849.8947368421052</v>
       </c>
       <c r="N41" s="15">
-        <v>-169.66666666666663</v>
+        <v>597.68421052631584</v>
       </c>
       <c r="O41" s="16">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="P41" s="17">
-        <v>688.80000000000007</v>
+        <v>387.45000000000005</v>
       </c>
       <c r="Q41" s="14">
-        <v>24.585365853658537</v>
+        <v>13.153846153846153</v>
       </c>
       <c r="R41" s="16">
-        <v>100.22222222222221</v>
+        <v>105.36842105263159</v>
       </c>
       <c r="S41" s="15">
-        <v>20.888888888888886</v>
+        <v>-32.789473684210535</v>
       </c>
       <c r="T41" s="18">
         <v>158</v>
@@ -5470,34 +5472,34 @@
         <v>971.7</v>
       </c>
       <c r="V41" s="14">
-        <v>14.22</v>
+        <v>14.572815533980581</v>
       </c>
       <c r="W41" s="16">
-        <v>244.44444444444443</v>
+        <v>238.5263157894737</v>
       </c>
       <c r="X41" s="15">
-        <v>-19.777777777777771</v>
+        <v>-15.473684210526329</v>
       </c>
       <c r="Y41" s="18">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="17">
-        <v>590.40000000000009</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="14">
-        <v>21.073170731707318</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>100.22222222222221</v>
+        <v>94.94736842105263</v>
       </c>
       <c r="AC41" s="15">
-        <v>-4.2222222222222143</v>
+        <v>-94.94736842105263</v>
       </c>
       <c r="AD41" s="19">
-        <v>1047</v>
+        <v>1597</v>
       </c>
       <c r="AE41" s="20">
-        <v>6439.05</v>
+        <v>9821.5500000000011</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5532,64 +5534,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>212</v>
+        <v>298</v>
       </c>
       <c r="F42" s="14">
-        <v>1303.8000000000002</v>
+        <v>1832.7</v>
       </c>
       <c r="G42" s="14">
-        <v>3.0430622009569377</v>
+        <v>4.0704529115744066</v>
       </c>
       <c r="H42" s="30">
-        <v>1532.6666666666667</v>
+        <v>1610.6315789473686</v>
       </c>
       <c r="I42" s="15">
-        <v>-484.66666666666674</v>
+        <v>-434.1052631578948</v>
       </c>
       <c r="J42" s="16">
-        <v>848</v>
+        <v>764</v>
       </c>
       <c r="K42" s="13">
-        <v>5215.2000000000007</v>
+        <v>4698.6000000000004</v>
       </c>
       <c r="L42" s="14">
-        <v>20.137203166226911</v>
+        <v>18.925684485006517</v>
       </c>
       <c r="M42" s="30">
-        <v>926.44444444444457</v>
+        <v>888.1052631578948</v>
       </c>
       <c r="N42" s="15">
-        <v>426.88888888888886</v>
+        <v>360.31578947368416</v>
       </c>
       <c r="O42" s="16">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="P42" s="17">
-        <v>836.40000000000009</v>
+        <v>719.55000000000007</v>
       </c>
       <c r="Q42" s="14">
-        <v>21.103448275862071</v>
+        <v>16.226277372262775</v>
       </c>
       <c r="R42" s="16">
-        <v>141.77777777777777</v>
+        <v>158.63157894736841</v>
       </c>
       <c r="S42" s="15">
-        <v>7.1111111111111143</v>
+        <v>-27.21052631578948</v>
       </c>
       <c r="T42" s="18">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U42" s="17">
-        <v>1580.5500000000002</v>
+        <v>1568.25</v>
       </c>
       <c r="V42" s="14">
-        <v>15.842465753424658</v>
+        <v>16.043046357615896</v>
       </c>
       <c r="W42" s="16">
-        <v>356.88888888888886</v>
+        <v>349.68421052631578</v>
       </c>
       <c r="X42" s="15">
-        <v>-2.5555555555555429</v>
+        <v>0.68421052631580892</v>
       </c>
       <c r="Y42" s="18">
         <v>82</v>
@@ -5598,19 +5600,19 @@
         <v>504.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>25.01694915254237</v>
+        <v>26.406779661016952</v>
       </c>
       <c r="AB42" s="16">
-        <v>72.111111111111114</v>
+        <v>68.315789473684205</v>
       </c>
       <c r="AC42" s="15">
-        <v>9.8888888888888857</v>
+        <v>13.684210526315795</v>
       </c>
       <c r="AD42" s="19">
-        <v>1535</v>
+        <v>1516</v>
       </c>
       <c r="AE42" s="20">
-        <v>9440.25</v>
+        <v>9323.4</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5645,85 +5647,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>1802</v>
+        <v>1919</v>
       </c>
       <c r="F43" s="14">
-        <v>2090.3199999999997</v>
+        <v>2226.04</v>
       </c>
       <c r="G43" s="14">
-        <v>5.4957641477465264</v>
+        <v>5.7095208268086441</v>
       </c>
       <c r="H43" s="30">
-        <v>7213.5555555555566</v>
+        <v>7394.3157894736842</v>
       </c>
       <c r="I43" s="15">
-        <v>-1476.8888888888891</v>
+        <v>-1442.0526315789475</v>
       </c>
       <c r="J43" s="16">
-        <v>3140</v>
+        <v>3432</v>
       </c>
       <c r="K43" s="13">
-        <v>3642.3999999999996</v>
+        <v>3981.12</v>
       </c>
       <c r="L43" s="14">
-        <v>12.454825914499779</v>
+        <v>14.200348432055748</v>
       </c>
       <c r="M43" s="30">
-        <v>5546.4444444444443</v>
+        <v>5317.0526315789475</v>
       </c>
       <c r="N43" s="15">
-        <v>618.88888888888869</v>
+        <v>1015.1578947368421</v>
       </c>
       <c r="O43" s="16">
-        <v>874</v>
+        <v>844</v>
       </c>
       <c r="P43" s="17">
-        <v>1013.8399999999999</v>
+        <v>979.04</v>
       </c>
       <c r="Q43" s="14">
-        <v>19.350553505535057</v>
+        <v>18.347826086956523</v>
       </c>
       <c r="R43" s="16">
-        <v>993.66666666666663</v>
+        <v>1012</v>
       </c>
       <c r="S43" s="15">
-        <v>-29.333333333333258</v>
+        <v>-76</v>
       </c>
       <c r="T43" s="18">
-        <v>1520</v>
+        <v>1465</v>
       </c>
       <c r="U43" s="17">
-        <v>1763.1999999999998</v>
+        <v>1699.3999999999999</v>
       </c>
       <c r="V43" s="14">
-        <v>12.82099343955014</v>
+        <v>12.133827375762859</v>
       </c>
       <c r="W43" s="16">
-        <v>2608.2222222222222</v>
+        <v>2656.2105263157896</v>
       </c>
       <c r="X43" s="15">
-        <v>-376.88888888888891</v>
+        <v>-466.78947368421063</v>
       </c>
       <c r="Y43" s="18">
-        <v>560</v>
+        <v>15</v>
       </c>
       <c r="Z43" s="17">
-        <v>649.59999999999991</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="AA43" s="14">
-        <v>18.294010889292196</v>
+        <v>0.51258992805755399</v>
       </c>
       <c r="AB43" s="16">
-        <v>673.44444444444446</v>
+        <v>643.78947368421052</v>
       </c>
       <c r="AC43" s="15">
-        <v>-113.44444444444446</v>
+        <v>-628.78947368421052</v>
       </c>
       <c r="AD43" s="19">
-        <v>7896</v>
+        <v>7675</v>
       </c>
       <c r="AE43" s="20">
-        <v>9159.3599999999988</v>
+        <v>8903</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5758,85 +5760,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>1879</v>
+        <v>2616</v>
       </c>
       <c r="F44" s="14">
-        <v>2179.64</v>
+        <v>3034.56</v>
       </c>
       <c r="G44" s="14">
-        <v>6.4793103448275859</v>
+        <v>8.9524495677233435</v>
       </c>
       <c r="H44" s="30">
-        <v>6380</v>
+        <v>6428.6315789473683</v>
       </c>
       <c r="I44" s="15">
-        <v>-1021</v>
+        <v>-306.10526315789502</v>
       </c>
       <c r="J44" s="16">
-        <v>4279</v>
+        <v>3772</v>
       </c>
       <c r="K44" s="13">
-        <v>4963.6399999999994</v>
+        <v>4375.5199999999995</v>
       </c>
       <c r="L44" s="14">
-        <v>22.075666380051587</v>
+        <v>20.262369239468477</v>
       </c>
       <c r="M44" s="30">
-        <v>4264.3333333333339</v>
+        <v>4095.4736842105262</v>
       </c>
       <c r="N44" s="15">
-        <v>2340.6666666666661</v>
+        <v>1910.421052631579</v>
       </c>
       <c r="O44" s="16">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="P44" s="17">
-        <v>670.4799999999999</v>
+        <v>643.79999999999995</v>
       </c>
       <c r="Q44" s="14">
-        <v>20.849699398797593</v>
+        <v>20.201149425287358</v>
       </c>
       <c r="R44" s="16">
-        <v>609.88888888888891</v>
+        <v>604.42105263157896</v>
       </c>
       <c r="S44" s="15">
-        <v>23.555555555555543</v>
+        <v>5.526315789473756</v>
       </c>
       <c r="T44" s="18">
-        <v>941</v>
+        <v>911</v>
       </c>
       <c r="U44" s="17">
-        <v>1091.56</v>
+        <v>1056.76</v>
       </c>
       <c r="V44" s="14">
-        <v>14.754355400696864</v>
+        <v>14.164484451718495</v>
       </c>
       <c r="W44" s="16">
-        <v>1403.1111111111111</v>
+        <v>1414.9473684210525</v>
       </c>
       <c r="X44" s="15">
-        <v>-79.444444444444457</v>
+        <v>-118.05263157894728</v>
       </c>
       <c r="Y44" s="18">
-        <v>479</v>
+        <v>97</v>
       </c>
       <c r="Z44" s="17">
-        <v>555.64</v>
+        <v>112.52</v>
       </c>
       <c r="AA44" s="14">
-        <v>16.026022304832715</v>
+        <v>3.4066543438077637</v>
       </c>
       <c r="AB44" s="16">
-        <v>657.55555555555554</v>
+        <v>626.42105263157896</v>
       </c>
       <c r="AC44" s="15">
-        <v>-178.55555555555554</v>
+        <v>-529.42105263157896</v>
       </c>
       <c r="AD44" s="19">
-        <v>8156</v>
+        <v>7951</v>
       </c>
       <c r="AE44" s="20">
-        <v>9460.9599999999991</v>
+        <v>9223.16</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5871,85 +5873,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>1501</v>
+        <v>2926</v>
       </c>
       <c r="F45" s="14">
-        <v>1741.1599999999999</v>
+        <v>3394.16</v>
       </c>
       <c r="G45" s="14">
-        <v>3.9896633195510929</v>
+        <v>7.5885885885885891</v>
       </c>
       <c r="H45" s="30">
-        <v>8276.8888888888887</v>
+        <v>8482.7368421052633</v>
       </c>
       <c r="I45" s="15">
-        <v>-2261.2222222222222</v>
+        <v>-929.78947368421041</v>
       </c>
       <c r="J45" s="16">
-        <v>5293</v>
+        <v>4388</v>
       </c>
       <c r="K45" s="13">
-        <v>6139.8799999999992</v>
+        <v>5090.08</v>
       </c>
       <c r="L45" s="14">
-        <v>20.379465240641711</v>
+        <v>17.678541136556404</v>
       </c>
       <c r="M45" s="30">
-        <v>5713.8888888888887</v>
+        <v>5460.6315789473683</v>
       </c>
       <c r="N45" s="15">
-        <v>2695.7777777777778</v>
+        <v>1905.894736842105</v>
       </c>
       <c r="O45" s="16">
-        <v>871</v>
+        <v>798</v>
       </c>
       <c r="P45" s="17">
-        <v>1010.3599999999999</v>
+        <v>925.68</v>
       </c>
       <c r="Q45" s="14">
-        <v>21.186486486486483</v>
+        <v>18.580882352941178</v>
       </c>
       <c r="R45" s="16">
-        <v>904.44444444444457</v>
+        <v>944.84210526315792</v>
       </c>
       <c r="S45" s="15">
-        <v>48.777777777777715</v>
+        <v>-60.947368421052602</v>
       </c>
       <c r="T45" s="18">
-        <v>1368</v>
+        <v>1325</v>
       </c>
       <c r="U45" s="17">
-        <v>1586.8799999999999</v>
+        <v>1537</v>
       </c>
       <c r="V45" s="14">
-        <v>14.527433628318581</v>
+        <v>13.862885462555067</v>
       </c>
       <c r="W45" s="16">
-        <v>2071.666666666667</v>
+        <v>2102.7368421052633</v>
       </c>
       <c r="X45" s="15">
-        <v>-138.66666666666697</v>
+        <v>-204.26315789473688</v>
       </c>
       <c r="Y45" s="18">
-        <v>489</v>
+        <v>50</v>
       </c>
       <c r="Z45" s="17">
-        <v>567.24</v>
+        <v>57.999999999999993</v>
       </c>
       <c r="AA45" s="14">
-        <v>17.225048923679061</v>
+        <v>1.8375241779497098</v>
       </c>
       <c r="AB45" s="16">
-        <v>624.55555555555554</v>
+        <v>598.63157894736844</v>
       </c>
       <c r="AC45" s="15">
-        <v>-135.55555555555554</v>
+        <v>-548.63157894736844</v>
       </c>
       <c r="AD45" s="19">
-        <v>9522</v>
+        <v>9487</v>
       </c>
       <c r="AE45" s="20">
-        <v>11045.519999999999</v>
+        <v>11004.92</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5984,85 +5986,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>1878</v>
+        <v>2127</v>
       </c>
       <c r="F46" s="14">
-        <v>2178.48</v>
+        <v>2467.3199999999997</v>
       </c>
       <c r="G46" s="14">
-        <v>6.7473053892215571</v>
+        <v>7.5327120223671953</v>
       </c>
       <c r="H46" s="30">
-        <v>6123.333333333333</v>
+        <v>6212.1052631578941</v>
       </c>
       <c r="I46" s="15">
-        <v>-905.33333333333303</v>
+        <v>-696.68421052631584</v>
       </c>
       <c r="J46" s="16">
-        <v>2401</v>
+        <v>2812</v>
       </c>
       <c r="K46" s="13">
-        <v>2785.16</v>
+        <v>3261.9199999999996</v>
       </c>
       <c r="L46" s="14">
-        <v>14.755206555138273</v>
+        <v>17.928859060402687</v>
       </c>
       <c r="M46" s="30">
-        <v>3579.8888888888891</v>
+        <v>3450.5263157894738</v>
       </c>
       <c r="N46" s="15">
-        <v>773.77777777777783</v>
+        <v>1243.578947368421</v>
       </c>
       <c r="O46" s="16">
-        <v>570</v>
+        <v>530</v>
       </c>
       <c r="P46" s="17">
-        <v>661.19999999999993</v>
+        <v>614.79999999999995</v>
       </c>
       <c r="Q46" s="14">
-        <v>22.749445676274942</v>
+        <v>20.509164969450101</v>
       </c>
       <c r="R46" s="16">
-        <v>551.22222222222229</v>
+        <v>568.52631578947364</v>
       </c>
       <c r="S46" s="15">
-        <v>68.888888888888857</v>
+        <v>13.157894736842081</v>
       </c>
       <c r="T46" s="18">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="U46" s="17">
-        <v>771.4</v>
+        <v>760.95999999999992</v>
       </c>
       <c r="V46" s="14">
-        <v>16.859154929577464</v>
+        <v>16.797843665768195</v>
       </c>
       <c r="W46" s="16">
-        <v>867.77777777777771</v>
+        <v>859.15789473684208</v>
       </c>
       <c r="X46" s="15">
-        <v>33.888888888888914</v>
+        <v>31.157894736842081</v>
       </c>
       <c r="Y46" s="18">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="17">
-        <v>626.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="14">
-        <v>22.8169014084507</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="16">
-        <v>520.66666666666674</v>
+        <v>493.26315789473688</v>
       </c>
       <c r="AC46" s="15">
-        <v>19.333333333333258</v>
+        <v>-493.26315789473688</v>
       </c>
       <c r="AD46" s="19">
-        <v>6054</v>
+        <v>6125</v>
       </c>
       <c r="AE46" s="20">
-        <v>7022.6399999999994</v>
+        <v>7104.9999999999991</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6110,19 +6112,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K47" s="13">
-        <v>18</v>
+        <v>378</v>
       </c>
       <c r="L47" s="14">
-        <v>0.31034482758620691</v>
+        <v>6.8793103448275854</v>
       </c>
       <c r="M47" s="30">
-        <v>70.888888888888886</v>
+        <v>67.15789473684211</v>
       </c>
       <c r="N47" s="15">
-        <v>-31.222222222222221</v>
+        <v>-9.526315789473685</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6146,13 +6148,13 @@
         <v>288</v>
       </c>
       <c r="V47" s="14">
-        <v>15.157894736842104</v>
+        <v>15.200000000000001</v>
       </c>
       <c r="W47" s="16">
-        <v>23.222222222222221</v>
+        <v>23.157894736842103</v>
       </c>
       <c r="X47" s="15">
-        <v>-0.88888888888888928</v>
+        <v>-0.8421052631578938</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6170,10 +6172,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="AE47" s="20">
-        <v>306</v>
+        <v>666</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6227,13 +6229,13 @@
         <v>108</v>
       </c>
       <c r="L48" s="14">
-        <v>9.8181818181818166</v>
+        <v>10.363636363636363</v>
       </c>
       <c r="M48" s="30">
-        <v>13.444444444444446</v>
+        <v>12.736842105263158</v>
       </c>
       <c r="N48" s="15">
-        <v>-0.1111111111111116</v>
+        <v>0.21052631578947345</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6319,64 +6321,64 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F49" s="14">
-        <v>91.64</v>
+        <v>48.72</v>
       </c>
       <c r="G49" s="14">
-        <v>1.4205794205794204</v>
+        <v>0.78620689655172404</v>
       </c>
       <c r="H49" s="30">
-        <v>1223.4444444444446</v>
+        <v>1175.2631578947369</v>
       </c>
       <c r="I49" s="15">
-        <v>-477.11111111111109</v>
+        <v>-492.21052631578948</v>
       </c>
       <c r="J49" s="16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K49" s="13">
-        <v>0</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="L49" s="14">
-        <v>0</v>
+        <v>0.47457627118644069</v>
       </c>
       <c r="M49" s="30">
-        <v>1370.1111111111111</v>
+        <v>1298</v>
       </c>
       <c r="N49" s="15">
-        <v>-622.77777777777783</v>
+        <v>-562</v>
       </c>
       <c r="O49" s="16">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P49" s="17">
-        <v>47.559999999999995</v>
+        <v>44.08</v>
       </c>
       <c r="Q49" s="14">
-        <v>5.5074626865671643</v>
+        <v>4.8456375838926178</v>
       </c>
       <c r="R49" s="16">
-        <v>163.77777777777777</v>
+        <v>172.52631578947367</v>
       </c>
       <c r="S49" s="15">
-        <v>-107.88888888888889</v>
+        <v>-118.84210526315786</v>
       </c>
       <c r="T49" s="18">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="U49" s="17">
-        <v>26.68</v>
+        <v>5.8</v>
       </c>
       <c r="V49" s="14">
-        <v>1.7999999999999998</v>
+        <v>0.41304347826086951</v>
       </c>
       <c r="W49" s="16">
-        <v>281.11111111111114</v>
+        <v>266.31578947368422</v>
       </c>
       <c r="X49" s="15">
-        <v>-181.44444444444446</v>
+        <v>-188.68421052631581</v>
       </c>
       <c r="Y49" s="18">
         <v>24</v>
@@ -6385,19 +6387,19 @@
         <v>27.839999999999996</v>
       </c>
       <c r="AA49" s="14">
-        <v>4.8</v>
+        <v>5.0666666666666673</v>
       </c>
       <c r="AB49" s="16">
-        <v>110</v>
+        <v>104.21052631578947</v>
       </c>
       <c r="AC49" s="15">
-        <v>-86</v>
+        <v>-80.210526315789465</v>
       </c>
       <c r="AD49" s="19">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="AE49" s="20">
-        <v>193.72</v>
+        <v>158.91999999999999</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6432,85 +6434,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>540</v>
+        <v>1557</v>
       </c>
       <c r="F50" s="14">
-        <v>626.4</v>
+        <v>1806.12</v>
       </c>
       <c r="G50" s="14">
-        <v>1.8822618125484119</v>
+        <v>5.4530875576036859</v>
       </c>
       <c r="H50" s="30">
-        <v>6311.5555555555566</v>
+        <v>6281.5789473684217</v>
       </c>
       <c r="I50" s="15">
-        <v>-2328.8888888888891</v>
+        <v>-1298.2631578947371</v>
       </c>
       <c r="J50" s="16">
-        <v>3666</v>
+        <v>2726</v>
       </c>
       <c r="K50" s="13">
-        <v>4252.5599999999995</v>
+        <v>3162.16</v>
       </c>
       <c r="L50" s="14">
-        <v>19.300380228136881</v>
+        <v>15.060773480662984</v>
       </c>
       <c r="M50" s="30">
-        <v>4178.7777777777783</v>
+        <v>3982</v>
       </c>
       <c r="N50" s="15">
-        <v>1766.5555555555554</v>
+        <v>916</v>
       </c>
       <c r="O50" s="16">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="P50" s="17">
-        <v>219.23999999999998</v>
+        <v>199.51999999999998</v>
       </c>
       <c r="Q50" s="14">
-        <v>4.4763157894736842</v>
+        <v>4.0196801968019678</v>
       </c>
       <c r="R50" s="16">
-        <v>928.88888888888891</v>
+        <v>941.36842105263156</v>
       </c>
       <c r="S50" s="15">
-        <v>-655.44444444444446</v>
+        <v>-683.78947368421052</v>
       </c>
       <c r="T50" s="18">
-        <v>670</v>
+        <v>607</v>
       </c>
       <c r="U50" s="17">
-        <v>777.19999999999993</v>
+        <v>704.12</v>
       </c>
       <c r="V50" s="14">
-        <v>18.582434514637903</v>
+        <v>15.43908969210174</v>
       </c>
       <c r="W50" s="16">
-        <v>793.22222222222229</v>
+        <v>864.94736842105272</v>
       </c>
       <c r="X50" s="15">
-        <v>93.111111111111086</v>
+        <v>-22.052631578947398</v>
       </c>
       <c r="Y50" s="18">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z50" s="17">
-        <v>34.799999999999997</v>
+        <v>31.319999999999997</v>
       </c>
       <c r="AA50" s="14">
-        <v>2.5714285714285721</v>
+        <v>2.408450704225352</v>
       </c>
       <c r="AB50" s="16">
-        <v>256.66666666666663</v>
+        <v>246.63157894736844</v>
       </c>
       <c r="AC50" s="15">
-        <v>-226.66666666666663</v>
+        <v>-219.63157894736844</v>
       </c>
       <c r="AD50" s="19">
-        <v>5095</v>
+        <v>5089</v>
       </c>
       <c r="AE50" s="20">
-        <v>5910.2</v>
+        <v>5903.24</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6548,34 +6550,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>547</v>
+        <v>919</v>
       </c>
       <c r="F51" s="14">
-        <v>634.52</v>
+        <v>1066.04</v>
       </c>
       <c r="G51" s="14">
-        <v>2.832566168009206</v>
+        <v>4.9006455234353075</v>
       </c>
       <c r="H51" s="30">
-        <v>4248.4444444444443</v>
+        <v>4125.5789473684208</v>
       </c>
       <c r="I51" s="15">
-        <v>-1384.1111111111111</v>
+        <v>-956.26315789473665</v>
       </c>
       <c r="J51" s="16">
-        <v>2533</v>
+        <v>2307</v>
       </c>
       <c r="K51" s="13">
-        <v>2938.2799999999997</v>
+        <v>2676.12</v>
       </c>
       <c r="L51" s="14">
-        <v>14.736263736263737</v>
+        <v>14.103281853281855</v>
       </c>
       <c r="M51" s="30">
-        <v>3781.5555555555557</v>
+        <v>3598.7368421052629</v>
       </c>
       <c r="N51" s="15">
-        <v>814.11111111111109</v>
+        <v>671.21052631578959</v>
       </c>
       <c r="O51" s="16">
         <v>258</v>
@@ -6584,49 +6586,49 @@
         <v>299.27999999999997</v>
       </c>
       <c r="Q51" s="14">
-        <v>17.861538461538462</v>
+        <v>18.638783269961976</v>
       </c>
       <c r="R51" s="16">
-        <v>317.77777777777777</v>
+        <v>304.5263157894737</v>
       </c>
       <c r="S51" s="15">
-        <v>-30.888888888888914</v>
+        <v>-18.842105263157919</v>
       </c>
       <c r="T51" s="18">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="U51" s="17">
-        <v>569.55999999999995</v>
+        <v>542.88</v>
       </c>
       <c r="V51" s="14">
-        <v>14.277867528271408</v>
+        <v>13.722222222222221</v>
       </c>
       <c r="W51" s="16">
-        <v>756.55555555555543</v>
+        <v>750.31578947368428</v>
       </c>
       <c r="X51" s="15">
-        <v>-59.222222222222172</v>
+        <v>-77.684210526315837</v>
       </c>
       <c r="Y51" s="18">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="Z51" s="17">
-        <v>153.11999999999998</v>
+        <v>90.47999999999999</v>
       </c>
       <c r="AA51" s="14">
-        <v>30.075949367088604</v>
+        <v>18.759493670886076</v>
       </c>
       <c r="AB51" s="16">
-        <v>96.555555555555571</v>
+        <v>91.473684210526315</v>
       </c>
       <c r="AC51" s="15">
-        <v>35.444444444444429</v>
+        <v>-13.473684210526315</v>
       </c>
       <c r="AD51" s="19">
-        <v>3961</v>
+        <v>4030</v>
       </c>
       <c r="AE51" s="20">
-        <v>4594.7599999999993</v>
+        <v>4674.7999999999993</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6665,85 +6667,85 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>2195</v>
+        <v>2022</v>
       </c>
       <c r="F52" s="14">
-        <v>1777.95</v>
+        <v>1637.8200000000002</v>
       </c>
       <c r="G52" s="14">
-        <v>14.005671747607231</v>
+        <v>12.844533600802405</v>
       </c>
       <c r="H52" s="30">
-        <v>3447.8888888888891</v>
+        <v>3463.2631578947371</v>
       </c>
       <c r="I52" s="15">
-        <v>627.77777777777783</v>
+        <v>447.78947368421041</v>
       </c>
       <c r="J52" s="16">
-        <v>694</v>
+        <v>4628</v>
       </c>
       <c r="K52" s="13">
-        <v>562.14</v>
+        <v>3748.6800000000003</v>
       </c>
       <c r="L52" s="14">
-        <v>14.276571428571428</v>
+        <v>97.919821826280611</v>
       </c>
       <c r="M52" s="30">
-        <v>1069.4444444444446</v>
+        <v>1039.7894736842106</v>
       </c>
       <c r="N52" s="15">
-        <v>207.88888888888886</v>
+        <v>4155.3684210526317</v>
       </c>
       <c r="O52" s="16">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="P52" s="17">
-        <v>126.36000000000001</v>
+        <v>110.97000000000001</v>
       </c>
       <c r="Q52" s="14">
-        <v>24</v>
+        <v>19.139705882352938</v>
       </c>
       <c r="R52" s="16">
-        <v>143</v>
+        <v>157.47368421052633</v>
       </c>
       <c r="S52" s="15">
-        <v>26</v>
+        <v>-6.1578947368421382</v>
       </c>
       <c r="T52" s="18">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="U52" s="17">
-        <v>315.90000000000003</v>
+        <v>301.32</v>
       </c>
       <c r="V52" s="14">
-        <v>19.180327868852459</v>
+        <v>17.582089552238806</v>
       </c>
       <c r="W52" s="16">
-        <v>447.33333333333331</v>
+        <v>465.47368421052636</v>
       </c>
       <c r="X52" s="15">
-        <v>64.666666666666686</v>
+        <v>33.473684210526301</v>
       </c>
       <c r="Y52" s="18">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="17">
-        <v>97.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="14">
-        <v>93.913043478260875</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="16">
-        <v>28.111111111111107</v>
+        <v>26.631578947368421</v>
       </c>
       <c r="AC52" s="15">
-        <v>91.888888888888886</v>
+        <v>-26.631578947368421</v>
       </c>
       <c r="AD52" s="19">
-        <v>3555</v>
+        <v>7159</v>
       </c>
       <c r="AE52" s="20">
-        <v>2879.55</v>
+        <v>5798.79</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6778,85 +6780,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>383</v>
+        <v>573</v>
       </c>
       <c r="F53" s="14">
-        <v>310.23</v>
+        <v>464.13000000000005</v>
       </c>
       <c r="G53" s="14">
-        <v>1.3713944698627412</v>
+        <v>2.030020510908074</v>
       </c>
       <c r="H53" s="30">
-        <v>6144.1111111111113</v>
+        <v>6209.78947368421</v>
       </c>
       <c r="I53" s="15">
-        <v>-2409.7777777777778</v>
+        <v>-2249.6315789473683</v>
       </c>
       <c r="J53" s="16">
-        <v>141</v>
+        <v>733</v>
       </c>
       <c r="K53" s="13">
-        <v>114.21000000000001</v>
+        <v>593.73</v>
       </c>
       <c r="L53" s="14">
-        <v>1.0963282937365011</v>
+        <v>5.9263829787234039</v>
       </c>
       <c r="M53" s="30">
-        <v>2829.4444444444443</v>
+        <v>2721.0526315789475</v>
       </c>
       <c r="N53" s="15">
-        <v>-1145.1111111111111</v>
+        <v>-503.84210526315792</v>
       </c>
       <c r="O53" s="16">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="P53" s="17">
-        <v>453.6</v>
+        <v>445.50000000000006</v>
       </c>
       <c r="Q53" s="14">
-        <v>21.401273885350314</v>
+        <v>20.37037037037037</v>
       </c>
       <c r="R53" s="16">
-        <v>575.66666666666674</v>
+        <v>594</v>
       </c>
       <c r="S53" s="15">
-        <v>36.666666666666515</v>
+        <v>10</v>
       </c>
       <c r="T53" s="18">
-        <v>848</v>
+        <v>808</v>
       </c>
       <c r="U53" s="17">
-        <v>686.88</v>
+        <v>654.48</v>
       </c>
       <c r="V53" s="14">
-        <v>16.773626373626374</v>
+        <v>15.475806451612904</v>
       </c>
       <c r="W53" s="16">
-        <v>1112.2222222222222</v>
+        <v>1148.6315789473683</v>
       </c>
       <c r="X53" s="15">
-        <v>39.1111111111112</v>
+        <v>-27.368421052631561</v>
       </c>
       <c r="Y53" s="18">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="17">
-        <v>194.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" s="14">
-        <v>36.30252100840336</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="16">
-        <v>145.44444444444443</v>
+        <v>137.78947368421052</v>
       </c>
       <c r="AC53" s="15">
-        <v>94.555555555555571</v>
+        <v>-137.78947368421052</v>
       </c>
       <c r="AD53" s="19">
-        <v>2172</v>
+        <v>2664</v>
       </c>
       <c r="AE53" s="20">
-        <v>1759.3200000000002</v>
+        <v>2157.84</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6891,49 +6893,49 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>2260</v>
+        <v>1994</v>
       </c>
       <c r="F54" s="14">
-        <v>1830.6000000000001</v>
+        <v>1615.14</v>
       </c>
       <c r="G54" s="14">
-        <v>11.815277374382804</v>
+        <v>10.111022151054176</v>
       </c>
       <c r="H54" s="30">
-        <v>4208.1111111111113</v>
+        <v>4338.6315789473683</v>
       </c>
       <c r="I54" s="15">
-        <v>347.22222222222194</v>
+        <v>21.894736842105203</v>
       </c>
       <c r="J54" s="16">
-        <v>3308</v>
+        <v>4221</v>
       </c>
       <c r="K54" s="13">
-        <v>2679.48</v>
+        <v>3419.01</v>
       </c>
       <c r="L54" s="14">
-        <v>52.507936507936506</v>
+        <v>69.981675392670155</v>
       </c>
       <c r="M54" s="30">
-        <v>1386</v>
+        <v>1326.9473684210527</v>
       </c>
       <c r="N54" s="15">
-        <v>2678</v>
+        <v>3617.8421052631579</v>
       </c>
       <c r="O54" s="16">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="P54" s="17">
-        <v>193.59</v>
+        <v>187.11</v>
       </c>
       <c r="Q54" s="14">
-        <v>19.378378378378375</v>
+        <v>18.287500000000001</v>
       </c>
       <c r="R54" s="16">
-        <v>271.33333333333337</v>
+        <v>277.89473684210526</v>
       </c>
       <c r="S54" s="15">
-        <v>-7.666666666666714</v>
+        <v>-21.631578947368439</v>
       </c>
       <c r="T54" s="18">
         <v>467</v>
@@ -6942,34 +6944,34 @@
         <v>378.27000000000004</v>
       </c>
       <c r="V54" s="14">
-        <v>20.110047846889952</v>
+        <v>19.939325842696629</v>
       </c>
       <c r="W54" s="16">
-        <v>510.88888888888886</v>
+        <v>515.26315789473688</v>
       </c>
       <c r="X54" s="15">
-        <v>95.444444444444457</v>
+        <v>92.263157894736821</v>
       </c>
       <c r="Y54" s="18">
-        <v>211</v>
+        <v>91</v>
       </c>
       <c r="Z54" s="17">
-        <v>170.91000000000003</v>
+        <v>73.710000000000008</v>
       </c>
       <c r="AA54" s="14">
-        <v>24.037974683544302</v>
+        <v>10.943037974683545</v>
       </c>
       <c r="AB54" s="16">
-        <v>193.11111111111114</v>
+        <v>182.94736842105263</v>
       </c>
       <c r="AC54" s="15">
-        <v>17.888888888888857</v>
+        <v>-91.94736842105263</v>
       </c>
       <c r="AD54" s="19">
-        <v>6485</v>
+        <v>7004</v>
       </c>
       <c r="AE54" s="20">
-        <v>5252.85</v>
+        <v>5673.2400000000007</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7004,85 +7006,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>2196</v>
+        <v>2100</v>
       </c>
       <c r="F55" s="14">
-        <v>1778.7600000000002</v>
+        <v>1701</v>
       </c>
       <c r="G55" s="14">
-        <v>12.888164329964134</v>
+        <v>12.186927306047647</v>
       </c>
       <c r="H55" s="30">
-        <v>3748.5555555555557</v>
+        <v>3790.9473684210529</v>
       </c>
       <c r="I55" s="15">
-        <v>492.11111111111109</v>
+        <v>376.84210526315792</v>
       </c>
       <c r="J55" s="16">
-        <v>6276</v>
+        <v>6796</v>
       </c>
       <c r="K55" s="13">
-        <v>5083.5600000000004</v>
+        <v>5504.76</v>
       </c>
       <c r="L55" s="14">
-        <v>80.576319543509271</v>
+        <v>90.044630404463035</v>
       </c>
       <c r="M55" s="30">
-        <v>1713.5555555555554</v>
+        <v>1660.421052631579</v>
       </c>
       <c r="N55" s="15">
-        <v>5497.1111111111113</v>
+        <v>6041.2631578947367</v>
       </c>
       <c r="O55" s="16">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P55" s="17">
-        <v>284.31</v>
+        <v>281.88</v>
       </c>
       <c r="Q55" s="14">
-        <v>20.25</v>
+        <v>20.344615384615384</v>
       </c>
       <c r="R55" s="16">
-        <v>381.33333333333331</v>
+        <v>376.31578947368422</v>
       </c>
       <c r="S55" s="15">
-        <v>4.3333333333333712</v>
+        <v>5.8947368421052602</v>
       </c>
       <c r="T55" s="18">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="U55" s="17">
-        <v>380.70000000000005</v>
+        <v>375.84000000000003</v>
       </c>
       <c r="V55" s="14">
-        <v>18.391304347826086</v>
+        <v>18.32848232848233</v>
       </c>
       <c r="W55" s="16">
-        <v>562.22222222222229</v>
+        <v>556.9473684210526</v>
       </c>
       <c r="X55" s="15">
-        <v>61.111111111111086</v>
+        <v>58.947368421052659</v>
       </c>
       <c r="Y55" s="18">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="Z55" s="17">
-        <v>182.25</v>
+        <v>85.050000000000011</v>
       </c>
       <c r="AA55" s="14">
-        <v>25.155279503105589</v>
+        <v>12.391304347826088</v>
       </c>
       <c r="AB55" s="16">
-        <v>196.77777777777777</v>
+        <v>186.42105263157893</v>
       </c>
       <c r="AC55" s="15">
-        <v>28.222222222222229</v>
+        <v>-81.421052631578931</v>
       </c>
       <c r="AD55" s="19">
-        <v>9518</v>
+        <v>9813</v>
       </c>
       <c r="AE55" s="20">
-        <v>7709.5800000000008</v>
+        <v>7948.5300000000007</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7117,64 +7119,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F56" s="14">
-        <v>822.68000000000006</v>
+        <v>809.58</v>
       </c>
       <c r="G56" s="14">
-        <v>9.8638743455497391</v>
+        <v>10.157439446366782</v>
       </c>
       <c r="H56" s="30">
-        <v>700.33333333333326</v>
+        <v>669.26315789473688</v>
       </c>
       <c r="I56" s="15">
-        <v>-4.3333333333332575</v>
+        <v>4.7894736842105203</v>
       </c>
       <c r="J56" s="32">
-        <v>121</v>
+        <v>311</v>
       </c>
       <c r="K56" s="13">
-        <v>317.02000000000004</v>
+        <v>814.82</v>
       </c>
       <c r="L56" s="14">
-        <v>9.1129707112970699</v>
+        <v>24.118367346938779</v>
       </c>
       <c r="M56" s="30">
-        <v>292.11111111111114</v>
+        <v>283.68421052631578</v>
       </c>
       <c r="N56" s="15">
-        <v>-11.777777777777771</v>
+        <v>182.05263157894737</v>
       </c>
       <c r="O56" s="32">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P56" s="17">
-        <v>144.1</v>
+        <v>141.48000000000002</v>
       </c>
       <c r="Q56" s="14">
-        <v>20.625</v>
+        <v>21.375</v>
       </c>
       <c r="R56" s="16">
-        <v>58.666666666666664</v>
+        <v>55.578947368421048</v>
       </c>
       <c r="S56" s="15">
-        <v>1.6666666666666714</v>
+        <v>3.473684210526315</v>
       </c>
       <c r="T56" s="18">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="U56" s="17">
-        <v>330.12</v>
+        <v>298.68</v>
       </c>
       <c r="V56" s="14">
-        <v>18.439024390243905</v>
+        <v>15.361702127659573</v>
       </c>
       <c r="W56" s="16">
-        <v>150.33333333333331</v>
+        <v>163.26315789473685</v>
       </c>
       <c r="X56" s="15">
-        <v>16.666666666666686</v>
+        <v>-4.7368421052631646</v>
       </c>
       <c r="Y56" s="18">
         <v>45</v>
@@ -7183,19 +7185,19 @@
         <v>117.9</v>
       </c>
       <c r="AA56" s="14">
-        <v>26.129032258064516</v>
+        <v>27.580645161290324</v>
       </c>
       <c r="AB56" s="16">
-        <v>37.888888888888893</v>
+        <v>35.89473684210526</v>
       </c>
       <c r="AC56" s="15">
-        <v>7.1111111111111072</v>
+        <v>9.1052631578947398</v>
       </c>
       <c r="AD56" s="19">
-        <v>661</v>
+        <v>833</v>
       </c>
       <c r="AE56" s="20">
-        <v>1731.8200000000002</v>
+        <v>2182.46</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7230,34 +7232,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="F57" s="14">
-        <v>599.98</v>
+        <v>461.12</v>
       </c>
       <c r="G57" s="14">
-        <v>3.3241935483870968</v>
+        <v>2.694601128122482</v>
       </c>
       <c r="H57" s="30">
-        <v>1515.5555555555554</v>
+        <v>1436.9473684210525</v>
       </c>
       <c r="I57" s="15">
-        <v>-459.88888888888891</v>
+        <v>-477.15789473684208</v>
       </c>
       <c r="J57" s="32">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="K57" s="13">
-        <v>89.08</v>
+        <v>421.82</v>
       </c>
       <c r="L57" s="14">
-        <v>1.1657142857142855</v>
+        <v>5.7826086956521738</v>
       </c>
       <c r="M57" s="30">
-        <v>641.66666666666674</v>
+        <v>612.52631578947364</v>
       </c>
       <c r="N57" s="15">
-        <v>-257.66666666666674</v>
+        <v>-117.42105263157896</v>
       </c>
       <c r="O57" s="32">
         <v>105</v>
@@ -7266,13 +7268,13 @@
         <v>275.10000000000002</v>
       </c>
       <c r="Q57" s="14">
-        <v>17.181818181818183</v>
+        <v>18.136363636363637</v>
       </c>
       <c r="R57" s="16">
-        <v>134.44444444444443</v>
+        <v>127.36842105263159</v>
       </c>
       <c r="S57" s="15">
-        <v>-17.222222222222214</v>
+        <v>-10.789473684210535</v>
       </c>
       <c r="T57" s="18">
         <v>120</v>
@@ -7281,13 +7283,13 @@
         <v>314.40000000000003</v>
       </c>
       <c r="V57" s="14">
-        <v>6.5060240963855431</v>
+        <v>6.8674698795180724</v>
       </c>
       <c r="W57" s="16">
-        <v>405.77777777777771</v>
+        <v>384.42105263157896</v>
       </c>
       <c r="X57" s="15">
-        <v>-175.11111111111109</v>
+        <v>-159.57894736842104</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7296,19 +7298,19 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>33.75</v>
+        <v>35.625</v>
       </c>
       <c r="AB57" s="16">
-        <v>39.111111111111107</v>
+        <v>37.05263157894737</v>
       </c>
       <c r="AC57" s="15">
-        <v>20.888888888888893</v>
+        <v>22.94736842105263</v>
       </c>
       <c r="AD57" s="19">
-        <v>548</v>
+        <v>622</v>
       </c>
       <c r="AE57" s="20">
-        <v>1435.76</v>
+        <v>1629.64</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7343,34 +7345,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F58" s="14">
-        <v>220.08</v>
+        <v>188.64000000000001</v>
       </c>
       <c r="G58" s="14">
-        <v>3.2869565217391301</v>
+        <v>2.9739130434782606</v>
       </c>
       <c r="H58" s="30">
-        <v>562.22222222222229</v>
+        <v>532.63157894736844</v>
       </c>
       <c r="I58" s="15">
-        <v>-171.55555555555557</v>
+        <v>-170.10526315789477</v>
       </c>
       <c r="J58" s="32">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="K58" s="13">
-        <v>151.96</v>
+        <v>324.88</v>
       </c>
       <c r="L58" s="14">
-        <v>6.2142857142857135</v>
+        <v>14.023809523809522</v>
       </c>
       <c r="M58" s="30">
-        <v>205.33333333333334</v>
+        <v>194.5263157894737</v>
       </c>
       <c r="N58" s="15">
-        <v>-35.333333333333343</v>
+        <v>35.578947368421041</v>
       </c>
       <c r="O58" s="32">
         <v>25</v>
@@ -7379,13 +7381,13 @@
         <v>65.5</v>
       </c>
       <c r="Q58" s="14">
-        <v>14.0625</v>
+        <v>14.843749999999998</v>
       </c>
       <c r="R58" s="16">
-        <v>39.111111111111107</v>
+        <v>37.05263157894737</v>
       </c>
       <c r="S58" s="15">
-        <v>-10.555555555555557</v>
+        <v>-8.6842105263157947</v>
       </c>
       <c r="T58" s="18">
         <v>100</v>
@@ -7394,13 +7396,13 @@
         <v>262</v>
       </c>
       <c r="V58" s="14">
-        <v>19.35483870967742</v>
+        <v>19.191919191919194</v>
       </c>
       <c r="W58" s="16">
-        <v>113.66666666666667</v>
+        <v>114.63157894736841</v>
       </c>
       <c r="X58" s="15">
-        <v>17.333333333333329</v>
+        <v>16.631578947368425</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7409,19 +7411,19 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>28</v>
+        <v>29.555555555555557</v>
       </c>
       <c r="AB58" s="16">
-        <v>33</v>
+        <v>31.263157894736842</v>
       </c>
       <c r="AC58" s="15">
-        <v>9</v>
+        <v>10.736842105263158</v>
       </c>
       <c r="AD58" s="19">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="AE58" s="20">
-        <v>809.58</v>
+        <v>951.06000000000006</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7459,34 +7461,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="F59" s="14">
-        <v>419.20000000000005</v>
+        <v>377.28000000000003</v>
       </c>
       <c r="G59" s="14">
-        <v>4.816053511705686</v>
+        <v>4.5752508361204018</v>
       </c>
       <c r="H59" s="30">
-        <v>730.88888888888891</v>
+        <v>692.42105263157896</v>
       </c>
       <c r="I59" s="15">
-        <v>-172.22222222222223</v>
+        <v>-170.73684210526312</v>
       </c>
       <c r="J59" s="32">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="K59" s="13">
-        <v>104.80000000000001</v>
+        <v>571.16</v>
       </c>
       <c r="L59" s="14">
-        <v>3.4285714285714293</v>
+        <v>19.630331753554504</v>
       </c>
       <c r="M59" s="30">
-        <v>256.66666666666663</v>
+        <v>244.31578947368419</v>
       </c>
       <c r="N59" s="15">
-        <v>-76.666666666666643</v>
+        <v>106.94736842105263</v>
       </c>
       <c r="O59" s="32">
         <v>38</v>
@@ -7495,28 +7497,28 @@
         <v>99.56</v>
       </c>
       <c r="Q59" s="14">
-        <v>13.411764705882351</v>
+        <v>14.15686274509804</v>
       </c>
       <c r="R59" s="16">
-        <v>62.333333333333336</v>
+        <v>59.05263157894737</v>
       </c>
       <c r="S59" s="15">
-        <v>-18.666666666666671</v>
+        <v>-15.684210526315788</v>
       </c>
       <c r="T59" s="18">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="U59" s="17">
-        <v>298.68</v>
+        <v>290.82</v>
       </c>
       <c r="V59" s="14">
-        <v>20.117647058823529</v>
+        <v>18.025641025641022</v>
       </c>
       <c r="W59" s="16">
-        <v>124.66666666666667</v>
+        <v>135.47368421052633</v>
       </c>
       <c r="X59" s="15">
-        <v>23.333333333333329</v>
+        <v>12.473684210526301</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7525,19 +7527,19 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>63.599999999999987</v>
+        <v>67.133333333333326</v>
       </c>
       <c r="AB59" s="16">
-        <v>18.333333333333336</v>
+        <v>17.368421052631579</v>
       </c>
       <c r="AC59" s="15">
-        <v>34.666666666666664</v>
+        <v>35.631578947368425</v>
       </c>
       <c r="AD59" s="19">
-        <v>405</v>
+        <v>564</v>
       </c>
       <c r="AE59" s="20">
-        <v>1061.1000000000001</v>
+        <v>1477.68</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7611,10 +7613,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7644,17 +7646,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>146949.73000000007</v>
+        <v>152319.97</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>31.805473083743799</v>
+        <v>28.931135640366456</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7692,11 +7694,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>197489.34999999989</v>
+        <v>274466.88</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>42.744156152931012</v>
+        <v>52.131303164438542</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7734,11 +7736,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>35265.999999999978</v>
+        <v>30462.32</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>7.6328946897099259</v>
+        <v>5.7859091742221844</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7776,11 +7778,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>63284.919999999984</v>
+        <v>60722.920000000006</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>13.697247485020068</v>
+        <v>11.533504339576231</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7818,11 +7820,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>18837.350000000006</v>
+        <v>8320.2099999999991</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>4.0771141831567919</v>
+        <v>1.580312312734393</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7854,19 +7856,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>462026.55</v>
-      </c>
-      <c r="E67" s="69">
+        <v>526491.50000000012</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7966,17 +7968,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>107928</v>
+        <v>113478</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>32.28989340218461</v>
+        <v>29.778390080692777</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8013,11 +8015,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>143604</v>
+        <v>198568</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>42.963437218583863</v>
+        <v>52.107327953814867</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8055,11 +8057,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>25199</v>
+        <v>21575</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>7.539035503684401</v>
+        <v>5.6616151676179234</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8097,11 +8099,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>44355</v>
+        <v>42312</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>13.270126583035898</v>
+        <v>11.103326116906121</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8139,11 +8141,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>13161</v>
+        <v>5142</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>3.9375072925112269</v>
+        <v>1.3493406809683133</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8175,19 +8177,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>334247</v>
-      </c>
-      <c r="E75" s="69">
+        <v>381075</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8734,17 +8736,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8753,6 +8744,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42BC924-C54E-44B0-A129-7C465A19A683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B685AF-D640-455D-AC6B-052DA32295F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1657,242 +1657,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2272,19 +2272,19 @@
         <v>-4707</v>
       </c>
       <c r="J13" s="16">
-        <v>6993</v>
+        <v>6269</v>
       </c>
       <c r="K13" s="13">
-        <v>9510.4800000000014</v>
+        <v>8525.84</v>
       </c>
       <c r="L13" s="14">
-        <v>29.03562062937063</v>
+        <v>26.02950174825175</v>
       </c>
       <c r="M13" s="30">
         <v>5298.5263157894733</v>
       </c>
       <c r="N13" s="15">
-        <v>4584.5789473684217</v>
+        <v>3860.5789473684213</v>
       </c>
       <c r="O13" s="16">
         <v>922</v>
@@ -2332,10 +2332,10 @@
         <v>-662.31578947368416</v>
       </c>
       <c r="AD13" s="19">
-        <v>11602</v>
+        <v>10878</v>
       </c>
       <c r="AE13" s="20">
-        <v>15778.720000000001</v>
+        <v>14794.080000000002</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2386,19 +2386,19 @@
         <v>-245.26315789473685</v>
       </c>
       <c r="J14" s="16">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K14" s="13">
-        <v>46.11</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14">
-        <v>2.2128514056224899</v>
+        <v>0</v>
       </c>
       <c r="M14" s="30">
         <v>288.31578947368422</v>
       </c>
       <c r="N14" s="15">
-        <v>-102.05263157894737</v>
+        <v>-131.05263157894737</v>
       </c>
       <c r="O14" s="16">
         <v>88</v>
@@ -2446,10 +2446,10 @@
         <v>-64.84210526315789</v>
       </c>
       <c r="AD14" s="19">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="AE14" s="20">
-        <v>232.14000000000001</v>
+        <v>186.03</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2500,19 +2500,19 @@
         <v>-1054.5263157894733</v>
       </c>
       <c r="J15" s="16">
-        <v>2243</v>
+        <v>1386</v>
       </c>
       <c r="K15" s="13">
-        <v>4553.29</v>
+        <v>2813.58</v>
       </c>
       <c r="L15" s="14">
-        <v>20.488942307692309</v>
+        <v>12.660576923076924</v>
       </c>
       <c r="M15" s="30">
         <v>2408.4210526315787</v>
       </c>
       <c r="N15" s="15">
-        <v>1148.2631578947371</v>
+        <v>291.26315789473711</v>
       </c>
       <c r="O15" s="16">
         <v>211</v>
@@ -2560,10 +2560,10 @@
         <v>-107.63157894736844</v>
       </c>
       <c r="AD15" s="19">
-        <v>5054</v>
+        <v>4197</v>
       </c>
       <c r="AE15" s="20">
-        <v>10259.619999999999</v>
+        <v>8519.91</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2613,19 +2613,19 @@
         <v>-388.63157894736833</v>
       </c>
       <c r="J16" s="16">
-        <v>338</v>
+        <v>297</v>
       </c>
       <c r="K16" s="13">
-        <v>1220.18</v>
+        <v>1072.17</v>
       </c>
       <c r="L16" s="14">
-        <v>12.895582329317268</v>
+        <v>11.331325301204819</v>
       </c>
       <c r="M16" s="30">
         <v>576.63157894736844</v>
       </c>
       <c r="N16" s="15">
-        <v>75.89473684210526</v>
+        <v>34.89473684210526</v>
       </c>
       <c r="O16" s="16">
         <v>44</v>
@@ -2673,10 +2673,10 @@
         <v>-41</v>
       </c>
       <c r="AD16" s="19">
-        <v>770</v>
+        <v>729</v>
       </c>
       <c r="AE16" s="20">
-        <v>2779.7</v>
+        <v>2631.69</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2726,19 +2726,19 @@
         <v>-45.421052631578959</v>
       </c>
       <c r="J17" s="16">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K17" s="13">
-        <v>746.3</v>
+        <v>623.38</v>
       </c>
       <c r="L17" s="14">
-        <v>41.410256410256409</v>
+        <v>34.589743589743584</v>
       </c>
       <c r="M17" s="30">
         <v>45.15789473684211</v>
       </c>
       <c r="N17" s="15">
-        <v>64.473684210526315</v>
+        <v>50.473684210526315</v>
       </c>
       <c r="O17" s="16">
         <v>12</v>
@@ -2786,10 +2786,10 @@
         <v>-2.4210526315789469</v>
       </c>
       <c r="AD17" s="19">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="AE17" s="20">
-        <v>1527.7199999999998</v>
+        <v>1404.8</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2839,19 +2839,19 @@
         <v>-2112.4736842105267</v>
       </c>
       <c r="J18" s="16">
-        <v>8387</v>
+        <v>7215</v>
       </c>
       <c r="K18" s="13">
-        <v>5283.81</v>
+        <v>4545.45</v>
       </c>
       <c r="L18" s="14">
-        <v>25.246039290240812</v>
+        <v>21.718155893536121</v>
       </c>
       <c r="M18" s="30">
         <v>7308.6315789473683</v>
       </c>
       <c r="N18" s="15">
-        <v>5064.894736842105</v>
+        <v>3892.894736842105</v>
       </c>
       <c r="O18" s="16">
         <v>1097</v>
@@ -2899,10 +2899,10 @@
         <v>-160.68421052631578</v>
       </c>
       <c r="AD18" s="19">
-        <v>17624</v>
+        <v>16452</v>
       </c>
       <c r="AE18" s="20">
-        <v>11103.12</v>
+        <v>10364.76</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2952,19 +2952,19 @@
         <v>-307.52631578947376</v>
       </c>
       <c r="J19" s="16">
-        <v>389</v>
+        <v>121</v>
       </c>
       <c r="K19" s="13">
-        <v>245.07</v>
+        <v>76.23</v>
       </c>
       <c r="L19" s="14">
-        <v>7.0390476190476177</v>
+        <v>2.1895238095238092</v>
       </c>
       <c r="M19" s="30">
         <v>1215.7894736842106</v>
       </c>
       <c r="N19" s="15">
-        <v>-163.63157894736855</v>
+        <v>-431.63157894736855</v>
       </c>
       <c r="O19" s="16">
         <v>126</v>
@@ -3012,10 +3012,10 @@
         <v>-105.15789473684211</v>
       </c>
       <c r="AD19" s="19">
-        <v>1109</v>
+        <v>841</v>
       </c>
       <c r="AE19" s="20">
-        <v>698.67</v>
+        <v>529.83000000000004</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3065,19 +3065,19 @@
         <v>145.8947368421052</v>
       </c>
       <c r="J20" s="16">
-        <v>3765</v>
+        <v>3447</v>
       </c>
       <c r="K20" s="13">
-        <v>2371.9499999999998</v>
+        <v>2171.61</v>
       </c>
       <c r="L20" s="14">
-        <v>29.993710691823896</v>
+        <v>27.460377358490561</v>
       </c>
       <c r="M20" s="30">
         <v>2761.5789473684213</v>
       </c>
       <c r="N20" s="15">
-        <v>2509.7368421052629</v>
+        <v>2191.7368421052629</v>
       </c>
       <c r="O20" s="16">
         <v>226</v>
@@ -3125,10 +3125,10 @@
         <v>-127.94736842105266</v>
       </c>
       <c r="AD20" s="19">
-        <v>5959</v>
+        <v>5641</v>
       </c>
       <c r="AE20" s="20">
-        <v>3754.17</v>
+        <v>3553.83</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3178,19 +3178,19 @@
         <v>-1111.7894736842104</v>
       </c>
       <c r="J21" s="16">
-        <v>3125</v>
+        <v>2722</v>
       </c>
       <c r="K21" s="13">
-        <v>3406.2500000000005</v>
+        <v>2966.98</v>
       </c>
       <c r="L21" s="14">
-        <v>9.4051956280690643</v>
+        <v>8.1923015998732787</v>
       </c>
       <c r="M21" s="30">
         <v>7309.78947368421</v>
       </c>
       <c r="N21" s="15">
-        <v>-197.63157894736833</v>
+        <v>-600.63157894736833</v>
       </c>
       <c r="O21" s="16">
         <v>502</v>
@@ -3238,10 +3238,10 @@
         <v>-221.47368421052636</v>
       </c>
       <c r="AD21" s="19">
-        <v>6629</v>
+        <v>6226</v>
       </c>
       <c r="AE21" s="20">
-        <v>7225.6100000000006</v>
+        <v>6786.34</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3291,19 +3291,19 @@
         <v>-96.842105263157919</v>
       </c>
       <c r="J22" s="16">
-        <v>2811</v>
+        <v>2478</v>
       </c>
       <c r="K22" s="13">
-        <v>3063.9900000000002</v>
+        <v>2701.02</v>
       </c>
       <c r="L22" s="14">
-        <v>19.081457663451232</v>
+        <v>16.821007502679528</v>
       </c>
       <c r="M22" s="30">
         <v>3240.9473684210529</v>
       </c>
       <c r="N22" s="15">
-        <v>1337.8421052631579</v>
+        <v>1004.8421052631579</v>
       </c>
       <c r="O22" s="16">
         <v>122</v>
@@ -3351,10 +3351,10 @@
         <v>-133.31578947368419</v>
       </c>
       <c r="AD22" s="19">
-        <v>5034</v>
+        <v>4701</v>
       </c>
       <c r="AE22" s="20">
-        <v>5487.06</v>
+        <v>5124.09</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3404,19 +3404,19 @@
         <v>-5891.4736842105267</v>
       </c>
       <c r="J23" s="16">
-        <v>31144</v>
+        <v>23344</v>
       </c>
       <c r="K23" s="13">
-        <v>36127.040000000001</v>
+        <v>27079.039999999997</v>
       </c>
       <c r="L23" s="14">
-        <v>33.13933691756273</v>
+        <v>24.839605734767026</v>
       </c>
       <c r="M23" s="30">
         <v>20675.36842105263</v>
       </c>
       <c r="N23" s="15">
-        <v>21746.105263157897</v>
+        <v>13946.105263157897</v>
       </c>
       <c r="O23" s="16">
         <v>1522</v>
@@ -3464,10 +3464,10 @@
         <v>-1053.8421052631579</v>
       </c>
       <c r="AD23" s="19">
-        <v>57976</v>
+        <v>50176</v>
       </c>
       <c r="AE23" s="20">
-        <v>67252.159999999989</v>
+        <v>58204.159999999996</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3517,19 +3517,19 @@
         <v>-1111.1578947368416</v>
       </c>
       <c r="J24" s="16">
-        <v>13917</v>
+        <v>10016</v>
       </c>
       <c r="K24" s="13">
-        <v>16143.72</v>
+        <v>11618.56</v>
       </c>
       <c r="L24" s="14">
-        <v>24.196833821376281</v>
+        <v>17.414348462664716</v>
       </c>
       <c r="M24" s="30">
         <v>12653.473684210527</v>
       </c>
       <c r="N24" s="15">
-        <v>8165.4210526315792</v>
+        <v>4264.4210526315792</v>
       </c>
       <c r="O24" s="16">
         <v>1871</v>
@@ -3577,10 +3577,10 @@
         <v>-640.94736842105272</v>
       </c>
       <c r="AD24" s="19">
-        <v>29768</v>
+        <v>25867</v>
       </c>
       <c r="AE24" s="20">
-        <v>34530.879999999997</v>
+        <v>30005.719999999998</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3630,19 +3630,19 @@
         <v>-3051.21052631579</v>
       </c>
       <c r="J25" s="16">
-        <v>23666</v>
+        <v>19156</v>
       </c>
       <c r="K25" s="13">
-        <v>27452.559999999998</v>
+        <v>22220.959999999999</v>
       </c>
       <c r="L25" s="14">
-        <v>38.880587980977083</v>
+        <v>31.471162991785558</v>
       </c>
       <c r="M25" s="30">
         <v>13391.052631578948</v>
       </c>
       <c r="N25" s="15">
-        <v>17579.15789473684</v>
+        <v>13069.157894736842</v>
       </c>
       <c r="O25" s="16">
         <v>1469</v>
@@ -3690,10 +3690,10 @@
         <v>-184.36842105263156</v>
       </c>
       <c r="AD25" s="19">
-        <v>36961</v>
+        <v>32451</v>
       </c>
       <c r="AE25" s="20">
-        <v>42874.759999999995</v>
+        <v>37643.159999999996</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3743,19 +3743,19 @@
         <v>-4762.8421052631602</v>
       </c>
       <c r="J26" s="16">
-        <v>16709</v>
+        <v>12272</v>
       </c>
       <c r="K26" s="13">
-        <v>19382.439999999999</v>
+        <v>14235.519999999999</v>
       </c>
       <c r="L26" s="14">
-        <v>23.307466412157694</v>
+        <v>17.118273254533438</v>
       </c>
       <c r="M26" s="30">
         <v>15771.684210526317</v>
       </c>
       <c r="N26" s="15">
-        <v>9540.0526315789466</v>
+        <v>5103.0526315789466</v>
       </c>
       <c r="O26" s="16">
         <v>0</v>
@@ -3803,10 +3803,10 @@
         <v>-613.15789473684208</v>
       </c>
       <c r="AD26" s="19">
-        <v>37361</v>
+        <v>32924</v>
       </c>
       <c r="AE26" s="20">
-        <v>43338.759999999995</v>
+        <v>38191.839999999997</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3856,19 +3856,19 @@
         <v>-117.15789473684208</v>
       </c>
       <c r="J27" s="16">
-        <v>4761</v>
+        <v>3174</v>
       </c>
       <c r="K27" s="13">
-        <v>5522.7599999999993</v>
+        <v>3681.8399999999997</v>
       </c>
       <c r="L27" s="14">
-        <v>24.468217473627263</v>
+        <v>16.312144982418175</v>
       </c>
       <c r="M27" s="30">
         <v>4280.7368421052633</v>
       </c>
       <c r="N27" s="15">
-        <v>2815.2105263157891</v>
+        <v>1228.2105263157894</v>
       </c>
       <c r="O27" s="16">
         <v>605</v>
@@ -3916,10 +3916,10 @@
         <v>75.736842105263179</v>
       </c>
       <c r="AD27" s="19">
-        <v>10646</v>
+        <v>9059</v>
       </c>
       <c r="AE27" s="20">
-        <v>12349.359999999999</v>
+        <v>10508.439999999999</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3969,19 +3969,19 @@
         <v>-228.42105263157919</v>
       </c>
       <c r="J28" s="16">
-        <v>6895</v>
+        <v>5266</v>
       </c>
       <c r="K28" s="13">
-        <v>7998.2</v>
+        <v>6108.5599999999995</v>
       </c>
       <c r="L28" s="14">
-        <v>25.149740833173357</v>
+        <v>19.207909387598388</v>
       </c>
       <c r="M28" s="30">
         <v>6031.4736842105258</v>
       </c>
       <c r="N28" s="15">
-        <v>4153.4210526315792</v>
+        <v>2524.4210526315792</v>
       </c>
       <c r="O28" s="16">
         <v>749</v>
@@ -4029,10 +4029,10 @@
         <v>-121.26315789473688</v>
       </c>
       <c r="AD28" s="19">
-        <v>12208</v>
+        <v>10579</v>
       </c>
       <c r="AE28" s="20">
-        <v>14161.279999999999</v>
+        <v>12271.64</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4082,19 +4082,19 @@
         <v>-451.36842105263167</v>
       </c>
       <c r="J29" s="16">
-        <v>1775</v>
+        <v>424</v>
       </c>
       <c r="K29" s="13">
-        <v>2059</v>
+        <v>491.84</v>
       </c>
       <c r="L29" s="14">
-        <v>6.8200202224469164</v>
+        <v>1.6291203235591507</v>
       </c>
       <c r="M29" s="30">
         <v>5725.78947368421</v>
       </c>
       <c r="N29" s="15">
-        <v>-827.63157894736833</v>
+        <v>-2178.6315789473683</v>
       </c>
       <c r="O29" s="16">
         <v>754</v>
@@ -4142,10 +4142,10 @@
         <v>-88.578947368421041</v>
       </c>
       <c r="AD29" s="19">
-        <v>7050</v>
+        <v>5699</v>
       </c>
       <c r="AE29" s="20">
-        <v>8177.9999999999991</v>
+        <v>6610.8399999999992</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4195,19 +4195,19 @@
         <v>-942.15789473684208</v>
       </c>
       <c r="J30" s="16">
-        <v>1335</v>
+        <v>1180</v>
       </c>
       <c r="K30" s="13">
-        <v>4912.8</v>
+        <v>4342.4000000000005</v>
       </c>
       <c r="L30" s="14">
-        <v>11.213527851458887</v>
+        <v>9.9115826702033605</v>
       </c>
       <c r="M30" s="30">
         <v>2619.1578947368421</v>
       </c>
       <c r="N30" s="15">
-        <v>144.47368421052624</v>
+        <v>-10.526315789473756</v>
       </c>
       <c r="O30" s="16">
         <v>124</v>
@@ -4255,10 +4255,10 @@
         <v>-107.68421052631578</v>
       </c>
       <c r="AD30" s="19">
-        <v>1948</v>
+        <v>1793</v>
       </c>
       <c r="AE30" s="20">
-        <v>7168.64</v>
+        <v>6598.2400000000007</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4308,19 +4308,19 @@
         <v>-83.263157894736878</v>
       </c>
       <c r="J31" s="16">
-        <v>1352</v>
+        <v>1280</v>
       </c>
       <c r="K31" s="13">
-        <v>4975.3600000000006</v>
+        <v>4710.4000000000005</v>
       </c>
       <c r="L31" s="14">
-        <v>20.115896632732966</v>
+        <v>19.044635865309317</v>
       </c>
       <c r="M31" s="30">
         <v>1478.6315789473686</v>
       </c>
       <c r="N31" s="15">
-        <v>679.8947368421052</v>
+        <v>607.8947368421052</v>
       </c>
       <c r="O31" s="16">
         <v>34</v>
@@ -4368,10 +4368,10 @@
         <v>16.210526315789476</v>
       </c>
       <c r="AD31" s="19">
-        <v>1974</v>
+        <v>1902</v>
       </c>
       <c r="AE31" s="20">
-        <v>7264.3200000000006</v>
+        <v>6999.3600000000006</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4421,19 +4421,19 @@
         <v>-893.21052631578914</v>
       </c>
       <c r="J32" s="16">
-        <v>4052</v>
+        <v>3396</v>
       </c>
       <c r="K32" s="13">
-        <v>16815.800000000003</v>
+        <v>14093.400000000001</v>
       </c>
       <c r="L32" s="14">
-        <v>22.603640634174983</v>
+        <v>18.944216089254258</v>
       </c>
       <c r="M32" s="30">
         <v>3943.7894736842109</v>
       </c>
       <c r="N32" s="15">
-        <v>2259.3684210526317</v>
+        <v>1603.3684210526314</v>
       </c>
       <c r="O32" s="16">
         <v>262</v>
@@ -4481,10 +4481,10 @@
         <v>194.63157894736844</v>
       </c>
       <c r="AD32" s="19">
-        <v>6995</v>
+        <v>6339</v>
       </c>
       <c r="AE32" s="20">
-        <v>29029.250000000004</v>
+        <v>26306.850000000002</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4534,19 +4534,19 @@
         <v>-1903.2631578947367</v>
       </c>
       <c r="J33" s="16">
-        <v>3710</v>
+        <v>2771</v>
       </c>
       <c r="K33" s="13">
-        <v>15396.500000000002</v>
+        <v>11499.650000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>13.767578125</v>
+        <v>10.283007812500001</v>
       </c>
       <c r="M33" s="30">
         <v>5928.4210526315783</v>
       </c>
       <c r="N33" s="15">
-        <v>1015.2631578947371</v>
+        <v>76.263157894737105</v>
       </c>
       <c r="O33" s="16">
         <v>378</v>
@@ -4594,10 +4594,10 @@
         <v>-246.78947368421052</v>
       </c>
       <c r="AD33" s="19">
-        <v>7806</v>
+        <v>6867</v>
       </c>
       <c r="AE33" s="20">
-        <v>32394.9</v>
+        <v>28498.050000000003</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4647,10 +4647,10 @@
         <v>146.42105263157896</v>
       </c>
       <c r="J34" s="16">
-        <v>433</v>
+        <v>256</v>
       </c>
       <c r="K34" s="13">
-        <v>1796.95</v>
+        <v>1062.4000000000001</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>433</v>
+        <v>256</v>
       </c>
       <c r="O34" s="16">
         <v>48</v>
@@ -4705,10 +4705,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1313</v>
+        <v>1136</v>
       </c>
       <c r="AE34" s="20">
-        <v>5448.9500000000007</v>
+        <v>4714.4000000000005</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4758,19 +4758,19 @@
         <v>-2855.894736842105</v>
       </c>
       <c r="J35" s="16">
-        <v>3957</v>
+        <v>3207</v>
       </c>
       <c r="K35" s="13">
-        <v>6449.91</v>
+        <v>5227.41</v>
       </c>
       <c r="L35" s="14">
-        <v>24.050863723608447</v>
+        <v>19.49232245681382</v>
       </c>
       <c r="M35" s="30">
         <v>3619.5789473684208</v>
       </c>
       <c r="N35" s="15">
-        <v>2311.7368421052633</v>
+        <v>1561.7368421052633</v>
       </c>
       <c r="O35" s="16">
         <v>739</v>
@@ -4818,10 +4818,10 @@
         <v>-61.947368421052659</v>
       </c>
       <c r="AD35" s="19">
-        <v>6946</v>
+        <v>6196</v>
       </c>
       <c r="AE35" s="20">
-        <v>11321.98</v>
+        <v>10099.48</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4871,19 +4871,19 @@
         <v>-2454.9473684210534</v>
       </c>
       <c r="J36" s="16">
-        <v>6299</v>
+        <v>4332</v>
       </c>
       <c r="K36" s="13">
-        <v>10267.369999999999</v>
+        <v>7061.16</v>
       </c>
       <c r="L36" s="14">
-        <v>28.094131455399062</v>
+        <v>19.321126760563381</v>
       </c>
       <c r="M36" s="30">
         <v>4932.6315789473683</v>
       </c>
       <c r="N36" s="15">
-        <v>4056.894736842105</v>
+        <v>2089.894736842105</v>
       </c>
       <c r="O36" s="16">
         <v>1678</v>
@@ -4931,10 +4931,10 @@
         <v>-355.89473684210532</v>
       </c>
       <c r="AD36" s="19">
-        <v>13456</v>
+        <v>11489</v>
       </c>
       <c r="AE36" s="20">
-        <v>21933.279999999999</v>
+        <v>18727.07</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4984,19 +4984,19 @@
         <v>-2022.3684210526317</v>
       </c>
       <c r="J37" s="16">
-        <v>1011</v>
+        <v>211</v>
       </c>
       <c r="K37" s="13">
-        <v>1647.9299999999998</v>
+        <v>343.92999999999995</v>
       </c>
       <c r="L37" s="14">
-        <v>7.4830541488118421</v>
+        <v>1.5617452278924815</v>
       </c>
       <c r="M37" s="30">
         <v>2972.3157894736842</v>
       </c>
       <c r="N37" s="15">
-        <v>-340.05263157894751</v>
+        <v>-1140.0526315789475</v>
       </c>
       <c r="O37" s="16">
         <v>1059</v>
@@ -5044,10 +5044,10 @@
         <v>-284.84210526315792</v>
       </c>
       <c r="AD37" s="19">
-        <v>3360</v>
+        <v>2560</v>
       </c>
       <c r="AE37" s="20">
-        <v>5476.7999999999993</v>
+        <v>4172.7999999999993</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5097,19 +5097,19 @@
         <v>-1414</v>
       </c>
       <c r="J38" s="16">
-        <v>4048</v>
+        <v>3441</v>
       </c>
       <c r="K38" s="13">
-        <v>6598.24</v>
+        <v>5608.83</v>
       </c>
       <c r="L38" s="14">
-        <v>35.673469387755105</v>
+        <v>30.324211502782937</v>
       </c>
       <c r="M38" s="30">
         <v>2496.4210526315787</v>
       </c>
       <c r="N38" s="15">
-        <v>2913.2631578947371</v>
+        <v>2306.2631578947371</v>
       </c>
       <c r="O38" s="16">
         <v>693</v>
@@ -5157,10 +5157,10 @@
         <v>-521.42105263157896</v>
       </c>
       <c r="AD38" s="19">
-        <v>5840</v>
+        <v>5233</v>
       </c>
       <c r="AE38" s="20">
-        <v>9519.1999999999989</v>
+        <v>8529.7899999999991</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5210,19 +5210,19 @@
         <v>65.210526315789366</v>
       </c>
       <c r="J39" s="16">
-        <v>4105</v>
+        <v>2525</v>
       </c>
       <c r="K39" s="13">
-        <v>6691.15</v>
+        <v>4115.75</v>
       </c>
       <c r="L39" s="14">
-        <v>73.999051233396585</v>
+        <v>45.517077798861479</v>
       </c>
       <c r="M39" s="30">
         <v>1220.421052631579</v>
       </c>
       <c r="N39" s="15">
-        <v>3550.2631578947367</v>
+        <v>1970.2631578947369</v>
       </c>
       <c r="O39" s="16">
         <v>613</v>
@@ -5270,10 +5270,10 @@
         <v>334.89473684210526</v>
       </c>
       <c r="AD39" s="19">
-        <v>6885</v>
+        <v>5305</v>
       </c>
       <c r="AE39" s="20">
-        <v>11222.55</v>
+        <v>8647.15</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5323,19 +5323,19 @@
         <v>-290.68421052631584</v>
       </c>
       <c r="J40" s="16">
-        <v>2802</v>
+        <v>1228</v>
       </c>
       <c r="K40" s="13">
-        <v>4567.2599999999993</v>
+        <v>2001.6399999999999</v>
       </c>
       <c r="L40" s="14">
-        <v>43.318144833197721</v>
+        <v>18.984540276647678</v>
       </c>
       <c r="M40" s="30">
         <v>1423.0526315789475</v>
       </c>
       <c r="N40" s="15">
-        <v>2155.1578947368421</v>
+        <v>581.15789473684208</v>
       </c>
       <c r="O40" s="16">
         <v>764</v>
@@ -5383,10 +5383,10 @@
         <v>340.73684210526312</v>
       </c>
       <c r="AD40" s="19">
-        <v>5809</v>
+        <v>4235</v>
       </c>
       <c r="AE40" s="20">
-        <v>9468.67</v>
+        <v>6903.0499999999993</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5436,19 +5436,19 @@
         <v>-292.73684210526312</v>
       </c>
       <c r="J41" s="16">
-        <v>984</v>
+        <v>638</v>
       </c>
       <c r="K41" s="13">
-        <v>6051.6</v>
+        <v>3923.7000000000003</v>
       </c>
       <c r="L41" s="14">
-        <v>25.471389645776568</v>
+        <v>16.514986376021799</v>
       </c>
       <c r="M41" s="30">
         <v>849.8947368421052</v>
       </c>
       <c r="N41" s="15">
-        <v>597.68421052631584</v>
+        <v>251.68421052631584</v>
       </c>
       <c r="O41" s="16">
         <v>63</v>
@@ -5496,10 +5496,10 @@
         <v>-94.94736842105263</v>
       </c>
       <c r="AD41" s="19">
-        <v>1597</v>
+        <v>1251</v>
       </c>
       <c r="AE41" s="20">
-        <v>9821.5500000000011</v>
+        <v>7693.6500000000005</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5549,19 +5549,19 @@
         <v>-434.1052631578948</v>
       </c>
       <c r="J42" s="16">
-        <v>764</v>
+        <v>632</v>
       </c>
       <c r="K42" s="13">
-        <v>4698.6000000000004</v>
+        <v>3886.8</v>
       </c>
       <c r="L42" s="14">
-        <v>18.925684485006517</v>
+        <v>15.655801825293349</v>
       </c>
       <c r="M42" s="30">
         <v>888.1052631578948</v>
       </c>
       <c r="N42" s="15">
-        <v>360.31578947368416</v>
+        <v>228.31578947368416</v>
       </c>
       <c r="O42" s="16">
         <v>117</v>
@@ -5609,10 +5609,10 @@
         <v>13.684210526315795</v>
       </c>
       <c r="AD42" s="19">
-        <v>1516</v>
+        <v>1384</v>
       </c>
       <c r="AE42" s="20">
-        <v>9323.4</v>
+        <v>8511.6</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5662,19 +5662,19 @@
         <v>-1442.0526315789475</v>
       </c>
       <c r="J43" s="16">
-        <v>3432</v>
+        <v>2476</v>
       </c>
       <c r="K43" s="13">
-        <v>3981.12</v>
+        <v>2872.16</v>
       </c>
       <c r="L43" s="14">
-        <v>14.200348432055748</v>
+        <v>10.244773519163763</v>
       </c>
       <c r="M43" s="30">
         <v>5317.0526315789475</v>
       </c>
       <c r="N43" s="15">
-        <v>1015.1578947368421</v>
+        <v>59.157894736842081</v>
       </c>
       <c r="O43" s="16">
         <v>844</v>
@@ -5722,10 +5722,10 @@
         <v>-628.78947368421052</v>
       </c>
       <c r="AD43" s="19">
-        <v>7675</v>
+        <v>6719</v>
       </c>
       <c r="AE43" s="20">
-        <v>8903</v>
+        <v>7794.0399999999991</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5775,19 +5775,19 @@
         <v>-306.10526315789502</v>
       </c>
       <c r="J44" s="16">
-        <v>3772</v>
+        <v>3207</v>
       </c>
       <c r="K44" s="13">
-        <v>4375.5199999999995</v>
+        <v>3720.12</v>
       </c>
       <c r="L44" s="14">
-        <v>20.262369239468477</v>
+        <v>17.227311280746395</v>
       </c>
       <c r="M44" s="30">
         <v>4095.4736842105262</v>
       </c>
       <c r="N44" s="15">
-        <v>1910.421052631579</v>
+        <v>1345.421052631579</v>
       </c>
       <c r="O44" s="16">
         <v>555</v>
@@ -5835,10 +5835,10 @@
         <v>-529.42105263157896</v>
       </c>
       <c r="AD44" s="19">
-        <v>7951</v>
+        <v>7386</v>
       </c>
       <c r="AE44" s="20">
-        <v>9223.16</v>
+        <v>8567.76</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5888,19 +5888,19 @@
         <v>-929.78947368421041</v>
       </c>
       <c r="J45" s="16">
-        <v>4388</v>
+        <v>3339</v>
       </c>
       <c r="K45" s="13">
-        <v>5090.08</v>
+        <v>3873.24</v>
       </c>
       <c r="L45" s="14">
-        <v>17.678541136556404</v>
+        <v>13.452290076335878</v>
       </c>
       <c r="M45" s="30">
         <v>5460.6315789473683</v>
       </c>
       <c r="N45" s="15">
-        <v>1905.894736842105</v>
+        <v>856.89473684210498</v>
       </c>
       <c r="O45" s="16">
         <v>798</v>
@@ -5948,10 +5948,10 @@
         <v>-548.63157894736844</v>
       </c>
       <c r="AD45" s="19">
-        <v>9487</v>
+        <v>8438</v>
       </c>
       <c r="AE45" s="20">
-        <v>11004.92</v>
+        <v>9788.08</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -6001,19 +6001,19 @@
         <v>-696.68421052631584</v>
       </c>
       <c r="J46" s="16">
-        <v>2812</v>
+        <v>1820</v>
       </c>
       <c r="K46" s="13">
-        <v>3261.9199999999996</v>
+        <v>2111.1999999999998</v>
       </c>
       <c r="L46" s="14">
-        <v>17.928859060402687</v>
+        <v>11.604026845637584</v>
       </c>
       <c r="M46" s="30">
         <v>3450.5263157894738</v>
       </c>
       <c r="N46" s="15">
-        <v>1243.578947368421</v>
+        <v>251.57894736842104</v>
       </c>
       <c r="O46" s="16">
         <v>530</v>
@@ -6061,10 +6061,10 @@
         <v>-493.26315789473688</v>
       </c>
       <c r="AD46" s="19">
-        <v>6125</v>
+        <v>5133</v>
       </c>
       <c r="AE46" s="20">
-        <v>7104.9999999999991</v>
+        <v>5954.28</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6336,19 +6336,19 @@
         <v>-492.21052631578948</v>
       </c>
       <c r="J49" s="16">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K49" s="13">
-        <v>32.479999999999997</v>
+        <v>5.8</v>
       </c>
       <c r="L49" s="14">
-        <v>0.47457627118644069</v>
+        <v>8.4745762711864403E-2</v>
       </c>
       <c r="M49" s="30">
         <v>1298</v>
       </c>
       <c r="N49" s="15">
-        <v>-562</v>
+        <v>-585</v>
       </c>
       <c r="O49" s="16">
         <v>38</v>
@@ -6396,10 +6396,10 @@
         <v>-80.210526315789465</v>
       </c>
       <c r="AD49" s="19">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="AE49" s="20">
-        <v>158.91999999999999</v>
+        <v>132.23999999999998</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6449,19 +6449,19 @@
         <v>-1298.2631578947371</v>
       </c>
       <c r="J50" s="16">
-        <v>2726</v>
+        <v>2333</v>
       </c>
       <c r="K50" s="13">
-        <v>3162.16</v>
+        <v>2706.2799999999997</v>
       </c>
       <c r="L50" s="14">
-        <v>15.060773480662984</v>
+        <v>12.88950276243094</v>
       </c>
       <c r="M50" s="30">
         <v>3982</v>
       </c>
       <c r="N50" s="15">
-        <v>916</v>
+        <v>523</v>
       </c>
       <c r="O50" s="16">
         <v>172</v>
@@ -6509,10 +6509,10 @@
         <v>-219.63157894736844</v>
       </c>
       <c r="AD50" s="19">
-        <v>5089</v>
+        <v>4696</v>
       </c>
       <c r="AE50" s="20">
-        <v>5903.24</v>
+        <v>5447.36</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6565,19 +6565,19 @@
         <v>-956.26315789473665</v>
       </c>
       <c r="J51" s="16">
-        <v>2307</v>
+        <v>1982</v>
       </c>
       <c r="K51" s="13">
-        <v>2676.12</v>
+        <v>2299.12</v>
       </c>
       <c r="L51" s="14">
-        <v>14.103281853281855</v>
+        <v>12.116473616473618</v>
       </c>
       <c r="M51" s="30">
         <v>3598.7368421052629</v>
       </c>
       <c r="N51" s="15">
-        <v>671.21052631578959</v>
+        <v>346.21052631578959</v>
       </c>
       <c r="O51" s="16">
         <v>258</v>
@@ -6625,10 +6625,10 @@
         <v>-13.473684210526315</v>
       </c>
       <c r="AD51" s="19">
-        <v>4030</v>
+        <v>3705</v>
       </c>
       <c r="AE51" s="20">
-        <v>4674.7999999999993</v>
+        <v>4297.7999999999993</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6682,19 +6682,19 @@
         <v>447.78947368421041</v>
       </c>
       <c r="J52" s="16">
-        <v>4628</v>
+        <v>3982</v>
       </c>
       <c r="K52" s="13">
-        <v>3748.6800000000003</v>
+        <v>3225.42</v>
       </c>
       <c r="L52" s="14">
-        <v>97.919821826280611</v>
+        <v>84.251670378619139</v>
       </c>
       <c r="M52" s="30">
         <v>1039.7894736842106</v>
       </c>
       <c r="N52" s="15">
-        <v>4155.3684210526317</v>
+        <v>3509.3684210526317</v>
       </c>
       <c r="O52" s="16">
         <v>137</v>
@@ -6742,10 +6742,10 @@
         <v>-26.631578947368421</v>
       </c>
       <c r="AD52" s="19">
-        <v>7159</v>
+        <v>6513</v>
       </c>
       <c r="AE52" s="20">
-        <v>5798.79</v>
+        <v>5275.5300000000007</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6795,19 +6795,19 @@
         <v>-2249.6315789473683</v>
       </c>
       <c r="J53" s="16">
-        <v>733</v>
+        <v>27</v>
       </c>
       <c r="K53" s="13">
-        <v>593.73</v>
+        <v>21.87</v>
       </c>
       <c r="L53" s="14">
-        <v>5.9263829787234039</v>
+        <v>0.21829787234042553</v>
       </c>
       <c r="M53" s="30">
         <v>2721.0526315789475</v>
       </c>
       <c r="N53" s="15">
-        <v>-503.84210526315792</v>
+        <v>-1209.8421052631579</v>
       </c>
       <c r="O53" s="16">
         <v>550</v>
@@ -6855,10 +6855,10 @@
         <v>-137.78947368421052</v>
       </c>
       <c r="AD53" s="19">
-        <v>2664</v>
+        <v>1958</v>
       </c>
       <c r="AE53" s="20">
-        <v>2157.84</v>
+        <v>1585.98</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6908,19 +6908,19 @@
         <v>21.894736842105203</v>
       </c>
       <c r="J54" s="16">
-        <v>4221</v>
+        <v>3248</v>
       </c>
       <c r="K54" s="13">
-        <v>3419.01</v>
+        <v>2630.88</v>
       </c>
       <c r="L54" s="14">
-        <v>69.981675392670155</v>
+        <v>53.849912739965092</v>
       </c>
       <c r="M54" s="30">
         <v>1326.9473684210527</v>
       </c>
       <c r="N54" s="15">
-        <v>3617.8421052631579</v>
+        <v>2644.8421052631579</v>
       </c>
       <c r="O54" s="16">
         <v>231</v>
@@ -6968,10 +6968,10 @@
         <v>-91.94736842105263</v>
       </c>
       <c r="AD54" s="19">
-        <v>7004</v>
+        <v>6031</v>
       </c>
       <c r="AE54" s="20">
-        <v>5673.2400000000007</v>
+        <v>4885.1100000000006</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7021,19 +7021,19 @@
         <v>376.84210526315792</v>
       </c>
       <c r="J55" s="16">
-        <v>6796</v>
+        <v>6237</v>
       </c>
       <c r="K55" s="13">
-        <v>5504.76</v>
+        <v>5051.97</v>
       </c>
       <c r="L55" s="14">
-        <v>90.044630404463035</v>
+        <v>82.638075313807533</v>
       </c>
       <c r="M55" s="30">
         <v>1660.421052631579</v>
       </c>
       <c r="N55" s="15">
-        <v>6041.2631578947367</v>
+        <v>5482.2631578947367</v>
       </c>
       <c r="O55" s="16">
         <v>348</v>
@@ -7081,10 +7081,10 @@
         <v>-81.421052631578931</v>
       </c>
       <c r="AD55" s="19">
-        <v>9813</v>
+        <v>9254</v>
       </c>
       <c r="AE55" s="20">
-        <v>7948.5300000000007</v>
+        <v>7495.7400000000007</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7134,19 +7134,19 @@
         <v>4.7894736842105203</v>
       </c>
       <c r="J56" s="32">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="K56" s="13">
-        <v>814.82</v>
+        <v>306.54000000000002</v>
       </c>
       <c r="L56" s="14">
-        <v>24.118367346938779</v>
+        <v>9.073469387755102</v>
       </c>
       <c r="M56" s="30">
         <v>283.68421052631578</v>
       </c>
       <c r="N56" s="15">
-        <v>182.05263157894737</v>
+        <v>-11.94736842105263</v>
       </c>
       <c r="O56" s="32">
         <v>54</v>
@@ -7194,10 +7194,10 @@
         <v>9.1052631578947398</v>
       </c>
       <c r="AD56" s="19">
-        <v>833</v>
+        <v>639</v>
       </c>
       <c r="AE56" s="20">
-        <v>2182.46</v>
+        <v>1674.18</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7247,19 +7247,19 @@
         <v>-477.15789473684208</v>
       </c>
       <c r="J57" s="32">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="K57" s="13">
-        <v>421.82</v>
+        <v>78.600000000000009</v>
       </c>
       <c r="L57" s="14">
-        <v>5.7826086956521738</v>
+        <v>1.0775047258979207</v>
       </c>
       <c r="M57" s="30">
         <v>612.52631578947364</v>
       </c>
       <c r="N57" s="15">
-        <v>-117.42105263157896</v>
+        <v>-248.42105263157896</v>
       </c>
       <c r="O57" s="32">
         <v>105</v>
@@ -7307,10 +7307,10 @@
         <v>22.94736842105263</v>
       </c>
       <c r="AD57" s="19">
-        <v>622</v>
+        <v>491</v>
       </c>
       <c r="AE57" s="20">
-        <v>1629.64</v>
+        <v>1286.42</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7360,19 +7360,19 @@
         <v>-170.10526315789477</v>
       </c>
       <c r="J58" s="32">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="K58" s="13">
-        <v>324.88</v>
+        <v>141.48000000000002</v>
       </c>
       <c r="L58" s="14">
-        <v>14.023809523809522</v>
+        <v>6.1071428571428568</v>
       </c>
       <c r="M58" s="30">
         <v>194.5263157894737</v>
       </c>
       <c r="N58" s="15">
-        <v>35.578947368421041</v>
+        <v>-34.421052631578959</v>
       </c>
       <c r="O58" s="32">
         <v>25</v>
@@ -7420,10 +7420,10 @@
         <v>10.736842105263158</v>
       </c>
       <c r="AD58" s="19">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="AE58" s="20">
-        <v>951.06000000000006</v>
+        <v>767.66000000000008</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7476,19 +7476,19 @@
         <v>-170.73684210526312</v>
       </c>
       <c r="J59" s="32">
-        <v>218</v>
+        <v>51</v>
       </c>
       <c r="K59" s="13">
-        <v>571.16</v>
+        <v>133.62</v>
       </c>
       <c r="L59" s="14">
-        <v>19.630331753554504</v>
+        <v>4.5924170616113749</v>
       </c>
       <c r="M59" s="30">
         <v>244.31578947368419</v>
       </c>
       <c r="N59" s="15">
-        <v>106.94736842105263</v>
+        <v>-60.05263157894737</v>
       </c>
       <c r="O59" s="32">
         <v>38</v>
@@ -7536,10 +7536,10 @@
         <v>35.631578947368425</v>
       </c>
       <c r="AD59" s="19">
-        <v>564</v>
+        <v>397</v>
       </c>
       <c r="AE59" s="20">
-        <v>1477.68</v>
+        <v>1040.1400000000001</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7613,10 +7613,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7646,17 +7646,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
         <v>152319.97</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>28.931135640366456</v>
+        <v>33.077157588430659</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7694,11 +7694,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>274466.88</v>
+        <v>208474.34999999998</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>52.131303164438542</v>
+        <v>45.271404190111433</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.7859091742221844</v>
+        <v>6.6150679989577403</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>11.533504339576231</v>
+        <v>13.18633133967705</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>1.580312312734393</v>
+        <v>1.8067814570790464</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7856,19 +7856,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>526491.50000000012</v>
-      </c>
-      <c r="E67" s="66">
+        <v>460498.96999999991</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7968,17 +7968,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
         <v>113478</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>29.778390080692777</v>
+        <v>33.955421502886026</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8015,11 +8015,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>198568</v>
+        <v>151690</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>52.107327953814867</v>
+        <v>45.389396074770268</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.6616151676179234</v>
+        <v>6.4557730919188385</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>11.103326116906121</v>
+        <v>12.660795877880412</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>1.3493406809683133</v>
+        <v>1.5386134525444572</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8177,19 +8177,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>381075</v>
-      </c>
-      <c r="E75" s="66">
+        <v>334197</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8736,6 +8736,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8744,17 +8755,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B685AF-D640-455D-AC6B-052DA32295F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E91F245-B5D0-40B5-A90F-FDDA76C31C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1186,6 +1186,7 @@
       <sheetName val="INVENTARIO NACIONAL 24-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1330,6 +1331,7 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1657,242 +1659,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2257,85 +2259,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>3063</v>
+        <v>5369</v>
       </c>
       <c r="F13" s="14">
-        <v>4165.68</v>
+        <v>7301.84</v>
       </c>
       <c r="G13" s="14">
-        <v>3.942084942084942</v>
+        <v>6.9019154132921967</v>
       </c>
       <c r="H13" s="30">
-        <v>17094</v>
+        <v>17113.8</v>
       </c>
       <c r="I13" s="15">
-        <v>-4707</v>
+        <v>-2410</v>
       </c>
       <c r="J13" s="16">
-        <v>6269</v>
+        <v>2121</v>
       </c>
       <c r="K13" s="13">
-        <v>8525.84</v>
+        <v>2884.5600000000004</v>
       </c>
       <c r="L13" s="14">
-        <v>26.02950174825175</v>
+        <v>8.8559498956158667</v>
       </c>
       <c r="M13" s="30">
-        <v>5298.5263157894733</v>
+        <v>5269</v>
       </c>
       <c r="N13" s="15">
-        <v>3860.5789473684213</v>
+        <v>-274</v>
       </c>
       <c r="O13" s="16">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="P13" s="17">
-        <v>1253.92</v>
+        <v>1229.44</v>
       </c>
       <c r="Q13" s="14">
-        <v>20.182027649769587</v>
+        <v>20.429378531073446</v>
       </c>
       <c r="R13" s="16">
-        <v>1005.0526315789473</v>
+        <v>973.5</v>
       </c>
       <c r="S13" s="15">
-        <v>8.3157894736842763</v>
+        <v>19</v>
       </c>
       <c r="T13" s="18">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="U13" s="17">
-        <v>848.6400000000001</v>
+        <v>802.40000000000009</v>
       </c>
       <c r="V13" s="14">
-        <v>12.943231441048034</v>
+        <v>12.407991587802314</v>
       </c>
       <c r="W13" s="16">
-        <v>1060.6315789473683</v>
+        <v>1046.0999999999999</v>
       </c>
       <c r="X13" s="15">
-        <v>-147.36842105263156</v>
+        <v>-170.79999999999995</v>
       </c>
       <c r="Y13" s="18">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="Z13" s="17">
-        <v>0</v>
+        <v>870.40000000000009</v>
       </c>
       <c r="AA13" s="14">
-        <v>0</v>
+        <v>22.377622377622377</v>
       </c>
       <c r="AB13" s="16">
-        <v>662.31578947368416</v>
+        <v>629.20000000000005</v>
       </c>
       <c r="AC13" s="15">
-        <v>-662.31578947368416</v>
+        <v>10.799999999999955</v>
       </c>
       <c r="AD13" s="19">
-        <v>10878</v>
+        <v>9624</v>
       </c>
       <c r="AE13" s="20">
-        <v>14794.080000000002</v>
+        <v>13088.640000000001</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2380,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>539.57894736842104</v>
+        <v>512.6</v>
       </c>
       <c r="I14" s="15">
-        <v>-245.26315789473685</v>
+        <v>-233</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2395,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>288.31578947368422</v>
+        <v>273.89999999999998</v>
       </c>
       <c r="N14" s="15">
-        <v>-131.05263157894737</v>
+        <v>-124.5</v>
       </c>
       <c r="O14" s="16">
         <v>88</v>
@@ -2407,13 +2409,13 @@
         <v>139.92000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>16.076923076923077</v>
+        <v>16.923076923076923</v>
       </c>
       <c r="R14" s="16">
-        <v>120.42105263157895</v>
+        <v>114.4</v>
       </c>
       <c r="S14" s="15">
-        <v>-21.473684210526315</v>
+        <v>-16</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2422,34 +2424,34 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>4.9259259259259256</v>
+        <v>5.1851851851851851</v>
       </c>
       <c r="W14" s="16">
-        <v>31.263157894736842</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="X14" s="15">
-        <v>-15.736842105263158</v>
+        <v>-14.600000000000001</v>
       </c>
       <c r="Y14" s="18">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z14" s="17">
-        <v>34.980000000000004</v>
+        <v>27.03</v>
       </c>
       <c r="AA14" s="14">
-        <v>5.5733333333333333</v>
+        <v>4.25</v>
       </c>
       <c r="AB14" s="16">
-        <v>86.84210526315789</v>
+        <v>88</v>
       </c>
       <c r="AC14" s="15">
-        <v>-64.84210526315789</v>
+        <v>-71</v>
       </c>
       <c r="AD14" s="19">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="AE14" s="20">
-        <v>186.03</v>
+        <v>178.08</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2485,85 +2487,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2346</v>
+        <v>2661</v>
       </c>
       <c r="F15" s="14">
-        <v>4762.3799999999992</v>
+        <v>5401.83</v>
       </c>
       <c r="G15" s="14">
-        <v>6.8989320538616319</v>
+        <v>7.8774422735346352</v>
       </c>
       <c r="H15" s="30">
-        <v>7481.1578947368416</v>
+        <v>7431.6</v>
       </c>
       <c r="I15" s="15">
-        <v>-1054.5263157894733</v>
+        <v>-717</v>
       </c>
       <c r="J15" s="16">
-        <v>1386</v>
+        <v>1936</v>
       </c>
       <c r="K15" s="13">
-        <v>2813.58</v>
+        <v>3930.0799999999995</v>
       </c>
       <c r="L15" s="14">
-        <v>12.660576923076924</v>
+        <v>17.36322869955157</v>
       </c>
       <c r="M15" s="30">
-        <v>2408.4210526315787</v>
+        <v>2453</v>
       </c>
       <c r="N15" s="15">
-        <v>291.26315789473711</v>
+        <v>821</v>
       </c>
       <c r="O15" s="16">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="P15" s="17">
-        <v>428.33</v>
+        <v>385.7</v>
       </c>
       <c r="Q15" s="14">
-        <v>18.821596244131456</v>
+        <v>16.309012875536482</v>
       </c>
       <c r="R15" s="16">
-        <v>246.63157894736844</v>
+        <v>256.3</v>
       </c>
       <c r="S15" s="15">
-        <v>-13.21052631578948</v>
+        <v>-43</v>
       </c>
       <c r="T15" s="18">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="U15" s="17">
-        <v>322.77</v>
+        <v>265.92999999999995</v>
       </c>
       <c r="V15" s="14">
-        <v>9.2668711656441705</v>
+        <v>7.7976190476190474</v>
       </c>
       <c r="W15" s="16">
-        <v>377.47368421052636</v>
+        <v>369.6</v>
       </c>
       <c r="X15" s="15">
-        <v>-115.5263157894737</v>
+        <v>-137.80000000000001</v>
       </c>
       <c r="Y15" s="18">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="Z15" s="17">
-        <v>192.85</v>
+        <v>430.35999999999996</v>
       </c>
       <c r="AA15" s="14">
-        <v>10.314285714285713</v>
+        <v>23.820224719101123</v>
       </c>
       <c r="AB15" s="16">
-        <v>202.63157894736844</v>
+        <v>195.8</v>
       </c>
       <c r="AC15" s="15">
-        <v>-107.63157894736844</v>
+        <v>16.199999999999989</v>
       </c>
       <c r="AD15" s="19">
-        <v>4197</v>
+        <v>5130</v>
       </c>
       <c r="AE15" s="20">
-        <v>8519.91</v>
+        <v>10413.9</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2598,49 +2600,49 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="F16" s="14">
-        <v>1169.6399999999999</v>
+        <v>1032.46</v>
       </c>
       <c r="G16" s="14">
-        <v>4.5465288035450522</v>
+        <v>3.9667128987517342</v>
       </c>
       <c r="H16" s="30">
-        <v>1567.7894736842104</v>
+        <v>1586.1999999999998</v>
       </c>
       <c r="I16" s="15">
-        <v>-388.63157894736833</v>
+        <v>-435</v>
       </c>
       <c r="J16" s="16">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="K16" s="13">
-        <v>1072.17</v>
+        <v>783.37</v>
       </c>
       <c r="L16" s="14">
-        <v>11.331325301204819</v>
+        <v>8.6111111111111107</v>
       </c>
       <c r="M16" s="30">
-        <v>576.63157894736844</v>
+        <v>554.4</v>
       </c>
       <c r="N16" s="15">
-        <v>34.89473684210526</v>
+        <v>-35</v>
       </c>
       <c r="O16" s="16">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="P16" s="17">
-        <v>158.84</v>
+        <v>129.96</v>
       </c>
       <c r="Q16" s="14">
-        <v>19</v>
+        <v>13.846153846153845</v>
       </c>
       <c r="R16" s="16">
-        <v>50.94736842105263</v>
+        <v>57.2</v>
       </c>
       <c r="S16" s="15">
-        <v>-2.3157894736842124</v>
+        <v>-16</v>
       </c>
       <c r="T16" s="18">
         <v>39</v>
@@ -2649,34 +2651,34 @@
         <v>140.79</v>
       </c>
       <c r="V16" s="14">
-        <v>35.285714285714285</v>
+        <v>37.142857142857139</v>
       </c>
       <c r="W16" s="16">
-        <v>24.315789473684212</v>
+        <v>23.1</v>
       </c>
       <c r="X16" s="15">
-        <v>21.315789473684209</v>
+        <v>22.2</v>
       </c>
       <c r="Y16" s="18">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="Z16" s="17">
-        <v>90.25</v>
+        <v>292.40999999999997</v>
       </c>
       <c r="AA16" s="14">
-        <v>8.3333333333333339</v>
+        <v>28.421052631578945</v>
       </c>
       <c r="AB16" s="16">
-        <v>66</v>
+        <v>62.7</v>
       </c>
       <c r="AC16" s="15">
-        <v>-41</v>
+        <v>18.299999999999997</v>
       </c>
       <c r="AD16" s="19">
-        <v>729</v>
+        <v>659</v>
       </c>
       <c r="AE16" s="20">
-        <v>2631.69</v>
+        <v>2378.9899999999998</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2711,34 +2713,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>465.34</v>
+        <v>438.99999999999994</v>
       </c>
       <c r="G17" s="14">
-        <v>5.3850267379679142</v>
+        <v>4.6511627906976747</v>
       </c>
       <c r="H17" s="30">
-        <v>216.5263157894737</v>
+        <v>236.5</v>
       </c>
       <c r="I17" s="15">
-        <v>-45.421052631578959</v>
+        <v>-57.5</v>
       </c>
       <c r="J17" s="16">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="K17" s="13">
-        <v>623.38</v>
+        <v>412.65999999999997</v>
       </c>
       <c r="L17" s="14">
-        <v>34.589743589743584</v>
+        <v>24.102564102564102</v>
       </c>
       <c r="M17" s="30">
-        <v>45.15789473684211</v>
+        <v>42.9</v>
       </c>
       <c r="N17" s="15">
-        <v>50.473684210526315</v>
+        <v>27.5</v>
       </c>
       <c r="O17" s="16">
         <v>12</v>
@@ -2747,13 +2749,13 @@
         <v>105.35999999999999</v>
       </c>
       <c r="Q17" s="14">
-        <v>20.727272727272727</v>
+        <v>21.818181818181817</v>
       </c>
       <c r="R17" s="16">
-        <v>12.736842105263158</v>
+        <v>12.100000000000001</v>
       </c>
       <c r="S17" s="15">
-        <v>0.4210526315789469</v>
+        <v>1</v>
       </c>
       <c r="T17" s="18">
         <v>16</v>
@@ -2771,25 +2773,25 @@
         <v>14.545454545454545</v>
       </c>
       <c r="Y17" s="18">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z17" s="17">
-        <v>70.239999999999995</v>
+        <v>114.13999999999999</v>
       </c>
       <c r="AA17" s="14">
-        <v>16.888888888888889</v>
+        <v>28.888888888888889</v>
       </c>
       <c r="AB17" s="16">
-        <v>10.421052631578947</v>
+        <v>9.9</v>
       </c>
       <c r="AC17" s="15">
-        <v>-2.4210526315789469</v>
+        <v>3.0999999999999996</v>
       </c>
       <c r="AD17" s="19">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="AE17" s="20">
-        <v>1404.8</v>
+        <v>1211.6399999999999</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2824,85 +2826,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6147</v>
+        <v>7069</v>
       </c>
       <c r="F18" s="14">
-        <v>3872.61</v>
+        <v>4453.47</v>
       </c>
       <c r="G18" s="14">
-        <v>7.4423628369336647</v>
+        <v>8.5271411338962597</v>
       </c>
       <c r="H18" s="30">
-        <v>18170.842105263157</v>
+        <v>18238</v>
       </c>
       <c r="I18" s="15">
-        <v>-2112.4736842105267</v>
+        <v>-1221</v>
       </c>
       <c r="J18" s="16">
-        <v>7215</v>
+        <v>13400</v>
       </c>
       <c r="K18" s="13">
-        <v>4545.45</v>
+        <v>8442</v>
       </c>
       <c r="L18" s="14">
-        <v>21.718155893536121</v>
+        <v>40.391861341371516</v>
       </c>
       <c r="M18" s="30">
-        <v>7308.6315789473683</v>
+        <v>7298.5</v>
       </c>
       <c r="N18" s="15">
-        <v>3892.894736842105</v>
+        <v>10082.5</v>
       </c>
       <c r="O18" s="16">
-        <v>1097</v>
+        <v>1000</v>
       </c>
       <c r="P18" s="17">
-        <v>691.11</v>
+        <v>630</v>
       </c>
       <c r="Q18" s="14">
-        <v>19.12201834862385</v>
+        <v>16.849199663016005</v>
       </c>
       <c r="R18" s="16">
-        <v>1262.1052631578948</v>
+        <v>1305.7</v>
       </c>
       <c r="S18" s="15">
-        <v>-50.368421052631675</v>
+        <v>-187</v>
       </c>
       <c r="T18" s="18">
-        <v>1848</v>
+        <v>2079</v>
       </c>
       <c r="U18" s="17">
-        <v>1164.24</v>
+        <v>1309.77</v>
       </c>
       <c r="V18" s="14">
-        <v>11.333763718528083</v>
+        <v>12.82541640962369</v>
       </c>
       <c r="W18" s="16">
-        <v>3587.1578947368421</v>
+        <v>3566.2</v>
       </c>
       <c r="X18" s="15">
-        <v>-760.84210526315792</v>
+        <v>-514.59999999999991</v>
       </c>
       <c r="Y18" s="18">
-        <v>145</v>
+        <v>297</v>
       </c>
       <c r="Z18" s="17">
-        <v>91.35</v>
+        <v>187.11</v>
       </c>
       <c r="AA18" s="14">
-        <v>10.435606060606062</v>
+        <v>20.553633217993081</v>
       </c>
       <c r="AB18" s="16">
-        <v>305.68421052631578</v>
+        <v>317.89999999999998</v>
       </c>
       <c r="AC18" s="15">
-        <v>-160.68421052631578</v>
+        <v>-20.899999999999977</v>
       </c>
       <c r="AD18" s="19">
-        <v>16452</v>
+        <v>23845</v>
       </c>
       <c r="AE18" s="20">
-        <v>10364.76</v>
+        <v>15022.35</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2937,34 +2939,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>313</v>
+        <v>237</v>
       </c>
       <c r="F19" s="14">
-        <v>197.19</v>
+        <v>149.31</v>
       </c>
       <c r="G19" s="14">
-        <v>5.044105173876166</v>
+        <v>3.7559429477020601</v>
       </c>
       <c r="H19" s="30">
-        <v>1365.1578947368421</v>
+        <v>1388.2</v>
       </c>
       <c r="I19" s="15">
-        <v>-307.52631578947376</v>
+        <v>-394</v>
       </c>
       <c r="J19" s="16">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="K19" s="13">
-        <v>76.23</v>
+        <v>42.21</v>
       </c>
       <c r="L19" s="14">
-        <v>2.1895238095238092</v>
+        <v>1.2170753860127157</v>
       </c>
       <c r="M19" s="30">
-        <v>1215.7894736842106</v>
+        <v>1211.0999999999999</v>
       </c>
       <c r="N19" s="15">
-        <v>-431.63157894736855</v>
+        <v>-483.5</v>
       </c>
       <c r="O19" s="16">
         <v>126</v>
@@ -2973,49 +2975,49 @@
         <v>79.38</v>
       </c>
       <c r="Q19" s="14">
-        <v>26.021739130434781</v>
+        <v>27.39130434782609</v>
       </c>
       <c r="R19" s="16">
-        <v>106.52631578947368</v>
+        <v>101.19999999999999</v>
       </c>
       <c r="S19" s="15">
-        <v>29.15789473684211</v>
+        <v>34</v>
       </c>
       <c r="T19" s="18">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="U19" s="17">
-        <v>103.95</v>
+        <v>96.39</v>
       </c>
       <c r="V19" s="14">
-        <v>11.568265682656826</v>
+        <v>11.29151291512915</v>
       </c>
       <c r="W19" s="16">
-        <v>313.78947368421052</v>
+        <v>298.10000000000002</v>
       </c>
       <c r="X19" s="15">
-        <v>-63.21052631578948</v>
+        <v>-63.800000000000011</v>
       </c>
       <c r="Y19" s="18">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="Z19" s="17">
-        <v>73.08</v>
+        <v>144.9</v>
       </c>
       <c r="AA19" s="14">
-        <v>11.539267015706807</v>
+        <v>23.711340206185568</v>
       </c>
       <c r="AB19" s="16">
-        <v>221.15789473684211</v>
+        <v>213.39999999999998</v>
       </c>
       <c r="AC19" s="15">
-        <v>-105.15789473684211</v>
+        <v>16.600000000000023</v>
       </c>
       <c r="AD19" s="19">
-        <v>841</v>
+        <v>813</v>
       </c>
       <c r="AE19" s="20">
-        <v>529.83000000000004</v>
+        <v>512.19000000000005</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3050,85 +3052,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1428</v>
+        <v>1213</v>
       </c>
       <c r="F20" s="14">
-        <v>899.64</v>
+        <v>764.19</v>
       </c>
       <c r="G20" s="14">
-        <v>11.137931034482758</v>
+        <v>9.0454884414615968</v>
       </c>
       <c r="H20" s="30">
-        <v>2820.6315789473683</v>
+        <v>2950.2</v>
       </c>
       <c r="I20" s="15">
-        <v>145.8947368421052</v>
+        <v>-128</v>
       </c>
       <c r="J20" s="16">
-        <v>3447</v>
+        <v>3260</v>
       </c>
       <c r="K20" s="13">
-        <v>2171.61</v>
+        <v>2053.8000000000002</v>
       </c>
       <c r="L20" s="14">
-        <v>27.460377358490561</v>
+        <v>26.21632488942501</v>
       </c>
       <c r="M20" s="30">
-        <v>2761.5789473684213</v>
+        <v>2735.7</v>
       </c>
       <c r="N20" s="15">
-        <v>2191.7368421052629</v>
+        <v>2016.5</v>
       </c>
       <c r="O20" s="16">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="P20" s="17">
-        <v>142.38</v>
+        <v>132.93</v>
       </c>
       <c r="Q20" s="14">
-        <v>24.678160919540232</v>
+        <v>22.328042328042329</v>
       </c>
       <c r="R20" s="16">
-        <v>201.4736842105263</v>
+        <v>207.89999999999998</v>
       </c>
       <c r="S20" s="15">
-        <v>42.842105263157919</v>
+        <v>22</v>
       </c>
       <c r="T20" s="18">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="U20" s="17">
-        <v>236.25</v>
+        <v>229.95</v>
       </c>
       <c r="V20" s="14">
-        <v>11.604234527687296</v>
+        <v>11.774193548387096</v>
       </c>
       <c r="W20" s="16">
-        <v>710.94736842105272</v>
+        <v>682</v>
       </c>
       <c r="X20" s="15">
-        <v>-142.0526315789474</v>
+        <v>-131</v>
       </c>
       <c r="Y20" s="18">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="Z20" s="17">
-        <v>103.95</v>
+        <v>173.25</v>
       </c>
       <c r="AA20" s="14">
-        <v>12.391304347826086</v>
+        <v>20.912547528517109</v>
       </c>
       <c r="AB20" s="16">
-        <v>292.94736842105266</v>
+        <v>289.3</v>
       </c>
       <c r="AC20" s="15">
-        <v>-127.94736842105266</v>
+        <v>-14.300000000000011</v>
       </c>
       <c r="AD20" s="19">
-        <v>5641</v>
+        <v>5324</v>
       </c>
       <c r="AE20" s="20">
-        <v>3553.83</v>
+        <v>3354.12</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3163,85 +3165,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>1924</v>
+        <v>1812</v>
       </c>
       <c r="F21" s="14">
-        <v>2097.1600000000003</v>
+        <v>1975.0800000000002</v>
       </c>
       <c r="G21" s="14">
-        <v>6.3377253814147023</v>
+        <v>6.1133603238866403</v>
       </c>
       <c r="H21" s="30">
-        <v>6678.7368421052633</v>
+        <v>6520.7999999999993</v>
       </c>
       <c r="I21" s="15">
-        <v>-1111.7894736842104</v>
+        <v>-1152</v>
       </c>
       <c r="J21" s="16">
-        <v>2722</v>
+        <v>5365</v>
       </c>
       <c r="K21" s="13">
-        <v>2966.98</v>
+        <v>5847.85</v>
       </c>
       <c r="L21" s="14">
-        <v>8.1923015998732787</v>
+        <v>16.324357218925911</v>
       </c>
       <c r="M21" s="30">
-        <v>7309.78947368421</v>
+        <v>7230.2999999999993</v>
       </c>
       <c r="N21" s="15">
-        <v>-600.63157894736833</v>
+        <v>2078.5</v>
       </c>
       <c r="O21" s="16">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="P21" s="17">
-        <v>547.18000000000006</v>
+        <v>529.74</v>
       </c>
       <c r="Q21" s="14">
-        <v>17.373406193078324</v>
+        <v>17.142857142857142</v>
       </c>
       <c r="R21" s="16">
-        <v>635.68421052631584</v>
+        <v>623.70000000000005</v>
       </c>
       <c r="S21" s="15">
-        <v>-75.894736842105317</v>
+        <v>-81</v>
       </c>
       <c r="T21" s="18">
-        <v>900</v>
+        <v>738</v>
       </c>
       <c r="U21" s="17">
-        <v>981.00000000000011</v>
+        <v>804.42000000000007</v>
       </c>
       <c r="V21" s="14">
-        <v>10.568603213844252</v>
+        <v>8.3959044368600679</v>
       </c>
       <c r="W21" s="16">
-        <v>1873.4736842105265</v>
+        <v>1933.8000000000002</v>
       </c>
       <c r="X21" s="15">
-        <v>-462.52631578947376</v>
+        <v>-668.40000000000009</v>
       </c>
       <c r="Y21" s="18">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="Z21" s="17">
-        <v>194.02</v>
+        <v>412.02000000000004</v>
       </c>
       <c r="AA21" s="14">
-        <v>9.8028985507246365</v>
+        <v>20.941828254847646</v>
       </c>
       <c r="AB21" s="16">
-        <v>399.47368421052636</v>
+        <v>397.1</v>
       </c>
       <c r="AC21" s="15">
-        <v>-221.47368421052636</v>
+        <v>-19.100000000000023</v>
       </c>
       <c r="AD21" s="19">
-        <v>6226</v>
+        <v>8779</v>
       </c>
       <c r="AE21" s="20">
-        <v>6786.34</v>
+        <v>9569.11</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3276,34 +3278,34 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1730</v>
+        <v>2142</v>
       </c>
       <c r="F22" s="14">
-        <v>1885.7</v>
+        <v>2334.7800000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>9.4698934024776733</v>
+        <v>11.847345132743362</v>
       </c>
       <c r="H22" s="30">
-        <v>4019.0526315789471</v>
+        <v>3977.6000000000004</v>
       </c>
       <c r="I22" s="15">
-        <v>-96.842105263157919</v>
+        <v>334</v>
       </c>
       <c r="J22" s="16">
-        <v>2478</v>
+        <v>1744</v>
       </c>
       <c r="K22" s="13">
-        <v>2701.02</v>
+        <v>1900.96</v>
       </c>
       <c r="L22" s="14">
-        <v>16.821007502679528</v>
+        <v>11.900375298532923</v>
       </c>
       <c r="M22" s="30">
-        <v>3240.9473684210529</v>
+        <v>3224.1000000000004</v>
       </c>
       <c r="N22" s="15">
-        <v>1004.8421052631579</v>
+        <v>278.5</v>
       </c>
       <c r="O22" s="16">
         <v>122</v>
@@ -3312,28 +3314,28 @@
         <v>132.98000000000002</v>
       </c>
       <c r="Q22" s="14">
-        <v>15.986206896551725</v>
+        <v>16.827586206896552</v>
       </c>
       <c r="R22" s="16">
-        <v>167.89473684210526</v>
+        <v>159.5</v>
       </c>
       <c r="S22" s="15">
-        <v>-30.631578947368439</v>
+        <v>-23</v>
       </c>
       <c r="T22" s="18">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="U22" s="17">
-        <v>355.34000000000003</v>
+        <v>294.3</v>
       </c>
       <c r="V22" s="14">
-        <v>12.985324947589099</v>
+        <v>10.207939508506616</v>
       </c>
       <c r="W22" s="16">
-        <v>552.31578947368416</v>
+        <v>581.9</v>
       </c>
       <c r="X22" s="15">
-        <v>-75.68421052631578</v>
+        <v>-153.19999999999999</v>
       </c>
       <c r="Y22" s="18">
         <v>45</v>
@@ -3342,19 +3344,19 @@
         <v>49.050000000000004</v>
       </c>
       <c r="AA22" s="14">
-        <v>5.5519480519480524</v>
+        <v>5.8441558441558437</v>
       </c>
       <c r="AB22" s="16">
-        <v>178.31578947368419</v>
+        <v>169.4</v>
       </c>
       <c r="AC22" s="15">
-        <v>-133.31578947368419</v>
+        <v>-124.4</v>
       </c>
       <c r="AD22" s="19">
-        <v>4701</v>
+        <v>4323</v>
       </c>
       <c r="AE22" s="20">
-        <v>5124.09</v>
+        <v>4712.0700000000006</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3389,85 +3391,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>18628</v>
+        <v>23343</v>
       </c>
       <c r="F23" s="14">
-        <v>21608.48</v>
+        <v>27077.879999999997</v>
       </c>
       <c r="G23" s="14">
-        <v>11.395840041213214</v>
+        <v>14.339332882855212</v>
       </c>
       <c r="H23" s="30">
-        <v>35961.894736842107</v>
+        <v>35813.800000000003</v>
       </c>
       <c r="I23" s="15">
-        <v>-5891.4736842105267</v>
+        <v>-1075.5</v>
       </c>
       <c r="J23" s="16">
-        <v>23344</v>
+        <v>16373</v>
       </c>
       <c r="K23" s="13">
-        <v>27079.039999999997</v>
+        <v>18992.68</v>
       </c>
       <c r="L23" s="14">
-        <v>24.839605734767026</v>
+        <v>17.480382213206642</v>
       </c>
       <c r="M23" s="30">
-        <v>20675.36842105263</v>
+        <v>20606.3</v>
       </c>
       <c r="N23" s="15">
-        <v>13946.105263157897</v>
+        <v>7006.5</v>
       </c>
       <c r="O23" s="16">
-        <v>1522</v>
+        <v>2445</v>
       </c>
       <c r="P23" s="17">
-        <v>1765.52</v>
+        <v>2836.2</v>
       </c>
       <c r="Q23" s="14">
-        <v>10.090020935101187</v>
+        <v>15.825242718446601</v>
       </c>
       <c r="R23" s="16">
-        <v>3318.5263157894738</v>
+        <v>3399</v>
       </c>
       <c r="S23" s="15">
-        <v>-1494.8421052631579</v>
+        <v>-645</v>
       </c>
       <c r="T23" s="18">
-        <v>6681</v>
+        <v>5945</v>
       </c>
       <c r="U23" s="17">
-        <v>7749.9599999999991</v>
+        <v>6896.2</v>
       </c>
       <c r="V23" s="14">
-        <v>11.941580432737535</v>
+        <v>10.582999554962171</v>
       </c>
       <c r="W23" s="16">
-        <v>12308.42105263158</v>
+        <v>12358.5</v>
       </c>
       <c r="X23" s="15">
-        <v>-2270.5789473684217</v>
+        <v>-3043</v>
       </c>
       <c r="Y23" s="18">
-        <v>1</v>
+        <v>1243</v>
       </c>
       <c r="Z23" s="17">
-        <v>1.1599999999999999</v>
+        <v>1441.8799999999999</v>
       </c>
       <c r="AA23" s="14">
-        <v>2.0856201975850714E-2</v>
+        <v>27.288693743139408</v>
       </c>
       <c r="AB23" s="16">
-        <v>1054.8421052631579</v>
+        <v>1002.0999999999999</v>
       </c>
       <c r="AC23" s="15">
-        <v>-1053.8421052631579</v>
+        <v>240.90000000000009</v>
       </c>
       <c r="AD23" s="19">
-        <v>50176</v>
+        <v>49349</v>
       </c>
       <c r="AE23" s="20">
-        <v>58204.159999999996</v>
+        <v>57244.84</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3502,85 +3504,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>9962</v>
+        <v>10222</v>
       </c>
       <c r="F24" s="14">
-        <v>11555.92</v>
+        <v>11857.519999999999</v>
       </c>
       <c r="G24" s="14">
-        <v>8.9965302533390368</v>
+        <v>9.2880832311117167</v>
       </c>
       <c r="H24" s="30">
-        <v>24360.947368421053</v>
+        <v>24212.1</v>
       </c>
       <c r="I24" s="15">
-        <v>-1111.1578947368416</v>
+        <v>-783.5</v>
       </c>
       <c r="J24" s="16">
-        <v>10016</v>
+        <v>8207</v>
       </c>
       <c r="K24" s="13">
-        <v>11618.56</v>
+        <v>9520.119999999999</v>
       </c>
       <c r="L24" s="14">
-        <v>17.414348462664716</v>
+        <v>14.381845264172435</v>
       </c>
       <c r="M24" s="30">
-        <v>12653.473684210527</v>
+        <v>12554.3</v>
       </c>
       <c r="N24" s="15">
-        <v>4264.4210526315792</v>
+        <v>2500.5</v>
       </c>
       <c r="O24" s="16">
-        <v>1871</v>
+        <v>1427</v>
       </c>
       <c r="P24" s="17">
-        <v>2170.3599999999997</v>
+        <v>1655.32</v>
       </c>
       <c r="Q24" s="14">
-        <v>20.898883009994123</v>
+        <v>15.89086859688196</v>
       </c>
       <c r="R24" s="16">
-        <v>1969.578947368421</v>
+        <v>1975.6</v>
       </c>
       <c r="S24" s="15">
-        <v>80.473684210526244</v>
+        <v>-369</v>
       </c>
       <c r="T24" s="18">
-        <v>3816</v>
+        <v>3393</v>
       </c>
       <c r="U24" s="17">
-        <v>4426.5599999999995</v>
+        <v>3935.8799999999997</v>
       </c>
       <c r="V24" s="14">
-        <v>12.791813690896259</v>
+        <v>11.293060409385921</v>
       </c>
       <c r="W24" s="16">
-        <v>6562.9473684210525</v>
+        <v>6609.9</v>
       </c>
       <c r="X24" s="15">
-        <v>-957.05263157894751</v>
+        <v>-1414.1999999999998</v>
       </c>
       <c r="Y24" s="18">
-        <v>202</v>
+        <v>722</v>
       </c>
       <c r="Z24" s="17">
-        <v>234.32</v>
+        <v>837.52</v>
       </c>
       <c r="AA24" s="14">
-        <v>5.2719780219780219</v>
+        <v>19.304812834224599</v>
       </c>
       <c r="AB24" s="16">
-        <v>842.94736842105272</v>
+        <v>822.8</v>
       </c>
       <c r="AC24" s="15">
-        <v>-640.94736842105272</v>
+        <v>-100.79999999999995</v>
       </c>
       <c r="AD24" s="19">
-        <v>25867</v>
+        <v>23971</v>
       </c>
       <c r="AE24" s="20">
-        <v>30005.719999999998</v>
+        <v>27806.359999999997</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3615,85 +3617,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>7533</v>
+        <v>9186</v>
       </c>
       <c r="F25" s="14">
-        <v>8738.2799999999988</v>
+        <v>10655.759999999998</v>
       </c>
       <c r="G25" s="14">
-        <v>7.1172053704624565</v>
+        <v>8.6541994441565784</v>
       </c>
       <c r="H25" s="30">
-        <v>23285.263157894737</v>
+        <v>23351.9</v>
       </c>
       <c r="I25" s="15">
-        <v>-3051.21052631579</v>
+        <v>-1428.5</v>
       </c>
       <c r="J25" s="16">
-        <v>19156</v>
+        <v>15934</v>
       </c>
       <c r="K25" s="13">
-        <v>22220.959999999999</v>
+        <v>18483.439999999999</v>
       </c>
       <c r="L25" s="14">
-        <v>31.471162991785558</v>
+        <v>26.407026847862117</v>
       </c>
       <c r="M25" s="30">
-        <v>13391.052631578948</v>
+        <v>13274.8</v>
       </c>
       <c r="N25" s="15">
-        <v>13069.157894736842</v>
+        <v>9900</v>
       </c>
       <c r="O25" s="16">
-        <v>1469</v>
+        <v>1729</v>
       </c>
       <c r="P25" s="17">
-        <v>1704.04</v>
+        <v>2005.6399999999999</v>
       </c>
       <c r="Q25" s="14">
-        <v>13.431665062560155</v>
+        <v>15.604693140794224</v>
       </c>
       <c r="R25" s="16">
-        <v>2406.1052631578946</v>
+        <v>2437.6</v>
       </c>
       <c r="S25" s="15">
-        <v>-718.36842105263167</v>
+        <v>-487</v>
       </c>
       <c r="T25" s="18">
-        <v>3866</v>
+        <v>3436</v>
       </c>
       <c r="U25" s="17">
-        <v>4484.5599999999995</v>
+        <v>3985.7599999999998</v>
       </c>
       <c r="V25" s="14">
-        <v>12.785726718885989</v>
+        <v>11.278516330215002</v>
       </c>
       <c r="W25" s="16">
-        <v>6652.1052631578941</v>
+        <v>6702.2999999999993</v>
       </c>
       <c r="X25" s="15">
-        <v>-971.89473684210498</v>
+        <v>-1438.3999999999996</v>
       </c>
       <c r="Y25" s="18">
-        <v>427</v>
+        <v>519</v>
       </c>
       <c r="Z25" s="17">
-        <v>495.32</v>
+        <v>602.04</v>
       </c>
       <c r="AA25" s="14">
-        <v>15.365530303030305</v>
+        <v>19.186691312384472</v>
       </c>
       <c r="AB25" s="16">
-        <v>611.36842105263156</v>
+        <v>595.1</v>
       </c>
       <c r="AC25" s="15">
-        <v>-184.36842105263156</v>
+        <v>-76.100000000000023</v>
       </c>
       <c r="AD25" s="19">
-        <v>32451</v>
+        <v>30804</v>
       </c>
       <c r="AE25" s="20">
-        <v>37643.159999999996</v>
+        <v>35732.639999999999</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3728,85 +3730,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>15874</v>
+        <v>18913</v>
       </c>
       <c r="F26" s="14">
-        <v>18413.84</v>
+        <v>21939.079999999998</v>
       </c>
       <c r="G26" s="14">
-        <v>11.538102524866105</v>
+        <v>13.819736217164152</v>
       </c>
       <c r="H26" s="30">
-        <v>30267.368421052633</v>
+        <v>30108.1</v>
       </c>
       <c r="I26" s="15">
-        <v>-4762.8421052631602</v>
+        <v>-1615.25</v>
       </c>
       <c r="J26" s="16">
-        <v>12272</v>
+        <v>11989</v>
       </c>
       <c r="K26" s="13">
-        <v>14235.519999999999</v>
+        <v>13907.24</v>
       </c>
       <c r="L26" s="14">
-        <v>17.118273254533438</v>
+        <v>16.871657754010695</v>
       </c>
       <c r="M26" s="30">
-        <v>15771.684210526317</v>
+        <v>15633.2</v>
       </c>
       <c r="N26" s="15">
-        <v>5103.0526315789466</v>
+        <v>4883</v>
       </c>
       <c r="O26" s="16">
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="P26" s="17">
-        <v>0</v>
+        <v>1561.36</v>
       </c>
       <c r="Q26" s="14">
-        <v>0</v>
+        <v>15.286768881317434</v>
       </c>
       <c r="R26" s="16">
-        <v>1896.6315789473686</v>
+        <v>1937.1</v>
       </c>
       <c r="S26" s="15">
-        <v>-1724.2105263157896</v>
+        <v>-415</v>
       </c>
       <c r="T26" s="18">
-        <v>4466</v>
+        <v>4008</v>
       </c>
       <c r="U26" s="17">
-        <v>5180.5599999999995</v>
+        <v>4649.28</v>
       </c>
       <c r="V26" s="14">
-        <v>11.710460943969085</v>
+        <v>10.481171548117155</v>
       </c>
       <c r="W26" s="16">
-        <v>8390.105263157895</v>
+        <v>8412.7999999999993</v>
       </c>
       <c r="X26" s="15">
-        <v>-1635.8947368421059</v>
+        <v>-2110.3999999999996</v>
       </c>
       <c r="Y26" s="18">
-        <v>312</v>
+        <v>896</v>
       </c>
       <c r="Z26" s="17">
-        <v>361.91999999999996</v>
+        <v>1039.3599999999999</v>
       </c>
       <c r="AA26" s="14">
-        <v>7.4192740926157699</v>
+        <v>22.150803461063038</v>
       </c>
       <c r="AB26" s="16">
-        <v>925.15789473684208</v>
+        <v>889.90000000000009</v>
       </c>
       <c r="AC26" s="15">
-        <v>-613.15789473684208</v>
+        <v>6.0999999999999091</v>
       </c>
       <c r="AD26" s="19">
-        <v>32924</v>
+        <v>37152</v>
       </c>
       <c r="AE26" s="20">
-        <v>38191.839999999997</v>
+        <v>43096.32</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3841,85 +3843,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>3366</v>
+        <v>1749</v>
       </c>
       <c r="F27" s="14">
-        <v>3904.56</v>
+        <v>2028.84</v>
       </c>
       <c r="G27" s="14">
-        <v>9.6636446056210339</v>
+        <v>4.958888573858804</v>
       </c>
       <c r="H27" s="30">
-        <v>7662.9473684210525</v>
+        <v>7759.4</v>
       </c>
       <c r="I27" s="15">
-        <v>-117.15789473684208</v>
+        <v>-1778</v>
       </c>
       <c r="J27" s="16">
-        <v>3174</v>
+        <v>2799</v>
       </c>
       <c r="K27" s="13">
-        <v>3681.8399999999997</v>
+        <v>3246.8399999999997</v>
       </c>
       <c r="L27" s="14">
-        <v>16.312144982418175</v>
+        <v>14.739336492890995</v>
       </c>
       <c r="M27" s="30">
-        <v>4280.7368421052633</v>
+        <v>4177.8</v>
       </c>
       <c r="N27" s="15">
-        <v>1228.2105263157894</v>
+        <v>900</v>
       </c>
       <c r="O27" s="16">
-        <v>605</v>
+        <v>568</v>
       </c>
       <c r="P27" s="17">
-        <v>701.8</v>
+        <v>658.88</v>
       </c>
       <c r="Q27" s="14">
-        <v>21.287037037037035</v>
+        <v>19.68804159445407</v>
       </c>
       <c r="R27" s="16">
-        <v>625.26315789473688</v>
+        <v>634.70000000000005</v>
       </c>
       <c r="S27" s="15">
-        <v>36.578947368421041</v>
+        <v>-9</v>
       </c>
       <c r="T27" s="18">
-        <v>1565</v>
+        <v>1512</v>
       </c>
       <c r="U27" s="17">
-        <v>1815.3999999999999</v>
+        <v>1753.9199999999998</v>
       </c>
       <c r="V27" s="14">
-        <v>12.783748925193466</v>
+        <v>12.873563218390805</v>
       </c>
       <c r="W27" s="16">
-        <v>2693.2631578947367</v>
+        <v>2583.9</v>
       </c>
       <c r="X27" s="15">
-        <v>-393.73684210526312</v>
+        <v>-367.20000000000005</v>
       </c>
       <c r="Y27" s="18">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="Z27" s="17">
-        <v>404.84</v>
+        <v>386.28</v>
       </c>
       <c r="AA27" s="14">
-        <v>28.097457627118644</v>
+        <v>26.428571428571431</v>
       </c>
       <c r="AB27" s="16">
-        <v>273.26315789473682</v>
+        <v>277.2</v>
       </c>
       <c r="AC27" s="15">
-        <v>75.736842105263179</v>
+        <v>55.800000000000011</v>
       </c>
       <c r="AD27" s="19">
-        <v>9059</v>
+        <v>6961</v>
       </c>
       <c r="AE27" s="20">
-        <v>10508.439999999999</v>
+        <v>8074.7599999999993</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3954,85 +3956,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>3300</v>
+        <v>3231</v>
       </c>
       <c r="F28" s="14">
-        <v>3827.9999999999995</v>
+        <v>3747.9599999999996</v>
       </c>
       <c r="G28" s="14">
-        <v>9.3526252983293556</v>
+        <v>9.0087829360100375</v>
       </c>
       <c r="H28" s="30">
-        <v>7762.5263157894742</v>
+        <v>7890.2999999999993</v>
       </c>
       <c r="I28" s="15">
-        <v>-228.42105263157919</v>
+        <v>-355.5</v>
       </c>
       <c r="J28" s="16">
-        <v>5266</v>
+        <v>4668</v>
       </c>
       <c r="K28" s="13">
-        <v>6108.5599999999995</v>
+        <v>5414.8799999999992</v>
       </c>
       <c r="L28" s="14">
-        <v>19.207909387598388</v>
+        <v>17.237813884785819</v>
       </c>
       <c r="M28" s="30">
-        <v>6031.4736842105258</v>
+        <v>5957.6</v>
       </c>
       <c r="N28" s="15">
-        <v>2524.4210526315792</v>
+        <v>1960</v>
       </c>
       <c r="O28" s="16">
-        <v>749</v>
+        <v>692</v>
       </c>
       <c r="P28" s="17">
-        <v>868.83999999999992</v>
+        <v>802.71999999999991</v>
       </c>
       <c r="Q28" s="14">
-        <v>18.457846952010375</v>
+        <v>16.594724220623501</v>
       </c>
       <c r="R28" s="16">
-        <v>892.73684210526324</v>
+        <v>917.40000000000009</v>
       </c>
       <c r="S28" s="15">
-        <v>-62.578947368421041</v>
+        <v>-142</v>
       </c>
       <c r="T28" s="18">
-        <v>1002</v>
+        <v>847</v>
       </c>
       <c r="U28" s="17">
-        <v>1162.32</v>
+        <v>982.52</v>
       </c>
       <c r="V28" s="14">
-        <v>6.7058823529411757</v>
+        <v>5.8193060803847469</v>
       </c>
       <c r="W28" s="16">
-        <v>3287.2631578947371</v>
+        <v>3202.1000000000004</v>
       </c>
       <c r="X28" s="15">
-        <v>-1388.7368421052633</v>
+        <v>-1481.8000000000002</v>
       </c>
       <c r="Y28" s="18">
-        <v>262</v>
+        <v>405</v>
       </c>
       <c r="Z28" s="17">
-        <v>303.91999999999996</v>
+        <v>469.79999999999995</v>
       </c>
       <c r="AA28" s="14">
-        <v>15.039274924471298</v>
+        <v>23.342939481268008</v>
       </c>
       <c r="AB28" s="16">
-        <v>383.26315789473688</v>
+        <v>381.70000000000005</v>
       </c>
       <c r="AC28" s="15">
-        <v>-121.26315789473688</v>
+        <v>23.299999999999955</v>
       </c>
       <c r="AD28" s="19">
-        <v>10579</v>
+        <v>9843</v>
       </c>
       <c r="AE28" s="20">
-        <v>12271.64</v>
+        <v>11417.88</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4067,85 +4069,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>3326</v>
+        <v>1499</v>
       </c>
       <c r="F29" s="14">
-        <v>3858.16</v>
+        <v>1738.84</v>
       </c>
       <c r="G29" s="14">
-        <v>8.8050717570015316</v>
+        <v>3.9174180060107151</v>
       </c>
       <c r="H29" s="30">
-        <v>8310.21052631579</v>
+        <v>8418.2999999999993</v>
       </c>
       <c r="I29" s="15">
-        <v>-451.36842105263167</v>
+        <v>-2327.5</v>
       </c>
       <c r="J29" s="16">
-        <v>424</v>
+        <v>202</v>
       </c>
       <c r="K29" s="13">
-        <v>491.84</v>
+        <v>234.32</v>
       </c>
       <c r="L29" s="14">
-        <v>1.6291203235591507</v>
+        <v>0.79324563125859016</v>
       </c>
       <c r="M29" s="30">
-        <v>5725.78947368421</v>
+        <v>5602.3</v>
       </c>
       <c r="N29" s="15">
-        <v>-2178.6315789473683</v>
+        <v>-2344.5</v>
       </c>
       <c r="O29" s="16">
-        <v>754</v>
+        <v>703</v>
       </c>
       <c r="P29" s="17">
-        <v>874.64</v>
+        <v>815.4799999999999</v>
       </c>
       <c r="Q29" s="14">
-        <v>18.020125786163522</v>
+        <v>16.580188679245282</v>
       </c>
       <c r="R29" s="16">
-        <v>920.52631578947376</v>
+        <v>932.8</v>
       </c>
       <c r="S29" s="15">
-        <v>-82.842105263157919</v>
+        <v>-145</v>
       </c>
       <c r="T29" s="18">
-        <v>920</v>
+        <v>826</v>
       </c>
       <c r="U29" s="17">
-        <v>1067.1999999999998</v>
+        <v>958.16</v>
       </c>
       <c r="V29" s="14">
-        <v>6.2162162162162158</v>
+        <v>5.6965517241379313</v>
       </c>
       <c r="W29" s="16">
-        <v>3256</v>
+        <v>3190</v>
       </c>
       <c r="X29" s="15">
-        <v>-1448</v>
+        <v>-1494</v>
       </c>
       <c r="Y29" s="18">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="Z29" s="17">
-        <v>319</v>
+        <v>425.71999999999997</v>
       </c>
       <c r="AA29" s="14">
-        <v>16.640127388535031</v>
+        <v>22.242424242424242</v>
       </c>
       <c r="AB29" s="16">
-        <v>363.57894736842104</v>
+        <v>363</v>
       </c>
       <c r="AC29" s="15">
-        <v>-88.578947368421041</v>
+        <v>4</v>
       </c>
       <c r="AD29" s="19">
-        <v>5699</v>
+        <v>3597</v>
       </c>
       <c r="AE29" s="20">
-        <v>6610.8399999999992</v>
+        <v>4172.5199999999995</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4180,85 +4182,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>121</v>
+        <v>349</v>
       </c>
       <c r="F30" s="14">
-        <v>445.28000000000003</v>
+        <v>1284.3200000000002</v>
       </c>
       <c r="G30" s="14">
-        <v>1.1381188118811882</v>
+        <v>3.2831608654750708</v>
       </c>
       <c r="H30" s="30">
-        <v>2338.9473684210525</v>
+        <v>2338.6</v>
       </c>
       <c r="I30" s="15">
-        <v>-942.15789473684208</v>
+        <v>-714</v>
       </c>
       <c r="J30" s="16">
-        <v>1180</v>
+        <v>1029</v>
       </c>
       <c r="K30" s="13">
-        <v>4342.4000000000005</v>
+        <v>3786.7200000000003</v>
       </c>
       <c r="L30" s="14">
-        <v>9.9115826702033605</v>
+        <v>8.7761194029850742</v>
       </c>
       <c r="M30" s="30">
-        <v>2619.1578947368421</v>
+        <v>2579.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-10.526315789473756</v>
+        <v>-143.5</v>
       </c>
       <c r="O30" s="16">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="P30" s="17">
-        <v>456.32</v>
+        <v>437.92</v>
       </c>
       <c r="Q30" s="14">
-        <v>20.310344827586206</v>
+        <v>19.833333333333332</v>
       </c>
       <c r="R30" s="16">
-        <v>134.31578947368422</v>
+        <v>132</v>
       </c>
       <c r="S30" s="15">
-        <v>1.8947368421052602</v>
+        <v>-1</v>
       </c>
       <c r="T30" s="18">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="U30" s="17">
-        <v>1354.24</v>
+        <v>1232.8</v>
       </c>
       <c r="V30" s="14">
-        <v>12.288224956063267</v>
+        <v>11.375212224108658</v>
       </c>
       <c r="W30" s="16">
-        <v>658.84210526315792</v>
+        <v>647.9</v>
       </c>
       <c r="X30" s="15">
-        <v>-111.15789473684214</v>
+        <v>-136.19999999999999</v>
       </c>
       <c r="Y30" s="18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z30" s="17">
-        <v>0</v>
+        <v>471.04</v>
       </c>
       <c r="AA30" s="14">
-        <v>0</v>
+        <v>27.526881720430104</v>
       </c>
       <c r="AB30" s="16">
-        <v>107.68421052631578</v>
+        <v>102.30000000000001</v>
       </c>
       <c r="AC30" s="15">
-        <v>-107.68421052631578</v>
+        <v>25.699999999999989</v>
       </c>
       <c r="AD30" s="19">
-        <v>1793</v>
+        <v>1960</v>
       </c>
       <c r="AE30" s="20">
-        <v>6598.2400000000007</v>
+        <v>7212.8</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4293,34 +4295,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="F31" s="14">
-        <v>1589.76</v>
+        <v>1729.6000000000001</v>
       </c>
       <c r="G31" s="14">
-        <v>8.3840653728294168</v>
+        <v>9.1976516634050878</v>
       </c>
       <c r="H31" s="30">
-        <v>1133.578947368421</v>
+        <v>1124.2</v>
       </c>
       <c r="I31" s="15">
-        <v>-83.263157894736878</v>
+        <v>-41</v>
       </c>
       <c r="J31" s="16">
-        <v>1280</v>
+        <v>1080</v>
       </c>
       <c r="K31" s="13">
-        <v>4710.4000000000005</v>
+        <v>3974.4</v>
       </c>
       <c r="L31" s="14">
-        <v>19.044635865309317</v>
+        <v>16.314199395770391</v>
       </c>
       <c r="M31" s="30">
-        <v>1478.6315789473686</v>
+        <v>1456.4</v>
       </c>
       <c r="N31" s="15">
-        <v>607.8947368421052</v>
+        <v>418</v>
       </c>
       <c r="O31" s="16">
         <v>34</v>
@@ -4329,28 +4331,28 @@
         <v>125.12</v>
       </c>
       <c r="Q31" s="14">
-        <v>35.888888888888893</v>
+        <v>37.777777777777779</v>
       </c>
       <c r="R31" s="16">
-        <v>20.842105263157894</v>
+        <v>19.8</v>
       </c>
       <c r="S31" s="15">
-        <v>15.05263157894737</v>
+        <v>16</v>
       </c>
       <c r="T31" s="18">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="U31" s="17">
-        <v>412.16</v>
+        <v>279.68</v>
       </c>
       <c r="V31" s="14">
-        <v>11.319148936170212</v>
+        <v>7.1698113207547172</v>
       </c>
       <c r="W31" s="16">
-        <v>217.68421052631581</v>
+        <v>233.2</v>
       </c>
       <c r="X31" s="15">
-        <v>-46.31578947368422</v>
+        <v>-93.6</v>
       </c>
       <c r="Y31" s="18">
         <v>44</v>
@@ -4359,19 +4361,19 @@
         <v>161.92000000000002</v>
       </c>
       <c r="AA31" s="14">
-        <v>34.833333333333336</v>
+        <v>36.666666666666671</v>
       </c>
       <c r="AB31" s="16">
-        <v>27.789473684210524</v>
+        <v>26.4</v>
       </c>
       <c r="AC31" s="15">
-        <v>16.210526315789476</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="AD31" s="19">
-        <v>1902</v>
+        <v>1704</v>
       </c>
       <c r="AE31" s="20">
-        <v>6999.3600000000006</v>
+        <v>6270.72</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4406,85 +4408,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1331</v>
+        <v>1169</v>
       </c>
       <c r="F32" s="14">
-        <v>5523.6500000000005</v>
+        <v>4851.3500000000004</v>
       </c>
       <c r="G32" s="14">
-        <v>5.9841457643161382</v>
+        <v>5.2824220515137821</v>
       </c>
       <c r="H32" s="30">
-        <v>4893.2631578947367</v>
+        <v>4868.6000000000004</v>
       </c>
       <c r="I32" s="15">
-        <v>-893.21052631578914</v>
+        <v>-1044</v>
       </c>
       <c r="J32" s="16">
-        <v>3396</v>
+        <v>3212</v>
       </c>
       <c r="K32" s="13">
-        <v>14093.400000000001</v>
+        <v>13329.800000000001</v>
       </c>
       <c r="L32" s="14">
-        <v>18.944216089254258</v>
+        <v>18.105975197294249</v>
       </c>
       <c r="M32" s="30">
-        <v>3943.7894736842109</v>
+        <v>3902.8</v>
       </c>
       <c r="N32" s="15">
-        <v>1603.3684210526314</v>
+        <v>1438</v>
       </c>
       <c r="O32" s="16">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="P32" s="17">
-        <v>1087.3000000000002</v>
+        <v>1037.5</v>
       </c>
       <c r="Q32" s="14">
-        <v>18.437037037037037</v>
+        <v>17.730496453900709</v>
       </c>
       <c r="R32" s="16">
-        <v>312.63157894736844</v>
+        <v>310.2</v>
       </c>
       <c r="S32" s="15">
-        <v>-22.21052631578948</v>
+        <v>-32</v>
       </c>
       <c r="T32" s="18">
-        <v>1072</v>
+        <v>910</v>
       </c>
       <c r="U32" s="17">
-        <v>4448.8</v>
+        <v>3776.5000000000005</v>
       </c>
       <c r="V32" s="14">
-        <v>13.166127989657403</v>
+        <v>10.859188544152746</v>
       </c>
       <c r="W32" s="16">
-        <v>1791.2631578947369</v>
+        <v>1843.6</v>
       </c>
       <c r="X32" s="15">
-        <v>-230.73684210526312</v>
+        <v>-430.79999999999995</v>
       </c>
       <c r="Y32" s="18">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Z32" s="17">
-        <v>1153.7</v>
+        <v>1141.25</v>
       </c>
       <c r="AA32" s="14">
-        <v>73.361111111111114</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="AB32" s="16">
-        <v>83.368421052631575</v>
+        <v>82.5</v>
       </c>
       <c r="AC32" s="15">
-        <v>194.63157894736844</v>
+        <v>192.5</v>
       </c>
       <c r="AD32" s="19">
-        <v>6339</v>
+        <v>5816</v>
       </c>
       <c r="AE32" s="20">
-        <v>26306.850000000002</v>
+        <v>24136.400000000001</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4519,85 +4521,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>2532</v>
+        <v>3115</v>
       </c>
       <c r="F33" s="14">
-        <v>10507.800000000001</v>
+        <v>12927.250000000002</v>
       </c>
       <c r="G33" s="14">
-        <v>5.7087931648273402</v>
+        <v>7.139582855833142</v>
       </c>
       <c r="H33" s="30">
-        <v>9757.5789473684217</v>
+        <v>9598.6</v>
       </c>
       <c r="I33" s="15">
-        <v>-1903.2631578947367</v>
+        <v>-1248</v>
       </c>
       <c r="J33" s="16">
-        <v>2771</v>
+        <v>3764</v>
       </c>
       <c r="K33" s="13">
-        <v>11499.650000000001</v>
+        <v>15620.600000000002</v>
       </c>
       <c r="L33" s="14">
-        <v>10.283007812500001</v>
+        <v>14.252177205603937</v>
       </c>
       <c r="M33" s="30">
-        <v>5928.4210526315783</v>
+        <v>5810.2000000000007</v>
       </c>
       <c r="N33" s="15">
-        <v>76.263157894737105</v>
+        <v>1123</v>
       </c>
       <c r="O33" s="16">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="P33" s="17">
-        <v>1568.7</v>
+        <v>1460.8000000000002</v>
       </c>
       <c r="Q33" s="14">
-        <v>19.785123966942148</v>
+        <v>18.097686375321338</v>
       </c>
       <c r="R33" s="16">
-        <v>420.31578947368422</v>
+        <v>427.9</v>
       </c>
       <c r="S33" s="15">
-        <v>-4.1052631578947398</v>
+        <v>-37</v>
       </c>
       <c r="T33" s="18">
-        <v>1163</v>
+        <v>1021</v>
       </c>
       <c r="U33" s="17">
-        <v>4826.4500000000007</v>
+        <v>4237.1500000000005</v>
       </c>
       <c r="V33" s="14">
-        <v>10.960813492063492</v>
+        <v>9.5065176908752331</v>
       </c>
       <c r="W33" s="16">
-        <v>2334.3157894736842</v>
+        <v>2362.8000000000002</v>
       </c>
       <c r="X33" s="15">
-        <v>-534.68421052631584</v>
+        <v>-697.40000000000009</v>
       </c>
       <c r="Y33" s="18">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="Z33" s="17">
-        <v>95.45</v>
+        <v>962.80000000000007</v>
       </c>
       <c r="AA33" s="14">
-        <v>1.8755364806866952</v>
+        <v>18.70967741935484</v>
       </c>
       <c r="AB33" s="16">
-        <v>269.78947368421052</v>
+        <v>272.8</v>
       </c>
       <c r="AC33" s="15">
-        <v>-246.78947368421052</v>
+        <v>-40.800000000000011</v>
       </c>
       <c r="AD33" s="19">
-        <v>6867</v>
+        <v>8484</v>
       </c>
       <c r="AE33" s="20">
-        <v>28498.050000000003</v>
+        <v>35208.600000000006</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4638,19 +4640,19 @@
         <v>2813.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>12.754455445544554</v>
+        <v>13.425742574257425</v>
       </c>
       <c r="H34" s="30">
-        <v>1169.4736842105262</v>
+        <v>1111</v>
       </c>
       <c r="I34" s="15">
-        <v>146.42105263157896</v>
+        <v>173</v>
       </c>
       <c r="J34" s="16">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="K34" s="13">
-        <v>1062.4000000000001</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4659,20 +4661,20 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="O34" s="16">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P34" s="17"/>
       <c r="Q34" s="14">
-        <v>28.499999999999996</v>
+        <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>37.05263157894737</v>
+        <v>88</v>
       </c>
       <c r="S34" s="15">
-        <v>14.315789473684205</v>
+        <v>-80</v>
       </c>
       <c r="T34" s="18">
         <v>122</v>
@@ -4681,13 +4683,13 @@
         <v>506.30000000000007</v>
       </c>
       <c r="V34" s="14">
-        <v>21.072727272727271</v>
+        <v>22.181818181818183</v>
       </c>
       <c r="W34" s="16">
-        <v>127.36842105263159</v>
+        <v>121</v>
       </c>
       <c r="X34" s="15">
-        <v>29.368421052631575</v>
+        <v>34</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4705,10 +4707,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>1136</v>
+        <v>832</v>
       </c>
       <c r="AE34" s="20">
-        <v>4714.4000000000005</v>
+        <v>3452.8</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4743,85 +4745,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="F35" s="14">
-        <v>2366.7599999999998</v>
+        <v>2356.98</v>
       </c>
       <c r="G35" s="14">
-        <v>3.3705558949297494</v>
+        <v>3.3414211438474868</v>
       </c>
       <c r="H35" s="30">
-        <v>9477.3684210526317</v>
+        <v>9520.5</v>
       </c>
       <c r="I35" s="15">
-        <v>-2855.894736842105</v>
+        <v>-2881.5</v>
       </c>
       <c r="J35" s="16">
-        <v>3207</v>
+        <v>2541</v>
       </c>
       <c r="K35" s="13">
-        <v>5227.41</v>
+        <v>4141.83</v>
       </c>
       <c r="L35" s="14">
-        <v>19.49232245681382</v>
+        <v>15.527039413382218</v>
       </c>
       <c r="M35" s="30">
-        <v>3619.5789473684208</v>
+        <v>3600.3</v>
       </c>
       <c r="N35" s="15">
-        <v>1561.7368421052633</v>
+        <v>904.5</v>
       </c>
       <c r="O35" s="16">
-        <v>739</v>
+        <v>708</v>
       </c>
       <c r="P35" s="17">
-        <v>1204.57</v>
+        <v>1154.04</v>
       </c>
       <c r="Q35" s="14">
-        <v>19.888101983002834</v>
+        <v>19.213025780189959</v>
       </c>
       <c r="R35" s="16">
-        <v>817.47368421052624</v>
+        <v>810.7</v>
       </c>
       <c r="S35" s="15">
-        <v>-4.1578947368420813</v>
+        <v>-29</v>
       </c>
       <c r="T35" s="18">
-        <v>567</v>
+        <v>445</v>
       </c>
       <c r="U35" s="17">
-        <v>924.20999999999992</v>
+        <v>725.34999999999991</v>
       </c>
       <c r="V35" s="14">
-        <v>12.570595099183196</v>
+        <v>9.2708333333333339</v>
       </c>
       <c r="W35" s="16">
-        <v>992.31578947368428</v>
+        <v>1056</v>
       </c>
       <c r="X35" s="15">
-        <v>-154.68421052631584</v>
+        <v>-323</v>
       </c>
       <c r="Y35" s="18">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="Z35" s="17">
-        <v>376.53</v>
+        <v>453.14</v>
       </c>
       <c r="AA35" s="14">
-        <v>17.34782608695652</v>
+        <v>21.384615384615383</v>
       </c>
       <c r="AB35" s="16">
-        <v>292.94736842105266</v>
+        <v>286</v>
       </c>
       <c r="AC35" s="15">
-        <v>-61.947368421052659</v>
+        <v>-8</v>
       </c>
       <c r="AD35" s="19">
-        <v>6196</v>
+        <v>5418</v>
       </c>
       <c r="AE35" s="20">
-        <v>10099.48</v>
+        <v>8831.34</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4856,85 +4858,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>3894</v>
+        <v>5729</v>
       </c>
       <c r="F36" s="14">
-        <v>6347.2199999999993</v>
+        <v>9338.2699999999986</v>
       </c>
       <c r="G36" s="14">
-        <v>6.133300174086048</v>
+        <v>9.0184966548602912</v>
       </c>
       <c r="H36" s="30">
-        <v>13967.684210526317</v>
+        <v>13975.5</v>
       </c>
       <c r="I36" s="15">
-        <v>-2454.9473684210534</v>
+        <v>-623.5</v>
       </c>
       <c r="J36" s="16">
-        <v>4332</v>
+        <v>1742</v>
       </c>
       <c r="K36" s="13">
-        <v>7061.16</v>
+        <v>2839.46</v>
       </c>
       <c r="L36" s="14">
-        <v>19.321126760563381</v>
+        <v>7.7715815302252951</v>
       </c>
       <c r="M36" s="30">
-        <v>4932.6315789473683</v>
+        <v>4931.3</v>
       </c>
       <c r="N36" s="15">
-        <v>2089.894736842105</v>
+        <v>-499.5</v>
       </c>
       <c r="O36" s="16">
-        <v>1678</v>
+        <v>1555</v>
       </c>
       <c r="P36" s="17">
-        <v>2735.14</v>
+        <v>2534.6499999999996</v>
       </c>
       <c r="Q36" s="14">
-        <v>18.396999422965955</v>
+        <v>16.838115863562535</v>
       </c>
       <c r="R36" s="16">
-        <v>2006.6315789473686</v>
+        <v>2031.6999999999998</v>
       </c>
       <c r="S36" s="15">
-        <v>-146.21052631578959</v>
+        <v>-292</v>
       </c>
       <c r="T36" s="18">
-        <v>1399</v>
+        <v>1193</v>
       </c>
       <c r="U36" s="17">
-        <v>2280.37</v>
+        <v>1944.59</v>
       </c>
       <c r="V36" s="14">
-        <v>13.575587334014299</v>
+        <v>11.196621304551854</v>
       </c>
       <c r="W36" s="16">
-        <v>2267.1578947368421</v>
+        <v>2344.1</v>
       </c>
       <c r="X36" s="15">
-        <v>-249.84210526315792</v>
+        <v>-511.79999999999995</v>
       </c>
       <c r="Y36" s="18">
-        <v>186</v>
+        <v>480</v>
       </c>
       <c r="Z36" s="17">
-        <v>303.18</v>
+        <v>782.4</v>
       </c>
       <c r="AA36" s="14">
-        <v>7.5512820512820502</v>
+        <v>19.277108433734941</v>
       </c>
       <c r="AB36" s="16">
-        <v>541.89473684210532</v>
+        <v>547.79999999999995</v>
       </c>
       <c r="AC36" s="15">
-        <v>-355.89473684210532</v>
+        <v>-67.799999999999955</v>
       </c>
       <c r="AD36" s="19">
-        <v>11489</v>
+        <v>10699</v>
       </c>
       <c r="AE36" s="20">
-        <v>18727.07</v>
+        <v>17439.37</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4969,85 +4971,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>875</v>
+        <v>616</v>
       </c>
       <c r="F37" s="14">
-        <v>1426.25</v>
+        <v>1004.0799999999999</v>
       </c>
       <c r="G37" s="14">
-        <v>3.0199818346957308</v>
+        <v>2.1482127288578901</v>
       </c>
       <c r="H37" s="30">
-        <v>6374.21052631579</v>
+        <v>6308.5</v>
       </c>
       <c r="I37" s="15">
-        <v>-2022.3684210526317</v>
+        <v>-2251.5</v>
       </c>
       <c r="J37" s="16">
-        <v>211</v>
+        <v>3225</v>
       </c>
       <c r="K37" s="13">
-        <v>343.92999999999995</v>
+        <v>5256.75</v>
       </c>
       <c r="L37" s="14">
-        <v>1.5617452278924815</v>
+        <v>24.431818181818183</v>
       </c>
       <c r="M37" s="30">
-        <v>2972.3157894736842</v>
+        <v>2904</v>
       </c>
       <c r="N37" s="15">
-        <v>-1140.0526315789475</v>
+        <v>1905</v>
       </c>
       <c r="O37" s="16">
-        <v>1059</v>
+        <v>989</v>
       </c>
       <c r="P37" s="17">
-        <v>1726.1699999999998</v>
+        <v>1612.07</v>
       </c>
       <c r="Q37" s="14">
-        <v>17.981233243967829</v>
+        <v>16.691983122362871</v>
       </c>
       <c r="R37" s="16">
-        <v>1295.6842105263158</v>
+        <v>1303.5</v>
       </c>
       <c r="S37" s="15">
-        <v>-118.89473684210543</v>
+        <v>-196</v>
       </c>
       <c r="T37" s="18">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="U37" s="17">
-        <v>676.44999999999993</v>
+        <v>603.09999999999991</v>
       </c>
       <c r="V37" s="14">
-        <v>7.2472426470588225</v>
+        <v>6.6606660666066606</v>
       </c>
       <c r="W37" s="16">
-        <v>1259.7894736842106</v>
+        <v>1222.0999999999999</v>
       </c>
       <c r="X37" s="15">
-        <v>-501.21052631578959</v>
+        <v>-518.79999999999995</v>
       </c>
       <c r="Y37" s="18">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="Z37" s="17">
-        <v>0</v>
+        <v>352.08</v>
       </c>
       <c r="AA37" s="14">
-        <v>0</v>
+        <v>17.560975609756095</v>
       </c>
       <c r="AB37" s="16">
-        <v>284.84210526315792</v>
+        <v>270.60000000000002</v>
       </c>
       <c r="AC37" s="15">
-        <v>-284.84210526315792</v>
+        <v>-54.600000000000023</v>
       </c>
       <c r="AD37" s="19">
-        <v>2560</v>
+        <v>5416</v>
       </c>
       <c r="AE37" s="20">
-        <v>4172.7999999999993</v>
+        <v>8828.08</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5082,85 +5084,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>536</v>
+        <v>1658</v>
       </c>
       <c r="F38" s="14">
-        <v>873.68</v>
+        <v>2702.54</v>
       </c>
       <c r="G38" s="14">
-        <v>2.7487179487179487</v>
+        <v>8.1414191013994603</v>
       </c>
       <c r="H38" s="30">
-        <v>4290</v>
+        <v>4480.3</v>
       </c>
       <c r="I38" s="15">
-        <v>-1414</v>
+        <v>-378.5</v>
       </c>
       <c r="J38" s="16">
-        <v>3441</v>
+        <v>1784</v>
       </c>
       <c r="K38" s="13">
-        <v>5608.83</v>
+        <v>2907.9199999999996</v>
       </c>
       <c r="L38" s="14">
-        <v>30.324211502782937</v>
+        <v>15.808595480726629</v>
       </c>
       <c r="M38" s="30">
-        <v>2496.4210526315787</v>
+        <v>2482.6999999999998</v>
       </c>
       <c r="N38" s="15">
-        <v>2306.2631578947371</v>
+        <v>655.5</v>
       </c>
       <c r="O38" s="16">
-        <v>693</v>
+        <v>633</v>
       </c>
       <c r="P38" s="17">
-        <v>1129.5899999999999</v>
+        <v>1031.79</v>
       </c>
       <c r="Q38" s="14">
-        <v>18.415384615384617</v>
+        <v>16.356589147286819</v>
       </c>
       <c r="R38" s="16">
-        <v>827.8947368421052</v>
+        <v>851.40000000000009</v>
       </c>
       <c r="S38" s="15">
-        <v>-59.631578947368325</v>
+        <v>-141</v>
       </c>
       <c r="T38" s="18">
-        <v>480</v>
+        <v>2207</v>
       </c>
       <c r="U38" s="17">
-        <v>782.4</v>
+        <v>3597.41</v>
       </c>
       <c r="V38" s="14">
-        <v>13.333333333333334</v>
+        <v>58.386243386243393</v>
       </c>
       <c r="W38" s="16">
-        <v>792</v>
+        <v>831.59999999999991</v>
       </c>
       <c r="X38" s="15">
-        <v>-96</v>
+        <v>1602.2</v>
       </c>
       <c r="Y38" s="18">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="Z38" s="17">
-        <v>135.29</v>
+        <v>735.13</v>
       </c>
       <c r="AA38" s="14">
-        <v>3.0210727969348659</v>
+        <v>16.954887218045112</v>
       </c>
       <c r="AB38" s="16">
-        <v>604.42105263157896</v>
+        <v>585.20000000000005</v>
       </c>
       <c r="AC38" s="15">
-        <v>-521.42105263157896</v>
+        <v>-134.20000000000005</v>
       </c>
       <c r="AD38" s="19">
-        <v>5233</v>
+        <v>6733</v>
       </c>
       <c r="AE38" s="20">
-        <v>8529.7899999999991</v>
+        <v>10974.789999999999</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5195,85 +5197,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1091</v>
+        <v>970</v>
       </c>
       <c r="F39" s="14">
-        <v>1778.33</v>
+        <v>1581.1</v>
       </c>
       <c r="G39" s="14">
-        <v>10.635710620831196</v>
+        <v>9.2161520190023758</v>
       </c>
       <c r="H39" s="30">
-        <v>2256.7368421052633</v>
+        <v>2315.5</v>
       </c>
       <c r="I39" s="15">
-        <v>65.210526315789366</v>
+        <v>-82.5</v>
       </c>
       <c r="J39" s="16">
-        <v>2525</v>
+        <v>2480</v>
       </c>
       <c r="K39" s="13">
-        <v>4115.75</v>
+        <v>4042.3999999999996</v>
       </c>
       <c r="L39" s="14">
-        <v>45.517077798861479</v>
+        <v>44.644464446444644</v>
       </c>
       <c r="M39" s="30">
-        <v>1220.421052631579</v>
+        <v>1222.0999999999999</v>
       </c>
       <c r="N39" s="15">
-        <v>1970.2631578947369</v>
+        <v>1924.5</v>
       </c>
       <c r="O39" s="16">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="P39" s="17">
-        <v>999.18999999999994</v>
+        <v>981.26</v>
       </c>
       <c r="Q39" s="14">
-        <v>20.947841726618705</v>
+        <v>21.234567901234566</v>
       </c>
       <c r="R39" s="16">
-        <v>643.78947368421052</v>
+        <v>623.70000000000005</v>
       </c>
       <c r="S39" s="15">
-        <v>27.736842105263122</v>
+        <v>35</v>
       </c>
       <c r="T39" s="18">
-        <v>645</v>
+        <v>549</v>
       </c>
       <c r="U39" s="17">
-        <v>1051.3499999999999</v>
+        <v>894.86999999999989</v>
       </c>
       <c r="V39" s="14">
-        <v>11.817743490838959</v>
+        <v>9.6740088105726869</v>
       </c>
       <c r="W39" s="16">
-        <v>1200.7368421052631</v>
+        <v>1248.5</v>
       </c>
       <c r="X39" s="15">
-        <v>-228.26315789473676</v>
+        <v>-359</v>
       </c>
       <c r="Y39" s="18">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="Z39" s="17">
-        <v>702.53</v>
+        <v>676.44999999999993</v>
       </c>
       <c r="AA39" s="14">
-        <v>98.662650602409641</v>
+        <v>83.838383838383834</v>
       </c>
       <c r="AB39" s="16">
-        <v>96.10526315789474</v>
+        <v>108.9</v>
       </c>
       <c r="AC39" s="15">
-        <v>334.89473684210526</v>
+        <v>306.10000000000002</v>
       </c>
       <c r="AD39" s="19">
-        <v>5305</v>
+        <v>5016</v>
       </c>
       <c r="AE39" s="20">
-        <v>8647.15</v>
+        <v>8176.079999999999</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5308,85 +5310,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1033</v>
+        <v>1418</v>
       </c>
       <c r="F40" s="14">
-        <v>1683.79</v>
+        <v>2311.3399999999997</v>
       </c>
       <c r="G40" s="14">
-        <v>7.8039761431411527</v>
+        <v>10.339044841414509</v>
       </c>
       <c r="H40" s="30">
-        <v>2912.105263157895</v>
+        <v>3017.3</v>
       </c>
       <c r="I40" s="15">
-        <v>-290.68421052631584</v>
+        <v>46.5</v>
       </c>
       <c r="J40" s="16">
-        <v>1228</v>
+        <v>634</v>
       </c>
       <c r="K40" s="13">
-        <v>2001.6399999999999</v>
+        <v>1033.4199999999998</v>
       </c>
       <c r="L40" s="14">
-        <v>18.984540276647678</v>
+        <v>9.3303899926416474</v>
       </c>
       <c r="M40" s="30">
-        <v>1423.0526315789475</v>
+        <v>1494.9</v>
       </c>
       <c r="N40" s="15">
-        <v>581.15789473684208</v>
+        <v>-45.5</v>
       </c>
       <c r="O40" s="16">
-        <v>764</v>
+        <v>721</v>
       </c>
       <c r="P40" s="17">
-        <v>1245.32</v>
+        <v>1175.23</v>
       </c>
       <c r="Q40" s="14">
-        <v>21.441654357459381</v>
+        <v>20.027777777777779</v>
       </c>
       <c r="R40" s="16">
-        <v>783.8947368421052</v>
+        <v>792</v>
       </c>
       <c r="S40" s="15">
-        <v>51.368421052631675</v>
+        <v>1</v>
       </c>
       <c r="T40" s="18">
-        <v>772</v>
+        <v>664</v>
       </c>
       <c r="U40" s="17">
-        <v>1258.3599999999999</v>
+        <v>1082.32</v>
       </c>
       <c r="V40" s="14">
-        <v>12.192851205320032</v>
+        <v>10.114242193450114</v>
       </c>
       <c r="W40" s="16">
-        <v>1392.9473684210527</v>
+        <v>1444.3000000000002</v>
       </c>
       <c r="X40" s="15">
-        <v>-241.0526315789474</v>
+        <v>-386.40000000000009</v>
       </c>
       <c r="Y40" s="18">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="Z40" s="17">
-        <v>713.93999999999994</v>
+        <v>699.27</v>
       </c>
       <c r="AA40" s="14">
-        <v>99.071428571428555</v>
+        <v>92.258064516129025</v>
       </c>
       <c r="AB40" s="16">
-        <v>97.26315789473685</v>
+        <v>102.30000000000001</v>
       </c>
       <c r="AC40" s="15">
-        <v>340.73684210526312</v>
+        <v>326.7</v>
       </c>
       <c r="AD40" s="19">
-        <v>4235</v>
+        <v>3866</v>
       </c>
       <c r="AE40" s="20">
-        <v>6903.0499999999993</v>
+        <v>6301.58</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5421,85 +5423,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>392</v>
+        <v>616</v>
       </c>
       <c r="F41" s="14">
-        <v>2410.8000000000002</v>
+        <v>3788.4</v>
       </c>
       <c r="G41" s="14">
-        <v>5.7248270561106844</v>
+        <v>9.2008961911874536</v>
       </c>
       <c r="H41" s="30">
-        <v>1506.421052631579</v>
+        <v>1472.9</v>
       </c>
       <c r="I41" s="15">
-        <v>-292.73684210526312</v>
+        <v>-53.5</v>
       </c>
       <c r="J41" s="16">
-        <v>638</v>
+        <v>333</v>
       </c>
       <c r="K41" s="13">
-        <v>3923.7000000000003</v>
+        <v>2047.95</v>
       </c>
       <c r="L41" s="14">
-        <v>16.514986376021799</v>
+        <v>8.9156626506024086</v>
       </c>
       <c r="M41" s="30">
-        <v>849.8947368421052</v>
+        <v>821.7</v>
       </c>
       <c r="N41" s="15">
-        <v>251.68421052631584</v>
+        <v>-40.5</v>
       </c>
       <c r="O41" s="16">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P41" s="17">
-        <v>387.45000000000005</v>
+        <v>369</v>
       </c>
       <c r="Q41" s="14">
-        <v>13.153846153846153</v>
+        <v>12.76595744680851</v>
       </c>
       <c r="R41" s="16">
-        <v>105.36842105263159</v>
+        <v>103.4</v>
       </c>
       <c r="S41" s="15">
-        <v>-32.789473684210535</v>
+        <v>-34</v>
       </c>
       <c r="T41" s="18">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="U41" s="17">
-        <v>971.7</v>
+        <v>651.90000000000009</v>
       </c>
       <c r="V41" s="14">
-        <v>14.572815533980581</v>
+        <v>8.346456692913387</v>
       </c>
       <c r="W41" s="16">
-        <v>238.5263157894737</v>
+        <v>279.39999999999998</v>
       </c>
       <c r="X41" s="15">
-        <v>-15.473684210526329</v>
+        <v>-97.199999999999989</v>
       </c>
       <c r="Y41" s="18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Z41" s="17">
-        <v>0</v>
+        <v>590.40000000000009</v>
       </c>
       <c r="AA41" s="14">
-        <v>0</v>
+        <v>23.414634146341466</v>
       </c>
       <c r="AB41" s="16">
-        <v>94.94736842105263</v>
+        <v>90.199999999999989</v>
       </c>
       <c r="AC41" s="15">
-        <v>-94.94736842105263</v>
+        <v>5.8000000000000114</v>
       </c>
       <c r="AD41" s="19">
-        <v>1251</v>
+        <v>1211</v>
       </c>
       <c r="AE41" s="20">
-        <v>7693.6500000000005</v>
+        <v>7447.6500000000005</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5534,64 +5536,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>298</v>
+        <v>389</v>
       </c>
       <c r="F42" s="14">
-        <v>1832.7</v>
+        <v>2392.3500000000004</v>
       </c>
       <c r="G42" s="14">
-        <v>4.0704529115744066</v>
+        <v>5.1901267511674449</v>
       </c>
       <c r="H42" s="30">
-        <v>1610.6315789473686</v>
+        <v>1648.9</v>
       </c>
       <c r="I42" s="15">
-        <v>-434.1052631578948</v>
+        <v>-360.5</v>
       </c>
       <c r="J42" s="16">
-        <v>632</v>
+        <v>352</v>
       </c>
       <c r="K42" s="13">
-        <v>3886.8</v>
+        <v>2164.8000000000002</v>
       </c>
       <c r="L42" s="14">
-        <v>15.655801825293349</v>
+        <v>8.7890137328339577</v>
       </c>
       <c r="M42" s="30">
-        <v>888.1052631578948</v>
+        <v>881.09999999999991</v>
       </c>
       <c r="N42" s="15">
-        <v>228.31578947368416</v>
+        <v>-48.5</v>
       </c>
       <c r="O42" s="16">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P42" s="17">
-        <v>719.55000000000007</v>
+        <v>707.25</v>
       </c>
       <c r="Q42" s="14">
-        <v>16.226277372262775</v>
+        <v>16.546762589928058</v>
       </c>
       <c r="R42" s="16">
-        <v>158.63157894736841</v>
+        <v>152.9</v>
       </c>
       <c r="S42" s="15">
-        <v>-27.21052631578948</v>
+        <v>-24</v>
       </c>
       <c r="T42" s="18">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="U42" s="17">
-        <v>1568.25</v>
+        <v>1211.5500000000002</v>
       </c>
       <c r="V42" s="14">
-        <v>16.043046357615896</v>
+        <v>11.005586592178771</v>
       </c>
       <c r="W42" s="16">
-        <v>349.68421052631578</v>
+        <v>393.79999999999995</v>
       </c>
       <c r="X42" s="15">
-        <v>0.68421052631580892</v>
+        <v>-89.399999999999977</v>
       </c>
       <c r="Y42" s="18">
         <v>82</v>
@@ -5600,19 +5602,19 @@
         <v>504.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>26.406779661016952</v>
+        <v>27.796610169491522</v>
       </c>
       <c r="AB42" s="16">
-        <v>68.315789473684205</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="AC42" s="15">
-        <v>13.684210526315795</v>
+        <v>17.099999999999994</v>
       </c>
       <c r="AD42" s="19">
-        <v>1384</v>
+        <v>1135</v>
       </c>
       <c r="AE42" s="20">
-        <v>8511.6</v>
+        <v>6980.25</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5647,85 +5649,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>1919</v>
+        <v>2452</v>
       </c>
       <c r="F43" s="14">
-        <v>2226.04</v>
+        <v>2844.3199999999997</v>
       </c>
       <c r="G43" s="14">
-        <v>5.7095208268086441</v>
+        <v>7.2856930619521618</v>
       </c>
       <c r="H43" s="30">
-        <v>7394.3157894736842</v>
+        <v>7404.1</v>
       </c>
       <c r="I43" s="15">
-        <v>-1442.0526315789475</v>
+        <v>-913.5</v>
       </c>
       <c r="J43" s="16">
-        <v>2476</v>
+        <v>3846</v>
       </c>
       <c r="K43" s="13">
-        <v>2872.16</v>
+        <v>4461.3599999999997</v>
       </c>
       <c r="L43" s="14">
-        <v>10.244773519163763</v>
+        <v>15.981716185331393</v>
       </c>
       <c r="M43" s="30">
-        <v>5317.0526315789475</v>
+        <v>5294.3</v>
       </c>
       <c r="N43" s="15">
-        <v>59.157894736842081</v>
+        <v>1439.5</v>
       </c>
       <c r="O43" s="16">
-        <v>844</v>
+        <v>772</v>
       </c>
       <c r="P43" s="17">
-        <v>979.04</v>
+        <v>895.52</v>
       </c>
       <c r="Q43" s="14">
-        <v>18.347826086956523</v>
+        <v>16.40807651434644</v>
       </c>
       <c r="R43" s="16">
-        <v>1012</v>
+        <v>1035.0999999999999</v>
       </c>
       <c r="S43" s="15">
-        <v>-76</v>
+        <v>-169</v>
       </c>
       <c r="T43" s="18">
-        <v>1465</v>
+        <v>1236</v>
       </c>
       <c r="U43" s="17">
-        <v>1699.3999999999999</v>
+        <v>1433.76</v>
       </c>
       <c r="V43" s="14">
-        <v>12.133827375762859</v>
+        <v>10.189612530915086</v>
       </c>
       <c r="W43" s="16">
-        <v>2656.2105263157896</v>
+        <v>2668.6</v>
       </c>
       <c r="X43" s="15">
-        <v>-466.78947368421063</v>
+        <v>-704.8</v>
       </c>
       <c r="Y43" s="18">
-        <v>15</v>
+        <v>548</v>
       </c>
       <c r="Z43" s="17">
-        <v>17.399999999999999</v>
+        <v>635.67999999999995</v>
       </c>
       <c r="AA43" s="14">
-        <v>0.51258992805755399</v>
+        <v>19.46714031971581</v>
       </c>
       <c r="AB43" s="16">
-        <v>643.78947368421052</v>
+        <v>619.29999999999995</v>
       </c>
       <c r="AC43" s="15">
-        <v>-628.78947368421052</v>
+        <v>-71.299999999999955</v>
       </c>
       <c r="AD43" s="19">
-        <v>6719</v>
+        <v>8854</v>
       </c>
       <c r="AE43" s="20">
-        <v>7794.0399999999991</v>
+        <v>10270.64</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5760,85 +5762,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2616</v>
+        <v>2725</v>
       </c>
       <c r="F44" s="14">
-        <v>3034.56</v>
+        <v>3161</v>
       </c>
       <c r="G44" s="14">
-        <v>8.9524495677233435</v>
+        <v>9.4997385393062572</v>
       </c>
       <c r="H44" s="30">
-        <v>6428.6315789473683</v>
+        <v>6310.7000000000007</v>
       </c>
       <c r="I44" s="15">
-        <v>-306.10526315789502</v>
+        <v>-143.5</v>
       </c>
       <c r="J44" s="16">
-        <v>3207</v>
+        <v>6479</v>
       </c>
       <c r="K44" s="13">
-        <v>3720.12</v>
+        <v>7515.6399999999994</v>
       </c>
       <c r="L44" s="14">
-        <v>17.227311280746395</v>
+        <v>35.173724212812161</v>
       </c>
       <c r="M44" s="30">
-        <v>4095.4736842105262</v>
+        <v>4052.3999999999996</v>
       </c>
       <c r="N44" s="15">
-        <v>1345.421052631579</v>
+        <v>4637</v>
       </c>
       <c r="O44" s="16">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="P44" s="17">
-        <v>643.79999999999995</v>
+        <v>620.59999999999991</v>
       </c>
       <c r="Q44" s="14">
-        <v>20.201149425287358</v>
+        <v>19.597069597069595</v>
       </c>
       <c r="R44" s="16">
-        <v>604.42105263157896</v>
+        <v>600.6</v>
       </c>
       <c r="S44" s="15">
-        <v>5.526315789473756</v>
+        <v>-11</v>
       </c>
       <c r="T44" s="18">
-        <v>911</v>
+        <v>776</v>
       </c>
       <c r="U44" s="17">
-        <v>1056.76</v>
+        <v>900.16</v>
       </c>
       <c r="V44" s="14">
-        <v>14.164484451718495</v>
+        <v>11.829268292682928</v>
       </c>
       <c r="W44" s="16">
-        <v>1414.9473684210525</v>
+        <v>1443.1999999999998</v>
       </c>
       <c r="X44" s="15">
-        <v>-118.05263157894728</v>
+        <v>-273.59999999999991</v>
       </c>
       <c r="Y44" s="18">
-        <v>97</v>
+        <v>457</v>
       </c>
       <c r="Z44" s="17">
-        <v>112.52</v>
+        <v>530.12</v>
       </c>
       <c r="AA44" s="14">
-        <v>3.4066543438077637</v>
+        <v>16.350626118067979</v>
       </c>
       <c r="AB44" s="16">
-        <v>626.42105263157896</v>
+        <v>614.9</v>
       </c>
       <c r="AC44" s="15">
-        <v>-529.42105263157896</v>
+        <v>-157.89999999999998</v>
       </c>
       <c r="AD44" s="19">
-        <v>7386</v>
+        <v>10972</v>
       </c>
       <c r="AE44" s="20">
-        <v>8567.76</v>
+        <v>12727.519999999999</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5873,85 +5875,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2926</v>
+        <v>2956</v>
       </c>
       <c r="F45" s="14">
-        <v>3394.16</v>
+        <v>3428.9599999999996</v>
       </c>
       <c r="G45" s="14">
-        <v>7.5885885885885891</v>
+        <v>7.7099634846113725</v>
       </c>
       <c r="H45" s="30">
-        <v>8482.7368421052633</v>
+        <v>8434.7999999999993</v>
       </c>
       <c r="I45" s="15">
-        <v>-929.78947368421041</v>
+        <v>-878</v>
       </c>
       <c r="J45" s="16">
-        <v>3339</v>
+        <v>7427</v>
       </c>
       <c r="K45" s="13">
-        <v>3873.24</v>
+        <v>8615.32</v>
       </c>
       <c r="L45" s="14">
-        <v>13.452290076335878</v>
+        <v>30.209477323571285</v>
       </c>
       <c r="M45" s="30">
-        <v>5460.6315789473683</v>
+        <v>5408.7</v>
       </c>
       <c r="N45" s="15">
-        <v>856.89473684210498</v>
+        <v>4968.5</v>
       </c>
       <c r="O45" s="16">
-        <v>798</v>
+        <v>707</v>
       </c>
       <c r="P45" s="17">
-        <v>925.68</v>
+        <v>820.11999999999989</v>
       </c>
       <c r="Q45" s="14">
-        <v>18.580882352941178</v>
+        <v>15.693673695893454</v>
       </c>
       <c r="R45" s="16">
-        <v>944.84210526315792</v>
+        <v>991.09999999999991</v>
       </c>
       <c r="S45" s="15">
-        <v>-60.947368421052602</v>
+        <v>-194</v>
       </c>
       <c r="T45" s="18">
-        <v>1325</v>
+        <v>1163</v>
       </c>
       <c r="U45" s="17">
-        <v>1537</v>
+        <v>1349.08</v>
       </c>
       <c r="V45" s="14">
-        <v>13.862885462555067</v>
+        <v>12.152560083594565</v>
       </c>
       <c r="W45" s="16">
-        <v>2102.7368421052633</v>
+        <v>2105.4</v>
       </c>
       <c r="X45" s="15">
-        <v>-204.26315789473688</v>
+        <v>-368.20000000000005</v>
       </c>
       <c r="Y45" s="18">
-        <v>50</v>
+        <v>472</v>
       </c>
       <c r="Z45" s="17">
-        <v>57.999999999999993</v>
+        <v>547.52</v>
       </c>
       <c r="AA45" s="14">
-        <v>1.8375241779497098</v>
+        <v>17.912713472485766</v>
       </c>
       <c r="AB45" s="16">
-        <v>598.63157894736844</v>
+        <v>579.70000000000005</v>
       </c>
       <c r="AC45" s="15">
-        <v>-548.63157894736844</v>
+        <v>-107.70000000000005</v>
       </c>
       <c r="AD45" s="19">
-        <v>8438</v>
+        <v>12725</v>
       </c>
       <c r="AE45" s="20">
-        <v>9788.08</v>
+        <v>14760.999999999998</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5986,85 +5988,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2127</v>
+        <v>2398</v>
       </c>
       <c r="F46" s="14">
-        <v>2467.3199999999997</v>
+        <v>2781.68</v>
       </c>
       <c r="G46" s="14">
-        <v>7.5327120223671953</v>
+        <v>8.5934420354775121</v>
       </c>
       <c r="H46" s="30">
-        <v>6212.1052631578941</v>
+        <v>6139.1</v>
       </c>
       <c r="I46" s="15">
-        <v>-696.68421052631584</v>
+        <v>-392.5</v>
       </c>
       <c r="J46" s="16">
-        <v>1820</v>
+        <v>5041</v>
       </c>
       <c r="K46" s="13">
-        <v>2111.1999999999998</v>
+        <v>5847.5599999999995</v>
       </c>
       <c r="L46" s="14">
-        <v>11.604026845637584</v>
+        <v>32.648963730569946</v>
       </c>
       <c r="M46" s="30">
-        <v>3450.5263157894738</v>
+        <v>3396.8</v>
       </c>
       <c r="N46" s="15">
-        <v>251.57894736842104</v>
+        <v>3497</v>
       </c>
       <c r="O46" s="16">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="P46" s="17">
-        <v>614.79999999999995</v>
+        <v>569.55999999999995</v>
       </c>
       <c r="Q46" s="14">
-        <v>20.509164969450101</v>
+        <v>18.528301886792452</v>
       </c>
       <c r="R46" s="16">
-        <v>568.52631578947364</v>
+        <v>583</v>
       </c>
       <c r="S46" s="15">
-        <v>13.157894736842081</v>
+        <v>-39</v>
       </c>
       <c r="T46" s="18">
-        <v>656</v>
+        <v>584</v>
       </c>
       <c r="U46" s="17">
-        <v>760.95999999999992</v>
+        <v>677.43999999999994</v>
       </c>
       <c r="V46" s="14">
-        <v>16.797843665768195</v>
+        <v>14.784810126582279</v>
       </c>
       <c r="W46" s="16">
-        <v>859.15789473684208</v>
+        <v>869</v>
       </c>
       <c r="X46" s="15">
-        <v>31.157894736842081</v>
+        <v>-48</v>
       </c>
       <c r="Y46" s="18">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="Z46" s="17">
-        <v>0</v>
+        <v>626.4</v>
       </c>
       <c r="AA46" s="14">
-        <v>0</v>
+        <v>25.352112676056336</v>
       </c>
       <c r="AB46" s="16">
-        <v>493.26315789473688</v>
+        <v>468.6</v>
       </c>
       <c r="AC46" s="15">
-        <v>-493.26315789473688</v>
+        <v>71.399999999999977</v>
       </c>
       <c r="AD46" s="19">
-        <v>5133</v>
+        <v>9054</v>
       </c>
       <c r="AE46" s="20">
-        <v>5954.28</v>
+        <v>10502.64</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6112,19 +6114,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K47" s="13">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="L47" s="14">
-        <v>6.8793103448275854</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="M47" s="30">
-        <v>67.15789473684211</v>
+        <v>66</v>
       </c>
       <c r="N47" s="15">
-        <v>-9.526315789473685</v>
+        <v>-11</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6142,19 +6144,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U47" s="17">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="V47" s="14">
-        <v>15.200000000000001</v>
+        <v>15</v>
       </c>
       <c r="W47" s="16">
-        <v>23.157894736842103</v>
+        <v>22</v>
       </c>
       <c r="X47" s="15">
-        <v>-0.8421052631578938</v>
+        <v>-1</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6172,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AE47" s="20">
-        <v>666</v>
+        <v>612</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6229,13 +6231,13 @@
         <v>108</v>
       </c>
       <c r="L48" s="14">
-        <v>10.363636363636363</v>
+        <v>10.909090909090908</v>
       </c>
       <c r="M48" s="30">
-        <v>12.736842105263158</v>
+        <v>12.100000000000001</v>
       </c>
       <c r="N48" s="15">
-        <v>0.21052631578947345</v>
+        <v>0.5</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6321,34 +6323,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F49" s="14">
-        <v>48.72</v>
+        <v>31.319999999999997</v>
       </c>
       <c r="G49" s="14">
-        <v>0.78620689655172404</v>
+        <v>0.51625239005736145</v>
       </c>
       <c r="H49" s="30">
-        <v>1175.2631578947369</v>
+        <v>1150.5999999999999</v>
       </c>
       <c r="I49" s="15">
-        <v>-492.21052631578948</v>
+        <v>-496</v>
       </c>
       <c r="J49" s="16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K49" s="13">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="L49" s="14">
-        <v>8.4745762711864403E-2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="30">
-        <v>1298</v>
+        <v>1238.5999999999999</v>
       </c>
       <c r="N49" s="15">
-        <v>-585</v>
+        <v>-563</v>
       </c>
       <c r="O49" s="16">
         <v>38</v>
@@ -6357,13 +6359,13 @@
         <v>44.08</v>
       </c>
       <c r="Q49" s="14">
-        <v>4.8456375838926178</v>
+        <v>5.1006711409395971</v>
       </c>
       <c r="R49" s="16">
-        <v>172.52631578947367</v>
+        <v>163.9</v>
       </c>
       <c r="S49" s="15">
-        <v>-118.84210526315786</v>
+        <v>-111</v>
       </c>
       <c r="T49" s="18">
         <v>5</v>
@@ -6372,34 +6374,34 @@
         <v>5.8</v>
       </c>
       <c r="V49" s="14">
-        <v>0.41304347826086951</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="W49" s="16">
-        <v>266.31578947368422</v>
+        <v>253</v>
       </c>
       <c r="X49" s="15">
-        <v>-188.68421052631581</v>
+        <v>-179</v>
       </c>
       <c r="Y49" s="18">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z49" s="17">
-        <v>27.839999999999996</v>
+        <v>20.88</v>
       </c>
       <c r="AA49" s="14">
-        <v>5.0666666666666673</v>
+        <v>3.75</v>
       </c>
       <c r="AB49" s="16">
-        <v>104.21052631578947</v>
+        <v>105.6</v>
       </c>
       <c r="AC49" s="15">
-        <v>-80.210526315789465</v>
+        <v>-87.6</v>
       </c>
       <c r="AD49" s="19">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="AE49" s="20">
-        <v>132.23999999999998</v>
+        <v>102.08</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6434,64 +6436,64 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1557</v>
+        <v>1712</v>
       </c>
       <c r="F50" s="14">
-        <v>1806.12</v>
+        <v>1985.9199999999998</v>
       </c>
       <c r="G50" s="14">
-        <v>5.4530875576036859</v>
+        <v>5.9361997226074896</v>
       </c>
       <c r="H50" s="30">
-        <v>6281.5789473684217</v>
+        <v>6344.7999999999993</v>
       </c>
       <c r="I50" s="15">
-        <v>-1298.2631578947371</v>
+        <v>-1172</v>
       </c>
       <c r="J50" s="16">
-        <v>2333</v>
+        <v>1187</v>
       </c>
       <c r="K50" s="13">
-        <v>2706.2799999999997</v>
+        <v>1376.9199999999998</v>
       </c>
       <c r="L50" s="14">
-        <v>12.88950276243094</v>
+        <v>6.4827962861824142</v>
       </c>
       <c r="M50" s="30">
-        <v>3982</v>
+        <v>4028.2</v>
       </c>
       <c r="N50" s="15">
-        <v>523</v>
+        <v>-644</v>
       </c>
       <c r="O50" s="16">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="P50" s="17">
-        <v>199.51999999999998</v>
+        <v>139.19999999999999</v>
       </c>
       <c r="Q50" s="14">
-        <v>4.0196801968019678</v>
+        <v>2.7874564459930316</v>
       </c>
       <c r="R50" s="16">
-        <v>941.36842105263156</v>
+        <v>947.09999999999991</v>
       </c>
       <c r="S50" s="15">
-        <v>-683.78947368421052</v>
+        <v>-741</v>
       </c>
       <c r="T50" s="18">
-        <v>607</v>
+        <v>561</v>
       </c>
       <c r="U50" s="17">
-        <v>704.12</v>
+        <v>650.76</v>
       </c>
       <c r="V50" s="14">
-        <v>15.43908969210174</v>
+        <v>14.571428571428571</v>
       </c>
       <c r="W50" s="16">
-        <v>864.94736842105272</v>
+        <v>847</v>
       </c>
       <c r="X50" s="15">
-        <v>-22.052631578947398</v>
+        <v>-55</v>
       </c>
       <c r="Y50" s="18">
         <v>27</v>
@@ -6500,19 +6502,19 @@
         <v>31.319999999999997</v>
       </c>
       <c r="AA50" s="14">
-        <v>2.408450704225352</v>
+        <v>2.5352112676056335</v>
       </c>
       <c r="AB50" s="16">
-        <v>246.63157894736844</v>
+        <v>234.3</v>
       </c>
       <c r="AC50" s="15">
-        <v>-219.63157894736844</v>
+        <v>-207.3</v>
       </c>
       <c r="AD50" s="19">
-        <v>4696</v>
+        <v>3607</v>
       </c>
       <c r="AE50" s="20">
-        <v>5447.36</v>
+        <v>4184.12</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6550,85 +6552,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>919</v>
+        <v>1272</v>
       </c>
       <c r="F51" s="14">
-        <v>1066.04</v>
+        <v>1475.52</v>
       </c>
       <c r="G51" s="14">
-        <v>4.9006455234353075</v>
+        <v>6.7230443974630028</v>
       </c>
       <c r="H51" s="30">
-        <v>4125.5789473684208</v>
+        <v>4162.3999999999996</v>
       </c>
       <c r="I51" s="15">
-        <v>-956.26315789473665</v>
+        <v>-620</v>
       </c>
       <c r="J51" s="16">
-        <v>1982</v>
+        <v>1249</v>
       </c>
       <c r="K51" s="13">
-        <v>2299.12</v>
+        <v>1448.84</v>
       </c>
       <c r="L51" s="14">
-        <v>12.116473616473618</v>
+        <v>7.6837896031990152</v>
       </c>
       <c r="M51" s="30">
-        <v>3598.7368421052629</v>
+        <v>3576.1000000000004</v>
       </c>
       <c r="N51" s="15">
-        <v>346.21052631578959</v>
+        <v>-376.5</v>
       </c>
       <c r="O51" s="16">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P51" s="17">
-        <v>299.27999999999997</v>
+        <v>291.15999999999997</v>
       </c>
       <c r="Q51" s="14">
-        <v>18.638783269961976</v>
+        <v>18.801498127340825</v>
       </c>
       <c r="R51" s="16">
-        <v>304.5263157894737</v>
+        <v>293.7</v>
       </c>
       <c r="S51" s="15">
-        <v>-18.842105263157919</v>
+        <v>-16</v>
       </c>
       <c r="T51" s="18">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="U51" s="17">
-        <v>542.88</v>
+        <v>517.36</v>
       </c>
       <c r="V51" s="14">
-        <v>13.722222222222221</v>
+        <v>13.313432835820896</v>
       </c>
       <c r="W51" s="16">
-        <v>750.31578947368428</v>
+        <v>737</v>
       </c>
       <c r="X51" s="15">
-        <v>-77.684210526315837</v>
+        <v>-90</v>
       </c>
       <c r="Y51" s="18">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="Z51" s="17">
-        <v>90.47999999999999</v>
+        <v>146.16</v>
       </c>
       <c r="AA51" s="14">
-        <v>18.759493670886076</v>
+        <v>29.647058823529413</v>
       </c>
       <c r="AB51" s="16">
-        <v>91.473684210526315</v>
+        <v>93.5</v>
       </c>
       <c r="AC51" s="15">
-        <v>-13.473684210526315</v>
+        <v>32.5</v>
       </c>
       <c r="AD51" s="19">
-        <v>3705</v>
+        <v>3344</v>
       </c>
       <c r="AE51" s="20">
-        <v>4297.7999999999993</v>
+        <v>3879.0399999999995</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6667,85 +6669,85 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>2022</v>
+        <v>1860</v>
       </c>
       <c r="F52" s="14">
-        <v>1637.8200000000002</v>
+        <v>1506.6000000000001</v>
       </c>
       <c r="G52" s="14">
-        <v>12.844533600802405</v>
+        <v>11.824539097266369</v>
       </c>
       <c r="H52" s="30">
-        <v>3463.2631578947371</v>
+        <v>3460.6000000000004</v>
       </c>
       <c r="I52" s="15">
-        <v>447.78947368421041</v>
+        <v>287</v>
       </c>
       <c r="J52" s="16">
-        <v>3982</v>
+        <v>3888</v>
       </c>
       <c r="K52" s="13">
-        <v>3225.42</v>
+        <v>3149.28</v>
       </c>
       <c r="L52" s="14">
-        <v>84.251670378619139</v>
+        <v>80.24767801857584</v>
       </c>
       <c r="M52" s="30">
-        <v>1039.7894736842106</v>
+        <v>1065.9000000000001</v>
       </c>
       <c r="N52" s="15">
-        <v>3509.3684210526317</v>
+        <v>3403.5</v>
       </c>
       <c r="O52" s="16">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="P52" s="17">
-        <v>110.97000000000001</v>
+        <v>33.21</v>
       </c>
       <c r="Q52" s="14">
-        <v>19.139705882352938</v>
+        <v>3.5344827586206899</v>
       </c>
       <c r="R52" s="16">
-        <v>157.47368421052633</v>
+        <v>255.2</v>
       </c>
       <c r="S52" s="15">
-        <v>-6.1578947368421382</v>
+        <v>-191</v>
       </c>
       <c r="T52" s="18">
-        <v>372</v>
+        <v>276</v>
       </c>
       <c r="U52" s="17">
-        <v>301.32</v>
+        <v>223.56</v>
       </c>
       <c r="V52" s="14">
-        <v>17.582089552238806</v>
+        <v>11.358024691358024</v>
       </c>
       <c r="W52" s="16">
-        <v>465.47368421052636</v>
+        <v>534.6</v>
       </c>
       <c r="X52" s="15">
-        <v>33.473684210526301</v>
+        <v>-112.80000000000001</v>
       </c>
       <c r="Y52" s="18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Z52" s="17">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="AA52" s="14">
-        <v>0</v>
+        <v>104.34782608695653</v>
       </c>
       <c r="AB52" s="16">
-        <v>26.631578947368421</v>
+        <v>25.299999999999997</v>
       </c>
       <c r="AC52" s="15">
-        <v>-26.631578947368421</v>
+        <v>94.7</v>
       </c>
       <c r="AD52" s="19">
-        <v>6513</v>
+        <v>6185</v>
       </c>
       <c r="AE52" s="20">
-        <v>5275.5300000000007</v>
+        <v>5009.8500000000004</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6780,85 +6782,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>573</v>
+        <v>480</v>
       </c>
       <c r="F53" s="14">
-        <v>464.13000000000005</v>
+        <v>388.8</v>
       </c>
       <c r="G53" s="14">
-        <v>2.030020510908074</v>
+        <v>1.7413386540903322</v>
       </c>
       <c r="H53" s="30">
-        <v>6209.78947368421</v>
+        <v>6064.2999999999993</v>
       </c>
       <c r="I53" s="15">
-        <v>-2249.6315789473683</v>
+        <v>-2276.5</v>
       </c>
       <c r="J53" s="16">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K53" s="13">
-        <v>21.87</v>
+        <v>0</v>
       </c>
       <c r="L53" s="14">
-        <v>0.21829787234042553</v>
+        <v>0</v>
       </c>
       <c r="M53" s="30">
-        <v>2721.0526315789475</v>
+        <v>2633.4</v>
       </c>
       <c r="N53" s="15">
-        <v>-1209.8421052631579</v>
+        <v>-1197</v>
       </c>
       <c r="O53" s="16">
-        <v>550</v>
+        <v>432</v>
       </c>
       <c r="P53" s="17">
-        <v>445.50000000000006</v>
+        <v>349.92</v>
       </c>
       <c r="Q53" s="14">
-        <v>20.37037037037037</v>
+        <v>13.692551505546751</v>
       </c>
       <c r="R53" s="16">
-        <v>594</v>
+        <v>694.1</v>
       </c>
       <c r="S53" s="15">
-        <v>10</v>
+        <v>-199</v>
       </c>
       <c r="T53" s="18">
-        <v>808</v>
+        <v>676</v>
       </c>
       <c r="U53" s="17">
-        <v>654.48</v>
+        <v>547.56000000000006</v>
       </c>
       <c r="V53" s="14">
-        <v>15.475806451612904</v>
+        <v>12.358318098720291</v>
       </c>
       <c r="W53" s="16">
-        <v>1148.6315789473683</v>
+        <v>1203.4000000000001</v>
       </c>
       <c r="X53" s="15">
-        <v>-27.368421052631561</v>
+        <v>-199.20000000000005</v>
       </c>
       <c r="Y53" s="18">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="Z53" s="17">
-        <v>0</v>
+        <v>194.4</v>
       </c>
       <c r="AA53" s="14">
-        <v>0</v>
+        <v>40.336134453781511</v>
       </c>
       <c r="AB53" s="16">
-        <v>137.78947368421052</v>
+        <v>130.9</v>
       </c>
       <c r="AC53" s="15">
-        <v>-137.78947368421052</v>
+        <v>109.1</v>
       </c>
       <c r="AD53" s="19">
-        <v>1958</v>
+        <v>1828</v>
       </c>
       <c r="AE53" s="20">
-        <v>1585.98</v>
+        <v>1480.68</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6893,85 +6895,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1994</v>
+        <v>3051</v>
       </c>
       <c r="F54" s="14">
-        <v>1615.14</v>
+        <v>2471.31</v>
       </c>
       <c r="G54" s="14">
-        <v>10.111022151054176</v>
+        <v>15.927956147220046</v>
       </c>
       <c r="H54" s="30">
-        <v>4338.6315789473683</v>
+        <v>4214.1000000000004</v>
       </c>
       <c r="I54" s="15">
-        <v>21.894736842105203</v>
+        <v>1135.5</v>
       </c>
       <c r="J54" s="16">
-        <v>3248</v>
+        <v>1988</v>
       </c>
       <c r="K54" s="13">
-        <v>2630.88</v>
+        <v>1610.2800000000002</v>
       </c>
       <c r="L54" s="14">
-        <v>53.849912739965092</v>
+        <v>32.064516129032256</v>
       </c>
       <c r="M54" s="30">
-        <v>1326.9473684210527</v>
+        <v>1364</v>
       </c>
       <c r="N54" s="15">
-        <v>2644.8421052631579</v>
+        <v>1368</v>
       </c>
       <c r="O54" s="16">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="P54" s="17">
-        <v>187.11</v>
+        <v>174.96</v>
       </c>
       <c r="Q54" s="14">
-        <v>18.287500000000001</v>
+        <v>16.941176470588236</v>
       </c>
       <c r="R54" s="16">
-        <v>277.89473684210526</v>
+        <v>280.5</v>
       </c>
       <c r="S54" s="15">
-        <v>-21.631578947368439</v>
+        <v>-39</v>
       </c>
       <c r="T54" s="18">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="U54" s="17">
-        <v>378.27000000000004</v>
+        <v>346.68</v>
       </c>
       <c r="V54" s="14">
-        <v>19.939325842696629</v>
+        <v>18.730853391684899</v>
       </c>
       <c r="W54" s="16">
-        <v>515.26315789473688</v>
+        <v>502.70000000000005</v>
       </c>
       <c r="X54" s="15">
-        <v>92.263157894736821</v>
+        <v>62.399999999999977</v>
       </c>
       <c r="Y54" s="18">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="Z54" s="17">
-        <v>73.710000000000008</v>
+        <v>170.91000000000003</v>
       </c>
       <c r="AA54" s="14">
-        <v>10.943037974683545</v>
+        <v>26.708860759493671</v>
       </c>
       <c r="AB54" s="16">
-        <v>182.94736842105263</v>
+        <v>173.8</v>
       </c>
       <c r="AC54" s="15">
-        <v>-91.94736842105263</v>
+        <v>37.199999999999989</v>
       </c>
       <c r="AD54" s="19">
-        <v>6031</v>
+        <v>5894</v>
       </c>
       <c r="AE54" s="20">
-        <v>4885.1100000000006</v>
+        <v>4774.1400000000003</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7006,85 +7008,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>2100</v>
+        <v>1884</v>
       </c>
       <c r="F55" s="14">
-        <v>1701</v>
+        <v>1526.0400000000002</v>
       </c>
       <c r="G55" s="14">
-        <v>12.186927306047647</v>
+        <v>11.237697584252908</v>
       </c>
       <c r="H55" s="30">
-        <v>3790.9473684210529</v>
+        <v>3688.3</v>
       </c>
       <c r="I55" s="15">
-        <v>376.84210526315792</v>
+        <v>207.5</v>
       </c>
       <c r="J55" s="16">
-        <v>6237</v>
+        <v>6183</v>
       </c>
       <c r="K55" s="13">
-        <v>5051.97</v>
+        <v>5008.2300000000005</v>
       </c>
       <c r="L55" s="14">
-        <v>82.638075313807533</v>
+        <v>82.715719063545151</v>
       </c>
       <c r="M55" s="30">
-        <v>1660.421052631579</v>
+        <v>1644.5</v>
       </c>
       <c r="N55" s="15">
-        <v>5482.2631578947367</v>
+        <v>5435.5</v>
       </c>
       <c r="O55" s="16">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="P55" s="17">
-        <v>281.88</v>
+        <v>260.01</v>
       </c>
       <c r="Q55" s="14">
-        <v>20.344615384615384</v>
+        <v>18.238636363636363</v>
       </c>
       <c r="R55" s="16">
-        <v>376.31578947368422</v>
+        <v>387.20000000000005</v>
       </c>
       <c r="S55" s="15">
-        <v>5.8947368421052602</v>
+        <v>-31</v>
       </c>
       <c r="T55" s="18">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="U55" s="17">
-        <v>375.84000000000003</v>
+        <v>334.53000000000003</v>
       </c>
       <c r="V55" s="14">
-        <v>18.32848232848233</v>
+        <v>15.976789168278529</v>
       </c>
       <c r="W55" s="16">
-        <v>556.9473684210526</v>
+        <v>568.70000000000005</v>
       </c>
       <c r="X55" s="15">
-        <v>58.947368421052659</v>
+        <v>-0.60000000000002274</v>
       </c>
       <c r="Y55" s="18">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="Z55" s="17">
-        <v>85.050000000000011</v>
+        <v>179.82000000000002</v>
       </c>
       <c r="AA55" s="14">
-        <v>12.391304347826088</v>
+        <v>27.073170731707318</v>
       </c>
       <c r="AB55" s="16">
-        <v>186.42105263157893</v>
+        <v>180.39999999999998</v>
       </c>
       <c r="AC55" s="15">
-        <v>-81.421052631578931</v>
+        <v>41.600000000000023</v>
       </c>
       <c r="AD55" s="19">
-        <v>9254</v>
+        <v>9023</v>
       </c>
       <c r="AE55" s="20">
-        <v>7495.7400000000007</v>
+        <v>7308.63</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7119,64 +7121,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>309</v>
+        <v>699</v>
       </c>
       <c r="F56" s="14">
-        <v>809.58</v>
+        <v>1831.38</v>
       </c>
       <c r="G56" s="14">
-        <v>10.157439446366782</v>
+        <v>23.456375838926174</v>
       </c>
       <c r="H56" s="30">
-        <v>669.26315789473688</v>
+        <v>655.6</v>
       </c>
       <c r="I56" s="15">
-        <v>4.7894736842105203</v>
+        <v>401</v>
       </c>
       <c r="J56" s="32">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="K56" s="13">
-        <v>306.54000000000002</v>
+        <v>136.24</v>
       </c>
       <c r="L56" s="14">
-        <v>9.073469387755102</v>
+        <v>4.0944881889763778</v>
       </c>
       <c r="M56" s="30">
-        <v>283.68421052631578</v>
+        <v>279.39999999999998</v>
       </c>
       <c r="N56" s="15">
-        <v>-11.94736842105263</v>
+        <v>-75</v>
       </c>
       <c r="O56" s="32">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="P56" s="17">
-        <v>141.48000000000002</v>
+        <v>110.04</v>
       </c>
       <c r="Q56" s="14">
-        <v>21.375</v>
+        <v>14</v>
       </c>
       <c r="R56" s="16">
-        <v>55.578947368421048</v>
+        <v>66</v>
       </c>
       <c r="S56" s="15">
-        <v>3.473684210526315</v>
+        <v>-18</v>
       </c>
       <c r="T56" s="18">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="U56" s="17">
-        <v>298.68</v>
+        <v>282.96000000000004</v>
       </c>
       <c r="V56" s="14">
-        <v>15.361702127659573</v>
+        <v>15.319148936170214</v>
       </c>
       <c r="W56" s="16">
-        <v>163.26315789473685</v>
+        <v>155.1</v>
       </c>
       <c r="X56" s="15">
-        <v>-4.7368421052631646</v>
+        <v>-4.7999999999999972</v>
       </c>
       <c r="Y56" s="18">
         <v>45</v>
@@ -7185,19 +7187,19 @@
         <v>117.9</v>
       </c>
       <c r="AA56" s="14">
-        <v>27.580645161290324</v>
+        <v>29.032258064516128</v>
       </c>
       <c r="AB56" s="16">
-        <v>35.89473684210526</v>
+        <v>34.1</v>
       </c>
       <c r="AC56" s="15">
-        <v>9.1052631578947398</v>
+        <v>10.899999999999999</v>
       </c>
       <c r="AD56" s="19">
-        <v>639</v>
+        <v>946</v>
       </c>
       <c r="AE56" s="20">
-        <v>1674.18</v>
+        <v>2478.52</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7232,19 +7234,19 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="F57" s="14">
-        <v>461.12</v>
+        <v>345.84000000000003</v>
       </c>
       <c r="G57" s="14">
-        <v>2.694601128122482</v>
+        <v>2.0576773187840995</v>
       </c>
       <c r="H57" s="30">
-        <v>1436.9473684210525</v>
+        <v>1411.3000000000002</v>
       </c>
       <c r="I57" s="15">
-        <v>-477.15789473684208</v>
+        <v>-509.5</v>
       </c>
       <c r="J57" s="32">
         <v>30</v>
@@ -7253,43 +7255,43 @@
         <v>78.600000000000009</v>
       </c>
       <c r="L57" s="14">
-        <v>1.0775047258979207</v>
+        <v>1.125703564727955</v>
       </c>
       <c r="M57" s="30">
-        <v>612.52631578947364</v>
+        <v>586.29999999999995</v>
       </c>
       <c r="N57" s="15">
-        <v>-248.42105263157896</v>
+        <v>-236.5</v>
       </c>
       <c r="O57" s="32">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="P57" s="17">
-        <v>275.10000000000002</v>
+        <v>180.78</v>
       </c>
       <c r="Q57" s="14">
-        <v>18.136363636363637</v>
+        <v>9.4520547945205475</v>
       </c>
       <c r="R57" s="16">
-        <v>127.36842105263159</v>
+        <v>160.6</v>
       </c>
       <c r="S57" s="15">
-        <v>-10.789473684210535</v>
+        <v>-77</v>
       </c>
       <c r="T57" s="18">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="U57" s="17">
-        <v>314.40000000000003</v>
+        <v>125.76</v>
       </c>
       <c r="V57" s="14">
-        <v>6.8674698795180724</v>
+        <v>2.3762376237623761</v>
       </c>
       <c r="W57" s="16">
-        <v>384.42105263157896</v>
+        <v>444.4</v>
       </c>
       <c r="X57" s="15">
-        <v>-159.57894736842104</v>
+        <v>-275.2</v>
       </c>
       <c r="Y57" s="18">
         <v>60</v>
@@ -7298,19 +7300,19 @@
         <v>157.20000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>35.625</v>
+        <v>37.5</v>
       </c>
       <c r="AB57" s="16">
-        <v>37.05263157894737</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AC57" s="15">
-        <v>22.94736842105263</v>
+        <v>24.799999999999997</v>
       </c>
       <c r="AD57" s="19">
-        <v>491</v>
+        <v>339</v>
       </c>
       <c r="AE57" s="20">
-        <v>1286.42</v>
+        <v>888.18000000000006</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7345,34 +7347,34 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F58" s="14">
-        <v>188.64000000000001</v>
+        <v>157.20000000000002</v>
       </c>
       <c r="G58" s="14">
-        <v>2.9739130434782606</v>
+        <v>2.5423728813559321</v>
       </c>
       <c r="H58" s="30">
-        <v>532.63157894736844</v>
+        <v>519.20000000000005</v>
       </c>
       <c r="I58" s="15">
-        <v>-170.10526315789477</v>
+        <v>-176</v>
       </c>
       <c r="J58" s="32">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K58" s="13">
-        <v>141.48000000000002</v>
+        <v>125.76</v>
       </c>
       <c r="L58" s="14">
-        <v>6.1071428571428568</v>
+        <v>5.5813953488372094</v>
       </c>
       <c r="M58" s="30">
-        <v>194.5263157894737</v>
+        <v>189.2</v>
       </c>
       <c r="N58" s="15">
-        <v>-34.421052631578959</v>
+        <v>-38</v>
       </c>
       <c r="O58" s="32">
         <v>25</v>
@@ -7381,28 +7383,28 @@
         <v>65.5</v>
       </c>
       <c r="Q58" s="14">
-        <v>14.843749999999998</v>
+        <v>15.625</v>
       </c>
       <c r="R58" s="16">
-        <v>37.05263157894737</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="S58" s="15">
-        <v>-8.6842105263157947</v>
+        <v>-7</v>
       </c>
       <c r="T58" s="18">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="U58" s="17">
-        <v>262</v>
+        <v>246.28</v>
       </c>
       <c r="V58" s="14">
-        <v>19.191919191919194</v>
+        <v>18.98989898989899</v>
       </c>
       <c r="W58" s="16">
-        <v>114.63157894736841</v>
+        <v>108.9</v>
       </c>
       <c r="X58" s="15">
-        <v>16.631578947368425</v>
+        <v>14.799999999999997</v>
       </c>
       <c r="Y58" s="18">
         <v>42</v>
@@ -7411,19 +7413,19 @@
         <v>110.04</v>
       </c>
       <c r="AA58" s="14">
-        <v>29.555555555555557</v>
+        <v>31.111111111111111</v>
       </c>
       <c r="AB58" s="16">
-        <v>31.263157894736842</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="AC58" s="15">
-        <v>10.736842105263158</v>
+        <v>12.299999999999997</v>
       </c>
       <c r="AD58" s="19">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="AE58" s="20">
-        <v>767.66000000000008</v>
+        <v>704.78</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7461,64 +7463,64 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F59" s="14">
-        <v>377.28000000000003</v>
+        <v>361.56</v>
       </c>
       <c r="G59" s="14">
-        <v>4.5752508361204018</v>
+        <v>4.5695364238410594</v>
       </c>
       <c r="H59" s="30">
-        <v>692.42105263157896</v>
+        <v>664.4</v>
       </c>
       <c r="I59" s="15">
-        <v>-170.73684210526312</v>
+        <v>-164</v>
       </c>
       <c r="J59" s="32">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K59" s="13">
-        <v>133.62</v>
+        <v>117.9</v>
       </c>
       <c r="L59" s="14">
-        <v>4.5924170616113749</v>
+        <v>4.1474654377880187</v>
       </c>
       <c r="M59" s="30">
-        <v>244.31578947368419</v>
+        <v>238.7</v>
       </c>
       <c r="N59" s="15">
-        <v>-60.05263157894737</v>
+        <v>-63.5</v>
       </c>
       <c r="O59" s="32">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="P59" s="17">
-        <v>99.56</v>
+        <v>52.400000000000006</v>
       </c>
       <c r="Q59" s="14">
-        <v>14.15686274509804</v>
+        <v>5.7971014492753623</v>
       </c>
       <c r="R59" s="16">
-        <v>59.05263157894737</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="S59" s="15">
-        <v>-15.684210526315788</v>
+        <v>-49</v>
       </c>
       <c r="T59" s="18">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="U59" s="17">
-        <v>290.82</v>
+        <v>251.52</v>
       </c>
       <c r="V59" s="14">
-        <v>18.025641025641022</v>
+        <v>16.410256410256412</v>
       </c>
       <c r="W59" s="16">
-        <v>135.47368421052633</v>
+        <v>128.69999999999999</v>
       </c>
       <c r="X59" s="15">
-        <v>12.473684210526301</v>
+        <v>2.4000000000000057</v>
       </c>
       <c r="Y59" s="18">
         <v>53</v>
@@ -7527,19 +7529,19 @@
         <v>138.86000000000001</v>
       </c>
       <c r="AA59" s="14">
-        <v>67.133333333333326</v>
+        <v>70.666666666666671</v>
       </c>
       <c r="AB59" s="16">
-        <v>17.368421052631579</v>
+        <v>16.5</v>
       </c>
       <c r="AC59" s="15">
-        <v>35.631578947368425</v>
+        <v>36.5</v>
       </c>
       <c r="AD59" s="19">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="AE59" s="20">
-        <v>1040.1400000000001</v>
+        <v>922.24</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7613,10 +7615,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7646,17 +7648,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>152319.97</v>
+        <v>176276.57</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>33.077157588430659</v>
+        <v>36.727274863810258</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7694,11 +7696,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>208474.34999999998</v>
+        <v>197184.99000000002</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>45.271404190111433</v>
+        <v>41.083550279811313</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7736,11 +7738,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>30462.32</v>
+        <v>31064.699999999997</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>6.6150679989577403</v>
+        <v>6.4723393214526821</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7778,11 +7780,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>60722.920000000006</v>
+        <v>56164.01</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>13.18633133967705</v>
+        <v>11.70178789344374</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7820,11 +7822,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>8320.2099999999991</v>
+        <v>19270.660000000003</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>1.8067814570790464</v>
+        <v>4.015047641481984</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7856,19 +7858,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>460498.96999999991</v>
-      </c>
-      <c r="E67" s="69">
+        <v>479960.93000000017</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7968,17 +7970,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>113478</v>
+        <v>129451</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>33.955421502886026</v>
+        <v>36.751420930404223</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8015,11 +8017,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>151690</v>
+        <v>147993</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>45.389396074770268</v>
+        <v>42.015535127216566</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8057,11 +8059,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>21575</v>
+        <v>22303</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>6.4557730919188385</v>
+        <v>6.3318702907726117</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8099,11 +8101,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>42312</v>
+        <v>39475</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>12.660795877880412</v>
+        <v>11.20703850281347</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8141,11 +8143,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>5142</v>
+        <v>13012</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>1.5386134525444572</v>
+        <v>3.6941351487931318</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8177,19 +8179,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>334197</v>
-      </c>
-      <c r="E75" s="69">
+        <v>352234</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8736,17 +8738,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8755,6 +8746,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E91F245-B5D0-40B5-A90F-FDDA76C31C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD73858E-1A6F-4301-9FEF-FC35027B0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -1187,6 +1187,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-09-26"/>
       <sheetName val="INVENTARIO NACIONAL 29-09-26"/>
+      <sheetName val="INVENTARIO NACIONAL 30-09-26"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU AGOSTO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -1332,6 +1333,7 @@
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2259,85 +2261,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5369</v>
+        <v>5468</v>
       </c>
       <c r="F13" s="14">
-        <v>7301.84</v>
+        <v>7436.4800000000005</v>
       </c>
       <c r="G13" s="14">
-        <v>6.9019154132921967</v>
+        <v>6.9537939805002109</v>
       </c>
       <c r="H13" s="30">
-        <v>17113.8</v>
+        <v>17299.333333333336</v>
       </c>
       <c r="I13" s="15">
-        <v>-2410</v>
+        <v>-2395.3333333333348</v>
       </c>
       <c r="J13" s="16">
-        <v>2121</v>
+        <v>7805</v>
       </c>
       <c r="K13" s="13">
-        <v>2884.5600000000004</v>
+        <v>10614.800000000001</v>
       </c>
       <c r="L13" s="14">
-        <v>8.8559498956158667</v>
+        <v>34.218162839248436</v>
       </c>
       <c r="M13" s="30">
-        <v>5269</v>
+        <v>5018.0952380952385</v>
       </c>
       <c r="N13" s="15">
-        <v>-274</v>
+        <v>5524.0476190476184</v>
       </c>
       <c r="O13" s="16">
-        <v>904</v>
+        <v>866</v>
       </c>
       <c r="P13" s="17">
-        <v>1229.44</v>
+        <v>1177.76</v>
       </c>
       <c r="Q13" s="14">
-        <v>20.429378531073446</v>
+        <v>20.319553072625698</v>
       </c>
       <c r="R13" s="16">
-        <v>973.5</v>
+        <v>937.61904761904771</v>
       </c>
       <c r="S13" s="15">
-        <v>19</v>
+        <v>13.619047619047592</v>
       </c>
       <c r="T13" s="18">
-        <v>590</v>
+        <v>510</v>
       </c>
       <c r="U13" s="17">
-        <v>802.40000000000009</v>
+        <v>693.6</v>
       </c>
       <c r="V13" s="14">
-        <v>12.407991587802314</v>
+        <v>10.500000000000002</v>
       </c>
       <c r="W13" s="16">
-        <v>1046.0999999999999</v>
+        <v>1068.5714285714284</v>
       </c>
       <c r="X13" s="15">
-        <v>-170.79999999999995</v>
+        <v>-267.142857142857</v>
       </c>
       <c r="Y13" s="18">
-        <v>640</v>
+        <v>584</v>
       </c>
       <c r="Z13" s="17">
-        <v>870.40000000000009</v>
+        <v>794.24</v>
       </c>
       <c r="AA13" s="14">
-        <v>22.377622377622377</v>
+        <v>19.528662420382165</v>
       </c>
       <c r="AB13" s="16">
-        <v>629.20000000000005</v>
+        <v>657.90476190476193</v>
       </c>
       <c r="AC13" s="15">
-        <v>10.799999999999955</v>
+        <v>-73.904761904761926</v>
       </c>
       <c r="AD13" s="19">
-        <v>9624</v>
+        <v>15233</v>
       </c>
       <c r="AE13" s="20">
-        <v>13088.640000000001</v>
+        <v>20716.88</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2382,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>512.6</v>
+        <v>492.38095238095235</v>
       </c>
       <c r="I14" s="15">
-        <v>-233</v>
+        <v>-223.8095238095238</v>
       </c>
       <c r="J14" s="16">
         <v>0</v>
@@ -2397,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>273.89999999999998</v>
+        <v>260.85714285714289</v>
       </c>
       <c r="N14" s="15">
-        <v>-124.5</v>
+        <v>-118.5714285714286</v>
       </c>
       <c r="O14" s="16">
         <v>88</v>
@@ -2409,13 +2411,13 @@
         <v>139.92000000000002</v>
       </c>
       <c r="Q14" s="14">
-        <v>16.923076923076923</v>
+        <v>17.76923076923077</v>
       </c>
       <c r="R14" s="16">
-        <v>114.4</v>
+        <v>108.95238095238096</v>
       </c>
       <c r="S14" s="15">
-        <v>-16</v>
+        <v>-11.047619047619051</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2424,34 +2426,34 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>5.1851851851851851</v>
+        <v>5.4444444444444438</v>
       </c>
       <c r="W14" s="16">
-        <v>29.700000000000003</v>
+        <v>28.285714285714288</v>
       </c>
       <c r="X14" s="15">
-        <v>-14.600000000000001</v>
+        <v>-13.571428571428573</v>
       </c>
       <c r="Y14" s="18">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z14" s="17">
-        <v>27.03</v>
+        <v>20.67</v>
       </c>
       <c r="AA14" s="14">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="AB14" s="16">
         <v>88</v>
       </c>
       <c r="AC14" s="15">
-        <v>-71</v>
+        <v>-75</v>
       </c>
       <c r="AD14" s="19">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="AE14" s="20">
-        <v>178.08</v>
+        <v>171.72</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2487,85 +2489,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2661</v>
+        <v>2281</v>
       </c>
       <c r="F15" s="14">
-        <v>5401.83</v>
+        <v>4630.4299999999994</v>
       </c>
       <c r="G15" s="14">
-        <v>7.8774422735346352</v>
+        <v>6.7858053548661275</v>
       </c>
       <c r="H15" s="30">
-        <v>7431.6</v>
+        <v>7395.1428571428578</v>
       </c>
       <c r="I15" s="15">
-        <v>-717</v>
+        <v>-1080.4285714285716</v>
       </c>
       <c r="J15" s="16">
-        <v>1936</v>
+        <v>4133</v>
       </c>
       <c r="K15" s="13">
-        <v>3930.0799999999995</v>
+        <v>8389.99</v>
       </c>
       <c r="L15" s="14">
-        <v>17.36322869955157</v>
+        <v>36.823504454815442</v>
       </c>
       <c r="M15" s="30">
-        <v>2453</v>
+        <v>2469.2380952380954</v>
       </c>
       <c r="N15" s="15">
-        <v>821</v>
+        <v>3010.6190476190477</v>
       </c>
       <c r="O15" s="16">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="P15" s="17">
-        <v>385.7</v>
+        <v>332.91999999999996</v>
       </c>
       <c r="Q15" s="14">
-        <v>16.309012875536482</v>
+        <v>14.410041841004183</v>
       </c>
       <c r="R15" s="16">
-        <v>256.3</v>
+        <v>250.38095238095238</v>
       </c>
       <c r="S15" s="15">
-        <v>-43</v>
+        <v>-63.61904761904762</v>
       </c>
       <c r="T15" s="18">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="U15" s="17">
-        <v>265.92999999999995</v>
+        <v>253.74999999999997</v>
       </c>
       <c r="V15" s="14">
-        <v>7.7976190476190474</v>
+        <v>7.6754385964912286</v>
       </c>
       <c r="W15" s="16">
-        <v>369.6</v>
+        <v>358.28571428571428</v>
       </c>
       <c r="X15" s="15">
-        <v>-137.80000000000001</v>
+        <v>-135.57142857142856</v>
       </c>
       <c r="Y15" s="18">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="Z15" s="17">
-        <v>430.35999999999996</v>
+        <v>418.17999999999995</v>
       </c>
       <c r="AA15" s="14">
-        <v>23.820224719101123</v>
+        <v>22.414507772020727</v>
       </c>
       <c r="AB15" s="16">
-        <v>195.8</v>
+        <v>202.19047619047618</v>
       </c>
       <c r="AC15" s="15">
-        <v>16.199999999999989</v>
+        <v>3.8095238095238244</v>
       </c>
       <c r="AD15" s="19">
-        <v>5130</v>
+        <v>6909</v>
       </c>
       <c r="AE15" s="20">
-        <v>10413.9</v>
+        <v>14025.269999999999</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2600,34 +2602,34 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>286</v>
+        <v>176</v>
       </c>
       <c r="F16" s="14">
-        <v>1032.46</v>
+        <v>635.36</v>
       </c>
       <c r="G16" s="14">
-        <v>3.9667128987517342</v>
+        <v>2.3677130044843051</v>
       </c>
       <c r="H16" s="30">
-        <v>1586.1999999999998</v>
+        <v>1635.3333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>-435</v>
+        <v>-567.33333333333326</v>
       </c>
       <c r="J16" s="16">
-        <v>217</v>
+        <v>694</v>
       </c>
       <c r="K16" s="13">
-        <v>783.37</v>
+        <v>2505.3399999999997</v>
       </c>
       <c r="L16" s="14">
-        <v>8.6111111111111107</v>
+        <v>26.741284403669724</v>
       </c>
       <c r="M16" s="30">
-        <v>554.4</v>
+        <v>570.95238095238096</v>
       </c>
       <c r="N16" s="15">
-        <v>-35</v>
+        <v>434.47619047619048</v>
       </c>
       <c r="O16" s="16">
         <v>36</v>
@@ -2636,13 +2638,13 @@
         <v>129.96</v>
       </c>
       <c r="Q16" s="14">
-        <v>13.846153846153845</v>
+        <v>14.538461538461538</v>
       </c>
       <c r="R16" s="16">
-        <v>57.2</v>
+        <v>54.476190476190482</v>
       </c>
       <c r="S16" s="15">
-        <v>-16</v>
+        <v>-13.523809523809526</v>
       </c>
       <c r="T16" s="18">
         <v>39</v>
@@ -2651,34 +2653,34 @@
         <v>140.79</v>
       </c>
       <c r="V16" s="14">
-        <v>37.142857142857139</v>
+        <v>39</v>
       </c>
       <c r="W16" s="16">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="X16" s="15">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="Y16" s="18">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Z16" s="17">
-        <v>292.40999999999997</v>
+        <v>274.36</v>
       </c>
       <c r="AA16" s="14">
-        <v>28.421052631578945</v>
+        <v>24.553846153846152</v>
       </c>
       <c r="AB16" s="16">
-        <v>62.7</v>
+        <v>68.095238095238102</v>
       </c>
       <c r="AC16" s="15">
-        <v>18.299999999999997</v>
+        <v>7.904761904761898</v>
       </c>
       <c r="AD16" s="19">
-        <v>659</v>
+        <v>1021</v>
       </c>
       <c r="AE16" s="20">
-        <v>2378.9899999999998</v>
+        <v>3685.81</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2713,34 +2715,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F17" s="14">
-        <v>438.99999999999994</v>
+        <v>307.29999999999995</v>
       </c>
       <c r="G17" s="14">
-        <v>4.6511627906976747</v>
+        <v>3.0625</v>
       </c>
       <c r="H17" s="30">
-        <v>236.5</v>
+        <v>251.42857142857144</v>
       </c>
       <c r="I17" s="15">
-        <v>-57.5</v>
+        <v>-79.285714285714292</v>
       </c>
       <c r="J17" s="16">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="K17" s="13">
-        <v>412.65999999999997</v>
+        <v>605.81999999999994</v>
       </c>
       <c r="L17" s="14">
-        <v>24.102564102564102</v>
+        <v>36.224999999999994</v>
       </c>
       <c r="M17" s="30">
-        <v>42.9</v>
+        <v>41.904761904761905</v>
       </c>
       <c r="N17" s="15">
-        <v>27.5</v>
+        <v>49.952380952380949</v>
       </c>
       <c r="O17" s="16">
         <v>12</v>
@@ -2749,13 +2751,13 @@
         <v>105.35999999999999</v>
       </c>
       <c r="Q17" s="14">
-        <v>21.818181818181817</v>
+        <v>22.909090909090907</v>
       </c>
       <c r="R17" s="16">
-        <v>12.100000000000001</v>
+        <v>11.523809523809524</v>
       </c>
       <c r="S17" s="15">
-        <v>1</v>
+        <v>1.5238095238095237</v>
       </c>
       <c r="T17" s="18">
         <v>16</v>
@@ -2773,19 +2775,19 @@
         <v>14.545454545454545</v>
       </c>
       <c r="Y17" s="18">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z17" s="17">
-        <v>114.13999999999999</v>
+        <v>52.679999999999993</v>
       </c>
       <c r="AA17" s="14">
-        <v>28.888888888888889</v>
+        <v>13.999999999999998</v>
       </c>
       <c r="AB17" s="16">
-        <v>9.9</v>
+        <v>9.4285714285714288</v>
       </c>
       <c r="AC17" s="15">
-        <v>3.0999999999999996</v>
+        <v>-3.4285714285714288</v>
       </c>
       <c r="AD17" s="19">
         <v>138</v>
@@ -2826,85 +2828,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>7069</v>
+        <v>7919</v>
       </c>
       <c r="F18" s="14">
-        <v>4453.47</v>
+        <v>4988.97</v>
       </c>
       <c r="G18" s="14">
-        <v>8.5271411338962597</v>
+        <v>9.7347655564011006</v>
       </c>
       <c r="H18" s="30">
-        <v>18238</v>
+        <v>17896.476190476191</v>
       </c>
       <c r="I18" s="15">
-        <v>-1221</v>
+        <v>-215.76190476190459</v>
       </c>
       <c r="J18" s="16">
-        <v>13400</v>
+        <v>11566</v>
       </c>
       <c r="K18" s="13">
-        <v>8442</v>
+        <v>7286.58</v>
       </c>
       <c r="L18" s="14">
-        <v>40.391861341371516</v>
+        <v>34.30593220338983</v>
       </c>
       <c r="M18" s="30">
-        <v>7298.5</v>
+        <v>7417.1428571428578</v>
       </c>
       <c r="N18" s="15">
-        <v>10082.5</v>
+        <v>8194.5714285714275</v>
       </c>
       <c r="O18" s="16">
-        <v>1000</v>
+        <v>968</v>
       </c>
       <c r="P18" s="17">
-        <v>630</v>
+        <v>609.84</v>
       </c>
       <c r="Q18" s="14">
-        <v>16.849199663016005</v>
+        <v>16.827814569536422</v>
       </c>
       <c r="R18" s="16">
-        <v>1305.7</v>
+        <v>1265.5238095238096</v>
       </c>
       <c r="S18" s="15">
-        <v>-187</v>
+        <v>-182.4761904761906</v>
       </c>
       <c r="T18" s="18">
-        <v>2079</v>
+        <v>1623</v>
       </c>
       <c r="U18" s="17">
-        <v>1309.77</v>
+        <v>1022.49</v>
       </c>
       <c r="V18" s="14">
-        <v>12.82541640962369</v>
+        <v>10.275248718721736</v>
       </c>
       <c r="W18" s="16">
-        <v>3566.2</v>
+        <v>3474.9523809523812</v>
       </c>
       <c r="X18" s="15">
-        <v>-514.59999999999991</v>
+        <v>-904.23809523809541</v>
       </c>
       <c r="Y18" s="18">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="Z18" s="17">
-        <v>187.11</v>
+        <v>161.91</v>
       </c>
       <c r="AA18" s="14">
-        <v>20.553633217993081</v>
+        <v>14.786301369863015</v>
       </c>
       <c r="AB18" s="16">
-        <v>317.89999999999998</v>
+        <v>382.38095238095235</v>
       </c>
       <c r="AC18" s="15">
-        <v>-20.899999999999977</v>
+        <v>-125.38095238095235</v>
       </c>
       <c r="AD18" s="19">
-        <v>23845</v>
+        <v>22333</v>
       </c>
       <c r="AE18" s="20">
-        <v>15022.35</v>
+        <v>14069.79</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2939,85 +2941,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="F19" s="14">
-        <v>149.31</v>
+        <v>97.65</v>
       </c>
       <c r="G19" s="14">
-        <v>3.7559429477020601</v>
+        <v>2.4022140221402215</v>
       </c>
       <c r="H19" s="30">
-        <v>1388.2</v>
+        <v>1419.5238095238094</v>
       </c>
       <c r="I19" s="15">
-        <v>-394</v>
+        <v>-490.23809523809518</v>
       </c>
       <c r="J19" s="16">
-        <v>67</v>
+        <v>1550</v>
       </c>
       <c r="K19" s="13">
-        <v>42.21</v>
+        <v>976.5</v>
       </c>
       <c r="L19" s="14">
-        <v>1.2170753860127157</v>
+        <v>28.157439446366784</v>
       </c>
       <c r="M19" s="30">
-        <v>1211.0999999999999</v>
+        <v>1211.047619047619</v>
       </c>
       <c r="N19" s="15">
-        <v>-483.5</v>
+        <v>999.52380952380952</v>
       </c>
       <c r="O19" s="16">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="P19" s="17">
-        <v>79.38</v>
+        <v>73.709999999999994</v>
       </c>
       <c r="Q19" s="14">
-        <v>27.39130434782609</v>
+        <v>25.071428571428569</v>
       </c>
       <c r="R19" s="16">
-        <v>101.19999999999999</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="S19" s="15">
-        <v>34</v>
+        <v>23.666666666666657</v>
       </c>
       <c r="T19" s="18">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="U19" s="17">
-        <v>96.39</v>
+        <v>88.83</v>
       </c>
       <c r="V19" s="14">
-        <v>11.29151291512915</v>
+        <v>10.462897526501767</v>
       </c>
       <c r="W19" s="16">
-        <v>298.10000000000002</v>
+        <v>296.47619047619048</v>
       </c>
       <c r="X19" s="15">
-        <v>-63.800000000000011</v>
+        <v>-74.61904761904762</v>
       </c>
       <c r="Y19" s="18">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Z19" s="17">
-        <v>144.9</v>
+        <v>143.01</v>
       </c>
       <c r="AA19" s="14">
-        <v>23.711340206185568</v>
+        <v>23.835000000000001</v>
       </c>
       <c r="AB19" s="16">
-        <v>213.39999999999998</v>
+        <v>209.52380952380952</v>
       </c>
       <c r="AC19" s="15">
-        <v>16.600000000000023</v>
+        <v>17.476190476190482</v>
       </c>
       <c r="AD19" s="19">
-        <v>813</v>
+        <v>2190</v>
       </c>
       <c r="AE19" s="20">
-        <v>512.19000000000005</v>
+        <v>1379.7</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3052,85 +3054,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1213</v>
+        <v>1269</v>
       </c>
       <c r="F20" s="14">
-        <v>764.19</v>
+        <v>799.47</v>
       </c>
       <c r="G20" s="14">
-        <v>9.0454884414615968</v>
+        <v>9.403316866619619</v>
       </c>
       <c r="H20" s="30">
-        <v>2950.2</v>
+        <v>2968.9523809523812</v>
       </c>
       <c r="I20" s="15">
-        <v>-128</v>
+        <v>-80.523809523809632</v>
       </c>
       <c r="J20" s="16">
-        <v>3260</v>
+        <v>2914</v>
       </c>
       <c r="K20" s="13">
-        <v>2053.8000000000002</v>
+        <v>1835.82</v>
       </c>
       <c r="L20" s="14">
-        <v>26.21632488942501</v>
+        <v>22.816554809843399</v>
       </c>
       <c r="M20" s="30">
-        <v>2735.7</v>
+        <v>2809.7142857142858</v>
       </c>
       <c r="N20" s="15">
-        <v>2016.5</v>
+        <v>1636.8571428571427</v>
       </c>
       <c r="O20" s="16">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="P20" s="17">
-        <v>132.93</v>
+        <v>127.26</v>
       </c>
       <c r="Q20" s="14">
-        <v>22.328042328042329</v>
+        <v>21.753846153846151</v>
       </c>
       <c r="R20" s="16">
-        <v>207.89999999999998</v>
+        <v>204.28571428571431</v>
       </c>
       <c r="S20" s="15">
-        <v>22</v>
+        <v>16.285714285714278</v>
       </c>
       <c r="T20" s="18">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="U20" s="17">
-        <v>229.95</v>
+        <v>207.9</v>
       </c>
       <c r="V20" s="14">
-        <v>11.774193548387096</v>
+        <v>10.5</v>
       </c>
       <c r="W20" s="16">
-        <v>682</v>
+        <v>691.42857142857144</v>
       </c>
       <c r="X20" s="15">
-        <v>-131</v>
+        <v>-172.85714285714289</v>
       </c>
       <c r="Y20" s="18">
-        <v>275</v>
+        <v>223</v>
       </c>
       <c r="Z20" s="17">
-        <v>173.25</v>
+        <v>140.49</v>
       </c>
       <c r="AA20" s="14">
-        <v>20.912547528517109</v>
+        <v>14.06306306306306</v>
       </c>
       <c r="AB20" s="16">
-        <v>289.3</v>
+        <v>348.85714285714289</v>
       </c>
       <c r="AC20" s="15">
-        <v>-14.300000000000011</v>
+        <v>-125.85714285714289</v>
       </c>
       <c r="AD20" s="19">
-        <v>5324</v>
+        <v>4938</v>
       </c>
       <c r="AE20" s="20">
-        <v>3354.12</v>
+        <v>3110.94</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3165,85 +3167,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>1812</v>
+        <v>2760</v>
       </c>
       <c r="F21" s="14">
-        <v>1975.0800000000002</v>
+        <v>3008.4</v>
       </c>
       <c r="G21" s="14">
-        <v>6.1133603238866403</v>
+        <v>9.191246431969553</v>
       </c>
       <c r="H21" s="30">
-        <v>6520.7999999999993</v>
+        <v>6606.2857142857138</v>
       </c>
       <c r="I21" s="15">
-        <v>-1152</v>
+        <v>-242.85714285714266</v>
       </c>
       <c r="J21" s="16">
-        <v>5365</v>
+        <v>3406</v>
       </c>
       <c r="K21" s="13">
-        <v>5847.85</v>
+        <v>3712.5400000000004</v>
       </c>
       <c r="L21" s="14">
-        <v>16.324357218925911</v>
+        <v>9.8738266151297616</v>
       </c>
       <c r="M21" s="30">
-        <v>7230.2999999999993</v>
+        <v>7588.9523809523816</v>
       </c>
       <c r="N21" s="15">
-        <v>2078.5</v>
+        <v>-43.523809523809632</v>
       </c>
       <c r="O21" s="16">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="P21" s="17">
-        <v>529.74</v>
+        <v>483.96000000000004</v>
       </c>
       <c r="Q21" s="14">
-        <v>17.142857142857142</v>
+        <v>16.243902439024392</v>
       </c>
       <c r="R21" s="16">
-        <v>623.70000000000005</v>
+        <v>601.33333333333326</v>
       </c>
       <c r="S21" s="15">
-        <v>-81</v>
+        <v>-102.66666666666652</v>
       </c>
       <c r="T21" s="18">
-        <v>738</v>
+        <v>688</v>
       </c>
       <c r="U21" s="17">
-        <v>804.42000000000007</v>
+        <v>749.92000000000007</v>
       </c>
       <c r="V21" s="14">
-        <v>8.3959044368600679</v>
+        <v>8</v>
       </c>
       <c r="W21" s="16">
-        <v>1933.8000000000002</v>
+        <v>1892</v>
       </c>
       <c r="X21" s="15">
-        <v>-668.40000000000009</v>
+        <v>-688</v>
       </c>
       <c r="Y21" s="18">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="Z21" s="17">
-        <v>412.02000000000004</v>
+        <v>320.46000000000004</v>
       </c>
       <c r="AA21" s="14">
-        <v>20.941828254847646</v>
+        <v>13.84304932735426</v>
       </c>
       <c r="AB21" s="16">
-        <v>397.1</v>
+        <v>467.23809523809524</v>
       </c>
       <c r="AC21" s="15">
-        <v>-19.100000000000023</v>
+        <v>-173.23809523809524</v>
       </c>
       <c r="AD21" s="19">
-        <v>8779</v>
+        <v>7592</v>
       </c>
       <c r="AE21" s="20">
-        <v>9569.11</v>
+        <v>8275.2800000000007</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3278,85 +3280,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>2142</v>
+        <v>1824</v>
       </c>
       <c r="F22" s="14">
-        <v>2334.7800000000002</v>
+        <v>1988.16</v>
       </c>
       <c r="G22" s="14">
-        <v>11.847345132743362</v>
+        <v>9.7416073245167851</v>
       </c>
       <c r="H22" s="30">
-        <v>3977.6000000000004</v>
+        <v>4119.2380952380954</v>
       </c>
       <c r="I22" s="15">
-        <v>334</v>
+        <v>-48.380952380952294</v>
       </c>
       <c r="J22" s="16">
-        <v>1744</v>
+        <v>1502</v>
       </c>
       <c r="K22" s="13">
-        <v>1900.96</v>
+        <v>1637.18</v>
       </c>
       <c r="L22" s="14">
-        <v>11.900375298532923</v>
+        <v>9.7713754646840147</v>
       </c>
       <c r="M22" s="30">
-        <v>3224.1000000000004</v>
+        <v>3381.7142857142858</v>
       </c>
       <c r="N22" s="15">
-        <v>278.5</v>
+        <v>-35.142857142857338</v>
       </c>
       <c r="O22" s="16">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="P22" s="17">
-        <v>132.98000000000002</v>
+        <v>113.36000000000001</v>
       </c>
       <c r="Q22" s="14">
-        <v>16.827586206896552</v>
+        <v>14.463576158940397</v>
       </c>
       <c r="R22" s="16">
-        <v>159.5</v>
+        <v>158.1904761904762</v>
       </c>
       <c r="S22" s="15">
-        <v>-23</v>
+        <v>-39.809523809523824</v>
       </c>
       <c r="T22" s="18">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="U22" s="17">
-        <v>294.3</v>
+        <v>276.86</v>
       </c>
       <c r="V22" s="14">
-        <v>10.207939508506616</v>
+        <v>9.8961038961038934</v>
       </c>
       <c r="W22" s="16">
-        <v>581.9</v>
+        <v>564.66666666666674</v>
       </c>
       <c r="X22" s="15">
-        <v>-153.19999999999999</v>
+        <v>-156.66666666666674</v>
       </c>
       <c r="Y22" s="18">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="Z22" s="17">
-        <v>49.050000000000004</v>
+        <v>22.89</v>
       </c>
       <c r="AA22" s="14">
-        <v>5.8441558441558437</v>
+        <v>2.4915254237288136</v>
       </c>
       <c r="AB22" s="16">
-        <v>169.4</v>
+        <v>185.42857142857144</v>
       </c>
       <c r="AC22" s="15">
-        <v>-124.4</v>
+        <v>-164.42857142857144</v>
       </c>
       <c r="AD22" s="19">
-        <v>4323</v>
+        <v>3705</v>
       </c>
       <c r="AE22" s="20">
-        <v>4712.0700000000006</v>
+        <v>4038.4500000000003</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3391,85 +3393,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>23343</v>
+        <v>21755</v>
       </c>
       <c r="F23" s="14">
-        <v>27077.879999999997</v>
+        <v>25235.8</v>
       </c>
       <c r="G23" s="14">
-        <v>14.339332882855212</v>
+        <v>13.444029191925138</v>
       </c>
       <c r="H23" s="30">
-        <v>35813.800000000003</v>
+        <v>35600.190476190473</v>
       </c>
       <c r="I23" s="15">
-        <v>-1075.5</v>
+        <v>-2517.8571428571413</v>
       </c>
       <c r="J23" s="16">
-        <v>16373</v>
+        <v>14701</v>
       </c>
       <c r="K23" s="13">
-        <v>18992.68</v>
+        <v>17053.16</v>
       </c>
       <c r="L23" s="14">
-        <v>17.480382213206642</v>
+        <v>15.110420439528168</v>
       </c>
       <c r="M23" s="30">
-        <v>20606.3</v>
+        <v>21403.904761904763</v>
       </c>
       <c r="N23" s="15">
-        <v>7006.5</v>
+        <v>4971.9523809523816</v>
       </c>
       <c r="O23" s="16">
-        <v>2445</v>
+        <v>2315</v>
       </c>
       <c r="P23" s="17">
-        <v>2836.2</v>
+        <v>2685.3999999999996</v>
       </c>
       <c r="Q23" s="14">
-        <v>15.825242718446601</v>
+        <v>15.526988182689236</v>
       </c>
       <c r="R23" s="16">
-        <v>3399</v>
+        <v>3280.0952380952381</v>
       </c>
       <c r="S23" s="15">
-        <v>-645</v>
+        <v>-666.90476190476193</v>
       </c>
       <c r="T23" s="18">
-        <v>5945</v>
+        <v>5600</v>
       </c>
       <c r="U23" s="17">
-        <v>6896.2</v>
+        <v>6496</v>
       </c>
       <c r="V23" s="14">
-        <v>10.582999554962171</v>
+        <v>10.059019758788812</v>
       </c>
       <c r="W23" s="16">
-        <v>12358.5</v>
+        <v>12247.714285714284</v>
       </c>
       <c r="X23" s="15">
-        <v>-3043</v>
+        <v>-3307.4285714285706</v>
       </c>
       <c r="Y23" s="18">
-        <v>1243</v>
+        <v>1156</v>
       </c>
       <c r="Z23" s="17">
-        <v>1441.8799999999999</v>
+        <v>1340.9599999999998</v>
       </c>
       <c r="AA23" s="14">
-        <v>27.288693743139408</v>
+        <v>23.409836065573771</v>
       </c>
       <c r="AB23" s="16">
-        <v>1002.0999999999999</v>
+        <v>1086.3809523809523</v>
       </c>
       <c r="AC23" s="15">
-        <v>240.90000000000009</v>
+        <v>69.619047619047706</v>
       </c>
       <c r="AD23" s="19">
-        <v>49349</v>
+        <v>45527</v>
       </c>
       <c r="AE23" s="20">
-        <v>57244.84</v>
+        <v>52811.32</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3504,85 +3506,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>10222</v>
+        <v>9245</v>
       </c>
       <c r="F24" s="14">
-        <v>11857.519999999999</v>
+        <v>10724.199999999999</v>
       </c>
       <c r="G24" s="14">
-        <v>9.2880832311117167</v>
+        <v>8.4650098103335516</v>
       </c>
       <c r="H24" s="30">
-        <v>24212.1</v>
+        <v>24027.142857142855</v>
       </c>
       <c r="I24" s="15">
-        <v>-783.5</v>
+        <v>-1676.4285714285706</v>
       </c>
       <c r="J24" s="16">
-        <v>8207</v>
+        <v>12059</v>
       </c>
       <c r="K24" s="13">
-        <v>9520.119999999999</v>
+        <v>13988.439999999999</v>
       </c>
       <c r="L24" s="14">
-        <v>14.381845264172435</v>
+        <v>20.412622924391421</v>
       </c>
       <c r="M24" s="30">
-        <v>12554.3</v>
+        <v>12996.761904761906</v>
       </c>
       <c r="N24" s="15">
-        <v>2500.5</v>
+        <v>6151.3809523809523</v>
       </c>
       <c r="O24" s="16">
-        <v>1427</v>
+        <v>1352</v>
       </c>
       <c r="P24" s="17">
-        <v>1655.32</v>
+        <v>1568.32</v>
       </c>
       <c r="Q24" s="14">
-        <v>15.89086859688196</v>
+        <v>15.557260273972604</v>
       </c>
       <c r="R24" s="16">
-        <v>1975.6</v>
+        <v>1911.9047619047617</v>
       </c>
       <c r="S24" s="15">
-        <v>-369</v>
+        <v>-386.09523809523807</v>
       </c>
       <c r="T24" s="18">
-        <v>3393</v>
+        <v>3242</v>
       </c>
       <c r="U24" s="17">
-        <v>3935.8799999999997</v>
+        <v>3760.72</v>
       </c>
       <c r="V24" s="14">
-        <v>11.293060409385921</v>
+        <v>10.968583856935718</v>
       </c>
       <c r="W24" s="16">
-        <v>6609.9</v>
+        <v>6502.5714285714284</v>
       </c>
       <c r="X24" s="15">
-        <v>-1414.1999999999998</v>
+        <v>-1487.1428571428569</v>
       </c>
       <c r="Y24" s="18">
-        <v>722</v>
+        <v>643</v>
       </c>
       <c r="Z24" s="17">
-        <v>837.52</v>
+        <v>745.88</v>
       </c>
       <c r="AA24" s="14">
-        <v>19.304812834224599</v>
+        <v>15.867215041128084</v>
       </c>
       <c r="AB24" s="16">
-        <v>822.8</v>
+        <v>891.52380952380952</v>
       </c>
       <c r="AC24" s="15">
-        <v>-100.79999999999995</v>
+        <v>-248.52380952380952</v>
       </c>
       <c r="AD24" s="19">
-        <v>23971</v>
+        <v>26541</v>
       </c>
       <c r="AE24" s="20">
-        <v>27806.359999999997</v>
+        <v>30787.559999999998</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3617,85 +3619,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>9186</v>
+        <v>9854</v>
       </c>
       <c r="F25" s="14">
-        <v>10655.759999999998</v>
+        <v>11430.64</v>
       </c>
       <c r="G25" s="14">
-        <v>8.6541994441565784</v>
+        <v>9.3652244750181026</v>
       </c>
       <c r="H25" s="30">
-        <v>23351.9</v>
+        <v>23148.190476190473</v>
       </c>
       <c r="I25" s="15">
-        <v>-1428.5</v>
+        <v>-667.90476190476147</v>
       </c>
       <c r="J25" s="16">
-        <v>15934</v>
+        <v>13327</v>
       </c>
       <c r="K25" s="13">
-        <v>18483.439999999999</v>
+        <v>15459.32</v>
       </c>
       <c r="L25" s="14">
-        <v>26.407026847862117</v>
+        <v>21.43917573157653</v>
       </c>
       <c r="M25" s="30">
-        <v>13274.8</v>
+        <v>13675.619047619048</v>
       </c>
       <c r="N25" s="15">
-        <v>9900</v>
+        <v>7110.8095238095239</v>
       </c>
       <c r="O25" s="16">
-        <v>1729</v>
+        <v>1648</v>
       </c>
       <c r="P25" s="17">
-        <v>2005.6399999999999</v>
+        <v>1911.6799999999998</v>
       </c>
       <c r="Q25" s="14">
-        <v>15.604693140794224</v>
+        <v>15.449999999999998</v>
       </c>
       <c r="R25" s="16">
-        <v>2437.6</v>
+        <v>2346.666666666667</v>
       </c>
       <c r="S25" s="15">
-        <v>-487</v>
+        <v>-485.33333333333394</v>
       </c>
       <c r="T25" s="18">
-        <v>3436</v>
+        <v>3238</v>
       </c>
       <c r="U25" s="17">
-        <v>3985.7599999999998</v>
+        <v>3756.08</v>
       </c>
       <c r="V25" s="14">
-        <v>11.278516330215002</v>
+        <v>10.740483335965882</v>
       </c>
       <c r="W25" s="16">
-        <v>6702.2999999999993</v>
+        <v>6632.4761904761908</v>
       </c>
       <c r="X25" s="15">
-        <v>-1438.3999999999996</v>
+        <v>-1585.6190476190477</v>
       </c>
       <c r="Y25" s="18">
-        <v>519</v>
+        <v>448</v>
       </c>
       <c r="Z25" s="17">
-        <v>602.04</v>
+        <v>519.67999999999995</v>
       </c>
       <c r="AA25" s="14">
-        <v>19.186691312384472</v>
+        <v>15.101123595505616</v>
       </c>
       <c r="AB25" s="16">
-        <v>595.1</v>
+        <v>652.66666666666674</v>
       </c>
       <c r="AC25" s="15">
-        <v>-76.100000000000023</v>
+        <v>-204.66666666666674</v>
       </c>
       <c r="AD25" s="19">
-        <v>30804</v>
+        <v>28515</v>
       </c>
       <c r="AE25" s="20">
-        <v>35732.639999999999</v>
+        <v>33077.399999999994</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3730,85 +3732,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>18913</v>
+        <v>17668</v>
       </c>
       <c r="F26" s="14">
-        <v>21939.079999999998</v>
+        <v>20494.879999999997</v>
       </c>
       <c r="G26" s="14">
-        <v>13.819736217164152</v>
+        <v>12.960771299821847</v>
       </c>
       <c r="H26" s="30">
-        <v>30108.1</v>
+        <v>29990.190476190473</v>
       </c>
       <c r="I26" s="15">
-        <v>-1615.25</v>
+        <v>-2779.8571428571413</v>
       </c>
       <c r="J26" s="16">
-        <v>11989</v>
+        <v>11173</v>
       </c>
       <c r="K26" s="13">
-        <v>13907.24</v>
+        <v>12960.679999999998</v>
       </c>
       <c r="L26" s="14">
-        <v>16.871657754010695</v>
+        <v>15.212201763485478</v>
       </c>
       <c r="M26" s="30">
-        <v>15633.2</v>
+        <v>16158.476190476191</v>
       </c>
       <c r="N26" s="15">
-        <v>4883</v>
+        <v>3828.2380952380954</v>
       </c>
       <c r="O26" s="16">
-        <v>1346</v>
+        <v>1283</v>
       </c>
       <c r="P26" s="17">
-        <v>1561.36</v>
+        <v>1488.28</v>
       </c>
       <c r="Q26" s="14">
-        <v>15.286768881317434</v>
+        <v>15.068791946308725</v>
       </c>
       <c r="R26" s="16">
-        <v>1937.1</v>
+        <v>1873.1428571428571</v>
       </c>
       <c r="S26" s="15">
-        <v>-415</v>
+        <v>-419.85714285714266</v>
       </c>
       <c r="T26" s="18">
-        <v>4008</v>
+        <v>3754</v>
       </c>
       <c r="U26" s="17">
-        <v>4649.28</v>
+        <v>4354.6399999999994</v>
       </c>
       <c r="V26" s="14">
-        <v>10.481171548117155</v>
+        <v>9.878947368421052</v>
       </c>
       <c r="W26" s="16">
-        <v>8412.7999999999993</v>
+        <v>8360</v>
       </c>
       <c r="X26" s="15">
-        <v>-2110.3999999999996</v>
+        <v>-2326</v>
       </c>
       <c r="Y26" s="18">
-        <v>896</v>
+        <v>770</v>
       </c>
       <c r="Z26" s="17">
-        <v>1039.3599999999999</v>
+        <v>893.19999999999993</v>
       </c>
       <c r="AA26" s="14">
-        <v>22.150803461063038</v>
+        <v>17.021052631578947</v>
       </c>
       <c r="AB26" s="16">
-        <v>889.90000000000009</v>
+        <v>995.2380952380953</v>
       </c>
       <c r="AC26" s="15">
-        <v>6.0999999999999091</v>
+        <v>-225.2380952380953</v>
       </c>
       <c r="AD26" s="19">
-        <v>37152</v>
+        <v>34648</v>
       </c>
       <c r="AE26" s="20">
-        <v>43096.32</v>
+        <v>40191.68</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3843,85 +3845,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>1749</v>
+        <v>3660</v>
       </c>
       <c r="F27" s="14">
-        <v>2028.84</v>
+        <v>4245.5999999999995</v>
       </c>
       <c r="G27" s="14">
-        <v>4.958888573858804</v>
+        <v>10.296048225050233</v>
       </c>
       <c r="H27" s="30">
-        <v>7759.4</v>
+        <v>7820.4761904761908</v>
       </c>
       <c r="I27" s="15">
-        <v>-1778</v>
+        <v>105.23809523809541</v>
       </c>
       <c r="J27" s="16">
-        <v>2799</v>
+        <v>5726</v>
       </c>
       <c r="K27" s="13">
-        <v>3246.8399999999997</v>
+        <v>6642.16</v>
       </c>
       <c r="L27" s="14">
-        <v>14.739336492890995</v>
+        <v>29.941733067729082</v>
       </c>
       <c r="M27" s="30">
-        <v>4177.8</v>
+        <v>4207.2380952380954</v>
       </c>
       <c r="N27" s="15">
-        <v>900</v>
+        <v>3813.6190476190477</v>
       </c>
       <c r="O27" s="16">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="P27" s="17">
-        <v>658.88</v>
+        <v>621.76</v>
       </c>
       <c r="Q27" s="14">
-        <v>19.68804159445407</v>
+        <v>18.885906040268459</v>
       </c>
       <c r="R27" s="16">
-        <v>634.70000000000005</v>
+        <v>624.38095238095229</v>
       </c>
       <c r="S27" s="15">
-        <v>-9</v>
+        <v>-31.619047619047478</v>
       </c>
       <c r="T27" s="18">
-        <v>1512</v>
+        <v>1397</v>
       </c>
       <c r="U27" s="17">
-        <v>1753.9199999999998</v>
+        <v>1620.52</v>
       </c>
       <c r="V27" s="14">
-        <v>12.873563218390805</v>
+        <v>11.66945107398568</v>
       </c>
       <c r="W27" s="16">
-        <v>2583.9</v>
+        <v>2633.7142857142858</v>
       </c>
       <c r="X27" s="15">
-        <v>-367.20000000000005</v>
+        <v>-518.42857142857156</v>
       </c>
       <c r="Y27" s="18">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="Z27" s="17">
-        <v>386.28</v>
+        <v>349.15999999999997</v>
       </c>
       <c r="AA27" s="14">
-        <v>26.428571428571431</v>
+        <v>22.101398601398603</v>
       </c>
       <c r="AB27" s="16">
-        <v>277.2</v>
+        <v>299.61904761904759</v>
       </c>
       <c r="AC27" s="15">
-        <v>55.800000000000011</v>
+        <v>1.380952380952408</v>
       </c>
       <c r="AD27" s="19">
-        <v>6961</v>
+        <v>11620</v>
       </c>
       <c r="AE27" s="20">
-        <v>8074.7599999999993</v>
+        <v>13479.199999999999</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3956,85 +3958,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>3231</v>
+        <v>3186</v>
       </c>
       <c r="F28" s="14">
-        <v>3747.9599999999996</v>
+        <v>3695.7599999999998</v>
       </c>
       <c r="G28" s="14">
-        <v>9.0087829360100375</v>
+        <v>8.7976331360946745</v>
       </c>
       <c r="H28" s="30">
-        <v>7890.2999999999993</v>
+        <v>7967.1428571428578</v>
       </c>
       <c r="I28" s="15">
-        <v>-355.5</v>
+        <v>-435.42857142857156</v>
       </c>
       <c r="J28" s="16">
-        <v>4668</v>
+        <v>7882</v>
       </c>
       <c r="K28" s="13">
-        <v>5414.8799999999992</v>
+        <v>9143.119999999999</v>
       </c>
       <c r="L28" s="14">
-        <v>17.237813884785819</v>
+        <v>28.318562874251498</v>
       </c>
       <c r="M28" s="30">
-        <v>5957.6</v>
+        <v>6123.333333333333</v>
       </c>
       <c r="N28" s="15">
-        <v>1960</v>
+        <v>5098.666666666667</v>
       </c>
       <c r="O28" s="16">
-        <v>692</v>
+        <v>643</v>
       </c>
       <c r="P28" s="17">
-        <v>802.71999999999991</v>
+        <v>745.88</v>
       </c>
       <c r="Q28" s="14">
-        <v>16.594724220623501</v>
+        <v>15.701162790697676</v>
       </c>
       <c r="R28" s="16">
-        <v>917.40000000000009</v>
+        <v>900.95238095238085</v>
       </c>
       <c r="S28" s="15">
-        <v>-142</v>
+        <v>-176.04761904761904</v>
       </c>
       <c r="T28" s="18">
-        <v>847</v>
+        <v>749</v>
       </c>
       <c r="U28" s="17">
-        <v>982.52</v>
+        <v>868.83999999999992</v>
       </c>
       <c r="V28" s="14">
-        <v>5.8193060803847469</v>
+        <v>5.1167859466493173</v>
       </c>
       <c r="W28" s="16">
-        <v>3202.1000000000004</v>
+        <v>3220.3809523809523</v>
       </c>
       <c r="X28" s="15">
-        <v>-1481.8000000000002</v>
+        <v>-1593.0952380952381</v>
       </c>
       <c r="Y28" s="18">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="Z28" s="17">
-        <v>469.79999999999995</v>
+        <v>425.71999999999997</v>
       </c>
       <c r="AA28" s="14">
-        <v>23.342939481268008</v>
+        <v>19.560913705583754</v>
       </c>
       <c r="AB28" s="16">
-        <v>381.70000000000005</v>
+        <v>412.76190476190476</v>
       </c>
       <c r="AC28" s="15">
-        <v>23.299999999999955</v>
+        <v>-45.761904761904759</v>
       </c>
       <c r="AD28" s="19">
-        <v>9843</v>
+        <v>12827</v>
       </c>
       <c r="AE28" s="20">
-        <v>11417.88</v>
+        <v>14879.32</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4069,85 +4071,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1499</v>
+        <v>1045</v>
       </c>
       <c r="F29" s="14">
-        <v>1738.84</v>
+        <v>1212.1999999999998</v>
       </c>
       <c r="G29" s="14">
-        <v>3.9174180060107151</v>
+        <v>2.6979345955249574</v>
       </c>
       <c r="H29" s="30">
-        <v>8418.2999999999993</v>
+        <v>8521.3333333333321</v>
       </c>
       <c r="I29" s="15">
-        <v>-2327.5</v>
+        <v>-2828.3333333333326</v>
       </c>
       <c r="J29" s="16">
-        <v>202</v>
+        <v>3904</v>
       </c>
       <c r="K29" s="13">
-        <v>234.32</v>
+        <v>4528.6399999999994</v>
       </c>
       <c r="L29" s="14">
-        <v>0.79324563125859016</v>
+        <v>15.201928425737067</v>
       </c>
       <c r="M29" s="30">
-        <v>5602.3</v>
+        <v>5649.8095238095239</v>
       </c>
       <c r="N29" s="15">
-        <v>-2344.5</v>
+        <v>1335.9047619047619</v>
       </c>
       <c r="O29" s="16">
-        <v>703</v>
+        <v>659</v>
       </c>
       <c r="P29" s="17">
-        <v>815.4799999999999</v>
+        <v>764.43999999999994</v>
       </c>
       <c r="Q29" s="14">
-        <v>16.580188679245282</v>
+        <v>15.761958997722095</v>
       </c>
       <c r="R29" s="16">
-        <v>932.8</v>
+        <v>919.80952380952385</v>
       </c>
       <c r="S29" s="15">
-        <v>-145</v>
+        <v>-177.19047619047615</v>
       </c>
       <c r="T29" s="18">
-        <v>826</v>
+        <v>686</v>
       </c>
       <c r="U29" s="17">
-        <v>958.16</v>
+        <v>795.76</v>
       </c>
       <c r="V29" s="14">
-        <v>5.6965517241379313</v>
+        <v>4.6833550065019507</v>
       </c>
       <c r="W29" s="16">
-        <v>3190</v>
+        <v>3222.4761904761908</v>
       </c>
       <c r="X29" s="15">
-        <v>-1494</v>
+        <v>-1657.6190476190477</v>
       </c>
       <c r="Y29" s="18">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="Z29" s="17">
-        <v>425.71999999999997</v>
+        <v>379.32</v>
       </c>
       <c r="AA29" s="14">
-        <v>22.242424242424242</v>
+        <v>18.263297872340424</v>
       </c>
       <c r="AB29" s="16">
-        <v>363</v>
+        <v>393.90476190476193</v>
       </c>
       <c r="AC29" s="15">
-        <v>4</v>
+        <v>-66.904761904761926</v>
       </c>
       <c r="AD29" s="19">
-        <v>3597</v>
+        <v>6621</v>
       </c>
       <c r="AE29" s="20">
-        <v>4172.5199999999995</v>
+        <v>7680.36</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4182,85 +4184,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>349</v>
+        <v>516</v>
       </c>
       <c r="F30" s="14">
-        <v>1284.3200000000002</v>
+        <v>1898.88</v>
       </c>
       <c r="G30" s="14">
-        <v>3.2831608654750708</v>
+        <v>4.779885310983679</v>
       </c>
       <c r="H30" s="30">
-        <v>2338.6</v>
+        <v>2374.9523809523807</v>
       </c>
       <c r="I30" s="15">
-        <v>-714</v>
+        <v>-563.5238095238094</v>
       </c>
       <c r="J30" s="16">
-        <v>1029</v>
+        <v>1466</v>
       </c>
       <c r="K30" s="13">
-        <v>3786.7200000000003</v>
+        <v>5394.88</v>
       </c>
       <c r="L30" s="14">
-        <v>8.7761194029850742</v>
+        <v>11.895672333848532</v>
       </c>
       <c r="M30" s="30">
-        <v>2579.5</v>
+        <v>2711.2380952380954</v>
       </c>
       <c r="N30" s="15">
-        <v>-143.5</v>
+        <v>233.61904761904771</v>
       </c>
       <c r="O30" s="16">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="P30" s="17">
-        <v>437.92</v>
+        <v>419.52000000000004</v>
       </c>
       <c r="Q30" s="14">
-        <v>19.833333333333332</v>
+        <v>19.152000000000001</v>
       </c>
       <c r="R30" s="16">
-        <v>132</v>
+        <v>130.95238095238096</v>
       </c>
       <c r="S30" s="15">
-        <v>-1</v>
+        <v>-5.047619047619051</v>
       </c>
       <c r="T30" s="18">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="U30" s="17">
-        <v>1232.8</v>
+        <v>1173.92</v>
       </c>
       <c r="V30" s="14">
-        <v>11.375212224108658</v>
+        <v>11</v>
       </c>
       <c r="W30" s="16">
-        <v>647.9</v>
+        <v>638</v>
       </c>
       <c r="X30" s="15">
-        <v>-136.19999999999999</v>
+        <v>-145</v>
       </c>
       <c r="Y30" s="18">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="Z30" s="17">
-        <v>471.04</v>
+        <v>371.68</v>
       </c>
       <c r="AA30" s="14">
-        <v>27.526881720430104</v>
+        <v>18.28448275862069</v>
       </c>
       <c r="AB30" s="16">
-        <v>102.30000000000001</v>
+        <v>121.52380952380952</v>
       </c>
       <c r="AC30" s="15">
-        <v>25.699999999999989</v>
+        <v>-20.523809523809518</v>
       </c>
       <c r="AD30" s="19">
-        <v>1960</v>
+        <v>2516</v>
       </c>
       <c r="AE30" s="20">
-        <v>7212.8</v>
+        <v>9258.880000000001</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4295,34 +4297,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>470</v>
+        <v>557</v>
       </c>
       <c r="F31" s="14">
-        <v>1729.6000000000001</v>
+        <v>2049.7600000000002</v>
       </c>
       <c r="G31" s="14">
-        <v>9.1976516634050878</v>
+        <v>10.731192660550459</v>
       </c>
       <c r="H31" s="30">
-        <v>1124.2</v>
+        <v>1141.9047619047619</v>
       </c>
       <c r="I31" s="15">
-        <v>-41</v>
+        <v>37.952380952380963</v>
       </c>
       <c r="J31" s="16">
-        <v>1080</v>
+        <v>780</v>
       </c>
       <c r="K31" s="13">
-        <v>3974.4</v>
+        <v>2870.4</v>
       </c>
       <c r="L31" s="14">
-        <v>16.314199395770391</v>
+        <v>10.949197860962567</v>
       </c>
       <c r="M31" s="30">
-        <v>1456.4</v>
+        <v>1567.2380952380954</v>
       </c>
       <c r="N31" s="15">
-        <v>418</v>
+        <v>67.619047619047592</v>
       </c>
       <c r="O31" s="16">
         <v>34</v>
@@ -4331,49 +4333,49 @@
         <v>125.12</v>
       </c>
       <c r="Q31" s="14">
-        <v>37.777777777777779</v>
+        <v>39.666666666666664</v>
       </c>
       <c r="R31" s="16">
-        <v>19.8</v>
+        <v>18.857142857142858</v>
       </c>
       <c r="S31" s="15">
-        <v>16</v>
+        <v>16.857142857142854</v>
       </c>
       <c r="T31" s="18">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="U31" s="17">
-        <v>279.68</v>
+        <v>264.96000000000004</v>
       </c>
       <c r="V31" s="14">
-        <v>7.1698113207547172</v>
+        <v>7.1320754716981138</v>
       </c>
       <c r="W31" s="16">
-        <v>233.2</v>
+        <v>222.09523809523807</v>
       </c>
       <c r="X31" s="15">
-        <v>-93.6</v>
+        <v>-89.523809523809518</v>
       </c>
       <c r="Y31" s="18">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Z31" s="17">
-        <v>161.92000000000002</v>
+        <v>110.4</v>
       </c>
       <c r="AA31" s="14">
-        <v>36.666666666666671</v>
+        <v>23.333333333333332</v>
       </c>
       <c r="AB31" s="16">
-        <v>26.4</v>
+        <v>28.285714285714288</v>
       </c>
       <c r="AC31" s="15">
-        <v>17.600000000000001</v>
+        <v>1.7142857142857117</v>
       </c>
       <c r="AD31" s="19">
-        <v>1704</v>
+        <v>1473</v>
       </c>
       <c r="AE31" s="20">
-        <v>6270.72</v>
+        <v>5420.64</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4408,85 +4410,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1169</v>
+        <v>1572</v>
       </c>
       <c r="F32" s="14">
-        <v>4851.3500000000004</v>
+        <v>6523.8</v>
       </c>
       <c r="G32" s="14">
-        <v>5.2824220515137821</v>
+        <v>7.0089171974522309</v>
       </c>
       <c r="H32" s="30">
-        <v>4868.6000000000004</v>
+        <v>4934.2857142857138</v>
       </c>
       <c r="I32" s="15">
-        <v>-1044</v>
+        <v>-670.85714285714266</v>
       </c>
       <c r="J32" s="16">
-        <v>3212</v>
+        <v>2131</v>
       </c>
       <c r="K32" s="13">
-        <v>13329.800000000001</v>
+        <v>8843.6500000000015</v>
       </c>
       <c r="L32" s="14">
-        <v>18.105975197294249</v>
+        <v>11.602540834845735</v>
       </c>
       <c r="M32" s="30">
-        <v>3902.8</v>
+        <v>4040.6666666666665</v>
       </c>
       <c r="N32" s="15">
-        <v>1438</v>
+        <v>294.33333333333348</v>
       </c>
       <c r="O32" s="16">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="P32" s="17">
-        <v>1037.5</v>
+        <v>979.40000000000009</v>
       </c>
       <c r="Q32" s="14">
-        <v>17.730496453900709</v>
+        <v>17.148788927335641</v>
       </c>
       <c r="R32" s="16">
-        <v>310.2</v>
+        <v>302.76190476190476</v>
       </c>
       <c r="S32" s="15">
-        <v>-32</v>
+        <v>-39.238095238095241</v>
       </c>
       <c r="T32" s="18">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="U32" s="17">
-        <v>3776.5000000000005</v>
+        <v>3639.55</v>
       </c>
       <c r="V32" s="14">
-        <v>10.859188544152746</v>
+        <v>10.169519602429597</v>
       </c>
       <c r="W32" s="16">
-        <v>1843.6</v>
+        <v>1897.2380952380954</v>
       </c>
       <c r="X32" s="15">
-        <v>-430.79999999999995</v>
+        <v>-502.80952380952385</v>
       </c>
       <c r="Y32" s="18">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="Z32" s="17">
-        <v>1141.25</v>
+        <v>1070.7</v>
       </c>
       <c r="AA32" s="14">
-        <v>73.333333333333329</v>
+        <v>55.285714285714285</v>
       </c>
       <c r="AB32" s="16">
-        <v>82.5</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="AC32" s="15">
-        <v>192.5</v>
+        <v>155.33333333333331</v>
       </c>
       <c r="AD32" s="19">
-        <v>5816</v>
+        <v>5074</v>
       </c>
       <c r="AE32" s="20">
-        <v>24136.400000000001</v>
+        <v>21057.100000000002</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4521,85 +4523,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3115</v>
+        <v>3270</v>
       </c>
       <c r="F33" s="14">
-        <v>12927.250000000002</v>
+        <v>13570.500000000002</v>
       </c>
       <c r="G33" s="14">
-        <v>7.139582855833142</v>
+        <v>7.3775247099269441</v>
       </c>
       <c r="H33" s="30">
-        <v>9598.6</v>
+        <v>9751.2380952380954</v>
       </c>
       <c r="I33" s="15">
-        <v>-1248</v>
+        <v>-1162.3809523809523</v>
       </c>
       <c r="J33" s="16">
-        <v>3764</v>
+        <v>3993</v>
       </c>
       <c r="K33" s="13">
-        <v>15620.600000000002</v>
+        <v>16570.95</v>
       </c>
       <c r="L33" s="14">
-        <v>14.252177205603937</v>
+        <v>14.311827956989248</v>
       </c>
       <c r="M33" s="30">
-        <v>5810.2000000000007</v>
+        <v>6138</v>
       </c>
       <c r="N33" s="15">
-        <v>1123</v>
+        <v>1203</v>
       </c>
       <c r="O33" s="16">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="P33" s="17">
-        <v>1460.8000000000002</v>
+        <v>1394.4</v>
       </c>
       <c r="Q33" s="14">
-        <v>18.097686375321338</v>
+        <v>17.596009975062344</v>
       </c>
       <c r="R33" s="16">
-        <v>427.9</v>
+        <v>420.09523809523807</v>
       </c>
       <c r="S33" s="15">
-        <v>-37</v>
+        <v>-45.904761904761926</v>
       </c>
       <c r="T33" s="18">
-        <v>1021</v>
+        <v>984</v>
       </c>
       <c r="U33" s="17">
-        <v>4237.1500000000005</v>
+        <v>4083.6000000000004</v>
       </c>
       <c r="V33" s="14">
-        <v>9.5065176908752331</v>
+        <v>9.0631578947368414</v>
       </c>
       <c r="W33" s="16">
-        <v>2362.8000000000002</v>
+        <v>2388.5714285714284</v>
       </c>
       <c r="X33" s="15">
-        <v>-697.40000000000009</v>
+        <v>-753.14285714285711</v>
       </c>
       <c r="Y33" s="18">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="Z33" s="17">
-        <v>962.80000000000007</v>
+        <v>780.2</v>
       </c>
       <c r="AA33" s="14">
-        <v>18.70967741935484</v>
+        <v>12.859934853420196</v>
       </c>
       <c r="AB33" s="16">
-        <v>272.8</v>
+        <v>321.61904761904759</v>
       </c>
       <c r="AC33" s="15">
-        <v>-40.800000000000011</v>
+        <v>-133.61904761904759</v>
       </c>
       <c r="AD33" s="19">
-        <v>8484</v>
+        <v>8771</v>
       </c>
       <c r="AE33" s="20">
-        <v>35208.600000000006</v>
+        <v>36399.65</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4634,25 +4636,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>678</v>
+        <v>478</v>
       </c>
       <c r="F34" s="14">
-        <v>2813.7000000000003</v>
+        <v>1983.7000000000003</v>
       </c>
       <c r="G34" s="14">
-        <v>13.425742574257425</v>
+        <v>8.2958677685950413</v>
       </c>
       <c r="H34" s="30">
-        <v>1111</v>
+        <v>1267.6190476190477</v>
       </c>
       <c r="I34" s="15">
-        <v>173</v>
+        <v>-98.190476190476147</v>
       </c>
       <c r="J34" s="16">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="K34" s="13">
-        <v>0</v>
+        <v>1062.4000000000001</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4661,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="O34" s="16">
         <v>0</v>
@@ -4671,25 +4673,25 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>88</v>
+        <v>83.80952380952381</v>
       </c>
       <c r="S34" s="15">
-        <v>-80</v>
+        <v>-76.19047619047619</v>
       </c>
       <c r="T34" s="18">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="U34" s="17">
-        <v>506.30000000000007</v>
+        <v>340.3</v>
       </c>
       <c r="V34" s="14">
-        <v>22.181818181818183</v>
+        <v>11.48</v>
       </c>
       <c r="W34" s="16">
-        <v>121</v>
+        <v>157.14285714285714</v>
       </c>
       <c r="X34" s="15">
-        <v>34</v>
+        <v>-32.285714285714278</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4707,10 +4709,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="AE34" s="20">
-        <v>3452.8</v>
+        <v>3519.2000000000003</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4745,85 +4747,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1446</v>
+        <v>1888</v>
       </c>
       <c r="F35" s="14">
-        <v>2356.98</v>
+        <v>3077.4399999999996</v>
       </c>
       <c r="G35" s="14">
-        <v>3.3414211438474868</v>
+        <v>4.4112149532710276</v>
       </c>
       <c r="H35" s="30">
-        <v>9520.5</v>
+        <v>9416</v>
       </c>
       <c r="I35" s="15">
-        <v>-2881.5</v>
+        <v>-2392</v>
       </c>
       <c r="J35" s="16">
-        <v>2541</v>
+        <v>4660</v>
       </c>
       <c r="K35" s="13">
-        <v>4141.83</v>
+        <v>7595.7999999999993</v>
       </c>
       <c r="L35" s="14">
-        <v>15.527039413382218</v>
+        <v>27.651879061881889</v>
       </c>
       <c r="M35" s="30">
-        <v>3600.3</v>
+        <v>3707.5238095238092</v>
       </c>
       <c r="N35" s="15">
-        <v>904.5</v>
+        <v>2974.7619047619046</v>
       </c>
       <c r="O35" s="16">
-        <v>708</v>
+        <v>622</v>
       </c>
       <c r="P35" s="17">
-        <v>1154.04</v>
+        <v>1013.8599999999999</v>
       </c>
       <c r="Q35" s="14">
-        <v>19.213025780189959</v>
+        <v>17.58008075370121</v>
       </c>
       <c r="R35" s="16">
-        <v>810.7</v>
+        <v>778.38095238095229</v>
       </c>
       <c r="S35" s="15">
-        <v>-29</v>
+        <v>-85.619047619047592</v>
       </c>
       <c r="T35" s="18">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="U35" s="17">
-        <v>725.34999999999991</v>
+        <v>678.07999999999993</v>
       </c>
       <c r="V35" s="14">
-        <v>9.2708333333333339</v>
+        <v>8.8421052631578956</v>
       </c>
       <c r="W35" s="16">
-        <v>1056</v>
+        <v>1035.047619047619</v>
       </c>
       <c r="X35" s="15">
-        <v>-323</v>
+        <v>-336.7619047619047</v>
       </c>
       <c r="Y35" s="18">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="Z35" s="17">
-        <v>453.14</v>
+        <v>339.03999999999996</v>
       </c>
       <c r="AA35" s="14">
-        <v>21.384615384615383</v>
+        <v>13.822784810126583</v>
       </c>
       <c r="AB35" s="16">
-        <v>286</v>
+        <v>331.04761904761904</v>
       </c>
       <c r="AC35" s="15">
-        <v>-8</v>
+        <v>-123.04761904761904</v>
       </c>
       <c r="AD35" s="19">
-        <v>5418</v>
+        <v>7794</v>
       </c>
       <c r="AE35" s="20">
-        <v>8831.34</v>
+        <v>12704.22</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4858,85 +4860,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>5729</v>
+        <v>5276</v>
       </c>
       <c r="F36" s="14">
-        <v>9338.2699999999986</v>
+        <v>8599.8799999999992</v>
       </c>
       <c r="G36" s="14">
-        <v>9.0184966548602912</v>
+        <v>8.4306802617562013</v>
       </c>
       <c r="H36" s="30">
-        <v>13975.5</v>
+        <v>13767.809523809525</v>
       </c>
       <c r="I36" s="15">
-        <v>-623.5</v>
+        <v>-982.09523809523853</v>
       </c>
       <c r="J36" s="16">
-        <v>1742</v>
+        <v>2763</v>
       </c>
       <c r="K36" s="13">
-        <v>2839.46</v>
+        <v>4503.6899999999996</v>
       </c>
       <c r="L36" s="14">
-        <v>7.7715815302252951</v>
+        <v>11.88022113022113</v>
       </c>
       <c r="M36" s="30">
-        <v>4931.3</v>
+        <v>5116.5714285714284</v>
       </c>
       <c r="N36" s="15">
-        <v>-499.5</v>
+        <v>437.28571428571468</v>
       </c>
       <c r="O36" s="16">
-        <v>1555</v>
+        <v>1456</v>
       </c>
       <c r="P36" s="17">
-        <v>2534.6499999999996</v>
+        <v>2373.2799999999997</v>
       </c>
       <c r="Q36" s="14">
-        <v>16.838115863562535</v>
+        <v>16.394638069705092</v>
       </c>
       <c r="R36" s="16">
-        <v>2031.6999999999998</v>
+        <v>1953.8095238095239</v>
       </c>
       <c r="S36" s="15">
-        <v>-292</v>
+        <v>-320.19047619047615</v>
       </c>
       <c r="T36" s="18">
-        <v>1193</v>
+        <v>1141</v>
       </c>
       <c r="U36" s="17">
-        <v>1944.59</v>
+        <v>1859.83</v>
       </c>
       <c r="V36" s="14">
-        <v>11.196621304551854</v>
+        <v>10.871597096188749</v>
       </c>
       <c r="W36" s="16">
-        <v>2344.1</v>
+        <v>2308.9523809523807</v>
       </c>
       <c r="X36" s="15">
-        <v>-511.79999999999995</v>
+        <v>-538.23809523809518</v>
       </c>
       <c r="Y36" s="18">
-        <v>480</v>
+        <v>404</v>
       </c>
       <c r="Z36" s="17">
-        <v>782.4</v>
+        <v>658.52</v>
       </c>
       <c r="AA36" s="14">
-        <v>19.277108433734941</v>
+        <v>14.989399293286219</v>
       </c>
       <c r="AB36" s="16">
-        <v>547.79999999999995</v>
+        <v>592.95238095238096</v>
       </c>
       <c r="AC36" s="15">
-        <v>-67.799999999999955</v>
+        <v>-188.95238095238096</v>
       </c>
       <c r="AD36" s="19">
-        <v>10699</v>
+        <v>11040</v>
       </c>
       <c r="AE36" s="20">
-        <v>17439.37</v>
+        <v>17995.199999999997</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4971,85 +4973,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>616</v>
+        <v>126</v>
       </c>
       <c r="F37" s="14">
-        <v>1004.0799999999999</v>
+        <v>205.38</v>
       </c>
       <c r="G37" s="14">
-        <v>2.1482127288578901</v>
+        <v>0.43185898482128288</v>
       </c>
       <c r="H37" s="30">
-        <v>6308.5</v>
+        <v>6418.7619047619046</v>
       </c>
       <c r="I37" s="15">
-        <v>-2251.5</v>
+        <v>-2791.6190476190477</v>
       </c>
       <c r="J37" s="16">
-        <v>3225</v>
+        <v>2130</v>
       </c>
       <c r="K37" s="13">
-        <v>5256.75</v>
+        <v>3471.8999999999996</v>
       </c>
       <c r="L37" s="14">
-        <v>24.431818181818183</v>
+        <v>15.137055837563452</v>
       </c>
       <c r="M37" s="30">
-        <v>2904</v>
+        <v>3095.7142857142858</v>
       </c>
       <c r="N37" s="15">
-        <v>1905</v>
+        <v>722.85714285714266</v>
       </c>
       <c r="O37" s="16">
-        <v>989</v>
+        <v>885</v>
       </c>
       <c r="P37" s="17">
-        <v>1612.07</v>
+        <v>1442.55</v>
       </c>
       <c r="Q37" s="14">
-        <v>16.691983122362871</v>
+        <v>15.487500000000001</v>
       </c>
       <c r="R37" s="16">
-        <v>1303.5</v>
+        <v>1257.1428571428571</v>
       </c>
       <c r="S37" s="15">
-        <v>-196</v>
+        <v>-257.85714285714266</v>
       </c>
       <c r="T37" s="18">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="U37" s="17">
-        <v>603.09999999999991</v>
+        <v>511.82</v>
       </c>
       <c r="V37" s="14">
-        <v>6.6606660666066606</v>
+        <v>5.6455479452054798</v>
       </c>
       <c r="W37" s="16">
-        <v>1222.0999999999999</v>
+        <v>1223.6190476190477</v>
       </c>
       <c r="X37" s="15">
-        <v>-518.79999999999995</v>
+        <v>-575.90476190476193</v>
       </c>
       <c r="Y37" s="18">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="Z37" s="17">
-        <v>352.08</v>
+        <v>260.79999999999995</v>
       </c>
       <c r="AA37" s="14">
-        <v>17.560975609756095</v>
+        <v>10.980392156862745</v>
       </c>
       <c r="AB37" s="16">
-        <v>270.60000000000002</v>
+        <v>320.57142857142856</v>
       </c>
       <c r="AC37" s="15">
-        <v>-54.600000000000023</v>
+        <v>-160.57142857142856</v>
       </c>
       <c r="AD37" s="19">
-        <v>5416</v>
+        <v>3615</v>
       </c>
       <c r="AE37" s="20">
-        <v>8828.08</v>
+        <v>5892.45</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5084,85 +5086,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1658</v>
+        <v>1846</v>
       </c>
       <c r="F38" s="14">
-        <v>2702.54</v>
+        <v>3008.98</v>
       </c>
       <c r="G38" s="14">
-        <v>8.1414191013994603</v>
+        <v>8.7666214382632308</v>
       </c>
       <c r="H38" s="30">
-        <v>4480.3</v>
+        <v>4632.5714285714284</v>
       </c>
       <c r="I38" s="15">
-        <v>-378.5</v>
+        <v>-259.71428571428532</v>
       </c>
       <c r="J38" s="16">
-        <v>1784</v>
+        <v>1034</v>
       </c>
       <c r="K38" s="13">
-        <v>2907.9199999999996</v>
+        <v>1685.4199999999998</v>
       </c>
       <c r="L38" s="14">
-        <v>15.808595480726629</v>
+        <v>8.682127149140344</v>
       </c>
       <c r="M38" s="30">
-        <v>2482.6999999999998</v>
+        <v>2620.0952380952381</v>
       </c>
       <c r="N38" s="15">
-        <v>655.5</v>
+        <v>-156.95238095238096</v>
       </c>
       <c r="O38" s="16">
-        <v>633</v>
+        <v>554</v>
       </c>
       <c r="P38" s="17">
-        <v>1031.79</v>
+        <v>903.02</v>
       </c>
       <c r="Q38" s="14">
-        <v>16.356589147286819</v>
+        <v>14.801526717557252</v>
       </c>
       <c r="R38" s="16">
-        <v>851.40000000000009</v>
+        <v>823.42857142857144</v>
       </c>
       <c r="S38" s="15">
-        <v>-141</v>
+        <v>-194.57142857142867</v>
       </c>
       <c r="T38" s="18">
-        <v>2207</v>
+        <v>391</v>
       </c>
       <c r="U38" s="17">
-        <v>3597.41</v>
+        <v>637.32999999999993</v>
       </c>
       <c r="V38" s="14">
-        <v>58.386243386243393</v>
+        <v>10.5</v>
       </c>
       <c r="W38" s="16">
-        <v>831.59999999999991</v>
+        <v>819.2380952380953</v>
       </c>
       <c r="X38" s="15">
-        <v>1602.2</v>
+        <v>-204.80952380952385</v>
       </c>
       <c r="Y38" s="18">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="Z38" s="17">
-        <v>735.13</v>
+        <v>634.06999999999994</v>
       </c>
       <c r="AA38" s="14">
-        <v>16.954887218045112</v>
+        <v>13.413793103448276</v>
       </c>
       <c r="AB38" s="16">
-        <v>585.20000000000005</v>
+        <v>638</v>
       </c>
       <c r="AC38" s="15">
-        <v>-134.20000000000005</v>
+        <v>-249</v>
       </c>
       <c r="AD38" s="19">
-        <v>6733</v>
+        <v>4214</v>
       </c>
       <c r="AE38" s="20">
-        <v>10974.789999999999</v>
+        <v>6868.82</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5197,85 +5199,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>970</v>
+        <v>1071</v>
       </c>
       <c r="F39" s="14">
-        <v>1581.1</v>
+        <v>1745.7299999999998</v>
       </c>
       <c r="G39" s="14">
-        <v>9.2161520190023758</v>
+        <v>10.504904250350304</v>
       </c>
       <c r="H39" s="30">
-        <v>2315.5</v>
+        <v>2242.9523809523807</v>
       </c>
       <c r="I39" s="15">
-        <v>-82.5</v>
+        <v>51.476190476190482</v>
       </c>
       <c r="J39" s="16">
-        <v>2480</v>
+        <v>2241</v>
       </c>
       <c r="K39" s="13">
-        <v>4042.3999999999996</v>
+        <v>3652.83</v>
       </c>
       <c r="L39" s="14">
-        <v>44.644464446444644</v>
+        <v>39.348662207357854</v>
       </c>
       <c r="M39" s="30">
-        <v>1222.0999999999999</v>
+        <v>1252.952380952381</v>
       </c>
       <c r="N39" s="15">
-        <v>1924.5</v>
+        <v>1671.4761904761904</v>
       </c>
       <c r="O39" s="16">
-        <v>602</v>
+        <v>548</v>
       </c>
       <c r="P39" s="17">
-        <v>981.26</v>
+        <v>893.2399999999999</v>
       </c>
       <c r="Q39" s="14">
-        <v>21.234567901234566</v>
+        <v>20.083769633507856</v>
       </c>
       <c r="R39" s="16">
-        <v>623.70000000000005</v>
+        <v>600.28571428571422</v>
       </c>
       <c r="S39" s="15">
-        <v>35</v>
+        <v>2.2857142857143344</v>
       </c>
       <c r="T39" s="18">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="U39" s="17">
-        <v>894.86999999999989</v>
+        <v>854.11999999999989</v>
       </c>
       <c r="V39" s="14">
-        <v>9.6740088105726869</v>
+        <v>9.6020942408376975</v>
       </c>
       <c r="W39" s="16">
-        <v>1248.5</v>
+        <v>1200.5714285714284</v>
       </c>
       <c r="X39" s="15">
-        <v>-359</v>
+        <v>-349.142857142857</v>
       </c>
       <c r="Y39" s="18">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="Z39" s="17">
-        <v>676.44999999999993</v>
+        <v>643.84999999999991</v>
       </c>
       <c r="AA39" s="14">
-        <v>83.838383838383834</v>
+        <v>66.36</v>
       </c>
       <c r="AB39" s="16">
-        <v>108.9</v>
+        <v>130.95238095238096</v>
       </c>
       <c r="AC39" s="15">
-        <v>306.10000000000002</v>
+        <v>264.04761904761904</v>
       </c>
       <c r="AD39" s="19">
-        <v>5016</v>
+        <v>4779</v>
       </c>
       <c r="AE39" s="20">
-        <v>8176.079999999999</v>
+        <v>7789.7699999999995</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5310,85 +5312,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1418</v>
+        <v>1357</v>
       </c>
       <c r="F40" s="14">
-        <v>2311.3399999999997</v>
+        <v>2211.91</v>
       </c>
       <c r="G40" s="14">
-        <v>10.339044841414509</v>
+        <v>10.2544080604534</v>
       </c>
       <c r="H40" s="30">
-        <v>3017.3</v>
+        <v>2911.3333333333335</v>
       </c>
       <c r="I40" s="15">
-        <v>46.5</v>
+        <v>33.666666666666515</v>
       </c>
       <c r="J40" s="16">
-        <v>634</v>
+        <v>579</v>
       </c>
       <c r="K40" s="13">
-        <v>1033.4199999999998</v>
+        <v>943.77</v>
       </c>
       <c r="L40" s="14">
-        <v>9.3303899926416474</v>
+        <v>8.4790794979079482</v>
       </c>
       <c r="M40" s="30">
-        <v>1494.9</v>
+        <v>1502.2857142857144</v>
       </c>
       <c r="N40" s="15">
-        <v>-45.5</v>
+        <v>-103.85714285714289</v>
       </c>
       <c r="O40" s="16">
-        <v>721</v>
+        <v>661</v>
       </c>
       <c r="P40" s="17">
-        <v>1175.23</v>
+        <v>1077.4299999999998</v>
       </c>
       <c r="Q40" s="14">
-        <v>20.027777777777779</v>
+        <v>19.119834710743802</v>
       </c>
       <c r="R40" s="16">
-        <v>792</v>
+        <v>760.57142857142856</v>
       </c>
       <c r="S40" s="15">
-        <v>1</v>
+        <v>-30.428571428571331</v>
       </c>
       <c r="T40" s="18">
-        <v>664</v>
+        <v>632</v>
       </c>
       <c r="U40" s="17">
-        <v>1082.32</v>
+        <v>1030.1599999999999</v>
       </c>
       <c r="V40" s="14">
-        <v>10.114242193450114</v>
+        <v>9.9789473684210517</v>
       </c>
       <c r="W40" s="16">
-        <v>1444.3000000000002</v>
+        <v>1393.3333333333335</v>
       </c>
       <c r="X40" s="15">
-        <v>-386.40000000000009</v>
+        <v>-381.33333333333348</v>
       </c>
       <c r="Y40" s="18">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="Z40" s="17">
-        <v>699.27</v>
+        <v>666.67</v>
       </c>
       <c r="AA40" s="14">
-        <v>92.258064516129025</v>
+        <v>72.17647058823529</v>
       </c>
       <c r="AB40" s="16">
-        <v>102.30000000000001</v>
+        <v>124.66666666666667</v>
       </c>
       <c r="AC40" s="15">
-        <v>326.7</v>
+        <v>284.33333333333331</v>
       </c>
       <c r="AD40" s="19">
-        <v>3866</v>
+        <v>3638</v>
       </c>
       <c r="AE40" s="20">
-        <v>6301.58</v>
+        <v>5929.94</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5423,85 +5425,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>616</v>
+        <v>461</v>
       </c>
       <c r="F41" s="14">
-        <v>3788.4</v>
+        <v>2835.15</v>
       </c>
       <c r="G41" s="14">
-        <v>9.2008961911874536</v>
+        <v>6.4755852842809363</v>
       </c>
       <c r="H41" s="30">
-        <v>1472.9</v>
+        <v>1566.1904761904761</v>
       </c>
       <c r="I41" s="15">
-        <v>-53.5</v>
+        <v>-250.90476190476193</v>
       </c>
       <c r="J41" s="16">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="K41" s="13">
-        <v>2047.95</v>
+        <v>1758.9</v>
       </c>
       <c r="L41" s="14">
-        <v>8.9156626506024086</v>
+        <v>7.4887780548628431</v>
       </c>
       <c r="M41" s="30">
-        <v>821.7</v>
+        <v>840.19047619047615</v>
       </c>
       <c r="N41" s="15">
-        <v>-40.5</v>
+        <v>-95.904761904761926</v>
       </c>
       <c r="O41" s="16">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P41" s="17">
-        <v>369</v>
+        <v>356.70000000000005</v>
       </c>
       <c r="Q41" s="14">
-        <v>12.76595744680851</v>
+        <v>12.821052631578947</v>
       </c>
       <c r="R41" s="16">
-        <v>103.4</v>
+        <v>99.523809523809518</v>
       </c>
       <c r="S41" s="15">
-        <v>-34</v>
+        <v>-32.476190476190482</v>
       </c>
       <c r="T41" s="18">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="U41" s="17">
-        <v>651.90000000000009</v>
+        <v>621.15000000000009</v>
       </c>
       <c r="V41" s="14">
-        <v>8.346456692913387</v>
+        <v>8.157692307692308</v>
       </c>
       <c r="W41" s="16">
-        <v>279.39999999999998</v>
+        <v>272.38095238095241</v>
       </c>
       <c r="X41" s="15">
-        <v>-97.199999999999989</v>
+        <v>-97.095238095238102</v>
       </c>
       <c r="Y41" s="18">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="Z41" s="17">
-        <v>590.40000000000009</v>
+        <v>399.75</v>
       </c>
       <c r="AA41" s="14">
-        <v>23.414634146341466</v>
+        <v>14.368421052631579</v>
       </c>
       <c r="AB41" s="16">
-        <v>90.199999999999989</v>
+        <v>99.523809523809518</v>
       </c>
       <c r="AC41" s="15">
-        <v>5.8000000000000114</v>
+        <v>-34.523809523809518</v>
       </c>
       <c r="AD41" s="19">
-        <v>1211</v>
+        <v>971</v>
       </c>
       <c r="AE41" s="20">
-        <v>7447.6500000000005</v>
+        <v>5971.6500000000005</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5536,85 +5538,85 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>389</v>
+        <v>270</v>
       </c>
       <c r="F42" s="14">
-        <v>2392.3500000000004</v>
+        <v>1660.5</v>
       </c>
       <c r="G42" s="14">
-        <v>5.1901267511674449</v>
+        <v>3.5130111524163565</v>
       </c>
       <c r="H42" s="30">
-        <v>1648.9</v>
+        <v>1690.8571428571429</v>
       </c>
       <c r="I42" s="15">
-        <v>-360.5</v>
+        <v>-498.57142857142867</v>
       </c>
       <c r="J42" s="16">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="K42" s="13">
-        <v>2164.8000000000002</v>
+        <v>1771.2</v>
       </c>
       <c r="L42" s="14">
-        <v>8.7890137328339577</v>
+        <v>6.8962371721778792</v>
       </c>
       <c r="M42" s="30">
-        <v>881.09999999999991</v>
+        <v>918.7619047619047</v>
       </c>
       <c r="N42" s="15">
-        <v>-48.5</v>
+        <v>-129.61904761904759</v>
       </c>
       <c r="O42" s="16">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="P42" s="17">
-        <v>707.25</v>
+        <v>584.25</v>
       </c>
       <c r="Q42" s="14">
-        <v>16.546762589928058</v>
+        <v>14.249999999999998</v>
       </c>
       <c r="R42" s="16">
-        <v>152.9</v>
+        <v>146.66666666666669</v>
       </c>
       <c r="S42" s="15">
-        <v>-24</v>
+        <v>-38.333333333333371</v>
       </c>
       <c r="T42" s="18">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="U42" s="17">
-        <v>1211.5500000000002</v>
+        <v>1143.9000000000001</v>
       </c>
       <c r="V42" s="14">
-        <v>11.005586592178771</v>
+        <v>10.790055248618785</v>
       </c>
       <c r="W42" s="16">
-        <v>393.79999999999995</v>
+        <v>379.23809523809524</v>
       </c>
       <c r="X42" s="15">
-        <v>-89.399999999999977</v>
+        <v>-89.809523809523796</v>
       </c>
       <c r="Y42" s="18">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="Z42" s="17">
-        <v>504.3</v>
+        <v>381.3</v>
       </c>
       <c r="AA42" s="14">
-        <v>27.796610169491522</v>
+        <v>19.147058823529413</v>
       </c>
       <c r="AB42" s="16">
-        <v>64.900000000000006</v>
+        <v>71.238095238095241</v>
       </c>
       <c r="AC42" s="15">
-        <v>17.099999999999994</v>
+        <v>-9.2380952380952408</v>
       </c>
       <c r="AD42" s="19">
-        <v>1135</v>
+        <v>901</v>
       </c>
       <c r="AE42" s="20">
-        <v>6980.25</v>
+        <v>5541.1500000000005</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5649,85 +5651,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2452</v>
+        <v>2916</v>
       </c>
       <c r="F43" s="14">
-        <v>2844.3199999999997</v>
+        <v>3382.56</v>
       </c>
       <c r="G43" s="14">
-        <v>7.2856930619521618</v>
+        <v>8.6175063326766104</v>
       </c>
       <c r="H43" s="30">
-        <v>7404.1</v>
+        <v>7444.3809523809532</v>
       </c>
       <c r="I43" s="15">
-        <v>-913.5</v>
+        <v>-467.80952380952385</v>
       </c>
       <c r="J43" s="16">
-        <v>3846</v>
+        <v>7767</v>
       </c>
       <c r="K43" s="13">
-        <v>4461.3599999999997</v>
+        <v>9009.7199999999993</v>
       </c>
       <c r="L43" s="14">
-        <v>15.981716185331393</v>
+        <v>31.068000000000001</v>
       </c>
       <c r="M43" s="30">
-        <v>5294.3</v>
+        <v>5500</v>
       </c>
       <c r="N43" s="15">
-        <v>1439.5</v>
+        <v>5267</v>
       </c>
       <c r="O43" s="16">
-        <v>772</v>
+        <v>705</v>
       </c>
       <c r="P43" s="17">
-        <v>895.52</v>
+        <v>817.8</v>
       </c>
       <c r="Q43" s="14">
-        <v>16.40807651434644</v>
+        <v>15.310237849017579</v>
       </c>
       <c r="R43" s="16">
-        <v>1035.0999999999999</v>
+        <v>1013.0476190476192</v>
       </c>
       <c r="S43" s="15">
-        <v>-169</v>
+        <v>-215.95238095238096</v>
       </c>
       <c r="T43" s="18">
-        <v>1236</v>
+        <v>1177</v>
       </c>
       <c r="U43" s="17">
-        <v>1433.76</v>
+        <v>1365.32</v>
       </c>
       <c r="V43" s="14">
-        <v>10.189612530915086</v>
+        <v>9.851335193304104</v>
       </c>
       <c r="W43" s="16">
-        <v>2668.6</v>
+        <v>2628.4761904761908</v>
       </c>
       <c r="X43" s="15">
-        <v>-704.8</v>
+        <v>-734.61904761904793</v>
       </c>
       <c r="Y43" s="18">
-        <v>548</v>
+        <v>476</v>
       </c>
       <c r="Z43" s="17">
-        <v>635.67999999999995</v>
+        <v>552.16</v>
       </c>
       <c r="AA43" s="14">
-        <v>19.46714031971581</v>
+        <v>15.099697885196376</v>
       </c>
       <c r="AB43" s="16">
-        <v>619.29999999999995</v>
+        <v>693.52380952380952</v>
       </c>
       <c r="AC43" s="15">
-        <v>-71.299999999999955</v>
+        <v>-217.52380952380952</v>
       </c>
       <c r="AD43" s="19">
-        <v>8854</v>
+        <v>13041</v>
       </c>
       <c r="AE43" s="20">
-        <v>10270.64</v>
+        <v>15127.56</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5762,85 +5764,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2725</v>
+        <v>2966</v>
       </c>
       <c r="F44" s="14">
-        <v>3161</v>
+        <v>3440.56</v>
       </c>
       <c r="G44" s="14">
-        <v>9.4997385393062572</v>
+        <v>10.310544611819235</v>
       </c>
       <c r="H44" s="30">
-        <v>6310.7000000000007</v>
+        <v>6328.666666666667</v>
       </c>
       <c r="I44" s="15">
-        <v>-143.5</v>
+        <v>89.33333333333303</v>
       </c>
       <c r="J44" s="16">
-        <v>6479</v>
+        <v>5587</v>
       </c>
       <c r="K44" s="13">
-        <v>7515.6399999999994</v>
+        <v>6480.9199999999992</v>
       </c>
       <c r="L44" s="14">
-        <v>35.173724212812161</v>
+        <v>28.962478400394964</v>
       </c>
       <c r="M44" s="30">
-        <v>4052.3999999999996</v>
+        <v>4243.9047619047615</v>
       </c>
       <c r="N44" s="15">
-        <v>4637</v>
+        <v>3657.9523809523807</v>
       </c>
       <c r="O44" s="16">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="P44" s="17">
-        <v>620.59999999999991</v>
+        <v>582.31999999999994</v>
       </c>
       <c r="Q44" s="14">
-        <v>19.597069597069595</v>
+        <v>19.028880866425997</v>
       </c>
       <c r="R44" s="16">
-        <v>600.6</v>
+        <v>580.38095238095229</v>
       </c>
       <c r="S44" s="15">
-        <v>-11</v>
+        <v>-25.619047619047478</v>
       </c>
       <c r="T44" s="18">
-        <v>776</v>
+        <v>735</v>
       </c>
       <c r="U44" s="17">
-        <v>900.16</v>
+        <v>852.59999999999991</v>
       </c>
       <c r="V44" s="14">
-        <v>11.829268292682928</v>
+        <v>11.241806263656228</v>
       </c>
       <c r="W44" s="16">
-        <v>1443.1999999999998</v>
+        <v>1438.3809523809523</v>
       </c>
       <c r="X44" s="15">
-        <v>-273.59999999999991</v>
+        <v>-311.09523809523807</v>
       </c>
       <c r="Y44" s="18">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="Z44" s="17">
-        <v>530.12</v>
+        <v>457.03999999999996</v>
       </c>
       <c r="AA44" s="14">
-        <v>16.350626118067979</v>
+        <v>12.84782608695652</v>
       </c>
       <c r="AB44" s="16">
-        <v>614.9</v>
+        <v>674.66666666666674</v>
       </c>
       <c r="AC44" s="15">
-        <v>-157.89999999999998</v>
+        <v>-280.66666666666674</v>
       </c>
       <c r="AD44" s="19">
-        <v>10972</v>
+        <v>10184</v>
       </c>
       <c r="AE44" s="20">
-        <v>12727.519999999999</v>
+        <v>11813.439999999999</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5875,85 +5877,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2956</v>
+        <v>3406</v>
       </c>
       <c r="F45" s="14">
-        <v>3428.9599999999996</v>
+        <v>3950.9599999999996</v>
       </c>
       <c r="G45" s="14">
-        <v>7.7099634846113725</v>
+        <v>8.8863212821468505</v>
       </c>
       <c r="H45" s="30">
-        <v>8434.7999999999993</v>
+        <v>8432.2857142857138</v>
       </c>
       <c r="I45" s="15">
-        <v>-878</v>
+        <v>-426.85714285714266</v>
       </c>
       <c r="J45" s="16">
-        <v>7427</v>
+        <v>6227</v>
       </c>
       <c r="K45" s="13">
-        <v>8615.32</v>
+        <v>7223.32</v>
       </c>
       <c r="L45" s="14">
-        <v>30.209477323571285</v>
+        <v>24.419607843137253</v>
       </c>
       <c r="M45" s="30">
-        <v>5408.7</v>
+        <v>5610</v>
       </c>
       <c r="N45" s="15">
-        <v>4968.5</v>
+        <v>3677</v>
       </c>
       <c r="O45" s="16">
-        <v>707</v>
+        <v>658</v>
       </c>
       <c r="P45" s="17">
-        <v>820.11999999999989</v>
+        <v>763.28</v>
       </c>
       <c r="Q45" s="14">
-        <v>15.693673695893454</v>
+        <v>15.234840132304301</v>
       </c>
       <c r="R45" s="16">
-        <v>991.09999999999991</v>
+        <v>950.19047619047615</v>
       </c>
       <c r="S45" s="15">
-        <v>-194</v>
+        <v>-205.80952380952385</v>
       </c>
       <c r="T45" s="18">
-        <v>1163</v>
+        <v>1095</v>
       </c>
       <c r="U45" s="17">
-        <v>1349.08</v>
+        <v>1270.1999999999998</v>
       </c>
       <c r="V45" s="14">
-        <v>12.152560083594565</v>
+        <v>11.549472626820693</v>
       </c>
       <c r="W45" s="16">
-        <v>2105.4</v>
+        <v>2085.8095238095239</v>
       </c>
       <c r="X45" s="15">
-        <v>-368.20000000000005</v>
+        <v>-421.95238095238096</v>
       </c>
       <c r="Y45" s="18">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="Z45" s="17">
-        <v>547.52</v>
+        <v>470.96</v>
       </c>
       <c r="AA45" s="14">
-        <v>17.912713472485766</v>
+        <v>13.796116504854368</v>
       </c>
       <c r="AB45" s="16">
-        <v>579.70000000000005</v>
+        <v>647.42857142857144</v>
       </c>
       <c r="AC45" s="15">
-        <v>-107.70000000000005</v>
+        <v>-241.42857142857144</v>
       </c>
       <c r="AD45" s="19">
-        <v>12725</v>
+        <v>11792</v>
       </c>
       <c r="AE45" s="20">
-        <v>14760.999999999998</v>
+        <v>13678.72</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5988,85 +5990,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2398</v>
+        <v>2523</v>
       </c>
       <c r="F46" s="14">
-        <v>2781.68</v>
+        <v>2926.68</v>
       </c>
       <c r="G46" s="14">
-        <v>8.5934420354775121</v>
+        <v>8.865963855421688</v>
       </c>
       <c r="H46" s="30">
-        <v>6139.1</v>
+        <v>6260.5714285714284</v>
       </c>
       <c r="I46" s="15">
-        <v>-392.5</v>
+        <v>-322.71428571428532</v>
       </c>
       <c r="J46" s="16">
-        <v>5041</v>
+        <v>4236</v>
       </c>
       <c r="K46" s="13">
-        <v>5847.5599999999995</v>
+        <v>4913.7599999999993</v>
       </c>
       <c r="L46" s="14">
-        <v>32.648963730569946</v>
+        <v>26.071512309495898</v>
       </c>
       <c r="M46" s="30">
-        <v>3396.8</v>
+        <v>3574.4761904761908</v>
       </c>
       <c r="N46" s="15">
-        <v>3497</v>
+        <v>2611.2380952380954</v>
       </c>
       <c r="O46" s="16">
-        <v>491</v>
+        <v>449</v>
       </c>
       <c r="P46" s="17">
-        <v>569.55999999999995</v>
+        <v>520.83999999999992</v>
       </c>
       <c r="Q46" s="14">
-        <v>18.528301886792452</v>
+        <v>17.428835489833642</v>
       </c>
       <c r="R46" s="16">
-        <v>583</v>
+        <v>566.76190476190482</v>
       </c>
       <c r="S46" s="15">
-        <v>-39</v>
+        <v>-66.238095238095298</v>
       </c>
       <c r="T46" s="18">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="U46" s="17">
-        <v>677.43999999999994</v>
+        <v>662.3599999999999</v>
       </c>
       <c r="V46" s="14">
-        <v>14.784810126582279</v>
+        <v>14.767241379310345</v>
       </c>
       <c r="W46" s="16">
-        <v>869</v>
+        <v>850.66666666666663</v>
       </c>
       <c r="X46" s="15">
-        <v>-48</v>
+        <v>-47.666666666666629</v>
       </c>
       <c r="Y46" s="18">
-        <v>540</v>
+        <v>506</v>
       </c>
       <c r="Z46" s="17">
-        <v>626.4</v>
+        <v>586.95999999999992</v>
       </c>
       <c r="AA46" s="14">
-        <v>25.352112676056336</v>
+        <v>22.656716417910449</v>
       </c>
       <c r="AB46" s="16">
-        <v>468.6</v>
+        <v>491.33333333333331</v>
       </c>
       <c r="AC46" s="15">
-        <v>71.399999999999977</v>
+        <v>14.666666666666686</v>
       </c>
       <c r="AD46" s="19">
-        <v>9054</v>
+        <v>8285</v>
       </c>
       <c r="AE46" s="20">
-        <v>10502.64</v>
+        <v>9610.5999999999985</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6114,19 +6116,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K47" s="13">
-        <v>342</v>
+        <v>522</v>
       </c>
       <c r="L47" s="14">
-        <v>6.333333333333333</v>
+        <v>10.15</v>
       </c>
       <c r="M47" s="30">
-        <v>66</v>
+        <v>62.857142857142861</v>
       </c>
       <c r="N47" s="15">
-        <v>-11</v>
+        <v>0.42857142857142705</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6150,13 +6152,13 @@
         <v>270</v>
       </c>
       <c r="V47" s="14">
-        <v>15</v>
+        <v>15.749999999999998</v>
       </c>
       <c r="W47" s="16">
-        <v>22</v>
+        <v>20.952380952380953</v>
       </c>
       <c r="X47" s="15">
-        <v>-1</v>
+        <v>-0.23809523809523903</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6174,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AE47" s="20">
-        <v>612</v>
+        <v>792</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6225,19 +6227,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K48" s="13">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="L48" s="14">
-        <v>10.909090909090908</v>
+        <v>21</v>
       </c>
       <c r="M48" s="30">
-        <v>12.100000000000001</v>
+        <v>11.523809523809524</v>
       </c>
       <c r="N48" s="15">
-        <v>0.5</v>
+        <v>5.7619047619047619</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6285,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AE48" s="20">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6323,19 +6325,19 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F49" s="14">
-        <v>31.319999999999997</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G49" s="14">
-        <v>0.51625239005736145</v>
+        <v>0.3</v>
       </c>
       <c r="H49" s="30">
-        <v>1150.5999999999999</v>
+        <v>1100</v>
       </c>
       <c r="I49" s="15">
-        <v>-496</v>
+        <v>-485</v>
       </c>
       <c r="J49" s="16">
         <v>0</v>
@@ -6347,61 +6349,61 @@
         <v>0</v>
       </c>
       <c r="M49" s="30">
-        <v>1238.5999999999999</v>
+        <v>1179.6190476190477</v>
       </c>
       <c r="N49" s="15">
-        <v>-563</v>
+        <v>-536.19047619047615</v>
       </c>
       <c r="O49" s="16">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P49" s="17">
-        <v>44.08</v>
+        <v>27.839999999999996</v>
       </c>
       <c r="Q49" s="14">
-        <v>5.1006711409395971</v>
+        <v>3.2101910828025479</v>
       </c>
       <c r="R49" s="16">
-        <v>163.9</v>
+        <v>164.47619047619048</v>
       </c>
       <c r="S49" s="15">
-        <v>-111</v>
+        <v>-125.52380952380952</v>
       </c>
       <c r="T49" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U49" s="17">
-        <v>5.8</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="V49" s="14">
-        <v>0.43478260869565216</v>
+        <v>8.9743589743589744E-2</v>
       </c>
       <c r="W49" s="16">
-        <v>253</v>
+        <v>245.14285714285714</v>
       </c>
       <c r="X49" s="15">
-        <v>-179</v>
+        <v>-177.28571428571428</v>
       </c>
       <c r="Y49" s="18">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Z49" s="17">
-        <v>20.88</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="AA49" s="14">
-        <v>3.75</v>
+        <v>1.6633663366336635</v>
       </c>
       <c r="AB49" s="16">
-        <v>105.6</v>
+        <v>105.80952380952381</v>
       </c>
       <c r="AC49" s="15">
-        <v>-87.6</v>
+        <v>-97.80952380952381</v>
       </c>
       <c r="AD49" s="19">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="AE49" s="20">
-        <v>102.08</v>
+        <v>55.679999999999993</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6436,85 +6438,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1712</v>
+        <v>1382</v>
       </c>
       <c r="F50" s="14">
-        <v>1985.9199999999998</v>
+        <v>1603.12</v>
       </c>
       <c r="G50" s="14">
-        <v>5.9361997226074896</v>
+        <v>4.7359660574412539</v>
       </c>
       <c r="H50" s="30">
-        <v>6344.7999999999993</v>
+        <v>6419.8095238095239</v>
       </c>
       <c r="I50" s="15">
-        <v>-1172</v>
+        <v>-1536.0952380952381</v>
       </c>
       <c r="J50" s="16">
-        <v>1187</v>
+        <v>789</v>
       </c>
       <c r="K50" s="13">
-        <v>1376.9199999999998</v>
+        <v>915.2399999999999</v>
       </c>
       <c r="L50" s="14">
-        <v>6.4827962861824142</v>
+        <v>4.0481309552895191</v>
       </c>
       <c r="M50" s="30">
-        <v>4028.2</v>
+        <v>4287.9047619047615</v>
       </c>
       <c r="N50" s="15">
-        <v>-644</v>
+        <v>-1160.047619047619</v>
       </c>
       <c r="O50" s="16">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="P50" s="17">
-        <v>139.19999999999999</v>
+        <v>80.039999999999992</v>
       </c>
       <c r="Q50" s="14">
-        <v>2.7874564459930316</v>
+        <v>1.6409966024915061</v>
       </c>
       <c r="R50" s="16">
-        <v>947.09999999999991</v>
+        <v>925.04761904761915</v>
       </c>
       <c r="S50" s="15">
-        <v>-741</v>
+        <v>-771.95238095238096</v>
       </c>
       <c r="T50" s="18">
-        <v>561</v>
+        <v>483</v>
       </c>
       <c r="U50" s="17">
-        <v>650.76</v>
+        <v>560.28</v>
       </c>
       <c r="V50" s="14">
-        <v>14.571428571428571</v>
+        <v>12.074999999999999</v>
       </c>
       <c r="W50" s="16">
-        <v>847</v>
+        <v>880</v>
       </c>
       <c r="X50" s="15">
-        <v>-55</v>
+        <v>-157</v>
       </c>
       <c r="Y50" s="18">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Z50" s="17">
-        <v>31.319999999999997</v>
+        <v>24.36</v>
       </c>
       <c r="AA50" s="14">
-        <v>2.5352112676056335</v>
+        <v>1.8374999999999999</v>
       </c>
       <c r="AB50" s="16">
-        <v>234.3</v>
+        <v>251.42857142857144</v>
       </c>
       <c r="AC50" s="15">
-        <v>-207.3</v>
+        <v>-230.42857142857144</v>
       </c>
       <c r="AD50" s="19">
-        <v>3607</v>
+        <v>2744</v>
       </c>
       <c r="AE50" s="20">
-        <v>4184.12</v>
+        <v>3183.04</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6552,85 +6554,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>1272</v>
+        <v>934</v>
       </c>
       <c r="F51" s="14">
-        <v>1475.52</v>
+        <v>1083.4399999999998</v>
       </c>
       <c r="G51" s="14">
-        <v>6.7230443974630028</v>
+        <v>4.7572156196943967</v>
       </c>
       <c r="H51" s="30">
-        <v>4162.3999999999996</v>
+        <v>4319.3333333333339</v>
       </c>
       <c r="I51" s="15">
-        <v>-620</v>
+        <v>-1029.3333333333337</v>
       </c>
       <c r="J51" s="16">
-        <v>1249</v>
+        <v>1046</v>
       </c>
       <c r="K51" s="13">
-        <v>1448.84</v>
+        <v>1213.3599999999999</v>
       </c>
       <c r="L51" s="14">
-        <v>7.6837896031990152</v>
+        <v>6.3467206009823753</v>
       </c>
       <c r="M51" s="30">
-        <v>3576.1000000000004</v>
+        <v>3625.8095238095234</v>
       </c>
       <c r="N51" s="15">
-        <v>-376.5</v>
+        <v>-602.09523809523807</v>
       </c>
       <c r="O51" s="16">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="P51" s="17">
-        <v>291.15999999999997</v>
+        <v>266.79999999999995</v>
       </c>
       <c r="Q51" s="14">
-        <v>18.801498127340825</v>
+        <v>17.627737226277372</v>
       </c>
       <c r="R51" s="16">
-        <v>293.7</v>
+        <v>287.04761904761904</v>
       </c>
       <c r="S51" s="15">
-        <v>-16</v>
+        <v>-30.952380952380963</v>
       </c>
       <c r="T51" s="18">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="U51" s="17">
-        <v>517.36</v>
+        <v>453.55999999999995</v>
       </c>
       <c r="V51" s="14">
-        <v>13.313432835820896</v>
+        <v>11.388349514563107</v>
       </c>
       <c r="W51" s="16">
-        <v>737</v>
+        <v>755.33333333333337</v>
       </c>
       <c r="X51" s="15">
-        <v>-90</v>
+        <v>-158.33333333333337</v>
       </c>
       <c r="Y51" s="18">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="Z51" s="17">
-        <v>146.16</v>
+        <v>102.08</v>
       </c>
       <c r="AA51" s="14">
-        <v>29.647058823529413</v>
+        <v>16.648648648648649</v>
       </c>
       <c r="AB51" s="16">
-        <v>93.5</v>
+        <v>116.28571428571428</v>
       </c>
       <c r="AC51" s="15">
-        <v>32.5</v>
+        <v>-28.285714285714278</v>
       </c>
       <c r="AD51" s="19">
-        <v>3344</v>
+        <v>2689</v>
       </c>
       <c r="AE51" s="20">
-        <v>3879.0399999999995</v>
+        <v>3119.24</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6669,85 +6671,85 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>1860</v>
+        <v>1761</v>
       </c>
       <c r="F52" s="14">
-        <v>1506.6000000000001</v>
+        <v>1426.41</v>
       </c>
       <c r="G52" s="14">
-        <v>11.824539097266369</v>
+        <v>11.250684514755097</v>
       </c>
       <c r="H52" s="30">
-        <v>3460.6000000000004</v>
+        <v>3443.5238095238092</v>
       </c>
       <c r="I52" s="15">
-        <v>287</v>
+        <v>195.76190476190482</v>
       </c>
       <c r="J52" s="16">
-        <v>3888</v>
+        <v>3733</v>
       </c>
       <c r="K52" s="13">
-        <v>3149.28</v>
+        <v>3023.73</v>
       </c>
       <c r="L52" s="14">
-        <v>80.24767801857584</v>
+        <v>68.947229551451187</v>
       </c>
       <c r="M52" s="30">
-        <v>1065.9000000000001</v>
+        <v>1191.1428571428571</v>
       </c>
       <c r="N52" s="15">
-        <v>3403.5</v>
+        <v>3191.5714285714284</v>
       </c>
       <c r="O52" s="16">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="P52" s="17">
-        <v>33.21</v>
+        <v>8.1000000000000014</v>
       </c>
       <c r="Q52" s="14">
-        <v>3.5344827586206899</v>
+        <v>0.8366533864541833</v>
       </c>
       <c r="R52" s="16">
-        <v>255.2</v>
+        <v>262.95238095238096</v>
       </c>
       <c r="S52" s="15">
-        <v>-191</v>
+        <v>-229.04761904761904</v>
       </c>
       <c r="T52" s="18">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="U52" s="17">
-        <v>223.56</v>
+        <v>189.54000000000002</v>
       </c>
       <c r="V52" s="14">
-        <v>11.358024691358024</v>
+        <v>9.4137931034482758</v>
       </c>
       <c r="W52" s="16">
-        <v>534.6</v>
+        <v>546.85714285714289</v>
       </c>
       <c r="X52" s="15">
-        <v>-112.80000000000001</v>
+        <v>-163.71428571428572</v>
       </c>
       <c r="Y52" s="18">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="Z52" s="17">
-        <v>97.2</v>
+        <v>74.52000000000001</v>
       </c>
       <c r="AA52" s="14">
-        <v>104.34782608695653</v>
+        <v>37.882352941176471</v>
       </c>
       <c r="AB52" s="16">
-        <v>25.299999999999997</v>
+        <v>53.428571428571423</v>
       </c>
       <c r="AC52" s="15">
-        <v>94.7</v>
+        <v>38.571428571428577</v>
       </c>
       <c r="AD52" s="19">
-        <v>6185</v>
+        <v>5830</v>
       </c>
       <c r="AE52" s="20">
-        <v>5009.8500000000004</v>
+        <v>4722.3</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6782,85 +6784,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="F53" s="14">
-        <v>388.8</v>
+        <v>63.180000000000007</v>
       </c>
       <c r="G53" s="14">
-        <v>1.7413386540903322</v>
+        <v>0.28762071992976296</v>
       </c>
       <c r="H53" s="30">
-        <v>6064.2999999999993</v>
+        <v>5966.1904761904761</v>
       </c>
       <c r="I53" s="15">
-        <v>-2276.5</v>
+        <v>-2633.9047619047619</v>
       </c>
       <c r="J53" s="16">
-        <v>0</v>
+        <v>9886</v>
       </c>
       <c r="K53" s="13">
-        <v>0</v>
+        <v>8007.6600000000008</v>
       </c>
       <c r="L53" s="14">
-        <v>0</v>
+        <v>80.002312138728328</v>
       </c>
       <c r="M53" s="30">
-        <v>2633.4</v>
+        <v>2718.5714285714284</v>
       </c>
       <c r="N53" s="15">
-        <v>-1197</v>
+        <v>8650.2857142857138</v>
       </c>
       <c r="O53" s="16">
-        <v>432</v>
+        <v>388</v>
       </c>
       <c r="P53" s="17">
-        <v>349.92</v>
+        <v>314.28000000000003</v>
       </c>
       <c r="Q53" s="14">
-        <v>13.692551505546751</v>
+        <v>12.535384615384615</v>
       </c>
       <c r="R53" s="16">
-        <v>694.1</v>
+        <v>680.95238095238096</v>
       </c>
       <c r="S53" s="15">
-        <v>-199</v>
+        <v>-231.04761904761904</v>
       </c>
       <c r="T53" s="18">
-        <v>676</v>
+        <v>592</v>
       </c>
       <c r="U53" s="17">
-        <v>547.56000000000006</v>
+        <v>479.52000000000004</v>
       </c>
       <c r="V53" s="14">
-        <v>12.358318098720291</v>
+        <v>10.607508532423209</v>
       </c>
       <c r="W53" s="16">
-        <v>1203.4000000000001</v>
+        <v>1227.8095238095239</v>
       </c>
       <c r="X53" s="15">
-        <v>-199.20000000000005</v>
+        <v>-300.95238095238096</v>
       </c>
       <c r="Y53" s="18">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="Z53" s="17">
-        <v>194.4</v>
+        <v>167.67000000000002</v>
       </c>
       <c r="AA53" s="14">
-        <v>40.336134453781511</v>
+        <v>28.598684210526315</v>
       </c>
       <c r="AB53" s="16">
-        <v>130.9</v>
+        <v>159.23809523809524</v>
       </c>
       <c r="AC53" s="15">
-        <v>109.1</v>
+        <v>47.761904761904759</v>
       </c>
       <c r="AD53" s="19">
-        <v>1828</v>
+        <v>11151</v>
       </c>
       <c r="AE53" s="20">
-        <v>1480.68</v>
+        <v>9032.3100000000013</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6895,85 +6897,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>3051</v>
+        <v>2994</v>
       </c>
       <c r="F54" s="14">
-        <v>2471.31</v>
+        <v>2425.1400000000003</v>
       </c>
       <c r="G54" s="14">
-        <v>15.927956147220046</v>
+        <v>16.084420567920183</v>
       </c>
       <c r="H54" s="30">
-        <v>4214.1000000000004</v>
+        <v>4095.1428571428569</v>
       </c>
       <c r="I54" s="15">
-        <v>1135.5</v>
+        <v>1132.5714285714287</v>
       </c>
       <c r="J54" s="16">
-        <v>1988</v>
+        <v>1955</v>
       </c>
       <c r="K54" s="13">
-        <v>1610.2800000000002</v>
+        <v>1583.5500000000002</v>
       </c>
       <c r="L54" s="14">
-        <v>32.064516129032256</v>
+        <v>31.899766899766899</v>
       </c>
       <c r="M54" s="30">
-        <v>1364</v>
+        <v>1348.2857142857142</v>
       </c>
       <c r="N54" s="15">
-        <v>1368</v>
+        <v>1342.1428571428571</v>
       </c>
       <c r="O54" s="16">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="P54" s="17">
-        <v>174.96</v>
+        <v>154.71</v>
       </c>
       <c r="Q54" s="14">
-        <v>16.941176470588236</v>
+        <v>15.309160305343511</v>
       </c>
       <c r="R54" s="16">
-        <v>280.5</v>
+        <v>274.47619047619048</v>
       </c>
       <c r="S54" s="15">
-        <v>-39</v>
+        <v>-58.523809523809518</v>
       </c>
       <c r="T54" s="18">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="U54" s="17">
-        <v>346.68</v>
+        <v>336.96000000000004</v>
       </c>
       <c r="V54" s="14">
-        <v>18.730853391684899</v>
+        <v>18.626865671641792</v>
       </c>
       <c r="W54" s="16">
-        <v>502.70000000000005</v>
+        <v>491.33333333333331</v>
       </c>
       <c r="X54" s="15">
-        <v>62.399999999999977</v>
+        <v>58.666666666666686</v>
       </c>
       <c r="Y54" s="18">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="Z54" s="17">
-        <v>170.91000000000003</v>
+        <v>144.18</v>
       </c>
       <c r="AA54" s="14">
-        <v>26.708860759493671</v>
+        <v>19.570680628272253</v>
       </c>
       <c r="AB54" s="16">
-        <v>173.8</v>
+        <v>200.09523809523807</v>
       </c>
       <c r="AC54" s="15">
-        <v>37.199999999999989</v>
+        <v>-22.095238095238074</v>
       </c>
       <c r="AD54" s="19">
-        <v>5894</v>
+        <v>5734</v>
       </c>
       <c r="AE54" s="20">
-        <v>4774.1400000000003</v>
+        <v>4644.54</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7008,85 +7010,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>1884</v>
+        <v>1832</v>
       </c>
       <c r="F55" s="14">
-        <v>1526.0400000000002</v>
+        <v>1483.92</v>
       </c>
       <c r="G55" s="14">
-        <v>11.237697584252908</v>
+        <v>11.216326530612244</v>
       </c>
       <c r="H55" s="30">
-        <v>3688.3</v>
+        <v>3593.3333333333335</v>
       </c>
       <c r="I55" s="15">
-        <v>207.5</v>
+        <v>198.66666666666652</v>
       </c>
       <c r="J55" s="16">
-        <v>6183</v>
+        <v>6135</v>
       </c>
       <c r="K55" s="13">
-        <v>5008.2300000000005</v>
+        <v>4969.3500000000004</v>
       </c>
       <c r="L55" s="14">
-        <v>82.715719063545151</v>
+        <v>83.713450292397653</v>
       </c>
       <c r="M55" s="30">
-        <v>1644.5</v>
+        <v>1612.2857142857144</v>
       </c>
       <c r="N55" s="15">
-        <v>5435.5</v>
+        <v>5402.1428571428569</v>
       </c>
       <c r="O55" s="16">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="P55" s="17">
-        <v>260.01</v>
+        <v>234.09</v>
       </c>
       <c r="Q55" s="14">
-        <v>18.238636363636363</v>
+        <v>16.905292479108635</v>
       </c>
       <c r="R55" s="16">
-        <v>387.20000000000005</v>
+        <v>376.09523809523807</v>
       </c>
       <c r="S55" s="15">
-        <v>-31</v>
+        <v>-52.904761904761926</v>
       </c>
       <c r="T55" s="18">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="U55" s="17">
-        <v>334.53000000000003</v>
+        <v>324.81</v>
       </c>
       <c r="V55" s="14">
-        <v>15.976789168278529</v>
+        <v>15.918714555765597</v>
       </c>
       <c r="W55" s="16">
-        <v>568.70000000000005</v>
+        <v>554.19047619047615</v>
       </c>
       <c r="X55" s="15">
-        <v>-0.60000000000002274</v>
+        <v>-2.0476190476190368</v>
       </c>
       <c r="Y55" s="18">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="Z55" s="17">
-        <v>179.82000000000002</v>
+        <v>157.14000000000001</v>
       </c>
       <c r="AA55" s="14">
-        <v>27.073170731707318</v>
+        <v>21.21875</v>
       </c>
       <c r="AB55" s="16">
-        <v>180.39999999999998</v>
+        <v>201.14285714285714</v>
       </c>
       <c r="AC55" s="15">
-        <v>41.600000000000023</v>
+        <v>-7.1428571428571388</v>
       </c>
       <c r="AD55" s="19">
-        <v>9023</v>
+        <v>8851</v>
       </c>
       <c r="AE55" s="20">
-        <v>7308.63</v>
+        <v>7169.31</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7121,34 +7123,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>699</v>
+        <v>357</v>
       </c>
       <c r="F56" s="14">
-        <v>1831.38</v>
+        <v>935.34</v>
       </c>
       <c r="G56" s="14">
-        <v>23.456375838926174</v>
+        <v>12.37128712871287</v>
       </c>
       <c r="H56" s="30">
-        <v>655.6</v>
+        <v>634.85714285714289</v>
       </c>
       <c r="I56" s="15">
-        <v>401</v>
+        <v>68.428571428571445</v>
       </c>
       <c r="J56" s="32">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="K56" s="13">
-        <v>136.24</v>
+        <v>26.200000000000003</v>
       </c>
       <c r="L56" s="14">
-        <v>4.0944881889763778</v>
+        <v>0.70945945945945943</v>
       </c>
       <c r="M56" s="30">
-        <v>279.39999999999998</v>
+        <v>310.09523809523807</v>
       </c>
       <c r="N56" s="15">
-        <v>-75</v>
+        <v>-130.95238095238096</v>
       </c>
       <c r="O56" s="32">
         <v>42</v>
@@ -7157,49 +7159,49 @@
         <v>110.04</v>
       </c>
       <c r="Q56" s="14">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="R56" s="16">
-        <v>66</v>
+        <v>62.857142857142861</v>
       </c>
       <c r="S56" s="15">
-        <v>-18</v>
+        <v>-15.142857142857146</v>
       </c>
       <c r="T56" s="18">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="U56" s="17">
-        <v>282.96000000000004</v>
+        <v>267.24</v>
       </c>
       <c r="V56" s="14">
-        <v>15.319148936170214</v>
+        <v>14.571428571428571</v>
       </c>
       <c r="W56" s="16">
-        <v>155.1</v>
+        <v>154</v>
       </c>
       <c r="X56" s="15">
-        <v>-4.7999999999999972</v>
+        <v>-10</v>
       </c>
       <c r="Y56" s="18">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Z56" s="17">
-        <v>117.9</v>
+        <v>102.18</v>
       </c>
       <c r="AA56" s="14">
-        <v>29.032258064516128</v>
+        <v>22.135135135135137</v>
       </c>
       <c r="AB56" s="16">
-        <v>34.1</v>
+        <v>38.761904761904759</v>
       </c>
       <c r="AC56" s="15">
-        <v>10.899999999999999</v>
+        <v>0.2380952380952408</v>
       </c>
       <c r="AD56" s="19">
-        <v>946</v>
+        <v>550</v>
       </c>
       <c r="AE56" s="20">
-        <v>2478.52</v>
+        <v>1441</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7234,34 +7236,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F57" s="14">
-        <v>345.84000000000003</v>
+        <v>314.40000000000003</v>
       </c>
       <c r="G57" s="14">
-        <v>2.0576773187840995</v>
+        <v>1.9236641221374047</v>
       </c>
       <c r="H57" s="30">
-        <v>1411.3000000000002</v>
+        <v>1372.3809523809523</v>
       </c>
       <c r="I57" s="15">
-        <v>-509.5</v>
+        <v>-503.80952380952385</v>
       </c>
       <c r="J57" s="32">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K57" s="13">
-        <v>78.600000000000009</v>
+        <v>0</v>
       </c>
       <c r="L57" s="14">
-        <v>1.125703564727955</v>
+        <v>0</v>
       </c>
       <c r="M57" s="30">
-        <v>586.29999999999995</v>
+        <v>589.80952380952385</v>
       </c>
       <c r="N57" s="15">
-        <v>-236.5</v>
+        <v>-268.09523809523807</v>
       </c>
       <c r="O57" s="32">
         <v>69</v>
@@ -7270,49 +7272,49 @@
         <v>180.78</v>
       </c>
       <c r="Q57" s="14">
-        <v>9.4520547945205475</v>
+        <v>9.9246575342465757</v>
       </c>
       <c r="R57" s="16">
-        <v>160.6</v>
+        <v>152.95238095238096</v>
       </c>
       <c r="S57" s="15">
-        <v>-77</v>
+        <v>-70.047619047619037</v>
       </c>
       <c r="T57" s="18">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="U57" s="17">
-        <v>125.76</v>
+        <v>78.600000000000009</v>
       </c>
       <c r="V57" s="14">
-        <v>2.3762376237623761</v>
+        <v>1.4928909952606635</v>
       </c>
       <c r="W57" s="16">
-        <v>444.4</v>
+        <v>442.09523809523807</v>
       </c>
       <c r="X57" s="15">
-        <v>-275.2</v>
+        <v>-291.52380952380952</v>
       </c>
       <c r="Y57" s="18">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Z57" s="17">
-        <v>157.20000000000002</v>
+        <v>141.48000000000002</v>
       </c>
       <c r="AA57" s="14">
-        <v>37.5</v>
+        <v>29.842105263157894</v>
       </c>
       <c r="AB57" s="16">
-        <v>35.200000000000003</v>
+        <v>39.80952380952381</v>
       </c>
       <c r="AC57" s="15">
-        <v>24.799999999999997</v>
+        <v>14.19047619047619</v>
       </c>
       <c r="AD57" s="19">
-        <v>339</v>
+        <v>273</v>
       </c>
       <c r="AE57" s="20">
-        <v>888.18000000000006</v>
+        <v>715.26</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7347,85 +7349,85 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F58" s="14">
-        <v>157.20000000000002</v>
+        <v>110.04</v>
       </c>
       <c r="G58" s="14">
-        <v>2.5423728813559321</v>
+        <v>1.785425101214575</v>
       </c>
       <c r="H58" s="30">
-        <v>519.20000000000005</v>
+        <v>517.52380952380952</v>
       </c>
       <c r="I58" s="15">
-        <v>-176</v>
+        <v>-193.23809523809521</v>
       </c>
       <c r="J58" s="32">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K58" s="13">
-        <v>125.76</v>
+        <v>57.64</v>
       </c>
       <c r="L58" s="14">
-        <v>5.5813953488372094</v>
+        <v>2.2647058823529416</v>
       </c>
       <c r="M58" s="30">
-        <v>189.2</v>
+        <v>213.71428571428569</v>
       </c>
       <c r="N58" s="15">
-        <v>-38</v>
+        <v>-75.142857142857139</v>
       </c>
       <c r="O58" s="32">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P58" s="17">
-        <v>65.5</v>
+        <v>55.02</v>
       </c>
       <c r="Q58" s="14">
-        <v>15.625</v>
+        <v>13.781250000000004</v>
       </c>
       <c r="R58" s="16">
-        <v>35.200000000000003</v>
+        <v>33.523809523809518</v>
       </c>
       <c r="S58" s="15">
-        <v>-7</v>
+        <v>-9.4761904761904709</v>
       </c>
       <c r="T58" s="18">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="U58" s="17">
-        <v>246.28</v>
+        <v>230.56</v>
       </c>
       <c r="V58" s="14">
-        <v>18.98989898989899</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="W58" s="16">
-        <v>108.9</v>
+        <v>110</v>
       </c>
       <c r="X58" s="15">
-        <v>14.799999999999997</v>
+        <v>8</v>
       </c>
       <c r="Y58" s="18">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z58" s="17">
-        <v>110.04</v>
+        <v>94.320000000000007</v>
       </c>
       <c r="AA58" s="14">
-        <v>31.111111111111111</v>
+        <v>22.90909090909091</v>
       </c>
       <c r="AB58" s="16">
-        <v>29.700000000000003</v>
+        <v>34.571428571428569</v>
       </c>
       <c r="AC58" s="15">
-        <v>12.299999999999997</v>
+        <v>1.4285714285714306</v>
       </c>
       <c r="AD58" s="19">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="AE58" s="20">
-        <v>704.78</v>
+        <v>547.58000000000004</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7463,34 +7465,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F59" s="14">
-        <v>361.56</v>
+        <v>322.26</v>
       </c>
       <c r="G59" s="14">
-        <v>4.5695364238410594</v>
+        <v>4.1594202898550732</v>
       </c>
       <c r="H59" s="30">
-        <v>664.4</v>
+        <v>650.57142857142856</v>
       </c>
       <c r="I59" s="15">
-        <v>-164</v>
+        <v>-172.71428571428567</v>
       </c>
       <c r="J59" s="32">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K59" s="13">
-        <v>117.9</v>
+        <v>89.08</v>
       </c>
       <c r="L59" s="14">
-        <v>4.1474654377880187</v>
+        <v>3.1315789473684208</v>
       </c>
       <c r="M59" s="30">
-        <v>238.7</v>
+        <v>238.85714285714286</v>
       </c>
       <c r="N59" s="15">
-        <v>-63.5</v>
+        <v>-74.571428571428584</v>
       </c>
       <c r="O59" s="32">
         <v>20</v>
@@ -7499,49 +7501,49 @@
         <v>52.400000000000006</v>
       </c>
       <c r="Q59" s="14">
-        <v>5.7971014492753623</v>
+        <v>6.0869565217391317</v>
       </c>
       <c r="R59" s="16">
-        <v>75.900000000000006</v>
+        <v>72.285714285714278</v>
       </c>
       <c r="S59" s="15">
-        <v>-49</v>
+        <v>-45.714285714285708</v>
       </c>
       <c r="T59" s="18">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="U59" s="17">
-        <v>251.52</v>
+        <v>235.8</v>
       </c>
       <c r="V59" s="14">
-        <v>16.410256410256412</v>
+        <v>15.365853658536585</v>
       </c>
       <c r="W59" s="16">
-        <v>128.69999999999999</v>
+        <v>128.85714285714286</v>
       </c>
       <c r="X59" s="15">
-        <v>2.4000000000000057</v>
+        <v>-3.7142857142857224</v>
       </c>
       <c r="Y59" s="18">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Z59" s="17">
-        <v>138.86000000000001</v>
+        <v>123.14</v>
       </c>
       <c r="AA59" s="14">
-        <v>70.666666666666671</v>
+        <v>47</v>
       </c>
       <c r="AB59" s="16">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AC59" s="15">
-        <v>36.5</v>
+        <v>25</v>
       </c>
       <c r="AD59" s="19">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="AE59" s="20">
-        <v>922.24</v>
+        <v>822.68000000000006</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7654,11 +7656,11 @@
       <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>176276.57</v>
+        <v>173788.32</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>36.727274863810258</v>
+        <v>35.136132855048153</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7696,11 +7698,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>197184.99000000002</v>
+        <v>225699.41</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>41.083550279811313</v>
+        <v>45.63140063190658</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7738,11 +7740,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>31064.699999999997</v>
+        <v>28810.92</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>6.4723393214526821</v>
+        <v>5.8249272033711117</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7780,11 +7782,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>56164.01</v>
+        <v>49655.54</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>11.70178789344374</v>
+        <v>10.039245735439284</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7822,11 +7824,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>19270.660000000003</v>
+        <v>16660.060000000001</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>4.015047641481984</v>
+        <v>3.3682935742348712</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7864,7 +7866,7 @@
       <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>479960.93000000017</v>
+        <v>494614.25</v>
       </c>
       <c r="E67" s="66">
         <f>D67*100/D67</f>
@@ -7976,11 +7978,11 @@
       <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>129451</v>
+        <v>128437</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>36.751420930404223</v>
+        <v>34.915590593992114</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8017,11 +8019,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>147993</v>
+        <v>172485</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>42.015535127216566</v>
+        <v>46.890036699741742</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8059,11 +8061,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>22303</v>
+        <v>20703</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>6.3318702907726117</v>
+        <v>5.6281092836754114</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8101,11 +8103,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>39475</v>
+        <v>34859</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>11.20703850281347</v>
+        <v>9.4764170178061704</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8143,11 +8145,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>13012</v>
+        <v>11366</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>3.6941351487931318</v>
+        <v>3.0898464047845589</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8185,7 +8187,7 @@
       <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>352234</v>
+        <v>367850</v>
       </c>
       <c r="E75" s="66">
         <f>D75*100/D75</f>

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD73858E-1A6F-4301-9FEF-FC35027B0CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E05AE50-C45A-45E4-B9FD-B7CB5CD65286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1661,242 +1661,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
     </row>
     <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
     </row>
     <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
     </row>
     <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
@@ -2261,85 +2261,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5468</v>
+        <v>5490</v>
       </c>
       <c r="F13" s="14">
-        <v>7436.4800000000005</v>
+        <v>7466.4000000000005</v>
       </c>
       <c r="G13" s="14">
-        <v>6.9537939805002109</v>
+        <v>7.4497028148480435</v>
       </c>
       <c r="H13" s="30">
-        <v>17299.333333333336</v>
+        <v>16212.727272727272</v>
       </c>
       <c r="I13" s="15">
-        <v>-2395.3333333333348</v>
+        <v>-1879.4214876033047</v>
       </c>
       <c r="J13" s="16">
-        <v>7805</v>
+        <v>5178</v>
       </c>
       <c r="K13" s="13">
-        <v>10614.800000000001</v>
+        <v>7042.0800000000008</v>
       </c>
       <c r="L13" s="14">
-        <v>34.218162839248436</v>
+        <v>24.951732377538825</v>
       </c>
       <c r="M13" s="30">
-        <v>5018.0952380952385</v>
+        <v>4565.454545454546</v>
       </c>
       <c r="N13" s="15">
-        <v>5524.0476190476184</v>
+        <v>3102.7933884297518</v>
       </c>
       <c r="O13" s="16">
-        <v>866</v>
+        <v>792</v>
       </c>
       <c r="P13" s="17">
-        <v>1177.76</v>
+        <v>1077.1200000000001</v>
       </c>
       <c r="Q13" s="14">
-        <v>20.319553072625698</v>
+        <v>19.82047569803516</v>
       </c>
       <c r="R13" s="16">
-        <v>937.61904761904771</v>
+        <v>879.09090909090901</v>
       </c>
       <c r="S13" s="15">
-        <v>13.619047619047592</v>
+        <v>-7.1735537190082823</v>
       </c>
       <c r="T13" s="18">
-        <v>510</v>
+        <v>397</v>
       </c>
       <c r="U13" s="17">
-        <v>693.6</v>
+        <v>539.92000000000007</v>
       </c>
       <c r="V13" s="14">
-        <v>10.500000000000002</v>
+        <v>8.5171985815602831</v>
       </c>
       <c r="W13" s="16">
-        <v>1068.5714285714284</v>
+        <v>1025.4545454545455</v>
       </c>
       <c r="X13" s="15">
-        <v>-267.142857142857</v>
+        <v>-348.78512396694214</v>
       </c>
       <c r="Y13" s="18">
-        <v>584</v>
+        <v>425</v>
       </c>
       <c r="Z13" s="17">
-        <v>794.24</v>
+        <v>578</v>
       </c>
       <c r="AA13" s="14">
-        <v>19.528662420382165</v>
+        <v>13.917456021650878</v>
       </c>
       <c r="AB13" s="16">
-        <v>657.90476190476193</v>
+        <v>671.81818181818187</v>
       </c>
       <c r="AC13" s="15">
-        <v>-73.904761904761926</v>
+        <v>-246.81818181818187</v>
       </c>
       <c r="AD13" s="19">
-        <v>15233</v>
+        <v>12282</v>
       </c>
       <c r="AE13" s="20">
-        <v>20716.88</v>
+        <v>16703.52</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2384,40 +2384,40 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>492.38095238095235</v>
+        <v>427.27272727272725</v>
       </c>
       <c r="I14" s="15">
-        <v>-223.8095238095238</v>
+        <v>-194.21487603305786</v>
       </c>
       <c r="J14" s="16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K14" s="13">
-        <v>0</v>
+        <v>36.57</v>
       </c>
       <c r="L14" s="14">
-        <v>0</v>
+        <v>2.2353413654618475</v>
       </c>
       <c r="M14" s="30">
-        <v>260.85714285714289</v>
+        <v>226.36363636363637</v>
       </c>
       <c r="N14" s="15">
-        <v>-118.5714285714286</v>
+        <v>-79.892561983471069</v>
       </c>
       <c r="O14" s="16">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="P14" s="17">
-        <v>139.92000000000002</v>
+        <v>127.2</v>
       </c>
       <c r="Q14" s="14">
-        <v>17.76923076923077</v>
+        <v>17.285714285714288</v>
       </c>
       <c r="R14" s="16">
-        <v>108.95238095238096</v>
+        <v>101.81818181818181</v>
       </c>
       <c r="S14" s="15">
-        <v>-11.047619047619051</v>
+        <v>-12.56198347107437</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2426,34 +2426,34 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>5.4444444444444438</v>
+        <v>6.2740740740740737</v>
       </c>
       <c r="W14" s="16">
-        <v>28.285714285714288</v>
+        <v>24.545454545454547</v>
       </c>
       <c r="X14" s="15">
-        <v>-13.571428571428573</v>
+        <v>-10.851239669421489</v>
       </c>
       <c r="Y14" s="18">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="17">
-        <v>20.67</v>
+        <v>11.13</v>
       </c>
       <c r="AA14" s="14">
-        <v>3.25</v>
+        <v>1.8822222222222225</v>
       </c>
       <c r="AB14" s="16">
-        <v>88</v>
+        <v>81.818181818181813</v>
       </c>
       <c r="AC14" s="15">
-        <v>-75</v>
+        <v>-74.818181818181813</v>
       </c>
       <c r="AD14" s="19">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="AE14" s="20">
-        <v>171.72</v>
+        <v>186.03</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2489,85 +2489,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2281</v>
+        <v>2426</v>
       </c>
       <c r="F15" s="14">
-        <v>4630.4299999999994</v>
+        <v>4924.78</v>
       </c>
       <c r="G15" s="14">
-        <v>6.7858053548661275</v>
+        <v>7.8372980910425838</v>
       </c>
       <c r="H15" s="30">
-        <v>7395.1428571428578</v>
+        <v>6810</v>
       </c>
       <c r="I15" s="15">
-        <v>-1080.4285714285716</v>
+        <v>-669.4545454545455</v>
       </c>
       <c r="J15" s="16">
-        <v>4133</v>
+        <v>3098</v>
       </c>
       <c r="K15" s="13">
-        <v>8389.99</v>
+        <v>6288.94</v>
       </c>
       <c r="L15" s="14">
-        <v>36.823504454815442</v>
+        <v>30.916123711340209</v>
       </c>
       <c r="M15" s="30">
-        <v>2469.2380952380954</v>
+        <v>2204.5454545454545</v>
       </c>
       <c r="N15" s="15">
-        <v>3010.6190476190477</v>
+        <v>2095.9338842975208</v>
       </c>
       <c r="O15" s="16">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="P15" s="17">
-        <v>332.91999999999996</v>
+        <v>265.92999999999995</v>
       </c>
       <c r="Q15" s="14">
-        <v>14.410041841004183</v>
+        <v>11.202120141342757</v>
       </c>
       <c r="R15" s="16">
-        <v>250.38095238095238</v>
+        <v>257.27272727272725</v>
       </c>
       <c r="S15" s="15">
-        <v>-63.61904761904762</v>
+        <v>-102.88429752066114</v>
       </c>
       <c r="T15" s="18">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="U15" s="17">
-        <v>253.74999999999997</v>
+        <v>156.30999999999997</v>
       </c>
       <c r="V15" s="14">
-        <v>7.6754385964912286</v>
+        <v>4.790231362467865</v>
       </c>
       <c r="W15" s="16">
-        <v>358.28571428571428</v>
+        <v>353.63636363636368</v>
       </c>
       <c r="X15" s="15">
-        <v>-135.57142857142856</v>
+        <v>-180.19008264462815</v>
       </c>
       <c r="Y15" s="18">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="Z15" s="17">
-        <v>418.17999999999995</v>
+        <v>355.24999999999994</v>
       </c>
       <c r="AA15" s="14">
-        <v>22.414507772020727</v>
+        <v>19.697674418604652</v>
       </c>
       <c r="AB15" s="16">
-        <v>202.19047619047618</v>
+        <v>195.45454545454547</v>
       </c>
       <c r="AC15" s="15">
-        <v>3.8095238095238244</v>
+        <v>-20.454545454545439</v>
       </c>
       <c r="AD15" s="19">
-        <v>6909</v>
+        <v>5907</v>
       </c>
       <c r="AE15" s="20">
-        <v>14025.269999999999</v>
+        <v>11991.21</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2602,85 +2602,85 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="F16" s="14">
-        <v>635.36</v>
+        <v>1007.1899999999999</v>
       </c>
       <c r="G16" s="14">
-        <v>2.3677130044843051</v>
+        <v>3.9484210526315784</v>
       </c>
       <c r="H16" s="30">
-        <v>1635.3333333333333</v>
+        <v>1554.5454545454547</v>
       </c>
       <c r="I16" s="15">
-        <v>-567.33333333333326</v>
+        <v>-427.61157024793397</v>
       </c>
       <c r="J16" s="16">
-        <v>694</v>
+        <v>489</v>
       </c>
       <c r="K16" s="13">
-        <v>2505.3399999999997</v>
+        <v>1765.29</v>
       </c>
       <c r="L16" s="14">
-        <v>26.741284403669724</v>
+        <v>21.399276672694395</v>
       </c>
       <c r="M16" s="30">
-        <v>570.95238095238096</v>
+        <v>502.72727272727275</v>
       </c>
       <c r="N16" s="15">
-        <v>434.47619047619048</v>
+        <v>260.48760330578511</v>
       </c>
       <c r="O16" s="16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P16" s="17">
-        <v>129.96</v>
+        <v>122.74</v>
       </c>
       <c r="Q16" s="14">
-        <v>14.538461538461538</v>
+        <v>15.237037037037036</v>
       </c>
       <c r="R16" s="16">
-        <v>54.476190476190482</v>
+        <v>49.090909090909093</v>
       </c>
       <c r="S16" s="15">
-        <v>-13.523809523809526</v>
+        <v>-10.628099173553721</v>
       </c>
       <c r="T16" s="18">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="U16" s="17">
-        <v>140.79</v>
+        <v>111.91</v>
       </c>
       <c r="V16" s="14">
-        <v>39</v>
+        <v>27.785185185185185</v>
       </c>
       <c r="W16" s="16">
-        <v>22</v>
+        <v>24.545454545454547</v>
       </c>
       <c r="X16" s="15">
-        <v>23</v>
+        <v>13.148760330578511</v>
       </c>
       <c r="Y16" s="18">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="Z16" s="17">
-        <v>274.36</v>
+        <v>234.65</v>
       </c>
       <c r="AA16" s="14">
-        <v>24.553846153846152</v>
+        <v>22.154929577464788</v>
       </c>
       <c r="AB16" s="16">
-        <v>68.095238095238102</v>
+        <v>64.545454545454547</v>
       </c>
       <c r="AC16" s="15">
-        <v>7.904761904761898</v>
+        <v>0.45454545454545325</v>
       </c>
       <c r="AD16" s="19">
-        <v>1021</v>
+        <v>898</v>
       </c>
       <c r="AE16" s="20">
-        <v>3685.81</v>
+        <v>3241.7799999999997</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2715,49 +2715,49 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F17" s="14">
-        <v>307.29999999999995</v>
+        <v>324.85999999999996</v>
       </c>
       <c r="G17" s="14">
-        <v>3.0625</v>
+        <v>3.4571428571428573</v>
       </c>
       <c r="H17" s="30">
-        <v>251.42857142857144</v>
+        <v>235.45454545454547</v>
       </c>
       <c r="I17" s="15">
-        <v>-79.285714285714292</v>
+        <v>-70.024793388429757</v>
       </c>
       <c r="J17" s="16">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="K17" s="13">
-        <v>605.81999999999994</v>
+        <v>342.41999999999996</v>
       </c>
       <c r="L17" s="14">
-        <v>36.224999999999994</v>
+        <v>20.080851063829787</v>
       </c>
       <c r="M17" s="30">
-        <v>41.904761904761905</v>
+        <v>42.727272727272727</v>
       </c>
       <c r="N17" s="15">
-        <v>49.952380952380949</v>
+        <v>19.578512396694215</v>
       </c>
       <c r="O17" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P17" s="17">
-        <v>105.35999999999999</v>
+        <v>70.239999999999995</v>
       </c>
       <c r="Q17" s="14">
-        <v>22.909090909090907</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="R17" s="16">
-        <v>11.523809523809524</v>
+        <v>10</v>
       </c>
       <c r="S17" s="15">
-        <v>1.5238095238095237</v>
+        <v>-1.0909090909090899</v>
       </c>
       <c r="T17" s="18">
         <v>16</v>
@@ -2781,19 +2781,19 @@
         <v>52.679999999999993</v>
       </c>
       <c r="AA17" s="14">
-        <v>13.999999999999998</v>
+        <v>16.133333333333333</v>
       </c>
       <c r="AB17" s="16">
-        <v>9.4285714285714288</v>
+        <v>8.1818181818181817</v>
       </c>
       <c r="AC17" s="15">
-        <v>-3.4285714285714288</v>
+        <v>-2.1818181818181817</v>
       </c>
       <c r="AD17" s="19">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="AE17" s="20">
-        <v>1211.6399999999999</v>
+        <v>930.68</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2828,85 +2828,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>7919</v>
+        <v>6166</v>
       </c>
       <c r="F18" s="14">
-        <v>4988.97</v>
+        <v>3884.58</v>
       </c>
       <c r="G18" s="14">
-        <v>9.7347655564011006</v>
+        <v>8.2742153709659529</v>
       </c>
       <c r="H18" s="30">
-        <v>17896.476190476191</v>
+        <v>16394.545454545456</v>
       </c>
       <c r="I18" s="15">
-        <v>-215.76190476190459</v>
+        <v>-1286.0661157024806</v>
       </c>
       <c r="J18" s="16">
-        <v>11566</v>
+        <v>10858</v>
       </c>
       <c r="K18" s="13">
-        <v>7286.58</v>
+        <v>6840.54</v>
       </c>
       <c r="L18" s="14">
-        <v>34.30593220338983</v>
+        <v>35.194695954995979</v>
       </c>
       <c r="M18" s="30">
-        <v>7417.1428571428578</v>
+        <v>6787.2727272727279</v>
       </c>
       <c r="N18" s="15">
-        <v>8194.5714285714275</v>
+        <v>7772.8760330578516</v>
       </c>
       <c r="O18" s="16">
-        <v>968</v>
+        <v>834</v>
       </c>
       <c r="P18" s="17">
-        <v>609.84</v>
+        <v>525.41999999999996</v>
       </c>
       <c r="Q18" s="14">
-        <v>16.827814569536422</v>
+        <v>15.561141094834234</v>
       </c>
       <c r="R18" s="16">
-        <v>1265.5238095238096</v>
+        <v>1179.090909090909</v>
       </c>
       <c r="S18" s="15">
-        <v>-182.4761904761906</v>
+        <v>-237.90082644628092</v>
       </c>
       <c r="T18" s="18">
-        <v>1623</v>
+        <v>1187</v>
       </c>
       <c r="U18" s="17">
-        <v>1022.49</v>
+        <v>747.81000000000006</v>
       </c>
       <c r="V18" s="14">
-        <v>10.275248718721736</v>
+        <v>7.6846976993044409</v>
       </c>
       <c r="W18" s="16">
-        <v>3474.9523809523812</v>
+        <v>3398.181818181818</v>
       </c>
       <c r="X18" s="15">
-        <v>-904.23809523809541</v>
+        <v>-1284.404958677686</v>
       </c>
       <c r="Y18" s="18">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="Z18" s="17">
-        <v>161.91</v>
+        <v>105.21</v>
       </c>
       <c r="AA18" s="14">
-        <v>14.786301369863015</v>
+        <v>9.8330900243309003</v>
       </c>
       <c r="AB18" s="16">
-        <v>382.38095238095235</v>
+        <v>373.63636363636368</v>
       </c>
       <c r="AC18" s="15">
-        <v>-125.38095238095235</v>
+        <v>-206.63636363636363</v>
       </c>
       <c r="AD18" s="19">
-        <v>22333</v>
+        <v>19212</v>
       </c>
       <c r="AE18" s="20">
-        <v>14069.79</v>
+        <v>12103.56</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2941,34 +2941,34 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>155</v>
+        <v>339</v>
       </c>
       <c r="F19" s="14">
-        <v>97.65</v>
+        <v>213.57</v>
       </c>
       <c r="G19" s="14">
-        <v>2.4022140221402215</v>
+        <v>5.753015427769987</v>
       </c>
       <c r="H19" s="30">
-        <v>1419.5238095238094</v>
+        <v>1296.3636363636363</v>
       </c>
       <c r="I19" s="15">
-        <v>-490.23809523809518</v>
+        <v>-250.25619834710733</v>
       </c>
       <c r="J19" s="16">
-        <v>1550</v>
+        <v>1160</v>
       </c>
       <c r="K19" s="13">
-        <v>976.5</v>
+        <v>730.8</v>
       </c>
       <c r="L19" s="14">
-        <v>28.157439446366784</v>
+        <v>23.709459459459456</v>
       </c>
       <c r="M19" s="30">
-        <v>1211.047619047619</v>
+        <v>1076.3636363636365</v>
       </c>
       <c r="N19" s="15">
-        <v>999.52380952380952</v>
+        <v>670.74380165289244</v>
       </c>
       <c r="O19" s="16">
         <v>117</v>
@@ -2977,49 +2977,49 @@
         <v>73.709999999999994</v>
       </c>
       <c r="Q19" s="14">
-        <v>25.071428571428569</v>
+        <v>28.033663366336633</v>
       </c>
       <c r="R19" s="16">
-        <v>102.66666666666667</v>
+        <v>91.818181818181813</v>
       </c>
       <c r="S19" s="15">
-        <v>23.666666666666657</v>
+        <v>33.528925619834709</v>
       </c>
       <c r="T19" s="18">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="U19" s="17">
-        <v>88.83</v>
+        <v>26.46</v>
       </c>
       <c r="V19" s="14">
-        <v>10.462897526501767</v>
+        <v>2.6607329842931939</v>
       </c>
       <c r="W19" s="16">
-        <v>296.47619047619048</v>
+        <v>347.27272727272725</v>
       </c>
       <c r="X19" s="15">
-        <v>-74.61904761904762</v>
+        <v>-210.56198347107437</v>
       </c>
       <c r="Y19" s="18">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="Z19" s="17">
-        <v>143.01</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="AA19" s="14">
-        <v>23.835000000000001</v>
+        <v>23.524651162790697</v>
       </c>
       <c r="AB19" s="16">
-        <v>209.52380952380952</v>
+        <v>195.45454545454547</v>
       </c>
       <c r="AC19" s="15">
-        <v>17.476190476190482</v>
+        <v>13.545454545454561</v>
       </c>
       <c r="AD19" s="19">
-        <v>2190</v>
+        <v>1867</v>
       </c>
       <c r="AE19" s="20">
-        <v>1379.7</v>
+        <v>1176.21</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3054,85 +3054,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="F20" s="14">
-        <v>799.47</v>
+        <v>797.58</v>
       </c>
       <c r="G20" s="14">
-        <v>9.403316866619619</v>
+        <v>9.9893055102706239</v>
       </c>
       <c r="H20" s="30">
-        <v>2968.9523809523812</v>
+        <v>2788.181818181818</v>
       </c>
       <c r="I20" s="15">
-        <v>-80.523809523809632</v>
+        <v>-1.3553719008264125</v>
       </c>
       <c r="J20" s="16">
-        <v>2914</v>
+        <v>2334</v>
       </c>
       <c r="K20" s="13">
-        <v>1835.82</v>
+        <v>1470.42</v>
       </c>
       <c r="L20" s="14">
-        <v>22.816554809843399</v>
+        <v>20.100640569395019</v>
       </c>
       <c r="M20" s="30">
-        <v>2809.7142857142858</v>
+        <v>2554.5454545454545</v>
       </c>
       <c r="N20" s="15">
-        <v>1636.8571428571427</v>
+        <v>1172.8429752066118</v>
       </c>
       <c r="O20" s="16">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="P20" s="17">
-        <v>127.26</v>
+        <v>124.11</v>
       </c>
       <c r="Q20" s="14">
-        <v>21.753846153846151</v>
+        <v>23.484729064039414</v>
       </c>
       <c r="R20" s="16">
-        <v>204.28571428571431</v>
+        <v>184.54545454545453</v>
       </c>
       <c r="S20" s="15">
-        <v>16.285714285714278</v>
+        <v>29.2314049586777</v>
       </c>
       <c r="T20" s="18">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="U20" s="17">
-        <v>207.9</v>
+        <v>86.31</v>
       </c>
       <c r="V20" s="14">
-        <v>10.5</v>
+        <v>3.87766081871345</v>
       </c>
       <c r="W20" s="16">
-        <v>691.42857142857144</v>
+        <v>777.27272727272737</v>
       </c>
       <c r="X20" s="15">
-        <v>-172.85714285714289</v>
+        <v>-428.28925619834718</v>
       </c>
       <c r="Y20" s="18">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="Z20" s="17">
-        <v>140.49</v>
+        <v>110.88</v>
       </c>
       <c r="AA20" s="14">
-        <v>14.06306306306306</v>
+        <v>12.134472934472933</v>
       </c>
       <c r="AB20" s="16">
-        <v>348.85714285714289</v>
+        <v>319.09090909090912</v>
       </c>
       <c r="AC20" s="15">
-        <v>-125.85714285714289</v>
+        <v>-143.09090909090912</v>
       </c>
       <c r="AD20" s="19">
-        <v>4938</v>
+        <v>4110</v>
       </c>
       <c r="AE20" s="20">
-        <v>3110.94</v>
+        <v>2589.3000000000002</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3167,85 +3167,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2760</v>
+        <v>1943</v>
       </c>
       <c r="F21" s="14">
-        <v>3008.4</v>
+        <v>2117.8700000000003</v>
       </c>
       <c r="G21" s="14">
-        <v>9.191246431969553</v>
+        <v>6.7811652725699441</v>
       </c>
       <c r="H21" s="30">
-        <v>6606.2857142857138</v>
+        <v>6303.636363636364</v>
       </c>
       <c r="I21" s="15">
-        <v>-242.85714285714266</v>
+        <v>-922.28925619834763</v>
       </c>
       <c r="J21" s="16">
-        <v>3406</v>
+        <v>5316</v>
       </c>
       <c r="K21" s="13">
-        <v>3712.5400000000004</v>
+        <v>5794.4400000000005</v>
       </c>
       <c r="L21" s="14">
-        <v>9.8738266151297616</v>
+        <v>16.896138691883376</v>
       </c>
       <c r="M21" s="30">
-        <v>7588.9523809523816</v>
+        <v>6921.8181818181811</v>
       </c>
       <c r="N21" s="15">
-        <v>-43.523809523809632</v>
+        <v>2169.7190082644634</v>
       </c>
       <c r="O21" s="16">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="P21" s="17">
-        <v>483.96000000000004</v>
+        <v>443.63000000000005</v>
       </c>
       <c r="Q21" s="14">
-        <v>16.243902439024392</v>
+        <v>15.413771517996867</v>
       </c>
       <c r="R21" s="16">
-        <v>601.33333333333326</v>
+        <v>580.90909090909099</v>
       </c>
       <c r="S21" s="15">
-        <v>-102.66666666666652</v>
+        <v>-121.09917355371908</v>
       </c>
       <c r="T21" s="18">
-        <v>688</v>
+        <v>390</v>
       </c>
       <c r="U21" s="17">
-        <v>749.92000000000007</v>
+        <v>425.1</v>
       </c>
       <c r="V21" s="14">
-        <v>8</v>
+        <v>4.4985700667302195</v>
       </c>
       <c r="W21" s="16">
-        <v>1892</v>
+        <v>1907.2727272727273</v>
       </c>
       <c r="X21" s="15">
-        <v>-688</v>
+        <v>-997.10743801652893</v>
       </c>
       <c r="Y21" s="18">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="Z21" s="17">
-        <v>320.46000000000004</v>
+        <v>248.52</v>
       </c>
       <c r="AA21" s="14">
-        <v>13.84304932735426</v>
+        <v>11.518997912317328</v>
       </c>
       <c r="AB21" s="16">
-        <v>467.23809523809524</v>
+        <v>435.4545454545455</v>
       </c>
       <c r="AC21" s="15">
-        <v>-173.23809523809524</v>
+        <v>-207.4545454545455</v>
       </c>
       <c r="AD21" s="19">
-        <v>7592</v>
+        <v>8284</v>
       </c>
       <c r="AE21" s="20">
-        <v>8275.2800000000007</v>
+        <v>9029.5600000000013</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3280,85 +3280,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1824</v>
+        <v>1256</v>
       </c>
       <c r="F22" s="14">
-        <v>1988.16</v>
+        <v>1369.0400000000002</v>
       </c>
       <c r="G22" s="14">
-        <v>9.7416073245167851</v>
+        <v>6.9379593700068485</v>
       </c>
       <c r="H22" s="30">
-        <v>4119.2380952380954</v>
+        <v>3982.7272727272725</v>
       </c>
       <c r="I22" s="15">
-        <v>-48.380952380952294</v>
+        <v>-554.33057851239641</v>
       </c>
       <c r="J22" s="16">
-        <v>1502</v>
+        <v>3721</v>
       </c>
       <c r="K22" s="13">
-        <v>1637.18</v>
+        <v>4055.8900000000003</v>
       </c>
       <c r="L22" s="14">
-        <v>9.7713754646840147</v>
+        <v>26.856009543692217</v>
       </c>
       <c r="M22" s="30">
-        <v>3381.7142857142858</v>
+        <v>3048.181818181818</v>
       </c>
       <c r="N22" s="15">
-        <v>-35.142857142857338</v>
+        <v>2335.4628099173551</v>
       </c>
       <c r="O22" s="16">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="P22" s="17">
-        <v>113.36000000000001</v>
+        <v>94.830000000000013</v>
       </c>
       <c r="Q22" s="14">
-        <v>14.463576158940397</v>
+        <v>12.030857142857142</v>
       </c>
       <c r="R22" s="16">
-        <v>158.1904761904762</v>
+        <v>159.09090909090909</v>
       </c>
       <c r="S22" s="15">
-        <v>-39.809523809523824</v>
+        <v>-57.628099173553721</v>
       </c>
       <c r="T22" s="18">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="U22" s="17">
-        <v>276.86</v>
+        <v>192.93</v>
       </c>
       <c r="V22" s="14">
-        <v>9.8961038961038934</v>
+        <v>6.9876019575856443</v>
       </c>
       <c r="W22" s="16">
-        <v>564.66666666666674</v>
+        <v>557.27272727272725</v>
       </c>
       <c r="X22" s="15">
-        <v>-156.66666666666674</v>
+        <v>-228.28925619834712</v>
       </c>
       <c r="Y22" s="18">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Z22" s="17">
-        <v>22.89</v>
+        <v>7.6300000000000008</v>
       </c>
       <c r="AA22" s="14">
-        <v>2.4915254237288136</v>
+        <v>0.93076923076923068</v>
       </c>
       <c r="AB22" s="16">
-        <v>185.42857142857144</v>
+        <v>165.45454545454547</v>
       </c>
       <c r="AC22" s="15">
-        <v>-164.42857142857144</v>
+        <v>-158.45454545454547</v>
       </c>
       <c r="AD22" s="19">
-        <v>3705</v>
+        <v>5248</v>
       </c>
       <c r="AE22" s="20">
-        <v>4038.4500000000003</v>
+        <v>5720.3200000000006</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3393,85 +3393,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>21755</v>
+        <v>18126</v>
       </c>
       <c r="F23" s="14">
-        <v>25235.8</v>
+        <v>21026.16</v>
       </c>
       <c r="G23" s="14">
-        <v>13.444029191925138</v>
+        <v>12.087996031746032</v>
       </c>
       <c r="H23" s="30">
-        <v>35600.190476190473</v>
+        <v>32989.090909090912</v>
       </c>
       <c r="I23" s="15">
-        <v>-2517.8571428571413</v>
+        <v>-4366.5619834710742</v>
       </c>
       <c r="J23" s="16">
-        <v>14701</v>
+        <v>19463</v>
       </c>
       <c r="K23" s="13">
-        <v>17053.16</v>
+        <v>22577.079999999998</v>
       </c>
       <c r="L23" s="14">
-        <v>15.110420439528168</v>
+        <v>22.186848179377265</v>
       </c>
       <c r="M23" s="30">
-        <v>21403.904761904763</v>
+        <v>19299.090909090912</v>
       </c>
       <c r="N23" s="15">
-        <v>4971.9523809523816</v>
+        <v>10690.685950413223</v>
       </c>
       <c r="O23" s="16">
-        <v>2315</v>
+        <v>1945</v>
       </c>
       <c r="P23" s="17">
-        <v>2685.3999999999996</v>
+        <v>2256.1999999999998</v>
       </c>
       <c r="Q23" s="14">
-        <v>15.526988182689236</v>
+        <v>13.851971748087108</v>
       </c>
       <c r="R23" s="16">
-        <v>3280.0952380952381</v>
+        <v>3089.0909090909095</v>
       </c>
       <c r="S23" s="15">
-        <v>-666.90476190476193</v>
+        <v>-863.26446280991786</v>
       </c>
       <c r="T23" s="18">
-        <v>5600</v>
+        <v>3993</v>
       </c>
       <c r="U23" s="17">
-        <v>6496</v>
+        <v>4631.88</v>
       </c>
       <c r="V23" s="14">
-        <v>10.059019758788812</v>
+        <v>7.3713174155160566</v>
       </c>
       <c r="W23" s="16">
-        <v>12247.714285714284</v>
+        <v>11917.272727272728</v>
       </c>
       <c r="X23" s="15">
-        <v>-3307.4285714285706</v>
+        <v>-4674.1074380165301</v>
       </c>
       <c r="Y23" s="18">
-        <v>1156</v>
+        <v>835</v>
       </c>
       <c r="Z23" s="17">
-        <v>1340.9599999999998</v>
+        <v>968.59999999999991</v>
       </c>
       <c r="AA23" s="14">
-        <v>23.409836065573771</v>
+        <v>15.973913043478261</v>
       </c>
       <c r="AB23" s="16">
-        <v>1086.3809523809523</v>
+        <v>1150</v>
       </c>
       <c r="AC23" s="15">
-        <v>69.619047619047706</v>
+        <v>-315</v>
       </c>
       <c r="AD23" s="19">
-        <v>45527</v>
+        <v>44362</v>
       </c>
       <c r="AE23" s="20">
-        <v>52811.32</v>
+        <v>51459.92</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3506,85 +3506,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>9245</v>
+        <v>8567</v>
       </c>
       <c r="F24" s="14">
-        <v>10724.199999999999</v>
+        <v>9937.7199999999993</v>
       </c>
       <c r="G24" s="14">
-        <v>8.4650098103335516</v>
+        <v>8.4448635437881858</v>
       </c>
       <c r="H24" s="30">
-        <v>24027.142857142855</v>
+        <v>22318.18181818182</v>
       </c>
       <c r="I24" s="15">
-        <v>-1676.4285714285706</v>
+        <v>-1577.6280991735548</v>
       </c>
       <c r="J24" s="16">
-        <v>12059</v>
+        <v>9486</v>
       </c>
       <c r="K24" s="13">
-        <v>13988.439999999999</v>
+        <v>11003.759999999998</v>
       </c>
       <c r="L24" s="14">
-        <v>20.412622924391421</v>
+        <v>17.744546649145864</v>
       </c>
       <c r="M24" s="30">
-        <v>12996.761904761906</v>
+        <v>11760.90909090909</v>
       </c>
       <c r="N24" s="15">
-        <v>6151.3809523809523</v>
+        <v>4140.1322314049594</v>
       </c>
       <c r="O24" s="16">
-        <v>1352</v>
+        <v>1156</v>
       </c>
       <c r="P24" s="17">
-        <v>1568.32</v>
+        <v>1340.9599999999998</v>
       </c>
       <c r="Q24" s="14">
-        <v>15.557260273972604</v>
+        <v>14.229501525940996</v>
       </c>
       <c r="R24" s="16">
-        <v>1911.9047619047617</v>
+        <v>1787.2727272727273</v>
       </c>
       <c r="S24" s="15">
-        <v>-386.09523809523807</v>
+        <v>-468.79338842975221</v>
       </c>
       <c r="T24" s="18">
-        <v>3242</v>
+        <v>2456</v>
       </c>
       <c r="U24" s="17">
-        <v>3760.72</v>
+        <v>2848.9599999999996</v>
       </c>
       <c r="V24" s="14">
-        <v>10.968583856935718</v>
+        <v>8.6100535998841092</v>
       </c>
       <c r="W24" s="16">
-        <v>6502.5714285714284</v>
+        <v>6275.454545454545</v>
       </c>
       <c r="X24" s="15">
-        <v>-1487.1428571428569</v>
+        <v>-2107.9669421487597</v>
       </c>
       <c r="Y24" s="18">
-        <v>643</v>
+        <v>496</v>
       </c>
       <c r="Z24" s="17">
-        <v>745.88</v>
+        <v>575.36</v>
       </c>
       <c r="AA24" s="14">
-        <v>15.867215041128084</v>
+        <v>12.769361702127659</v>
       </c>
       <c r="AB24" s="16">
-        <v>891.52380952380952</v>
+        <v>854.5454545454545</v>
       </c>
       <c r="AC24" s="15">
-        <v>-248.52380952380952</v>
+        <v>-358.5454545454545</v>
       </c>
       <c r="AD24" s="19">
-        <v>26541</v>
+        <v>22161</v>
       </c>
       <c r="AE24" s="20">
-        <v>30787.559999999998</v>
+        <v>25706.76</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3619,85 +3619,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>9854</v>
+        <v>14761</v>
       </c>
       <c r="F25" s="14">
-        <v>11430.64</v>
+        <v>17122.759999999998</v>
       </c>
       <c r="G25" s="14">
-        <v>9.3652244750181026</v>
+        <v>15.048919408518346</v>
       </c>
       <c r="H25" s="30">
-        <v>23148.190476190473</v>
+        <v>21579.090909090912</v>
       </c>
       <c r="I25" s="15">
-        <v>-667.90476190476147</v>
+        <v>4952.3223140495866</v>
       </c>
       <c r="J25" s="16">
-        <v>13327</v>
+        <v>18518</v>
       </c>
       <c r="K25" s="13">
-        <v>15459.32</v>
+        <v>21480.879999999997</v>
       </c>
       <c r="L25" s="14">
-        <v>21.43917573157653</v>
+        <v>33.016694909010532</v>
       </c>
       <c r="M25" s="30">
-        <v>13675.619047619048</v>
+        <v>12339.09090909091</v>
       </c>
       <c r="N25" s="15">
-        <v>7110.8095238095239</v>
+        <v>12909.322314049587</v>
       </c>
       <c r="O25" s="16">
-        <v>1648</v>
+        <v>1454</v>
       </c>
       <c r="P25" s="17">
-        <v>1911.6799999999998</v>
+        <v>1686.6399999999999</v>
       </c>
       <c r="Q25" s="14">
-        <v>15.449999999999998</v>
+        <v>14.728673084972792</v>
       </c>
       <c r="R25" s="16">
-        <v>2346.666666666667</v>
+        <v>2171.818181818182</v>
       </c>
       <c r="S25" s="15">
-        <v>-485.33333333333394</v>
+        <v>-520.38016528925618</v>
       </c>
       <c r="T25" s="18">
-        <v>3238</v>
+        <v>2470</v>
       </c>
       <c r="U25" s="17">
-        <v>3756.08</v>
+        <v>2865.2</v>
       </c>
       <c r="V25" s="14">
-        <v>10.740483335965882</v>
+        <v>8.4023053134664032</v>
       </c>
       <c r="W25" s="16">
-        <v>6632.4761904761908</v>
+        <v>6467.2727272727279</v>
       </c>
       <c r="X25" s="15">
-        <v>-1585.6190476190477</v>
+        <v>-2233.4710743801661</v>
       </c>
       <c r="Y25" s="18">
-        <v>448</v>
+        <v>361</v>
       </c>
       <c r="Z25" s="17">
-        <v>519.67999999999995</v>
+        <v>418.76</v>
       </c>
       <c r="AA25" s="14">
-        <v>15.101123595505616</v>
+        <v>12.809677419354838</v>
       </c>
       <c r="AB25" s="16">
-        <v>652.66666666666674</v>
+        <v>620</v>
       </c>
       <c r="AC25" s="15">
-        <v>-204.66666666666674</v>
+        <v>-259</v>
       </c>
       <c r="AD25" s="19">
-        <v>28515</v>
+        <v>37564</v>
       </c>
       <c r="AE25" s="20">
-        <v>33077.399999999994</v>
+        <v>43574.239999999998</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3732,85 +3732,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>17668</v>
+        <v>2779</v>
       </c>
       <c r="F26" s="14">
-        <v>20494.879999999997</v>
+        <v>3223.64</v>
       </c>
       <c r="G26" s="14">
-        <v>12.960771299821847</v>
+        <v>2.2030989975758373</v>
       </c>
       <c r="H26" s="30">
-        <v>29990.190476190473</v>
+        <v>27750.909090909088</v>
       </c>
       <c r="I26" s="15">
-        <v>-2779.8571428571413</v>
+        <v>-16142.074380165286</v>
       </c>
       <c r="J26" s="16">
-        <v>11173</v>
+        <v>17740</v>
       </c>
       <c r="K26" s="13">
-        <v>12960.679999999998</v>
+        <v>20578.399999999998</v>
       </c>
       <c r="L26" s="14">
-        <v>15.212201763485478</v>
+        <v>26.774853436447547</v>
       </c>
       <c r="M26" s="30">
-        <v>16158.476190476191</v>
+        <v>14576.363636363638</v>
       </c>
       <c r="N26" s="15">
-        <v>3828.2380952380954</v>
+        <v>11114.380165289256</v>
       </c>
       <c r="O26" s="16">
-        <v>1283</v>
+        <v>1088</v>
       </c>
       <c r="P26" s="17">
-        <v>1488.28</v>
+        <v>1262.08</v>
       </c>
       <c r="Q26" s="14">
-        <v>15.068791946308725</v>
+        <v>13.677714285714286</v>
       </c>
       <c r="R26" s="16">
-        <v>1873.1428571428571</v>
+        <v>1750</v>
       </c>
       <c r="S26" s="15">
-        <v>-419.85714285714266</v>
+        <v>-502.90909090909099</v>
       </c>
       <c r="T26" s="18">
-        <v>3754</v>
+        <v>2697</v>
       </c>
       <c r="U26" s="17">
-        <v>4354.6399999999994</v>
+        <v>3128.52</v>
       </c>
       <c r="V26" s="14">
-        <v>9.878947368421052</v>
+        <v>7.3940636682904719</v>
       </c>
       <c r="W26" s="16">
-        <v>8360</v>
+        <v>8024.545454545455</v>
       </c>
       <c r="X26" s="15">
-        <v>-2326</v>
+        <v>-3139.0330578512403</v>
       </c>
       <c r="Y26" s="18">
-        <v>770</v>
+        <v>585</v>
       </c>
       <c r="Z26" s="17">
-        <v>893.19999999999993</v>
+        <v>678.59999999999991</v>
       </c>
       <c r="AA26" s="14">
-        <v>17.021052631578947</v>
+        <v>13.368271954674221</v>
       </c>
       <c r="AB26" s="16">
-        <v>995.2380952380953</v>
+        <v>962.72727272727263</v>
       </c>
       <c r="AC26" s="15">
-        <v>-225.2380952380953</v>
+        <v>-377.72727272727275</v>
       </c>
       <c r="AD26" s="19">
-        <v>34648</v>
+        <v>24889</v>
       </c>
       <c r="AE26" s="20">
-        <v>40191.68</v>
+        <v>28871.239999999998</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3845,85 +3845,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>3660</v>
+        <v>2779</v>
       </c>
       <c r="F27" s="14">
-        <v>4245.5999999999995</v>
+        <v>3223.64</v>
       </c>
       <c r="G27" s="14">
-        <v>10.296048225050233</v>
+        <v>8.4254322225006266</v>
       </c>
       <c r="H27" s="30">
-        <v>7820.4761904761908</v>
+        <v>7256.363636363636</v>
       </c>
       <c r="I27" s="15">
-        <v>105.23809523809541</v>
+        <v>-519.34710743801634</v>
       </c>
       <c r="J27" s="16">
-        <v>5726</v>
+        <v>5418</v>
       </c>
       <c r="K27" s="13">
-        <v>6642.16</v>
+        <v>6284.8799999999992</v>
       </c>
       <c r="L27" s="14">
-        <v>29.941733067729082</v>
+        <v>30.981947069943285</v>
       </c>
       <c r="M27" s="30">
-        <v>4207.2380952380954</v>
+        <v>3847.2727272727275</v>
       </c>
       <c r="N27" s="15">
-        <v>3813.6190476190477</v>
+        <v>3669.2396694214876</v>
       </c>
       <c r="O27" s="16">
-        <v>536</v>
+        <v>501</v>
       </c>
       <c r="P27" s="17">
-        <v>621.76</v>
+        <v>581.16</v>
       </c>
       <c r="Q27" s="14">
-        <v>18.885906040268459</v>
+        <v>18.914508580343213</v>
       </c>
       <c r="R27" s="16">
-        <v>624.38095238095229</v>
+        <v>582.72727272727275</v>
       </c>
       <c r="S27" s="15">
-        <v>-31.619047619047478</v>
+        <v>-28.752066115702519</v>
       </c>
       <c r="T27" s="18">
-        <v>1397</v>
+        <v>947</v>
       </c>
       <c r="U27" s="17">
-        <v>1620.52</v>
+        <v>1098.52</v>
       </c>
       <c r="V27" s="14">
-        <v>11.66945107398568</v>
+        <v>7.9491501907735014</v>
       </c>
       <c r="W27" s="16">
-        <v>2633.7142857142858</v>
+        <v>2620.9090909090905</v>
       </c>
       <c r="X27" s="15">
-        <v>-518.42857142857156</v>
+        <v>-959.11570247933855</v>
       </c>
       <c r="Y27" s="18">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="Z27" s="17">
-        <v>349.15999999999997</v>
+        <v>310.88</v>
       </c>
       <c r="AA27" s="14">
-        <v>22.101398601398603</v>
+        <v>21.910810810810808</v>
       </c>
       <c r="AB27" s="16">
-        <v>299.61904761904759</v>
+        <v>269.09090909090912</v>
       </c>
       <c r="AC27" s="15">
-        <v>1.380952380952408</v>
+        <v>-1.0909090909091219</v>
       </c>
       <c r="AD27" s="19">
-        <v>11620</v>
+        <v>9913</v>
       </c>
       <c r="AE27" s="20">
-        <v>13479.199999999999</v>
+        <v>11499.08</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3958,85 +3958,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>3186</v>
+        <v>2654</v>
       </c>
       <c r="F28" s="14">
-        <v>3695.7599999999998</v>
+        <v>3078.64</v>
       </c>
       <c r="G28" s="14">
-        <v>8.7976331360946745</v>
+        <v>7.7400337430706196</v>
       </c>
       <c r="H28" s="30">
-        <v>7967.1428571428578</v>
+        <v>7543.636363636364</v>
       </c>
       <c r="I28" s="15">
-        <v>-435.42857142857156</v>
+        <v>-774.92561983471069</v>
       </c>
       <c r="J28" s="16">
-        <v>7882</v>
+        <v>9182</v>
       </c>
       <c r="K28" s="13">
-        <v>9143.119999999999</v>
+        <v>10651.119999999999</v>
       </c>
       <c r="L28" s="14">
-        <v>28.318562874251498</v>
+        <v>36.207332572918368</v>
       </c>
       <c r="M28" s="30">
-        <v>6123.333333333333</v>
+        <v>5579.090909090909</v>
       </c>
       <c r="N28" s="15">
-        <v>5098.666666666667</v>
+        <v>6646.0495867768595</v>
       </c>
       <c r="O28" s="16">
-        <v>643</v>
+        <v>598</v>
       </c>
       <c r="P28" s="17">
-        <v>745.88</v>
+        <v>693.68</v>
       </c>
       <c r="Q28" s="14">
-        <v>15.701162790697676</v>
+        <v>15.798689956331881</v>
       </c>
       <c r="R28" s="16">
-        <v>900.95238095238085</v>
+        <v>832.72727272727263</v>
       </c>
       <c r="S28" s="15">
-        <v>-176.04761904761904</v>
+        <v>-159.02479338842966</v>
       </c>
       <c r="T28" s="18">
-        <v>749</v>
+        <v>316</v>
       </c>
       <c r="U28" s="17">
-        <v>868.83999999999992</v>
+        <v>366.56</v>
       </c>
       <c r="V28" s="14">
-        <v>5.1167859466493173</v>
+        <v>2.2301545640128313</v>
       </c>
       <c r="W28" s="16">
-        <v>3220.3809523809523</v>
+        <v>3117.2727272727275</v>
       </c>
       <c r="X28" s="15">
-        <v>-1593.0952380952381</v>
+        <v>-1951.1074380165292</v>
       </c>
       <c r="Y28" s="18">
-        <v>367</v>
+        <v>307</v>
       </c>
       <c r="Z28" s="17">
-        <v>425.71999999999997</v>
+        <v>356.11999999999995</v>
       </c>
       <c r="AA28" s="14">
-        <v>19.560913705583754</v>
+        <v>17.399063231850114</v>
       </c>
       <c r="AB28" s="16">
-        <v>412.76190476190476</v>
+        <v>388.18181818181819</v>
       </c>
       <c r="AC28" s="15">
-        <v>-45.761904761904759</v>
+        <v>-81.181818181818244</v>
       </c>
       <c r="AD28" s="19">
-        <v>12827</v>
+        <v>13057</v>
       </c>
       <c r="AE28" s="20">
-        <v>14879.32</v>
+        <v>15146.119999999999</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4071,85 +4071,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>1045</v>
+        <v>550</v>
       </c>
       <c r="F29" s="14">
-        <v>1212.1999999999998</v>
+        <v>638</v>
       </c>
       <c r="G29" s="14">
-        <v>2.6979345955249574</v>
+        <v>1.5164634841061868</v>
       </c>
       <c r="H29" s="30">
-        <v>8521.3333333333321</v>
+        <v>7979.090909090909</v>
       </c>
       <c r="I29" s="15">
-        <v>-2828.3333333333326</v>
+        <v>-3076.859504132231</v>
       </c>
       <c r="J29" s="16">
-        <v>3904</v>
+        <v>2884</v>
       </c>
       <c r="K29" s="13">
-        <v>4528.6399999999994</v>
+        <v>3345.4399999999996</v>
       </c>
       <c r="L29" s="14">
-        <v>15.201928425737067</v>
+        <v>12.447440699126091</v>
       </c>
       <c r="M29" s="30">
-        <v>5649.8095238095239</v>
+        <v>5097.2727272727279</v>
       </c>
       <c r="N29" s="15">
-        <v>1335.9047619047619</v>
+        <v>567.05785123966916</v>
       </c>
       <c r="O29" s="16">
-        <v>659</v>
+        <v>617</v>
       </c>
       <c r="P29" s="17">
-        <v>764.43999999999994</v>
+        <v>715.71999999999991</v>
       </c>
       <c r="Q29" s="14">
-        <v>15.761958997722095</v>
+        <v>16.072551130247579</v>
       </c>
       <c r="R29" s="16">
-        <v>919.80952380952385</v>
+        <v>844.5454545454545</v>
       </c>
       <c r="S29" s="15">
-        <v>-177.19047619047615</v>
+        <v>-150.76859504132233</v>
       </c>
       <c r="T29" s="18">
-        <v>686</v>
+        <v>270</v>
       </c>
       <c r="U29" s="17">
-        <v>795.76</v>
+        <v>313.2</v>
       </c>
       <c r="V29" s="14">
-        <v>4.6833550065019507</v>
+        <v>1.9144447699970704</v>
       </c>
       <c r="W29" s="16">
-        <v>3222.4761904761908</v>
+        <v>3102.7272727272725</v>
       </c>
       <c r="X29" s="15">
-        <v>-1657.6190476190477</v>
+        <v>-1986.5289256198344</v>
       </c>
       <c r="Y29" s="18">
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="Z29" s="17">
-        <v>379.32</v>
+        <v>329.44</v>
       </c>
       <c r="AA29" s="14">
-        <v>18.263297872340424</v>
+        <v>17.532653061224494</v>
       </c>
       <c r="AB29" s="16">
-        <v>393.90476190476193</v>
+        <v>356.36363636363632</v>
       </c>
       <c r="AC29" s="15">
-        <v>-66.904761904761926</v>
+        <v>-72.363636363636317</v>
       </c>
       <c r="AD29" s="19">
-        <v>6621</v>
+        <v>4605</v>
       </c>
       <c r="AE29" s="20">
-        <v>7680.36</v>
+        <v>5341.7999999999993</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4184,85 +4184,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="F30" s="14">
-        <v>1898.88</v>
+        <v>1637.6000000000001</v>
       </c>
       <c r="G30" s="14">
-        <v>4.779885310983679</v>
+        <v>4.4117165096272029</v>
       </c>
       <c r="H30" s="30">
-        <v>2374.9523809523807</v>
+        <v>2219.090909090909</v>
       </c>
       <c r="I30" s="15">
-        <v>-563.5238095238094</v>
+        <v>-563.67768595041309</v>
       </c>
       <c r="J30" s="16">
-        <v>1466</v>
+        <v>1701</v>
       </c>
       <c r="K30" s="13">
-        <v>5394.88</v>
+        <v>6259.68</v>
       </c>
       <c r="L30" s="14">
-        <v>11.895672333848532</v>
+        <v>15.268620178041543</v>
       </c>
       <c r="M30" s="30">
-        <v>2711.2380952380954</v>
+        <v>2450.909090909091</v>
       </c>
       <c r="N30" s="15">
-        <v>233.61904761904771</v>
+        <v>586.95041322314046</v>
       </c>
       <c r="O30" s="16">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="P30" s="17">
-        <v>419.52000000000004</v>
+        <v>371.68</v>
       </c>
       <c r="Q30" s="14">
-        <v>19.152000000000001</v>
+        <v>18.105185185185185</v>
       </c>
       <c r="R30" s="16">
-        <v>130.95238095238096</v>
+        <v>122.72727272727273</v>
       </c>
       <c r="S30" s="15">
-        <v>-5.047619047619051</v>
+        <v>-10.570247933884303</v>
       </c>
       <c r="T30" s="18">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="U30" s="17">
-        <v>1173.92</v>
+        <v>736</v>
       </c>
       <c r="V30" s="14">
-        <v>11</v>
+        <v>6.7222222222222232</v>
       </c>
       <c r="W30" s="16">
-        <v>638</v>
+        <v>654.5454545454545</v>
       </c>
       <c r="X30" s="15">
-        <v>-145</v>
+        <v>-276.03305785123962</v>
       </c>
       <c r="Y30" s="18">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="Z30" s="17">
-        <v>371.68</v>
+        <v>224.48000000000002</v>
       </c>
       <c r="AA30" s="14">
-        <v>18.28448275862069</v>
+        <v>10.180689655172415</v>
       </c>
       <c r="AB30" s="16">
-        <v>121.52380952380952</v>
+        <v>131.81818181818181</v>
       </c>
       <c r="AC30" s="15">
-        <v>-20.523809523809518</v>
+        <v>-70.818181818181813</v>
       </c>
       <c r="AD30" s="19">
-        <v>2516</v>
+        <v>2508</v>
       </c>
       <c r="AE30" s="20">
-        <v>9258.880000000001</v>
+        <v>9229.44</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4297,85 +4297,85 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>557</v>
+        <v>414</v>
       </c>
       <c r="F31" s="14">
-        <v>2049.7600000000002</v>
+        <v>1523.52</v>
       </c>
       <c r="G31" s="14">
-        <v>10.731192660550459</v>
+        <v>8.205405405405406</v>
       </c>
       <c r="H31" s="30">
-        <v>1141.9047619047619</v>
+        <v>1110</v>
       </c>
       <c r="I31" s="15">
-        <v>37.952380952380963</v>
+        <v>-90.545454545454504</v>
       </c>
       <c r="J31" s="16">
-        <v>780</v>
+        <v>1357</v>
       </c>
       <c r="K31" s="13">
-        <v>2870.4</v>
+        <v>4993.76</v>
       </c>
       <c r="L31" s="14">
-        <v>10.949197860962567</v>
+        <v>20.930146590184833</v>
       </c>
       <c r="M31" s="30">
-        <v>1567.2380952380954</v>
+        <v>1426.3636363636363</v>
       </c>
       <c r="N31" s="15">
-        <v>67.619047619047592</v>
+        <v>708.65289256198344</v>
       </c>
       <c r="O31" s="16">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="P31" s="17">
-        <v>125.12</v>
+        <v>62.56</v>
       </c>
       <c r="Q31" s="14">
-        <v>39.666666666666664</v>
+        <v>12.856249999999999</v>
       </c>
       <c r="R31" s="16">
-        <v>18.857142857142858</v>
+        <v>29.090909090909093</v>
       </c>
       <c r="S31" s="15">
-        <v>16.857142857142854</v>
+        <v>-9.4462809917355379</v>
       </c>
       <c r="T31" s="18">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="U31" s="17">
-        <v>264.96000000000004</v>
+        <v>77.28</v>
       </c>
       <c r="V31" s="14">
-        <v>7.1320754716981138</v>
+        <v>1.932319391634981</v>
       </c>
       <c r="W31" s="16">
-        <v>222.09523809523807</v>
+        <v>239.09090909090909</v>
       </c>
       <c r="X31" s="15">
-        <v>-89.523809523809518</v>
+        <v>-152.88429752066116</v>
       </c>
       <c r="Y31" s="18">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z31" s="17">
-        <v>110.4</v>
+        <v>66.240000000000009</v>
       </c>
       <c r="AA31" s="14">
-        <v>23.333333333333332</v>
+        <v>12.100000000000001</v>
       </c>
       <c r="AB31" s="16">
-        <v>28.285714285714288</v>
+        <v>32.727272727272727</v>
       </c>
       <c r="AC31" s="15">
-        <v>1.7142857142857117</v>
+        <v>-14.727272727272727</v>
       </c>
       <c r="AD31" s="19">
-        <v>1473</v>
+        <v>1827</v>
       </c>
       <c r="AE31" s="20">
-        <v>5420.64</v>
+        <v>6723.3600000000006</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4410,85 +4410,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1572</v>
+        <v>1260</v>
       </c>
       <c r="F32" s="14">
-        <v>6523.8</v>
+        <v>5229</v>
       </c>
       <c r="G32" s="14">
-        <v>7.0089171974522309</v>
+        <v>5.9811690859160462</v>
       </c>
       <c r="H32" s="30">
-        <v>4934.2857142857138</v>
+        <v>4634.545454545454</v>
       </c>
       <c r="I32" s="15">
-        <v>-670.85714285714266</v>
+        <v>-846.61157024793374</v>
       </c>
       <c r="J32" s="16">
-        <v>2131</v>
+        <v>2751</v>
       </c>
       <c r="K32" s="13">
-        <v>8843.6500000000015</v>
+        <v>11416.650000000001</v>
       </c>
       <c r="L32" s="14">
-        <v>11.602540834845735</v>
+        <v>16.672727272727272</v>
       </c>
       <c r="M32" s="30">
-        <v>4040.6666666666665</v>
+        <v>3630</v>
       </c>
       <c r="N32" s="15">
-        <v>294.33333333333348</v>
+        <v>1101</v>
       </c>
       <c r="O32" s="16">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="P32" s="17">
-        <v>979.40000000000009</v>
+        <v>834.15000000000009</v>
       </c>
       <c r="Q32" s="14">
-        <v>17.148788927335641</v>
+        <v>15.248275862068965</v>
       </c>
       <c r="R32" s="16">
-        <v>302.76190476190476</v>
+        <v>290</v>
       </c>
       <c r="S32" s="15">
-        <v>-39.238095238095241</v>
+        <v>-62.636363636363626</v>
       </c>
       <c r="T32" s="18">
-        <v>877</v>
+        <v>605</v>
       </c>
       <c r="U32" s="17">
-        <v>3639.55</v>
+        <v>2510.75</v>
       </c>
       <c r="V32" s="14">
-        <v>10.169519602429597</v>
+        <v>7.3981808994441636</v>
       </c>
       <c r="W32" s="16">
-        <v>1897.2380952380954</v>
+        <v>1799.090909090909</v>
       </c>
       <c r="X32" s="15">
-        <v>-502.80952380952385</v>
+        <v>-703.42975206611573</v>
       </c>
       <c r="Y32" s="18">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="Z32" s="17">
-        <v>1070.7</v>
+        <v>1008.45</v>
       </c>
       <c r="AA32" s="14">
-        <v>55.285714285714285</v>
+        <v>59.4</v>
       </c>
       <c r="AB32" s="16">
-        <v>102.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="AC32" s="15">
-        <v>155.33333333333331</v>
+        <v>153</v>
       </c>
       <c r="AD32" s="19">
-        <v>5074</v>
+        <v>5060</v>
       </c>
       <c r="AE32" s="20">
-        <v>21057.100000000002</v>
+        <v>20999</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4523,85 +4523,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3270</v>
+        <v>3035</v>
       </c>
       <c r="F33" s="14">
-        <v>13570.500000000002</v>
+        <v>12595.250000000002</v>
       </c>
       <c r="G33" s="14">
-        <v>7.3775247099269441</v>
+        <v>7.2683819891143004</v>
       </c>
       <c r="H33" s="30">
-        <v>9751.2380952380954</v>
+        <v>9186.363636363636</v>
       </c>
       <c r="I33" s="15">
-        <v>-1162.3809523809523</v>
+        <v>-1140.6198347107438</v>
       </c>
       <c r="J33" s="16">
-        <v>3993</v>
+        <v>6256</v>
       </c>
       <c r="K33" s="13">
-        <v>16570.95</v>
+        <v>25962.400000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>14.311827956989248</v>
+        <v>24.921020576131689</v>
       </c>
       <c r="M33" s="30">
-        <v>6138</v>
+        <v>5522.7272727272721</v>
       </c>
       <c r="N33" s="15">
-        <v>1203</v>
+        <v>3745.6694214876034</v>
       </c>
       <c r="O33" s="16">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="P33" s="17">
-        <v>1394.4</v>
+        <v>1265.75</v>
       </c>
       <c r="Q33" s="14">
-        <v>17.596009975062344</v>
+        <v>17.125290023201856</v>
       </c>
       <c r="R33" s="16">
-        <v>420.09523809523807</v>
+        <v>391.81818181818181</v>
       </c>
       <c r="S33" s="15">
-        <v>-45.904761904761926</v>
+        <v>-51.198347107438053</v>
       </c>
       <c r="T33" s="18">
-        <v>984</v>
+        <v>611</v>
       </c>
       <c r="U33" s="17">
-        <v>4083.6000000000004</v>
+        <v>2535.65</v>
       </c>
       <c r="V33" s="14">
-        <v>9.0631578947368414</v>
+        <v>5.821338582677166</v>
       </c>
       <c r="W33" s="16">
-        <v>2388.5714285714284</v>
+        <v>2309.090909090909</v>
       </c>
       <c r="X33" s="15">
-        <v>-753.14285714285711</v>
+        <v>-1068.3388429752065</v>
       </c>
       <c r="Y33" s="18">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="Z33" s="17">
-        <v>780.2</v>
+        <v>381.8</v>
       </c>
       <c r="AA33" s="14">
-        <v>12.859934853420196</v>
+        <v>6.2016713091922018</v>
       </c>
       <c r="AB33" s="16">
-        <v>321.61904761904759</v>
+        <v>326.36363636363632</v>
       </c>
       <c r="AC33" s="15">
-        <v>-133.61904761904759</v>
+        <v>-234.36363636363632</v>
       </c>
       <c r="AD33" s="19">
-        <v>8771</v>
+        <v>10299</v>
       </c>
       <c r="AE33" s="20">
-        <v>36399.65</v>
+        <v>42740.850000000006</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4636,25 +4636,25 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>478</v>
+        <v>734</v>
       </c>
       <c r="F34" s="14">
-        <v>1983.7000000000003</v>
+        <v>3046.1000000000004</v>
       </c>
       <c r="G34" s="14">
-        <v>8.2958677685950413</v>
+        <v>14.68</v>
       </c>
       <c r="H34" s="30">
-        <v>1267.6190476190477</v>
+        <v>1100</v>
       </c>
       <c r="I34" s="15">
-        <v>-98.190476190476147</v>
+        <v>234</v>
       </c>
       <c r="J34" s="16">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="K34" s="13">
-        <v>1062.4000000000001</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="15">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="O34" s="16">
         <v>0</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>83.80952380952381</v>
+        <v>72.72727272727272</v>
       </c>
       <c r="S34" s="15">
-        <v>-76.19047619047619</v>
+        <v>-66.115702479338836</v>
       </c>
       <c r="T34" s="18">
         <v>82</v>
@@ -4685,13 +4685,13 @@
         <v>340.3</v>
       </c>
       <c r="V34" s="14">
-        <v>11.48</v>
+        <v>13.229333333333333</v>
       </c>
       <c r="W34" s="16">
-        <v>157.14285714285714</v>
+        <v>136.36363636363637</v>
       </c>
       <c r="X34" s="15">
-        <v>-32.285714285714278</v>
+        <v>-17.173553719008268</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4747,85 +4747,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1888</v>
+        <v>1376</v>
       </c>
       <c r="F35" s="14">
-        <v>3077.4399999999996</v>
+        <v>2242.8799999999997</v>
       </c>
       <c r="G35" s="14">
-        <v>4.4112149532710276</v>
+        <v>3.4510519224790133</v>
       </c>
       <c r="H35" s="30">
-        <v>9416</v>
+        <v>8771.818181818182</v>
       </c>
       <c r="I35" s="15">
-        <v>-2392</v>
+        <v>-2611.1900826446285</v>
       </c>
       <c r="J35" s="16">
-        <v>4660</v>
+        <v>3586</v>
       </c>
       <c r="K35" s="13">
-        <v>7595.7999999999993</v>
+        <v>5845.1799999999994</v>
       </c>
       <c r="L35" s="14">
-        <v>27.651879061881889</v>
+        <v>23.723674138873701</v>
       </c>
       <c r="M35" s="30">
-        <v>3707.5238095238092</v>
+        <v>3325.4545454545455</v>
       </c>
       <c r="N35" s="15">
-        <v>2974.7619047619046</v>
+        <v>2074.4297520661157</v>
       </c>
       <c r="O35" s="16">
-        <v>622</v>
+        <v>551</v>
       </c>
       <c r="P35" s="17">
-        <v>1013.8599999999999</v>
+        <v>898.13</v>
       </c>
       <c r="Q35" s="14">
-        <v>17.58008075370121</v>
+        <v>15.595555555555555</v>
       </c>
       <c r="R35" s="16">
-        <v>778.38095238095229</v>
+        <v>777.27272727272737</v>
       </c>
       <c r="S35" s="15">
-        <v>-85.619047619047592</v>
+        <v>-155.61157024793397</v>
       </c>
       <c r="T35" s="18">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="U35" s="17">
-        <v>678.07999999999993</v>
+        <v>523.23</v>
       </c>
       <c r="V35" s="14">
-        <v>8.8421052631578956</v>
+        <v>7.2195167286245354</v>
       </c>
       <c r="W35" s="16">
-        <v>1035.047619047619</v>
+        <v>978.18181818181813</v>
       </c>
       <c r="X35" s="15">
-        <v>-336.7619047619047</v>
+        <v>-390.40495867768595</v>
       </c>
       <c r="Y35" s="18">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="Z35" s="17">
-        <v>339.03999999999996</v>
+        <v>255.91</v>
       </c>
       <c r="AA35" s="14">
-        <v>13.822784810126583</v>
+        <v>11.141935483870967</v>
       </c>
       <c r="AB35" s="16">
-        <v>331.04761904761904</v>
+        <v>310</v>
       </c>
       <c r="AC35" s="15">
-        <v>-123.04761904761904</v>
+        <v>-153</v>
       </c>
       <c r="AD35" s="19">
-        <v>7794</v>
+        <v>5991</v>
       </c>
       <c r="AE35" s="20">
-        <v>12704.22</v>
+        <v>9765.33</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4860,85 +4860,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>5276</v>
+        <v>3776</v>
       </c>
       <c r="F36" s="14">
-        <v>8599.8799999999992</v>
+        <v>6154.8799999999992</v>
       </c>
       <c r="G36" s="14">
-        <v>8.4306802617562013</v>
+        <v>6.5098810287098381</v>
       </c>
       <c r="H36" s="30">
-        <v>13767.809523809525</v>
+        <v>12760.90909090909</v>
       </c>
       <c r="I36" s="15">
-        <v>-982.09523809523853</v>
+        <v>-2024.4132231404956</v>
       </c>
       <c r="J36" s="16">
-        <v>2763</v>
+        <v>4175</v>
       </c>
       <c r="K36" s="13">
-        <v>4503.6899999999996</v>
+        <v>6805.25</v>
       </c>
       <c r="L36" s="14">
-        <v>11.88022113022113</v>
+        <v>19.830225711481845</v>
       </c>
       <c r="M36" s="30">
-        <v>5116.5714285714284</v>
+        <v>4631.818181818182</v>
       </c>
       <c r="N36" s="15">
-        <v>437.28571428571468</v>
+        <v>2069.6280991735539</v>
       </c>
       <c r="O36" s="16">
-        <v>1456</v>
+        <v>1298</v>
       </c>
       <c r="P36" s="17">
-        <v>2373.2799999999997</v>
+        <v>2115.7399999999998</v>
       </c>
       <c r="Q36" s="14">
-        <v>16.394638069705092</v>
+        <v>15.367710371819964</v>
       </c>
       <c r="R36" s="16">
-        <v>1953.8095238095239</v>
+        <v>1858.181818181818</v>
       </c>
       <c r="S36" s="15">
-        <v>-320.19047619047615</v>
+        <v>-391.2561983471071</v>
       </c>
       <c r="T36" s="18">
-        <v>1141</v>
+        <v>933</v>
       </c>
       <c r="U36" s="17">
-        <v>1859.83</v>
+        <v>1520.79</v>
       </c>
       <c r="V36" s="14">
-        <v>10.871597096188749</v>
+        <v>9.4471129707112951</v>
       </c>
       <c r="W36" s="16">
-        <v>2308.9523809523807</v>
+        <v>2172.727272727273</v>
       </c>
       <c r="X36" s="15">
-        <v>-538.23809523809518</v>
+        <v>-647.16528925619855</v>
       </c>
       <c r="Y36" s="18">
-        <v>404</v>
+        <v>281</v>
       </c>
       <c r="Z36" s="17">
-        <v>658.52</v>
+        <v>458.03</v>
       </c>
       <c r="AA36" s="14">
-        <v>14.989399293286219</v>
+        <v>10.542945736434108</v>
       </c>
       <c r="AB36" s="16">
-        <v>592.95238095238096</v>
+        <v>586.36363636363637</v>
       </c>
       <c r="AC36" s="15">
-        <v>-188.95238095238096</v>
+        <v>-305.36363636363637</v>
       </c>
       <c r="AD36" s="19">
-        <v>11040</v>
+        <v>10463</v>
       </c>
       <c r="AE36" s="20">
-        <v>17995.199999999997</v>
+        <v>17054.689999999999</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4973,85 +4973,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>126</v>
+        <v>1067</v>
       </c>
       <c r="F37" s="14">
-        <v>205.38</v>
+        <v>1739.2099999999998</v>
       </c>
       <c r="G37" s="14">
-        <v>0.43185898482128288</v>
+        <v>3.9706904505612797</v>
       </c>
       <c r="H37" s="30">
-        <v>6418.7619047619046</v>
+        <v>5911.8181818181811</v>
       </c>
       <c r="I37" s="15">
-        <v>-2791.6190476190477</v>
+        <v>-1620.1900826446281</v>
       </c>
       <c r="J37" s="16">
-        <v>2130</v>
+        <v>4681</v>
       </c>
       <c r="K37" s="13">
-        <v>3471.8999999999996</v>
+        <v>7630.03</v>
       </c>
       <c r="L37" s="14">
-        <v>15.137055837563452</v>
+        <v>36.272878642331086</v>
       </c>
       <c r="M37" s="30">
-        <v>3095.7142857142858</v>
+        <v>2839.0909090909095</v>
       </c>
       <c r="N37" s="15">
-        <v>722.85714285714266</v>
+        <v>3390.5041322314046</v>
       </c>
       <c r="O37" s="16">
-        <v>885</v>
+        <v>842</v>
       </c>
       <c r="P37" s="17">
-        <v>1442.55</v>
+        <v>1372.4599999999998</v>
       </c>
       <c r="Q37" s="14">
-        <v>15.487500000000001</v>
+        <v>15.343674698795182</v>
       </c>
       <c r="R37" s="16">
-        <v>1257.1428571428571</v>
+        <v>1207.2727272727273</v>
       </c>
       <c r="S37" s="15">
-        <v>-257.85714285714266</v>
+        <v>-255.52066115702473</v>
       </c>
       <c r="T37" s="18">
-        <v>314</v>
+        <v>168</v>
       </c>
       <c r="U37" s="17">
-        <v>511.82</v>
+        <v>273.83999999999997</v>
       </c>
       <c r="V37" s="14">
-        <v>5.6455479452054798</v>
+        <v>3.1297921478060045</v>
       </c>
       <c r="W37" s="16">
-        <v>1223.6190476190477</v>
+        <v>1180.909090909091</v>
       </c>
       <c r="X37" s="15">
-        <v>-575.90476190476193</v>
+        <v>-690.84297520661164</v>
       </c>
       <c r="Y37" s="18">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="17">
-        <v>260.79999999999995</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="14">
-        <v>10.980392156862745</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>320.57142857142856</v>
+        <v>395.4545454545455</v>
       </c>
       <c r="AC37" s="15">
-        <v>-160.57142857142856</v>
+        <v>-395.4545454545455</v>
       </c>
       <c r="AD37" s="19">
-        <v>3615</v>
+        <v>6758</v>
       </c>
       <c r="AE37" s="20">
-        <v>5892.45</v>
+        <v>11015.539999999999</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5086,85 +5086,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1846</v>
+        <v>1141</v>
       </c>
       <c r="F38" s="14">
-        <v>3008.98</v>
+        <v>1859.83</v>
       </c>
       <c r="G38" s="14">
-        <v>8.7666214382632308</v>
+        <v>5.551306795335746</v>
       </c>
       <c r="H38" s="30">
-        <v>4632.5714285714284</v>
+        <v>4521.818181818182</v>
       </c>
       <c r="I38" s="15">
-        <v>-259.71428571428532</v>
+        <v>-914.37190082644611</v>
       </c>
       <c r="J38" s="16">
-        <v>1034</v>
+        <v>4179</v>
       </c>
       <c r="K38" s="13">
-        <v>1685.4199999999998</v>
+        <v>6811.7699999999995</v>
       </c>
       <c r="L38" s="14">
-        <v>8.682127149140344</v>
+        <v>38.822188099808066</v>
       </c>
       <c r="M38" s="30">
-        <v>2620.0952380952381</v>
+        <v>2368.181818181818</v>
       </c>
       <c r="N38" s="15">
-        <v>-156.95238095238096</v>
+        <v>3102.5537190082646</v>
       </c>
       <c r="O38" s="16">
-        <v>554</v>
+        <v>497</v>
       </c>
       <c r="P38" s="17">
-        <v>903.02</v>
+        <v>810.1099999999999</v>
       </c>
       <c r="Q38" s="14">
-        <v>14.801526717557252</v>
+        <v>13.260639470782802</v>
       </c>
       <c r="R38" s="16">
-        <v>823.42857142857144</v>
+        <v>824.5454545454545</v>
       </c>
       <c r="S38" s="15">
-        <v>-194.57142857142867</v>
+        <v>-252.58677685950408</v>
       </c>
       <c r="T38" s="18">
-        <v>391</v>
+        <v>314</v>
       </c>
       <c r="U38" s="17">
-        <v>637.32999999999993</v>
+        <v>511.82</v>
       </c>
       <c r="V38" s="14">
-        <v>10.5</v>
+        <v>8.9083235638921447</v>
       </c>
       <c r="W38" s="16">
-        <v>819.2380952380953</v>
+        <v>775.4545454545455</v>
       </c>
       <c r="X38" s="15">
-        <v>-204.80952380952385</v>
+        <v>-249.96694214876038</v>
       </c>
       <c r="Y38" s="18">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="Z38" s="17">
-        <v>634.06999999999994</v>
+        <v>386.31</v>
       </c>
       <c r="AA38" s="14">
-        <v>13.413793103448276</v>
+        <v>7.8782967032967033</v>
       </c>
       <c r="AB38" s="16">
-        <v>638</v>
+        <v>661.81818181818187</v>
       </c>
       <c r="AC38" s="15">
-        <v>-249</v>
+        <v>-424.81818181818187</v>
       </c>
       <c r="AD38" s="19">
-        <v>4214</v>
+        <v>6368</v>
       </c>
       <c r="AE38" s="20">
-        <v>6868.82</v>
+        <v>10379.84</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5199,85 +5199,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>1071</v>
+        <v>969</v>
       </c>
       <c r="F39" s="14">
-        <v>1745.7299999999998</v>
+        <v>1579.4699999999998</v>
       </c>
       <c r="G39" s="14">
-        <v>10.504904250350304</v>
+        <v>10.712562814070353</v>
       </c>
       <c r="H39" s="30">
-        <v>2242.9523809523807</v>
+        <v>1990</v>
       </c>
       <c r="I39" s="15">
-        <v>51.476190476190482</v>
+        <v>64.454545454545496</v>
       </c>
       <c r="J39" s="16">
-        <v>2241</v>
+        <v>2076</v>
       </c>
       <c r="K39" s="13">
-        <v>3652.83</v>
+        <v>3383.8799999999997</v>
       </c>
       <c r="L39" s="14">
-        <v>39.348662207357854</v>
+        <v>40.352771084337348</v>
       </c>
       <c r="M39" s="30">
-        <v>1252.952380952381</v>
+        <v>1131.818181818182</v>
       </c>
       <c r="N39" s="15">
-        <v>1671.4761904761904</v>
+        <v>1561.5371900826444</v>
       </c>
       <c r="O39" s="16">
-        <v>548</v>
+        <v>466</v>
       </c>
       <c r="P39" s="17">
-        <v>893.2399999999999</v>
+        <v>759.57999999999993</v>
       </c>
       <c r="Q39" s="14">
-        <v>20.083769633507856</v>
+        <v>17.32288786482335</v>
       </c>
       <c r="R39" s="16">
-        <v>600.28571428571422</v>
+        <v>591.81818181818176</v>
       </c>
       <c r="S39" s="15">
-        <v>2.2857142857143344</v>
+        <v>-72.016528925619696</v>
       </c>
       <c r="T39" s="18">
-        <v>524</v>
+        <v>393</v>
       </c>
       <c r="U39" s="17">
-        <v>854.11999999999989</v>
+        <v>640.58999999999992</v>
       </c>
       <c r="V39" s="14">
-        <v>9.6020942408376975</v>
+        <v>7.5063930544593518</v>
       </c>
       <c r="W39" s="16">
-        <v>1200.5714285714284</v>
+        <v>1151.818181818182</v>
       </c>
       <c r="X39" s="15">
-        <v>-349.142857142857</v>
+        <v>-444.68595041322328</v>
       </c>
       <c r="Y39" s="18">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="Z39" s="17">
-        <v>643.84999999999991</v>
+        <v>590.05999999999995</v>
       </c>
       <c r="AA39" s="14">
-        <v>66.36</v>
+        <v>63.024460431654667</v>
       </c>
       <c r="AB39" s="16">
-        <v>130.95238095238096</v>
+        <v>126.36363636363637</v>
       </c>
       <c r="AC39" s="15">
-        <v>264.04761904761904</v>
+        <v>235.63636363636363</v>
       </c>
       <c r="AD39" s="19">
-        <v>4779</v>
+        <v>4266</v>
       </c>
       <c r="AE39" s="20">
-        <v>7789.7699999999995</v>
+        <v>6953.58</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5312,85 +5312,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1357</v>
+        <v>1146</v>
       </c>
       <c r="F40" s="14">
-        <v>2211.91</v>
+        <v>1867.9799999999998</v>
       </c>
       <c r="G40" s="14">
-        <v>10.2544080604534</v>
+        <v>9.6062348458607545</v>
       </c>
       <c r="H40" s="30">
-        <v>2911.3333333333335</v>
+        <v>2624.5454545454545</v>
       </c>
       <c r="I40" s="15">
-        <v>33.666666666666515</v>
+        <v>-46.975206611570229</v>
       </c>
       <c r="J40" s="16">
-        <v>579</v>
+        <v>227</v>
       </c>
       <c r="K40" s="13">
-        <v>943.77</v>
+        <v>370.01</v>
       </c>
       <c r="L40" s="14">
-        <v>8.4790794979079482</v>
+        <v>3.7192958700067704</v>
       </c>
       <c r="M40" s="30">
-        <v>1502.2857142857144</v>
+        <v>1342.7272727272727</v>
       </c>
       <c r="N40" s="15">
-        <v>-103.85714285714289</v>
+        <v>-383.33057851239664</v>
       </c>
       <c r="O40" s="16">
-        <v>661</v>
+        <v>569</v>
       </c>
       <c r="P40" s="17">
-        <v>1077.4299999999998</v>
+        <v>927.46999999999991</v>
       </c>
       <c r="Q40" s="14">
-        <v>19.119834710743802</v>
+        <v>16.999753086419751</v>
       </c>
       <c r="R40" s="16">
-        <v>760.57142857142856</v>
+        <v>736.36363636363637</v>
       </c>
       <c r="S40" s="15">
-        <v>-30.428571428571331</v>
+        <v>-100.42148760330588</v>
       </c>
       <c r="T40" s="18">
-        <v>632</v>
+        <v>508</v>
       </c>
       <c r="U40" s="17">
-        <v>1030.1599999999999</v>
+        <v>828.04</v>
       </c>
       <c r="V40" s="14">
-        <v>9.9789473684210517</v>
+        <v>8.4959225984796145</v>
       </c>
       <c r="W40" s="16">
-        <v>1393.3333333333335</v>
+        <v>1315.4545454545453</v>
       </c>
       <c r="X40" s="15">
-        <v>-381.33333333333348</v>
+        <v>-448.6942148760329</v>
       </c>
       <c r="Y40" s="18">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="Z40" s="17">
-        <v>666.67</v>
+        <v>593.31999999999994</v>
       </c>
       <c r="AA40" s="14">
-        <v>72.17647058823529</v>
+        <v>60.750344827586211</v>
       </c>
       <c r="AB40" s="16">
-        <v>124.66666666666667</v>
+        <v>131.81818181818181</v>
       </c>
       <c r="AC40" s="15">
-        <v>284.33333333333331</v>
+        <v>232.18181818181819</v>
       </c>
       <c r="AD40" s="19">
-        <v>3638</v>
+        <v>2814</v>
       </c>
       <c r="AE40" s="20">
-        <v>5929.94</v>
+        <v>4586.82</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5425,85 +5425,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>461</v>
+        <v>325</v>
       </c>
       <c r="F41" s="14">
-        <v>2835.15</v>
+        <v>1998.7500000000002</v>
       </c>
       <c r="G41" s="14">
-        <v>6.4755852842809363</v>
+        <v>4.9156249999999995</v>
       </c>
       <c r="H41" s="30">
-        <v>1566.1904761904761</v>
+        <v>1454.5454545454547</v>
       </c>
       <c r="I41" s="15">
-        <v>-250.90476190476193</v>
+        <v>-336.15702479338847</v>
       </c>
       <c r="J41" s="16">
-        <v>286</v>
+        <v>853</v>
       </c>
       <c r="K41" s="13">
-        <v>1758.9</v>
+        <v>5245.9500000000007</v>
       </c>
       <c r="L41" s="14">
-        <v>7.4887780548628431</v>
+        <v>25.082138517618475</v>
       </c>
       <c r="M41" s="30">
-        <v>840.19047619047615</v>
+        <v>748.18181818181813</v>
       </c>
       <c r="N41" s="15">
-        <v>-95.904761904761926</v>
+        <v>512.91735537190084</v>
       </c>
       <c r="O41" s="16">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="P41" s="17">
-        <v>356.70000000000005</v>
+        <v>172.20000000000002</v>
       </c>
       <c r="Q41" s="14">
-        <v>12.821052631578947</v>
+        <v>5.2527131782945737</v>
       </c>
       <c r="R41" s="16">
-        <v>99.523809523809518</v>
+        <v>117.27272727272727</v>
       </c>
       <c r="S41" s="15">
-        <v>-32.476190476190482</v>
+        <v>-78.611570247933884</v>
       </c>
       <c r="T41" s="18">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="U41" s="17">
-        <v>621.15000000000009</v>
+        <v>338.25</v>
       </c>
       <c r="V41" s="14">
-        <v>8.157692307692308</v>
+        <v>4.3927392739273916</v>
       </c>
       <c r="W41" s="16">
-        <v>272.38095238095241</v>
+        <v>275.4545454545455</v>
       </c>
       <c r="X41" s="15">
-        <v>-97.095238095238102</v>
+        <v>-145.33057851239673</v>
       </c>
       <c r="Y41" s="18">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="Z41" s="17">
-        <v>399.75</v>
+        <v>147.60000000000002</v>
       </c>
       <c r="AA41" s="14">
-        <v>14.368421052631579</v>
+        <v>4.3669172932330822</v>
       </c>
       <c r="AB41" s="16">
-        <v>99.523809523809518</v>
+        <v>120.90909090909092</v>
       </c>
       <c r="AC41" s="15">
-        <v>-34.523809523809518</v>
+        <v>-96.909090909090907</v>
       </c>
       <c r="AD41" s="19">
-        <v>971</v>
+        <v>1285</v>
       </c>
       <c r="AE41" s="20">
-        <v>5971.6500000000005</v>
+        <v>7902.7500000000009</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5538,34 +5538,34 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>270</v>
+        <v>71</v>
       </c>
       <c r="F42" s="14">
-        <v>1660.5</v>
+        <v>436.65000000000003</v>
       </c>
       <c r="G42" s="14">
-        <v>3.5130111524163565</v>
+        <v>0.97018633540372667</v>
       </c>
       <c r="H42" s="30">
-        <v>1690.8571428571429</v>
+        <v>1610</v>
       </c>
       <c r="I42" s="15">
-        <v>-498.57142857142867</v>
+        <v>-660.81818181818187</v>
       </c>
       <c r="J42" s="16">
-        <v>288</v>
+        <v>753</v>
       </c>
       <c r="K42" s="13">
-        <v>1771.2</v>
+        <v>4630.95</v>
       </c>
       <c r="L42" s="14">
-        <v>6.8962371721778792</v>
+        <v>20.292427616926503</v>
       </c>
       <c r="M42" s="30">
-        <v>918.7619047619047</v>
+        <v>816.36363636363637</v>
       </c>
       <c r="N42" s="15">
-        <v>-129.61904761904759</v>
+        <v>381.92561983471074</v>
       </c>
       <c r="O42" s="16">
         <v>95</v>
@@ -5574,49 +5574,49 @@
         <v>584.25</v>
       </c>
       <c r="Q42" s="14">
-        <v>14.249999999999998</v>
+        <v>14.459119496855346</v>
       </c>
       <c r="R42" s="16">
-        <v>146.66666666666669</v>
+        <v>144.54545454545456</v>
       </c>
       <c r="S42" s="15">
-        <v>-38.333333333333371</v>
+        <v>-36.404958677685954</v>
       </c>
       <c r="T42" s="18">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="U42" s="17">
-        <v>1143.9000000000001</v>
+        <v>897.90000000000009</v>
       </c>
       <c r="V42" s="14">
-        <v>10.790055248618785</v>
+        <v>8.7672456575682407</v>
       </c>
       <c r="W42" s="16">
-        <v>379.23809523809524</v>
+        <v>366.36363636363632</v>
       </c>
       <c r="X42" s="15">
-        <v>-89.809523809523796</v>
+        <v>-120.44628099173548</v>
       </c>
       <c r="Y42" s="18">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="Z42" s="17">
-        <v>381.3</v>
+        <v>215.25</v>
       </c>
       <c r="AA42" s="14">
-        <v>19.147058823529413</v>
+        <v>10.5875</v>
       </c>
       <c r="AB42" s="16">
-        <v>71.238095238095241</v>
+        <v>72.72727272727272</v>
       </c>
       <c r="AC42" s="15">
-        <v>-9.2380952380952408</v>
+        <v>-37.72727272727272</v>
       </c>
       <c r="AD42" s="19">
-        <v>901</v>
+        <v>1100</v>
       </c>
       <c r="AE42" s="20">
-        <v>5541.1500000000005</v>
+        <v>6765</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5651,85 +5651,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2916</v>
+        <v>2571</v>
       </c>
       <c r="F43" s="14">
-        <v>3382.56</v>
+        <v>2982.3599999999997</v>
       </c>
       <c r="G43" s="14">
-        <v>8.6175063326766104</v>
+        <v>8.0333376371852818</v>
       </c>
       <c r="H43" s="30">
-        <v>7444.3809523809532</v>
+        <v>7040.909090909091</v>
       </c>
       <c r="I43" s="15">
-        <v>-467.80952380952385</v>
+        <v>-629.41322314049557</v>
       </c>
       <c r="J43" s="16">
-        <v>7767</v>
+        <v>7296</v>
       </c>
       <c r="K43" s="13">
-        <v>9009.7199999999993</v>
+        <v>8463.3599999999988</v>
       </c>
       <c r="L43" s="14">
-        <v>31.068000000000001</v>
+        <v>32.231325301204819</v>
       </c>
       <c r="M43" s="30">
-        <v>5500</v>
+        <v>4980</v>
       </c>
       <c r="N43" s="15">
-        <v>5267</v>
+        <v>5032.363636363636</v>
       </c>
       <c r="O43" s="16">
-        <v>705</v>
+        <v>555</v>
       </c>
       <c r="P43" s="17">
-        <v>817.8</v>
+        <v>643.79999999999995</v>
       </c>
       <c r="Q43" s="14">
-        <v>15.310237849017579</v>
+        <v>11.760945709281962</v>
       </c>
       <c r="R43" s="16">
-        <v>1013.0476190476192</v>
+        <v>1038.181818181818</v>
       </c>
       <c r="S43" s="15">
-        <v>-215.95238095238096</v>
+        <v>-388.80165289256183</v>
       </c>
       <c r="T43" s="18">
-        <v>1177</v>
+        <v>866</v>
       </c>
       <c r="U43" s="17">
-        <v>1365.32</v>
+        <v>1004.56</v>
       </c>
       <c r="V43" s="14">
-        <v>9.851335193304104</v>
+        <v>7.5223259152907387</v>
       </c>
       <c r="W43" s="16">
-        <v>2628.4761904761908</v>
+        <v>2532.727272727273</v>
       </c>
       <c r="X43" s="15">
-        <v>-734.61904761904793</v>
+        <v>-975.9834710743803</v>
       </c>
       <c r="Y43" s="18">
-        <v>476</v>
+        <v>350</v>
       </c>
       <c r="Z43" s="17">
-        <v>552.16</v>
+        <v>406</v>
       </c>
       <c r="AA43" s="14">
-        <v>15.099697885196376</v>
+        <v>11.829608938547484</v>
       </c>
       <c r="AB43" s="16">
-        <v>693.52380952380952</v>
+        <v>650.90909090909099</v>
       </c>
       <c r="AC43" s="15">
-        <v>-217.52380952380952</v>
+        <v>-300.90909090909099</v>
       </c>
       <c r="AD43" s="19">
-        <v>13041</v>
+        <v>11638</v>
       </c>
       <c r="AE43" s="20">
-        <v>15127.56</v>
+        <v>13500.08</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5764,85 +5764,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2966</v>
+        <v>2426</v>
       </c>
       <c r="F44" s="14">
-        <v>3440.56</v>
+        <v>2814.16</v>
       </c>
       <c r="G44" s="14">
-        <v>10.310544611819235</v>
+        <v>9.0058597944470016</v>
       </c>
       <c r="H44" s="30">
-        <v>6328.666666666667</v>
+        <v>5926.363636363636</v>
       </c>
       <c r="I44" s="15">
-        <v>89.33333333333303</v>
+        <v>-267.80165289256183</v>
       </c>
       <c r="J44" s="16">
-        <v>5587</v>
+        <v>5132</v>
       </c>
       <c r="K44" s="13">
-        <v>6480.9199999999992</v>
+        <v>5953.12</v>
       </c>
       <c r="L44" s="14">
-        <v>28.962478400394964</v>
+        <v>29.07852961835636</v>
       </c>
       <c r="M44" s="30">
-        <v>4243.9047619047615</v>
+        <v>3882.7272727272725</v>
       </c>
       <c r="N44" s="15">
-        <v>3657.9523809523807</v>
+        <v>3367.1239669421489</v>
       </c>
       <c r="O44" s="16">
-        <v>502</v>
+        <v>423</v>
       </c>
       <c r="P44" s="17">
-        <v>582.31999999999994</v>
+        <v>490.67999999999995</v>
       </c>
       <c r="Q44" s="14">
-        <v>19.028880866425997</v>
+        <v>15.797222222222224</v>
       </c>
       <c r="R44" s="16">
-        <v>580.38095238095229</v>
+        <v>589.09090909090901</v>
       </c>
       <c r="S44" s="15">
-        <v>-25.619047619047478</v>
+        <v>-112.53719008264454</v>
       </c>
       <c r="T44" s="18">
-        <v>735</v>
+        <v>594</v>
       </c>
       <c r="U44" s="17">
-        <v>852.59999999999991</v>
+        <v>689.04</v>
       </c>
       <c r="V44" s="14">
-        <v>11.241806263656228</v>
+        <v>9.6734858681022882</v>
       </c>
       <c r="W44" s="16">
-        <v>1438.3809523809523</v>
+        <v>1350.909090909091</v>
       </c>
       <c r="X44" s="15">
-        <v>-311.09523809523807</v>
+        <v>-388.47933884297527</v>
       </c>
       <c r="Y44" s="18">
-        <v>394</v>
+        <v>248</v>
       </c>
       <c r="Z44" s="17">
-        <v>457.03999999999996</v>
+        <v>287.68</v>
       </c>
       <c r="AA44" s="14">
-        <v>12.84782608695652</v>
+        <v>8.1322493224932249</v>
       </c>
       <c r="AB44" s="16">
-        <v>674.66666666666674</v>
+        <v>670.90909090909099</v>
       </c>
       <c r="AC44" s="15">
-        <v>-280.66666666666674</v>
+        <v>-422.90909090909099</v>
       </c>
       <c r="AD44" s="19">
-        <v>10184</v>
+        <v>8823</v>
       </c>
       <c r="AE44" s="20">
-        <v>11813.439999999999</v>
+        <v>10234.679999999998</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5877,85 +5877,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3406</v>
+        <v>3147</v>
       </c>
       <c r="F45" s="14">
-        <v>3950.9599999999996</v>
+        <v>3650.5199999999995</v>
       </c>
       <c r="G45" s="14">
-        <v>8.8863212821468505</v>
+        <v>8.8524235731721497</v>
       </c>
       <c r="H45" s="30">
-        <v>8432.2857142857138</v>
+        <v>7820.909090909091</v>
       </c>
       <c r="I45" s="15">
-        <v>-426.85714285714266</v>
+        <v>-407.95867768595008</v>
       </c>
       <c r="J45" s="16">
-        <v>6227</v>
+        <v>5295</v>
       </c>
       <c r="K45" s="13">
-        <v>7223.32</v>
+        <v>6142.2</v>
       </c>
       <c r="L45" s="14">
-        <v>24.419607843137253</v>
+        <v>23.129783393501807</v>
       </c>
       <c r="M45" s="30">
-        <v>5610</v>
+        <v>5036.363636363636</v>
       </c>
       <c r="N45" s="15">
-        <v>3677</v>
+        <v>3005.7438016528927</v>
       </c>
       <c r="O45" s="16">
-        <v>658</v>
+        <v>543</v>
       </c>
       <c r="P45" s="17">
-        <v>763.28</v>
+        <v>629.88</v>
       </c>
       <c r="Q45" s="14">
-        <v>15.234840132304301</v>
+        <v>12.502949571836346</v>
       </c>
       <c r="R45" s="16">
-        <v>950.19047619047615</v>
+        <v>955.4545454545455</v>
       </c>
       <c r="S45" s="15">
-        <v>-205.80952380952385</v>
+        <v>-325.59504132231405</v>
       </c>
       <c r="T45" s="18">
-        <v>1095</v>
+        <v>824</v>
       </c>
       <c r="U45" s="17">
-        <v>1270.1999999999998</v>
+        <v>955.83999999999992</v>
       </c>
       <c r="V45" s="14">
-        <v>11.549472626820693</v>
+        <v>8.9581311769990997</v>
       </c>
       <c r="W45" s="16">
-        <v>2085.8095238095239</v>
+        <v>2023.6363636363637</v>
       </c>
       <c r="X45" s="15">
-        <v>-421.95238095238096</v>
+        <v>-647.73553719008282</v>
       </c>
       <c r="Y45" s="18">
-        <v>406</v>
+        <v>236</v>
       </c>
       <c r="Z45" s="17">
-        <v>470.96</v>
+        <v>273.76</v>
       </c>
       <c r="AA45" s="14">
-        <v>13.796116504854368</v>
+        <v>7.9988795518207292</v>
       </c>
       <c r="AB45" s="16">
-        <v>647.42857142857144</v>
+        <v>649.09090909090901</v>
       </c>
       <c r="AC45" s="15">
-        <v>-241.42857142857144</v>
+        <v>-413.09090909090901</v>
       </c>
       <c r="AD45" s="19">
-        <v>11792</v>
+        <v>10045</v>
       </c>
       <c r="AE45" s="20">
-        <v>13678.72</v>
+        <v>11652.199999999999</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5990,85 +5990,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2523</v>
+        <v>2492</v>
       </c>
       <c r="F46" s="14">
-        <v>2926.68</v>
+        <v>2890.72</v>
       </c>
       <c r="G46" s="14">
-        <v>8.865963855421688</v>
+        <v>9.4140493287542935</v>
       </c>
       <c r="H46" s="30">
-        <v>6260.5714285714284</v>
+        <v>5823.636363636364</v>
       </c>
       <c r="I46" s="15">
-        <v>-322.71428571428532</v>
+        <v>-155.1074380165287</v>
       </c>
       <c r="J46" s="16">
-        <v>4236</v>
+        <v>3400</v>
       </c>
       <c r="K46" s="13">
-        <v>4913.7599999999993</v>
+        <v>3943.9999999999995</v>
       </c>
       <c r="L46" s="14">
-        <v>26.071512309495898</v>
+        <v>23.118853610564763</v>
       </c>
       <c r="M46" s="30">
-        <v>3574.4761904761908</v>
+        <v>3235.4545454545455</v>
       </c>
       <c r="N46" s="15">
-        <v>2611.2380952380954</v>
+        <v>1929.3388429752065</v>
       </c>
       <c r="O46" s="16">
-        <v>449</v>
+        <v>349</v>
       </c>
       <c r="P46" s="17">
-        <v>520.83999999999992</v>
+        <v>404.84</v>
       </c>
       <c r="Q46" s="14">
-        <v>17.428835489833642</v>
+        <v>13.013559322033899</v>
       </c>
       <c r="R46" s="16">
-        <v>566.76190476190482</v>
+        <v>590</v>
       </c>
       <c r="S46" s="15">
-        <v>-66.238095238095298</v>
+        <v>-187.36363636363637</v>
       </c>
       <c r="T46" s="18">
-        <v>571</v>
+        <v>493</v>
       </c>
       <c r="U46" s="17">
-        <v>662.3599999999999</v>
+        <v>571.88</v>
       </c>
       <c r="V46" s="14">
-        <v>14.767241379310345</v>
+        <v>13.588382687927108</v>
       </c>
       <c r="W46" s="16">
-        <v>850.66666666666663</v>
+        <v>798.18181818181813</v>
       </c>
       <c r="X46" s="15">
-        <v>-47.666666666666629</v>
+        <v>-87.495867768594962</v>
       </c>
       <c r="Y46" s="18">
-        <v>506</v>
+        <v>361</v>
       </c>
       <c r="Z46" s="17">
-        <v>586.95999999999992</v>
+        <v>418.76</v>
       </c>
       <c r="AA46" s="14">
-        <v>22.656716417910449</v>
+        <v>15.088428324697755</v>
       </c>
       <c r="AB46" s="16">
-        <v>491.33333333333331</v>
+        <v>526.36363636363637</v>
       </c>
       <c r="AC46" s="15">
-        <v>14.666666666666686</v>
+        <v>-165.36363636363637</v>
       </c>
       <c r="AD46" s="19">
-        <v>8285</v>
+        <v>7095</v>
       </c>
       <c r="AE46" s="20">
-        <v>9610.5999999999985</v>
+        <v>8230.1999999999989</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6116,19 +6116,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K47" s="13">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="L47" s="14">
-        <v>10.15</v>
+        <v>11.293333333333335</v>
       </c>
       <c r="M47" s="30">
-        <v>62.857142857142861</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="N47" s="15">
-        <v>0.42857142857142705</v>
+        <v>3.2066115702479365</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6146,19 +6146,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U47" s="17">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="V47" s="14">
-        <v>15.749999999999998</v>
+        <v>14.3</v>
       </c>
       <c r="W47" s="16">
-        <v>20.952380952380953</v>
+        <v>20</v>
       </c>
       <c r="X47" s="15">
-        <v>-0.23809523809523903</v>
+        <v>-1.545454545454545</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AE47" s="20">
-        <v>792</v>
+        <v>738</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6227,19 +6227,19 @@
         <v>0</v>
       </c>
       <c r="J48" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K48" s="13">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="L48" s="14">
-        <v>21</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="M48" s="30">
-        <v>11.523809523809524</v>
+        <v>10</v>
       </c>
       <c r="N48" s="15">
-        <v>5.7619047619047619</v>
+        <v>7.454545454545455</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6287,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE48" s="20">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6325,85 +6325,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F49" s="14">
-        <v>17.399999999999999</v>
+        <v>6.9599999999999991</v>
       </c>
       <c r="G49" s="14">
-        <v>0.3</v>
+        <v>0.13685202639019792</v>
       </c>
       <c r="H49" s="30">
-        <v>1100</v>
+        <v>964.5454545454545</v>
       </c>
       <c r="I49" s="15">
-        <v>-485</v>
+        <v>-432.42975206611573</v>
       </c>
       <c r="J49" s="16">
+        <v>161</v>
+      </c>
+      <c r="K49" s="13">
+        <v>186.76</v>
+      </c>
+      <c r="L49" s="14">
+        <v>3.4297535211267602</v>
+      </c>
+      <c r="M49" s="30">
+        <v>1032.7272727272727</v>
+      </c>
+      <c r="N49" s="15">
+        <v>-308.42148760330582</v>
+      </c>
+      <c r="O49" s="16">
+        <v>10</v>
+      </c>
+      <c r="P49" s="17">
+        <v>11.6</v>
+      </c>
+      <c r="Q49" s="14">
+        <v>1.4319526627218935</v>
+      </c>
+      <c r="R49" s="16">
+        <v>153.63636363636363</v>
+      </c>
+      <c r="S49" s="15">
+        <v>-129.6694214876033</v>
+      </c>
+      <c r="T49" s="18">
+        <v>4</v>
+      </c>
+      <c r="U49" s="17">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="V49" s="14">
+        <v>0.41367521367521365</v>
+      </c>
+      <c r="W49" s="16">
+        <v>212.72727272727275</v>
+      </c>
+      <c r="X49" s="15">
+        <v>-150.71074380165291</v>
+      </c>
+      <c r="Y49" s="18">
         <v>0</v>
       </c>
-      <c r="K49" s="13">
+      <c r="Z49" s="17">
         <v>0</v>
       </c>
-      <c r="L49" s="14">
+      <c r="AA49" s="14">
         <v>0</v>
       </c>
-      <c r="M49" s="30">
-        <v>1179.6190476190477</v>
-      </c>
-      <c r="N49" s="15">
-        <v>-536.19047619047615</v>
-      </c>
-      <c r="O49" s="16">
-        <v>24</v>
-      </c>
-      <c r="P49" s="17">
-        <v>27.839999999999996</v>
-      </c>
-      <c r="Q49" s="14">
-        <v>3.2101910828025479</v>
-      </c>
-      <c r="R49" s="16">
-        <v>164.47619047619048</v>
-      </c>
-      <c r="S49" s="15">
-        <v>-125.52380952380952</v>
-      </c>
-      <c r="T49" s="18">
-        <v>1</v>
-      </c>
-      <c r="U49" s="17">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="V49" s="14">
-        <v>8.9743589743589744E-2</v>
-      </c>
-      <c r="W49" s="16">
-        <v>245.14285714285714</v>
-      </c>
-      <c r="X49" s="15">
-        <v>-177.28571428571428</v>
-      </c>
-      <c r="Y49" s="18">
-        <v>8</v>
-      </c>
-      <c r="Z49" s="17">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="AA49" s="14">
-        <v>1.6633663366336635</v>
-      </c>
       <c r="AB49" s="16">
-        <v>105.80952380952381</v>
+        <v>96.363636363636374</v>
       </c>
       <c r="AC49" s="15">
-        <v>-97.80952380952381</v>
+        <v>-96.36363636363636</v>
       </c>
       <c r="AD49" s="19">
-        <v>48</v>
+        <v>181</v>
       </c>
       <c r="AE49" s="20">
-        <v>55.679999999999993</v>
+        <v>209.95999999999998</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6438,85 +6438,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1382</v>
+        <v>1122</v>
       </c>
       <c r="F50" s="14">
-        <v>1603.12</v>
+        <v>1301.52</v>
       </c>
       <c r="G50" s="14">
-        <v>4.7359660574412539</v>
+        <v>4.1747232472324729</v>
       </c>
       <c r="H50" s="30">
-        <v>6419.8095238095239</v>
+        <v>5912.7272727272721</v>
       </c>
       <c r="I50" s="15">
-        <v>-1536.0952380952381</v>
+        <v>-1565.6033057851237</v>
       </c>
       <c r="J50" s="16">
-        <v>789</v>
+        <v>2363</v>
       </c>
       <c r="K50" s="13">
-        <v>915.2399999999999</v>
+        <v>2741.08</v>
       </c>
       <c r="L50" s="14">
-        <v>4.0481309552895191</v>
+        <v>12.902662454873646</v>
       </c>
       <c r="M50" s="30">
-        <v>4287.9047619047615</v>
+        <v>4029.0909090909095</v>
       </c>
       <c r="N50" s="15">
-        <v>-1160.047619047619</v>
+        <v>531.59504132231405</v>
       </c>
       <c r="O50" s="16">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="P50" s="17">
-        <v>80.039999999999992</v>
+        <v>44.08</v>
       </c>
       <c r="Q50" s="14">
-        <v>1.6409966024915061</v>
+        <v>0.98038379530916853</v>
       </c>
       <c r="R50" s="16">
-        <v>925.04761904761915</v>
+        <v>852.72727272727263</v>
       </c>
       <c r="S50" s="15">
-        <v>-771.95238095238096</v>
+        <v>-737.2066115702479</v>
       </c>
       <c r="T50" s="18">
-        <v>483</v>
+        <v>239</v>
       </c>
       <c r="U50" s="17">
-        <v>560.28</v>
+        <v>277.24</v>
       </c>
       <c r="V50" s="14">
-        <v>12.074999999999999</v>
+        <v>5.3702878365831017</v>
       </c>
       <c r="W50" s="16">
-        <v>880</v>
+        <v>979.09090909090901</v>
       </c>
       <c r="X50" s="15">
-        <v>-157</v>
+        <v>-473.06611570247924</v>
       </c>
       <c r="Y50" s="18">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="17">
-        <v>24.36</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="14">
-        <v>1.8374999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="16">
-        <v>251.42857142857144</v>
+        <v>218.18181818181816</v>
       </c>
       <c r="AC50" s="15">
-        <v>-230.42857142857144</v>
+        <v>-218.18181818181816</v>
       </c>
       <c r="AD50" s="19">
-        <v>2744</v>
+        <v>3762</v>
       </c>
       <c r="AE50" s="20">
-        <v>3183.04</v>
+        <v>4363.92</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6554,85 +6554,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>934</v>
+        <v>355</v>
       </c>
       <c r="F51" s="14">
-        <v>1083.4399999999998</v>
+        <v>411.79999999999995</v>
       </c>
       <c r="G51" s="14">
-        <v>4.7572156196943967</v>
+        <v>1.9044557747727777</v>
       </c>
       <c r="H51" s="30">
-        <v>4319.3333333333339</v>
+        <v>4100.909090909091</v>
       </c>
       <c r="I51" s="15">
-        <v>-1029.3333333333337</v>
+        <v>-1509.0495867768595</v>
       </c>
       <c r="J51" s="16">
-        <v>1046</v>
+        <v>2882</v>
       </c>
       <c r="K51" s="13">
-        <v>1213.3599999999999</v>
+        <v>3343.12</v>
       </c>
       <c r="L51" s="14">
-        <v>6.3467206009823753</v>
+        <v>19.035043668122274</v>
       </c>
       <c r="M51" s="30">
-        <v>3625.8095238095234</v>
+        <v>3330.9090909090905</v>
       </c>
       <c r="N51" s="15">
-        <v>-602.09523809523807</v>
+        <v>1367.9504132231407</v>
       </c>
       <c r="O51" s="16">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="P51" s="17">
-        <v>266.79999999999995</v>
+        <v>255.2</v>
       </c>
       <c r="Q51" s="14">
-        <v>17.627737226277372</v>
+        <v>18.486111111111111</v>
       </c>
       <c r="R51" s="16">
-        <v>287.04761904761904</v>
+        <v>261.81818181818181</v>
       </c>
       <c r="S51" s="15">
-        <v>-30.952380952380963</v>
+        <v>-18.016528925619809</v>
       </c>
       <c r="T51" s="18">
-        <v>391</v>
+        <v>271</v>
       </c>
       <c r="U51" s="17">
-        <v>453.55999999999995</v>
+        <v>314.35999999999996</v>
       </c>
       <c r="V51" s="14">
-        <v>11.388349514563107</v>
+        <v>7.8260143198090688</v>
       </c>
       <c r="W51" s="16">
-        <v>755.33333333333337</v>
+        <v>761.81818181818187</v>
       </c>
       <c r="X51" s="15">
-        <v>-158.33333333333337</v>
+        <v>-283.04958677685954</v>
       </c>
       <c r="Y51" s="18">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="Z51" s="17">
-        <v>102.08</v>
+        <v>52.199999999999996</v>
       </c>
       <c r="AA51" s="14">
-        <v>16.648648648648649</v>
+        <v>8.3769230769230756</v>
       </c>
       <c r="AB51" s="16">
-        <v>116.28571428571428</v>
+        <v>118.18181818181819</v>
       </c>
       <c r="AC51" s="15">
-        <v>-28.285714285714278</v>
+        <v>-73.181818181818187</v>
       </c>
       <c r="AD51" s="19">
-        <v>2689</v>
+        <v>3773</v>
       </c>
       <c r="AE51" s="20">
-        <v>3119.24</v>
+        <v>4376.6799999999994</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6671,85 +6671,85 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>1761</v>
+        <v>1451</v>
       </c>
       <c r="F52" s="14">
-        <v>1426.41</v>
+        <v>1175.3100000000002</v>
       </c>
       <c r="G52" s="14">
-        <v>11.250684514755097</v>
+        <v>8.9622766717713116</v>
       </c>
       <c r="H52" s="30">
-        <v>3443.5238095238092</v>
+        <v>3561.818181818182</v>
       </c>
       <c r="I52" s="15">
-        <v>195.76190476190482</v>
+        <v>-168.00826446281008</v>
       </c>
       <c r="J52" s="16">
-        <v>3733</v>
+        <v>5811</v>
       </c>
       <c r="K52" s="13">
-        <v>3023.73</v>
+        <v>4706.9100000000008</v>
       </c>
       <c r="L52" s="14">
-        <v>68.947229551451187</v>
+        <v>118.2726661059714</v>
       </c>
       <c r="M52" s="30">
-        <v>1191.1428571428571</v>
+        <v>1080.909090909091</v>
       </c>
       <c r="N52" s="15">
-        <v>3191.5714285714284</v>
+        <v>5319.6776859504134</v>
       </c>
       <c r="O52" s="16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P52" s="17">
-        <v>8.1000000000000014</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="Q52" s="14">
-        <v>0.8366533864541833</v>
+        <v>0.54382022471910108</v>
       </c>
       <c r="R52" s="16">
-        <v>262.95238095238096</v>
+        <v>242.72727272727275</v>
       </c>
       <c r="S52" s="15">
-        <v>-229.04761904761904</v>
+        <v>-214.6611570247934</v>
       </c>
       <c r="T52" s="18">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="U52" s="17">
-        <v>189.54000000000002</v>
+        <v>165.24</v>
       </c>
       <c r="V52" s="14">
-        <v>9.4137931034482758</v>
+        <v>8.9434782608695649</v>
       </c>
       <c r="W52" s="16">
-        <v>546.85714285714289</v>
+        <v>501.81818181818181</v>
       </c>
       <c r="X52" s="15">
-        <v>-163.71428571428572</v>
+        <v>-160.95867768595042</v>
       </c>
       <c r="Y52" s="18">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="Z52" s="17">
-        <v>74.52000000000001</v>
+        <v>49.410000000000004</v>
       </c>
       <c r="AA52" s="14">
-        <v>37.882352941176471</v>
+        <v>20.221917808219175</v>
       </c>
       <c r="AB52" s="16">
-        <v>53.428571428571423</v>
+        <v>66.363636363636374</v>
       </c>
       <c r="AC52" s="15">
-        <v>38.571428571428577</v>
+        <v>-5.363636363636374</v>
       </c>
       <c r="AD52" s="19">
-        <v>5830</v>
+        <v>7533</v>
       </c>
       <c r="AE52" s="20">
-        <v>4722.3</v>
+        <v>6101.7300000000005</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6784,85 +6784,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>78</v>
+        <v>2256</v>
       </c>
       <c r="F53" s="14">
-        <v>63.180000000000007</v>
+        <v>1827.3600000000001</v>
       </c>
       <c r="G53" s="14">
-        <v>0.28762071992976296</v>
+        <v>8.700430278884463</v>
       </c>
       <c r="H53" s="30">
-        <v>5966.1904761904761</v>
+        <v>5704.545454545455</v>
       </c>
       <c r="I53" s="15">
-        <v>-2633.9047619047619</v>
+        <v>-336.97520661157023</v>
       </c>
       <c r="J53" s="16">
-        <v>9886</v>
+        <v>7787</v>
       </c>
       <c r="K53" s="13">
-        <v>8007.6600000000008</v>
+        <v>6307.47</v>
       </c>
       <c r="L53" s="14">
-        <v>80.002312138728328</v>
+        <v>70.525973053892216</v>
       </c>
       <c r="M53" s="30">
-        <v>2718.5714285714284</v>
+        <v>2429.090909090909</v>
       </c>
       <c r="N53" s="15">
-        <v>8650.2857142857138</v>
+        <v>6682.8677685950415</v>
       </c>
       <c r="O53" s="16">
-        <v>388</v>
+        <v>327</v>
       </c>
       <c r="P53" s="17">
-        <v>314.28000000000003</v>
+        <v>264.87</v>
       </c>
       <c r="Q53" s="14">
-        <v>12.535384615384615</v>
+        <v>10.622013422818791</v>
       </c>
       <c r="R53" s="16">
-        <v>680.95238095238096</v>
+        <v>677.27272727272737</v>
       </c>
       <c r="S53" s="15">
-        <v>-231.04761904761904</v>
+        <v>-288.70247933884298</v>
       </c>
       <c r="T53" s="18">
-        <v>592</v>
+        <v>497</v>
       </c>
       <c r="U53" s="17">
-        <v>479.52000000000004</v>
+        <v>402.57000000000005</v>
       </c>
       <c r="V53" s="14">
-        <v>10.607508532423209</v>
+        <v>9.5379857256145897</v>
       </c>
       <c r="W53" s="16">
-        <v>1227.8095238095239</v>
+        <v>1146.3636363636365</v>
       </c>
       <c r="X53" s="15">
-        <v>-300.95238095238096</v>
+        <v>-336.7190082644629</v>
       </c>
       <c r="Y53" s="18">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="Z53" s="17">
-        <v>167.67000000000002</v>
+        <v>147.42000000000002</v>
       </c>
       <c r="AA53" s="14">
-        <v>28.598684210526315</v>
+        <v>25.312643678160917</v>
       </c>
       <c r="AB53" s="16">
-        <v>159.23809523809524</v>
+        <v>158.18181818181819</v>
       </c>
       <c r="AC53" s="15">
-        <v>47.761904761904759</v>
+        <v>23.818181818181813</v>
       </c>
       <c r="AD53" s="19">
-        <v>11151</v>
+        <v>11049</v>
       </c>
       <c r="AE53" s="20">
-        <v>9032.3100000000013</v>
+        <v>8949.69</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6897,85 +6897,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>2994</v>
+        <v>2772</v>
       </c>
       <c r="F54" s="14">
-        <v>2425.1400000000003</v>
+        <v>2245.3200000000002</v>
       </c>
       <c r="G54" s="14">
-        <v>16.084420567920183</v>
+        <v>14.31549295774648</v>
       </c>
       <c r="H54" s="30">
-        <v>4095.1428571428569</v>
+        <v>4260</v>
       </c>
       <c r="I54" s="15">
-        <v>1132.5714285714287</v>
+        <v>835.63636363636374</v>
       </c>
       <c r="J54" s="16">
-        <v>1955</v>
+        <v>1843</v>
       </c>
       <c r="K54" s="13">
-        <v>1583.5500000000002</v>
+        <v>1492.8300000000002</v>
       </c>
       <c r="L54" s="14">
-        <v>31.899766899766899</v>
+        <v>34.574108527131784</v>
       </c>
       <c r="M54" s="30">
-        <v>1348.2857142857142</v>
+        <v>1172.7272727272727</v>
       </c>
       <c r="N54" s="15">
-        <v>1342.1428571428571</v>
+        <v>1309.9421487603306</v>
       </c>
       <c r="O54" s="16">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="P54" s="17">
-        <v>154.71</v>
+        <v>104.49000000000001</v>
       </c>
       <c r="Q54" s="14">
-        <v>15.309160305343511</v>
+        <v>9.403012048192771</v>
       </c>
       <c r="R54" s="16">
-        <v>274.47619047619048</v>
+        <v>301.81818181818181</v>
       </c>
       <c r="S54" s="15">
-        <v>-58.523809523809518</v>
+        <v>-145.38016528925618</v>
       </c>
       <c r="T54" s="18">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="U54" s="17">
-        <v>336.96000000000004</v>
+        <v>324.81</v>
       </c>
       <c r="V54" s="14">
-        <v>18.626865671641792</v>
+        <v>20.05</v>
       </c>
       <c r="W54" s="16">
-        <v>491.33333333333331</v>
+        <v>440</v>
       </c>
       <c r="X54" s="15">
-        <v>58.666666666666686</v>
+        <v>81</v>
       </c>
       <c r="Y54" s="18">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="Z54" s="17">
-        <v>144.18</v>
+        <v>138.51000000000002</v>
       </c>
       <c r="AA54" s="14">
-        <v>19.570680628272253</v>
+        <v>21.221538461538465</v>
       </c>
       <c r="AB54" s="16">
-        <v>200.09523809523807</v>
+        <v>177.27272727272725</v>
       </c>
       <c r="AC54" s="15">
-        <v>-22.095238095238074</v>
+        <v>-6.2727272727272236</v>
       </c>
       <c r="AD54" s="19">
-        <v>5734</v>
+        <v>5316</v>
       </c>
       <c r="AE54" s="20">
-        <v>4644.54</v>
+        <v>4305.96</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7010,85 +7010,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>1832</v>
+        <v>1577</v>
       </c>
       <c r="F55" s="14">
-        <v>1483.92</v>
+        <v>1277.3700000000001</v>
       </c>
       <c r="G55" s="14">
-        <v>11.216326530612244</v>
+        <v>9.6591748924322935</v>
       </c>
       <c r="H55" s="30">
-        <v>3593.3333333333335</v>
+        <v>3591.818181818182</v>
       </c>
       <c r="I55" s="15">
-        <v>198.66666666666652</v>
+        <v>-55.644628099173815</v>
       </c>
       <c r="J55" s="16">
-        <v>6135</v>
+        <v>6017</v>
       </c>
       <c r="K55" s="13">
-        <v>4969.3500000000004</v>
+        <v>4873.7700000000004</v>
       </c>
       <c r="L55" s="14">
-        <v>83.713450292397653</v>
+        <v>93.280845611787328</v>
       </c>
       <c r="M55" s="30">
-        <v>1612.2857142857144</v>
+        <v>1419.090909090909</v>
       </c>
       <c r="N55" s="15">
-        <v>5402.1428571428569</v>
+        <v>5371.9586776859505</v>
       </c>
       <c r="O55" s="16">
-        <v>289</v>
+        <v>238</v>
       </c>
       <c r="P55" s="17">
-        <v>234.09</v>
+        <v>192.78</v>
       </c>
       <c r="Q55" s="14">
-        <v>16.905292479108635</v>
+        <v>13.210091743119266</v>
       </c>
       <c r="R55" s="16">
-        <v>376.09523809523807</v>
+        <v>396.36363636363632</v>
       </c>
       <c r="S55" s="15">
-        <v>-52.904761904761926</v>
+        <v>-122.3305785123967</v>
       </c>
       <c r="T55" s="18">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="U55" s="17">
-        <v>324.81</v>
+        <v>300.51000000000005</v>
       </c>
       <c r="V55" s="14">
-        <v>15.918714555765597</v>
+        <v>16.06118067978533</v>
       </c>
       <c r="W55" s="16">
-        <v>554.19047619047615</v>
+        <v>508.18181818181819</v>
       </c>
       <c r="X55" s="15">
-        <v>-2.0476190476190368</v>
+        <v>1.4132231404958588</v>
       </c>
       <c r="Y55" s="18">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="Z55" s="17">
-        <v>157.14000000000001</v>
+        <v>151.47</v>
       </c>
       <c r="AA55" s="14">
-        <v>21.21875</v>
+        <v>23.088775510204083</v>
       </c>
       <c r="AB55" s="16">
-        <v>201.14285714285714</v>
+        <v>178.18181818181816</v>
       </c>
       <c r="AC55" s="15">
-        <v>-7.1428571428571388</v>
+        <v>8.8181818181818414</v>
       </c>
       <c r="AD55" s="19">
-        <v>8851</v>
+        <v>8390</v>
       </c>
       <c r="AE55" s="20">
-        <v>7169.31</v>
+        <v>6795.9000000000005</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7123,34 +7123,34 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="F56" s="14">
-        <v>935.34</v>
+        <v>867.22</v>
       </c>
       <c r="G56" s="14">
-        <v>12.37128712871287</v>
+        <v>10.088413098236776</v>
       </c>
       <c r="H56" s="30">
-        <v>634.85714285714289</v>
+        <v>721.81818181818187</v>
       </c>
       <c r="I56" s="15">
-        <v>68.428571428571445</v>
+        <v>2.9008264462809734</v>
       </c>
       <c r="J56" s="32">
-        <v>10</v>
+        <v>261</v>
       </c>
       <c r="K56" s="13">
-        <v>26.200000000000003</v>
+        <v>683.82</v>
       </c>
       <c r="L56" s="14">
-        <v>0.70945945945945943</v>
+        <v>21.338513513513512</v>
       </c>
       <c r="M56" s="30">
-        <v>310.09523809523807</v>
+        <v>269.09090909090912</v>
       </c>
       <c r="N56" s="15">
-        <v>-130.95238095238096</v>
+        <v>138.68595041322311</v>
       </c>
       <c r="O56" s="32">
         <v>42</v>
@@ -7159,49 +7159,49 @@
         <v>110.04</v>
       </c>
       <c r="Q56" s="14">
-        <v>14.7</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="R56" s="16">
-        <v>62.857142857142861</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="S56" s="15">
-        <v>-15.142857142857146</v>
+        <v>-7.5867768595041269</v>
       </c>
       <c r="T56" s="18">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="U56" s="17">
-        <v>267.24</v>
+        <v>243.66</v>
       </c>
       <c r="V56" s="14">
-        <v>14.571428571428571</v>
+        <v>14.426923076923078</v>
       </c>
       <c r="W56" s="16">
-        <v>154</v>
+        <v>141.81818181818181</v>
       </c>
       <c r="X56" s="15">
-        <v>-10</v>
+        <v>-10.140495867768593</v>
       </c>
       <c r="Y56" s="18">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Z56" s="17">
-        <v>102.18</v>
+        <v>94.320000000000007</v>
       </c>
       <c r="AA56" s="14">
-        <v>22.135135135135137</v>
+        <v>20.260465116279068</v>
       </c>
       <c r="AB56" s="16">
-        <v>38.761904761904759</v>
+        <v>39.090909090909093</v>
       </c>
       <c r="AC56" s="15">
-        <v>0.2380952380952408</v>
+        <v>-3.0909090909090935</v>
       </c>
       <c r="AD56" s="19">
-        <v>550</v>
+        <v>763</v>
       </c>
       <c r="AE56" s="20">
-        <v>1441</v>
+        <v>1999.0600000000002</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7236,34 +7236,34 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="F57" s="14">
-        <v>314.40000000000003</v>
+        <v>136.24</v>
       </c>
       <c r="G57" s="14">
-        <v>1.9236641221374047</v>
+        <v>0.93561338289962825</v>
       </c>
       <c r="H57" s="30">
-        <v>1372.3809523809523</v>
+        <v>1222.7272727272727</v>
       </c>
       <c r="I57" s="15">
-        <v>-503.80952380952385</v>
+        <v>-503.78512396694214</v>
       </c>
       <c r="J57" s="32">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="K57" s="13">
-        <v>0</v>
+        <v>678.58</v>
       </c>
       <c r="L57" s="14">
-        <v>0</v>
+        <v>11.132859680284191</v>
       </c>
       <c r="M57" s="30">
-        <v>589.80952380952385</v>
+        <v>511.81818181818181</v>
       </c>
       <c r="N57" s="15">
-        <v>-268.09523809523807</v>
+        <v>26.355371900826469</v>
       </c>
       <c r="O57" s="32">
         <v>69</v>
@@ -7272,49 +7272,49 @@
         <v>180.78</v>
       </c>
       <c r="Q57" s="14">
-        <v>9.9246575342465757</v>
+        <v>11.436986301369862</v>
       </c>
       <c r="R57" s="16">
-        <v>152.95238095238096</v>
+        <v>132.72727272727275</v>
       </c>
       <c r="S57" s="15">
-        <v>-70.047619047619037</v>
+        <v>-51.661157024793397</v>
       </c>
       <c r="T57" s="18">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="U57" s="17">
-        <v>78.600000000000009</v>
+        <v>10.48</v>
       </c>
       <c r="V57" s="14">
-        <v>1.4928909952606635</v>
+        <v>0.21607142857142858</v>
       </c>
       <c r="W57" s="16">
-        <v>442.09523809523807</v>
+        <v>407.27272727272725</v>
       </c>
       <c r="X57" s="15">
-        <v>-291.52380952380952</v>
+        <v>-292.198347107438</v>
       </c>
       <c r="Y57" s="18">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Z57" s="17">
-        <v>141.48000000000002</v>
+        <v>117.9</v>
       </c>
       <c r="AA57" s="14">
-        <v>29.842105263157894</v>
+        <v>24.75</v>
       </c>
       <c r="AB57" s="16">
-        <v>39.80952380952381</v>
+        <v>40</v>
       </c>
       <c r="AC57" s="15">
-        <v>14.19047619047619</v>
+        <v>5</v>
       </c>
       <c r="AD57" s="19">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="AE57" s="20">
-        <v>715.26</v>
+        <v>1123.98</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7349,85 +7349,85 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F58" s="14">
-        <v>110.04</v>
+        <v>47.160000000000004</v>
       </c>
       <c r="G58" s="14">
-        <v>1.785425101214575</v>
+        <v>0.84747081712062267</v>
       </c>
       <c r="H58" s="30">
-        <v>517.52380952380952</v>
+        <v>467.27272727272725</v>
       </c>
       <c r="I58" s="15">
-        <v>-193.23809523809521</v>
+        <v>-194.39669421487602</v>
       </c>
       <c r="J58" s="32">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="K58" s="13">
-        <v>57.64</v>
+        <v>424.44</v>
       </c>
       <c r="L58" s="14">
-        <v>2.2647058823529416</v>
+        <v>19.217647058823527</v>
       </c>
       <c r="M58" s="30">
-        <v>213.71428571428569</v>
+        <v>185.45454545454547</v>
       </c>
       <c r="N58" s="15">
-        <v>-75.142857142857139</v>
+        <v>77.702479338842963</v>
       </c>
       <c r="O58" s="32">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P58" s="17">
-        <v>55.02</v>
+        <v>34.06</v>
       </c>
       <c r="Q58" s="14">
-        <v>13.781250000000004</v>
+        <v>7.15</v>
       </c>
       <c r="R58" s="16">
-        <v>33.523809523809518</v>
+        <v>40</v>
       </c>
       <c r="S58" s="15">
-        <v>-9.4761904761904709</v>
+        <v>-23.36363636363636</v>
       </c>
       <c r="T58" s="18">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="U58" s="17">
-        <v>230.56</v>
+        <v>214.84</v>
       </c>
       <c r="V58" s="14">
-        <v>17.600000000000001</v>
+        <v>17.877477477477473</v>
       </c>
       <c r="W58" s="16">
-        <v>110</v>
+        <v>100.90909090909092</v>
       </c>
       <c r="X58" s="15">
-        <v>8</v>
+        <v>8.6115702479338694</v>
       </c>
       <c r="Y58" s="18">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Z58" s="17">
-        <v>94.320000000000007</v>
+        <v>102.18</v>
       </c>
       <c r="AA58" s="14">
-        <v>22.90909090909091</v>
+        <v>28.6</v>
       </c>
       <c r="AB58" s="16">
-        <v>34.571428571428569</v>
+        <v>30</v>
       </c>
       <c r="AC58" s="15">
-        <v>1.4285714285714306</v>
+        <v>9.0000000000000036</v>
       </c>
       <c r="AD58" s="19">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="AE58" s="20">
-        <v>547.58000000000004</v>
+        <v>822.68000000000006</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7465,34 +7465,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F59" s="14">
-        <v>322.26</v>
+        <v>269.86</v>
       </c>
       <c r="G59" s="14">
-        <v>4.1594202898550732</v>
+        <v>3.9377567140600314</v>
       </c>
       <c r="H59" s="30">
-        <v>650.57142857142856</v>
+        <v>575.4545454545455</v>
       </c>
       <c r="I59" s="15">
-        <v>-172.71428571428567</v>
+        <v>-158.57024793388427</v>
       </c>
       <c r="J59" s="32">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="K59" s="13">
-        <v>89.08</v>
+        <v>379.90000000000003</v>
       </c>
       <c r="L59" s="14">
-        <v>3.1315789473684208</v>
+        <v>14.620833333333335</v>
       </c>
       <c r="M59" s="30">
-        <v>238.85714285714286</v>
+        <v>218.18181818181816</v>
       </c>
       <c r="N59" s="15">
-        <v>-74.571428571428584</v>
+        <v>45.826446280991746</v>
       </c>
       <c r="O59" s="32">
         <v>20</v>
@@ -7501,49 +7501,49 @@
         <v>52.400000000000006</v>
       </c>
       <c r="Q59" s="14">
-        <v>6.0869565217391317</v>
+        <v>7.0144927536231885</v>
       </c>
       <c r="R59" s="16">
-        <v>72.285714285714278</v>
+        <v>62.727272727272727</v>
       </c>
       <c r="S59" s="15">
-        <v>-45.714285714285708</v>
+        <v>-37.024793388429757</v>
       </c>
       <c r="T59" s="18">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="U59" s="17">
-        <v>235.8</v>
+        <v>204.36</v>
       </c>
       <c r="V59" s="14">
-        <v>15.365853658536585</v>
+        <v>13.982222222222221</v>
       </c>
       <c r="W59" s="16">
-        <v>128.85714285714286</v>
+        <v>122.72727272727273</v>
       </c>
       <c r="X59" s="15">
-        <v>-3.7142857142857224</v>
+        <v>-11.256198347107443</v>
       </c>
       <c r="Y59" s="18">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Z59" s="17">
-        <v>123.14</v>
+        <v>115.28</v>
       </c>
       <c r="AA59" s="14">
-        <v>47</v>
+        <v>50.704761904761895</v>
       </c>
       <c r="AB59" s="16">
-        <v>22</v>
+        <v>19.090909090909093</v>
       </c>
       <c r="AC59" s="15">
-        <v>25</v>
+        <v>24.909090909090907</v>
       </c>
       <c r="AD59" s="19">
-        <v>314</v>
+        <v>390</v>
       </c>
       <c r="AE59" s="20">
-        <v>822.68000000000006</v>
+        <v>1021.8000000000001</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7617,10 +7617,10 @@
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7650,17 +7650,17 @@
       <c r="AG61" s="36"/>
     </row>
     <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>173788.32</v>
+        <v>144171.42999999996</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>35.136132855048153</v>
+        <v>29.570639273878474</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7698,11 +7698,11 @@
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>225699.41</v>
+        <v>270685.82000000007</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>45.63140063190658</v>
+        <v>55.519687498237367</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7740,11 +7740,11 @@
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>28810.92</v>
+        <v>25059.810000000005</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.8249272033711117</v>
+        <v>5.1399545789476653</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7782,11 +7782,11 @@
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>49655.54</v>
+        <v>35343.670000000006</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>10.039245735439284</v>
+        <v>7.2492512294911746</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7824,11 +7824,11 @@
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>16660.060000000001</v>
+        <v>12288.52</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>3.3682935742348712</v>
+        <v>2.5204674194453172</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7860,19 +7860,19 @@
       <c r="AG66" s="36"/>
     </row>
     <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>494614.25</v>
-      </c>
-      <c r="E67" s="66">
+        <v>487549.25000000006</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7972,17 +7972,17 @@
       <c r="AG69" s="36"/>
     </row>
     <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>128437</v>
+        <v>105856</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>34.915590593992114</v>
+        <v>29.926241720216101</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8019,11 +8019,11 @@
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>172485</v>
+        <v>196356</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>46.890036699741742</v>
+        <v>55.511233366221589</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8061,11 +8061,11 @@
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>20703</v>
+        <v>17998</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.6281092836754114</v>
+        <v>5.0881622060199652</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8103,11 +8103,11 @@
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>34859</v>
+        <v>25001</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>9.4764170178061704</v>
+        <v>7.0679599573677709</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8145,11 +8145,11 @@
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>11366</v>
+        <v>8512</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>3.0898464047845589</v>
+        <v>2.4064027501745717</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8181,19 +8181,19 @@
       <c r="AG74" s="36"/>
     </row>
     <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="65"/>
+      <c r="C75" s="68"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>367850</v>
-      </c>
-      <c r="E75" s="66">
+        <v>353723</v>
+      </c>
+      <c r="E75" s="69">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="66"/>
+      <c r="F75" s="69"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8740,6 +8740,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8748,17 +8759,6 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E05AE50-C45A-45E4-B9FD-B7CB5CD65286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0541FDD-7290-4684-8366-634006005792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -802,6 +802,12 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -810,12 +816,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1164,6 +1164,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INVENTARIO NACIONAL INICIO"/>
@@ -1332,7 +1333,13 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
+      <sheetData sheetId="24">
+        <row r="1">
+          <cell r="G1" t="str">
+            <v>DASHBOARD</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
@@ -1637,268 +1644,268 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2ADD65-CD71-49F6-BA3C-8A3390E00AC0}">
   <dimension ref="A1:AM93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="51" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="34"/>
-    <col min="3" max="3" width="35.42578125" style="48" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="51" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="34"/>
+    <col min="3" max="3" width="35.44140625" style="48" customWidth="1"/>
     <col min="4" max="4" width="11" style="48" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="53" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="53" customWidth="1"/>
     <col min="6" max="9" width="11" style="53" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="48" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="48" customWidth="1"/>
     <col min="11" max="14" width="11" style="48" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="48" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" style="48" customWidth="1"/>
     <col min="16" max="19" width="11" style="48" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" style="48" customWidth="1"/>
+    <col min="20" max="20" width="12.109375" style="48" customWidth="1"/>
     <col min="21" max="24" width="11" style="48" customWidth="1"/>
-    <col min="25" max="25" width="12.140625" style="48" customWidth="1"/>
+    <col min="25" max="25" width="12.109375" style="48" customWidth="1"/>
     <col min="26" max="29" width="11" style="48" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="48" customWidth="1"/>
+    <col min="30" max="30" width="13.44140625" style="48" customWidth="1"/>
     <col min="31" max="31" width="11" style="48" customWidth="1"/>
-    <col min="32" max="33" width="12.7109375" style="54" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" customWidth="1"/>
+    <col min="32" max="33" width="12.6640625" style="54" customWidth="1"/>
+    <col min="38" max="38" width="9.109375" customWidth="1"/>
     <col min="39" max="39" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="66" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="66"/>
-      <c r="AK1" s="66"/>
-      <c r="AL1" s="66"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="65"/>
-      <c r="AD2" s="65"/>
-      <c r="AE2" s="65"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
-    </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66"/>
-      <c r="AG3" s="66"/>
-      <c r="AH3" s="66"/>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="66"/>
-      <c r="AK3" s="66"/>
-      <c r="AL3" s="66"/>
-    </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="65"/>
-      <c r="AA4" s="65"/>
-      <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
-      <c r="AE4" s="65"/>
-      <c r="AF4" s="66"/>
-      <c r="AG4" s="66"/>
-      <c r="AH4" s="66"/>
-      <c r="AI4" s="66"/>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="66"/>
-      <c r="AL4" s="66"/>
-    </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="65"/>
-      <c r="AB5" s="65"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="65"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
-    </row>
-    <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="65"/>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="65"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="65"/>
-      <c r="AA6" s="65"/>
-      <c r="AB6" s="65"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="65"/>
-      <c r="AF6" s="66"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
-      <c r="AL6" s="66"/>
-    </row>
-    <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
+      <c r="AL1" s="68"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+    </row>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="67"/>
+      <c r="U3" s="67"/>
+      <c r="V3" s="67"/>
+      <c r="W3" s="67"/>
+      <c r="X3" s="67"/>
+      <c r="Y3" s="67"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
+    </row>
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
+      <c r="Y4" s="67"/>
+      <c r="Z4" s="67"/>
+      <c r="AA4" s="67"/>
+      <c r="AB4" s="67"/>
+      <c r="AC4" s="67"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="68"/>
+      <c r="AG4" s="68"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
+      <c r="Y5" s="67"/>
+      <c r="Z5" s="67"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="67"/>
+      <c r="AC5" s="67"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+    </row>
+    <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
+      <c r="AK6" s="68"/>
+      <c r="AL6" s="68"/>
+    </row>
+    <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1938,7 +1945,7 @@
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
     </row>
-    <row r="8" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1978,7 +1985,7 @@
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
     </row>
-    <row r="9" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -2018,7 +2025,7 @@
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
@@ -2058,7 +2065,7 @@
       <c r="AK10" s="5"/>
       <c r="AL10" s="5"/>
     </row>
-    <row r="11" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
@@ -2098,7 +2105,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" s="61" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" s="61" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A12" s="56"/>
       <c r="B12" s="57" t="str">
         <f>'[1]INVENTARIO NACIONAL 03-09-26'!B12</f>
@@ -2249,7 +2256,7 @@
         <v>Inventario de Cestas</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="56"/>
       <c r="B13" s="10" t="s">
         <v>20</v>
@@ -2261,85 +2268,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5490</v>
+        <v>5308</v>
       </c>
       <c r="F13" s="14">
-        <v>7466.4000000000005</v>
+        <v>7218.88</v>
       </c>
       <c r="G13" s="14">
-        <v>7.4497028148480435</v>
+        <v>7.5301334529550292</v>
       </c>
       <c r="H13" s="30">
-        <v>16212.727272727272</v>
+        <v>15507.826086956522</v>
       </c>
       <c r="I13" s="15">
-        <v>-1879.4214876033047</v>
+        <v>-1741.01185770751</v>
       </c>
       <c r="J13" s="16">
-        <v>5178</v>
+        <v>2539</v>
       </c>
       <c r="K13" s="13">
-        <v>7042.0800000000008</v>
+        <v>3453.0400000000004</v>
       </c>
       <c r="L13" s="14">
-        <v>24.951732377538825</v>
+        <v>12.7910593389088</v>
       </c>
       <c r="M13" s="30">
-        <v>4565.454545454546</v>
+        <v>4366.9565217391309</v>
       </c>
       <c r="N13" s="15">
-        <v>3102.7933884297518</v>
+        <v>554.01976284584975</v>
       </c>
       <c r="O13" s="16">
-        <v>792</v>
+        <v>696</v>
       </c>
       <c r="P13" s="17">
-        <v>1077.1200000000001</v>
+        <v>946.56000000000006</v>
       </c>
       <c r="Q13" s="14">
-        <v>19.82047569803516</v>
+        <v>18.209720785935886</v>
       </c>
       <c r="R13" s="16">
-        <v>879.09090909090901</v>
+        <v>840.86956521739125</v>
       </c>
       <c r="S13" s="15">
-        <v>-7.1735537190082823</v>
+        <v>-68.426877470355635</v>
       </c>
       <c r="T13" s="18">
-        <v>397</v>
+        <v>725</v>
       </c>
       <c r="U13" s="17">
-        <v>539.92000000000007</v>
+        <v>986.00000000000011</v>
       </c>
       <c r="V13" s="14">
-        <v>8.5171985815602831</v>
+        <v>16.261081560283689</v>
       </c>
       <c r="W13" s="16">
-        <v>1025.4545454545455</v>
+        <v>980.86956521739125</v>
       </c>
       <c r="X13" s="15">
-        <v>-348.78512396694214</v>
+        <v>11.640316205533622</v>
       </c>
       <c r="Y13" s="18">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="Z13" s="17">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="AA13" s="14">
-        <v>13.917456021650878</v>
+        <v>13.694181326116375</v>
       </c>
       <c r="AB13" s="16">
-        <v>671.81818181818187</v>
+        <v>642.60869565217388</v>
       </c>
       <c r="AC13" s="15">
-        <v>-246.81818181818187</v>
+        <v>-242.60869565217388</v>
       </c>
       <c r="AD13" s="19">
-        <v>12282</v>
+        <v>9668</v>
       </c>
       <c r="AE13" s="20">
-        <v>16703.52</v>
+        <v>13148.480000000001</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2363,7 +2370,7 @@
         <v>109.4</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="56"/>
       <c r="B14" s="10" t="s">
         <v>22</v>
@@ -2374,9 +2381,7 @@
       <c r="D14" s="12">
         <v>1.59</v>
       </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="14">
         <v>0</v>
       </c>
@@ -2384,25 +2389,25 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>427.27272727272725</v>
+        <v>408.69565217391306</v>
       </c>
       <c r="I14" s="15">
-        <v>-194.21487603305786</v>
+        <v>-185.77075098814231</v>
       </c>
       <c r="J14" s="16">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K14" s="13">
-        <v>36.57</v>
+        <v>31.8</v>
       </c>
       <c r="L14" s="14">
-        <v>2.2353413654618475</v>
+        <v>2.0321285140562253</v>
       </c>
       <c r="M14" s="30">
-        <v>226.36363636363637</v>
+        <v>216.52173913043475</v>
       </c>
       <c r="N14" s="15">
-        <v>-79.892561983471069</v>
+        <v>-78.418972332015798</v>
       </c>
       <c r="O14" s="16">
         <v>80</v>
@@ -2411,13 +2416,13 @@
         <v>127.2</v>
       </c>
       <c r="Q14" s="14">
-        <v>17.285714285714288</v>
+        <v>18.071428571428569</v>
       </c>
       <c r="R14" s="16">
-        <v>101.81818181818181</v>
+        <v>97.391304347826093</v>
       </c>
       <c r="S14" s="15">
-        <v>-12.56198347107437</v>
+        <v>-8.537549407114625</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2426,13 +2431,13 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>6.2740740740740737</v>
+        <v>6.5592592592592593</v>
       </c>
       <c r="W14" s="16">
-        <v>24.545454545454547</v>
+        <v>23.478260869565219</v>
       </c>
       <c r="X14" s="15">
-        <v>-10.851239669421489</v>
+        <v>-10.07509881422925</v>
       </c>
       <c r="Y14" s="18">
         <v>7</v>
@@ -2441,19 +2446,19 @@
         <v>11.13</v>
       </c>
       <c r="AA14" s="14">
-        <v>1.8822222222222225</v>
+        <v>1.9677777777777778</v>
       </c>
       <c r="AB14" s="16">
-        <v>81.818181818181813</v>
+        <v>78.260869565217391</v>
       </c>
       <c r="AC14" s="15">
-        <v>-74.818181818181813</v>
+        <v>-71.260869565217391</v>
       </c>
       <c r="AD14" s="19">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AE14" s="20">
-        <v>186.03</v>
+        <v>181.26000000000002</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2477,7 +2482,7 @@
         <v>8.1125000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="56"/>
       <c r="B15" s="10" t="s">
         <v>24</v>
@@ -2489,85 +2494,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2426</v>
+        <v>2236</v>
       </c>
       <c r="F15" s="14">
-        <v>4924.78</v>
+        <v>4539.08</v>
       </c>
       <c r="G15" s="14">
-        <v>7.8372980910425838</v>
+        <v>7.5518355359765055</v>
       </c>
       <c r="H15" s="30">
-        <v>6810</v>
+        <v>6513.913043478261</v>
       </c>
       <c r="I15" s="15">
-        <v>-669.4545454545455</v>
+        <v>-724.86956521739103</v>
       </c>
       <c r="J15" s="16">
-        <v>3098</v>
+        <v>2287</v>
       </c>
       <c r="K15" s="13">
-        <v>6288.94</v>
+        <v>4642.6099999999997</v>
       </c>
       <c r="L15" s="14">
-        <v>30.916123711340209</v>
+        <v>23.860247422680413</v>
       </c>
       <c r="M15" s="30">
-        <v>2204.5454545454545</v>
+        <v>2108.695652173913</v>
       </c>
       <c r="N15" s="15">
-        <v>2095.9338842975208</v>
+        <v>1328.501976284585</v>
       </c>
       <c r="O15" s="16">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="P15" s="17">
-        <v>265.92999999999995</v>
+        <v>207.05999999999997</v>
       </c>
       <c r="Q15" s="14">
-        <v>11.202120141342757</v>
+        <v>9.1187279151943468</v>
       </c>
       <c r="R15" s="16">
-        <v>257.27272727272725</v>
+        <v>246.08695652173913</v>
       </c>
       <c r="S15" s="15">
-        <v>-102.88429752066114</v>
+        <v>-121.71541501976284</v>
       </c>
       <c r="T15" s="18">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="U15" s="17">
-        <v>156.30999999999997</v>
+        <v>468.92999999999995</v>
       </c>
       <c r="V15" s="14">
-        <v>4.790231362467865</v>
+        <v>15.02390745501285</v>
       </c>
       <c r="W15" s="16">
-        <v>353.63636363636368</v>
+        <v>338.26086956521743</v>
       </c>
       <c r="X15" s="15">
-        <v>-180.19008264462815</v>
+        <v>-15.007905138339964</v>
       </c>
       <c r="Y15" s="18">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="Z15" s="17">
-        <v>355.24999999999994</v>
+        <v>320.73999999999995</v>
       </c>
       <c r="AA15" s="14">
-        <v>19.697674418604652</v>
+        <v>18.592558139534884</v>
       </c>
       <c r="AB15" s="16">
-        <v>195.45454545454547</v>
+        <v>186.95652173913044</v>
       </c>
       <c r="AC15" s="15">
-        <v>-20.454545454545439</v>
+        <v>-28.956521739130437</v>
       </c>
       <c r="AD15" s="19">
-        <v>5907</v>
+        <v>5014</v>
       </c>
       <c r="AE15" s="20">
-        <v>11991.21</v>
+        <v>10178.419999999998</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2591,7 +2596,7 @@
         <v>40.416666666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="10" t="s">
         <v>26</v>
       </c>
@@ -2602,85 +2607,85 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>279</v>
+        <v>357</v>
       </c>
       <c r="F16" s="14">
-        <v>1007.1899999999999</v>
+        <v>1288.77</v>
       </c>
       <c r="G16" s="14">
-        <v>3.9484210526315784</v>
+        <v>5.2819298245614039</v>
       </c>
       <c r="H16" s="30">
-        <v>1554.5454545454547</v>
+        <v>1486.9565217391303</v>
       </c>
       <c r="I16" s="15">
-        <v>-427.61157024793397</v>
+        <v>-318.88932806324112</v>
       </c>
       <c r="J16" s="16">
-        <v>489</v>
+        <v>261</v>
       </c>
       <c r="K16" s="13">
-        <v>1765.29</v>
+        <v>942.20999999999992</v>
       </c>
       <c r="L16" s="14">
-        <v>21.399276672694395</v>
+        <v>11.940867992766728</v>
       </c>
       <c r="M16" s="30">
-        <v>502.72727272727275</v>
+        <v>480.86956521739131</v>
       </c>
       <c r="N16" s="15">
-        <v>260.48760330578511</v>
+        <v>42.42292490118578</v>
       </c>
       <c r="O16" s="16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P16" s="17">
-        <v>122.74</v>
+        <v>108.3</v>
       </c>
       <c r="Q16" s="14">
-        <v>15.237037037037036</v>
+        <v>14.055555555555555</v>
       </c>
       <c r="R16" s="16">
-        <v>49.090909090909093</v>
+        <v>46.956521739130437</v>
       </c>
       <c r="S16" s="15">
-        <v>-10.628099173553721</v>
+        <v>-12.687747035573125</v>
       </c>
       <c r="T16" s="18">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U16" s="17">
-        <v>111.91</v>
+        <v>104.69</v>
       </c>
       <c r="V16" s="14">
-        <v>27.785185185185185</v>
+        <v>27.174074074074074</v>
       </c>
       <c r="W16" s="16">
-        <v>24.545454545454547</v>
+        <v>23.478260869565219</v>
       </c>
       <c r="X16" s="15">
-        <v>13.148760330578511</v>
+        <v>11.92490118577075</v>
       </c>
       <c r="Y16" s="18">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z16" s="17">
-        <v>234.65</v>
+        <v>231.04</v>
       </c>
       <c r="AA16" s="14">
-        <v>22.154929577464788</v>
+        <v>22.805633802816899</v>
       </c>
       <c r="AB16" s="16">
-        <v>64.545454545454547</v>
+        <v>61.739130434782609</v>
       </c>
       <c r="AC16" s="15">
-        <v>0.45454545454545325</v>
+        <v>2.2608695652173836</v>
       </c>
       <c r="AD16" s="19">
-        <v>898</v>
+        <v>741</v>
       </c>
       <c r="AE16" s="20">
-        <v>3241.7799999999997</v>
+        <v>2675.0099999999998</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2704,7 +2709,7 @@
         <v>24.678571428571427</v>
       </c>
     </row>
-    <row r="17" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="10" t="s">
         <v>28</v>
       </c>
@@ -2715,34 +2720,34 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F17" s="14">
-        <v>324.85999999999996</v>
+        <v>342.41999999999996</v>
       </c>
       <c r="G17" s="14">
-        <v>3.4571428571428573</v>
+        <v>3.8096525096525102</v>
       </c>
       <c r="H17" s="30">
-        <v>235.45454545454547</v>
+        <v>225.21739130434781</v>
       </c>
       <c r="I17" s="15">
-        <v>-70.024793388429757</v>
+        <v>-63.371541501976267</v>
       </c>
       <c r="J17" s="16">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K17" s="13">
-        <v>342.41999999999996</v>
+        <v>149.26</v>
       </c>
       <c r="L17" s="14">
-        <v>20.080851063829787</v>
+        <v>9.1510638297872315</v>
       </c>
       <c r="M17" s="30">
-        <v>42.727272727272727</v>
+        <v>40.869565217391312</v>
       </c>
       <c r="N17" s="15">
-        <v>19.578512396694215</v>
+        <v>-1.5770750988142339</v>
       </c>
       <c r="O17" s="16">
         <v>8</v>
@@ -2751,13 +2756,13 @@
         <v>70.239999999999995</v>
       </c>
       <c r="Q17" s="14">
-        <v>17.600000000000001</v>
+        <v>18.400000000000002</v>
       </c>
       <c r="R17" s="16">
-        <v>10</v>
+        <v>9.5652173913043477</v>
       </c>
       <c r="S17" s="15">
-        <v>-1.0909090909090899</v>
+        <v>-0.69565217391304301</v>
       </c>
       <c r="T17" s="18">
         <v>16</v>
@@ -2781,19 +2786,19 @@
         <v>52.679999999999993</v>
       </c>
       <c r="AA17" s="14">
-        <v>16.133333333333333</v>
+        <v>16.866666666666667</v>
       </c>
       <c r="AB17" s="16">
-        <v>8.1818181818181817</v>
+        <v>7.8260869565217392</v>
       </c>
       <c r="AC17" s="15">
-        <v>-2.1818181818181817</v>
+        <v>-1.8260869565217392</v>
       </c>
       <c r="AD17" s="19">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="AE17" s="20">
-        <v>930.68</v>
+        <v>755.07999999999993</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2817,7 +2822,7 @@
         <v>6.833333333333333</v>
       </c>
     </row>
-    <row r="18" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="10" t="s">
         <v>30</v>
       </c>
@@ -2828,85 +2833,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6166</v>
+        <v>6279</v>
       </c>
       <c r="F18" s="14">
-        <v>3884.58</v>
+        <v>3955.77</v>
       </c>
       <c r="G18" s="14">
-        <v>8.2742153709659529</v>
+        <v>8.8088444050127546</v>
       </c>
       <c r="H18" s="30">
-        <v>16394.545454545456</v>
+        <v>15681.739130434782</v>
       </c>
       <c r="I18" s="15">
-        <v>-1286.0661157024806</v>
+        <v>-849.06324110671903</v>
       </c>
       <c r="J18" s="16">
-        <v>10858</v>
+        <v>6907</v>
       </c>
       <c r="K18" s="13">
-        <v>6840.54</v>
+        <v>4351.41</v>
       </c>
       <c r="L18" s="14">
-        <v>35.194695954995979</v>
+        <v>23.405719260648269</v>
       </c>
       <c r="M18" s="30">
-        <v>6787.2727272727279</v>
+        <v>6492.1739130434789</v>
       </c>
       <c r="N18" s="15">
-        <v>7772.8760330578516</v>
+        <v>3956.0118577075095</v>
       </c>
       <c r="O18" s="16">
-        <v>834</v>
+        <v>716</v>
       </c>
       <c r="P18" s="17">
-        <v>525.41999999999996</v>
+        <v>451.08</v>
       </c>
       <c r="Q18" s="14">
-        <v>15.561141094834234</v>
+        <v>13.966692367000771</v>
       </c>
       <c r="R18" s="16">
-        <v>1179.090909090909</v>
+        <v>1127.8260869565217</v>
       </c>
       <c r="S18" s="15">
-        <v>-237.90082644628092</v>
+        <v>-309.296442687747</v>
       </c>
       <c r="T18" s="18">
-        <v>1187</v>
+        <v>2129</v>
       </c>
       <c r="U18" s="17">
-        <v>747.81000000000006</v>
+        <v>1341.27</v>
       </c>
       <c r="V18" s="14">
-        <v>7.6846976993044409</v>
+        <v>14.409764579989298</v>
       </c>
       <c r="W18" s="16">
-        <v>3398.181818181818</v>
+        <v>3250.4347826086955</v>
       </c>
       <c r="X18" s="15">
-        <v>-1284.404958677686</v>
+        <v>-234.9525691699605</v>
       </c>
       <c r="Y18" s="18">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="Z18" s="17">
-        <v>105.21</v>
+        <v>91.35</v>
       </c>
       <c r="AA18" s="14">
-        <v>9.8330900243309003</v>
+        <v>8.9257907542579069</v>
       </c>
       <c r="AB18" s="16">
-        <v>373.63636363636368</v>
+        <v>357.39130434782612</v>
       </c>
       <c r="AC18" s="15">
-        <v>-206.63636363636363</v>
+        <v>-212.39130434782612</v>
       </c>
       <c r="AD18" s="19">
-        <v>19212</v>
+        <v>16176</v>
       </c>
       <c r="AE18" s="20">
-        <v>12103.56</v>
+        <v>10190.879999999999</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2930,7 +2935,7 @@
         <v>235.45</v>
       </c>
     </row>
-    <row r="19" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="10" t="s">
         <v>32</v>
       </c>
@@ -2941,85 +2946,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>339</v>
+        <v>514</v>
       </c>
       <c r="F19" s="14">
-        <v>213.57</v>
+        <v>323.82</v>
       </c>
       <c r="G19" s="14">
-        <v>5.753015427769987</v>
+        <v>9.1193548387096772</v>
       </c>
       <c r="H19" s="30">
-        <v>1296.3636363636363</v>
+        <v>1240</v>
       </c>
       <c r="I19" s="15">
-        <v>-250.25619834710733</v>
+        <v>-49.636363636363626</v>
       </c>
       <c r="J19" s="16">
-        <v>1160</v>
+        <v>441</v>
       </c>
       <c r="K19" s="13">
-        <v>730.8</v>
+        <v>277.83</v>
       </c>
       <c r="L19" s="14">
-        <v>23.709459459459456</v>
+        <v>9.4233952702702695</v>
       </c>
       <c r="M19" s="30">
-        <v>1076.3636363636365</v>
+        <v>1029.5652173913045</v>
       </c>
       <c r="N19" s="15">
-        <v>670.74380165289244</v>
+        <v>-26.984189723320242</v>
       </c>
       <c r="O19" s="16">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="P19" s="17">
-        <v>73.709999999999994</v>
+        <v>57.33</v>
       </c>
       <c r="Q19" s="14">
-        <v>28.033663366336633</v>
+        <v>22.795049504950498</v>
       </c>
       <c r="R19" s="16">
-        <v>91.818181818181813</v>
+        <v>87.826086956521735</v>
       </c>
       <c r="S19" s="15">
-        <v>33.528925619834709</v>
+        <v>11.158102766798422</v>
       </c>
       <c r="T19" s="18">
-        <v>42</v>
+        <v>270</v>
       </c>
       <c r="U19" s="17">
-        <v>26.46</v>
+        <v>170.1</v>
       </c>
       <c r="V19" s="14">
-        <v>2.6607329842931939</v>
+        <v>17.88219895287958</v>
       </c>
       <c r="W19" s="16">
-        <v>347.27272727272725</v>
+        <v>332.17391304347825</v>
       </c>
       <c r="X19" s="15">
-        <v>-210.56198347107437</v>
+        <v>28.418972332015812</v>
       </c>
       <c r="Y19" s="18">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="Z19" s="17">
-        <v>131.66999999999999</v>
+        <v>121.59</v>
       </c>
       <c r="AA19" s="14">
-        <v>23.524651162790697</v>
+        <v>22.711162790697674</v>
       </c>
       <c r="AB19" s="16">
-        <v>195.45454545454547</v>
+        <v>186.95652173913044</v>
       </c>
       <c r="AC19" s="15">
-        <v>13.545454545454561</v>
+        <v>6.0434782608695627</v>
       </c>
       <c r="AD19" s="19">
-        <v>1867</v>
+        <v>1509</v>
       </c>
       <c r="AE19" s="20">
-        <v>1176.21</v>
+        <v>950.67</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3043,7 +3048,7 @@
         <v>29.683333333333334</v>
       </c>
     </row>
-    <row r="20" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="10" t="s">
         <v>34</v>
       </c>
@@ -3054,34 +3059,34 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1266</v>
+        <v>1387</v>
       </c>
       <c r="F20" s="14">
-        <v>797.58</v>
+        <v>873.81000000000006</v>
       </c>
       <c r="G20" s="14">
-        <v>9.9893055102706239</v>
+        <v>11.441506358004565</v>
       </c>
       <c r="H20" s="30">
-        <v>2788.181818181818</v>
+        <v>2666.9565217391305</v>
       </c>
       <c r="I20" s="15">
-        <v>-1.3553719008264125</v>
+        <v>174.7470355731225</v>
       </c>
       <c r="J20" s="16">
-        <v>2334</v>
+        <v>846</v>
       </c>
       <c r="K20" s="13">
-        <v>1470.42</v>
+        <v>532.98</v>
       </c>
       <c r="L20" s="14">
-        <v>20.100640569395019</v>
+        <v>7.6170106761565828</v>
       </c>
       <c r="M20" s="30">
-        <v>2554.5454545454545</v>
+        <v>2443.4782608695655</v>
       </c>
       <c r="N20" s="15">
-        <v>1172.8429752066118</v>
+        <v>-264.67193675889348</v>
       </c>
       <c r="O20" s="16">
         <v>197</v>
@@ -3090,49 +3095,49 @@
         <v>124.11</v>
       </c>
       <c r="Q20" s="14">
-        <v>23.484729064039414</v>
+        <v>24.552216748768476</v>
       </c>
       <c r="R20" s="16">
-        <v>184.54545454545453</v>
+        <v>176.52173913043475</v>
       </c>
       <c r="S20" s="15">
-        <v>29.2314049586777</v>
+        <v>36.525691699604749</v>
       </c>
       <c r="T20" s="18">
-        <v>137</v>
+        <v>596</v>
       </c>
       <c r="U20" s="17">
-        <v>86.31</v>
+        <v>375.48</v>
       </c>
       <c r="V20" s="14">
-        <v>3.87766081871345</v>
+        <v>17.636023391812866</v>
       </c>
       <c r="W20" s="16">
-        <v>777.27272727272737</v>
+        <v>743.47826086956513</v>
       </c>
       <c r="X20" s="15">
-        <v>-428.28925619834718</v>
+        <v>55.288537549407124</v>
       </c>
       <c r="Y20" s="18">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="Z20" s="17">
-        <v>110.88</v>
+        <v>97.02</v>
       </c>
       <c r="AA20" s="14">
-        <v>12.134472934472933</v>
+        <v>11.100284900284901</v>
       </c>
       <c r="AB20" s="16">
-        <v>319.09090909090912</v>
+        <v>305.21739130434781</v>
       </c>
       <c r="AC20" s="15">
-        <v>-143.09090909090912</v>
+        <v>-151.21739130434781</v>
       </c>
       <c r="AD20" s="19">
-        <v>4110</v>
+        <v>3180</v>
       </c>
       <c r="AE20" s="20">
-        <v>2589.3000000000002</v>
+        <v>2003.4</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3156,7 +3161,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="21" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10" t="s">
         <v>36</v>
       </c>
@@ -3167,85 +3172,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>1943</v>
+        <v>2348</v>
       </c>
       <c r="F21" s="14">
-        <v>2117.8700000000003</v>
+        <v>2559.3200000000002</v>
       </c>
       <c r="G21" s="14">
-        <v>6.7811652725699441</v>
+        <v>8.5671185462936261</v>
       </c>
       <c r="H21" s="30">
-        <v>6303.636363636364</v>
+        <v>6029.565217391304</v>
       </c>
       <c r="I21" s="15">
-        <v>-922.28925619834763</v>
+        <v>-392.71146245059253</v>
       </c>
       <c r="J21" s="16">
-        <v>5316</v>
+        <v>1864</v>
       </c>
       <c r="K21" s="13">
-        <v>5794.4400000000005</v>
+        <v>2031.7600000000002</v>
       </c>
       <c r="L21" s="14">
-        <v>16.896138691883376</v>
+        <v>6.1937483582873654</v>
       </c>
       <c r="M21" s="30">
-        <v>6921.8181818181811</v>
+        <v>6620.869565217391</v>
       </c>
       <c r="N21" s="15">
-        <v>2169.7190082644634</v>
+        <v>-1145.486166007905</v>
       </c>
       <c r="O21" s="16">
-        <v>407</v>
+        <v>343</v>
       </c>
       <c r="P21" s="17">
-        <v>443.63000000000005</v>
+        <v>373.87</v>
       </c>
       <c r="Q21" s="14">
-        <v>15.413771517996867</v>
+        <v>13.580438184663535</v>
       </c>
       <c r="R21" s="16">
-        <v>580.90909090909099</v>
+        <v>555.6521739130435</v>
       </c>
       <c r="S21" s="15">
-        <v>-121.09917355371908</v>
+        <v>-162.13833992094868</v>
       </c>
       <c r="T21" s="18">
-        <v>390</v>
+        <v>1135</v>
       </c>
       <c r="U21" s="17">
-        <v>425.1</v>
+        <v>1237.1500000000001</v>
       </c>
       <c r="V21" s="14">
-        <v>4.4985700667302195</v>
+        <v>13.687082936129647</v>
       </c>
       <c r="W21" s="16">
-        <v>1907.2727272727273</v>
+        <v>1824.3478260869565</v>
       </c>
       <c r="X21" s="15">
-        <v>-997.10743801652893</v>
+        <v>-191.798418972332</v>
       </c>
       <c r="Y21" s="18">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="Z21" s="17">
-        <v>248.52</v>
+        <v>232.17000000000002</v>
       </c>
       <c r="AA21" s="14">
-        <v>11.518997912317328</v>
+        <v>11.250313152400835</v>
       </c>
       <c r="AB21" s="16">
-        <v>435.4545454545455</v>
+        <v>416.52173913043475</v>
       </c>
       <c r="AC21" s="15">
-        <v>-207.4545454545455</v>
+        <v>-203.52173913043475</v>
       </c>
       <c r="AD21" s="19">
-        <v>8284</v>
+        <v>5903</v>
       </c>
       <c r="AE21" s="20">
-        <v>9029.5600000000013</v>
+        <v>6434.27</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3269,7 +3274,7 @@
         <v>117.87037037037037</v>
       </c>
     </row>
-    <row r="22" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
         <v>38</v>
       </c>
@@ -3280,85 +3285,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1256</v>
+        <v>1646</v>
       </c>
       <c r="F22" s="14">
-        <v>1369.0400000000002</v>
+        <v>1794.14</v>
       </c>
       <c r="G22" s="14">
-        <v>6.9379593700068485</v>
+        <v>9.5055466788404477</v>
       </c>
       <c r="H22" s="30">
-        <v>3982.7272727272725</v>
+        <v>3809.5652173913045</v>
       </c>
       <c r="I22" s="15">
-        <v>-554.33057851239641</v>
+        <v>-85.620553359683754</v>
       </c>
       <c r="J22" s="16">
-        <v>3721</v>
+        <v>2361</v>
       </c>
       <c r="K22" s="13">
-        <v>4055.8900000000003</v>
+        <v>2573.4900000000002</v>
       </c>
       <c r="L22" s="14">
-        <v>26.856009543692217</v>
+        <v>17.814882195049208</v>
       </c>
       <c r="M22" s="30">
-        <v>3048.181818181818</v>
+        <v>2915.652173913044</v>
       </c>
       <c r="N22" s="15">
-        <v>2335.4628099173551</v>
+        <v>1035.7035573122528</v>
       </c>
       <c r="O22" s="16">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="P22" s="17">
-        <v>94.830000000000013</v>
+        <v>73.03</v>
       </c>
       <c r="Q22" s="14">
-        <v>12.030857142857142</v>
+        <v>9.6862857142857148</v>
       </c>
       <c r="R22" s="16">
-        <v>159.09090909090909</v>
+        <v>152.17391304347825</v>
       </c>
       <c r="S22" s="15">
-        <v>-57.628099173553721</v>
+        <v>-71.339920948616594</v>
       </c>
       <c r="T22" s="18">
-        <v>177</v>
+        <v>355</v>
       </c>
       <c r="U22" s="17">
-        <v>192.93</v>
+        <v>386.95000000000005</v>
       </c>
       <c r="V22" s="14">
-        <v>6.9876019575856443</v>
+        <v>14.651712887438828</v>
       </c>
       <c r="W22" s="16">
-        <v>557.27272727272725</v>
+        <v>533.04347826086951</v>
       </c>
       <c r="X22" s="15">
-        <v>-228.28925619834712</v>
+        <v>-32.667984189723256</v>
       </c>
       <c r="Y22" s="18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22" s="17">
-        <v>7.6300000000000008</v>
+        <v>5.45</v>
       </c>
       <c r="AA22" s="14">
-        <v>0.93076923076923068</v>
+        <v>0.69505494505494514</v>
       </c>
       <c r="AB22" s="16">
-        <v>165.45454545454547</v>
+        <v>158.26086956521738</v>
       </c>
       <c r="AC22" s="15">
-        <v>-158.45454545454547</v>
+        <v>-153.26086956521738</v>
       </c>
       <c r="AD22" s="19">
-        <v>5248</v>
+        <v>4434</v>
       </c>
       <c r="AE22" s="20">
-        <v>5720.3200000000006</v>
+        <v>4833.0600000000004</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3382,7 +3387,7 @@
         <v>50.092592592592595</v>
       </c>
     </row>
-    <row r="23" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="10" t="s">
         <v>40</v>
       </c>
@@ -3393,85 +3398,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>18126</v>
+        <v>20089</v>
       </c>
       <c r="F23" s="14">
-        <v>21026.16</v>
+        <v>23303.239999999998</v>
       </c>
       <c r="G23" s="14">
-        <v>12.087996031746032</v>
+        <v>14.006054343033512</v>
       </c>
       <c r="H23" s="30">
-        <v>32989.090909090912</v>
+        <v>31554.782608695648</v>
       </c>
       <c r="I23" s="15">
-        <v>-4366.5619834710742</v>
+        <v>-1425.6245059288522</v>
       </c>
       <c r="J23" s="16">
-        <v>19463</v>
+        <v>10065</v>
       </c>
       <c r="K23" s="13">
-        <v>22577.079999999998</v>
+        <v>11675.4</v>
       </c>
       <c r="L23" s="14">
-        <v>22.186848179377265</v>
+        <v>11.995124593716142</v>
       </c>
       <c r="M23" s="30">
-        <v>19299.090909090912</v>
+        <v>18460</v>
       </c>
       <c r="N23" s="15">
-        <v>10690.685950413223</v>
+        <v>1674.0909090909081</v>
       </c>
       <c r="O23" s="16">
-        <v>1945</v>
+        <v>1747</v>
       </c>
       <c r="P23" s="17">
-        <v>2256.1999999999998</v>
+        <v>2026.5199999999998</v>
       </c>
       <c r="Q23" s="14">
-        <v>13.851971748087108</v>
+        <v>13.007386698057681</v>
       </c>
       <c r="R23" s="16">
-        <v>3089.0909090909095</v>
+        <v>2954.782608695652</v>
       </c>
       <c r="S23" s="15">
-        <v>-863.26446280991786</v>
+        <v>-939.16600790513803</v>
       </c>
       <c r="T23" s="18">
-        <v>3993</v>
+        <v>5090</v>
       </c>
       <c r="U23" s="17">
-        <v>4631.88</v>
+        <v>5904.4</v>
       </c>
       <c r="V23" s="14">
-        <v>7.3713174155160566</v>
+        <v>9.8235563353421327</v>
       </c>
       <c r="W23" s="16">
-        <v>11917.272727272728</v>
+        <v>11399.130434782608</v>
       </c>
       <c r="X23" s="15">
-        <v>-4674.1074380165301</v>
+        <v>-3200.2766798418961</v>
       </c>
       <c r="Y23" s="18">
-        <v>835</v>
+        <v>768</v>
       </c>
       <c r="Z23" s="17">
-        <v>968.59999999999991</v>
+        <v>890.87999999999988</v>
       </c>
       <c r="AA23" s="14">
-        <v>15.973913043478261</v>
+        <v>15.36</v>
       </c>
       <c r="AB23" s="16">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="AC23" s="15">
-        <v>-315</v>
+        <v>-332</v>
       </c>
       <c r="AD23" s="19">
-        <v>44362</v>
+        <v>37759</v>
       </c>
       <c r="AE23" s="20">
-        <v>51459.92</v>
+        <v>43800.439999999995</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3495,7 +3500,7 @@
         <v>682.05555555555554</v>
       </c>
     </row>
-    <row r="24" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="10" t="s">
         <v>42</v>
       </c>
@@ -3506,85 +3511,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>8567</v>
+        <v>9044</v>
       </c>
       <c r="F24" s="14">
-        <v>9937.7199999999993</v>
+        <v>10491.039999999999</v>
       </c>
       <c r="G24" s="14">
-        <v>8.4448635437881858</v>
+        <v>9.3202932790224047</v>
       </c>
       <c r="H24" s="30">
-        <v>22318.18181818182</v>
+        <v>21347.82608695652</v>
       </c>
       <c r="I24" s="15">
-        <v>-1577.6280991735548</v>
+        <v>-659.55731225296404</v>
       </c>
       <c r="J24" s="16">
-        <v>9486</v>
+        <v>4307</v>
       </c>
       <c r="K24" s="13">
-        <v>11003.759999999998</v>
+        <v>4996.12</v>
       </c>
       <c r="L24" s="14">
-        <v>17.744546649145864</v>
+        <v>8.4229033006106508</v>
       </c>
       <c r="M24" s="30">
-        <v>11760.90909090909</v>
+        <v>11249.565217391304</v>
       </c>
       <c r="N24" s="15">
-        <v>4140.1322314049594</v>
+        <v>-806.43873517786596</v>
       </c>
       <c r="O24" s="16">
-        <v>1156</v>
+        <v>1014</v>
       </c>
       <c r="P24" s="17">
-        <v>1340.9599999999998</v>
+        <v>1176.24</v>
       </c>
       <c r="Q24" s="14">
-        <v>14.229501525940996</v>
+        <v>13.048931841302135</v>
       </c>
       <c r="R24" s="16">
-        <v>1787.2727272727273</v>
+        <v>1709.5652173913045</v>
       </c>
       <c r="S24" s="15">
-        <v>-468.79338842975221</v>
+        <v>-540.15019762845873</v>
       </c>
       <c r="T24" s="18">
-        <v>2456</v>
+        <v>3520</v>
       </c>
       <c r="U24" s="17">
-        <v>2848.9599999999996</v>
+        <v>4083.2</v>
       </c>
       <c r="V24" s="14">
-        <v>8.6100535998841092</v>
+        <v>12.901057511227002</v>
       </c>
       <c r="W24" s="16">
-        <v>6275.454545454545</v>
+        <v>6002.608695652174</v>
       </c>
       <c r="X24" s="15">
-        <v>-2107.9669421487597</v>
+        <v>-845.53359683794497</v>
       </c>
       <c r="Y24" s="18">
-        <v>496</v>
+        <v>445</v>
       </c>
       <c r="Z24" s="17">
-        <v>575.36</v>
+        <v>516.19999999999993</v>
       </c>
       <c r="AA24" s="14">
-        <v>12.769361702127659</v>
+        <v>11.977127659574467</v>
       </c>
       <c r="AB24" s="16">
-        <v>854.5454545454545</v>
+        <v>817.39130434782612</v>
       </c>
       <c r="AC24" s="15">
-        <v>-358.5454545454545</v>
+        <v>-372.39130434782612</v>
       </c>
       <c r="AD24" s="19">
-        <v>22161</v>
+        <v>18330</v>
       </c>
       <c r="AE24" s="20">
-        <v>25706.76</v>
+        <v>21262.799999999999</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3608,7 +3613,7 @@
         <v>423.14814814814815</v>
       </c>
     </row>
-    <row r="25" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="10" t="s">
         <v>44</v>
       </c>
@@ -3619,85 +3624,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>14761</v>
+        <v>8555</v>
       </c>
       <c r="F25" s="14">
-        <v>17122.759999999998</v>
+        <v>9923.7999999999993</v>
       </c>
       <c r="G25" s="14">
-        <v>15.048919408518346</v>
+        <v>9.118317394784512</v>
       </c>
       <c r="H25" s="30">
-        <v>21579.090909090912</v>
+        <v>20640.869565217392</v>
       </c>
       <c r="I25" s="15">
-        <v>4952.3223140495866</v>
+        <v>-827.21343873517799</v>
       </c>
       <c r="J25" s="16">
-        <v>18518</v>
+        <v>12733</v>
       </c>
       <c r="K25" s="13">
-        <v>21480.879999999997</v>
+        <v>14770.279999999999</v>
       </c>
       <c r="L25" s="14">
-        <v>33.016694909010532</v>
+        <v>23.734244455905102</v>
       </c>
       <c r="M25" s="30">
-        <v>12339.09090909091</v>
+        <v>11802.608695652176</v>
       </c>
       <c r="N25" s="15">
-        <v>12909.322314049587</v>
+        <v>7368.177865612648</v>
       </c>
       <c r="O25" s="16">
-        <v>1454</v>
+        <v>1310</v>
       </c>
       <c r="P25" s="17">
-        <v>1686.6399999999999</v>
+        <v>1519.6</v>
       </c>
       <c r="Q25" s="14">
-        <v>14.728673084972792</v>
+        <v>13.873168689828379</v>
       </c>
       <c r="R25" s="16">
-        <v>2171.818181818182</v>
+        <v>2077.391304347826</v>
       </c>
       <c r="S25" s="15">
-        <v>-520.38016528925618</v>
+        <v>-578.53754940711474</v>
       </c>
       <c r="T25" s="18">
-        <v>2470</v>
+        <v>3402</v>
       </c>
       <c r="U25" s="17">
-        <v>2865.2</v>
+        <v>3946.3199999999997</v>
       </c>
       <c r="V25" s="14">
-        <v>8.4023053134664032</v>
+        <v>12.098763002530223</v>
       </c>
       <c r="W25" s="16">
-        <v>6467.2727272727279</v>
+        <v>6186.086956521739</v>
       </c>
       <c r="X25" s="15">
-        <v>-2233.4710743801661</v>
+        <v>-1096.97233201581</v>
       </c>
       <c r="Y25" s="18">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="Z25" s="17">
-        <v>418.76</v>
+        <v>370.03999999999996</v>
       </c>
       <c r="AA25" s="14">
-        <v>12.809677419354838</v>
+        <v>11.833870967741936</v>
       </c>
       <c r="AB25" s="16">
-        <v>620</v>
+        <v>593.04347826086951</v>
       </c>
       <c r="AC25" s="15">
-        <v>-259</v>
+        <v>-274.04347826086951</v>
       </c>
       <c r="AD25" s="19">
-        <v>37564</v>
+        <v>26319</v>
       </c>
       <c r="AE25" s="20">
-        <v>43574.239999999998</v>
+        <v>30530.039999999997</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3721,7 +3726,7 @@
         <v>339.75925925925924</v>
       </c>
     </row>
-    <row r="26" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
         <v>46</v>
       </c>
@@ -3732,85 +3737,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>2779</v>
+        <v>17059</v>
       </c>
       <c r="F26" s="14">
-        <v>3223.64</v>
+        <v>19788.439999999999</v>
       </c>
       <c r="G26" s="14">
-        <v>2.2030989975758373</v>
+        <v>14.138527812356681</v>
       </c>
       <c r="H26" s="30">
-        <v>27750.909090909088</v>
+        <v>26544.347826086956</v>
       </c>
       <c r="I26" s="15">
-        <v>-16142.074380165286</v>
+        <v>-1039.4189723320123</v>
       </c>
       <c r="J26" s="16">
-        <v>17740</v>
+        <v>9895</v>
       </c>
       <c r="K26" s="13">
-        <v>20578.399999999998</v>
+        <v>11478.199999999999</v>
       </c>
       <c r="L26" s="14">
-        <v>26.774853436447547</v>
+        <v>15.613290507671197</v>
       </c>
       <c r="M26" s="30">
-        <v>14576.363636363638</v>
+        <v>13942.608695652176</v>
       </c>
       <c r="N26" s="15">
-        <v>11114.380165289256</v>
+        <v>3557.450592885375</v>
       </c>
       <c r="O26" s="16">
-        <v>1088</v>
+        <v>918</v>
       </c>
       <c r="P26" s="17">
-        <v>1262.08</v>
+        <v>1064.8799999999999</v>
       </c>
       <c r="Q26" s="14">
-        <v>13.677714285714286</v>
+        <v>12.065142857142856</v>
       </c>
       <c r="R26" s="16">
-        <v>1750</v>
+        <v>1673.913043478261</v>
       </c>
       <c r="S26" s="15">
-        <v>-502.90909090909099</v>
+        <v>-603.73913043478274</v>
       </c>
       <c r="T26" s="18">
-        <v>2697</v>
+        <v>3478</v>
       </c>
       <c r="U26" s="17">
-        <v>3128.52</v>
+        <v>4034.4799999999996</v>
       </c>
       <c r="V26" s="14">
-        <v>7.3940636682904719</v>
+        <v>9.9686643253653564</v>
       </c>
       <c r="W26" s="16">
-        <v>8024.545454545455</v>
+        <v>7675.652173913044</v>
       </c>
       <c r="X26" s="15">
-        <v>-3139.0330578512403</v>
+        <v>-2104.292490118577</v>
       </c>
       <c r="Y26" s="18">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="Z26" s="17">
-        <v>678.59999999999991</v>
+        <v>635.67999999999995</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.368271954674221</v>
+        <v>13.091973559962229</v>
       </c>
       <c r="AB26" s="16">
-        <v>962.72727272727263</v>
+        <v>920.86956521739125</v>
       </c>
       <c r="AC26" s="15">
-        <v>-377.72727272727275</v>
+        <v>-372.86956521739125</v>
       </c>
       <c r="AD26" s="19">
-        <v>24889</v>
+        <v>31898</v>
       </c>
       <c r="AE26" s="20">
-        <v>28871.239999999998</v>
+        <v>37001.68</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3834,7 +3839,7 @@
         <v>438.35185185185185</v>
       </c>
     </row>
-    <row r="27" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="10">
         <v>130157</v>
       </c>
@@ -3845,85 +3850,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>2779</v>
+        <v>2998</v>
       </c>
       <c r="F27" s="14">
-        <v>3223.64</v>
+        <v>3477.68</v>
       </c>
       <c r="G27" s="14">
-        <v>8.4254322225006266</v>
+        <v>9.5025557504384857</v>
       </c>
       <c r="H27" s="30">
-        <v>7256.363636363636</v>
+        <v>6940.869565217391</v>
       </c>
       <c r="I27" s="15">
-        <v>-519.34710743801634</v>
+        <v>-156.94071146245051</v>
       </c>
       <c r="J27" s="16">
-        <v>5418</v>
+        <v>2950</v>
       </c>
       <c r="K27" s="13">
-        <v>6284.8799999999992</v>
+        <v>3421.9999999999995</v>
       </c>
       <c r="L27" s="14">
-        <v>30.981947069943285</v>
+        <v>17.635869565217391</v>
       </c>
       <c r="M27" s="30">
-        <v>3847.2727272727275</v>
+        <v>3680</v>
       </c>
       <c r="N27" s="15">
-        <v>3669.2396694214876</v>
+        <v>1277.2727272727273</v>
       </c>
       <c r="O27" s="16">
-        <v>501</v>
+        <v>441</v>
       </c>
       <c r="P27" s="17">
-        <v>581.16</v>
+        <v>511.55999999999995</v>
       </c>
       <c r="Q27" s="14">
-        <v>18.914508580343213</v>
+        <v>17.406084243369733</v>
       </c>
       <c r="R27" s="16">
-        <v>582.72727272727275</v>
+        <v>557.39130434782612</v>
       </c>
       <c r="S27" s="15">
-        <v>-28.752066115702519</v>
+        <v>-65.719367588932812</v>
       </c>
       <c r="T27" s="18">
-        <v>947</v>
+        <v>1372</v>
       </c>
       <c r="U27" s="17">
-        <v>1098.52</v>
+        <v>1591.52</v>
       </c>
       <c r="V27" s="14">
-        <v>7.9491501907735014</v>
+        <v>12.040097121054457</v>
       </c>
       <c r="W27" s="16">
-        <v>2620.9090909090905</v>
+        <v>2506.9565217391305</v>
       </c>
       <c r="X27" s="15">
-        <v>-959.11570247933855</v>
+        <v>-451.24110671936774</v>
       </c>
       <c r="Y27" s="18">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="Z27" s="17">
-        <v>310.88</v>
+        <v>278.39999999999998</v>
       </c>
       <c r="AA27" s="14">
-        <v>21.910810810810808</v>
+        <v>20.513513513513509</v>
       </c>
       <c r="AB27" s="16">
-        <v>269.09090909090912</v>
+        <v>257.39130434782612</v>
       </c>
       <c r="AC27" s="15">
-        <v>-1.0909090909091219</v>
+        <v>-17.391304347826122</v>
       </c>
       <c r="AD27" s="19">
-        <v>9913</v>
+        <v>8001</v>
       </c>
       <c r="AE27" s="20">
-        <v>11499.08</v>
+        <v>9281.16</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3947,7 +3952,7 @@
         <v>152.72222222222223</v>
       </c>
     </row>
-    <row r="28" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="10">
         <v>130158</v>
       </c>
@@ -3958,85 +3963,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>2654</v>
+        <v>3190</v>
       </c>
       <c r="F28" s="14">
-        <v>3078.64</v>
+        <v>3700.3999999999996</v>
       </c>
       <c r="G28" s="14">
-        <v>7.7400337430706196</v>
+        <v>9.726078573150156</v>
       </c>
       <c r="H28" s="30">
-        <v>7543.636363636364</v>
+        <v>7215.652173913044</v>
       </c>
       <c r="I28" s="15">
-        <v>-774.92561983471069</v>
+        <v>-89.841897233201962</v>
       </c>
       <c r="J28" s="16">
-        <v>9182</v>
+        <v>5161</v>
       </c>
       <c r="K28" s="13">
-        <v>10651.119999999999</v>
+        <v>5986.7599999999993</v>
       </c>
       <c r="L28" s="14">
-        <v>36.207332572918368</v>
+        <v>21.276405409809353</v>
       </c>
       <c r="M28" s="30">
-        <v>5579.090909090909</v>
+        <v>5336.521739130435</v>
       </c>
       <c r="N28" s="15">
-        <v>6646.0495867768595</v>
+        <v>2735.308300395257</v>
       </c>
       <c r="O28" s="16">
-        <v>598</v>
+        <v>543</v>
       </c>
       <c r="P28" s="17">
-        <v>693.68</v>
+        <v>629.88</v>
       </c>
       <c r="Q28" s="14">
-        <v>15.798689956331881</v>
+        <v>14.997707423580787</v>
       </c>
       <c r="R28" s="16">
-        <v>832.72727272727263</v>
+        <v>796.52173913043487</v>
       </c>
       <c r="S28" s="15">
-        <v>-159.02479338842966</v>
+        <v>-181.11067193675888</v>
       </c>
       <c r="T28" s="18">
-        <v>316</v>
+        <v>673</v>
       </c>
       <c r="U28" s="17">
-        <v>366.56</v>
+        <v>780.68</v>
       </c>
       <c r="V28" s="14">
-        <v>2.2301545640128313</v>
+        <v>4.9655584718576851</v>
       </c>
       <c r="W28" s="16">
-        <v>3117.2727272727275</v>
+        <v>2981.7391304347825</v>
       </c>
       <c r="X28" s="15">
-        <v>-1951.1074380165292</v>
+        <v>-1495.5375494071145</v>
       </c>
       <c r="Y28" s="18">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="Z28" s="17">
-        <v>356.11999999999995</v>
+        <v>323.64</v>
       </c>
       <c r="AA28" s="14">
-        <v>17.399063231850114</v>
+        <v>16.53091334894614</v>
       </c>
       <c r="AB28" s="16">
-        <v>388.18181818181819</v>
+        <v>371.30434782608694</v>
       </c>
       <c r="AC28" s="15">
-        <v>-81.181818181818244</v>
+        <v>-92.304347826086882</v>
       </c>
       <c r="AD28" s="19">
-        <v>13057</v>
+        <v>9846</v>
       </c>
       <c r="AE28" s="20">
-        <v>15146.119999999999</v>
+        <v>11421.359999999999</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4060,7 +4065,7 @@
         <v>67.203703703703709</v>
       </c>
     </row>
-    <row r="29" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="10">
         <v>130159</v>
       </c>
@@ -4071,85 +4076,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>550</v>
+        <v>2676</v>
       </c>
       <c r="F29" s="14">
-        <v>638</v>
+        <v>3104.16</v>
       </c>
       <c r="G29" s="14">
-        <v>1.5164634841061868</v>
+        <v>7.7136607041130221</v>
       </c>
       <c r="H29" s="30">
-        <v>7979.090909090909</v>
+        <v>7632.1739130434789</v>
       </c>
       <c r="I29" s="15">
-        <v>-3076.859504132231</v>
+        <v>-793.16996047430894</v>
       </c>
       <c r="J29" s="16">
-        <v>2884</v>
+        <v>4538</v>
       </c>
       <c r="K29" s="13">
-        <v>3345.4399999999996</v>
+        <v>5264.08</v>
       </c>
       <c r="L29" s="14">
-        <v>12.447440699126091</v>
+        <v>20.476440164080611</v>
       </c>
       <c r="M29" s="30">
-        <v>5097.2727272727279</v>
+        <v>4875.652173913044</v>
       </c>
       <c r="N29" s="15">
-        <v>567.05785123966916</v>
+        <v>2321.794466403162</v>
       </c>
       <c r="O29" s="16">
-        <v>617</v>
+        <v>548</v>
       </c>
       <c r="P29" s="17">
-        <v>715.71999999999991</v>
+        <v>635.67999999999995</v>
       </c>
       <c r="Q29" s="14">
-        <v>16.072551130247579</v>
+        <v>14.92400430570506</v>
       </c>
       <c r="R29" s="16">
-        <v>844.5454545454545</v>
+        <v>807.82608695652175</v>
       </c>
       <c r="S29" s="15">
-        <v>-150.76859504132233</v>
+        <v>-186.38735177865613</v>
       </c>
       <c r="T29" s="18">
-        <v>270</v>
+        <v>590</v>
       </c>
       <c r="U29" s="17">
-        <v>313.2</v>
+        <v>684.4</v>
       </c>
       <c r="V29" s="14">
-        <v>1.9144447699970704</v>
+        <v>4.3735716378552594</v>
       </c>
       <c r="W29" s="16">
-        <v>3102.7272727272725</v>
+        <v>2967.826086956522</v>
       </c>
       <c r="X29" s="15">
-        <v>-1986.5289256198344</v>
+        <v>-1568.418972332016</v>
       </c>
       <c r="Y29" s="18">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="Z29" s="17">
-        <v>329.44</v>
+        <v>306.23999999999995</v>
       </c>
       <c r="AA29" s="14">
-        <v>17.532653061224494</v>
+        <v>17.038775510204079</v>
       </c>
       <c r="AB29" s="16">
-        <v>356.36363636363632</v>
+        <v>340.86956521739131</v>
       </c>
       <c r="AC29" s="15">
-        <v>-72.363636363636317</v>
+        <v>-76.869565217391312</v>
       </c>
       <c r="AD29" s="19">
-        <v>4605</v>
+        <v>8616</v>
       </c>
       <c r="AE29" s="20">
-        <v>5341.7999999999993</v>
+        <v>9994.56</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4173,7 +4178,7 @@
         <v>148.44444444444446</v>
       </c>
     </row>
-    <row r="30" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="10">
         <v>130700</v>
       </c>
@@ -4184,64 +4189,64 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>445</v>
+        <v>668</v>
       </c>
       <c r="F30" s="14">
-        <v>1637.6000000000001</v>
+        <v>2458.2400000000002</v>
       </c>
       <c r="G30" s="14">
-        <v>4.4117165096272029</v>
+        <v>6.9235559197050387</v>
       </c>
       <c r="H30" s="30">
-        <v>2219.090909090909</v>
+        <v>2122.608695652174</v>
       </c>
       <c r="I30" s="15">
-        <v>-563.67768595041309</v>
+        <v>-296.82213438735187</v>
       </c>
       <c r="J30" s="16">
-        <v>1701</v>
+        <v>922</v>
       </c>
       <c r="K30" s="13">
-        <v>6259.68</v>
+        <v>3392.96</v>
       </c>
       <c r="L30" s="14">
-        <v>15.268620178041543</v>
+        <v>8.6522997032640951</v>
       </c>
       <c r="M30" s="30">
-        <v>2450.909090909091</v>
+        <v>2344.3478260869565</v>
       </c>
       <c r="N30" s="15">
-        <v>586.95041322314046</v>
+        <v>-143.61264822134399</v>
       </c>
       <c r="O30" s="16">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="P30" s="17">
-        <v>371.68</v>
+        <v>331.2</v>
       </c>
       <c r="Q30" s="14">
-        <v>18.105185185185185</v>
+        <v>16.866666666666667</v>
       </c>
       <c r="R30" s="16">
-        <v>122.72727272727273</v>
+        <v>117.39130434782609</v>
       </c>
       <c r="S30" s="15">
-        <v>-10.570247933884303</v>
+        <v>-16.719367588932812</v>
       </c>
       <c r="T30" s="18">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="U30" s="17">
-        <v>736</v>
+        <v>1306.4000000000001</v>
       </c>
       <c r="V30" s="14">
-        <v>6.7222222222222232</v>
+        <v>12.474305555555556</v>
       </c>
       <c r="W30" s="16">
-        <v>654.5454545454545</v>
+        <v>626.08695652173913</v>
       </c>
       <c r="X30" s="15">
-        <v>-276.03305785123962</v>
+        <v>-100.33596837944663</v>
       </c>
       <c r="Y30" s="18">
         <v>61</v>
@@ -4250,19 +4255,19 @@
         <v>224.48000000000002</v>
       </c>
       <c r="AA30" s="14">
-        <v>10.180689655172415</v>
+        <v>10.643448275862069</v>
       </c>
       <c r="AB30" s="16">
-        <v>131.81818181818181</v>
+        <v>126.08695652173913</v>
       </c>
       <c r="AC30" s="15">
-        <v>-70.818181818181813</v>
+        <v>-65.086956521739125</v>
       </c>
       <c r="AD30" s="19">
-        <v>2508</v>
+        <v>2096</v>
       </c>
       <c r="AE30" s="20">
-        <v>9229.44</v>
+        <v>7713.2800000000007</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4286,7 +4291,7 @@
         <v>175.3125</v>
       </c>
     </row>
-    <row r="31" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="10">
         <v>130701</v>
       </c>
@@ -4297,34 +4302,34 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F31" s="14">
-        <v>1523.52</v>
+        <v>1460.96</v>
       </c>
       <c r="G31" s="14">
-        <v>8.205405405405406</v>
+        <v>8.2261261261261254</v>
       </c>
       <c r="H31" s="30">
-        <v>1110</v>
+        <v>1061.7391304347827</v>
       </c>
       <c r="I31" s="15">
-        <v>-90.545454545454504</v>
+        <v>-85.608695652173992</v>
       </c>
       <c r="J31" s="16">
-        <v>1357</v>
+        <v>850</v>
       </c>
       <c r="K31" s="13">
-        <v>4993.76</v>
+        <v>3128</v>
       </c>
       <c r="L31" s="14">
-        <v>20.930146590184833</v>
+        <v>13.706182281708093</v>
       </c>
       <c r="M31" s="30">
-        <v>1426.3636363636363</v>
+        <v>1364.3478260869565</v>
       </c>
       <c r="N31" s="15">
-        <v>708.65289256198344</v>
+        <v>229.84189723320151</v>
       </c>
       <c r="O31" s="16">
         <v>17</v>
@@ -4333,49 +4338,49 @@
         <v>62.56</v>
       </c>
       <c r="Q31" s="14">
-        <v>12.856249999999999</v>
+        <v>13.440624999999999</v>
       </c>
       <c r="R31" s="16">
-        <v>29.090909090909093</v>
+        <v>27.826086956521738</v>
       </c>
       <c r="S31" s="15">
-        <v>-9.4462809917355379</v>
+        <v>-8.2964426877470352</v>
       </c>
       <c r="T31" s="18">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="U31" s="17">
-        <v>77.28</v>
+        <v>655.04000000000008</v>
       </c>
       <c r="V31" s="14">
-        <v>1.932319391634981</v>
+        <v>17.123193916349809</v>
       </c>
       <c r="W31" s="16">
-        <v>239.09090909090909</v>
+        <v>228.69565217391306</v>
       </c>
       <c r="X31" s="15">
-        <v>-152.88429752066116</v>
+        <v>11.675889328063221</v>
       </c>
       <c r="Y31" s="18">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Z31" s="17">
-        <v>66.240000000000009</v>
+        <v>99.36</v>
       </c>
       <c r="AA31" s="14">
-        <v>12.100000000000001</v>
+        <v>18.975000000000001</v>
       </c>
       <c r="AB31" s="16">
-        <v>32.727272727272727</v>
+        <v>31.304347826086957</v>
       </c>
       <c r="AC31" s="15">
-        <v>-14.727272727272727</v>
+        <v>-4.304347826086957</v>
       </c>
       <c r="AD31" s="19">
-        <v>1827</v>
+        <v>1469</v>
       </c>
       <c r="AE31" s="20">
-        <v>6723.3600000000006</v>
+        <v>5405.92</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4399,7 +4404,7 @@
         <v>94.375</v>
       </c>
     </row>
-    <row r="32" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="10">
         <v>130702</v>
       </c>
@@ -4410,85 +4415,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1260</v>
+        <v>1770</v>
       </c>
       <c r="F32" s="14">
-        <v>5229</v>
+        <v>7345.5000000000009</v>
       </c>
       <c r="G32" s="14">
-        <v>5.9811690859160462</v>
+        <v>8.7840329540996471</v>
       </c>
       <c r="H32" s="30">
-        <v>4634.545454545454</v>
+        <v>4433.0434782608691</v>
       </c>
       <c r="I32" s="15">
-        <v>-846.61157024793374</v>
+        <v>-245.01976284584975</v>
       </c>
       <c r="J32" s="16">
-        <v>2751</v>
+        <v>1203</v>
       </c>
       <c r="K32" s="13">
-        <v>11416.650000000001</v>
+        <v>4992.4500000000007</v>
       </c>
       <c r="L32" s="14">
-        <v>16.672727272727272</v>
+        <v>7.6223140495867776</v>
       </c>
       <c r="M32" s="30">
-        <v>3630</v>
+        <v>3472.173913043478</v>
       </c>
       <c r="N32" s="15">
-        <v>1101</v>
+        <v>-375.26086956521726</v>
       </c>
       <c r="O32" s="16">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="P32" s="17">
-        <v>834.15000000000009</v>
+        <v>759.45</v>
       </c>
       <c r="Q32" s="14">
-        <v>15.248275862068965</v>
+        <v>14.513793103448275</v>
       </c>
       <c r="R32" s="16">
-        <v>290</v>
+        <v>277.39130434782612</v>
       </c>
       <c r="S32" s="15">
-        <v>-62.636363636363626</v>
+        <v>-69.173913043478279</v>
       </c>
       <c r="T32" s="18">
-        <v>605</v>
+        <v>826</v>
       </c>
       <c r="U32" s="17">
-        <v>2510.75</v>
+        <v>3427.9</v>
       </c>
       <c r="V32" s="14">
-        <v>7.3981808994441636</v>
+        <v>10.559777665487621</v>
       </c>
       <c r="W32" s="16">
-        <v>1799.090909090909</v>
+        <v>1720.8695652173913</v>
       </c>
       <c r="X32" s="15">
-        <v>-703.42975206611573</v>
+        <v>-425.54150197628451</v>
       </c>
       <c r="Y32" s="18">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Z32" s="17">
-        <v>1008.45</v>
+        <v>987.7</v>
       </c>
       <c r="AA32" s="14">
-        <v>59.4</v>
+        <v>60.82222222222223</v>
       </c>
       <c r="AB32" s="16">
-        <v>90</v>
+        <v>86.086956521739125</v>
       </c>
       <c r="AC32" s="15">
-        <v>153</v>
+        <v>151.91304347826087</v>
       </c>
       <c r="AD32" s="19">
-        <v>5060</v>
+        <v>4220</v>
       </c>
       <c r="AE32" s="20">
-        <v>20999</v>
+        <v>17513</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4512,7 +4517,7 @@
         <v>308.3125</v>
       </c>
     </row>
-    <row r="33" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="10">
         <v>130703</v>
       </c>
@@ -4523,85 +4528,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3035</v>
+        <v>3515</v>
       </c>
       <c r="F33" s="14">
-        <v>12595.250000000002</v>
+        <v>14587.250000000002</v>
       </c>
       <c r="G33" s="14">
-        <v>7.2683819891143004</v>
+        <v>8.8005442850074225</v>
       </c>
       <c r="H33" s="30">
-        <v>9186.363636363636</v>
+        <v>8786.95652173913</v>
       </c>
       <c r="I33" s="15">
-        <v>-1140.6198347107438</v>
+        <v>-479.07114624505948</v>
       </c>
       <c r="J33" s="16">
-        <v>6256</v>
+        <v>4303</v>
       </c>
       <c r="K33" s="13">
-        <v>25962.400000000001</v>
+        <v>17857.45</v>
       </c>
       <c r="L33" s="14">
-        <v>24.921020576131689</v>
+        <v>17.920312757201646</v>
       </c>
       <c r="M33" s="30">
-        <v>5522.7272727272721</v>
+        <v>5282.608695652174</v>
       </c>
       <c r="N33" s="15">
-        <v>3745.6694214876034</v>
+        <v>1901.814229249012</v>
       </c>
       <c r="O33" s="16">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="P33" s="17">
-        <v>1265.75</v>
+        <v>1199.3500000000001</v>
       </c>
       <c r="Q33" s="14">
-        <v>17.125290023201856</v>
+        <v>16.964501160092809</v>
       </c>
       <c r="R33" s="16">
-        <v>391.81818181818181</v>
+        <v>374.78260869565219</v>
       </c>
       <c r="S33" s="15">
-        <v>-51.198347107438053</v>
+        <v>-51.711462450592876</v>
       </c>
       <c r="T33" s="18">
-        <v>611</v>
+        <v>820</v>
       </c>
       <c r="U33" s="17">
-        <v>2535.65</v>
+        <v>3403.0000000000005</v>
       </c>
       <c r="V33" s="14">
-        <v>5.821338582677166</v>
+        <v>8.1677165354330707</v>
       </c>
       <c r="W33" s="16">
-        <v>2309.090909090909</v>
+        <v>2208.695652173913</v>
       </c>
       <c r="X33" s="15">
-        <v>-1068.3388429752065</v>
+        <v>-786.32411067193675</v>
       </c>
       <c r="Y33" s="18">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Z33" s="17">
-        <v>381.8</v>
+        <v>361.05</v>
       </c>
       <c r="AA33" s="14">
-        <v>6.2016713091922018</v>
+        <v>6.1311977715877441</v>
       </c>
       <c r="AB33" s="16">
-        <v>326.36363636363632</v>
+        <v>312.17391304347825</v>
       </c>
       <c r="AC33" s="15">
-        <v>-234.36363636363632</v>
+        <v>-225.17391304347825</v>
       </c>
       <c r="AD33" s="19">
-        <v>10299</v>
+        <v>9014</v>
       </c>
       <c r="AE33" s="20">
-        <v>42740.850000000006</v>
+        <v>37408.100000000006</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4625,7 +4630,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="34" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <v>130707</v>
       </c>
@@ -4636,19 +4641,19 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>734</v>
+        <v>674</v>
       </c>
       <c r="F34" s="14">
-        <v>3046.1000000000004</v>
+        <v>2797.1000000000004</v>
       </c>
       <c r="G34" s="14">
-        <v>14.68</v>
+        <v>14.092727272727272</v>
       </c>
       <c r="H34" s="30">
-        <v>1100</v>
+        <v>1052.1739130434783</v>
       </c>
       <c r="I34" s="15">
-        <v>234</v>
+        <v>195.73913043478257</v>
       </c>
       <c r="J34" s="16">
         <v>0</v>
@@ -4673,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>72.72727272727272</v>
+        <v>69.565217391304344</v>
       </c>
       <c r="S34" s="15">
-        <v>-66.115702479338836</v>
+        <v>-63.241106719367586</v>
       </c>
       <c r="T34" s="18">
         <v>82</v>
@@ -4685,13 +4690,13 @@
         <v>340.3</v>
       </c>
       <c r="V34" s="14">
-        <v>13.229333333333333</v>
+        <v>13.830666666666666</v>
       </c>
       <c r="W34" s="16">
-        <v>136.36363636363637</v>
+        <v>130.43478260869566</v>
       </c>
       <c r="X34" s="15">
-        <v>-17.173553719008268</v>
+        <v>-12.86166007905139</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4709,10 +4714,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>848</v>
+        <v>788</v>
       </c>
       <c r="AE34" s="20">
-        <v>3519.2000000000003</v>
+        <v>3270.2000000000003</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4736,7 +4741,7 @@
         <v>58.6875</v>
       </c>
     </row>
-    <row r="35" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="10">
         <v>131150</v>
       </c>
@@ -4747,85 +4752,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>1376</v>
+        <v>2850</v>
       </c>
       <c r="F35" s="14">
-        <v>2242.8799999999997</v>
+        <v>4645.5</v>
       </c>
       <c r="G35" s="14">
-        <v>3.4510519224790133</v>
+        <v>7.4727951083013782</v>
       </c>
       <c r="H35" s="30">
-        <v>8771.818181818182</v>
+        <v>8390.434782608696</v>
       </c>
       <c r="I35" s="15">
-        <v>-2611.1900826446285</v>
+        <v>-963.83399209486197</v>
       </c>
       <c r="J35" s="16">
-        <v>3586</v>
+        <v>670</v>
       </c>
       <c r="K35" s="13">
-        <v>5845.1799999999994</v>
+        <v>1092.0999999999999</v>
       </c>
       <c r="L35" s="14">
-        <v>23.723674138873701</v>
+        <v>4.6339529797703669</v>
       </c>
       <c r="M35" s="30">
-        <v>3325.4545454545455</v>
+        <v>3180.869565217391</v>
       </c>
       <c r="N35" s="15">
-        <v>2074.4297520661157</v>
+        <v>-775.84980237154127</v>
       </c>
       <c r="O35" s="16">
-        <v>551</v>
+        <v>503</v>
       </c>
       <c r="P35" s="17">
-        <v>898.13</v>
+        <v>819.89</v>
       </c>
       <c r="Q35" s="14">
-        <v>15.595555555555555</v>
+        <v>14.884093567251462</v>
       </c>
       <c r="R35" s="16">
-        <v>777.27272727272737</v>
+        <v>743.47826086956513</v>
       </c>
       <c r="S35" s="15">
-        <v>-155.61157024793397</v>
+        <v>-172.88932806324112</v>
       </c>
       <c r="T35" s="18">
-        <v>321</v>
+        <v>632</v>
       </c>
       <c r="U35" s="17">
-        <v>523.23</v>
+        <v>1030.1599999999999</v>
       </c>
       <c r="V35" s="14">
-        <v>7.2195167286245354</v>
+        <v>14.860223048327137</v>
       </c>
       <c r="W35" s="16">
-        <v>978.18181818181813</v>
+        <v>935.6521739130435</v>
       </c>
       <c r="X35" s="15">
-        <v>-390.40495867768595</v>
+        <v>-48.474308300395251</v>
       </c>
       <c r="Y35" s="18">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="Z35" s="17">
-        <v>255.91</v>
+        <v>241.23999999999998</v>
       </c>
       <c r="AA35" s="14">
-        <v>11.141935483870967</v>
+        <v>10.980645161290322</v>
       </c>
       <c r="AB35" s="16">
-        <v>310</v>
+        <v>296.52173913043475</v>
       </c>
       <c r="AC35" s="15">
-        <v>-153</v>
+        <v>-148.52173913043475</v>
       </c>
       <c r="AD35" s="19">
-        <v>5991</v>
+        <v>4803</v>
       </c>
       <c r="AE35" s="20">
-        <v>9765.33</v>
+        <v>7828.8899999999994</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4849,7 +4854,7 @@
         <v>98.851851851851848</v>
       </c>
     </row>
-    <row r="36" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="10">
         <v>131151</v>
       </c>
@@ -4860,85 +4865,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>3776</v>
+        <v>4548</v>
       </c>
       <c r="F36" s="14">
-        <v>6154.8799999999992</v>
+        <v>7413.24</v>
       </c>
       <c r="G36" s="14">
-        <v>6.5098810287098381</v>
+        <v>8.197221628553109</v>
       </c>
       <c r="H36" s="30">
-        <v>12760.90909090909</v>
+        <v>12206.08695652174</v>
       </c>
       <c r="I36" s="15">
-        <v>-2024.4132231404956</v>
+        <v>-1000.2213438735189</v>
       </c>
       <c r="J36" s="16">
-        <v>4175</v>
+        <v>1065</v>
       </c>
       <c r="K36" s="13">
-        <v>6805.25</v>
+        <v>1735.9499999999998</v>
       </c>
       <c r="L36" s="14">
-        <v>19.830225711481845</v>
+        <v>5.2884200196270852</v>
       </c>
       <c r="M36" s="30">
-        <v>4631.818181818182</v>
+        <v>4430.434782608696</v>
       </c>
       <c r="N36" s="15">
-        <v>2069.6280991735539</v>
+        <v>-948.83399209486197</v>
       </c>
       <c r="O36" s="16">
-        <v>1298</v>
+        <v>1230</v>
       </c>
       <c r="P36" s="17">
-        <v>2115.7399999999998</v>
+        <v>2004.8999999999999</v>
       </c>
       <c r="Q36" s="14">
-        <v>15.367710371819964</v>
+        <v>15.224559686888455</v>
       </c>
       <c r="R36" s="16">
-        <v>1858.181818181818</v>
+        <v>1777.391304347826</v>
       </c>
       <c r="S36" s="15">
-        <v>-391.2561983471071</v>
+        <v>-385.81027667984199</v>
       </c>
       <c r="T36" s="18">
-        <v>933</v>
+        <v>1222</v>
       </c>
       <c r="U36" s="17">
-        <v>1520.79</v>
+        <v>1991.86</v>
       </c>
       <c r="V36" s="14">
-        <v>9.4471129707112951</v>
+        <v>12.93581589958159</v>
       </c>
       <c r="W36" s="16">
-        <v>2172.727272727273</v>
+        <v>2078.2608695652175</v>
       </c>
       <c r="X36" s="15">
-        <v>-647.16528925619855</v>
+        <v>-289.46245059288549</v>
       </c>
       <c r="Y36" s="18">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="Z36" s="17">
-        <v>458.03</v>
+        <v>428.69</v>
       </c>
       <c r="AA36" s="14">
-        <v>10.542945736434108</v>
+        <v>10.316124031007751</v>
       </c>
       <c r="AB36" s="16">
-        <v>586.36363636363637</v>
+        <v>560.86956521739137</v>
       </c>
       <c r="AC36" s="15">
-        <v>-305.36363636363637</v>
+        <v>-297.86956521739137</v>
       </c>
       <c r="AD36" s="19">
-        <v>10463</v>
+        <v>8328</v>
       </c>
       <c r="AE36" s="20">
-        <v>17054.689999999999</v>
+        <v>13574.64</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4962,7 +4967,7 @@
         <v>168.33333333333334</v>
       </c>
     </row>
-    <row r="37" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="10">
         <v>131152</v>
       </c>
@@ -4973,64 +4978,64 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1067</v>
+        <v>1903</v>
       </c>
       <c r="F37" s="14">
-        <v>1739.2099999999998</v>
+        <v>3101.89</v>
       </c>
       <c r="G37" s="14">
-        <v>3.9706904505612797</v>
+        <v>7.4036444717822549</v>
       </c>
       <c r="H37" s="30">
-        <v>5911.8181818181811</v>
+        <v>5654.782608695652</v>
       </c>
       <c r="I37" s="15">
-        <v>-1620.1900826446281</v>
+        <v>-667.35573122529604</v>
       </c>
       <c r="J37" s="16">
-        <v>4681</v>
+        <v>1811</v>
       </c>
       <c r="K37" s="13">
-        <v>7630.03</v>
+        <v>2951.93</v>
       </c>
       <c r="L37" s="14">
-        <v>36.272878642331086</v>
+        <v>14.671245597182194</v>
       </c>
       <c r="M37" s="30">
-        <v>2839.0909090909095</v>
+        <v>2715.652173913044</v>
       </c>
       <c r="N37" s="15">
-        <v>3390.5041322314046</v>
+        <v>576.61264822134353</v>
       </c>
       <c r="O37" s="16">
-        <v>842</v>
+        <v>789</v>
       </c>
       <c r="P37" s="17">
-        <v>1372.4599999999998</v>
+        <v>1286.07</v>
       </c>
       <c r="Q37" s="14">
-        <v>15.343674698795182</v>
+        <v>15.031400602409638</v>
       </c>
       <c r="R37" s="16">
-        <v>1207.2727272727273</v>
+        <v>1154.7826086956522</v>
       </c>
       <c r="S37" s="15">
-        <v>-255.52066115702473</v>
+        <v>-260.802371541502</v>
       </c>
       <c r="T37" s="18">
-        <v>168</v>
+        <v>640</v>
       </c>
       <c r="U37" s="17">
-        <v>273.83999999999997</v>
+        <v>1043.1999999999998</v>
       </c>
       <c r="V37" s="14">
-        <v>3.1297921478060045</v>
+        <v>12.464973056197072</v>
       </c>
       <c r="W37" s="16">
-        <v>1180.909090909091</v>
+        <v>1129.5652173913045</v>
       </c>
       <c r="X37" s="15">
-        <v>-690.84297520661164</v>
+        <v>-181.50197628458511</v>
       </c>
       <c r="Y37" s="18">
         <v>0</v>
@@ -5042,16 +5047,16 @@
         <v>0</v>
       </c>
       <c r="AB37" s="16">
-        <v>395.4545454545455</v>
+        <v>378.26086956521743</v>
       </c>
       <c r="AC37" s="15">
-        <v>-395.4545454545455</v>
+        <v>-378.26086956521743</v>
       </c>
       <c r="AD37" s="19">
-        <v>6758</v>
+        <v>5143</v>
       </c>
       <c r="AE37" s="20">
-        <v>11015.539999999999</v>
+        <v>8383.09</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5075,7 +5080,7 @@
         <v>59.962962962962962</v>
       </c>
     </row>
-    <row r="38" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="10">
         <v>131153</v>
       </c>
@@ -5086,85 +5091,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1141</v>
+        <v>1445</v>
       </c>
       <c r="F38" s="14">
-        <v>1859.83</v>
+        <v>2355.35</v>
       </c>
       <c r="G38" s="14">
-        <v>5.551306795335746</v>
+        <v>7.3499195818254925</v>
       </c>
       <c r="H38" s="30">
-        <v>4521.818181818182</v>
+        <v>4325.217391304348</v>
       </c>
       <c r="I38" s="15">
-        <v>-914.37190082644611</v>
+        <v>-521.00790513833999</v>
       </c>
       <c r="J38" s="16">
-        <v>4179</v>
+        <v>1947</v>
       </c>
       <c r="K38" s="13">
-        <v>6811.7699999999995</v>
+        <v>3173.6099999999997</v>
       </c>
       <c r="L38" s="14">
-        <v>38.822188099808066</v>
+        <v>18.909443378119001</v>
       </c>
       <c r="M38" s="30">
-        <v>2368.181818181818</v>
+        <v>2265.217391304348</v>
       </c>
       <c r="N38" s="15">
-        <v>3102.5537190082646</v>
+        <v>917.35573122529649</v>
       </c>
       <c r="O38" s="16">
+        <v>445</v>
+      </c>
+      <c r="P38" s="17">
+        <v>725.34999999999991</v>
+      </c>
+      <c r="Q38" s="14">
+        <v>12.41289966923925</v>
+      </c>
+      <c r="R38" s="16">
+        <v>788.695652173913</v>
+      </c>
+      <c r="S38" s="15">
+        <v>-271.99604743083</v>
+      </c>
+      <c r="T38" s="18">
         <v>497</v>
       </c>
-      <c r="P38" s="17">
+      <c r="U38" s="17">
         <v>810.1099999999999</v>
       </c>
-      <c r="Q38" s="14">
-        <v>13.260639470782802</v>
-      </c>
-      <c r="R38" s="16">
-        <v>824.5454545454545</v>
-      </c>
-      <c r="S38" s="15">
-        <v>-252.58677685950408</v>
-      </c>
-      <c r="T38" s="18">
-        <v>314</v>
-      </c>
-      <c r="U38" s="17">
-        <v>511.82</v>
-      </c>
       <c r="V38" s="14">
-        <v>8.9083235638921447</v>
+        <v>14.741031652989451</v>
       </c>
       <c r="W38" s="16">
-        <v>775.4545454545455</v>
+        <v>741.73913043478262</v>
       </c>
       <c r="X38" s="15">
-        <v>-249.96694214876038</v>
+        <v>-42.446640316205503</v>
       </c>
       <c r="Y38" s="18">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="Z38" s="17">
-        <v>386.31</v>
+        <v>361.85999999999996</v>
       </c>
       <c r="AA38" s="14">
-        <v>7.8782967032967033</v>
+        <v>7.7151098901098907</v>
       </c>
       <c r="AB38" s="16">
-        <v>661.81818181818187</v>
+        <v>633.04347826086951</v>
       </c>
       <c r="AC38" s="15">
-        <v>-424.81818181818187</v>
+        <v>-411.04347826086951</v>
       </c>
       <c r="AD38" s="19">
-        <v>6368</v>
+        <v>4556</v>
       </c>
       <c r="AE38" s="20">
-        <v>10379.84</v>
+        <v>7426.28</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5188,7 +5193,7 @@
         <v>66.518518518518519</v>
       </c>
     </row>
-    <row r="39" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="10">
         <v>131154</v>
       </c>
@@ -5199,85 +5204,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>969</v>
+        <v>802</v>
       </c>
       <c r="F39" s="14">
-        <v>1579.4699999999998</v>
+        <v>1307.26</v>
       </c>
       <c r="G39" s="14">
-        <v>10.712562814070353</v>
+        <v>9.2693467336683426</v>
       </c>
       <c r="H39" s="30">
-        <v>1990</v>
+        <v>1903.4782608695652</v>
       </c>
       <c r="I39" s="15">
-        <v>64.454545454545496</v>
+        <v>-63.217391304347757</v>
       </c>
       <c r="J39" s="16">
-        <v>2076</v>
+        <v>805</v>
       </c>
       <c r="K39" s="13">
-        <v>3383.8799999999997</v>
+        <v>1312.1499999999999</v>
       </c>
       <c r="L39" s="14">
-        <v>40.352771084337348</v>
+        <v>16.358634538152611</v>
       </c>
       <c r="M39" s="30">
-        <v>1131.818181818182</v>
+        <v>1082.608695652174</v>
       </c>
       <c r="N39" s="15">
-        <v>1561.5371900826444</v>
+        <v>312.90513833992094</v>
       </c>
       <c r="O39" s="16">
-        <v>466</v>
+        <v>417</v>
       </c>
       <c r="P39" s="17">
-        <v>759.57999999999993</v>
+        <v>679.70999999999992</v>
       </c>
       <c r="Q39" s="14">
-        <v>17.32288786482335</v>
+        <v>16.205990783410137</v>
       </c>
       <c r="R39" s="16">
-        <v>591.81818181818176</v>
+        <v>566.08695652173913</v>
       </c>
       <c r="S39" s="15">
-        <v>-72.016528925619696</v>
+        <v>-97.62450592885375</v>
       </c>
       <c r="T39" s="18">
-        <v>393</v>
+        <v>780</v>
       </c>
       <c r="U39" s="17">
-        <v>640.58999999999992</v>
+        <v>1271.3999999999999</v>
       </c>
       <c r="V39" s="14">
-        <v>7.5063930544593518</v>
+        <v>15.57537490134175</v>
       </c>
       <c r="W39" s="16">
-        <v>1151.818181818182</v>
+        <v>1101.7391304347827</v>
       </c>
       <c r="X39" s="15">
-        <v>-444.68595041322328</v>
+        <v>-21.264822134387487</v>
       </c>
       <c r="Y39" s="18">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="Z39" s="17">
-        <v>590.05999999999995</v>
+        <v>578.65</v>
       </c>
       <c r="AA39" s="14">
-        <v>63.024460431654667</v>
+        <v>64.615107913669064</v>
       </c>
       <c r="AB39" s="16">
-        <v>126.36363636363637</v>
+        <v>120.86956521739131</v>
       </c>
       <c r="AC39" s="15">
-        <v>235.63636363636363</v>
+        <v>234.13043478260869</v>
       </c>
       <c r="AD39" s="19">
-        <v>4266</v>
+        <v>3159</v>
       </c>
       <c r="AE39" s="20">
-        <v>6953.58</v>
+        <v>5149.17</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5301,7 +5306,7 @@
         <v>166.44444444444446</v>
       </c>
     </row>
-    <row r="40" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="10">
         <v>131155</v>
       </c>
@@ -5312,85 +5317,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>1146</v>
+        <v>941</v>
       </c>
       <c r="F40" s="14">
-        <v>1867.9799999999998</v>
+        <v>1533.83</v>
       </c>
       <c r="G40" s="14">
-        <v>9.6062348458607545</v>
+        <v>8.2463803255975066</v>
       </c>
       <c r="H40" s="30">
-        <v>2624.5454545454545</v>
+        <v>2510.4347826086955</v>
       </c>
       <c r="I40" s="15">
-        <v>-46.975206611570229</v>
+        <v>-200.10671936758899</v>
       </c>
       <c r="J40" s="16">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="K40" s="13">
-        <v>370.01</v>
+        <v>32.599999999999994</v>
       </c>
       <c r="L40" s="14">
-        <v>3.7192958700067704</v>
+        <v>0.34258632362897767</v>
       </c>
       <c r="M40" s="30">
-        <v>1342.7272727272727</v>
+        <v>1284.3478260869565</v>
       </c>
       <c r="N40" s="15">
-        <v>-383.33057851239664</v>
+        <v>-563.79446640316201</v>
       </c>
       <c r="O40" s="16">
-        <v>569</v>
+        <v>490</v>
       </c>
       <c r="P40" s="17">
-        <v>927.46999999999991</v>
+        <v>798.69999999999993</v>
       </c>
       <c r="Q40" s="14">
-        <v>16.999753086419751</v>
+        <v>15.304938271604938</v>
       </c>
       <c r="R40" s="16">
-        <v>736.36363636363637</v>
+        <v>704.3478260869565</v>
       </c>
       <c r="S40" s="15">
-        <v>-100.42148760330588</v>
+        <v>-150.31620553359687</v>
       </c>
       <c r="T40" s="18">
-        <v>508</v>
+        <v>432</v>
       </c>
       <c r="U40" s="17">
-        <v>828.04</v>
+        <v>704.16</v>
       </c>
       <c r="V40" s="14">
-        <v>8.4959225984796145</v>
+        <v>7.5532826537664146</v>
       </c>
       <c r="W40" s="16">
-        <v>1315.4545454545453</v>
+        <v>1258.2608695652173</v>
       </c>
       <c r="X40" s="15">
-        <v>-448.6942148760329</v>
+        <v>-483.09881422924889</v>
       </c>
       <c r="Y40" s="18">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="Z40" s="17">
-        <v>593.31999999999994</v>
+        <v>585.16999999999996</v>
       </c>
       <c r="AA40" s="14">
-        <v>60.750344827586211</v>
+        <v>62.639310344827585</v>
       </c>
       <c r="AB40" s="16">
-        <v>131.81818181818181</v>
+        <v>126.08695652173913</v>
       </c>
       <c r="AC40" s="15">
-        <v>232.18181818181819</v>
+        <v>232.91304347826087</v>
       </c>
       <c r="AD40" s="19">
-        <v>2814</v>
+        <v>2242</v>
       </c>
       <c r="AE40" s="20">
-        <v>4586.82</v>
+        <v>3654.4599999999996</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5414,7 +5419,7 @@
         <v>162.90740740740742</v>
       </c>
     </row>
-    <row r="41" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="10">
         <v>131700</v>
       </c>
@@ -5425,34 +5430,34 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>325</v>
+        <v>695</v>
       </c>
       <c r="F41" s="14">
-        <v>1998.7500000000002</v>
+        <v>4274.25</v>
       </c>
       <c r="G41" s="14">
-        <v>4.9156249999999995</v>
+        <v>10.989687499999999</v>
       </c>
       <c r="H41" s="30">
-        <v>1454.5454545454547</v>
+        <v>1391.304347826087</v>
       </c>
       <c r="I41" s="15">
-        <v>-336.15702479338847</v>
+        <v>62.58893280632401</v>
       </c>
       <c r="J41" s="16">
-        <v>853</v>
+        <v>240</v>
       </c>
       <c r="K41" s="13">
-        <v>5245.9500000000007</v>
+        <v>1476</v>
       </c>
       <c r="L41" s="14">
-        <v>25.082138517618475</v>
+        <v>7.3778857837181047</v>
       </c>
       <c r="M41" s="30">
-        <v>748.18181818181813</v>
+        <v>715.6521739130435</v>
       </c>
       <c r="N41" s="15">
-        <v>512.91735537190084</v>
+        <v>-85.296442687747003</v>
       </c>
       <c r="O41" s="16">
         <v>28</v>
@@ -5461,49 +5466,49 @@
         <v>172.20000000000002</v>
       </c>
       <c r="Q41" s="14">
-        <v>5.2527131782945737</v>
+        <v>5.4914728682170546</v>
       </c>
       <c r="R41" s="16">
-        <v>117.27272727272727</v>
+        <v>112.17391304347827</v>
       </c>
       <c r="S41" s="15">
-        <v>-78.611570247933884</v>
+        <v>-73.976284584980235</v>
       </c>
       <c r="T41" s="18">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="U41" s="17">
-        <v>338.25</v>
+        <v>1260.75</v>
       </c>
       <c r="V41" s="14">
-        <v>4.3927392739273916</v>
+        <v>17.117161716171616</v>
       </c>
       <c r="W41" s="16">
-        <v>275.4545454545455</v>
+        <v>263.47826086956525</v>
       </c>
       <c r="X41" s="15">
-        <v>-145.33057851239673</v>
+        <v>13.379446640316189</v>
       </c>
       <c r="Y41" s="18">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Z41" s="17">
-        <v>147.60000000000002</v>
+        <v>116.85000000000001</v>
       </c>
       <c r="AA41" s="14">
-        <v>4.3669172932330822</v>
+        <v>3.6142857142857143</v>
       </c>
       <c r="AB41" s="16">
-        <v>120.90909090909092</v>
+        <v>115.65217391304347</v>
       </c>
       <c r="AC41" s="15">
-        <v>-96.909090909090907</v>
+        <v>-96.65217391304347</v>
       </c>
       <c r="AD41" s="19">
-        <v>1285</v>
+        <v>1187</v>
       </c>
       <c r="AE41" s="20">
-        <v>7902.7500000000009</v>
+        <v>7300.05</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5527,7 +5532,7 @@
         <v>24.87037037037037</v>
       </c>
     </row>
-    <row r="42" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="10">
         <v>131701</v>
       </c>
@@ -5538,64 +5543,64 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="F42" s="14">
-        <v>436.65000000000003</v>
+        <v>984</v>
       </c>
       <c r="G42" s="14">
-        <v>0.97018633540372667</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="H42" s="30">
-        <v>1610</v>
+        <v>1540</v>
       </c>
       <c r="I42" s="15">
-        <v>-660.81818181818187</v>
+        <v>-540</v>
       </c>
       <c r="J42" s="16">
-        <v>753</v>
+        <v>213</v>
       </c>
       <c r="K42" s="13">
-        <v>4630.95</v>
+        <v>1309.95</v>
       </c>
       <c r="L42" s="14">
-        <v>20.292427616926503</v>
+        <v>6.0010022271714929</v>
       </c>
       <c r="M42" s="30">
-        <v>816.36363636363637</v>
+        <v>780.86956521739125</v>
       </c>
       <c r="N42" s="15">
-        <v>381.92561983471074</v>
+        <v>-141.94071146245057</v>
       </c>
       <c r="O42" s="16">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P42" s="17">
-        <v>584.25</v>
+        <v>565.80000000000007</v>
       </c>
       <c r="Q42" s="14">
-        <v>14.459119496855346</v>
+        <v>14.638993710691826</v>
       </c>
       <c r="R42" s="16">
-        <v>144.54545454545456</v>
+        <v>138.26086956521738</v>
       </c>
       <c r="S42" s="15">
-        <v>-36.404958677685954</v>
+        <v>-33.691699604743064</v>
       </c>
       <c r="T42" s="18">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="U42" s="17">
-        <v>897.90000000000009</v>
+        <v>1734.3000000000002</v>
       </c>
       <c r="V42" s="14">
-        <v>8.7672456575682407</v>
+        <v>17.703722084367246</v>
       </c>
       <c r="W42" s="16">
-        <v>366.36363636363632</v>
+        <v>350.43478260869563</v>
       </c>
       <c r="X42" s="15">
-        <v>-120.44628099173548</v>
+        <v>27.138339920948624</v>
       </c>
       <c r="Y42" s="18">
         <v>35</v>
@@ -5604,19 +5609,19 @@
         <v>215.25</v>
       </c>
       <c r="AA42" s="14">
-        <v>10.5875</v>
+        <v>11.06875</v>
       </c>
       <c r="AB42" s="16">
-        <v>72.72727272727272</v>
+        <v>69.565217391304344</v>
       </c>
       <c r="AC42" s="15">
-        <v>-37.72727272727272</v>
+        <v>-34.565217391304344</v>
       </c>
       <c r="AD42" s="19">
-        <v>1100</v>
+        <v>782</v>
       </c>
       <c r="AE42" s="20">
-        <v>6765</v>
+        <v>4809.3</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5640,7 +5645,7 @@
         <v>11.277777777777779</v>
       </c>
     </row>
-    <row r="43" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="10">
         <v>132150</v>
       </c>
@@ -5651,85 +5656,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2571</v>
+        <v>2363</v>
       </c>
       <c r="F43" s="14">
-        <v>2982.3599999999997</v>
+        <v>2741.08</v>
       </c>
       <c r="G43" s="14">
-        <v>8.0333376371852818</v>
+        <v>7.7190316333118139</v>
       </c>
       <c r="H43" s="30">
-        <v>7040.909090909091</v>
+        <v>6734.782608695652</v>
       </c>
       <c r="I43" s="15">
-        <v>-629.41322314049557</v>
+        <v>-698.26482213438749</v>
       </c>
       <c r="J43" s="16">
-        <v>7296</v>
+        <v>5329</v>
       </c>
       <c r="K43" s="13">
-        <v>8463.3599999999988</v>
+        <v>6181.6399999999994</v>
       </c>
       <c r="L43" s="14">
-        <v>32.231325301204819</v>
+        <v>24.611847389558232</v>
       </c>
       <c r="M43" s="30">
-        <v>4980</v>
+        <v>4763.478260869565</v>
       </c>
       <c r="N43" s="15">
-        <v>5032.363636363636</v>
+        <v>3163.782608695652</v>
       </c>
       <c r="O43" s="16">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="P43" s="17">
-        <v>643.79999999999995</v>
+        <v>607.83999999999992</v>
       </c>
       <c r="Q43" s="14">
-        <v>11.760945709281962</v>
+        <v>11.608756567425569</v>
       </c>
       <c r="R43" s="16">
-        <v>1038.181818181818</v>
+        <v>993.04347826086951</v>
       </c>
       <c r="S43" s="15">
-        <v>-388.80165289256183</v>
+        <v>-378.76679841897237</v>
       </c>
       <c r="T43" s="18">
-        <v>866</v>
+        <v>1280</v>
       </c>
       <c r="U43" s="17">
-        <v>1004.56</v>
+        <v>1484.8</v>
       </c>
       <c r="V43" s="14">
-        <v>7.5223259152907387</v>
+        <v>11.623833452979182</v>
       </c>
       <c r="W43" s="16">
-        <v>2532.727272727273</v>
+        <v>2422.608695652174</v>
       </c>
       <c r="X43" s="15">
-        <v>-975.9834710743803</v>
+        <v>-481.897233201581</v>
       </c>
       <c r="Y43" s="18">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="Z43" s="17">
-        <v>406</v>
+        <v>364.23999999999995</v>
       </c>
       <c r="AA43" s="14">
-        <v>11.829608938547484</v>
+        <v>11.095251396648045</v>
       </c>
       <c r="AB43" s="16">
-        <v>650.90909090909099</v>
+        <v>622.60869565217388</v>
       </c>
       <c r="AC43" s="15">
-        <v>-300.90909090909099</v>
+        <v>-308.60869565217388</v>
       </c>
       <c r="AD43" s="19">
-        <v>11638</v>
+        <v>9810</v>
       </c>
       <c r="AE43" s="20">
-        <v>13500.08</v>
+        <v>11379.599999999999</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5753,7 +5758,7 @@
         <v>162.59259259259258</v>
       </c>
     </row>
-    <row r="44" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="10">
         <v>132151</v>
       </c>
@@ -5764,85 +5769,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2426</v>
+        <v>2013</v>
       </c>
       <c r="F44" s="14">
-        <v>2814.16</v>
+        <v>2335.08</v>
       </c>
       <c r="G44" s="14">
-        <v>9.0058597944470016</v>
+        <v>7.8123791992636926</v>
       </c>
       <c r="H44" s="30">
-        <v>5926.363636363636</v>
+        <v>5668.6956521739121</v>
       </c>
       <c r="I44" s="15">
-        <v>-267.80165289256183</v>
+        <v>-563.67984189723256</v>
       </c>
       <c r="J44" s="16">
-        <v>5132</v>
+        <v>3162</v>
       </c>
       <c r="K44" s="13">
-        <v>5953.12</v>
+        <v>3667.9199999999996</v>
       </c>
       <c r="L44" s="14">
-        <v>29.07852961835636</v>
+        <v>18.730648560056196</v>
       </c>
       <c r="M44" s="30">
-        <v>3882.7272727272725</v>
+        <v>3713.9130434782605</v>
       </c>
       <c r="N44" s="15">
-        <v>3367.1239669421489</v>
+        <v>1473.8577075098815</v>
       </c>
       <c r="O44" s="16">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="P44" s="17">
-        <v>490.67999999999995</v>
+        <v>475.59999999999997</v>
       </c>
       <c r="Q44" s="14">
-        <v>15.797222222222224</v>
+        <v>16.007716049382715</v>
       </c>
       <c r="R44" s="16">
-        <v>589.09090909090901</v>
+        <v>563.47826086956525</v>
       </c>
       <c r="S44" s="15">
-        <v>-112.53719008264454</v>
+        <v>-102.2529644268775</v>
       </c>
       <c r="T44" s="18">
-        <v>594</v>
+        <v>1060</v>
       </c>
       <c r="U44" s="17">
-        <v>689.04</v>
+        <v>1229.5999999999999</v>
       </c>
       <c r="V44" s="14">
-        <v>9.6734858681022882</v>
+        <v>18.047106325706601</v>
       </c>
       <c r="W44" s="16">
-        <v>1350.909090909091</v>
+        <v>1292.173913043478</v>
       </c>
       <c r="X44" s="15">
-        <v>-388.47933884297527</v>
+        <v>120.23715415019785</v>
       </c>
       <c r="Y44" s="18">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="Z44" s="17">
-        <v>287.68</v>
+        <v>251.71999999999997</v>
       </c>
       <c r="AA44" s="14">
-        <v>8.1322493224932249</v>
+        <v>7.4391598915989157</v>
       </c>
       <c r="AB44" s="16">
-        <v>670.90909090909099</v>
+        <v>641.73913043478262</v>
       </c>
       <c r="AC44" s="15">
-        <v>-422.90909090909099</v>
+        <v>-424.73913043478262</v>
       </c>
       <c r="AD44" s="19">
-        <v>8823</v>
+        <v>6862</v>
       </c>
       <c r="AE44" s="20">
-        <v>10234.679999999998</v>
+        <v>7959.9199999999992</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5866,7 +5871,7 @@
         <v>126.44444444444444</v>
       </c>
     </row>
-    <row r="45" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="10">
         <v>132152</v>
       </c>
@@ -5877,85 +5882,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>3147</v>
+        <v>2530</v>
       </c>
       <c r="F45" s="14">
-        <v>3650.5199999999995</v>
+        <v>2934.7999999999997</v>
       </c>
       <c r="G45" s="14">
-        <v>8.8524235731721497</v>
+        <v>7.4403115192374765</v>
       </c>
       <c r="H45" s="30">
-        <v>7820.909090909091</v>
+        <v>7480.869565217391</v>
       </c>
       <c r="I45" s="15">
-        <v>-407.95867768595008</v>
+        <v>-870.39525691699555</v>
       </c>
       <c r="J45" s="16">
-        <v>5295</v>
+        <v>3246</v>
       </c>
       <c r="K45" s="13">
-        <v>6142.2</v>
+        <v>3765.3599999999997</v>
       </c>
       <c r="L45" s="14">
-        <v>23.129783393501807</v>
+        <v>14.823790613718412</v>
       </c>
       <c r="M45" s="30">
-        <v>5036.363636363636</v>
+        <v>4817.391304347826</v>
       </c>
       <c r="N45" s="15">
-        <v>3005.7438016528927</v>
+        <v>1056.276679841897</v>
       </c>
       <c r="O45" s="16">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="P45" s="17">
-        <v>629.88</v>
+        <v>611.31999999999994</v>
       </c>
       <c r="Q45" s="14">
-        <v>12.502949571836346</v>
+        <v>12.686108468125592</v>
       </c>
       <c r="R45" s="16">
-        <v>955.4545454545455</v>
+        <v>913.91304347826099</v>
       </c>
       <c r="S45" s="15">
-        <v>-325.59504132231405</v>
+        <v>-303.83003952569186</v>
       </c>
       <c r="T45" s="18">
-        <v>824</v>
+        <v>1260</v>
       </c>
       <c r="U45" s="17">
-        <v>955.83999999999992</v>
+        <v>1461.6</v>
       </c>
       <c r="V45" s="14">
-        <v>8.9581311769990997</v>
+        <v>14.320754716981133</v>
       </c>
       <c r="W45" s="16">
-        <v>2023.6363636363637</v>
+        <v>1935.6521739130435</v>
       </c>
       <c r="X45" s="15">
-        <v>-647.73553719008282</v>
+        <v>-147.7470355731225</v>
       </c>
       <c r="Y45" s="18">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="Z45" s="17">
-        <v>273.76</v>
+        <v>240.11999999999998</v>
       </c>
       <c r="AA45" s="14">
-        <v>7.9988795518207292</v>
+        <v>7.3348739495798316</v>
       </c>
       <c r="AB45" s="16">
-        <v>649.09090909090901</v>
+        <v>620.86956521739137</v>
       </c>
       <c r="AC45" s="15">
-        <v>-413.09090909090901</v>
+        <v>-413.86956521739137</v>
       </c>
       <c r="AD45" s="19">
-        <v>10045</v>
+        <v>7770</v>
       </c>
       <c r="AE45" s="20">
-        <v>11652.199999999999</v>
+        <v>9013.1999999999989</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5979,7 +5984,7 @@
         <v>154.42592592592592</v>
       </c>
     </row>
-    <row r="46" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="10">
         <v>132153</v>
       </c>
@@ -5990,85 +5995,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2492</v>
+        <v>2144</v>
       </c>
       <c r="F46" s="14">
-        <v>2890.72</v>
+        <v>2487.04</v>
       </c>
       <c r="G46" s="14">
-        <v>9.4140493287542935</v>
+        <v>8.4675616609428648</v>
       </c>
       <c r="H46" s="30">
-        <v>5823.636363636364</v>
+        <v>5570.434782608696</v>
       </c>
       <c r="I46" s="15">
-        <v>-155.1074380165287</v>
+        <v>-388.01581027667999</v>
       </c>
       <c r="J46" s="16">
-        <v>3400</v>
+        <v>2347</v>
       </c>
       <c r="K46" s="13">
-        <v>3943.9999999999995</v>
+        <v>2722.52</v>
       </c>
       <c r="L46" s="14">
-        <v>23.118853610564763</v>
+        <v>16.684209047485247</v>
       </c>
       <c r="M46" s="30">
-        <v>3235.4545454545455</v>
+        <v>3094.782608695652</v>
       </c>
       <c r="N46" s="15">
-        <v>1929.3388429752065</v>
+        <v>940.28063241106724</v>
       </c>
       <c r="O46" s="16">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="P46" s="17">
-        <v>404.84</v>
+        <v>387.44</v>
       </c>
       <c r="Q46" s="14">
-        <v>13.013559322033899</v>
+        <v>13.020338983050848</v>
       </c>
       <c r="R46" s="16">
-        <v>590</v>
+        <v>564.3478260869565</v>
       </c>
       <c r="S46" s="15">
-        <v>-187.36363636363637</v>
+        <v>-179.04347826086951</v>
       </c>
       <c r="T46" s="18">
-        <v>493</v>
+        <v>556</v>
       </c>
       <c r="U46" s="17">
-        <v>571.88</v>
+        <v>644.95999999999992</v>
       </c>
       <c r="V46" s="14">
-        <v>13.588382687927108</v>
+        <v>16.021412300683373</v>
       </c>
       <c r="W46" s="16">
-        <v>798.18181818181813</v>
+        <v>763.47826086956513</v>
       </c>
       <c r="X46" s="15">
-        <v>-87.495867768594962</v>
+        <v>0.74308300395261995</v>
       </c>
       <c r="Y46" s="18">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="Z46" s="17">
-        <v>418.76</v>
+        <v>389.76</v>
       </c>
       <c r="AA46" s="14">
-        <v>15.088428324697755</v>
+        <v>14.681865284974092</v>
       </c>
       <c r="AB46" s="16">
-        <v>526.36363636363637</v>
+        <v>503.47826086956525</v>
       </c>
       <c r="AC46" s="15">
-        <v>-165.36363636363637</v>
+        <v>-167.47826086956525</v>
       </c>
       <c r="AD46" s="19">
-        <v>7095</v>
+        <v>5717</v>
       </c>
       <c r="AE46" s="20">
-        <v>8230.1999999999989</v>
+        <v>6631.7199999999993</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6092,7 +6097,7 @@
         <v>115.46296296296296</v>
       </c>
     </row>
-    <row r="47" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="10">
         <v>134000</v>
       </c>
@@ -6116,19 +6121,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K47" s="13">
-        <v>504</v>
+        <v>396</v>
       </c>
       <c r="L47" s="14">
-        <v>11.293333333333335</v>
+        <v>9.2766666666666655</v>
       </c>
       <c r="M47" s="30">
-        <v>54.54545454545454</v>
+        <v>52.173913043478265</v>
       </c>
       <c r="N47" s="15">
-        <v>3.2066115702479365</v>
+        <v>-1.7154150197628475</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6146,19 +6151,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U47" s="17">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="V47" s="14">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="W47" s="16">
-        <v>20</v>
+        <v>19.130434782608695</v>
       </c>
       <c r="X47" s="15">
-        <v>-1.545454545454545</v>
+        <v>-1.9130434782608692</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6176,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AE47" s="20">
-        <v>738</v>
+        <v>612</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6203,7 +6208,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="48" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="10">
         <v>134001</v>
       </c>
@@ -6233,13 +6238,13 @@
         <v>216</v>
       </c>
       <c r="L48" s="14">
-        <v>26.400000000000002</v>
+        <v>27.6</v>
       </c>
       <c r="M48" s="30">
-        <v>10</v>
+        <v>9.5652173913043477</v>
       </c>
       <c r="N48" s="15">
-        <v>7.454545454545455</v>
+        <v>7.6521739130434785</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6314,7 +6319,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="10">
         <v>140230</v>
       </c>
@@ -6331,58 +6336,58 @@
         <v>6.9599999999999991</v>
       </c>
       <c r="G49" s="14">
-        <v>0.13685202639019792</v>
+        <v>0.14307257304429782</v>
       </c>
       <c r="H49" s="30">
-        <v>964.5454545454545</v>
+        <v>922.60869565217388</v>
       </c>
       <c r="I49" s="15">
-        <v>-432.42975206611573</v>
+        <v>-413.36758893280631</v>
       </c>
       <c r="J49" s="16">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="K49" s="13">
-        <v>186.76</v>
+        <v>97.44</v>
       </c>
       <c r="L49" s="14">
-        <v>3.4297535211267602</v>
+        <v>1.8707746478873237</v>
       </c>
       <c r="M49" s="30">
-        <v>1032.7272727272727</v>
+        <v>987.82608695652175</v>
       </c>
       <c r="N49" s="15">
-        <v>-308.42148760330582</v>
+        <v>-365.01185770750993</v>
       </c>
       <c r="O49" s="16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P49" s="17">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="14">
-        <v>1.4319526627218935</v>
+        <v>0</v>
       </c>
       <c r="R49" s="16">
-        <v>153.63636363636363</v>
+        <v>146.95652173913044</v>
       </c>
       <c r="S49" s="15">
-        <v>-129.6694214876033</v>
+        <v>-133.59683794466403</v>
       </c>
       <c r="T49" s="18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U49" s="17">
-        <v>4.6399999999999997</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="V49" s="14">
-        <v>0.41367521367521365</v>
+        <v>0.1081196581196581</v>
       </c>
       <c r="W49" s="16">
-        <v>212.72727272727275</v>
+        <v>203.47826086956525</v>
       </c>
       <c r="X49" s="15">
-        <v>-150.71074380165291</v>
+        <v>-146.98418972332018</v>
       </c>
       <c r="Y49" s="18">
         <v>0</v>
@@ -6394,16 +6399,16 @@
         <v>0</v>
       </c>
       <c r="AB49" s="16">
-        <v>96.363636363636374</v>
+        <v>92.173913043478265</v>
       </c>
       <c r="AC49" s="15">
-        <v>-96.36363636363636</v>
+        <v>-92.173913043478251</v>
       </c>
       <c r="AD49" s="19">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="AE49" s="20">
-        <v>209.95999999999998</v>
+        <v>105.55999999999999</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6427,7 +6432,7 @@
         <v>53.674999999999997</v>
       </c>
     </row>
-    <row r="50" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="10">
         <v>140231</v>
       </c>
@@ -6438,64 +6443,64 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>1122</v>
+        <v>989</v>
       </c>
       <c r="F50" s="14">
-        <v>1301.52</v>
+        <v>1147.24</v>
       </c>
       <c r="G50" s="14">
-        <v>4.1747232472324729</v>
+        <v>3.8471248462484624</v>
       </c>
       <c r="H50" s="30">
-        <v>5912.7272727272721</v>
+        <v>5655.652173913044</v>
       </c>
       <c r="I50" s="15">
-        <v>-1565.6033057851237</v>
+        <v>-1581.7509881422925</v>
       </c>
       <c r="J50" s="16">
-        <v>2363</v>
+        <v>1267</v>
       </c>
       <c r="K50" s="13">
-        <v>2741.08</v>
+        <v>1469.7199999999998</v>
       </c>
       <c r="L50" s="14">
-        <v>12.902662454873646</v>
+        <v>7.2326489169675092</v>
       </c>
       <c r="M50" s="30">
-        <v>4029.0909090909095</v>
+        <v>3853.9130434782605</v>
       </c>
       <c r="N50" s="15">
-        <v>531.59504132231405</v>
+        <v>-484.77865612648225</v>
       </c>
       <c r="O50" s="16">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P50" s="17">
-        <v>44.08</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="14">
-        <v>0.98038379530916853</v>
+        <v>0</v>
       </c>
       <c r="R50" s="16">
-        <v>852.72727272727263</v>
+        <v>815.6521739130435</v>
       </c>
       <c r="S50" s="15">
-        <v>-737.2066115702479</v>
+        <v>-741.501976284585</v>
       </c>
       <c r="T50" s="18">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="U50" s="17">
-        <v>277.24</v>
+        <v>147.32</v>
       </c>
       <c r="V50" s="14">
-        <v>5.3702878365831017</v>
+        <v>2.9833797585886721</v>
       </c>
       <c r="W50" s="16">
-        <v>979.09090909090901</v>
+        <v>936.52173913043487</v>
       </c>
       <c r="X50" s="15">
-        <v>-473.06611570247924</v>
+        <v>-554.10671936758899</v>
       </c>
       <c r="Y50" s="18">
         <v>0</v>
@@ -6507,16 +6512,16 @@
         <v>0</v>
       </c>
       <c r="AB50" s="16">
-        <v>218.18181818181816</v>
+        <v>208.69565217391306</v>
       </c>
       <c r="AC50" s="15">
-        <v>-218.18181818181816</v>
+        <v>-208.69565217391306</v>
       </c>
       <c r="AD50" s="19">
-        <v>3762</v>
+        <v>2383</v>
       </c>
       <c r="AE50" s="20">
-        <v>4363.92</v>
+        <v>2764.2799999999997</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6543,7 +6548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B51" s="10">
         <v>140232</v>
       </c>
@@ -6554,85 +6559,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>355</v>
+        <v>1346</v>
       </c>
       <c r="F51" s="14">
-        <v>411.79999999999995</v>
+        <v>1561.36</v>
       </c>
       <c r="G51" s="14">
-        <v>1.9044557747727777</v>
+        <v>7.5490578585679451</v>
       </c>
       <c r="H51" s="30">
-        <v>4100.909090909091</v>
+        <v>3922.608695652174</v>
       </c>
       <c r="I51" s="15">
-        <v>-1509.0495867768595</v>
+        <v>-437.00395256917</v>
       </c>
       <c r="J51" s="16">
-        <v>2882</v>
+        <v>916</v>
       </c>
       <c r="K51" s="13">
-        <v>3343.12</v>
+        <v>1062.56</v>
       </c>
       <c r="L51" s="14">
-        <v>19.035043668122274</v>
+        <v>6.3250000000000002</v>
       </c>
       <c r="M51" s="30">
-        <v>3330.9090909090905</v>
+        <v>3186.0869565217395</v>
       </c>
       <c r="N51" s="15">
-        <v>1367.9504132231407</v>
+        <v>-532.22134387351775</v>
       </c>
       <c r="O51" s="16">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="P51" s="17">
-        <v>255.2</v>
+        <v>216.92</v>
       </c>
       <c r="Q51" s="14">
-        <v>18.486111111111111</v>
+        <v>16.427430555555556</v>
       </c>
       <c r="R51" s="16">
-        <v>261.81818181818181</v>
+        <v>250.43478260869566</v>
       </c>
       <c r="S51" s="15">
-        <v>-18.016528925619809</v>
+        <v>-40.667984189723313</v>
       </c>
       <c r="T51" s="18">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="U51" s="17">
-        <v>314.35999999999996</v>
+        <v>237.79999999999998</v>
       </c>
       <c r="V51" s="14">
-        <v>7.8260143198090688</v>
+        <v>6.1891408114558475</v>
       </c>
       <c r="W51" s="16">
-        <v>761.81818181818187</v>
+        <v>728.695652173913</v>
       </c>
       <c r="X51" s="15">
-        <v>-283.04958677685954</v>
+        <v>-324.96047430830038</v>
       </c>
       <c r="Y51" s="18">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Z51" s="17">
-        <v>52.199999999999996</v>
+        <v>41.76</v>
       </c>
       <c r="AA51" s="14">
-        <v>8.3769230769230756</v>
+        <v>7.0061538461538468</v>
       </c>
       <c r="AB51" s="16">
-        <v>118.18181818181819</v>
+        <v>113.04347826086956</v>
       </c>
       <c r="AC51" s="15">
-        <v>-73.181818181818187</v>
+        <v>-77.043478260869563</v>
       </c>
       <c r="AD51" s="19">
-        <v>3773</v>
+        <v>2690</v>
       </c>
       <c r="AE51" s="20">
-        <v>4376.6799999999994</v>
+        <v>3120.3999999999996</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6660,7 +6665,7 @@
         <v>5580.5526455026438</v>
       </c>
     </row>
-    <row r="52" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="10">
         <v>150360</v>
       </c>
@@ -6671,49 +6676,49 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>1451</v>
+        <v>720</v>
       </c>
       <c r="F52" s="14">
-        <v>1175.3100000000002</v>
+        <v>583.20000000000005</v>
       </c>
       <c r="G52" s="14">
-        <v>8.9622766717713116</v>
+        <v>4.6493108728943344</v>
       </c>
       <c r="H52" s="30">
-        <v>3561.818181818182</v>
+        <v>3406.9565217391305</v>
       </c>
       <c r="I52" s="15">
-        <v>-168.00826446281008</v>
+        <v>-828.61660079051376</v>
       </c>
       <c r="J52" s="16">
-        <v>5811</v>
+        <v>7018</v>
       </c>
       <c r="K52" s="13">
-        <v>4706.9100000000008</v>
+        <v>5684.58</v>
       </c>
       <c r="L52" s="14">
-        <v>118.2726661059714</v>
+        <v>149.33170731707315</v>
       </c>
       <c r="M52" s="30">
-        <v>1080.909090909091</v>
+        <v>1033.913043478261</v>
       </c>
       <c r="N52" s="15">
-        <v>5319.6776859504134</v>
+        <v>6548.0395256917</v>
       </c>
       <c r="O52" s="16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P52" s="17">
-        <v>4.8600000000000003</v>
+        <v>3.24</v>
       </c>
       <c r="Q52" s="14">
-        <v>0.54382022471910108</v>
+        <v>0.37902621722846441</v>
       </c>
       <c r="R52" s="16">
-        <v>242.72727272727275</v>
+        <v>232.17391304347825</v>
       </c>
       <c r="S52" s="15">
-        <v>-214.6611570247934</v>
+        <v>-207.06719367588934</v>
       </c>
       <c r="T52" s="18">
         <v>204</v>
@@ -6722,34 +6727,34 @@
         <v>165.24</v>
       </c>
       <c r="V52" s="14">
-        <v>8.9434782608695649</v>
+        <v>9.3500000000000014</v>
       </c>
       <c r="W52" s="16">
-        <v>501.81818181818181</v>
+        <v>480</v>
       </c>
       <c r="X52" s="15">
-        <v>-160.95867768595042</v>
+        <v>-145.09090909090907</v>
       </c>
       <c r="Y52" s="18">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="Z52" s="17">
-        <v>49.410000000000004</v>
+        <v>42.120000000000005</v>
       </c>
       <c r="AA52" s="14">
-        <v>20.221917808219175</v>
+        <v>18.021917808219175</v>
       </c>
       <c r="AB52" s="16">
-        <v>66.363636363636374</v>
+        <v>63.478260869565219</v>
       </c>
       <c r="AC52" s="15">
-        <v>-5.363636363636374</v>
+        <v>-11.478260869565219</v>
       </c>
       <c r="AD52" s="19">
-        <v>7533</v>
+        <v>7998</v>
       </c>
       <c r="AE52" s="20">
-        <v>6101.7300000000005</v>
+        <v>6478.38</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6773,7 +6778,7 @@
         <v>336.91666666666669</v>
       </c>
     </row>
-    <row r="53" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="10">
         <v>150361</v>
       </c>
@@ -6784,85 +6789,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>2256</v>
+        <v>1560</v>
       </c>
       <c r="F53" s="14">
-        <v>1827.3600000000001</v>
+        <v>1263.6000000000001</v>
       </c>
       <c r="G53" s="14">
-        <v>8.700430278884463</v>
+        <v>6.2897211155378479</v>
       </c>
       <c r="H53" s="30">
-        <v>5704.545454545455</v>
+        <v>5456.521739130435</v>
       </c>
       <c r="I53" s="15">
-        <v>-336.97520661157023</v>
+        <v>-920.23715415019797</v>
       </c>
       <c r="J53" s="16">
-        <v>7787</v>
+        <v>6808</v>
       </c>
       <c r="K53" s="13">
-        <v>6307.47</v>
+        <v>5514.4800000000005</v>
       </c>
       <c r="L53" s="14">
-        <v>70.525973053892216</v>
+        <v>64.461976047904187</v>
       </c>
       <c r="M53" s="30">
-        <v>2429.090909090909</v>
+        <v>2323.4782608695655</v>
       </c>
       <c r="N53" s="15">
-        <v>6682.8677685950415</v>
+        <v>5751.873517786561</v>
       </c>
       <c r="O53" s="16">
-        <v>327</v>
+        <v>220</v>
       </c>
       <c r="P53" s="17">
-        <v>264.87</v>
+        <v>178.20000000000002</v>
       </c>
       <c r="Q53" s="14">
-        <v>10.622013422818791</v>
+        <v>7.4711409395973147</v>
       </c>
       <c r="R53" s="16">
-        <v>677.27272727272737</v>
+        <v>647.82608695652175</v>
       </c>
       <c r="S53" s="15">
-        <v>-288.70247933884298</v>
+        <v>-368.93280632411074</v>
       </c>
       <c r="T53" s="18">
-        <v>497</v>
+        <v>414</v>
       </c>
       <c r="U53" s="17">
-        <v>402.57000000000005</v>
+        <v>335.34000000000003</v>
       </c>
       <c r="V53" s="14">
-        <v>9.5379857256145897</v>
+        <v>8.3062648691514678</v>
       </c>
       <c r="W53" s="16">
-        <v>1146.3636363636365</v>
+        <v>1096.5217391304348</v>
       </c>
       <c r="X53" s="15">
-        <v>-336.7190082644629</v>
+        <v>-383.47035573122525</v>
       </c>
       <c r="Y53" s="18">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="Z53" s="17">
-        <v>147.42000000000002</v>
+        <v>140.13</v>
       </c>
       <c r="AA53" s="14">
-        <v>25.312643678160917</v>
+        <v>25.154597701149427</v>
       </c>
       <c r="AB53" s="16">
-        <v>158.18181818181819</v>
+        <v>151.30434782608694</v>
       </c>
       <c r="AC53" s="15">
-        <v>23.818181818181813</v>
+        <v>21.695652173913061</v>
       </c>
       <c r="AD53" s="19">
-        <v>11049</v>
+        <v>9175</v>
       </c>
       <c r="AE53" s="20">
-        <v>8949.69</v>
+        <v>7431.7500000000009</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6886,7 +6891,7 @@
         <v>739.16666666666663</v>
       </c>
     </row>
-    <row r="54" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="10">
         <v>150362</v>
       </c>
@@ -6897,85 +6902,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>2772</v>
+        <v>1926</v>
       </c>
       <c r="F54" s="14">
-        <v>2245.3200000000002</v>
+        <v>1560.0600000000002</v>
       </c>
       <c r="G54" s="14">
-        <v>14.31549295774648</v>
+        <v>10.398591549295775</v>
       </c>
       <c r="H54" s="30">
-        <v>4260</v>
+        <v>4074.782608695652</v>
       </c>
       <c r="I54" s="15">
-        <v>835.63636363636374</v>
+        <v>73.826086956521976</v>
       </c>
       <c r="J54" s="16">
-        <v>1843</v>
+        <v>981</v>
       </c>
       <c r="K54" s="13">
-        <v>1492.8300000000002</v>
+        <v>794.61</v>
       </c>
       <c r="L54" s="14">
-        <v>34.574108527131784</v>
+        <v>19.239767441860462</v>
       </c>
       <c r="M54" s="30">
-        <v>1172.7272727272727</v>
+        <v>1121.7391304347827</v>
       </c>
       <c r="N54" s="15">
-        <v>1309.9421487603306</v>
+        <v>471.11857707509876</v>
       </c>
       <c r="O54" s="16">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P54" s="17">
-        <v>104.49000000000001</v>
+        <v>99.63000000000001</v>
       </c>
       <c r="Q54" s="14">
-        <v>9.403012048192771</v>
+        <v>9.3731927710843372</v>
       </c>
       <c r="R54" s="16">
-        <v>301.81818181818181</v>
+        <v>288.69565217391306</v>
       </c>
       <c r="S54" s="15">
-        <v>-145.38016528925618</v>
+        <v>-139.4505928853755</v>
       </c>
       <c r="T54" s="18">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="U54" s="17">
-        <v>324.81</v>
+        <v>295.65000000000003</v>
       </c>
       <c r="V54" s="14">
-        <v>20.05</v>
+        <v>19.079545454545453</v>
       </c>
       <c r="W54" s="16">
-        <v>440</v>
+        <v>420.86956521739131</v>
       </c>
       <c r="X54" s="15">
-        <v>81</v>
+        <v>58.913043478260875</v>
       </c>
       <c r="Y54" s="18">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="Z54" s="17">
-        <v>138.51000000000002</v>
+        <v>131.22</v>
       </c>
       <c r="AA54" s="14">
-        <v>21.221538461538465</v>
+        <v>21.018461538461537</v>
       </c>
       <c r="AB54" s="16">
-        <v>177.27272727272725</v>
+        <v>169.56521739130434</v>
       </c>
       <c r="AC54" s="15">
-        <v>-6.2727272727272236</v>
+        <v>-7.5652173913043441</v>
       </c>
       <c r="AD54" s="19">
-        <v>5316</v>
+        <v>3557</v>
       </c>
       <c r="AE54" s="20">
-        <v>4305.96</v>
+        <v>2881.17</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -6999,7 +7004,7 @@
         <v>1015.4166666666666</v>
       </c>
     </row>
-    <row r="55" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B55" s="10">
         <v>150363</v>
       </c>
@@ -7010,85 +7015,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>1577</v>
+        <v>978</v>
       </c>
       <c r="F55" s="14">
-        <v>1277.3700000000001</v>
+        <v>792.18000000000006</v>
       </c>
       <c r="G55" s="14">
-        <v>9.6591748924322935</v>
+        <v>6.2625664388762328</v>
       </c>
       <c r="H55" s="30">
-        <v>3591.818181818182</v>
+        <v>3435.652173913044</v>
       </c>
       <c r="I55" s="15">
-        <v>-55.644628099173815</v>
+        <v>-583.66007905138372</v>
       </c>
       <c r="J55" s="16">
-        <v>6017</v>
+        <v>5640</v>
       </c>
       <c r="K55" s="13">
-        <v>4873.7700000000004</v>
+        <v>4568.4000000000005</v>
       </c>
       <c r="L55" s="14">
-        <v>93.280845611787328</v>
+        <v>91.410634208840492</v>
       </c>
       <c r="M55" s="30">
-        <v>1419.090909090909</v>
+        <v>1357.391304347826</v>
       </c>
       <c r="N55" s="15">
-        <v>5371.9586776859505</v>
+        <v>5023.00395256917</v>
       </c>
       <c r="O55" s="16">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="P55" s="17">
-        <v>192.78</v>
+        <v>164.43</v>
       </c>
       <c r="Q55" s="14">
-        <v>13.210091743119266</v>
+        <v>11.779587155963302</v>
       </c>
       <c r="R55" s="16">
-        <v>396.36363636363632</v>
+        <v>379.13043478260869</v>
       </c>
       <c r="S55" s="15">
-        <v>-122.3305785123967</v>
+        <v>-141.66403162055337</v>
       </c>
       <c r="T55" s="18">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="U55" s="17">
-        <v>300.51000000000005</v>
+        <v>280.26</v>
       </c>
       <c r="V55" s="14">
-        <v>16.06118067978533</v>
+        <v>15.659749552772809</v>
       </c>
       <c r="W55" s="16">
-        <v>508.18181818181819</v>
+        <v>486.08695652173913</v>
       </c>
       <c r="X55" s="15">
-        <v>1.4132231404958588</v>
+        <v>-7.5177865612648134</v>
       </c>
       <c r="Y55" s="18">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="Z55" s="17">
-        <v>151.47</v>
+        <v>144.18</v>
       </c>
       <c r="AA55" s="14">
-        <v>23.088775510204083</v>
+        <v>22.976530612244897</v>
       </c>
       <c r="AB55" s="16">
-        <v>178.18181818181816</v>
+        <v>170.43478260869566</v>
       </c>
       <c r="AC55" s="15">
-        <v>8.8181818181818414</v>
+        <v>7.5652173913043441</v>
       </c>
       <c r="AD55" s="19">
-        <v>8390</v>
+        <v>7345</v>
       </c>
       <c r="AE55" s="20">
-        <v>6795.9000000000005</v>
+        <v>5949.4500000000007</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7112,7 +7117,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="56" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B56" s="10">
         <v>151500</v>
       </c>
@@ -7123,64 +7128,64 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="F56" s="14">
-        <v>867.22</v>
+        <v>987.74</v>
       </c>
       <c r="G56" s="14">
-        <v>10.088413098236776</v>
+        <v>12.012720403022671</v>
       </c>
       <c r="H56" s="30">
-        <v>721.81818181818187</v>
+        <v>690.43478260869563</v>
       </c>
       <c r="I56" s="15">
-        <v>2.9008264462809734</v>
+        <v>63.166007905138372</v>
       </c>
       <c r="J56" s="32">
-        <v>261</v>
+        <v>189</v>
       </c>
       <c r="K56" s="13">
-        <v>683.82</v>
+        <v>495.18</v>
       </c>
       <c r="L56" s="14">
-        <v>21.338513513513512</v>
+        <v>16.154391891891891</v>
       </c>
       <c r="M56" s="30">
-        <v>269.09090909090912</v>
+        <v>257.39130434782612</v>
       </c>
       <c r="N56" s="15">
-        <v>138.68595041322311</v>
+        <v>72.00395256916994</v>
       </c>
       <c r="O56" s="32">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P56" s="17">
-        <v>110.04</v>
+        <v>107.42</v>
       </c>
       <c r="Q56" s="14">
-        <v>16.940000000000001</v>
+        <v>17.288333333333334</v>
       </c>
       <c r="R56" s="16">
-        <v>54.54545454545454</v>
+        <v>52.173913043478265</v>
       </c>
       <c r="S56" s="15">
-        <v>-7.5867768595041269</v>
+        <v>-6.430830039525695</v>
       </c>
       <c r="T56" s="18">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="U56" s="17">
-        <v>243.66</v>
+        <v>196.5</v>
       </c>
       <c r="V56" s="14">
-        <v>14.426923076923078</v>
+        <v>12.163461538461538</v>
       </c>
       <c r="W56" s="16">
-        <v>141.81818181818181</v>
+        <v>135.65217391304347</v>
       </c>
       <c r="X56" s="15">
-        <v>-10.140495867768593</v>
+        <v>-23.656126482213438</v>
       </c>
       <c r="Y56" s="18">
         <v>36</v>
@@ -7189,19 +7194,19 @@
         <v>94.320000000000007</v>
       </c>
       <c r="AA56" s="14">
-        <v>20.260465116279068</v>
+        <v>21.18139534883721</v>
       </c>
       <c r="AB56" s="16">
-        <v>39.090909090909093</v>
+        <v>37.391304347826086</v>
       </c>
       <c r="AC56" s="15">
-        <v>-3.0909090909090935</v>
+        <v>-1.391304347826086</v>
       </c>
       <c r="AD56" s="19">
-        <v>763</v>
+        <v>718</v>
       </c>
       <c r="AE56" s="20">
-        <v>1999.0600000000002</v>
+        <v>1881.16</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7225,7 +7230,7 @@
         <v>142.66666666666666</v>
       </c>
     </row>
-    <row r="57" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B57" s="10">
         <v>151501</v>
       </c>
@@ -7236,49 +7241,49 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>52</v>
+        <v>383</v>
       </c>
       <c r="F57" s="14">
-        <v>136.24</v>
+        <v>1003.46</v>
       </c>
       <c r="G57" s="14">
-        <v>0.93561338289962825</v>
+        <v>7.2043866171003712</v>
       </c>
       <c r="H57" s="30">
-        <v>1222.7272727272727</v>
+        <v>1169.5652173913045</v>
       </c>
       <c r="I57" s="15">
-        <v>-503.78512396694214</v>
+        <v>-148.62055335968387</v>
       </c>
       <c r="J57" s="32">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="K57" s="13">
-        <v>678.58</v>
+        <v>432.3</v>
       </c>
       <c r="L57" s="14">
-        <v>11.132859680284191</v>
+        <v>7.4147424511545283</v>
       </c>
       <c r="M57" s="30">
-        <v>511.81818181818181</v>
+        <v>489.56521739130437</v>
       </c>
       <c r="N57" s="15">
-        <v>26.355371900826469</v>
+        <v>-57.529644268774717</v>
       </c>
       <c r="O57" s="32">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P57" s="17">
-        <v>180.78</v>
+        <v>175.54000000000002</v>
       </c>
       <c r="Q57" s="14">
-        <v>11.436986301369862</v>
+        <v>11.610273972602739</v>
       </c>
       <c r="R57" s="16">
-        <v>132.72727272727275</v>
+        <v>126.95652173913044</v>
       </c>
       <c r="S57" s="15">
-        <v>-51.661157024793397</v>
+        <v>-48.415019762845859</v>
       </c>
       <c r="T57" s="18">
         <v>4</v>
@@ -7287,34 +7292,34 @@
         <v>10.48</v>
       </c>
       <c r="V57" s="14">
-        <v>0.21607142857142858</v>
+        <v>0.22589285714285715</v>
       </c>
       <c r="W57" s="16">
-        <v>407.27272727272725</v>
+        <v>389.56521739130437</v>
       </c>
       <c r="X57" s="15">
-        <v>-292.198347107438</v>
+        <v>-279.32015810276681</v>
       </c>
       <c r="Y57" s="18">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z57" s="17">
-        <v>117.9</v>
+        <v>115.28</v>
       </c>
       <c r="AA57" s="14">
-        <v>24.75</v>
+        <v>25.3</v>
       </c>
       <c r="AB57" s="16">
-        <v>40</v>
+        <v>38.260869565217391</v>
       </c>
       <c r="AC57" s="15">
-        <v>5</v>
+        <v>5.7391304347826093</v>
       </c>
       <c r="AD57" s="19">
-        <v>429</v>
+        <v>663</v>
       </c>
       <c r="AE57" s="20">
-        <v>1123.98</v>
+        <v>1737.0600000000002</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7338,7 +7343,7 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="58" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B58" s="10">
         <v>151502</v>
       </c>
@@ -7349,64 +7354,64 @@
         <v>2.62</v>
       </c>
       <c r="E58" s="13">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="F58" s="14">
-        <v>47.160000000000004</v>
+        <v>345.84000000000003</v>
       </c>
       <c r="G58" s="14">
-        <v>0.84747081712062267</v>
+        <v>6.4972762645914388</v>
       </c>
       <c r="H58" s="30">
-        <v>467.27272727272725</v>
+        <v>446.95652173913049</v>
       </c>
       <c r="I58" s="15">
-        <v>-194.39669421487602</v>
+        <v>-71.162055335968404</v>
       </c>
       <c r="J58" s="32">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="K58" s="13">
-        <v>424.44</v>
+        <v>199.12</v>
       </c>
       <c r="L58" s="14">
-        <v>19.217647058823527</v>
+        <v>9.4254901960784316</v>
       </c>
       <c r="M58" s="30">
-        <v>185.45454545454547</v>
+        <v>177.39130434782609</v>
       </c>
       <c r="N58" s="15">
-        <v>77.702479338842963</v>
+        <v>-4.6324110671936722</v>
       </c>
       <c r="O58" s="32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P58" s="17">
-        <v>34.06</v>
+        <v>31.44</v>
       </c>
       <c r="Q58" s="14">
-        <v>7.15</v>
+        <v>6.9</v>
       </c>
       <c r="R58" s="16">
-        <v>40</v>
+        <v>38.260869565217391</v>
       </c>
       <c r="S58" s="15">
-        <v>-23.36363636363636</v>
+        <v>-22.782608695652172</v>
       </c>
       <c r="T58" s="18">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="U58" s="17">
-        <v>214.84</v>
+        <v>133.62</v>
       </c>
       <c r="V58" s="14">
-        <v>17.877477477477473</v>
+        <v>11.624324324324325</v>
       </c>
       <c r="W58" s="16">
-        <v>100.90909090909092</v>
+        <v>96.521739130434781</v>
       </c>
       <c r="X58" s="15">
-        <v>8.6115702479338694</v>
+        <v>-19.197628458498016</v>
       </c>
       <c r="Y58" s="18">
         <v>39</v>
@@ -7415,19 +7420,19 @@
         <v>102.18</v>
       </c>
       <c r="AA58" s="14">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="AB58" s="16">
-        <v>30</v>
+        <v>28.695652173913043</v>
       </c>
       <c r="AC58" s="15">
-        <v>9.0000000000000036</v>
+        <v>10.304347826086957</v>
       </c>
       <c r="AD58" s="19">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AE58" s="20">
-        <v>822.68000000000006</v>
+        <v>812.2</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7454,7 +7459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B59" s="33">
         <v>151503</v>
       </c>
@@ -7465,34 +7470,34 @@
         <v>2.62</v>
       </c>
       <c r="E59" s="13">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F59" s="14">
-        <v>269.86</v>
+        <v>358.94</v>
       </c>
       <c r="G59" s="14">
-        <v>3.9377567140600314</v>
+        <v>5.4756714060031602</v>
       </c>
       <c r="H59" s="30">
-        <v>575.4545454545455</v>
+        <v>550.43478260869563</v>
       </c>
       <c r="I59" s="15">
-        <v>-158.57024793388427</v>
+        <v>-113.197628458498</v>
       </c>
       <c r="J59" s="32">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="K59" s="13">
-        <v>379.90000000000003</v>
+        <v>345.84000000000003</v>
       </c>
       <c r="L59" s="14">
-        <v>14.620833333333335</v>
+        <v>13.914999999999999</v>
       </c>
       <c r="M59" s="30">
-        <v>218.18181818181816</v>
+        <v>208.69565217391306</v>
       </c>
       <c r="N59" s="15">
-        <v>45.826446280991746</v>
+        <v>37.13833992094861</v>
       </c>
       <c r="O59" s="32">
         <v>20</v>
@@ -7501,28 +7506,28 @@
         <v>52.400000000000006</v>
       </c>
       <c r="Q59" s="14">
-        <v>7.0144927536231885</v>
+        <v>7.3333333333333339</v>
       </c>
       <c r="R59" s="16">
-        <v>62.727272727272727</v>
+        <v>60</v>
       </c>
       <c r="S59" s="15">
-        <v>-37.024793388429757</v>
+        <v>-34.54545454545454</v>
       </c>
       <c r="T59" s="18">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U59" s="17">
-        <v>204.36</v>
+        <v>157.20000000000002</v>
       </c>
       <c r="V59" s="14">
-        <v>13.982222222222221</v>
+        <v>11.244444444444444</v>
       </c>
       <c r="W59" s="16">
-        <v>122.72727272727273</v>
+        <v>117.39130434782609</v>
       </c>
       <c r="X59" s="15">
-        <v>-11.256198347107443</v>
+        <v>-25.37549407114625</v>
       </c>
       <c r="Y59" s="18">
         <v>44</v>
@@ -7531,19 +7536,19 @@
         <v>115.28</v>
       </c>
       <c r="AA59" s="14">
-        <v>50.704761904761895</v>
+        <v>53.009523809523813</v>
       </c>
       <c r="AB59" s="16">
-        <v>19.090909090909093</v>
+        <v>18.260869565217391</v>
       </c>
       <c r="AC59" s="15">
-        <v>24.909090909090907</v>
+        <v>25.739130434782609</v>
       </c>
       <c r="AD59" s="19">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AE59" s="20">
-        <v>1021.8000000000001</v>
+        <v>1029.6600000000001</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7571,7 +7576,7 @@
         <v>3753</v>
       </c>
     </row>
-    <row r="60" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:39" x14ac:dyDescent="0.3">
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
       <c r="E60" s="35"/>
@@ -7611,16 +7616,16 @@
         <v>147790.42857142861</v>
       </c>
     </row>
-    <row r="61" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B61" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="67"/>
+      <c r="F61" s="69"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7649,18 +7654,18 @@
       <c r="AF61" s="36"/>
       <c r="AG61" s="36"/>
     </row>
-    <row r="62" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B62" s="68" t="s">
+    <row r="62" spans="2:39" x14ac:dyDescent="0.3">
+      <c r="B62" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="68"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>144171.42999999996</v>
+        <v>171057.71999999994</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>29.570639273878474</v>
+        <v>41.310061768856357</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7691,18 +7696,18 @@
       <c r="AF62" s="36"/>
       <c r="AG62" s="36"/>
     </row>
-    <row r="63" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B63" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>270685.82000000007</v>
+        <v>156648.04999999993</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>55.519687498237367</v>
+        <v>37.830158273306218</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7733,18 +7738,18 @@
       <c r="AF63" s="36"/>
       <c r="AG63" s="36"/>
     </row>
-    <row r="64" spans="2:39" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B64" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>25059.810000000005</v>
+        <v>22619.739999999994</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.1399545789476653</v>
+        <v>5.4626172767617334</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7775,18 +7780,18 @@
       <c r="AF64" s="36"/>
       <c r="AG64" s="36"/>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B65" s="41" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>35343.670000000006</v>
+        <v>52223.290000000023</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>7.2492512294911746</v>
+        <v>12.611809251712815</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7817,18 +7822,18 @@
       <c r="AF65" s="36"/>
       <c r="AG65" s="36"/>
     </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B66" s="41" t="s">
         <v>18</v>
       </c>
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>12288.52</v>
+        <v>11533.66</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.5204674194453172</v>
+        <v>2.7853534293628375</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7859,20 +7864,20 @@
       <c r="AF66" s="36"/>
       <c r="AG66" s="36"/>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B67" s="68" t="s">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B67" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="68"/>
+      <c r="C67" s="65"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>487549.25000000006</v>
-      </c>
-      <c r="E67" s="69">
+        <v>414082.46</v>
+      </c>
+      <c r="E67" s="66">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="69"/>
+      <c r="F67" s="66"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7901,7 +7906,7 @@
       <c r="AF67" s="36"/>
       <c r="AG67" s="36"/>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B68" s="46"/>
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
@@ -7935,7 +7940,7 @@
       <c r="AF68" s="36"/>
       <c r="AG68" s="36"/>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B69" s="39" t="s">
         <v>9</v>
       </c>
@@ -7971,18 +7976,18 @@
       <c r="AF69" s="36"/>
       <c r="AG69" s="36"/>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B70" s="68" t="s">
+    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B70" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="68"/>
+      <c r="C70" s="65"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>105856</v>
+        <v>121697</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>29.926241720216101</v>
+        <v>40.443124000943804</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8012,18 +8017,18 @@
       <c r="AF70" s="36"/>
       <c r="AG70" s="36"/>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B71" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>196356</v>
+        <v>118635</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>55.511233366221589</v>
+        <v>39.425540611945806</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8054,18 +8059,18 @@
       <c r="AF71" s="36"/>
       <c r="AG71" s="36"/>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B72" s="41" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>17998</v>
+        <v>16096</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.0881622060199652</v>
+        <v>5.3491254831194812</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8096,18 +8101,18 @@
       <c r="AF72" s="36"/>
       <c r="AG72" s="36"/>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B73" s="41" t="s">
         <v>13</v>
       </c>
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>25001</v>
+        <v>36589</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>7.0679599573677709</v>
+        <v>12.159490078395795</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8138,18 +8143,18 @@
       <c r="AF73" s="36"/>
       <c r="AG73" s="36"/>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B74" s="41" t="s">
         <v>19</v>
       </c>
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>8512</v>
+        <v>7892</v>
       </c>
       <c r="E74" s="64">
         <f>D74*100/D75</f>
-        <v>2.4064027501745717</v>
+        <v>2.6227198255951136</v>
       </c>
       <c r="F74" s="64"/>
       <c r="G74" s="50"/>
@@ -8180,20 +8185,20 @@
       <c r="AF74" s="36"/>
       <c r="AG74" s="36"/>
     </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B75" s="68" t="s">
+    <row r="75" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="B75" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="68"/>
+      <c r="C75" s="65"/>
       <c r="D75" s="49">
         <f>SUM(AD13:AD59)</f>
-        <v>353723</v>
-      </c>
-      <c r="E75" s="69">
+        <v>300909</v>
+      </c>
+      <c r="E75" s="66">
         <f>D75*100/D75</f>
         <v>100</v>
       </c>
-      <c r="F75" s="69"/>
+      <c r="F75" s="66"/>
       <c r="G75" s="50"/>
       <c r="H75" s="50"/>
       <c r="I75" s="50"/>
@@ -8222,7 +8227,7 @@
       <c r="AF75" s="36"/>
       <c r="AG75" s="36"/>
     </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B76" s="46"/>
       <c r="C76" s="35"/>
       <c r="D76" s="52"/>
@@ -8256,7 +8261,7 @@
       <c r="AF76" s="36"/>
       <c r="AG76" s="36"/>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B77" s="46"/>
       <c r="C77" s="35"/>
       <c r="D77" s="35"/>
@@ -8290,7 +8295,7 @@
       <c r="AF77" s="36"/>
       <c r="AG77" s="36"/>
     </row>
-    <row r="78" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B78" s="46"/>
       <c r="C78" s="35"/>
       <c r="D78" s="35"/>
@@ -8324,7 +8329,7 @@
       <c r="AF78" s="36"/>
       <c r="AG78" s="36"/>
     </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B79" s="46"/>
       <c r="C79" s="35"/>
       <c r="D79" s="35"/>
@@ -8358,7 +8363,7 @@
       <c r="AF79" s="36"/>
       <c r="AG79" s="36"/>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B80" s="46"/>
       <c r="C80" s="35"/>
       <c r="D80" s="35"/>
@@ -8392,7 +8397,7 @@
       <c r="AF80" s="36"/>
       <c r="AG80" s="36"/>
     </row>
-    <row r="81" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B81" s="46"/>
       <c r="C81" s="35"/>
       <c r="D81" s="35"/>
@@ -8426,7 +8431,7 @@
       <c r="AF81" s="36"/>
       <c r="AG81" s="36"/>
     </row>
-    <row r="82" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B82" s="46"/>
       <c r="C82" s="35"/>
       <c r="D82" s="35"/>
@@ -8460,7 +8465,7 @@
       <c r="AF82" s="36"/>
       <c r="AG82" s="36"/>
     </row>
-    <row r="83" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B83" s="46"/>
       <c r="C83" s="35"/>
       <c r="D83" s="35"/>
@@ -8494,7 +8499,7 @@
       <c r="AF83" s="36"/>
       <c r="AG83" s="36"/>
     </row>
-    <row r="84" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B84" s="46"/>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -8528,7 +8533,7 @@
       <c r="AF84" s="36"/>
       <c r="AG84" s="36"/>
     </row>
-    <row r="85" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B85" s="46"/>
       <c r="C85" s="35"/>
       <c r="D85" s="35"/>
@@ -8562,7 +8567,7 @@
       <c r="AF85" s="36"/>
       <c r="AG85" s="36"/>
     </row>
-    <row r="86" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B86" s="46"/>
       <c r="C86" s="35"/>
       <c r="D86" s="35"/>
@@ -8596,7 +8601,7 @@
       <c r="AF86" s="36"/>
       <c r="AG86" s="36"/>
     </row>
-    <row r="87" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B87" s="46"/>
       <c r="C87" s="35"/>
       <c r="D87" s="35"/>
@@ -8630,7 +8635,7 @@
       <c r="AF87" s="36"/>
       <c r="AG87" s="36"/>
     </row>
-    <row r="88" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B88" s="46"/>
       <c r="C88" s="35"/>
       <c r="D88" s="35"/>
@@ -8664,7 +8669,7 @@
       <c r="AF88" s="36"/>
       <c r="AG88" s="36"/>
     </row>
-    <row r="89" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B89" s="46"/>
       <c r="C89" s="35"/>
       <c r="D89" s="35"/>
@@ -8698,7 +8703,7 @@
       <c r="AF89" s="36"/>
       <c r="AG89" s="36"/>
     </row>
-    <row r="90" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B90" s="46"/>
       <c r="C90" s="35"/>
       <c r="D90" s="35"/>
@@ -8708,7 +8713,7 @@
       <c r="AF90" s="36"/>
       <c r="AG90" s="36"/>
     </row>
-    <row r="91" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B91" s="46"/>
       <c r="C91" s="35"/>
       <c r="D91" s="35"/>
@@ -8718,7 +8723,7 @@
       <c r="AF91" s="36"/>
       <c r="AG91" s="36"/>
     </row>
-    <row r="92" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B92" s="46"/>
       <c r="C92" s="35"/>
       <c r="D92" s="35"/>
@@ -8728,7 +8733,7 @@
       <c r="AF92" s="36"/>
       <c r="AG92" s="36"/>
     </row>
-    <row r="93" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B93" s="46"/>
       <c r="C93" s="35"/>
       <c r="D93" s="35"/>
@@ -8740,17 +8745,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
     <mergeCell ref="E65:F65"/>
     <mergeCell ref="E63:F63"/>
     <mergeCell ref="E64:F64"/>
@@ -8759,6 +8753,17 @@
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="E75:F75"/>
   </mergeCells>
   <conditionalFormatting sqref="G13:G59">
     <cfRule type="colorScale" priority="14">

--- a/data/Sistema Integral de Control de Inventarios.xlsx
+++ b/data/Sistema Integral de Control de Inventarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0541FDD-7290-4684-8366-634006005792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FF0E40-0F04-4866-9EE0-41DDACFB05A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75DCD74C-609F-43BF-97F7-A30B35570E21}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -802,12 +802,6 @@
     <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -816,6 +810,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1644,268 +1644,268 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2ADD65-CD71-49F6-BA3C-8A3390E00AC0}">
   <dimension ref="A1:AM93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="51" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="34"/>
-    <col min="3" max="3" width="35.44140625" style="48" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="51" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="34"/>
+    <col min="3" max="3" width="35.42578125" style="48" customWidth="1"/>
     <col min="4" max="4" width="11" style="48" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" style="53" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="53" customWidth="1"/>
     <col min="6" max="9" width="11" style="53" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="48" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="48" customWidth="1"/>
     <col min="11" max="14" width="11" style="48" customWidth="1"/>
-    <col min="15" max="15" width="12.109375" style="48" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" style="48" customWidth="1"/>
     <col min="16" max="19" width="11" style="48" customWidth="1"/>
-    <col min="20" max="20" width="12.109375" style="48" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" style="48" customWidth="1"/>
     <col min="21" max="24" width="11" style="48" customWidth="1"/>
-    <col min="25" max="25" width="12.109375" style="48" customWidth="1"/>
+    <col min="25" max="25" width="12.140625" style="48" customWidth="1"/>
     <col min="26" max="29" width="11" style="48" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" style="48" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="48" customWidth="1"/>
     <col min="31" max="31" width="11" style="48" customWidth="1"/>
-    <col min="32" max="33" width="12.6640625" style="54" customWidth="1"/>
-    <col min="38" max="38" width="9.109375" customWidth="1"/>
+    <col min="32" max="33" width="12.7109375" style="54" customWidth="1"/>
+    <col min="38" max="38" width="9.140625" customWidth="1"/>
     <col min="39" max="39" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="67" t="s">
+    <row r="1" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="68" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
+      <c r="AB1" s="65"/>
+      <c r="AC1" s="65"/>
+      <c r="AD1" s="65"/>
+      <c r="AE1" s="65"/>
+      <c r="AF1" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
-      <c r="AI1" s="68"/>
-      <c r="AJ1" s="68"/>
-      <c r="AK1" s="68"/>
-      <c r="AL1" s="68"/>
-    </row>
-    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-    </row>
-    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="67"/>
-      <c r="AE3" s="67"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
-    </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
-      <c r="U4" s="67"/>
-      <c r="V4" s="67"/>
-      <c r="W4" s="67"/>
-      <c r="X4" s="67"/>
-      <c r="Y4" s="67"/>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="67"/>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="67"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="68"/>
-      <c r="AG4" s="68"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
-      <c r="AK4" s="68"/>
-      <c r="AL4" s="68"/>
-    </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="67"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="67"/>
-      <c r="X5" s="67"/>
-      <c r="Y5" s="67"/>
-      <c r="Z5" s="67"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="67"/>
-      <c r="AC5" s="67"/>
-      <c r="AD5" s="67"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
-    </row>
-    <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
-      <c r="AK6" s="68"/>
-      <c r="AL6" s="68"/>
-    </row>
-    <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG1" s="66"/>
+      <c r="AH1" s="66"/>
+      <c r="AI1" s="66"/>
+      <c r="AJ1" s="66"/>
+      <c r="AK1" s="66"/>
+      <c r="AL1" s="66"/>
+    </row>
+    <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="65"/>
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="65"/>
+      <c r="Q2" s="65"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+      <c r="X2" s="65"/>
+      <c r="Y2" s="65"/>
+      <c r="Z2" s="65"/>
+      <c r="AA2" s="65"/>
+      <c r="AB2" s="65"/>
+      <c r="AC2" s="65"/>
+      <c r="AD2" s="65"/>
+      <c r="AE2" s="65"/>
+      <c r="AF2" s="66"/>
+      <c r="AG2" s="66"/>
+      <c r="AH2" s="66"/>
+      <c r="AI2" s="66"/>
+      <c r="AJ2" s="66"/>
+      <c r="AK2" s="66"/>
+      <c r="AL2" s="66"/>
+    </row>
+    <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="65"/>
+      <c r="N3" s="65"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="66"/>
+      <c r="AG3" s="66"/>
+      <c r="AH3" s="66"/>
+      <c r="AI3" s="66"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="66"/>
+    </row>
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66"/>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
+    </row>
+    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="66"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="66"/>
+      <c r="AL5" s="66"/>
+    </row>
+    <row r="6" spans="1:38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="65"/>
+      <c r="Q6" s="65"/>
+      <c r="R6" s="65"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
+      <c r="AL6" s="66"/>
+    </row>
+    <row r="7" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1945,7 +1945,7 @@
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
     </row>
-    <row r="8" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1985,7 +1985,7 @@
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
     </row>
-    <row r="9" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -2025,7 +2025,7 @@
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
     </row>
-    <row r="10" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
@@ -2065,7 +2065,7 @@
       <c r="AK10" s="5"/>
       <c r="AL10" s="5"/>
     </row>
-    <row r="11" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" s="55" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
@@ -2105,7 +2105,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" s="61" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" s="61" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A12" s="56"/>
       <c r="B12" s="57" t="str">
         <f>'[1]INVENTARIO NACIONAL 03-09-26'!B12</f>
@@ -2256,7 +2256,7 @@
         <v>Inventario de Cestas</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56"/>
       <c r="B13" s="10" t="s">
         <v>20</v>
@@ -2268,85 +2268,85 @@
         <v>1.36</v>
       </c>
       <c r="E13" s="13">
-        <v>5308</v>
+        <v>3770</v>
       </c>
       <c r="F13" s="14">
-        <v>7218.88</v>
+        <v>5127.2000000000007</v>
       </c>
       <c r="G13" s="14">
-        <v>7.5301334529550292</v>
+        <v>6.2784008074464515</v>
       </c>
       <c r="H13" s="30">
-        <v>15507.826086956522</v>
+        <v>13210.370370370369</v>
       </c>
       <c r="I13" s="15">
-        <v>-1741.01185770751</v>
+        <v>-2234.7138047138033</v>
       </c>
       <c r="J13" s="16">
-        <v>2539</v>
+        <v>2172</v>
       </c>
       <c r="K13" s="13">
-        <v>3453.0400000000004</v>
+        <v>2953.92</v>
       </c>
       <c r="L13" s="14">
-        <v>12.7910593389088</v>
+        <v>12.845161290322581</v>
       </c>
       <c r="M13" s="30">
-        <v>4366.9565217391309</v>
+        <v>3720</v>
       </c>
       <c r="N13" s="15">
-        <v>554.01976284584975</v>
+        <v>481.09090909090901</v>
       </c>
       <c r="O13" s="16">
-        <v>696</v>
+        <v>560</v>
       </c>
       <c r="P13" s="17">
-        <v>946.56000000000006</v>
+        <v>761.6</v>
       </c>
       <c r="Q13" s="14">
-        <v>18.209720785935886</v>
+        <v>17.199586349534641</v>
       </c>
       <c r="R13" s="16">
-        <v>840.86956521739125</v>
+        <v>716.2962962962963</v>
       </c>
       <c r="S13" s="15">
-        <v>-68.426877470355635</v>
+        <v>-91.178451178451269</v>
       </c>
       <c r="T13" s="18">
-        <v>725</v>
+        <v>651</v>
       </c>
       <c r="U13" s="17">
-        <v>986.00000000000011</v>
+        <v>885.36</v>
       </c>
       <c r="V13" s="14">
-        <v>16.261081560283689</v>
+        <v>17.140691489361704</v>
       </c>
       <c r="W13" s="16">
-        <v>980.86956521739125</v>
+        <v>835.55555555555554</v>
       </c>
       <c r="X13" s="15">
-        <v>11.640316205533622</v>
+        <v>43.323232323232332</v>
       </c>
       <c r="Y13" s="18">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z13" s="17">
-        <v>544</v>
+        <v>408.00000000000006</v>
       </c>
       <c r="AA13" s="14">
-        <v>13.694181326116375</v>
+        <v>12.056833558863328</v>
       </c>
       <c r="AB13" s="16">
-        <v>642.60869565217388</v>
+        <v>547.40740740740739</v>
       </c>
       <c r="AC13" s="15">
-        <v>-242.60869565217388</v>
+        <v>-247.40740740740739</v>
       </c>
       <c r="AD13" s="19">
-        <v>9668</v>
+        <v>7453</v>
       </c>
       <c r="AE13" s="20">
-        <v>13148.480000000001</v>
+        <v>10136.08</v>
       </c>
       <c r="AF13" s="21">
         <v>11880.952380952382</v>
@@ -2370,7 +2370,7 @@
         <v>109.4</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56"/>
       <c r="B14" s="10" t="s">
         <v>22</v>
@@ -2381,7 +2381,9 @@
       <c r="D14" s="12">
         <v>1.59</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
       <c r="F14" s="14">
         <v>0</v>
       </c>
@@ -2389,40 +2391,40 @@
         <v>0</v>
       </c>
       <c r="H14" s="30">
-        <v>408.69565217391306</v>
+        <v>348.14814814814815</v>
       </c>
       <c r="I14" s="15">
-        <v>-185.77075098814231</v>
+        <v>-158.24915824915826</v>
       </c>
       <c r="J14" s="16">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K14" s="13">
-        <v>31.8</v>
+        <v>12.72</v>
       </c>
       <c r="L14" s="14">
-        <v>2.0321285140562253</v>
+        <v>0.95421686746987966</v>
       </c>
       <c r="M14" s="30">
-        <v>216.52173913043475</v>
+        <v>184.44444444444443</v>
       </c>
       <c r="N14" s="15">
-        <v>-78.418972332015798</v>
+        <v>-75.83838383838382</v>
       </c>
       <c r="O14" s="16">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="P14" s="17">
-        <v>127.2</v>
+        <v>92.22</v>
       </c>
       <c r="Q14" s="14">
-        <v>18.071428571428569</v>
+        <v>15.380357142857143</v>
       </c>
       <c r="R14" s="16">
-        <v>97.391304347826093</v>
+        <v>82.962962962962962</v>
       </c>
       <c r="S14" s="15">
-        <v>-8.537549407114625</v>
+        <v>-17.420875420875419</v>
       </c>
       <c r="T14" s="18">
         <v>7</v>
@@ -2431,13 +2433,13 @@
         <v>11.13</v>
       </c>
       <c r="V14" s="14">
-        <v>6.5592592592592593</v>
+        <v>7.7</v>
       </c>
       <c r="W14" s="16">
-        <v>23.478260869565219</v>
+        <v>20</v>
       </c>
       <c r="X14" s="15">
-        <v>-10.07509881422925</v>
+        <v>-7.545454545454545</v>
       </c>
       <c r="Y14" s="18">
         <v>7</v>
@@ -2446,19 +2448,19 @@
         <v>11.13</v>
       </c>
       <c r="AA14" s="14">
-        <v>1.9677777777777778</v>
+        <v>2.3099999999999996</v>
       </c>
       <c r="AB14" s="16">
-        <v>78.260869565217391</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="AC14" s="15">
-        <v>-71.260869565217391</v>
+        <v>-59.666666666666671</v>
       </c>
       <c r="AD14" s="19">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AE14" s="20">
-        <v>181.26000000000002</v>
+        <v>127.2</v>
       </c>
       <c r="AF14" s="21">
         <v>763.80952380952385</v>
@@ -2482,7 +2484,7 @@
         <v>8.1125000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56"/>
       <c r="B15" s="10" t="s">
         <v>24</v>
@@ -2494,85 +2496,85 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="13">
-        <v>2236</v>
+        <v>1977</v>
       </c>
       <c r="F15" s="14">
-        <v>4539.08</v>
+        <v>4013.3099999999995</v>
       </c>
       <c r="G15" s="14">
-        <v>7.5518355359765055</v>
+        <v>7.8383259911894276</v>
       </c>
       <c r="H15" s="30">
-        <v>6513.913043478261</v>
+        <v>5548.8888888888887</v>
       </c>
       <c r="I15" s="15">
-        <v>-724.86956521739103</v>
+        <v>-545.22222222222217</v>
       </c>
       <c r="J15" s="16">
-        <v>2287</v>
+        <v>1427</v>
       </c>
       <c r="K15" s="13">
-        <v>4642.6099999999997</v>
+        <v>2896.81</v>
       </c>
       <c r="L15" s="14">
-        <v>23.860247422680413</v>
+        <v>17.477072164948456</v>
       </c>
       <c r="M15" s="30">
-        <v>2108.695652173913</v>
+        <v>1796.2962962962961</v>
       </c>
       <c r="N15" s="15">
-        <v>1328.501976284585</v>
+        <v>610.5016835016836</v>
       </c>
       <c r="O15" s="16">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="P15" s="17">
-        <v>207.05999999999997</v>
+        <v>83.22999999999999</v>
       </c>
       <c r="Q15" s="14">
-        <v>9.1187279151943468</v>
+        <v>4.3028268551236755</v>
       </c>
       <c r="R15" s="16">
-        <v>246.08695652173913</v>
+        <v>209.62962962962962</v>
       </c>
       <c r="S15" s="15">
-        <v>-121.71541501976284</v>
+        <v>-149.57239057239056</v>
       </c>
       <c r="T15" s="18">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="U15" s="17">
-        <v>468.92999999999995</v>
+        <v>460.80999999999995</v>
       </c>
       <c r="V15" s="14">
-        <v>15.02390745501285</v>
+        <v>17.331362467866324</v>
       </c>
       <c r="W15" s="16">
-        <v>338.26086956521743</v>
+        <v>288.14814814814815</v>
       </c>
       <c r="X15" s="15">
-        <v>-15.007905138339964</v>
+        <v>17.437710437710422</v>
       </c>
       <c r="Y15" s="18">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="Z15" s="17">
-        <v>320.73999999999995</v>
+        <v>278.10999999999996</v>
       </c>
       <c r="AA15" s="14">
-        <v>18.592558139534884</v>
+        <v>18.925116279069766</v>
       </c>
       <c r="AB15" s="16">
-        <v>186.95652173913044</v>
+        <v>159.25925925925927</v>
       </c>
       <c r="AC15" s="15">
-        <v>-28.956521739130437</v>
+        <v>-22.259259259259267</v>
       </c>
       <c r="AD15" s="19">
-        <v>5014</v>
+        <v>3809</v>
       </c>
       <c r="AE15" s="20">
-        <v>10178.419999999998</v>
+        <v>7732.2699999999995</v>
       </c>
       <c r="AF15" s="21">
         <v>5094.7619047619046</v>
@@ -2596,7 +2598,7 @@
         <v>40.416666666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>26</v>
       </c>
@@ -2607,85 +2609,85 @@
         <v>3.61</v>
       </c>
       <c r="E16" s="13">
-        <v>357</v>
+        <v>222</v>
       </c>
       <c r="F16" s="14">
-        <v>1288.77</v>
+        <v>801.42</v>
       </c>
       <c r="G16" s="14">
-        <v>5.2819298245614039</v>
+        <v>3.8557894736842102</v>
       </c>
       <c r="H16" s="30">
-        <v>1486.9565217391303</v>
+        <v>1266.6666666666667</v>
       </c>
       <c r="I16" s="15">
-        <v>-318.88932806324112</v>
+        <v>-353.75757575757575</v>
       </c>
       <c r="J16" s="16">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="K16" s="13">
-        <v>942.20999999999992</v>
+        <v>815.86</v>
       </c>
       <c r="L16" s="14">
-        <v>11.940867992766728</v>
+        <v>12.137793851717902</v>
       </c>
       <c r="M16" s="30">
-        <v>480.86956521739131</v>
+        <v>409.62962962962962</v>
       </c>
       <c r="N16" s="15">
-        <v>42.42292490118578</v>
+        <v>39.804713804713799</v>
       </c>
       <c r="O16" s="16">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P16" s="17">
-        <v>108.3</v>
+        <v>43.32</v>
       </c>
       <c r="Q16" s="14">
-        <v>14.055555555555555</v>
+        <v>6.6000000000000005</v>
       </c>
       <c r="R16" s="16">
-        <v>46.956521739130437</v>
+        <v>40</v>
       </c>
       <c r="S16" s="15">
-        <v>-12.687747035573125</v>
+        <v>-24.36363636363636</v>
       </c>
       <c r="T16" s="18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U16" s="17">
-        <v>104.69</v>
+        <v>101.08</v>
       </c>
       <c r="V16" s="14">
-        <v>27.174074074074074</v>
+        <v>30.8</v>
       </c>
       <c r="W16" s="16">
-        <v>23.478260869565219</v>
+        <v>20</v>
       </c>
       <c r="X16" s="15">
-        <v>11.92490118577075</v>
+        <v>13.454545454545455</v>
       </c>
       <c r="Y16" s="18">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="Z16" s="17">
-        <v>231.04</v>
+        <v>180.5</v>
       </c>
       <c r="AA16" s="14">
-        <v>22.805633802816899</v>
+        <v>20.91549295774648</v>
       </c>
       <c r="AB16" s="16">
-        <v>61.739130434782609</v>
+        <v>52.592592592592595</v>
       </c>
       <c r="AC16" s="15">
-        <v>2.2608695652173836</v>
+        <v>-2.5925925925925952</v>
       </c>
       <c r="AD16" s="19">
-        <v>741</v>
+        <v>538</v>
       </c>
       <c r="AE16" s="20">
-        <v>2675.0099999999998</v>
+        <v>1942.1799999999998</v>
       </c>
       <c r="AF16" s="21">
         <v>980</v>
@@ -2709,7 +2711,7 @@
         <v>24.678571428571427</v>
       </c>
     </row>
-    <row r="17" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>28</v>
       </c>
@@ -2720,19 +2722,19 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="E17" s="13">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>342.41999999999996</v>
+        <v>184.38</v>
       </c>
       <c r="G17" s="14">
-        <v>3.8096525096525102</v>
+        <v>2.4081081081081077</v>
       </c>
       <c r="H17" s="30">
-        <v>225.21739130434781</v>
+        <v>191.85185185185188</v>
       </c>
       <c r="I17" s="15">
-        <v>-63.371541501976267</v>
+        <v>-66.205387205387211</v>
       </c>
       <c r="J17" s="16">
         <v>17</v>
@@ -2741,28 +2743,28 @@
         <v>149.26</v>
       </c>
       <c r="L17" s="14">
-        <v>9.1510638297872315</v>
+        <v>10.74255319148936</v>
       </c>
       <c r="M17" s="30">
-        <v>40.869565217391312</v>
+        <v>34.814814814814817</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.5770750988142339</v>
+        <v>1.175084175084173</v>
       </c>
       <c r="O17" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P17" s="17">
-        <v>70.239999999999995</v>
+        <v>52.679999999999993</v>
       </c>
       <c r="Q17" s="14">
-        <v>18.400000000000002</v>
+        <v>16.200000000000003</v>
       </c>
       <c r="R17" s="16">
-        <v>9.5652173913043477</v>
+        <v>8.148148148148147</v>
       </c>
       <c r="S17" s="15">
-        <v>-0.69565217391304301</v>
+        <v>-1.4074074074074057</v>
       </c>
       <c r="T17" s="18">
         <v>16</v>
@@ -2780,25 +2782,25 @@
         <v>14.545454545454545</v>
       </c>
       <c r="Y17" s="18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z17" s="17">
-        <v>52.679999999999993</v>
+        <v>26.339999999999996</v>
       </c>
       <c r="AA17" s="14">
-        <v>16.866666666666667</v>
+        <v>9.9000000000000021</v>
       </c>
       <c r="AB17" s="16">
-        <v>7.8260869565217392</v>
+        <v>6.6666666666666661</v>
       </c>
       <c r="AC17" s="15">
-        <v>-1.8260869565217392</v>
+        <v>-3.6666666666666661</v>
       </c>
       <c r="AD17" s="19">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AE17" s="20">
-        <v>755.07999999999993</v>
+        <v>553.14</v>
       </c>
       <c r="AF17" s="21">
         <v>119.52380952380952</v>
@@ -2822,7 +2824,7 @@
         <v>6.833333333333333</v>
       </c>
     </row>
-    <row r="18" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>30</v>
       </c>
@@ -2833,85 +2835,85 @@
         <v>0.63</v>
       </c>
       <c r="E18" s="13">
-        <v>6279</v>
+        <v>5836</v>
       </c>
       <c r="F18" s="14">
-        <v>3955.77</v>
+        <v>3676.68</v>
       </c>
       <c r="G18" s="14">
-        <v>8.8088444050127546</v>
+        <v>9.6112454253077502</v>
       </c>
       <c r="H18" s="30">
-        <v>15681.739130434782</v>
+        <v>13358.51851851852</v>
       </c>
       <c r="I18" s="15">
-        <v>-849.06324110671903</v>
+        <v>-236.05387205387342</v>
       </c>
       <c r="J18" s="16">
-        <v>6907</v>
+        <v>3086</v>
       </c>
       <c r="K18" s="13">
-        <v>4351.41</v>
+        <v>1944.18</v>
       </c>
       <c r="L18" s="14">
-        <v>23.405719260648269</v>
+        <v>12.27621216180016</v>
       </c>
       <c r="M18" s="30">
-        <v>6492.1739130434789</v>
+        <v>5530.3703703703704</v>
       </c>
       <c r="N18" s="15">
-        <v>3956.0118577075095</v>
+        <v>572.19528619528592</v>
       </c>
       <c r="O18" s="16">
-        <v>716</v>
+        <v>524</v>
       </c>
       <c r="P18" s="17">
-        <v>451.08</v>
+        <v>330.12</v>
       </c>
       <c r="Q18" s="14">
-        <v>13.966692367000771</v>
+        <v>11.999074787972244</v>
       </c>
       <c r="R18" s="16">
-        <v>1127.8260869565217</v>
+        <v>960.74074074074076</v>
       </c>
       <c r="S18" s="15">
-        <v>-309.296442687747</v>
+        <v>-349.40067340067333</v>
       </c>
       <c r="T18" s="18">
-        <v>2129</v>
+        <v>1760</v>
       </c>
       <c r="U18" s="17">
-        <v>1341.27</v>
+        <v>1108.8</v>
       </c>
       <c r="V18" s="14">
-        <v>14.409764579989298</v>
+        <v>13.983948635634027</v>
       </c>
       <c r="W18" s="16">
-        <v>3250.4347826086955</v>
+        <v>2768.8888888888891</v>
       </c>
       <c r="X18" s="15">
-        <v>-234.9525691699605</v>
+        <v>-253.7373737373739</v>
       </c>
       <c r="Y18" s="18">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Z18" s="17">
-        <v>91.35</v>
+        <v>49.77</v>
       </c>
       <c r="AA18" s="14">
-        <v>8.9257907542579069</v>
+        <v>5.7087591240875906</v>
       </c>
       <c r="AB18" s="16">
-        <v>357.39130434782612</v>
+        <v>304.44444444444446</v>
       </c>
       <c r="AC18" s="15">
-        <v>-212.39130434782612</v>
+        <v>-225.44444444444446</v>
       </c>
       <c r="AD18" s="19">
-        <v>16176</v>
+        <v>11285</v>
       </c>
       <c r="AE18" s="20">
-        <v>10190.879999999999</v>
+        <v>7109.55</v>
       </c>
       <c r="AF18" s="21">
         <v>14603.333333333332</v>
@@ -2935,7 +2937,7 @@
         <v>235.45</v>
       </c>
     </row>
-    <row r="19" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
         <v>32</v>
       </c>
@@ -2946,85 +2948,85 @@
         <v>0.63</v>
       </c>
       <c r="E19" s="13">
-        <v>514</v>
+        <v>416</v>
       </c>
       <c r="F19" s="14">
-        <v>323.82</v>
+        <v>262.08</v>
       </c>
       <c r="G19" s="14">
-        <v>9.1193548387096772</v>
+        <v>8.6642356241234229</v>
       </c>
       <c r="H19" s="30">
-        <v>1240</v>
+        <v>1056.2962962962963</v>
       </c>
       <c r="I19" s="15">
-        <v>-49.636363636363626</v>
+        <v>-64.134680134680139</v>
       </c>
       <c r="J19" s="16">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="K19" s="13">
-        <v>277.83</v>
+        <v>213.57</v>
       </c>
       <c r="L19" s="14">
-        <v>9.4233952702702695</v>
+        <v>8.5036317567567554</v>
       </c>
       <c r="M19" s="30">
-        <v>1029.5652173913045</v>
+        <v>877.03703703703707</v>
       </c>
       <c r="N19" s="15">
-        <v>-26.984189723320242</v>
+        <v>-59.653198653198672</v>
       </c>
       <c r="O19" s="16">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="P19" s="17">
-        <v>57.33</v>
+        <v>69.930000000000007</v>
       </c>
       <c r="Q19" s="14">
-        <v>22.795049504950498</v>
+        <v>32.640594059405935</v>
       </c>
       <c r="R19" s="16">
-        <v>87.826086956521735</v>
+        <v>74.814814814814824</v>
       </c>
       <c r="S19" s="15">
-        <v>11.158102766798422</v>
+        <v>42.986531986531986</v>
       </c>
       <c r="T19" s="18">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="U19" s="17">
-        <v>170.1</v>
+        <v>142.38</v>
       </c>
       <c r="V19" s="14">
-        <v>17.88219895287958</v>
+        <v>17.571204188481673</v>
       </c>
       <c r="W19" s="16">
-        <v>332.17391304347825</v>
+        <v>282.96296296296299</v>
       </c>
       <c r="X19" s="15">
-        <v>28.418972332015812</v>
+        <v>20.208754208754186</v>
       </c>
       <c r="Y19" s="18">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="Z19" s="17">
-        <v>121.59</v>
+        <v>106.47</v>
       </c>
       <c r="AA19" s="14">
-        <v>22.711162790697674</v>
+        <v>23.345581395348834</v>
       </c>
       <c r="AB19" s="16">
-        <v>186.95652173913044</v>
+        <v>159.25925925925927</v>
       </c>
       <c r="AC19" s="15">
-        <v>6.0434782608695627</v>
+        <v>9.7407407407407334</v>
       </c>
       <c r="AD19" s="19">
-        <v>1509</v>
+        <v>1261</v>
       </c>
       <c r="AE19" s="20">
-        <v>950.67</v>
+        <v>794.43</v>
       </c>
       <c r="AF19" s="21">
         <v>1503.8095238095239</v>
@@ -3048,7 +3050,7 @@
         <v>29.683333333333334</v>
       </c>
     </row>
-    <row r="20" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>34</v>
       </c>
@@ -3059,85 +3061,85 @@
         <v>0.63</v>
       </c>
       <c r="E20" s="13">
-        <v>1387</v>
+        <v>856</v>
       </c>
       <c r="F20" s="14">
-        <v>873.81000000000006</v>
+        <v>539.28</v>
       </c>
       <c r="G20" s="14">
-        <v>11.441506358004565</v>
+        <v>8.2892729051190095</v>
       </c>
       <c r="H20" s="30">
-        <v>2666.9565217391305</v>
+        <v>2271.8518518518517</v>
       </c>
       <c r="I20" s="15">
-        <v>174.7470355731225</v>
+        <v>-176.65993265993257</v>
       </c>
       <c r="J20" s="16">
-        <v>846</v>
+        <v>829</v>
       </c>
       <c r="K20" s="13">
-        <v>532.98</v>
+        <v>522.27</v>
       </c>
       <c r="L20" s="14">
-        <v>7.6170106761565828</v>
+        <v>8.7620284697508879</v>
       </c>
       <c r="M20" s="30">
-        <v>2443.4782608695655</v>
+        <v>2081.4814814814818</v>
       </c>
       <c r="N20" s="15">
-        <v>-264.67193675889348</v>
+        <v>-117.1279461279463</v>
       </c>
       <c r="O20" s="16">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="P20" s="17">
-        <v>124.11</v>
+        <v>95.76</v>
       </c>
       <c r="Q20" s="14">
-        <v>24.552216748768476</v>
+        <v>22.2384236453202</v>
       </c>
       <c r="R20" s="16">
-        <v>176.52173913043475</v>
+        <v>150.37037037037035</v>
       </c>
       <c r="S20" s="15">
-        <v>36.525691699604749</v>
+        <v>15.299663299663337</v>
       </c>
       <c r="T20" s="18">
-        <v>596</v>
+        <v>505</v>
       </c>
       <c r="U20" s="17">
-        <v>375.48</v>
+        <v>318.14999999999998</v>
       </c>
       <c r="V20" s="14">
-        <v>17.636023391812866</v>
+        <v>17.542105263157893</v>
       </c>
       <c r="W20" s="16">
-        <v>743.47826086956513</v>
+        <v>633.33333333333337</v>
       </c>
       <c r="X20" s="15">
-        <v>55.288537549407124</v>
+        <v>44.393939393939377</v>
       </c>
       <c r="Y20" s="18">
-        <v>154</v>
+        <v>90</v>
       </c>
       <c r="Z20" s="17">
-        <v>97.02</v>
+        <v>56.7</v>
       </c>
       <c r="AA20" s="14">
-        <v>11.100284900284901</v>
+        <v>7.615384615384615</v>
       </c>
       <c r="AB20" s="16">
-        <v>305.21739130434781</v>
+        <v>260</v>
       </c>
       <c r="AC20" s="15">
-        <v>-151.21739130434781</v>
+        <v>-170</v>
       </c>
       <c r="AD20" s="19">
-        <v>3180</v>
+        <v>2432</v>
       </c>
       <c r="AE20" s="20">
-        <v>2003.4</v>
+        <v>1532.16</v>
       </c>
       <c r="AF20" s="21">
         <v>3435.7142857142853</v>
@@ -3161,7 +3163,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="21" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
         <v>36</v>
       </c>
@@ -3172,85 +3174,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E21" s="13">
-        <v>2348</v>
+        <v>1324</v>
       </c>
       <c r="F21" s="14">
-        <v>2559.3200000000002</v>
+        <v>1443.16</v>
       </c>
       <c r="G21" s="14">
-        <v>8.5671185462936261</v>
+        <v>5.6710124026535906</v>
       </c>
       <c r="H21" s="30">
-        <v>6029.565217391304</v>
+        <v>5136.2962962962965</v>
       </c>
       <c r="I21" s="15">
-        <v>-392.71146245059253</v>
+        <v>-1010.6801346801349</v>
       </c>
       <c r="J21" s="16">
-        <v>1864</v>
+        <v>6835</v>
       </c>
       <c r="K21" s="13">
-        <v>2031.7600000000002</v>
+        <v>7450.1500000000005</v>
       </c>
       <c r="L21" s="14">
-        <v>6.1937483582873654</v>
+        <v>26.661347517730494</v>
       </c>
       <c r="M21" s="30">
-        <v>6620.869565217391</v>
+        <v>5640</v>
       </c>
       <c r="N21" s="15">
-        <v>-1145.486166007905</v>
+        <v>4271.363636363636</v>
       </c>
       <c r="O21" s="16">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="P21" s="17">
-        <v>373.87</v>
+        <v>349.89000000000004</v>
       </c>
       <c r="Q21" s="14">
-        <v>13.580438184663535</v>
+        <v>14.919718309859155</v>
       </c>
       <c r="R21" s="16">
-        <v>555.6521739130435</v>
+        <v>473.33333333333337</v>
       </c>
       <c r="S21" s="15">
-        <v>-162.13833992094868</v>
+        <v>-109.30303030303031</v>
       </c>
       <c r="T21" s="18">
-        <v>1135</v>
+        <v>1042</v>
       </c>
       <c r="U21" s="17">
-        <v>1237.1500000000001</v>
+        <v>1135.78</v>
       </c>
       <c r="V21" s="14">
-        <v>13.687082936129647</v>
+        <v>14.750905624404194</v>
       </c>
       <c r="W21" s="16">
-        <v>1824.3478260869565</v>
+        <v>1554.0740740740741</v>
       </c>
       <c r="X21" s="15">
-        <v>-191.798418972332</v>
+        <v>-88.235690235690299</v>
       </c>
       <c r="Y21" s="18">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="Z21" s="17">
-        <v>232.17000000000002</v>
+        <v>140.61000000000001</v>
       </c>
       <c r="AA21" s="14">
-        <v>11.250313152400835</v>
+        <v>7.9985386221294359</v>
       </c>
       <c r="AB21" s="16">
-        <v>416.52173913043475</v>
+        <v>354.81481481481478</v>
       </c>
       <c r="AC21" s="15">
-        <v>-203.52173913043475</v>
+        <v>-225.81481481481484</v>
       </c>
       <c r="AD21" s="19">
-        <v>5903</v>
+        <v>9651</v>
       </c>
       <c r="AE21" s="20">
-        <v>6434.27</v>
+        <v>10519.59</v>
       </c>
       <c r="AF21" s="21">
         <v>7661.9047619047615</v>
@@ -3274,7 +3276,7 @@
         <v>117.87037037037037</v>
       </c>
     </row>
-    <row r="22" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
         <v>38</v>
       </c>
@@ -3285,85 +3287,85 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E22" s="13">
-        <v>1646</v>
+        <v>990</v>
       </c>
       <c r="F22" s="14">
-        <v>1794.14</v>
+        <v>1079.1000000000001</v>
       </c>
       <c r="G22" s="14">
-        <v>9.5055466788404477</v>
+        <v>6.7114813969413367</v>
       </c>
       <c r="H22" s="30">
-        <v>3809.5652173913045</v>
+        <v>3245.1851851851852</v>
       </c>
       <c r="I22" s="15">
-        <v>-85.620553359683754</v>
+        <v>-485.08417508417529</v>
       </c>
       <c r="J22" s="16">
-        <v>2361</v>
+        <v>4687</v>
       </c>
       <c r="K22" s="13">
-        <v>2573.4900000000002</v>
+        <v>5108.83</v>
       </c>
       <c r="L22" s="14">
-        <v>17.814882195049208</v>
+        <v>41.516224276767069</v>
       </c>
       <c r="M22" s="30">
-        <v>2915.652173913044</v>
+        <v>2483.7037037037039</v>
       </c>
       <c r="N22" s="15">
-        <v>1035.7035573122528</v>
+        <v>3558.0437710437709</v>
       </c>
       <c r="O22" s="16">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="P22" s="17">
-        <v>73.03</v>
+        <v>64.31</v>
       </c>
       <c r="Q22" s="14">
-        <v>9.6862857142857148</v>
+        <v>10.013142857142856</v>
       </c>
       <c r="R22" s="16">
-        <v>152.17391304347825</v>
+        <v>129.62962962962965</v>
       </c>
       <c r="S22" s="15">
-        <v>-71.339920948616594</v>
+        <v>-58.845117845117855</v>
       </c>
       <c r="T22" s="18">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="U22" s="17">
-        <v>386.95000000000005</v>
+        <v>362.97</v>
       </c>
       <c r="V22" s="14">
-        <v>14.651712887438828</v>
+        <v>16.133931484502451</v>
       </c>
       <c r="W22" s="16">
-        <v>533.04347826086951</v>
+        <v>454.07407407407402</v>
       </c>
       <c r="X22" s="15">
-        <v>-32.667984189723256</v>
+        <v>2.7643097643098145</v>
       </c>
       <c r="Y22" s="18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="17">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="14">
-        <v>0.69505494505494514</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="16">
-        <v>158.26086956521738</v>
+        <v>134.81481481481481</v>
       </c>
       <c r="AC22" s="15">
-        <v>-153.26086956521738</v>
+        <v>-134.81481481481481</v>
       </c>
       <c r="AD22" s="19">
-        <v>4434</v>
+        <v>6069</v>
       </c>
       <c r="AE22" s="20">
-        <v>4833.0600000000004</v>
+        <v>6615.21</v>
       </c>
       <c r="AF22" s="21">
         <v>3628.0952380952381</v>
@@ -3387,7 +3389,7 @@
         <v>50.092592592592595</v>
       </c>
     </row>
-    <row r="23" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
         <v>40</v>
       </c>
@@ -3398,85 +3400,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E23" s="13">
-        <v>20089</v>
+        <v>16953</v>
       </c>
       <c r="F23" s="14">
-        <v>23303.239999999998</v>
+        <v>19665.48</v>
       </c>
       <c r="G23" s="14">
-        <v>14.006054343033512</v>
+        <v>13.875223214285715</v>
       </c>
       <c r="H23" s="30">
-        <v>31554.782608695648</v>
+        <v>26880</v>
       </c>
       <c r="I23" s="15">
-        <v>-1425.6245059288522</v>
+        <v>-1374.2727272727279</v>
       </c>
       <c r="J23" s="16">
-        <v>10065</v>
+        <v>9196</v>
       </c>
       <c r="K23" s="13">
-        <v>11675.4</v>
+        <v>10667.359999999999</v>
       </c>
       <c r="L23" s="14">
-        <v>11.995124593716142</v>
+        <v>12.865476470865328</v>
       </c>
       <c r="M23" s="30">
-        <v>18460</v>
+        <v>15725.185185185184</v>
       </c>
       <c r="N23" s="15">
-        <v>1674.0909090909081</v>
+        <v>2048.1885521885533</v>
       </c>
       <c r="O23" s="16">
-        <v>1747</v>
+        <v>1385</v>
       </c>
       <c r="P23" s="17">
-        <v>2026.5199999999998</v>
+        <v>1606.6</v>
       </c>
       <c r="Q23" s="14">
-        <v>13.007386698057681</v>
+        <v>12.105503237198352</v>
       </c>
       <c r="R23" s="16">
-        <v>2954.782608695652</v>
+        <v>2517.037037037037</v>
       </c>
       <c r="S23" s="15">
-        <v>-939.16600790513803</v>
+        <v>-903.21548821548822</v>
       </c>
       <c r="T23" s="18">
-        <v>5090</v>
+        <v>4186</v>
       </c>
       <c r="U23" s="17">
-        <v>5904.4</v>
+        <v>4855.7599999999993</v>
       </c>
       <c r="V23" s="14">
-        <v>9.8235563353421327</v>
+        <v>9.4838813029216578</v>
       </c>
       <c r="W23" s="16">
-        <v>11399.130434782608</v>
+        <v>9710.3703703703704</v>
       </c>
       <c r="X23" s="15">
-        <v>-3200.2766798418961</v>
+        <v>-2876.0875420875418</v>
       </c>
       <c r="Y23" s="18">
-        <v>768</v>
+        <v>595</v>
       </c>
       <c r="Z23" s="17">
-        <v>890.87999999999988</v>
+        <v>690.19999999999993</v>
       </c>
       <c r="AA23" s="14">
-        <v>15.36</v>
+        <v>13.969565217391304</v>
       </c>
       <c r="AB23" s="16">
-        <v>1100</v>
+        <v>937.03703703703707</v>
       </c>
       <c r="AC23" s="15">
-        <v>-332</v>
+        <v>-342.03703703703707</v>
       </c>
       <c r="AD23" s="19">
-        <v>37759</v>
+        <v>32315</v>
       </c>
       <c r="AE23" s="20">
-        <v>43800.439999999995</v>
+        <v>37485.399999999994</v>
       </c>
       <c r="AF23" s="21">
         <v>35215.238095238099</v>
@@ -3500,7 +3502,7 @@
         <v>682.05555555555554</v>
       </c>
     </row>
-    <row r="24" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
         <v>42</v>
       </c>
@@ -3511,85 +3513,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E24" s="13">
-        <v>9044</v>
+        <v>7490</v>
       </c>
       <c r="F24" s="14">
-        <v>10491.039999999999</v>
+        <v>8688.4</v>
       </c>
       <c r="G24" s="14">
-        <v>9.3202932790224047</v>
+        <v>9.0612219959266795</v>
       </c>
       <c r="H24" s="30">
-        <v>21347.82608695652</v>
+        <v>18185.185185185186</v>
       </c>
       <c r="I24" s="15">
-        <v>-659.55731225296404</v>
+        <v>-775.99326599326741</v>
       </c>
       <c r="J24" s="16">
-        <v>4307</v>
+        <v>5298</v>
       </c>
       <c r="K24" s="13">
-        <v>4996.12</v>
+        <v>6145.6799999999994</v>
       </c>
       <c r="L24" s="14">
-        <v>8.4229033006106508</v>
+        <v>12.162835278658111</v>
       </c>
       <c r="M24" s="30">
-        <v>11249.565217391304</v>
+        <v>9582.9629629629635</v>
       </c>
       <c r="N24" s="15">
-        <v>-806.43873517786596</v>
+        <v>942.1077441077432</v>
       </c>
       <c r="O24" s="16">
-        <v>1014</v>
+        <v>857</v>
       </c>
       <c r="P24" s="17">
-        <v>1176.24</v>
+        <v>994.11999999999989</v>
       </c>
       <c r="Q24" s="14">
-        <v>13.048931841302135</v>
+        <v>12.946541200406919</v>
       </c>
       <c r="R24" s="16">
-        <v>1709.5652173913045</v>
+        <v>1456.2962962962961</v>
       </c>
       <c r="S24" s="15">
-        <v>-540.15019762845873</v>
+        <v>-466.90572390572379</v>
       </c>
       <c r="T24" s="18">
-        <v>3520</v>
+        <v>3144</v>
       </c>
       <c r="U24" s="17">
-        <v>4083.2</v>
+        <v>3647.04</v>
       </c>
       <c r="V24" s="14">
-        <v>12.901057511227002</v>
+        <v>13.526988265971317</v>
       </c>
       <c r="W24" s="16">
-        <v>6002.608695652174</v>
+        <v>5113.333333333333</v>
       </c>
       <c r="X24" s="15">
-        <v>-845.53359683794497</v>
+        <v>-574.78787878787853</v>
       </c>
       <c r="Y24" s="18">
-        <v>445</v>
+        <v>300</v>
       </c>
       <c r="Z24" s="17">
-        <v>516.19999999999993</v>
+        <v>348</v>
       </c>
       <c r="AA24" s="14">
-        <v>11.977127659574467</v>
+        <v>9.4787234042553195</v>
       </c>
       <c r="AB24" s="16">
-        <v>817.39130434782612</v>
+        <v>696.2962962962963</v>
       </c>
       <c r="AC24" s="15">
-        <v>-372.39130434782612</v>
+        <v>-396.2962962962963</v>
       </c>
       <c r="AD24" s="19">
-        <v>18330</v>
+        <v>17089</v>
       </c>
       <c r="AE24" s="20">
-        <v>21262.799999999999</v>
+        <v>19823.239999999998</v>
       </c>
       <c r="AF24" s="21">
         <v>23050</v>
@@ -3613,7 +3615,7 @@
         <v>423.14814814814815</v>
       </c>
     </row>
-    <row r="25" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
         <v>44</v>
       </c>
@@ -3624,85 +3626,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E25" s="13">
-        <v>8555</v>
+        <v>7258</v>
       </c>
       <c r="F25" s="14">
-        <v>9923.7999999999993</v>
+        <v>8419.2799999999988</v>
       </c>
       <c r="G25" s="14">
-        <v>9.118317394784512</v>
+        <v>9.0812908118127815</v>
       </c>
       <c r="H25" s="30">
-        <v>20640.869565217392</v>
+        <v>17582.962962962964</v>
       </c>
       <c r="I25" s="15">
-        <v>-827.21343873517799</v>
+        <v>-734.25589225589283</v>
       </c>
       <c r="J25" s="16">
-        <v>12733</v>
+        <v>11714</v>
       </c>
       <c r="K25" s="13">
-        <v>14770.279999999999</v>
+        <v>13588.24</v>
       </c>
       <c r="L25" s="14">
-        <v>23.734244455905102</v>
+        <v>25.63219627201061</v>
       </c>
       <c r="M25" s="30">
-        <v>11802.608695652176</v>
+        <v>10054.074074074073</v>
       </c>
       <c r="N25" s="15">
-        <v>7368.177865612648</v>
+        <v>7143.9663299663298</v>
       </c>
       <c r="O25" s="16">
-        <v>1310</v>
+        <v>1136</v>
       </c>
       <c r="P25" s="17">
-        <v>1519.6</v>
+        <v>1317.76</v>
       </c>
       <c r="Q25" s="14">
-        <v>13.873168689828379</v>
+        <v>14.122729175387192</v>
       </c>
       <c r="R25" s="16">
-        <v>2077.391304347826</v>
+        <v>1769.6296296296296</v>
       </c>
       <c r="S25" s="15">
-        <v>-578.53754940711474</v>
+        <v>-472.75420875420878</v>
       </c>
       <c r="T25" s="18">
-        <v>3402</v>
+        <v>2967</v>
       </c>
       <c r="U25" s="17">
-        <v>3946.3199999999997</v>
+        <v>3441.72</v>
       </c>
       <c r="V25" s="14">
-        <v>12.098763002530223</v>
+        <v>12.386828788304753</v>
       </c>
       <c r="W25" s="16">
-        <v>6186.086956521739</v>
+        <v>5269.6296296296296</v>
       </c>
       <c r="X25" s="15">
-        <v>-1096.97233201581</v>
+        <v>-865.45791245791224</v>
       </c>
       <c r="Y25" s="18">
-        <v>319</v>
+        <v>202</v>
       </c>
       <c r="Z25" s="17">
-        <v>370.03999999999996</v>
+        <v>234.32</v>
       </c>
       <c r="AA25" s="14">
-        <v>11.833870967741936</v>
+        <v>8.7967741935483854</v>
       </c>
       <c r="AB25" s="16">
-        <v>593.04347826086951</v>
+        <v>505.18518518518522</v>
       </c>
       <c r="AC25" s="15">
-        <v>-274.04347826086951</v>
+        <v>-303.18518518518522</v>
       </c>
       <c r="AD25" s="19">
-        <v>26319</v>
+        <v>23277</v>
       </c>
       <c r="AE25" s="20">
-        <v>30530.039999999997</v>
+        <v>27001.32</v>
       </c>
       <c r="AF25" s="21">
         <v>22664.761904761905</v>
@@ -3726,7 +3728,7 @@
         <v>339.75925925925924</v>
       </c>
     </row>
-    <row r="26" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
         <v>46</v>
       </c>
@@ -3737,85 +3739,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E26" s="13">
-        <v>17059</v>
+        <v>14561</v>
       </c>
       <c r="F26" s="14">
-        <v>19788.439999999999</v>
+        <v>16890.759999999998</v>
       </c>
       <c r="G26" s="14">
-        <v>14.138527812356681</v>
+        <v>14.16699534822774</v>
       </c>
       <c r="H26" s="30">
-        <v>26544.347826086956</v>
+        <v>22611.851851851854</v>
       </c>
       <c r="I26" s="15">
-        <v>-1039.4189723320123</v>
+        <v>-856.17171717171732</v>
       </c>
       <c r="J26" s="16">
-        <v>9895</v>
+        <v>12131</v>
       </c>
       <c r="K26" s="13">
-        <v>11478.199999999999</v>
+        <v>14071.96</v>
       </c>
       <c r="L26" s="14">
-        <v>15.613290507671197</v>
+        <v>22.470419109392541</v>
       </c>
       <c r="M26" s="30">
-        <v>13942.608695652176</v>
+        <v>11877.037037037036</v>
       </c>
       <c r="N26" s="15">
-        <v>3557.450592885375</v>
+        <v>6732.3468013468009</v>
       </c>
       <c r="O26" s="16">
-        <v>918</v>
+        <v>709</v>
       </c>
       <c r="P26" s="17">
-        <v>1064.8799999999999</v>
+        <v>822.43999999999994</v>
       </c>
       <c r="Q26" s="14">
-        <v>12.065142857142856</v>
+        <v>10.938857142857144</v>
       </c>
       <c r="R26" s="16">
-        <v>1673.913043478261</v>
+        <v>1425.9259259259259</v>
       </c>
       <c r="S26" s="15">
-        <v>-603.73913043478274</v>
+        <v>-587.29629629629608</v>
       </c>
       <c r="T26" s="18">
-        <v>3478</v>
+        <v>2816</v>
       </c>
       <c r="U26" s="17">
-        <v>4034.4799999999996</v>
+        <v>3266.56</v>
       </c>
       <c r="V26" s="14">
-        <v>9.9686643253653564</v>
+        <v>9.4749291945168235</v>
       </c>
       <c r="W26" s="16">
-        <v>7675.652173913044</v>
+        <v>6538.5185185185182</v>
       </c>
       <c r="X26" s="15">
-        <v>-2104.292490118577</v>
+        <v>-1939.2861952861949</v>
       </c>
       <c r="Y26" s="18">
-        <v>548</v>
+        <v>408</v>
       </c>
       <c r="Z26" s="17">
-        <v>635.67999999999995</v>
+        <v>473.28</v>
       </c>
       <c r="AA26" s="14">
-        <v>13.091973559962229</v>
+        <v>11.442492917847026</v>
       </c>
       <c r="AB26" s="16">
-        <v>920.86956521739125</v>
+        <v>784.44444444444446</v>
       </c>
       <c r="AC26" s="15">
-        <v>-372.86956521739125</v>
+        <v>-376.44444444444434</v>
       </c>
       <c r="AD26" s="19">
-        <v>31898</v>
+        <v>30625</v>
       </c>
       <c r="AE26" s="20">
-        <v>37001.68</v>
+        <v>35525</v>
       </c>
       <c r="AF26" s="21">
         <v>26740</v>
@@ -3839,7 +3841,7 @@
         <v>438.35185185185185</v>
       </c>
     </row>
-    <row r="27" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="10">
         <v>130157</v>
       </c>
@@ -3850,85 +3852,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E27" s="13">
-        <v>2998</v>
+        <v>1871</v>
       </c>
       <c r="F27" s="14">
-        <v>3477.68</v>
+        <v>2170.3599999999997</v>
       </c>
       <c r="G27" s="14">
-        <v>9.5025557504384857</v>
+        <v>6.9617514407416694</v>
       </c>
       <c r="H27" s="30">
-        <v>6940.869565217391</v>
+        <v>5912.5925925925922</v>
       </c>
       <c r="I27" s="15">
-        <v>-156.94071146245051</v>
+        <v>-816.5420875420873</v>
       </c>
       <c r="J27" s="16">
-        <v>2950</v>
+        <v>2399</v>
       </c>
       <c r="K27" s="13">
-        <v>3421.9999999999995</v>
+        <v>2782.8399999999997</v>
       </c>
       <c r="L27" s="14">
-        <v>17.635869565217391</v>
+        <v>16.83608223062382</v>
       </c>
       <c r="M27" s="30">
-        <v>3680</v>
+        <v>3134.8148148148148</v>
       </c>
       <c r="N27" s="15">
-        <v>1277.2727272727273</v>
+        <v>974.08417508417529</v>
       </c>
       <c r="O27" s="16">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="P27" s="17">
-        <v>511.55999999999995</v>
+        <v>488.35999999999996</v>
       </c>
       <c r="Q27" s="14">
-        <v>17.406084243369733</v>
+        <v>19.506552262090484</v>
       </c>
       <c r="R27" s="16">
-        <v>557.39130434782612</v>
+        <v>474.81481481481478</v>
       </c>
       <c r="S27" s="15">
-        <v>-65.719367588932812</v>
+        <v>-10.64983164983164</v>
       </c>
       <c r="T27" s="18">
-        <v>1372</v>
+        <v>1077</v>
       </c>
       <c r="U27" s="17">
-        <v>1591.52</v>
+        <v>1249.32</v>
       </c>
       <c r="V27" s="14">
-        <v>12.040097121054457</v>
+        <v>11.095005202913631</v>
       </c>
       <c r="W27" s="16">
-        <v>2506.9565217391305</v>
+        <v>2135.5555555555557</v>
       </c>
       <c r="X27" s="15">
-        <v>-451.24110671936774</v>
+        <v>-476.13131313131316</v>
       </c>
       <c r="Y27" s="18">
-        <v>240</v>
+        <v>142</v>
       </c>
       <c r="Z27" s="17">
-        <v>278.39999999999998</v>
+        <v>164.72</v>
       </c>
       <c r="AA27" s="14">
-        <v>20.513513513513509</v>
+        <v>14.247972972972972</v>
       </c>
       <c r="AB27" s="16">
-        <v>257.39130434782612</v>
+        <v>219.25925925925927</v>
       </c>
       <c r="AC27" s="15">
-        <v>-17.391304347826122</v>
+        <v>-77.259259259259267</v>
       </c>
       <c r="AD27" s="19">
-        <v>8001</v>
+        <v>5910</v>
       </c>
       <c r="AE27" s="20">
-        <v>9281.16</v>
+        <v>6855.5999999999995</v>
       </c>
       <c r="AF27" s="21">
         <v>3891.9047619047619</v>
@@ -3952,7 +3954,7 @@
         <v>152.72222222222223</v>
       </c>
     </row>
-    <row r="28" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="10">
         <v>130158</v>
       </c>
@@ -3963,85 +3965,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E28" s="13">
-        <v>3190</v>
+        <v>2830</v>
       </c>
       <c r="F28" s="14">
-        <v>3700.3999999999996</v>
+        <v>3282.7999999999997</v>
       </c>
       <c r="G28" s="14">
-        <v>9.726078573150156</v>
+        <v>10.129067245119307</v>
       </c>
       <c r="H28" s="30">
-        <v>7215.652173913044</v>
+        <v>6146.6666666666661</v>
       </c>
       <c r="I28" s="15">
-        <v>-89.841897233201962</v>
+        <v>36.060606060606005</v>
       </c>
       <c r="J28" s="16">
-        <v>5161</v>
+        <v>3816</v>
       </c>
       <c r="K28" s="13">
-        <v>5986.7599999999993</v>
+        <v>4426.5599999999995</v>
       </c>
       <c r="L28" s="14">
-        <v>21.276405409809353</v>
+        <v>18.467524849274888</v>
       </c>
       <c r="M28" s="30">
-        <v>5336.521739130435</v>
+        <v>4545.9259259259261</v>
       </c>
       <c r="N28" s="15">
-        <v>2735.308300395257</v>
+        <v>1749.6700336700333</v>
       </c>
       <c r="O28" s="16">
-        <v>543</v>
+        <v>464</v>
       </c>
       <c r="P28" s="17">
-        <v>629.88</v>
+        <v>538.24</v>
       </c>
       <c r="Q28" s="14">
-        <v>14.997707423580787</v>
+        <v>15.044541484716158</v>
       </c>
       <c r="R28" s="16">
-        <v>796.52173913043487</v>
+        <v>678.51851851851848</v>
       </c>
       <c r="S28" s="15">
-        <v>-181.11067193675888</v>
+        <v>-152.83501683501686</v>
       </c>
       <c r="T28" s="18">
-        <v>673</v>
+        <v>282</v>
       </c>
       <c r="U28" s="17">
-        <v>780.68</v>
+        <v>327.12</v>
       </c>
       <c r="V28" s="14">
-        <v>4.9655584718576851</v>
+        <v>2.44251968503937</v>
       </c>
       <c r="W28" s="16">
-        <v>2981.7391304347825</v>
+        <v>2540</v>
       </c>
       <c r="X28" s="15">
-        <v>-1495.5375494071145</v>
+        <v>-1565.2727272727273</v>
       </c>
       <c r="Y28" s="18">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="Z28" s="17">
-        <v>323.64</v>
+        <v>225.04</v>
       </c>
       <c r="AA28" s="14">
-        <v>16.53091334894614</v>
+        <v>13.493676814988291</v>
       </c>
       <c r="AB28" s="16">
-        <v>371.30434782608694</v>
+        <v>316.2962962962963</v>
       </c>
       <c r="AC28" s="15">
-        <v>-92.304347826086882</v>
+        <v>-122.2962962962963</v>
       </c>
       <c r="AD28" s="19">
-        <v>9846</v>
+        <v>7586</v>
       </c>
       <c r="AE28" s="20">
-        <v>11421.359999999999</v>
+        <v>8799.76</v>
       </c>
       <c r="AF28" s="21">
         <v>4283.8095238095239</v>
@@ -4065,7 +4067,7 @@
         <v>67.203703703703709</v>
       </c>
     </row>
-    <row r="29" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>130159</v>
       </c>
@@ -4076,85 +4078,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E29" s="13">
-        <v>2676</v>
+        <v>1067</v>
       </c>
       <c r="F29" s="14">
-        <v>3104.16</v>
+        <v>1237.72</v>
       </c>
       <c r="G29" s="14">
-        <v>7.7136607041130221</v>
+        <v>3.6105616953400936</v>
       </c>
       <c r="H29" s="30">
-        <v>7632.1739130434789</v>
+        <v>6501.4814814814818</v>
       </c>
       <c r="I29" s="15">
-        <v>-793.16996047430894</v>
+        <v>-1888.218855218855</v>
       </c>
       <c r="J29" s="16">
-        <v>4538</v>
+        <v>2882</v>
       </c>
       <c r="K29" s="13">
-        <v>5264.08</v>
+        <v>3343.12</v>
       </c>
       <c r="L29" s="14">
-        <v>20.476440164080611</v>
+        <v>15.265810593900483</v>
       </c>
       <c r="M29" s="30">
-        <v>4875.652173913044</v>
+        <v>4153.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>2321.794466403162</v>
+        <v>994.12121212121224</v>
       </c>
       <c r="O29" s="16">
-        <v>548</v>
+        <v>450</v>
       </c>
       <c r="P29" s="17">
-        <v>635.67999999999995</v>
+        <v>522</v>
       </c>
       <c r="Q29" s="14">
-        <v>14.92400430570506</v>
+        <v>14.386437029063512</v>
       </c>
       <c r="R29" s="16">
-        <v>807.82608695652175</v>
+        <v>688.14814814814804</v>
       </c>
       <c r="S29" s="15">
-        <v>-186.38735177865613</v>
+        <v>-175.58922558922541</v>
       </c>
       <c r="T29" s="18">
-        <v>590</v>
+        <v>266</v>
       </c>
       <c r="U29" s="17">
-        <v>684.4</v>
+        <v>308.56</v>
       </c>
       <c r="V29" s="14">
-        <v>4.3735716378552594</v>
+        <v>2.3147377673600937</v>
       </c>
       <c r="W29" s="16">
-        <v>2967.826086956522</v>
+        <v>2528.1481481481483</v>
       </c>
       <c r="X29" s="15">
-        <v>-1568.418972332016</v>
+        <v>-1572.6531986531988</v>
       </c>
       <c r="Y29" s="18">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="Z29" s="17">
-        <v>306.23999999999995</v>
+        <v>180.95999999999998</v>
       </c>
       <c r="AA29" s="14">
-        <v>17.038775510204079</v>
+        <v>11.81938775510204</v>
       </c>
       <c r="AB29" s="16">
-        <v>340.86956521739131</v>
+        <v>290.37037037037038</v>
       </c>
       <c r="AC29" s="15">
-        <v>-76.869565217391312</v>
+        <v>-134.37037037037038</v>
       </c>
       <c r="AD29" s="19">
-        <v>8616</v>
+        <v>4821</v>
       </c>
       <c r="AE29" s="20">
-        <v>9994.56</v>
+        <v>5592.36</v>
       </c>
       <c r="AF29" s="21">
         <v>3907.6190476190477</v>
@@ -4178,7 +4180,7 @@
         <v>148.44444444444446</v>
       </c>
     </row>
-    <row r="30" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="10">
         <v>130700</v>
       </c>
@@ -4189,85 +4191,85 @@
         <v>3.68</v>
       </c>
       <c r="E30" s="13">
-        <v>668</v>
+        <v>633</v>
       </c>
       <c r="F30" s="14">
-        <v>2458.2400000000002</v>
+        <v>2329.44</v>
       </c>
       <c r="G30" s="14">
-        <v>6.9235559197050387</v>
+        <v>7.7018025399426469</v>
       </c>
       <c r="H30" s="30">
-        <v>2122.608695652174</v>
+        <v>1808.148148148148</v>
       </c>
       <c r="I30" s="15">
-        <v>-296.82213438735187</v>
+        <v>-188.88552188552183</v>
       </c>
       <c r="J30" s="16">
-        <v>922</v>
+        <v>1391</v>
       </c>
       <c r="K30" s="13">
-        <v>3392.96</v>
+        <v>5118.88</v>
       </c>
       <c r="L30" s="14">
-        <v>8.6522997032640951</v>
+        <v>15.323701780415432</v>
       </c>
       <c r="M30" s="30">
-        <v>2344.3478260869565</v>
+        <v>1997.037037037037</v>
       </c>
       <c r="N30" s="15">
-        <v>-143.61264822134399</v>
+        <v>483.25589225589238</v>
       </c>
       <c r="O30" s="16">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="P30" s="17">
-        <v>331.2</v>
+        <v>382.72</v>
       </c>
       <c r="Q30" s="14">
-        <v>16.866666666666667</v>
+        <v>22.88</v>
       </c>
       <c r="R30" s="16">
-        <v>117.39130434782609</v>
+        <v>100</v>
       </c>
       <c r="S30" s="15">
-        <v>-16.719367588932812</v>
+        <v>13.090909090909079</v>
       </c>
       <c r="T30" s="18">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="U30" s="17">
-        <v>1306.4000000000001</v>
+        <v>1192.3200000000002</v>
       </c>
       <c r="V30" s="14">
-        <v>12.474305555555556</v>
+        <v>13.364999999999998</v>
       </c>
       <c r="W30" s="16">
-        <v>626.08695652173913</v>
+        <v>533.33333333333337</v>
       </c>
       <c r="X30" s="15">
-        <v>-100.33596837944663</v>
+        <v>-63.878787878787932</v>
       </c>
       <c r="Y30" s="18">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="Z30" s="17">
-        <v>224.48000000000002</v>
+        <v>110.4</v>
       </c>
       <c r="AA30" s="14">
-        <v>10.643448275862069</v>
+        <v>6.1448275862068966</v>
       </c>
       <c r="AB30" s="16">
-        <v>126.08695652173913</v>
+        <v>107.4074074074074</v>
       </c>
       <c r="AC30" s="15">
-        <v>-65.086956521739125</v>
+        <v>-77.407407407407419</v>
       </c>
       <c r="AD30" s="19">
-        <v>2096</v>
+        <v>2482</v>
       </c>
       <c r="AE30" s="20">
-        <v>7713.2800000000007</v>
+        <v>9133.76</v>
       </c>
       <c r="AF30" s="21">
         <v>2420</v>
@@ -4291,7 +4293,7 @@
         <v>175.3125</v>
       </c>
     </row>
-    <row r="31" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="10">
         <v>130701</v>
       </c>
@@ -4302,85 +4304,85 @@
         <v>3.68</v>
       </c>
       <c r="E31" s="13">
-        <v>397</v>
+        <v>263</v>
       </c>
       <c r="F31" s="14">
-        <v>1460.96</v>
+        <v>967.84</v>
       </c>
       <c r="G31" s="14">
-        <v>8.2261261261261254</v>
+        <v>6.397297297297297</v>
       </c>
       <c r="H31" s="30">
-        <v>1061.7391304347827</v>
+        <v>904.44444444444446</v>
       </c>
       <c r="I31" s="15">
-        <v>-85.608695652173992</v>
+        <v>-148.11111111111114</v>
       </c>
       <c r="J31" s="16">
-        <v>850</v>
+        <v>1315</v>
       </c>
       <c r="K31" s="13">
-        <v>3128</v>
+        <v>4839.2</v>
       </c>
       <c r="L31" s="14">
-        <v>13.706182281708093</v>
+        <v>24.891969407265776</v>
       </c>
       <c r="M31" s="30">
-        <v>1364.3478260869565</v>
+        <v>1162.2222222222222</v>
       </c>
       <c r="N31" s="15">
-        <v>229.84189723320151</v>
+        <v>786.71717171717182</v>
       </c>
       <c r="O31" s="16">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P31" s="17">
-        <v>62.56</v>
+        <v>47.84</v>
       </c>
       <c r="Q31" s="14">
-        <v>13.440624999999999</v>
+        <v>12.065625000000001</v>
       </c>
       <c r="R31" s="16">
-        <v>27.826086956521738</v>
+        <v>23.703703703703702</v>
       </c>
       <c r="S31" s="15">
-        <v>-8.2964426877470352</v>
+        <v>-8.5488215488215502</v>
       </c>
       <c r="T31" s="18">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="U31" s="17">
-        <v>655.04000000000008</v>
+        <v>625.6</v>
       </c>
       <c r="V31" s="14">
-        <v>17.123193916349809</v>
+        <v>19.197718631178709</v>
       </c>
       <c r="W31" s="16">
-        <v>228.69565217391306</v>
+        <v>194.81481481481481</v>
       </c>
       <c r="X31" s="15">
-        <v>11.675889328063221</v>
+        <v>28.316498316498325</v>
       </c>
       <c r="Y31" s="18">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Z31" s="17">
-        <v>99.36</v>
+        <v>80.960000000000008</v>
       </c>
       <c r="AA31" s="14">
-        <v>18.975000000000001</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="AB31" s="16">
-        <v>31.304347826086957</v>
+        <v>26.666666666666664</v>
       </c>
       <c r="AC31" s="15">
-        <v>-4.304347826086957</v>
+        <v>-4.6666666666666643</v>
       </c>
       <c r="AD31" s="19">
-        <v>1469</v>
+        <v>1783</v>
       </c>
       <c r="AE31" s="20">
-        <v>5405.92</v>
+        <v>6561.4400000000005</v>
       </c>
       <c r="AF31" s="21">
         <v>1421.9047619047619</v>
@@ -4404,7 +4406,7 @@
         <v>94.375</v>
       </c>
     </row>
-    <row r="32" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>130702</v>
       </c>
@@ -4415,85 +4417,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E32" s="13">
-        <v>1770</v>
+        <v>1478</v>
       </c>
       <c r="F32" s="14">
-        <v>7345.5000000000009</v>
+        <v>6133.7000000000007</v>
       </c>
       <c r="G32" s="14">
-        <v>8.7840329540996471</v>
+        <v>8.6105531581012169</v>
       </c>
       <c r="H32" s="30">
-        <v>4433.0434782608691</v>
+        <v>3776.2962962962961</v>
       </c>
       <c r="I32" s="15">
-        <v>-245.01976284584975</v>
+        <v>-238.4983164983164</v>
       </c>
       <c r="J32" s="16">
-        <v>1203</v>
+        <v>1384</v>
       </c>
       <c r="K32" s="13">
-        <v>4992.4500000000007</v>
+        <v>5743.6</v>
       </c>
       <c r="L32" s="14">
-        <v>7.6223140495867776</v>
+        <v>10.294214876033056</v>
       </c>
       <c r="M32" s="30">
-        <v>3472.173913043478</v>
+        <v>2957.7777777777778</v>
       </c>
       <c r="N32" s="15">
-        <v>-375.26086956521726</v>
+        <v>39.555555555555429</v>
       </c>
       <c r="O32" s="16">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="P32" s="17">
-        <v>759.45</v>
+        <v>581</v>
       </c>
       <c r="Q32" s="14">
-        <v>14.513793103448275</v>
+        <v>13.03448275862069</v>
       </c>
       <c r="R32" s="16">
-        <v>277.39130434782612</v>
+        <v>236.2962962962963</v>
       </c>
       <c r="S32" s="15">
-        <v>-69.173913043478279</v>
+        <v>-74.81481481481481</v>
       </c>
       <c r="T32" s="18">
-        <v>826</v>
+        <v>615</v>
       </c>
       <c r="U32" s="17">
-        <v>3427.9</v>
+        <v>2552.25</v>
       </c>
       <c r="V32" s="14">
-        <v>10.559777665487621</v>
+        <v>9.2296614451743295</v>
       </c>
       <c r="W32" s="16">
-        <v>1720.8695652173913</v>
+        <v>1465.9259259259259</v>
       </c>
       <c r="X32" s="15">
-        <v>-425.54150197628451</v>
+        <v>-451.12794612794619</v>
       </c>
       <c r="Y32" s="18">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="Z32" s="17">
-        <v>987.7</v>
+        <v>904.7</v>
       </c>
       <c r="AA32" s="14">
-        <v>60.82222222222223</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="AB32" s="16">
-        <v>86.086956521739125</v>
+        <v>73.333333333333329</v>
       </c>
       <c r="AC32" s="15">
-        <v>151.91304347826087</v>
+        <v>144.66666666666669</v>
       </c>
       <c r="AD32" s="19">
-        <v>4220</v>
+        <v>3835</v>
       </c>
       <c r="AE32" s="20">
-        <v>17513</v>
+        <v>15915.250000000002</v>
       </c>
       <c r="AF32" s="21">
         <v>5130.9523809523807</v>
@@ -4517,7 +4519,7 @@
         <v>308.3125</v>
       </c>
     </row>
-    <row r="33" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="10">
         <v>130703</v>
       </c>
@@ -4528,85 +4530,85 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E33" s="13">
-        <v>3515</v>
+        <v>2728</v>
       </c>
       <c r="F33" s="14">
-        <v>14587.250000000002</v>
+        <v>11321.2</v>
       </c>
       <c r="G33" s="14">
-        <v>8.8005442850074225</v>
+        <v>8.0179713013359741</v>
       </c>
       <c r="H33" s="30">
-        <v>8786.95652173913</v>
+        <v>7485.1851851851843</v>
       </c>
       <c r="I33" s="15">
-        <v>-479.07114624505948</v>
+        <v>-674.35690235690163</v>
       </c>
       <c r="J33" s="16">
-        <v>4303</v>
+        <v>3881</v>
       </c>
       <c r="K33" s="13">
-        <v>17857.45</v>
+        <v>16106.150000000001</v>
       </c>
       <c r="L33" s="14">
-        <v>17.920312757201646</v>
+        <v>18.97377777777778</v>
       </c>
       <c r="M33" s="30">
-        <v>5282.608695652174</v>
+        <v>4500</v>
       </c>
       <c r="N33" s="15">
-        <v>1901.814229249012</v>
+        <v>1835.5454545454547</v>
       </c>
       <c r="O33" s="16">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="P33" s="17">
-        <v>1199.3500000000001</v>
+        <v>1033.3500000000001</v>
       </c>
       <c r="Q33" s="14">
-        <v>16.964501160092809</v>
+        <v>17.158468677494199</v>
       </c>
       <c r="R33" s="16">
-        <v>374.78260869565219</v>
+        <v>319.2592592592593</v>
       </c>
       <c r="S33" s="15">
-        <v>-51.711462450592876</v>
+        <v>-41.235690235690299</v>
       </c>
       <c r="T33" s="18">
-        <v>820</v>
+        <v>576</v>
       </c>
       <c r="U33" s="17">
-        <v>3403.0000000000005</v>
+        <v>2390.4</v>
       </c>
       <c r="V33" s="14">
-        <v>8.1677165354330707</v>
+        <v>6.7351181102362201</v>
       </c>
       <c r="W33" s="16">
-        <v>2208.695652173913</v>
+        <v>1881.4814814814815</v>
       </c>
       <c r="X33" s="15">
-        <v>-786.32411067193675</v>
+        <v>-792.35016835016836</v>
       </c>
       <c r="Y33" s="18">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="Z33" s="17">
-        <v>361.05</v>
+        <v>211.65</v>
       </c>
       <c r="AA33" s="14">
-        <v>6.1311977715877441</v>
+        <v>4.2192200557103066</v>
       </c>
       <c r="AB33" s="16">
-        <v>312.17391304347825</v>
+        <v>265.92592592592592</v>
       </c>
       <c r="AC33" s="15">
-        <v>-225.17391304347825</v>
+        <v>-214.92592592592592</v>
       </c>
       <c r="AD33" s="19">
-        <v>9014</v>
+        <v>7485</v>
       </c>
       <c r="AE33" s="20">
-        <v>37408.100000000006</v>
+        <v>31062.750000000004</v>
       </c>
       <c r="AF33" s="21">
         <v>8113.8095238095239</v>
@@ -4630,7 +4632,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="34" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="10">
         <v>130707</v>
       </c>
@@ -4641,19 +4643,19 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="E34" s="13">
-        <v>674</v>
+        <v>474</v>
       </c>
       <c r="F34" s="14">
-        <v>2797.1000000000004</v>
+        <v>1967.1000000000001</v>
       </c>
       <c r="G34" s="14">
-        <v>14.092727272727272</v>
+        <v>11.634545454545455</v>
       </c>
       <c r="H34" s="30">
-        <v>1052.1739130434783</v>
+        <v>896.2962962962963</v>
       </c>
       <c r="I34" s="15">
-        <v>195.73913043478257</v>
+        <v>66.592592592592609</v>
       </c>
       <c r="J34" s="16">
         <v>0</v>
@@ -4678,10 +4680,10 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
-        <v>69.565217391304344</v>
+        <v>59.259259259259252</v>
       </c>
       <c r="S34" s="15">
-        <v>-63.241106719367586</v>
+        <v>-53.872053872053868</v>
       </c>
       <c r="T34" s="18">
         <v>82</v>
@@ -4690,13 +4692,13 @@
         <v>340.3</v>
       </c>
       <c r="V34" s="14">
-        <v>13.830666666666666</v>
+        <v>16.235999999999997</v>
       </c>
       <c r="W34" s="16">
-        <v>130.43478260869566</v>
+        <v>111.11111111111111</v>
       </c>
       <c r="X34" s="15">
-        <v>-12.86166007905139</v>
+        <v>1.1919191919191832</v>
       </c>
       <c r="Y34" s="18">
         <v>32</v>
@@ -4714,10 +4716,10 @@
         <v>32</v>
       </c>
       <c r="AD34" s="19">
-        <v>788</v>
+        <v>588</v>
       </c>
       <c r="AE34" s="20">
-        <v>3270.2000000000003</v>
+        <v>2440.2000000000003</v>
       </c>
       <c r="AF34" s="31">
         <v>749.52380952380952</v>
@@ -4741,7 +4743,7 @@
         <v>58.6875</v>
       </c>
     </row>
-    <row r="35" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="10">
         <v>131150</v>
       </c>
@@ -4752,85 +4754,85 @@
         <v>1.63</v>
       </c>
       <c r="E35" s="13">
-        <v>2850</v>
+        <v>2465</v>
       </c>
       <c r="F35" s="14">
-        <v>4645.5</v>
+        <v>4017.95</v>
       </c>
       <c r="G35" s="14">
-        <v>7.4727951083013782</v>
+        <v>7.5873665664835732</v>
       </c>
       <c r="H35" s="30">
-        <v>8390.434782608696</v>
+        <v>7147.4074074074078</v>
       </c>
       <c r="I35" s="15">
-        <v>-963.83399209486197</v>
+        <v>-783.82154882154919</v>
       </c>
       <c r="J35" s="16">
-        <v>670</v>
+        <v>4160</v>
       </c>
       <c r="K35" s="13">
-        <v>1092.0999999999999</v>
+        <v>6780.7999999999993</v>
       </c>
       <c r="L35" s="14">
-        <v>4.6339529797703669</v>
+        <v>33.775833788955708</v>
       </c>
       <c r="M35" s="30">
-        <v>3180.869565217391</v>
+        <v>2709.62962962963</v>
       </c>
       <c r="N35" s="15">
-        <v>-775.84980237154127</v>
+        <v>2928.3501683501681</v>
       </c>
       <c r="O35" s="16">
-        <v>503</v>
+        <v>351</v>
       </c>
       <c r="P35" s="17">
-        <v>819.89</v>
+        <v>572.13</v>
       </c>
       <c r="Q35" s="14">
-        <v>14.884093567251462</v>
+        <v>12.192631578947369</v>
       </c>
       <c r="R35" s="16">
-        <v>743.47826086956513</v>
+        <v>633.33333333333337</v>
       </c>
       <c r="S35" s="15">
-        <v>-172.88932806324112</v>
+        <v>-224.75757575757575</v>
       </c>
       <c r="T35" s="18">
-        <v>632</v>
+        <v>602</v>
       </c>
       <c r="U35" s="17">
-        <v>1030.1599999999999</v>
+        <v>981.26</v>
       </c>
       <c r="V35" s="14">
-        <v>14.860223048327137</v>
+        <v>16.616542750929369</v>
       </c>
       <c r="W35" s="16">
-        <v>935.6521739130435</v>
+        <v>797.03703703703707</v>
       </c>
       <c r="X35" s="15">
-        <v>-48.474308300395251</v>
+        <v>22.336700336700346</v>
       </c>
       <c r="Y35" s="18">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="Z35" s="17">
-        <v>241.23999999999998</v>
+        <v>179.29999999999998</v>
       </c>
       <c r="AA35" s="14">
-        <v>10.980645161290322</v>
+        <v>9.5806451612903221</v>
       </c>
       <c r="AB35" s="16">
-        <v>296.52173913043475</v>
+        <v>252.59259259259261</v>
       </c>
       <c r="AC35" s="15">
-        <v>-148.52173913043475</v>
+        <v>-142.59259259259261</v>
       </c>
       <c r="AD35" s="19">
-        <v>4803</v>
+        <v>7688</v>
       </c>
       <c r="AE35" s="20">
-        <v>7828.8899999999994</v>
+        <v>12531.439999999999</v>
       </c>
       <c r="AF35" s="21">
         <v>7879.5238095238092</v>
@@ -4854,7 +4856,7 @@
         <v>98.851851851851848</v>
       </c>
     </row>
-    <row r="36" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="10">
         <v>131151</v>
       </c>
@@ -4865,85 +4867,85 @@
         <v>1.63</v>
       </c>
       <c r="E36" s="13">
-        <v>4548</v>
+        <v>4264</v>
       </c>
       <c r="F36" s="14">
-        <v>7413.24</v>
+        <v>6950.32</v>
       </c>
       <c r="G36" s="14">
-        <v>8.197221628553109</v>
+        <v>9.021927762342381</v>
       </c>
       <c r="H36" s="30">
-        <v>12206.08695652174</v>
+        <v>10397.777777777777</v>
       </c>
       <c r="I36" s="15">
-        <v>-1000.2213438735189</v>
+        <v>-462.26262626262542</v>
       </c>
       <c r="J36" s="16">
-        <v>1065</v>
+        <v>3943</v>
       </c>
       <c r="K36" s="13">
-        <v>1735.9499999999998</v>
+        <v>6427.0899999999992</v>
       </c>
       <c r="L36" s="14">
-        <v>5.2884200196270852</v>
+        <v>22.984710500490678</v>
       </c>
       <c r="M36" s="30">
-        <v>4430.434782608696</v>
+        <v>3774.0740740740739</v>
       </c>
       <c r="N36" s="15">
-        <v>-948.83399209486197</v>
+        <v>2227.5117845117848</v>
       </c>
       <c r="O36" s="16">
-        <v>1230</v>
+        <v>983</v>
       </c>
       <c r="P36" s="17">
-        <v>2004.8999999999999</v>
+        <v>1602.29</v>
       </c>
       <c r="Q36" s="14">
-        <v>15.224559686888455</v>
+        <v>14.283317025440311</v>
       </c>
       <c r="R36" s="16">
-        <v>1777.391304347826</v>
+        <v>1514.0740740740741</v>
       </c>
       <c r="S36" s="15">
-        <v>-385.81027667984199</v>
+        <v>-393.43097643097667</v>
       </c>
       <c r="T36" s="18">
-        <v>1222</v>
+        <v>1119</v>
       </c>
       <c r="U36" s="17">
-        <v>1991.86</v>
+        <v>1823.9699999999998</v>
       </c>
       <c r="V36" s="14">
-        <v>12.93581589958159</v>
+        <v>13.905564853556486</v>
       </c>
       <c r="W36" s="16">
-        <v>2078.2608695652175</v>
+        <v>1770.3703703703704</v>
       </c>
       <c r="X36" s="15">
-        <v>-289.46245059288549</v>
+        <v>-168.54208754208753</v>
       </c>
       <c r="Y36" s="18">
-        <v>263</v>
+        <v>206</v>
       </c>
       <c r="Z36" s="17">
-        <v>428.69</v>
+        <v>335.78</v>
       </c>
       <c r="AA36" s="14">
-        <v>10.316124031007751</v>
+        <v>9.4855813953488379</v>
       </c>
       <c r="AB36" s="16">
-        <v>560.86956521739137</v>
+        <v>477.77777777777777</v>
       </c>
       <c r="AC36" s="15">
-        <v>-297.86956521739137</v>
+        <v>-271.77777777777777</v>
       </c>
       <c r="AD36" s="19">
-        <v>8328</v>
+        <v>10515</v>
       </c>
       <c r="AE36" s="20">
-        <v>13574.64</v>
+        <v>17139.449999999997</v>
       </c>
       <c r="AF36" s="21">
         <v>12737.142857142859</v>
@@ -4967,7 +4969,7 @@
         <v>168.33333333333334</v>
       </c>
     </row>
-    <row r="37" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="10">
         <v>131152</v>
       </c>
@@ -4978,85 +4980,85 @@
         <v>1.63</v>
       </c>
       <c r="E37" s="13">
-        <v>1903</v>
+        <v>1932</v>
       </c>
       <c r="F37" s="14">
-        <v>3101.89</v>
+        <v>3149.16</v>
       </c>
       <c r="G37" s="14">
-        <v>7.4036444717822549</v>
+        <v>8.8236813778256202</v>
       </c>
       <c r="H37" s="30">
-        <v>5654.782608695652</v>
+        <v>4817.0370370370365</v>
       </c>
       <c r="I37" s="15">
-        <v>-667.35573122529604</v>
+        <v>-257.56228956228915</v>
       </c>
       <c r="J37" s="16">
-        <v>1811</v>
+        <v>2222</v>
       </c>
       <c r="K37" s="13">
-        <v>2951.93</v>
+        <v>3621.8599999999997</v>
       </c>
       <c r="L37" s="14">
-        <v>14.671245597182194</v>
+        <v>21.131412103746396</v>
       </c>
       <c r="M37" s="30">
-        <v>2715.652173913044</v>
+        <v>2313.3333333333335</v>
       </c>
       <c r="N37" s="15">
-        <v>576.61264822134353</v>
+        <v>1170.4848484848485</v>
       </c>
       <c r="O37" s="16">
-        <v>789</v>
+        <v>529</v>
       </c>
       <c r="P37" s="17">
-        <v>1286.07</v>
+        <v>862.27</v>
       </c>
       <c r="Q37" s="14">
-        <v>15.031400602409638</v>
+        <v>11.830798192771084</v>
       </c>
       <c r="R37" s="16">
-        <v>1154.7826086956522</v>
+        <v>983.7037037037037</v>
       </c>
       <c r="S37" s="15">
-        <v>-260.802371541502</v>
+        <v>-365.27609427609423</v>
       </c>
       <c r="T37" s="18">
-        <v>640</v>
+        <v>551</v>
       </c>
       <c r="U37" s="17">
-        <v>1043.1999999999998</v>
+        <v>898.13</v>
       </c>
       <c r="V37" s="14">
-        <v>12.464973056197072</v>
+        <v>12.597921478060046</v>
       </c>
       <c r="W37" s="16">
-        <v>1129.5652173913045</v>
+        <v>962.22222222222229</v>
       </c>
       <c r="X37" s="15">
-        <v>-181.50197628458511</v>
+        <v>-148.79797979797979</v>
       </c>
       <c r="Y37" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z37" s="17">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="AA37" s="14">
-        <v>0</v>
+        <v>0.27310344827586208</v>
       </c>
       <c r="AB37" s="16">
-        <v>378.26086956521743</v>
+        <v>322.22222222222223</v>
       </c>
       <c r="AC37" s="15">
-        <v>-378.26086956521743</v>
+        <v>-318.22222222222223</v>
       </c>
       <c r="AD37" s="19">
-        <v>5143</v>
+        <v>5238</v>
       </c>
       <c r="AE37" s="20">
-        <v>8383.09</v>
+        <v>8537.9399999999987</v>
       </c>
       <c r="AF37" s="21">
         <v>5291.9047619047615</v>
@@ -5080,7 +5082,7 @@
         <v>59.962962962962962</v>
       </c>
     </row>
-    <row r="38" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="10">
         <v>131153</v>
       </c>
@@ -5091,85 +5093,85 @@
         <v>1.63</v>
       </c>
       <c r="E38" s="13">
-        <v>1445</v>
+        <v>1401</v>
       </c>
       <c r="F38" s="14">
-        <v>2355.35</v>
+        <v>2283.6299999999997</v>
       </c>
       <c r="G38" s="14">
-        <v>7.3499195818254925</v>
+        <v>8.365440289505429</v>
       </c>
       <c r="H38" s="30">
-        <v>4325.217391304348</v>
+        <v>3684.4444444444443</v>
       </c>
       <c r="I38" s="15">
-        <v>-521.00790513833999</v>
+        <v>-273.7474747474746</v>
       </c>
       <c r="J38" s="16">
-        <v>1947</v>
+        <v>2460</v>
       </c>
       <c r="K38" s="13">
-        <v>3173.6099999999997</v>
+        <v>4009.7999999999997</v>
       </c>
       <c r="L38" s="14">
-        <v>18.909443378119001</v>
+        <v>28.046833013435702</v>
       </c>
       <c r="M38" s="30">
-        <v>2265.217391304348</v>
+        <v>1929.6296296296296</v>
       </c>
       <c r="N38" s="15">
-        <v>917.35573122529649</v>
+        <v>1582.8956228956231</v>
       </c>
       <c r="O38" s="16">
-        <v>445</v>
+        <v>252</v>
       </c>
       <c r="P38" s="17">
-        <v>725.34999999999991</v>
+        <v>410.76</v>
       </c>
       <c r="Q38" s="14">
-        <v>12.41289966923925</v>
+        <v>8.251819184123482</v>
       </c>
       <c r="R38" s="16">
-        <v>788.695652173913</v>
+        <v>671.85185185185196</v>
       </c>
       <c r="S38" s="15">
-        <v>-271.99604743083</v>
+        <v>-358.77441077441085</v>
       </c>
       <c r="T38" s="18">
-        <v>497</v>
+        <v>438</v>
       </c>
       <c r="U38" s="17">
-        <v>810.1099999999999</v>
+        <v>713.93999999999994</v>
       </c>
       <c r="V38" s="14">
-        <v>14.741031652989451</v>
+        <v>15.250410316529894</v>
       </c>
       <c r="W38" s="16">
-        <v>741.73913043478262</v>
+        <v>631.85185185185185</v>
       </c>
       <c r="X38" s="15">
-        <v>-42.446640316205503</v>
+        <v>-21.528619528619515</v>
       </c>
       <c r="Y38" s="18">
-        <v>222</v>
+        <v>151</v>
       </c>
       <c r="Z38" s="17">
-        <v>361.85999999999996</v>
+        <v>246.13</v>
       </c>
       <c r="AA38" s="14">
-        <v>7.7151098901098907</v>
+        <v>6.1603021978021975</v>
       </c>
       <c r="AB38" s="16">
-        <v>633.04347826086951</v>
+        <v>539.25925925925924</v>
       </c>
       <c r="AC38" s="15">
-        <v>-411.04347826086951</v>
+        <v>-388.25925925925924</v>
       </c>
       <c r="AD38" s="19">
-        <v>4556</v>
+        <v>4702</v>
       </c>
       <c r="AE38" s="20">
-        <v>7426.28</v>
+        <v>7664.2599999999993</v>
       </c>
       <c r="AF38" s="21">
         <v>4018.5714285714284</v>
@@ -5193,7 +5195,7 @@
         <v>66.518518518518519</v>
       </c>
     </row>
-    <row r="39" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
         <v>131154</v>
       </c>
@@ -5204,85 +5206,85 @@
         <v>1.63</v>
       </c>
       <c r="E39" s="13">
-        <v>802</v>
+        <v>717</v>
       </c>
       <c r="F39" s="14">
-        <v>1307.26</v>
+        <v>1168.71</v>
       </c>
       <c r="G39" s="14">
-        <v>9.2693467336683426</v>
+        <v>9.7281407035175871</v>
       </c>
       <c r="H39" s="30">
-        <v>1903.4782608695652</v>
+        <v>1621.4814814814815</v>
       </c>
       <c r="I39" s="15">
-        <v>-63.217391304347757</v>
+        <v>-20.037037037037067</v>
       </c>
       <c r="J39" s="16">
-        <v>805</v>
+        <v>985</v>
       </c>
       <c r="K39" s="13">
-        <v>1312.1499999999999</v>
+        <v>1605.55</v>
       </c>
       <c r="L39" s="14">
-        <v>16.358634538152611</v>
+        <v>23.497590361445781</v>
       </c>
       <c r="M39" s="30">
-        <v>1082.608695652174</v>
+        <v>922.22222222222229</v>
       </c>
       <c r="N39" s="15">
-        <v>312.90513833992094</v>
+        <v>565.80808080808083</v>
       </c>
       <c r="O39" s="16">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="P39" s="17">
-        <v>679.70999999999992</v>
+        <v>611.25</v>
       </c>
       <c r="Q39" s="14">
-        <v>16.205990783410137</v>
+        <v>17.108294930875577</v>
       </c>
       <c r="R39" s="16">
-        <v>566.08695652173913</v>
+        <v>482.22222222222223</v>
       </c>
       <c r="S39" s="15">
-        <v>-97.62450592885375</v>
+        <v>-63.383838383838395</v>
       </c>
       <c r="T39" s="18">
-        <v>780</v>
+        <v>750</v>
       </c>
       <c r="U39" s="17">
-        <v>1271.3999999999999</v>
+        <v>1222.5</v>
       </c>
       <c r="V39" s="14">
-        <v>15.57537490134175</v>
+        <v>17.580899763220206</v>
       </c>
       <c r="W39" s="16">
-        <v>1101.7391304347827</v>
+        <v>938.51851851851848</v>
       </c>
       <c r="X39" s="15">
-        <v>-21.264822134387487</v>
+        <v>67.441077441077482</v>
       </c>
       <c r="Y39" s="18">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="Z39" s="17">
-        <v>578.65</v>
+        <v>498.78</v>
       </c>
       <c r="AA39" s="14">
-        <v>64.615107913669064</v>
+        <v>65.382733812949638</v>
       </c>
       <c r="AB39" s="16">
-        <v>120.86956521739131</v>
+        <v>102.96296296296296</v>
       </c>
       <c r="AC39" s="15">
-        <v>234.13043478260869</v>
+        <v>203.03703703703704</v>
       </c>
       <c r="AD39" s="19">
-        <v>3159</v>
+        <v>3133</v>
       </c>
       <c r="AE39" s="20">
-        <v>5149.17</v>
+        <v>5106.79</v>
       </c>
       <c r="AF39" s="21">
         <v>760.95238095238096</v>
@@ -5306,7 +5308,7 @@
         <v>166.44444444444446</v>
       </c>
     </row>
-    <row r="40" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="10">
         <v>131155</v>
       </c>
@@ -5317,85 +5319,85 @@
         <v>1.63</v>
       </c>
       <c r="E40" s="13">
-        <v>941</v>
+        <v>662</v>
       </c>
       <c r="F40" s="14">
-        <v>1533.83</v>
+        <v>1079.06</v>
       </c>
       <c r="G40" s="14">
-        <v>8.2463803255975066</v>
+        <v>6.8103221337028064</v>
       </c>
       <c r="H40" s="30">
-        <v>2510.4347826086955</v>
+        <v>2138.5185185185182</v>
       </c>
       <c r="I40" s="15">
-        <v>-200.10671936758899</v>
+        <v>-310.05387205387194</v>
       </c>
       <c r="J40" s="16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K40" s="13">
-        <v>32.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14">
-        <v>0.34258632362897767</v>
+        <v>0</v>
       </c>
       <c r="M40" s="30">
-        <v>1284.3478260869565</v>
+        <v>1094.0740740740741</v>
       </c>
       <c r="N40" s="15">
-        <v>-563.79446640316201</v>
+        <v>-497.30639730639729</v>
       </c>
       <c r="O40" s="16">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="P40" s="17">
-        <v>798.69999999999993</v>
+        <v>722.08999999999992</v>
       </c>
       <c r="Q40" s="14">
-        <v>15.304938271604938</v>
+        <v>16.243333333333332</v>
       </c>
       <c r="R40" s="16">
-        <v>704.3478260869565</v>
+        <v>600</v>
       </c>
       <c r="S40" s="15">
-        <v>-150.31620553359687</v>
+        <v>-102.4545454545455</v>
       </c>
       <c r="T40" s="18">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="U40" s="17">
-        <v>704.16</v>
+        <v>650.37</v>
       </c>
       <c r="V40" s="14">
-        <v>7.5532826537664146</v>
+        <v>8.1895646164478215</v>
       </c>
       <c r="W40" s="16">
-        <v>1258.2608695652173</v>
+        <v>1071.851851851852</v>
       </c>
       <c r="X40" s="15">
-        <v>-483.09881422924889</v>
+        <v>-380.52861952861963</v>
       </c>
       <c r="Y40" s="18">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="Z40" s="17">
-        <v>585.16999999999996</v>
+        <v>498.78</v>
       </c>
       <c r="AA40" s="14">
-        <v>62.639310344827585</v>
+        <v>62.677241379310345</v>
       </c>
       <c r="AB40" s="16">
-        <v>126.08695652173913</v>
+        <v>107.4074074074074</v>
       </c>
       <c r="AC40" s="15">
-        <v>232.91304347826087</v>
+        <v>198.59259259259258</v>
       </c>
       <c r="AD40" s="19">
-        <v>2242</v>
+        <v>1810</v>
       </c>
       <c r="AE40" s="20">
-        <v>3654.4599999999996</v>
+        <v>2950.2999999999997</v>
       </c>
       <c r="AF40" s="21">
         <v>720.95238095238096</v>
@@ -5419,7 +5421,7 @@
         <v>162.90740740740742</v>
       </c>
     </row>
-    <row r="41" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="10">
         <v>131700</v>
       </c>
@@ -5430,85 +5432,85 @@
         <v>6.15</v>
       </c>
       <c r="E41" s="13">
-        <v>695</v>
+        <v>579</v>
       </c>
       <c r="F41" s="14">
-        <v>4274.25</v>
+        <v>3560.8500000000004</v>
       </c>
       <c r="G41" s="14">
-        <v>10.989687499999999</v>
+        <v>10.7476875</v>
       </c>
       <c r="H41" s="30">
-        <v>1391.304347826087</v>
+        <v>1185.1851851851852</v>
       </c>
       <c r="I41" s="15">
-        <v>62.58893280632401</v>
+        <v>40.279461279461202</v>
       </c>
       <c r="J41" s="16">
-        <v>240</v>
+        <v>818</v>
       </c>
       <c r="K41" s="13">
-        <v>1476</v>
+        <v>5030.7000000000007</v>
       </c>
       <c r="L41" s="14">
-        <v>7.3778857837181047</v>
+        <v>29.519562575941681</v>
       </c>
       <c r="M41" s="30">
-        <v>715.6521739130435</v>
+        <v>609.62962962962956</v>
       </c>
       <c r="N41" s="15">
-        <v>-85.296442687747003</v>
+        <v>540.89562289562286</v>
       </c>
       <c r="O41" s="16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P41" s="17">
-        <v>172.20000000000002</v>
+        <v>159.9</v>
       </c>
       <c r="Q41" s="14">
-        <v>5.4914728682170546</v>
+        <v>5.9860465116279071</v>
       </c>
       <c r="R41" s="16">
-        <v>112.17391304347827</v>
+        <v>95.555555555555557</v>
       </c>
       <c r="S41" s="15">
-        <v>-73.976284584980235</v>
+        <v>-60.868686868686865</v>
       </c>
       <c r="T41" s="18">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="U41" s="17">
-        <v>1260.75</v>
+        <v>1168.5</v>
       </c>
       <c r="V41" s="14">
-        <v>17.117161716171616</v>
+        <v>18.623762376237625</v>
       </c>
       <c r="W41" s="16">
-        <v>263.47826086956525</v>
+        <v>224.44444444444443</v>
       </c>
       <c r="X41" s="15">
-        <v>13.379446640316189</v>
+        <v>26.767676767676789</v>
       </c>
       <c r="Y41" s="18">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="17">
-        <v>116.85000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="14">
-        <v>3.6142857142857143</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="16">
-        <v>115.65217391304347</v>
+        <v>98.518518518518505</v>
       </c>
       <c r="AC41" s="15">
-        <v>-96.65217391304347</v>
+        <v>-98.518518518518505</v>
       </c>
       <c r="AD41" s="19">
-        <v>1187</v>
+        <v>1613</v>
       </c>
       <c r="AE41" s="20">
-        <v>7300.05</v>
+        <v>9919.9500000000007</v>
       </c>
       <c r="AF41" s="21">
         <v>1278.5714285714287</v>
@@ -5532,7 +5534,7 @@
         <v>24.87037037037037</v>
       </c>
     </row>
-    <row r="42" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="10">
         <v>131701</v>
       </c>
@@ -5543,85 +5545,85 @@
         <v>6.15</v>
       </c>
       <c r="E42" s="13">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="F42" s="14">
-        <v>984</v>
+        <v>6.15</v>
       </c>
       <c r="G42" s="14">
-        <v>2.2857142857142856</v>
+        <v>1.6770186335403725E-2</v>
       </c>
       <c r="H42" s="30">
-        <v>1540</v>
+        <v>1311.851851851852</v>
       </c>
       <c r="I42" s="15">
-        <v>-540</v>
+        <v>-595.2962962962963</v>
       </c>
       <c r="J42" s="16">
-        <v>213</v>
+        <v>1189</v>
       </c>
       <c r="K42" s="13">
-        <v>1309.95</v>
+        <v>7312.35</v>
       </c>
       <c r="L42" s="14">
-        <v>6.0010022271714929</v>
+        <v>39.32438752783964</v>
       </c>
       <c r="M42" s="30">
-        <v>780.86956521739125</v>
+        <v>665.18518518518522</v>
       </c>
       <c r="N42" s="15">
-        <v>-141.94071146245057</v>
+        <v>886.64309764309769</v>
       </c>
       <c r="O42" s="16">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="P42" s="17">
-        <v>565.80000000000007</v>
+        <v>412.05</v>
       </c>
       <c r="Q42" s="14">
-        <v>14.638993710691826</v>
+        <v>12.515094339622641</v>
       </c>
       <c r="R42" s="16">
-        <v>138.26086956521738</v>
+        <v>117.77777777777779</v>
       </c>
       <c r="S42" s="15">
-        <v>-33.691699604743064</v>
+        <v>-40.070707070707073</v>
       </c>
       <c r="T42" s="18">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="U42" s="17">
-        <v>1734.3000000000002</v>
+        <v>1660.5</v>
       </c>
       <c r="V42" s="14">
-        <v>17.703722084367246</v>
+        <v>19.898263027295286</v>
       </c>
       <c r="W42" s="16">
-        <v>350.43478260869563</v>
+        <v>298.51851851851853</v>
       </c>
       <c r="X42" s="15">
-        <v>27.138339920948624</v>
+        <v>52.895622895622893</v>
       </c>
       <c r="Y42" s="18">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="Z42" s="17">
-        <v>215.25</v>
+        <v>86.100000000000009</v>
       </c>
       <c r="AA42" s="14">
-        <v>11.06875</v>
+        <v>5.1975000000000007</v>
       </c>
       <c r="AB42" s="16">
-        <v>69.565217391304344</v>
+        <v>59.259259259259252</v>
       </c>
       <c r="AC42" s="15">
-        <v>-34.565217391304344</v>
+        <v>-45.259259259259252</v>
       </c>
       <c r="AD42" s="19">
-        <v>782</v>
+        <v>1541</v>
       </c>
       <c r="AE42" s="20">
-        <v>4809.3</v>
+        <v>9477.1500000000015</v>
       </c>
       <c r="AF42" s="21">
         <v>1433.3333333333335</v>
@@ -5645,7 +5647,7 @@
         <v>11.277777777777779</v>
       </c>
     </row>
-    <row r="43" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
         <v>132150</v>
       </c>
@@ -5656,85 +5658,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E43" s="13">
-        <v>2363</v>
+        <v>1600</v>
       </c>
       <c r="F43" s="14">
-        <v>2741.08</v>
+        <v>1855.9999999999998</v>
       </c>
       <c r="G43" s="14">
-        <v>7.7190316333118139</v>
+        <v>6.1355713363460307</v>
       </c>
       <c r="H43" s="30">
-        <v>6734.782608695652</v>
+        <v>5737.0370370370365</v>
       </c>
       <c r="I43" s="15">
-        <v>-698.26482213438749</v>
+        <v>-1007.7441077441072</v>
       </c>
       <c r="J43" s="16">
-        <v>5329</v>
+        <v>4093</v>
       </c>
       <c r="K43" s="13">
-        <v>6181.6399999999994</v>
+        <v>4747.88</v>
       </c>
       <c r="L43" s="14">
-        <v>24.611847389558232</v>
+        <v>22.190963855421685</v>
       </c>
       <c r="M43" s="30">
-        <v>4763.478260869565</v>
+        <v>4057.7777777777778</v>
       </c>
       <c r="N43" s="15">
-        <v>3163.782608695652</v>
+        <v>2248.5555555555557</v>
       </c>
       <c r="O43" s="16">
-        <v>524</v>
+        <v>326</v>
       </c>
       <c r="P43" s="17">
-        <v>607.83999999999992</v>
+        <v>378.15999999999997</v>
       </c>
       <c r="Q43" s="14">
-        <v>11.608756567425569</v>
+        <v>8.478283712784588</v>
       </c>
       <c r="R43" s="16">
-        <v>993.04347826086951</v>
+        <v>845.92592592592598</v>
       </c>
       <c r="S43" s="15">
-        <v>-378.76679841897237</v>
+        <v>-443.02356902356917</v>
       </c>
       <c r="T43" s="18">
-        <v>1280</v>
+        <v>1033</v>
       </c>
       <c r="U43" s="17">
-        <v>1484.8</v>
+        <v>1198.28</v>
       </c>
       <c r="V43" s="14">
-        <v>11.623833452979182</v>
+        <v>11.012239770279971</v>
       </c>
       <c r="W43" s="16">
-        <v>2422.608695652174</v>
+        <v>2063.7037037037039</v>
       </c>
       <c r="X43" s="15">
-        <v>-481.897233201581</v>
+        <v>-467.87542087542101</v>
       </c>
       <c r="Y43" s="18">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="Z43" s="17">
-        <v>364.23999999999995</v>
+        <v>278.39999999999998</v>
       </c>
       <c r="AA43" s="14">
-        <v>11.095251396648045</v>
+        <v>9.955307262569832</v>
       </c>
       <c r="AB43" s="16">
-        <v>622.60869565217388</v>
+        <v>530.37037037037044</v>
       </c>
       <c r="AC43" s="15">
-        <v>-308.60869565217388</v>
+        <v>-290.37037037037044</v>
       </c>
       <c r="AD43" s="19">
-        <v>9810</v>
+        <v>7292</v>
       </c>
       <c r="AE43" s="20">
-        <v>11379.599999999999</v>
+        <v>8458.7199999999993</v>
       </c>
       <c r="AF43" s="21">
         <v>6521.9047619047615</v>
@@ -5758,7 +5760,7 @@
         <v>162.59259259259258</v>
       </c>
     </row>
-    <row r="44" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="10">
         <v>132151</v>
       </c>
@@ -5769,85 +5771,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E44" s="13">
-        <v>2013</v>
+        <v>1296</v>
       </c>
       <c r="F44" s="14">
-        <v>2335.08</v>
+        <v>1503.36</v>
       </c>
       <c r="G44" s="14">
-        <v>7.8123791992636926</v>
+        <v>5.9044638748274281</v>
       </c>
       <c r="H44" s="30">
-        <v>5668.6956521739121</v>
+        <v>4828.8888888888887</v>
       </c>
       <c r="I44" s="15">
-        <v>-563.67984189723256</v>
+        <v>-898.94949494949469</v>
       </c>
       <c r="J44" s="16">
-        <v>3162</v>
+        <v>3488</v>
       </c>
       <c r="K44" s="13">
-        <v>3667.9199999999996</v>
+        <v>4046.08</v>
       </c>
       <c r="L44" s="14">
-        <v>18.730648560056196</v>
+        <v>24.255115897916173</v>
       </c>
       <c r="M44" s="30">
-        <v>3713.9130434782605</v>
+        <v>3163.7037037037039</v>
       </c>
       <c r="N44" s="15">
-        <v>1473.8577075098815</v>
+        <v>2049.9528619528619</v>
       </c>
       <c r="O44" s="16">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="P44" s="17">
-        <v>475.59999999999997</v>
+        <v>351.47999999999996</v>
       </c>
       <c r="Q44" s="14">
-        <v>16.007716049382715</v>
+        <v>13.887500000000001</v>
       </c>
       <c r="R44" s="16">
-        <v>563.47826086956525</v>
+        <v>480</v>
       </c>
       <c r="S44" s="15">
-        <v>-102.2529644268775</v>
+        <v>-133.36363636363632</v>
       </c>
       <c r="T44" s="18">
-        <v>1060</v>
+        <v>921</v>
       </c>
       <c r="U44" s="17">
-        <v>1229.5999999999999</v>
+        <v>1068.3599999999999</v>
       </c>
       <c r="V44" s="14">
-        <v>18.047106325706601</v>
+        <v>18.407604306864062</v>
       </c>
       <c r="W44" s="16">
-        <v>1292.173913043478</v>
+        <v>1100.7407407407409</v>
       </c>
       <c r="X44" s="15">
-        <v>120.23715415019785</v>
+        <v>120.46127946127933</v>
       </c>
       <c r="Y44" s="18">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="Z44" s="17">
-        <v>251.71999999999997</v>
+        <v>127.6</v>
       </c>
       <c r="AA44" s="14">
-        <v>7.4391598915989157</v>
+        <v>4.4268292682926829</v>
       </c>
       <c r="AB44" s="16">
-        <v>641.73913043478262</v>
+        <v>546.66666666666663</v>
       </c>
       <c r="AC44" s="15">
-        <v>-424.73913043478262</v>
+        <v>-436.66666666666663</v>
       </c>
       <c r="AD44" s="19">
-        <v>6862</v>
+        <v>6118</v>
       </c>
       <c r="AE44" s="20">
-        <v>7959.9199999999992</v>
+        <v>7096.8799999999992</v>
       </c>
       <c r="AF44" s="21">
         <v>6290.4761904761908</v>
@@ -5871,7 +5873,7 @@
         <v>126.44444444444444</v>
       </c>
     </row>
-    <row r="45" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="10">
         <v>132152</v>
       </c>
@@ -5882,85 +5884,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E45" s="13">
-        <v>2530</v>
+        <v>2206</v>
       </c>
       <c r="F45" s="14">
-        <v>2934.7999999999997</v>
+        <v>2558.96</v>
       </c>
       <c r="G45" s="14">
-        <v>7.4403115192374765</v>
+        <v>7.61573869580379</v>
       </c>
       <c r="H45" s="30">
-        <v>7480.869565217391</v>
+        <v>6372.5925925925922</v>
       </c>
       <c r="I45" s="15">
-        <v>-870.39525691699555</v>
+        <v>-690.63299663299676</v>
       </c>
       <c r="J45" s="16">
-        <v>3246</v>
+        <v>2563</v>
       </c>
       <c r="K45" s="13">
-        <v>3765.3599999999997</v>
+        <v>2973.08</v>
       </c>
       <c r="L45" s="14">
-        <v>14.823790613718412</v>
+        <v>13.740270758122744</v>
       </c>
       <c r="M45" s="30">
-        <v>4817.391304347826</v>
+        <v>4103.7037037037035</v>
       </c>
       <c r="N45" s="15">
-        <v>1056.276679841897</v>
+        <v>697.68013468013487</v>
       </c>
       <c r="O45" s="16">
-        <v>527</v>
+        <v>343</v>
       </c>
       <c r="P45" s="17">
-        <v>611.31999999999994</v>
+        <v>397.88</v>
       </c>
       <c r="Q45" s="14">
-        <v>12.686108468125592</v>
+        <v>9.6927687916270227</v>
       </c>
       <c r="R45" s="16">
-        <v>913.91304347826099</v>
+        <v>778.51851851851848</v>
       </c>
       <c r="S45" s="15">
-        <v>-303.83003952569186</v>
+        <v>-364.74410774410762</v>
       </c>
       <c r="T45" s="18">
-        <v>1260</v>
+        <v>1071</v>
       </c>
       <c r="U45" s="17">
-        <v>1461.6</v>
+        <v>1242.3599999999999</v>
       </c>
       <c r="V45" s="14">
-        <v>14.320754716981133</v>
+        <v>14.289622641509434</v>
       </c>
       <c r="W45" s="16">
-        <v>1935.6521739130435</v>
+        <v>1648.8888888888889</v>
       </c>
       <c r="X45" s="15">
-        <v>-147.7470355731225</v>
+        <v>-128.19191919191917</v>
       </c>
       <c r="Y45" s="18">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="Z45" s="17">
-        <v>240.11999999999998</v>
+        <v>151.95999999999998</v>
       </c>
       <c r="AA45" s="14">
-        <v>7.3348739495798316</v>
+        <v>5.4491596638655464</v>
       </c>
       <c r="AB45" s="16">
-        <v>620.86956521739137</v>
+        <v>528.88888888888891</v>
       </c>
       <c r="AC45" s="15">
-        <v>-413.86956521739137</v>
+        <v>-397.88888888888891</v>
       </c>
       <c r="AD45" s="19">
-        <v>7770</v>
+        <v>6314</v>
       </c>
       <c r="AE45" s="20">
-        <v>9013.1999999999989</v>
+        <v>7324.24</v>
       </c>
       <c r="AF45" s="21">
         <v>8521.9047619047615</v>
@@ -5984,7 +5986,7 @@
         <v>154.42592592592592</v>
       </c>
     </row>
-    <row r="46" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
         <v>132153</v>
       </c>
@@ -5995,85 +5997,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E46" s="13">
-        <v>2144</v>
+        <v>1488</v>
       </c>
       <c r="F46" s="14">
-        <v>2487.04</v>
+        <v>1726.08</v>
       </c>
       <c r="G46" s="14">
-        <v>8.4675616609428648</v>
+        <v>6.8987823915079618</v>
       </c>
       <c r="H46" s="30">
-        <v>5570.434782608696</v>
+        <v>4745.1851851851852</v>
       </c>
       <c r="I46" s="15">
-        <v>-388.01581027667999</v>
+        <v>-668.90235690235659</v>
       </c>
       <c r="J46" s="16">
-        <v>2347</v>
+        <v>2255</v>
       </c>
       <c r="K46" s="13">
-        <v>2722.52</v>
+        <v>2615.7999999999997</v>
       </c>
       <c r="L46" s="14">
-        <v>16.684209047485247</v>
+        <v>18.818066872717058</v>
       </c>
       <c r="M46" s="30">
-        <v>3094.782608695652</v>
+        <v>2636.2962962962961</v>
       </c>
       <c r="N46" s="15">
-        <v>940.28063241106724</v>
+        <v>1056.6835016835016</v>
       </c>
       <c r="O46" s="16">
-        <v>334</v>
+        <v>243</v>
       </c>
       <c r="P46" s="17">
-        <v>387.44</v>
+        <v>281.88</v>
       </c>
       <c r="Q46" s="14">
-        <v>13.020338983050848</v>
+        <v>11.120338983050848</v>
       </c>
       <c r="R46" s="16">
-        <v>564.3478260869565</v>
+        <v>480.74074074074076</v>
       </c>
       <c r="S46" s="15">
-        <v>-179.04347826086951</v>
+        <v>-194.03703703703701</v>
       </c>
       <c r="T46" s="18">
-        <v>556</v>
+        <v>492</v>
       </c>
       <c r="U46" s="17">
-        <v>644.95999999999992</v>
+        <v>570.71999999999991</v>
       </c>
       <c r="V46" s="14">
-        <v>16.021412300683373</v>
+        <v>16.64282460136674</v>
       </c>
       <c r="W46" s="16">
-        <v>763.47826086956513</v>
+        <v>650.37037037037044</v>
       </c>
       <c r="X46" s="15">
-        <v>0.74308300395261995</v>
+        <v>19.003367003366975</v>
       </c>
       <c r="Y46" s="18">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="Z46" s="17">
-        <v>389.76</v>
+        <v>313.2</v>
       </c>
       <c r="AA46" s="14">
-        <v>14.681865284974092</v>
+        <v>13.849740932642487</v>
       </c>
       <c r="AB46" s="16">
-        <v>503.47826086956525</v>
+        <v>428.88888888888886</v>
       </c>
       <c r="AC46" s="15">
-        <v>-167.47826086956525</v>
+        <v>-158.88888888888891</v>
       </c>
       <c r="AD46" s="19">
-        <v>5717</v>
+        <v>4748</v>
       </c>
       <c r="AE46" s="20">
-        <v>6631.7199999999993</v>
+        <v>5507.6799999999994</v>
       </c>
       <c r="AF46" s="21">
         <v>5790</v>
@@ -6097,7 +6099,7 @@
         <v>115.46296296296296</v>
       </c>
     </row>
-    <row r="47" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="10">
         <v>134000</v>
       </c>
@@ -6107,7 +6109,9 @@
       <c r="D47" s="12">
         <v>18</v>
       </c>
-      <c r="E47" s="13"/>
+      <c r="E47" s="13">
+        <v>0</v>
+      </c>
       <c r="F47" s="14">
         <v>0</v>
       </c>
@@ -6121,19 +6125,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="16">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K47" s="13">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="L47" s="14">
-        <v>9.2766666666666655</v>
+        <v>8.91</v>
       </c>
       <c r="M47" s="30">
-        <v>52.173913043478265</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="N47" s="15">
-        <v>-1.7154150197628475</v>
+        <v>-2.2020202020202042</v>
       </c>
       <c r="O47" s="16">
         <v>0</v>
@@ -6157,13 +6161,13 @@
         <v>216</v>
       </c>
       <c r="V47" s="14">
-        <v>13.8</v>
+        <v>16.200000000000003</v>
       </c>
       <c r="W47" s="16">
-        <v>19.130434782608695</v>
+        <v>16.296296296296294</v>
       </c>
       <c r="X47" s="15">
-        <v>-1.9130434782608692</v>
+        <v>0.14814814814815058</v>
       </c>
       <c r="Y47" s="18">
         <v>0</v>
@@ -6181,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="AD47" s="19">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE47" s="20">
-        <v>612</v>
+        <v>540</v>
       </c>
       <c r="AF47" s="31">
         <v>24.761904761904763</v>
@@ -6208,7 +6212,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="48" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="10">
         <v>134001</v>
       </c>
@@ -6218,9 +6222,11 @@
       <c r="D48" s="12">
         <v>18</v>
       </c>
-      <c r="E48" s="13"/>
+      <c r="E48" s="13">
+        <v>549</v>
+      </c>
       <c r="F48" s="14">
-        <v>0</v>
+        <v>9882</v>
       </c>
       <c r="G48" s="14">
         <v>0</v>
@@ -6229,22 +6235,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="15">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="J48" s="16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K48" s="13">
-        <v>216</v>
+        <v>72</v>
       </c>
       <c r="L48" s="14">
-        <v>27.6</v>
+        <v>10.800000000000002</v>
       </c>
       <c r="M48" s="30">
-        <v>9.5652173913043477</v>
+        <v>8.148148148148147</v>
       </c>
       <c r="N48" s="15">
-        <v>7.6521739130434785</v>
+        <v>0.29629629629629717</v>
       </c>
       <c r="O48" s="16">
         <v>0</v>
@@ -6292,10 +6298,10 @@
         <v>0</v>
       </c>
       <c r="AD48" s="19">
-        <v>12</v>
+        <v>553</v>
       </c>
       <c r="AE48" s="20">
-        <v>216</v>
+        <v>9954</v>
       </c>
       <c r="AF48" s="31">
         <v>4.2857142857142856</v>
@@ -6319,7 +6325,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="10">
         <v>140230</v>
       </c>
@@ -6330,34 +6336,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E49" s="13">
-        <v>6</v>
+        <v>1248</v>
       </c>
       <c r="F49" s="14">
-        <v>6.9599999999999991</v>
+        <v>1447.6799999999998</v>
       </c>
       <c r="G49" s="14">
-        <v>0.14307257304429782</v>
+        <v>34.934590009425072</v>
       </c>
       <c r="H49" s="30">
-        <v>922.60869565217388</v>
+        <v>785.92592592592598</v>
       </c>
       <c r="I49" s="15">
-        <v>-413.36758893280631</v>
+        <v>890.76094276094273</v>
       </c>
       <c r="J49" s="16">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="K49" s="13">
-        <v>97.44</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="L49" s="14">
-        <v>1.8707746478873237</v>
+        <v>2.6144366197183098E-2</v>
       </c>
       <c r="M49" s="30">
-        <v>987.82608695652175</v>
+        <v>841.48148148148152</v>
       </c>
       <c r="N49" s="15">
-        <v>-365.01185770750993</v>
+        <v>-381.49158249158251</v>
       </c>
       <c r="O49" s="16">
         <v>0</v>
@@ -6369,10 +6375,10 @@
         <v>0</v>
       </c>
       <c r="R49" s="16">
-        <v>146.95652173913044</v>
+        <v>125.18518518518519</v>
       </c>
       <c r="S49" s="15">
-        <v>-133.59683794466403</v>
+        <v>-113.8047138047138</v>
       </c>
       <c r="T49" s="18">
         <v>1</v>
@@ -6381,13 +6387,13 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="V49" s="14">
-        <v>0.1081196581196581</v>
+        <v>0.12692307692307694</v>
       </c>
       <c r="W49" s="16">
-        <v>203.47826086956525</v>
+        <v>173.33333333333331</v>
       </c>
       <c r="X49" s="15">
-        <v>-146.98418972332018</v>
+        <v>-125.06060606060605</v>
       </c>
       <c r="Y49" s="18">
         <v>0</v>
@@ -6399,16 +6405,16 @@
         <v>0</v>
       </c>
       <c r="AB49" s="16">
-        <v>92.173913043478265</v>
+        <v>78.518518518518519</v>
       </c>
       <c r="AC49" s="15">
-        <v>-92.173913043478251</v>
+        <v>-78.518518518518519</v>
       </c>
       <c r="AD49" s="19">
-        <v>91</v>
+        <v>1250</v>
       </c>
       <c r="AE49" s="20">
-        <v>105.55999999999999</v>
+        <v>1450</v>
       </c>
       <c r="AF49" s="21">
         <v>1371.4285714285713</v>
@@ -6432,7 +6438,7 @@
         <v>53.674999999999997</v>
       </c>
     </row>
-    <row r="50" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="10">
         <v>140231</v>
       </c>
@@ -6443,34 +6449,34 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E50" s="13">
-        <v>989</v>
+        <v>493</v>
       </c>
       <c r="F50" s="14">
-        <v>1147.24</v>
+        <v>571.88</v>
       </c>
       <c r="G50" s="14">
-        <v>3.8471248462484624</v>
+        <v>2.2512453874538747</v>
       </c>
       <c r="H50" s="30">
-        <v>5655.652173913044</v>
+        <v>4817.7777777777774</v>
       </c>
       <c r="I50" s="15">
-        <v>-1581.7509881422925</v>
+        <v>-1696.8989898989894</v>
       </c>
       <c r="J50" s="16">
-        <v>1267</v>
+        <v>24</v>
       </c>
       <c r="K50" s="13">
-        <v>1469.7199999999998</v>
+        <v>27.839999999999996</v>
       </c>
       <c r="L50" s="14">
-        <v>7.2326489169675092</v>
+        <v>0.16083032490974727</v>
       </c>
       <c r="M50" s="30">
-        <v>3853.9130434782605</v>
+        <v>3282.962962962963</v>
       </c>
       <c r="N50" s="15">
-        <v>-484.77865612648225</v>
+        <v>-1468.2558922558924</v>
       </c>
       <c r="O50" s="16">
         <v>0</v>
@@ -6482,25 +6488,25 @@
         <v>0</v>
       </c>
       <c r="R50" s="16">
-        <v>815.6521739130435</v>
+        <v>694.81481481481478</v>
       </c>
       <c r="S50" s="15">
-        <v>-741.501976284585</v>
+        <v>-631.64983164983164</v>
       </c>
       <c r="T50" s="18">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="U50" s="17">
-        <v>147.32</v>
+        <v>92.8</v>
       </c>
       <c r="V50" s="14">
-        <v>2.9833797585886721</v>
+        <v>2.2061281337047354</v>
       </c>
       <c r="W50" s="16">
-        <v>936.52173913043487</v>
+        <v>797.77777777777771</v>
       </c>
       <c r="X50" s="15">
-        <v>-554.10671936758899</v>
+        <v>-500.20202020202021</v>
       </c>
       <c r="Y50" s="18">
         <v>0</v>
@@ -6512,16 +6518,16 @@
         <v>0</v>
       </c>
       <c r="AB50" s="16">
-        <v>208.69565217391306</v>
+        <v>177.77777777777777</v>
       </c>
       <c r="AC50" s="15">
-        <v>-208.69565217391306</v>
+        <v>-177.7777777777778</v>
       </c>
       <c r="AD50" s="19">
-        <v>2383</v>
+        <v>597</v>
       </c>
       <c r="AE50" s="20">
-        <v>2764.2799999999997</v>
+        <v>692.52</v>
       </c>
       <c r="AF50" s="21">
         <v>5544.2857142857147</v>
@@ -6548,7 +6554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B51" s="10">
         <v>140232</v>
       </c>
@@ -6559,85 +6565,85 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="E51" s="13">
-        <v>1346</v>
+        <v>1191</v>
       </c>
       <c r="F51" s="14">
-        <v>1561.36</v>
+        <v>1381.56</v>
       </c>
       <c r="G51" s="14">
-        <v>7.5490578585679451</v>
+        <v>7.841432054976722</v>
       </c>
       <c r="H51" s="30">
-        <v>3922.608695652174</v>
+        <v>3341.4814814814818</v>
       </c>
       <c r="I51" s="15">
-        <v>-437.00395256917</v>
+        <v>-327.85521885521916</v>
       </c>
       <c r="J51" s="16">
-        <v>916</v>
+        <v>594</v>
       </c>
       <c r="K51" s="13">
-        <v>1062.56</v>
+        <v>689.04</v>
       </c>
       <c r="L51" s="14">
-        <v>6.3250000000000002</v>
+        <v>4.8149017467248907</v>
       </c>
       <c r="M51" s="30">
-        <v>3186.0869565217395</v>
+        <v>2714.0740740740739</v>
       </c>
       <c r="N51" s="15">
-        <v>-532.22134387351775</v>
+        <v>-639.67003367003372</v>
       </c>
       <c r="O51" s="16">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="P51" s="17">
-        <v>216.92</v>
+        <v>176.32</v>
       </c>
       <c r="Q51" s="14">
-        <v>16.427430555555556</v>
+        <v>15.675000000000002</v>
       </c>
       <c r="R51" s="16">
-        <v>250.43478260869566</v>
+        <v>213.33333333333331</v>
       </c>
       <c r="S51" s="15">
-        <v>-40.667984189723313</v>
+        <v>-41.939393939393909</v>
       </c>
       <c r="T51" s="18">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="U51" s="17">
-        <v>237.79999999999998</v>
+        <v>146.16</v>
       </c>
       <c r="V51" s="14">
-        <v>6.1891408114558475</v>
+        <v>4.4656324582338902</v>
       </c>
       <c r="W51" s="16">
-        <v>728.695652173913</v>
+        <v>620.74074074074076</v>
       </c>
       <c r="X51" s="15">
-        <v>-324.96047430830038</v>
+        <v>-325.44781144781149</v>
       </c>
       <c r="Y51" s="18">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="Z51" s="17">
-        <v>41.76</v>
+        <v>13.919999999999998</v>
       </c>
       <c r="AA51" s="14">
-        <v>7.0061538461538468</v>
+        <v>2.7415384615384615</v>
       </c>
       <c r="AB51" s="16">
-        <v>113.04347826086956</v>
+        <v>96.296296296296305</v>
       </c>
       <c r="AC51" s="15">
-        <v>-77.043478260869563</v>
+        <v>-84.296296296296305</v>
       </c>
       <c r="AD51" s="19">
-        <v>2690</v>
+        <v>2075</v>
       </c>
       <c r="AE51" s="20">
-        <v>3120.3999999999996</v>
+        <v>2407</v>
       </c>
       <c r="AF51" s="21">
         <v>1328.0952380952381</v>
@@ -6665,7 +6671,7 @@
         <v>5580.5526455026438</v>
       </c>
     </row>
-    <row r="52" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="10">
         <v>150360</v>
       </c>
@@ -6676,85 +6682,85 @@
         <v>0.81</v>
       </c>
       <c r="E52" s="13">
-        <v>720</v>
+        <v>1632</v>
       </c>
       <c r="F52" s="14">
-        <v>583.20000000000005</v>
+        <v>1321.92</v>
       </c>
       <c r="G52" s="14">
-        <v>4.6493108728943344</v>
+        <v>12.371209800918836</v>
       </c>
       <c r="H52" s="30">
-        <v>3406.9565217391305</v>
+        <v>2902.2222222222222</v>
       </c>
       <c r="I52" s="15">
-        <v>-828.61660079051376</v>
+        <v>312.80808080808083</v>
       </c>
       <c r="J52" s="16">
-        <v>7018</v>
+        <v>7909</v>
       </c>
       <c r="K52" s="13">
-        <v>5684.58</v>
+        <v>6406.2900000000009</v>
       </c>
       <c r="L52" s="14">
-        <v>149.33170731707315</v>
+        <v>197.55870479394449</v>
       </c>
       <c r="M52" s="30">
-        <v>1033.913043478261</v>
+        <v>880.74074074074076</v>
       </c>
       <c r="N52" s="15">
-        <v>6548.0395256917</v>
+        <v>7508.6632996632998</v>
       </c>
       <c r="O52" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" s="17">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="14">
-        <v>0.37902621722846441</v>
+        <v>0</v>
       </c>
       <c r="R52" s="16">
-        <v>232.17391304347825</v>
+        <v>197.77777777777777</v>
       </c>
       <c r="S52" s="15">
-        <v>-207.06719367588934</v>
+        <v>-179.79797979797979</v>
       </c>
       <c r="T52" s="18">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="U52" s="17">
-        <v>165.24</v>
+        <v>65.61</v>
       </c>
       <c r="V52" s="14">
-        <v>9.3500000000000014</v>
+        <v>4.3581521739130435</v>
       </c>
       <c r="W52" s="16">
-        <v>480</v>
+        <v>408.88888888888886</v>
       </c>
       <c r="X52" s="15">
-        <v>-145.09090909090907</v>
+        <v>-216.37373737373736</v>
       </c>
       <c r="Y52" s="18">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Z52" s="17">
-        <v>42.120000000000005</v>
+        <v>23.490000000000002</v>
       </c>
       <c r="AA52" s="14">
-        <v>18.021917808219175</v>
+        <v>11.798630136986301</v>
       </c>
       <c r="AB52" s="16">
-        <v>63.478260869565219</v>
+        <v>54.074074074074076</v>
       </c>
       <c r="AC52" s="15">
-        <v>-11.478260869565219</v>
+        <v>-25.074074074074076</v>
       </c>
       <c r="AD52" s="19">
-        <v>7998</v>
+        <v>9651</v>
       </c>
       <c r="AE52" s="20">
-        <v>6478.38</v>
+        <v>7817.31</v>
       </c>
       <c r="AF52" s="21">
         <v>2961.4285714285716</v>
@@ -6778,7 +6784,7 @@
         <v>336.91666666666669</v>
       </c>
     </row>
-    <row r="53" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10">
         <v>150361</v>
       </c>
@@ -6789,85 +6795,85 @@
         <v>0.81</v>
       </c>
       <c r="E53" s="13">
-        <v>1560</v>
+        <v>180</v>
       </c>
       <c r="F53" s="14">
-        <v>1263.6000000000001</v>
+        <v>145.80000000000001</v>
       </c>
       <c r="G53" s="14">
-        <v>6.2897211155378479</v>
+        <v>0.85195219123505961</v>
       </c>
       <c r="H53" s="30">
-        <v>5456.521739130435</v>
+        <v>4648.1481481481487</v>
       </c>
       <c r="I53" s="15">
-        <v>-920.23715415019797</v>
+        <v>-1932.7946127946134</v>
       </c>
       <c r="J53" s="16">
-        <v>6808</v>
+        <v>6750</v>
       </c>
       <c r="K53" s="13">
-        <v>5514.4800000000005</v>
+        <v>5467.5</v>
       </c>
       <c r="L53" s="14">
-        <v>64.461976047904187</v>
+        <v>75.028068862275447</v>
       </c>
       <c r="M53" s="30">
-        <v>2323.4782608695655</v>
+        <v>1979.2592592592591</v>
       </c>
       <c r="N53" s="15">
-        <v>5751.873517786561</v>
+        <v>5850.3367003367002</v>
       </c>
       <c r="O53" s="16">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="P53" s="17">
-        <v>178.20000000000002</v>
+        <v>59.13</v>
       </c>
       <c r="Q53" s="14">
-        <v>7.4711409395973147</v>
+        <v>2.9102013422818795</v>
       </c>
       <c r="R53" s="16">
-        <v>647.82608695652175</v>
+        <v>551.85185185185185</v>
       </c>
       <c r="S53" s="15">
-        <v>-368.93280632411074</v>
+        <v>-428.68350168350167</v>
       </c>
       <c r="T53" s="18">
-        <v>414</v>
+        <v>288</v>
       </c>
       <c r="U53" s="17">
-        <v>335.34000000000003</v>
+        <v>233.28000000000003</v>
       </c>
       <c r="V53" s="14">
-        <v>8.3062648691514678</v>
+        <v>6.7831879460745439</v>
       </c>
       <c r="W53" s="16">
-        <v>1096.5217391304348</v>
+        <v>934.07407407407402</v>
       </c>
       <c r="X53" s="15">
-        <v>-383.47035573122525</v>
+        <v>-391.32659932659931</v>
       </c>
       <c r="Y53" s="18">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="Z53" s="17">
-        <v>140.13</v>
+        <v>127.98</v>
       </c>
       <c r="AA53" s="14">
-        <v>25.154597701149427</v>
+        <v>26.968965517241383</v>
       </c>
       <c r="AB53" s="16">
-        <v>151.30434782608694</v>
+        <v>128.88888888888889</v>
       </c>
       <c r="AC53" s="15">
-        <v>21.695652173913061</v>
+        <v>29.111111111111114</v>
       </c>
       <c r="AD53" s="19">
-        <v>9175</v>
+        <v>7449</v>
       </c>
       <c r="AE53" s="20">
-        <v>7431.7500000000009</v>
+        <v>6033.6900000000005</v>
       </c>
       <c r="AF53" s="21">
         <v>5287.1428571428569</v>
@@ -6891,7 +6897,7 @@
         <v>739.16666666666663</v>
       </c>
     </row>
-    <row r="54" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10">
         <v>150362</v>
       </c>
@@ -6902,85 +6908,85 @@
         <v>0.81</v>
       </c>
       <c r="E54" s="13">
-        <v>1926</v>
+        <v>345</v>
       </c>
       <c r="F54" s="14">
-        <v>1560.0600000000002</v>
+        <v>279.45000000000005</v>
       </c>
       <c r="G54" s="14">
-        <v>10.398591549295775</v>
+        <v>2.1866197183098595</v>
       </c>
       <c r="H54" s="30">
-        <v>4074.782608695652</v>
+        <v>3471.1111111111109</v>
       </c>
       <c r="I54" s="15">
-        <v>73.826086956521976</v>
+        <v>-1232.7777777777778</v>
       </c>
       <c r="J54" s="16">
-        <v>981</v>
+        <v>1455</v>
       </c>
       <c r="K54" s="13">
-        <v>794.61</v>
+        <v>1178.5500000000002</v>
       </c>
       <c r="L54" s="14">
-        <v>19.239767441860462</v>
+        <v>33.49883720930233</v>
       </c>
       <c r="M54" s="30">
-        <v>1121.7391304347827</v>
+        <v>955.55555555555554</v>
       </c>
       <c r="N54" s="15">
-        <v>471.11857707509876</v>
+        <v>1020.6565656565657</v>
       </c>
       <c r="O54" s="16">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="P54" s="17">
-        <v>99.63000000000001</v>
+        <v>72.09</v>
       </c>
       <c r="Q54" s="14">
-        <v>9.3731927710843372</v>
+        <v>7.9617469879518072</v>
       </c>
       <c r="R54" s="16">
-        <v>288.69565217391306</v>
+        <v>245.92592592592592</v>
       </c>
       <c r="S54" s="15">
-        <v>-139.4505928853755</v>
+        <v>-134.56902356902356</v>
       </c>
       <c r="T54" s="18">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="U54" s="17">
-        <v>295.65000000000003</v>
+        <v>259.20000000000005</v>
       </c>
       <c r="V54" s="14">
-        <v>19.079545454545453</v>
+        <v>19.636363636363633</v>
       </c>
       <c r="W54" s="16">
-        <v>420.86956521739131</v>
+        <v>358.51851851851853</v>
       </c>
       <c r="X54" s="15">
-        <v>58.913043478260875</v>
+        <v>59.259259259259238</v>
       </c>
       <c r="Y54" s="18">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Z54" s="17">
-        <v>131.22</v>
+        <v>128.79000000000002</v>
       </c>
       <c r="AA54" s="14">
-        <v>21.018461538461537</v>
+        <v>24.216923076923074</v>
       </c>
       <c r="AB54" s="16">
-        <v>169.56521739130434</v>
+        <v>144.44444444444446</v>
       </c>
       <c r="AC54" s="15">
-        <v>-7.5652173913043441</v>
+        <v>14.555555555555543</v>
       </c>
       <c r="AD54" s="19">
-        <v>3557</v>
+        <v>2368</v>
       </c>
       <c r="AE54" s="20">
-        <v>2881.17</v>
+        <v>1918.0800000000002</v>
       </c>
       <c r="AF54" s="21">
         <v>3055.7142857142853</v>
@@ -7004,7 +7010,7 @@
         <v>1015.4166666666666</v>
       </c>
     </row>
-    <row r="55" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B55" s="10">
         <v>150363</v>
       </c>
@@ -7015,85 +7021,85 @@
         <v>0.81</v>
       </c>
       <c r="E55" s="13">
-        <v>978</v>
+        <v>287</v>
       </c>
       <c r="F55" s="14">
-        <v>792.18000000000006</v>
+        <v>232.47000000000003</v>
       </c>
       <c r="G55" s="14">
-        <v>6.2625664388762328</v>
+        <v>2.1574031890660592</v>
       </c>
       <c r="H55" s="30">
-        <v>3435.652173913044</v>
+        <v>2926.666666666667</v>
       </c>
       <c r="I55" s="15">
-        <v>-583.66007905138372</v>
+        <v>-1043.3030303030303</v>
       </c>
       <c r="J55" s="16">
-        <v>5640</v>
+        <v>5536</v>
       </c>
       <c r="K55" s="13">
-        <v>4568.4000000000005</v>
+        <v>4484.16</v>
       </c>
       <c r="L55" s="14">
-        <v>91.410634208840492</v>
+        <v>105.32940422805893</v>
       </c>
       <c r="M55" s="30">
-        <v>1357.391304347826</v>
+        <v>1156.2962962962963</v>
       </c>
       <c r="N55" s="15">
-        <v>5023.00395256917</v>
+        <v>5010.4107744107741</v>
       </c>
       <c r="O55" s="16">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="P55" s="17">
-        <v>164.43</v>
+        <v>91.53</v>
       </c>
       <c r="Q55" s="14">
-        <v>11.779587155963302</v>
+        <v>7.6974770642201831</v>
       </c>
       <c r="R55" s="16">
-        <v>379.13043478260869</v>
+        <v>322.96296296296299</v>
       </c>
       <c r="S55" s="15">
-        <v>-141.66403162055337</v>
+        <v>-180.60269360269365</v>
       </c>
       <c r="T55" s="18">
-        <v>346</v>
+        <v>289</v>
       </c>
       <c r="U55" s="17">
-        <v>280.26</v>
+        <v>234.09</v>
       </c>
       <c r="V55" s="14">
-        <v>15.659749552772809</v>
+        <v>15.354740608228981</v>
       </c>
       <c r="W55" s="16">
-        <v>486.08695652173913</v>
+        <v>414.07407407407402</v>
       </c>
       <c r="X55" s="15">
-        <v>-7.5177865612648134</v>
+        <v>-12.14478114478112</v>
       </c>
       <c r="Y55" s="18">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Z55" s="17">
-        <v>144.18</v>
+        <v>141.75</v>
       </c>
       <c r="AA55" s="14">
-        <v>22.976530612244897</v>
+        <v>26.517857142857142</v>
       </c>
       <c r="AB55" s="16">
-        <v>170.43478260869566</v>
+        <v>145.18518518518519</v>
       </c>
       <c r="AC55" s="15">
-        <v>7.5652173913043441</v>
+        <v>29.81481481481481</v>
       </c>
       <c r="AD55" s="19">
-        <v>7345</v>
+        <v>6400</v>
       </c>
       <c r="AE55" s="20">
-        <v>5949.4500000000007</v>
+        <v>5184</v>
       </c>
       <c r="AF55" s="21">
         <v>2899.0476190476193</v>
@@ -7117,7 +7123,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="56" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B56" s="10">
         <v>151500</v>
       </c>
@@ -7128,85 +7134,85 @@
         <v>2.62</v>
       </c>
       <c r="E56" s="13">
-        <v>377</v>
+        <v>118</v>
       </c>
       <c r="F56" s="14">
-        <v>987.74</v>
+        <v>309.16000000000003</v>
       </c>
       <c r="G56" s="14">
-        <v>12.012720403022671</v>
+        <v>4.4138539042821163</v>
       </c>
       <c r="H56" s="30">
-        <v>690.43478260869563</v>
+        <v>588.14814814814815</v>
       </c>
       <c r="I56" s="15">
-        <v>63.166007905138372</v>
+        <v>-149.34006734006732</v>
       </c>
       <c r="J56" s="32">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="K56" s="13">
-        <v>495.18</v>
+        <v>461.12</v>
       </c>
       <c r="L56" s="14">
-        <v>16.154391891891891</v>
+        <v>17.659459459459459</v>
       </c>
       <c r="M56" s="30">
-        <v>257.39130434782612</v>
+        <v>219.25925925925927</v>
       </c>
       <c r="N56" s="15">
-        <v>72.00395256916994</v>
+        <v>76.336700336700332</v>
       </c>
       <c r="O56" s="32">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P56" s="17">
-        <v>107.42</v>
+        <v>99.56</v>
       </c>
       <c r="Q56" s="14">
-        <v>17.288333333333334</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="R56" s="16">
-        <v>52.173913043478265</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="S56" s="15">
-        <v>-6.430830039525695</v>
+        <v>-2.4040404040404084</v>
       </c>
       <c r="T56" s="18">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="U56" s="17">
-        <v>196.5</v>
+        <v>178.16</v>
       </c>
       <c r="V56" s="14">
-        <v>12.163461538461538</v>
+        <v>12.946153846153846</v>
       </c>
       <c r="W56" s="16">
-        <v>135.65217391304347</v>
+        <v>115.55555555555556</v>
       </c>
       <c r="X56" s="15">
-        <v>-23.656126482213438</v>
+        <v>-16.040404040404042</v>
       </c>
       <c r="Y56" s="18">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Z56" s="17">
-        <v>94.320000000000007</v>
+        <v>78.600000000000009</v>
       </c>
       <c r="AA56" s="14">
-        <v>21.18139534883721</v>
+        <v>20.720930232558139</v>
       </c>
       <c r="AB56" s="16">
-        <v>37.391304347826086</v>
+        <v>31.851851851851851</v>
       </c>
       <c r="AC56" s="15">
-        <v>-1.391304347826086</v>
+        <v>-1.8518518518518547</v>
       </c>
       <c r="AD56" s="19">
-        <v>718</v>
+        <v>430</v>
       </c>
       <c r="AE56" s="20">
-        <v>1881.16</v>
+        <v>1126.6000000000001</v>
       </c>
       <c r="AF56" s="21">
         <v>577.14285714285711</v>
@@ -7230,7 +7236,7 @@
         <v>142.66666666666666</v>
       </c>
     </row>
-    <row r="57" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B57" s="10">
         <v>151501</v>
       </c>
@@ -7241,49 +7247,49 @@
         <v>2.62</v>
       </c>
       <c r="E57" s="13">
-        <v>383</v>
+        <v>43</v>
       </c>
       <c r="F57" s="14">
-        <v>1003.46</v>
+        <v>112.66000000000001</v>
       </c>
       <c r="G57" s="14">
-        <v>7.2043866171003712</v>
+        <v>0.94951672862453529</v>
       </c>
       <c r="H57" s="30">
-        <v>1169.5652173913045</v>
+        <v>996.2962962962963</v>
       </c>
       <c r="I57" s="15">
-        <v>-148.62055335968387</v>
+        <v>-409.86195286195289</v>
       </c>
       <c r="J57" s="32">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="K57" s="13">
-        <v>432.3</v>
+        <v>364.18</v>
       </c>
       <c r="L57" s="14">
-        <v>7.4147424511545283</v>
+        <v>7.3326820603907645</v>
       </c>
       <c r="M57" s="30">
-        <v>489.56521739130437</v>
+        <v>417.03703703703701</v>
       </c>
       <c r="N57" s="15">
-        <v>-57.529644268774717</v>
+        <v>-50.56228956228955</v>
       </c>
       <c r="O57" s="32">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="P57" s="17">
-        <v>175.54000000000002</v>
+        <v>28.82</v>
       </c>
       <c r="Q57" s="14">
-        <v>11.610273972602739</v>
+        <v>2.2376712328767123</v>
       </c>
       <c r="R57" s="16">
-        <v>126.95652173913044</v>
+        <v>108.14814814814815</v>
       </c>
       <c r="S57" s="15">
-        <v>-48.415019762845859</v>
+        <v>-87.316498316498325</v>
       </c>
       <c r="T57" s="18">
         <v>4</v>
@@ -7292,34 +7298,34 @@
         <v>10.48</v>
       </c>
       <c r="V57" s="14">
-        <v>0.22589285714285715</v>
+        <v>0.26517857142857143</v>
       </c>
       <c r="W57" s="16">
-        <v>389.56521739130437</v>
+        <v>331.85185185185185</v>
       </c>
       <c r="X57" s="15">
-        <v>-279.32015810276681</v>
+        <v>-237.34680134680136</v>
       </c>
       <c r="Y57" s="18">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z57" s="17">
-        <v>115.28</v>
+        <v>99.56</v>
       </c>
       <c r="AA57" s="14">
-        <v>25.3</v>
+        <v>25.650000000000006</v>
       </c>
       <c r="AB57" s="16">
-        <v>38.260869565217391</v>
+        <v>32.592592592592588</v>
       </c>
       <c r="AC57" s="15">
-        <v>5.7391304347826093</v>
+        <v>5.4074074074074119</v>
       </c>
       <c r="AD57" s="19">
-        <v>663</v>
+        <v>235</v>
       </c>
       <c r="AE57" s="20">
-        <v>1737.0600000000002</v>
+        <v>615.70000000000005</v>
       </c>
       <c r="AF57" s="21">
         <v>1047.1428571428571</v>
@@ -7343,7 +7349,7 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="58" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B58" s="10">
         <v>151502</v>
       </c>
@@ -7353,65 +7359,63 @@
       <c r="D58" s="12">
         <v>2.62</v>
       </c>
-      <c r="E58" s="13">
-        <v>132</v>
-      </c>
+      <c r="E58" s="13"/>
       <c r="F58" s="14">
-        <v>345.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="G58" s="14">
-        <v>6.4972762645914388</v>
+        <v>0</v>
       </c>
       <c r="H58" s="30">
-        <v>446.95652173913049</v>
+        <v>380.74074074074076</v>
       </c>
       <c r="I58" s="15">
-        <v>-71.162055335968404</v>
+        <v>-173.06397306397309</v>
       </c>
       <c r="J58" s="32">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="K58" s="13">
-        <v>199.12</v>
+        <v>96.94</v>
       </c>
       <c r="L58" s="14">
-        <v>9.4254901960784316</v>
+        <v>5.3867647058823529</v>
       </c>
       <c r="M58" s="30">
-        <v>177.39130434782609</v>
+        <v>151.11111111111111</v>
       </c>
       <c r="N58" s="15">
-        <v>-4.6324110671936722</v>
+        <v>-31.686868686868678</v>
       </c>
       <c r="O58" s="32">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P58" s="17">
-        <v>31.44</v>
+        <v>23.580000000000002</v>
       </c>
       <c r="Q58" s="14">
-        <v>6.9</v>
+        <v>6.0750000000000011</v>
       </c>
       <c r="R58" s="16">
-        <v>38.260869565217391</v>
+        <v>32.592592592592588</v>
       </c>
       <c r="S58" s="15">
-        <v>-22.782608695652172</v>
+        <v>-20.629629629629623</v>
       </c>
       <c r="T58" s="18">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="U58" s="17">
-        <v>133.62</v>
+        <v>125.76</v>
       </c>
       <c r="V58" s="14">
-        <v>11.624324324324325</v>
+        <v>12.843243243243245</v>
       </c>
       <c r="W58" s="16">
-        <v>96.521739130434781</v>
+        <v>82.222222222222214</v>
       </c>
       <c r="X58" s="15">
-        <v>-19.197628458498016</v>
+        <v>-11.797979797979792</v>
       </c>
       <c r="Y58" s="18">
         <v>39</v>
@@ -7420,19 +7424,19 @@
         <v>102.18</v>
       </c>
       <c r="AA58" s="14">
-        <v>29.9</v>
+        <v>35.1</v>
       </c>
       <c r="AB58" s="16">
-        <v>28.695652173913043</v>
+        <v>24.444444444444446</v>
       </c>
       <c r="AC58" s="15">
-        <v>10.304347826086957</v>
+        <v>14.555555555555554</v>
       </c>
       <c r="AD58" s="19">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="AE58" s="20">
-        <v>812.2</v>
+        <v>348.46000000000004</v>
       </c>
       <c r="AF58" s="21">
         <v>493.33333333333337</v>
@@ -7459,7 +7463,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B59" s="33">
         <v>151503</v>
       </c>
@@ -7469,65 +7473,63 @@
       <c r="D59" s="12">
         <v>2.62</v>
       </c>
-      <c r="E59" s="13">
-        <v>137</v>
-      </c>
+      <c r="E59" s="13"/>
       <c r="F59" s="14">
-        <v>358.94</v>
+        <v>0</v>
       </c>
       <c r="G59" s="14">
-        <v>5.4756714060031602</v>
+        <v>0</v>
       </c>
       <c r="H59" s="30">
-        <v>550.43478260869563</v>
+        <v>468.88888888888886</v>
       </c>
       <c r="I59" s="15">
-        <v>-113.197628458498</v>
+        <v>-213.13131313131311</v>
       </c>
       <c r="J59" s="32">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="K59" s="13">
-        <v>345.84000000000003</v>
+        <v>455.88</v>
       </c>
       <c r="L59" s="14">
-        <v>13.914999999999999</v>
+        <v>21.532499999999999</v>
       </c>
       <c r="M59" s="30">
-        <v>208.69565217391306</v>
+        <v>177.77777777777777</v>
       </c>
       <c r="N59" s="15">
-        <v>37.13833992094861</v>
+        <v>93.191919191919183</v>
       </c>
       <c r="O59" s="32">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P59" s="17">
-        <v>52.400000000000006</v>
+        <v>44.54</v>
       </c>
       <c r="Q59" s="14">
-        <v>7.3333333333333339</v>
+        <v>7.3173913043478267</v>
       </c>
       <c r="R59" s="16">
-        <v>60</v>
+        <v>51.111111111111107</v>
       </c>
       <c r="S59" s="15">
-        <v>-34.54545454545454</v>
+        <v>-29.464646464646464</v>
       </c>
       <c r="T59" s="18">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="U59" s="17">
-        <v>157.20000000000002</v>
+        <v>117.9</v>
       </c>
       <c r="V59" s="14">
-        <v>11.244444444444444</v>
+        <v>9.8999999999999986</v>
       </c>
       <c r="W59" s="16">
-        <v>117.39130434782609</v>
+        <v>100</v>
       </c>
       <c r="X59" s="15">
-        <v>-25.37549407114625</v>
+        <v>-27.727272727272734</v>
       </c>
       <c r="Y59" s="18">
         <v>44</v>
@@ -7536,19 +7538,19 @@
         <v>115.28</v>
       </c>
       <c r="AA59" s="14">
-        <v>53.009523809523813</v>
+        <v>62.228571428571428</v>
       </c>
       <c r="AB59" s="16">
-        <v>18.260869565217391</v>
+        <v>15.555555555555555</v>
       </c>
       <c r="AC59" s="15">
-        <v>25.739130434782609</v>
+        <v>28.444444444444443</v>
       </c>
       <c r="AD59" s="19">
-        <v>393</v>
+        <v>280</v>
       </c>
       <c r="AE59" s="20">
-        <v>1029.6600000000001</v>
+        <v>733.6</v>
       </c>
       <c r="AF59" s="21">
         <v>553.33333333333337</v>
@@ -7576,7 +7578,7 @@
         <v>3753</v>
       </c>
     </row>
-    <row r="60" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:39" x14ac:dyDescent="0.25">
       <c r="C60" s="35"/>
       <c r="D60" s="35"/>
       <c r="E60" s="35"/>
@@ -7616,16 +7618,16 @@
         <v>147790.42857142861</v>
       </c>
     </row>
-    <row r="61" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B61" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="F61" s="69"/>
+      <c r="F61" s="67"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -7654,18 +7656,18 @@
       <c r="AF61" s="36"/>
       <c r="AG61" s="36"/>
     </row>
-    <row r="62" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B62" s="65" t="s">
+    <row r="62" spans="2:39" x14ac:dyDescent="0.25">
+      <c r="B62" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="65"/>
+      <c r="C62" s="68"/>
       <c r="D62" s="42">
         <f>SUM(F13:F59)</f>
-        <v>171057.71999999994</v>
+        <v>145745.50000000003</v>
       </c>
       <c r="E62" s="64">
         <f>D62*100/D67</f>
-        <v>41.310061768856357</v>
+        <v>37.010627266336073</v>
       </c>
       <c r="F62" s="64"/>
       <c r="G62" s="43"/>
@@ -7696,18 +7698,18 @@
       <c r="AF62" s="36"/>
       <c r="AG62" s="36"/>
     </row>
-    <row r="63" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B63" s="41" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="41"/>
       <c r="D63" s="44">
         <f>SUM(K13:K59)</f>
-        <v>156648.04999999993</v>
+        <v>178100.81</v>
       </c>
       <c r="E63" s="64">
         <f>D63*100/D67</f>
-        <v>37.830158273306218</v>
+        <v>45.226938016903013</v>
       </c>
       <c r="F63" s="64"/>
       <c r="G63" s="43"/>
@@ -7738,18 +7740,18 @@
       <c r="AF63" s="36"/>
       <c r="AG63" s="36"/>
     </row>
-    <row r="64" spans="2:39" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B64" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="41"/>
       <c r="D64" s="44">
         <f>SUM(P13:P59)</f>
-        <v>22619.739999999994</v>
+        <v>17635.2</v>
       </c>
       <c r="E64" s="64">
         <f>D64*100/D67</f>
-        <v>5.4626172767617334</v>
+        <v>4.4782845025560976</v>
       </c>
       <c r="F64" s="64"/>
       <c r="G64" s="43"/>
@@ -7780,18 +7782,18 @@
       <c r="AF64" s="36"/>
       <c r="AG64" s="36"/>
     </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B65" s="41" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="41"/>
       <c r="D65" s="44">
         <f>SUM(U13:U59)</f>
-        <v>52223.290000000023</v>
+        <v>43743.380000000019</v>
       </c>
       <c r="E65" s="64">
         <f>D65*100/D67</f>
-        <v>12.611809251712815</v>
+        <v>11.108198418130922</v>
       </c>
       <c r="F65" s="64"/>
       <c r="G65" s="43"/>
@@ -7822,18 +7824,18 @@
       <c r="AF65" s="36"/>
       <c r="AG65" s="36"/>
     </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B66" s="41" t="s">
         <v>18</v>
       </c>
       <c r="C66" s="41"/>
       <c r="D66" s="44">
         <f>SUM(Z13:Z59)</f>
-        <v>11533.66</v>
+        <v>8568.76</v>
       </c>
       <c r="E66" s="64">
         <f>D66*100/D67</f>
-        <v>2.7853534293628375</v>
+        <v>2.1759517960739081</v>
       </c>
       <c r="F66" s="64"/>
       <c r="G66" s="43"/>
@@ -7864,20 +7866,20 @@
       <c r="AF66" s="36"/>
       <c r="AG66" s="36"/>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B67" s="65" t="s">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B67" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="65"/>
+      <c r="C67" s="68"/>
       <c r="D67" s="44">
         <f>SUM(AE13:AE59)</f>
-        <v>414082.46</v>
-      </c>
-      <c r="E67" s="66">
+        <v>393793.65</v>
+      </c>
+      <c r="E67" s="69">
         <f>D67*100/D67</f>
         <v>100</v>
       </c>
-      <c r="F67" s="66"/>
+      <c r="F67" s="69"/>
       <c r="G67" s="45"/>
       <c r="H67" s="45"/>
       <c r="I67" s="45"/>
@@ -7906,7 +7908,7 @@
       <c r="AF67" s="36"/>
       <c r="AG67" s="36"/>
     </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B68" s="46"/>
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
@@ -7940,7 +7942,7 @@
       <c r="AF68" s="36"/>
       <c r="AG68" s="36"/>
     </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B69" s="39" t="s">
         <v>9</v>
       </c>
@@ -7976,18 +7978,18 @@
       <c r="AF69" s="36"/>
       <c r="AG69" s="36"/>
     </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B70" s="65" t="s">
+    <row r="70" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B70" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="68"/>
       <c r="D70" s="3">
         <f>SUM(E13:E59)</f>
-        <v>121697</v>
+        <v>97715</v>
       </c>
       <c r="E70" s="64">
         <f>D70*100/D75</f>
-        <v>40.443124000943804</v>
+        <v>35.845561261922228</v>
       </c>
       <c r="F70" s="64"/>
       <c r="G70" s="43"/>
@@ -8017,18 +8019,18 @@
       <c r="AF70" s="36"/>
       <c r="AG70" s="36"/>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B71" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="41"/>
       <c r="D71" s="49">
         <f>SUM(J13:J59)</f>
-        <v>118635</v>
+        <v>126026</v>
       </c>
       <c r="E71" s="64">
         <f>D71*100/D75</f>
-        <v>39.425540611945806</v>
+        <v>46.231107850330154</v>
       </c>
       <c r="F71" s="64"/>
       <c r="G71" s="43"/>
@@ -8059,18 +8061,18 @@
       <c r="AF71" s="36"/>
       <c r="AG71" s="36"/>
     </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B72" s="41" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="41"/>
       <c r="D72" s="49">
         <f>SUM(O13:O59)</f>
-        <v>16096</v>
+        <v>12515</v>
       </c>
       <c r="E72" s="64">
         <f>D72*100/D75</f>
-        <v>5.3491254831194812</v>
+        <v>4.5909757887013942</v>
       </c>
       <c r="F72" s="64"/>
       <c r="G72" s="43"/>
@@ -8101,18 +8103,18 @@
       <c r="AF72" s="36"/>
       <c r="AG72" s="36"/>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B73" s="41" t="s">
         <v>13</v>
       </c>
       <c r="C73" s="41"/>
       <c r="D73" s="49">
         <f>SUM(T13:T59)</f>
-        <v>36589</v>
+        <v>30498</v>
       </c>
       <c r="E73" s="64">
         <f>D73*100/D75</f>
-        <v>12.159490078395795</v>
+        <v>11.187820983125459</v>
       </c>
       <c r="F73" s="64"/>
       <c r="G73" s="50"/>
@@ -8143,18 +8145,18 @@
       <c r="AF73" s="36"/>
       <c r="AG73" s="36"/>
     </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B74" s="41" t="s">
         <v>19</v>
       </c>
       <c r="C74" s="41"/>
       <c r="D74" s="49">
         <f>SUM(Y13:Y59)</f>
-        <v>